--- a/stores.xlsx
+++ b/stores.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
-  <workbookPr defaultThemeVersion="166925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <workbookPr checkCompatibility="1" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\YUMIN\Desktop\B0KT2A_RSVN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F032283-55C0-4DD5-81E4-9768852B4E24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E76B24D9-6C7E-4A93-8EDB-686BBA6C9387}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{ABFC3117-FCCB-4FF3-804A-FE19451A2004}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{ABFC3117-FCCB-4FF3-804A-FE19451A2004}"/>
   </bookViews>
   <sheets>
     <sheet name="stores" sheetId="2" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="745" uniqueCount="673">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="741" uniqueCount="669">
   <si>
     <t>룸익스케이프 WHITE</t>
   </si>
@@ -237,9 +237,6 @@
     <t>플레이더월드 강남점</t>
   </si>
   <si>
-    <t>먹루마블,이웃집 또도와,이웃집 또털어,두근두근 러브대작전,조선피자몰,조피몰,이상한 나라로 출두요</t>
-  </si>
-  <si>
     <t>플레이더월드 건대점</t>
   </si>
   <si>
@@ -702,12 +699,6 @@
     <t>나의신방</t>
   </si>
   <si>
-    <t>프로젝트30</t>
-  </si>
-  <si>
-    <t>언더더씨,언더더마린,언더더케이브</t>
-  </si>
-  <si>
     <t>클레버타운</t>
   </si>
   <si>
@@ -798,9 +789,6 @@
     <t>이스케이프# 건대점</t>
   </si>
   <si>
-    <t>고양학개론,캠프ING,옥순양갱,철수네 슈퍼,오메가,더 라스트 노트,MR.BANG,미스터뱅,튜링테스트</t>
-  </si>
-  <si>
     <t>매화,순백향,3318,수곡리</t>
   </si>
   <si>
@@ -980,10 +968,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>MY PRIVATE HEAVEN,마이프라이빗헤븐,BROOKLYN MY LOVE,브루클린마이러브,PLAN TO SAVE MY DEAR,플랜투세이브마이디어,마헤븐,브마럽</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>메가게임,MEGA GAME,쎄비지,SAVAGE GANGSTARS,비틀배틀,BEETLE BATTLE,GALAXY HYPRESS,갤럭시하이프레스,갤하이</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1520,10 +1504,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>pj_30</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>hp_ad</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1796,26 +1776,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>eps_dj</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>eps_dsr</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>이스케이퍼스 대구동성로점</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>eps_hd1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>eps_hd2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>ecs_kd</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2265,9 +2229,6 @@
     <t>https://thefrank.co.kr/</t>
   </si>
   <si>
-    <t>http://project30.co.kr</t>
-  </si>
-  <si>
     <t>https://naver.me/5Q37ULvz</t>
   </si>
   <si>
@@ -2333,6 +2294,30 @@
   </si>
   <si>
     <t>난너의보이,난너보,좌뇌우뇌연구소</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>고양학개론,캠프ING,옥순양갱,철수네 슈퍼,철수네수퍼,오메가,더 라스트 노트,MR.BANG,미스터뱅</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ecp_dj</t>
+  </si>
+  <si>
+    <t>ecp_dsr</t>
+  </si>
+  <si>
+    <t>ecp_hd1</t>
+  </si>
+  <si>
+    <t>ecp_hd2</t>
+  </si>
+  <si>
+    <t>먹루마블,이웃집또도와,이웃집또털어,두근두근러브대작전,조선피자몰,조피몰,이상한나라로출두요,두러대,두두러,이나출</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MY PRIVATE HEAVEN,마이프라이빗헤븐,BROOKLYN MY LOVE,브루클린마이러브,PLAN TO SAVE MY DEAR,플랜투세이브마이디어,마헤븐,브마럽,마프헤</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2736,7 +2721,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D839462D-4719-40BB-8925-C1B9F93734CF}">
-  <dimension ref="A1:H192"/>
+  <dimension ref="A1:H191"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="2"/>
@@ -2748,7 +2733,7 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>12</v>
@@ -2774,10 +2759,10 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="C2" s="3">
         <v>6</v>
@@ -2786,22 +2771,22 @@
         <v>0</v>
       </c>
       <c r="E2" t="s">
-        <v>537</v>
+        <v>527</v>
       </c>
       <c r="F2" s="3">
         <v>0</v>
       </c>
       <c r="G2" s="1"/>
       <c r="H2" s="1" t="s">
-        <v>552</v>
+        <v>542</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="C3" s="3">
         <v>7</v>
@@ -2810,22 +2795,22 @@
         <v>0</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="F3" s="3">
         <v>0</v>
       </c>
       <c r="G3" s="1"/>
       <c r="H3" s="1" t="s">
-        <v>553</v>
+        <v>543</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C4" s="3">
         <v>8</v>
@@ -2834,22 +2819,22 @@
         <v>0</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="F4" s="3">
         <v>0</v>
       </c>
       <c r="G4" s="1"/>
       <c r="H4" s="1" t="s">
-        <v>554</v>
+        <v>544</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="C5" s="3">
         <v>7</v>
@@ -2858,22 +2843,22 @@
         <v>0</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="F5" s="3">
         <v>0</v>
       </c>
       <c r="G5" s="1"/>
       <c r="H5" t="s">
-        <v>555</v>
+        <v>545</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="C6" s="3">
         <v>7</v>
@@ -2882,22 +2867,22 @@
         <v>0</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="F6" s="3">
         <v>0</v>
       </c>
       <c r="G6" s="1"/>
       <c r="H6" t="s">
-        <v>555</v>
+        <v>545</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C7" s="3">
         <v>13</v>
@@ -2906,22 +2891,22 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F7" s="3">
         <v>0</v>
       </c>
       <c r="G7" s="1"/>
       <c r="H7" s="1" t="s">
-        <v>556</v>
+        <v>546</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C8" s="3">
         <v>13</v>
@@ -2930,22 +2915,22 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F8" s="3">
         <v>0</v>
       </c>
       <c r="G8" s="1"/>
       <c r="H8" s="1" t="s">
-        <v>557</v>
+        <v>547</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="C9" s="3">
         <v>9</v>
@@ -2954,22 +2939,22 @@
         <v>0</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="F9" s="3">
         <v>0</v>
       </c>
       <c r="G9" s="1"/>
       <c r="H9" s="1" t="s">
-        <v>558</v>
+        <v>548</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="C10" s="3">
         <v>9</v>
@@ -2978,22 +2963,22 @@
         <v>0</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="F10" s="3">
         <v>0</v>
       </c>
       <c r="G10" s="1"/>
       <c r="H10" s="1" t="s">
-        <v>558</v>
+        <v>548</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="C11" s="3">
         <v>9</v>
@@ -3002,22 +2987,22 @@
         <v>0</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="F11" s="3">
         <v>0</v>
       </c>
       <c r="G11" s="1"/>
       <c r="H11" s="1" t="s">
-        <v>558</v>
+        <v>548</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="C12" s="3">
         <v>6</v>
@@ -3026,22 +3011,22 @@
         <v>0</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="F12" s="3">
         <v>0</v>
       </c>
       <c r="G12" s="1"/>
       <c r="H12" s="1" t="s">
-        <v>559</v>
+        <v>549</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="C13" s="3">
         <v>6</v>
@@ -3050,22 +3035,22 @@
         <v>0</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="F13" s="3">
         <v>0</v>
       </c>
       <c r="G13" s="1"/>
       <c r="H13" s="1" t="s">
-        <v>559</v>
+        <v>549</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C14" s="3">
         <v>13</v>
@@ -3074,22 +3059,22 @@
         <v>0</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="F14" s="3">
         <v>0</v>
       </c>
       <c r="G14" s="1"/>
       <c r="H14" s="1" t="s">
-        <v>560</v>
+        <v>550</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C15" s="3">
         <v>27</v>
@@ -3098,22 +3083,22 @@
         <v>0</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="F15" s="3">
         <v>0</v>
       </c>
       <c r="G15" s="1"/>
       <c r="H15" s="1" t="s">
-        <v>561</v>
+        <v>551</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C16" s="3">
         <v>7</v>
@@ -3122,22 +3107,22 @@
         <v>0</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F16" s="3">
         <v>0</v>
       </c>
       <c r="G16" s="1"/>
       <c r="H16" s="1" t="s">
-        <v>562</v>
+        <v>552</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C17" s="3">
         <v>27</v>
@@ -3146,22 +3131,22 @@
         <v>0</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F17" s="3">
         <v>0</v>
       </c>
       <c r="G17" s="1"/>
       <c r="H17" s="1" t="s">
-        <v>563</v>
+        <v>553</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C18" s="3">
         <v>7</v>
@@ -3170,22 +3155,22 @@
         <v>0</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="F18" s="3">
         <v>0</v>
       </c>
       <c r="G18" s="1"/>
       <c r="H18" s="1" t="s">
-        <v>564</v>
+        <v>554</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C19" s="3">
         <v>28</v>
@@ -3194,22 +3179,22 @@
         <v>0</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F19" s="3">
         <v>0</v>
       </c>
       <c r="G19" s="1"/>
       <c r="H19" s="1" t="s">
-        <v>565</v>
+        <v>555</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="C20" s="3">
         <v>30</v>
@@ -3218,22 +3203,22 @@
         <v>0</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="F20" s="3">
         <v>0</v>
       </c>
       <c r="G20" s="1"/>
       <c r="H20" s="1" t="s">
-        <v>566</v>
+        <v>556</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C21" s="3">
         <v>28</v>
@@ -3242,22 +3227,22 @@
         <v>0</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F21" s="3">
         <v>0</v>
       </c>
       <c r="G21" s="1"/>
       <c r="H21" s="1" t="s">
-        <v>567</v>
+        <v>557</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C22" s="3">
         <v>28</v>
@@ -3266,22 +3251,22 @@
         <v>0</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F22" s="3">
         <v>0</v>
       </c>
       <c r="G22" s="1"/>
       <c r="H22" s="1" t="s">
-        <v>568</v>
+        <v>558</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>461</v>
+        <v>455</v>
       </c>
       <c r="C23" s="3">
         <v>6</v>
@@ -3290,21 +3275,21 @@
         <v>0</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="F23" s="3">
         <v>0</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>569</v>
+        <v>559</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>462</v>
+        <v>456</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>460</v>
+        <v>454</v>
       </c>
       <c r="C24" s="3">
         <v>6</v>
@@ -3313,21 +3298,21 @@
         <v>0</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="F24" s="3">
         <v>0</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>569</v>
+        <v>559</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C25" s="3">
         <v>6</v>
@@ -3336,22 +3321,22 @@
         <v>0</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F25" s="3">
         <v>0</v>
       </c>
       <c r="G25" s="1"/>
       <c r="H25" s="1" t="s">
-        <v>570</v>
+        <v>560</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C26" s="3">
         <v>6</v>
@@ -3360,22 +3345,22 @@
         <v>0</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="F26" s="3">
         <v>0</v>
       </c>
       <c r="G26" s="1"/>
       <c r="H26" s="1" t="s">
-        <v>571</v>
+        <v>561</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="C27" s="3">
         <v>6</v>
@@ -3384,22 +3369,22 @@
         <v>0</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="F27" s="3">
         <v>0</v>
       </c>
       <c r="G27" s="1"/>
       <c r="H27" s="2" t="s">
-        <v>572</v>
+        <v>562</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C28" s="3">
         <v>6</v>
@@ -3408,22 +3393,22 @@
         <v>0</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F28" s="3">
         <v>0</v>
       </c>
       <c r="G28" s="1"/>
       <c r="H28" s="1" t="s">
-        <v>573</v>
+        <v>563</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C29" s="3">
         <v>37</v>
@@ -3432,22 +3417,22 @@
         <v>0</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F29" s="3">
         <v>0</v>
       </c>
       <c r="G29" s="1"/>
       <c r="H29" s="1" t="s">
-        <v>574</v>
+        <v>564</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C30" s="3">
         <v>6</v>
@@ -3456,22 +3441,22 @@
         <v>0</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F30" s="3">
         <v>0</v>
       </c>
       <c r="G30" s="1"/>
       <c r="H30" s="1" t="s">
-        <v>575</v>
+        <v>565</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C31" s="3">
         <v>6</v>
@@ -3480,22 +3465,22 @@
         <v>0</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F31" s="3">
         <v>0</v>
       </c>
       <c r="G31" s="1"/>
       <c r="H31" s="1" t="s">
-        <v>576</v>
+        <v>566</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C32" s="3">
         <v>6</v>
@@ -3504,22 +3489,22 @@
         <v>0</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F32" s="3">
         <v>0</v>
       </c>
       <c r="G32" s="1"/>
       <c r="H32" s="1" t="s">
-        <v>577</v>
+        <v>567</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C33" s="3">
         <v>37</v>
@@ -3528,22 +3513,22 @@
         <v>0</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F33" s="3">
         <v>0</v>
       </c>
       <c r="G33" s="1"/>
       <c r="H33" s="1" t="s">
-        <v>578</v>
+        <v>568</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C34" s="3">
         <v>37</v>
@@ -3552,22 +3537,22 @@
         <v>0</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F34" s="3">
         <v>0</v>
       </c>
       <c r="G34" s="1"/>
       <c r="H34" s="1" t="s">
-        <v>579</v>
+        <v>569</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C35" s="3">
         <v>6</v>
@@ -3576,19 +3561,19 @@
         <v>0</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F35" s="3">
         <v>0</v>
       </c>
       <c r="G35" s="1"/>
       <c r="H35" s="1" t="s">
-        <v>580</v>
+        <v>570</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>8</v>
@@ -3607,15 +3592,15 @@
       </c>
       <c r="G36" s="1"/>
       <c r="H36" t="s">
-        <v>581</v>
+        <v>571</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="C37" s="3">
         <v>14</v>
@@ -3624,22 +3609,22 @@
         <v>0</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="F37" s="3">
         <v>0</v>
       </c>
       <c r="G37" s="1"/>
       <c r="H37" t="s">
-        <v>582</v>
+        <v>572</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="C38" s="3">
         <v>15</v>
@@ -3648,22 +3633,22 @@
         <v>0.95833333333333337</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="F38" s="3">
         <v>0</v>
       </c>
       <c r="G38" s="1"/>
       <c r="H38" t="s">
-        <v>582</v>
+        <v>572</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C39" s="3">
         <v>7</v>
@@ -3672,22 +3657,22 @@
         <v>0.97916666666666663</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="F39" s="3">
         <v>0</v>
       </c>
       <c r="G39" s="1"/>
       <c r="H39" t="s">
-        <v>582</v>
+        <v>572</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C40" s="3">
         <v>6</v>
@@ -3696,22 +3681,22 @@
         <v>0</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F40" s="3">
         <v>0</v>
       </c>
       <c r="G40" s="1"/>
       <c r="H40" s="1" t="s">
-        <v>583</v>
+        <v>573</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="C41" s="1">
         <v>13</v>
@@ -3720,44 +3705,44 @@
         <v>0</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="F41" s="1">
         <v>0</v>
       </c>
       <c r="G41" s="1"/>
       <c r="H41" s="1" t="s">
-        <v>584</v>
+        <v>574</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="C42" s="1"/>
       <c r="D42" s="1"/>
       <c r="E42" s="1" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="F42" s="3">
         <v>1</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>585</v>
+        <v>575</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C43" s="3">
         <v>7</v>
@@ -3766,22 +3751,22 @@
         <v>0.875</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F43" s="3">
         <v>0</v>
       </c>
       <c r="G43" s="1"/>
       <c r="H43" s="1" t="s">
-        <v>586</v>
+        <v>576</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="C44" s="3">
         <v>6</v>
@@ -3790,22 +3775,22 @@
         <v>0</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="F44" s="3">
         <v>0</v>
       </c>
       <c r="G44" s="1"/>
       <c r="H44" s="1" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="C45" s="3">
         <v>55</v>
@@ -3814,22 +3799,22 @@
         <v>0</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="F45" s="3">
         <v>0</v>
       </c>
       <c r="G45" s="1"/>
       <c r="H45" s="1" t="s">
-        <v>588</v>
+        <v>578</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="C46" s="3">
         <v>6</v>
@@ -3838,19 +3823,19 @@
         <v>0</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="F46" s="3">
         <v>0</v>
       </c>
       <c r="G46" s="1"/>
       <c r="H46" s="1" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>2</v>
@@ -3869,12 +3854,12 @@
       </c>
       <c r="G47" s="1"/>
       <c r="H47" s="2" t="s">
-        <v>589</v>
+        <v>579</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>6</v>
@@ -3893,12 +3878,12 @@
       </c>
       <c r="G48" s="1"/>
       <c r="H48" s="2" t="s">
-        <v>590</v>
+        <v>580</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>4</v>
@@ -3917,12 +3902,12 @@
       </c>
       <c r="G49" s="1"/>
       <c r="H49" s="2" t="s">
-        <v>591</v>
+        <v>581</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>0</v>
@@ -3941,15 +3926,15 @@
       </c>
       <c r="G50" s="1"/>
       <c r="H50" s="2" t="s">
-        <v>592</v>
+        <v>582</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="C51" s="3">
         <v>7</v>
@@ -3958,18 +3943,18 @@
         <v>0</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="F51" s="3">
         <v>0</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>593</v>
+        <v>583</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B52" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C52" s="3">
         <v>30</v>
@@ -3978,18 +3963,18 @@
         <v>0</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F52" s="3">
         <v>0</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>594</v>
+        <v>584</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B53" s="1" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="C53" s="3">
         <v>30</v>
@@ -3998,18 +3983,18 @@
         <v>0</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="F53" s="3">
         <v>0</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>595</v>
+        <v>585</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B54" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C54" s="3">
         <v>30</v>
@@ -4018,18 +4003,18 @@
         <v>0</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F54" s="3">
         <v>0</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>596</v>
+        <v>586</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B55" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C55" s="3">
         <v>15</v>
@@ -4038,18 +4023,18 @@
         <v>0</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F55" s="3">
         <v>0</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>597</v>
+        <v>587</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B56" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C56" s="3">
         <v>15</v>
@@ -4058,18 +4043,18 @@
         <v>0</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F56" s="3">
         <v>0</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>598</v>
+        <v>588</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B57" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C57" s="3">
         <v>30</v>
@@ -4078,18 +4063,18 @@
         <v>0</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F57" s="3">
         <v>0</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>599</v>
+        <v>589</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B58" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C58" s="3">
         <v>30</v>
@@ -4098,21 +4083,21 @@
         <v>0</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F58" s="3">
         <v>0</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>600</v>
+        <v>590</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C59" s="3">
         <v>30</v>
@@ -4121,18 +4106,18 @@
         <v>0</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F59" s="3">
         <v>0</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>601</v>
+        <v>591</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B60" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C60" s="3">
         <v>15</v>
@@ -4141,18 +4126,18 @@
         <v>0</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F60" s="3">
         <v>0</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>602</v>
+        <v>592</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B61" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C61" s="3">
         <v>30</v>
@@ -4161,18 +4146,18 @@
         <v>0</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F61" s="3">
         <v>0</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>603</v>
+        <v>593</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B62" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C62" s="3">
         <v>15</v>
@@ -4181,18 +4166,18 @@
         <v>0</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F62" s="3">
         <v>0</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>604</v>
+        <v>594</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B63" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C63" s="3">
         <v>7</v>
@@ -4201,18 +4186,18 @@
         <v>0</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F63" s="3">
         <v>0</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>605</v>
+        <v>595</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B64" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C64" s="3">
         <v>7</v>
@@ -4221,18 +4206,18 @@
         <v>0</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F64" s="3">
         <v>0</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>606</v>
+        <v>596</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B65" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C65" s="3">
         <v>14</v>
@@ -4241,18 +4226,18 @@
         <v>0</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F65" s="3">
         <v>0</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>607</v>
+        <v>597</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B66" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C66" s="3">
         <v>30</v>
@@ -4261,18 +4246,18 @@
         <v>0</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F66" s="3">
         <v>0</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>608</v>
+        <v>598</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B67" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C67" s="3">
         <v>30</v>
@@ -4281,18 +4266,18 @@
         <v>0</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F67" s="3">
         <v>0</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>609</v>
+        <v>599</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B68" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C68" s="3">
         <v>30</v>
@@ -4301,18 +4286,18 @@
         <v>0</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F68" s="3">
         <v>0</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>610</v>
+        <v>600</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B69" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C69" s="3">
         <v>30</v>
@@ -4321,18 +4306,18 @@
         <v>0</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F69" s="3">
         <v>0</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>611</v>
+        <v>601</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B70" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C70" s="3">
         <v>30</v>
@@ -4341,18 +4326,18 @@
         <v>0</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F70" s="3">
         <v>0</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>612</v>
+        <v>602</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B71" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C71" s="3">
         <v>15</v>
@@ -4361,21 +4346,21 @@
         <v>0</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F71" s="3">
         <v>0</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>613</v>
+        <v>603</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
-        <v>498</v>
+        <v>492</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C72" s="3">
         <v>7</v>
@@ -4384,22 +4369,22 @@
         <v>0</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F72" s="3">
         <v>0</v>
       </c>
       <c r="G72" s="1"/>
       <c r="H72" s="1" t="s">
-        <v>664</v>
+        <v>653</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
-        <v>502</v>
+        <v>496</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>518</v>
+        <v>508</v>
       </c>
       <c r="C73" s="3">
         <v>7</v>
@@ -4408,22 +4393,22 @@
         <v>0</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F73" s="3">
         <v>0</v>
       </c>
       <c r="G73" s="1"/>
       <c r="H73" s="1" t="s">
-        <v>664</v>
+        <v>653</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
-        <v>499</v>
+        <v>493</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>519</v>
+        <v>509</v>
       </c>
       <c r="C74" s="3">
         <v>7</v>
@@ -4432,22 +4417,22 @@
         <v>0</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F74" s="3">
         <v>0</v>
       </c>
       <c r="G74" s="1"/>
       <c r="H74" s="1" t="s">
-        <v>664</v>
+        <v>653</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
-        <v>503</v>
+        <v>497</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C75" s="3">
         <v>7</v>
@@ -4456,22 +4441,22 @@
         <v>0</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F75" s="3">
         <v>0</v>
       </c>
       <c r="G75" s="1"/>
       <c r="H75" s="1" t="s">
-        <v>664</v>
+        <v>653</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
-        <v>504</v>
+        <v>498</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C76" s="3">
         <v>7</v>
@@ -4480,22 +4465,22 @@
         <v>0</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F76" s="3">
         <v>0</v>
       </c>
       <c r="G76" s="1"/>
       <c r="H76" s="1" t="s">
-        <v>664</v>
+        <v>653</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A77" s="2" t="s">
-        <v>500</v>
+        <v>494</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>520</v>
+        <v>510</v>
       </c>
       <c r="C77" s="3">
         <v>7</v>
@@ -4504,22 +4489,22 @@
         <v>0</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F77" s="3">
         <v>0</v>
       </c>
       <c r="G77" s="1"/>
       <c r="H77" s="1" t="s">
-        <v>664</v>
+        <v>653</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>522</v>
+        <v>512</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>521</v>
+        <v>511</v>
       </c>
       <c r="C78" s="3">
         <v>7</v>
@@ -4528,22 +4513,22 @@
         <v>0</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F78" s="3">
         <v>0</v>
       </c>
       <c r="G78" s="1"/>
       <c r="H78" s="1" t="s">
-        <v>665</v>
+        <v>654</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
-        <v>501</v>
+        <v>495</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>523</v>
+        <v>513</v>
       </c>
       <c r="C79" s="3">
         <v>7</v>
@@ -4552,22 +4537,22 @@
         <v>0</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F79" s="3">
         <v>0</v>
       </c>
       <c r="G79" s="1"/>
       <c r="H79" s="1" t="s">
-        <v>664</v>
+        <v>653</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A80" s="2" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="C80" s="3">
         <v>6</v>
@@ -4576,22 +4561,22 @@
         <v>0</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="F80" s="3">
         <v>0</v>
       </c>
       <c r="G80" s="1"/>
       <c r="H80" t="s">
-        <v>614</v>
+        <v>604</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A81" s="2" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="C81" s="3">
         <v>7</v>
@@ -4600,22 +4585,22 @@
         <v>0</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F81" s="3">
         <v>0</v>
       </c>
       <c r="G81" s="1"/>
       <c r="H81" s="1" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A82" s="2" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="C82" s="1">
         <v>76</v>
@@ -4624,20 +4609,20 @@
         <v>0</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="F82" s="1"/>
       <c r="G82" s="1"/>
       <c r="H82" s="1" t="s">
-        <v>616</v>
+        <v>606</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A83" s="2" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="C83" s="3">
         <v>14</v>
@@ -4646,19 +4631,19 @@
         <v>0</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="F83" s="3">
         <v>0</v>
       </c>
       <c r="G83" s="1"/>
       <c r="H83" s="1" t="s">
-        <v>617</v>
+        <v>607</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A84" s="2" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>48</v>
@@ -4677,12 +4662,12 @@
       </c>
       <c r="G84" s="1"/>
       <c r="H84" s="2" t="s">
-        <v>618</v>
+        <v>608</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A85" s="2" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>50</v>
@@ -4701,15 +4686,15 @@
       </c>
       <c r="G85" s="1"/>
       <c r="H85" s="2" t="s">
-        <v>618</v>
+        <v>608</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A86" s="2" t="s">
-        <v>444</v>
+        <v>438</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="C86" s="3">
         <v>6</v>
@@ -4718,19 +4703,19 @@
         <v>0</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="F86" s="3">
         <v>0</v>
       </c>
       <c r="G86" s="1"/>
       <c r="H86" s="7" t="s">
-        <v>670</v>
+        <v>659</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A87" s="2" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>44</v>
@@ -4749,12 +4734,12 @@
       </c>
       <c r="G87" s="1"/>
       <c r="H87" s="2" t="s">
-        <v>618</v>
+        <v>608</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A88" s="2" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>52</v>
@@ -4773,12 +4758,12 @@
       </c>
       <c r="G88" s="1"/>
       <c r="H88" s="2" t="s">
-        <v>618</v>
+        <v>608</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A89" s="2" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>54</v>
@@ -4797,15 +4782,15 @@
       </c>
       <c r="G89" s="1"/>
       <c r="H89" s="2" t="s">
-        <v>618</v>
+        <v>608</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A90" s="2" t="s">
-        <v>445</v>
+        <v>439</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="C90" s="3">
         <v>6</v>
@@ -4814,22 +4799,22 @@
         <v>0</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="F90" s="3">
         <v>0</v>
       </c>
       <c r="G90" s="1"/>
       <c r="H90" s="7" t="s">
-        <v>670</v>
+        <v>659</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A91" s="2" t="s">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="C91" s="3">
         <v>6</v>
@@ -4838,19 +4823,19 @@
         <v>0</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="F91" s="3">
         <v>0</v>
       </c>
       <c r="G91" s="1"/>
       <c r="H91" s="7" t="s">
-        <v>670</v>
+        <v>659</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A92" s="2" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>56</v>
@@ -4869,12 +4854,12 @@
       </c>
       <c r="G92" s="1"/>
       <c r="H92" s="2" t="s">
-        <v>618</v>
+        <v>608</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A93" s="2" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>58</v>
@@ -4886,22 +4871,22 @@
         <v>0.875</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="F93" s="3">
         <v>0</v>
       </c>
       <c r="G93" s="1"/>
       <c r="H93" s="2" t="s">
-        <v>618</v>
+        <v>608</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A94" s="2" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="C94" s="3">
         <v>6</v>
@@ -4910,19 +4895,19 @@
         <v>0</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="F94" s="3">
         <v>0</v>
       </c>
       <c r="G94" s="1"/>
       <c r="H94" s="7" t="s">
-        <v>670</v>
+        <v>659</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A95" s="2" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>42</v>
@@ -4941,12 +4926,12 @@
       </c>
       <c r="G95" s="1"/>
       <c r="H95" s="2" t="s">
-        <v>618</v>
+        <v>608</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A96" s="2" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>46</v>
@@ -4965,15 +4950,15 @@
       </c>
       <c r="G96" s="1"/>
       <c r="H96" s="2" t="s">
-        <v>618</v>
+        <v>608</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="C97" s="3">
         <v>6</v>
@@ -4982,22 +4967,22 @@
         <v>0</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="F97" s="3">
         <v>0</v>
       </c>
       <c r="G97" s="1"/>
       <c r="H97" s="1" t="s">
-        <v>619</v>
+        <v>609</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="C98" s="3">
         <v>6</v>
@@ -5006,22 +4991,22 @@
         <v>0</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="F98" s="3">
         <v>0</v>
       </c>
       <c r="G98" s="1"/>
       <c r="H98" s="1" t="s">
-        <v>619</v>
+        <v>609</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="C99" s="3">
         <v>6</v>
@@ -5030,22 +5015,22 @@
         <v>0</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="F99" s="3">
         <v>0</v>
       </c>
       <c r="G99" s="1"/>
       <c r="H99" s="1" t="s">
-        <v>619</v>
+        <v>609</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>451</v>
+        <v>445</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="C100" s="3">
         <v>6</v>
@@ -5054,22 +5039,22 @@
         <v>0</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="F100" s="3">
         <v>0</v>
       </c>
       <c r="G100" s="1"/>
       <c r="H100" s="1" t="s">
-        <v>619</v>
+        <v>609</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="C101" s="3">
         <v>6</v>
@@ -5078,22 +5063,22 @@
         <v>0</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="F101" s="3">
         <v>0</v>
       </c>
       <c r="G101" s="1"/>
       <c r="H101" s="1" t="s">
-        <v>619</v>
+        <v>609</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>453</v>
+        <v>447</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="C102" s="3">
         <v>6</v>
@@ -5102,22 +5087,22 @@
         <v>0</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="F102" s="3">
         <v>0</v>
       </c>
       <c r="G102" s="1"/>
       <c r="H102" s="1" t="s">
-        <v>619</v>
+        <v>609</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="C103" s="3">
         <v>6</v>
@@ -5126,22 +5111,22 @@
         <v>0</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="F103" s="3">
         <v>0</v>
       </c>
       <c r="G103" s="1"/>
       <c r="H103" s="1" t="s">
-        <v>619</v>
+        <v>609</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A104" s="2" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="C104" s="3">
         <v>6</v>
@@ -5150,22 +5135,22 @@
         <v>0</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="F104" s="3">
         <v>0</v>
       </c>
       <c r="G104" s="1"/>
       <c r="H104" s="8" t="s">
-        <v>669</v>
+        <v>658</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A105" s="2" t="s">
-        <v>456</v>
+        <v>450</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="C105" s="3">
         <v>6</v>
@@ -5174,22 +5159,22 @@
         <v>0.54166666666666663</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="F105" s="3">
         <v>0</v>
       </c>
       <c r="G105" s="1"/>
       <c r="H105" s="1" t="s">
-        <v>620</v>
+        <v>610</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A106" s="2" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C106" s="3">
         <v>13</v>
@@ -5198,22 +5183,22 @@
         <v>0</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="F106" s="3">
         <v>0</v>
       </c>
       <c r="G106" s="1"/>
       <c r="H106" s="1" t="s">
-        <v>621</v>
+        <v>611</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A107" s="2" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="C107" s="3">
         <v>13</v>
@@ -5222,22 +5207,22 @@
         <v>0</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="F107" s="3">
         <v>0</v>
       </c>
       <c r="G107" s="1"/>
       <c r="H107" s="1" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A108" s="2" t="s">
-        <v>505</v>
+        <v>499</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C108" s="3">
         <v>6</v>
@@ -5246,22 +5231,22 @@
         <v>0</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F108" s="3">
         <v>0</v>
       </c>
       <c r="G108" s="1"/>
       <c r="H108" s="1" t="s">
-        <v>623</v>
+        <v>613</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A109" s="2" t="s">
-        <v>508</v>
+        <v>502</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C109" s="3">
         <v>30</v>
@@ -5270,22 +5255,22 @@
         <v>0</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F109" s="3">
         <v>0</v>
       </c>
       <c r="G109" s="1"/>
       <c r="H109" s="1" t="s">
-        <v>623</v>
+        <v>613</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A110" s="2" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C110" s="3">
         <v>10</v>
@@ -5294,22 +5279,22 @@
         <v>0</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F110" s="3">
         <v>0</v>
       </c>
       <c r="G110" s="1"/>
       <c r="H110" s="1" t="s">
-        <v>623</v>
+        <v>613</v>
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A111" s="2" t="s">
-        <v>507</v>
+        <v>501</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C111" s="3">
         <v>10</v>
@@ -5318,66 +5303,66 @@
         <v>0</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F111" s="3">
         <v>0</v>
       </c>
       <c r="G111" s="1"/>
       <c r="H111" s="1" t="s">
-        <v>623</v>
+        <v>613</v>
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A112" s="2" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="C112" s="1"/>
       <c r="D112" s="1"/>
       <c r="E112" s="1" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="F112" s="3">
         <v>1</v>
       </c>
       <c r="G112" s="1" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="H112" s="2" t="s">
-        <v>624</v>
+        <v>614</v>
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A113" s="2" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C113" s="1"/>
       <c r="D113" s="1"/>
       <c r="E113" s="1" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="F113" s="3">
         <v>1</v>
       </c>
       <c r="G113" s="1" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="H113" s="2" t="s">
-        <v>624</v>
+        <v>614</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A114" s="2" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C114" s="3">
         <v>7</v>
@@ -5386,22 +5371,22 @@
         <v>0.91666666666666663</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F114" s="3">
         <v>0</v>
       </c>
       <c r="G114" s="1"/>
       <c r="H114" s="1" t="s">
-        <v>625</v>
+        <v>615</v>
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A115" s="2" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="C115" s="3">
         <v>6</v>
@@ -5410,22 +5395,22 @@
         <v>0</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="F115" s="3">
         <v>0</v>
       </c>
       <c r="G115" s="1"/>
       <c r="H115" s="1" t="s">
-        <v>626</v>
+        <v>616</v>
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A116" s="2" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C116" s="3">
         <v>6</v>
@@ -5434,22 +5419,22 @@
         <v>0</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="F116" s="3">
         <v>0</v>
       </c>
       <c r="G116" s="1"/>
       <c r="H116" s="1" t="s">
-        <v>666</v>
+        <v>655</v>
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A117" s="2" t="s">
-        <v>458</v>
+        <v>452</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C117" s="3">
         <v>6</v>
@@ -5458,22 +5443,22 @@
         <v>0</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F117" s="3">
         <v>0</v>
       </c>
       <c r="G117" s="1"/>
       <c r="H117" s="2" t="s">
-        <v>627</v>
+        <v>617</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A118" s="2" t="s">
-        <v>509</v>
+        <v>663</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="C118" s="1">
         <v>7</v>
@@ -5482,88 +5467,88 @@
         <v>0.91666666666666663</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="F118" s="1">
         <v>0</v>
       </c>
       <c r="G118" s="1"/>
       <c r="H118" s="1" t="s">
-        <v>628</v>
+        <v>618</v>
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A119" s="2" t="s">
-        <v>510</v>
+        <v>664</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>511</v>
+        <v>503</v>
       </c>
       <c r="C119" s="1"/>
       <c r="D119" s="5"/>
       <c r="E119" s="1" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="F119" s="1">
         <v>1</v>
       </c>
       <c r="G119" s="1" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="H119" s="1" t="s">
-        <v>629</v>
+        <v>619</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A120" s="2" t="s">
-        <v>512</v>
+        <v>665</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="C120" s="1"/>
       <c r="D120" s="1"/>
       <c r="E120" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="F120" s="1">
         <v>1</v>
       </c>
       <c r="G120" s="1" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="H120" s="1" t="s">
-        <v>629</v>
+        <v>619</v>
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A121" s="2" t="s">
-        <v>513</v>
+        <v>666</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="C121" s="1"/>
       <c r="D121" s="1"/>
       <c r="E121" s="1" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="F121" s="1">
         <v>1</v>
       </c>
       <c r="G121" s="1" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="H121" s="1" t="s">
-        <v>629</v>
+        <v>619</v>
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A122" s="2" t="s">
-        <v>514</v>
+        <v>504</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="C122" s="3">
         <v>6</v>
@@ -5572,22 +5557,22 @@
         <v>0</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>254</v>
+        <v>662</v>
       </c>
       <c r="F122" s="3">
         <v>0</v>
       </c>
       <c r="G122" s="1"/>
       <c r="H122" s="1" t="s">
-        <v>630</v>
+        <v>620</v>
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A123" s="2" t="s">
-        <v>515</v>
+        <v>505</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="C123" s="3">
         <v>29</v>
@@ -5596,19 +5581,19 @@
         <v>0</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="F123" s="3">
         <v>0</v>
       </c>
       <c r="G123" s="1"/>
       <c r="H123" s="2" t="s">
-        <v>631</v>
+        <v>621</v>
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A124" s="2" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="B124" s="1" t="s">
         <v>59</v>
@@ -5627,12 +5612,12 @@
       </c>
       <c r="G124" s="1"/>
       <c r="H124" s="2" t="s">
-        <v>632</v>
+        <v>622</v>
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A125" s="2" t="s">
-        <v>471</v>
+        <v>465</v>
       </c>
       <c r="B125" s="1" t="s">
         <v>63</v>
@@ -5644,39 +5629,39 @@
         <v>0</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>516</v>
+        <v>506</v>
       </c>
       <c r="F125" s="3">
         <v>0</v>
       </c>
       <c r="G125" s="1"/>
       <c r="H125" s="2" t="s">
-        <v>633</v>
+        <v>623</v>
       </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A126" s="2" t="s">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>474</v>
+        <v>468</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>517</v>
+        <v>507</v>
       </c>
       <c r="F126" s="3">
         <v>1</v>
       </c>
       <c r="G126" s="2" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="H126" s="1" t="s">
-        <v>634</v>
+        <v>624</v>
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A127" s="2" t="s">
-        <v>470</v>
+        <v>464</v>
       </c>
       <c r="B127" s="1" t="s">
         <v>61</v>
@@ -5695,12 +5680,12 @@
       </c>
       <c r="G127" s="1"/>
       <c r="H127" s="2" t="s">
-        <v>635</v>
+        <v>625</v>
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A128" s="2" t="s">
-        <v>472</v>
+        <v>466</v>
       </c>
       <c r="B128" s="1" t="s">
         <v>64</v>
@@ -5719,15 +5704,15 @@
       </c>
       <c r="G128" s="1"/>
       <c r="H128" s="2" t="s">
-        <v>636</v>
+        <v>626</v>
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A129" s="2" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C129" s="3">
         <v>14</v>
@@ -5736,22 +5721,22 @@
         <v>0</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F129" s="3">
         <v>0</v>
       </c>
       <c r="G129" s="1"/>
       <c r="H129" s="1" t="s">
-        <v>637</v>
+        <v>627</v>
       </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A130" s="2" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C130" s="3">
         <v>7</v>
@@ -5760,22 +5745,22 @@
         <v>0.91666666666666663</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F130" s="3">
         <v>0</v>
       </c>
       <c r="G130" s="1"/>
       <c r="H130" s="1" t="s">
-        <v>637</v>
+        <v>627</v>
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A131" s="2" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C131" s="3">
         <v>7</v>
@@ -5784,22 +5769,22 @@
         <v>0.91666666666666663</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="F131" s="3">
         <v>0</v>
       </c>
       <c r="G131" s="1"/>
       <c r="H131" s="1" t="s">
-        <v>637</v>
+        <v>627</v>
       </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A132" s="2" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="C132" s="3">
         <v>7</v>
@@ -5808,19 +5793,19 @@
         <v>0.875</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="F132" s="3">
         <v>0</v>
       </c>
       <c r="G132" s="1"/>
       <c r="H132" s="1" t="s">
-        <v>638</v>
+        <v>628</v>
       </c>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A133" s="2" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="B133" s="1" t="s">
         <v>10</v>
@@ -5839,15 +5824,15 @@
       </c>
       <c r="G133" s="1"/>
       <c r="H133" s="2" t="s">
-        <v>639</v>
+        <v>629</v>
       </c>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>529</v>
+        <v>519</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="C134" s="3">
         <v>13</v>
@@ -5856,22 +5841,22 @@
         <v>0</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="F134" s="3">
         <v>0</v>
       </c>
       <c r="G134" s="1"/>
       <c r="H134" s="1" t="s">
-        <v>640</v>
+        <v>630</v>
       </c>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>530</v>
+        <v>520</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="C135" s="3">
         <v>45</v>
@@ -5880,22 +5865,22 @@
         <v>0</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="F135" s="3">
         <v>0</v>
       </c>
       <c r="G135" s="1"/>
       <c r="H135" s="1" t="s">
-        <v>641</v>
+        <v>631</v>
       </c>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A136" s="2" t="s">
-        <v>525</v>
+        <v>515</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>526</v>
+        <v>516</v>
       </c>
       <c r="C136" s="3">
         <v>30</v>
@@ -5904,22 +5889,22 @@
         <v>0</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>527</v>
+        <v>517</v>
       </c>
       <c r="F136" s="3">
         <v>0</v>
       </c>
       <c r="G136" s="1"/>
       <c r="H136" s="1" t="s">
-        <v>642</v>
+        <v>632</v>
       </c>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A137" s="2" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="C137" s="3">
         <v>30</v>
@@ -5928,22 +5913,22 @@
         <v>0</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="F137" s="3">
         <v>0</v>
       </c>
       <c r="G137" s="1"/>
       <c r="H137" s="1" t="s">
-        <v>642</v>
+        <v>632</v>
       </c>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A138" s="2" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="C138" s="3">
         <v>7</v>
@@ -5952,22 +5937,22 @@
         <v>0.91666666666666663</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="F138" s="3">
         <v>0</v>
       </c>
       <c r="G138" s="1"/>
       <c r="H138" s="1" t="s">
-        <v>643</v>
+        <v>633</v>
       </c>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A139" s="2" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="C139" s="3">
         <v>6</v>
@@ -5976,22 +5961,22 @@
         <v>0</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>672</v>
+        <v>661</v>
       </c>
       <c r="F139" s="3">
         <v>0</v>
       </c>
       <c r="G139" s="1"/>
       <c r="H139" s="1" t="s">
-        <v>644</v>
+        <v>634</v>
       </c>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A140" s="2" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="C140" s="3">
         <v>13</v>
@@ -6000,19 +5985,19 @@
         <v>0</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>671</v>
+        <v>660</v>
       </c>
       <c r="F140" s="3">
         <v>0</v>
       </c>
       <c r="G140" s="1"/>
       <c r="H140" s="1" t="s">
-        <v>644</v>
+        <v>634</v>
       </c>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="B141" s="1" t="s">
         <v>26</v>
@@ -6031,12 +6016,12 @@
       </c>
       <c r="G141" s="1"/>
       <c r="H141" s="2" t="s">
-        <v>645</v>
+        <v>635</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="B142" s="1" t="s">
         <v>28</v>
@@ -6055,12 +6040,12 @@
       </c>
       <c r="G142" s="1"/>
       <c r="H142" s="2" t="s">
-        <v>645</v>
+        <v>635</v>
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="B143" s="1" t="s">
         <v>24</v>
@@ -6079,12 +6064,12 @@
       </c>
       <c r="G143" s="1"/>
       <c r="H143" s="2" t="s">
-        <v>645</v>
+        <v>635</v>
       </c>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="B144" s="1" t="s">
         <v>32</v>
@@ -6103,12 +6088,12 @@
       </c>
       <c r="G144" s="1"/>
       <c r="H144" s="2" t="s">
-        <v>645</v>
+        <v>635</v>
       </c>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="B145" s="1" t="s">
         <v>34</v>
@@ -6127,12 +6112,12 @@
       </c>
       <c r="G145" s="1"/>
       <c r="H145" s="2" t="s">
-        <v>645</v>
+        <v>635</v>
       </c>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="B146" s="1" t="s">
         <v>21</v>
@@ -6151,12 +6136,12 @@
       </c>
       <c r="G146" s="1"/>
       <c r="H146" s="2" t="s">
-        <v>645</v>
+        <v>635</v>
       </c>
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="B147" s="1" t="s">
         <v>19</v>
@@ -6175,12 +6160,12 @@
       </c>
       <c r="G147" s="1"/>
       <c r="H147" s="2" t="s">
-        <v>645</v>
+        <v>635</v>
       </c>
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A148" s="2" t="s">
-        <v>477</v>
+        <v>471</v>
       </c>
       <c r="B148" s="1" t="s">
         <v>38</v>
@@ -6199,12 +6184,12 @@
       </c>
       <c r="G148" s="1"/>
       <c r="H148" s="2" t="s">
-        <v>645</v>
+        <v>635</v>
       </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="B149" s="1" t="s">
         <v>30</v>
@@ -6223,12 +6208,12 @@
       </c>
       <c r="G149" s="1"/>
       <c r="H149" s="2" t="s">
-        <v>645</v>
+        <v>635</v>
       </c>
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A150" s="2" t="s">
-        <v>478</v>
+        <v>472</v>
       </c>
       <c r="B150" s="1" t="s">
         <v>40</v>
@@ -6247,12 +6232,12 @@
       </c>
       <c r="G150" s="1"/>
       <c r="H150" s="2" t="s">
-        <v>645</v>
+        <v>635</v>
       </c>
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="B151" s="1" t="s">
         <v>36</v>
@@ -6271,12 +6256,12 @@
       </c>
       <c r="G151" s="1"/>
       <c r="H151" s="2" t="s">
-        <v>645</v>
+        <v>635</v>
       </c>
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="B152" s="1" t="s">
         <v>23</v>
@@ -6288,22 +6273,22 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="F152" s="3">
         <v>0</v>
       </c>
       <c r="G152" s="1"/>
       <c r="H152" s="2" t="s">
-        <v>645</v>
+        <v>635</v>
       </c>
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A153" s="2" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>476</v>
+        <v>470</v>
       </c>
       <c r="C153" s="3">
         <v>8</v>
@@ -6312,21 +6297,21 @@
         <v>0</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>468</v>
+        <v>462</v>
       </c>
       <c r="F153" s="3">
         <v>0</v>
       </c>
       <c r="H153" s="1" t="s">
-        <v>646</v>
+        <v>636</v>
       </c>
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A154" s="2" t="s">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="C154" s="3">
         <v>7</v>
@@ -6335,22 +6320,22 @@
         <v>0</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F154" s="3">
         <v>0</v>
       </c>
       <c r="G154" s="1"/>
       <c r="H154" s="8" t="s">
-        <v>663</v>
+        <v>652</v>
       </c>
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>524</v>
+        <v>514</v>
       </c>
       <c r="C155" s="3">
         <v>7</v>
@@ -6359,22 +6344,22 @@
         <v>0.95833333333333337</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="F155" s="3">
         <v>0</v>
       </c>
       <c r="G155" s="1"/>
       <c r="H155" s="1" t="s">
-        <v>647</v>
+        <v>637</v>
       </c>
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A156" s="2" t="s">
-        <v>528</v>
+        <v>518</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C156" s="3">
         <v>7</v>
@@ -6383,22 +6368,22 @@
         <v>0</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="F156" s="3">
         <v>0</v>
       </c>
       <c r="G156" s="1"/>
       <c r="H156" s="1" t="s">
-        <v>648</v>
+        <v>638</v>
       </c>
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C157" s="3">
         <v>6</v>
@@ -6407,22 +6392,22 @@
         <v>0</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F157" s="3">
         <v>0</v>
       </c>
       <c r="G157" s="1"/>
       <c r="H157" s="1" t="s">
-        <v>649</v>
+        <v>639</v>
       </c>
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C158" s="3">
         <v>6</v>
@@ -6431,22 +6416,22 @@
         <v>0</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F158" s="3">
         <v>0</v>
       </c>
       <c r="G158" s="1"/>
       <c r="H158" s="1" t="s">
-        <v>649</v>
+        <v>639</v>
       </c>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C159" s="3">
         <v>6</v>
@@ -6455,22 +6440,22 @@
         <v>0</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F159" s="3">
         <v>0</v>
       </c>
       <c r="G159" s="1"/>
       <c r="H159" s="1" t="s">
-        <v>649</v>
+        <v>639</v>
       </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C160" s="3">
         <v>7</v>
@@ -6479,94 +6464,94 @@
         <v>0.97916666666666663</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>305</v>
+        <v>668</v>
       </c>
       <c r="F160" s="3">
         <v>0</v>
       </c>
       <c r="G160" s="1"/>
       <c r="H160" s="1" t="s">
-        <v>650</v>
+        <v>640</v>
       </c>
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A161" t="s">
-        <v>440</v>
+      <c r="A161" s="2" t="s">
+        <v>476</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>222</v>
+        <v>66</v>
       </c>
       <c r="C161" s="3">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="D161" s="4">
         <v>0</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>223</v>
+        <v>667</v>
       </c>
       <c r="F161" s="3">
         <v>0</v>
       </c>
       <c r="G161" s="1"/>
-      <c r="H161" s="1" t="s">
-        <v>651</v>
+      <c r="H161" s="2" t="s">
+        <v>641</v>
       </c>
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A162" s="2" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C162" s="3">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D162" s="4">
         <v>0</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F162" s="3">
         <v>0</v>
       </c>
       <c r="G162" s="1"/>
       <c r="H162" s="2" t="s">
-        <v>652</v>
+        <v>642</v>
       </c>
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A163" s="2" t="s">
-        <v>483</v>
+        <v>478</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C163" s="3">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D163" s="4">
         <v>0</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F163" s="3">
         <v>0</v>
       </c>
       <c r="G163" s="1"/>
       <c r="H163" s="2" t="s">
-        <v>653</v>
+        <v>643</v>
       </c>
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A164" s="2" t="s">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C164" s="3">
         <v>6</v>
@@ -6575,22 +6560,22 @@
         <v>0</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="F164" s="3">
         <v>0</v>
       </c>
       <c r="G164" s="1"/>
       <c r="H164" s="2" t="s">
-        <v>654</v>
+        <v>644</v>
       </c>
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A165" s="2" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C165" s="3">
         <v>6</v>
@@ -6599,22 +6584,22 @@
         <v>0</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="F165" s="3">
         <v>0</v>
       </c>
       <c r="G165" s="1"/>
       <c r="H165" s="2" t="s">
-        <v>655</v>
+        <v>645</v>
       </c>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A166" s="2" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C166" s="3">
         <v>6</v>
@@ -6623,46 +6608,46 @@
         <v>0</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F166" s="3">
         <v>0</v>
       </c>
       <c r="G166" s="1"/>
       <c r="H166" s="2" t="s">
-        <v>656</v>
+        <v>646</v>
       </c>
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A167" s="2" t="s">
-        <v>487</v>
+        <v>482</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="C167" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D167" s="4">
         <v>0</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>77</v>
+        <v>98</v>
       </c>
       <c r="F167" s="3">
         <v>0</v>
       </c>
       <c r="G167" s="1"/>
-      <c r="H167" s="2" t="s">
-        <v>657</v>
+      <c r="H167" s="8" t="s">
+        <v>656</v>
       </c>
     </row>
     <row r="168" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A168" s="2" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C168" s="3">
         <v>7</v>
@@ -6671,22 +6656,22 @@
         <v>0</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="F168" s="3">
         <v>0</v>
       </c>
       <c r="G168" s="1"/>
       <c r="H168" s="8" t="s">
-        <v>667</v>
+        <v>656</v>
       </c>
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A169" s="2" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="C169" s="3">
         <v>7</v>
@@ -6695,22 +6680,22 @@
         <v>0</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="F169" s="3">
         <v>0</v>
       </c>
       <c r="G169" s="1"/>
-      <c r="H169" s="8" t="s">
-        <v>667</v>
+      <c r="H169" s="1" t="s">
+        <v>656</v>
       </c>
     </row>
     <row r="170" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A170" s="2" t="s">
-        <v>491</v>
+        <v>486</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C170" s="3">
         <v>7</v>
@@ -6719,22 +6704,22 @@
         <v>0</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F170" s="3">
         <v>0</v>
       </c>
       <c r="G170" s="1"/>
       <c r="H170" s="1" t="s">
-        <v>667</v>
+        <v>656</v>
       </c>
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A171" s="2" t="s">
-        <v>492</v>
+        <v>487</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>94</v>
+        <v>107</v>
       </c>
       <c r="C171" s="3">
         <v>7</v>
@@ -6743,22 +6728,22 @@
         <v>0</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="F171" s="3">
         <v>0</v>
       </c>
       <c r="G171" s="1"/>
       <c r="H171" s="1" t="s">
-        <v>667</v>
+        <v>656</v>
       </c>
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A172" s="2" t="s">
-        <v>493</v>
+        <v>488</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="C172" s="3">
         <v>7</v>
@@ -6767,22 +6752,22 @@
         <v>0</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="F172" s="3">
         <v>0</v>
       </c>
       <c r="G172" s="1"/>
       <c r="H172" s="1" t="s">
-        <v>667</v>
+        <v>656</v>
       </c>
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A173" s="2" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="C173" s="3">
         <v>7</v>
@@ -6791,22 +6776,22 @@
         <v>0</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="F173" s="3">
         <v>0</v>
       </c>
       <c r="G173" s="1"/>
       <c r="H173" s="1" t="s">
-        <v>667</v>
+        <v>656</v>
       </c>
     </row>
     <row r="174" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A174" s="2" t="s">
-        <v>495</v>
+        <v>490</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="C174" s="3">
         <v>7</v>
@@ -6815,22 +6800,22 @@
         <v>0</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>111</v>
+        <v>483</v>
       </c>
       <c r="F174" s="3">
         <v>0</v>
       </c>
       <c r="G174" s="1"/>
       <c r="H174" s="1" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
     </row>
     <row r="175" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A175" s="2" t="s">
-        <v>496</v>
+        <v>491</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="C175" s="3">
         <v>7</v>
@@ -6839,70 +6824,70 @@
         <v>0</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>489</v>
+        <v>114</v>
       </c>
       <c r="F175" s="3">
         <v>0</v>
       </c>
       <c r="G175" s="1"/>
       <c r="H175" s="1" t="s">
-        <v>668</v>
+        <v>656</v>
       </c>
     </row>
     <row r="176" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A176" s="2" t="s">
-        <v>497</v>
+      <c r="A176" t="s">
+        <v>435</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>114</v>
+        <v>292</v>
       </c>
       <c r="C176" s="3">
-        <v>7</v>
-      </c>
-      <c r="D176" s="4">
+        <v>13</v>
+      </c>
+      <c r="D176" s="5">
         <v>0</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>115</v>
+        <v>293</v>
       </c>
       <c r="F176" s="3">
         <v>0</v>
       </c>
       <c r="G176" s="1"/>
       <c r="H176" s="1" t="s">
-        <v>667</v>
+        <v>647</v>
       </c>
     </row>
     <row r="177" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
-        <v>441</v>
+        <v>521</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>296</v>
+        <v>211</v>
       </c>
       <c r="C177" s="3">
-        <v>13</v>
-      </c>
-      <c r="D177" s="5">
+        <v>6</v>
+      </c>
+      <c r="D177" s="4">
         <v>0</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>297</v>
+        <v>212</v>
       </c>
       <c r="F177" s="3">
         <v>0</v>
       </c>
       <c r="G177" s="1"/>
       <c r="H177" s="1" t="s">
-        <v>658</v>
+        <v>648</v>
       </c>
     </row>
     <row r="178" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
-        <v>531</v>
+        <v>522</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C178" s="3">
         <v>6</v>
@@ -6911,22 +6896,22 @@
         <v>0</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F178" s="3">
         <v>0</v>
       </c>
       <c r="G178" s="1"/>
       <c r="H178" s="1" t="s">
-        <v>659</v>
+        <v>648</v>
       </c>
     </row>
     <row r="179" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
-        <v>532</v>
+        <v>525</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="C179" s="3">
         <v>6</v>
@@ -6935,22 +6920,22 @@
         <v>0</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="F179" s="3">
         <v>0</v>
       </c>
       <c r="G179" s="1"/>
       <c r="H179" s="1" t="s">
-        <v>659</v>
+        <v>648</v>
       </c>
     </row>
     <row r="180" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
-        <v>535</v>
+        <v>524</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="C180" s="3">
         <v>6</v>
@@ -6959,22 +6944,22 @@
         <v>0</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="F180" s="3">
         <v>0</v>
       </c>
       <c r="G180" s="1"/>
       <c r="H180" s="1" t="s">
-        <v>659</v>
+        <v>648</v>
       </c>
     </row>
     <row r="181" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
-        <v>534</v>
+        <v>523</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C181" s="3">
         <v>6</v>
@@ -6983,171 +6968,147 @@
         <v>0</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>218</v>
+        <v>526</v>
       </c>
       <c r="F181" s="3">
         <v>0</v>
       </c>
       <c r="G181" s="1"/>
       <c r="H181" s="1" t="s">
-        <v>659</v>
+        <v>648</v>
       </c>
     </row>
     <row r="182" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
-        <v>533</v>
+        <v>436</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="C182" s="3">
-        <v>6</v>
-      </c>
-      <c r="D182" s="4">
-        <v>0</v>
-      </c>
+        <v>308</v>
+      </c>
+      <c r="C182" s="1"/>
+      <c r="D182" s="1"/>
       <c r="E182" s="1" t="s">
-        <v>536</v>
-      </c>
-      <c r="F182" s="3">
-        <v>0</v>
-      </c>
-      <c r="G182" s="1"/>
+        <v>324</v>
+      </c>
+      <c r="F182" s="1">
+        <v>1</v>
+      </c>
+      <c r="G182" s="1" t="s">
+        <v>320</v>
+      </c>
       <c r="H182" s="1" t="s">
-        <v>659</v>
+        <v>649</v>
       </c>
     </row>
     <row r="183" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A183" t="s">
-        <v>442</v>
+      <c r="A183" s="2" t="s">
+        <v>473</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="C183" s="1"/>
-      <c r="D183" s="1"/>
+        <v>474</v>
+      </c>
       <c r="E183" s="1" t="s">
-        <v>329</v>
-      </c>
-      <c r="F183" s="1">
-        <v>1</v>
-      </c>
-      <c r="G183" s="1" t="s">
-        <v>325</v>
-      </c>
-      <c r="H183" s="1" t="s">
-        <v>660</v>
+        <v>475</v>
       </c>
     </row>
     <row r="184" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A184" s="2" t="s">
-        <v>479</v>
-      </c>
       <c r="B184" s="1" t="s">
-        <v>480</v>
+        <v>528</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>481</v>
+        <v>529</v>
+      </c>
+      <c r="F184" s="3">
+        <v>0</v>
       </c>
     </row>
     <row r="185" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B185" s="1" t="s">
-        <v>538</v>
+        <v>530</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>539</v>
-      </c>
-      <c r="F185" s="3">
+        <v>531</v>
+      </c>
+      <c r="F185" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="186" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B186" s="1" t="s">
-        <v>540</v>
+        <v>530</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="F186" s="2">
         <v>0</v>
+      </c>
+      <c r="H186" s="2" t="s">
+        <v>650</v>
       </c>
     </row>
     <row r="187" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B187" s="1" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>547</v>
+        <v>533</v>
       </c>
       <c r="F187" s="2">
         <v>0</v>
       </c>
       <c r="H187" s="2" t="s">
-        <v>661</v>
+        <v>651</v>
       </c>
     </row>
     <row r="188" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B188" s="1" t="s">
-        <v>542</v>
-      </c>
-      <c r="E188" s="1" t="s">
-        <v>543</v>
-      </c>
-      <c r="F188" s="2">
-        <v>0</v>
-      </c>
-      <c r="H188" s="2" t="s">
-        <v>662</v>
+        <v>534</v>
       </c>
     </row>
     <row r="189" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B189" s="1" t="s">
-        <v>544</v>
+        <v>535</v>
       </c>
     </row>
     <row r="190" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B190" s="1" t="s">
-        <v>545</v>
+        <v>536</v>
       </c>
     </row>
     <row r="191" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A191" s="2" t="s">
+        <v>539</v>
+      </c>
       <c r="B191" s="1" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="192" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A192" s="2" t="s">
-        <v>549</v>
-      </c>
-      <c r="B192" s="1" t="s">
-        <v>548</v>
-      </c>
-      <c r="C192" s="2">
+        <v>538</v>
+      </c>
+      <c r="C191" s="2">
         <v>30</v>
       </c>
-      <c r="D192" s="6">
-        <v>0</v>
-      </c>
-      <c r="E192" s="2" t="s">
-        <v>550</v>
-      </c>
-      <c r="F192" s="2">
-        <v>0</v>
-      </c>
-      <c r="H192" s="7" t="s">
-        <v>551</v>
+      <c r="D191" s="6">
+        <v>0</v>
+      </c>
+      <c r="E191" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="F191" s="2">
+        <v>0</v>
+      </c>
+      <c r="H191" s="7" t="s">
+        <v>541</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H183">
-    <sortCondition ref="B2:B183"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H182">
+    <sortCondition ref="B2:B182"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="H192" r:id="rId1" xr:uid="{79761F97-15D2-497A-876C-4F087647F759}"/>
+    <hyperlink ref="H191" r:id="rId1" xr:uid="{79761F97-15D2-497A-876C-4F087647F759}"/>
     <hyperlink ref="H154" r:id="rId2" xr:uid="{135A9EAA-53A1-4C6C-86B4-EA1E459FCF29}"/>
-    <hyperlink ref="H168" r:id="rId3" display="https://playpointlab.com/&gt; &lt;/a&gt;" xr:uid="{E664F694-AC8E-4F9E-AC58-F59D21B9D99B}"/>
-    <hyperlink ref="H169" r:id="rId4" display="https://playpointlab.com/&gt; &lt;/a&gt;" xr:uid="{24D8477A-84BC-417A-A9F7-D15CF3A0F305}"/>
+    <hyperlink ref="H167" r:id="rId3" display="https://playpointlab.com/&gt; &lt;/a&gt;" xr:uid="{E664F694-AC8E-4F9E-AC58-F59D21B9D99B}"/>
+    <hyperlink ref="H168" r:id="rId4" display="https://playpointlab.com/&gt; &lt;/a&gt;" xr:uid="{24D8477A-84BC-417A-A9F7-D15CF3A0F305}"/>
     <hyperlink ref="H104" r:id="rId5" xr:uid="{1AB750C9-076B-44E1-A1C1-42D804ED6043}"/>
     <hyperlink ref="H94" r:id="rId6" xr:uid="{02B7B66A-8C7C-4429-9DD0-E7B36896002B}"/>
     <hyperlink ref="H91" r:id="rId7" xr:uid="{47FAF52E-8D8D-4DEF-9078-74E8499F1823}"/>

--- a/stores.xlsx
+++ b/stores.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\YUMIN\Desktop\B0KT2A_RSVN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5FDDE6BA-E731-4BC7-BF8F-69054C2F06E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{11F55747-95A9-4B4F-A5A6-E315B512ADE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{ABFC3117-FCCB-4FF3-804A-FE19451A2004}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="745" uniqueCount="673">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="799" uniqueCount="729">
   <si>
     <t>룸익스케이프 WHITE</t>
   </si>
@@ -207,9 +207,6 @@
     <t>오늘나는,꿈의공장,날씨의신,꿈공,날신</t>
   </si>
   <si>
-    <t>비트포비아 서면던전레드</t>
-  </si>
-  <si>
     <t>제로월드 강남점</t>
   </si>
   <si>
@@ -1041,10 +1038,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>상시예약</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>네모네모마믈메는무슨밀미밌멌믈까?,멍스타그램,인생낚시,만약당신이길을잃었다면,만당길,테라포밍마스,테포마</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1637,10 +1630,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>상시예약</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>테라스페이스 아트갤러리점</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1653,10 +1642,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>dn_dm</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>덤앤더머 홍대점</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1897,10 +1882,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>러시아워 시네마틱</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>판타지아</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2275,9 +2256,6 @@
     <t>https://playpointlab.com/</t>
   </si>
   <si>
-    <t>https://playpointlab.com/'</t>
-  </si>
-  <si>
     <t>http://sowoojoo-escape.com/</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2334,6 +2312,249 @@
   </si>
   <si>
     <t>33_kd</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ra_bp2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ra_bp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>러시아워</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>러시아워 2호점 로드맨션</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>러시아워 3호점 시네마틱</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>전생연분,녀,하루끝,미끼,빔프로젝트</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>악녀,은화기숙학원,빨간집</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://naver.me/5TQMYzbQ</t>
+  </si>
+  <si>
+    <t>https://naver.me/5HksuiTR</t>
+  </si>
+  <si>
+    <t>지난날,오드의마법사,우당탕탕치즈탈환대작전!,듀얼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://naver.me/GI3hw5ys</t>
+  </si>
+  <si>
+    <t>찬미특수진료센터,inspecto,getogeto,</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>매주 목요일 23:50 ~ 금요일 00:00 사이에&lt;br&gt;3주 뒤 수요일까지 열립니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dkdk,쇼쿠진,chaser:한마음폐공장,혼숨,hereiam,직박구리:남친탐구생활,영안실,복도끝:못다한이야기,못다恨이야기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>chaser:한마음폐공장,영안실,시크릿왕국의스캔들(완전판),혼숨:리마스터,복도끝:못다한이야기,못다恨이야기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ra_sm</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ra_sw2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ra_sw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ra_dsr2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ra_dsr</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ra_ds</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ra_eh</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ra_ay</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ra_ui</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ra_lf</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ra_wd</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cb_ch</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cb_js</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>큐브이스케이프 천호점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>큐브이스케이프 잠실점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>the cube,the maze,장기밀매 part2,stepfather,사라진천사들,piggies,마녀의꿈,aphilia,장미의비밀,피고인</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>romeo point,신데렐라,집착,마션,타이타닉,카타콤</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ra_gsw2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ra_gsw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ra_np</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ra_psm</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ra_dsra</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ra_ph</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rs_hr</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rh_rm</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rh_ct</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>he_gj2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>he_gj3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>he_gj</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gt_gj</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gt_dsr</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ft_sia</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>비트포비아 서면던전 레드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>시간의 문 대구동성로점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>d_doo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dd_dhr</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>덤앤더머 대학로점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dd_sm</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>덤앤더머 서면점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>observer,옵저버,크라임시티,crime city,love-clinic,러브클리닉,to allice,투 앨리스,blue beard,푸른수염,glamping,글램핑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>소공녀,love-clinic,러브클리닉,to allice,투 앨리스,blue beard,푸른수염,glamping,글램핑b,knock knock,낙낙,녹녹,x테마,학교괴담,기담,동전노래방,observer,옵저버,crime city,크라임시티</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://m.dumbndumber.kr</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://m.dumbndumber-sm.kr</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://playpointlab.com/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://cheonho.cubeescape.co.kr/</t>
+  </si>
+  <si>
+    <t>http://jamsil.cubeescape.co.kr/</t>
+  </si>
+  <si>
+    <t>화-&gt;수 0:00&lt;BR&gt;다음주 토~다다음주 금 1주일치 오픈</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2418,10 +2639,10 @@
     <xf numFmtId="20" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -2737,7 +2958,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D839462D-4719-40BB-8925-C1B9F93734CF}">
-  <dimension ref="A1:H192"/>
+  <dimension ref="A1:H199"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="2"/>
@@ -2749,7 +2970,7 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>11</v>
@@ -2775,272 +2996,269 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>344</v>
+        <v>666</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>330</v>
-      </c>
-      <c r="C2" s="3">
-        <v>6</v>
-      </c>
-      <c r="D2" s="5">
-        <v>0</v>
-      </c>
-      <c r="E2" t="s">
-        <v>526</v>
-      </c>
-      <c r="F2" s="3">
-        <v>0</v>
-      </c>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1" t="s">
-        <v>541</v>
+        <v>663</v>
+      </c>
+      <c r="C2" s="2">
+        <v>7</v>
+      </c>
+      <c r="D2" s="6">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>664</v>
+      </c>
+      <c r="F2" s="2">
+        <v>0</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>665</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>354</v>
+        <v>342</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>237</v>
+        <v>328</v>
       </c>
       <c r="C3" s="3">
         <v>6</v>
       </c>
-      <c r="D3" s="4">
-        <v>0</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>286</v>
+      <c r="D3" s="5">
+        <v>0</v>
+      </c>
+      <c r="E3" t="s">
+        <v>522</v>
       </c>
       <c r="F3" s="3">
         <v>0</v>
       </c>
       <c r="G3" s="1"/>
       <c r="H3" s="1" t="s">
-        <v>548</v>
+        <v>536</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>355</v>
+        <v>343</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>238</v>
+        <v>274</v>
       </c>
       <c r="C4" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D4" s="4">
         <v>0</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>239</v>
+        <v>275</v>
       </c>
       <c r="F4" s="3">
         <v>0</v>
       </c>
       <c r="G4" s="1"/>
       <c r="H4" s="1" t="s">
-        <v>548</v>
+        <v>537</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>456</v>
+        <v>344</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>454</v>
-      </c>
-      <c r="C5" s="3">
-        <v>6</v>
-      </c>
-      <c r="D5" s="6">
-        <v>0</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="C5" s="3"/>
+      <c r="D5" s="4"/>
       <c r="E5" s="1" t="s">
-        <v>458</v>
+        <v>331</v>
       </c>
       <c r="F5" s="3">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G5" s="1"/>
       <c r="H5" s="1" t="s">
-        <v>558</v>
+        <v>538</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>455</v>
+        <v>345</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>453</v>
+        <v>268</v>
       </c>
       <c r="C6" s="3">
-        <v>6</v>
-      </c>
-      <c r="D6" s="6">
+        <v>7</v>
+      </c>
+      <c r="D6" s="4">
         <v>0</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>457</v>
+        <v>249</v>
       </c>
       <c r="F6" s="3">
         <v>0</v>
       </c>
-      <c r="H6" s="1" t="s">
-        <v>558</v>
+      <c r="G6" s="1"/>
+      <c r="H6" t="s">
+        <v>539</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>365</v>
+        <v>346</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>145</v>
+        <v>269</v>
       </c>
       <c r="C7" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D7" s="4">
         <v>0</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>146</v>
+        <v>332</v>
       </c>
       <c r="F7" s="3">
         <v>0</v>
       </c>
       <c r="G7" s="1"/>
-      <c r="H7" s="1" t="s">
-        <v>559</v>
+      <c r="H7" t="s">
+        <v>539</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>366</v>
+        <v>347</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="C8" s="3">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D8" s="4">
-        <v>0</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>287</v>
+        <v>140</v>
       </c>
       <c r="F8" s="3">
         <v>0</v>
       </c>
       <c r="G8" s="1"/>
       <c r="H8" s="1" t="s">
-        <v>560</v>
+        <v>540</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>367</v>
+        <v>348</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>336</v>
+        <v>141</v>
       </c>
       <c r="C9" s="3">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D9" s="4">
-        <v>0</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>285</v>
+        <v>142</v>
       </c>
       <c r="F9" s="3">
         <v>0</v>
       </c>
       <c r="G9" s="1"/>
-      <c r="H9" s="2" t="s">
-        <v>561</v>
+      <c r="H9" s="1" t="s">
+        <v>541</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>368</v>
+        <v>349</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>148</v>
+        <v>239</v>
       </c>
       <c r="C10" s="3">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D10" s="4">
         <v>0</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>149</v>
+        <v>295</v>
       </c>
       <c r="F10" s="3">
         <v>0</v>
       </c>
       <c r="G10" s="1"/>
       <c r="H10" s="1" t="s">
-        <v>562</v>
+        <v>542</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>370</v>
+        <v>350</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>162</v>
+        <v>240</v>
       </c>
       <c r="C11" s="3">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D11" s="4">
         <v>0</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>163</v>
+        <v>333</v>
       </c>
       <c r="F11" s="3">
         <v>0</v>
       </c>
       <c r="G11" s="1"/>
       <c r="H11" s="1" t="s">
-        <v>564</v>
+        <v>542</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>371</v>
+        <v>351</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>150</v>
+        <v>241</v>
       </c>
       <c r="C12" s="3">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D12" s="4">
         <v>0</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>151</v>
+        <v>296</v>
       </c>
       <c r="F12" s="3">
         <v>0</v>
       </c>
       <c r="G12" s="1"/>
       <c r="H12" s="1" t="s">
-        <v>565</v>
+        <v>542</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>372</v>
+        <v>352</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>152</v>
+        <v>236</v>
       </c>
       <c r="C13" s="3">
         <v>6</v>
@@ -3049,22 +3267,22 @@
         <v>0</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>153</v>
+        <v>285</v>
       </c>
       <c r="F13" s="3">
         <v>0</v>
       </c>
       <c r="G13" s="1"/>
       <c r="H13" s="1" t="s">
-        <v>566</v>
+        <v>543</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>375</v>
+        <v>353</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>154</v>
+        <v>237</v>
       </c>
       <c r="C14" s="3">
         <v>6</v>
@@ -3073,382 +3291,370 @@
         <v>0</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>155</v>
+        <v>238</v>
       </c>
       <c r="F14" s="3">
         <v>0</v>
       </c>
       <c r="G14" s="1"/>
       <c r="H14" s="1" t="s">
-        <v>569</v>
+        <v>543</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>376</v>
+        <v>354</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>8</v>
+        <v>218</v>
       </c>
       <c r="C15" s="3">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D15" s="4">
         <v>0</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>668</v>
+        <v>330</v>
       </c>
       <c r="F15" s="3">
         <v>0</v>
       </c>
       <c r="G15" s="1"/>
-      <c r="H15" t="s">
-        <v>570</v>
+      <c r="H15" s="1" t="s">
+        <v>544</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>380</v>
+        <v>355</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>132</v>
+        <v>88</v>
       </c>
       <c r="C16" s="3">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="D16" s="4">
         <v>0</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>133</v>
+        <v>329</v>
       </c>
       <c r="F16" s="3">
         <v>0</v>
       </c>
       <c r="G16" s="1"/>
       <c r="H16" s="1" t="s">
-        <v>572</v>
+        <v>545</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>384</v>
+        <v>356</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>313</v>
+        <v>83</v>
       </c>
       <c r="C17" s="3">
-        <v>6</v>
-      </c>
-      <c r="D17" s="5">
+        <v>7</v>
+      </c>
+      <c r="D17" s="4">
         <v>0</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>315</v>
+        <v>84</v>
       </c>
       <c r="F17" s="3">
         <v>0</v>
       </c>
       <c r="G17" s="1"/>
       <c r="H17" s="1" t="s">
-        <v>576</v>
+        <v>546</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>386</v>
+        <v>357</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>302</v>
+        <v>85</v>
       </c>
       <c r="C18" s="3">
-        <v>6</v>
-      </c>
-      <c r="D18" s="5">
+        <v>27</v>
+      </c>
+      <c r="D18" s="4">
         <v>0</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>311</v>
+        <v>86</v>
       </c>
       <c r="F18" s="3">
         <v>0</v>
       </c>
       <c r="G18" s="1"/>
       <c r="H18" s="1" t="s">
-        <v>576</v>
+        <v>547</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>387</v>
+        <v>358</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>2</v>
+        <v>87</v>
       </c>
       <c r="C19" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D19" s="4">
         <v>0</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>3</v>
+        <v>294</v>
       </c>
       <c r="F19" s="3">
         <v>0</v>
       </c>
       <c r="G19" s="1"/>
-      <c r="H19" s="2" t="s">
-        <v>578</v>
+      <c r="H19" s="1" t="s">
+        <v>548</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>389</v>
+        <v>359</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>4</v>
+        <v>81</v>
       </c>
       <c r="C20" s="3">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="D20" s="4">
         <v>0</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>5</v>
+        <v>82</v>
       </c>
       <c r="F20" s="3">
         <v>0</v>
       </c>
       <c r="G20" s="1"/>
-      <c r="H20" s="2" t="s">
-        <v>580</v>
+      <c r="H20" s="1" t="s">
+        <v>549</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>390</v>
+        <v>360</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>0</v>
+        <v>336</v>
       </c>
       <c r="C21" s="3">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="D21" s="4">
         <v>0</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>1</v>
+        <v>337</v>
       </c>
       <c r="F21" s="3">
         <v>0</v>
       </c>
       <c r="G21" s="1"/>
-      <c r="H21" s="2" t="s">
-        <v>581</v>
+      <c r="H21" s="1" t="s">
+        <v>550</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>393</v>
+        <v>361</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>251</v>
+        <v>79</v>
       </c>
       <c r="C22" s="3">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="D22" s="4">
         <v>0</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>252</v>
+        <v>80</v>
       </c>
       <c r="F22" s="3">
         <v>0</v>
       </c>
       <c r="G22" s="1"/>
-      <c r="H22" t="s">
-        <v>603</v>
+      <c r="H22" s="1" t="s">
+        <v>551</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>395</v>
+        <v>362</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>47</v>
+        <v>77</v>
       </c>
       <c r="C23" s="3">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="D23" s="4">
-        <v>0.66666666666666663</v>
+        <v>0</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>48</v>
+        <v>78</v>
       </c>
       <c r="F23" s="3">
         <v>0</v>
       </c>
       <c r="G23" s="1"/>
-      <c r="H23" s="2" t="s">
-        <v>607</v>
+      <c r="H23" s="1" t="s">
+        <v>552</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>396</v>
+        <v>454</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>49</v>
+        <v>452</v>
       </c>
       <c r="C24" s="3">
         <v>6</v>
       </c>
-      <c r="D24" s="4">
-        <v>0.70833333333333337</v>
+      <c r="D24" s="6">
+        <v>0</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>50</v>
+        <v>456</v>
       </c>
       <c r="F24" s="3">
         <v>0</v>
       </c>
-      <c r="G24" s="1"/>
-      <c r="H24" s="2" t="s">
-        <v>607</v>
+      <c r="H24" s="1" t="s">
+        <v>553</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
-        <v>437</v>
+        <v>453</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>278</v>
+        <v>451</v>
       </c>
       <c r="C25" s="3">
         <v>6</v>
       </c>
-      <c r="D25" s="4">
+      <c r="D25" s="6">
         <v>0</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>281</v>
+        <v>455</v>
       </c>
       <c r="F25" s="3">
         <v>0</v>
       </c>
-      <c r="G25" s="1"/>
-      <c r="H25" s="7" t="s">
-        <v>658</v>
+      <c r="H25" s="1" t="s">
+        <v>553</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>397</v>
+        <v>363</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>43</v>
+        <v>144</v>
       </c>
       <c r="C26" s="3">
         <v>6</v>
       </c>
       <c r="D26" s="4">
-        <v>0.58333333333333337</v>
+        <v>0</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>44</v>
+        <v>145</v>
       </c>
       <c r="F26" s="3">
         <v>0</v>
       </c>
       <c r="G26" s="1"/>
-      <c r="H26" s="2" t="s">
-        <v>607</v>
+      <c r="H26" s="1" t="s">
+        <v>554</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
-        <v>398</v>
+        <v>364</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>51</v>
+        <v>146</v>
       </c>
       <c r="C27" s="3">
         <v>6</v>
       </c>
       <c r="D27" s="4">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>52</v>
+        <v>286</v>
       </c>
       <c r="F27" s="3">
         <v>0</v>
       </c>
       <c r="G27" s="1"/>
-      <c r="H27" s="2" t="s">
-        <v>607</v>
+      <c r="H27" s="1" t="s">
+        <v>555</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
-        <v>399</v>
+        <v>365</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>53</v>
+        <v>334</v>
       </c>
       <c r="C28" s="3">
         <v>6</v>
       </c>
       <c r="D28" s="4">
-        <v>0.79166666666666663</v>
+        <v>0</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>54</v>
+        <v>284</v>
       </c>
       <c r="F28" s="3">
         <v>0</v>
       </c>
       <c r="G28" s="1"/>
       <c r="H28" s="2" t="s">
-        <v>607</v>
+        <v>556</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
-        <v>438</v>
+        <v>392</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="C29" s="3">
-        <v>6</v>
-      </c>
-      <c r="D29" s="4">
-        <v>0</v>
+        <v>469</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>284</v>
+        <v>470</v>
       </c>
       <c r="F29" s="3">
-        <v>0</v>
-      </c>
-      <c r="G29" s="1"/>
-      <c r="H29" s="7" t="s">
-        <v>658</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
-        <v>439</v>
+        <v>366</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>277</v>
+        <v>147</v>
       </c>
       <c r="C30" s="3">
         <v>6</v>
@@ -3457,70 +3663,66 @@
         <v>0</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>282</v>
+        <v>148</v>
       </c>
       <c r="F30" s="3">
         <v>0</v>
       </c>
       <c r="G30" s="1"/>
-      <c r="H30" s="7" t="s">
-        <v>658</v>
+      <c r="H30" s="1" t="s">
+        <v>557</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
-        <v>400</v>
+        <v>367</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C31" s="3">
-        <v>6</v>
-      </c>
-      <c r="D31" s="4">
-        <v>0.83333333333333337</v>
-      </c>
+        <v>159</v>
+      </c>
+      <c r="C31" s="3"/>
+      <c r="D31" s="4"/>
       <c r="E31" s="1" t="s">
-        <v>56</v>
+        <v>160</v>
       </c>
       <c r="F31" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G31" s="1"/>
-      <c r="H31" s="2" t="s">
-        <v>607</v>
+      <c r="H31" s="1" t="s">
+        <v>558</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
-        <v>401</v>
+        <v>368</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>57</v>
+        <v>161</v>
       </c>
       <c r="C32" s="3">
         <v>6</v>
       </c>
       <c r="D32" s="4">
-        <v>0.875</v>
+        <v>0</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>341</v>
+        <v>162</v>
       </c>
       <c r="F32" s="3">
         <v>0</v>
       </c>
       <c r="G32" s="1"/>
-      <c r="H32" s="2" t="s">
-        <v>607</v>
+      <c r="H32" s="1" t="s">
+        <v>559</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
-        <v>440</v>
+        <v>369</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>279</v>
+        <v>149</v>
       </c>
       <c r="C33" s="3">
         <v>6</v>
@@ -3529,94 +3731,86 @@
         <v>0</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>283</v>
+        <v>150</v>
       </c>
       <c r="F33" s="3">
         <v>0</v>
       </c>
       <c r="G33" s="1"/>
-      <c r="H33" s="7" t="s">
-        <v>658</v>
+      <c r="H33" s="1" t="s">
+        <v>560</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
-        <v>402</v>
+        <v>370</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>41</v>
+        <v>151</v>
       </c>
       <c r="C34" s="3">
         <v>6</v>
       </c>
       <c r="D34" s="4">
-        <v>0.54166666666666663</v>
+        <v>0</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>42</v>
+        <v>152</v>
       </c>
       <c r="F34" s="3">
         <v>0</v>
       </c>
       <c r="G34" s="1"/>
-      <c r="H34" s="2" t="s">
-        <v>607</v>
+      <c r="H34" s="1" t="s">
+        <v>561</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
-        <v>403</v>
+        <v>371</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C35" s="3">
-        <v>6</v>
-      </c>
-      <c r="D35" s="4">
-        <v>0.625</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="C35" s="3"/>
+      <c r="D35" s="4"/>
       <c r="E35" s="1" t="s">
-        <v>46</v>
+        <v>158</v>
       </c>
       <c r="F35" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G35" s="1"/>
-      <c r="H35" s="2" t="s">
-        <v>607</v>
+      <c r="H35" s="1" t="s">
+        <v>562</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
-        <v>441</v>
+      <c r="A36" s="2" t="s">
+        <v>372</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="C36" s="3">
-        <v>6</v>
-      </c>
-      <c r="D36" s="4">
-        <v>0</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="C36" s="3"/>
+      <c r="D36" s="4"/>
       <c r="E36" s="1" t="s">
-        <v>228</v>
+        <v>156</v>
       </c>
       <c r="F36" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G36" s="1"/>
       <c r="H36" s="1" t="s">
-        <v>608</v>
+        <v>563</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
-        <v>442</v>
+      <c r="A37" s="2" t="s">
+        <v>373</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>221</v>
+        <v>153</v>
       </c>
       <c r="C37" s="3">
         <v>6</v>
@@ -3625,22 +3819,22 @@
         <v>0</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>222</v>
+        <v>154</v>
       </c>
       <c r="F37" s="3">
         <v>0</v>
       </c>
       <c r="G37" s="1"/>
       <c r="H37" s="1" t="s">
-        <v>608</v>
+        <v>564</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
-        <v>443</v>
+      <c r="A38" s="2" t="s">
+        <v>374</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>233</v>
+        <v>8</v>
       </c>
       <c r="C38" s="3">
         <v>6</v>
@@ -3649,94 +3843,94 @@
         <v>0</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>234</v>
+        <v>662</v>
       </c>
       <c r="F38" s="3">
         <v>0</v>
       </c>
       <c r="G38" s="1"/>
-      <c r="H38" s="1" t="s">
-        <v>608</v>
+      <c r="H38" t="s">
+        <v>565</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
-        <v>444</v>
+      <c r="A39" s="2" t="s">
+        <v>375</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>223</v>
+        <v>252</v>
       </c>
       <c r="C39" s="3">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="D39" s="4">
         <v>0</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>224</v>
+        <v>253</v>
       </c>
       <c r="F39" s="3">
         <v>0</v>
       </c>
       <c r="G39" s="1"/>
-      <c r="H39" s="1" t="s">
-        <v>608</v>
+      <c r="H39" t="s">
+        <v>566</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
-        <v>445</v>
+      <c r="A40" s="2" t="s">
+        <v>376</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>231</v>
+        <v>254</v>
       </c>
       <c r="C40" s="3">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="D40" s="4">
-        <v>0</v>
+        <v>0.95833333333333337</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>232</v>
+        <v>255</v>
       </c>
       <c r="F40" s="3">
         <v>0</v>
       </c>
       <c r="G40" s="1"/>
-      <c r="H40" s="1" t="s">
-        <v>608</v>
+      <c r="H40" t="s">
+        <v>566</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
-        <v>446</v>
+      <c r="A41" s="2" t="s">
+        <v>377</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>229</v>
+        <v>256</v>
       </c>
       <c r="C41" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D41" s="4">
-        <v>0</v>
+        <v>0.97916666666666663</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>230</v>
+        <v>257</v>
       </c>
       <c r="F41" s="3">
         <v>0</v>
       </c>
       <c r="G41" s="1"/>
-      <c r="H41" s="1" t="s">
-        <v>608</v>
+      <c r="H41" t="s">
+        <v>566</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
-        <v>447</v>
+      <c r="A42" s="2" t="s">
+        <v>378</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>225</v>
+        <v>131</v>
       </c>
       <c r="C42" s="3">
         <v>6</v>
@@ -3745,838 +3939,792 @@
         <v>0</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>226</v>
+        <v>132</v>
       </c>
       <c r="F42" s="3">
         <v>0</v>
       </c>
       <c r="G42" s="1"/>
       <c r="H42" s="1" t="s">
-        <v>608</v>
+        <v>567</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
-        <v>448</v>
+        <v>379</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="C43" s="3">
-        <v>6</v>
-      </c>
-      <c r="D43" s="4">
+        <v>303</v>
+      </c>
+      <c r="C43" s="1">
+        <v>13</v>
+      </c>
+      <c r="D43" s="5">
         <v>0</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="F43" s="3">
+        <v>309</v>
+      </c>
+      <c r="F43" s="1">
         <v>0</v>
       </c>
       <c r="G43" s="1"/>
-      <c r="H43" s="8" t="s">
-        <v>657</v>
+      <c r="H43" s="1" t="s">
+        <v>568</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
-        <v>449</v>
+        <v>380</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="C44" s="3">
-        <v>6</v>
-      </c>
-      <c r="D44" s="4">
-        <v>0.54166666666666663</v>
-      </c>
+        <v>258</v>
+      </c>
+      <c r="C44" s="1"/>
+      <c r="D44" s="1"/>
       <c r="E44" s="1" t="s">
-        <v>274</v>
+        <v>259</v>
       </c>
       <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="1"/>
-      <c r="H44" s="1" t="s">
-        <v>609</v>
+        <v>1</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>569</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A45" s="2" t="s">
-        <v>498</v>
+      <c r="A45" t="s">
+        <v>705</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="C45" s="3">
-        <v>6</v>
-      </c>
-      <c r="D45" s="4">
-        <v>0</v>
+        <v>669</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="F45" s="3">
-        <v>0</v>
-      </c>
-      <c r="G45" s="1"/>
-      <c r="H45" s="1" t="s">
-        <v>612</v>
+        <v>672</v>
+      </c>
+      <c r="F45" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A46" s="2" t="s">
-        <v>450</v>
+      <c r="A46" t="s">
+        <v>706</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="C46" s="3">
-        <v>6</v>
-      </c>
-      <c r="D46" s="4">
-        <v>0</v>
+        <v>670</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>236</v>
+        <v>676</v>
       </c>
       <c r="F46" s="3">
-        <v>0</v>
-      </c>
-      <c r="G46" s="1"/>
-      <c r="H46" s="1" t="s">
-        <v>615</v>
+        <v>1</v>
+      </c>
+      <c r="H46" s="8" t="s">
+        <v>675</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A47" s="2" t="s">
-        <v>409</v>
+      <c r="A47" t="s">
+        <v>707</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="C47" s="3">
-        <v>6</v>
-      </c>
-      <c r="D47" s="5">
-        <v>0</v>
-      </c>
+        <v>671</v>
+      </c>
+      <c r="C47" s="3"/>
+      <c r="D47" s="6"/>
       <c r="E47" s="1" t="s">
-        <v>299</v>
+        <v>673</v>
       </c>
       <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="1"/>
-      <c r="H47" s="1" t="s">
-        <v>654</v>
+        <v>1</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>728</v>
+      </c>
+      <c r="H47" s="8" t="s">
+        <v>674</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
-        <v>451</v>
+        <v>381</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>76</v>
+        <v>133</v>
       </c>
       <c r="C48" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D48" s="4">
-        <v>0</v>
+        <v>0.875</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>77</v>
+        <v>134</v>
       </c>
       <c r="F48" s="3">
         <v>0</v>
       </c>
       <c r="G48" s="1"/>
-      <c r="H48" s="2" t="s">
-        <v>616</v>
+      <c r="H48" s="1" t="s">
+        <v>570</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
-        <v>503</v>
+        <v>382</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>249</v>
+        <v>312</v>
       </c>
       <c r="C49" s="3">
         <v>6</v>
       </c>
-      <c r="D49" s="4">
+      <c r="D49" s="5">
         <v>0</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>661</v>
+        <v>314</v>
       </c>
       <c r="F49" s="3">
         <v>0</v>
       </c>
       <c r="G49" s="1"/>
       <c r="H49" s="1" t="s">
-        <v>619</v>
+        <v>571</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
-        <v>414</v>
+        <v>383</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C50" s="3">
-        <v>6</v>
-      </c>
-      <c r="D50" s="4">
-        <v>0</v>
-      </c>
+        <v>311</v>
+      </c>
+      <c r="C50" s="3"/>
+      <c r="D50" s="5"/>
       <c r="E50" s="1" t="s">
-        <v>10</v>
+        <v>313</v>
       </c>
       <c r="F50" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G50" s="1"/>
-      <c r="H50" s="2" t="s">
-        <v>628</v>
+      <c r="H50" s="1" t="s">
+        <v>572</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
-        <v>419</v>
+        <v>384</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>220</v>
+        <v>301</v>
       </c>
       <c r="C51" s="3">
         <v>6</v>
       </c>
-      <c r="D51" s="4">
+      <c r="D51" s="5">
         <v>0</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>660</v>
+        <v>310</v>
       </c>
       <c r="F51" s="3">
         <v>0</v>
       </c>
       <c r="G51" s="1"/>
       <c r="H51" s="1" t="s">
-        <v>633</v>
+        <v>571</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A52" t="s">
-        <v>420</v>
+      <c r="A52" s="2" t="s">
+        <v>385</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="C52" s="3">
         <v>6</v>
       </c>
       <c r="D52" s="4">
-        <v>0.41666666666666669</v>
+        <v>0</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="F52" s="3">
         <v>0</v>
       </c>
       <c r="G52" s="1"/>
       <c r="H52" s="2" t="s">
-        <v>634</v>
+        <v>573</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A53" t="s">
-        <v>421</v>
+      <c r="A53" s="2" t="s">
+        <v>386</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="C53" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D53" s="4">
-        <v>0.41666666666666669</v>
+        <v>0.91666666666666663</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="F53" s="3">
         <v>0</v>
       </c>
       <c r="G53" s="1"/>
       <c r="H53" s="2" t="s">
-        <v>634</v>
+        <v>574</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A54" t="s">
-        <v>422</v>
+      <c r="A54" s="2" t="s">
+        <v>387</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="C54" s="3">
         <v>6</v>
       </c>
       <c r="D54" s="4">
-        <v>0.47916666666666669</v>
+        <v>0</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="F54" s="3">
         <v>0</v>
       </c>
       <c r="G54" s="1"/>
       <c r="H54" s="2" t="s">
-        <v>634</v>
+        <v>575</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A55" t="s">
-        <v>423</v>
+      <c r="A55" s="2" t="s">
+        <v>388</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="C55" s="3">
         <v>6</v>
       </c>
       <c r="D55" s="4">
-        <v>0.41666666666666669</v>
+        <v>0</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="F55" s="3">
         <v>0</v>
       </c>
       <c r="G55" s="1"/>
       <c r="H55" s="2" t="s">
-        <v>634</v>
+        <v>576</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A56" t="s">
-        <v>425</v>
+      <c r="A56" s="2" t="s">
+        <v>389</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>20</v>
+        <v>267</v>
       </c>
       <c r="C56" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D56" s="4">
-        <v>0.4375</v>
+        <v>0</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>21</v>
+        <v>299</v>
       </c>
       <c r="F56" s="3">
         <v>0</v>
       </c>
-      <c r="G56" s="1"/>
-      <c r="H56" s="2" t="s">
-        <v>634</v>
+      <c r="H56" s="1" t="s">
+        <v>577</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A57" t="s">
-        <v>426</v>
+      <c r="A57" s="2" t="s">
+        <v>682</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>18</v>
+        <v>187</v>
       </c>
       <c r="C57" s="3">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="D57" s="4">
-        <v>0.5625</v>
+        <v>0</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>19</v>
+        <v>188</v>
       </c>
       <c r="F57" s="3">
         <v>0</v>
       </c>
-      <c r="G57" s="1"/>
-      <c r="H57" s="2" t="s">
-        <v>634</v>
+      <c r="H57" s="1" t="s">
+        <v>578</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>427</v>
+        <v>699</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>29</v>
+        <v>270</v>
       </c>
       <c r="C58" s="3">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="D58" s="4">
-        <v>0.41666666666666669</v>
+        <v>0</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>30</v>
+        <v>271</v>
       </c>
       <c r="F58" s="3">
         <v>0</v>
       </c>
-      <c r="G58" s="1"/>
-      <c r="H58" s="2" t="s">
-        <v>634</v>
+      <c r="H58" s="1" t="s">
+        <v>579</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>429</v>
+        <v>700</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>22</v>
+        <v>185</v>
       </c>
       <c r="C59" s="3">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="D59" s="4">
-        <v>0.45833333333333331</v>
+        <v>0</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>289</v>
+        <v>186</v>
       </c>
       <c r="F59" s="3">
         <v>0</v>
       </c>
-      <c r="G59" s="1"/>
-      <c r="H59" s="2" t="s">
-        <v>634</v>
+      <c r="H59" s="1" t="s">
+        <v>580</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>430</v>
+        <v>685</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>206</v>
+        <v>191</v>
       </c>
       <c r="C60" s="3">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="D60" s="4">
         <v>0</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>207</v>
+        <v>192</v>
       </c>
       <c r="F60" s="3">
         <v>0</v>
       </c>
-      <c r="G60" s="1"/>
       <c r="H60" s="1" t="s">
-        <v>638</v>
+        <v>581</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A61" t="s">
-        <v>431</v>
+      <c r="A61" s="2" t="s">
+        <v>686</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="C61" s="3">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="D61" s="4">
         <v>0</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>205</v>
+        <v>190</v>
       </c>
       <c r="F61" s="3">
         <v>0</v>
       </c>
-      <c r="G61" s="1"/>
       <c r="H61" s="1" t="s">
-        <v>638</v>
+        <v>582</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>432</v>
+        <v>687</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>208</v>
+        <v>177</v>
       </c>
       <c r="C62" s="3">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="D62" s="4">
         <v>0</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>209</v>
+        <v>178</v>
       </c>
       <c r="F62" s="3">
         <v>0</v>
       </c>
-      <c r="G62" s="1"/>
       <c r="H62" s="1" t="s">
-        <v>638</v>
+        <v>583</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A63" s="2" t="s">
-        <v>475</v>
+      <c r="A63" t="s">
+        <v>688</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>65</v>
+        <v>179</v>
       </c>
       <c r="C63" s="3">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="D63" s="4">
         <v>0</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>666</v>
+        <v>180</v>
       </c>
       <c r="F63" s="3">
         <v>0</v>
       </c>
-      <c r="G63" s="1"/>
-      <c r="H63" s="2" t="s">
-        <v>640</v>
+      <c r="H63" s="1" t="s">
+        <v>584</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
-        <v>477</v>
+        <v>390</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>70</v>
+        <v>163</v>
       </c>
       <c r="C64" s="3">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="D64" s="4">
         <v>0</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>71</v>
+        <v>164</v>
       </c>
       <c r="F64" s="3">
         <v>0</v>
       </c>
-      <c r="G64" s="1"/>
-      <c r="H64" s="2" t="s">
-        <v>642</v>
+      <c r="H64" s="1" t="s">
+        <v>585</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A65" s="2" t="s">
-        <v>478</v>
+      <c r="A65" t="s">
+        <v>703</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>68</v>
+        <v>193</v>
       </c>
       <c r="C65" s="3">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="D65" s="4">
         <v>0</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>69</v>
+        <v>194</v>
       </c>
       <c r="F65" s="3">
         <v>0</v>
       </c>
-      <c r="G65" s="1"/>
-      <c r="H65" s="2" t="s">
-        <v>643</v>
+      <c r="H65" s="1" t="s">
+        <v>586</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A66" s="2" t="s">
-        <v>479</v>
+      <c r="A66" t="s">
+        <v>701</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>72</v>
+        <v>181</v>
       </c>
       <c r="C66" s="3">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="D66" s="4">
         <v>0</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>73</v>
+        <v>182</v>
       </c>
       <c r="F66" s="3">
         <v>0</v>
       </c>
-      <c r="G66" s="1"/>
-      <c r="H66" s="2" t="s">
-        <v>644</v>
+      <c r="H66" s="1" t="s">
+        <v>587</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A67" s="2" t="s">
-        <v>480</v>
+      <c r="A67" t="s">
+        <v>702</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>74</v>
+        <v>183</v>
       </c>
       <c r="C67" s="3">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="D67" s="4">
         <v>0</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>75</v>
+        <v>184</v>
       </c>
       <c r="F67" s="3">
         <v>0</v>
       </c>
-      <c r="G67" s="1"/>
-      <c r="H67" s="2" t="s">
-        <v>645</v>
+      <c r="H67" s="1" t="s">
+        <v>588</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A68" t="s">
-        <v>520</v>
+      <c r="A68" s="2" t="s">
+        <v>667</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>210</v>
+        <v>199</v>
       </c>
       <c r="C68" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D68" s="4">
         <v>0</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>211</v>
+        <v>200</v>
       </c>
       <c r="F68" s="3">
         <v>0</v>
       </c>
-      <c r="G68" s="1"/>
       <c r="H68" s="1" t="s">
-        <v>647</v>
+        <v>589</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A69" t="s">
-        <v>521</v>
+      <c r="A69" s="2" t="s">
+        <v>668</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>212</v>
+        <v>197</v>
       </c>
       <c r="C69" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D69" s="4">
         <v>0</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="F69" s="3">
         <v>0</v>
       </c>
-      <c r="G69" s="1"/>
       <c r="H69" s="1" t="s">
-        <v>647</v>
+        <v>590</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A70" t="s">
-        <v>524</v>
+      <c r="A70" s="2" t="s">
+        <v>683</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>217</v>
+        <v>175</v>
       </c>
       <c r="C70" s="3">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="D70" s="4">
         <v>0</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>218</v>
+        <v>176</v>
       </c>
       <c r="F70" s="3">
         <v>0</v>
       </c>
-      <c r="G70" s="1"/>
       <c r="H70" s="1" t="s">
-        <v>647</v>
+        <v>591</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A71" t="s">
-        <v>523</v>
+      <c r="A71" s="2" t="s">
+        <v>684</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>215</v>
+        <v>173</v>
       </c>
       <c r="C71" s="3">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="D71" s="4">
         <v>0</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>216</v>
+        <v>174</v>
       </c>
       <c r="F71" s="3">
         <v>0</v>
       </c>
-      <c r="G71" s="1"/>
       <c r="H71" s="1" t="s">
-        <v>647</v>
+        <v>592</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>522</v>
+        <v>689</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>214</v>
+        <v>165</v>
       </c>
       <c r="C72" s="3">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="D72" s="4">
         <v>0</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>525</v>
+        <v>166</v>
       </c>
       <c r="F72" s="3">
         <v>0</v>
       </c>
-      <c r="G72" s="1"/>
       <c r="H72" s="1" t="s">
-        <v>647</v>
+        <v>593</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A73" s="2" t="s">
-        <v>345</v>
+      <c r="A73" t="s">
+        <v>690</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>275</v>
+        <v>171</v>
       </c>
       <c r="C73" s="3">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="D73" s="4">
         <v>0</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>276</v>
+        <v>172</v>
       </c>
       <c r="F73" s="3">
         <v>0</v>
       </c>
-      <c r="G73" s="1"/>
       <c r="H73" s="1" t="s">
-        <v>542</v>
+        <v>594</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A74" s="2" t="s">
-        <v>347</v>
+      <c r="A74" t="s">
+        <v>691</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>269</v>
+        <v>169</v>
       </c>
       <c r="C74" s="3">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="D74" s="4">
         <v>0</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>250</v>
+        <v>170</v>
       </c>
       <c r="F74" s="3">
         <v>0</v>
       </c>
-      <c r="G74" s="1"/>
-      <c r="H74" t="s">
-        <v>544</v>
+      <c r="H74" s="1" t="s">
+        <v>595</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A75" s="2" t="s">
-        <v>348</v>
+      <c r="A75" t="s">
+        <v>692</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>270</v>
+        <v>167</v>
       </c>
       <c r="C75" s="3">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="D75" s="4">
         <v>0</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>334</v>
+        <v>168</v>
       </c>
       <c r="F75" s="3">
         <v>0</v>
       </c>
-      <c r="G75" s="1"/>
-      <c r="H75" t="s">
-        <v>544</v>
+      <c r="H75" s="1" t="s">
+        <v>596</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A76" s="2" t="s">
-        <v>358</v>
+      <c r="A76" t="s">
+        <v>704</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>84</v>
+        <v>195</v>
       </c>
       <c r="C76" s="3">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="D76" s="4">
         <v>0</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>85</v>
+        <v>196</v>
       </c>
       <c r="F76" s="3">
         <v>0</v>
       </c>
-      <c r="G76" s="1"/>
       <c r="H76" s="1" t="s">
-        <v>551</v>
+        <v>597</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A77" s="2" t="s">
-        <v>360</v>
+        <v>487</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="C77" s="3">
         <v>7</v>
@@ -4585,94 +4733,94 @@
         <v>0</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>295</v>
+        <v>102</v>
       </c>
       <c r="F77" s="3">
         <v>0</v>
       </c>
       <c r="G77" s="1"/>
       <c r="H77" s="1" t="s">
-        <v>553</v>
+        <v>647</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
-        <v>379</v>
+        <v>491</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>257</v>
+        <v>503</v>
       </c>
       <c r="C78" s="3">
         <v>7</v>
       </c>
       <c r="D78" s="4">
-        <v>0.97916666666666663</v>
+        <v>0</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>258</v>
+        <v>117</v>
       </c>
       <c r="F78" s="3">
         <v>0</v>
       </c>
       <c r="G78" s="1"/>
-      <c r="H78" t="s">
-        <v>571</v>
+      <c r="H78" s="1" t="s">
+        <v>647</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
-        <v>383</v>
+        <v>492</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>134</v>
+        <v>109</v>
       </c>
       <c r="C79" s="3">
         <v>7</v>
       </c>
       <c r="D79" s="4">
-        <v>0.875</v>
+        <v>0</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>135</v>
+        <v>110</v>
       </c>
       <c r="F79" s="3">
         <v>0</v>
       </c>
       <c r="G79" s="1"/>
       <c r="H79" s="1" t="s">
-        <v>575</v>
+        <v>647</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A80" s="2" t="s">
-        <v>388</v>
+        <v>493</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>6</v>
+        <v>115</v>
       </c>
       <c r="C80" s="3">
         <v>7</v>
       </c>
       <c r="D80" s="4">
-        <v>0.91666666666666663</v>
+        <v>0</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>7</v>
+        <v>116</v>
       </c>
       <c r="F80" s="3">
         <v>0</v>
       </c>
       <c r="G80" s="1"/>
-      <c r="H80" s="2" t="s">
-        <v>579</v>
+      <c r="H80" s="1" t="s">
+        <v>647</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A81" s="2" t="s">
-        <v>391</v>
+        <v>488</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>268</v>
+        <v>504</v>
       </c>
       <c r="C81" s="3">
         <v>7</v>
@@ -4681,18 +4829,22 @@
         <v>0</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="F81" s="3">
         <v>0</v>
       </c>
+      <c r="G81" s="1"/>
       <c r="H81" s="1" t="s">
-        <v>582</v>
+        <v>647</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A82" s="2" t="s">
+        <v>489</v>
+      </c>
       <c r="B82" s="1" t="s">
-        <v>200</v>
+        <v>505</v>
       </c>
       <c r="C82" s="3">
         <v>7</v>
@@ -4701,18 +4853,22 @@
         <v>0</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>201</v>
+        <v>103</v>
       </c>
       <c r="F82" s="3">
         <v>0</v>
       </c>
+      <c r="G82" s="1"/>
       <c r="H82" s="1" t="s">
-        <v>594</v>
+        <v>647</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A83" s="2" t="s">
+        <v>490</v>
+      </c>
       <c r="B83" s="1" t="s">
-        <v>198</v>
+        <v>508</v>
       </c>
       <c r="C83" s="3">
         <v>7</v>
@@ -4721,45 +4877,46 @@
         <v>0</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>199</v>
+        <v>104</v>
       </c>
       <c r="F83" s="3">
         <v>0</v>
       </c>
+      <c r="G83" s="1"/>
       <c r="H83" s="1" t="s">
-        <v>595</v>
+        <v>647</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A84" s="2" t="s">
-        <v>491</v>
+        <v>391</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>102</v>
+        <v>250</v>
       </c>
       <c r="C84" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D84" s="4">
         <v>0</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>103</v>
+        <v>251</v>
       </c>
       <c r="F84" s="3">
         <v>0</v>
       </c>
       <c r="G84" s="1"/>
-      <c r="H84" s="1" t="s">
-        <v>652</v>
+      <c r="H84" t="s">
+        <v>598</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A85" s="2" t="s">
-        <v>495</v>
+        <v>413</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>507</v>
+        <v>414</v>
       </c>
       <c r="C85" s="3">
         <v>7</v>
@@ -4768,1241 +4925,1177 @@
         <v>0</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>118</v>
+        <v>202</v>
       </c>
       <c r="F85" s="3">
         <v>0</v>
       </c>
       <c r="G85" s="1"/>
       <c r="H85" s="1" t="s">
-        <v>652</v>
+        <v>599</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A86" s="2" t="s">
-        <v>492</v>
+      <c r="A86" t="s">
+        <v>450</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C86" s="3">
         <v>7</v>
       </c>
       <c r="D86" s="4">
-        <v>0</v>
+        <v>0.95833333333333337</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>101</v>
+        <v>289</v>
       </c>
       <c r="F86" s="3">
         <v>0</v>
       </c>
       <c r="G86" s="1"/>
       <c r="H86" s="1" t="s">
-        <v>652</v>
+        <v>631</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A87" s="2" t="s">
-        <v>496</v>
+        <v>716</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="C87" s="3">
-        <v>7</v>
-      </c>
-      <c r="D87" s="4">
-        <v>0</v>
-      </c>
+        <v>307</v>
+      </c>
+      <c r="C87" s="1"/>
+      <c r="D87" s="5"/>
       <c r="E87" s="1" t="s">
-        <v>111</v>
+        <v>320</v>
       </c>
       <c r="F87" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G87" s="1"/>
       <c r="H87" s="1" t="s">
-        <v>652</v>
+        <v>600</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A88" s="2" t="s">
-        <v>497</v>
+        <v>434</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>116</v>
+        <v>244</v>
       </c>
       <c r="C88" s="3">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D88" s="4">
         <v>0</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>117</v>
+        <v>245</v>
       </c>
       <c r="F88" s="3">
         <v>0</v>
       </c>
       <c r="G88" s="1"/>
       <c r="H88" s="1" t="s">
-        <v>652</v>
+        <v>601</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A89" s="2" t="s">
-        <v>493</v>
+        <v>393</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>509</v>
+        <v>47</v>
       </c>
       <c r="C89" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D89" s="4">
-        <v>0</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>104</v>
+        <v>48</v>
       </c>
       <c r="F89" s="3">
         <v>0</v>
       </c>
       <c r="G89" s="1"/>
-      <c r="H89" s="1" t="s">
-        <v>652</v>
+      <c r="H89" s="2" t="s">
+        <v>602</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A90" t="s">
-        <v>511</v>
+      <c r="A90" s="2" t="s">
+        <v>394</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>510</v>
+        <v>49</v>
       </c>
       <c r="C90" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D90" s="4">
-        <v>0</v>
+        <v>0.70833333333333337</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>98</v>
+        <v>50</v>
       </c>
       <c r="F90" s="3">
         <v>0</v>
       </c>
       <c r="G90" s="1"/>
-      <c r="H90" s="1" t="s">
-        <v>653</v>
+      <c r="H90" s="2" t="s">
+        <v>602</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A91" s="2" t="s">
-        <v>494</v>
+        <v>435</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>512</v>
+        <v>277</v>
       </c>
       <c r="C91" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D91" s="4">
         <v>0</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>105</v>
+        <v>280</v>
       </c>
       <c r="F91" s="3">
         <v>0</v>
       </c>
       <c r="G91" s="1"/>
-      <c r="H91" s="1" t="s">
+      <c r="H91" s="8" t="s">
         <v>652</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A92" s="2" t="s">
-        <v>415</v>
+        <v>395</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>416</v>
+        <v>43</v>
       </c>
       <c r="C92" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D92" s="4">
-        <v>0</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>203</v>
+        <v>44</v>
       </c>
       <c r="F92" s="3">
         <v>0</v>
       </c>
       <c r="G92" s="1"/>
-      <c r="H92" s="1" t="s">
-        <v>604</v>
+      <c r="H92" s="2" t="s">
+        <v>602</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A93" s="2" t="s">
-        <v>408</v>
+        <v>396</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>138</v>
+        <v>51</v>
       </c>
       <c r="C93" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D93" s="4">
-        <v>0.91666666666666663</v>
+        <v>0.75</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>139</v>
+        <v>52</v>
       </c>
       <c r="F93" s="3">
         <v>0</v>
       </c>
       <c r="G93" s="1"/>
-      <c r="H93" s="1" t="s">
-        <v>614</v>
+      <c r="H93" s="2" t="s">
+        <v>602</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A94" s="2" t="s">
-        <v>662</v>
+        <v>397</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>316</v>
-      </c>
-      <c r="C94" s="1">
-        <v>7</v>
-      </c>
-      <c r="D94" s="5">
-        <v>0.91666666666666663</v>
+        <v>53</v>
+      </c>
+      <c r="C94" s="3">
+        <v>6</v>
+      </c>
+      <c r="D94" s="4">
+        <v>0.79166666666666663</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>317</v>
-      </c>
-      <c r="F94" s="1">
+        <v>54</v>
+      </c>
+      <c r="F94" s="3">
         <v>0</v>
       </c>
       <c r="G94" s="1"/>
-      <c r="H94" s="1" t="s">
-        <v>617</v>
+      <c r="H94" s="2" t="s">
+        <v>602</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A95" s="2" t="s">
-        <v>411</v>
+        <v>436</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>130</v>
+        <v>279</v>
       </c>
       <c r="C95" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D95" s="4">
-        <v>0.91666666666666663</v>
+        <v>0</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>131</v>
+        <v>283</v>
       </c>
       <c r="F95" s="3">
         <v>0</v>
       </c>
       <c r="G95" s="1"/>
-      <c r="H95" s="1" t="s">
-        <v>626</v>
+      <c r="H95" s="8" t="s">
+        <v>652</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A96" s="2" t="s">
-        <v>412</v>
+        <v>437</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>129</v>
+        <v>276</v>
       </c>
       <c r="C96" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D96" s="4">
-        <v>0.91666666666666663</v>
+        <v>0</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="F96" s="3">
         <v>0</v>
       </c>
       <c r="G96" s="1"/>
-      <c r="H96" s="1" t="s">
-        <v>626</v>
+      <c r="H96" s="8" t="s">
+        <v>652</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A97" s="2" t="s">
-        <v>413</v>
+        <v>398</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>293</v>
+        <v>55</v>
       </c>
       <c r="C97" s="3">
-        <v>7</v>
-      </c>
-      <c r="D97" s="5">
-        <v>0.875</v>
+        <v>6</v>
+      </c>
+      <c r="D97" s="4">
+        <v>0.83333333333333337</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>294</v>
+        <v>56</v>
       </c>
       <c r="F97" s="3">
         <v>0</v>
       </c>
       <c r="G97" s="1"/>
-      <c r="H97" s="1" t="s">
-        <v>627</v>
+      <c r="H97" s="2" t="s">
+        <v>602</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A98" s="2" t="s">
-        <v>418</v>
+        <v>399</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>301</v>
+        <v>714</v>
       </c>
       <c r="C98" s="3">
-        <v>7</v>
-      </c>
-      <c r="D98" s="5">
-        <v>0.91666666666666663</v>
+        <v>6</v>
+      </c>
+      <c r="D98" s="4">
+        <v>0.875</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>301</v>
+        <v>339</v>
       </c>
       <c r="F98" s="3">
         <v>0</v>
       </c>
       <c r="G98" s="1"/>
-      <c r="H98" s="1" t="s">
-        <v>632</v>
+      <c r="H98" s="2" t="s">
+        <v>602</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A99" s="2" t="s">
-        <v>459</v>
+        <v>438</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>340</v>
+        <v>278</v>
       </c>
       <c r="C99" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D99" s="4">
         <v>0</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>94</v>
+        <v>282</v>
       </c>
       <c r="F99" s="3">
         <v>0</v>
       </c>
       <c r="G99" s="1"/>
       <c r="H99" s="8" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A100" t="s">
-        <v>452</v>
+      <c r="A100" s="2" t="s">
+        <v>400</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>513</v>
+        <v>41</v>
       </c>
       <c r="C100" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D100" s="4">
-        <v>0.95833333333333337</v>
+        <v>0.54166666666666663</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>290</v>
+        <v>42</v>
       </c>
       <c r="F100" s="3">
         <v>0</v>
       </c>
       <c r="G100" s="1"/>
-      <c r="H100" s="1" t="s">
-        <v>636</v>
+      <c r="H100" s="2" t="s">
+        <v>602</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A101" s="2" t="s">
-        <v>517</v>
+        <v>401</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>136</v>
+        <v>45</v>
       </c>
       <c r="C101" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D101" s="4">
-        <v>0</v>
+        <v>0.625</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>342</v>
+        <v>46</v>
       </c>
       <c r="F101" s="3">
         <v>0</v>
       </c>
       <c r="G101" s="1"/>
-      <c r="H101" s="1" t="s">
-        <v>637</v>
+      <c r="H101" s="2" t="s">
+        <v>602</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>433</v>
+        <v>439</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>137</v>
+        <v>226</v>
       </c>
       <c r="C102" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D102" s="4">
-        <v>0.97916666666666663</v>
+        <v>0</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>667</v>
+        <v>227</v>
       </c>
       <c r="F102" s="3">
         <v>0</v>
       </c>
       <c r="G102" s="1"/>
       <c r="H102" s="1" t="s">
-        <v>639</v>
+        <v>603</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A103" s="2" t="s">
-        <v>481</v>
+      <c r="A103" t="s">
+        <v>440</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>96</v>
+        <v>220</v>
       </c>
       <c r="C103" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D103" s="4">
         <v>0</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>97</v>
+        <v>221</v>
       </c>
       <c r="F103" s="3">
         <v>0</v>
       </c>
       <c r="G103" s="1"/>
-      <c r="H103" s="8" t="s">
-        <v>655</v>
+      <c r="H103" s="1" t="s">
+        <v>603</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A104" s="2" t="s">
-        <v>483</v>
+      <c r="A104" t="s">
+        <v>441</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>99</v>
+        <v>232</v>
       </c>
       <c r="C104" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D104" s="4">
         <v>0</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>100</v>
+        <v>233</v>
       </c>
       <c r="F104" s="3">
         <v>0</v>
       </c>
       <c r="G104" s="1"/>
-      <c r="H104" s="8" t="s">
-        <v>655</v>
+      <c r="H104" s="1" t="s">
+        <v>603</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A105" s="2" t="s">
-        <v>484</v>
+      <c r="A105" t="s">
+        <v>442</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>90</v>
+        <v>222</v>
       </c>
       <c r="C105" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D105" s="4">
         <v>0</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>91</v>
+        <v>223</v>
       </c>
       <c r="F105" s="3">
         <v>0</v>
       </c>
       <c r="G105" s="1"/>
       <c r="H105" s="1" t="s">
-        <v>655</v>
+        <v>603</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A106" s="2" t="s">
-        <v>485</v>
+      <c r="A106" t="s">
+        <v>443</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>92</v>
+        <v>230</v>
       </c>
       <c r="C106" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D106" s="4">
         <v>0</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>93</v>
+        <v>231</v>
       </c>
       <c r="F106" s="3">
         <v>0</v>
       </c>
       <c r="G106" s="1"/>
       <c r="H106" s="1" t="s">
-        <v>655</v>
+        <v>603</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A107" s="2" t="s">
-        <v>486</v>
+      <c r="A107" t="s">
+        <v>444</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>106</v>
+        <v>228</v>
       </c>
       <c r="C107" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D107" s="4">
         <v>0</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>107</v>
+        <v>229</v>
       </c>
       <c r="F107" s="3">
         <v>0</v>
       </c>
       <c r="G107" s="1"/>
       <c r="H107" s="1" t="s">
-        <v>655</v>
+        <v>603</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A108" s="2" t="s">
-        <v>487</v>
+      <c r="A108" t="s">
+        <v>445</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>114</v>
+        <v>224</v>
       </c>
       <c r="C108" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D108" s="4">
         <v>0</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>115</v>
+        <v>225</v>
       </c>
       <c r="F108" s="3">
         <v>0</v>
       </c>
       <c r="G108" s="1"/>
       <c r="H108" s="1" t="s">
-        <v>655</v>
+        <v>603</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A109" s="2" t="s">
-        <v>488</v>
+        <v>446</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>108</v>
+        <v>242</v>
       </c>
       <c r="C109" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D109" s="4">
         <v>0</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>109</v>
+        <v>243</v>
       </c>
       <c r="F109" s="3">
         <v>0</v>
       </c>
       <c r="G109" s="1"/>
-      <c r="H109" s="1" t="s">
-        <v>655</v>
+      <c r="H109" s="8" t="s">
+        <v>651</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A110" s="2" t="s">
-        <v>489</v>
+        <v>447</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>95</v>
+        <v>272</v>
       </c>
       <c r="C110" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D110" s="4">
-        <v>0</v>
+        <v>0.54166666666666663</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>482</v>
+        <v>273</v>
       </c>
       <c r="F110" s="3">
         <v>0</v>
       </c>
       <c r="G110" s="1"/>
       <c r="H110" s="1" t="s">
-        <v>656</v>
+        <v>604</v>
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A111" s="2" t="s">
-        <v>490</v>
+        <v>402</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>112</v>
+        <v>201</v>
       </c>
       <c r="C111" s="3">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D111" s="4">
         <v>0</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>113</v>
+        <v>335</v>
       </c>
       <c r="F111" s="3">
         <v>0</v>
       </c>
       <c r="G111" s="1"/>
       <c r="H111" s="1" t="s">
-        <v>655</v>
+        <v>605</v>
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A112" s="2" t="s">
-        <v>346</v>
+      <c r="A112" t="s">
+        <v>708</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="C112" s="3">
-        <v>8</v>
-      </c>
-      <c r="D112" s="4">
-        <v>0</v>
+        <v>525</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>333</v>
-      </c>
-      <c r="F112" s="3">
-        <v>0</v>
-      </c>
-      <c r="G112" s="1"/>
-      <c r="H112" s="1" t="s">
-        <v>543</v>
+        <v>526</v>
+      </c>
+      <c r="F112" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A113" s="2" t="s">
-        <v>460</v>
+      <c r="A113" t="s">
+        <v>708</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>469</v>
-      </c>
-      <c r="C113" s="3">
-        <v>8</v>
-      </c>
-      <c r="D113" s="6">
-        <v>0</v>
+        <v>525</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>461</v>
-      </c>
-      <c r="F113" s="3">
-        <v>0</v>
-      </c>
-      <c r="H113" s="1" t="s">
-        <v>635</v>
+        <v>531</v>
+      </c>
+      <c r="F113" s="2">
+        <v>0</v>
+      </c>
+      <c r="H113" s="2" t="s">
+        <v>644</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A114" s="2" t="s">
-        <v>351</v>
+      <c r="A114" t="s">
+        <v>709</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="C114" s="3">
-        <v>9</v>
-      </c>
-      <c r="D114" s="4">
-        <v>0</v>
+        <v>527</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>296</v>
-      </c>
-      <c r="F114" s="3">
-        <v>0</v>
-      </c>
-      <c r="G114" s="1"/>
-      <c r="H114" s="1" t="s">
-        <v>547</v>
+        <v>528</v>
+      </c>
+      <c r="F114" s="2">
+        <v>0</v>
+      </c>
+      <c r="H114" s="2" t="s">
+        <v>645</v>
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A115" s="2" t="s">
-        <v>352</v>
+      <c r="A115" t="s">
+        <v>710</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="C115" s="3">
-        <v>9</v>
-      </c>
-      <c r="D115" s="4">
-        <v>0</v>
+        <v>523</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>335</v>
+        <v>524</v>
       </c>
       <c r="F115" s="3">
         <v>0</v>
-      </c>
-      <c r="G115" s="1"/>
-      <c r="H115" s="1" t="s">
-        <v>547</v>
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A116" s="2" t="s">
-        <v>353</v>
+        <v>403</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>242</v>
+        <v>326</v>
       </c>
       <c r="C116" s="3">
-        <v>9</v>
-      </c>
-      <c r="D116" s="4">
+        <v>13</v>
+      </c>
+      <c r="D116" s="5">
         <v>0</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>297</v>
+        <v>327</v>
       </c>
       <c r="F116" s="3">
         <v>0</v>
       </c>
       <c r="G116" s="1"/>
       <c r="H116" s="1" t="s">
-        <v>547</v>
+        <v>606</v>
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A117" s="2" t="s">
-        <v>499</v>
+      <c r="A117" t="s">
+        <v>711</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="C117" s="3">
-        <v>10</v>
-      </c>
-      <c r="D117" s="4">
+        <v>530</v>
+      </c>
+      <c r="C117" s="2">
+        <v>13</v>
+      </c>
+      <c r="D117" s="6">
         <v>0</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="F117" s="3">
-        <v>0</v>
-      </c>
-      <c r="G117" s="1"/>
-      <c r="H117" s="1" t="s">
-        <v>612</v>
+        <v>680</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A118" s="2" t="s">
-        <v>500</v>
+      <c r="A118" t="s">
+        <v>712</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="C118" s="3">
-        <v>10</v>
-      </c>
-      <c r="D118" s="4">
+        <v>715</v>
+      </c>
+      <c r="C118" s="2">
+        <v>13</v>
+      </c>
+      <c r="D118" s="6">
         <v>0</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="F118" s="3">
-        <v>0</v>
-      </c>
-      <c r="G118" s="1"/>
-      <c r="H118" s="1" t="s">
-        <v>612</v>
+        <v>681</v>
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A119" s="2" t="s">
-        <v>349</v>
+      <c r="A119" t="s">
+        <v>507</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>140</v>
+        <v>506</v>
       </c>
       <c r="C119" s="3">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D119" s="4">
-        <v>0.41666666666666669</v>
+        <v>0</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>141</v>
+        <v>97</v>
       </c>
       <c r="F119" s="3">
         <v>0</v>
       </c>
       <c r="G119" s="1"/>
       <c r="H119" s="1" t="s">
-        <v>545</v>
+        <v>648</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A120" s="2" t="s">
-        <v>350</v>
+        <v>494</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>142</v>
+        <v>118</v>
       </c>
       <c r="C120" s="3">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D120" s="4">
-        <v>0.45833333333333331</v>
+        <v>0</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="F120" s="3">
         <v>0</v>
       </c>
       <c r="G120" s="1"/>
       <c r="H120" s="1" t="s">
-        <v>546</v>
+        <v>607</v>
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A121" s="2" t="s">
-        <v>356</v>
+        <v>497</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>219</v>
+        <v>124</v>
       </c>
       <c r="C121" s="3">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="D121" s="4">
         <v>0</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>332</v>
+        <v>125</v>
       </c>
       <c r="F121" s="3">
         <v>0</v>
       </c>
       <c r="G121" s="1"/>
       <c r="H121" s="1" t="s">
-        <v>549</v>
+        <v>607</v>
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A122" s="2" t="s">
-        <v>381</v>
+        <v>495</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="C122" s="1">
-        <v>13</v>
-      </c>
-      <c r="D122" s="5">
+        <v>122</v>
+      </c>
+      <c r="C122" s="3">
+        <v>10</v>
+      </c>
+      <c r="D122" s="4">
         <v>0</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="F122" s="1">
+        <v>123</v>
+      </c>
+      <c r="F122" s="3">
         <v>0</v>
       </c>
       <c r="G122" s="1"/>
       <c r="H122" s="1" t="s">
-        <v>573</v>
+        <v>607</v>
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A123" s="2" t="s">
-        <v>404</v>
+        <v>496</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>202</v>
+        <v>120</v>
       </c>
       <c r="C123" s="3">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D123" s="4">
         <v>0</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>337</v>
+        <v>121</v>
       </c>
       <c r="F123" s="3">
         <v>0</v>
       </c>
       <c r="G123" s="1"/>
       <c r="H123" s="1" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A124" s="2" t="s">
-        <v>405</v>
+        <v>533</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>328</v>
-      </c>
-      <c r="C124" s="3">
-        <v>13</v>
-      </c>
-      <c r="D124" s="5">
-        <v>0</v>
-      </c>
-      <c r="E124" s="1" t="s">
-        <v>329</v>
-      </c>
-      <c r="F124" s="3">
-        <v>0</v>
-      </c>
-      <c r="G124" s="1"/>
-      <c r="H124" s="1" t="s">
-        <v>611</v>
+        <v>532</v>
+      </c>
+      <c r="C124" s="2">
+        <v>30</v>
+      </c>
+      <c r="D124" s="6">
+        <v>0</v>
+      </c>
+      <c r="E124" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="F124" s="2">
+        <v>0</v>
+      </c>
+      <c r="H124" s="8" t="s">
+        <v>535</v>
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A125" t="s">
-        <v>518</v>
+      <c r="A125" s="2" t="s">
+        <v>404</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>324</v>
-      </c>
-      <c r="C125" s="3">
-        <v>13</v>
-      </c>
-      <c r="D125" s="5">
-        <v>0</v>
-      </c>
+        <v>261</v>
+      </c>
+      <c r="C125" s="1"/>
+      <c r="D125" s="1"/>
       <c r="E125" s="1" t="s">
-        <v>325</v>
+        <v>262</v>
       </c>
       <c r="F125" s="3">
-        <v>0</v>
-      </c>
-      <c r="G125" s="1"/>
-      <c r="H125" s="1" t="s">
-        <v>629</v>
+        <v>1</v>
+      </c>
+      <c r="G125" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="H125" s="2" t="s">
+        <v>608</v>
       </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A126" s="2" t="s">
-        <v>419</v>
+        <v>405</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="C126" s="3">
-        <v>13</v>
-      </c>
-      <c r="D126" s="4">
-        <v>0</v>
-      </c>
+        <v>264</v>
+      </c>
+      <c r="C126" s="1"/>
+      <c r="D126" s="1"/>
       <c r="E126" s="1" t="s">
-        <v>659</v>
+        <v>265</v>
       </c>
       <c r="F126" s="3">
-        <v>0</v>
-      </c>
-      <c r="G126" s="1"/>
-      <c r="H126" s="1" t="s">
-        <v>633</v>
+        <v>1</v>
+      </c>
+      <c r="G126" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="H126" s="2" t="s">
+        <v>608</v>
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A127" t="s">
-        <v>424</v>
+      <c r="A127" s="2" t="s">
+        <v>406</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>33</v>
+        <v>137</v>
       </c>
       <c r="C127" s="3">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D127" s="4">
-        <v>0.75</v>
+        <v>0.91666666666666663</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>34</v>
+        <v>138</v>
       </c>
       <c r="F127" s="3">
         <v>0</v>
       </c>
       <c r="G127" s="1"/>
-      <c r="H127" s="2" t="s">
-        <v>634</v>
+      <c r="H127" s="1" t="s">
+        <v>609</v>
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A128" s="2" t="s">
-        <v>470</v>
+        <v>448</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>37</v>
+        <v>234</v>
       </c>
       <c r="C128" s="3">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D128" s="4">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>38</v>
+        <v>235</v>
       </c>
       <c r="F128" s="3">
         <v>0</v>
       </c>
       <c r="G128" s="1"/>
-      <c r="H128" s="2" t="s">
-        <v>634</v>
+      <c r="H128" s="1" t="s">
+        <v>610</v>
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A129" s="2" t="s">
-        <v>471</v>
+        <v>407</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>39</v>
+        <v>297</v>
       </c>
       <c r="C129" s="3">
-        <v>13</v>
-      </c>
-      <c r="D129" s="4">
-        <v>0.75</v>
+        <v>6</v>
+      </c>
+      <c r="D129" s="5">
+        <v>0</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>40</v>
+        <v>298</v>
       </c>
       <c r="F129" s="3">
         <v>0</v>
       </c>
       <c r="G129" s="1"/>
-      <c r="H129" s="2" t="s">
-        <v>634</v>
+      <c r="H129" s="1" t="s">
+        <v>649</v>
       </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A130" t="s">
-        <v>428</v>
+      <c r="A130" s="2" t="s">
+        <v>449</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="C130" s="3">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D130" s="4">
-        <v>0.83333333333333337</v>
+        <v>0</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>36</v>
+        <v>76</v>
       </c>
       <c r="F130" s="3">
         <v>0</v>
       </c>
       <c r="G130" s="1"/>
       <c r="H130" s="2" t="s">
-        <v>634</v>
+        <v>611</v>
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A131" s="2" t="s">
-        <v>476</v>
+        <v>656</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="C131" s="3">
-        <v>13</v>
-      </c>
-      <c r="D131" s="4">
-        <v>0</v>
+        <v>315</v>
+      </c>
+      <c r="C131" s="1">
+        <v>7</v>
+      </c>
+      <c r="D131" s="5">
+        <v>0.91666666666666663</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="F131" s="3">
+        <v>316</v>
+      </c>
+      <c r="F131" s="1">
         <v>0</v>
       </c>
       <c r="G131" s="1"/>
-      <c r="H131" s="2" t="s">
-        <v>641</v>
+      <c r="H131" s="1" t="s">
+        <v>612</v>
       </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A132" t="s">
-        <v>434</v>
+      <c r="A132" s="2" t="s">
+        <v>657</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="C132" s="3">
-        <v>13</v>
-      </c>
-      <c r="D132" s="5">
-        <v>0</v>
-      </c>
+        <v>498</v>
+      </c>
+      <c r="C132" s="1"/>
+      <c r="D132" s="5"/>
       <c r="E132" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="F132" s="3">
-        <v>0</v>
+        <v>319</v>
+      </c>
+      <c r="F132" s="1">
+        <v>1</v>
       </c>
       <c r="G132" s="1"/>
       <c r="H132" s="1" t="s">
-        <v>646</v>
+        <v>613</v>
       </c>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A133" s="2" t="s">
-        <v>377</v>
+        <v>658</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="C133" s="3">
-        <v>14</v>
-      </c>
-      <c r="D133" s="4">
-        <v>0</v>
-      </c>
+        <v>304</v>
+      </c>
+      <c r="C133" s="1"/>
+      <c r="D133" s="1"/>
       <c r="E133" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="F133" s="3">
-        <v>0</v>
+        <v>317</v>
+      </c>
+      <c r="F133" s="1">
+        <v>1</v>
       </c>
       <c r="G133" s="1"/>
-      <c r="H133" t="s">
-        <v>571</v>
+      <c r="H133" s="1" t="s">
+        <v>613</v>
       </c>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A134" s="2" t="s">
+        <v>659</v>
+      </c>
       <c r="B134" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="C134" s="3">
-        <v>14</v>
-      </c>
-      <c r="D134" s="4">
-        <v>0</v>
-      </c>
+        <v>305</v>
+      </c>
+      <c r="C134" s="1"/>
+      <c r="D134" s="1"/>
       <c r="E134" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="F134" s="3">
-        <v>0</v>
-      </c>
+        <v>318</v>
+      </c>
+      <c r="F134" s="1">
+        <v>1</v>
+      </c>
+      <c r="G134" s="1"/>
       <c r="H134" s="1" t="s">
-        <v>596</v>
+        <v>613</v>
       </c>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A135" s="2" t="s">
-        <v>436</v>
+        <v>499</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="C135" s="3">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="D135" s="4">
         <v>0</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>246</v>
+        <v>655</v>
       </c>
       <c r="F135" s="3">
         <v>0</v>
       </c>
       <c r="G135" s="1"/>
       <c r="H135" s="1" t="s">
-        <v>606</v>
+        <v>614</v>
       </c>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A136" s="2" t="s">
-        <v>462</v>
+        <v>500</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>58</v>
+        <v>246</v>
       </c>
       <c r="C136" s="3">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="D136" s="4">
         <v>0</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>59</v>
+        <v>247</v>
       </c>
       <c r="F136" s="3">
         <v>0</v>
       </c>
       <c r="G136" s="1"/>
       <c r="H136" s="2" t="s">
-        <v>621</v>
+        <v>615</v>
       </c>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A137" s="2" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C137" s="3">
         <v>14</v>
@@ -6011,22 +6104,22 @@
         <v>0</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>505</v>
+        <v>58</v>
       </c>
       <c r="F137" s="3">
         <v>0</v>
       </c>
       <c r="G137" s="1"/>
       <c r="H137" s="2" t="s">
-        <v>622</v>
+        <v>616</v>
       </c>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A138" s="2" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C138" s="3">
         <v>14</v>
@@ -6035,46 +6128,39 @@
         <v>0</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>61</v>
+        <v>501</v>
       </c>
       <c r="F138" s="3">
         <v>0</v>
       </c>
       <c r="G138" s="1"/>
       <c r="H138" s="2" t="s">
-        <v>624</v>
+        <v>617</v>
       </c>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A139" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="B139" s="1" t="s">
         <v>465</v>
       </c>
-      <c r="B139" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="C139" s="3">
-        <v>14</v>
-      </c>
-      <c r="D139" s="4">
-        <v>0</v>
-      </c>
       <c r="E139" s="1" t="s">
-        <v>64</v>
+        <v>502</v>
       </c>
       <c r="F139" s="3">
-        <v>0</v>
-      </c>
-      <c r="G139" s="1"/>
-      <c r="H139" s="2" t="s">
-        <v>625</v>
+        <v>1</v>
+      </c>
+      <c r="H139" s="1" t="s">
+        <v>618</v>
       </c>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A140" s="2" t="s">
-        <v>410</v>
+        <v>461</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>127</v>
+        <v>59</v>
       </c>
       <c r="C140" s="3">
         <v>14</v>
@@ -6083,1078 +6169,1402 @@
         <v>0</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>128</v>
+        <v>60</v>
       </c>
       <c r="F140" s="3">
         <v>0</v>
       </c>
       <c r="G140" s="1"/>
-      <c r="H140" s="1" t="s">
-        <v>626</v>
+      <c r="H140" s="2" t="s">
+        <v>619</v>
       </c>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A141" s="2" t="s">
-        <v>378</v>
+        <v>463</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>255</v>
+        <v>62</v>
       </c>
       <c r="C141" s="3">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D141" s="4">
-        <v>0.95833333333333337</v>
+        <v>0</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>256</v>
+        <v>63</v>
       </c>
       <c r="F141" s="3">
         <v>0</v>
       </c>
       <c r="G141" s="1"/>
-      <c r="H141" t="s">
-        <v>571</v>
+      <c r="H141" s="2" t="s">
+        <v>620</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A142" s="2" t="s">
+        <v>408</v>
+      </c>
       <c r="B142" s="1" t="s">
-        <v>192</v>
+        <v>126</v>
       </c>
       <c r="C142" s="3">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D142" s="4">
         <v>0</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>193</v>
+        <v>127</v>
       </c>
       <c r="F142" s="3">
         <v>0</v>
       </c>
+      <c r="G142" s="1"/>
       <c r="H142" s="1" t="s">
-        <v>586</v>
+        <v>621</v>
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A143" s="2" t="s">
+        <v>409</v>
+      </c>
       <c r="B143" s="1" t="s">
-        <v>190</v>
+        <v>129</v>
       </c>
       <c r="C143" s="3">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="D143" s="4">
-        <v>0</v>
+        <v>0.91666666666666663</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>191</v>
+        <v>130</v>
       </c>
       <c r="F143" s="3">
         <v>0</v>
       </c>
+      <c r="G143" s="1"/>
       <c r="H143" s="1" t="s">
-        <v>587</v>
+        <v>621</v>
       </c>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A144" s="2" t="s">
+        <v>410</v>
+      </c>
       <c r="B144" s="1" t="s">
-        <v>194</v>
+        <v>128</v>
       </c>
       <c r="C144" s="3">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="D144" s="4">
-        <v>0</v>
+        <v>0.91666666666666663</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>195</v>
+        <v>287</v>
       </c>
       <c r="F144" s="3">
         <v>0</v>
       </c>
+      <c r="G144" s="1"/>
       <c r="H144" s="1" t="s">
-        <v>591</v>
+        <v>621</v>
       </c>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A145" s="2" t="s">
+        <v>411</v>
+      </c>
       <c r="B145" s="1" t="s">
-        <v>184</v>
+        <v>292</v>
       </c>
       <c r="C145" s="3">
-        <v>15</v>
-      </c>
-      <c r="D145" s="4">
-        <v>0</v>
+        <v>7</v>
+      </c>
+      <c r="D145" s="5">
+        <v>0.875</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>185</v>
+        <v>293</v>
       </c>
       <c r="F145" s="3">
         <v>0</v>
       </c>
+      <c r="G145" s="1"/>
       <c r="H145" s="1" t="s">
-        <v>593</v>
+        <v>622</v>
       </c>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A146" s="2" t="s">
+        <v>412</v>
+      </c>
       <c r="B146" s="1" t="s">
-        <v>196</v>
+        <v>9</v>
       </c>
       <c r="C146" s="3">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D146" s="4">
         <v>0</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>197</v>
+        <v>10</v>
       </c>
       <c r="F146" s="3">
         <v>0</v>
       </c>
-      <c r="H146" s="1" t="s">
-        <v>602</v>
+      <c r="G146" s="1"/>
+      <c r="H146" s="2" t="s">
+        <v>623</v>
       </c>
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A147" s="2" t="s">
-        <v>357</v>
+      <c r="A147" t="s">
+        <v>514</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>89</v>
+        <v>322</v>
       </c>
       <c r="C147" s="3">
-        <v>27</v>
-      </c>
-      <c r="D147" s="4">
+        <v>13</v>
+      </c>
+      <c r="D147" s="5">
         <v>0</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>331</v>
+        <v>323</v>
       </c>
       <c r="F147" s="3">
         <v>0</v>
       </c>
       <c r="G147" s="1"/>
       <c r="H147" s="1" t="s">
-        <v>550</v>
+        <v>624</v>
       </c>
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A148" s="2" t="s">
-        <v>359</v>
+      <c r="A148" t="s">
+        <v>515</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="C148" s="3">
-        <v>27</v>
-      </c>
-      <c r="D148" s="4">
-        <v>0</v>
-      </c>
+        <v>324</v>
+      </c>
+      <c r="C148" s="3"/>
+      <c r="D148" s="5"/>
       <c r="E148" s="1" t="s">
-        <v>87</v>
+        <v>325</v>
       </c>
       <c r="F148" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G148" s="1"/>
       <c r="H148" s="1" t="s">
-        <v>552</v>
+        <v>625</v>
       </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A149" s="2" t="s">
-        <v>361</v>
+        <v>510</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>82</v>
+        <v>511</v>
       </c>
       <c r="C149" s="3">
-        <v>28</v>
-      </c>
-      <c r="D149" s="4">
+        <v>30</v>
+      </c>
+      <c r="D149" s="5">
         <v>0</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>83</v>
+        <v>512</v>
       </c>
       <c r="F149" s="3">
         <v>0</v>
       </c>
       <c r="G149" s="1"/>
       <c r="H149" s="1" t="s">
-        <v>554</v>
+        <v>626</v>
       </c>
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A150" s="2" t="s">
-        <v>363</v>
+        <v>415</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>80</v>
+        <v>302</v>
       </c>
       <c r="C150" s="3">
-        <v>28</v>
-      </c>
-      <c r="D150" s="4">
+        <v>30</v>
+      </c>
+      <c r="D150" s="5">
         <v>0</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>81</v>
+        <v>308</v>
       </c>
       <c r="F150" s="3">
         <v>0</v>
       </c>
       <c r="G150" s="1"/>
       <c r="H150" s="1" t="s">
-        <v>556</v>
+        <v>626</v>
       </c>
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A151" s="2" t="s">
-        <v>364</v>
+        <v>416</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>78</v>
+        <v>300</v>
       </c>
       <c r="C151" s="3">
-        <v>28</v>
-      </c>
-      <c r="D151" s="4">
-        <v>0</v>
+        <v>7</v>
+      </c>
+      <c r="D151" s="5">
+        <v>0.91666666666666663</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>79</v>
+        <v>300</v>
       </c>
       <c r="F151" s="3">
         <v>0</v>
       </c>
       <c r="G151" s="1"/>
       <c r="H151" s="1" t="s">
-        <v>557</v>
+        <v>627</v>
       </c>
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A152" s="2" t="s">
-        <v>504</v>
+        <v>694</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="C152" s="3">
-        <v>29</v>
-      </c>
-      <c r="D152" s="4">
-        <v>0</v>
+        <v>696</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="F152" s="3">
-        <v>0</v>
-      </c>
-      <c r="G152" s="1"/>
+        <v>698</v>
+      </c>
+      <c r="F152" s="2">
+        <v>1</v>
+      </c>
       <c r="H152" s="2" t="s">
-        <v>620</v>
+        <v>727</v>
       </c>
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A153" s="2" t="s">
-        <v>362</v>
+        <v>693</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>338</v>
-      </c>
-      <c r="C153" s="3">
+        <v>695</v>
+      </c>
+      <c r="E153" s="1" t="s">
+        <v>697</v>
+      </c>
+      <c r="F153" s="2">
+        <v>1</v>
+      </c>
+      <c r="H153" s="2" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="154" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A154" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="B154" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="C154" s="3">
+        <v>6</v>
+      </c>
+      <c r="D154" s="4">
+        <v>0</v>
+      </c>
+      <c r="E154" s="1" t="s">
+        <v>654</v>
+      </c>
+      <c r="F154" s="3">
+        <v>0</v>
+      </c>
+      <c r="G154" s="1"/>
+      <c r="H154" s="1" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="155" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A155" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="B155" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="C155" s="3">
+        <v>13</v>
+      </c>
+      <c r="D155" s="4">
+        <v>0</v>
+      </c>
+      <c r="E155" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="F155" s="3">
+        <v>0</v>
+      </c>
+      <c r="G155" s="1"/>
+      <c r="H155" s="1" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="156" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A156" t="s">
+        <v>418</v>
+      </c>
+      <c r="B156" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C156" s="3">
+        <v>6</v>
+      </c>
+      <c r="D156" s="4">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="E156" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F156" s="3">
+        <v>0</v>
+      </c>
+      <c r="G156" s="1"/>
+      <c r="H156" s="2" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="157" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A157" t="s">
+        <v>419</v>
+      </c>
+      <c r="B157" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C157" s="3">
+        <v>6</v>
+      </c>
+      <c r="D157" s="4">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="E157" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F157" s="3">
+        <v>0</v>
+      </c>
+      <c r="G157" s="1"/>
+      <c r="H157" s="2" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="158" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A158" t="s">
+        <v>420</v>
+      </c>
+      <c r="B158" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C158" s="3">
+        <v>6</v>
+      </c>
+      <c r="D158" s="4">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="E158" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F158" s="3">
+        <v>0</v>
+      </c>
+      <c r="G158" s="1"/>
+      <c r="H158" s="2" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="159" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A159" t="s">
+        <v>421</v>
+      </c>
+      <c r="B159" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C159" s="3">
+        <v>6</v>
+      </c>
+      <c r="D159" s="4">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="E159" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F159" s="3">
+        <v>0</v>
+      </c>
+      <c r="G159" s="1"/>
+      <c r="H159" s="2" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="160" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A160" t="s">
+        <v>422</v>
+      </c>
+      <c r="B160" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C160" s="3">
+        <v>13</v>
+      </c>
+      <c r="D160" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="E160" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F160" s="3">
+        <v>0</v>
+      </c>
+      <c r="G160" s="1"/>
+      <c r="H160" s="2" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="161" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A161" t="s">
+        <v>423</v>
+      </c>
+      <c r="B161" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C161" s="3">
+        <v>6</v>
+      </c>
+      <c r="D161" s="4">
+        <v>0.4375</v>
+      </c>
+      <c r="E161" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F161" s="3">
+        <v>0</v>
+      </c>
+      <c r="G161" s="1"/>
+      <c r="H161" s="2" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="162" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A162" t="s">
+        <v>424</v>
+      </c>
+      <c r="B162" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C162" s="3">
+        <v>6</v>
+      </c>
+      <c r="D162" s="4">
+        <v>0.5625</v>
+      </c>
+      <c r="E162" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F162" s="3">
+        <v>0</v>
+      </c>
+      <c r="G162" s="1"/>
+      <c r="H162" s="2" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="163" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A163" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="B163" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C163" s="3">
+        <v>13</v>
+      </c>
+      <c r="D163" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="E163" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F163" s="3">
+        <v>0</v>
+      </c>
+      <c r="G163" s="1"/>
+      <c r="H163" s="2" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="164" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A164" t="s">
+        <v>425</v>
+      </c>
+      <c r="B164" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C164" s="3">
+        <v>6</v>
+      </c>
+      <c r="D164" s="4">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="E164" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D153" s="4">
-        <v>0</v>
-      </c>
-      <c r="E153" s="1" t="s">
-        <v>339</v>
-      </c>
-      <c r="F153" s="3">
-        <v>0</v>
-      </c>
-      <c r="G153" s="1"/>
-      <c r="H153" s="1" t="s">
-        <v>555</v>
-      </c>
-    </row>
-    <row r="154" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B154" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="C154" s="3">
-        <v>30</v>
-      </c>
-      <c r="D154" s="4">
-        <v>0</v>
-      </c>
-      <c r="E154" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="F154" s="3">
-        <v>0</v>
-      </c>
-      <c r="H154" s="1" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="155" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B155" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="C155" s="3">
-        <v>30</v>
-      </c>
-      <c r="D155" s="4">
-        <v>0</v>
-      </c>
-      <c r="E155" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="F155" s="3">
-        <v>0</v>
-      </c>
-      <c r="H155" s="1" t="s">
-        <v>584</v>
-      </c>
-    </row>
-    <row r="156" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B156" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="C156" s="3">
-        <v>30</v>
-      </c>
-      <c r="D156" s="4">
-        <v>0</v>
-      </c>
-      <c r="E156" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="F156" s="3">
-        <v>0</v>
-      </c>
-      <c r="H156" s="1" t="s">
-        <v>585</v>
-      </c>
-    </row>
-    <row r="157" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B157" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="C157" s="3">
-        <v>30</v>
-      </c>
-      <c r="D157" s="4">
-        <v>0</v>
-      </c>
-      <c r="E157" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="F157" s="3">
-        <v>0</v>
-      </c>
-      <c r="H157" s="1" t="s">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="158" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B158" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="C158" s="3">
-        <v>30</v>
-      </c>
-      <c r="D158" s="4">
-        <v>0</v>
-      </c>
-      <c r="E158" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="F158" s="3">
-        <v>0</v>
-      </c>
-      <c r="H158" s="1" t="s">
-        <v>589</v>
-      </c>
-    </row>
-    <row r="159" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A159" s="2" t="s">
-        <v>392</v>
-      </c>
-      <c r="B159" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="C159" s="3">
-        <v>30</v>
-      </c>
-      <c r="D159" s="4">
-        <v>0</v>
-      </c>
-      <c r="E159" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="F159" s="3">
-        <v>0</v>
-      </c>
-      <c r="H159" s="1" t="s">
-        <v>590</v>
-      </c>
-    </row>
-    <row r="160" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B160" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="C160" s="3">
-        <v>30</v>
-      </c>
-      <c r="D160" s="4">
-        <v>0</v>
-      </c>
-      <c r="E160" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="F160" s="3">
-        <v>0</v>
-      </c>
-      <c r="H160" s="1" t="s">
-        <v>592</v>
-      </c>
-    </row>
-    <row r="161" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B161" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="C161" s="3">
-        <v>30</v>
-      </c>
-      <c r="D161" s="4">
-        <v>0</v>
-      </c>
-      <c r="E161" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="F161" s="3">
-        <v>0</v>
-      </c>
-      <c r="H161" s="1" t="s">
-        <v>597</v>
-      </c>
-    </row>
-    <row r="162" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B162" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="C162" s="3">
-        <v>30</v>
-      </c>
-      <c r="D162" s="4">
-        <v>0</v>
-      </c>
-      <c r="E162" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="F162" s="3">
-        <v>0</v>
-      </c>
-      <c r="H162" s="1" t="s">
-        <v>598</v>
-      </c>
-    </row>
-    <row r="163" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B163" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="C163" s="3">
-        <v>30</v>
-      </c>
-      <c r="D163" s="4">
-        <v>0</v>
-      </c>
-      <c r="E163" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="F163" s="3">
-        <v>0</v>
-      </c>
-      <c r="H163" s="1" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="164" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B164" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="C164" s="3">
-        <v>30</v>
-      </c>
-      <c r="D164" s="4">
-        <v>0</v>
-      </c>
-      <c r="E164" s="1" t="s">
-        <v>171</v>
-      </c>
       <c r="F164" s="3">
         <v>0</v>
       </c>
-      <c r="H164" s="1" t="s">
-        <v>600</v>
+      <c r="G164" s="1"/>
+      <c r="H164" s="2" t="s">
+        <v>629</v>
       </c>
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A165" s="2" t="s">
+        <v>468</v>
+      </c>
       <c r="B165" s="1" t="s">
-        <v>168</v>
+        <v>39</v>
       </c>
       <c r="C165" s="3">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="D165" s="4">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>169</v>
+        <v>40</v>
       </c>
       <c r="F165" s="3">
         <v>0</v>
       </c>
-      <c r="H165" s="1" t="s">
-        <v>601</v>
+      <c r="G165" s="1"/>
+      <c r="H165" s="2" t="s">
+        <v>629</v>
       </c>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A166" s="2" t="s">
-        <v>501</v>
+      <c r="A166" t="s">
+        <v>426</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>125</v>
+        <v>35</v>
       </c>
       <c r="C166" s="3">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="D166" s="4">
-        <v>0</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>126</v>
+        <v>36</v>
       </c>
       <c r="F166" s="3">
         <v>0</v>
       </c>
       <c r="G166" s="1"/>
-      <c r="H166" s="1" t="s">
-        <v>612</v>
+      <c r="H166" s="2" t="s">
+        <v>629</v>
       </c>
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A167" s="2" t="s">
-        <v>514</v>
+      <c r="A167" t="s">
+        <v>427</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>515</v>
+        <v>22</v>
       </c>
       <c r="C167" s="3">
-        <v>30</v>
-      </c>
-      <c r="D167" s="5">
-        <v>0</v>
+        <v>6</v>
+      </c>
+      <c r="D167" s="4">
+        <v>0.45833333333333331</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>516</v>
+        <v>288</v>
       </c>
       <c r="F167" s="3">
         <v>0</v>
       </c>
       <c r="G167" s="1"/>
-      <c r="H167" s="1" t="s">
-        <v>631</v>
+      <c r="H167" s="2" t="s">
+        <v>629</v>
       </c>
     </row>
     <row r="168" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A168" s="2" t="s">
-        <v>417</v>
+        <v>458</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>303</v>
+        <v>466</v>
       </c>
       <c r="C168" s="3">
-        <v>30</v>
-      </c>
-      <c r="D168" s="5">
+        <v>8</v>
+      </c>
+      <c r="D168" s="6">
         <v>0</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>309</v>
+        <v>459</v>
       </c>
       <c r="F168" s="3">
         <v>0</v>
       </c>
-      <c r="G168" s="1"/>
       <c r="H168" s="1" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A169" s="2" t="s">
-        <v>538</v>
+        <v>457</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>537</v>
-      </c>
-      <c r="C169" s="2">
-        <v>30</v>
-      </c>
-      <c r="D169" s="6">
-        <v>0</v>
-      </c>
-      <c r="E169" s="2" t="s">
-        <v>539</v>
-      </c>
-      <c r="F169" s="2">
-        <v>0</v>
-      </c>
-      <c r="H169" s="7" t="s">
-        <v>540</v>
+        <v>338</v>
+      </c>
+      <c r="C169" s="3">
+        <v>7</v>
+      </c>
+      <c r="D169" s="4">
+        <v>0</v>
+      </c>
+      <c r="E169" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="F169" s="3">
+        <v>0</v>
+      </c>
+      <c r="G169" s="1"/>
+      <c r="H169" s="8" t="s">
+        <v>646</v>
       </c>
     </row>
     <row r="170" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A170" s="2" t="s">
-        <v>369</v>
+        <v>513</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>160</v>
+        <v>135</v>
       </c>
       <c r="C170" s="3">
-        <v>37</v>
+        <v>7</v>
       </c>
       <c r="D170" s="4">
         <v>0</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>161</v>
+        <v>340</v>
       </c>
       <c r="F170" s="3">
         <v>0</v>
       </c>
       <c r="G170" s="1"/>
       <c r="H170" s="1" t="s">
-        <v>563</v>
+        <v>632</v>
       </c>
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A171" s="2" t="s">
-        <v>373</v>
+        <v>713</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="C171" s="3">
-        <v>37</v>
-      </c>
-      <c r="D171" s="4">
-        <v>0</v>
-      </c>
+        <v>529</v>
+      </c>
+      <c r="C171" s="3"/>
+      <c r="D171" s="6"/>
       <c r="E171" s="1" t="s">
-        <v>159</v>
+        <v>678</v>
       </c>
       <c r="F171" s="3">
-        <v>0</v>
-      </c>
-      <c r="G171" s="1"/>
-      <c r="H171" s="1" t="s">
-        <v>567</v>
+        <v>1</v>
+      </c>
+      <c r="G171" s="2" t="s">
+        <v>679</v>
+      </c>
+      <c r="H171" s="8" t="s">
+        <v>677</v>
       </c>
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A172" s="2" t="s">
-        <v>374</v>
+      <c r="A172" t="s">
+        <v>428</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>156</v>
+        <v>205</v>
       </c>
       <c r="C172" s="3">
-        <v>37</v>
+        <v>6</v>
       </c>
       <c r="D172" s="4">
         <v>0</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>157</v>
+        <v>206</v>
       </c>
       <c r="F172" s="3">
         <v>0</v>
       </c>
       <c r="G172" s="1"/>
       <c r="H172" s="1" t="s">
-        <v>568</v>
+        <v>633</v>
       </c>
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
-        <v>519</v>
+        <v>429</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>326</v>
+        <v>203</v>
       </c>
       <c r="C173" s="3">
-        <v>45</v>
-      </c>
-      <c r="D173" s="5">
+        <v>6</v>
+      </c>
+      <c r="D173" s="4">
         <v>0</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>327</v>
+        <v>204</v>
       </c>
       <c r="F173" s="3">
         <v>0</v>
       </c>
       <c r="G173" s="1"/>
       <c r="H173" s="1" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
     </row>
     <row r="174" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A174" s="2" t="s">
-        <v>385</v>
+      <c r="A174" t="s">
+        <v>430</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>312</v>
+        <v>207</v>
       </c>
       <c r="C174" s="3">
-        <v>55</v>
-      </c>
-      <c r="D174" s="5">
+        <v>6</v>
+      </c>
+      <c r="D174" s="4">
         <v>0</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>314</v>
+        <v>208</v>
       </c>
       <c r="F174" s="3">
         <v>0</v>
       </c>
       <c r="G174" s="1"/>
       <c r="H174" s="1" t="s">
-        <v>577</v>
+        <v>633</v>
       </c>
     </row>
     <row r="175" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A175" s="2" t="s">
-        <v>394</v>
+      <c r="A175" t="s">
+        <v>431</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="C175" s="1">
-        <v>76</v>
-      </c>
-      <c r="D175" s="5">
-        <v>0</v>
+        <v>136</v>
+      </c>
+      <c r="C175" s="3">
+        <v>7</v>
+      </c>
+      <c r="D175" s="4">
+        <v>0.97916666666666663</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>322</v>
-      </c>
-      <c r="F175" s="1"/>
+        <v>661</v>
+      </c>
+      <c r="F175" s="3">
+        <v>0</v>
+      </c>
       <c r="G175" s="1"/>
       <c r="H175" s="1" t="s">
-        <v>605</v>
+        <v>634</v>
       </c>
     </row>
     <row r="176" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A176" s="2" t="s">
-        <v>382</v>
+        <v>471</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="C176" s="1"/>
-      <c r="D176" s="1"/>
+        <v>64</v>
+      </c>
+      <c r="C176" s="3">
+        <v>6</v>
+      </c>
+      <c r="D176" s="4">
+        <v>0</v>
+      </c>
       <c r="E176" s="1" t="s">
-        <v>260</v>
+        <v>660</v>
       </c>
       <c r="F176" s="3">
-        <v>1</v>
-      </c>
-      <c r="G176" s="1" t="s">
-        <v>261</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G176" s="1"/>
       <c r="H176" s="2" t="s">
-        <v>574</v>
+        <v>635</v>
       </c>
     </row>
     <row r="177" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A177" s="2" t="s">
-        <v>406</v>
+        <v>472</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="C177" s="1"/>
-      <c r="D177" s="1"/>
+        <v>65</v>
+      </c>
+      <c r="C177" s="3">
+        <v>13</v>
+      </c>
+      <c r="D177" s="4">
+        <v>0</v>
+      </c>
       <c r="E177" s="1" t="s">
-        <v>263</v>
+        <v>66</v>
       </c>
       <c r="F177" s="3">
-        <v>1</v>
-      </c>
-      <c r="G177" s="1" t="s">
-        <v>264</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G177" s="1"/>
       <c r="H177" s="2" t="s">
-        <v>613</v>
+        <v>636</v>
       </c>
     </row>
     <row r="178" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A178" s="2" t="s">
-        <v>407</v>
+        <v>473</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>265</v>
-      </c>
-      <c r="C178" s="1"/>
-      <c r="D178" s="1"/>
+        <v>69</v>
+      </c>
+      <c r="C178" s="3">
+        <v>6</v>
+      </c>
+      <c r="D178" s="4">
+        <v>0</v>
+      </c>
       <c r="E178" s="1" t="s">
-        <v>266</v>
+        <v>70</v>
       </c>
       <c r="F178" s="3">
-        <v>1</v>
-      </c>
-      <c r="G178" s="1" t="s">
-        <v>267</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G178" s="1"/>
       <c r="H178" s="2" t="s">
-        <v>613</v>
+        <v>637</v>
       </c>
     </row>
     <row r="179" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A179" s="2" t="s">
-        <v>663</v>
+        <v>474</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>502</v>
-      </c>
-      <c r="C179" s="1"/>
-      <c r="D179" s="5"/>
+        <v>67</v>
+      </c>
+      <c r="C179" s="3">
+        <v>6</v>
+      </c>
+      <c r="D179" s="4">
+        <v>0</v>
+      </c>
       <c r="E179" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="F179" s="1">
-        <v>1</v>
-      </c>
-      <c r="G179" s="1" t="s">
-        <v>319</v>
-      </c>
-      <c r="H179" s="1" t="s">
-        <v>618</v>
+        <v>68</v>
+      </c>
+      <c r="F179" s="3">
+        <v>0</v>
+      </c>
+      <c r="G179" s="1"/>
+      <c r="H179" s="2" t="s">
+        <v>638</v>
       </c>
     </row>
     <row r="180" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A180" s="2" t="s">
-        <v>664</v>
+        <v>475</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>305</v>
-      </c>
-      <c r="C180" s="1"/>
-      <c r="D180" s="1"/>
+        <v>71</v>
+      </c>
+      <c r="C180" s="3">
+        <v>6</v>
+      </c>
+      <c r="D180" s="4">
+        <v>0</v>
+      </c>
       <c r="E180" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="F180" s="1">
-        <v>1</v>
-      </c>
-      <c r="G180" s="1" t="s">
-        <v>319</v>
-      </c>
-      <c r="H180" s="1" t="s">
-        <v>618</v>
+        <v>72</v>
+      </c>
+      <c r="F180" s="3">
+        <v>0</v>
+      </c>
+      <c r="G180" s="1"/>
+      <c r="H180" s="2" t="s">
+        <v>639</v>
       </c>
     </row>
     <row r="181" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A181" s="2" t="s">
-        <v>665</v>
+        <v>476</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="C181" s="1"/>
-      <c r="D181" s="1"/>
+        <v>73</v>
+      </c>
+      <c r="C181" s="3">
+        <v>6</v>
+      </c>
+      <c r="D181" s="4">
+        <v>0</v>
+      </c>
       <c r="E181" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="F181" s="1">
-        <v>1</v>
-      </c>
-      <c r="G181" s="1" t="s">
-        <v>319</v>
-      </c>
-      <c r="H181" s="1" t="s">
-        <v>618</v>
+        <v>74</v>
+      </c>
+      <c r="F181" s="3">
+        <v>0</v>
+      </c>
+      <c r="G181" s="1"/>
+      <c r="H181" s="2" t="s">
+        <v>640</v>
       </c>
     </row>
     <row r="182" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A182" s="2" t="s">
-        <v>466</v>
+        <v>477</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>467</v>
+        <v>95</v>
+      </c>
+      <c r="C182" s="3">
+        <v>7</v>
+      </c>
+      <c r="D182" s="4">
+        <v>0</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>506</v>
+        <v>96</v>
       </c>
       <c r="F182" s="3">
-        <v>1</v>
-      </c>
-      <c r="G182" s="2" t="s">
-        <v>468</v>
-      </c>
-      <c r="H182" s="1" t="s">
-        <v>623</v>
+        <v>0</v>
+      </c>
+      <c r="G182" s="1"/>
+      <c r="H182" s="8" t="s">
+        <v>650</v>
       </c>
     </row>
     <row r="183" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A183" t="s">
-        <v>435</v>
+      <c r="A183" s="2" t="s">
+        <v>479</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>307</v>
-      </c>
-      <c r="C183" s="1"/>
-      <c r="D183" s="1"/>
+        <v>98</v>
+      </c>
+      <c r="C183" s="3">
+        <v>7</v>
+      </c>
+      <c r="D183" s="4">
+        <v>0</v>
+      </c>
       <c r="E183" s="1" t="s">
-        <v>323</v>
-      </c>
-      <c r="F183" s="1">
-        <v>1</v>
-      </c>
-      <c r="G183" s="1" t="s">
-        <v>319</v>
-      </c>
-      <c r="H183" s="1" t="s">
-        <v>648</v>
+        <v>99</v>
+      </c>
+      <c r="F183" s="3">
+        <v>0</v>
+      </c>
+      <c r="G183" s="1"/>
+      <c r="H183" s="8" t="s">
+        <v>650</v>
       </c>
     </row>
     <row r="184" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A184" s="2" t="s">
-        <v>472</v>
+        <v>480</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>473</v>
+        <v>89</v>
+      </c>
+      <c r="C184" s="3">
+        <v>7</v>
+      </c>
+      <c r="D184" s="4">
+        <v>0</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>474</v>
+        <v>90</v>
+      </c>
+      <c r="F184" s="3">
+        <v>0</v>
+      </c>
+      <c r="G184" s="1"/>
+      <c r="H184" s="1" t="s">
+        <v>650</v>
       </c>
     </row>
     <row r="185" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A185" s="2" t="s">
+        <v>481</v>
+      </c>
       <c r="B185" s="1" t="s">
-        <v>527</v>
+        <v>91</v>
+      </c>
+      <c r="C185" s="3">
+        <v>7</v>
+      </c>
+      <c r="D185" s="4">
+        <v>0</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>528</v>
+        <v>92</v>
       </c>
       <c r="F185" s="3">
         <v>0</v>
       </c>
+      <c r="G185" s="1"/>
+      <c r="H185" s="1" t="s">
+        <v>650</v>
+      </c>
     </row>
     <row r="186" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A186" s="2" t="s">
+        <v>482</v>
+      </c>
       <c r="B186" s="1" t="s">
-        <v>529</v>
+        <v>105</v>
+      </c>
+      <c r="C186" s="3">
+        <v>7</v>
+      </c>
+      <c r="D186" s="4">
+        <v>0</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>530</v>
-      </c>
-      <c r="F186" s="2">
-        <v>0</v>
+        <v>106</v>
+      </c>
+      <c r="F186" s="3">
+        <v>0</v>
+      </c>
+      <c r="G186" s="1"/>
+      <c r="H186" s="1" t="s">
+        <v>650</v>
       </c>
     </row>
     <row r="187" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A187" s="2" t="s">
+        <v>483</v>
+      </c>
       <c r="B187" s="1" t="s">
-        <v>529</v>
+        <v>113</v>
+      </c>
+      <c r="C187" s="3">
+        <v>7</v>
+      </c>
+      <c r="D187" s="4">
+        <v>0</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>536</v>
-      </c>
-      <c r="F187" s="2">
-        <v>0</v>
-      </c>
-      <c r="H187" s="2" t="s">
-        <v>649</v>
+        <v>114</v>
+      </c>
+      <c r="F187" s="3">
+        <v>0</v>
+      </c>
+      <c r="G187" s="1"/>
+      <c r="H187" s="1" t="s">
+        <v>650</v>
       </c>
     </row>
     <row r="188" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A188" s="2" t="s">
+        <v>484</v>
+      </c>
       <c r="B188" s="1" t="s">
-        <v>531</v>
+        <v>107</v>
+      </c>
+      <c r="C188" s="3">
+        <v>7</v>
+      </c>
+      <c r="D188" s="4">
+        <v>0</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>532</v>
-      </c>
-      <c r="F188" s="2">
-        <v>0</v>
-      </c>
-      <c r="H188" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="F188" s="3">
+        <v>0</v>
+      </c>
+      <c r="G188" s="1"/>
+      <c r="H188" s="1" t="s">
         <v>650</v>
       </c>
     </row>
     <row r="189" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A189" s="2" t="s">
+        <v>485</v>
+      </c>
       <c r="B189" s="1" t="s">
-        <v>533</v>
+        <v>94</v>
+      </c>
+      <c r="C189" s="3">
+        <v>7</v>
+      </c>
+      <c r="D189" s="4">
+        <v>0</v>
+      </c>
+      <c r="E189" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="F189" s="3">
+        <v>0</v>
+      </c>
+      <c r="G189" s="1"/>
+      <c r="H189" s="7" t="s">
+        <v>725</v>
       </c>
     </row>
     <row r="190" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A190" s="2" t="s">
+        <v>486</v>
+      </c>
       <c r="B190" s="1" t="s">
-        <v>534</v>
+        <v>111</v>
+      </c>
+      <c r="C190" s="3">
+        <v>7</v>
+      </c>
+      <c r="D190" s="4">
+        <v>0</v>
+      </c>
+      <c r="E190" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="F190" s="3">
+        <v>0</v>
+      </c>
+      <c r="G190" s="1"/>
+      <c r="H190" s="1" t="s">
+        <v>650</v>
       </c>
     </row>
     <row r="191" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A191" t="s">
+        <v>432</v>
+      </c>
       <c r="B191" s="1" t="s">
-        <v>535</v>
+        <v>290</v>
+      </c>
+      <c r="C191" s="3">
+        <v>13</v>
+      </c>
+      <c r="D191" s="5">
+        <v>0</v>
+      </c>
+      <c r="E191" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="F191" s="3">
+        <v>0</v>
+      </c>
+      <c r="G191" s="1"/>
+      <c r="H191" s="1" t="s">
+        <v>641</v>
       </c>
     </row>
     <row r="192" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A192" s="2" t="s">
-        <v>672</v>
+      <c r="A192" t="s">
+        <v>516</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>669</v>
-      </c>
-      <c r="C192" s="2">
-        <v>7</v>
-      </c>
-      <c r="D192" s="6">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="E192" s="2" t="s">
-        <v>670</v>
-      </c>
-      <c r="F192" s="2">
-        <v>0</v>
-      </c>
-      <c r="H192" s="2" t="s">
-        <v>671</v>
+        <v>209</v>
+      </c>
+      <c r="C192" s="3">
+        <v>6</v>
+      </c>
+      <c r="D192" s="4">
+        <v>0</v>
+      </c>
+      <c r="E192" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="F192" s="3">
+        <v>0</v>
+      </c>
+      <c r="G192" s="1"/>
+      <c r="H192" s="1" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="193" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A193" t="s">
+        <v>517</v>
+      </c>
+      <c r="B193" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="C193" s="3">
+        <v>6</v>
+      </c>
+      <c r="D193" s="4">
+        <v>0</v>
+      </c>
+      <c r="E193" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="F193" s="3">
+        <v>0</v>
+      </c>
+      <c r="G193" s="1"/>
+      <c r="H193" s="1" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="194" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A194" t="s">
+        <v>520</v>
+      </c>
+      <c r="B194" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="C194" s="3">
+        <v>6</v>
+      </c>
+      <c r="D194" s="4">
+        <v>0</v>
+      </c>
+      <c r="E194" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="F194" s="3">
+        <v>0</v>
+      </c>
+      <c r="G194" s="1"/>
+      <c r="H194" s="1" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="195" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A195" t="s">
+        <v>519</v>
+      </c>
+      <c r="B195" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="C195" s="3">
+        <v>6</v>
+      </c>
+      <c r="D195" s="4">
+        <v>0</v>
+      </c>
+      <c r="E195" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="F195" s="3">
+        <v>0</v>
+      </c>
+      <c r="G195" s="1"/>
+      <c r="H195" s="1" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="196" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A196" t="s">
+        <v>518</v>
+      </c>
+      <c r="B196" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="C196" s="3">
+        <v>6</v>
+      </c>
+      <c r="D196" s="4">
+        <v>0</v>
+      </c>
+      <c r="E196" s="1" t="s">
+        <v>521</v>
+      </c>
+      <c r="F196" s="3">
+        <v>0</v>
+      </c>
+      <c r="G196" s="1"/>
+      <c r="H196" s="1" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="197" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A197" t="s">
+        <v>433</v>
+      </c>
+      <c r="B197" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="C197" s="1"/>
+      <c r="D197" s="1"/>
+      <c r="E197" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="F197" s="1">
+        <v>1</v>
+      </c>
+      <c r="G197" s="1"/>
+      <c r="H197" s="1" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="198" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A198" s="2" t="s">
+        <v>717</v>
+      </c>
+      <c r="B198" s="1" t="s">
+        <v>718</v>
+      </c>
+      <c r="E198" s="1" t="s">
+        <v>721</v>
+      </c>
+      <c r="F198" s="3">
+        <v>1</v>
+      </c>
+      <c r="H198" s="8" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="199" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A199" s="2" t="s">
+        <v>719</v>
+      </c>
+      <c r="B199" s="1" t="s">
+        <v>720</v>
+      </c>
+      <c r="E199" s="1" t="s">
+        <v>722</v>
+      </c>
+      <c r="F199" s="3">
+        <v>1</v>
+      </c>
+      <c r="H199" s="8" t="s">
+        <v>724</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H191">
-    <sortCondition ref="C2:C191"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H197">
+    <sortCondition ref="B2:B197"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="H169" r:id="rId1" xr:uid="{79761F97-15D2-497A-876C-4F087647F759}"/>
-    <hyperlink ref="H99" r:id="rId2" xr:uid="{135A9EAA-53A1-4C6C-86B4-EA1E459FCF29}"/>
-    <hyperlink ref="H103" r:id="rId3" display="https://playpointlab.com/&gt; &lt;/a&gt;" xr:uid="{E664F694-AC8E-4F9E-AC58-F59D21B9D99B}"/>
-    <hyperlink ref="H104" r:id="rId4" display="https://playpointlab.com/&gt; &lt;/a&gt;" xr:uid="{24D8477A-84BC-417A-A9F7-D15CF3A0F305}"/>
-    <hyperlink ref="H43" r:id="rId5" xr:uid="{1AB750C9-076B-44E1-A1C1-42D804ED6043}"/>
-    <hyperlink ref="H33" r:id="rId6" xr:uid="{02B7B66A-8C7C-4429-9DD0-E7B36896002B}"/>
-    <hyperlink ref="H30" r:id="rId7" xr:uid="{47FAF52E-8D8D-4DEF-9078-74E8499F1823}"/>
-    <hyperlink ref="H29" r:id="rId8" xr:uid="{EB17BCE6-05D4-4DBC-8BA5-36725923A3F4}"/>
-    <hyperlink ref="H25" r:id="rId9" xr:uid="{CBF9E267-F776-4DA4-A228-FE69CAF6E18D}"/>
+    <hyperlink ref="H189" r:id="rId1" xr:uid="{08510EB6-59FE-461F-9934-59900452DB70}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId10"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId2"/>
 </worksheet>
 </file>
--- a/stores.xlsx
+++ b/stores.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\YUMIN\Desktop\B0KT2A_RSVN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{11F55747-95A9-4B4F-A5A6-E315B512ADE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{02CBCB94-CD67-4BA8-B36B-862CC74CEE53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{ABFC3117-FCCB-4FF3-804A-FE19451A2004}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{ABFC3117-FCCB-4FF3-804A-FE19451A2004}"/>
   </bookViews>
   <sheets>
     <sheet name="stores" sheetId="2" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="799" uniqueCount="729">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="871" uniqueCount="787">
   <si>
     <t>룸익스케이프 WHITE</t>
   </si>
@@ -2536,14 +2536,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>http://m.dumbndumber.kr</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>http://m.dumbndumber-sm.kr</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>https://playpointlab.com/</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2555,6 +2547,243 @@
   </si>
   <si>
     <t>화-&gt;수 0:00&lt;BR&gt;다음주 토~다다음주 금 1주일치 오픈</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>key_el</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>키이스케이프X에버랜드 메모리카니발</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>memory of ricky,memory of poppy,memory of tony,메모리오브리키,메모리오브포피,메모리오브토니,메모리오브파피</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>머더파커 WOW 홍대점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이스케이프월드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이스케이프컴퍼니,이케컴,escape company</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://naver.me/5FEJkSkH</t>
+  </si>
+  <si>
+    <t>ecw_sw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mp_jj1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>머더파커 전주1호점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mp_jj2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>머더파커 전주2호점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mp_ys</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>머더파커 양산점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mp_jj3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>머더파커 전주3호점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>머더파커 대구1호점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mp_kd1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mp_tg1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>머더파커 건대1호점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mp_gj</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>머더파커 광주점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mp_kd2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>머더파커 건대2호점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mp_hd1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>머더파커 홍대1호점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mp_tg2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>머더파커 대구2호점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mp_js</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>머더파커 잠실점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mp_bs</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>머더파커 부산점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mpw_hd</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mpw_js</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>머더파커 WOW 잠실점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mp_is</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>머더파커 익산점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>머더파커분노의살인,내이름지배만,일주,one week</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://murderparker</t>
+  </si>
+  <si>
+    <t>com/</t>
+  </si>
+  <si>
+    <t>http://dumbndumber-sm.kr</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://dumbndumber.kr</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://reservation.everland.com/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스모커,new토니파커숨겨진과거,목격자들,인턴사원의크리스마스생존기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>머더파커분노의살인,엘리스사라진아이,유코사스미치밀한복수,오씨네장난감가게,언타이틀,untitle</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>제임스완벽한도피,박엠마엄마의향기,김파커끝없는복수,박마담의비밀클럽,전당포불편한거래</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pc방가는길,괴짜중딩사차원,백,파커vs파커,8585세탁소,파커대파커</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>음대출신김수학,파커4,우리꼰대진분홍,여행,꽁노리,어은꿈이진루다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>파커투,머더파커광주점의비밀,선물,포수장덕팔,한림축산</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>동창회,이상한하루,r003,동물병원,5010</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>구둣방손님,밴드의탄생,밴탄,주마등,칠칠77,엠m</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>도레미용실,전국일이삼,타겟,target,사건의재구성</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>집으로가자야호!,두목이스케이프,정육각형</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>레디,ready,도굴왕,액션,action,사라진보물2056,잭,jack</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>홈그라운드,home ground,선택받은자,하,ha</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>난그저여행만했을뿐인데,gasa,g.a.s.a.,가사,파커랜드,아틀라스,atlas</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>파커:끝없는이야기,전기:사라진아이들,5dh game,심신무역</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>판타스트릭 1호점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>판타스트릭 2호점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>판타스트릭 TGC</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2621,7 +2850,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2639,8 +2868,14 @@
     <xf numFmtId="20" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2958,14 +3193,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D839462D-4719-40BB-8925-C1B9F93734CF}">
-  <dimension ref="A1:H199"/>
+  <dimension ref="A1:I219"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="2"/>
     <col min="2" max="2" width="48.5" style="2" customWidth="1"/>
     <col min="3" max="4" width="9" style="2"/>
     <col min="5" max="5" width="85.875" style="2" customWidth="1"/>
-    <col min="6" max="16384" width="9" style="2"/>
+    <col min="6" max="7" width="9" style="2"/>
+    <col min="8" max="8" width="62.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
@@ -4022,7 +4259,7 @@
       <c r="F46" s="3">
         <v>1</v>
       </c>
-      <c r="H46" s="8" t="s">
+      <c r="H46" s="9" t="s">
         <v>675</v>
       </c>
     </row>
@@ -4042,9 +4279,9 @@
         <v>1</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>728</v>
-      </c>
-      <c r="H47" s="8" t="s">
+        <v>726</v>
+      </c>
+      <c r="H47" s="9" t="s">
         <v>674</v>
       </c>
     </row>
@@ -5071,7 +5308,7 @@
         <v>0</v>
       </c>
       <c r="G91" s="1"/>
-      <c r="H91" s="8" t="s">
+      <c r="H91" s="9" t="s">
         <v>652</v>
       </c>
     </row>
@@ -5167,7 +5404,7 @@
         <v>0</v>
       </c>
       <c r="G95" s="1"/>
-      <c r="H95" s="8" t="s">
+      <c r="H95" s="9" t="s">
         <v>652</v>
       </c>
     </row>
@@ -5191,7 +5428,7 @@
         <v>0</v>
       </c>
       <c r="G96" s="1"/>
-      <c r="H96" s="8" t="s">
+      <c r="H96" s="9" t="s">
         <v>652</v>
       </c>
     </row>
@@ -5263,7 +5500,7 @@
         <v>0</v>
       </c>
       <c r="G99" s="1"/>
-      <c r="H99" s="8" t="s">
+      <c r="H99" s="9" t="s">
         <v>652</v>
       </c>
     </row>
@@ -5503,7 +5740,7 @@
         <v>0</v>
       </c>
       <c r="G109" s="1"/>
-      <c r="H109" s="8" t="s">
+      <c r="H109" s="9" t="s">
         <v>651</v>
       </c>
     </row>
@@ -5814,7 +6051,7 @@
       <c r="F124" s="2">
         <v>0</v>
       </c>
-      <c r="H124" s="8" t="s">
+      <c r="H124" s="9" t="s">
         <v>535</v>
       </c>
     </row>
@@ -6453,7 +6690,7 @@
         <v>1</v>
       </c>
       <c r="H152" s="2" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.3">
@@ -6470,7 +6707,7 @@
         <v>1</v>
       </c>
       <c r="H153" s="2" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.3">
@@ -6852,7 +7089,7 @@
         <v>0</v>
       </c>
       <c r="G169" s="1"/>
-      <c r="H169" s="8" t="s">
+      <c r="H169" s="9" t="s">
         <v>646</v>
       </c>
     </row>
@@ -6898,7 +7135,7 @@
       <c r="G171" s="2" t="s">
         <v>679</v>
       </c>
-      <c r="H171" s="8" t="s">
+      <c r="H171" s="9" t="s">
         <v>677</v>
       </c>
     </row>
@@ -7162,7 +7399,7 @@
         <v>0</v>
       </c>
       <c r="G182" s="1"/>
-      <c r="H182" s="8" t="s">
+      <c r="H182" s="9" t="s">
         <v>650</v>
       </c>
     </row>
@@ -7186,7 +7423,7 @@
         <v>0</v>
       </c>
       <c r="G183" s="1"/>
-      <c r="H183" s="8" t="s">
+      <c r="H183" s="9" t="s">
         <v>650</v>
       </c>
     </row>
@@ -7330,8 +7567,8 @@
         <v>0</v>
       </c>
       <c r="G189" s="1"/>
-      <c r="H189" s="7" t="s">
-        <v>725</v>
+      <c r="H189" s="8" t="s">
+        <v>723</v>
       </c>
     </row>
     <row r="190" spans="1:8" x14ac:dyDescent="0.3">
@@ -7406,7 +7643,7 @@
         <v>642</v>
       </c>
     </row>
-    <row r="193" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>517</v>
       </c>
@@ -7430,7 +7667,7 @@
         <v>642</v>
       </c>
     </row>
-    <row r="194" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>520</v>
       </c>
@@ -7454,7 +7691,7 @@
         <v>642</v>
       </c>
     </row>
-    <row r="195" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>519</v>
       </c>
@@ -7478,7 +7715,7 @@
         <v>642</v>
       </c>
     </row>
-    <row r="196" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>518</v>
       </c>
@@ -7502,7 +7739,7 @@
         <v>642</v>
       </c>
     </row>
-    <row r="197" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>433</v>
       </c>
@@ -7522,7 +7759,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="198" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A198" s="2" t="s">
         <v>717</v>
       </c>
@@ -7535,11 +7772,11 @@
       <c r="F198" s="3">
         <v>1</v>
       </c>
-      <c r="H198" s="8" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="199" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H198" s="10" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="199" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A199" s="2" t="s">
         <v>719</v>
       </c>
@@ -7552,8 +7789,327 @@
       <c r="F199" s="3">
         <v>1</v>
       </c>
-      <c r="H199" s="8" t="s">
-        <v>724</v>
+      <c r="H199" s="10" t="s">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="200" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A200" s="2" t="s">
+        <v>727</v>
+      </c>
+      <c r="B200" s="1" t="s">
+        <v>728</v>
+      </c>
+      <c r="C200" s="2">
+        <v>6</v>
+      </c>
+      <c r="D200" s="6">
+        <v>0</v>
+      </c>
+      <c r="E200" s="1" t="s">
+        <v>729</v>
+      </c>
+      <c r="F200" s="3">
+        <v>0</v>
+      </c>
+      <c r="H200" s="7" t="s">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="201" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A201" s="2" t="s">
+        <v>734</v>
+      </c>
+      <c r="B201" s="1" t="s">
+        <v>731</v>
+      </c>
+      <c r="C201" s="2">
+        <v>7</v>
+      </c>
+      <c r="D201" s="6">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="E201" s="1" t="s">
+        <v>732</v>
+      </c>
+      <c r="F201" s="3">
+        <v>0</v>
+      </c>
+      <c r="H201" s="7" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="202" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A202" s="2" t="s">
+        <v>735</v>
+      </c>
+      <c r="B202" s="1" t="s">
+        <v>736</v>
+      </c>
+      <c r="E202" s="1" t="s">
+        <v>764</v>
+      </c>
+      <c r="F202" s="3">
+        <v>1</v>
+      </c>
+      <c r="H202" s="2" t="s">
+        <v>765</v>
+      </c>
+      <c r="I202" s="2" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="203" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A203" s="2" t="s">
+        <v>737</v>
+      </c>
+      <c r="B203" s="1" t="s">
+        <v>738</v>
+      </c>
+      <c r="E203" s="1" t="s">
+        <v>770</v>
+      </c>
+      <c r="F203" s="3">
+        <v>1</v>
+      </c>
+      <c r="H203" s="2" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="204" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A204" s="2" t="s">
+        <v>739</v>
+      </c>
+      <c r="B204" s="1" t="s">
+        <v>740</v>
+      </c>
+      <c r="E204" s="1" t="s">
+        <v>771</v>
+      </c>
+      <c r="F204" s="3">
+        <v>1</v>
+      </c>
+      <c r="H204" s="2" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="205" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A205" s="2" t="s">
+        <v>741</v>
+      </c>
+      <c r="B205" s="1" t="s">
+        <v>742</v>
+      </c>
+      <c r="E205" s="1" t="s">
+        <v>772</v>
+      </c>
+      <c r="F205" s="3">
+        <v>1</v>
+      </c>
+      <c r="H205" s="2" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="206" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A206" s="2" t="s">
+        <v>745</v>
+      </c>
+      <c r="B206" s="1" t="s">
+        <v>743</v>
+      </c>
+      <c r="E206" s="1" t="s">
+        <v>773</v>
+      </c>
+      <c r="F206" s="3">
+        <v>1</v>
+      </c>
+      <c r="H206" s="2" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="207" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A207" s="2" t="s">
+        <v>744</v>
+      </c>
+      <c r="B207" s="1" t="s">
+        <v>746</v>
+      </c>
+      <c r="E207" s="1" t="s">
+        <v>774</v>
+      </c>
+      <c r="F207" s="3">
+        <v>1</v>
+      </c>
+      <c r="H207" s="2" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="208" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A208" s="2" t="s">
+        <v>747</v>
+      </c>
+      <c r="B208" s="1" t="s">
+        <v>748</v>
+      </c>
+      <c r="E208" s="1" t="s">
+        <v>775</v>
+      </c>
+      <c r="F208" s="3">
+        <v>1</v>
+      </c>
+      <c r="H208" s="2" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="209" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A209" s="2" t="s">
+        <v>749</v>
+      </c>
+      <c r="B209" s="1" t="s">
+        <v>750</v>
+      </c>
+      <c r="E209" s="1" t="s">
+        <v>776</v>
+      </c>
+      <c r="F209" s="3">
+        <v>1</v>
+      </c>
+      <c r="H209" s="2" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="210" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A210" s="2" t="s">
+        <v>751</v>
+      </c>
+      <c r="B210" s="1" t="s">
+        <v>752</v>
+      </c>
+      <c r="E210" s="1" t="s">
+        <v>777</v>
+      </c>
+      <c r="F210" s="3">
+        <v>1</v>
+      </c>
+      <c r="H210" s="2" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="211" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A211" s="2" t="s">
+        <v>753</v>
+      </c>
+      <c r="B211" s="1" t="s">
+        <v>754</v>
+      </c>
+      <c r="E211" s="1" t="s">
+        <v>778</v>
+      </c>
+      <c r="F211" s="3">
+        <v>1</v>
+      </c>
+      <c r="H211" s="2" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="212" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A212" s="2" t="s">
+        <v>755</v>
+      </c>
+      <c r="B212" s="1" t="s">
+        <v>756</v>
+      </c>
+      <c r="E212" s="1" t="s">
+        <v>779</v>
+      </c>
+      <c r="F212" s="3">
+        <v>1</v>
+      </c>
+      <c r="H212" s="2" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="213" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A213" s="2" t="s">
+        <v>757</v>
+      </c>
+      <c r="B213" s="1" t="s">
+        <v>758</v>
+      </c>
+      <c r="E213" s="1" t="s">
+        <v>780</v>
+      </c>
+      <c r="F213" s="3">
+        <v>1</v>
+      </c>
+      <c r="H213" s="2" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="214" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A214" s="2" t="s">
+        <v>759</v>
+      </c>
+      <c r="B214" s="1" t="s">
+        <v>730</v>
+      </c>
+      <c r="E214" s="1" t="s">
+        <v>781</v>
+      </c>
+      <c r="F214" s="3">
+        <v>1</v>
+      </c>
+      <c r="H214" s="2" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="215" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A215" s="2" t="s">
+        <v>760</v>
+      </c>
+      <c r="B215" s="1" t="s">
+        <v>761</v>
+      </c>
+      <c r="E215" s="1" t="s">
+        <v>782</v>
+      </c>
+      <c r="F215" s="3">
+        <v>1</v>
+      </c>
+      <c r="H215" s="2" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="216" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A216" s="2" t="s">
+        <v>762</v>
+      </c>
+      <c r="B216" s="1" t="s">
+        <v>763</v>
+      </c>
+      <c r="E216" s="1" t="s">
+        <v>783</v>
+      </c>
+      <c r="F216" s="3">
+        <v>1</v>
+      </c>
+      <c r="H216" s="2" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="217" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B217" s="1" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="218" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B218" s="1" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="219" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B219" s="1" t="s">
+        <v>786</v>
       </c>
     </row>
   </sheetData>
@@ -7563,8 +8119,12 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="H189" r:id="rId1" xr:uid="{08510EB6-59FE-461F-9934-59900452DB70}"/>
+    <hyperlink ref="H201" r:id="rId2" xr:uid="{092C464B-EEF0-45C5-9E7F-9E5BB1389ECD}"/>
+    <hyperlink ref="H200" r:id="rId3" xr:uid="{D8D98BE9-F998-4931-BC78-1FA8DBB2DF8D}"/>
+    <hyperlink ref="H199" r:id="rId4" xr:uid="{3BEBF5F8-81B1-4909-98FA-8DDD635C8EA6}"/>
+    <hyperlink ref="H198" r:id="rId5" xr:uid="{65D202DC-0DAE-445A-B96C-C36AAC898769}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId6"/>
 </worksheet>
 </file>
--- a/stores.xlsx
+++ b/stores.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\YUMIN\Desktop\B0KT2A_RSVN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{02CBCB94-CD67-4BA8-B36B-862CC74CEE53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{EEB83404-098C-49C5-95E1-ED84C0BE242F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{ABFC3117-FCCB-4FF3-804A-FE19451A2004}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{ABFC3117-FCCB-4FF3-804A-FE19451A2004}"/>
   </bookViews>
   <sheets>
     <sheet name="stores" sheetId="2" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="871" uniqueCount="787">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="870" uniqueCount="785">
   <si>
     <t>룸익스케이프 WHITE</t>
   </si>
@@ -1906,885 +1906,871 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>https://studioesc.co.kr/</t>
+  </si>
+  <si>
+    <t>https://naver.me/FtThdKdO</t>
+  </si>
+  <si>
+    <t>https://naver.me/F0z6ANR6</t>
+  </si>
+  <si>
+    <t>https://xn--bb0b44mb8pfwi.kr/</t>
+  </si>
+  <si>
+    <t>https://naver.me/xNLIbPmw</t>
+  </si>
+  <si>
+    <t>https://naver.me/G4GjeB1L</t>
+  </si>
+  <si>
+    <t>http://dreampicnicescape.com/</t>
+  </si>
+  <si>
+    <t>https://nabijam.com/</t>
+  </si>
+  <si>
+    <t>https://xn--910bj3tlmfz4e.com/</t>
+  </si>
+  <si>
+    <t>https://naver.me/5fIpux7C</t>
+  </si>
+  <si>
+    <t>https://naver.me/FDnPXiO0</t>
+  </si>
+  <si>
+    <t>https://naver.me/GrmFdTpH</t>
+  </si>
+  <si>
+    <t>https://naver.me/FBe2Fubv</t>
+  </si>
+  <si>
+    <t>https://naver.me/xVGl5GCX</t>
+  </si>
+  <si>
+    <t>https://naver.me/FCA0aZUK</t>
+  </si>
+  <si>
+    <t>https://naver.me/G58gERgp</t>
+  </si>
+  <si>
+    <t>https://naver.me/xhzxnFCz</t>
+  </si>
+  <si>
+    <t>https://diaegg.com/</t>
+  </si>
+  <si>
+    <t>https://www.dpsnnn.com/</t>
+  </si>
+  <si>
+    <t>https://dpsnnn-s.imweb.me/</t>
+  </si>
+  <si>
+    <t>https://naver.me/xhlW1KP1</t>
+  </si>
+  <si>
+    <t>https://naver.me/xa5Rl2IV</t>
+  </si>
+  <si>
+    <t>https://naver.me/Fw7311EP</t>
+  </si>
+  <si>
+    <t>https://naver.me/F9N5tI0a</t>
+  </si>
+  <si>
+    <t>https://naver.me/5UEyu4kt</t>
+  </si>
+  <si>
+    <t>https://naver.me/5UEkbVmh</t>
+  </si>
+  <si>
+    <t>https://naver.me/5YFAZ1Zd</t>
+  </si>
+  <si>
+    <t>https://naver.me/Gxk1Gtcb</t>
+  </si>
+  <si>
+    <t>https://naver.me/xtgpdbnY</t>
+  </si>
+  <si>
+    <t>https://doloescape.co.kr/</t>
+  </si>
+  <si>
+    <t>https://doomescape.com/</t>
+  </si>
+  <si>
+    <t>https://naver.me/FBe2kT4H</t>
+  </si>
+  <si>
+    <t>https://deepthinker.co.kr/</t>
+  </si>
+  <si>
+    <t>https://naver.me/5D8tUCV4</t>
+  </si>
+  <si>
+    <t>https://ledasquare.com/</t>
+  </si>
+  <si>
+    <t>https://www.roomlescape.com/</t>
+  </si>
+  <si>
+    <t>https://naver.me/F2ZkG0hQ</t>
+  </si>
+  <si>
+    <t>https://naver.me/5T4A8qTG</t>
+  </si>
+  <si>
+    <t>https://naver.me/5PVFo2un</t>
+  </si>
+  <si>
+    <t>https://naver.me/GTnuWDRM</t>
+  </si>
+  <si>
+    <t>https://naver.me/xrSQmE4m</t>
+  </si>
+  <si>
+    <t>https://naver.me/5bVsnofH</t>
+  </si>
+  <si>
+    <t>https://naver.me/xKEV9xUN</t>
+  </si>
+  <si>
+    <t>https://naver.me/x4GumZ1y</t>
+  </si>
+  <si>
+    <t>https://naver.me/5huXHZbj</t>
+  </si>
+  <si>
+    <t>https://naver.me/GzEYV9W9</t>
+  </si>
+  <si>
+    <t>https://naver.me/xcnUjHM7</t>
+  </si>
+  <si>
+    <t>https://naver.me/Gq84QBmG</t>
+  </si>
+  <si>
+    <t>https://naver.me/FlZnhH8u</t>
+  </si>
+  <si>
+    <t>https://naver.me/5hu6ub84</t>
+  </si>
+  <si>
+    <t>https://naver.me/5S9Qurwl</t>
+  </si>
+  <si>
+    <t>https://naver.me/FXwGCxVE</t>
+  </si>
+  <si>
+    <t>https://naver.me/5xjpArFx</t>
+  </si>
+  <si>
+    <t>https://naver.me/GbD3DUKL</t>
+  </si>
+  <si>
+    <t>https://naver.me/FRLvSLdJ</t>
+  </si>
+  <si>
+    <t>https://naver.me/5FmSgFOM</t>
+  </si>
+  <si>
+    <t>https://naver.me/Gip4S99q</t>
+  </si>
+  <si>
+    <t>https://naver.me/FwjwOcMi</t>
+  </si>
+  <si>
+    <t>https://naver.me/FV7VxgkU</t>
+  </si>
+  <si>
+    <t>https://naver.me/Fr7BJBEp</t>
+  </si>
+  <si>
+    <t>https://naver.me/xcn4g3Tb</t>
+  </si>
+  <si>
+    <t>https://naver.me/53lJii2a</t>
+  </si>
+  <si>
+    <t>https://xn--h32b25mu4dba377gzscs2k.com/</t>
+  </si>
+  <si>
+    <t>https://www.portraiteller.com/</t>
+  </si>
+  <si>
+    <t>https://naver.me/5LHs4CxM</t>
+  </si>
+  <si>
+    <t>https://busted.kr/</t>
+  </si>
+  <si>
+    <t>https://xdungeon.net/</t>
+  </si>
+  <si>
+    <t>https://xn--z92b74ha268d.com/</t>
+  </si>
+  <si>
+    <t>https://naver.me/5YSvb8vM</t>
+  </si>
+  <si>
+    <t>https://showroom404.com/</t>
+  </si>
+  <si>
+    <t>https://speakeasyescape.co.kr/</t>
+  </si>
+  <si>
+    <t>http://www.signescape.com/</t>
+  </si>
+  <si>
+    <t>https://naver.me/GQ1MvYQo</t>
+  </si>
+  <si>
+    <t>https://naver.me/xDJhQDFm</t>
+  </si>
+  <si>
+    <t>https://oasismuseum.com</t>
+  </si>
+  <si>
+    <t>https://eroom8.co.kr/</t>
+  </si>
+  <si>
+    <t>https://naver.me/5Eninabc</t>
+  </si>
+  <si>
+    <t>http://www.escapers.co.kr/</t>
+  </si>
+  <si>
+    <t>https://naver.me/57VZ2oRv</t>
+  </si>
+  <si>
+    <t>https://naver.me/5yPJqzhk</t>
+  </si>
+  <si>
+    <t>&lt;a href=https://zerogangnam.com/</t>
+  </si>
+  <si>
+    <t>https://zeroesc.com</t>
+  </si>
+  <si>
+    <t>http://zeroworldesc.co.kr/</t>
+  </si>
+  <si>
+    <t>https://zerohongdae.com/</t>
+  </si>
+  <si>
+    <t>https://zerolotteworld.com</t>
+  </si>
+  <si>
+    <t>https://www.xn--2e0b040a4xj.com/</t>
+  </si>
+  <si>
+    <t>https://naver.me/5dAKHysP</t>
+  </si>
+  <si>
+    <t>https://naver.me/5owEKRF1</t>
+  </si>
+  <si>
+    <t>http://www.code-escape-garosu.com/</t>
+  </si>
+  <si>
+    <t>http://www.code-escape-ms.com/</t>
+  </si>
+  <si>
+    <t>http://code-k.co.kr/</t>
+  </si>
+  <si>
+    <t>https://question-mark.co.kr/</t>
+  </si>
+  <si>
+    <t>https://clevertown.co.kr/</t>
+  </si>
+  <si>
+    <t>https://www.keyescape.com</t>
+  </si>
+  <si>
+    <t>https://teraspace.co.kr/</t>
+  </si>
+  <si>
+    <t>https://www.rabbitholeescape.co.kr/</t>
+  </si>
+  <si>
+    <t>https://naver.me/5CFZW3oM</t>
+  </si>
+  <si>
+    <t>https://point-nine.com/</t>
+  </si>
+  <si>
+    <t>https://thefrank.co.kr/</t>
+  </si>
+  <si>
+    <t>https://naver.me/5Q37ULvz</t>
+  </si>
+  <si>
+    <t>https://naver.me/5bVswA91</t>
+  </si>
+  <si>
+    <t>https://naver.me/xmxzvAmq</t>
+  </si>
+  <si>
+    <t>https://naver.me/5qDjHU39</t>
+  </si>
+  <si>
+    <t>https://naver.me/G1wJC8Ra</t>
+  </si>
+  <si>
+    <t>https://naver.me/GalJsgzw</t>
+  </si>
+  <si>
+    <t>https://happyanding.co.kr/</t>
+  </si>
+  <si>
+    <t>http://xn--jj0b998aq3cptw.com/</t>
+  </si>
+  <si>
+    <t>https://naver.me/GQ1lYd0z</t>
+  </si>
+  <si>
+    <t>https://naver.me/F16XN84H</t>
+  </si>
+  <si>
+    <t>https://naver.me/5mIHh0h3</t>
+  </si>
+  <si>
+    <t>https://www.master-key.co.kr/'</t>
+  </si>
+  <si>
+    <t>https://naver.me/xJGs1P63'</t>
+  </si>
+  <si>
+    <t>https://weyol.com/'</t>
+  </si>
+  <si>
+    <t>https://playpointlab.com/</t>
+  </si>
+  <si>
+    <t>가암성당</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>난너의보이,난너보,좌뇌우뇌연구소</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>고양학개론,캠프ING,옥순양갱,철수네 슈퍼,철수네수퍼,오메가,더 라스트 노트,MR.BANG,미스터뱅</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ecp_dj</t>
+  </si>
+  <si>
+    <t>ecp_dsr</t>
+  </si>
+  <si>
+    <t>ecp_hd1</t>
+  </si>
+  <si>
+    <t>ecp_hd2</t>
+  </si>
+  <si>
+    <t>먹루마블,이웃집또도와,이웃집또털어,두근두근러브대작전,조선피자몰,조피몰,이상한나라로출두요,두러대,두두러,이나출</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MY PRIVATE HEAVEN,마이프라이빗헤븐,BROOKLYN MY LOVE,브루클린마이러브,PLAN TO SAVE MY DEAR,플랜투세이브마이디어,마헤븐,브마럽,마프헤</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>무엇에 썼던 물건인고?,시선,아로새김</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PLAY33 건대점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>다이얼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://play33.kr/</t>
+  </si>
+  <si>
+    <t>33_kd</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ra_bp2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ra_bp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>러시아워</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>러시아워 2호점 로드맨션</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>러시아워 3호점 시네마틱</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>전생연분,녀,하루끝,미끼,빔프로젝트</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>악녀,은화기숙학원,빨간집</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://naver.me/5TQMYzbQ</t>
+  </si>
+  <si>
+    <t>https://naver.me/5HksuiTR</t>
+  </si>
+  <si>
+    <t>지난날,오드의마법사,우당탕탕치즈탈환대작전!,듀얼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://naver.me/GI3hw5ys</t>
+  </si>
+  <si>
+    <t>찬미특수진료센터,inspecto,getogeto,</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>매주 목요일 23:50 ~ 금요일 00:00 사이에&lt;br&gt;3주 뒤 수요일까지 열립니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dkdk,쇼쿠진,chaser:한마음폐공장,혼숨,hereiam,직박구리:남친탐구생활,영안실,복도끝:못다한이야기,못다恨이야기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>chaser:한마음폐공장,영안실,시크릿왕국의스캔들(완전판),혼숨:리마스터,복도끝:못다한이야기,못다恨이야기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ra_sm</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ra_sw2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ra_sw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ra_dsr2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ra_dsr</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ra_ds</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ra_eh</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ra_ay</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ra_ui</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ra_lf</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ra_wd</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cb_ch</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cb_js</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>큐브이스케이프 천호점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>큐브이스케이프 잠실점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>the cube,the maze,장기밀매 part2,stepfather,사라진천사들,piggies,마녀의꿈,aphilia,장미의비밀,피고인</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>romeo point,신데렐라,집착,마션,타이타닉,카타콤</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ra_gsw2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ra_gsw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ra_np</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ra_psm</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ra_dsra</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ra_ph</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rs_hr</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rh_rm</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rh_ct</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>he_gj2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>he_gj3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>he_gj</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gt_gj</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gt_dsr</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ft_sia</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>비트포비아 서면던전 레드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>시간의 문 대구동성로점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>d_doo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dd_dhr</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>덤앤더머 대학로점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dd_sm</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>덤앤더머 서면점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>observer,옵저버,크라임시티,crime city,love-clinic,러브클리닉,to allice,투 앨리스,blue beard,푸른수염,glamping,글램핑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>소공녀,love-clinic,러브클리닉,to allice,투 앨리스,blue beard,푸른수염,glamping,글램핑b,knock knock,낙낙,녹녹,x테마,학교괴담,기담,동전노래방,observer,옵저버,crime city,크라임시티</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://cheonho.cubeescape.co.kr/</t>
+  </si>
+  <si>
+    <t>http://jamsil.cubeescape.co.kr/</t>
+  </si>
+  <si>
+    <t>화-&gt;수 0:00&lt;BR&gt;다음주 토~다다음주 금 1주일치 오픈</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>key_el</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>키이스케이프X에버랜드 메모리카니발</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>memory of ricky,memory of poppy,memory of tony,메모리오브리키,메모리오브포피,메모리오브토니,메모리오브파피</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>머더파커 WOW 홍대점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이스케이프월드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이스케이프컴퍼니,이케컴,escape company</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://naver.me/5FEJkSkH</t>
+  </si>
+  <si>
+    <t>ecw_sw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mp_jj1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>머더파커 전주1호점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mp_jj2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>머더파커 전주2호점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mp_ys</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>머더파커 양산점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mp_jj3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>머더파커 전주3호점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>머더파커 대구1호점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mp_kd1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mp_tg1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>머더파커 건대1호점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mp_gj</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>머더파커 광주점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mp_kd2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>머더파커 건대2호점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mp_hd1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>머더파커 홍대1호점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mp_tg2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>머더파커 대구2호점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mp_js</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>머더파커 잠실점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mp_bs</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>머더파커 부산점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mpw_hd</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mpw_js</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>머더파커 WOW 잠실점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mp_is</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>머더파커 익산점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>머더파커분노의살인,내이름지배만,일주,one week</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://dumbndumber-sm.kr</t>
+  </si>
+  <si>
+    <t>http://dumbndumber.kr</t>
+  </si>
+  <si>
+    <t>https://reservation.everland.com/</t>
+  </si>
+  <si>
+    <t>스모커,new토니파커숨겨진과거,목격자들,인턴사원의크리스마스생존기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>머더파커분노의살인,엘리스사라진아이,유코사스미치밀한복수,오씨네장난감가게,언타이틀,untitle</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>제임스완벽한도피,박엠마엄마의향기,김파커끝없는복수,박마담의비밀클럽,전당포불편한거래</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pc방가는길,괴짜중딩사차원,백,파커vs파커,8585세탁소,파커대파커</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>음대출신김수학,파커4,우리꼰대진분홍,여행,꽁노리,어은꿈이진루다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>파커투,머더파커광주점의비밀,선물,포수장덕팔,한림축산</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>동창회,이상한하루,r003,동물병원,5010</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>구둣방손님,밴드의탄생,밴탄,주마등,칠칠77,엠m</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>도레미용실,전국일이삼,타겟,target,사건의재구성</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>집으로가자야호!,두목이스케이프,정육각형</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>레디,ready,도굴왕,액션,action,사라진보물2056,잭,jack</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>홈그라운드,home ground,선택받은자,하,ha</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>난그저여행만했을뿐인데,gasa,g.a.s.a.,가사,파커랜드,아틀라스,atlas</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>파커:끝없는이야기,전기:사라진아이들,5dh game,심신무역</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>판타스트릭 1호점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>판타스트릭 2호점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>판타스트릭 TGC</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://www.murderparker.com/</t>
+  </si>
+  <si>
+    <t>https://www.xphobia.net/</t>
+  </si>
+  <si>
+    <t>http://sowoojoo-escape.com/</t>
+  </si>
+  <si>
     <t>https://exodusescape.co.kr/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://studioesc.co.kr/</t>
-  </si>
-  <si>
-    <t>https://naver.me/FtThdKdO</t>
-  </si>
-  <si>
-    <t>https://naver.me/F0z6ANR6</t>
-  </si>
-  <si>
-    <t>https://xn--bb0b44mb8pfwi.kr/</t>
-  </si>
-  <si>
-    <t>https://naver.me/xNLIbPmw</t>
-  </si>
-  <si>
-    <t>https://naver.me/G4GjeB1L</t>
-  </si>
-  <si>
-    <t>http://dreampicnicescape.com/</t>
-  </si>
-  <si>
-    <t>https://nabijam.com/</t>
-  </si>
-  <si>
-    <t>https://xn--910bj3tlmfz4e.com/</t>
-  </si>
-  <si>
-    <t>https://naver.me/5fIpux7C</t>
-  </si>
-  <si>
-    <t>https://naver.me/FDnPXiO0</t>
-  </si>
-  <si>
-    <t>https://naver.me/GrmFdTpH</t>
-  </si>
-  <si>
-    <t>https://naver.me/FBe2Fubv</t>
-  </si>
-  <si>
-    <t>https://naver.me/xVGl5GCX</t>
-  </si>
-  <si>
-    <t>https://naver.me/FCA0aZUK</t>
-  </si>
-  <si>
-    <t>https://naver.me/G58gERgp</t>
-  </si>
-  <si>
-    <t>https://naver.me/xhzxnFCz</t>
-  </si>
-  <si>
-    <t>https://diaegg.com/</t>
-  </si>
-  <si>
-    <t>https://www.dpsnnn.com/</t>
-  </si>
-  <si>
-    <t>https://dpsnnn-s.imweb.me/</t>
-  </si>
-  <si>
-    <t>https://naver.me/xhlW1KP1</t>
-  </si>
-  <si>
-    <t>https://naver.me/xa5Rl2IV</t>
-  </si>
-  <si>
-    <t>https://naver.me/Fw7311EP</t>
-  </si>
-  <si>
-    <t>https://naver.me/F9N5tI0a</t>
-  </si>
-  <si>
-    <t>https://naver.me/5UEyu4kt</t>
-  </si>
-  <si>
-    <t>https://naver.me/5UEkbVmh</t>
-  </si>
-  <si>
-    <t>https://naver.me/5YFAZ1Zd</t>
-  </si>
-  <si>
-    <t>https://naver.me/Gxk1Gtcb</t>
-  </si>
-  <si>
-    <t>https://naver.me/xtgpdbnY</t>
-  </si>
-  <si>
-    <t>https://doloescape.co.kr/</t>
-  </si>
-  <si>
-    <t>https://doomescape.com/</t>
-  </si>
-  <si>
-    <t>https://naver.me/FBe2kT4H</t>
-  </si>
-  <si>
-    <t>https://deepthinker.co.kr/</t>
-  </si>
-  <si>
-    <t>https://naver.me/5D8tUCV4</t>
-  </si>
-  <si>
-    <t>https://ledasquare.com/</t>
-  </si>
-  <si>
-    <t>https://www.roomlescape.com/</t>
-  </si>
-  <si>
-    <t>https://naver.me/F2ZkG0hQ</t>
-  </si>
-  <si>
-    <t>https://naver.me/5T4A8qTG</t>
-  </si>
-  <si>
-    <t>https://naver.me/5PVFo2un</t>
-  </si>
-  <si>
-    <t>https://naver.me/GTnuWDRM</t>
-  </si>
-  <si>
-    <t>https://naver.me/xrSQmE4m</t>
-  </si>
-  <si>
-    <t>https://naver.me/5bVsnofH</t>
-  </si>
-  <si>
-    <t>https://naver.me/xKEV9xUN</t>
-  </si>
-  <si>
-    <t>https://naver.me/x4GumZ1y</t>
-  </si>
-  <si>
-    <t>https://naver.me/5huXHZbj</t>
-  </si>
-  <si>
-    <t>https://naver.me/GzEYV9W9</t>
-  </si>
-  <si>
-    <t>https://naver.me/xcnUjHM7</t>
-  </si>
-  <si>
-    <t>https://naver.me/Gq84QBmG</t>
-  </si>
-  <si>
-    <t>https://naver.me/FlZnhH8u</t>
-  </si>
-  <si>
-    <t>https://naver.me/5hu6ub84</t>
-  </si>
-  <si>
-    <t>https://naver.me/5S9Qurwl</t>
-  </si>
-  <si>
-    <t>https://naver.me/FXwGCxVE</t>
-  </si>
-  <si>
-    <t>https://naver.me/5xjpArFx</t>
-  </si>
-  <si>
-    <t>https://naver.me/GbD3DUKL</t>
-  </si>
-  <si>
-    <t>https://naver.me/FRLvSLdJ</t>
-  </si>
-  <si>
-    <t>https://naver.me/5FmSgFOM</t>
-  </si>
-  <si>
-    <t>https://naver.me/Gip4S99q</t>
-  </si>
-  <si>
-    <t>https://naver.me/FwjwOcMi</t>
-  </si>
-  <si>
-    <t>https://naver.me/FV7VxgkU</t>
-  </si>
-  <si>
-    <t>https://naver.me/Fr7BJBEp</t>
-  </si>
-  <si>
-    <t>https://naver.me/xcn4g3Tb</t>
-  </si>
-  <si>
-    <t>https://naver.me/53lJii2a</t>
-  </si>
-  <si>
-    <t>https://xn--h32b25mu4dba377gzscs2k.com/</t>
-  </si>
-  <si>
-    <t>https://www.portraiteller.com/</t>
-  </si>
-  <si>
-    <t>https://naver.me/5LHs4CxM</t>
-  </si>
-  <si>
-    <t>https://busted.kr/</t>
-  </si>
-  <si>
-    <t>https://xdungeon.net/</t>
-  </si>
-  <si>
-    <t>https://xn--z92b74ha268d.com/</t>
-  </si>
-  <si>
-    <t>https://naver.me/5YSvb8vM</t>
-  </si>
-  <si>
-    <t>https://showroom404.com/</t>
-  </si>
-  <si>
-    <t>https://speakeasyescape.co.kr/</t>
-  </si>
-  <si>
-    <t>http://www.signescape.com/</t>
-  </si>
-  <si>
-    <t>https://naver.me/GQ1MvYQo</t>
-  </si>
-  <si>
-    <t>https://naver.me/xDJhQDFm</t>
-  </si>
-  <si>
-    <t>https://oasismuseum.com</t>
-  </si>
-  <si>
-    <t>https://eroom8.co.kr/</t>
-  </si>
-  <si>
-    <t>https://naver.me/5Eninabc</t>
-  </si>
-  <si>
-    <t>http://www.escapers.co.kr/</t>
-  </si>
-  <si>
-    <t>https://naver.me/57VZ2oRv</t>
-  </si>
-  <si>
-    <t>https://naver.me/5yPJqzhk</t>
-  </si>
-  <si>
-    <t>&lt;a href=https://zerogangnam.com/</t>
-  </si>
-  <si>
-    <t>https://zeroesc.com</t>
-  </si>
-  <si>
-    <t>http://zeroworldesc.co.kr/</t>
-  </si>
-  <si>
-    <t>https://zerohongdae.com/</t>
-  </si>
-  <si>
-    <t>https://zerolotteworld.com</t>
-  </si>
-  <si>
-    <t>https://www.xn--2e0b040a4xj.com/</t>
-  </si>
-  <si>
-    <t>https://naver.me/5dAKHysP</t>
-  </si>
-  <si>
-    <t>https://naver.me/5owEKRF1</t>
-  </si>
-  <si>
-    <t>http://www.code-escape-garosu.com/</t>
-  </si>
-  <si>
-    <t>http://www.code-escape-ms.com/</t>
-  </si>
-  <si>
-    <t>http://code-k.co.kr/</t>
-  </si>
-  <si>
-    <t>https://question-mark.co.kr/</t>
-  </si>
-  <si>
-    <t>https://clevertown.co.kr/</t>
-  </si>
-  <si>
-    <t>https://www.keyescape.com</t>
-  </si>
-  <si>
-    <t>https://teraspace.co.kr/</t>
-  </si>
-  <si>
-    <t>https://www.rabbitholeescape.co.kr/</t>
-  </si>
-  <si>
-    <t>https://naver.me/5CFZW3oM</t>
-  </si>
-  <si>
-    <t>https://point-nine.com/</t>
-  </si>
-  <si>
-    <t>https://thefrank.co.kr/</t>
-  </si>
-  <si>
-    <t>https://naver.me/5Q37ULvz</t>
-  </si>
-  <si>
-    <t>https://naver.me/5bVswA91</t>
-  </si>
-  <si>
-    <t>https://naver.me/xmxzvAmq</t>
-  </si>
-  <si>
-    <t>https://naver.me/5qDjHU39</t>
-  </si>
-  <si>
-    <t>https://naver.me/G1wJC8Ra</t>
-  </si>
-  <si>
-    <t>https://naver.me/GalJsgzw</t>
-  </si>
-  <si>
-    <t>https://happyanding.co.kr/</t>
-  </si>
-  <si>
-    <t>http://xn--jj0b998aq3cptw.com/</t>
-  </si>
-  <si>
-    <t>https://naver.me/GQ1lYd0z</t>
-  </si>
-  <si>
-    <t>https://naver.me/F16XN84H</t>
-  </si>
-  <si>
-    <t>https://naver.me/5mIHh0h3</t>
   </si>
   <si>
     <t>https://www.master-key.co.kr/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.master-key.co.kr/'</t>
-  </si>
-  <si>
-    <t>https://naver.me/xJGs1P63'</t>
-  </si>
-  <si>
-    <t>https://weyol.com/'</t>
-  </si>
-  <si>
-    <t>https://playpointlab.com/</t>
-  </si>
-  <si>
-    <t>http://sowoojoo-escape.com/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.xphobia.net/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>가암성당</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>난너의보이,난너보,좌뇌우뇌연구소</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>고양학개론,캠프ING,옥순양갱,철수네 슈퍼,철수네수퍼,오메가,더 라스트 노트,MR.BANG,미스터뱅</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ecp_dj</t>
-  </si>
-  <si>
-    <t>ecp_dsr</t>
-  </si>
-  <si>
-    <t>ecp_hd1</t>
-  </si>
-  <si>
-    <t>ecp_hd2</t>
-  </si>
-  <si>
-    <t>먹루마블,이웃집또도와,이웃집또털어,두근두근러브대작전,조선피자몰,조피몰,이상한나라로출두요,두러대,두두러,이나출</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>MY PRIVATE HEAVEN,마이프라이빗헤븐,BROOKLYN MY LOVE,브루클린마이러브,PLAN TO SAVE MY DEAR,플랜투세이브마이디어,마헤븐,브마럽,마프헤</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>무엇에 썼던 물건인고?,시선,아로새김</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>PLAY33 건대점</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>다이얼</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://play33.kr/</t>
-  </si>
-  <si>
-    <t>33_kd</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ra_bp2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ra_bp</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>러시아워</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>러시아워 2호점 로드맨션</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>러시아워 3호점 시네마틱</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>전생연분,녀,하루끝,미끼,빔프로젝트</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>악녀,은화기숙학원,빨간집</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://naver.me/5TQMYzbQ</t>
-  </si>
-  <si>
-    <t>https://naver.me/5HksuiTR</t>
-  </si>
-  <si>
-    <t>지난날,오드의마법사,우당탕탕치즈탈환대작전!,듀얼</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://naver.me/GI3hw5ys</t>
-  </si>
-  <si>
-    <t>찬미특수진료센터,inspecto,getogeto,</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>매주 목요일 23:50 ~ 금요일 00:00 사이에&lt;br&gt;3주 뒤 수요일까지 열립니다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>dkdk,쇼쿠진,chaser:한마음폐공장,혼숨,hereiam,직박구리:남친탐구생활,영안실,복도끝:못다한이야기,못다恨이야기</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>chaser:한마음폐공장,영안실,시크릿왕국의스캔들(완전판),혼숨:리마스터,복도끝:못다한이야기,못다恨이야기</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ra_sm</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ra_sw2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ra_sw</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ra_dsr2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ra_dsr</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ra_ds</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ra_eh</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ra_ay</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ra_ui</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ra_lf</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ra_wd</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>cb_ch</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>cb_js</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>큐브이스케이프 천호점</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>큐브이스케이프 잠실점</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>the cube,the maze,장기밀매 part2,stepfather,사라진천사들,piggies,마녀의꿈,aphilia,장미의비밀,피고인</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>romeo point,신데렐라,집착,마션,타이타닉,카타콤</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ra_gsw2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ra_gsw</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ra_np</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ra_psm</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ra_dsra</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ra_ph</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>rs_hr</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>rh_rm</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>rh_ct</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>he_gj2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>he_gj3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>he_gj</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>gt_gj</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>gt_dsr</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ft_sia</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>비트포비아 서면던전 레드</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>시간의 문 대구동성로점</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>d_doo</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>dd_dhr</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>덤앤더머 대학로점</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>dd_sm</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>덤앤더머 서면점</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>observer,옵저버,크라임시티,crime city,love-clinic,러브클리닉,to allice,투 앨리스,blue beard,푸른수염,glamping,글램핑</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>소공녀,love-clinic,러브클리닉,to allice,투 앨리스,blue beard,푸른수염,glamping,글램핑b,knock knock,낙낙,녹녹,x테마,학교괴담,기담,동전노래방,observer,옵저버,crime city,크라임시티</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://playpointlab.com/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>http://cheonho.cubeescape.co.kr/</t>
-  </si>
-  <si>
-    <t>http://jamsil.cubeescape.co.kr/</t>
-  </si>
-  <si>
-    <t>화-&gt;수 0:00&lt;BR&gt;다음주 토~다다음주 금 1주일치 오픈</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>key_el</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>키이스케이프X에버랜드 메모리카니발</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>memory of ricky,memory of poppy,memory of tony,메모리오브리키,메모리오브포피,메모리오브토니,메모리오브파피</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>머더파커 WOW 홍대점</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>이스케이프월드</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>이스케이프컴퍼니,이케컴,escape company</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://naver.me/5FEJkSkH</t>
-  </si>
-  <si>
-    <t>ecw_sw</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>mp_jj1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>머더파커 전주1호점</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>mp_jj2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>머더파커 전주2호점</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>mp_ys</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>머더파커 양산점</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>mp_jj3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>머더파커 전주3호점</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>머더파커 대구1호점</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>mp_kd1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>mp_tg1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>머더파커 건대1호점</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>mp_gj</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>머더파커 광주점</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>mp_kd2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>머더파커 건대2호점</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>mp_hd1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>머더파커 홍대1호점</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>mp_tg2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>머더파커 대구2호점</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>mp_js</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>머더파커 잠실점</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>mp_bs</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>머더파커 부산점</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>mpw_hd</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>mpw_js</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>머더파커 WOW 잠실점</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>mp_is</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>머더파커 익산점</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>머더파커분노의살인,내이름지배만,일주,one week</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>http://murderparker</t>
-  </si>
-  <si>
-    <t>com/</t>
-  </si>
-  <si>
-    <t>http://dumbndumber-sm.kr</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>http://dumbndumber.kr</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://reservation.everland.com/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>스모커,new토니파커숨겨진과거,목격자들,인턴사원의크리스마스생존기</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>머더파커분노의살인,엘리스사라진아이,유코사스미치밀한복수,오씨네장난감가게,언타이틀,untitle</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>제임스완벽한도피,박엠마엄마의향기,김파커끝없는복수,박마담의비밀클럽,전당포불편한거래</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>pc방가는길,괴짜중딩사차원,백,파커vs파커,8585세탁소,파커대파커</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>음대출신김수학,파커4,우리꼰대진분홍,여행,꽁노리,어은꿈이진루다</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>파커투,머더파커광주점의비밀,선물,포수장덕팔,한림축산</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>동창회,이상한하루,r003,동물병원,5010</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>구둣방손님,밴드의탄생,밴탄,주마등,칠칠77,엠m</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>도레미용실,전국일이삼,타겟,target,사건의재구성</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>집으로가자야호!,두목이스케이프,정육각형</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>레디,ready,도굴왕,액션,action,사라진보물2056,잭,jack</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>홈그라운드,home ground,선택받은자,하,ha</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>난그저여행만했을뿐인데,gasa,g.a.s.a.,가사,파커랜드,아틀라스,atlas</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>파커:끝없는이야기,전기:사라진아이들,5dh game,심신무역</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>판타스트릭 1호점</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>판타스트릭 2호점</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>판타스트릭 TGC</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -3193,14 +3179,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D839462D-4719-40BB-8925-C1B9F93734CF}">
-  <dimension ref="A1:I219"/>
+  <dimension ref="A1:H219"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="2"/>
     <col min="2" max="2" width="48.5" style="2" customWidth="1"/>
     <col min="3" max="4" width="9" style="2"/>
     <col min="5" max="5" width="85.875" style="2" customWidth="1"/>
-    <col min="6" max="7" width="9" style="2"/>
+    <col min="6" max="6" width="9" style="2"/>
+    <col min="7" max="7" width="5.75" style="2" customWidth="1"/>
     <col min="8" max="8" width="62.75" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="16384" width="9" style="2"/>
   </cols>
@@ -3233,10 +3220,10 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>666</v>
+        <v>662</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>663</v>
+        <v>659</v>
       </c>
       <c r="C2" s="2">
         <v>7</v>
@@ -3245,13 +3232,13 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>664</v>
+        <v>660</v>
       </c>
       <c r="F2" s="2">
         <v>0</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>665</v>
+        <v>661</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -3275,7 +3262,7 @@
       </c>
       <c r="G3" s="1"/>
       <c r="H3" s="1" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
@@ -3299,7 +3286,7 @@
       </c>
       <c r="G4" s="1"/>
       <c r="H4" s="1" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
@@ -3319,7 +3306,7 @@
       </c>
       <c r="G5" s="1"/>
       <c r="H5" s="1" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
@@ -3343,7 +3330,7 @@
       </c>
       <c r="G6" s="1"/>
       <c r="H6" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
@@ -3367,7 +3354,7 @@
       </c>
       <c r="G7" s="1"/>
       <c r="H7" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
@@ -3391,7 +3378,7 @@
       </c>
       <c r="G8" s="1"/>
       <c r="H8" s="1" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
@@ -3415,7 +3402,7 @@
       </c>
       <c r="G9" s="1"/>
       <c r="H9" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
@@ -3439,7 +3426,7 @@
       </c>
       <c r="G10" s="1"/>
       <c r="H10" s="1" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
@@ -3463,7 +3450,7 @@
       </c>
       <c r="G11" s="1"/>
       <c r="H11" s="1" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
@@ -3487,7 +3474,7 @@
       </c>
       <c r="G12" s="1"/>
       <c r="H12" s="1" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
@@ -3511,7 +3498,7 @@
       </c>
       <c r="G13" s="1"/>
       <c r="H13" s="1" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
@@ -3535,7 +3522,7 @@
       </c>
       <c r="G14" s="1"/>
       <c r="H14" s="1" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
@@ -3559,7 +3546,7 @@
       </c>
       <c r="G15" s="1"/>
       <c r="H15" s="1" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
@@ -3583,7 +3570,7 @@
       </c>
       <c r="G16" s="1"/>
       <c r="H16" s="1" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
@@ -3607,7 +3594,7 @@
       </c>
       <c r="G17" s="1"/>
       <c r="H17" s="1" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
@@ -3631,7 +3618,7 @@
       </c>
       <c r="G18" s="1"/>
       <c r="H18" s="1" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
@@ -3655,7 +3642,7 @@
       </c>
       <c r="G19" s="1"/>
       <c r="H19" s="1" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
@@ -3679,7 +3666,7 @@
       </c>
       <c r="G20" s="1"/>
       <c r="H20" s="1" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
@@ -3703,7 +3690,7 @@
       </c>
       <c r="G21" s="1"/>
       <c r="H21" s="1" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
@@ -3727,7 +3714,7 @@
       </c>
       <c r="G22" s="1"/>
       <c r="H22" s="1" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
@@ -3751,7 +3738,7 @@
       </c>
       <c r="G23" s="1"/>
       <c r="H23" s="1" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
@@ -3774,7 +3761,7 @@
         <v>0</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
@@ -3797,7 +3784,7 @@
         <v>0</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
@@ -3821,7 +3808,7 @@
       </c>
       <c r="G26" s="1"/>
       <c r="H26" s="1" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
@@ -3845,7 +3832,7 @@
       </c>
       <c r="G27" s="1"/>
       <c r="H27" s="1" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
@@ -3869,7 +3856,7 @@
       </c>
       <c r="G28" s="1"/>
       <c r="H28" s="2" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
@@ -3907,7 +3894,7 @@
       </c>
       <c r="G30" s="1"/>
       <c r="H30" s="1" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
@@ -3927,7 +3914,7 @@
       </c>
       <c r="G31" s="1"/>
       <c r="H31" s="1" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
@@ -3951,7 +3938,7 @@
       </c>
       <c r="G32" s="1"/>
       <c r="H32" s="1" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
@@ -3975,7 +3962,7 @@
       </c>
       <c r="G33" s="1"/>
       <c r="H33" s="1" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
@@ -3999,7 +3986,7 @@
       </c>
       <c r="G34" s="1"/>
       <c r="H34" s="1" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
@@ -4019,7 +4006,7 @@
       </c>
       <c r="G35" s="1"/>
       <c r="H35" s="1" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
@@ -4039,7 +4026,7 @@
       </c>
       <c r="G36" s="1"/>
       <c r="H36" s="1" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
@@ -4063,7 +4050,7 @@
       </c>
       <c r="G37" s="1"/>
       <c r="H37" s="1" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
@@ -4080,14 +4067,14 @@
         <v>0</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="F38" s="3">
         <v>0</v>
       </c>
       <c r="G38" s="1"/>
       <c r="H38" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
@@ -4111,7 +4098,7 @@
       </c>
       <c r="G39" s="1"/>
       <c r="H39" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
@@ -4135,7 +4122,7 @@
       </c>
       <c r="G40" s="1"/>
       <c r="H40" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
@@ -4159,7 +4146,7 @@
       </c>
       <c r="G41" s="1"/>
       <c r="H41" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
@@ -4183,7 +4170,7 @@
       </c>
       <c r="G42" s="1"/>
       <c r="H42" s="1" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
@@ -4207,7 +4194,7 @@
       </c>
       <c r="G43" s="1"/>
       <c r="H43" s="1" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
@@ -4229,18 +4216,18 @@
         <v>260</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>669</v>
+        <v>665</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>672</v>
+        <v>668</v>
       </c>
       <c r="F45" s="2">
         <v>1</v>
@@ -4248,41 +4235,41 @@
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>706</v>
+        <v>702</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>670</v>
+        <v>666</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>676</v>
+        <v>672</v>
       </c>
       <c r="F46" s="3">
         <v>1</v>
       </c>
       <c r="H46" s="9" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>671</v>
+        <v>667</v>
       </c>
       <c r="C47" s="3"/>
       <c r="D47" s="6"/>
       <c r="E47" s="1" t="s">
-        <v>673</v>
+        <v>669</v>
       </c>
       <c r="F47" s="3">
         <v>1</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>726</v>
+        <v>721</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>674</v>
+        <v>670</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
@@ -4306,7 +4293,7 @@
       </c>
       <c r="G48" s="1"/>
       <c r="H48" s="1" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.3">
@@ -4330,7 +4317,7 @@
       </c>
       <c r="G49" s="1"/>
       <c r="H49" s="1" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.3">
@@ -4350,7 +4337,7 @@
       </c>
       <c r="G50" s="1"/>
       <c r="H50" s="1" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.3">
@@ -4374,7 +4361,7 @@
       </c>
       <c r="G51" s="1"/>
       <c r="H51" s="1" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.3">
@@ -4398,7 +4385,7 @@
       </c>
       <c r="G52" s="1"/>
       <c r="H52" s="2" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.3">
@@ -4422,7 +4409,7 @@
       </c>
       <c r="G53" s="1"/>
       <c r="H53" s="2" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.3">
@@ -4446,7 +4433,7 @@
       </c>
       <c r="G54" s="1"/>
       <c r="H54" s="2" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.3">
@@ -4470,7 +4457,7 @@
       </c>
       <c r="G55" s="1"/>
       <c r="H55" s="2" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.3">
@@ -4493,12 +4480,12 @@
         <v>0</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
-        <v>682</v>
+        <v>678</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>187</v>
@@ -4516,12 +4503,12 @@
         <v>0</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>270</v>
@@ -4539,12 +4526,12 @@
         <v>0</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>700</v>
+        <v>696</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>185</v>
@@ -4562,12 +4549,12 @@
         <v>0</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>685</v>
+        <v>681</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>191</v>
@@ -4585,12 +4572,12 @@
         <v>0</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
-        <v>686</v>
+        <v>682</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>189</v>
@@ -4608,12 +4595,12 @@
         <v>0</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>687</v>
+        <v>683</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>177</v>
@@ -4631,12 +4618,12 @@
         <v>0</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>688</v>
+        <v>684</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>179</v>
@@ -4654,7 +4641,7 @@
         <v>0</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.3">
@@ -4677,12 +4664,12 @@
         <v>0</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>703</v>
+        <v>699</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>193</v>
@@ -4700,12 +4687,12 @@
         <v>0</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>701</v>
+        <v>697</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>181</v>
@@ -4723,12 +4710,12 @@
         <v>0</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>702</v>
+        <v>698</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>183</v>
@@ -4746,12 +4733,12 @@
         <v>0</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
-        <v>667</v>
+        <v>663</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>199</v>
@@ -4769,12 +4756,12 @@
         <v>0</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
-        <v>668</v>
+        <v>664</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>197</v>
@@ -4792,12 +4779,12 @@
         <v>0</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
-        <v>683</v>
+        <v>679</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>175</v>
@@ -4815,12 +4802,12 @@
         <v>0</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
-        <v>684</v>
+        <v>680</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>173</v>
@@ -4838,12 +4825,12 @@
         <v>0</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>689</v>
+        <v>685</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>165</v>
@@ -4861,12 +4848,12 @@
         <v>0</v>
       </c>
       <c r="H72" s="1" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>171</v>
@@ -4884,12 +4871,12 @@
         <v>0</v>
       </c>
       <c r="H73" s="1" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>691</v>
+        <v>687</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>169</v>
@@ -4907,12 +4894,12 @@
         <v>0</v>
       </c>
       <c r="H74" s="1" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>167</v>
@@ -4930,12 +4917,12 @@
         <v>0</v>
       </c>
       <c r="H75" s="1" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>195</v>
@@ -4953,7 +4940,7 @@
         <v>0</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.3">
@@ -4977,7 +4964,7 @@
       </c>
       <c r="G77" s="1"/>
       <c r="H77" s="1" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.3">
@@ -5001,7 +4988,7 @@
       </c>
       <c r="G78" s="1"/>
       <c r="H78" s="1" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.3">
@@ -5025,7 +5012,7 @@
       </c>
       <c r="G79" s="1"/>
       <c r="H79" s="1" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.3">
@@ -5049,7 +5036,7 @@
       </c>
       <c r="G80" s="1"/>
       <c r="H80" s="1" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.3">
@@ -5073,7 +5060,7 @@
       </c>
       <c r="G81" s="1"/>
       <c r="H81" s="1" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.3">
@@ -5097,7 +5084,7 @@
       </c>
       <c r="G82" s="1"/>
       <c r="H82" s="1" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.3">
@@ -5121,7 +5108,7 @@
       </c>
       <c r="G83" s="1"/>
       <c r="H83" s="1" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.3">
@@ -5145,7 +5132,7 @@
       </c>
       <c r="G84" s="1"/>
       <c r="H84" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.3">
@@ -5169,7 +5156,7 @@
       </c>
       <c r="G85" s="1"/>
       <c r="H85" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.3">
@@ -5193,12 +5180,12 @@
       </c>
       <c r="G86" s="1"/>
       <c r="H86" s="1" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A87" s="2" t="s">
-        <v>716</v>
+        <v>712</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>307</v>
@@ -5213,7 +5200,7 @@
       </c>
       <c r="G87" s="1"/>
       <c r="H87" s="1" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.3">
@@ -5237,7 +5224,7 @@
       </c>
       <c r="G88" s="1"/>
       <c r="H88" s="1" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.3">
@@ -5261,7 +5248,7 @@
       </c>
       <c r="G89" s="1"/>
       <c r="H89" s="2" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.3">
@@ -5285,7 +5272,7 @@
       </c>
       <c r="G90" s="1"/>
       <c r="H90" s="2" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.3">
@@ -5309,7 +5296,7 @@
       </c>
       <c r="G91" s="1"/>
       <c r="H91" s="9" t="s">
-        <v>652</v>
+        <v>781</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.3">
@@ -5333,7 +5320,7 @@
       </c>
       <c r="G92" s="1"/>
       <c r="H92" s="2" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.3">
@@ -5357,7 +5344,7 @@
       </c>
       <c r="G93" s="1"/>
       <c r="H93" s="2" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.3">
@@ -5381,7 +5368,7 @@
       </c>
       <c r="G94" s="1"/>
       <c r="H94" s="2" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.3">
@@ -5405,7 +5392,7 @@
       </c>
       <c r="G95" s="1"/>
       <c r="H95" s="9" t="s">
-        <v>652</v>
+        <v>781</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.3">
@@ -5429,7 +5416,7 @@
       </c>
       <c r="G96" s="1"/>
       <c r="H96" s="9" t="s">
-        <v>652</v>
+        <v>781</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.3">
@@ -5453,7 +5440,7 @@
       </c>
       <c r="G97" s="1"/>
       <c r="H97" s="2" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.3">
@@ -5461,7 +5448,7 @@
         <v>399</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>714</v>
+        <v>710</v>
       </c>
       <c r="C98" s="3">
         <v>6</v>
@@ -5477,7 +5464,7 @@
       </c>
       <c r="G98" s="1"/>
       <c r="H98" s="2" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.3">
@@ -5501,7 +5488,7 @@
       </c>
       <c r="G99" s="1"/>
       <c r="H99" s="9" t="s">
-        <v>652</v>
+        <v>781</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.3">
@@ -5525,7 +5512,7 @@
       </c>
       <c r="G100" s="1"/>
       <c r="H100" s="2" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.3">
@@ -5549,7 +5536,7 @@
       </c>
       <c r="G101" s="1"/>
       <c r="H101" s="2" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.3">
@@ -5573,7 +5560,7 @@
       </c>
       <c r="G102" s="1"/>
       <c r="H102" s="1" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.3">
@@ -5597,7 +5584,7 @@
       </c>
       <c r="G103" s="1"/>
       <c r="H103" s="1" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.3">
@@ -5621,7 +5608,7 @@
       </c>
       <c r="G104" s="1"/>
       <c r="H104" s="1" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.3">
@@ -5645,7 +5632,7 @@
       </c>
       <c r="G105" s="1"/>
       <c r="H105" s="1" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.3">
@@ -5669,7 +5656,7 @@
       </c>
       <c r="G106" s="1"/>
       <c r="H106" s="1" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.3">
@@ -5693,7 +5680,7 @@
       </c>
       <c r="G107" s="1"/>
       <c r="H107" s="1" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.3">
@@ -5717,7 +5704,7 @@
       </c>
       <c r="G108" s="1"/>
       <c r="H108" s="1" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.3">
@@ -5741,7 +5728,7 @@
       </c>
       <c r="G109" s="1"/>
       <c r="H109" s="9" t="s">
-        <v>651</v>
+        <v>782</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.3">
@@ -5765,7 +5752,7 @@
       </c>
       <c r="G110" s="1"/>
       <c r="H110" s="1" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.3">
@@ -5789,12 +5776,12 @@
       </c>
       <c r="G111" s="1"/>
       <c r="H111" s="1" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>708</v>
+        <v>704</v>
       </c>
       <c r="B112" s="1" t="s">
         <v>525</v>
@@ -5808,7 +5795,7 @@
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>708</v>
+        <v>704</v>
       </c>
       <c r="B113" s="1" t="s">
         <v>525</v>
@@ -5820,12 +5807,12 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>709</v>
+        <v>705</v>
       </c>
       <c r="B114" s="1" t="s">
         <v>527</v>
@@ -5837,12 +5824,12 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>710</v>
+        <v>706</v>
       </c>
       <c r="B115" s="1" t="s">
         <v>523</v>
@@ -5875,12 +5862,12 @@
       </c>
       <c r="G116" s="1"/>
       <c r="H116" s="1" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="B117" s="1" t="s">
         <v>530</v>
@@ -5892,15 +5879,15 @@
         <v>0</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>680</v>
+        <v>676</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>715</v>
+        <v>711</v>
       </c>
       <c r="C118" s="2">
         <v>13</v>
@@ -5909,7 +5896,7 @@
         <v>0</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.3">
@@ -5933,7 +5920,7 @@
       </c>
       <c r="G119" s="1"/>
       <c r="H119" s="1" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.3">
@@ -5957,7 +5944,7 @@
       </c>
       <c r="G120" s="1"/>
       <c r="H120" s="1" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.3">
@@ -5981,7 +5968,7 @@
       </c>
       <c r="G121" s="1"/>
       <c r="H121" s="1" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.3">
@@ -6005,7 +5992,7 @@
       </c>
       <c r="G122" s="1"/>
       <c r="H122" s="1" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.3">
@@ -6029,7 +6016,7 @@
       </c>
       <c r="G123" s="1"/>
       <c r="H123" s="1" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.3">
@@ -6052,7 +6039,7 @@
         <v>0</v>
       </c>
       <c r="H124" s="9" t="s">
-        <v>535</v>
+        <v>783</v>
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.3">
@@ -6074,7 +6061,7 @@
         <v>263</v>
       </c>
       <c r="H125" s="2" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.3">
@@ -6096,7 +6083,7 @@
         <v>266</v>
       </c>
       <c r="H126" s="2" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.3">
@@ -6120,7 +6107,7 @@
       </c>
       <c r="G127" s="1"/>
       <c r="H127" s="1" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.3">
@@ -6144,7 +6131,7 @@
       </c>
       <c r="G128" s="1"/>
       <c r="H128" s="1" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.3">
@@ -6168,7 +6155,7 @@
       </c>
       <c r="G129" s="1"/>
       <c r="H129" s="1" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.3">
@@ -6192,12 +6179,12 @@
       </c>
       <c r="G130" s="1"/>
       <c r="H130" s="2" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A131" s="2" t="s">
-        <v>656</v>
+        <v>652</v>
       </c>
       <c r="B131" s="1" t="s">
         <v>315</v>
@@ -6216,12 +6203,12 @@
       </c>
       <c r="G131" s="1"/>
       <c r="H131" s="1" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A132" s="2" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="B132" s="1" t="s">
         <v>498</v>
@@ -6236,12 +6223,12 @@
       </c>
       <c r="G132" s="1"/>
       <c r="H132" s="1" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A133" s="2" t="s">
-        <v>658</v>
+        <v>654</v>
       </c>
       <c r="B133" s="1" t="s">
         <v>304</v>
@@ -6256,12 +6243,12 @@
       </c>
       <c r="G133" s="1"/>
       <c r="H133" s="1" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A134" s="2" t="s">
-        <v>659</v>
+        <v>655</v>
       </c>
       <c r="B134" s="1" t="s">
         <v>305</v>
@@ -6276,7 +6263,7 @@
       </c>
       <c r="G134" s="1"/>
       <c r="H134" s="1" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.3">
@@ -6293,14 +6280,14 @@
         <v>0</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>655</v>
+        <v>651</v>
       </c>
       <c r="F135" s="3">
         <v>0</v>
       </c>
       <c r="G135" s="1"/>
       <c r="H135" s="1" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.3">
@@ -6324,7 +6311,7 @@
       </c>
       <c r="G136" s="1"/>
       <c r="H136" s="2" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.3">
@@ -6348,7 +6335,7 @@
       </c>
       <c r="G137" s="1"/>
       <c r="H137" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.3">
@@ -6372,7 +6359,7 @@
       </c>
       <c r="G138" s="1"/>
       <c r="H138" s="2" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.3">
@@ -6389,7 +6376,7 @@
         <v>1</v>
       </c>
       <c r="H139" s="1" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.3">
@@ -6413,7 +6400,7 @@
       </c>
       <c r="G140" s="1"/>
       <c r="H140" s="2" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.3">
@@ -6437,7 +6424,7 @@
       </c>
       <c r="G141" s="1"/>
       <c r="H141" s="2" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.3">
@@ -6461,7 +6448,7 @@
       </c>
       <c r="G142" s="1"/>
       <c r="H142" s="1" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.3">
@@ -6485,7 +6472,7 @@
       </c>
       <c r="G143" s="1"/>
       <c r="H143" s="1" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.3">
@@ -6509,7 +6496,7 @@
       </c>
       <c r="G144" s="1"/>
       <c r="H144" s="1" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.3">
@@ -6533,7 +6520,7 @@
       </c>
       <c r="G145" s="1"/>
       <c r="H145" s="1" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.3">
@@ -6557,7 +6544,7 @@
       </c>
       <c r="G146" s="1"/>
       <c r="H146" s="2" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.3">
@@ -6581,7 +6568,7 @@
       </c>
       <c r="G147" s="1"/>
       <c r="H147" s="1" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.3">
@@ -6601,7 +6588,7 @@
       </c>
       <c r="G148" s="1"/>
       <c r="H148" s="1" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.3">
@@ -6625,7 +6612,7 @@
       </c>
       <c r="G149" s="1"/>
       <c r="H149" s="1" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.3">
@@ -6649,7 +6636,7 @@
       </c>
       <c r="G150" s="1"/>
       <c r="H150" s="1" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.3">
@@ -6673,41 +6660,41 @@
       </c>
       <c r="G151" s="1"/>
       <c r="H151" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A152" s="2" t="s">
+        <v>690</v>
+      </c>
+      <c r="B152" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="E152" s="1" t="s">
         <v>694</v>
-      </c>
-      <c r="B152" s="1" t="s">
-        <v>696</v>
-      </c>
-      <c r="E152" s="1" t="s">
-        <v>698</v>
       </c>
       <c r="F152" s="2">
         <v>1</v>
       </c>
       <c r="H152" s="2" t="s">
-        <v>725</v>
+        <v>720</v>
       </c>
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A153" s="2" t="s">
+        <v>689</v>
+      </c>
+      <c r="B153" s="1" t="s">
+        <v>691</v>
+      </c>
+      <c r="E153" s="1" t="s">
         <v>693</v>
-      </c>
-      <c r="B153" s="1" t="s">
-        <v>695</v>
-      </c>
-      <c r="E153" s="1" t="s">
-        <v>697</v>
       </c>
       <c r="F153" s="2">
         <v>1</v>
       </c>
       <c r="H153" s="2" t="s">
-        <v>724</v>
+        <v>719</v>
       </c>
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.3">
@@ -6724,14 +6711,14 @@
         <v>0</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>654</v>
+        <v>650</v>
       </c>
       <c r="F154" s="3">
         <v>0</v>
       </c>
       <c r="G154" s="1"/>
       <c r="H154" s="1" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.3">
@@ -6748,14 +6735,14 @@
         <v>0</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>653</v>
+        <v>649</v>
       </c>
       <c r="F155" s="3">
         <v>0</v>
       </c>
       <c r="G155" s="1"/>
       <c r="H155" s="1" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.3">
@@ -6779,7 +6766,7 @@
       </c>
       <c r="G156" s="1"/>
       <c r="H156" s="2" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.3">
@@ -6803,7 +6790,7 @@
       </c>
       <c r="G157" s="1"/>
       <c r="H157" s="2" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.3">
@@ -6827,7 +6814,7 @@
       </c>
       <c r="G158" s="1"/>
       <c r="H158" s="2" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.3">
@@ -6851,7 +6838,7 @@
       </c>
       <c r="G159" s="1"/>
       <c r="H159" s="2" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.3">
@@ -6875,7 +6862,7 @@
       </c>
       <c r="G160" s="1"/>
       <c r="H160" s="2" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.3">
@@ -6899,7 +6886,7 @@
       </c>
       <c r="G161" s="1"/>
       <c r="H161" s="2" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.3">
@@ -6923,7 +6910,7 @@
       </c>
       <c r="G162" s="1"/>
       <c r="H162" s="2" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.3">
@@ -6947,7 +6934,7 @@
       </c>
       <c r="G163" s="1"/>
       <c r="H163" s="2" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.3">
@@ -6971,7 +6958,7 @@
       </c>
       <c r="G164" s="1"/>
       <c r="H164" s="2" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.3">
@@ -6995,7 +6982,7 @@
       </c>
       <c r="G165" s="1"/>
       <c r="H165" s="2" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.3">
@@ -7019,7 +7006,7 @@
       </c>
       <c r="G166" s="1"/>
       <c r="H166" s="2" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.3">
@@ -7043,7 +7030,7 @@
       </c>
       <c r="G167" s="1"/>
       <c r="H167" s="2" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="168" spans="1:8" x14ac:dyDescent="0.3">
@@ -7066,7 +7053,7 @@
         <v>0</v>
       </c>
       <c r="H168" s="1" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.3">
@@ -7090,7 +7077,7 @@
       </c>
       <c r="G169" s="1"/>
       <c r="H169" s="9" t="s">
-        <v>646</v>
+        <v>784</v>
       </c>
     </row>
     <row r="170" spans="1:8" x14ac:dyDescent="0.3">
@@ -7114,12 +7101,12 @@
       </c>
       <c r="G170" s="1"/>
       <c r="H170" s="1" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A171" s="2" t="s">
-        <v>713</v>
+        <v>709</v>
       </c>
       <c r="B171" s="1" t="s">
         <v>529</v>
@@ -7127,16 +7114,16 @@
       <c r="C171" s="3"/>
       <c r="D171" s="6"/>
       <c r="E171" s="1" t="s">
-        <v>678</v>
+        <v>674</v>
       </c>
       <c r="F171" s="3">
         <v>1</v>
       </c>
       <c r="G171" s="2" t="s">
-        <v>679</v>
+        <v>675</v>
       </c>
       <c r="H171" s="9" t="s">
-        <v>677</v>
+        <v>673</v>
       </c>
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.3">
@@ -7160,7 +7147,7 @@
       </c>
       <c r="G172" s="1"/>
       <c r="H172" s="1" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.3">
@@ -7184,7 +7171,7 @@
       </c>
       <c r="G173" s="1"/>
       <c r="H173" s="1" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
     </row>
     <row r="174" spans="1:8" x14ac:dyDescent="0.3">
@@ -7208,7 +7195,7 @@
       </c>
       <c r="G174" s="1"/>
       <c r="H174" s="1" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
     </row>
     <row r="175" spans="1:8" x14ac:dyDescent="0.3">
@@ -7225,14 +7212,14 @@
         <v>0.97916666666666663</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>661</v>
+        <v>657</v>
       </c>
       <c r="F175" s="3">
         <v>0</v>
       </c>
       <c r="G175" s="1"/>
       <c r="H175" s="1" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
     </row>
     <row r="176" spans="1:8" x14ac:dyDescent="0.3">
@@ -7249,14 +7236,14 @@
         <v>0</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>660</v>
+        <v>656</v>
       </c>
       <c r="F176" s="3">
         <v>0</v>
       </c>
       <c r="G176" s="1"/>
       <c r="H176" s="2" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
     </row>
     <row r="177" spans="1:8" x14ac:dyDescent="0.3">
@@ -7280,7 +7267,7 @@
       </c>
       <c r="G177" s="1"/>
       <c r="H177" s="2" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
     </row>
     <row r="178" spans="1:8" x14ac:dyDescent="0.3">
@@ -7304,7 +7291,7 @@
       </c>
       <c r="G178" s="1"/>
       <c r="H178" s="2" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
     </row>
     <row r="179" spans="1:8" x14ac:dyDescent="0.3">
@@ -7328,7 +7315,7 @@
       </c>
       <c r="G179" s="1"/>
       <c r="H179" s="2" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
     </row>
     <row r="180" spans="1:8" x14ac:dyDescent="0.3">
@@ -7352,7 +7339,7 @@
       </c>
       <c r="G180" s="1"/>
       <c r="H180" s="2" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
     </row>
     <row r="181" spans="1:8" x14ac:dyDescent="0.3">
@@ -7376,7 +7363,7 @@
       </c>
       <c r="G181" s="1"/>
       <c r="H181" s="2" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
     </row>
     <row r="182" spans="1:8" x14ac:dyDescent="0.3">
@@ -7400,7 +7387,7 @@
       </c>
       <c r="G182" s="1"/>
       <c r="H182" s="9" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="183" spans="1:8" x14ac:dyDescent="0.3">
@@ -7424,7 +7411,7 @@
       </c>
       <c r="G183" s="1"/>
       <c r="H183" s="9" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="184" spans="1:8" x14ac:dyDescent="0.3">
@@ -7448,7 +7435,7 @@
       </c>
       <c r="G184" s="1"/>
       <c r="H184" s="1" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="185" spans="1:8" x14ac:dyDescent="0.3">
@@ -7472,7 +7459,7 @@
       </c>
       <c r="G185" s="1"/>
       <c r="H185" s="1" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="186" spans="1:8" x14ac:dyDescent="0.3">
@@ -7496,7 +7483,7 @@
       </c>
       <c r="G186" s="1"/>
       <c r="H186" s="1" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="187" spans="1:8" x14ac:dyDescent="0.3">
@@ -7520,7 +7507,7 @@
       </c>
       <c r="G187" s="1"/>
       <c r="H187" s="1" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="188" spans="1:8" x14ac:dyDescent="0.3">
@@ -7544,7 +7531,7 @@
       </c>
       <c r="G188" s="1"/>
       <c r="H188" s="1" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="189" spans="1:8" x14ac:dyDescent="0.3">
@@ -7568,7 +7555,7 @@
       </c>
       <c r="G189" s="1"/>
       <c r="H189" s="8" t="s">
-        <v>723</v>
+        <v>648</v>
       </c>
     </row>
     <row r="190" spans="1:8" x14ac:dyDescent="0.3">
@@ -7592,7 +7579,7 @@
       </c>
       <c r="G190" s="1"/>
       <c r="H190" s="1" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="191" spans="1:8" x14ac:dyDescent="0.3">
@@ -7616,7 +7603,7 @@
       </c>
       <c r="G191" s="1"/>
       <c r="H191" s="1" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
     </row>
     <row r="192" spans="1:8" x14ac:dyDescent="0.3">
@@ -7640,10 +7627,10 @@
       </c>
       <c r="G192" s="1"/>
       <c r="H192" s="1" t="s">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="193" spans="1:9" x14ac:dyDescent="0.3">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="193" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>517</v>
       </c>
@@ -7664,10 +7651,10 @@
       </c>
       <c r="G193" s="1"/>
       <c r="H193" s="1" t="s">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="194" spans="1:9" x14ac:dyDescent="0.3">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="194" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>520</v>
       </c>
@@ -7688,10 +7675,10 @@
       </c>
       <c r="G194" s="1"/>
       <c r="H194" s="1" t="s">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="195" spans="1:9" x14ac:dyDescent="0.3">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="195" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>519</v>
       </c>
@@ -7712,10 +7699,10 @@
       </c>
       <c r="G195" s="1"/>
       <c r="H195" s="1" t="s">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="196" spans="1:9" x14ac:dyDescent="0.3">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="196" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>518</v>
       </c>
@@ -7736,10 +7723,10 @@
       </c>
       <c r="G196" s="1"/>
       <c r="H196" s="1" t="s">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="197" spans="1:9" x14ac:dyDescent="0.3">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="197" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>433</v>
       </c>
@@ -7756,49 +7743,49 @@
       </c>
       <c r="G197" s="1"/>
       <c r="H197" s="1" t="s">
-        <v>643</v>
-      </c>
-    </row>
-    <row r="198" spans="1:9" x14ac:dyDescent="0.3">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="198" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A198" s="2" t="s">
+        <v>713</v>
+      </c>
+      <c r="B198" s="1" t="s">
+        <v>714</v>
+      </c>
+      <c r="E198" s="1" t="s">
         <v>717</v>
-      </c>
-      <c r="B198" s="1" t="s">
-        <v>718</v>
-      </c>
-      <c r="E198" s="1" t="s">
-        <v>721</v>
       </c>
       <c r="F198" s="3">
         <v>1</v>
       </c>
       <c r="H198" s="10" t="s">
-        <v>768</v>
-      </c>
-    </row>
-    <row r="199" spans="1:9" x14ac:dyDescent="0.3">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="199" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A199" s="2" t="s">
-        <v>719</v>
+        <v>715</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>720</v>
+        <v>716</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>722</v>
+        <v>718</v>
       </c>
       <c r="F199" s="3">
         <v>1</v>
       </c>
       <c r="H199" s="10" t="s">
-        <v>767</v>
-      </c>
-    </row>
-    <row r="200" spans="1:9" x14ac:dyDescent="0.3">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="200" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A200" s="2" t="s">
-        <v>727</v>
+        <v>722</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>728</v>
+        <v>723</v>
       </c>
       <c r="C200" s="2">
         <v>6</v>
@@ -7807,21 +7794,21 @@
         <v>0</v>
       </c>
       <c r="E200" s="1" t="s">
+        <v>724</v>
+      </c>
+      <c r="F200" s="3">
+        <v>0</v>
+      </c>
+      <c r="H200" s="7" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="201" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A201" s="2" t="s">
         <v>729</v>
       </c>
-      <c r="F200" s="3">
-        <v>0</v>
-      </c>
-      <c r="H200" s="7" t="s">
-        <v>769</v>
-      </c>
-    </row>
-    <row r="201" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A201" s="2" t="s">
-        <v>734</v>
-      </c>
       <c r="B201" s="1" t="s">
-        <v>731</v>
+        <v>726</v>
       </c>
       <c r="C201" s="2">
         <v>7</v>
@@ -7830,286 +7817,284 @@
         <v>0.95833333333333337</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>732</v>
+        <v>727</v>
       </c>
       <c r="F201" s="3">
         <v>0</v>
       </c>
       <c r="H201" s="7" t="s">
-        <v>733</v>
-      </c>
-    </row>
-    <row r="202" spans="1:9" x14ac:dyDescent="0.3">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="202" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A202" s="2" t="s">
-        <v>735</v>
+        <v>730</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>736</v>
+        <v>731</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>764</v>
+        <v>759</v>
       </c>
       <c r="F202" s="3">
         <v>1</v>
       </c>
-      <c r="H202" s="2" t="s">
-        <v>765</v>
-      </c>
-      <c r="I202" s="2" t="s">
-        <v>766</v>
-      </c>
-    </row>
-    <row r="203" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H202" s="7" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="203" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A203" s="2" t="s">
-        <v>737</v>
+        <v>732</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>738</v>
+        <v>733</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>770</v>
+        <v>763</v>
       </c>
       <c r="F203" s="3">
         <v>1</v>
       </c>
-      <c r="H203" s="2" t="s">
-        <v>765</v>
-      </c>
-    </row>
-    <row r="204" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H203" s="7" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="204" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A204" s="2" t="s">
-        <v>739</v>
+        <v>734</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>740</v>
+        <v>735</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>771</v>
+        <v>764</v>
       </c>
       <c r="F204" s="3">
         <v>1</v>
       </c>
-      <c r="H204" s="2" t="s">
+      <c r="H204" s="7" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="205" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A205" s="2" t="s">
+        <v>736</v>
+      </c>
+      <c r="B205" s="1" t="s">
+        <v>737</v>
+      </c>
+      <c r="E205" s="1" t="s">
         <v>765</v>
-      </c>
-    </row>
-    <row r="205" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A205" s="2" t="s">
-        <v>741</v>
-      </c>
-      <c r="B205" s="1" t="s">
-        <v>742</v>
-      </c>
-      <c r="E205" s="1" t="s">
-        <v>772</v>
       </c>
       <c r="F205" s="3">
         <v>1</v>
       </c>
-      <c r="H205" s="2" t="s">
-        <v>765</v>
-      </c>
-    </row>
-    <row r="206" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H205" s="7" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="206" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A206" s="2" t="s">
-        <v>745</v>
+        <v>740</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>743</v>
+        <v>738</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>773</v>
+        <v>766</v>
       </c>
       <c r="F206" s="3">
         <v>1</v>
       </c>
-      <c r="H206" s="2" t="s">
-        <v>765</v>
-      </c>
-    </row>
-    <row r="207" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H206" s="7" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="207" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A207" s="2" t="s">
-        <v>744</v>
+        <v>739</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>746</v>
+        <v>741</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>774</v>
+        <v>767</v>
       </c>
       <c r="F207" s="3">
         <v>1</v>
       </c>
-      <c r="H207" s="2" t="s">
-        <v>765</v>
-      </c>
-    </row>
-    <row r="208" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H207" s="7" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="208" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A208" s="2" t="s">
-        <v>747</v>
+        <v>742</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>748</v>
+        <v>743</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>775</v>
+        <v>768</v>
       </c>
       <c r="F208" s="3">
         <v>1</v>
       </c>
-      <c r="H208" s="2" t="s">
-        <v>765</v>
+      <c r="H208" s="7" t="s">
+        <v>780</v>
       </c>
     </row>
     <row r="209" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A209" s="2" t="s">
-        <v>749</v>
+        <v>744</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>750</v>
+        <v>745</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="F209" s="3">
         <v>1</v>
       </c>
-      <c r="H209" s="2" t="s">
-        <v>765</v>
+      <c r="H209" s="7" t="s">
+        <v>780</v>
       </c>
     </row>
     <row r="210" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A210" s="2" t="s">
-        <v>751</v>
+        <v>746</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>752</v>
+        <v>747</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>777</v>
+        <v>770</v>
       </c>
       <c r="F210" s="3">
         <v>1</v>
       </c>
-      <c r="H210" s="2" t="s">
-        <v>765</v>
+      <c r="H210" s="7" t="s">
+        <v>780</v>
       </c>
     </row>
     <row r="211" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A211" s="2" t="s">
-        <v>753</v>
+        <v>748</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>754</v>
+        <v>749</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>778</v>
+        <v>771</v>
       </c>
       <c r="F211" s="3">
         <v>1</v>
       </c>
-      <c r="H211" s="2" t="s">
-        <v>765</v>
+      <c r="H211" s="7" t="s">
+        <v>780</v>
       </c>
     </row>
     <row r="212" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A212" s="2" t="s">
-        <v>755</v>
+        <v>750</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>756</v>
+        <v>751</v>
       </c>
       <c r="E212" s="1" t="s">
-        <v>779</v>
+        <v>772</v>
       </c>
       <c r="F212" s="3">
         <v>1</v>
       </c>
-      <c r="H212" s="2" t="s">
-        <v>765</v>
+      <c r="H212" s="7" t="s">
+        <v>780</v>
       </c>
     </row>
     <row r="213" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A213" s="2" t="s">
-        <v>757</v>
+        <v>752</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>758</v>
+        <v>753</v>
       </c>
       <c r="E213" s="1" t="s">
-        <v>780</v>
+        <v>773</v>
       </c>
       <c r="F213" s="3">
         <v>1</v>
       </c>
-      <c r="H213" s="2" t="s">
-        <v>765</v>
+      <c r="H213" s="7" t="s">
+        <v>780</v>
       </c>
     </row>
     <row r="214" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A214" s="2" t="s">
-        <v>759</v>
+        <v>754</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>730</v>
+        <v>725</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>781</v>
+        <v>774</v>
       </c>
       <c r="F214" s="3">
         <v>1</v>
       </c>
-      <c r="H214" s="2" t="s">
-        <v>765</v>
+      <c r="H214" s="7" t="s">
+        <v>780</v>
       </c>
     </row>
     <row r="215" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A215" s="2" t="s">
-        <v>760</v>
+        <v>755</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>761</v>
+        <v>756</v>
       </c>
       <c r="E215" s="1" t="s">
-        <v>782</v>
+        <v>775</v>
       </c>
       <c r="F215" s="3">
         <v>1</v>
       </c>
-      <c r="H215" s="2" t="s">
-        <v>765</v>
+      <c r="H215" s="7" t="s">
+        <v>780</v>
       </c>
     </row>
     <row r="216" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A216" s="2" t="s">
-        <v>762</v>
+        <v>757</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>763</v>
+        <v>758</v>
       </c>
       <c r="E216" s="1" t="s">
-        <v>783</v>
+        <v>776</v>
       </c>
       <c r="F216" s="3">
         <v>1</v>
       </c>
-      <c r="H216" s="2" t="s">
-        <v>765</v>
+      <c r="H216" s="7" t="s">
+        <v>780</v>
       </c>
     </row>
     <row r="217" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B217" s="1" t="s">
-        <v>784</v>
-      </c>
+        <v>777</v>
+      </c>
+      <c r="E217" s="7"/>
     </row>
     <row r="218" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B218" s="1" t="s">
-        <v>785</v>
+        <v>778</v>
       </c>
     </row>
     <row r="219" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B219" s="1" t="s">
-        <v>786</v>
+        <v>779</v>
       </c>
     </row>
   </sheetData>
@@ -8123,8 +8108,10 @@
     <hyperlink ref="H200" r:id="rId3" xr:uid="{D8D98BE9-F998-4931-BC78-1FA8DBB2DF8D}"/>
     <hyperlink ref="H199" r:id="rId4" xr:uid="{3BEBF5F8-81B1-4909-98FA-8DDD635C8EA6}"/>
     <hyperlink ref="H198" r:id="rId5" xr:uid="{65D202DC-0DAE-445A-B96C-C36AAC898769}"/>
+    <hyperlink ref="H202" r:id="rId6" xr:uid="{25A9BA66-0BC2-4AD9-A0BE-F4C36298AC2D}"/>
+    <hyperlink ref="H203:H216" r:id="rId7" display="http://www.murderparker.com/" xr:uid="{E958893D-4F52-4648-BDD7-4971EF621EF9}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId6"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId8"/>
 </worksheet>
 </file>
--- a/stores.xlsx
+++ b/stores.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\YUMIN\Desktop\B0KT2A_RSVN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{EEB83404-098C-49C5-95E1-ED84C0BE242F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{540738B7-C9EC-48AA-AEA8-592F77160A40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{ABFC3117-FCCB-4FF3-804A-FE19451A2004}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{ABFC3117-FCCB-4FF3-804A-FE19451A2004}"/>
   </bookViews>
   <sheets>
     <sheet name="stores" sheetId="2" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="870" uniqueCount="785">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="911" uniqueCount="824">
   <si>
     <t>룸익스케이프 WHITE</t>
   </si>
@@ -882,10 +882,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>비트포비아 동성로점</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>구룡잠들지않는도시,이런변이있나,이일호씨,잭더리퍼,지금만나러갑니다</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -898,10 +894,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>TRADE 동성로,트레이드동성로,모자가게의비밀,심야식당,쏘우,용의선상,웃는남자,잭더리퍼,테러라이브</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>선택,더챕터,쿠키</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1510,10 +1502,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>bp_dsr</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>bp_md</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1870,18 +1858,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>무죄2,명당,재개발구역:관계자외출입금지</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>숨바꼭질 3호점</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>종결사건,비공개모드</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>판타지아</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1890,10 +1870,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>호렵:범의탈을쓴여우</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>엑소더스 강남점</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2256,10 +2232,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>고양학개론,캠프ING,옥순양갱,철수네 슈퍼,철수네수퍼,오메가,더 라스트 노트,MR.BANG,미스터뱅</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>ecp_dj</t>
   </si>
   <si>
@@ -2771,13 +2743,189 @@
   </si>
   <si>
     <t>https://www.master-key.co.kr/</t>
+  </si>
+  <si>
+    <t>고양학개론,캠프ING,옥순양갱,철수네 슈퍼,철수네수퍼,오메가,더 라스트 노트,MR.BANG,미스터뱅,미스터방,치로의여름방학</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ft_str1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ft_str2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ft_str3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://fantastrick.co.kr/</t>
+  </si>
+  <si>
+    <t>태초의신부,이브프로젝트,태이프</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>북오브두아트,사자의서,BOOK OF DUAT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LOCKDOWN CITY,락다운시티</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>무죄2,명당,재개발구역:관계자외출입금지,호렵:범의탈을쓴여우</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>매주 일요일 13:00 2주 뒤(8일 뒤) 월~일 예약 오픈</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>종결사건</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>비공개모드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>매주 수요일 14:55 다음주 월~일 예약오픈</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>매주 수요일 14:50 다음주 월~일 예약 오픈</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tcd_wsn</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>더 코드 왕십리점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>도둑들#2:다이아몬드블루문,피의일요일,냉동창고:살인사건#2,도박꾼:마지막베팅</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://www.thecode12.kr/</t>
+  </si>
+  <si>
+    <t>tcd_sl</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>더 코드 신림점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아파트,위자보드:위험한장난,다시시작된살인사건,세기의명화를훔치는도둑들,의문의동창회</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://www.thecode11.kr/</t>
+  </si>
+  <si>
+    <t>tcd_hg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>더 코드 회기점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>다시시작된살인사건,세기의명화를훔치는도둑들,재즈바W:위험한거래,강력1반:추격자</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tcd_sgp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>더 코드 제주서귀포점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://thecode06.kr/</t>
+  </si>
+  <si>
+    <t>http://thecode09.kr/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>재즈바W:위험한거래,위자보드:위험한장난,세기의명화를훔치는도둑들</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://thecode02.kr/</t>
+  </si>
+  <si>
+    <t>tcd_gj</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>더 코드 경주점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>몽타주:강력1반#2,취부장의비밀,박물관:도둑들#3,도박꾼:마지막베팅</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://thecode03.kr/</t>
+  </si>
+  <si>
+    <t>tcd_cc</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>더 코드 춘천점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>세기의명화를훔치는도둑들,다시시작된살인사건,냉동창고:살인사건#2,의문의동창회</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://thecode07.kr/</t>
+  </si>
+  <si>
+    <t>tcd_jj</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>더 코드 진주점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>의문의동창회,아파트,세기의명화를훔치는도둑들,위자보드:위험한장난,재즈바W:위험한거래,강력1반:사라진아이들</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://www.thecode-escape.com/</t>
+  </si>
+  <si>
+    <t>tcd_jgj</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>타짜,곤지암,경찰서를털어라,미생,탈옥,탐정,나홀로집에,도둑들</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>더 코드 광주</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2805,6 +2953,13 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
       <charset val="129"/>
@@ -2858,10 +3013,10 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFill="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -3179,8 +3334,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D839462D-4719-40BB-8925-C1B9F93734CF}">
-  <dimension ref="A1:H219"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:H226"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="2"/>
     <col min="2" max="2" width="48.5" style="2" customWidth="1"/>
@@ -3192,9 +3347,9 @@
     <col min="9" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8">
       <c r="A1" s="2" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>11</v>
@@ -3218,12 +3373,12 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8">
       <c r="A2" s="2" t="s">
-        <v>662</v>
+        <v>655</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>659</v>
+        <v>652</v>
       </c>
       <c r="C2" s="2">
         <v>7</v>
@@ -3232,21 +3387,21 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>660</v>
+        <v>653</v>
       </c>
       <c r="F2" s="2">
         <v>0</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>661</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" s="2" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C3" s="3">
         <v>6</v>
@@ -3255,19 +3410,19 @@
         <v>0</v>
       </c>
       <c r="E3" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="F3" s="3">
         <v>0</v>
       </c>
       <c r="G3" s="1"/>
       <c r="H3" s="1" t="s">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" s="2" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>274</v>
@@ -3286,12 +3441,12 @@
       </c>
       <c r="G4" s="1"/>
       <c r="H4" s="1" t="s">
-        <v>536</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" s="2" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>143</v>
@@ -3299,19 +3454,19 @@
       <c r="C5" s="3"/>
       <c r="D5" s="4"/>
       <c r="E5" s="1" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="F5" s="3">
         <v>1</v>
       </c>
       <c r="G5" s="1"/>
       <c r="H5" s="1" t="s">
-        <v>537</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" s="2" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>268</v>
@@ -3330,12 +3485,12 @@
       </c>
       <c r="G6" s="1"/>
       <c r="H6" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" s="2" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>269</v>
@@ -3347,19 +3502,19 @@
         <v>0</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="F7" s="3">
         <v>0</v>
       </c>
       <c r="G7" s="1"/>
       <c r="H7" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8" s="2" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>139</v>
@@ -3378,12 +3533,12 @@
       </c>
       <c r="G8" s="1"/>
       <c r="H8" s="1" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9" s="2" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>141</v>
@@ -3402,12 +3557,12 @@
       </c>
       <c r="G9" s="1"/>
       <c r="H9" s="1" t="s">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
       <c r="A10" s="2" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>239</v>
@@ -3419,19 +3574,19 @@
         <v>0</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="F10" s="3">
         <v>0</v>
       </c>
       <c r="G10" s="1"/>
       <c r="H10" s="1" t="s">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
       <c r="A11" s="2" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>240</v>
@@ -3443,19 +3598,19 @@
         <v>0</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="F11" s="3">
         <v>0</v>
       </c>
       <c r="G11" s="1"/>
       <c r="H11" s="1" t="s">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
       <c r="A12" s="2" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>241</v>
@@ -3467,19 +3622,19 @@
         <v>0</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="F12" s="3">
         <v>0</v>
       </c>
       <c r="G12" s="1"/>
       <c r="H12" s="1" t="s">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
       <c r="A13" s="2" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>236</v>
@@ -3491,19 +3646,19 @@
         <v>0</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="F13" s="3">
         <v>0</v>
       </c>
       <c r="G13" s="1"/>
       <c r="H13" s="1" t="s">
-        <v>542</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
       <c r="A14" s="2" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>237</v>
@@ -3522,12 +3677,12 @@
       </c>
       <c r="G14" s="1"/>
       <c r="H14" s="1" t="s">
-        <v>542</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
       <c r="A15" s="2" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>218</v>
@@ -3539,19 +3694,19 @@
         <v>0</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="F15" s="3">
         <v>0</v>
       </c>
       <c r="G15" s="1"/>
       <c r="H15" s="1" t="s">
-        <v>543</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
       <c r="A16" s="2" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>88</v>
@@ -3563,19 +3718,19 @@
         <v>0</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="F16" s="3">
         <v>0</v>
       </c>
       <c r="G16" s="1"/>
       <c r="H16" s="1" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
       <c r="A17" s="2" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>83</v>
@@ -3594,12 +3749,12 @@
       </c>
       <c r="G17" s="1"/>
       <c r="H17" s="1" t="s">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
       <c r="A18" s="2" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>85</v>
@@ -3618,12 +3773,12 @@
       </c>
       <c r="G18" s="1"/>
       <c r="H18" s="1" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
       <c r="A19" s="2" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>87</v>
@@ -3635,19 +3790,19 @@
         <v>0</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="F19" s="3">
         <v>0</v>
       </c>
       <c r="G19" s="1"/>
       <c r="H19" s="1" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
       <c r="A20" s="2" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>81</v>
@@ -3666,15 +3821,15 @@
       </c>
       <c r="G20" s="1"/>
       <c r="H20" s="1" t="s">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
       <c r="A21" s="2" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C21" s="3">
         <v>30</v>
@@ -3683,19 +3838,19 @@
         <v>0</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="F21" s="3">
         <v>0</v>
       </c>
       <c r="G21" s="1"/>
       <c r="H21" s="1" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
       <c r="A22" s="2" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>79</v>
@@ -3714,12 +3869,12 @@
       </c>
       <c r="G22" s="1"/>
       <c r="H22" s="1" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
       <c r="A23" s="2" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>77</v>
@@ -3738,15 +3893,15 @@
       </c>
       <c r="G23" s="1"/>
       <c r="H23" s="1" t="s">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
       <c r="A24" s="2" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="C24" s="3">
         <v>6</v>
@@ -3755,21 +3910,21 @@
         <v>0</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="F24" s="3">
         <v>0</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
       <c r="A25" s="2" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="C25" s="3">
         <v>6</v>
@@ -3778,18 +3933,18 @@
         <v>0</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="F25" s="3">
         <v>0</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
       <c r="A26" s="2" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>144</v>
@@ -3808,12 +3963,12 @@
       </c>
       <c r="G26" s="1"/>
       <c r="H26" s="1" t="s">
-        <v>553</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8">
       <c r="A27" s="2" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>146</v>
@@ -3825,22 +3980,22 @@
         <v>0</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="F27" s="3">
         <v>0</v>
       </c>
       <c r="G27" s="1"/>
       <c r="H27" s="1" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8">
       <c r="A28" s="2" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C28" s="3">
         <v>6</v>
@@ -3849,33 +4004,33 @@
         <v>0</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="F28" s="3">
         <v>0</v>
       </c>
       <c r="G28" s="1"/>
       <c r="H28" s="2" t="s">
-        <v>555</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
       <c r="A29" s="2" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="F29" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8">
       <c r="A30" s="2" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>147</v>
@@ -3894,12 +4049,12 @@
       </c>
       <c r="G30" s="1"/>
       <c r="H30" s="1" t="s">
-        <v>556</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8">
       <c r="A31" s="2" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>159</v>
@@ -3914,12 +4069,12 @@
       </c>
       <c r="G31" s="1"/>
       <c r="H31" s="1" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8">
       <c r="A32" s="2" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>161</v>
@@ -3938,12 +4093,12 @@
       </c>
       <c r="G32" s="1"/>
       <c r="H32" s="1" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8">
       <c r="A33" s="2" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>149</v>
@@ -3962,12 +4117,12 @@
       </c>
       <c r="G33" s="1"/>
       <c r="H33" s="1" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8">
       <c r="A34" s="2" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>151</v>
@@ -3986,12 +4141,12 @@
       </c>
       <c r="G34" s="1"/>
       <c r="H34" s="1" t="s">
-        <v>560</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8">
       <c r="A35" s="2" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>157</v>
@@ -4006,12 +4161,12 @@
       </c>
       <c r="G35" s="1"/>
       <c r="H35" s="1" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8">
       <c r="A36" s="2" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>155</v>
@@ -4026,12 +4181,12 @@
       </c>
       <c r="G36" s="1"/>
       <c r="H36" s="1" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8">
       <c r="A37" s="2" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>153</v>
@@ -4050,12 +4205,12 @@
       </c>
       <c r="G37" s="1"/>
       <c r="H37" s="1" t="s">
-        <v>563</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8">
       <c r="A38" s="2" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>8</v>
@@ -4067,19 +4222,19 @@
         <v>0</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>658</v>
+        <v>651</v>
       </c>
       <c r="F38" s="3">
         <v>0</v>
       </c>
       <c r="G38" s="1"/>
       <c r="H38" t="s">
-        <v>564</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8">
       <c r="A39" s="2" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>252</v>
@@ -4098,12 +4253,12 @@
       </c>
       <c r="G39" s="1"/>
       <c r="H39" t="s">
-        <v>565</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8">
       <c r="A40" s="2" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>254</v>
@@ -4122,12 +4277,12 @@
       </c>
       <c r="G40" s="1"/>
       <c r="H40" t="s">
-        <v>565</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8">
       <c r="A41" s="2" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>256</v>
@@ -4146,12 +4301,12 @@
       </c>
       <c r="G41" s="1"/>
       <c r="H41" t="s">
-        <v>565</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8">
       <c r="A42" s="2" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>131</v>
@@ -4170,15 +4325,15 @@
       </c>
       <c r="G42" s="1"/>
       <c r="H42" s="1" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8">
       <c r="A43" s="2" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C43" s="1">
         <v>13</v>
@@ -4187,19 +4342,19 @@
         <v>0</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="F43" s="1">
         <v>0</v>
       </c>
       <c r="G43" s="1"/>
       <c r="H43" s="1" t="s">
-        <v>567</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8">
       <c r="A44" s="2" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>258</v>
@@ -4216,65 +4371,65 @@
         <v>260</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>568</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8">
       <c r="A45" t="s">
-        <v>701</v>
+        <v>694</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>665</v>
+        <v>658</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>668</v>
+        <v>661</v>
       </c>
       <c r="F45" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:8">
       <c r="A46" t="s">
-        <v>702</v>
+        <v>695</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>666</v>
+        <v>659</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>672</v>
+        <v>665</v>
       </c>
       <c r="F46" s="3">
         <v>1</v>
       </c>
-      <c r="H46" s="9" t="s">
-        <v>671</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H46" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8">
       <c r="A47" t="s">
-        <v>703</v>
+        <v>696</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>667</v>
+        <v>660</v>
       </c>
       <c r="C47" s="3"/>
       <c r="D47" s="6"/>
       <c r="E47" s="1" t="s">
-        <v>669</v>
+        <v>662</v>
       </c>
       <c r="F47" s="3">
         <v>1</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>721</v>
-      </c>
-      <c r="H47" s="9" t="s">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+        <v>714</v>
+      </c>
+      <c r="H47" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8">
       <c r="A48" s="2" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>133</v>
@@ -4293,15 +4448,15 @@
       </c>
       <c r="G48" s="1"/>
       <c r="H48" s="1" t="s">
-        <v>569</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8">
       <c r="A49" s="2" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C49" s="3">
         <v>6</v>
@@ -4310,42 +4465,42 @@
         <v>0</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="F49" s="3">
         <v>0</v>
       </c>
       <c r="G49" s="1"/>
       <c r="H49" s="1" t="s">
-        <v>570</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8">
       <c r="A50" s="2" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C50" s="3"/>
       <c r="D50" s="5"/>
       <c r="E50" s="1" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="F50" s="3">
         <v>1</v>
       </c>
       <c r="G50" s="1"/>
       <c r="H50" s="1" t="s">
-        <v>571</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8">
       <c r="A51" s="2" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C51" s="3">
         <v>6</v>
@@ -4354,19 +4509,19 @@
         <v>0</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="F51" s="3">
         <v>0</v>
       </c>
       <c r="G51" s="1"/>
       <c r="H51" s="1" t="s">
-        <v>570</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8">
       <c r="A52" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>2</v>
@@ -4385,12 +4540,12 @@
       </c>
       <c r="G52" s="1"/>
       <c r="H52" s="2" t="s">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8">
       <c r="A53" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>6</v>
@@ -4409,12 +4564,12 @@
       </c>
       <c r="G53" s="1"/>
       <c r="H53" s="2" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8">
       <c r="A54" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>4</v>
@@ -4433,12 +4588,12 @@
       </c>
       <c r="G54" s="1"/>
       <c r="H54" s="2" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8">
       <c r="A55" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>0</v>
@@ -4457,12 +4612,12 @@
       </c>
       <c r="G55" s="1"/>
       <c r="H55" s="2" t="s">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8">
       <c r="A56" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>267</v>
@@ -4474,18 +4629,18 @@
         <v>0</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="F56" s="3">
         <v>0</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8">
       <c r="A57" s="2" t="s">
-        <v>678</v>
+        <v>671</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>187</v>
@@ -4503,12 +4658,12 @@
         <v>0</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>577</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8">
       <c r="A58" t="s">
-        <v>695</v>
+        <v>688</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>270</v>
@@ -4526,12 +4681,12 @@
         <v>0</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8">
       <c r="A59" t="s">
-        <v>696</v>
+        <v>689</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>185</v>
@@ -4549,12 +4704,12 @@
         <v>0</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8">
       <c r="A60" t="s">
-        <v>681</v>
+        <v>674</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>191</v>
@@ -4572,12 +4727,12 @@
         <v>0</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>580</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8">
       <c r="A61" s="2" t="s">
-        <v>682</v>
+        <v>675</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>189</v>
@@ -4595,12 +4750,12 @@
         <v>0</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8">
       <c r="A62" t="s">
-        <v>683</v>
+        <v>676</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>177</v>
@@ -4618,12 +4773,12 @@
         <v>0</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>582</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8">
       <c r="A63" t="s">
-        <v>684</v>
+        <v>677</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>179</v>
@@ -4641,12 +4796,12 @@
         <v>0</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8">
       <c r="A64" s="2" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>163</v>
@@ -4664,12 +4819,12 @@
         <v>0</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>584</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8">
       <c r="A65" t="s">
-        <v>699</v>
+        <v>692</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>193</v>
@@ -4687,12 +4842,12 @@
         <v>0</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>585</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8">
       <c r="A66" t="s">
-        <v>697</v>
+        <v>690</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>181</v>
@@ -4710,12 +4865,12 @@
         <v>0</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>586</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8">
       <c r="A67" t="s">
-        <v>698</v>
+        <v>691</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>183</v>
@@ -4733,12 +4888,12 @@
         <v>0</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>587</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8">
       <c r="A68" s="2" t="s">
-        <v>663</v>
+        <v>656</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>199</v>
@@ -4756,12 +4911,12 @@
         <v>0</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8">
       <c r="A69" s="2" t="s">
-        <v>664</v>
+        <v>657</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>197</v>
@@ -4779,12 +4934,12 @@
         <v>0</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>589</v>
-      </c>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8">
       <c r="A70" s="2" t="s">
-        <v>679</v>
+        <v>672</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>175</v>
@@ -4802,12 +4957,12 @@
         <v>0</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>590</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8">
       <c r="A71" s="2" t="s">
-        <v>680</v>
+        <v>673</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>173</v>
@@ -4825,12 +4980,12 @@
         <v>0</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8">
       <c r="A72" t="s">
-        <v>685</v>
+        <v>678</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>165</v>
@@ -4848,12 +5003,12 @@
         <v>0</v>
       </c>
       <c r="H72" s="1" t="s">
-        <v>592</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8">
       <c r="A73" t="s">
-        <v>686</v>
+        <v>679</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>171</v>
@@ -4871,12 +5026,12 @@
         <v>0</v>
       </c>
       <c r="H73" s="1" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8">
       <c r="A74" t="s">
-        <v>687</v>
+        <v>680</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>169</v>
@@ -4894,12 +5049,12 @@
         <v>0</v>
       </c>
       <c r="H74" s="1" t="s">
-        <v>594</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8">
       <c r="A75" t="s">
-        <v>688</v>
+        <v>681</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>167</v>
@@ -4917,12 +5072,12 @@
         <v>0</v>
       </c>
       <c r="H75" s="1" t="s">
-        <v>595</v>
-      </c>
-    </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8">
       <c r="A76" t="s">
-        <v>700</v>
+        <v>693</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>195</v>
@@ -4940,12 +5095,12 @@
         <v>0</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>596</v>
-      </c>
-    </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8">
       <c r="A77" s="2" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>101</v>
@@ -4964,15 +5119,15 @@
       </c>
       <c r="G77" s="1"/>
       <c r="H77" s="1" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8">
       <c r="A78" s="2" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="C78" s="3">
         <v>7</v>
@@ -4988,12 +5143,12 @@
       </c>
       <c r="G78" s="1"/>
       <c r="H78" s="1" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8">
       <c r="A79" s="2" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>109</v>
@@ -5012,12 +5167,12 @@
       </c>
       <c r="G79" s="1"/>
       <c r="H79" s="1" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8">
       <c r="A80" s="2" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>115</v>
@@ -5036,15 +5191,15 @@
       </c>
       <c r="G80" s="1"/>
       <c r="H80" s="1" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8">
       <c r="A81" s="2" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="C81" s="3">
         <v>7</v>
@@ -5060,15 +5215,15 @@
       </c>
       <c r="G81" s="1"/>
       <c r="H81" s="1" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8">
       <c r="A82" s="2" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="C82" s="3">
         <v>7</v>
@@ -5084,15 +5239,15 @@
       </c>
       <c r="G82" s="1"/>
       <c r="H82" s="1" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8">
       <c r="A83" s="2" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="C83" s="3">
         <v>7</v>
@@ -5108,12 +5263,12 @@
       </c>
       <c r="G83" s="1"/>
       <c r="H83" s="1" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8">
       <c r="A84" s="2" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>250</v>
@@ -5132,15 +5287,15 @@
       </c>
       <c r="G84" s="1"/>
       <c r="H84" t="s">
-        <v>597</v>
-      </c>
-    </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8">
       <c r="A85" s="2" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="C85" s="3">
         <v>7</v>
@@ -5156,15 +5311,15 @@
       </c>
       <c r="G85" s="1"/>
       <c r="H85" s="1" t="s">
-        <v>598</v>
-      </c>
-    </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8">
       <c r="A86" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="C86" s="3">
         <v>7</v>
@@ -5173,39 +5328,39 @@
         <v>0.95833333333333337</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="F86" s="3">
         <v>0</v>
       </c>
       <c r="G86" s="1"/>
       <c r="H86" s="1" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8">
       <c r="A87" s="2" t="s">
-        <v>712</v>
+        <v>705</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C87" s="1"/>
       <c r="D87" s="5"/>
       <c r="E87" s="1" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="F87" s="3">
         <v>1</v>
       </c>
       <c r="G87" s="1"/>
       <c r="H87" s="1" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8">
       <c r="A88" s="2" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>244</v>
@@ -5224,12 +5379,12 @@
       </c>
       <c r="G88" s="1"/>
       <c r="H88" s="1" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8">
       <c r="A89" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>47</v>
@@ -5248,12 +5403,12 @@
       </c>
       <c r="G89" s="1"/>
       <c r="H89" s="2" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8">
       <c r="A90" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>49</v>
@@ -5272,12 +5427,12 @@
       </c>
       <c r="G90" s="1"/>
       <c r="H90" s="2" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8">
       <c r="A91" s="2" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>277</v>
@@ -5289,19 +5444,19 @@
         <v>0</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F91" s="3">
         <v>0</v>
       </c>
       <c r="G91" s="1"/>
-      <c r="H91" s="9" t="s">
-        <v>781</v>
-      </c>
-    </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H91" t="s">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8">
       <c r="A92" s="2" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>43</v>
@@ -5320,12 +5475,12 @@
       </c>
       <c r="G92" s="1"/>
       <c r="H92" s="2" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8">
       <c r="A93" s="2" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>51</v>
@@ -5344,12 +5499,12 @@
       </c>
       <c r="G93" s="1"/>
       <c r="H93" s="2" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8">
       <c r="A94" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>53</v>
@@ -5368,15 +5523,15 @@
       </c>
       <c r="G94" s="1"/>
       <c r="H94" s="2" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8">
       <c r="A95" s="2" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="C95" s="3">
         <v>6</v>
@@ -5385,166 +5540,166 @@
         <v>0</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F95" s="3">
         <v>0</v>
       </c>
       <c r="G95" s="1"/>
-      <c r="H95" s="9" t="s">
-        <v>781</v>
-      </c>
-    </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H95" t="s">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8">
       <c r="A96" s="2" t="s">
-        <v>437</v>
+        <v>396</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>276</v>
+        <v>55</v>
       </c>
       <c r="C96" s="3">
         <v>6</v>
       </c>
       <c r="D96" s="4">
-        <v>0</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>281</v>
+        <v>56</v>
       </c>
       <c r="F96" s="3">
         <v>0</v>
       </c>
       <c r="G96" s="1"/>
-      <c r="H96" s="9" t="s">
-        <v>781</v>
-      </c>
-    </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H96" s="2" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8">
       <c r="A97" s="2" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>55</v>
+        <v>703</v>
       </c>
       <c r="C97" s="3">
         <v>6</v>
       </c>
       <c r="D97" s="4">
-        <v>0.83333333333333337</v>
+        <v>0.875</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>56</v>
+        <v>337</v>
       </c>
       <c r="F97" s="3">
         <v>0</v>
       </c>
       <c r="G97" s="1"/>
       <c r="H97" s="2" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8">
       <c r="A98" s="2" t="s">
-        <v>399</v>
+        <v>435</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>710</v>
+        <v>278</v>
       </c>
       <c r="C98" s="3">
         <v>6</v>
       </c>
       <c r="D98" s="4">
-        <v>0.875</v>
+        <v>0</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>339</v>
+        <v>281</v>
       </c>
       <c r="F98" s="3">
         <v>0</v>
       </c>
       <c r="G98" s="1"/>
-      <c r="H98" s="2" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H98" t="s">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8">
       <c r="A99" s="2" t="s">
-        <v>438</v>
+        <v>398</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>278</v>
+        <v>41</v>
       </c>
       <c r="C99" s="3">
         <v>6</v>
       </c>
       <c r="D99" s="4">
-        <v>0</v>
+        <v>0.54166666666666663</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>282</v>
+        <v>42</v>
       </c>
       <c r="F99" s="3">
         <v>0</v>
       </c>
       <c r="G99" s="1"/>
-      <c r="H99" s="9" t="s">
-        <v>781</v>
-      </c>
-    </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H99" s="2" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8">
       <c r="A100" s="2" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C100" s="3">
         <v>6</v>
       </c>
       <c r="D100" s="4">
-        <v>0.54166666666666663</v>
+        <v>0.625</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F100" s="3">
         <v>0</v>
       </c>
       <c r="G100" s="1"/>
       <c r="H100" s="2" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A101" s="2" t="s">
-        <v>401</v>
+        <v>595</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8">
+      <c r="A101" t="s">
+        <v>436</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>45</v>
+        <v>226</v>
       </c>
       <c r="C101" s="3">
         <v>6</v>
       </c>
       <c r="D101" s="4">
-        <v>0.625</v>
+        <v>0</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>46</v>
+        <v>227</v>
       </c>
       <c r="F101" s="3">
         <v>0</v>
       </c>
       <c r="G101" s="1"/>
-      <c r="H101" s="2" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H101" s="1" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8">
       <c r="A102" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="C102" s="3">
         <v>6</v>
@@ -5553,22 +5708,22 @@
         <v>0</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="F102" s="3">
         <v>0</v>
       </c>
       <c r="G102" s="1"/>
       <c r="H102" s="1" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.3">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8">
       <c r="A103" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="C103" s="3">
         <v>6</v>
@@ -5577,22 +5732,22 @@
         <v>0</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>221</v>
+        <v>233</v>
       </c>
       <c r="F103" s="3">
         <v>0</v>
       </c>
       <c r="G103" s="1"/>
       <c r="H103" s="1" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8">
       <c r="A104" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>232</v>
+        <v>222</v>
       </c>
       <c r="C104" s="3">
         <v>6</v>
@@ -5601,22 +5756,22 @@
         <v>0</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>233</v>
+        <v>223</v>
       </c>
       <c r="F104" s="3">
         <v>0</v>
       </c>
       <c r="G104" s="1"/>
       <c r="H104" s="1" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.3">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8">
       <c r="A105" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="C105" s="3">
         <v>6</v>
@@ -5625,22 +5780,22 @@
         <v>0</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="F105" s="3">
         <v>0</v>
       </c>
       <c r="G105" s="1"/>
       <c r="H105" s="1" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.3">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8">
       <c r="A106" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C106" s="3">
         <v>6</v>
@@ -5649,22 +5804,22 @@
         <v>0</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="F106" s="3">
         <v>0</v>
       </c>
       <c r="G106" s="1"/>
       <c r="H106" s="1" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.3">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8">
       <c r="A107" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="C107" s="3">
         <v>6</v>
@@ -5673,22 +5828,22 @@
         <v>0</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="F107" s="3">
         <v>0</v>
       </c>
       <c r="G107" s="1"/>
       <c r="H107" s="1" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A108" t="s">
-        <v>445</v>
+        <v>596</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8">
+      <c r="A108" s="2" t="s">
+        <v>443</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>224</v>
+        <v>242</v>
       </c>
       <c r="C108" s="3">
         <v>6</v>
@@ -5697,180 +5852,185 @@
         <v>0</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>225</v>
+        <v>243</v>
       </c>
       <c r="F108" s="3">
         <v>0</v>
       </c>
       <c r="G108" s="1"/>
-      <c r="H108" s="1" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H108" t="s">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8">
       <c r="A109" s="2" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>242</v>
+        <v>272</v>
       </c>
       <c r="C109" s="3">
         <v>6</v>
       </c>
       <c r="D109" s="4">
-        <v>0</v>
+        <v>0.54166666666666663</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>243</v>
+        <v>273</v>
       </c>
       <c r="F109" s="3">
         <v>0</v>
       </c>
       <c r="G109" s="1"/>
-      <c r="H109" s="9" t="s">
-        <v>782</v>
-      </c>
-    </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H109" s="1" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8">
       <c r="A110" s="2" t="s">
-        <v>447</v>
+        <v>400</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>272</v>
+        <v>201</v>
       </c>
       <c r="C110" s="3">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D110" s="4">
-        <v>0.54166666666666663</v>
+        <v>0</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>273</v>
+        <v>333</v>
       </c>
       <c r="F110" s="3">
         <v>0</v>
       </c>
       <c r="G110" s="1"/>
       <c r="H110" s="1" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A111" s="2" t="s">
-        <v>402</v>
+        <v>598</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8">
+      <c r="A111" t="s">
+        <v>697</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="C111" s="3">
+        <v>522</v>
+      </c>
+      <c r="E111" s="1" t="s">
+        <v>786</v>
+      </c>
+      <c r="F111" s="2">
+        <v>1</v>
+      </c>
+      <c r="G111" s="2" t="s">
+        <v>787</v>
+      </c>
+      <c r="H111" s="2" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8">
+      <c r="A112" t="s">
+        <v>698</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>523</v>
+      </c>
+      <c r="E112" s="1" t="s">
+        <v>788</v>
+      </c>
+      <c r="F112" s="2">
+        <v>1</v>
+      </c>
+      <c r="G112" s="2" t="s">
+        <v>791</v>
+      </c>
+      <c r="H112" s="2" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8">
+      <c r="A113" t="s">
+        <v>698</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>523</v>
+      </c>
+      <c r="E113" s="1" t="s">
+        <v>789</v>
+      </c>
+      <c r="F113" s="2">
+        <v>1</v>
+      </c>
+      <c r="G113" s="2" t="s">
+        <v>790</v>
+      </c>
+      <c r="H113" s="2" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8">
+      <c r="A114" t="s">
+        <v>699</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="E114" s="1" t="s">
+        <v>521</v>
+      </c>
+      <c r="F114" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8">
+      <c r="A115" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="C115" s="3">
         <v>13</v>
       </c>
-      <c r="D111" s="4">
-        <v>0</v>
-      </c>
-      <c r="E111" s="1" t="s">
-        <v>335</v>
-      </c>
-      <c r="F111" s="3">
-        <v>0</v>
-      </c>
-      <c r="G111" s="1"/>
-      <c r="H111" s="1" t="s">
-        <v>604</v>
-      </c>
-    </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A112" t="s">
+      <c r="D115" s="5">
+        <v>0</v>
+      </c>
+      <c r="E115" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="F115" s="3">
+        <v>0</v>
+      </c>
+      <c r="G115" s="1"/>
+      <c r="H115" s="1" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8">
+      <c r="A116" t="s">
+        <v>700</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>525</v>
+      </c>
+      <c r="C116" s="2">
+        <v>13</v>
+      </c>
+      <c r="D116" s="6">
+        <v>0</v>
+      </c>
+      <c r="E116" s="1" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8">
+      <c r="A117" t="s">
+        <v>701</v>
+      </c>
+      <c r="B117" s="1" t="s">
         <v>704</v>
-      </c>
-      <c r="B112" s="1" t="s">
-        <v>525</v>
-      </c>
-      <c r="E112" s="1" t="s">
-        <v>526</v>
-      </c>
-      <c r="F112" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A113" t="s">
-        <v>704</v>
-      </c>
-      <c r="B113" s="1" t="s">
-        <v>525</v>
-      </c>
-      <c r="E113" s="1" t="s">
-        <v>531</v>
-      </c>
-      <c r="F113" s="2">
-        <v>0</v>
-      </c>
-      <c r="H113" s="2" t="s">
-        <v>643</v>
-      </c>
-    </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A114" t="s">
-        <v>705</v>
-      </c>
-      <c r="B114" s="1" t="s">
-        <v>527</v>
-      </c>
-      <c r="E114" s="1" t="s">
-        <v>528</v>
-      </c>
-      <c r="F114" s="2">
-        <v>0</v>
-      </c>
-      <c r="H114" s="2" t="s">
-        <v>644</v>
-      </c>
-    </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A115" t="s">
-        <v>706</v>
-      </c>
-      <c r="B115" s="1" t="s">
-        <v>523</v>
-      </c>
-      <c r="E115" s="1" t="s">
-        <v>524</v>
-      </c>
-      <c r="F115" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A116" s="2" t="s">
-        <v>403</v>
-      </c>
-      <c r="B116" s="1" t="s">
-        <v>326</v>
-      </c>
-      <c r="C116" s="3">
-        <v>13</v>
-      </c>
-      <c r="D116" s="5">
-        <v>0</v>
-      </c>
-      <c r="E116" s="1" t="s">
-        <v>327</v>
-      </c>
-      <c r="F116" s="3">
-        <v>0</v>
-      </c>
-      <c r="G116" s="1"/>
-      <c r="H116" s="1" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A117" t="s">
-        <v>707</v>
-      </c>
-      <c r="B117" s="1" t="s">
-        <v>530</v>
       </c>
       <c r="C117" s="2">
         <v>13</v>
@@ -5879,104 +6039,111 @@
         <v>0</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>676</v>
-      </c>
-    </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.3">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8">
       <c r="A118" t="s">
-        <v>708</v>
+        <v>504</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>711</v>
-      </c>
-      <c r="C118" s="2">
-        <v>13</v>
-      </c>
-      <c r="D118" s="6">
+        <v>503</v>
+      </c>
+      <c r="C118" s="3">
+        <v>7</v>
+      </c>
+      <c r="D118" s="4">
         <v>0</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>677</v>
-      </c>
-    </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A119" t="s">
-        <v>507</v>
+        <v>97</v>
+      </c>
+      <c r="F118" s="3">
+        <v>0</v>
+      </c>
+      <c r="G118" s="1"/>
+      <c r="H118" s="1" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8">
+      <c r="A119" s="2" t="s">
+        <v>491</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>506</v>
+        <v>118</v>
       </c>
       <c r="C119" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D119" s="4">
         <v>0</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>97</v>
+        <v>119</v>
       </c>
       <c r="F119" s="3">
         <v>0</v>
       </c>
       <c r="G119" s="1"/>
       <c r="H119" s="1" t="s">
-        <v>646</v>
-      </c>
-    </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.3">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8">
       <c r="A120" s="2" t="s">
         <v>494</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="C120" s="3">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="D120" s="4">
         <v>0</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="F120" s="3">
         <v>0</v>
       </c>
       <c r="G120" s="1"/>
       <c r="H120" s="1" t="s">
-        <v>606</v>
-      </c>
-    </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.3">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8">
       <c r="A121" s="2" t="s">
-        <v>497</v>
+        <v>492</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C121" s="3">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="D121" s="4">
         <v>0</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="F121" s="3">
         <v>0</v>
       </c>
       <c r="G121" s="1"/>
       <c r="H121" s="1" t="s">
-        <v>606</v>
-      </c>
-    </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.3">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8">
       <c r="A122" s="2" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C122" s="3">
         <v>10</v>
@@ -5985,341 +6152,341 @@
         <v>0</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F122" s="3">
         <v>0</v>
       </c>
       <c r="G122" s="1"/>
       <c r="H122" s="1" t="s">
-        <v>606</v>
-      </c>
-    </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.3">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8">
       <c r="A123" s="2" t="s">
-        <v>496</v>
+        <v>527</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="C123" s="3">
-        <v>10</v>
-      </c>
-      <c r="D123" s="4">
-        <v>0</v>
-      </c>
-      <c r="E123" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="F123" s="3">
-        <v>0</v>
-      </c>
-      <c r="G123" s="1"/>
-      <c r="H123" s="1" t="s">
-        <v>606</v>
-      </c>
-    </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.3">
+        <v>526</v>
+      </c>
+      <c r="C123" s="2">
+        <v>30</v>
+      </c>
+      <c r="D123" s="6">
+        <v>0</v>
+      </c>
+      <c r="E123" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="F123" s="2">
+        <v>0</v>
+      </c>
+      <c r="H123" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8">
       <c r="A124" s="2" t="s">
-        <v>533</v>
+        <v>402</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>532</v>
-      </c>
-      <c r="C124" s="2">
-        <v>30</v>
-      </c>
-      <c r="D124" s="6">
-        <v>0</v>
-      </c>
-      <c r="E124" s="2" t="s">
-        <v>534</v>
-      </c>
-      <c r="F124" s="2">
-        <v>0</v>
-      </c>
-      <c r="H124" s="9" t="s">
-        <v>783</v>
-      </c>
-    </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.3">
+        <v>261</v>
+      </c>
+      <c r="C124" s="1"/>
+      <c r="D124" s="1"/>
+      <c r="E124" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="F124" s="3">
+        <v>1</v>
+      </c>
+      <c r="G124" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="H124" s="2" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8">
       <c r="A125" s="2" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="C125" s="1"/>
       <c r="D125" s="1"/>
       <c r="E125" s="1" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="F125" s="3">
         <v>1</v>
       </c>
       <c r="G125" s="1" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="H125" s="2" t="s">
-        <v>607</v>
-      </c>
-    </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.3">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8">
       <c r="A126" s="2" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="C126" s="1"/>
-      <c r="D126" s="1"/>
+        <v>137</v>
+      </c>
+      <c r="C126" s="3">
+        <v>7</v>
+      </c>
+      <c r="D126" s="4">
+        <v>0.91666666666666663</v>
+      </c>
       <c r="E126" s="1" t="s">
-        <v>265</v>
+        <v>138</v>
       </c>
       <c r="F126" s="3">
-        <v>1</v>
-      </c>
-      <c r="G126" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="H126" s="2" t="s">
-        <v>607</v>
-      </c>
-    </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="G126" s="1"/>
+      <c r="H126" s="1" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8">
       <c r="A127" s="2" t="s">
-        <v>406</v>
+        <v>445</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>137</v>
+        <v>234</v>
       </c>
       <c r="C127" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D127" s="4">
-        <v>0.91666666666666663</v>
+        <v>0</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>138</v>
+        <v>235</v>
       </c>
       <c r="F127" s="3">
         <v>0</v>
       </c>
       <c r="G127" s="1"/>
       <c r="H127" s="1" t="s">
-        <v>608</v>
-      </c>
-    </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.3">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8">
       <c r="A128" s="2" t="s">
-        <v>448</v>
+        <v>405</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>234</v>
+        <v>295</v>
       </c>
       <c r="C128" s="3">
         <v>6</v>
       </c>
-      <c r="D128" s="4">
+      <c r="D128" s="5">
         <v>0</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>235</v>
+        <v>296</v>
       </c>
       <c r="F128" s="3">
         <v>0</v>
       </c>
       <c r="G128" s="1"/>
       <c r="H128" s="1" t="s">
-        <v>609</v>
-      </c>
-    </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.3">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8">
       <c r="A129" s="2" t="s">
-        <v>407</v>
+        <v>446</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>297</v>
+        <v>75</v>
       </c>
       <c r="C129" s="3">
         <v>6</v>
       </c>
-      <c r="D129" s="5">
+      <c r="D129" s="4">
         <v>0</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>298</v>
+        <v>76</v>
       </c>
       <c r="F129" s="3">
         <v>0</v>
       </c>
       <c r="G129" s="1"/>
-      <c r="H129" s="1" t="s">
-        <v>647</v>
-      </c>
-    </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H129" s="2" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8">
       <c r="A130" s="2" t="s">
-        <v>449</v>
+        <v>645</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="C130" s="3">
-        <v>6</v>
-      </c>
-      <c r="D130" s="4">
-        <v>0</v>
+        <v>313</v>
+      </c>
+      <c r="C130" s="1">
+        <v>7</v>
+      </c>
+      <c r="D130" s="5">
+        <v>0.91666666666666663</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="F130" s="3">
+        <v>314</v>
+      </c>
+      <c r="F130" s="1">
         <v>0</v>
       </c>
       <c r="G130" s="1"/>
-      <c r="H130" s="2" t="s">
-        <v>610</v>
-      </c>
-    </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H130" s="1" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8">
       <c r="A131" s="2" t="s">
-        <v>652</v>
+        <v>646</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="C131" s="1">
-        <v>7</v>
-      </c>
-      <c r="D131" s="5">
-        <v>0.91666666666666663</v>
-      </c>
+        <v>495</v>
+      </c>
+      <c r="C131" s="1"/>
+      <c r="D131" s="5"/>
       <c r="E131" s="1" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F131" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G131" s="1"/>
       <c r="H131" s="1" t="s">
-        <v>611</v>
-      </c>
-    </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.3">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8">
       <c r="A132" s="2" t="s">
-        <v>653</v>
+        <v>647</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>498</v>
+        <v>302</v>
       </c>
       <c r="C132" s="1"/>
-      <c r="D132" s="5"/>
+      <c r="D132" s="1"/>
       <c r="E132" s="1" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="F132" s="1">
         <v>1</v>
       </c>
       <c r="G132" s="1"/>
       <c r="H132" s="1" t="s">
-        <v>612</v>
-      </c>
-    </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.3">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8">
       <c r="A133" s="2" t="s">
-        <v>654</v>
+        <v>648</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C133" s="1"/>
       <c r="D133" s="1"/>
       <c r="E133" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="F133" s="1">
         <v>1</v>
       </c>
       <c r="G133" s="1"/>
       <c r="H133" s="1" t="s">
-        <v>612</v>
-      </c>
-    </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.3">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8">
       <c r="A134" s="2" t="s">
-        <v>655</v>
+        <v>496</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>305</v>
-      </c>
-      <c r="C134" s="1"/>
-      <c r="D134" s="1"/>
+        <v>248</v>
+      </c>
+      <c r="C134" s="3">
+        <v>6</v>
+      </c>
+      <c r="D134" s="4">
+        <v>0</v>
+      </c>
       <c r="E134" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="F134" s="1">
-        <v>1</v>
+        <v>778</v>
+      </c>
+      <c r="F134" s="3">
+        <v>0</v>
       </c>
       <c r="G134" s="1"/>
       <c r="H134" s="1" t="s">
-        <v>612</v>
-      </c>
-    </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.3">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8">
       <c r="A135" s="2" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C135" s="3">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="D135" s="4">
         <v>0</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>651</v>
+        <v>247</v>
       </c>
       <c r="F135" s="3">
         <v>0</v>
       </c>
       <c r="G135" s="1"/>
-      <c r="H135" s="1" t="s">
-        <v>613</v>
-      </c>
-    </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H135" s="2" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8">
       <c r="A136" s="2" t="s">
-        <v>500</v>
+        <v>457</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>246</v>
+        <v>57</v>
       </c>
       <c r="C136" s="3">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="D136" s="4">
         <v>0</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>247</v>
+        <v>58</v>
       </c>
       <c r="F136" s="3">
         <v>0</v>
       </c>
       <c r="G136" s="1"/>
       <c r="H136" s="2" t="s">
-        <v>614</v>
-      </c>
-    </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.3">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8">
       <c r="A137" s="2" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C137" s="3">
         <v>14</v>
@@ -6328,63 +6495,63 @@
         <v>0</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>58</v>
+        <v>498</v>
       </c>
       <c r="F137" s="3">
         <v>0</v>
       </c>
       <c r="G137" s="1"/>
       <c r="H137" s="2" t="s">
-        <v>615</v>
-      </c>
-    </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.3">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8">
       <c r="A138" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="B138" s="1" t="s">
         <v>462</v>
       </c>
-      <c r="B138" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C138" s="3">
+      <c r="E138" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="F138" s="3">
+        <v>1</v>
+      </c>
+      <c r="H138" s="1" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8">
+      <c r="A139" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="B139" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C139" s="3">
         <v>14</v>
       </c>
-      <c r="D138" s="4">
-        <v>0</v>
-      </c>
-      <c r="E138" s="1" t="s">
-        <v>501</v>
-      </c>
-      <c r="F138" s="3">
-        <v>0</v>
-      </c>
-      <c r="G138" s="1"/>
-      <c r="H138" s="2" t="s">
-        <v>616</v>
-      </c>
-    </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A139" s="2" t="s">
-        <v>464</v>
-      </c>
-      <c r="B139" s="1" t="s">
-        <v>465</v>
+      <c r="D139" s="4">
+        <v>0</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>502</v>
+        <v>60</v>
       </c>
       <c r="F139" s="3">
-        <v>1</v>
-      </c>
-      <c r="H139" s="1" t="s">
-        <v>617</v>
-      </c>
-    </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="G139" s="1"/>
+      <c r="H139" s="2" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8">
       <c r="A140" s="2" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C140" s="3">
         <v>14</v>
@@ -6393,22 +6560,22 @@
         <v>0</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F140" s="3">
         <v>0</v>
       </c>
       <c r="G140" s="1"/>
       <c r="H140" s="2" t="s">
-        <v>618</v>
-      </c>
-    </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.3">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8">
       <c r="A141" s="2" t="s">
-        <v>463</v>
+        <v>406</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>62</v>
+        <v>126</v>
       </c>
       <c r="C141" s="3">
         <v>14</v>
@@ -6417,46 +6584,46 @@
         <v>0</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>63</v>
+        <v>127</v>
       </c>
       <c r="F141" s="3">
         <v>0</v>
       </c>
       <c r="G141" s="1"/>
-      <c r="H141" s="2" t="s">
-        <v>619</v>
-      </c>
-    </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H141" s="1" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8">
       <c r="A142" s="2" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C142" s="3">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D142" s="4">
-        <v>0</v>
+        <v>0.91666666666666663</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F142" s="3">
         <v>0</v>
       </c>
       <c r="G142" s="1"/>
       <c r="H142" s="1" t="s">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.3">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8">
       <c r="A143" s="2" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C143" s="3">
         <v>7</v>
@@ -6465,138 +6632,138 @@
         <v>0.91666666666666663</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>130</v>
+        <v>285</v>
       </c>
       <c r="F143" s="3">
         <v>0</v>
       </c>
       <c r="G143" s="1"/>
       <c r="H143" s="1" t="s">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.3">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8">
       <c r="A144" s="2" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>128</v>
+        <v>290</v>
       </c>
       <c r="C144" s="3">
         <v>7</v>
       </c>
-      <c r="D144" s="4">
-        <v>0.91666666666666663</v>
+      <c r="D144" s="5">
+        <v>0.875</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="F144" s="3">
         <v>0</v>
       </c>
       <c r="G144" s="1"/>
       <c r="H144" s="1" t="s">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="145" spans="1:8" x14ac:dyDescent="0.3">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8">
       <c r="A145" s="2" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>292</v>
+        <v>9</v>
       </c>
       <c r="C145" s="3">
-        <v>7</v>
-      </c>
-      <c r="D145" s="5">
-        <v>0.875</v>
+        <v>6</v>
+      </c>
+      <c r="D145" s="4">
+        <v>0</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>293</v>
+        <v>10</v>
       </c>
       <c r="F145" s="3">
         <v>0</v>
       </c>
       <c r="G145" s="1"/>
-      <c r="H145" s="1" t="s">
-        <v>621</v>
-      </c>
-    </row>
-    <row r="146" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A146" s="2" t="s">
-        <v>412</v>
+      <c r="H145" s="2" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8">
+      <c r="A146" t="s">
+        <v>511</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>9</v>
+        <v>320</v>
       </c>
       <c r="C146" s="3">
-        <v>6</v>
-      </c>
-      <c r="D146" s="4">
+        <v>13</v>
+      </c>
+      <c r="D146" s="5">
         <v>0</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>10</v>
+        <v>321</v>
       </c>
       <c r="F146" s="3">
         <v>0</v>
       </c>
       <c r="G146" s="1"/>
-      <c r="H146" s="2" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="147" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H146" s="1" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8">
       <c r="A147" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="B147" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="C147" s="3">
-        <v>13</v>
-      </c>
-      <c r="D147" s="5">
-        <v>0</v>
-      </c>
+      <c r="C147" s="3"/>
+      <c r="D147" s="5"/>
       <c r="E147" s="1" t="s">
         <v>323</v>
       </c>
       <c r="F147" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G147" s="1"/>
       <c r="H147" s="1" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="148" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A148" t="s">
-        <v>515</v>
+        <v>618</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8">
+      <c r="A148" s="2" t="s">
+        <v>507</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>324</v>
-      </c>
-      <c r="C148" s="3"/>
-      <c r="D148" s="5"/>
+        <v>508</v>
+      </c>
+      <c r="C148" s="3">
+        <v>30</v>
+      </c>
+      <c r="D148" s="5">
+        <v>0</v>
+      </c>
       <c r="E148" s="1" t="s">
-        <v>325</v>
+        <v>509</v>
       </c>
       <c r="F148" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G148" s="1"/>
       <c r="H148" s="1" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="149" spans="1:8" x14ac:dyDescent="0.3">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8">
       <c r="A149" s="2" t="s">
-        <v>510</v>
+        <v>413</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>511</v>
+        <v>300</v>
       </c>
       <c r="C149" s="3">
         <v>30</v>
@@ -6605,152 +6772,152 @@
         <v>0</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>512</v>
+        <v>306</v>
       </c>
       <c r="F149" s="3">
         <v>0</v>
       </c>
       <c r="G149" s="1"/>
       <c r="H149" s="1" t="s">
-        <v>625</v>
-      </c>
-    </row>
-    <row r="150" spans="1:8" x14ac:dyDescent="0.3">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8">
       <c r="A150" s="2" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="C150" s="3">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="D150" s="5">
-        <v>0</v>
+        <v>0.91666666666666663</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>308</v>
+        <v>298</v>
       </c>
       <c r="F150" s="3">
         <v>0</v>
       </c>
       <c r="G150" s="1"/>
       <c r="H150" s="1" t="s">
-        <v>625</v>
-      </c>
-    </row>
-    <row r="151" spans="1:8" x14ac:dyDescent="0.3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8">
       <c r="A151" s="2" t="s">
-        <v>416</v>
+        <v>683</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>300</v>
-      </c>
-      <c r="C151" s="3">
-        <v>7</v>
-      </c>
-      <c r="D151" s="5">
-        <v>0.91666666666666663</v>
+        <v>685</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>300</v>
-      </c>
-      <c r="F151" s="3">
-        <v>0</v>
-      </c>
-      <c r="G151" s="1"/>
-      <c r="H151" s="1" t="s">
-        <v>626</v>
-      </c>
-    </row>
-    <row r="152" spans="1:8" x14ac:dyDescent="0.3">
+        <v>687</v>
+      </c>
+      <c r="F151" s="2">
+        <v>1</v>
+      </c>
+      <c r="H151" s="2" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8">
       <c r="A152" s="2" t="s">
-        <v>690</v>
+        <v>682</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>692</v>
+        <v>684</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>694</v>
+        <v>686</v>
       </c>
       <c r="F152" s="2">
         <v>1</v>
       </c>
       <c r="H152" s="2" t="s">
-        <v>720</v>
-      </c>
-    </row>
-    <row r="153" spans="1:8" x14ac:dyDescent="0.3">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="153" spans="1:8">
       <c r="A153" s="2" t="s">
-        <v>689</v>
+        <v>415</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>691</v>
+        <v>219</v>
+      </c>
+      <c r="C153" s="3">
+        <v>6</v>
+      </c>
+      <c r="D153" s="4">
+        <v>0</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>693</v>
-      </c>
-      <c r="F153" s="2">
-        <v>1</v>
-      </c>
-      <c r="H153" s="2" t="s">
-        <v>719</v>
-      </c>
-    </row>
-    <row r="154" spans="1:8" x14ac:dyDescent="0.3">
+        <v>644</v>
+      </c>
+      <c r="F153" s="3">
+        <v>0</v>
+      </c>
+      <c r="G153" s="1"/>
+      <c r="H153" s="1" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="154" spans="1:8">
       <c r="A154" s="2" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="B154" s="1" t="s">
         <v>219</v>
       </c>
       <c r="C154" s="3">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D154" s="4">
         <v>0</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>650</v>
+        <v>643</v>
       </c>
       <c r="F154" s="3">
         <v>0</v>
       </c>
       <c r="G154" s="1"/>
       <c r="H154" s="1" t="s">
-        <v>627</v>
-      </c>
-    </row>
-    <row r="155" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A155" s="2" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="155" spans="1:8">
+      <c r="A155" t="s">
+        <v>416</v>
+      </c>
+      <c r="B155" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C155" s="3">
+        <v>6</v>
+      </c>
+      <c r="D155" s="4">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="E155" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F155" s="3">
+        <v>0</v>
+      </c>
+      <c r="G155" s="1"/>
+      <c r="H155" s="2" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="156" spans="1:8">
+      <c r="A156" t="s">
         <v>417</v>
       </c>
-      <c r="B155" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="C155" s="3">
-        <v>13</v>
-      </c>
-      <c r="D155" s="4">
-        <v>0</v>
-      </c>
-      <c r="E155" s="1" t="s">
-        <v>649</v>
-      </c>
-      <c r="F155" s="3">
-        <v>0</v>
-      </c>
-      <c r="G155" s="1"/>
-      <c r="H155" s="1" t="s">
-        <v>627</v>
-      </c>
-    </row>
-    <row r="156" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A156" t="s">
-        <v>418</v>
-      </c>
       <c r="B156" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C156" s="3">
         <v>6</v>
@@ -6759,309 +6926,309 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F156" s="3">
         <v>0</v>
       </c>
       <c r="G156" s="1"/>
       <c r="H156" s="2" t="s">
-        <v>628</v>
-      </c>
-    </row>
-    <row r="157" spans="1:8" x14ac:dyDescent="0.3">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="157" spans="1:8">
       <c r="A157" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C157" s="3">
         <v>6</v>
       </c>
       <c r="D157" s="4">
-        <v>0.41666666666666669</v>
+        <v>0.47916666666666669</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="F157" s="3">
         <v>0</v>
       </c>
       <c r="G157" s="1"/>
       <c r="H157" s="2" t="s">
-        <v>628</v>
-      </c>
-    </row>
-    <row r="158" spans="1:8" x14ac:dyDescent="0.3">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="158" spans="1:8">
       <c r="A158" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="C158" s="3">
         <v>6</v>
       </c>
       <c r="D158" s="4">
-        <v>0.47916666666666669</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="F158" s="3">
         <v>0</v>
       </c>
       <c r="G158" s="1"/>
       <c r="H158" s="2" t="s">
-        <v>628</v>
-      </c>
-    </row>
-    <row r="159" spans="1:8" x14ac:dyDescent="0.3">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="159" spans="1:8">
       <c r="A159" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C159" s="3">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D159" s="4">
-        <v>0.41666666666666669</v>
+        <v>0.75</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F159" s="3">
         <v>0</v>
       </c>
       <c r="G159" s="1"/>
       <c r="H159" s="2" t="s">
-        <v>628</v>
-      </c>
-    </row>
-    <row r="160" spans="1:8" x14ac:dyDescent="0.3">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="160" spans="1:8">
       <c r="A160" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="C160" s="3">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D160" s="4">
-        <v>0.75</v>
+        <v>0.4375</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="F160" s="3">
         <v>0</v>
       </c>
       <c r="G160" s="1"/>
       <c r="H160" s="2" t="s">
-        <v>628</v>
-      </c>
-    </row>
-    <row r="161" spans="1:8" x14ac:dyDescent="0.3">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="161" spans="1:8">
       <c r="A161" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C161" s="3">
         <v>6</v>
       </c>
       <c r="D161" s="4">
-        <v>0.4375</v>
+        <v>0.5625</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F161" s="3">
         <v>0</v>
       </c>
       <c r="G161" s="1"/>
       <c r="H161" s="2" t="s">
-        <v>628</v>
-      </c>
-    </row>
-    <row r="162" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A162" t="s">
-        <v>424</v>
+        <v>622</v>
+      </c>
+    </row>
+    <row r="162" spans="1:8">
+      <c r="A162" s="2" t="s">
+        <v>464</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="C162" s="3">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D162" s="4">
-        <v>0.5625</v>
+        <v>0.75</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="F162" s="3">
         <v>0</v>
       </c>
       <c r="G162" s="1"/>
       <c r="H162" s="2" t="s">
-        <v>628</v>
-      </c>
-    </row>
-    <row r="163" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A163" s="2" t="s">
-        <v>467</v>
+        <v>622</v>
+      </c>
+    </row>
+    <row r="163" spans="1:8">
+      <c r="A163" t="s">
+        <v>423</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="C163" s="3">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D163" s="4">
-        <v>0.75</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="F163" s="3">
         <v>0</v>
       </c>
       <c r="G163" s="1"/>
       <c r="H163" s="2" t="s">
-        <v>628</v>
-      </c>
-    </row>
-    <row r="164" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A164" t="s">
-        <v>425</v>
+        <v>622</v>
+      </c>
+    </row>
+    <row r="164" spans="1:8">
+      <c r="A164" s="2" t="s">
+        <v>465</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="C164" s="3">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D164" s="4">
-        <v>0.41666666666666669</v>
+        <v>0.75</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="F164" s="3">
         <v>0</v>
       </c>
       <c r="G164" s="1"/>
       <c r="H164" s="2" t="s">
-        <v>628</v>
-      </c>
-    </row>
-    <row r="165" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A165" s="2" t="s">
-        <v>468</v>
+        <v>622</v>
+      </c>
+    </row>
+    <row r="165" spans="1:8">
+      <c r="A165" t="s">
+        <v>424</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C165" s="3">
         <v>13</v>
       </c>
       <c r="D165" s="4">
-        <v>0.75</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F165" s="3">
         <v>0</v>
       </c>
       <c r="G165" s="1"/>
       <c r="H165" s="2" t="s">
-        <v>628</v>
-      </c>
-    </row>
-    <row r="166" spans="1:8" x14ac:dyDescent="0.3">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="166" spans="1:8">
       <c r="A166" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="C166" s="3">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D166" s="4">
-        <v>0.83333333333333337</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>36</v>
+        <v>286</v>
       </c>
       <c r="F166" s="3">
         <v>0</v>
       </c>
       <c r="G166" s="1"/>
       <c r="H166" s="2" t="s">
-        <v>628</v>
-      </c>
-    </row>
-    <row r="167" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A167" t="s">
-        <v>427</v>
+        <v>622</v>
+      </c>
+    </row>
+    <row r="167" spans="1:8">
+      <c r="A167" s="2" t="s">
+        <v>455</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>22</v>
+        <v>463</v>
       </c>
       <c r="C167" s="3">
-        <v>6</v>
-      </c>
-      <c r="D167" s="4">
-        <v>0.45833333333333331</v>
+        <v>8</v>
+      </c>
+      <c r="D167" s="6">
+        <v>0</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>288</v>
+        <v>456</v>
       </c>
       <c r="F167" s="3">
         <v>0</v>
       </c>
-      <c r="G167" s="1"/>
-      <c r="H167" s="2" t="s">
-        <v>628</v>
-      </c>
-    </row>
-    <row r="168" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H167" s="1" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="168" spans="1:8">
       <c r="A168" s="2" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>466</v>
+        <v>336</v>
       </c>
       <c r="C168" s="3">
-        <v>8</v>
-      </c>
-      <c r="D168" s="6">
+        <v>7</v>
+      </c>
+      <c r="D168" s="4">
         <v>0</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>459</v>
+        <v>93</v>
       </c>
       <c r="F168" s="3">
         <v>0</v>
       </c>
-      <c r="H168" s="1" t="s">
-        <v>629</v>
-      </c>
-    </row>
-    <row r="169" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G168" s="1"/>
+      <c r="H168" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="169" spans="1:8">
       <c r="A169" s="2" t="s">
-        <v>457</v>
+        <v>510</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>338</v>
+        <v>135</v>
       </c>
       <c r="C169" s="3">
         <v>7</v>
@@ -7070,68 +7237,68 @@
         <v>0</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>93</v>
+        <v>338</v>
       </c>
       <c r="F169" s="3">
         <v>0</v>
       </c>
       <c r="G169" s="1"/>
-      <c r="H169" s="9" t="s">
-        <v>784</v>
-      </c>
-    </row>
-    <row r="170" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H169" s="1" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="170" spans="1:8">
       <c r="A170" s="2" t="s">
-        <v>513</v>
+        <v>702</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="C170" s="3">
-        <v>7</v>
-      </c>
-      <c r="D170" s="4">
-        <v>0</v>
-      </c>
+        <v>524</v>
+      </c>
+      <c r="C170" s="3"/>
+      <c r="D170" s="6"/>
       <c r="E170" s="1" t="s">
-        <v>340</v>
+        <v>667</v>
       </c>
       <c r="F170" s="3">
-        <v>0</v>
-      </c>
-      <c r="G170" s="1"/>
-      <c r="H170" s="1" t="s">
-        <v>631</v>
-      </c>
-    </row>
-    <row r="171" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A171" s="2" t="s">
-        <v>709</v>
+        <v>1</v>
+      </c>
+      <c r="G170" s="2" t="s">
+        <v>668</v>
+      </c>
+      <c r="H170" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="171" spans="1:8">
+      <c r="A171" t="s">
+        <v>426</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>529</v>
-      </c>
-      <c r="C171" s="3"/>
-      <c r="D171" s="6"/>
+        <v>205</v>
+      </c>
+      <c r="C171" s="3">
+        <v>6</v>
+      </c>
+      <c r="D171" s="4">
+        <v>0</v>
+      </c>
       <c r="E171" s="1" t="s">
-        <v>674</v>
+        <v>206</v>
       </c>
       <c r="F171" s="3">
-        <v>1</v>
-      </c>
-      <c r="G171" s="2" t="s">
-        <v>675</v>
-      </c>
-      <c r="H171" s="9" t="s">
-        <v>673</v>
-      </c>
-    </row>
-    <row r="172" spans="1:8" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="G171" s="1"/>
+      <c r="H171" s="1" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="172" spans="1:8">
       <c r="A172" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C172" s="3">
         <v>6</v>
@@ -7140,22 +7307,22 @@
         <v>0</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="F172" s="3">
         <v>0</v>
       </c>
       <c r="G172" s="1"/>
       <c r="H172" s="1" t="s">
-        <v>632</v>
-      </c>
-    </row>
-    <row r="173" spans="1:8" x14ac:dyDescent="0.3">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="173" spans="1:8">
       <c r="A173" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="C173" s="3">
         <v>6</v>
@@ -7164,118 +7331,118 @@
         <v>0</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="F173" s="3">
         <v>0</v>
       </c>
       <c r="G173" s="1"/>
       <c r="H173" s="1" t="s">
-        <v>632</v>
-      </c>
-    </row>
-    <row r="174" spans="1:8" x14ac:dyDescent="0.3">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="174" spans="1:8">
       <c r="A174" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>207</v>
+        <v>136</v>
       </c>
       <c r="C174" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D174" s="4">
-        <v>0</v>
+        <v>0.97916666666666663</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>208</v>
+        <v>650</v>
       </c>
       <c r="F174" s="3">
         <v>0</v>
       </c>
       <c r="G174" s="1"/>
       <c r="H174" s="1" t="s">
-        <v>632</v>
-      </c>
-    </row>
-    <row r="175" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A175" t="s">
-        <v>431</v>
+        <v>627</v>
+      </c>
+    </row>
+    <row r="175" spans="1:8">
+      <c r="A175" s="2" t="s">
+        <v>468</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>136</v>
+        <v>64</v>
       </c>
       <c r="C175" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D175" s="4">
-        <v>0.97916666666666663</v>
+        <v>0</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>657</v>
+        <v>649</v>
       </c>
       <c r="F175" s="3">
         <v>0</v>
       </c>
       <c r="G175" s="1"/>
-      <c r="H175" s="1" t="s">
-        <v>633</v>
-      </c>
-    </row>
-    <row r="176" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H175" s="2" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="176" spans="1:8">
       <c r="A176" s="2" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C176" s="3">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D176" s="4">
         <v>0</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>656</v>
+        <v>66</v>
       </c>
       <c r="F176" s="3">
         <v>0</v>
       </c>
       <c r="G176" s="1"/>
       <c r="H176" s="2" t="s">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="177" spans="1:8" x14ac:dyDescent="0.3">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="177" spans="1:8">
       <c r="A177" s="2" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C177" s="3">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D177" s="4">
         <v>0</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="F177" s="3">
         <v>0</v>
       </c>
       <c r="G177" s="1"/>
       <c r="H177" s="2" t="s">
-        <v>635</v>
-      </c>
-    </row>
-    <row r="178" spans="1:8" x14ac:dyDescent="0.3">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="178" spans="1:8">
       <c r="A178" s="2" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C178" s="3">
         <v>6</v>
@@ -7284,22 +7451,22 @@
         <v>0</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F178" s="3">
         <v>0</v>
       </c>
       <c r="G178" s="1"/>
       <c r="H178" s="2" t="s">
-        <v>636</v>
-      </c>
-    </row>
-    <row r="179" spans="1:8" x14ac:dyDescent="0.3">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="179" spans="1:8">
       <c r="A179" s="2" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C179" s="3">
         <v>6</v>
@@ -7308,22 +7475,22 @@
         <v>0</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="F179" s="3">
         <v>0</v>
       </c>
       <c r="G179" s="1"/>
       <c r="H179" s="2" t="s">
-        <v>637</v>
-      </c>
-    </row>
-    <row r="180" spans="1:8" x14ac:dyDescent="0.3">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="180" spans="1:8">
       <c r="A180" s="2" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C180" s="3">
         <v>6</v>
@@ -7332,46 +7499,46 @@
         <v>0</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F180" s="3">
         <v>0</v>
       </c>
       <c r="G180" s="1"/>
       <c r="H180" s="2" t="s">
-        <v>638</v>
-      </c>
-    </row>
-    <row r="181" spans="1:8" x14ac:dyDescent="0.3">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="181" spans="1:8">
       <c r="A181" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="B181" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C181" s="3">
+        <v>7</v>
+      </c>
+      <c r="D181" s="4">
+        <v>0</v>
+      </c>
+      <c r="E181" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="F181" s="3">
+        <v>0</v>
+      </c>
+      <c r="G181" s="1"/>
+      <c r="H181" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="182" spans="1:8">
+      <c r="A182" s="2" t="s">
         <v>476</v>
       </c>
-      <c r="B181" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C181" s="3">
-        <v>6</v>
-      </c>
-      <c r="D181" s="4">
-        <v>0</v>
-      </c>
-      <c r="E181" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="F181" s="3">
-        <v>0</v>
-      </c>
-      <c r="G181" s="1"/>
-      <c r="H181" s="2" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="182" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A182" s="2" t="s">
-        <v>477</v>
-      </c>
       <c r="B182" s="1" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C182" s="3">
         <v>7</v>
@@ -7380,22 +7547,22 @@
         <v>0</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F182" s="3">
         <v>0</v>
       </c>
       <c r="G182" s="1"/>
-      <c r="H182" s="9" t="s">
-        <v>648</v>
-      </c>
-    </row>
-    <row r="183" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H182" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="183" spans="1:8">
       <c r="A183" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="C183" s="3">
         <v>7</v>
@@ -7404,22 +7571,22 @@
         <v>0</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="F183" s="3">
         <v>0</v>
       </c>
       <c r="G183" s="1"/>
-      <c r="H183" s="9" t="s">
-        <v>648</v>
-      </c>
-    </row>
-    <row r="184" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H183" s="1" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="184" spans="1:8">
       <c r="A184" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C184" s="3">
         <v>7</v>
@@ -7428,22 +7595,22 @@
         <v>0</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F184" s="3">
         <v>0</v>
       </c>
       <c r="G184" s="1"/>
       <c r="H184" s="1" t="s">
-        <v>648</v>
-      </c>
-    </row>
-    <row r="185" spans="1:8" x14ac:dyDescent="0.3">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="185" spans="1:8">
       <c r="A185" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="C185" s="3">
         <v>7</v>
@@ -7452,22 +7619,22 @@
         <v>0</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="F185" s="3">
         <v>0</v>
       </c>
       <c r="G185" s="1"/>
       <c r="H185" s="1" t="s">
-        <v>648</v>
-      </c>
-    </row>
-    <row r="186" spans="1:8" x14ac:dyDescent="0.3">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="186" spans="1:8">
       <c r="A186" s="2" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="C186" s="3">
         <v>7</v>
@@ -7476,22 +7643,22 @@
         <v>0</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="F186" s="3">
         <v>0</v>
       </c>
       <c r="G186" s="1"/>
       <c r="H186" s="1" t="s">
-        <v>648</v>
-      </c>
-    </row>
-    <row r="187" spans="1:8" x14ac:dyDescent="0.3">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="187" spans="1:8">
       <c r="A187" s="2" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="C187" s="3">
         <v>7</v>
@@ -7500,22 +7667,22 @@
         <v>0</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="F187" s="3">
         <v>0</v>
       </c>
       <c r="G187" s="1"/>
       <c r="H187" s="1" t="s">
-        <v>648</v>
-      </c>
-    </row>
-    <row r="188" spans="1:8" x14ac:dyDescent="0.3">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="188" spans="1:8">
       <c r="A188" s="2" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="C188" s="3">
         <v>7</v>
@@ -7524,22 +7691,22 @@
         <v>0</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>108</v>
+        <v>475</v>
       </c>
       <c r="F188" s="3">
         <v>0</v>
       </c>
       <c r="G188" s="1"/>
-      <c r="H188" s="1" t="s">
-        <v>648</v>
-      </c>
-    </row>
-    <row r="189" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H188" s="8" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="189" spans="1:8">
       <c r="A189" s="2" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>94</v>
+        <v>111</v>
       </c>
       <c r="C189" s="3">
         <v>7</v>
@@ -7548,70 +7715,70 @@
         <v>0</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>478</v>
+        <v>112</v>
       </c>
       <c r="F189" s="3">
         <v>0</v>
       </c>
       <c r="G189" s="1"/>
-      <c r="H189" s="8" t="s">
-        <v>648</v>
-      </c>
-    </row>
-    <row r="190" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A190" s="2" t="s">
-        <v>486</v>
+      <c r="H189" s="1" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="190" spans="1:8">
+      <c r="A190" t="s">
+        <v>430</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>111</v>
+        <v>288</v>
       </c>
       <c r="C190" s="3">
-        <v>7</v>
-      </c>
-      <c r="D190" s="4">
+        <v>13</v>
+      </c>
+      <c r="D190" s="5">
         <v>0</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>112</v>
+        <v>289</v>
       </c>
       <c r="F190" s="3">
         <v>0</v>
       </c>
       <c r="G190" s="1"/>
       <c r="H190" s="1" t="s">
-        <v>648</v>
-      </c>
-    </row>
-    <row r="191" spans="1:8" x14ac:dyDescent="0.3">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="191" spans="1:8">
       <c r="A191" t="s">
-        <v>432</v>
+        <v>513</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>290</v>
+        <v>209</v>
       </c>
       <c r="C191" s="3">
-        <v>13</v>
-      </c>
-      <c r="D191" s="5">
+        <v>6</v>
+      </c>
+      <c r="D191" s="4">
         <v>0</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>291</v>
+        <v>210</v>
       </c>
       <c r="F191" s="3">
         <v>0</v>
       </c>
       <c r="G191" s="1"/>
       <c r="H191" s="1" t="s">
-        <v>640</v>
-      </c>
-    </row>
-    <row r="192" spans="1:8" x14ac:dyDescent="0.3">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="192" spans="1:8">
       <c r="A192" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C192" s="3">
         <v>6</v>
@@ -7620,22 +7787,22 @@
         <v>0</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="F192" s="3">
         <v>0</v>
       </c>
       <c r="G192" s="1"/>
       <c r="H192" s="1" t="s">
-        <v>641</v>
-      </c>
-    </row>
-    <row r="193" spans="1:8" x14ac:dyDescent="0.3">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="193" spans="1:8">
       <c r="A193" t="s">
         <v>517</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="C193" s="3">
         <v>6</v>
@@ -7644,22 +7811,22 @@
         <v>0</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="F193" s="3">
         <v>0</v>
       </c>
       <c r="G193" s="1"/>
       <c r="H193" s="1" t="s">
-        <v>641</v>
-      </c>
-    </row>
-    <row r="194" spans="1:8" x14ac:dyDescent="0.3">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="194" spans="1:8">
       <c r="A194" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C194" s="3">
         <v>6</v>
@@ -7668,22 +7835,22 @@
         <v>0</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="F194" s="3">
         <v>0</v>
       </c>
       <c r="G194" s="1"/>
       <c r="H194" s="1" t="s">
-        <v>641</v>
-      </c>
-    </row>
-    <row r="195" spans="1:8" x14ac:dyDescent="0.3">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="195" spans="1:8">
       <c r="A195" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C195" s="3">
         <v>6</v>
@@ -7692,426 +7859,598 @@
         <v>0</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>215</v>
+        <v>518</v>
       </c>
       <c r="F195" s="3">
         <v>0</v>
       </c>
       <c r="G195" s="1"/>
       <c r="H195" s="1" t="s">
-        <v>641</v>
-      </c>
-    </row>
-    <row r="196" spans="1:8" x14ac:dyDescent="0.3">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="196" spans="1:8">
       <c r="A196" t="s">
-        <v>518</v>
+        <v>431</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="C196" s="3">
-        <v>6</v>
-      </c>
-      <c r="D196" s="4">
-        <v>0</v>
-      </c>
+        <v>304</v>
+      </c>
+      <c r="C196" s="1"/>
+      <c r="D196" s="1"/>
       <c r="E196" s="1" t="s">
-        <v>521</v>
-      </c>
-      <c r="F196" s="3">
-        <v>0</v>
+        <v>319</v>
+      </c>
+      <c r="F196" s="1">
+        <v>1</v>
       </c>
       <c r="G196" s="1"/>
       <c r="H196" s="1" t="s">
-        <v>641</v>
-      </c>
-    </row>
-    <row r="197" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A197" t="s">
-        <v>433</v>
+        <v>636</v>
+      </c>
+    </row>
+    <row r="197" spans="1:8">
+      <c r="A197" s="2" t="s">
+        <v>706</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="C197" s="1"/>
-      <c r="D197" s="1"/>
+        <v>707</v>
+      </c>
       <c r="E197" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="F197" s="1">
+        <v>710</v>
+      </c>
+      <c r="F197" s="3">
         <v>1</v>
       </c>
-      <c r="G197" s="1"/>
-      <c r="H197" s="1" t="s">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="198" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H197" s="9" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="198" spans="1:8">
       <c r="A198" s="2" t="s">
-        <v>713</v>
+        <v>708</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>714</v>
+        <v>709</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>717</v>
+        <v>711</v>
       </c>
       <c r="F198" s="3">
         <v>1</v>
       </c>
-      <c r="H198" s="10" t="s">
-        <v>761</v>
-      </c>
-    </row>
-    <row r="199" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H198" s="9" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="199" spans="1:8">
       <c r="A199" s="2" t="s">
         <v>715</v>
       </c>
       <c r="B199" s="1" t="s">
         <v>716</v>
       </c>
+      <c r="C199" s="2">
+        <v>6</v>
+      </c>
+      <c r="D199" s="6">
+        <v>0</v>
+      </c>
       <c r="E199" s="1" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="F199" s="3">
-        <v>1</v>
-      </c>
-      <c r="H199" s="10" t="s">
-        <v>760</v>
-      </c>
-    </row>
-    <row r="200" spans="1:8" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="H199" s="7" t="s">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="200" spans="1:8">
       <c r="A200" s="2" t="s">
         <v>722</v>
       </c>
       <c r="B200" s="1" t="s">
+        <v>719</v>
+      </c>
+      <c r="C200" s="2">
+        <v>7</v>
+      </c>
+      <c r="D200" s="6">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="E200" s="1" t="s">
+        <v>720</v>
+      </c>
+      <c r="F200" s="3">
+        <v>0</v>
+      </c>
+      <c r="H200" s="7" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="201" spans="1:8">
+      <c r="A201" s="2" t="s">
         <v>723</v>
       </c>
-      <c r="C200" s="2">
-        <v>6</v>
-      </c>
-      <c r="D200" s="6">
-        <v>0</v>
-      </c>
-      <c r="E200" s="1" t="s">
+      <c r="B201" s="1" t="s">
         <v>724</v>
       </c>
-      <c r="F200" s="3">
-        <v>0</v>
-      </c>
-      <c r="H200" s="7" t="s">
-        <v>762</v>
-      </c>
-    </row>
-    <row r="201" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A201" s="2" t="s">
-        <v>729</v>
-      </c>
-      <c r="B201" s="1" t="s">
+      <c r="E201" s="1" t="s">
+        <v>752</v>
+      </c>
+      <c r="F201" s="3">
+        <v>1</v>
+      </c>
+      <c r="H201" s="7" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="202" spans="1:8">
+      <c r="A202" s="2" t="s">
+        <v>725</v>
+      </c>
+      <c r="B202" s="1" t="s">
         <v>726</v>
       </c>
-      <c r="C201" s="2">
-        <v>7</v>
-      </c>
-      <c r="D201" s="6">
-        <v>0.95833333333333337</v>
-      </c>
-      <c r="E201" s="1" t="s">
-        <v>727</v>
-      </c>
-      <c r="F201" s="3">
-        <v>0</v>
-      </c>
-      <c r="H201" s="7" t="s">
-        <v>728</v>
-      </c>
-    </row>
-    <row r="202" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A202" s="2" t="s">
-        <v>730</v>
-      </c>
-      <c r="B202" s="1" t="s">
-        <v>731</v>
-      </c>
       <c r="E202" s="1" t="s">
-        <v>759</v>
+        <v>756</v>
       </c>
       <c r="F202" s="3">
         <v>1</v>
       </c>
       <c r="H202" s="7" t="s">
-        <v>780</v>
-      </c>
-    </row>
-    <row r="203" spans="1:8" x14ac:dyDescent="0.3">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="203" spans="1:8">
       <c r="A203" s="2" t="s">
-        <v>732</v>
+        <v>727</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>733</v>
+        <v>728</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>763</v>
+        <v>757</v>
       </c>
       <c r="F203" s="3">
         <v>1</v>
       </c>
       <c r="H203" s="7" t="s">
-        <v>780</v>
-      </c>
-    </row>
-    <row r="204" spans="1:8" x14ac:dyDescent="0.3">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="204" spans="1:8">
       <c r="A204" s="2" t="s">
-        <v>734</v>
+        <v>729</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>735</v>
+        <v>730</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>764</v>
+        <v>758</v>
       </c>
       <c r="F204" s="3">
         <v>1</v>
       </c>
       <c r="H204" s="7" t="s">
-        <v>780</v>
-      </c>
-    </row>
-    <row r="205" spans="1:8" x14ac:dyDescent="0.3">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="205" spans="1:8">
       <c r="A205" s="2" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>737</v>
+        <v>731</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>765</v>
+        <v>759</v>
       </c>
       <c r="F205" s="3">
         <v>1</v>
       </c>
       <c r="H205" s="7" t="s">
-        <v>780</v>
-      </c>
-    </row>
-    <row r="206" spans="1:8" x14ac:dyDescent="0.3">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="206" spans="1:8">
       <c r="A206" s="2" t="s">
-        <v>740</v>
+        <v>732</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>738</v>
+        <v>734</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>766</v>
+        <v>760</v>
       </c>
       <c r="F206" s="3">
         <v>1</v>
       </c>
       <c r="H206" s="7" t="s">
-        <v>780</v>
-      </c>
-    </row>
-    <row r="207" spans="1:8" x14ac:dyDescent="0.3">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="207" spans="1:8">
       <c r="A207" s="2" t="s">
-        <v>739</v>
+        <v>735</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>741</v>
+        <v>736</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>767</v>
+        <v>761</v>
       </c>
       <c r="F207" s="3">
         <v>1</v>
       </c>
       <c r="H207" s="7" t="s">
-        <v>780</v>
-      </c>
-    </row>
-    <row r="208" spans="1:8" x14ac:dyDescent="0.3">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="208" spans="1:8">
       <c r="A208" s="2" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>743</v>
+        <v>738</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>768</v>
+        <v>762</v>
       </c>
       <c r="F208" s="3">
         <v>1</v>
       </c>
       <c r="H208" s="7" t="s">
-        <v>780</v>
-      </c>
-    </row>
-    <row r="209" spans="1:8" x14ac:dyDescent="0.3">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="209" spans="1:8">
       <c r="A209" s="2" t="s">
-        <v>744</v>
+        <v>739</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>745</v>
+        <v>740</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>769</v>
+        <v>763</v>
       </c>
       <c r="F209" s="3">
         <v>1</v>
       </c>
       <c r="H209" s="7" t="s">
-        <v>780</v>
-      </c>
-    </row>
-    <row r="210" spans="1:8" x14ac:dyDescent="0.3">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="210" spans="1:8">
       <c r="A210" s="2" t="s">
-        <v>746</v>
+        <v>741</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>747</v>
+        <v>742</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>770</v>
+        <v>764</v>
       </c>
       <c r="F210" s="3">
         <v>1</v>
       </c>
       <c r="H210" s="7" t="s">
-        <v>780</v>
-      </c>
-    </row>
-    <row r="211" spans="1:8" x14ac:dyDescent="0.3">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="211" spans="1:8">
       <c r="A211" s="2" t="s">
-        <v>748</v>
+        <v>743</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>749</v>
+        <v>744</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>771</v>
+        <v>765</v>
       </c>
       <c r="F211" s="3">
         <v>1</v>
       </c>
       <c r="H211" s="7" t="s">
-        <v>780</v>
-      </c>
-    </row>
-    <row r="212" spans="1:8" x14ac:dyDescent="0.3">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="212" spans="1:8">
       <c r="A212" s="2" t="s">
-        <v>750</v>
+        <v>745</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>751</v>
+        <v>746</v>
       </c>
       <c r="E212" s="1" t="s">
-        <v>772</v>
+        <v>766</v>
       </c>
       <c r="F212" s="3">
         <v>1</v>
       </c>
       <c r="H212" s="7" t="s">
-        <v>780</v>
-      </c>
-    </row>
-    <row r="213" spans="1:8" x14ac:dyDescent="0.3">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="213" spans="1:8">
       <c r="A213" s="2" t="s">
-        <v>752</v>
+        <v>747</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>753</v>
+        <v>718</v>
       </c>
       <c r="E213" s="1" t="s">
-        <v>773</v>
+        <v>767</v>
       </c>
       <c r="F213" s="3">
         <v>1</v>
       </c>
       <c r="H213" s="7" t="s">
-        <v>780</v>
-      </c>
-    </row>
-    <row r="214" spans="1:8" x14ac:dyDescent="0.3">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="214" spans="1:8">
       <c r="A214" s="2" t="s">
-        <v>754</v>
+        <v>748</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>725</v>
+        <v>749</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>774</v>
+        <v>768</v>
       </c>
       <c r="F214" s="3">
         <v>1</v>
       </c>
       <c r="H214" s="7" t="s">
-        <v>780</v>
-      </c>
-    </row>
-    <row r="215" spans="1:8" x14ac:dyDescent="0.3">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="215" spans="1:8">
       <c r="A215" s="2" t="s">
-        <v>755</v>
+        <v>750</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>756</v>
+        <v>751</v>
       </c>
       <c r="E215" s="1" t="s">
-        <v>775</v>
+        <v>769</v>
       </c>
       <c r="F215" s="3">
         <v>1</v>
       </c>
       <c r="H215" s="7" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="216" spans="1:8">
+      <c r="A216" s="2" t="s">
+        <v>779</v>
+      </c>
+      <c r="B216" s="1" t="s">
+        <v>770</v>
+      </c>
+      <c r="C216" s="2">
+        <v>6</v>
+      </c>
+      <c r="D216" s="6">
+        <v>0</v>
+      </c>
+      <c r="E216" s="10" t="s">
+        <v>783</v>
+      </c>
+      <c r="F216" s="3">
+        <v>0</v>
+      </c>
+      <c r="H216" s="2" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="217" spans="1:8">
+      <c r="A217" s="2" t="s">
         <v>780</v>
       </c>
-    </row>
-    <row r="216" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A216" s="2" t="s">
-        <v>757</v>
-      </c>
-      <c r="B216" s="1" t="s">
-        <v>758</v>
-      </c>
-      <c r="E216" s="1" t="s">
-        <v>776</v>
-      </c>
-      <c r="F216" s="3">
+      <c r="B217" s="1" t="s">
+        <v>771</v>
+      </c>
+      <c r="C217" s="2">
+        <v>6</v>
+      </c>
+      <c r="D217" s="6">
+        <v>0</v>
+      </c>
+      <c r="E217" s="1" t="s">
+        <v>784</v>
+      </c>
+      <c r="F217" s="3">
+        <v>0</v>
+      </c>
+      <c r="H217" s="2" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="218" spans="1:8">
+      <c r="A218" s="2" t="s">
+        <v>781</v>
+      </c>
+      <c r="B218" s="1" t="s">
+        <v>772</v>
+      </c>
+      <c r="C218" s="2">
+        <v>6</v>
+      </c>
+      <c r="D218" s="6">
+        <v>0</v>
+      </c>
+      <c r="E218" s="1" t="s">
+        <v>785</v>
+      </c>
+      <c r="F218" s="3">
+        <v>0</v>
+      </c>
+      <c r="H218" s="2" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="219" spans="1:8">
+      <c r="A219" s="2" t="s">
+        <v>792</v>
+      </c>
+      <c r="B219" s="1" t="s">
+        <v>793</v>
+      </c>
+      <c r="E219" s="1" t="s">
+        <v>794</v>
+      </c>
+      <c r="F219" s="3">
         <v>1</v>
       </c>
-      <c r="H216" s="7" t="s">
-        <v>780</v>
-      </c>
-    </row>
-    <row r="217" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B217" s="1" t="s">
-        <v>777</v>
-      </c>
-      <c r="E217" s="7"/>
-    </row>
-    <row r="218" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B218" s="1" t="s">
-        <v>778</v>
-      </c>
-    </row>
-    <row r="219" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B219" s="1" t="s">
-        <v>779</v>
+      <c r="H219" s="2" t="s">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="220" spans="1:8">
+      <c r="A220" s="2" t="s">
+        <v>796</v>
+      </c>
+      <c r="B220" s="1" t="s">
+        <v>797</v>
+      </c>
+      <c r="E220" s="1" t="s">
+        <v>798</v>
+      </c>
+      <c r="F220" s="3">
+        <v>1</v>
+      </c>
+      <c r="H220" s="7" t="s">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="221" spans="1:8">
+      <c r="A221" s="2" t="s">
+        <v>800</v>
+      </c>
+      <c r="B221" s="1" t="s">
+        <v>801</v>
+      </c>
+      <c r="E221" s="1" t="s">
+        <v>802</v>
+      </c>
+      <c r="F221" s="3">
+        <v>1</v>
+      </c>
+      <c r="H221" s="2" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="222" spans="1:8">
+      <c r="A222" s="2" t="s">
+        <v>803</v>
+      </c>
+      <c r="B222" s="1" t="s">
+        <v>804</v>
+      </c>
+      <c r="E222" s="1" t="s">
+        <v>807</v>
+      </c>
+      <c r="F222" s="3">
+        <v>1</v>
+      </c>
+      <c r="H222" s="2" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="223" spans="1:8">
+      <c r="A223" s="2" t="s">
+        <v>809</v>
+      </c>
+      <c r="B223" s="1" t="s">
+        <v>810</v>
+      </c>
+      <c r="E223" s="1" t="s">
+        <v>811</v>
+      </c>
+      <c r="F223" s="3">
+        <v>1</v>
+      </c>
+      <c r="H223" s="2" t="s">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="224" spans="1:8">
+      <c r="A224" s="2" t="s">
+        <v>813</v>
+      </c>
+      <c r="B224" s="1" t="s">
+        <v>814</v>
+      </c>
+      <c r="E224" s="1" t="s">
+        <v>815</v>
+      </c>
+      <c r="F224" s="3">
+        <v>1</v>
+      </c>
+      <c r="H224" s="2" t="s">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="225" spans="1:8">
+      <c r="A225" s="2" t="s">
+        <v>817</v>
+      </c>
+      <c r="B225" s="1" t="s">
+        <v>818</v>
+      </c>
+      <c r="E225" s="1" t="s">
+        <v>819</v>
+      </c>
+      <c r="F225" s="3">
+        <v>1</v>
+      </c>
+      <c r="H225" s="2" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="226" spans="1:8">
+      <c r="A226" s="2" t="s">
+        <v>821</v>
+      </c>
+      <c r="B226" s="1" t="s">
+        <v>823</v>
+      </c>
+      <c r="C226" s="2">
+        <v>20</v>
+      </c>
+      <c r="D226" s="6">
+        <v>0</v>
+      </c>
+      <c r="E226" s="1" t="s">
+        <v>822</v>
+      </c>
+      <c r="F226" s="2">
+        <v>0</v>
+      </c>
+      <c r="H226" s="2" t="s">
+        <v>820</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H197">
-    <sortCondition ref="B2:B197"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H196">
+    <sortCondition ref="B2:B196"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="H189" r:id="rId1" xr:uid="{08510EB6-59FE-461F-9934-59900452DB70}"/>
-    <hyperlink ref="H201" r:id="rId2" xr:uid="{092C464B-EEF0-45C5-9E7F-9E5BB1389ECD}"/>
-    <hyperlink ref="H200" r:id="rId3" xr:uid="{D8D98BE9-F998-4931-BC78-1FA8DBB2DF8D}"/>
-    <hyperlink ref="H199" r:id="rId4" xr:uid="{3BEBF5F8-81B1-4909-98FA-8DDD635C8EA6}"/>
-    <hyperlink ref="H198" r:id="rId5" xr:uid="{65D202DC-0DAE-445A-B96C-C36AAC898769}"/>
-    <hyperlink ref="H202" r:id="rId6" xr:uid="{25A9BA66-0BC2-4AD9-A0BE-F4C36298AC2D}"/>
-    <hyperlink ref="H203:H216" r:id="rId7" display="http://www.murderparker.com/" xr:uid="{E958893D-4F52-4648-BDD7-4971EF621EF9}"/>
+    <hyperlink ref="H188" r:id="rId1" xr:uid="{08510EB6-59FE-461F-9934-59900452DB70}"/>
+    <hyperlink ref="H200" r:id="rId2" xr:uid="{092C464B-EEF0-45C5-9E7F-9E5BB1389ECD}"/>
+    <hyperlink ref="H199" r:id="rId3" xr:uid="{D8D98BE9-F998-4931-BC78-1FA8DBB2DF8D}"/>
+    <hyperlink ref="H198" r:id="rId4" xr:uid="{3BEBF5F8-81B1-4909-98FA-8DDD635C8EA6}"/>
+    <hyperlink ref="H197" r:id="rId5" xr:uid="{65D202DC-0DAE-445A-B96C-C36AAC898769}"/>
+    <hyperlink ref="H201" r:id="rId6" xr:uid="{25A9BA66-0BC2-4AD9-A0BE-F4C36298AC2D}"/>
+    <hyperlink ref="H202:H215" r:id="rId7" display="http://www.murderparker.com/" xr:uid="{E958893D-4F52-4648-BDD7-4971EF621EF9}"/>
+    <hyperlink ref="H220" r:id="rId8" xr:uid="{4B96B214-31AC-4DCE-B6F6-D54C0FEB4666}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId8"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId9"/>
 </worksheet>
 </file>
--- a/stores.xlsx
+++ b/stores.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\YUMIN\Desktop\B0KT2A_RSVN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{540738B7-C9EC-48AA-AEA8-592F77160A40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B31AB1EF-35C8-448E-B07F-E9019B7DEB75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{ABFC3117-FCCB-4FF3-804A-FE19451A2004}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="911" uniqueCount="824">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="915" uniqueCount="829">
   <si>
     <t>룸익스케이프 WHITE</t>
   </si>
@@ -300,9 +300,6 @@
     <t>넥스트에디션 건대2호점</t>
   </si>
   <si>
-    <t>넥스트에디션 강남5호점</t>
-  </si>
-  <si>
     <t>플레이포인트랩 부산서면오리진점</t>
   </si>
   <si>
@@ -402,12 +399,6 @@
     <t>거상,졸업,하이팜</t>
   </si>
   <si>
-    <t>싸인이스케이프 인계점</t>
-  </si>
-  <si>
-    <t>신비의베이커리,악은어디에나존재한다,트라이위저드,GATE:CCZ,NEW,뉴</t>
-  </si>
-  <si>
     <t>싸인이스케이프 성대역점</t>
   </si>
   <si>
@@ -1074,10 +1065,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>SOS,에스오에스,그래도피망은먹기싫단말이에욧,그피망,BANK RUPT,뱅크럽,우리동네김선의</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>신촌성심병원,CHASER:한마음폐공장,HANNA IS FIRED,한나는해고됐어,플로이드호텔,FLOYD HOTEL</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1178,10 +1165,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>ne_gn5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>ne_bnr</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1734,10 +1717,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>se_ig</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>se_hd</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1909,9 +1888,6 @@
     <t>https://xn--910bj3tlmfz4e.com/</t>
   </si>
   <si>
-    <t>https://naver.me/5fIpux7C</t>
-  </si>
-  <si>
     <t>https://naver.me/FDnPXiO0</t>
   </si>
   <si>
@@ -2919,6 +2895,51 @@
   <si>
     <t>더 코드 광주</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cn_gr</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>코난 방탈출</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>미대생의죽음,악마를보았다,버스안에서,대저택의비밀,의문의의뢰편지</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://www.conanescape.kr/</t>
+  </si>
+  <si>
+    <t>mi_ro</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>방탈출미로</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://naver.me/5S9QxwaA</t>
+  </si>
+  <si>
+    <t>PINO,피노,무속인살인사건,호텔:사라진다이아몬드,프로젝트:노아,연:그날의기억</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>str_mk</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스토리메이커스</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n,엔</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://naver.me/FCrTZq6Q</t>
   </si>
 </sst>
 </file>
@@ -3334,7 +3355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D839462D-4719-40BB-8925-C1B9F93734CF}">
-  <dimension ref="A1:H226"/>
+  <dimension ref="A1:H227"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="2"/>
@@ -3349,7 +3370,7 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="2" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>11</v>
@@ -3375,10 +3396,10 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="2" t="s">
-        <v>655</v>
+        <v>648</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>652</v>
+        <v>645</v>
       </c>
       <c r="C2" s="2">
         <v>7</v>
@@ -3387,21 +3408,21 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>653</v>
+        <v>646</v>
       </c>
       <c r="F2" s="2">
         <v>0</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>654</v>
+        <v>647</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="2" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="C3" s="3">
         <v>6</v>
@@ -3410,22 +3431,22 @@
         <v>0</v>
       </c>
       <c r="E3" t="s">
-        <v>519</v>
+        <v>513</v>
       </c>
       <c r="F3" s="3">
         <v>0</v>
       </c>
       <c r="G3" s="1"/>
       <c r="H3" s="1" t="s">
-        <v>529</v>
+        <v>523</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="2" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="C4" s="3">
         <v>7</v>
@@ -3434,42 +3455,42 @@
         <v>0</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="F4" s="3">
         <v>0</v>
       </c>
       <c r="G4" s="1"/>
       <c r="H4" s="1" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="2" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C5" s="3"/>
       <c r="D5" s="4"/>
       <c r="E5" s="1" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="F5" s="3">
         <v>1</v>
       </c>
       <c r="G5" s="1"/>
       <c r="H5" s="1" t="s">
-        <v>531</v>
+        <v>525</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="2" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="C6" s="3">
         <v>7</v>
@@ -3478,22 +3499,22 @@
         <v>0</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="F6" s="3">
         <v>0</v>
       </c>
       <c r="G6" s="1"/>
       <c r="H6" t="s">
-        <v>532</v>
+        <v>526</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="2" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="C7" s="3">
         <v>7</v>
@@ -3502,22 +3523,22 @@
         <v>0</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="F7" s="3">
         <v>0</v>
       </c>
       <c r="G7" s="1"/>
       <c r="H7" t="s">
-        <v>532</v>
+        <v>526</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="2" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="C8" s="3">
         <v>13</v>
@@ -3526,22 +3547,22 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="F8" s="3">
         <v>0</v>
       </c>
       <c r="G8" s="1"/>
       <c r="H8" s="1" t="s">
-        <v>533</v>
+        <v>527</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="2" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C9" s="3">
         <v>13</v>
@@ -3550,22 +3571,22 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="F9" s="3">
         <v>0</v>
       </c>
       <c r="G9" s="1"/>
       <c r="H9" s="1" t="s">
-        <v>534</v>
+        <v>528</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="2" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="C10" s="3">
         <v>9</v>
@@ -3574,22 +3595,22 @@
         <v>0</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="F10" s="3">
         <v>0</v>
       </c>
       <c r="G10" s="1"/>
       <c r="H10" s="1" t="s">
-        <v>535</v>
+        <v>529</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="2" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="C11" s="3">
         <v>9</v>
@@ -3598,22 +3619,22 @@
         <v>0</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="F11" s="3">
         <v>0</v>
       </c>
       <c r="G11" s="1"/>
       <c r="H11" s="1" t="s">
-        <v>535</v>
+        <v>529</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="2" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="C12" s="3">
         <v>9</v>
@@ -3622,22 +3643,22 @@
         <v>0</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="F12" s="3">
         <v>0</v>
       </c>
       <c r="G12" s="1"/>
       <c r="H12" s="1" t="s">
-        <v>535</v>
+        <v>529</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="2" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="C13" s="3">
         <v>6</v>
@@ -3646,22 +3667,22 @@
         <v>0</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F13" s="3">
         <v>0</v>
       </c>
       <c r="G13" s="1"/>
       <c r="H13" s="1" t="s">
-        <v>536</v>
+        <v>530</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="2" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="C14" s="3">
         <v>6</v>
@@ -3670,22 +3691,22 @@
         <v>0</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="F14" s="3">
         <v>0</v>
       </c>
       <c r="G14" s="1"/>
       <c r="H14" s="1" t="s">
-        <v>536</v>
+        <v>530</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="2" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C15" s="3">
         <v>13</v>
@@ -3694,166 +3715,166 @@
         <v>0</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="F15" s="3">
         <v>0</v>
       </c>
       <c r="G15" s="1"/>
       <c r="H15" s="1" t="s">
-        <v>537</v>
+        <v>531</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="2" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="C16" s="3">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="D16" s="4">
         <v>0</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>327</v>
+        <v>84</v>
       </c>
       <c r="F16" s="3">
         <v>0</v>
       </c>
       <c r="G16" s="1"/>
       <c r="H16" s="1" t="s">
-        <v>538</v>
+        <v>532</v>
       </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="2" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C17" s="3">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="D17" s="4">
         <v>0</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F17" s="3">
         <v>0</v>
       </c>
       <c r="G17" s="1"/>
       <c r="H17" s="1" t="s">
-        <v>539</v>
+        <v>533</v>
       </c>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="2" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C18" s="3">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="D18" s="4">
         <v>0</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>86</v>
+        <v>289</v>
       </c>
       <c r="F18" s="3">
         <v>0</v>
       </c>
       <c r="G18" s="1"/>
       <c r="H18" s="1" t="s">
-        <v>540</v>
+        <v>534</v>
       </c>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="2" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="C19" s="3">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="D19" s="4">
         <v>0</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>292</v>
+        <v>82</v>
       </c>
       <c r="F19" s="3">
         <v>0</v>
       </c>
       <c r="G19" s="1"/>
       <c r="H19" s="1" t="s">
-        <v>541</v>
+        <v>535</v>
       </c>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="2" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>81</v>
+        <v>330</v>
       </c>
       <c r="C20" s="3">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D20" s="4">
         <v>0</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>82</v>
+        <v>331</v>
       </c>
       <c r="F20" s="3">
         <v>0</v>
       </c>
       <c r="G20" s="1"/>
       <c r="H20" s="1" t="s">
-        <v>542</v>
+        <v>536</v>
       </c>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="2" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>334</v>
+        <v>79</v>
       </c>
       <c r="C21" s="3">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D21" s="4">
         <v>0</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>335</v>
+        <v>80</v>
       </c>
       <c r="F21" s="3">
         <v>0</v>
       </c>
       <c r="G21" s="1"/>
       <c r="H21" s="1" t="s">
-        <v>543</v>
+        <v>537</v>
       </c>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="2" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C22" s="3">
         <v>28</v>
@@ -3862,46 +3883,45 @@
         <v>0</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F22" s="3">
         <v>0</v>
       </c>
       <c r="G22" s="1"/>
       <c r="H22" s="1" t="s">
-        <v>544</v>
+        <v>538</v>
       </c>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="2" t="s">
-        <v>360</v>
+        <v>446</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>77</v>
+        <v>444</v>
       </c>
       <c r="C23" s="3">
-        <v>28</v>
-      </c>
-      <c r="D23" s="4">
+        <v>6</v>
+      </c>
+      <c r="D23" s="6">
         <v>0</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>78</v>
+        <v>448</v>
       </c>
       <c r="F23" s="3">
         <v>0</v>
       </c>
-      <c r="G23" s="1"/>
       <c r="H23" s="1" t="s">
-        <v>545</v>
+        <v>539</v>
       </c>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="2" t="s">
-        <v>451</v>
+        <v>445</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="C24" s="3">
         <v>6</v>
@@ -3910,44 +3930,45 @@
         <v>0</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>453</v>
+        <v>447</v>
       </c>
       <c r="F24" s="3">
         <v>0</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>546</v>
+        <v>539</v>
       </c>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="2" t="s">
-        <v>450</v>
+        <v>356</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>448</v>
+        <v>141</v>
       </c>
       <c r="C25" s="3">
         <v>6</v>
       </c>
-      <c r="D25" s="6">
+      <c r="D25" s="4">
         <v>0</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>452</v>
+        <v>142</v>
       </c>
       <c r="F25" s="3">
         <v>0</v>
       </c>
+      <c r="G25" s="1"/>
       <c r="H25" s="1" t="s">
-        <v>546</v>
+        <v>540</v>
       </c>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="2" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C26" s="3">
         <v>6</v>
@@ -3956,360 +3977,304 @@
         <v>0</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>145</v>
+        <v>281</v>
       </c>
       <c r="F26" s="3">
         <v>0</v>
       </c>
       <c r="G26" s="1"/>
       <c r="H26" s="1" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="2" t="s">
-        <v>362</v>
+        <v>802</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="C27" s="3">
-        <v>6</v>
-      </c>
-      <c r="D27" s="4">
-        <v>0</v>
+        <v>803</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>284</v>
+        <v>804</v>
       </c>
       <c r="F27" s="3">
-        <v>0</v>
-      </c>
-      <c r="G27" s="1"/>
-      <c r="H27" s="1" t="s">
-        <v>548</v>
+        <v>1</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>801</v>
       </c>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="2" t="s">
-        <v>363</v>
+        <v>814</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>332</v>
-      </c>
-      <c r="C28" s="3">
-        <v>6</v>
-      </c>
-      <c r="D28" s="4">
+        <v>816</v>
+      </c>
+      <c r="C28" s="2">
+        <v>20</v>
+      </c>
+      <c r="D28" s="6">
         <v>0</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="F28" s="3">
-        <v>0</v>
-      </c>
-      <c r="G28" s="1"/>
+        <v>815</v>
+      </c>
+      <c r="F28" s="2">
+        <v>0</v>
+      </c>
       <c r="H28" s="2" t="s">
-        <v>549</v>
+        <v>813</v>
       </c>
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="2" t="s">
-        <v>390</v>
+        <v>789</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>466</v>
+        <v>790</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>467</v>
+        <v>791</v>
       </c>
       <c r="F29" s="3">
         <v>1</v>
       </c>
+      <c r="H29" s="7" t="s">
+        <v>799</v>
+      </c>
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="2" t="s">
-        <v>364</v>
+        <v>785</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="C30" s="3">
-        <v>6</v>
-      </c>
-      <c r="D30" s="4">
-        <v>0</v>
+        <v>786</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>148</v>
+        <v>787</v>
       </c>
       <c r="F30" s="3">
-        <v>0</v>
-      </c>
-      <c r="G30" s="1"/>
-      <c r="H30" s="1" t="s">
-        <v>550</v>
+        <v>1</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>788</v>
       </c>
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="2" t="s">
-        <v>365</v>
+        <v>796</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="C31" s="3"/>
-      <c r="D31" s="4"/>
+        <v>797</v>
+      </c>
       <c r="E31" s="1" t="s">
-        <v>160</v>
+        <v>800</v>
       </c>
       <c r="F31" s="3">
         <v>1</v>
       </c>
-      <c r="G31" s="1"/>
-      <c r="H31" s="1" t="s">
-        <v>551</v>
+      <c r="H31" s="2" t="s">
+        <v>798</v>
       </c>
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="2" t="s">
-        <v>366</v>
+        <v>810</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="C32" s="3">
-        <v>6</v>
-      </c>
-      <c r="D32" s="4">
-        <v>0</v>
+        <v>811</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>162</v>
+        <v>812</v>
       </c>
       <c r="F32" s="3">
-        <v>0</v>
-      </c>
-      <c r="G32" s="1"/>
-      <c r="H32" s="1" t="s">
-        <v>552</v>
+        <v>1</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>809</v>
       </c>
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="2" t="s">
-        <v>367</v>
+        <v>806</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="C33" s="3">
-        <v>6</v>
-      </c>
-      <c r="D33" s="4">
-        <v>0</v>
+        <v>807</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>150</v>
+        <v>808</v>
       </c>
       <c r="F33" s="3">
-        <v>0</v>
-      </c>
-      <c r="G33" s="1"/>
-      <c r="H33" s="1" t="s">
-        <v>553</v>
+        <v>1</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>805</v>
       </c>
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="2" t="s">
-        <v>368</v>
+        <v>793</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="C34" s="3">
-        <v>6</v>
-      </c>
-      <c r="D34" s="4">
-        <v>0</v>
+        <v>794</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>152</v>
+        <v>795</v>
       </c>
       <c r="F34" s="3">
-        <v>0</v>
-      </c>
-      <c r="G34" s="1"/>
-      <c r="H34" s="1" t="s">
-        <v>554</v>
+        <v>1</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>792</v>
       </c>
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="2" t="s">
-        <v>369</v>
+        <v>358</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="C35" s="3"/>
-      <c r="D35" s="4"/>
+        <v>328</v>
+      </c>
+      <c r="C35" s="3">
+        <v>6</v>
+      </c>
+      <c r="D35" s="4">
+        <v>0</v>
+      </c>
       <c r="E35" s="1" t="s">
-        <v>158</v>
+        <v>279</v>
       </c>
       <c r="F35" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G35" s="1"/>
-      <c r="H35" s="1" t="s">
-        <v>555</v>
+      <c r="H35" s="2" t="s">
+        <v>542</v>
       </c>
     </row>
     <row r="36" spans="1:8">
       <c r="A36" s="2" t="s">
-        <v>370</v>
+        <v>699</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="C36" s="3"/>
-      <c r="D36" s="4"/>
+        <v>700</v>
+      </c>
       <c r="E36" s="1" t="s">
-        <v>156</v>
+        <v>703</v>
       </c>
       <c r="F36" s="3">
         <v>1</v>
       </c>
-      <c r="G36" s="1"/>
-      <c r="H36" s="1" t="s">
-        <v>556</v>
+      <c r="H36" s="9" t="s">
+        <v>747</v>
       </c>
     </row>
     <row r="37" spans="1:8">
       <c r="A37" s="2" t="s">
-        <v>371</v>
+        <v>701</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="C37" s="3">
-        <v>6</v>
-      </c>
-      <c r="D37" s="4">
-        <v>0</v>
+        <v>702</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>154</v>
+        <v>704</v>
       </c>
       <c r="F37" s="3">
-        <v>0</v>
-      </c>
-      <c r="G37" s="1"/>
-      <c r="H37" s="1" t="s">
-        <v>557</v>
+        <v>1</v>
+      </c>
+      <c r="H37" s="9" t="s">
+        <v>746</v>
       </c>
     </row>
     <row r="38" spans="1:8">
       <c r="A38" s="2" t="s">
-        <v>372</v>
+        <v>385</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C38" s="3">
-        <v>6</v>
-      </c>
-      <c r="D38" s="4">
-        <v>0</v>
+        <v>461</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>651</v>
+        <v>462</v>
       </c>
       <c r="F38" s="3">
-        <v>0</v>
-      </c>
-      <c r="G38" s="1"/>
-      <c r="H38" t="s">
-        <v>558</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39" spans="1:8">
       <c r="A39" s="2" t="s">
-        <v>373</v>
+        <v>359</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>252</v>
+        <v>144</v>
       </c>
       <c r="C39" s="3">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="D39" s="4">
         <v>0</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>253</v>
+        <v>145</v>
       </c>
       <c r="F39" s="3">
         <v>0</v>
       </c>
       <c r="G39" s="1"/>
-      <c r="H39" t="s">
-        <v>559</v>
+      <c r="H39" s="1" t="s">
+        <v>543</v>
       </c>
     </row>
     <row r="40" spans="1:8">
       <c r="A40" s="2" t="s">
-        <v>374</v>
+        <v>360</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="C40" s="3">
-        <v>15</v>
-      </c>
-      <c r="D40" s="4">
-        <v>0.95833333333333337</v>
-      </c>
+        <v>156</v>
+      </c>
+      <c r="C40" s="3"/>
+      <c r="D40" s="4"/>
       <c r="E40" s="1" t="s">
-        <v>255</v>
+        <v>157</v>
       </c>
       <c r="F40" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G40" s="1"/>
-      <c r="H40" t="s">
-        <v>559</v>
+      <c r="H40" s="1" t="s">
+        <v>544</v>
       </c>
     </row>
     <row r="41" spans="1:8">
       <c r="A41" s="2" t="s">
-        <v>375</v>
+        <v>361</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>256</v>
+        <v>158</v>
       </c>
       <c r="C41" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D41" s="4">
-        <v>0.97916666666666663</v>
+        <v>0</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>257</v>
+        <v>159</v>
       </c>
       <c r="F41" s="3">
         <v>0</v>
       </c>
       <c r="G41" s="1"/>
-      <c r="H41" t="s">
-        <v>559</v>
+      <c r="H41" s="1" t="s">
+        <v>545</v>
       </c>
     </row>
     <row r="42" spans="1:8">
       <c r="A42" s="2" t="s">
-        <v>376</v>
+        <v>362</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="C42" s="3">
         <v>6</v>
@@ -4318,539 +4283,540 @@
         <v>0</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>132</v>
+        <v>147</v>
       </c>
       <c r="F42" s="3">
         <v>0</v>
       </c>
       <c r="G42" s="1"/>
       <c r="H42" s="1" t="s">
-        <v>560</v>
+        <v>546</v>
       </c>
     </row>
     <row r="43" spans="1:8">
       <c r="A43" s="2" t="s">
-        <v>377</v>
+        <v>363</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>301</v>
-      </c>
-      <c r="C43" s="1">
-        <v>13</v>
-      </c>
-      <c r="D43" s="5">
+        <v>148</v>
+      </c>
+      <c r="C43" s="3">
+        <v>6</v>
+      </c>
+      <c r="D43" s="4">
         <v>0</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>307</v>
-      </c>
-      <c r="F43" s="1">
+        <v>149</v>
+      </c>
+      <c r="F43" s="3">
         <v>0</v>
       </c>
       <c r="G43" s="1"/>
       <c r="H43" s="1" t="s">
-        <v>561</v>
+        <v>547</v>
       </c>
     </row>
     <row r="44" spans="1:8">
       <c r="A44" s="2" t="s">
-        <v>378</v>
+        <v>364</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="C44" s="1"/>
-      <c r="D44" s="1"/>
+        <v>154</v>
+      </c>
+      <c r="C44" s="3"/>
+      <c r="D44" s="4"/>
       <c r="E44" s="1" t="s">
-        <v>259</v>
+        <v>155</v>
       </c>
       <c r="F44" s="3">
         <v>1</v>
       </c>
-      <c r="G44" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="H44" s="2" t="s">
-        <v>562</v>
+      <c r="G44" s="1"/>
+      <c r="H44" s="1" t="s">
+        <v>548</v>
       </c>
     </row>
     <row r="45" spans="1:8">
-      <c r="A45" t="s">
-        <v>694</v>
+      <c r="A45" s="2" t="s">
+        <v>365</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>658</v>
-      </c>
+        <v>152</v>
+      </c>
+      <c r="C45" s="3"/>
+      <c r="D45" s="4"/>
       <c r="E45" s="1" t="s">
-        <v>661</v>
-      </c>
-      <c r="F45" s="2">
+        <v>153</v>
+      </c>
+      <c r="F45" s="3">
         <v>1</v>
       </c>
+      <c r="G45" s="1"/>
+      <c r="H45" s="1" t="s">
+        <v>549</v>
+      </c>
     </row>
     <row r="46" spans="1:8">
-      <c r="A46" t="s">
-        <v>695</v>
+      <c r="A46" s="2" t="s">
+        <v>366</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>659</v>
+        <v>150</v>
+      </c>
+      <c r="C46" s="3">
+        <v>6</v>
+      </c>
+      <c r="D46" s="4">
+        <v>0</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>665</v>
+        <v>151</v>
       </c>
       <c r="F46" s="3">
-        <v>1</v>
-      </c>
-      <c r="H46" t="s">
-        <v>664</v>
+        <v>0</v>
+      </c>
+      <c r="G46" s="1"/>
+      <c r="H46" s="1" t="s">
+        <v>550</v>
       </c>
     </row>
     <row r="47" spans="1:8">
-      <c r="A47" t="s">
-        <v>696</v>
+      <c r="A47" s="2" t="s">
+        <v>367</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>660</v>
-      </c>
-      <c r="C47" s="3"/>
-      <c r="D47" s="6"/>
+        <v>8</v>
+      </c>
+      <c r="C47" s="3">
+        <v>6</v>
+      </c>
+      <c r="D47" s="4">
+        <v>0</v>
+      </c>
       <c r="E47" s="1" t="s">
-        <v>662</v>
+        <v>644</v>
       </c>
       <c r="F47" s="3">
-        <v>1</v>
-      </c>
-      <c r="G47" s="1" t="s">
-        <v>714</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G47" s="1"/>
       <c r="H47" t="s">
-        <v>663</v>
+        <v>551</v>
       </c>
     </row>
     <row r="48" spans="1:8">
       <c r="A48" s="2" t="s">
-        <v>379</v>
+        <v>368</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>133</v>
+        <v>249</v>
       </c>
       <c r="C48" s="3">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D48" s="4">
-        <v>0.875</v>
+        <v>0</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>134</v>
+        <v>250</v>
       </c>
       <c r="F48" s="3">
         <v>0</v>
       </c>
       <c r="G48" s="1"/>
-      <c r="H48" s="1" t="s">
-        <v>563</v>
+      <c r="H48" t="s">
+        <v>552</v>
       </c>
     </row>
     <row r="49" spans="1:8">
       <c r="A49" s="2" t="s">
-        <v>380</v>
+        <v>369</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>310</v>
+        <v>251</v>
       </c>
       <c r="C49" s="3">
-        <v>6</v>
-      </c>
-      <c r="D49" s="5">
-        <v>0</v>
+        <v>15</v>
+      </c>
+      <c r="D49" s="4">
+        <v>0.95833333333333337</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>312</v>
+        <v>252</v>
       </c>
       <c r="F49" s="3">
         <v>0</v>
       </c>
       <c r="G49" s="1"/>
-      <c r="H49" s="1" t="s">
-        <v>564</v>
+      <c r="H49" t="s">
+        <v>552</v>
       </c>
     </row>
     <row r="50" spans="1:8">
       <c r="A50" s="2" t="s">
-        <v>381</v>
+        <v>370</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="C50" s="3"/>
-      <c r="D50" s="5"/>
+        <v>253</v>
+      </c>
+      <c r="C50" s="3">
+        <v>7</v>
+      </c>
+      <c r="D50" s="4">
+        <v>0.97916666666666663</v>
+      </c>
       <c r="E50" s="1" t="s">
-        <v>311</v>
+        <v>254</v>
       </c>
       <c r="F50" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G50" s="1"/>
-      <c r="H50" s="1" t="s">
-        <v>565</v>
+      <c r="H50" t="s">
+        <v>552</v>
       </c>
     </row>
     <row r="51" spans="1:8">
       <c r="A51" s="2" t="s">
-        <v>382</v>
+        <v>371</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>299</v>
+        <v>128</v>
       </c>
       <c r="C51" s="3">
         <v>6</v>
       </c>
-      <c r="D51" s="5">
+      <c r="D51" s="4">
         <v>0</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>308</v>
+        <v>129</v>
       </c>
       <c r="F51" s="3">
         <v>0</v>
       </c>
       <c r="G51" s="1"/>
       <c r="H51" s="1" t="s">
-        <v>564</v>
+        <v>553</v>
       </c>
     </row>
     <row r="52" spans="1:8">
       <c r="A52" s="2" t="s">
-        <v>383</v>
+        <v>372</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C52" s="3">
-        <v>6</v>
-      </c>
-      <c r="D52" s="4">
+        <v>298</v>
+      </c>
+      <c r="C52" s="1">
+        <v>13</v>
+      </c>
+      <c r="D52" s="5">
         <v>0</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F52" s="3">
+        <v>304</v>
+      </c>
+      <c r="F52" s="1">
         <v>0</v>
       </c>
       <c r="G52" s="1"/>
-      <c r="H52" s="2" t="s">
-        <v>566</v>
+      <c r="H52" s="1" t="s">
+        <v>554</v>
       </c>
     </row>
     <row r="53" spans="1:8">
       <c r="A53" s="2" t="s">
-        <v>384</v>
+        <v>373</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C53" s="3">
-        <v>7</v>
-      </c>
-      <c r="D53" s="4">
-        <v>0.91666666666666663</v>
-      </c>
+        <v>255</v>
+      </c>
+      <c r="C53" s="1"/>
+      <c r="D53" s="1"/>
       <c r="E53" s="1" t="s">
-        <v>7</v>
+        <v>256</v>
       </c>
       <c r="F53" s="3">
-        <v>0</v>
-      </c>
-      <c r="G53" s="1"/>
+        <v>1</v>
+      </c>
+      <c r="G53" s="1" t="s">
+        <v>257</v>
+      </c>
       <c r="H53" s="2" t="s">
-        <v>567</v>
+        <v>555</v>
       </c>
     </row>
     <row r="54" spans="1:8">
-      <c r="A54" s="2" t="s">
-        <v>385</v>
+      <c r="A54" t="s">
+        <v>687</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C54" s="3">
-        <v>6</v>
-      </c>
-      <c r="D54" s="4">
-        <v>0</v>
+        <v>651</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F54" s="3">
-        <v>0</v>
-      </c>
-      <c r="G54" s="1"/>
-      <c r="H54" s="2" t="s">
-        <v>568</v>
+        <v>654</v>
+      </c>
+      <c r="F54" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="55" spans="1:8">
-      <c r="A55" s="2" t="s">
-        <v>386</v>
+      <c r="A55" t="s">
+        <v>688</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C55" s="3">
-        <v>6</v>
-      </c>
-      <c r="D55" s="4">
-        <v>0</v>
+        <v>652</v>
       </c>
       <c r="E55" s="1" t="s">
+        <v>658</v>
+      </c>
+      <c r="F55" s="3">
         <v>1</v>
       </c>
-      <c r="F55" s="3">
-        <v>0</v>
-      </c>
-      <c r="G55" s="1"/>
-      <c r="H55" s="2" t="s">
-        <v>569</v>
+      <c r="H55" t="s">
+        <v>657</v>
       </c>
     </row>
     <row r="56" spans="1:8">
-      <c r="A56" s="2" t="s">
-        <v>387</v>
+      <c r="A56" t="s">
+        <v>689</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>267</v>
-      </c>
-      <c r="C56" s="3">
-        <v>7</v>
-      </c>
-      <c r="D56" s="4">
-        <v>0</v>
-      </c>
+        <v>653</v>
+      </c>
+      <c r="C56" s="3"/>
+      <c r="D56" s="6"/>
       <c r="E56" s="1" t="s">
-        <v>297</v>
+        <v>655</v>
       </c>
       <c r="F56" s="3">
-        <v>0</v>
-      </c>
-      <c r="H56" s="1" t="s">
-        <v>570</v>
+        <v>1</v>
+      </c>
+      <c r="G56" s="1" t="s">
+        <v>707</v>
+      </c>
+      <c r="H56" t="s">
+        <v>656</v>
       </c>
     </row>
     <row r="57" spans="1:8">
       <c r="A57" s="2" t="s">
-        <v>671</v>
+        <v>374</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>187</v>
+        <v>130</v>
       </c>
       <c r="C57" s="3">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="D57" s="4">
-        <v>0</v>
+        <v>0.875</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>188</v>
+        <v>131</v>
       </c>
       <c r="F57" s="3">
         <v>0</v>
       </c>
+      <c r="G57" s="1"/>
       <c r="H57" s="1" t="s">
-        <v>571</v>
+        <v>556</v>
       </c>
     </row>
     <row r="58" spans="1:8">
-      <c r="A58" t="s">
-        <v>688</v>
+      <c r="A58" s="2" t="s">
+        <v>375</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>270</v>
+        <v>307</v>
       </c>
       <c r="C58" s="3">
-        <v>30</v>
-      </c>
-      <c r="D58" s="4">
+        <v>6</v>
+      </c>
+      <c r="D58" s="5">
         <v>0</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>271</v>
+        <v>309</v>
       </c>
       <c r="F58" s="3">
         <v>0</v>
       </c>
+      <c r="G58" s="1"/>
       <c r="H58" s="1" t="s">
-        <v>572</v>
+        <v>557</v>
       </c>
     </row>
     <row r="59" spans="1:8">
-      <c r="A59" t="s">
-        <v>689</v>
+      <c r="A59" s="2" t="s">
+        <v>376</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="C59" s="3">
-        <v>30</v>
-      </c>
-      <c r="D59" s="4">
-        <v>0</v>
-      </c>
+        <v>306</v>
+      </c>
+      <c r="C59" s="3"/>
+      <c r="D59" s="5"/>
       <c r="E59" s="1" t="s">
-        <v>186</v>
+        <v>308</v>
       </c>
       <c r="F59" s="3">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G59" s="1"/>
       <c r="H59" s="1" t="s">
-        <v>573</v>
+        <v>558</v>
       </c>
     </row>
     <row r="60" spans="1:8">
-      <c r="A60" t="s">
-        <v>674</v>
+      <c r="A60" s="2" t="s">
+        <v>377</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>191</v>
+        <v>296</v>
       </c>
       <c r="C60" s="3">
-        <v>15</v>
-      </c>
-      <c r="D60" s="4">
+        <v>6</v>
+      </c>
+      <c r="D60" s="5">
         <v>0</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>192</v>
+        <v>305</v>
       </c>
       <c r="F60" s="3">
         <v>0</v>
       </c>
+      <c r="G60" s="1"/>
       <c r="H60" s="1" t="s">
-        <v>574</v>
+        <v>557</v>
       </c>
     </row>
     <row r="61" spans="1:8">
       <c r="A61" s="2" t="s">
-        <v>675</v>
+        <v>378</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>189</v>
+        <v>2</v>
       </c>
       <c r="C61" s="3">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D61" s="4">
         <v>0</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>190</v>
+        <v>3</v>
       </c>
       <c r="F61" s="3">
         <v>0</v>
       </c>
-      <c r="H61" s="1" t="s">
-        <v>575</v>
+      <c r="G61" s="1"/>
+      <c r="H61" s="2" t="s">
+        <v>559</v>
       </c>
     </row>
     <row r="62" spans="1:8">
-      <c r="A62" t="s">
-        <v>676</v>
+      <c r="A62" s="2" t="s">
+        <v>379</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>177</v>
+        <v>6</v>
       </c>
       <c r="C62" s="3">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="D62" s="4">
-        <v>0</v>
+        <v>0.91666666666666663</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>178</v>
+        <v>7</v>
       </c>
       <c r="F62" s="3">
         <v>0</v>
       </c>
-      <c r="H62" s="1" t="s">
-        <v>576</v>
+      <c r="G62" s="1"/>
+      <c r="H62" s="2" t="s">
+        <v>560</v>
       </c>
     </row>
     <row r="63" spans="1:8">
-      <c r="A63" t="s">
-        <v>677</v>
+      <c r="A63" s="2" t="s">
+        <v>380</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>179</v>
+        <v>4</v>
       </c>
       <c r="C63" s="3">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="D63" s="4">
         <v>0</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>180</v>
+        <v>5</v>
       </c>
       <c r="F63" s="3">
         <v>0</v>
       </c>
-      <c r="H63" s="1" t="s">
-        <v>577</v>
+      <c r="G63" s="1"/>
+      <c r="H63" s="2" t="s">
+        <v>561</v>
       </c>
     </row>
     <row r="64" spans="1:8">
       <c r="A64" s="2" t="s">
-        <v>388</v>
+        <v>381</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>163</v>
+        <v>0</v>
       </c>
       <c r="C64" s="3">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="D64" s="4">
         <v>0</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>164</v>
+        <v>1</v>
       </c>
       <c r="F64" s="3">
         <v>0</v>
       </c>
-      <c r="H64" s="1" t="s">
-        <v>578</v>
+      <c r="G64" s="1"/>
+      <c r="H64" s="2" t="s">
+        <v>562</v>
       </c>
     </row>
     <row r="65" spans="1:8">
-      <c r="A65" t="s">
-        <v>692</v>
+      <c r="A65" s="2" t="s">
+        <v>382</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>193</v>
+        <v>264</v>
       </c>
       <c r="C65" s="3">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="D65" s="4">
         <v>0</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>194</v>
+        <v>294</v>
       </c>
       <c r="F65" s="3">
         <v>0</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>579</v>
+        <v>563</v>
       </c>
     </row>
     <row r="66" spans="1:8">
-      <c r="A66" t="s">
-        <v>690</v>
+      <c r="A66" s="2" t="s">
+        <v>664</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="C66" s="3">
         <v>30</v>
@@ -4859,113 +4825,113 @@
         <v>0</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="F66" s="3">
         <v>0</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>580</v>
+        <v>564</v>
       </c>
     </row>
     <row r="67" spans="1:8">
       <c r="A67" t="s">
-        <v>691</v>
+        <v>681</v>
       </c>
       <c r="B67" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="C67" s="3">
+        <v>30</v>
+      </c>
+      <c r="D67" s="4">
+        <v>0</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="F67" s="3">
+        <v>0</v>
+      </c>
+      <c r="H67" s="1" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8">
+      <c r="A68" t="s">
+        <v>682</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="C68" s="3">
+        <v>30</v>
+      </c>
+      <c r="D68" s="4">
+        <v>0</v>
+      </c>
+      <c r="E68" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="C67" s="3">
+      <c r="F68" s="3">
+        <v>0</v>
+      </c>
+      <c r="H68" s="1" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8">
+      <c r="A69" t="s">
+        <v>667</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="C69" s="3">
         <v>15</v>
       </c>
-      <c r="D67" s="4">
-        <v>0</v>
-      </c>
-      <c r="E67" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="F67" s="3">
-        <v>0</v>
-      </c>
-      <c r="H67" s="1" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8">
-      <c r="A68" s="2" t="s">
-        <v>656</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="C68" s="3">
-        <v>7</v>
-      </c>
-      <c r="D68" s="4">
-        <v>0</v>
-      </c>
-      <c r="E68" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="F68" s="3">
-        <v>0</v>
-      </c>
-      <c r="H68" s="1" t="s">
-        <v>582</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8">
-      <c r="A69" s="2" t="s">
-        <v>657</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="C69" s="3">
-        <v>7</v>
-      </c>
       <c r="D69" s="4">
         <v>0</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="F69" s="3">
         <v>0</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>583</v>
+        <v>567</v>
       </c>
     </row>
     <row r="70" spans="1:8">
       <c r="A70" s="2" t="s">
-        <v>672</v>
+        <v>668</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="C70" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D70" s="4">
         <v>0</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="F70" s="3">
         <v>0</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>584</v>
+        <v>568</v>
       </c>
     </row>
     <row r="71" spans="1:8">
-      <c r="A71" s="2" t="s">
-        <v>673</v>
+      <c r="A71" t="s">
+        <v>669</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C71" s="3">
         <v>30</v>
@@ -4974,21 +4940,21 @@
         <v>0</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F71" s="3">
         <v>0</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>585</v>
+        <v>569</v>
       </c>
     </row>
     <row r="72" spans="1:8">
       <c r="A72" t="s">
-        <v>678</v>
+        <v>670</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="C72" s="3">
         <v>30</v>
@@ -4997,21 +4963,21 @@
         <v>0</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="F72" s="3">
         <v>0</v>
       </c>
       <c r="H72" s="1" t="s">
-        <v>586</v>
+        <v>570</v>
       </c>
     </row>
     <row r="73" spans="1:8">
-      <c r="A73" t="s">
-        <v>679</v>
+      <c r="A73" s="2" t="s">
+        <v>383</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>171</v>
+        <v>160</v>
       </c>
       <c r="C73" s="3">
         <v>30</v>
@@ -5020,44 +4986,44 @@
         <v>0</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="F73" s="3">
         <v>0</v>
       </c>
       <c r="H73" s="1" t="s">
-        <v>587</v>
+        <v>571</v>
       </c>
     </row>
     <row r="74" spans="1:8">
       <c r="A74" t="s">
-        <v>680</v>
+        <v>685</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>169</v>
+        <v>190</v>
       </c>
       <c r="C74" s="3">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="D74" s="4">
         <v>0</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>170</v>
+        <v>191</v>
       </c>
       <c r="F74" s="3">
         <v>0</v>
       </c>
       <c r="H74" s="1" t="s">
-        <v>588</v>
+        <v>572</v>
       </c>
     </row>
     <row r="75" spans="1:8">
       <c r="A75" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>167</v>
+        <v>178</v>
       </c>
       <c r="C75" s="3">
         <v>30</v>
@@ -5066,21 +5032,21 @@
         <v>0</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="F75" s="3">
         <v>0</v>
       </c>
       <c r="H75" s="1" t="s">
-        <v>589</v>
+        <v>573</v>
       </c>
     </row>
     <row r="76" spans="1:8">
       <c r="A76" t="s">
-        <v>693</v>
+        <v>684</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>195</v>
+        <v>180</v>
       </c>
       <c r="C76" s="3">
         <v>15</v>
@@ -5089,21 +5055,21 @@
         <v>0</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>196</v>
+        <v>181</v>
       </c>
       <c r="F76" s="3">
         <v>0</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>590</v>
+        <v>574</v>
       </c>
     </row>
     <row r="77" spans="1:8">
       <c r="A77" s="2" t="s">
-        <v>484</v>
+        <v>649</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>101</v>
+        <v>196</v>
       </c>
       <c r="C77" s="3">
         <v>7</v>
@@ -5112,22 +5078,21 @@
         <v>0</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>102</v>
+        <v>197</v>
       </c>
       <c r="F77" s="3">
         <v>0</v>
       </c>
-      <c r="G77" s="1"/>
       <c r="H77" s="1" t="s">
-        <v>639</v>
+        <v>575</v>
       </c>
     </row>
     <row r="78" spans="1:8">
       <c r="A78" s="2" t="s">
-        <v>488</v>
+        <v>650</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>500</v>
+        <v>194</v>
       </c>
       <c r="C78" s="3">
         <v>7</v>
@@ -5136,714 +5101,605 @@
         <v>0</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>117</v>
+        <v>195</v>
       </c>
       <c r="F78" s="3">
         <v>0</v>
       </c>
-      <c r="G78" s="1"/>
       <c r="H78" s="1" t="s">
-        <v>639</v>
+        <v>576</v>
       </c>
     </row>
     <row r="79" spans="1:8">
       <c r="A79" s="2" t="s">
-        <v>489</v>
+        <v>665</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>109</v>
+        <v>172</v>
       </c>
       <c r="C79" s="3">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D79" s="4">
         <v>0</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>110</v>
+        <v>173</v>
       </c>
       <c r="F79" s="3">
         <v>0</v>
       </c>
-      <c r="G79" s="1"/>
       <c r="H79" s="1" t="s">
-        <v>639</v>
+        <v>577</v>
       </c>
     </row>
     <row r="80" spans="1:8">
       <c r="A80" s="2" t="s">
-        <v>490</v>
+        <v>666</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>115</v>
+        <v>170</v>
       </c>
       <c r="C80" s="3">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="D80" s="4">
         <v>0</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>116</v>
+        <v>171</v>
       </c>
       <c r="F80" s="3">
         <v>0</v>
       </c>
-      <c r="G80" s="1"/>
       <c r="H80" s="1" t="s">
-        <v>639</v>
+        <v>578</v>
       </c>
     </row>
     <row r="81" spans="1:8">
-      <c r="A81" s="2" t="s">
-        <v>485</v>
+      <c r="A81" t="s">
+        <v>671</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>501</v>
+        <v>162</v>
       </c>
       <c r="C81" s="3">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="D81" s="4">
         <v>0</v>
       </c>
       <c r="E81" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="F81" s="3">
+        <v>0</v>
+      </c>
+      <c r="H81" s="1" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8">
+      <c r="A82" t="s">
+        <v>672</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="C82" s="3">
+        <v>30</v>
+      </c>
+      <c r="D82" s="4">
+        <v>0</v>
+      </c>
+      <c r="E82" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F82" s="3">
+        <v>0</v>
+      </c>
+      <c r="H82" s="1" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8">
+      <c r="A83" t="s">
+        <v>673</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="C83" s="3">
+        <v>30</v>
+      </c>
+      <c r="D83" s="4">
+        <v>0</v>
+      </c>
+      <c r="E83" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="F83" s="3">
+        <v>0</v>
+      </c>
+      <c r="H83" s="1" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8">
+      <c r="A84" t="s">
+        <v>674</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="C84" s="3">
+        <v>30</v>
+      </c>
+      <c r="D84" s="4">
+        <v>0</v>
+      </c>
+      <c r="E84" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="F84" s="3">
+        <v>0</v>
+      </c>
+      <c r="H84" s="1" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8">
+      <c r="A85" t="s">
+        <v>686</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="C85" s="3">
+        <v>15</v>
+      </c>
+      <c r="D85" s="4">
+        <v>0</v>
+      </c>
+      <c r="E85" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="F85" s="3">
+        <v>0</v>
+      </c>
+      <c r="H85" s="1" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8">
+      <c r="A86" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="B86" s="1" t="s">
         <v>100</v>
-      </c>
-      <c r="F81" s="3">
-        <v>0</v>
-      </c>
-      <c r="G81" s="1"/>
-      <c r="H81" s="1" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="82" spans="1:8">
-      <c r="A82" s="2" t="s">
-        <v>486</v>
-      </c>
-      <c r="B82" s="1" t="s">
-        <v>502</v>
-      </c>
-      <c r="C82" s="3">
-        <v>7</v>
-      </c>
-      <c r="D82" s="4">
-        <v>0</v>
-      </c>
-      <c r="E82" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="F82" s="3">
-        <v>0</v>
-      </c>
-      <c r="G82" s="1"/>
-      <c r="H82" s="1" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="83" spans="1:8">
-      <c r="A83" s="2" t="s">
-        <v>487</v>
-      </c>
-      <c r="B83" s="1" t="s">
-        <v>505</v>
-      </c>
-      <c r="C83" s="3">
-        <v>7</v>
-      </c>
-      <c r="D83" s="4">
-        <v>0</v>
-      </c>
-      <c r="E83" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="F83" s="3">
-        <v>0</v>
-      </c>
-      <c r="G83" s="1"/>
-      <c r="H83" s="1" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="84" spans="1:8">
-      <c r="A84" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="B84" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="C84" s="3">
-        <v>6</v>
-      </c>
-      <c r="D84" s="4">
-        <v>0</v>
-      </c>
-      <c r="E84" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="F84" s="3">
-        <v>0</v>
-      </c>
-      <c r="G84" s="1"/>
-      <c r="H84" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="85" spans="1:8">
-      <c r="A85" s="2" t="s">
-        <v>411</v>
-      </c>
-      <c r="B85" s="1" t="s">
-        <v>412</v>
-      </c>
-      <c r="C85" s="3">
-        <v>7</v>
-      </c>
-      <c r="D85" s="4">
-        <v>0</v>
-      </c>
-      <c r="E85" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="F85" s="3">
-        <v>0</v>
-      </c>
-      <c r="G85" s="1"/>
-      <c r="H85" s="1" t="s">
-        <v>592</v>
-      </c>
-    </row>
-    <row r="86" spans="1:8">
-      <c r="A86" t="s">
-        <v>447</v>
-      </c>
-      <c r="B86" s="1" t="s">
-        <v>506</v>
       </c>
       <c r="C86" s="3">
         <v>7</v>
       </c>
       <c r="D86" s="4">
-        <v>0.95833333333333337</v>
+        <v>0</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>287</v>
+        <v>101</v>
       </c>
       <c r="F86" s="3">
         <v>0</v>
       </c>
       <c r="G86" s="1"/>
       <c r="H86" s="1" t="s">
-        <v>624</v>
+        <v>632</v>
       </c>
     </row>
     <row r="87" spans="1:8">
       <c r="A87" s="2" t="s">
-        <v>705</v>
+        <v>483</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>305</v>
-      </c>
-      <c r="C87" s="1"/>
-      <c r="D87" s="5"/>
+        <v>494</v>
+      </c>
+      <c r="C87" s="3">
+        <v>7</v>
+      </c>
+      <c r="D87" s="4">
+        <v>0</v>
+      </c>
       <c r="E87" s="1" t="s">
-        <v>318</v>
+        <v>116</v>
       </c>
       <c r="F87" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G87" s="1"/>
       <c r="H87" s="1" t="s">
-        <v>593</v>
+        <v>632</v>
       </c>
     </row>
     <row r="88" spans="1:8">
       <c r="A88" s="2" t="s">
-        <v>432</v>
+        <v>484</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>244</v>
+        <v>108</v>
       </c>
       <c r="C88" s="3">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D88" s="4">
         <v>0</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>245</v>
+        <v>109</v>
       </c>
       <c r="F88" s="3">
         <v>0</v>
       </c>
       <c r="G88" s="1"/>
       <c r="H88" s="1" t="s">
-        <v>594</v>
+        <v>632</v>
       </c>
     </row>
     <row r="89" spans="1:8">
       <c r="A89" s="2" t="s">
-        <v>391</v>
+        <v>485</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>47</v>
+        <v>114</v>
       </c>
       <c r="C89" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D89" s="4">
-        <v>0.66666666666666663</v>
+        <v>0</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>48</v>
+        <v>115</v>
       </c>
       <c r="F89" s="3">
         <v>0</v>
       </c>
       <c r="G89" s="1"/>
-      <c r="H89" s="2" t="s">
-        <v>595</v>
+      <c r="H89" s="1" t="s">
+        <v>632</v>
       </c>
     </row>
     <row r="90" spans="1:8">
       <c r="A90" s="2" t="s">
-        <v>392</v>
+        <v>480</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>49</v>
+        <v>495</v>
       </c>
       <c r="C90" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D90" s="4">
-        <v>0.70833333333333337</v>
+        <v>0</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>50</v>
+        <v>99</v>
       </c>
       <c r="F90" s="3">
         <v>0</v>
       </c>
       <c r="G90" s="1"/>
-      <c r="H90" s="2" t="s">
-        <v>595</v>
+      <c r="H90" s="1" t="s">
+        <v>632</v>
       </c>
     </row>
     <row r="91" spans="1:8">
       <c r="A91" s="2" t="s">
-        <v>433</v>
+        <v>481</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>277</v>
+        <v>496</v>
       </c>
       <c r="C91" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D91" s="4">
         <v>0</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>279</v>
+        <v>102</v>
       </c>
       <c r="F91" s="3">
         <v>0</v>
       </c>
       <c r="G91" s="1"/>
-      <c r="H91" t="s">
-        <v>774</v>
+      <c r="H91" s="1" t="s">
+        <v>632</v>
       </c>
     </row>
     <row r="92" spans="1:8">
       <c r="A92" s="2" t="s">
-        <v>393</v>
+        <v>482</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>43</v>
+        <v>499</v>
       </c>
       <c r="C92" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D92" s="4">
-        <v>0.58333333333333337</v>
+        <v>0</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>44</v>
+        <v>103</v>
       </c>
       <c r="F92" s="3">
         <v>0</v>
       </c>
       <c r="G92" s="1"/>
-      <c r="H92" s="2" t="s">
-        <v>595</v>
+      <c r="H92" s="1" t="s">
+        <v>632</v>
       </c>
     </row>
     <row r="93" spans="1:8">
       <c r="A93" s="2" t="s">
-        <v>394</v>
+        <v>741</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C93" s="3">
-        <v>6</v>
-      </c>
-      <c r="D93" s="4">
-        <v>0.75</v>
+        <v>742</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>52</v>
+        <v>761</v>
       </c>
       <c r="F93" s="3">
-        <v>0</v>
-      </c>
-      <c r="G93" s="1"/>
-      <c r="H93" s="2" t="s">
-        <v>595</v>
+        <v>1</v>
+      </c>
+      <c r="H93" s="7" t="s">
+        <v>766</v>
       </c>
     </row>
     <row r="94" spans="1:8">
       <c r="A94" s="2" t="s">
-        <v>395</v>
+        <v>740</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C94" s="3">
-        <v>6</v>
-      </c>
-      <c r="D94" s="4">
-        <v>0.79166666666666663</v>
+        <v>711</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>54</v>
+        <v>760</v>
       </c>
       <c r="F94" s="3">
-        <v>0</v>
-      </c>
-      <c r="G94" s="1"/>
-      <c r="H94" s="2" t="s">
-        <v>595</v>
+        <v>1</v>
+      </c>
+      <c r="H94" s="7" t="s">
+        <v>766</v>
       </c>
     </row>
     <row r="95" spans="1:8">
       <c r="A95" s="2" t="s">
-        <v>434</v>
+        <v>725</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>276</v>
-      </c>
-      <c r="C95" s="3">
-        <v>6</v>
-      </c>
-      <c r="D95" s="4">
-        <v>0</v>
+        <v>727</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>280</v>
+        <v>753</v>
       </c>
       <c r="F95" s="3">
-        <v>0</v>
-      </c>
-      <c r="G95" s="1"/>
-      <c r="H95" t="s">
-        <v>774</v>
+        <v>1</v>
+      </c>
+      <c r="H95" s="7" t="s">
+        <v>766</v>
       </c>
     </row>
     <row r="96" spans="1:8">
       <c r="A96" s="2" t="s">
-        <v>396</v>
+        <v>730</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C96" s="3">
-        <v>6</v>
-      </c>
-      <c r="D96" s="4">
-        <v>0.83333333333333337</v>
+        <v>731</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>56</v>
+        <v>755</v>
       </c>
       <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="1"/>
-      <c r="H96" s="2" t="s">
-        <v>595</v>
+        <v>1</v>
+      </c>
+      <c r="H96" s="7" t="s">
+        <v>766</v>
       </c>
     </row>
     <row r="97" spans="1:8">
       <c r="A97" s="2" t="s">
-        <v>397</v>
+        <v>728</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>703</v>
-      </c>
-      <c r="C97" s="3">
-        <v>6</v>
-      </c>
-      <c r="D97" s="4">
-        <v>0.875</v>
+        <v>729</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>337</v>
+        <v>754</v>
       </c>
       <c r="F97" s="3">
-        <v>0</v>
-      </c>
-      <c r="G97" s="1"/>
-      <c r="H97" s="2" t="s">
-        <v>595</v>
+        <v>1</v>
+      </c>
+      <c r="H97" s="7" t="s">
+        <v>766</v>
       </c>
     </row>
     <row r="98" spans="1:8">
       <c r="A98" s="2" t="s">
-        <v>435</v>
+        <v>726</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>278</v>
-      </c>
-      <c r="C98" s="3">
-        <v>6</v>
-      </c>
-      <c r="D98" s="4">
-        <v>0</v>
+        <v>724</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>281</v>
+        <v>752</v>
       </c>
       <c r="F98" s="3">
-        <v>0</v>
-      </c>
-      <c r="G98" s="1"/>
-      <c r="H98" t="s">
-        <v>774</v>
+        <v>1</v>
+      </c>
+      <c r="H98" s="7" t="s">
+        <v>766</v>
       </c>
     </row>
     <row r="99" spans="1:8">
       <c r="A99" s="2" t="s">
-        <v>398</v>
+        <v>734</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C99" s="3">
-        <v>6</v>
-      </c>
-      <c r="D99" s="4">
-        <v>0.54166666666666663</v>
+        <v>735</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>42</v>
+        <v>757</v>
       </c>
       <c r="F99" s="3">
-        <v>0</v>
-      </c>
-      <c r="G99" s="1"/>
-      <c r="H99" s="2" t="s">
-        <v>595</v>
+        <v>1</v>
+      </c>
+      <c r="H99" s="7" t="s">
+        <v>766</v>
       </c>
     </row>
     <row r="100" spans="1:8">
       <c r="A100" s="2" t="s">
-        <v>399</v>
+        <v>738</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C100" s="3">
-        <v>6</v>
-      </c>
-      <c r="D100" s="4">
-        <v>0.625</v>
+        <v>739</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>46</v>
+        <v>759</v>
       </c>
       <c r="F100" s="3">
-        <v>0</v>
-      </c>
-      <c r="G100" s="1"/>
-      <c r="H100" s="2" t="s">
-        <v>595</v>
+        <v>1</v>
+      </c>
+      <c r="H100" s="7" t="s">
+        <v>766</v>
       </c>
     </row>
     <row r="101" spans="1:8">
-      <c r="A101" t="s">
-        <v>436</v>
+      <c r="A101" s="2" t="s">
+        <v>720</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="C101" s="3">
-        <v>6</v>
-      </c>
-      <c r="D101" s="4">
-        <v>0</v>
+        <v>721</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>227</v>
+        <v>750</v>
       </c>
       <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="1"/>
-      <c r="H101" s="1" t="s">
-        <v>596</v>
+        <v>1</v>
+      </c>
+      <c r="H101" s="7" t="s">
+        <v>766</v>
       </c>
     </row>
     <row r="102" spans="1:8">
-      <c r="A102" t="s">
-        <v>437</v>
+      <c r="A102" s="2" t="s">
+        <v>743</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="C102" s="3">
-        <v>6</v>
-      </c>
-      <c r="D102" s="4">
-        <v>0</v>
+        <v>744</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>221</v>
+        <v>762</v>
       </c>
       <c r="F102" s="3">
-        <v>0</v>
-      </c>
-      <c r="G102" s="1"/>
-      <c r="H102" s="1" t="s">
-        <v>596</v>
+        <v>1</v>
+      </c>
+      <c r="H102" s="7" t="s">
+        <v>766</v>
       </c>
     </row>
     <row r="103" spans="1:8">
-      <c r="A103" t="s">
-        <v>438</v>
+      <c r="A103" s="2" t="s">
+        <v>736</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="C103" s="3">
-        <v>6</v>
-      </c>
-      <c r="D103" s="4">
-        <v>0</v>
+        <v>737</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>233</v>
+        <v>758</v>
       </c>
       <c r="F103" s="3">
-        <v>0</v>
-      </c>
-      <c r="G103" s="1"/>
-      <c r="H103" s="1" t="s">
-        <v>596</v>
+        <v>1</v>
+      </c>
+      <c r="H103" s="7" t="s">
+        <v>766</v>
       </c>
     </row>
     <row r="104" spans="1:8">
-      <c r="A104" t="s">
-        <v>439</v>
+      <c r="A104" s="2" t="s">
+        <v>716</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="C104" s="3">
-        <v>6</v>
-      </c>
-      <c r="D104" s="4">
-        <v>0</v>
+        <v>717</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>223</v>
+        <v>745</v>
       </c>
       <c r="F104" s="3">
-        <v>0</v>
-      </c>
-      <c r="G104" s="1"/>
-      <c r="H104" s="1" t="s">
-        <v>596</v>
+        <v>1</v>
+      </c>
+      <c r="H104" s="7" t="s">
+        <v>766</v>
       </c>
     </row>
     <row r="105" spans="1:8">
-      <c r="A105" t="s">
-        <v>440</v>
+      <c r="A105" s="2" t="s">
+        <v>718</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="C105" s="3">
-        <v>6</v>
-      </c>
-      <c r="D105" s="4">
-        <v>0</v>
+        <v>719</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>231</v>
+        <v>749</v>
       </c>
       <c r="F105" s="3">
-        <v>0</v>
-      </c>
-      <c r="G105" s="1"/>
-      <c r="H105" s="1" t="s">
-        <v>596</v>
+        <v>1</v>
+      </c>
+      <c r="H105" s="7" t="s">
+        <v>766</v>
       </c>
     </row>
     <row r="106" spans="1:8">
-      <c r="A106" t="s">
-        <v>441</v>
+      <c r="A106" s="2" t="s">
+        <v>722</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="C106" s="3">
-        <v>6</v>
-      </c>
-      <c r="D106" s="4">
-        <v>0</v>
+        <v>723</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>229</v>
+        <v>751</v>
       </c>
       <c r="F106" s="3">
-        <v>0</v>
-      </c>
-      <c r="G106" s="1"/>
-      <c r="H106" s="1" t="s">
-        <v>596</v>
+        <v>1</v>
+      </c>
+      <c r="H106" s="7" t="s">
+        <v>766</v>
       </c>
     </row>
     <row r="107" spans="1:8">
-      <c r="A107" t="s">
-        <v>442</v>
+      <c r="A107" s="2" t="s">
+        <v>732</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="C107" s="3">
-        <v>6</v>
-      </c>
-      <c r="D107" s="4">
-        <v>0</v>
+        <v>733</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>225</v>
+        <v>756</v>
       </c>
       <c r="F107" s="3">
-        <v>0</v>
-      </c>
-      <c r="G107" s="1"/>
-      <c r="H107" s="1" t="s">
-        <v>596</v>
+        <v>1</v>
+      </c>
+      <c r="H107" s="7" t="s">
+        <v>766</v>
       </c>
     </row>
     <row r="108" spans="1:8">
       <c r="A108" s="2" t="s">
-        <v>443</v>
+        <v>384</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="C108" s="3">
         <v>6</v>
@@ -5852,226 +5708,258 @@
         <v>0</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="F108" s="3">
         <v>0</v>
       </c>
       <c r="G108" s="1"/>
       <c r="H108" t="s">
-        <v>775</v>
+        <v>584</v>
       </c>
     </row>
     <row r="109" spans="1:8">
       <c r="A109" s="2" t="s">
-        <v>444</v>
+        <v>406</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>272</v>
+        <v>407</v>
       </c>
       <c r="C109" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D109" s="4">
-        <v>0.54166666666666663</v>
+        <v>0</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>273</v>
+        <v>199</v>
       </c>
       <c r="F109" s="3">
         <v>0</v>
       </c>
       <c r="G109" s="1"/>
       <c r="H109" s="1" t="s">
-        <v>597</v>
+        <v>585</v>
       </c>
     </row>
     <row r="110" spans="1:8">
-      <c r="A110" s="2" t="s">
-        <v>400</v>
+      <c r="A110" t="s">
+        <v>442</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>201</v>
+        <v>500</v>
       </c>
       <c r="C110" s="3">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D110" s="4">
-        <v>0</v>
+        <v>0.95833333333333337</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>333</v>
+        <v>284</v>
       </c>
       <c r="F110" s="3">
         <v>0</v>
       </c>
       <c r="G110" s="1"/>
       <c r="H110" s="1" t="s">
-        <v>598</v>
+        <v>617</v>
       </c>
     </row>
     <row r="111" spans="1:8">
-      <c r="A111" t="s">
-        <v>697</v>
+      <c r="A111" s="2" t="s">
+        <v>698</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>522</v>
-      </c>
+        <v>302</v>
+      </c>
+      <c r="C111" s="1"/>
+      <c r="D111" s="5"/>
       <c r="E111" s="1" t="s">
-        <v>786</v>
-      </c>
-      <c r="F111" s="2">
+        <v>315</v>
+      </c>
+      <c r="F111" s="3">
         <v>1</v>
       </c>
-      <c r="G111" s="2" t="s">
-        <v>787</v>
-      </c>
-      <c r="H111" s="2" t="s">
-        <v>637</v>
+      <c r="G111" s="1"/>
+      <c r="H111" s="1" t="s">
+        <v>586</v>
       </c>
     </row>
     <row r="112" spans="1:8">
-      <c r="A112" t="s">
-        <v>698</v>
+      <c r="A112" s="2" t="s">
+        <v>427</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>523</v>
+        <v>241</v>
+      </c>
+      <c r="C112" s="3">
+        <v>14</v>
+      </c>
+      <c r="D112" s="4">
+        <v>0</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>788</v>
-      </c>
-      <c r="F112" s="2">
-        <v>1</v>
-      </c>
-      <c r="G112" s="2" t="s">
-        <v>791</v>
-      </c>
-      <c r="H112" s="2" t="s">
-        <v>638</v>
+        <v>242</v>
+      </c>
+      <c r="F112" s="3">
+        <v>0</v>
+      </c>
+      <c r="G112" s="1"/>
+      <c r="H112" s="1" t="s">
+        <v>587</v>
       </c>
     </row>
     <row r="113" spans="1:8">
-      <c r="A113" t="s">
-        <v>698</v>
+      <c r="A113" s="2" t="s">
+        <v>386</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>523</v>
+        <v>47</v>
+      </c>
+      <c r="C113" s="3">
+        <v>6</v>
+      </c>
+      <c r="D113" s="4">
+        <v>0.66666666666666663</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>789</v>
-      </c>
-      <c r="F113" s="2">
-        <v>1</v>
-      </c>
-      <c r="G113" s="2" t="s">
-        <v>790</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="F113" s="3">
+        <v>0</v>
+      </c>
+      <c r="G113" s="1"/>
       <c r="H113" s="2" t="s">
-        <v>638</v>
+        <v>588</v>
       </c>
     </row>
     <row r="114" spans="1:8">
-      <c r="A114" t="s">
-        <v>699</v>
+      <c r="A114" s="2" t="s">
+        <v>387</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>520</v>
+        <v>49</v>
+      </c>
+      <c r="C114" s="3">
+        <v>6</v>
+      </c>
+      <c r="D114" s="4">
+        <v>0.70833333333333337</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>521</v>
+        <v>50</v>
       </c>
       <c r="F114" s="3">
         <v>0</v>
+      </c>
+      <c r="G114" s="1"/>
+      <c r="H114" s="2" t="s">
+        <v>588</v>
       </c>
     </row>
     <row r="115" spans="1:8">
       <c r="A115" s="2" t="s">
-        <v>401</v>
+        <v>428</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>324</v>
+        <v>274</v>
       </c>
       <c r="C115" s="3">
-        <v>13</v>
-      </c>
-      <c r="D115" s="5">
+        <v>6</v>
+      </c>
+      <c r="D115" s="4">
         <v>0</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>325</v>
+        <v>276</v>
       </c>
       <c r="F115" s="3">
         <v>0</v>
       </c>
       <c r="G115" s="1"/>
-      <c r="H115" s="1" t="s">
-        <v>599</v>
+      <c r="H115" t="s">
+        <v>767</v>
       </c>
     </row>
     <row r="116" spans="1:8">
-      <c r="A116" t="s">
-        <v>700</v>
+      <c r="A116" s="2" t="s">
+        <v>388</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>525</v>
-      </c>
-      <c r="C116" s="2">
-        <v>13</v>
-      </c>
-      <c r="D116" s="6">
-        <v>0</v>
+        <v>43</v>
+      </c>
+      <c r="C116" s="3">
+        <v>6</v>
+      </c>
+      <c r="D116" s="4">
+        <v>0.58333333333333337</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>669</v>
+        <v>44</v>
+      </c>
+      <c r="F116" s="3">
+        <v>0</v>
+      </c>
+      <c r="G116" s="1"/>
+      <c r="H116" s="2" t="s">
+        <v>588</v>
       </c>
     </row>
     <row r="117" spans="1:8">
-      <c r="A117" t="s">
-        <v>701</v>
+      <c r="A117" s="2" t="s">
+        <v>389</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>704</v>
-      </c>
-      <c r="C117" s="2">
-        <v>13</v>
-      </c>
-      <c r="D117" s="6">
-        <v>0</v>
+        <v>51</v>
+      </c>
+      <c r="C117" s="3">
+        <v>6</v>
+      </c>
+      <c r="D117" s="4">
+        <v>0.75</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>670</v>
+        <v>52</v>
+      </c>
+      <c r="F117" s="3">
+        <v>0</v>
+      </c>
+      <c r="G117" s="1"/>
+      <c r="H117" s="2" t="s">
+        <v>588</v>
       </c>
     </row>
     <row r="118" spans="1:8">
-      <c r="A118" t="s">
-        <v>504</v>
+      <c r="A118" s="2" t="s">
+        <v>390</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>503</v>
+        <v>53</v>
       </c>
       <c r="C118" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D118" s="4">
-        <v>0</v>
+        <v>0.79166666666666663</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>97</v>
+        <v>54</v>
       </c>
       <c r="F118" s="3">
         <v>0</v>
       </c>
       <c r="G118" s="1"/>
-      <c r="H118" s="1" t="s">
-        <v>640</v>
+      <c r="H118" s="2" t="s">
+        <v>588</v>
       </c>
     </row>
     <row r="119" spans="1:8">
       <c r="A119" s="2" t="s">
-        <v>491</v>
+        <v>429</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>118</v>
+        <v>273</v>
       </c>
       <c r="C119" s="3">
         <v>6</v>
@@ -6080,185 +5968,190 @@
         <v>0</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>119</v>
+        <v>277</v>
       </c>
       <c r="F119" s="3">
         <v>0</v>
       </c>
       <c r="G119" s="1"/>
-      <c r="H119" s="1" t="s">
-        <v>600</v>
+      <c r="H119" t="s">
+        <v>767</v>
       </c>
     </row>
     <row r="120" spans="1:8">
       <c r="A120" s="2" t="s">
-        <v>494</v>
+        <v>391</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>124</v>
+        <v>55</v>
       </c>
       <c r="C120" s="3">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="D120" s="4">
-        <v>0</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>125</v>
+        <v>56</v>
       </c>
       <c r="F120" s="3">
         <v>0</v>
       </c>
       <c r="G120" s="1"/>
-      <c r="H120" s="1" t="s">
-        <v>600</v>
+      <c r="H120" s="2" t="s">
+        <v>588</v>
       </c>
     </row>
     <row r="121" spans="1:8">
       <c r="A121" s="2" t="s">
-        <v>492</v>
+        <v>392</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>122</v>
+        <v>696</v>
       </c>
       <c r="C121" s="3">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D121" s="4">
-        <v>0</v>
+        <v>0.875</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>123</v>
+        <v>333</v>
       </c>
       <c r="F121" s="3">
         <v>0</v>
       </c>
       <c r="G121" s="1"/>
-      <c r="H121" s="1" t="s">
-        <v>600</v>
+      <c r="H121" s="2" t="s">
+        <v>588</v>
       </c>
     </row>
     <row r="122" spans="1:8">
       <c r="A122" s="2" t="s">
-        <v>493</v>
+        <v>430</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>120</v>
+        <v>275</v>
       </c>
       <c r="C122" s="3">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D122" s="4">
         <v>0</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>121</v>
+        <v>278</v>
       </c>
       <c r="F122" s="3">
         <v>0</v>
       </c>
       <c r="G122" s="1"/>
-      <c r="H122" s="1" t="s">
-        <v>600</v>
+      <c r="H122" t="s">
+        <v>767</v>
       </c>
     </row>
     <row r="123" spans="1:8">
       <c r="A123" s="2" t="s">
-        <v>527</v>
+        <v>393</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>526</v>
-      </c>
-      <c r="C123" s="2">
-        <v>30</v>
-      </c>
-      <c r="D123" s="6">
-        <v>0</v>
-      </c>
-      <c r="E123" s="2" t="s">
-        <v>528</v>
-      </c>
-      <c r="F123" s="2">
-        <v>0</v>
-      </c>
-      <c r="H123" t="s">
-        <v>776</v>
+        <v>41</v>
+      </c>
+      <c r="C123" s="3">
+        <v>6</v>
+      </c>
+      <c r="D123" s="4">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="E123" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F123" s="3">
+        <v>0</v>
+      </c>
+      <c r="G123" s="1"/>
+      <c r="H123" s="2" t="s">
+        <v>588</v>
       </c>
     </row>
     <row r="124" spans="1:8">
       <c r="A124" s="2" t="s">
-        <v>402</v>
+        <v>394</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="C124" s="1"/>
-      <c r="D124" s="1"/>
+        <v>45</v>
+      </c>
+      <c r="C124" s="3">
+        <v>6</v>
+      </c>
+      <c r="D124" s="4">
+        <v>0.625</v>
+      </c>
       <c r="E124" s="1" t="s">
-        <v>262</v>
+        <v>46</v>
       </c>
       <c r="F124" s="3">
-        <v>1</v>
-      </c>
-      <c r="G124" s="1" t="s">
-        <v>263</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G124" s="1"/>
       <c r="H124" s="2" t="s">
-        <v>601</v>
+        <v>588</v>
       </c>
     </row>
     <row r="125" spans="1:8">
-      <c r="A125" s="2" t="s">
-        <v>403</v>
+      <c r="A125" t="s">
+        <v>431</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="C125" s="1"/>
-      <c r="D125" s="1"/>
+        <v>223</v>
+      </c>
+      <c r="C125" s="3">
+        <v>6</v>
+      </c>
+      <c r="D125" s="4">
+        <v>0</v>
+      </c>
       <c r="E125" s="1" t="s">
-        <v>265</v>
+        <v>224</v>
       </c>
       <c r="F125" s="3">
-        <v>1</v>
-      </c>
-      <c r="G125" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="H125" s="2" t="s">
-        <v>601</v>
+        <v>0</v>
+      </c>
+      <c r="G125" s="1"/>
+      <c r="H125" s="1" t="s">
+        <v>589</v>
       </c>
     </row>
     <row r="126" spans="1:8">
-      <c r="A126" s="2" t="s">
-        <v>404</v>
+      <c r="A126" t="s">
+        <v>432</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>137</v>
+        <v>217</v>
       </c>
       <c r="C126" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D126" s="4">
-        <v>0.91666666666666663</v>
+        <v>0</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>138</v>
+        <v>218</v>
       </c>
       <c r="F126" s="3">
         <v>0</v>
       </c>
       <c r="G126" s="1"/>
       <c r="H126" s="1" t="s">
-        <v>602</v>
+        <v>589</v>
       </c>
     </row>
     <row r="127" spans="1:8">
-      <c r="A127" s="2" t="s">
-        <v>445</v>
+      <c r="A127" t="s">
+        <v>433</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="C127" s="3">
         <v>6</v>
@@ -6267,46 +6160,46 @@
         <v>0</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="F127" s="3">
         <v>0</v>
       </c>
       <c r="G127" s="1"/>
       <c r="H127" s="1" t="s">
-        <v>603</v>
+        <v>589</v>
       </c>
     </row>
     <row r="128" spans="1:8">
-      <c r="A128" s="2" t="s">
-        <v>405</v>
+      <c r="A128" t="s">
+        <v>434</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>295</v>
+        <v>219</v>
       </c>
       <c r="C128" s="3">
         <v>6</v>
       </c>
-      <c r="D128" s="5">
+      <c r="D128" s="4">
         <v>0</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>296</v>
+        <v>220</v>
       </c>
       <c r="F128" s="3">
         <v>0</v>
       </c>
       <c r="G128" s="1"/>
       <c r="H128" s="1" t="s">
-        <v>641</v>
+        <v>589</v>
       </c>
     </row>
     <row r="129" spans="1:8">
-      <c r="A129" s="2" t="s">
-        <v>446</v>
+      <c r="A129" t="s">
+        <v>435</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>75</v>
+        <v>227</v>
       </c>
       <c r="C129" s="3">
         <v>6</v>
@@ -6315,1110 +6208,1071 @@
         <v>0</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>76</v>
+        <v>228</v>
       </c>
       <c r="F129" s="3">
         <v>0</v>
       </c>
       <c r="G129" s="1"/>
-      <c r="H129" s="2" t="s">
-        <v>604</v>
+      <c r="H129" s="1" t="s">
+        <v>589</v>
       </c>
     </row>
     <row r="130" spans="1:8">
-      <c r="A130" s="2" t="s">
-        <v>645</v>
+      <c r="A130" t="s">
+        <v>436</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="C130" s="1">
-        <v>7</v>
-      </c>
-      <c r="D130" s="5">
-        <v>0.91666666666666663</v>
+        <v>225</v>
+      </c>
+      <c r="C130" s="3">
+        <v>6</v>
+      </c>
+      <c r="D130" s="4">
+        <v>0</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="F130" s="1">
+        <v>226</v>
+      </c>
+      <c r="F130" s="3">
         <v>0</v>
       </c>
       <c r="G130" s="1"/>
       <c r="H130" s="1" t="s">
-        <v>605</v>
+        <v>589</v>
       </c>
     </row>
     <row r="131" spans="1:8">
-      <c r="A131" s="2" t="s">
-        <v>646</v>
+      <c r="A131" t="s">
+        <v>437</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>495</v>
-      </c>
-      <c r="C131" s="1"/>
-      <c r="D131" s="5"/>
+        <v>221</v>
+      </c>
+      <c r="C131" s="3">
+        <v>6</v>
+      </c>
+      <c r="D131" s="4">
+        <v>0</v>
+      </c>
       <c r="E131" s="1" t="s">
-        <v>317</v>
-      </c>
-      <c r="F131" s="1">
-        <v>1</v>
+        <v>222</v>
+      </c>
+      <c r="F131" s="3">
+        <v>0</v>
       </c>
       <c r="G131" s="1"/>
       <c r="H131" s="1" t="s">
-        <v>606</v>
+        <v>589</v>
       </c>
     </row>
     <row r="132" spans="1:8">
       <c r="A132" s="2" t="s">
-        <v>647</v>
+        <v>438</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>302</v>
-      </c>
-      <c r="C132" s="1"/>
-      <c r="D132" s="1"/>
+        <v>239</v>
+      </c>
+      <c r="C132" s="3">
+        <v>6</v>
+      </c>
+      <c r="D132" s="4">
+        <v>0</v>
+      </c>
       <c r="E132" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="F132" s="1">
-        <v>1</v>
+        <v>240</v>
+      </c>
+      <c r="F132" s="3">
+        <v>0</v>
       </c>
       <c r="G132" s="1"/>
-      <c r="H132" s="1" t="s">
-        <v>606</v>
+      <c r="H132" t="s">
+        <v>768</v>
       </c>
     </row>
     <row r="133" spans="1:8">
       <c r="A133" s="2" t="s">
-        <v>648</v>
+        <v>439</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="C133" s="1"/>
-      <c r="D133" s="1"/>
+        <v>269</v>
+      </c>
+      <c r="C133" s="3">
+        <v>6</v>
+      </c>
+      <c r="D133" s="4">
+        <v>0.54166666666666663</v>
+      </c>
       <c r="E133" s="1" t="s">
-        <v>316</v>
-      </c>
-      <c r="F133" s="1">
-        <v>1</v>
+        <v>270</v>
+      </c>
+      <c r="F133" s="3">
+        <v>0</v>
       </c>
       <c r="G133" s="1"/>
       <c r="H133" s="1" t="s">
-        <v>606</v>
+        <v>590</v>
       </c>
     </row>
     <row r="134" spans="1:8">
       <c r="A134" s="2" t="s">
-        <v>496</v>
+        <v>395</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>248</v>
+        <v>198</v>
       </c>
       <c r="C134" s="3">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D134" s="4">
         <v>0</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>778</v>
+        <v>329</v>
       </c>
       <c r="F134" s="3">
         <v>0</v>
       </c>
       <c r="G134" s="1"/>
       <c r="H134" s="1" t="s">
-        <v>607</v>
+        <v>591</v>
       </c>
     </row>
     <row r="135" spans="1:8">
-      <c r="A135" s="2" t="s">
-        <v>497</v>
+      <c r="A135" t="s">
+        <v>690</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="C135" s="3">
-        <v>29</v>
-      </c>
-      <c r="D135" s="4">
-        <v>0</v>
+        <v>516</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="F135" s="3">
-        <v>0</v>
-      </c>
-      <c r="G135" s="1"/>
+        <v>779</v>
+      </c>
+      <c r="F135" s="2">
+        <v>1</v>
+      </c>
+      <c r="G135" s="2" t="s">
+        <v>780</v>
+      </c>
       <c r="H135" s="2" t="s">
-        <v>608</v>
+        <v>630</v>
       </c>
     </row>
     <row r="136" spans="1:8">
-      <c r="A136" s="2" t="s">
-        <v>457</v>
+      <c r="A136" t="s">
+        <v>691</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C136" s="3">
-        <v>14</v>
-      </c>
-      <c r="D136" s="4">
-        <v>0</v>
+        <v>517</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="F136" s="3">
-        <v>0</v>
-      </c>
-      <c r="G136" s="1"/>
+        <v>781</v>
+      </c>
+      <c r="F136" s="2">
+        <v>1</v>
+      </c>
+      <c r="G136" s="2" t="s">
+        <v>784</v>
+      </c>
       <c r="H136" s="2" t="s">
-        <v>609</v>
+        <v>631</v>
       </c>
     </row>
     <row r="137" spans="1:8">
-      <c r="A137" s="2" t="s">
-        <v>459</v>
+      <c r="A137" t="s">
+        <v>691</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C137" s="3">
-        <v>14</v>
-      </c>
-      <c r="D137" s="4">
-        <v>0</v>
+        <v>517</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>498</v>
-      </c>
-      <c r="F137" s="3">
-        <v>0</v>
-      </c>
-      <c r="G137" s="1"/>
+        <v>782</v>
+      </c>
+      <c r="F137" s="2">
+        <v>1</v>
+      </c>
+      <c r="G137" s="2" t="s">
+        <v>783</v>
+      </c>
       <c r="H137" s="2" t="s">
-        <v>610</v>
+        <v>631</v>
       </c>
     </row>
     <row r="138" spans="1:8">
-      <c r="A138" s="2" t="s">
-        <v>461</v>
+      <c r="A138" t="s">
+        <v>692</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>462</v>
+        <v>514</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>499</v>
+        <v>515</v>
       </c>
       <c r="F138" s="3">
-        <v>1</v>
-      </c>
-      <c r="H138" s="1" t="s">
-        <v>611</v>
+        <v>0</v>
       </c>
     </row>
     <row r="139" spans="1:8">
       <c r="A139" s="2" t="s">
-        <v>458</v>
+        <v>396</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>59</v>
+        <v>321</v>
       </c>
       <c r="C139" s="3">
-        <v>14</v>
-      </c>
-      <c r="D139" s="4">
+        <v>13</v>
+      </c>
+      <c r="D139" s="5">
         <v>0</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>60</v>
+        <v>322</v>
       </c>
       <c r="F139" s="3">
         <v>0</v>
       </c>
       <c r="G139" s="1"/>
-      <c r="H139" s="2" t="s">
-        <v>612</v>
+      <c r="H139" s="1" t="s">
+        <v>592</v>
       </c>
     </row>
     <row r="140" spans="1:8">
-      <c r="A140" s="2" t="s">
-        <v>460</v>
+      <c r="A140" t="s">
+        <v>693</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="C140" s="3">
-        <v>14</v>
-      </c>
-      <c r="D140" s="4">
+        <v>519</v>
+      </c>
+      <c r="C140" s="2">
+        <v>13</v>
+      </c>
+      <c r="D140" s="6">
         <v>0</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="F140" s="3">
-        <v>0</v>
-      </c>
-      <c r="G140" s="1"/>
-      <c r="H140" s="2" t="s">
-        <v>613</v>
+        <v>662</v>
       </c>
     </row>
     <row r="141" spans="1:8">
-      <c r="A141" s="2" t="s">
-        <v>406</v>
+      <c r="A141" t="s">
+        <v>694</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="C141" s="3">
-        <v>14</v>
-      </c>
-      <c r="D141" s="4">
+        <v>697</v>
+      </c>
+      <c r="C141" s="2">
+        <v>13</v>
+      </c>
+      <c r="D141" s="6">
         <v>0</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="F141" s="3">
-        <v>0</v>
-      </c>
-      <c r="G141" s="1"/>
-      <c r="H141" s="1" t="s">
-        <v>614</v>
+        <v>663</v>
       </c>
     </row>
     <row r="142" spans="1:8">
-      <c r="A142" s="2" t="s">
-        <v>407</v>
+      <c r="A142" t="s">
+        <v>498</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>129</v>
+        <v>497</v>
       </c>
       <c r="C142" s="3">
         <v>7</v>
       </c>
       <c r="D142" s="4">
-        <v>0.91666666666666663</v>
+        <v>0</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>130</v>
+        <v>96</v>
       </c>
       <c r="F142" s="3">
         <v>0</v>
       </c>
       <c r="G142" s="1"/>
       <c r="H142" s="1" t="s">
-        <v>614</v>
+        <v>633</v>
       </c>
     </row>
     <row r="143" spans="1:8">
       <c r="A143" s="2" t="s">
-        <v>408</v>
+        <v>486</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="C143" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D143" s="4">
-        <v>0.91666666666666663</v>
+        <v>0</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>285</v>
+        <v>118</v>
       </c>
       <c r="F143" s="3">
         <v>0</v>
       </c>
       <c r="G143" s="1"/>
       <c r="H143" s="1" t="s">
-        <v>614</v>
+        <v>593</v>
       </c>
     </row>
     <row r="144" spans="1:8">
       <c r="A144" s="2" t="s">
-        <v>409</v>
+        <v>488</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>290</v>
+        <v>121</v>
       </c>
       <c r="C144" s="3">
-        <v>7</v>
-      </c>
-      <c r="D144" s="5">
-        <v>0.875</v>
+        <v>30</v>
+      </c>
+      <c r="D144" s="4">
+        <v>0</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>291</v>
+        <v>122</v>
       </c>
       <c r="F144" s="3">
         <v>0</v>
       </c>
       <c r="G144" s="1"/>
       <c r="H144" s="1" t="s">
-        <v>615</v>
+        <v>593</v>
       </c>
     </row>
     <row r="145" spans="1:8">
       <c r="A145" s="2" t="s">
-        <v>410</v>
+        <v>487</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>9</v>
+        <v>119</v>
       </c>
       <c r="C145" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D145" s="4">
         <v>0</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>10</v>
+        <v>120</v>
       </c>
       <c r="F145" s="3">
         <v>0</v>
       </c>
       <c r="G145" s="1"/>
-      <c r="H145" s="2" t="s">
-        <v>616</v>
+      <c r="H145" s="1" t="s">
+        <v>593</v>
       </c>
     </row>
     <row r="146" spans="1:8">
-      <c r="A146" t="s">
-        <v>511</v>
+      <c r="A146" s="2" t="s">
+        <v>521</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="C146" s="3">
-        <v>13</v>
-      </c>
-      <c r="D146" s="5">
-        <v>0</v>
-      </c>
-      <c r="E146" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="F146" s="3">
-        <v>0</v>
-      </c>
-      <c r="G146" s="1"/>
-      <c r="H146" s="1" t="s">
-        <v>617</v>
+        <v>520</v>
+      </c>
+      <c r="C146" s="2">
+        <v>30</v>
+      </c>
+      <c r="D146" s="6">
+        <v>0</v>
+      </c>
+      <c r="E146" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="F146" s="2">
+        <v>0</v>
+      </c>
+      <c r="H146" t="s">
+        <v>769</v>
       </c>
     </row>
     <row r="147" spans="1:8">
-      <c r="A147" t="s">
-        <v>512</v>
+      <c r="A147" s="2" t="s">
+        <v>397</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>322</v>
-      </c>
-      <c r="C147" s="3"/>
-      <c r="D147" s="5"/>
+        <v>258</v>
+      </c>
+      <c r="C147" s="1"/>
+      <c r="D147" s="1"/>
       <c r="E147" s="1" t="s">
-        <v>323</v>
+        <v>259</v>
       </c>
       <c r="F147" s="3">
         <v>1</v>
       </c>
-      <c r="G147" s="1"/>
-      <c r="H147" s="1" t="s">
-        <v>618</v>
+      <c r="G147" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="H147" s="2" t="s">
+        <v>594</v>
       </c>
     </row>
     <row r="148" spans="1:8">
       <c r="A148" s="2" t="s">
-        <v>507</v>
+        <v>398</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>508</v>
-      </c>
-      <c r="C148" s="3">
-        <v>30</v>
-      </c>
-      <c r="D148" s="5">
-        <v>0</v>
-      </c>
+        <v>261</v>
+      </c>
+      <c r="C148" s="1"/>
+      <c r="D148" s="1"/>
       <c r="E148" s="1" t="s">
-        <v>509</v>
+        <v>262</v>
       </c>
       <c r="F148" s="3">
-        <v>0</v>
-      </c>
-      <c r="G148" s="1"/>
-      <c r="H148" s="1" t="s">
-        <v>619</v>
+        <v>1</v>
+      </c>
+      <c r="G148" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="H148" s="2" t="s">
+        <v>594</v>
       </c>
     </row>
     <row r="149" spans="1:8">
       <c r="A149" s="2" t="s">
-        <v>413</v>
+        <v>399</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>300</v>
+        <v>134</v>
       </c>
       <c r="C149" s="3">
-        <v>30</v>
-      </c>
-      <c r="D149" s="5">
-        <v>0</v>
+        <v>7</v>
+      </c>
+      <c r="D149" s="4">
+        <v>0.91666666666666663</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>306</v>
+        <v>135</v>
       </c>
       <c r="F149" s="3">
         <v>0</v>
       </c>
       <c r="G149" s="1"/>
       <c r="H149" s="1" t="s">
-        <v>619</v>
+        <v>595</v>
       </c>
     </row>
     <row r="150" spans="1:8">
       <c r="A150" s="2" t="s">
-        <v>414</v>
+        <v>440</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>298</v>
+        <v>231</v>
       </c>
       <c r="C150" s="3">
-        <v>7</v>
-      </c>
-      <c r="D150" s="5">
-        <v>0.91666666666666663</v>
+        <v>6</v>
+      </c>
+      <c r="D150" s="4">
+        <v>0</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>298</v>
+        <v>232</v>
       </c>
       <c r="F150" s="3">
         <v>0</v>
       </c>
       <c r="G150" s="1"/>
       <c r="H150" s="1" t="s">
-        <v>620</v>
+        <v>596</v>
       </c>
     </row>
     <row r="151" spans="1:8">
       <c r="A151" s="2" t="s">
-        <v>683</v>
+        <v>400</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>685</v>
+        <v>292</v>
+      </c>
+      <c r="C151" s="3">
+        <v>6</v>
+      </c>
+      <c r="D151" s="5">
+        <v>0</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>687</v>
-      </c>
-      <c r="F151" s="2">
-        <v>1</v>
-      </c>
-      <c r="H151" s="2" t="s">
-        <v>713</v>
+        <v>293</v>
+      </c>
+      <c r="F151" s="3">
+        <v>0</v>
+      </c>
+      <c r="G151" s="1"/>
+      <c r="H151" s="1" t="s">
+        <v>634</v>
       </c>
     </row>
     <row r="152" spans="1:8">
       <c r="A152" s="2" t="s">
-        <v>682</v>
+        <v>441</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>684</v>
+        <v>75</v>
+      </c>
+      <c r="C152" s="3">
+        <v>6</v>
+      </c>
+      <c r="D152" s="4">
+        <v>0</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>686</v>
-      </c>
-      <c r="F152" s="2">
-        <v>1</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="F152" s="3">
+        <v>0</v>
+      </c>
+      <c r="G152" s="1"/>
       <c r="H152" s="2" t="s">
-        <v>712</v>
+        <v>597</v>
       </c>
     </row>
     <row r="153" spans="1:8">
       <c r="A153" s="2" t="s">
-        <v>415</v>
+        <v>638</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="C153" s="3">
-        <v>6</v>
-      </c>
-      <c r="D153" s="4">
-        <v>0</v>
+        <v>310</v>
+      </c>
+      <c r="C153" s="1">
+        <v>7</v>
+      </c>
+      <c r="D153" s="5">
+        <v>0.91666666666666663</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>644</v>
-      </c>
-      <c r="F153" s="3">
+        <v>311</v>
+      </c>
+      <c r="F153" s="1">
         <v>0</v>
       </c>
       <c r="G153" s="1"/>
       <c r="H153" s="1" t="s">
-        <v>621</v>
+        <v>598</v>
       </c>
     </row>
     <row r="154" spans="1:8">
       <c r="A154" s="2" t="s">
-        <v>415</v>
+        <v>639</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="C154" s="3">
-        <v>13</v>
-      </c>
-      <c r="D154" s="4">
-        <v>0</v>
-      </c>
+        <v>489</v>
+      </c>
+      <c r="C154" s="1"/>
+      <c r="D154" s="5"/>
       <c r="E154" s="1" t="s">
-        <v>643</v>
-      </c>
-      <c r="F154" s="3">
-        <v>0</v>
+        <v>314</v>
+      </c>
+      <c r="F154" s="1">
+        <v>1</v>
       </c>
       <c r="G154" s="1"/>
       <c r="H154" s="1" t="s">
-        <v>621</v>
+        <v>599</v>
       </c>
     </row>
     <row r="155" spans="1:8">
-      <c r="A155" t="s">
-        <v>416</v>
+      <c r="A155" s="2" t="s">
+        <v>640</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C155" s="3">
-        <v>6</v>
-      </c>
-      <c r="D155" s="4">
-        <v>0.41666666666666669</v>
-      </c>
+        <v>299</v>
+      </c>
+      <c r="C155" s="1"/>
+      <c r="D155" s="1"/>
       <c r="E155" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F155" s="3">
-        <v>0</v>
+        <v>312</v>
+      </c>
+      <c r="F155" s="1">
+        <v>1</v>
       </c>
       <c r="G155" s="1"/>
-      <c r="H155" s="2" t="s">
-        <v>622</v>
+      <c r="H155" s="1" t="s">
+        <v>599</v>
       </c>
     </row>
     <row r="156" spans="1:8">
-      <c r="A156" t="s">
-        <v>417</v>
+      <c r="A156" s="2" t="s">
+        <v>641</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C156" s="3">
-        <v>6</v>
-      </c>
-      <c r="D156" s="4">
-        <v>0.41666666666666669</v>
-      </c>
+        <v>300</v>
+      </c>
+      <c r="C156" s="1"/>
+      <c r="D156" s="1"/>
       <c r="E156" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F156" s="3">
-        <v>0</v>
+        <v>313</v>
+      </c>
+      <c r="F156" s="1">
+        <v>1</v>
       </c>
       <c r="G156" s="1"/>
-      <c r="H156" s="2" t="s">
-        <v>622</v>
+      <c r="H156" s="1" t="s">
+        <v>599</v>
       </c>
     </row>
     <row r="157" spans="1:8">
-      <c r="A157" t="s">
-        <v>418</v>
+      <c r="A157" s="2" t="s">
+        <v>490</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>23</v>
+        <v>245</v>
       </c>
       <c r="C157" s="3">
         <v>6</v>
       </c>
       <c r="D157" s="4">
-        <v>0.47916666666666669</v>
+        <v>0</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>24</v>
+        <v>771</v>
       </c>
       <c r="F157" s="3">
         <v>0</v>
       </c>
       <c r="G157" s="1"/>
-      <c r="H157" s="2" t="s">
-        <v>622</v>
+      <c r="H157" s="1" t="s">
+        <v>600</v>
       </c>
     </row>
     <row r="158" spans="1:8">
-      <c r="A158" t="s">
-        <v>419</v>
+      <c r="A158" s="2" t="s">
+        <v>491</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>31</v>
+        <v>243</v>
       </c>
       <c r="C158" s="3">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="D158" s="4">
-        <v>0.41666666666666669</v>
+        <v>0</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>32</v>
+        <v>244</v>
       </c>
       <c r="F158" s="3">
         <v>0</v>
       </c>
       <c r="G158" s="1"/>
       <c r="H158" s="2" t="s">
-        <v>622</v>
+        <v>601</v>
       </c>
     </row>
     <row r="159" spans="1:8">
-      <c r="A159" t="s">
-        <v>420</v>
+      <c r="A159" s="2" t="s">
+        <v>715</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C159" s="3">
-        <v>13</v>
-      </c>
-      <c r="D159" s="4">
-        <v>0.75</v>
+        <v>712</v>
+      </c>
+      <c r="C159" s="2">
+        <v>7</v>
+      </c>
+      <c r="D159" s="6">
+        <v>0.95833333333333337</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>34</v>
+        <v>713</v>
       </c>
       <c r="F159" s="3">
         <v>0</v>
       </c>
-      <c r="G159" s="1"/>
-      <c r="H159" s="2" t="s">
-        <v>622</v>
+      <c r="H159" s="7" t="s">
+        <v>714</v>
       </c>
     </row>
     <row r="160" spans="1:8">
-      <c r="A160" t="s">
-        <v>421</v>
+      <c r="A160" s="2" t="s">
+        <v>452</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>20</v>
+        <v>57</v>
       </c>
       <c r="C160" s="3">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="D160" s="4">
-        <v>0.4375</v>
+        <v>0</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>21</v>
+        <v>58</v>
       </c>
       <c r="F160" s="3">
         <v>0</v>
       </c>
       <c r="G160" s="1"/>
       <c r="H160" s="2" t="s">
-        <v>622</v>
+        <v>602</v>
       </c>
     </row>
     <row r="161" spans="1:8">
-      <c r="A161" t="s">
-        <v>422</v>
+      <c r="A161" s="2" t="s">
+        <v>454</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>18</v>
+        <v>61</v>
       </c>
       <c r="C161" s="3">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="D161" s="4">
-        <v>0.5625</v>
+        <v>0</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>19</v>
+        <v>492</v>
       </c>
       <c r="F161" s="3">
         <v>0</v>
       </c>
       <c r="G161" s="1"/>
       <c r="H161" s="2" t="s">
-        <v>622</v>
+        <v>603</v>
       </c>
     </row>
     <row r="162" spans="1:8">
       <c r="A162" s="2" t="s">
-        <v>464</v>
+        <v>456</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C162" s="3">
-        <v>13</v>
-      </c>
-      <c r="D162" s="4">
-        <v>0.75</v>
+        <v>457</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>38</v>
+        <v>493</v>
       </c>
       <c r="F162" s="3">
-        <v>0</v>
-      </c>
-      <c r="G162" s="1"/>
-      <c r="H162" s="2" t="s">
-        <v>622</v>
+        <v>1</v>
+      </c>
+      <c r="H162" s="1" t="s">
+        <v>604</v>
       </c>
     </row>
     <row r="163" spans="1:8">
-      <c r="A163" t="s">
-        <v>423</v>
+      <c r="A163" s="2" t="s">
+        <v>453</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>29</v>
+        <v>59</v>
       </c>
       <c r="C163" s="3">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="D163" s="4">
-        <v>0.41666666666666669</v>
+        <v>0</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="F163" s="3">
         <v>0</v>
       </c>
       <c r="G163" s="1"/>
       <c r="H163" s="2" t="s">
-        <v>622</v>
+        <v>605</v>
       </c>
     </row>
     <row r="164" spans="1:8">
       <c r="A164" s="2" t="s">
-        <v>465</v>
+        <v>455</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="C164" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D164" s="4">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>40</v>
+        <v>63</v>
       </c>
       <c r="F164" s="3">
         <v>0</v>
       </c>
       <c r="G164" s="1"/>
       <c r="H164" s="2" t="s">
-        <v>622</v>
+        <v>606</v>
       </c>
     </row>
     <row r="165" spans="1:8">
-      <c r="A165" t="s">
-        <v>424</v>
+      <c r="A165" s="2" t="s">
+        <v>401</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>35</v>
+        <v>123</v>
       </c>
       <c r="C165" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D165" s="4">
-        <v>0.83333333333333337</v>
+        <v>0</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>36</v>
+        <v>124</v>
       </c>
       <c r="F165" s="3">
         <v>0</v>
       </c>
       <c r="G165" s="1"/>
-      <c r="H165" s="2" t="s">
-        <v>622</v>
+      <c r="H165" s="1" t="s">
+        <v>607</v>
       </c>
     </row>
     <row r="166" spans="1:8">
-      <c r="A166" t="s">
-        <v>425</v>
+      <c r="A166" s="2" t="s">
+        <v>402</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>22</v>
+        <v>126</v>
       </c>
       <c r="C166" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D166" s="4">
-        <v>0.45833333333333331</v>
+        <v>0.91666666666666663</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>286</v>
+        <v>127</v>
       </c>
       <c r="F166" s="3">
         <v>0</v>
       </c>
       <c r="G166" s="1"/>
-      <c r="H166" s="2" t="s">
-        <v>622</v>
+      <c r="H166" s="1" t="s">
+        <v>607</v>
       </c>
     </row>
     <row r="167" spans="1:8">
       <c r="A167" s="2" t="s">
-        <v>455</v>
+        <v>403</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>463</v>
+        <v>125</v>
       </c>
       <c r="C167" s="3">
-        <v>8</v>
-      </c>
-      <c r="D167" s="6">
-        <v>0</v>
+        <v>7</v>
+      </c>
+      <c r="D167" s="4">
+        <v>0.91666666666666663</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>456</v>
+        <v>282</v>
       </c>
       <c r="F167" s="3">
         <v>0</v>
       </c>
+      <c r="G167" s="1"/>
       <c r="H167" s="1" t="s">
-        <v>623</v>
+        <v>607</v>
       </c>
     </row>
     <row r="168" spans="1:8">
       <c r="A168" s="2" t="s">
-        <v>454</v>
+        <v>404</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>336</v>
+        <v>287</v>
       </c>
       <c r="C168" s="3">
         <v>7</v>
       </c>
-      <c r="D168" s="4">
-        <v>0</v>
+      <c r="D168" s="5">
+        <v>0.875</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>93</v>
+        <v>288</v>
       </c>
       <c r="F168" s="3">
         <v>0</v>
       </c>
       <c r="G168" s="1"/>
-      <c r="H168" t="s">
-        <v>777</v>
+      <c r="H168" s="1" t="s">
+        <v>608</v>
       </c>
     </row>
     <row r="169" spans="1:8">
       <c r="A169" s="2" t="s">
-        <v>510</v>
+        <v>405</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>135</v>
+        <v>9</v>
       </c>
       <c r="C169" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D169" s="4">
         <v>0</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>338</v>
+        <v>10</v>
       </c>
       <c r="F169" s="3">
         <v>0</v>
       </c>
       <c r="G169" s="1"/>
-      <c r="H169" s="1" t="s">
-        <v>625</v>
+      <c r="H169" s="2" t="s">
+        <v>609</v>
       </c>
     </row>
     <row r="170" spans="1:8">
-      <c r="A170" s="2" t="s">
-        <v>702</v>
+      <c r="A170" t="s">
+        <v>505</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>524</v>
-      </c>
-      <c r="C170" s="3"/>
-      <c r="D170" s="6"/>
+        <v>317</v>
+      </c>
+      <c r="C170" s="3">
+        <v>13</v>
+      </c>
+      <c r="D170" s="5">
+        <v>0</v>
+      </c>
       <c r="E170" s="1" t="s">
-        <v>667</v>
+        <v>318</v>
       </c>
       <c r="F170" s="3">
-        <v>1</v>
-      </c>
-      <c r="G170" s="2" t="s">
-        <v>668</v>
-      </c>
-      <c r="H170" t="s">
-        <v>666</v>
+        <v>0</v>
+      </c>
+      <c r="G170" s="1"/>
+      <c r="H170" s="1" t="s">
+        <v>610</v>
       </c>
     </row>
     <row r="171" spans="1:8">
       <c r="A171" t="s">
-        <v>426</v>
+        <v>506</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="C171" s="3">
-        <v>6</v>
-      </c>
-      <c r="D171" s="4">
-        <v>0</v>
-      </c>
+        <v>319</v>
+      </c>
+      <c r="C171" s="3"/>
+      <c r="D171" s="5"/>
       <c r="E171" s="1" t="s">
-        <v>206</v>
+        <v>320</v>
       </c>
       <c r="F171" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G171" s="1"/>
       <c r="H171" s="1" t="s">
-        <v>626</v>
+        <v>611</v>
       </c>
     </row>
     <row r="172" spans="1:8">
-      <c r="A172" t="s">
-        <v>427</v>
+      <c r="A172" s="2" t="s">
+        <v>501</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>203</v>
+        <v>502</v>
       </c>
       <c r="C172" s="3">
-        <v>6</v>
-      </c>
-      <c r="D172" s="4">
+        <v>30</v>
+      </c>
+      <c r="D172" s="5">
         <v>0</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>204</v>
+        <v>503</v>
       </c>
       <c r="F172" s="3">
         <v>0</v>
       </c>
       <c r="G172" s="1"/>
       <c r="H172" s="1" t="s">
-        <v>626</v>
+        <v>612</v>
       </c>
     </row>
     <row r="173" spans="1:8">
-      <c r="A173" t="s">
-        <v>428</v>
+      <c r="A173" s="2" t="s">
+        <v>408</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>207</v>
+        <v>297</v>
       </c>
       <c r="C173" s="3">
-        <v>6</v>
-      </c>
-      <c r="D173" s="4">
+        <v>30</v>
+      </c>
+      <c r="D173" s="5">
         <v>0</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>208</v>
+        <v>303</v>
       </c>
       <c r="F173" s="3">
         <v>0</v>
       </c>
       <c r="G173" s="1"/>
       <c r="H173" s="1" t="s">
-        <v>626</v>
+        <v>612</v>
       </c>
     </row>
     <row r="174" spans="1:8">
-      <c r="A174" t="s">
-        <v>429</v>
+      <c r="A174" s="2" t="s">
+        <v>409</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>136</v>
+        <v>295</v>
       </c>
       <c r="C174" s="3">
         <v>7</v>
       </c>
-      <c r="D174" s="4">
-        <v>0.97916666666666663</v>
+      <c r="D174" s="5">
+        <v>0.91666666666666663</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>650</v>
+        <v>295</v>
       </c>
       <c r="F174" s="3">
         <v>0</v>
       </c>
       <c r="G174" s="1"/>
       <c r="H174" s="1" t="s">
-        <v>627</v>
+        <v>613</v>
       </c>
     </row>
     <row r="175" spans="1:8">
       <c r="A175" s="2" t="s">
-        <v>468</v>
+        <v>676</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C175" s="3">
-        <v>6</v>
-      </c>
-      <c r="D175" s="4">
-        <v>0</v>
+        <v>678</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>649</v>
-      </c>
-      <c r="F175" s="3">
-        <v>0</v>
-      </c>
-      <c r="G175" s="1"/>
+        <v>680</v>
+      </c>
+      <c r="F175" s="2">
+        <v>1</v>
+      </c>
       <c r="H175" s="2" t="s">
-        <v>628</v>
+        <v>706</v>
       </c>
     </row>
     <row r="176" spans="1:8">
       <c r="A176" s="2" t="s">
-        <v>469</v>
+        <v>675</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="C176" s="3">
-        <v>13</v>
-      </c>
-      <c r="D176" s="4">
-        <v>0</v>
+        <v>677</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="F176" s="3">
-        <v>0</v>
-      </c>
-      <c r="G176" s="1"/>
+        <v>679</v>
+      </c>
+      <c r="F176" s="2">
+        <v>1</v>
+      </c>
       <c r="H176" s="2" t="s">
-        <v>629</v>
+        <v>705</v>
       </c>
     </row>
     <row r="177" spans="1:8">
       <c r="A177" s="2" t="s">
-        <v>470</v>
+        <v>410</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>69</v>
+        <v>216</v>
       </c>
       <c r="C177" s="3">
         <v>6</v>
@@ -7427,972 +7281,1131 @@
         <v>0</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>70</v>
+        <v>637</v>
       </c>
       <c r="F177" s="3">
         <v>0</v>
       </c>
       <c r="G177" s="1"/>
-      <c r="H177" s="2" t="s">
-        <v>630</v>
+      <c r="H177" s="1" t="s">
+        <v>614</v>
       </c>
     </row>
     <row r="178" spans="1:8">
       <c r="A178" s="2" t="s">
-        <v>471</v>
+        <v>410</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>67</v>
+        <v>216</v>
       </c>
       <c r="C178" s="3">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D178" s="4">
         <v>0</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>68</v>
+        <v>636</v>
       </c>
       <c r="F178" s="3">
         <v>0</v>
       </c>
       <c r="G178" s="1"/>
-      <c r="H178" s="2" t="s">
-        <v>631</v>
+      <c r="H178" s="1" t="s">
+        <v>614</v>
       </c>
     </row>
     <row r="179" spans="1:8">
-      <c r="A179" s="2" t="s">
-        <v>472</v>
+      <c r="A179" t="s">
+        <v>411</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>71</v>
+        <v>25</v>
       </c>
       <c r="C179" s="3">
         <v>6</v>
       </c>
       <c r="D179" s="4">
-        <v>0</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>72</v>
+        <v>26</v>
       </c>
       <c r="F179" s="3">
         <v>0</v>
       </c>
       <c r="G179" s="1"/>
       <c r="H179" s="2" t="s">
-        <v>632</v>
+        <v>615</v>
       </c>
     </row>
     <row r="180" spans="1:8">
-      <c r="A180" s="2" t="s">
-        <v>473</v>
+      <c r="A180" t="s">
+        <v>412</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>73</v>
+        <v>27</v>
       </c>
       <c r="C180" s="3">
         <v>6</v>
       </c>
       <c r="D180" s="4">
-        <v>0</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>74</v>
+        <v>28</v>
       </c>
       <c r="F180" s="3">
         <v>0</v>
       </c>
       <c r="G180" s="1"/>
       <c r="H180" s="2" t="s">
-        <v>633</v>
+        <v>615</v>
       </c>
     </row>
     <row r="181" spans="1:8">
-      <c r="A181" s="2" t="s">
-        <v>474</v>
+      <c r="A181" t="s">
+        <v>413</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>95</v>
+        <v>23</v>
       </c>
       <c r="C181" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D181" s="4">
-        <v>0</v>
+        <v>0.47916666666666669</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>96</v>
+        <v>24</v>
       </c>
       <c r="F181" s="3">
         <v>0</v>
       </c>
       <c r="G181" s="1"/>
-      <c r="H181" t="s">
-        <v>642</v>
+      <c r="H181" s="2" t="s">
+        <v>615</v>
       </c>
     </row>
     <row r="182" spans="1:8">
-      <c r="A182" s="2" t="s">
-        <v>476</v>
+      <c r="A182" t="s">
+        <v>414</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>98</v>
+        <v>31</v>
       </c>
       <c r="C182" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D182" s="4">
-        <v>0</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>99</v>
+        <v>32</v>
       </c>
       <c r="F182" s="3">
         <v>0</v>
       </c>
       <c r="G182" s="1"/>
-      <c r="H182" t="s">
-        <v>642</v>
+      <c r="H182" s="2" t="s">
+        <v>615</v>
       </c>
     </row>
     <row r="183" spans="1:8">
-      <c r="A183" s="2" t="s">
-        <v>477</v>
+      <c r="A183" t="s">
+        <v>415</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>89</v>
+        <v>33</v>
       </c>
       <c r="C183" s="3">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D183" s="4">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>90</v>
+        <v>34</v>
       </c>
       <c r="F183" s="3">
         <v>0</v>
       </c>
       <c r="G183" s="1"/>
-      <c r="H183" s="1" t="s">
-        <v>642</v>
+      <c r="H183" s="2" t="s">
+        <v>615</v>
       </c>
     </row>
     <row r="184" spans="1:8">
-      <c r="A184" s="2" t="s">
-        <v>478</v>
+      <c r="A184" t="s">
+        <v>416</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="C184" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D184" s="4">
-        <v>0</v>
+        <v>0.4375</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>92</v>
+        <v>21</v>
       </c>
       <c r="F184" s="3">
         <v>0</v>
       </c>
       <c r="G184" s="1"/>
-      <c r="H184" s="1" t="s">
-        <v>642</v>
+      <c r="H184" s="2" t="s">
+        <v>615</v>
       </c>
     </row>
     <row r="185" spans="1:8">
-      <c r="A185" s="2" t="s">
-        <v>479</v>
+      <c r="A185" t="s">
+        <v>417</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>105</v>
+        <v>18</v>
       </c>
       <c r="C185" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D185" s="4">
-        <v>0</v>
+        <v>0.5625</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>106</v>
+        <v>19</v>
       </c>
       <c r="F185" s="3">
         <v>0</v>
       </c>
       <c r="G185" s="1"/>
-      <c r="H185" s="1" t="s">
-        <v>642</v>
+      <c r="H185" s="2" t="s">
+        <v>615</v>
       </c>
     </row>
     <row r="186" spans="1:8">
       <c r="A186" s="2" t="s">
-        <v>480</v>
+        <v>459</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>113</v>
+        <v>37</v>
       </c>
       <c r="C186" s="3">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D186" s="4">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>114</v>
+        <v>38</v>
       </c>
       <c r="F186" s="3">
         <v>0</v>
       </c>
       <c r="G186" s="1"/>
-      <c r="H186" s="1" t="s">
-        <v>642</v>
+      <c r="H186" s="2" t="s">
+        <v>615</v>
       </c>
     </row>
     <row r="187" spans="1:8">
-      <c r="A187" s="2" t="s">
-        <v>481</v>
+      <c r="A187" t="s">
+        <v>418</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>107</v>
+        <v>29</v>
       </c>
       <c r="C187" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D187" s="4">
-        <v>0</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>108</v>
+        <v>30</v>
       </c>
       <c r="F187" s="3">
         <v>0</v>
       </c>
       <c r="G187" s="1"/>
-      <c r="H187" s="1" t="s">
-        <v>642</v>
+      <c r="H187" s="2" t="s">
+        <v>615</v>
       </c>
     </row>
     <row r="188" spans="1:8">
       <c r="A188" s="2" t="s">
-        <v>482</v>
+        <v>460</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>94</v>
+        <v>39</v>
       </c>
       <c r="C188" s="3">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D188" s="4">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>475</v>
+        <v>40</v>
       </c>
       <c r="F188" s="3">
         <v>0</v>
       </c>
       <c r="G188" s="1"/>
-      <c r="H188" s="8" t="s">
-        <v>642</v>
+      <c r="H188" s="2" t="s">
+        <v>615</v>
       </c>
     </row>
     <row r="189" spans="1:8">
-      <c r="A189" s="2" t="s">
-        <v>483</v>
+      <c r="A189" t="s">
+        <v>419</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>111</v>
+        <v>35</v>
       </c>
       <c r="C189" s="3">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D189" s="4">
-        <v>0</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>112</v>
+        <v>36</v>
       </c>
       <c r="F189" s="3">
         <v>0</v>
       </c>
       <c r="G189" s="1"/>
-      <c r="H189" s="1" t="s">
-        <v>642</v>
+      <c r="H189" s="2" t="s">
+        <v>615</v>
       </c>
     </row>
     <row r="190" spans="1:8">
       <c r="A190" t="s">
-        <v>430</v>
+        <v>420</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>288</v>
+        <v>22</v>
       </c>
       <c r="C190" s="3">
-        <v>13</v>
-      </c>
-      <c r="D190" s="5">
-        <v>0</v>
+        <v>6</v>
+      </c>
+      <c r="D190" s="4">
+        <v>0.45833333333333331</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="F190" s="3">
         <v>0</v>
       </c>
       <c r="G190" s="1"/>
-      <c r="H190" s="1" t="s">
-        <v>634</v>
+      <c r="H190" s="2" t="s">
+        <v>615</v>
       </c>
     </row>
     <row r="191" spans="1:8">
-      <c r="A191" t="s">
-        <v>513</v>
+      <c r="A191" s="2" t="s">
+        <v>708</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="C191" s="3">
+        <v>709</v>
+      </c>
+      <c r="C191" s="2">
         <v>6</v>
       </c>
-      <c r="D191" s="4">
+      <c r="D191" s="6">
         <v>0</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>210</v>
+        <v>710</v>
       </c>
       <c r="F191" s="3">
         <v>0</v>
       </c>
-      <c r="G191" s="1"/>
-      <c r="H191" s="1" t="s">
-        <v>635</v>
+      <c r="H191" s="7" t="s">
+        <v>748</v>
       </c>
     </row>
     <row r="192" spans="1:8">
-      <c r="A192" t="s">
-        <v>514</v>
+      <c r="A192" s="2" t="s">
+        <v>450</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>211</v>
+        <v>458</v>
       </c>
       <c r="C192" s="3">
-        <v>6</v>
-      </c>
-      <c r="D192" s="4">
+        <v>8</v>
+      </c>
+      <c r="D192" s="6">
         <v>0</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>212</v>
+        <v>451</v>
       </c>
       <c r="F192" s="3">
         <v>0</v>
       </c>
-      <c r="G192" s="1"/>
       <c r="H192" s="1" t="s">
-        <v>635</v>
+        <v>616</v>
       </c>
     </row>
     <row r="193" spans="1:8">
-      <c r="A193" t="s">
-        <v>517</v>
+      <c r="A193" s="2" t="s">
+        <v>449</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>216</v>
+        <v>332</v>
       </c>
       <c r="C193" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D193" s="4">
         <v>0</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>217</v>
+        <v>92</v>
       </c>
       <c r="F193" s="3">
         <v>0</v>
       </c>
       <c r="G193" s="1"/>
-      <c r="H193" s="1" t="s">
-        <v>635</v>
+      <c r="H193" t="s">
+        <v>770</v>
       </c>
     </row>
     <row r="194" spans="1:8">
-      <c r="A194" t="s">
-        <v>516</v>
+      <c r="A194" s="2" t="s">
+        <v>504</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>214</v>
+        <v>132</v>
       </c>
       <c r="C194" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D194" s="4">
         <v>0</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>215</v>
+        <v>334</v>
       </c>
       <c r="F194" s="3">
         <v>0</v>
       </c>
       <c r="G194" s="1"/>
       <c r="H194" s="1" t="s">
-        <v>635</v>
+        <v>618</v>
       </c>
     </row>
     <row r="195" spans="1:8">
-      <c r="A195" t="s">
-        <v>515</v>
+      <c r="A195" s="2" t="s">
+        <v>772</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="C195" s="3">
+        <v>763</v>
+      </c>
+      <c r="C195" s="2">
         <v>6</v>
       </c>
-      <c r="D195" s="4">
-        <v>0</v>
-      </c>
-      <c r="E195" s="1" t="s">
-        <v>518</v>
+      <c r="D195" s="6">
+        <v>0</v>
+      </c>
+      <c r="E195" s="10" t="s">
+        <v>776</v>
       </c>
       <c r="F195" s="3">
         <v>0</v>
       </c>
-      <c r="G195" s="1"/>
-      <c r="H195" s="1" t="s">
-        <v>635</v>
+      <c r="H195" s="2" t="s">
+        <v>775</v>
       </c>
     </row>
     <row r="196" spans="1:8">
-      <c r="A196" t="s">
-        <v>431</v>
+      <c r="A196" s="2" t="s">
+        <v>773</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="C196" s="1"/>
-      <c r="D196" s="1"/>
+        <v>764</v>
+      </c>
+      <c r="C196" s="2">
+        <v>6</v>
+      </c>
+      <c r="D196" s="6">
+        <v>0</v>
+      </c>
       <c r="E196" s="1" t="s">
-        <v>319</v>
-      </c>
-      <c r="F196" s="1">
-        <v>1</v>
-      </c>
-      <c r="G196" s="1"/>
-      <c r="H196" s="1" t="s">
-        <v>636</v>
+        <v>777</v>
+      </c>
+      <c r="F196" s="3">
+        <v>0</v>
+      </c>
+      <c r="H196" s="2" t="s">
+        <v>775</v>
       </c>
     </row>
     <row r="197" spans="1:8">
       <c r="A197" s="2" t="s">
-        <v>706</v>
+        <v>774</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>707</v>
+        <v>765</v>
+      </c>
+      <c r="C197" s="2">
+        <v>6</v>
+      </c>
+      <c r="D197" s="6">
+        <v>0</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>710</v>
+        <v>778</v>
       </c>
       <c r="F197" s="3">
-        <v>1</v>
-      </c>
-      <c r="H197" s="9" t="s">
-        <v>754</v>
+        <v>0</v>
+      </c>
+      <c r="H197" s="2" t="s">
+        <v>775</v>
       </c>
     </row>
     <row r="198" spans="1:8">
       <c r="A198" s="2" t="s">
-        <v>708</v>
+        <v>695</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>709</v>
-      </c>
+        <v>518</v>
+      </c>
+      <c r="C198" s="3"/>
+      <c r="D198" s="6"/>
       <c r="E198" s="1" t="s">
-        <v>711</v>
+        <v>660</v>
       </c>
       <c r="F198" s="3">
         <v>1</v>
       </c>
-      <c r="H198" s="9" t="s">
-        <v>753</v>
+      <c r="G198" s="2" t="s">
+        <v>661</v>
+      </c>
+      <c r="H198" t="s">
+        <v>659</v>
       </c>
     </row>
     <row r="199" spans="1:8">
-      <c r="A199" s="2" t="s">
-        <v>715</v>
+      <c r="A199" t="s">
+        <v>421</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>716</v>
-      </c>
-      <c r="C199" s="2">
+        <v>202</v>
+      </c>
+      <c r="C199" s="3">
         <v>6</v>
       </c>
-      <c r="D199" s="6">
+      <c r="D199" s="4">
         <v>0</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>717</v>
+        <v>203</v>
       </c>
       <c r="F199" s="3">
         <v>0</v>
       </c>
-      <c r="H199" s="7" t="s">
-        <v>755</v>
+      <c r="G199" s="1"/>
+      <c r="H199" s="1" t="s">
+        <v>619</v>
       </c>
     </row>
     <row r="200" spans="1:8">
-      <c r="A200" s="2" t="s">
-        <v>722</v>
+      <c r="A200" t="s">
+        <v>422</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>719</v>
-      </c>
-      <c r="C200" s="2">
+        <v>200</v>
+      </c>
+      <c r="C200" s="3">
+        <v>6</v>
+      </c>
+      <c r="D200" s="4">
+        <v>0</v>
+      </c>
+      <c r="E200" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="F200" s="3">
+        <v>0</v>
+      </c>
+      <c r="G200" s="1"/>
+      <c r="H200" s="1" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="201" spans="1:8">
+      <c r="A201" t="s">
+        <v>423</v>
+      </c>
+      <c r="B201" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C201" s="3">
+        <v>6</v>
+      </c>
+      <c r="D201" s="4">
+        <v>0</v>
+      </c>
+      <c r="E201" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="F201" s="3">
+        <v>0</v>
+      </c>
+      <c r="G201" s="1"/>
+      <c r="H201" s="1" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="202" spans="1:8">
+      <c r="A202" t="s">
+        <v>424</v>
+      </c>
+      <c r="B202" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="C202" s="3">
         <v>7</v>
       </c>
-      <c r="D200" s="6">
-        <v>0.95833333333333337</v>
-      </c>
-      <c r="E200" s="1" t="s">
-        <v>720</v>
-      </c>
-      <c r="F200" s="3">
-        <v>0</v>
-      </c>
-      <c r="H200" s="7" t="s">
-        <v>721</v>
-      </c>
-    </row>
-    <row r="201" spans="1:8">
-      <c r="A201" s="2" t="s">
-        <v>723</v>
-      </c>
-      <c r="B201" s="1" t="s">
-        <v>724</v>
-      </c>
-      <c r="E201" s="1" t="s">
-        <v>752</v>
-      </c>
-      <c r="F201" s="3">
-        <v>1</v>
-      </c>
-      <c r="H201" s="7" t="s">
-        <v>773</v>
-      </c>
-    </row>
-    <row r="202" spans="1:8">
-      <c r="A202" s="2" t="s">
-        <v>725</v>
-      </c>
-      <c r="B202" s="1" t="s">
-        <v>726</v>
+      <c r="D202" s="4">
+        <v>0.97916666666666663</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>756</v>
+        <v>643</v>
       </c>
       <c r="F202" s="3">
-        <v>1</v>
-      </c>
-      <c r="H202" s="7" t="s">
-        <v>773</v>
+        <v>0</v>
+      </c>
+      <c r="G202" s="1"/>
+      <c r="H202" s="1" t="s">
+        <v>620</v>
       </c>
     </row>
     <row r="203" spans="1:8">
       <c r="A203" s="2" t="s">
-        <v>727</v>
+        <v>463</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>728</v>
+        <v>64</v>
+      </c>
+      <c r="C203" s="3">
+        <v>6</v>
+      </c>
+      <c r="D203" s="4">
+        <v>0</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>757</v>
+        <v>642</v>
       </c>
       <c r="F203" s="3">
-        <v>1</v>
-      </c>
-      <c r="H203" s="7" t="s">
-        <v>773</v>
+        <v>0</v>
+      </c>
+      <c r="G203" s="1"/>
+      <c r="H203" s="2" t="s">
+        <v>621</v>
       </c>
     </row>
     <row r="204" spans="1:8">
       <c r="A204" s="2" t="s">
-        <v>729</v>
+        <v>464</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>730</v>
+        <v>65</v>
+      </c>
+      <c r="C204" s="3">
+        <v>13</v>
+      </c>
+      <c r="D204" s="4">
+        <v>0</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>758</v>
+        <v>66</v>
       </c>
       <c r="F204" s="3">
-        <v>1</v>
-      </c>
-      <c r="H204" s="7" t="s">
-        <v>773</v>
+        <v>0</v>
+      </c>
+      <c r="G204" s="1"/>
+      <c r="H204" s="2" t="s">
+        <v>622</v>
       </c>
     </row>
     <row r="205" spans="1:8">
       <c r="A205" s="2" t="s">
-        <v>733</v>
+        <v>465</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>731</v>
+        <v>69</v>
+      </c>
+      <c r="C205" s="3">
+        <v>6</v>
+      </c>
+      <c r="D205" s="4">
+        <v>0</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>759</v>
+        <v>70</v>
       </c>
       <c r="F205" s="3">
-        <v>1</v>
-      </c>
-      <c r="H205" s="7" t="s">
-        <v>773</v>
+        <v>0</v>
+      </c>
+      <c r="G205" s="1"/>
+      <c r="H205" s="2" t="s">
+        <v>623</v>
       </c>
     </row>
     <row r="206" spans="1:8">
       <c r="A206" s="2" t="s">
-        <v>732</v>
+        <v>466</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>734</v>
+        <v>67</v>
+      </c>
+      <c r="C206" s="3">
+        <v>6</v>
+      </c>
+      <c r="D206" s="4">
+        <v>0</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>760</v>
+        <v>68</v>
       </c>
       <c r="F206" s="3">
-        <v>1</v>
-      </c>
-      <c r="H206" s="7" t="s">
-        <v>773</v>
+        <v>0</v>
+      </c>
+      <c r="G206" s="1"/>
+      <c r="H206" s="2" t="s">
+        <v>624</v>
       </c>
     </row>
     <row r="207" spans="1:8">
       <c r="A207" s="2" t="s">
-        <v>735</v>
+        <v>467</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>736</v>
+        <v>71</v>
+      </c>
+      <c r="C207" s="3">
+        <v>6</v>
+      </c>
+      <c r="D207" s="4">
+        <v>0</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>761</v>
+        <v>72</v>
       </c>
       <c r="F207" s="3">
-        <v>1</v>
-      </c>
-      <c r="H207" s="7" t="s">
-        <v>773</v>
+        <v>0</v>
+      </c>
+      <c r="G207" s="1"/>
+      <c r="H207" s="2" t="s">
+        <v>625</v>
       </c>
     </row>
     <row r="208" spans="1:8">
       <c r="A208" s="2" t="s">
-        <v>737</v>
+        <v>468</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>738</v>
+        <v>73</v>
+      </c>
+      <c r="C208" s="3">
+        <v>6</v>
+      </c>
+      <c r="D208" s="4">
+        <v>0</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>762</v>
+        <v>74</v>
       </c>
       <c r="F208" s="3">
-        <v>1</v>
-      </c>
-      <c r="H208" s="7" t="s">
-        <v>773</v>
+        <v>0</v>
+      </c>
+      <c r="G208" s="1"/>
+      <c r="H208" s="2" t="s">
+        <v>626</v>
       </c>
     </row>
     <row r="209" spans="1:8">
       <c r="A209" s="2" t="s">
-        <v>739</v>
+        <v>469</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>740</v>
+        <v>94</v>
+      </c>
+      <c r="C209" s="3">
+        <v>7</v>
+      </c>
+      <c r="D209" s="4">
+        <v>0</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>763</v>
+        <v>95</v>
       </c>
       <c r="F209" s="3">
-        <v>1</v>
-      </c>
-      <c r="H209" s="7" t="s">
-        <v>773</v>
+        <v>0</v>
+      </c>
+      <c r="G209" s="1"/>
+      <c r="H209" t="s">
+        <v>635</v>
       </c>
     </row>
     <row r="210" spans="1:8">
       <c r="A210" s="2" t="s">
-        <v>741</v>
+        <v>471</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>742</v>
+        <v>97</v>
+      </c>
+      <c r="C210" s="3">
+        <v>7</v>
+      </c>
+      <c r="D210" s="4">
+        <v>0</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>764</v>
+        <v>98</v>
       </c>
       <c r="F210" s="3">
-        <v>1</v>
-      </c>
-      <c r="H210" s="7" t="s">
-        <v>773</v>
+        <v>0</v>
+      </c>
+      <c r="G210" s="1"/>
+      <c r="H210" t="s">
+        <v>635</v>
       </c>
     </row>
     <row r="211" spans="1:8">
       <c r="A211" s="2" t="s">
-        <v>743</v>
+        <v>472</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>744</v>
+        <v>88</v>
+      </c>
+      <c r="C211" s="3">
+        <v>7</v>
+      </c>
+      <c r="D211" s="4">
+        <v>0</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>765</v>
+        <v>89</v>
       </c>
       <c r="F211" s="3">
-        <v>1</v>
-      </c>
-      <c r="H211" s="7" t="s">
-        <v>773</v>
+        <v>0</v>
+      </c>
+      <c r="G211" s="1"/>
+      <c r="H211" s="1" t="s">
+        <v>635</v>
       </c>
     </row>
     <row r="212" spans="1:8">
       <c r="A212" s="2" t="s">
-        <v>745</v>
+        <v>473</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>746</v>
+        <v>90</v>
+      </c>
+      <c r="C212" s="3">
+        <v>7</v>
+      </c>
+      <c r="D212" s="4">
+        <v>0</v>
       </c>
       <c r="E212" s="1" t="s">
-        <v>766</v>
+        <v>91</v>
       </c>
       <c r="F212" s="3">
-        <v>1</v>
-      </c>
-      <c r="H212" s="7" t="s">
-        <v>773</v>
+        <v>0</v>
+      </c>
+      <c r="G212" s="1"/>
+      <c r="H212" s="1" t="s">
+        <v>635</v>
       </c>
     </row>
     <row r="213" spans="1:8">
       <c r="A213" s="2" t="s">
-        <v>747</v>
+        <v>474</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>718</v>
+        <v>104</v>
+      </c>
+      <c r="C213" s="3">
+        <v>7</v>
+      </c>
+      <c r="D213" s="4">
+        <v>0</v>
       </c>
       <c r="E213" s="1" t="s">
-        <v>767</v>
+        <v>105</v>
       </c>
       <c r="F213" s="3">
-        <v>1</v>
-      </c>
-      <c r="H213" s="7" t="s">
-        <v>773</v>
+        <v>0</v>
+      </c>
+      <c r="G213" s="1"/>
+      <c r="H213" s="1" t="s">
+        <v>635</v>
       </c>
     </row>
     <row r="214" spans="1:8">
       <c r="A214" s="2" t="s">
-        <v>748</v>
+        <v>475</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>749</v>
+        <v>112</v>
+      </c>
+      <c r="C214" s="3">
+        <v>7</v>
+      </c>
+      <c r="D214" s="4">
+        <v>0</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>768</v>
+        <v>113</v>
       </c>
       <c r="F214" s="3">
-        <v>1</v>
-      </c>
-      <c r="H214" s="7" t="s">
-        <v>773</v>
+        <v>0</v>
+      </c>
+      <c r="G214" s="1"/>
+      <c r="H214" s="1" t="s">
+        <v>635</v>
       </c>
     </row>
     <row r="215" spans="1:8">
       <c r="A215" s="2" t="s">
-        <v>750</v>
+        <v>476</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>751</v>
+        <v>106</v>
+      </c>
+      <c r="C215" s="3">
+        <v>7</v>
+      </c>
+      <c r="D215" s="4">
+        <v>0</v>
       </c>
       <c r="E215" s="1" t="s">
-        <v>769</v>
+        <v>107</v>
       </c>
       <c r="F215" s="3">
-        <v>1</v>
-      </c>
-      <c r="H215" s="7" t="s">
-        <v>773</v>
+        <v>0</v>
+      </c>
+      <c r="G215" s="1"/>
+      <c r="H215" s="1" t="s">
+        <v>635</v>
       </c>
     </row>
     <row r="216" spans="1:8">
       <c r="A216" s="2" t="s">
-        <v>779</v>
+        <v>477</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>770</v>
-      </c>
-      <c r="C216" s="2">
-        <v>6</v>
-      </c>
-      <c r="D216" s="6">
-        <v>0</v>
-      </c>
-      <c r="E216" s="10" t="s">
-        <v>783</v>
+        <v>93</v>
+      </c>
+      <c r="C216" s="3">
+        <v>7</v>
+      </c>
+      <c r="D216" s="4">
+        <v>0</v>
+      </c>
+      <c r="E216" s="1" t="s">
+        <v>470</v>
       </c>
       <c r="F216" s="3">
         <v>0</v>
       </c>
-      <c r="H216" s="2" t="s">
-        <v>782</v>
+      <c r="G216" s="1"/>
+      <c r="H216" s="8" t="s">
+        <v>635</v>
       </c>
     </row>
     <row r="217" spans="1:8">
       <c r="A217" s="2" t="s">
-        <v>780</v>
+        <v>478</v>
       </c>
       <c r="B217" s="1" t="s">
-        <v>771</v>
-      </c>
-      <c r="C217" s="2">
+        <v>110</v>
+      </c>
+      <c r="C217" s="3">
+        <v>7</v>
+      </c>
+      <c r="D217" s="4">
+        <v>0</v>
+      </c>
+      <c r="E217" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="F217" s="3">
+        <v>0</v>
+      </c>
+      <c r="G217" s="1"/>
+      <c r="H217" s="1" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="218" spans="1:8">
+      <c r="A218" t="s">
+        <v>425</v>
+      </c>
+      <c r="B218" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="C218" s="3">
+        <v>13</v>
+      </c>
+      <c r="D218" s="5">
+        <v>0</v>
+      </c>
+      <c r="E218" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="F218" s="3">
+        <v>0</v>
+      </c>
+      <c r="G218" s="1"/>
+      <c r="H218" s="1" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="219" spans="1:8">
+      <c r="A219" t="s">
+        <v>507</v>
+      </c>
+      <c r="B219" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="C219" s="3">
         <v>6</v>
       </c>
-      <c r="D217" s="6">
-        <v>0</v>
-      </c>
-      <c r="E217" s="1" t="s">
-        <v>784</v>
-      </c>
-      <c r="F217" s="3">
-        <v>0</v>
-      </c>
-      <c r="H217" s="2" t="s">
-        <v>782</v>
-      </c>
-    </row>
-    <row r="218" spans="1:8">
-      <c r="A218" s="2" t="s">
-        <v>781</v>
-      </c>
-      <c r="B218" s="1" t="s">
-        <v>772</v>
-      </c>
-      <c r="C218" s="2">
+      <c r="D219" s="4">
+        <v>0</v>
+      </c>
+      <c r="E219" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="F219" s="3">
+        <v>0</v>
+      </c>
+      <c r="G219" s="1"/>
+      <c r="H219" s="1" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="220" spans="1:8">
+      <c r="A220" t="s">
+        <v>508</v>
+      </c>
+      <c r="B220" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="C220" s="3">
         <v>6</v>
       </c>
-      <c r="D218" s="6">
-        <v>0</v>
-      </c>
-      <c r="E218" s="1" t="s">
-        <v>785</v>
-      </c>
-      <c r="F218" s="3">
-        <v>0</v>
-      </c>
-      <c r="H218" s="2" t="s">
-        <v>782</v>
-      </c>
-    </row>
-    <row r="219" spans="1:8">
-      <c r="A219" s="2" t="s">
-        <v>792</v>
-      </c>
-      <c r="B219" s="1" t="s">
-        <v>793</v>
-      </c>
-      <c r="E219" s="1" t="s">
-        <v>794</v>
-      </c>
-      <c r="F219" s="3">
+      <c r="D220" s="4">
+        <v>0</v>
+      </c>
+      <c r="E220" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="F220" s="3">
+        <v>0</v>
+      </c>
+      <c r="G220" s="1"/>
+      <c r="H220" s="1" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="221" spans="1:8">
+      <c r="A221" t="s">
+        <v>511</v>
+      </c>
+      <c r="B221" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="C221" s="3">
+        <v>6</v>
+      </c>
+      <c r="D221" s="4">
+        <v>0</v>
+      </c>
+      <c r="E221" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="F221" s="3">
+        <v>0</v>
+      </c>
+      <c r="G221" s="1"/>
+      <c r="H221" s="1" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="222" spans="1:8">
+      <c r="A222" t="s">
+        <v>510</v>
+      </c>
+      <c r="B222" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="C222" s="3">
+        <v>6</v>
+      </c>
+      <c r="D222" s="4">
+        <v>0</v>
+      </c>
+      <c r="E222" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="F222" s="3">
+        <v>0</v>
+      </c>
+      <c r="G222" s="1"/>
+      <c r="H222" s="1" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="223" spans="1:8">
+      <c r="A223" t="s">
+        <v>509</v>
+      </c>
+      <c r="B223" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="C223" s="3">
+        <v>6</v>
+      </c>
+      <c r="D223" s="4">
+        <v>0</v>
+      </c>
+      <c r="E223" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="F223" s="3">
+        <v>0</v>
+      </c>
+      <c r="G223" s="1"/>
+      <c r="H223" s="1" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="224" spans="1:8">
+      <c r="A224" t="s">
+        <v>426</v>
+      </c>
+      <c r="B224" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="C224" s="1"/>
+      <c r="D224" s="1"/>
+      <c r="E224" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="F224" s="1">
         <v>1</v>
       </c>
-      <c r="H219" s="2" t="s">
-        <v>795</v>
-      </c>
-    </row>
-    <row r="220" spans="1:8">
-      <c r="A220" s="2" t="s">
-        <v>796</v>
-      </c>
-      <c r="B220" s="1" t="s">
-        <v>797</v>
-      </c>
-      <c r="E220" s="1" t="s">
-        <v>798</v>
-      </c>
-      <c r="F220" s="3">
-        <v>1</v>
-      </c>
-      <c r="H220" s="7" t="s">
-        <v>806</v>
-      </c>
-    </row>
-    <row r="221" spans="1:8">
-      <c r="A221" s="2" t="s">
-        <v>800</v>
-      </c>
-      <c r="B221" s="1" t="s">
-        <v>801</v>
-      </c>
-      <c r="E221" s="1" t="s">
-        <v>802</v>
-      </c>
-      <c r="F221" s="3">
-        <v>1</v>
-      </c>
-      <c r="H221" s="2" t="s">
-        <v>799</v>
-      </c>
-    </row>
-    <row r="222" spans="1:8">
-      <c r="A222" s="2" t="s">
-        <v>803</v>
-      </c>
-      <c r="B222" s="1" t="s">
-        <v>804</v>
-      </c>
-      <c r="E222" s="1" t="s">
-        <v>807</v>
-      </c>
-      <c r="F222" s="3">
-        <v>1</v>
-      </c>
-      <c r="H222" s="2" t="s">
-        <v>805</v>
-      </c>
-    </row>
-    <row r="223" spans="1:8">
-      <c r="A223" s="2" t="s">
-        <v>809</v>
-      </c>
-      <c r="B223" s="1" t="s">
-        <v>810</v>
-      </c>
-      <c r="E223" s="1" t="s">
-        <v>811</v>
-      </c>
-      <c r="F223" s="3">
-        <v>1</v>
-      </c>
-      <c r="H223" s="2" t="s">
-        <v>808</v>
-      </c>
-    </row>
-    <row r="224" spans="1:8">
-      <c r="A224" s="2" t="s">
-        <v>813</v>
-      </c>
-      <c r="B224" s="1" t="s">
-        <v>814</v>
-      </c>
-      <c r="E224" s="1" t="s">
-        <v>815</v>
-      </c>
-      <c r="F224" s="3">
-        <v>1</v>
-      </c>
-      <c r="H224" s="2" t="s">
-        <v>812</v>
+      <c r="G224" s="1"/>
+      <c r="H224" s="1" t="s">
+        <v>629</v>
       </c>
     </row>
     <row r="225" spans="1:8">
@@ -8408,8 +8421,8 @@
       <c r="F225" s="3">
         <v>1</v>
       </c>
-      <c r="H225" s="2" t="s">
-        <v>816</v>
+      <c r="H225" s="7" t="s">
+        <v>820</v>
       </c>
     </row>
     <row r="226" spans="1:8">
@@ -8417,40 +8430,60 @@
         <v>821</v>
       </c>
       <c r="B226" s="1" t="s">
+        <v>822</v>
+      </c>
+      <c r="E226" s="1" t="s">
+        <v>824</v>
+      </c>
+      <c r="F226" s="3">
+        <v>1</v>
+      </c>
+      <c r="H226" s="7" t="s">
         <v>823</v>
       </c>
-      <c r="C226" s="2">
-        <v>20</v>
-      </c>
-      <c r="D226" s="6">
-        <v>0</v>
-      </c>
-      <c r="E226" s="1" t="s">
-        <v>822</v>
-      </c>
-      <c r="F226" s="2">
-        <v>0</v>
-      </c>
-      <c r="H226" s="2" t="s">
-        <v>820</v>
+    </row>
+    <row r="227" spans="1:8">
+      <c r="A227" s="2" t="s">
+        <v>825</v>
+      </c>
+      <c r="B227" s="1" t="s">
+        <v>826</v>
+      </c>
+      <c r="C227" s="2">
+        <v>30</v>
+      </c>
+      <c r="D227" s="6">
+        <v>0</v>
+      </c>
+      <c r="E227" s="1" t="s">
+        <v>827</v>
+      </c>
+      <c r="F227" s="3">
+        <v>0</v>
+      </c>
+      <c r="H227" s="7" t="s">
+        <v>828</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H196">
-    <sortCondition ref="B2:B196"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H224">
+    <sortCondition ref="B2:B224"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="H188" r:id="rId1" xr:uid="{08510EB6-59FE-461F-9934-59900452DB70}"/>
-    <hyperlink ref="H200" r:id="rId2" xr:uid="{092C464B-EEF0-45C5-9E7F-9E5BB1389ECD}"/>
-    <hyperlink ref="H199" r:id="rId3" xr:uid="{D8D98BE9-F998-4931-BC78-1FA8DBB2DF8D}"/>
-    <hyperlink ref="H198" r:id="rId4" xr:uid="{3BEBF5F8-81B1-4909-98FA-8DDD635C8EA6}"/>
-    <hyperlink ref="H197" r:id="rId5" xr:uid="{65D202DC-0DAE-445A-B96C-C36AAC898769}"/>
-    <hyperlink ref="H201" r:id="rId6" xr:uid="{25A9BA66-0BC2-4AD9-A0BE-F4C36298AC2D}"/>
-    <hyperlink ref="H202:H215" r:id="rId7" display="http://www.murderparker.com/" xr:uid="{E958893D-4F52-4648-BDD7-4971EF621EF9}"/>
-    <hyperlink ref="H220" r:id="rId8" xr:uid="{4B96B214-31AC-4DCE-B6F6-D54C0FEB4666}"/>
+    <hyperlink ref="H216" r:id="rId1" xr:uid="{08510EB6-59FE-461F-9934-59900452DB70}"/>
+    <hyperlink ref="H159" r:id="rId2" xr:uid="{092C464B-EEF0-45C5-9E7F-9E5BB1389ECD}"/>
+    <hyperlink ref="H191" r:id="rId3" xr:uid="{D8D98BE9-F998-4931-BC78-1FA8DBB2DF8D}"/>
+    <hyperlink ref="H37" r:id="rId4" xr:uid="{3BEBF5F8-81B1-4909-98FA-8DDD635C8EA6}"/>
+    <hyperlink ref="H36" r:id="rId5" xr:uid="{65D202DC-0DAE-445A-B96C-C36AAC898769}"/>
+    <hyperlink ref="H104" r:id="rId6" xr:uid="{25A9BA66-0BC2-4AD9-A0BE-F4C36298AC2D}"/>
+    <hyperlink ref="H200:H213" r:id="rId7" display="http://www.murderparker.com/" xr:uid="{E958893D-4F52-4648-BDD7-4971EF621EF9}"/>
+    <hyperlink ref="H29" r:id="rId8" xr:uid="{4B96B214-31AC-4DCE-B6F6-D54C0FEB4666}"/>
+    <hyperlink ref="H225" r:id="rId9" xr:uid="{7887DCFC-D844-46A5-A06B-C3E53BC46BA9}"/>
+    <hyperlink ref="H226" r:id="rId10" xr:uid="{25B31E9F-543F-4E86-89DB-207AA2179ACF}"/>
+    <hyperlink ref="H227" r:id="rId11" xr:uid="{9827A6D5-ED28-4225-87FD-B74EDF207367}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId9"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId12"/>
 </worksheet>
 </file>
--- a/stores.xlsx
+++ b/stores.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\YUMIN\Desktop\B0KT2A_RSVN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B31AB1EF-35C8-448E-B07F-E9019B7DEB75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{219D7848-3BA3-41DB-BC8E-ADAAFC21AAD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{ABFC3117-FCCB-4FF3-804A-FE19451A2004}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{ABFC3117-FCCB-4FF3-804A-FE19451A2004}"/>
   </bookViews>
   <sheets>
     <sheet name="stores" sheetId="2" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="915" uniqueCount="829">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="923" uniqueCount="837">
   <si>
     <t>룸익스케이프 WHITE</t>
   </si>
@@ -1029,10 +1029,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>THE LAST EPISODE:마지막화,카르마,KARMA,행복을드림니다,둡두의정석</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>히든스위치,AUDREY,오드리,MISSING,미씽</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2721,10 +2717,6 @@
     <t>https://www.master-key.co.kr/</t>
   </si>
   <si>
-    <t>고양학개론,캠프ING,옥순양갱,철수네 슈퍼,철수네수퍼,오메가,더 라스트 노트,MR.BANG,미스터뱅,미스터방,치로의여름방학</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>ft_str1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2940,6 +2932,44 @@
   </si>
   <si>
     <t>https://naver.me/FCrTZq6Q</t>
+  </si>
+  <si>
+    <t>파노라마 홍대삼거리점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>퍼펫플레이,puppetplay</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pm_hs</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://naver.me/xYvoyDqy</t>
+  </si>
+  <si>
+    <t>THE LAST EPISODE:마지막화,카르마,KARMA,행복을드림니다,둡두의정석,아이디어,idea</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lk_wd</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>링크월드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>우당탕바그,사하라바자,곤충커키우기,아템전,웁스리페어,뿌성뿌성,햄버거타이쿤,사막상점,귀여운곤충배틀,복불복,레이싱,성뿌시기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://naver.me/xZj2P3wt</t>
+  </si>
+  <si>
+    <t>고양학개론,캠프ING,옥순양갱,철수네 슈퍼,철수네수퍼,오메가,더 라스트 노트,MR.BANG,미스터뱅,미스터방,치로의여름방학,영원교실</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -3355,7 +3385,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D839462D-4719-40BB-8925-C1B9F93734CF}">
-  <dimension ref="A1:H227"/>
+  <dimension ref="A1:H229"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="2"/>
@@ -3370,7 +3400,7 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="2" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>11</v>
@@ -3396,10 +3426,10 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="2" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="C2" s="2">
         <v>7</v>
@@ -3408,21 +3438,21 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="E2" s="2" t="s">
+        <v>645</v>
+      </c>
+      <c r="F2" s="2">
+        <v>0</v>
+      </c>
+      <c r="H2" s="2" t="s">
         <v>646</v>
-      </c>
-      <c r="F2" s="2">
-        <v>0</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>647</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="2" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C3" s="3">
         <v>6</v>
@@ -3431,19 +3461,19 @@
         <v>0</v>
       </c>
       <c r="E3" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="F3" s="3">
         <v>0</v>
       </c>
       <c r="G3" s="1"/>
       <c r="H3" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="2" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>271</v>
@@ -3462,12 +3492,12 @@
       </c>
       <c r="G4" s="1"/>
       <c r="H4" s="1" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="2" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>140</v>
@@ -3475,19 +3505,19 @@
       <c r="C5" s="3"/>
       <c r="D5" s="4"/>
       <c r="E5" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F5" s="3">
         <v>1</v>
       </c>
       <c r="G5" s="1"/>
       <c r="H5" s="1" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="2" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>265</v>
@@ -3506,12 +3536,12 @@
       </c>
       <c r="G6" s="1"/>
       <c r="H6" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>266</v>
@@ -3523,19 +3553,19 @@
         <v>0</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="F7" s="3">
         <v>0</v>
       </c>
       <c r="G7" s="1"/>
       <c r="H7" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>136</v>
@@ -3554,12 +3584,12 @@
       </c>
       <c r="G8" s="1"/>
       <c r="H8" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="2" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>138</v>
@@ -3578,12 +3608,12 @@
       </c>
       <c r="G9" s="1"/>
       <c r="H9" s="1" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="2" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>236</v>
@@ -3602,12 +3632,12 @@
       </c>
       <c r="G10" s="1"/>
       <c r="H10" s="1" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="2" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>237</v>
@@ -3619,19 +3649,19 @@
         <v>0</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="F11" s="3">
         <v>0</v>
       </c>
       <c r="G11" s="1"/>
       <c r="H11" s="1" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="2" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>238</v>
@@ -3650,12 +3680,12 @@
       </c>
       <c r="G12" s="1"/>
       <c r="H12" s="1" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="2" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>233</v>
@@ -3674,12 +3704,12 @@
       </c>
       <c r="G13" s="1"/>
       <c r="H13" s="1" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="2" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>234</v>
@@ -3698,12 +3728,12 @@
       </c>
       <c r="G14" s="1"/>
       <c r="H14" s="1" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="2" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>215</v>
@@ -3715,19 +3745,19 @@
         <v>0</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="F15" s="3">
         <v>0</v>
       </c>
       <c r="G15" s="1"/>
       <c r="H15" s="1" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="2" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>83</v>
@@ -3746,12 +3776,12 @@
       </c>
       <c r="G16" s="1"/>
       <c r="H16" s="1" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="2" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>85</v>
@@ -3770,12 +3800,12 @@
       </c>
       <c r="G17" s="1"/>
       <c r="H17" s="1" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="2" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>87</v>
@@ -3794,12 +3824,12 @@
       </c>
       <c r="G18" s="1"/>
       <c r="H18" s="1" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="2" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>81</v>
@@ -3818,15 +3848,15 @@
       </c>
       <c r="G19" s="1"/>
       <c r="H19" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="2" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C20" s="3">
         <v>30</v>
@@ -3835,19 +3865,19 @@
         <v>0</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="F20" s="3">
         <v>0</v>
       </c>
       <c r="G20" s="1"/>
       <c r="H20" s="1" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="2" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>79</v>
@@ -3866,12 +3896,12 @@
       </c>
       <c r="G21" s="1"/>
       <c r="H21" s="1" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="2" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>77</v>
@@ -3890,15 +3920,15 @@
       </c>
       <c r="G22" s="1"/>
       <c r="H22" s="1" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="2" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C23" s="3">
         <v>6</v>
@@ -3907,21 +3937,21 @@
         <v>0</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="F23" s="3">
         <v>0</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="2" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C24" s="3">
         <v>6</v>
@@ -3930,18 +3960,18 @@
         <v>0</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="F24" s="3">
         <v>0</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>141</v>
@@ -3960,12 +3990,12 @@
       </c>
       <c r="G25" s="1"/>
       <c r="H25" s="1" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>143</v>
@@ -3984,32 +4014,32 @@
       </c>
       <c r="G26" s="1"/>
       <c r="H26" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="2" t="s">
+        <v>800</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>801</v>
+      </c>
+      <c r="E27" s="1" t="s">
         <v>802</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>803</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>804</v>
       </c>
       <c r="F27" s="3">
         <v>1</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="2" t="s">
+        <v>812</v>
+      </c>
+      <c r="B28" s="1" t="s">
         <v>814</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>816</v>
       </c>
       <c r="C28" s="2">
         <v>20</v>
@@ -4018,123 +4048,123 @@
         <v>0</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="F28" s="2">
         <v>0</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="2" t="s">
+        <v>787</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>788</v>
+      </c>
+      <c r="E29" s="1" t="s">
         <v>789</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>790</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>791</v>
       </c>
       <c r="F29" s="3">
         <v>1</v>
       </c>
       <c r="H29" s="7" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="2" t="s">
+        <v>783</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>784</v>
+      </c>
+      <c r="E30" s="1" t="s">
         <v>785</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>786</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>787</v>
       </c>
       <c r="F30" s="3">
         <v>1</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="2" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="F31" s="3">
         <v>1</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="2" t="s">
+        <v>808</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>809</v>
+      </c>
+      <c r="E32" s="1" t="s">
         <v>810</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>811</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>812</v>
       </c>
       <c r="F32" s="3">
         <v>1</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="2" t="s">
+        <v>804</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>805</v>
+      </c>
+      <c r="E33" s="1" t="s">
         <v>806</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>807</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>808</v>
       </c>
       <c r="F33" s="3">
         <v>1</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="2" t="s">
+        <v>791</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>792</v>
+      </c>
+      <c r="E34" s="1" t="s">
         <v>793</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>794</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>795</v>
       </c>
       <c r="F34" s="3">
         <v>1</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="2" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C35" s="3">
         <v>6</v>
@@ -4150,52 +4180,52 @@
       </c>
       <c r="G35" s="1"/>
       <c r="H35" s="2" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="36" spans="1:8">
       <c r="A36" s="2" t="s">
+        <v>698</v>
+      </c>
+      <c r="B36" s="1" t="s">
         <v>699</v>
       </c>
-      <c r="B36" s="1" t="s">
-        <v>700</v>
-      </c>
       <c r="E36" s="1" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="F36" s="3">
         <v>1</v>
       </c>
       <c r="H36" s="9" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
     </row>
     <row r="37" spans="1:8">
       <c r="A37" s="2" t="s">
+        <v>700</v>
+      </c>
+      <c r="B37" s="1" t="s">
         <v>701</v>
       </c>
-      <c r="B37" s="1" t="s">
-        <v>702</v>
-      </c>
       <c r="E37" s="1" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="F37" s="3">
         <v>1</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
     </row>
     <row r="38" spans="1:8">
       <c r="A38" s="2" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B38" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="E38" s="1" t="s">
         <v>461</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>462</v>
       </c>
       <c r="F38" s="3">
         <v>1</v>
@@ -4203,7 +4233,7 @@
     </row>
     <row r="39" spans="1:8">
       <c r="A39" s="2" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>144</v>
@@ -4222,12 +4252,12 @@
       </c>
       <c r="G39" s="1"/>
       <c r="H39" s="1" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
     </row>
     <row r="40" spans="1:8">
       <c r="A40" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>156</v>
@@ -4242,12 +4272,12 @@
       </c>
       <c r="G40" s="1"/>
       <c r="H40" s="1" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
     </row>
     <row r="41" spans="1:8">
       <c r="A41" s="2" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>158</v>
@@ -4266,12 +4296,12 @@
       </c>
       <c r="G41" s="1"/>
       <c r="H41" s="1" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
     </row>
     <row r="42" spans="1:8">
       <c r="A42" s="2" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>146</v>
@@ -4290,12 +4320,12 @@
       </c>
       <c r="G42" s="1"/>
       <c r="H42" s="1" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="43" spans="1:8">
       <c r="A43" s="2" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>148</v>
@@ -4314,12 +4344,12 @@
       </c>
       <c r="G43" s="1"/>
       <c r="H43" s="1" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="44" spans="1:8">
       <c r="A44" s="2" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>154</v>
@@ -4334,12 +4364,12 @@
       </c>
       <c r="G44" s="1"/>
       <c r="H44" s="1" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="45" spans="1:8">
       <c r="A45" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>152</v>
@@ -4354,12 +4384,12 @@
       </c>
       <c r="G45" s="1"/>
       <c r="H45" s="1" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="46" spans="1:8">
       <c r="A46" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>150</v>
@@ -4378,12 +4408,12 @@
       </c>
       <c r="G46" s="1"/>
       <c r="H46" s="1" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="47" spans="1:8">
       <c r="A47" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>8</v>
@@ -4395,19 +4425,19 @@
         <v>0</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="F47" s="3">
         <v>0</v>
       </c>
       <c r="G47" s="1"/>
       <c r="H47" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="48" spans="1:8">
       <c r="A48" s="2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>249</v>
@@ -4426,12 +4456,12 @@
       </c>
       <c r="G48" s="1"/>
       <c r="H48" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="49" spans="1:8">
       <c r="A49" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>251</v>
@@ -4450,12 +4480,12 @@
       </c>
       <c r="G49" s="1"/>
       <c r="H49" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="50" spans="1:8">
       <c r="A50" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>253</v>
@@ -4474,12 +4504,12 @@
       </c>
       <c r="G50" s="1"/>
       <c r="H50" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="51" spans="1:8">
       <c r="A51" s="2" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>128</v>
@@ -4498,12 +4528,12 @@
       </c>
       <c r="G51" s="1"/>
       <c r="H51" s="1" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="52" spans="1:8">
       <c r="A52" s="2" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>298</v>
@@ -4522,12 +4552,12 @@
       </c>
       <c r="G52" s="1"/>
       <c r="H52" s="1" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="53" spans="1:8">
       <c r="A53" s="2" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>255</v>
@@ -4544,18 +4574,18 @@
         <v>257</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="54" spans="1:8">
       <c r="A54" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="F54" s="2">
         <v>1</v>
@@ -4563,46 +4593,46 @@
     </row>
     <row r="55" spans="1:8">
       <c r="A55" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="F55" s="3">
         <v>1</v>
       </c>
       <c r="H55" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
     </row>
     <row r="56" spans="1:8">
       <c r="A56" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="C56" s="3"/>
       <c r="D56" s="6"/>
       <c r="E56" s="1" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="F56" s="3">
         <v>1</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="H56" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
     </row>
     <row r="57" spans="1:8">
       <c r="A57" s="2" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>130</v>
@@ -4621,12 +4651,12 @@
       </c>
       <c r="G57" s="1"/>
       <c r="H57" s="1" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="58" spans="1:8">
       <c r="A58" s="2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>307</v>
@@ -4645,12 +4675,12 @@
       </c>
       <c r="G58" s="1"/>
       <c r="H58" s="1" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
     </row>
     <row r="59" spans="1:8">
       <c r="A59" s="2" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>306</v>
@@ -4665,12 +4695,12 @@
       </c>
       <c r="G59" s="1"/>
       <c r="H59" s="1" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
     </row>
     <row r="60" spans="1:8">
       <c r="A60" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>296</v>
@@ -4689,12 +4719,12 @@
       </c>
       <c r="G60" s="1"/>
       <c r="H60" s="1" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
     </row>
     <row r="61" spans="1:8">
       <c r="A61" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>2</v>
@@ -4713,12 +4743,12 @@
       </c>
       <c r="G61" s="1"/>
       <c r="H61" s="2" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="62" spans="1:8">
       <c r="A62" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>6</v>
@@ -4737,12 +4767,12 @@
       </c>
       <c r="G62" s="1"/>
       <c r="H62" s="2" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
     </row>
     <row r="63" spans="1:8">
       <c r="A63" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>4</v>
@@ -4761,12 +4791,12 @@
       </c>
       <c r="G63" s="1"/>
       <c r="H63" s="2" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
     </row>
     <row r="64" spans="1:8">
       <c r="A64" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>0</v>
@@ -4785,12 +4815,12 @@
       </c>
       <c r="G64" s="1"/>
       <c r="H64" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="65" spans="1:8">
       <c r="A65" s="2" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>264</v>
@@ -4808,12 +4838,12 @@
         <v>0</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="66" spans="1:8">
       <c r="A66" s="2" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>184</v>
@@ -4831,12 +4861,12 @@
         <v>0</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
     </row>
     <row r="67" spans="1:8">
       <c r="A67" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>267</v>
@@ -4854,12 +4884,12 @@
         <v>0</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
     </row>
     <row r="68" spans="1:8">
       <c r="A68" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>182</v>
@@ -4877,12 +4907,12 @@
         <v>0</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="69" spans="1:8">
       <c r="A69" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>188</v>
@@ -4900,12 +4930,12 @@
         <v>0</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="70" spans="1:8">
       <c r="A70" s="2" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>186</v>
@@ -4923,12 +4953,12 @@
         <v>0</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
     </row>
     <row r="71" spans="1:8">
       <c r="A71" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>174</v>
@@ -4946,12 +4976,12 @@
         <v>0</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="72" spans="1:8">
       <c r="A72" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>176</v>
@@ -4969,12 +4999,12 @@
         <v>0</v>
       </c>
       <c r="H72" s="1" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
     </row>
     <row r="73" spans="1:8">
       <c r="A73" s="2" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>160</v>
@@ -4992,12 +5022,12 @@
         <v>0</v>
       </c>
       <c r="H73" s="1" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
     </row>
     <row r="74" spans="1:8">
       <c r="A74" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>190</v>
@@ -5015,12 +5045,12 @@
         <v>0</v>
       </c>
       <c r="H74" s="1" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
     <row r="75" spans="1:8">
       <c r="A75" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>178</v>
@@ -5038,12 +5068,12 @@
         <v>0</v>
       </c>
       <c r="H75" s="1" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="76" spans="1:8">
       <c r="A76" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>180</v>
@@ -5061,12 +5091,12 @@
         <v>0</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="77" spans="1:8">
       <c r="A77" s="2" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>196</v>
@@ -5084,12 +5114,12 @@
         <v>0</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="78" spans="1:8">
       <c r="A78" s="2" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>194</v>
@@ -5107,12 +5137,12 @@
         <v>0</v>
       </c>
       <c r="H78" s="1" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
     </row>
     <row r="79" spans="1:8">
       <c r="A79" s="2" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>172</v>
@@ -5130,12 +5160,12 @@
         <v>0</v>
       </c>
       <c r="H79" s="1" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
     </row>
     <row r="80" spans="1:8">
       <c r="A80" s="2" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>170</v>
@@ -5153,12 +5183,12 @@
         <v>0</v>
       </c>
       <c r="H80" s="1" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
     </row>
     <row r="81" spans="1:8">
       <c r="A81" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>162</v>
@@ -5176,12 +5206,12 @@
         <v>0</v>
       </c>
       <c r="H81" s="1" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
     </row>
     <row r="82" spans="1:8">
       <c r="A82" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>168</v>
@@ -5199,12 +5229,12 @@
         <v>0</v>
       </c>
       <c r="H82" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="83" spans="1:8">
       <c r="A83" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>166</v>
@@ -5222,12 +5252,12 @@
         <v>0</v>
       </c>
       <c r="H83" s="1" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
     </row>
     <row r="84" spans="1:8">
       <c r="A84" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>164</v>
@@ -5245,12 +5275,12 @@
         <v>0</v>
       </c>
       <c r="H84" s="1" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
     </row>
     <row r="85" spans="1:8">
       <c r="A85" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>192</v>
@@ -5268,12 +5298,12 @@
         <v>0</v>
       </c>
       <c r="H85" s="1" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="86" spans="1:8">
       <c r="A86" s="2" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>100</v>
@@ -5292,15 +5322,15 @@
       </c>
       <c r="G86" s="1"/>
       <c r="H86" s="1" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
     </row>
     <row r="87" spans="1:8">
       <c r="A87" s="2" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C87" s="3">
         <v>7</v>
@@ -5316,12 +5346,12 @@
       </c>
       <c r="G87" s="1"/>
       <c r="H87" s="1" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
     </row>
     <row r="88" spans="1:8">
       <c r="A88" s="2" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>108</v>
@@ -5340,12 +5370,12 @@
       </c>
       <c r="G88" s="1"/>
       <c r="H88" s="1" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
     </row>
     <row r="89" spans="1:8">
       <c r="A89" s="2" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>114</v>
@@ -5364,15 +5394,15 @@
       </c>
       <c r="G89" s="1"/>
       <c r="H89" s="1" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
     </row>
     <row r="90" spans="1:8">
       <c r="A90" s="2" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C90" s="3">
         <v>7</v>
@@ -5388,15 +5418,15 @@
       </c>
       <c r="G90" s="1"/>
       <c r="H90" s="1" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
     </row>
     <row r="91" spans="1:8">
       <c r="A91" s="2" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C91" s="3">
         <v>7</v>
@@ -5412,15 +5442,15 @@
       </c>
       <c r="G91" s="1"/>
       <c r="H91" s="1" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
     </row>
     <row r="92" spans="1:8">
       <c r="A92" s="2" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C92" s="3">
         <v>7</v>
@@ -5436,267 +5466,267 @@
       </c>
       <c r="G92" s="1"/>
       <c r="H92" s="1" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
     </row>
     <row r="93" spans="1:8">
       <c r="A93" s="2" t="s">
+        <v>740</v>
+      </c>
+      <c r="B93" s="1" t="s">
         <v>741</v>
       </c>
-      <c r="B93" s="1" t="s">
-        <v>742</v>
-      </c>
       <c r="E93" s="1" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="F93" s="3">
         <v>1</v>
       </c>
       <c r="H93" s="7" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="94" spans="1:8">
       <c r="A94" s="2" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="F94" s="3">
         <v>1</v>
       </c>
       <c r="H94" s="7" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="95" spans="1:8">
       <c r="A95" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F95" s="3">
         <v>1</v>
       </c>
       <c r="H95" s="7" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="96" spans="1:8">
       <c r="A96" s="2" t="s">
+        <v>729</v>
+      </c>
+      <c r="B96" s="1" t="s">
         <v>730</v>
       </c>
-      <c r="B96" s="1" t="s">
-        <v>731</v>
-      </c>
       <c r="E96" s="1" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="F96" s="3">
         <v>1</v>
       </c>
       <c r="H96" s="7" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="97" spans="1:8">
       <c r="A97" s="2" t="s">
+        <v>727</v>
+      </c>
+      <c r="B97" s="1" t="s">
         <v>728</v>
       </c>
-      <c r="B97" s="1" t="s">
-        <v>729</v>
-      </c>
       <c r="E97" s="1" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="F97" s="3">
         <v>1</v>
       </c>
       <c r="H97" s="7" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="98" spans="1:8">
       <c r="A98" s="2" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="F98" s="3">
         <v>1</v>
       </c>
       <c r="H98" s="7" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="99" spans="1:8">
       <c r="A99" s="2" t="s">
+        <v>733</v>
+      </c>
+      <c r="B99" s="1" t="s">
         <v>734</v>
       </c>
-      <c r="B99" s="1" t="s">
-        <v>735</v>
-      </c>
       <c r="E99" s="1" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="F99" s="3">
         <v>1</v>
       </c>
       <c r="H99" s="7" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="100" spans="1:8">
       <c r="A100" s="2" t="s">
+        <v>737</v>
+      </c>
+      <c r="B100" s="1" t="s">
         <v>738</v>
       </c>
-      <c r="B100" s="1" t="s">
-        <v>739</v>
-      </c>
       <c r="E100" s="1" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="F100" s="3">
         <v>1</v>
       </c>
       <c r="H100" s="7" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="101" spans="1:8">
       <c r="A101" s="2" t="s">
+        <v>719</v>
+      </c>
+      <c r="B101" s="1" t="s">
         <v>720</v>
       </c>
-      <c r="B101" s="1" t="s">
-        <v>721</v>
-      </c>
       <c r="E101" s="1" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="F101" s="3">
         <v>1</v>
       </c>
       <c r="H101" s="7" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="102" spans="1:8">
       <c r="A102" s="2" t="s">
+        <v>742</v>
+      </c>
+      <c r="B102" s="1" t="s">
         <v>743</v>
       </c>
-      <c r="B102" s="1" t="s">
-        <v>744</v>
-      </c>
       <c r="E102" s="1" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="F102" s="3">
         <v>1</v>
       </c>
       <c r="H102" s="7" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="103" spans="1:8">
       <c r="A103" s="2" t="s">
+        <v>735</v>
+      </c>
+      <c r="B103" s="1" t="s">
         <v>736</v>
       </c>
-      <c r="B103" s="1" t="s">
-        <v>737</v>
-      </c>
       <c r="E103" s="1" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="F103" s="3">
         <v>1</v>
       </c>
       <c r="H103" s="7" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="104" spans="1:8">
       <c r="A104" s="2" t="s">
+        <v>715</v>
+      </c>
+      <c r="B104" s="1" t="s">
         <v>716</v>
       </c>
-      <c r="B104" s="1" t="s">
-        <v>717</v>
-      </c>
       <c r="E104" s="1" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="F104" s="3">
         <v>1</v>
       </c>
       <c r="H104" s="7" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="105" spans="1:8">
       <c r="A105" s="2" t="s">
+        <v>717</v>
+      </c>
+      <c r="B105" s="1" t="s">
         <v>718</v>
       </c>
-      <c r="B105" s="1" t="s">
-        <v>719</v>
-      </c>
       <c r="E105" s="1" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="F105" s="3">
         <v>1</v>
       </c>
       <c r="H105" s="7" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="106" spans="1:8">
       <c r="A106" s="2" t="s">
+        <v>721</v>
+      </c>
+      <c r="B106" s="1" t="s">
         <v>722</v>
       </c>
-      <c r="B106" s="1" t="s">
-        <v>723</v>
-      </c>
       <c r="E106" s="1" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="F106" s="3">
         <v>1</v>
       </c>
       <c r="H106" s="7" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="107" spans="1:8">
       <c r="A107" s="2" t="s">
+        <v>731</v>
+      </c>
+      <c r="B107" s="1" t="s">
         <v>732</v>
       </c>
-      <c r="B107" s="1" t="s">
-        <v>733</v>
-      </c>
       <c r="E107" s="1" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="F107" s="3">
         <v>1</v>
       </c>
       <c r="H107" s="7" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="108" spans="1:8">
       <c r="A108" s="2" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B108" s="1" t="s">
         <v>247</v>
@@ -5715,15 +5745,15 @@
       </c>
       <c r="G108" s="1"/>
       <c r="H108" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
     </row>
     <row r="109" spans="1:8">
       <c r="A109" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="B109" s="1" t="s">
         <v>406</v>
-      </c>
-      <c r="B109" s="1" t="s">
-        <v>407</v>
       </c>
       <c r="C109" s="3">
         <v>7</v>
@@ -5739,15 +5769,15 @@
       </c>
       <c r="G109" s="1"/>
       <c r="H109" s="1" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
     </row>
     <row r="110" spans="1:8">
       <c r="A110" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="C110" s="3">
         <v>7</v>
@@ -5763,12 +5793,12 @@
       </c>
       <c r="G110" s="1"/>
       <c r="H110" s="1" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="111" spans="1:8">
       <c r="A111" s="2" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="B111" s="1" t="s">
         <v>302</v>
@@ -5776,19 +5806,19 @@
       <c r="C111" s="1"/>
       <c r="D111" s="5"/>
       <c r="E111" s="1" t="s">
-        <v>315</v>
+        <v>831</v>
       </c>
       <c r="F111" s="3">
         <v>1</v>
       </c>
       <c r="G111" s="1"/>
       <c r="H111" s="1" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
     </row>
     <row r="112" spans="1:8">
       <c r="A112" s="2" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B112" s="1" t="s">
         <v>241</v>
@@ -5807,12 +5837,12 @@
       </c>
       <c r="G112" s="1"/>
       <c r="H112" s="1" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
     </row>
     <row r="113" spans="1:8">
       <c r="A113" s="2" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B113" s="1" t="s">
         <v>47</v>
@@ -5831,12 +5861,12 @@
       </c>
       <c r="G113" s="1"/>
       <c r="H113" s="2" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
     <row r="114" spans="1:8">
       <c r="A114" s="2" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B114" s="1" t="s">
         <v>49</v>
@@ -5855,12 +5885,12 @@
       </c>
       <c r="G114" s="1"/>
       <c r="H114" s="2" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
     <row r="115" spans="1:8">
       <c r="A115" s="2" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B115" s="1" t="s">
         <v>274</v>
@@ -5879,12 +5909,12 @@
       </c>
       <c r="G115" s="1"/>
       <c r="H115" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
     </row>
     <row r="116" spans="1:8">
       <c r="A116" s="2" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B116" s="1" t="s">
         <v>43</v>
@@ -5903,12 +5933,12 @@
       </c>
       <c r="G116" s="1"/>
       <c r="H116" s="2" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
     <row r="117" spans="1:8">
       <c r="A117" s="2" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B117" s="1" t="s">
         <v>51</v>
@@ -5927,12 +5957,12 @@
       </c>
       <c r="G117" s="1"/>
       <c r="H117" s="2" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
     <row r="118" spans="1:8">
       <c r="A118" s="2" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B118" s="1" t="s">
         <v>53</v>
@@ -5951,12 +5981,12 @@
       </c>
       <c r="G118" s="1"/>
       <c r="H118" s="2" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
     <row r="119" spans="1:8">
       <c r="A119" s="2" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B119" s="1" t="s">
         <v>273</v>
@@ -5975,12 +6005,12 @@
       </c>
       <c r="G119" s="1"/>
       <c r="H119" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
     </row>
     <row r="120" spans="1:8">
       <c r="A120" s="2" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B120" s="1" t="s">
         <v>55</v>
@@ -5999,15 +6029,15 @@
       </c>
       <c r="G120" s="1"/>
       <c r="H120" s="2" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
     <row r="121" spans="1:8">
       <c r="A121" s="2" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="C121" s="3">
         <v>6</v>
@@ -6016,19 +6046,19 @@
         <v>0.875</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="F121" s="3">
         <v>0</v>
       </c>
       <c r="G121" s="1"/>
       <c r="H121" s="2" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
     <row r="122" spans="1:8">
       <c r="A122" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B122" s="1" t="s">
         <v>275</v>
@@ -6047,12 +6077,12 @@
       </c>
       <c r="G122" s="1"/>
       <c r="H122" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
     </row>
     <row r="123" spans="1:8">
       <c r="A123" s="2" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B123" s="1" t="s">
         <v>41</v>
@@ -6071,12 +6101,12 @@
       </c>
       <c r="G123" s="1"/>
       <c r="H123" s="2" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
     <row r="124" spans="1:8">
       <c r="A124" s="2" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B124" s="1" t="s">
         <v>45</v>
@@ -6095,12 +6125,12 @@
       </c>
       <c r="G124" s="1"/>
       <c r="H124" s="2" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
     <row r="125" spans="1:8">
       <c r="A125" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B125" s="1" t="s">
         <v>223</v>
@@ -6119,12 +6149,12 @@
       </c>
       <c r="G125" s="1"/>
       <c r="H125" s="1" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="126" spans="1:8">
       <c r="A126" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B126" s="1" t="s">
         <v>217</v>
@@ -6143,12 +6173,12 @@
       </c>
       <c r="G126" s="1"/>
       <c r="H126" s="1" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="127" spans="1:8">
       <c r="A127" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B127" s="1" t="s">
         <v>229</v>
@@ -6167,12 +6197,12 @@
       </c>
       <c r="G127" s="1"/>
       <c r="H127" s="1" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="128" spans="1:8">
       <c r="A128" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B128" s="1" t="s">
         <v>219</v>
@@ -6191,12 +6221,12 @@
       </c>
       <c r="G128" s="1"/>
       <c r="H128" s="1" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="129" spans="1:8">
       <c r="A129" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B129" s="1" t="s">
         <v>227</v>
@@ -6215,12 +6245,12 @@
       </c>
       <c r="G129" s="1"/>
       <c r="H129" s="1" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="130" spans="1:8">
       <c r="A130" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B130" s="1" t="s">
         <v>225</v>
@@ -6239,12 +6269,12 @@
       </c>
       <c r="G130" s="1"/>
       <c r="H130" s="1" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="131" spans="1:8">
       <c r="A131" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B131" s="1" t="s">
         <v>221</v>
@@ -6263,12 +6293,12 @@
       </c>
       <c r="G131" s="1"/>
       <c r="H131" s="1" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="132" spans="1:8">
       <c r="A132" s="2" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B132" s="1" t="s">
         <v>239</v>
@@ -6287,12 +6317,12 @@
       </c>
       <c r="G132" s="1"/>
       <c r="H132" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
     </row>
     <row r="133" spans="1:8">
       <c r="A133" s="2" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B133" s="1" t="s">
         <v>269</v>
@@ -6311,12 +6341,12 @@
       </c>
       <c r="G133" s="1"/>
       <c r="H133" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="134" spans="1:8">
       <c r="A134" s="2" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B134" s="1" t="s">
         <v>198</v>
@@ -6328,85 +6358,85 @@
         <v>0</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="F134" s="3">
         <v>0</v>
       </c>
       <c r="G134" s="1"/>
       <c r="H134" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="135" spans="1:8">
       <c r="A135" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="F135" s="2">
         <v>1</v>
       </c>
       <c r="G135" s="2" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="H135" s="2" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
     </row>
     <row r="136" spans="1:8">
       <c r="A136" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="F136" s="2">
         <v>1</v>
       </c>
       <c r="G136" s="2" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="H136" s="2" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
     </row>
     <row r="137" spans="1:8">
       <c r="A137" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="F137" s="2">
         <v>1</v>
       </c>
       <c r="G137" s="2" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="H137" s="2" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
     </row>
     <row r="138" spans="1:8">
       <c r="A138" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="B138" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="E138" s="1" t="s">
         <v>514</v>
-      </c>
-      <c r="E138" s="1" t="s">
-        <v>515</v>
       </c>
       <c r="F138" s="3">
         <v>0</v>
@@ -6414,10 +6444,10 @@
     </row>
     <row r="139" spans="1:8">
       <c r="A139" s="2" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C139" s="3">
         <v>13</v>
@@ -6426,22 +6456,22 @@
         <v>0</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="F139" s="3">
         <v>0</v>
       </c>
       <c r="G139" s="1"/>
       <c r="H139" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
     </row>
     <row r="140" spans="1:8">
       <c r="A140" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C140" s="2">
         <v>13</v>
@@ -6450,15 +6480,15 @@
         <v>0</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
     </row>
     <row r="141" spans="1:8">
       <c r="A141" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="C141" s="2">
         <v>13</v>
@@ -6467,15 +6497,15 @@
         <v>0</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
     </row>
     <row r="142" spans="1:8">
       <c r="A142" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C142" s="3">
         <v>7</v>
@@ -6491,12 +6521,12 @@
       </c>
       <c r="G142" s="1"/>
       <c r="H142" s="1" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
     </row>
     <row r="143" spans="1:8">
       <c r="A143" s="2" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B143" s="1" t="s">
         <v>117</v>
@@ -6515,12 +6545,12 @@
       </c>
       <c r="G143" s="1"/>
       <c r="H143" s="1" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="144" spans="1:8">
       <c r="A144" s="2" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B144" s="1" t="s">
         <v>121</v>
@@ -6539,12 +6569,12 @@
       </c>
       <c r="G144" s="1"/>
       <c r="H144" s="1" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="145" spans="1:8">
       <c r="A145" s="2" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B145" s="1" t="s">
         <v>119</v>
@@ -6563,15 +6593,15 @@
       </c>
       <c r="G145" s="1"/>
       <c r="H145" s="1" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="146" spans="1:8">
       <c r="A146" s="2" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C146" s="2">
         <v>30</v>
@@ -6580,18 +6610,18 @@
         <v>0</v>
       </c>
       <c r="E146" s="2" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F146" s="2">
         <v>0</v>
       </c>
       <c r="H146" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
     </row>
     <row r="147" spans="1:8">
       <c r="A147" s="2" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B147" s="1" t="s">
         <v>258</v>
@@ -6608,12 +6638,12 @@
         <v>260</v>
       </c>
       <c r="H147" s="2" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
     </row>
     <row r="148" spans="1:8">
       <c r="A148" s="2" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B148" s="1" t="s">
         <v>261</v>
@@ -6630,12 +6660,12 @@
         <v>263</v>
       </c>
       <c r="H148" s="2" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
     </row>
     <row r="149" spans="1:8">
       <c r="A149" s="2" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B149" s="1" t="s">
         <v>134</v>
@@ -6654,12 +6684,12 @@
       </c>
       <c r="G149" s="1"/>
       <c r="H149" s="1" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
     </row>
     <row r="150" spans="1:8">
       <c r="A150" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B150" s="1" t="s">
         <v>231</v>
@@ -6678,12 +6708,12 @@
       </c>
       <c r="G150" s="1"/>
       <c r="H150" s="1" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
     </row>
     <row r="151" spans="1:8">
       <c r="A151" s="2" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B151" s="1" t="s">
         <v>292</v>
@@ -6702,12 +6732,12 @@
       </c>
       <c r="G151" s="1"/>
       <c r="H151" s="1" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
     </row>
     <row r="152" spans="1:8">
       <c r="A152" s="2" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B152" s="1" t="s">
         <v>75</v>
@@ -6726,12 +6756,12 @@
       </c>
       <c r="G152" s="1"/>
       <c r="H152" s="2" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
     </row>
     <row r="153" spans="1:8">
       <c r="A153" s="2" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B153" s="1" t="s">
         <v>310</v>
@@ -6750,15 +6780,15 @@
       </c>
       <c r="G153" s="1"/>
       <c r="H153" s="1" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
     </row>
     <row r="154" spans="1:8">
       <c r="A154" s="2" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C154" s="1"/>
       <c r="D154" s="5"/>
@@ -6770,12 +6800,12 @@
       </c>
       <c r="G154" s="1"/>
       <c r="H154" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
     </row>
     <row r="155" spans="1:8">
       <c r="A155" s="2" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="B155" s="1" t="s">
         <v>299</v>
@@ -6790,12 +6820,12 @@
       </c>
       <c r="G155" s="1"/>
       <c r="H155" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
     </row>
     <row r="156" spans="1:8">
       <c r="A156" s="2" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="B156" s="1" t="s">
         <v>300</v>
@@ -6810,12 +6840,12 @@
       </c>
       <c r="G156" s="1"/>
       <c r="H156" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
     </row>
     <row r="157" spans="1:8">
       <c r="A157" s="2" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B157" s="1" t="s">
         <v>245</v>
@@ -6827,19 +6857,19 @@
         <v>0</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>771</v>
+        <v>836</v>
       </c>
       <c r="F157" s="3">
         <v>0</v>
       </c>
       <c r="G157" s="1"/>
       <c r="H157" s="1" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
     </row>
     <row r="158" spans="1:8">
       <c r="A158" s="2" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B158" s="1" t="s">
         <v>243</v>
@@ -6858,15 +6888,15 @@
       </c>
       <c r="G158" s="1"/>
       <c r="H158" s="2" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
     </row>
     <row r="159" spans="1:8">
       <c r="A159" s="2" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="C159" s="2">
         <v>7</v>
@@ -6875,18 +6905,18 @@
         <v>0.95833333333333337</v>
       </c>
       <c r="E159" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="F159" s="3">
+        <v>0</v>
+      </c>
+      <c r="H159" s="7" t="s">
         <v>713</v>
-      </c>
-      <c r="F159" s="3">
-        <v>0</v>
-      </c>
-      <c r="H159" s="7" t="s">
-        <v>714</v>
       </c>
     </row>
     <row r="160" spans="1:8">
       <c r="A160" s="2" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B160" s="1" t="s">
         <v>57</v>
@@ -6905,12 +6935,12 @@
       </c>
       <c r="G160" s="1"/>
       <c r="H160" s="2" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="161" spans="1:8">
       <c r="A161" s="2" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B161" s="1" t="s">
         <v>61</v>
@@ -6922,36 +6952,36 @@
         <v>0</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="F161" s="3">
         <v>0</v>
       </c>
       <c r="G161" s="1"/>
       <c r="H161" s="2" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="162" spans="1:8">
       <c r="A162" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="B162" s="1" t="s">
         <v>456</v>
       </c>
-      <c r="B162" s="1" t="s">
-        <v>457</v>
-      </c>
       <c r="E162" s="1" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="F162" s="3">
         <v>1</v>
       </c>
       <c r="H162" s="1" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
     </row>
     <row r="163" spans="1:8">
       <c r="A163" s="2" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B163" s="1" t="s">
         <v>59</v>
@@ -6970,12 +7000,12 @@
       </c>
       <c r="G163" s="1"/>
       <c r="H163" s="2" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
     </row>
     <row r="164" spans="1:8">
       <c r="A164" s="2" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B164" s="1" t="s">
         <v>62</v>
@@ -6994,12 +7024,12 @@
       </c>
       <c r="G164" s="1"/>
       <c r="H164" s="2" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
     </row>
     <row r="165" spans="1:8">
       <c r="A165" s="2" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B165" s="1" t="s">
         <v>123</v>
@@ -7018,12 +7048,12 @@
       </c>
       <c r="G165" s="1"/>
       <c r="H165" s="1" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="166" spans="1:8">
       <c r="A166" s="2" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B166" s="1" t="s">
         <v>126</v>
@@ -7042,12 +7072,12 @@
       </c>
       <c r="G166" s="1"/>
       <c r="H166" s="1" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="167" spans="1:8">
       <c r="A167" s="2" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B167" s="1" t="s">
         <v>125</v>
@@ -7066,12 +7096,12 @@
       </c>
       <c r="G167" s="1"/>
       <c r="H167" s="1" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="168" spans="1:8">
       <c r="A168" s="2" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B168" s="1" t="s">
         <v>287</v>
@@ -7090,12 +7120,12 @@
       </c>
       <c r="G168" s="1"/>
       <c r="H168" s="1" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="169" spans="1:8">
       <c r="A169" s="2" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B169" s="1" t="s">
         <v>9</v>
@@ -7114,15 +7144,15 @@
       </c>
       <c r="G169" s="1"/>
       <c r="H169" s="2" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
     <row r="170" spans="1:8">
       <c r="A170" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C170" s="3">
         <v>13</v>
@@ -7131,42 +7161,42 @@
         <v>0</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F170" s="3">
         <v>0</v>
       </c>
       <c r="G170" s="1"/>
       <c r="H170" s="1" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="171" spans="1:8">
       <c r="A171" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C171" s="3"/>
       <c r="D171" s="5"/>
       <c r="E171" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F171" s="3">
         <v>1</v>
       </c>
       <c r="G171" s="1"/>
       <c r="H171" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="172" spans="1:8">
       <c r="A172" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="B172" s="1" t="s">
         <v>501</v>
-      </c>
-      <c r="B172" s="1" t="s">
-        <v>502</v>
       </c>
       <c r="C172" s="3">
         <v>30</v>
@@ -7175,19 +7205,19 @@
         <v>0</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="F172" s="3">
         <v>0</v>
       </c>
       <c r="G172" s="1"/>
       <c r="H172" s="1" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="173" spans="1:8">
       <c r="A173" s="2" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B173" s="1" t="s">
         <v>297</v>
@@ -7206,12 +7236,12 @@
       </c>
       <c r="G173" s="1"/>
       <c r="H173" s="1" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="174" spans="1:8">
       <c r="A174" s="2" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B174" s="1" t="s">
         <v>295</v>
@@ -7230,46 +7260,46 @@
       </c>
       <c r="G174" s="1"/>
       <c r="H174" s="1" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="175" spans="1:8">
       <c r="A175" s="2" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="F175" s="2">
         <v>1</v>
       </c>
       <c r="H175" s="2" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
     </row>
     <row r="176" spans="1:8">
       <c r="A176" s="2" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="F176" s="2">
         <v>1</v>
       </c>
       <c r="H176" s="2" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
     </row>
     <row r="177" spans="1:8">
       <c r="A177" s="2" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B177" s="1" t="s">
         <v>216</v>
@@ -7281,19 +7311,19 @@
         <v>0</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="F177" s="3">
         <v>0</v>
       </c>
       <c r="G177" s="1"/>
       <c r="H177" s="1" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="178" spans="1:8">
       <c r="A178" s="2" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B178" s="1" t="s">
         <v>216</v>
@@ -7305,19 +7335,19 @@
         <v>0</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="F178" s="3">
         <v>0</v>
       </c>
       <c r="G178" s="1"/>
       <c r="H178" s="1" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="179" spans="1:8">
       <c r="A179" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B179" s="1" t="s">
         <v>25</v>
@@ -7336,12 +7366,12 @@
       </c>
       <c r="G179" s="1"/>
       <c r="H179" s="2" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="180" spans="1:8">
       <c r="A180" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B180" s="1" t="s">
         <v>27</v>
@@ -7360,12 +7390,12 @@
       </c>
       <c r="G180" s="1"/>
       <c r="H180" s="2" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="181" spans="1:8">
       <c r="A181" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B181" s="1" t="s">
         <v>23</v>
@@ -7384,12 +7414,12 @@
       </c>
       <c r="G181" s="1"/>
       <c r="H181" s="2" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="182" spans="1:8">
       <c r="A182" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B182" s="1" t="s">
         <v>31</v>
@@ -7408,12 +7438,12 @@
       </c>
       <c r="G182" s="1"/>
       <c r="H182" s="2" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="183" spans="1:8">
       <c r="A183" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B183" s="1" t="s">
         <v>33</v>
@@ -7432,12 +7462,12 @@
       </c>
       <c r="G183" s="1"/>
       <c r="H183" s="2" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="184" spans="1:8">
       <c r="A184" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B184" s="1" t="s">
         <v>20</v>
@@ -7456,12 +7486,12 @@
       </c>
       <c r="G184" s="1"/>
       <c r="H184" s="2" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="185" spans="1:8">
       <c r="A185" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B185" s="1" t="s">
         <v>18</v>
@@ -7480,12 +7510,12 @@
       </c>
       <c r="G185" s="1"/>
       <c r="H185" s="2" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="186" spans="1:8">
       <c r="A186" s="2" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B186" s="1" t="s">
         <v>37</v>
@@ -7504,12 +7534,12 @@
       </c>
       <c r="G186" s="1"/>
       <c r="H186" s="2" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="187" spans="1:8">
       <c r="A187" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B187" s="1" t="s">
         <v>29</v>
@@ -7528,12 +7558,12 @@
       </c>
       <c r="G187" s="1"/>
       <c r="H187" s="2" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="188" spans="1:8">
       <c r="A188" s="2" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B188" s="1" t="s">
         <v>39</v>
@@ -7552,12 +7582,12 @@
       </c>
       <c r="G188" s="1"/>
       <c r="H188" s="2" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="189" spans="1:8">
       <c r="A189" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B189" s="1" t="s">
         <v>35</v>
@@ -7576,12 +7606,12 @@
       </c>
       <c r="G189" s="1"/>
       <c r="H189" s="2" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="190" spans="1:8">
       <c r="A190" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B190" s="1" t="s">
         <v>22</v>
@@ -7600,15 +7630,15 @@
       </c>
       <c r="G190" s="1"/>
       <c r="H190" s="2" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="191" spans="1:8">
       <c r="A191" s="2" t="s">
+        <v>707</v>
+      </c>
+      <c r="B191" s="1" t="s">
         <v>708</v>
-      </c>
-      <c r="B191" s="1" t="s">
-        <v>709</v>
       </c>
       <c r="C191" s="2">
         <v>6</v>
@@ -7617,21 +7647,21 @@
         <v>0</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="F191" s="3">
         <v>0</v>
       </c>
       <c r="H191" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
     </row>
     <row r="192" spans="1:8">
       <c r="A192" s="2" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C192" s="3">
         <v>8</v>
@@ -7640,21 +7670,21 @@
         <v>0</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="F192" s="3">
         <v>0</v>
       </c>
       <c r="H192" s="1" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="193" spans="1:8">
       <c r="A193" s="2" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C193" s="3">
         <v>7</v>
@@ -7670,12 +7700,12 @@
       </c>
       <c r="G193" s="1"/>
       <c r="H193" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
     </row>
     <row r="194" spans="1:8">
       <c r="A194" s="2" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B194" s="1" t="s">
         <v>132</v>
@@ -7687,22 +7717,22 @@
         <v>0</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="F194" s="3">
         <v>0</v>
       </c>
       <c r="G194" s="1"/>
       <c r="H194" s="1" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="195" spans="1:8">
       <c r="A195" s="2" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="C195" s="2">
         <v>6</v>
@@ -7711,21 +7741,21 @@
         <v>0</v>
       </c>
       <c r="E195" s="10" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="F195" s="3">
         <v>0</v>
       </c>
       <c r="H195" s="2" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
     </row>
     <row r="196" spans="1:8">
       <c r="A196" s="2" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="C196" s="2">
         <v>6</v>
@@ -7734,21 +7764,21 @@
         <v>0</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="F196" s="3">
         <v>0</v>
       </c>
       <c r="H196" s="2" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
     </row>
     <row r="197" spans="1:8">
       <c r="A197" s="2" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="C197" s="2">
         <v>6</v>
@@ -7757,40 +7787,40 @@
         <v>0</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="F197" s="3">
         <v>0</v>
       </c>
       <c r="H197" s="2" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
     </row>
     <row r="198" spans="1:8">
       <c r="A198" s="2" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C198" s="3"/>
       <c r="D198" s="6"/>
       <c r="E198" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="F198" s="3">
         <v>1</v>
       </c>
       <c r="G198" s="2" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="H198" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
     </row>
     <row r="199" spans="1:8">
       <c r="A199" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B199" s="1" t="s">
         <v>202</v>
@@ -7809,12 +7839,12 @@
       </c>
       <c r="G199" s="1"/>
       <c r="H199" s="1" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="200" spans="1:8">
       <c r="A200" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B200" s="1" t="s">
         <v>200</v>
@@ -7833,12 +7863,12 @@
       </c>
       <c r="G200" s="1"/>
       <c r="H200" s="1" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="201" spans="1:8">
       <c r="A201" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B201" s="1" t="s">
         <v>204</v>
@@ -7857,12 +7887,12 @@
       </c>
       <c r="G201" s="1"/>
       <c r="H201" s="1" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="202" spans="1:8">
       <c r="A202" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B202" s="1" t="s">
         <v>133</v>
@@ -7874,19 +7904,19 @@
         <v>0.97916666666666663</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="F202" s="3">
         <v>0</v>
       </c>
       <c r="G202" s="1"/>
       <c r="H202" s="1" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
     </row>
     <row r="203" spans="1:8">
       <c r="A203" s="2" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B203" s="1" t="s">
         <v>64</v>
@@ -7898,19 +7928,19 @@
         <v>0</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="F203" s="3">
         <v>0</v>
       </c>
       <c r="G203" s="1"/>
       <c r="H203" s="2" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="204" spans="1:8">
       <c r="A204" s="2" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B204" s="1" t="s">
         <v>65</v>
@@ -7929,12 +7959,12 @@
       </c>
       <c r="G204" s="1"/>
       <c r="H204" s="2" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
     </row>
     <row r="205" spans="1:8">
       <c r="A205" s="2" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B205" s="1" t="s">
         <v>69</v>
@@ -7953,12 +7983,12 @@
       </c>
       <c r="G205" s="1"/>
       <c r="H205" s="2" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="206" spans="1:8">
       <c r="A206" s="2" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B206" s="1" t="s">
         <v>67</v>
@@ -7977,12 +8007,12 @@
       </c>
       <c r="G206" s="1"/>
       <c r="H206" s="2" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="207" spans="1:8">
       <c r="A207" s="2" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B207" s="1" t="s">
         <v>71</v>
@@ -8001,12 +8031,12 @@
       </c>
       <c r="G207" s="1"/>
       <c r="H207" s="2" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
     </row>
     <row r="208" spans="1:8">
       <c r="A208" s="2" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B208" s="1" t="s">
         <v>73</v>
@@ -8025,12 +8055,12 @@
       </c>
       <c r="G208" s="1"/>
       <c r="H208" s="2" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="209" spans="1:8">
       <c r="A209" s="2" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B209" s="1" t="s">
         <v>94</v>
@@ -8049,12 +8079,12 @@
       </c>
       <c r="G209" s="1"/>
       <c r="H209" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
     </row>
     <row r="210" spans="1:8">
       <c r="A210" s="2" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B210" s="1" t="s">
         <v>97</v>
@@ -8073,12 +8103,12 @@
       </c>
       <c r="G210" s="1"/>
       <c r="H210" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
     </row>
     <row r="211" spans="1:8">
       <c r="A211" s="2" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B211" s="1" t="s">
         <v>88</v>
@@ -8097,12 +8127,12 @@
       </c>
       <c r="G211" s="1"/>
       <c r="H211" s="1" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
     </row>
     <row r="212" spans="1:8">
       <c r="A212" s="2" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B212" s="1" t="s">
         <v>90</v>
@@ -8121,12 +8151,12 @@
       </c>
       <c r="G212" s="1"/>
       <c r="H212" s="1" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
     </row>
     <row r="213" spans="1:8">
       <c r="A213" s="2" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B213" s="1" t="s">
         <v>104</v>
@@ -8145,12 +8175,12 @@
       </c>
       <c r="G213" s="1"/>
       <c r="H213" s="1" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
     </row>
     <row r="214" spans="1:8">
       <c r="A214" s="2" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B214" s="1" t="s">
         <v>112</v>
@@ -8169,12 +8199,12 @@
       </c>
       <c r="G214" s="1"/>
       <c r="H214" s="1" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
     </row>
     <row r="215" spans="1:8">
       <c r="A215" s="2" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B215" s="1" t="s">
         <v>106</v>
@@ -8193,12 +8223,12 @@
       </c>
       <c r="G215" s="1"/>
       <c r="H215" s="1" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
     </row>
     <row r="216" spans="1:8">
       <c r="A216" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B216" s="1" t="s">
         <v>93</v>
@@ -8210,19 +8240,19 @@
         <v>0</v>
       </c>
       <c r="E216" s="1" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="F216" s="3">
         <v>0</v>
       </c>
       <c r="G216" s="1"/>
       <c r="H216" s="8" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
     </row>
     <row r="217" spans="1:8">
       <c r="A217" s="2" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B217" s="1" t="s">
         <v>110</v>
@@ -8241,12 +8271,12 @@
       </c>
       <c r="G217" s="1"/>
       <c r="H217" s="1" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
     </row>
     <row r="218" spans="1:8">
       <c r="A218" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B218" s="1" t="s">
         <v>285</v>
@@ -8265,12 +8295,12 @@
       </c>
       <c r="G218" s="1"/>
       <c r="H218" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
     </row>
     <row r="219" spans="1:8">
       <c r="A219" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B219" s="1" t="s">
         <v>206</v>
@@ -8289,12 +8319,12 @@
       </c>
       <c r="G219" s="1"/>
       <c r="H219" s="1" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
     </row>
     <row r="220" spans="1:8">
       <c r="A220" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B220" s="1" t="s">
         <v>208</v>
@@ -8313,12 +8343,12 @@
       </c>
       <c r="G220" s="1"/>
       <c r="H220" s="1" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
     </row>
     <row r="221" spans="1:8">
       <c r="A221" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B221" s="1" t="s">
         <v>213</v>
@@ -8337,12 +8367,12 @@
       </c>
       <c r="G221" s="1"/>
       <c r="H221" s="1" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
     </row>
     <row r="222" spans="1:8">
       <c r="A222" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B222" s="1" t="s">
         <v>211</v>
@@ -8361,12 +8391,12 @@
       </c>
       <c r="G222" s="1"/>
       <c r="H222" s="1" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
     </row>
     <row r="223" spans="1:8">
       <c r="A223" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B223" s="1" t="s">
         <v>210</v>
@@ -8378,19 +8408,19 @@
         <v>0</v>
       </c>
       <c r="E223" s="1" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="F223" s="3">
         <v>0</v>
       </c>
       <c r="G223" s="1"/>
       <c r="H223" s="1" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
     </row>
     <row r="224" spans="1:8">
       <c r="A224" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B224" s="1" t="s">
         <v>301</v>
@@ -8398,56 +8428,56 @@
       <c r="C224" s="1"/>
       <c r="D224" s="1"/>
       <c r="E224" s="1" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F224" s="1">
         <v>1</v>
       </c>
       <c r="G224" s="1"/>
       <c r="H224" s="1" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="225" spans="1:8">
       <c r="A225" s="2" t="s">
+        <v>815</v>
+      </c>
+      <c r="B225" s="1" t="s">
+        <v>816</v>
+      </c>
+      <c r="E225" s="1" t="s">
         <v>817</v>
-      </c>
-      <c r="B225" s="1" t="s">
-        <v>818</v>
-      </c>
-      <c r="E225" s="1" t="s">
-        <v>819</v>
       </c>
       <c r="F225" s="3">
         <v>1</v>
       </c>
       <c r="H225" s="7" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
     </row>
     <row r="226" spans="1:8">
       <c r="A226" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="B226" s="1" t="s">
+        <v>820</v>
+      </c>
+      <c r="E226" s="1" t="s">
         <v>822</v>
-      </c>
-      <c r="E226" s="1" t="s">
-        <v>824</v>
       </c>
       <c r="F226" s="3">
         <v>1</v>
       </c>
       <c r="H226" s="7" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
     </row>
     <row r="227" spans="1:8">
       <c r="A227" s="2" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="B227" s="1" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="C227" s="2">
         <v>30</v>
@@ -8456,13 +8486,53 @@
         <v>0</v>
       </c>
       <c r="E227" s="1" t="s">
+        <v>825</v>
+      </c>
+      <c r="F227" s="3">
+        <v>0</v>
+      </c>
+      <c r="H227" s="7" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="228" spans="1:8">
+      <c r="A228" s="2" t="s">
+        <v>829</v>
+      </c>
+      <c r="B228" s="1" t="s">
         <v>827</v>
       </c>
-      <c r="F227" s="3">
-        <v>0</v>
-      </c>
-      <c r="H227" s="7" t="s">
+      <c r="C228" s="2">
+        <v>6</v>
+      </c>
+      <c r="D228" s="6">
+        <v>0</v>
+      </c>
+      <c r="E228" s="1" t="s">
         <v>828</v>
+      </c>
+      <c r="F228" s="3">
+        <v>0</v>
+      </c>
+      <c r="H228" s="7" t="s">
+        <v>830</v>
+      </c>
+    </row>
+    <row r="229" spans="1:8">
+      <c r="A229" s="2" t="s">
+        <v>832</v>
+      </c>
+      <c r="B229" s="1" t="s">
+        <v>833</v>
+      </c>
+      <c r="E229" s="1" t="s">
+        <v>834</v>
+      </c>
+      <c r="F229" s="3">
+        <v>1</v>
+      </c>
+      <c r="H229" s="7" t="s">
+        <v>835</v>
       </c>
     </row>
   </sheetData>
@@ -8482,8 +8552,10 @@
     <hyperlink ref="H225" r:id="rId9" xr:uid="{7887DCFC-D844-46A5-A06B-C3E53BC46BA9}"/>
     <hyperlink ref="H226" r:id="rId10" xr:uid="{25B31E9F-543F-4E86-89DB-207AA2179ACF}"/>
     <hyperlink ref="H227" r:id="rId11" xr:uid="{9827A6D5-ED28-4225-87FD-B74EDF207367}"/>
+    <hyperlink ref="H228" r:id="rId12" xr:uid="{5FF5509A-E557-47E9-9497-31CDE0FE2F49}"/>
+    <hyperlink ref="H229" r:id="rId13" xr:uid="{C22B731B-9B71-4E64-B35B-0DA8918E1D6C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId12"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId14"/>
 </worksheet>
 </file>
--- a/stores.xlsx
+++ b/stores.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\YUMIN\Desktop\B0KT2A_RSVN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DE18051A-D7B1-4A2A-9179-5B125FB340D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{14E82B27-2BD8-4F39-BCA5-43A020EF53AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{ABFC3117-FCCB-4FF3-804A-FE19451A2004}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1181" uniqueCount="1050">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1188" uniqueCount="1059">
   <si>
     <t>룸익스케이프 WHITE</t>
   </si>
@@ -2178,14 +2178,6 @@
     <t>https://playpointlab.com/</t>
   </si>
   <si>
-    <t>가암성당</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>난너의보이,난너보,좌뇌우뇌연구소</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>ecp_dj</t>
   </si>
   <si>
@@ -3630,6 +3622,45 @@
   </si>
   <si>
     <t>https://naver.me/x7jdGdAZ</t>
+  </si>
+  <si>
+    <t>퀘스천마크,퀘마</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>퀴즈카페2,퀴카2,QUIZ CAFE2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://naver.me/FbVPDyTq</t>
+  </si>
+  <si>
+    <t>가암성당,감성당</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>난너의보이,난너보,좌뇌우뇌연구소,좌우연</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://naver.me/GHLnaipV</t>
+  </si>
+  <si>
+    <t>http://www.mysteryroomescape-gn.com/</t>
+  </si>
+  <si>
+    <t>mre_gn</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>미스터리 룸 이스케이프 강남점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://naver.me/5jJTmSwX</t>
+  </si>
+  <si>
+    <t>https://naver.me/xzxwgnk1</t>
   </si>
 </sst>
 </file>
@@ -3708,7 +3739,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3740,6 +3771,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
@@ -4061,7 +4095,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D839462D-4719-40BB-8925-C1B9F93734CF}">
-  <dimension ref="A1:H294"/>
+  <dimension ref="A1:H295"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="2"/>
@@ -4102,10 +4136,10 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="2" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="C2" s="2">
         <v>7</v>
@@ -4114,18 +4148,18 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="2" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="C3" s="2">
         <v>7</v>
@@ -4134,18 +4168,18 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="2" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="C4" s="2">
         <v>7</v>
@@ -4154,7 +4188,7 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -4415,8 +4449,8 @@
       </c>
       <c r="F16" s="3"/>
       <c r="G16" s="1"/>
-      <c r="H16" s="1" t="s">
-        <v>524</v>
+      <c r="H16" s="7" t="s">
+        <v>1053</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -4595,10 +4629,10 @@
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="2" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="C25" s="3">
         <v>15</v>
@@ -4607,12 +4641,12 @@
         <v>0</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="F25" s="3"/>
       <c r="G25" s="1"/>
       <c r="H25" s="11" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -4703,27 +4737,27 @@
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="2" t="s">
+        <v>793</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>794</v>
+      </c>
+      <c r="E30" s="1" t="s">
         <v>795</v>
       </c>
-      <c r="B30" s="1" t="s">
-        <v>796</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>797</v>
-      </c>
       <c r="F30" s="3">
         <v>1</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="2" t="s">
+        <v>805</v>
+      </c>
+      <c r="B31" s="1" t="s">
         <v>807</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>809</v>
       </c>
       <c r="C31" s="2">
         <v>20</v>
@@ -4732,112 +4766,112 @@
         <v>0</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="2" t="s">
+        <v>780</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>781</v>
+      </c>
+      <c r="E32" s="1" t="s">
         <v>782</v>
       </c>
-      <c r="B32" s="1" t="s">
-        <v>783</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>784</v>
-      </c>
       <c r="F32" s="3">
         <v>1</v>
       </c>
       <c r="H32" s="7" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="2" t="s">
+        <v>776</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>777</v>
+      </c>
+      <c r="E33" s="1" t="s">
         <v>778</v>
       </c>
-      <c r="B33" s="1" t="s">
+      <c r="F33" s="3">
+        <v>1</v>
+      </c>
+      <c r="H33" s="2" t="s">
         <v>779</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>780</v>
-      </c>
-      <c r="F33" s="3">
-        <v>1</v>
-      </c>
-      <c r="H33" s="2" t="s">
-        <v>781</v>
       </c>
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="2" t="s">
+        <v>787</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>788</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>791</v>
+      </c>
+      <c r="F34" s="3">
+        <v>1</v>
+      </c>
+      <c r="H34" s="2" t="s">
         <v>789</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>790</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>793</v>
-      </c>
-      <c r="F34" s="3">
-        <v>1</v>
-      </c>
-      <c r="H34" s="2" t="s">
-        <v>791</v>
       </c>
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="2" t="s">
+        <v>801</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>802</v>
+      </c>
+      <c r="E35" s="1" t="s">
         <v>803</v>
       </c>
-      <c r="B35" s="1" t="s">
-        <v>804</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>805</v>
-      </c>
       <c r="F35" s="3">
         <v>1</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
     </row>
     <row r="36" spans="1:8">
       <c r="A36" s="2" t="s">
+        <v>797</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>798</v>
+      </c>
+      <c r="E36" s="1" t="s">
         <v>799</v>
       </c>
-      <c r="B36" s="1" t="s">
-        <v>800</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>801</v>
-      </c>
       <c r="F36" s="3">
         <v>1</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
     </row>
     <row r="37" spans="1:8">
       <c r="A37" s="2" t="s">
+        <v>784</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>785</v>
+      </c>
+      <c r="E37" s="1" t="s">
         <v>786</v>
       </c>
-      <c r="B37" s="1" t="s">
-        <v>787</v>
-      </c>
-      <c r="E37" s="1" t="s">
-        <v>788</v>
-      </c>
       <c r="F37" s="3">
         <v>1</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -4864,36 +4898,36 @@
     </row>
     <row r="39" spans="1:8">
       <c r="A39" s="2" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="F39" s="3">
         <v>1</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
     </row>
     <row r="40" spans="1:8">
       <c r="A40" s="2" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="B40" s="1" t="s">
+        <v>694</v>
+      </c>
+      <c r="E40" s="1" t="s">
         <v>696</v>
       </c>
-      <c r="E40" s="1" t="s">
-        <v>698</v>
-      </c>
       <c r="F40" s="3">
         <v>1</v>
       </c>
       <c r="H40" s="9" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -5094,7 +5128,7 @@
         <v>0</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="F50" s="3"/>
       <c r="G50" s="1"/>
@@ -5236,13 +5270,13 @@
     </row>
     <row r="57" spans="1:8">
       <c r="A57" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="F57" s="2">
         <v>1</v>
@@ -5250,41 +5284,41 @@
     </row>
     <row r="58" spans="1:8">
       <c r="A58" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="F58" s="3">
         <v>1</v>
       </c>
       <c r="H58" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
     </row>
     <row r="59" spans="1:8">
       <c r="A59" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="C59" s="3"/>
       <c r="D59" s="6"/>
       <c r="E59" s="1" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="F59" s="3">
         <v>1</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="H59" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="60" spans="1:8">
@@ -5311,10 +5345,10 @@
     </row>
     <row r="61" spans="1:8">
       <c r="A61" s="11" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="B61" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="C61">
         <v>6</v>
@@ -5323,7 +5357,7 @@
         <v>0</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="F61" s="3"/>
       <c r="G61" s="1"/>
@@ -5506,7 +5540,7 @@
     </row>
     <row r="70" spans="1:8">
       <c r="A70" s="2" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>182</v>
@@ -5525,7 +5559,7 @@
     </row>
     <row r="71" spans="1:8">
       <c r="A71" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>265</v>
@@ -5544,7 +5578,7 @@
     </row>
     <row r="72" spans="1:8">
       <c r="A72" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>180</v>
@@ -5563,7 +5597,7 @@
     </row>
     <row r="73" spans="1:8">
       <c r="A73" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>186</v>
@@ -5584,7 +5618,7 @@
     </row>
     <row r="74" spans="1:8">
       <c r="A74" s="2" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>184</v>
@@ -5605,7 +5639,7 @@
     </row>
     <row r="75" spans="1:8">
       <c r="A75" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>172</v>
@@ -5624,7 +5658,7 @@
     </row>
     <row r="76" spans="1:8">
       <c r="A76" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>174</v>
@@ -5662,7 +5696,7 @@
     </row>
     <row r="78" spans="1:8">
       <c r="A78" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>188</v>
@@ -5683,7 +5717,7 @@
     </row>
     <row r="79" spans="1:8">
       <c r="A79" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>176</v>
@@ -5702,7 +5736,7 @@
     </row>
     <row r="80" spans="1:8">
       <c r="A80" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>178</v>
@@ -5723,7 +5757,7 @@
     </row>
     <row r="81" spans="1:8">
       <c r="A81" s="2" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>194</v>
@@ -5744,7 +5778,7 @@
     </row>
     <row r="82" spans="1:8">
       <c r="A82" s="2" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>192</v>
@@ -5765,7 +5799,7 @@
     </row>
     <row r="83" spans="1:8">
       <c r="A83" s="2" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>170</v>
@@ -5786,7 +5820,7 @@
     </row>
     <row r="84" spans="1:8">
       <c r="A84" s="2" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>168</v>
@@ -5805,7 +5839,7 @@
     </row>
     <row r="85" spans="1:8">
       <c r="A85" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>160</v>
@@ -5824,7 +5858,7 @@
     </row>
     <row r="86" spans="1:8">
       <c r="A86" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>166</v>
@@ -5843,7 +5877,7 @@
     </row>
     <row r="87" spans="1:8">
       <c r="A87" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>164</v>
@@ -5862,7 +5896,7 @@
     </row>
     <row r="88" spans="1:8">
       <c r="A88" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>162</v>
@@ -5881,7 +5915,7 @@
     </row>
     <row r="89" spans="1:8">
       <c r="A89" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>190</v>
@@ -5902,38 +5936,38 @@
     </row>
     <row r="90" spans="1:8">
       <c r="A90" t="s">
-        <v>844</v>
-      </c>
-      <c r="B90" s="12" t="s">
-        <v>845</v>
+        <v>842</v>
+      </c>
+      <c r="B90" s="13" t="s">
+        <v>843</v>
       </c>
       <c r="C90" s="3"/>
       <c r="D90" s="4"/>
       <c r="E90" s="1" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="F90" s="3">
         <v>1</v>
       </c>
       <c r="H90" s="11" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
     </row>
     <row r="91" spans="1:8">
       <c r="A91" s="2" t="s">
+        <v>825</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>826</v>
+      </c>
+      <c r="E91" s="1" t="s">
         <v>827</v>
       </c>
-      <c r="B91" s="1" t="s">
+      <c r="F91" s="3">
+        <v>1</v>
+      </c>
+      <c r="H91" s="7" t="s">
         <v>828</v>
-      </c>
-      <c r="E91" s="1" t="s">
-        <v>829</v>
-      </c>
-      <c r="F91" s="3">
-        <v>1</v>
-      </c>
-      <c r="H91" s="7" t="s">
-        <v>830</v>
       </c>
     </row>
     <row r="92" spans="1:8">
@@ -6092,257 +6126,257 @@
     </row>
     <row r="99" spans="1:8">
       <c r="A99" s="2" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="F99" s="3">
         <v>1</v>
       </c>
       <c r="H99" s="7" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
     </row>
     <row r="100" spans="1:8">
       <c r="A100" s="2" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="F100" s="3">
         <v>1</v>
       </c>
       <c r="H100" s="7" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
     </row>
     <row r="101" spans="1:8">
       <c r="A101" s="2" t="s">
+        <v>717</v>
+      </c>
+      <c r="B101" s="1" t="s">
         <v>719</v>
       </c>
-      <c r="B101" s="1" t="s">
-        <v>721</v>
-      </c>
       <c r="E101" s="1" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="F101" s="3">
         <v>1</v>
       </c>
       <c r="H101" s="7" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
     </row>
     <row r="102" spans="1:8">
       <c r="A102" s="2" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="F102" s="3">
         <v>1</v>
       </c>
       <c r="H102" s="7" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
     </row>
     <row r="103" spans="1:8">
       <c r="A103" s="2" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="F103" s="3">
         <v>1</v>
       </c>
       <c r="H103" s="7" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
     </row>
     <row r="104" spans="1:8">
       <c r="A104" s="2" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="F104" s="3">
         <v>1</v>
       </c>
       <c r="H104" s="7" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
     </row>
     <row r="105" spans="1:8">
       <c r="A105" s="2" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="F105" s="3">
         <v>1</v>
       </c>
       <c r="H105" s="7" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
     </row>
     <row r="106" spans="1:8">
       <c r="A106" s="2" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="F106" s="3">
         <v>1</v>
       </c>
       <c r="H106" s="7" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
     </row>
     <row r="107" spans="1:8">
       <c r="A107" s="2" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="F107" s="3">
         <v>1</v>
       </c>
       <c r="H107" s="7" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
     </row>
     <row r="108" spans="1:8">
       <c r="A108" s="2" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="F108" s="3">
         <v>1</v>
       </c>
       <c r="H108" s="7" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
     </row>
     <row r="109" spans="1:8">
       <c r="A109" s="2" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="F109" s="3">
         <v>1</v>
       </c>
       <c r="H109" s="7" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
     </row>
     <row r="110" spans="1:8">
       <c r="A110" s="2" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="F110" s="3">
         <v>1</v>
       </c>
       <c r="H110" s="7" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
     </row>
     <row r="111" spans="1:8">
       <c r="A111" s="2" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="F111" s="3">
         <v>1</v>
       </c>
       <c r="H111" s="7" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
     </row>
     <row r="112" spans="1:8">
       <c r="A112" s="2" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="F112" s="3">
         <v>1</v>
       </c>
       <c r="H112" s="7" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
     </row>
     <row r="113" spans="1:8">
       <c r="A113" s="2" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="F113" s="3">
         <v>1</v>
       </c>
       <c r="H113" s="7" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
     </row>
     <row r="114" spans="1:8">
@@ -6369,64 +6403,64 @@
     </row>
     <row r="115" spans="1:8">
       <c r="A115" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="B115" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="C115" s="3"/>
       <c r="D115" s="4"/>
       <c r="E115" s="1" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="F115" s="3">
         <v>1</v>
       </c>
       <c r="G115" s="1"/>
       <c r="H115" s="11" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8">
+      <c r="A116" s="13" t="s">
+        <v>850</v>
+      </c>
+      <c r="B116" s="13" t="s">
         <v>851</v>
-      </c>
-    </row>
-    <row r="116" spans="1:8">
-      <c r="A116" t="s">
-        <v>852</v>
-      </c>
-      <c r="B116" s="12" t="s">
-        <v>853</v>
       </c>
       <c r="C116" s="3"/>
       <c r="D116" s="4"/>
       <c r="E116" s="1" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="F116" s="3">
         <v>1</v>
       </c>
       <c r="G116" s="1"/>
       <c r="H116" s="11" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
     </row>
     <row r="117" spans="1:8">
       <c r="A117" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
       <c r="B117" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="C117" s="3"/>
       <c r="D117" s="4"/>
       <c r="E117" s="1" t="s">
+        <v>856</v>
+      </c>
+      <c r="F117" s="3">
+        <v>1</v>
+      </c>
+      <c r="G117" s="1" t="s">
+        <v>857</v>
+      </c>
+      <c r="H117" s="11" t="s">
         <v>858</v>
-      </c>
-      <c r="F117" s="3">
-        <v>1</v>
-      </c>
-      <c r="G117" s="1" t="s">
-        <v>859</v>
-      </c>
-      <c r="H117" s="11" t="s">
-        <v>860</v>
       </c>
     </row>
     <row r="118" spans="1:8">
@@ -6475,7 +6509,7 @@
     </row>
     <row r="120" spans="1:8">
       <c r="A120" s="2" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="B120" s="1" t="s">
         <v>298</v>
@@ -6483,7 +6517,7 @@
       <c r="C120" s="1"/>
       <c r="D120" s="5"/>
       <c r="E120" s="1" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="F120" s="3">
         <v>1</v>
@@ -6495,19 +6529,19 @@
     </row>
     <row r="121" spans="1:8">
       <c r="A121" s="2" t="s">
+        <v>812</v>
+      </c>
+      <c r="B121" s="1" t="s">
+        <v>813</v>
+      </c>
+      <c r="E121" s="1" t="s">
+        <v>815</v>
+      </c>
+      <c r="F121" s="3">
+        <v>1</v>
+      </c>
+      <c r="H121" s="7" t="s">
         <v>814</v>
-      </c>
-      <c r="B121" s="1" t="s">
-        <v>815</v>
-      </c>
-      <c r="E121" s="1" t="s">
-        <v>817</v>
-      </c>
-      <c r="F121" s="3">
-        <v>1</v>
-      </c>
-      <c r="H121" s="7" t="s">
-        <v>816</v>
       </c>
     </row>
     <row r="122" spans="1:8">
@@ -6533,176 +6567,176 @@
       </c>
     </row>
     <row r="123" spans="1:8">
-      <c r="A123" t="s">
-        <v>861</v>
-      </c>
-      <c r="B123" s="12" t="s">
-        <v>862</v>
+      <c r="A123" s="13" t="s">
+        <v>859</v>
+      </c>
+      <c r="B123" s="13" t="s">
+        <v>860</v>
       </c>
       <c r="C123"/>
       <c r="D123" s="11"/>
       <c r="E123" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="F123" s="1">
         <v>1</v>
       </c>
       <c r="G123"/>
-      <c r="H123" s="14" t="s">
-        <v>891</v>
+      <c r="H123" s="15" t="s">
+        <v>889</v>
       </c>
     </row>
     <row r="124" spans="1:8">
       <c r="A124" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="B124" s="12" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="E124" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
       <c r="F124" s="1">
         <v>1</v>
       </c>
-      <c r="H124" s="14" t="s">
-        <v>892</v>
+      <c r="H124" s="15" t="s">
+        <v>890</v>
       </c>
     </row>
     <row r="125" spans="1:8">
       <c r="A125" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="B125" s="12" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="E125" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
       <c r="F125" s="1">
         <v>1</v>
       </c>
-      <c r="H125" s="14" t="s">
-        <v>893</v>
+      <c r="H125" s="15" t="s">
+        <v>891</v>
       </c>
     </row>
     <row r="126" spans="1:8">
       <c r="A126" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="B126" s="12" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="E126" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
       <c r="F126" s="1">
         <v>1</v>
       </c>
-      <c r="H126" s="14" t="s">
-        <v>893</v>
+      <c r="H126" s="15" t="s">
+        <v>891</v>
       </c>
     </row>
     <row r="127" spans="1:8">
       <c r="A127" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
       <c r="B127" s="12" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="E127" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="F127" s="1">
         <v>1</v>
       </c>
-      <c r="H127" s="14" t="s">
-        <v>893</v>
+      <c r="H127" s="15" t="s">
+        <v>891</v>
       </c>
     </row>
     <row r="128" spans="1:8">
       <c r="A128" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="B128" s="12" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="E128" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="F128" s="1">
         <v>1</v>
       </c>
-      <c r="H128" s="14" t="s">
-        <v>893</v>
+      <c r="H128" s="15" t="s">
+        <v>891</v>
       </c>
     </row>
     <row r="129" spans="1:8">
       <c r="A129" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="B129" s="12" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
       <c r="E129" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
       <c r="F129" s="1">
         <v>1</v>
       </c>
-      <c r="H129" s="14" t="s">
-        <v>893</v>
+      <c r="H129" s="15" t="s">
+        <v>891</v>
       </c>
     </row>
     <row r="130" spans="1:8">
       <c r="A130" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="B130" s="12" t="s">
-        <v>876</v>
+        <v>874</v>
       </c>
       <c r="E130" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="F130" s="1">
         <v>1</v>
       </c>
-      <c r="H130" s="14" t="s">
-        <v>893</v>
+      <c r="H130" s="15" t="s">
+        <v>891</v>
       </c>
     </row>
     <row r="131" spans="1:8">
       <c r="A131" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="B131" s="12" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
       <c r="E131" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="F131" s="1">
         <v>1</v>
       </c>
-      <c r="H131" s="14" t="s">
-        <v>893</v>
+      <c r="H131" s="15" t="s">
+        <v>891</v>
       </c>
     </row>
     <row r="132" spans="1:8">
       <c r="A132" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="B132" s="12" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
       <c r="E132" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="F132" s="1">
         <v>1</v>
       </c>
-      <c r="H132" s="14" t="s">
-        <v>893</v>
+      <c r="H132" s="15" t="s">
+        <v>891</v>
       </c>
     </row>
     <row r="133" spans="1:8">
@@ -6768,7 +6802,7 @@
       <c r="F135" s="3"/>
       <c r="G135" s="1"/>
       <c r="H135" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
     </row>
     <row r="136" spans="1:8">
@@ -6856,7 +6890,7 @@
       <c r="F139" s="3"/>
       <c r="G139" s="1"/>
       <c r="H139" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
     </row>
     <row r="140" spans="1:8">
@@ -6886,7 +6920,7 @@
         <v>387</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="C141" s="3">
         <v>6</v>
@@ -7103,746 +7137,746 @@
     </row>
     <row r="151" spans="1:8">
       <c r="A151" s="11" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="B151" s="11" t="s">
-        <v>895</v>
-      </c>
-      <c r="C151" s="14">
+        <v>893</v>
+      </c>
+      <c r="C151" s="15">
         <v>14</v>
       </c>
       <c r="D151" s="4">
         <v>0</v>
       </c>
-      <c r="E151" s="14"/>
-      <c r="F151" s="14"/>
-      <c r="G151" s="14"/>
-      <c r="H151" s="14" t="s">
-        <v>1006</v>
+      <c r="E151" s="15"/>
+      <c r="F151" s="15"/>
+      <c r="G151" s="15"/>
+      <c r="H151" s="15" t="s">
+        <v>1004</v>
       </c>
     </row>
     <row r="152" spans="1:8">
       <c r="A152" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="B152" s="12" t="s">
-        <v>897</v>
-      </c>
-      <c r="C152" s="14"/>
-      <c r="D152" s="14"/>
-      <c r="E152" s="14" t="s">
-        <v>968</v>
-      </c>
-      <c r="F152" s="14">
-        <v>1</v>
-      </c>
-      <c r="G152" s="14"/>
-      <c r="H152" s="14" t="s">
-        <v>969</v>
+        <v>895</v>
+      </c>
+      <c r="C152" s="15"/>
+      <c r="D152" s="15"/>
+      <c r="E152" s="15" t="s">
+        <v>966</v>
+      </c>
+      <c r="F152" s="15">
+        <v>1</v>
+      </c>
+      <c r="G152" s="15"/>
+      <c r="H152" s="15" t="s">
+        <v>967</v>
       </c>
     </row>
     <row r="153" spans="1:8">
       <c r="A153" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
       <c r="B153" s="12" t="s">
-        <v>899</v>
-      </c>
-      <c r="C153" s="14"/>
-      <c r="D153" s="14"/>
-      <c r="E153" s="14" t="s">
-        <v>970</v>
-      </c>
-      <c r="F153" s="14">
-        <v>1</v>
-      </c>
-      <c r="G153" s="14"/>
-      <c r="H153" s="14" t="s">
-        <v>969</v>
+        <v>897</v>
+      </c>
+      <c r="C153" s="15"/>
+      <c r="D153" s="15"/>
+      <c r="E153" s="15" t="s">
+        <v>968</v>
+      </c>
+      <c r="F153" s="15">
+        <v>1</v>
+      </c>
+      <c r="G153" s="15"/>
+      <c r="H153" s="15" t="s">
+        <v>967</v>
       </c>
     </row>
     <row r="154" spans="1:8">
       <c r="A154" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="B154" s="12" t="s">
-        <v>901</v>
-      </c>
-      <c r="C154" s="14"/>
-      <c r="D154" s="14"/>
-      <c r="E154" s="14" t="s">
-        <v>971</v>
-      </c>
-      <c r="F154" s="14">
-        <v>1</v>
-      </c>
-      <c r="G154" s="14"/>
-      <c r="H154" s="14" t="s">
+        <v>899</v>
+      </c>
+      <c r="C154" s="15"/>
+      <c r="D154" s="15"/>
+      <c r="E154" s="15" t="s">
         <v>969</v>
+      </c>
+      <c r="F154" s="15">
+        <v>1</v>
+      </c>
+      <c r="G154" s="15"/>
+      <c r="H154" s="15" t="s">
+        <v>967</v>
       </c>
     </row>
     <row r="155" spans="1:8">
       <c r="A155" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="B155" s="12" t="s">
-        <v>903</v>
-      </c>
-      <c r="C155" s="14"/>
-      <c r="D155" s="14"/>
-      <c r="E155" s="14" t="s">
-        <v>972</v>
-      </c>
-      <c r="F155" s="14">
-        <v>1</v>
-      </c>
-      <c r="G155" s="14"/>
-      <c r="H155" s="14" t="s">
-        <v>969</v>
+        <v>901</v>
+      </c>
+      <c r="C155" s="15"/>
+      <c r="D155" s="15"/>
+      <c r="E155" s="15" t="s">
+        <v>970</v>
+      </c>
+      <c r="F155" s="15">
+        <v>1</v>
+      </c>
+      <c r="G155" s="15"/>
+      <c r="H155" s="15" t="s">
+        <v>967</v>
       </c>
     </row>
     <row r="156" spans="1:8">
       <c r="A156" t="s">
-        <v>904</v>
+        <v>902</v>
       </c>
       <c r="B156" s="12" t="s">
-        <v>905</v>
-      </c>
-      <c r="C156" s="14"/>
-      <c r="D156" s="14"/>
-      <c r="E156" s="14" t="s">
-        <v>973</v>
-      </c>
-      <c r="F156" s="14">
-        <v>1</v>
-      </c>
-      <c r="G156" s="14"/>
-      <c r="H156" s="14" t="s">
-        <v>969</v>
+        <v>903</v>
+      </c>
+      <c r="C156" s="15"/>
+      <c r="D156" s="15"/>
+      <c r="E156" s="15" t="s">
+        <v>971</v>
+      </c>
+      <c r="F156" s="15">
+        <v>1</v>
+      </c>
+      <c r="G156" s="15"/>
+      <c r="H156" s="15" t="s">
+        <v>967</v>
       </c>
     </row>
     <row r="157" spans="1:8">
       <c r="A157" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
       <c r="B157" s="12" t="s">
-        <v>907</v>
-      </c>
-      <c r="C157" s="14"/>
-      <c r="D157" s="14"/>
-      <c r="E157" s="14" t="s">
-        <v>974</v>
-      </c>
-      <c r="F157" s="14">
-        <v>1</v>
-      </c>
-      <c r="G157" s="14"/>
-      <c r="H157" s="14" t="s">
-        <v>969</v>
+        <v>905</v>
+      </c>
+      <c r="C157" s="15"/>
+      <c r="D157" s="15"/>
+      <c r="E157" s="15" t="s">
+        <v>972</v>
+      </c>
+      <c r="F157" s="15">
+        <v>1</v>
+      </c>
+      <c r="G157" s="15"/>
+      <c r="H157" s="15" t="s">
+        <v>967</v>
       </c>
     </row>
     <row r="158" spans="1:8">
       <c r="A158" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
       <c r="B158" s="12" t="s">
-        <v>909</v>
-      </c>
-      <c r="C158" s="14"/>
-      <c r="D158" s="14"/>
-      <c r="E158" s="14" t="s">
-        <v>975</v>
-      </c>
-      <c r="F158" s="14">
-        <v>1</v>
-      </c>
-      <c r="G158" s="14"/>
-      <c r="H158" s="14" t="s">
-        <v>969</v>
+        <v>907</v>
+      </c>
+      <c r="C158" s="15"/>
+      <c r="D158" s="15"/>
+      <c r="E158" s="15" t="s">
+        <v>973</v>
+      </c>
+      <c r="F158" s="15">
+        <v>1</v>
+      </c>
+      <c r="G158" s="15"/>
+      <c r="H158" s="15" t="s">
+        <v>967</v>
       </c>
     </row>
     <row r="159" spans="1:8">
       <c r="A159" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="B159" s="12" t="s">
-        <v>911</v>
-      </c>
-      <c r="C159" s="14"/>
-      <c r="D159" s="14"/>
-      <c r="E159" s="14" t="s">
-        <v>976</v>
-      </c>
-      <c r="F159" s="14">
-        <v>1</v>
-      </c>
-      <c r="G159" s="14"/>
-      <c r="H159" s="14" t="s">
-        <v>969</v>
+        <v>909</v>
+      </c>
+      <c r="C159" s="15"/>
+      <c r="D159" s="15"/>
+      <c r="E159" s="15" t="s">
+        <v>974</v>
+      </c>
+      <c r="F159" s="15">
+        <v>1</v>
+      </c>
+      <c r="G159" s="15"/>
+      <c r="H159" s="15" t="s">
+        <v>967</v>
       </c>
     </row>
     <row r="160" spans="1:8">
       <c r="A160" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="B160" s="12" t="s">
-        <v>913</v>
-      </c>
-      <c r="C160" s="14"/>
-      <c r="D160" s="14"/>
-      <c r="E160" s="14" t="s">
-        <v>977</v>
-      </c>
-      <c r="F160" s="14">
-        <v>1</v>
-      </c>
-      <c r="G160" s="14"/>
-      <c r="H160" s="14" t="s">
-        <v>969</v>
+        <v>911</v>
+      </c>
+      <c r="C160" s="15"/>
+      <c r="D160" s="15"/>
+      <c r="E160" s="15" t="s">
+        <v>975</v>
+      </c>
+      <c r="F160" s="15">
+        <v>1</v>
+      </c>
+      <c r="G160" s="15"/>
+      <c r="H160" s="15" t="s">
+        <v>967</v>
       </c>
     </row>
     <row r="161" spans="1:8">
       <c r="A161" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
       <c r="B161" s="12" t="s">
-        <v>915</v>
-      </c>
-      <c r="C161" s="14"/>
-      <c r="D161" s="14"/>
-      <c r="E161" s="14" t="s">
-        <v>978</v>
-      </c>
-      <c r="F161" s="14">
-        <v>1</v>
-      </c>
-      <c r="G161" s="14"/>
-      <c r="H161" s="14" t="s">
-        <v>969</v>
+        <v>913</v>
+      </c>
+      <c r="C161" s="15"/>
+      <c r="D161" s="15"/>
+      <c r="E161" s="15" t="s">
+        <v>976</v>
+      </c>
+      <c r="F161" s="15">
+        <v>1</v>
+      </c>
+      <c r="G161" s="15"/>
+      <c r="H161" s="15" t="s">
+        <v>967</v>
       </c>
     </row>
     <row r="162" spans="1:8">
       <c r="A162" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
       <c r="B162" s="12" t="s">
-        <v>917</v>
-      </c>
-      <c r="C162" s="14"/>
-      <c r="D162" s="14"/>
-      <c r="E162" s="14" t="s">
-        <v>979</v>
-      </c>
-      <c r="F162" s="14">
-        <v>1</v>
-      </c>
-      <c r="G162" s="14"/>
-      <c r="H162" s="14" t="s">
-        <v>969</v>
+        <v>915</v>
+      </c>
+      <c r="C162" s="15"/>
+      <c r="D162" s="15"/>
+      <c r="E162" s="15" t="s">
+        <v>977</v>
+      </c>
+      <c r="F162" s="15">
+        <v>1</v>
+      </c>
+      <c r="G162" s="15"/>
+      <c r="H162" s="15" t="s">
+        <v>967</v>
       </c>
     </row>
     <row r="163" spans="1:8">
       <c r="A163" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="B163" s="12" t="s">
-        <v>919</v>
-      </c>
-      <c r="C163" s="14"/>
-      <c r="D163" s="14"/>
-      <c r="E163" s="14" t="s">
-        <v>980</v>
-      </c>
-      <c r="F163" s="14">
-        <v>1</v>
-      </c>
-      <c r="G163" s="14"/>
-      <c r="H163" s="14" t="s">
-        <v>969</v>
+        <v>917</v>
+      </c>
+      <c r="C163" s="15"/>
+      <c r="D163" s="15"/>
+      <c r="E163" s="15" t="s">
+        <v>978</v>
+      </c>
+      <c r="F163" s="15">
+        <v>1</v>
+      </c>
+      <c r="G163" s="15"/>
+      <c r="H163" s="15" t="s">
+        <v>967</v>
       </c>
     </row>
     <row r="164" spans="1:8">
       <c r="A164" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
       <c r="B164" s="12" t="s">
-        <v>921</v>
-      </c>
-      <c r="C164" s="14"/>
-      <c r="D164" s="14"/>
-      <c r="E164" s="14" t="s">
-        <v>981</v>
-      </c>
-      <c r="F164" s="14">
-        <v>1</v>
-      </c>
-      <c r="G164" s="14"/>
-      <c r="H164" s="14" t="s">
-        <v>982</v>
+        <v>919</v>
+      </c>
+      <c r="C164" s="15"/>
+      <c r="D164" s="15"/>
+      <c r="E164" s="15" t="s">
+        <v>979</v>
+      </c>
+      <c r="F164" s="15">
+        <v>1</v>
+      </c>
+      <c r="G164" s="15"/>
+      <c r="H164" s="15" t="s">
+        <v>980</v>
       </c>
     </row>
     <row r="165" spans="1:8">
       <c r="A165" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="B165" s="12" t="s">
-        <v>923</v>
-      </c>
-      <c r="C165" s="14"/>
-      <c r="D165" s="14"/>
-      <c r="E165" s="14" t="s">
-        <v>983</v>
-      </c>
-      <c r="F165" s="14">
-        <v>1</v>
-      </c>
-      <c r="G165" s="14"/>
-      <c r="H165" s="14" t="s">
-        <v>969</v>
+        <v>921</v>
+      </c>
+      <c r="C165" s="15"/>
+      <c r="D165" s="15"/>
+      <c r="E165" s="15" t="s">
+        <v>981</v>
+      </c>
+      <c r="F165" s="15">
+        <v>1</v>
+      </c>
+      <c r="G165" s="15"/>
+      <c r="H165" s="15" t="s">
+        <v>967</v>
       </c>
     </row>
     <row r="166" spans="1:8">
       <c r="A166" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
       <c r="B166" s="12" t="s">
-        <v>925</v>
-      </c>
-      <c r="C166" s="14"/>
-      <c r="D166" s="14"/>
-      <c r="E166" s="14" t="s">
-        <v>984</v>
-      </c>
-      <c r="F166" s="14">
-        <v>1</v>
-      </c>
-      <c r="G166" s="14"/>
-      <c r="H166" s="14" t="s">
-        <v>969</v>
+        <v>923</v>
+      </c>
+      <c r="C166" s="15"/>
+      <c r="D166" s="15"/>
+      <c r="E166" s="15" t="s">
+        <v>982</v>
+      </c>
+      <c r="F166" s="15">
+        <v>1</v>
+      </c>
+      <c r="G166" s="15"/>
+      <c r="H166" s="15" t="s">
+        <v>967</v>
       </c>
     </row>
     <row r="167" spans="1:8">
       <c r="A167" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="B167" s="12" t="s">
-        <v>927</v>
-      </c>
-      <c r="C167" s="14"/>
-      <c r="D167" s="14"/>
-      <c r="E167" s="14" t="s">
-        <v>985</v>
-      </c>
-      <c r="F167" s="14">
-        <v>1</v>
-      </c>
-      <c r="G167" s="14"/>
-      <c r="H167" s="14" t="s">
-        <v>969</v>
+        <v>925</v>
+      </c>
+      <c r="C167" s="15"/>
+      <c r="D167" s="15"/>
+      <c r="E167" s="15" t="s">
+        <v>983</v>
+      </c>
+      <c r="F167" s="15">
+        <v>1</v>
+      </c>
+      <c r="G167" s="15"/>
+      <c r="H167" s="15" t="s">
+        <v>967</v>
       </c>
     </row>
     <row r="168" spans="1:8">
       <c r="A168" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="B168" s="12" t="s">
-        <v>929</v>
-      </c>
-      <c r="C168" s="14"/>
-      <c r="D168" s="14"/>
-      <c r="E168" s="14" t="s">
-        <v>986</v>
-      </c>
-      <c r="F168" s="14">
-        <v>1</v>
-      </c>
-      <c r="G168" s="14"/>
-      <c r="H168" s="14" t="s">
-        <v>969</v>
+        <v>927</v>
+      </c>
+      <c r="C168" s="15"/>
+      <c r="D168" s="15"/>
+      <c r="E168" s="15" t="s">
+        <v>984</v>
+      </c>
+      <c r="F168" s="15">
+        <v>1</v>
+      </c>
+      <c r="G168" s="15"/>
+      <c r="H168" s="15" t="s">
+        <v>967</v>
       </c>
     </row>
     <row r="169" spans="1:8">
       <c r="A169" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="B169" s="12" t="s">
-        <v>931</v>
-      </c>
-      <c r="C169" s="14"/>
-      <c r="D169" s="14"/>
-      <c r="E169" s="14" t="s">
-        <v>987</v>
-      </c>
-      <c r="F169" s="14">
-        <v>1</v>
-      </c>
-      <c r="G169" s="14"/>
-      <c r="H169" s="14" t="s">
-        <v>969</v>
+        <v>929</v>
+      </c>
+      <c r="C169" s="15"/>
+      <c r="D169" s="15"/>
+      <c r="E169" s="15" t="s">
+        <v>985</v>
+      </c>
+      <c r="F169" s="15">
+        <v>1</v>
+      </c>
+      <c r="G169" s="15"/>
+      <c r="H169" s="15" t="s">
+        <v>967</v>
       </c>
     </row>
     <row r="170" spans="1:8">
       <c r="A170" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
       <c r="B170" s="12" t="s">
-        <v>933</v>
-      </c>
-      <c r="C170" s="14"/>
-      <c r="D170" s="14"/>
-      <c r="E170" s="14" t="s">
-        <v>988</v>
-      </c>
-      <c r="F170" s="14">
-        <v>1</v>
-      </c>
-      <c r="G170" s="14"/>
-      <c r="H170" s="14" t="s">
-        <v>969</v>
+        <v>931</v>
+      </c>
+      <c r="C170" s="15"/>
+      <c r="D170" s="15"/>
+      <c r="E170" s="15" t="s">
+        <v>986</v>
+      </c>
+      <c r="F170" s="15">
+        <v>1</v>
+      </c>
+      <c r="G170" s="15"/>
+      <c r="H170" s="15" t="s">
+        <v>967</v>
       </c>
     </row>
     <row r="171" spans="1:8">
       <c r="A171" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
       <c r="B171" s="12" t="s">
-        <v>935</v>
-      </c>
-      <c r="C171" s="14"/>
-      <c r="D171" s="14"/>
-      <c r="E171" s="14" t="s">
-        <v>989</v>
-      </c>
-      <c r="F171" s="14">
-        <v>1</v>
-      </c>
-      <c r="G171" s="14"/>
-      <c r="H171" s="14" t="s">
-        <v>969</v>
+        <v>933</v>
+      </c>
+      <c r="C171" s="15"/>
+      <c r="D171" s="15"/>
+      <c r="E171" s="15" t="s">
+        <v>987</v>
+      </c>
+      <c r="F171" s="15">
+        <v>1</v>
+      </c>
+      <c r="G171" s="15"/>
+      <c r="H171" s="15" t="s">
+        <v>967</v>
       </c>
     </row>
     <row r="172" spans="1:8">
       <c r="A172" t="s">
-        <v>936</v>
+        <v>934</v>
       </c>
       <c r="B172" s="12" t="s">
-        <v>937</v>
-      </c>
-      <c r="C172" s="14"/>
-      <c r="D172" s="14"/>
-      <c r="E172" s="14" t="s">
-        <v>990</v>
-      </c>
-      <c r="F172" s="14">
-        <v>1</v>
-      </c>
-      <c r="G172" s="14"/>
-      <c r="H172" s="14" t="s">
-        <v>969</v>
+        <v>935</v>
+      </c>
+      <c r="C172" s="15"/>
+      <c r="D172" s="15"/>
+      <c r="E172" s="15" t="s">
+        <v>988</v>
+      </c>
+      <c r="F172" s="15">
+        <v>1</v>
+      </c>
+      <c r="G172" s="15"/>
+      <c r="H172" s="15" t="s">
+        <v>967</v>
       </c>
     </row>
     <row r="173" spans="1:8">
       <c r="A173" t="s">
-        <v>938</v>
+        <v>936</v>
       </c>
       <c r="B173" s="12" t="s">
-        <v>939</v>
-      </c>
-      <c r="C173" s="14"/>
-      <c r="D173" s="14"/>
-      <c r="E173" s="14" t="s">
-        <v>991</v>
-      </c>
-      <c r="F173" s="14">
-        <v>1</v>
-      </c>
-      <c r="G173" s="14"/>
-      <c r="H173" s="14" t="s">
-        <v>969</v>
+        <v>937</v>
+      </c>
+      <c r="C173" s="15"/>
+      <c r="D173" s="15"/>
+      <c r="E173" s="15" t="s">
+        <v>989</v>
+      </c>
+      <c r="F173" s="15">
+        <v>1</v>
+      </c>
+      <c r="G173" s="15"/>
+      <c r="H173" s="15" t="s">
+        <v>967</v>
       </c>
     </row>
     <row r="174" spans="1:8">
       <c r="A174" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
       <c r="B174" s="12" t="s">
-        <v>941</v>
-      </c>
-      <c r="C174" s="14"/>
-      <c r="D174" s="14"/>
-      <c r="E174" s="14" t="s">
-        <v>992</v>
-      </c>
-      <c r="F174" s="14">
-        <v>1</v>
-      </c>
-      <c r="G174" s="14"/>
-      <c r="H174" s="14" t="s">
-        <v>969</v>
+        <v>939</v>
+      </c>
+      <c r="C174" s="15"/>
+      <c r="D174" s="15"/>
+      <c r="E174" s="15" t="s">
+        <v>990</v>
+      </c>
+      <c r="F174" s="15">
+        <v>1</v>
+      </c>
+      <c r="G174" s="15"/>
+      <c r="H174" s="15" t="s">
+        <v>967</v>
       </c>
     </row>
     <row r="175" spans="1:8">
       <c r="A175" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
       <c r="B175" s="12" t="s">
-        <v>943</v>
-      </c>
-      <c r="C175" s="14"/>
-      <c r="D175" s="14"/>
-      <c r="E175" s="14" t="s">
-        <v>993</v>
-      </c>
-      <c r="F175" s="14">
-        <v>1</v>
-      </c>
-      <c r="G175" s="14"/>
-      <c r="H175" s="14" t="s">
-        <v>969</v>
+        <v>941</v>
+      </c>
+      <c r="C175" s="15"/>
+      <c r="D175" s="15"/>
+      <c r="E175" s="15" t="s">
+        <v>991</v>
+      </c>
+      <c r="F175" s="15">
+        <v>1</v>
+      </c>
+      <c r="G175" s="15"/>
+      <c r="H175" s="15" t="s">
+        <v>967</v>
       </c>
     </row>
     <row r="176" spans="1:8">
       <c r="A176" t="s">
-        <v>944</v>
+        <v>942</v>
       </c>
       <c r="B176" s="12" t="s">
-        <v>945</v>
-      </c>
-      <c r="C176" s="14">
+        <v>943</v>
+      </c>
+      <c r="C176" s="15">
         <v>14</v>
       </c>
       <c r="D176" s="4">
         <v>0</v>
       </c>
-      <c r="E176" s="14" t="s">
-        <v>994</v>
-      </c>
-      <c r="F176" s="14"/>
-      <c r="G176" s="14"/>
-      <c r="H176" s="14" t="s">
-        <v>969</v>
+      <c r="E176" s="15" t="s">
+        <v>992</v>
+      </c>
+      <c r="F176" s="15"/>
+      <c r="G176" s="15"/>
+      <c r="H176" s="15" t="s">
+        <v>967</v>
       </c>
     </row>
     <row r="177" spans="1:8">
       <c r="A177" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
       <c r="B177" s="12" t="s">
-        <v>947</v>
-      </c>
-      <c r="C177" s="14"/>
-      <c r="D177" s="14"/>
-      <c r="E177" s="14" t="s">
-        <v>995</v>
-      </c>
-      <c r="F177" s="14">
-        <v>1</v>
-      </c>
-      <c r="G177" s="14"/>
-      <c r="H177" s="14" t="s">
-        <v>969</v>
+        <v>945</v>
+      </c>
+      <c r="C177" s="15"/>
+      <c r="D177" s="15"/>
+      <c r="E177" s="15" t="s">
+        <v>993</v>
+      </c>
+      <c r="F177" s="15">
+        <v>1</v>
+      </c>
+      <c r="G177" s="15"/>
+      <c r="H177" s="15" t="s">
+        <v>967</v>
       </c>
     </row>
     <row r="178" spans="1:8">
       <c r="A178" t="s">
-        <v>948</v>
+        <v>946</v>
       </c>
       <c r="B178" s="12" t="s">
-        <v>949</v>
-      </c>
-      <c r="C178" s="14"/>
-      <c r="D178" s="14"/>
-      <c r="E178" s="14" t="s">
-        <v>996</v>
-      </c>
-      <c r="F178" s="14">
-        <v>1</v>
-      </c>
-      <c r="G178" s="14"/>
-      <c r="H178" s="14" t="s">
-        <v>969</v>
+        <v>947</v>
+      </c>
+      <c r="C178" s="15"/>
+      <c r="D178" s="15"/>
+      <c r="E178" s="15" t="s">
+        <v>994</v>
+      </c>
+      <c r="F178" s="15">
+        <v>1</v>
+      </c>
+      <c r="G178" s="15"/>
+      <c r="H178" s="15" t="s">
+        <v>967</v>
       </c>
     </row>
     <row r="179" spans="1:8">
       <c r="A179" t="s">
-        <v>950</v>
+        <v>948</v>
       </c>
       <c r="B179" s="12" t="s">
-        <v>951</v>
-      </c>
-      <c r="C179" s="14"/>
-      <c r="D179" s="14"/>
-      <c r="E179" s="14" t="s">
-        <v>997</v>
-      </c>
-      <c r="F179" s="14">
-        <v>1</v>
-      </c>
-      <c r="G179" s="14"/>
-      <c r="H179" s="14" t="s">
-        <v>969</v>
+        <v>949</v>
+      </c>
+      <c r="C179" s="15"/>
+      <c r="D179" s="15"/>
+      <c r="E179" s="15" t="s">
+        <v>995</v>
+      </c>
+      <c r="F179" s="15">
+        <v>1</v>
+      </c>
+      <c r="G179" s="15"/>
+      <c r="H179" s="15" t="s">
+        <v>967</v>
       </c>
     </row>
     <row r="180" spans="1:8">
       <c r="A180" t="s">
-        <v>952</v>
+        <v>950</v>
       </c>
       <c r="B180" s="12" t="s">
-        <v>953</v>
-      </c>
-      <c r="C180" s="14"/>
-      <c r="D180" s="14"/>
-      <c r="E180" s="14" t="s">
-        <v>998</v>
-      </c>
-      <c r="F180" s="14">
-        <v>1</v>
-      </c>
-      <c r="G180" s="14"/>
-      <c r="H180" s="14" t="s">
-        <v>969</v>
+        <v>951</v>
+      </c>
+      <c r="C180" s="15"/>
+      <c r="D180" s="15"/>
+      <c r="E180" s="15" t="s">
+        <v>996</v>
+      </c>
+      <c r="F180" s="15">
+        <v>1</v>
+      </c>
+      <c r="G180" s="15"/>
+      <c r="H180" s="15" t="s">
+        <v>967</v>
       </c>
     </row>
     <row r="181" spans="1:8">
       <c r="A181" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="B181" s="12" t="s">
-        <v>955</v>
-      </c>
-      <c r="C181" s="14">
+        <v>953</v>
+      </c>
+      <c r="C181" s="15">
         <v>14</v>
       </c>
       <c r="D181" s="4">
         <v>0</v>
       </c>
-      <c r="E181" s="14" t="s">
-        <v>999</v>
-      </c>
-      <c r="F181" s="14"/>
-      <c r="G181" s="14"/>
-      <c r="H181" s="14" t="s">
-        <v>969</v>
+      <c r="E181" s="15" t="s">
+        <v>997</v>
+      </c>
+      <c r="F181" s="15"/>
+      <c r="G181" s="15"/>
+      <c r="H181" s="15" t="s">
+        <v>967</v>
       </c>
     </row>
     <row r="182" spans="1:8">
       <c r="A182" t="s">
-        <v>956</v>
+        <v>954</v>
       </c>
       <c r="B182" s="12" t="s">
-        <v>957</v>
-      </c>
-      <c r="C182" s="14"/>
-      <c r="D182" s="14"/>
-      <c r="E182" s="14" t="s">
-        <v>1000</v>
-      </c>
-      <c r="F182" s="14">
-        <v>1</v>
-      </c>
-      <c r="G182" s="14"/>
-      <c r="H182" s="14" t="s">
-        <v>969</v>
+        <v>955</v>
+      </c>
+      <c r="C182" s="15"/>
+      <c r="D182" s="15"/>
+      <c r="E182" s="15" t="s">
+        <v>998</v>
+      </c>
+      <c r="F182" s="15">
+        <v>1</v>
+      </c>
+      <c r="G182" s="15"/>
+      <c r="H182" s="15" t="s">
+        <v>967</v>
       </c>
     </row>
     <row r="183" spans="1:8">
       <c r="A183" t="s">
-        <v>958</v>
+        <v>956</v>
       </c>
       <c r="B183" s="12" t="s">
-        <v>959</v>
-      </c>
-      <c r="C183" s="14"/>
-      <c r="D183" s="14"/>
-      <c r="E183" s="14" t="s">
-        <v>1001</v>
-      </c>
-      <c r="F183" s="14">
-        <v>1</v>
-      </c>
-      <c r="G183" s="14"/>
-      <c r="H183" s="14" t="s">
-        <v>969</v>
+        <v>957</v>
+      </c>
+      <c r="C183" s="15"/>
+      <c r="D183" s="15"/>
+      <c r="E183" s="15" t="s">
+        <v>999</v>
+      </c>
+      <c r="F183" s="15">
+        <v>1</v>
+      </c>
+      <c r="G183" s="15"/>
+      <c r="H183" s="15" t="s">
+        <v>967</v>
       </c>
     </row>
     <row r="184" spans="1:8">
       <c r="A184" t="s">
-        <v>960</v>
+        <v>958</v>
       </c>
       <c r="B184" s="12" t="s">
-        <v>961</v>
-      </c>
-      <c r="C184" s="14"/>
-      <c r="D184" s="14"/>
-      <c r="E184" s="14" t="s">
-        <v>1002</v>
-      </c>
-      <c r="F184" s="14">
-        <v>1</v>
-      </c>
-      <c r="G184" s="14"/>
-      <c r="H184" s="14" t="s">
-        <v>969</v>
+        <v>959</v>
+      </c>
+      <c r="C184" s="15"/>
+      <c r="D184" s="15"/>
+      <c r="E184" s="15" t="s">
+        <v>1000</v>
+      </c>
+      <c r="F184" s="15">
+        <v>1</v>
+      </c>
+      <c r="G184" s="15"/>
+      <c r="H184" s="15" t="s">
+        <v>967</v>
       </c>
     </row>
     <row r="185" spans="1:8">
       <c r="A185" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
       <c r="B185" s="12" t="s">
-        <v>963</v>
-      </c>
-      <c r="C185" s="14"/>
-      <c r="D185" s="14"/>
-      <c r="E185" s="14" t="s">
-        <v>1003</v>
-      </c>
-      <c r="F185" s="14">
-        <v>1</v>
-      </c>
-      <c r="G185" s="14"/>
-      <c r="H185" s="14" t="s">
-        <v>969</v>
+        <v>961</v>
+      </c>
+      <c r="C185" s="15"/>
+      <c r="D185" s="15"/>
+      <c r="E185" s="15" t="s">
+        <v>1001</v>
+      </c>
+      <c r="F185" s="15">
+        <v>1</v>
+      </c>
+      <c r="G185" s="15"/>
+      <c r="H185" s="15" t="s">
+        <v>967</v>
       </c>
     </row>
     <row r="186" spans="1:8">
       <c r="A186" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
       <c r="B186" s="12" t="s">
-        <v>965</v>
-      </c>
-      <c r="C186" s="14"/>
-      <c r="D186" s="14"/>
-      <c r="E186" s="14" t="s">
-        <v>1004</v>
-      </c>
-      <c r="F186" s="14">
-        <v>1</v>
-      </c>
-      <c r="G186" s="14"/>
-      <c r="H186" s="14" t="s">
-        <v>969</v>
+        <v>963</v>
+      </c>
+      <c r="C186" s="15"/>
+      <c r="D186" s="15"/>
+      <c r="E186" s="15" t="s">
+        <v>1002</v>
+      </c>
+      <c r="F186" s="15">
+        <v>1</v>
+      </c>
+      <c r="G186" s="15"/>
+      <c r="H186" s="15" t="s">
+        <v>967</v>
       </c>
     </row>
     <row r="187" spans="1:8">
       <c r="A187" t="s">
-        <v>966</v>
+        <v>964</v>
       </c>
       <c r="B187" s="12" t="s">
+        <v>965</v>
+      </c>
+      <c r="C187" s="15"/>
+      <c r="D187" s="15"/>
+      <c r="E187" s="15" t="s">
+        <v>1003</v>
+      </c>
+      <c r="F187" s="15">
+        <v>1</v>
+      </c>
+      <c r="G187" s="15"/>
+      <c r="H187" s="15" t="s">
         <v>967</v>
-      </c>
-      <c r="C187" s="14"/>
-      <c r="D187" s="14"/>
-      <c r="E187" s="14" t="s">
-        <v>1005</v>
-      </c>
-      <c r="F187" s="14">
-        <v>1</v>
-      </c>
-      <c r="G187" s="14"/>
-      <c r="H187" s="14" t="s">
-        <v>969</v>
       </c>
     </row>
     <row r="188" spans="1:8">
@@ -7864,7 +7898,7 @@
       <c r="F188" s="3"/>
       <c r="G188" s="1"/>
       <c r="H188" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
     </row>
     <row r="189" spans="1:8">
@@ -7913,19 +7947,19 @@
     </row>
     <row r="191" spans="1:8">
       <c r="A191" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="B191" s="1" t="s">
         <v>510</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="F191" s="2">
         <v>1</v>
       </c>
       <c r="G191" s="2" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="H191" s="2" t="s">
         <v>624</v>
@@ -7933,19 +7967,19 @@
     </row>
     <row r="192" spans="1:8">
       <c r="A192" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="B192" s="1" t="s">
         <v>511</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="F192" s="2">
         <v>1</v>
       </c>
       <c r="G192" s="2" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="H192" s="2" t="s">
         <v>625</v>
@@ -7953,19 +7987,19 @@
     </row>
     <row r="193" spans="1:8">
       <c r="A193" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="B193" s="1" t="s">
         <v>511</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="F193" s="2">
         <v>1</v>
       </c>
       <c r="G193" s="2" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="H193" s="2" t="s">
         <v>625</v>
@@ -7973,7 +8007,7 @@
     </row>
     <row r="194" spans="1:8">
       <c r="A194" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="B194" s="1" t="s">
         <v>508</v>
@@ -7985,20 +8019,20 @@
     </row>
     <row r="195" spans="1:8">
       <c r="A195" s="2" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="D195" s="6"/>
       <c r="E195" s="1" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="F195" s="3">
         <v>1</v>
       </c>
       <c r="H195" s="7" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
     </row>
     <row r="196" spans="1:8">
@@ -8025,64 +8059,70 @@
     </row>
     <row r="197" spans="1:8">
       <c r="A197" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="B197" s="1" t="s">
         <v>513</v>
       </c>
       <c r="C197" s="2">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D197" s="6">
         <v>0</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>656</v>
+        <v>654</v>
+      </c>
+      <c r="H197" s="2" t="s">
+        <v>1058</v>
       </c>
     </row>
     <row r="198" spans="1:8">
       <c r="A198" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="C198" s="2">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D198" s="6">
         <v>0</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>657</v>
+        <v>655</v>
+      </c>
+      <c r="H198" s="2" t="s">
+        <v>1057</v>
       </c>
     </row>
     <row r="199" spans="1:8">
       <c r="A199" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
       <c r="B199" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
       <c r="C199"/>
       <c r="D199" s="11"/>
       <c r="E199" t="s">
-        <v>1042</v>
+        <v>1040</v>
       </c>
       <c r="F199">
         <v>1</v>
       </c>
       <c r="G199"/>
       <c r="H199" s="11" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="200" spans="1:8">
       <c r="A200" t="s">
-        <v>936</v>
+        <v>934</v>
       </c>
       <c r="B200" t="s">
-        <v>1044</v>
+        <v>1042</v>
       </c>
       <c r="C200">
         <v>10</v>
@@ -8091,32 +8131,32 @@
         <v>0</v>
       </c>
       <c r="E200" t="s">
-        <v>1045</v>
+        <v>1043</v>
       </c>
       <c r="F200"/>
       <c r="G200"/>
       <c r="H200" s="11" t="s">
-        <v>1046</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="201" spans="1:8">
       <c r="A201" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
       <c r="B201" t="s">
-        <v>1047</v>
+        <v>1045</v>
       </c>
       <c r="C201"/>
       <c r="D201" s="11"/>
       <c r="E201" t="s">
-        <v>1048</v>
+        <v>1046</v>
       </c>
       <c r="F201">
         <v>1</v>
       </c>
       <c r="G201"/>
       <c r="H201" s="11" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="202" spans="1:8">
@@ -8220,15 +8260,15 @@
         <v>1</v>
       </c>
       <c r="H206" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
     </row>
     <row r="207" spans="1:8">
       <c r="A207" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="B207" s="12" t="s">
-        <v>1008</v>
+        <v>1006</v>
       </c>
       <c r="C207">
         <v>15</v>
@@ -8237,20 +8277,20 @@
         <v>0</v>
       </c>
       <c r="E207" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="F207"/>
       <c r="G207"/>
       <c r="H207" s="11" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="208" spans="1:8">
       <c r="A208" t="s">
-        <v>1011</v>
+        <v>1009</v>
       </c>
       <c r="B208" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="C208">
         <v>15</v>
@@ -8259,20 +8299,20 @@
         <v>0</v>
       </c>
       <c r="E208" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="F208"/>
       <c r="G208"/>
       <c r="H208" s="11" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="209" spans="1:8">
       <c r="A209" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
       <c r="B209" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
       <c r="C209">
         <v>15</v>
@@ -8281,20 +8321,20 @@
         <v>0</v>
       </c>
       <c r="E209" t="s">
-        <v>1017</v>
+        <v>1015</v>
       </c>
       <c r="F209"/>
       <c r="G209"/>
       <c r="H209" s="11" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="210" spans="1:8">
       <c r="A210" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="B210" t="s">
-        <v>1020</v>
+        <v>1018</v>
       </c>
       <c r="C210">
         <v>20</v>
@@ -8303,20 +8343,20 @@
         <v>0</v>
       </c>
       <c r="E210" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="F210"/>
       <c r="G210"/>
       <c r="H210" s="11" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="211" spans="1:8">
       <c r="A211" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="B211" s="12" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
       <c r="C211">
         <v>15</v>
@@ -8325,12 +8365,12 @@
         <v>0</v>
       </c>
       <c r="E211" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="F211"/>
       <c r="G211"/>
       <c r="H211" s="11" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="212" spans="1:8">
@@ -8457,7 +8497,7 @@
         <v>0</v>
       </c>
       <c r="E217" s="1" t="s">
-        <v>1027</v>
+        <v>1025</v>
       </c>
       <c r="F217" s="3"/>
       <c r="G217" s="1"/>
@@ -8467,7 +8507,7 @@
     </row>
     <row r="218" spans="1:8">
       <c r="A218" s="2" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="B218" s="1" t="s">
         <v>306</v>
@@ -8489,7 +8529,7 @@
     </row>
     <row r="219" spans="1:8">
       <c r="A219" s="2" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="B219" s="1" t="s">
         <v>483</v>
@@ -8509,7 +8549,7 @@
     </row>
     <row r="220" spans="1:8">
       <c r="A220" s="2" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="B220" s="1" t="s">
         <v>295</v>
@@ -8529,7 +8569,7 @@
     </row>
     <row r="221" spans="1:8">
       <c r="A221" s="2" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="B221" s="1" t="s">
         <v>296</v>
@@ -8561,7 +8601,7 @@
         <v>0</v>
       </c>
       <c r="E222" s="1" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="F222" s="3"/>
       <c r="G222" s="1"/>
@@ -8593,10 +8633,10 @@
     </row>
     <row r="224" spans="1:8">
       <c r="A224" s="2" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="B224" s="1" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="C224" s="2">
         <v>7</v>
@@ -8605,11 +8645,11 @@
         <v>0.95833333333333337</v>
       </c>
       <c r="E224" s="1" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="F224" s="3"/>
       <c r="H224" s="7" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
     </row>
     <row r="225" spans="1:8">
@@ -8731,7 +8771,7 @@
         <v>0</v>
       </c>
       <c r="E230" s="1" t="s">
-        <v>1028</v>
+        <v>1026</v>
       </c>
       <c r="F230" s="3"/>
       <c r="G230" s="1"/>
@@ -8785,10 +8825,10 @@
     </row>
     <row r="233" spans="1:8">
       <c r="A233" t="s">
-        <v>1029</v>
+        <v>1027</v>
       </c>
       <c r="B233" t="s">
-        <v>1030</v>
+        <v>1028</v>
       </c>
       <c r="C233">
         <v>6</v>
@@ -8797,27 +8837,35 @@
         <v>0</v>
       </c>
       <c r="E233" t="s">
-        <v>1031</v>
+        <v>1029</v>
       </c>
       <c r="F233"/>
       <c r="G233"/>
       <c r="H233" s="7" t="s">
+        <v>1030</v>
+      </c>
+    </row>
+    <row r="234" spans="1:8">
+      <c r="A234" s="11" t="s">
+        <v>1031</v>
+      </c>
+      <c r="B234" t="s">
         <v>1032</v>
       </c>
-    </row>
-    <row r="234" spans="1:8">
-      <c r="A234" t="s">
-        <v>1033</v>
-      </c>
-      <c r="B234" t="s">
-        <v>1034</v>
-      </c>
-      <c r="C234"/>
-      <c r="D234" s="11"/>
-      <c r="E234"/>
+      <c r="C234" s="3">
+        <v>7</v>
+      </c>
+      <c r="D234" s="4">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="E234" s="1" t="s">
+        <v>1049</v>
+      </c>
       <c r="F234"/>
       <c r="G234"/>
-      <c r="H234"/>
+      <c r="H234" s="7" t="s">
+        <v>1050</v>
+      </c>
     </row>
     <row r="235" spans="1:8">
       <c r="A235" s="2" t="s">
@@ -8865,22 +8913,22 @@
     </row>
     <row r="237" spans="1:8" customFormat="1">
       <c r="A237" s="2" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="B237" s="1" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="C237" s="2"/>
       <c r="D237" s="2"/>
       <c r="E237" s="1" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="F237" s="3">
         <v>1</v>
       </c>
       <c r="G237" s="2"/>
       <c r="H237" s="7" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
     </row>
     <row r="238" spans="1:8">
@@ -8967,24 +9015,24 @@
     </row>
     <row r="242" spans="1:8">
       <c r="A242" s="11" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="B242" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="C242"/>
       <c r="D242" s="11"/>
       <c r="E242" t="s">
+        <v>1035</v>
+      </c>
+      <c r="F242">
+        <v>1</v>
+      </c>
+      <c r="G242" t="s">
+        <v>1036</v>
+      </c>
+      <c r="H242" s="7" t="s">
         <v>1037</v>
-      </c>
-      <c r="F242">
-        <v>1</v>
-      </c>
-      <c r="G242" t="s">
-        <v>1038</v>
-      </c>
-      <c r="H242" s="7" t="s">
-        <v>1039</v>
       </c>
     </row>
     <row r="243" spans="1:8">
@@ -9001,7 +9049,7 @@
         <v>0.91666666666666663</v>
       </c>
       <c r="E243" s="1" t="s">
-        <v>291</v>
+        <v>1048</v>
       </c>
       <c r="F243" s="3"/>
       <c r="G243" s="1"/>
@@ -9011,36 +9059,36 @@
     </row>
     <row r="244" spans="1:8">
       <c r="A244" s="2" t="s">
+        <v>668</v>
+      </c>
+      <c r="B244" s="1" t="s">
         <v>670</v>
       </c>
-      <c r="B244" s="1" t="s">
+      <c r="E244" s="1" t="s">
         <v>672</v>
       </c>
-      <c r="E244" s="1" t="s">
-        <v>674</v>
-      </c>
       <c r="F244" s="2">
         <v>1</v>
       </c>
       <c r="H244" s="2" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
     </row>
     <row r="245" spans="1:8">
       <c r="A245" s="2" t="s">
+        <v>667</v>
+      </c>
+      <c r="B245" s="1" t="s">
         <v>669</v>
       </c>
-      <c r="B245" s="1" t="s">
+      <c r="E245" s="1" t="s">
         <v>671</v>
       </c>
-      <c r="E245" s="1" t="s">
-        <v>673</v>
-      </c>
       <c r="F245" s="2">
         <v>1</v>
       </c>
       <c r="H245" s="2" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
     </row>
     <row r="246" spans="1:8">
@@ -9057,7 +9105,7 @@
         <v>0</v>
       </c>
       <c r="E246" s="1" t="s">
-        <v>631</v>
+        <v>1052</v>
       </c>
       <c r="F246" s="3"/>
       <c r="G246" s="1"/>
@@ -9079,7 +9127,7 @@
         <v>0</v>
       </c>
       <c r="E247" s="1" t="s">
-        <v>630</v>
+        <v>1051</v>
       </c>
       <c r="F247" s="3"/>
       <c r="G247" s="1"/>
@@ -9353,10 +9401,10 @@
     </row>
     <row r="260" spans="1:8">
       <c r="A260" s="2" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="B260" s="1" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="C260" s="2">
         <v>6</v>
@@ -9365,11 +9413,11 @@
         <v>0</v>
       </c>
       <c r="E260" s="1" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="F260" s="3"/>
       <c r="H260" s="7" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
     </row>
     <row r="261" spans="1:8">
@@ -9412,7 +9460,7 @@
       <c r="F262" s="3"/>
       <c r="G262" s="1"/>
       <c r="H262" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
     </row>
     <row r="263" spans="1:8">
@@ -9439,10 +9487,10 @@
     </row>
     <row r="264" spans="1:8">
       <c r="A264" s="2" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="B264" s="1" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="C264" s="2">
         <v>6</v>
@@ -9451,19 +9499,19 @@
         <v>0</v>
       </c>
       <c r="E264" s="1" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="F264" s="3"/>
       <c r="H264" s="7" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
     </row>
     <row r="265" spans="1:8">
       <c r="A265" s="2" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="B265" s="1" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="C265" s="2">
         <v>6</v>
@@ -9472,19 +9520,19 @@
         <v>0</v>
       </c>
       <c r="E265" s="10" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="F265" s="3"/>
       <c r="H265" s="2" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
     </row>
     <row r="266" spans="1:8">
       <c r="A266" s="2" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="B266" s="1" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="C266" s="2">
         <v>6</v>
@@ -9493,19 +9541,19 @@
         <v>0</v>
       </c>
       <c r="E266" s="1" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="F266" s="3"/>
       <c r="H266" s="2" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
     </row>
     <row r="267" spans="1:8">
       <c r="A267" s="2" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="B267" s="1" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="C267" s="2">
         <v>6</v>
@@ -9514,16 +9562,16 @@
         <v>0</v>
       </c>
       <c r="E267" s="1" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="F267" s="3"/>
       <c r="H267" s="2" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
     </row>
     <row r="268" spans="1:8">
       <c r="A268" s="2" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="B268" s="1" t="s">
         <v>512</v>
@@ -9531,16 +9579,16 @@
       <c r="C268" s="3"/>
       <c r="D268" s="6"/>
       <c r="E268" s="1" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="F268" s="3">
         <v>1</v>
       </c>
       <c r="G268" s="2" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="H268" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
     </row>
     <row r="269" spans="1:8">
@@ -9623,7 +9671,7 @@
         <v>0.97916666666666663</v>
       </c>
       <c r="E272" s="1" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="F272" s="3"/>
       <c r="G272" s="1"/>
@@ -9645,7 +9693,7 @@
         <v>0</v>
       </c>
       <c r="E273" s="1" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="F273" s="3"/>
       <c r="G273" s="1"/>
@@ -10109,8 +10157,19 @@
         <v>1</v>
       </c>
       <c r="G294" s="1"/>
-      <c r="H294" s="13" t="s">
+      <c r="H294" s="14" t="s">
         <v>623</v>
+      </c>
+    </row>
+    <row r="295" spans="1:8">
+      <c r="A295" t="s">
+        <v>1055</v>
+      </c>
+      <c r="B295" s="1" t="s">
+        <v>1056</v>
+      </c>
+      <c r="H295" s="2" t="s">
+        <v>1054</v>
       </c>
     </row>
   </sheetData>
@@ -10134,8 +10193,10 @@
     <hyperlink ref="H91" r:id="rId13" xr:uid="{C22B731B-9B71-4E64-B35B-0DA8918E1D6C}"/>
     <hyperlink ref="H233" r:id="rId14" xr:uid="{9F031169-FBE6-490D-BE8C-7652770F2FC7}"/>
     <hyperlink ref="H242" r:id="rId15" xr:uid="{8A0F8F21-47D9-40AB-B76D-AB1080B92C60}"/>
+    <hyperlink ref="H234" r:id="rId16" xr:uid="{D68E4B30-7851-4C83-872C-73CB17EC5222}"/>
+    <hyperlink ref="H16" r:id="rId17" xr:uid="{D73F1000-43A8-440E-9154-148CA29F608D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId16"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId18"/>
 </worksheet>
 </file>
--- a/stores.xlsx
+++ b/stores.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\YUMIN\Desktop\B0KT2A_RSVN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{63FC8947-054D-42B6-85DD-2FBFC650840B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D48EB21F-E98A-4FDA-B699-B492D70B591C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{ABFC3117-FCCB-4FF3-804A-FE19451A2004}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1196" uniqueCount="1068">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1270" uniqueCount="1141">
   <si>
     <t>룸익스케이프 WHITE</t>
   </si>
@@ -3701,6 +3701,281 @@
   </si>
   <si>
     <t>비밀의 화원 포레스트건대점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>미씽스노우맨,더데이,새벽베이커리,라스트잡</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cc_hd</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>시크릿코드 홍대점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>백마교의최후,제페토,독립군,조난자들,미션이지,미션하드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://www.s-code.co.kr/</t>
+  </si>
+  <si>
+    <t>플레이아레나 홍대점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pa_hd</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://naver.me/GVELNSpA</t>
+  </si>
+  <si>
+    <t>풀리지 않는 49칸의 수수께끼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>방탈출 이스케이프 하우스</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>살인호텔,임파서블,미드나이트,사라진목소리,3인의저주</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://www.escapehouse.co.kr/</t>
+  </si>
+  <si>
+    <t>Decoder</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tempo Rubato,템포루바토,템루,furious revenge,남자방,퓨리어스리벤지,퓨리오스리벤지,여자방,introverted thief</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>라스트 이스케이프</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>d_coder</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>last_esc</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>esc_hus</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ALCATRAZ,알카트라즈,SECRETARY,비서,오감,CLUB LE7ELS,클럽레벨스,CLUBLEVELS,五感</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://lastescape.co.kr/</t>
+  </si>
+  <si>
+    <t>http://decoder.kr/</t>
+  </si>
+  <si>
+    <t>에피소드 방탈출 강남점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>귀문기담,메아리,그래서님몇방?,그님몇</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>쿠쿠룸 1089</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>신비로운 직원생활, 실직요정 비상대책위원회,백순대,쿠쿠마스터</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ccr_1089</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>epsd_gn</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://naver.me/FZ2CmMn8</t>
+  </si>
+  <si>
+    <t>epsd_sh</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>에피소드 방탈출 분당점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>솔버 1호점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>솔버 2호점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>방탈출 ESC</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이스케이프시티 그랜드시티 신촌점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>탐정크루 신촌2호점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>시크릿 챔버</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>에필로그</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>상상락원</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>파노라마X롯데월드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>파란</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>더메이즈 노원점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>더트랩 수유점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>더파인더 방탈출</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>알카트래즈</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>월투월방탈출 서울대입구점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이스케이프시티 성신여대점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이스케이프시티 영등포점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>탈출 브라더스</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>패닉이스케이프 목동점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>호텔 레토 성수</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>큐브이스케이프 홍대점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>큐브이스케이프 인천구월점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>큐브이스케이프 전주점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>큐브이스케이프 대전둔산점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>큐브이스케이프 수유점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>deliver,딜리버,좀비스쿨,피고인,헨젤과그레텔,제시의시크릿,피라미드의비밀,신데렐라,집착</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>장기밀매,신데렐라,집착,마션,타이타닉,카타콤,통곡의문</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cb_hd</t>
+  </si>
+  <si>
+    <t>cb_jj</t>
+  </si>
+  <si>
+    <t>cb_dj</t>
+  </si>
+  <si>
+    <t>cb_sy</t>
+  </si>
+  <si>
+    <t>피라미드의 비밀,헨젤과그레텔,towering,타워링,gestapo,게슈타포,게스타포,monkeyhouse,몽키하우스,장기밀매,deliver,딜리버,romeo point,로미오포인트</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>타이타닉,신데렐라,장기밀매,towering,타워링,집착</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cb_ic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>우든펍의비밀,빅토리아호의침몰,거미의둥지,골든아이,the cube,더큐브,사라진천사들,stepfather,마녀의꿈,piggies,집착,트레저헌터,트레져헌터,obsession,treasure hunters</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://suyu.cubeescape.co.kr/</t>
+  </si>
+  <si>
+    <t>http://daejeon.cubeescape.co.kr/</t>
+  </si>
+  <si>
+    <t>http://junju.cubeescape.co.kr/</t>
+  </si>
+  <si>
+    <t>http://incheon.cubeescape.co.kr/</t>
+  </si>
+  <si>
+    <t>http://cubeescape.co.kr/</t>
+  </si>
+  <si>
+    <t>https://naver.me/GJTSSEZr</t>
+  </si>
+  <si>
+    <t>https://naver.me/G65wsmnX</t>
+  </si>
+  <si>
+    <t>소녀괴담,파파라치,이레이저,럭키가이,데이드림</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3781,7 +4056,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3813,17 +4088,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -4139,15 +4403,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D839462D-4719-40BB-8925-C1B9F93734CF}">
-  <dimension ref="A1:H297"/>
+  <dimension ref="A1:H329"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="2"/>
-    <col min="2" max="2" width="25.375" style="17" customWidth="1"/>
+    <col min="2" max="2" width="25.375" style="2" customWidth="1"/>
     <col min="3" max="4" width="9" style="2" customWidth="1"/>
     <col min="5" max="5" width="85.875" style="2" customWidth="1"/>
     <col min="6" max="6" width="9" style="2" customWidth="1"/>
-    <col min="7" max="7" width="16.875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="5" style="2" customWidth="1"/>
     <col min="8" max="8" width="62.75" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="16384" width="9" style="2"/>
   </cols>
@@ -4156,7 +4420,7 @@
       <c r="A1" s="2" t="s">
         <v>329</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C1" s="1" t="s">
@@ -4182,7 +4446,7 @@
       <c r="A2" s="2" t="s">
         <v>639</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="1" t="s">
         <v>636</v>
       </c>
       <c r="C2" s="2">
@@ -4202,7 +4466,7 @@
       <c r="A3" s="2" t="s">
         <v>828</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="1" t="s">
         <v>829</v>
       </c>
       <c r="C3" s="2">
@@ -4222,7 +4486,7 @@
       <c r="A4" s="2" t="s">
         <v>831</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="1" t="s">
         <v>832</v>
       </c>
       <c r="C4" s="2">
@@ -4239,7 +4503,7 @@
       <c r="A5" s="2" t="s">
         <v>330</v>
       </c>
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="1" t="s">
         <v>317</v>
       </c>
       <c r="C5" s="3">
@@ -4261,7 +4525,7 @@
       <c r="A6" s="2" t="s">
         <v>331</v>
       </c>
-      <c r="B6" s="13" t="s">
+      <c r="B6" s="1" t="s">
         <v>268</v>
       </c>
       <c r="C6" s="3">
@@ -4283,7 +4547,7 @@
       <c r="A7" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="B7" s="13" t="s">
+      <c r="B7" s="1" t="s">
         <v>137</v>
       </c>
       <c r="C7" s="3"/>
@@ -4303,7 +4567,7 @@
       <c r="A8" s="2" t="s">
         <v>333</v>
       </c>
-      <c r="B8" s="13" t="s">
+      <c r="B8" s="1" t="s">
         <v>262</v>
       </c>
       <c r="C8" s="3">
@@ -4325,7 +4589,7 @@
       <c r="A9" s="2" t="s">
         <v>334</v>
       </c>
-      <c r="B9" s="13" t="s">
+      <c r="B9" s="1" t="s">
         <v>263</v>
       </c>
       <c r="C9" s="3">
@@ -4347,7 +4611,7 @@
       <c r="A10" s="2" t="s">
         <v>335</v>
       </c>
-      <c r="B10" s="13" t="s">
+      <c r="B10" s="1" t="s">
         <v>133</v>
       </c>
       <c r="C10" s="3">
@@ -4369,7 +4633,7 @@
       <c r="A11" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="B11" s="13" t="s">
+      <c r="B11" s="1" t="s">
         <v>135</v>
       </c>
       <c r="C11" s="3">
@@ -4391,7 +4655,7 @@
       <c r="A12" s="2" t="s">
         <v>337</v>
       </c>
-      <c r="B12" s="13" t="s">
+      <c r="B12" s="1" t="s">
         <v>233</v>
       </c>
       <c r="C12" s="3">
@@ -4413,7 +4677,7 @@
       <c r="A13" s="2" t="s">
         <v>338</v>
       </c>
-      <c r="B13" s="13" t="s">
+      <c r="B13" s="1" t="s">
         <v>234</v>
       </c>
       <c r="C13" s="3">
@@ -4435,7 +4699,7 @@
       <c r="A14" s="2" t="s">
         <v>339</v>
       </c>
-      <c r="B14" s="13" t="s">
+      <c r="B14" s="1" t="s">
         <v>235</v>
       </c>
       <c r="C14" s="3">
@@ -4457,7 +4721,7 @@
       <c r="A15" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="B15" s="13" t="s">
+      <c r="B15" s="1" t="s">
         <v>230</v>
       </c>
       <c r="C15" s="3">
@@ -4479,7 +4743,7 @@
       <c r="A16" s="2" t="s">
         <v>341</v>
       </c>
-      <c r="B16" s="13" t="s">
+      <c r="B16" s="1" t="s">
         <v>231</v>
       </c>
       <c r="C16" s="3">
@@ -4501,7 +4765,7 @@
       <c r="A17" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="B17" s="13" t="s">
+      <c r="B17" s="1" t="s">
         <v>212</v>
       </c>
       <c r="C17" s="3">
@@ -4523,7 +4787,7 @@
       <c r="A18" s="2" t="s">
         <v>343</v>
       </c>
-      <c r="B18" s="13" t="s">
+      <c r="B18" s="1" t="s">
         <v>81</v>
       </c>
       <c r="C18" s="3">
@@ -4545,7 +4809,7 @@
       <c r="A19" s="2" t="s">
         <v>344</v>
       </c>
-      <c r="B19" s="13" t="s">
+      <c r="B19" s="1" t="s">
         <v>83</v>
       </c>
       <c r="C19" s="3">
@@ -4567,7 +4831,7 @@
       <c r="A20" s="2" t="s">
         <v>345</v>
       </c>
-      <c r="B20" s="13" t="s">
+      <c r="B20" s="1" t="s">
         <v>85</v>
       </c>
       <c r="C20" s="3">
@@ -4589,7 +4853,7 @@
       <c r="A21" s="2" t="s">
         <v>346</v>
       </c>
-      <c r="B21" s="13" t="s">
+      <c r="B21" s="1" t="s">
         <v>79</v>
       </c>
       <c r="C21" s="3">
@@ -4611,7 +4875,7 @@
       <c r="A22" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="B22" s="13" t="s">
+      <c r="B22" s="1" t="s">
         <v>324</v>
       </c>
       <c r="C22" s="3"/>
@@ -4631,7 +4895,7 @@
       <c r="A23" s="2" t="s">
         <v>348</v>
       </c>
-      <c r="B23" s="13" t="s">
+      <c r="B23" s="1" t="s">
         <v>77</v>
       </c>
       <c r="C23" s="3">
@@ -4653,7 +4917,7 @@
       <c r="A24" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="B24" s="13" t="s">
+      <c r="B24" s="1" t="s">
         <v>75</v>
       </c>
       <c r="C24" s="3">
@@ -4675,7 +4939,7 @@
       <c r="A25" s="2" t="s">
         <v>833</v>
       </c>
-      <c r="B25" s="13" t="s">
+      <c r="B25" s="1" t="s">
         <v>834</v>
       </c>
       <c r="C25" s="3">
@@ -4697,7 +4961,7 @@
       <c r="A26" s="2" t="s">
         <v>439</v>
       </c>
-      <c r="B26" s="13" t="s">
+      <c r="B26" s="1" t="s">
         <v>437</v>
       </c>
       <c r="C26" s="3">
@@ -4718,7 +4982,7 @@
       <c r="A27" s="2" t="s">
         <v>438</v>
       </c>
-      <c r="B27" s="13" t="s">
+      <c r="B27" s="1" t="s">
         <v>436</v>
       </c>
       <c r="C27" s="3">
@@ -4739,7 +5003,7 @@
       <c r="A28" s="2" t="s">
         <v>350</v>
       </c>
-      <c r="B28" s="13" t="s">
+      <c r="B28" s="1" t="s">
         <v>138</v>
       </c>
       <c r="C28" s="3">
@@ -4761,7 +5025,7 @@
       <c r="A29" s="2" t="s">
         <v>351</v>
       </c>
-      <c r="B29" s="13" t="s">
+      <c r="B29" s="1" t="s">
         <v>140</v>
       </c>
       <c r="C29" s="3">
@@ -4783,7 +5047,7 @@
       <c r="A30" s="2" t="s">
         <v>791</v>
       </c>
-      <c r="B30" s="13" t="s">
+      <c r="B30" s="1" t="s">
         <v>792</v>
       </c>
       <c r="E30" s="1" t="s">
@@ -4800,7 +5064,7 @@
       <c r="A31" s="2" t="s">
         <v>803</v>
       </c>
-      <c r="B31" s="13" t="s">
+      <c r="B31" s="1" t="s">
         <v>805</v>
       </c>
       <c r="C31" s="2">
@@ -4820,7 +5084,7 @@
       <c r="A32" s="2" t="s">
         <v>778</v>
       </c>
-      <c r="B32" s="13" t="s">
+      <c r="B32" s="1" t="s">
         <v>779</v>
       </c>
       <c r="E32" s="1" t="s">
@@ -4837,7 +5101,7 @@
       <c r="A33" s="2" t="s">
         <v>774</v>
       </c>
-      <c r="B33" s="13" t="s">
+      <c r="B33" s="1" t="s">
         <v>775</v>
       </c>
       <c r="E33" s="1" t="s">
@@ -4854,7 +5118,7 @@
       <c r="A34" s="2" t="s">
         <v>785</v>
       </c>
-      <c r="B34" s="13" t="s">
+      <c r="B34" s="1" t="s">
         <v>786</v>
       </c>
       <c r="E34" s="1" t="s">
@@ -4871,7 +5135,7 @@
       <c r="A35" s="2" t="s">
         <v>799</v>
       </c>
-      <c r="B35" s="13" t="s">
+      <c r="B35" s="1" t="s">
         <v>800</v>
       </c>
       <c r="E35" s="1" t="s">
@@ -4888,7 +5152,7 @@
       <c r="A36" s="2" t="s">
         <v>795</v>
       </c>
-      <c r="B36" s="13" t="s">
+      <c r="B36" s="1" t="s">
         <v>796</v>
       </c>
       <c r="E36" s="1" t="s">
@@ -4905,7 +5169,7 @@
       <c r="A37" s="2" t="s">
         <v>782</v>
       </c>
-      <c r="B37" s="13" t="s">
+      <c r="B37" s="1" t="s">
         <v>783</v>
       </c>
       <c r="E37" s="1" t="s">
@@ -4922,7 +5186,7 @@
       <c r="A38" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="B38" s="13" t="s">
+      <c r="B38" s="1" t="s">
         <v>322</v>
       </c>
       <c r="C38" s="3">
@@ -4944,7 +5208,7 @@
       <c r="A39" s="2" t="s">
         <v>689</v>
       </c>
-      <c r="B39" s="13" t="s">
+      <c r="B39" s="1" t="s">
         <v>690</v>
       </c>
       <c r="E39" s="1" t="s">
@@ -4961,7 +5225,7 @@
       <c r="A40" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="B40" s="13" t="s">
+      <c r="B40" s="1" t="s">
         <v>692</v>
       </c>
       <c r="E40" s="1" t="s">
@@ -4978,7 +5242,7 @@
       <c r="A41" s="2" t="s">
         <v>379</v>
       </c>
-      <c r="B41" s="13" t="s">
+      <c r="B41" s="1" t="s">
         <v>454</v>
       </c>
       <c r="E41" s="1" t="s">
@@ -4992,7 +5256,7 @@
       <c r="A42" s="2" t="s">
         <v>353</v>
       </c>
-      <c r="B42" s="13" t="s">
+      <c r="B42" s="1" t="s">
         <v>141</v>
       </c>
       <c r="C42" s="3">
@@ -5014,7 +5278,7 @@
       <c r="A43" s="2" t="s">
         <v>354</v>
       </c>
-      <c r="B43" s="13" t="s">
+      <c r="B43" s="1" t="s">
         <v>153</v>
       </c>
       <c r="C43" s="3"/>
@@ -5034,7 +5298,7 @@
       <c r="A44" s="2" t="s">
         <v>355</v>
       </c>
-      <c r="B44" s="13" t="s">
+      <c r="B44" s="1" t="s">
         <v>155</v>
       </c>
       <c r="C44" s="3">
@@ -5056,7 +5320,7 @@
       <c r="A45" s="2" t="s">
         <v>356</v>
       </c>
-      <c r="B45" s="13" t="s">
+      <c r="B45" s="1" t="s">
         <v>143</v>
       </c>
       <c r="C45" s="3">
@@ -5078,7 +5342,7 @@
       <c r="A46" s="2" t="s">
         <v>357</v>
       </c>
-      <c r="B46" s="13" t="s">
+      <c r="B46" s="1" t="s">
         <v>145</v>
       </c>
       <c r="C46" s="3">
@@ -5100,7 +5364,7 @@
       <c r="A47" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="B47" s="13" t="s">
+      <c r="B47" s="1" t="s">
         <v>151</v>
       </c>
       <c r="C47" s="3"/>
@@ -5120,7 +5384,7 @@
       <c r="A48" s="2" t="s">
         <v>359</v>
       </c>
-      <c r="B48" s="13" t="s">
+      <c r="B48" s="1" t="s">
         <v>149</v>
       </c>
       <c r="C48" s="3"/>
@@ -5140,7 +5404,7 @@
       <c r="A49" s="2" t="s">
         <v>360</v>
       </c>
-      <c r="B49" s="13" t="s">
+      <c r="B49" s="1" t="s">
         <v>147</v>
       </c>
       <c r="C49" s="3">
@@ -5162,7 +5426,7 @@
       <c r="A50" s="2" t="s">
         <v>361</v>
       </c>
-      <c r="B50" s="13" t="s">
+      <c r="B50" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C50" s="3">
@@ -5184,7 +5448,7 @@
       <c r="A51" s="2" t="s">
         <v>362</v>
       </c>
-      <c r="B51" s="13" t="s">
+      <c r="B51" s="1" t="s">
         <v>246</v>
       </c>
       <c r="C51" s="3">
@@ -5206,7 +5470,7 @@
       <c r="A52" s="2" t="s">
         <v>363</v>
       </c>
-      <c r="B52" s="13" t="s">
+      <c r="B52" s="1" t="s">
         <v>248</v>
       </c>
       <c r="C52" s="3">
@@ -5228,7 +5492,7 @@
       <c r="A53" s="2" t="s">
         <v>364</v>
       </c>
-      <c r="B53" s="13" t="s">
+      <c r="B53" s="1" t="s">
         <v>250</v>
       </c>
       <c r="C53" s="3">
@@ -5250,7 +5514,7 @@
       <c r="A54" s="2" t="s">
         <v>365</v>
       </c>
-      <c r="B54" s="13" t="s">
+      <c r="B54" s="1" t="s">
         <v>125</v>
       </c>
       <c r="C54" s="3">
@@ -5272,7 +5536,7 @@
       <c r="A55" s="2" t="s">
         <v>366</v>
       </c>
-      <c r="B55" s="13" t="s">
+      <c r="B55" s="1" t="s">
         <v>293</v>
       </c>
       <c r="C55" s="1">
@@ -5294,7 +5558,7 @@
       <c r="A56" s="2" t="s">
         <v>367</v>
       </c>
-      <c r="B56" s="13" t="s">
+      <c r="B56" s="1" t="s">
         <v>252</v>
       </c>
       <c r="C56" s="1"/>
@@ -5316,7 +5580,7 @@
       <c r="A57" t="s">
         <v>677</v>
       </c>
-      <c r="B57" s="13" t="s">
+      <c r="B57" s="1" t="s">
         <v>642</v>
       </c>
       <c r="E57" s="1" t="s">
@@ -5330,7 +5594,7 @@
       <c r="A58" t="s">
         <v>678</v>
       </c>
-      <c r="B58" s="13" t="s">
+      <c r="B58" s="1" t="s">
         <v>643</v>
       </c>
       <c r="E58" s="1" t="s">
@@ -5347,7 +5611,7 @@
       <c r="A59" t="s">
         <v>679</v>
       </c>
-      <c r="B59" s="13" t="s">
+      <c r="B59" s="1" t="s">
         <v>644</v>
       </c>
       <c r="C59" s="3"/>
@@ -5369,7 +5633,7 @@
       <c r="A60" s="2" t="s">
         <v>368</v>
       </c>
-      <c r="B60" s="13" t="s">
+      <c r="B60" s="1" t="s">
         <v>127</v>
       </c>
       <c r="C60" s="3">
@@ -5391,7 +5655,7 @@
       <c r="A61" s="11" t="s">
         <v>837</v>
       </c>
-      <c r="B61" s="14" t="s">
+      <c r="B61" t="s">
         <v>838</v>
       </c>
       <c r="C61">
@@ -5413,7 +5677,7 @@
       <c r="A62" s="2" t="s">
         <v>369</v>
       </c>
-      <c r="B62" s="13" t="s">
+      <c r="B62" s="1" t="s">
         <v>302</v>
       </c>
       <c r="C62" s="3">
@@ -5435,7 +5699,7 @@
       <c r="A63" s="2" t="s">
         <v>370</v>
       </c>
-      <c r="B63" s="13" t="s">
+      <c r="B63" s="1" t="s">
         <v>301</v>
       </c>
       <c r="C63" s="3"/>
@@ -5455,7 +5719,7 @@
       <c r="A64" s="2" t="s">
         <v>371</v>
       </c>
-      <c r="B64" s="13" t="s">
+      <c r="B64" s="1" t="s">
         <v>291</v>
       </c>
       <c r="C64" s="3">
@@ -5477,7 +5741,7 @@
       <c r="A65" s="2" t="s">
         <v>372</v>
       </c>
-      <c r="B65" s="13" t="s">
+      <c r="B65" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C65" s="3">
@@ -5499,7 +5763,7 @@
       <c r="A66" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="B66" s="13" t="s">
+      <c r="B66" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C66" s="3">
@@ -5521,7 +5785,7 @@
       <c r="A67" s="2" t="s">
         <v>374</v>
       </c>
-      <c r="B67" s="13" t="s">
+      <c r="B67" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C67" s="3">
@@ -5543,7 +5807,7 @@
       <c r="A68" s="2" t="s">
         <v>375</v>
       </c>
-      <c r="B68" s="13" t="s">
+      <c r="B68" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C68" s="3">
@@ -5565,7 +5829,7 @@
       <c r="A69" s="2" t="s">
         <v>376</v>
       </c>
-      <c r="B69" s="13" t="s">
+      <c r="B69" s="1" t="s">
         <v>261</v>
       </c>
       <c r="C69" s="3">
@@ -5586,7 +5850,7 @@
       <c r="A70" s="2" t="s">
         <v>654</v>
       </c>
-      <c r="B70" s="13" t="s">
+      <c r="B70" s="1" t="s">
         <v>181</v>
       </c>
       <c r="C70" s="3"/>
@@ -5605,7 +5869,7 @@
       <c r="A71" t="s">
         <v>671</v>
       </c>
-      <c r="B71" s="13" t="s">
+      <c r="B71" s="1" t="s">
         <v>264</v>
       </c>
       <c r="C71" s="3"/>
@@ -5624,7 +5888,7 @@
       <c r="A72" t="s">
         <v>672</v>
       </c>
-      <c r="B72" s="13" t="s">
+      <c r="B72" s="1" t="s">
         <v>179</v>
       </c>
       <c r="C72" s="3"/>
@@ -5643,7 +5907,7 @@
       <c r="A73" t="s">
         <v>657</v>
       </c>
-      <c r="B73" s="13" t="s">
+      <c r="B73" s="1" t="s">
         <v>185</v>
       </c>
       <c r="C73" s="3">
@@ -5664,7 +5928,7 @@
       <c r="A74" s="2" t="s">
         <v>658</v>
       </c>
-      <c r="B74" s="13" t="s">
+      <c r="B74" s="1" t="s">
         <v>183</v>
       </c>
       <c r="C74" s="3">
@@ -5685,7 +5949,7 @@
       <c r="A75" t="s">
         <v>659</v>
       </c>
-      <c r="B75" s="13" t="s">
+      <c r="B75" s="1" t="s">
         <v>171</v>
       </c>
       <c r="C75" s="3"/>
@@ -5704,7 +5968,7 @@
       <c r="A76" t="s">
         <v>660</v>
       </c>
-      <c r="B76" s="13" t="s">
+      <c r="B76" s="1" t="s">
         <v>173</v>
       </c>
       <c r="C76" s="3"/>
@@ -5723,7 +5987,7 @@
       <c r="A77" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="B77" s="13" t="s">
+      <c r="B77" s="1" t="s">
         <v>157</v>
       </c>
       <c r="C77" s="3"/>
@@ -5742,7 +6006,7 @@
       <c r="A78" t="s">
         <v>675</v>
       </c>
-      <c r="B78" s="13" t="s">
+      <c r="B78" s="1" t="s">
         <v>187</v>
       </c>
       <c r="C78" s="3">
@@ -5763,7 +6027,7 @@
       <c r="A79" t="s">
         <v>673</v>
       </c>
-      <c r="B79" s="13" t="s">
+      <c r="B79" s="1" t="s">
         <v>175</v>
       </c>
       <c r="C79" s="3"/>
@@ -5782,7 +6046,7 @@
       <c r="A80" t="s">
         <v>674</v>
       </c>
-      <c r="B80" s="13" t="s">
+      <c r="B80" s="1" t="s">
         <v>177</v>
       </c>
       <c r="C80" s="3">
@@ -5803,7 +6067,7 @@
       <c r="A81" s="2" t="s">
         <v>640</v>
       </c>
-      <c r="B81" s="13" t="s">
+      <c r="B81" s="1" t="s">
         <v>193</v>
       </c>
       <c r="C81" s="3">
@@ -5824,7 +6088,7 @@
       <c r="A82" s="2" t="s">
         <v>641</v>
       </c>
-      <c r="B82" s="13" t="s">
+      <c r="B82" s="1" t="s">
         <v>191</v>
       </c>
       <c r="C82" s="3">
@@ -5845,7 +6109,7 @@
       <c r="A83" s="2" t="s">
         <v>655</v>
       </c>
-      <c r="B83" s="13" t="s">
+      <c r="B83" s="1" t="s">
         <v>169</v>
       </c>
       <c r="C83" s="3">
@@ -5866,7 +6130,7 @@
       <c r="A84" s="2" t="s">
         <v>656</v>
       </c>
-      <c r="B84" s="13" t="s">
+      <c r="B84" s="1" t="s">
         <v>167</v>
       </c>
       <c r="C84" s="3"/>
@@ -5885,7 +6149,7 @@
       <c r="A85" t="s">
         <v>661</v>
       </c>
-      <c r="B85" s="13" t="s">
+      <c r="B85" s="1" t="s">
         <v>159</v>
       </c>
       <c r="C85" s="3"/>
@@ -5904,7 +6168,7 @@
       <c r="A86" t="s">
         <v>662</v>
       </c>
-      <c r="B86" s="13" t="s">
+      <c r="B86" s="1" t="s">
         <v>165</v>
       </c>
       <c r="C86" s="3"/>
@@ -5923,7 +6187,7 @@
       <c r="A87" t="s">
         <v>663</v>
       </c>
-      <c r="B87" s="13" t="s">
+      <c r="B87" s="1" t="s">
         <v>163</v>
       </c>
       <c r="C87" s="3"/>
@@ -5942,7 +6206,7 @@
       <c r="A88" t="s">
         <v>664</v>
       </c>
-      <c r="B88" s="13" t="s">
+      <c r="B88" s="1" t="s">
         <v>161</v>
       </c>
       <c r="C88" s="3"/>
@@ -5961,7 +6225,7 @@
       <c r="A89" t="s">
         <v>676</v>
       </c>
-      <c r="B89" s="13" t="s">
+      <c r="B89" s="1" t="s">
         <v>189</v>
       </c>
       <c r="C89" s="3">
@@ -5982,7 +6246,7 @@
       <c r="A90" t="s">
         <v>840</v>
       </c>
-      <c r="B90" s="14" t="s">
+      <c r="B90" t="s">
         <v>841</v>
       </c>
       <c r="C90" s="3"/>
@@ -6001,7 +6265,7 @@
       <c r="A91" s="2" t="s">
         <v>823</v>
       </c>
-      <c r="B91" s="13" t="s">
+      <c r="B91" s="1" t="s">
         <v>824</v>
       </c>
       <c r="E91" s="1" t="s">
@@ -6018,7 +6282,7 @@
       <c r="A92" s="2" t="s">
         <v>472</v>
       </c>
-      <c r="B92" s="13" t="s">
+      <c r="B92" s="1" t="s">
         <v>98</v>
       </c>
       <c r="C92" s="3">
@@ -6040,7 +6304,7 @@
       <c r="A93" s="2" t="s">
         <v>476</v>
       </c>
-      <c r="B93" s="13" t="s">
+      <c r="B93" s="1" t="s">
         <v>487</v>
       </c>
       <c r="C93" s="3">
@@ -6062,7 +6326,7 @@
       <c r="A94" s="2" t="s">
         <v>477</v>
       </c>
-      <c r="B94" s="13" t="s">
+      <c r="B94" s="1" t="s">
         <v>106</v>
       </c>
       <c r="C94" s="3">
@@ -6084,7 +6348,7 @@
       <c r="A95" s="2" t="s">
         <v>478</v>
       </c>
-      <c r="B95" s="13" t="s">
+      <c r="B95" s="1" t="s">
         <v>112</v>
       </c>
       <c r="C95" s="3">
@@ -6106,7 +6370,7 @@
       <c r="A96" s="2" t="s">
         <v>473</v>
       </c>
-      <c r="B96" s="13" t="s">
+      <c r="B96" s="1" t="s">
         <v>488</v>
       </c>
       <c r="C96" s="3">
@@ -6128,7 +6392,7 @@
       <c r="A97" s="2" t="s">
         <v>474</v>
       </c>
-      <c r="B97" s="13" t="s">
+      <c r="B97" s="1" t="s">
         <v>489</v>
       </c>
       <c r="C97" s="3">
@@ -6150,7 +6414,7 @@
       <c r="A98" s="2" t="s">
         <v>475</v>
       </c>
-      <c r="B98" s="13" t="s">
+      <c r="B98" s="1" t="s">
         <v>492</v>
       </c>
       <c r="C98" s="3">
@@ -6172,7 +6436,7 @@
       <c r="A99" s="2" t="s">
         <v>731</v>
       </c>
-      <c r="B99" s="13" t="s">
+      <c r="B99" s="1" t="s">
         <v>732</v>
       </c>
       <c r="E99" s="1" t="s">
@@ -6189,7 +6453,7 @@
       <c r="A100" s="2" t="s">
         <v>730</v>
       </c>
-      <c r="B100" s="13" t="s">
+      <c r="B100" s="1" t="s">
         <v>701</v>
       </c>
       <c r="E100" s="1" t="s">
@@ -6206,7 +6470,7 @@
       <c r="A101" s="2" t="s">
         <v>715</v>
       </c>
-      <c r="B101" s="13" t="s">
+      <c r="B101" s="1" t="s">
         <v>717</v>
       </c>
       <c r="E101" s="1" t="s">
@@ -6223,7 +6487,7 @@
       <c r="A102" s="2" t="s">
         <v>720</v>
       </c>
-      <c r="B102" s="13" t="s">
+      <c r="B102" s="1" t="s">
         <v>721</v>
       </c>
       <c r="E102" s="1" t="s">
@@ -6240,7 +6504,7 @@
       <c r="A103" s="2" t="s">
         <v>718</v>
       </c>
-      <c r="B103" s="13" t="s">
+      <c r="B103" s="1" t="s">
         <v>719</v>
       </c>
       <c r="E103" s="1" t="s">
@@ -6257,7 +6521,7 @@
       <c r="A104" s="2" t="s">
         <v>716</v>
       </c>
-      <c r="B104" s="13" t="s">
+      <c r="B104" s="1" t="s">
         <v>714</v>
       </c>
       <c r="E104" s="1" t="s">
@@ -6274,7 +6538,7 @@
       <c r="A105" s="2" t="s">
         <v>724</v>
       </c>
-      <c r="B105" s="13" t="s">
+      <c r="B105" s="1" t="s">
         <v>725</v>
       </c>
       <c r="E105" s="1" t="s">
@@ -6291,7 +6555,7 @@
       <c r="A106" s="2" t="s">
         <v>728</v>
       </c>
-      <c r="B106" s="13" t="s">
+      <c r="B106" s="1" t="s">
         <v>729</v>
       </c>
       <c r="E106" s="1" t="s">
@@ -6308,7 +6572,7 @@
       <c r="A107" s="2" t="s">
         <v>710</v>
       </c>
-      <c r="B107" s="13" t="s">
+      <c r="B107" s="1" t="s">
         <v>711</v>
       </c>
       <c r="E107" s="1" t="s">
@@ -6325,7 +6589,7 @@
       <c r="A108" s="2" t="s">
         <v>733</v>
       </c>
-      <c r="B108" s="13" t="s">
+      <c r="B108" s="1" t="s">
         <v>734</v>
       </c>
       <c r="E108" s="1" t="s">
@@ -6342,7 +6606,7 @@
       <c r="A109" s="2" t="s">
         <v>726</v>
       </c>
-      <c r="B109" s="13" t="s">
+      <c r="B109" s="1" t="s">
         <v>727</v>
       </c>
       <c r="E109" s="1" t="s">
@@ -6359,7 +6623,7 @@
       <c r="A110" s="2" t="s">
         <v>706</v>
       </c>
-      <c r="B110" s="13" t="s">
+      <c r="B110" s="1" t="s">
         <v>707</v>
       </c>
       <c r="E110" s="1" t="s">
@@ -6376,7 +6640,7 @@
       <c r="A111" s="2" t="s">
         <v>708</v>
       </c>
-      <c r="B111" s="13" t="s">
+      <c r="B111" s="1" t="s">
         <v>709</v>
       </c>
       <c r="E111" s="1" t="s">
@@ -6393,7 +6657,7 @@
       <c r="A112" s="2" t="s">
         <v>712</v>
       </c>
-      <c r="B112" s="13" t="s">
+      <c r="B112" s="1" t="s">
         <v>713</v>
       </c>
       <c r="E112" s="1" t="s">
@@ -6410,7 +6674,7 @@
       <c r="A113" s="2" t="s">
         <v>722</v>
       </c>
-      <c r="B113" s="13" t="s">
+      <c r="B113" s="1" t="s">
         <v>723</v>
       </c>
       <c r="E113" s="1" t="s">
@@ -6427,7 +6691,7 @@
       <c r="A114" s="2" t="s">
         <v>378</v>
       </c>
-      <c r="B114" s="13" t="s">
+      <c r="B114" s="1" t="s">
         <v>244</v>
       </c>
       <c r="C114" s="3">
@@ -6449,7 +6713,7 @@
       <c r="A115" t="s">
         <v>844</v>
       </c>
-      <c r="B115" s="14" t="s">
+      <c r="B115" t="s">
         <v>845</v>
       </c>
       <c r="C115" s="3"/>
@@ -6469,7 +6733,7 @@
       <c r="A116" t="s">
         <v>848</v>
       </c>
-      <c r="B116" s="14" t="s">
+      <c r="B116" t="s">
         <v>849</v>
       </c>
       <c r="C116" s="3"/>
@@ -6489,7 +6753,7 @@
       <c r="A117" t="s">
         <v>852</v>
       </c>
-      <c r="B117" s="14" t="s">
+      <c r="B117" t="s">
         <v>853</v>
       </c>
       <c r="C117" s="3"/>
@@ -6511,7 +6775,7 @@
       <c r="A118" s="2" t="s">
         <v>400</v>
       </c>
-      <c r="B118" s="13" t="s">
+      <c r="B118" s="1" t="s">
         <v>401</v>
       </c>
       <c r="C118" s="3">
@@ -6533,7 +6797,7 @@
       <c r="A119" t="s">
         <v>435</v>
       </c>
-      <c r="B119" s="13" t="s">
+      <c r="B119" s="1" t="s">
         <v>493</v>
       </c>
       <c r="C119" s="3">
@@ -6555,7 +6819,7 @@
       <c r="A120" s="2" t="s">
         <v>688</v>
       </c>
-      <c r="B120" s="13" t="s">
+      <c r="B120" s="1" t="s">
         <v>297</v>
       </c>
       <c r="C120" s="1"/>
@@ -6575,7 +6839,7 @@
       <c r="A121" s="2" t="s">
         <v>810</v>
       </c>
-      <c r="B121" s="13" t="s">
+      <c r="B121" s="1" t="s">
         <v>811</v>
       </c>
       <c r="E121" s="1" t="s">
@@ -6592,7 +6856,7 @@
       <c r="A122" s="2" t="s">
         <v>421</v>
       </c>
-      <c r="B122" s="13" t="s">
+      <c r="B122" s="1" t="s">
         <v>238</v>
       </c>
       <c r="C122" s="3">
@@ -6614,7 +6878,7 @@
       <c r="A123" t="s">
         <v>857</v>
       </c>
-      <c r="B123" s="14" t="s">
+      <c r="B123" t="s">
         <v>858</v>
       </c>
       <c r="C123"/>
@@ -6634,7 +6898,7 @@
       <c r="A124" t="s">
         <v>859</v>
       </c>
-      <c r="B124" s="14" t="s">
+      <c r="B124" t="s">
         <v>860</v>
       </c>
       <c r="E124" t="s">
@@ -6651,7 +6915,7 @@
       <c r="A125" t="s">
         <v>861</v>
       </c>
-      <c r="B125" s="14" t="s">
+      <c r="B125" t="s">
         <v>862</v>
       </c>
       <c r="E125" t="s">
@@ -6668,7 +6932,7 @@
       <c r="A126" t="s">
         <v>863</v>
       </c>
-      <c r="B126" s="14" t="s">
+      <c r="B126" t="s">
         <v>864</v>
       </c>
       <c r="E126" t="s">
@@ -6685,7 +6949,7 @@
       <c r="A127" t="s">
         <v>865</v>
       </c>
-      <c r="B127" s="14" t="s">
+      <c r="B127" t="s">
         <v>866</v>
       </c>
       <c r="E127" t="s">
@@ -6702,7 +6966,7 @@
       <c r="A128" t="s">
         <v>867</v>
       </c>
-      <c r="B128" s="14" t="s">
+      <c r="B128" t="s">
         <v>868</v>
       </c>
       <c r="E128" t="s">
@@ -6719,7 +6983,7 @@
       <c r="A129" t="s">
         <v>869</v>
       </c>
-      <c r="B129" s="14" t="s">
+      <c r="B129" t="s">
         <v>870</v>
       </c>
       <c r="C129" s="2">
@@ -6740,7 +7004,7 @@
       <c r="A130" t="s">
         <v>871</v>
       </c>
-      <c r="B130" s="14" t="s">
+      <c r="B130" t="s">
         <v>872</v>
       </c>
       <c r="E130" t="s">
@@ -6757,7 +7021,7 @@
       <c r="A131" t="s">
         <v>873</v>
       </c>
-      <c r="B131" s="14" t="s">
+      <c r="B131" t="s">
         <v>874</v>
       </c>
       <c r="C131" s="2">
@@ -6778,7 +7042,7 @@
       <c r="A132" t="s">
         <v>875</v>
       </c>
-      <c r="B132" s="14" t="s">
+      <c r="B132" t="s">
         <v>876</v>
       </c>
       <c r="E132" t="s">
@@ -6795,18 +7059,24 @@
       <c r="A133" t="s">
         <v>1066</v>
       </c>
-      <c r="B133" s="14" t="s">
+      <c r="B133" t="s">
         <v>1067</v>
       </c>
-      <c r="E133"/>
-      <c r="F133" s="1"/>
-      <c r="H133"/>
+      <c r="E133" t="s">
+        <v>1068</v>
+      </c>
+      <c r="F133" s="1">
+        <v>1</v>
+      </c>
+      <c r="H133" t="s">
+        <v>888</v>
+      </c>
     </row>
     <row r="134" spans="1:8">
       <c r="A134" s="2" t="s">
         <v>380</v>
       </c>
-      <c r="B134" s="13" t="s">
+      <c r="B134" s="1" t="s">
         <v>47</v>
       </c>
       <c r="C134" s="3">
@@ -6828,7 +7098,7 @@
       <c r="A135" s="2" t="s">
         <v>381</v>
       </c>
-      <c r="B135" s="13" t="s">
+      <c r="B135" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C135" s="3">
@@ -6850,7 +7120,7 @@
       <c r="A136" s="2" t="s">
         <v>422</v>
       </c>
-      <c r="B136" s="13" t="s">
+      <c r="B136" s="1" t="s">
         <v>271</v>
       </c>
       <c r="C136" s="3">
@@ -6872,7 +7142,7 @@
       <c r="A137" s="2" t="s">
         <v>382</v>
       </c>
-      <c r="B137" s="13" t="s">
+      <c r="B137" s="1" t="s">
         <v>43</v>
       </c>
       <c r="C137" s="3">
@@ -6894,7 +7164,7 @@
       <c r="A138" s="2" t="s">
         <v>383</v>
       </c>
-      <c r="B138" s="13" t="s">
+      <c r="B138" s="1" t="s">
         <v>51</v>
       </c>
       <c r="C138" s="3">
@@ -6916,7 +7186,7 @@
       <c r="A139" s="2" t="s">
         <v>384</v>
       </c>
-      <c r="B139" s="13" t="s">
+      <c r="B139" s="1" t="s">
         <v>53</v>
       </c>
       <c r="C139" s="3">
@@ -6938,7 +7208,7 @@
       <c r="A140" s="2" t="s">
         <v>423</v>
       </c>
-      <c r="B140" s="13" t="s">
+      <c r="B140" s="1" t="s">
         <v>270</v>
       </c>
       <c r="C140" s="3">
@@ -6960,7 +7230,7 @@
       <c r="A141" s="2" t="s">
         <v>385</v>
       </c>
-      <c r="B141" s="13" t="s">
+      <c r="B141" s="1" t="s">
         <v>55</v>
       </c>
       <c r="C141" s="3">
@@ -6982,7 +7252,7 @@
       <c r="A142" s="2" t="s">
         <v>386</v>
       </c>
-      <c r="B142" s="13" t="s">
+      <c r="B142" s="1" t="s">
         <v>686</v>
       </c>
       <c r="C142" s="3">
@@ -7004,7 +7274,7 @@
       <c r="A143" s="2" t="s">
         <v>387</v>
       </c>
-      <c r="B143" s="13" t="s">
+      <c r="B143" s="1" t="s">
         <v>41</v>
       </c>
       <c r="C143" s="3">
@@ -7026,7 +7296,7 @@
       <c r="A144" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="B144" s="13" t="s">
+      <c r="B144" s="1" t="s">
         <v>45</v>
       </c>
       <c r="C144" s="3">
@@ -7048,7 +7318,7 @@
       <c r="A145" t="s">
         <v>424</v>
       </c>
-      <c r="B145" s="13" t="s">
+      <c r="B145" s="1" t="s">
         <v>220</v>
       </c>
       <c r="C145" s="3">
@@ -7070,7 +7340,7 @@
       <c r="A146" t="s">
         <v>425</v>
       </c>
-      <c r="B146" s="13" t="s">
+      <c r="B146" s="1" t="s">
         <v>214</v>
       </c>
       <c r="C146" s="3">
@@ -7092,7 +7362,7 @@
       <c r="A147" t="s">
         <v>426</v>
       </c>
-      <c r="B147" s="13" t="s">
+      <c r="B147" s="1" t="s">
         <v>226</v>
       </c>
       <c r="C147" s="3">
@@ -7114,7 +7384,7 @@
       <c r="A148" t="s">
         <v>427</v>
       </c>
-      <c r="B148" s="13" t="s">
+      <c r="B148" s="1" t="s">
         <v>216</v>
       </c>
       <c r="C148" s="3">
@@ -7136,7 +7406,7 @@
       <c r="A149" t="s">
         <v>428</v>
       </c>
-      <c r="B149" s="13" t="s">
+      <c r="B149" s="1" t="s">
         <v>224</v>
       </c>
       <c r="C149" s="3">
@@ -7158,7 +7428,7 @@
       <c r="A150" t="s">
         <v>429</v>
       </c>
-      <c r="B150" s="13" t="s">
+      <c r="B150" s="1" t="s">
         <v>222</v>
       </c>
       <c r="C150" s="3">
@@ -7180,7 +7450,7 @@
       <c r="A151" t="s">
         <v>430</v>
       </c>
-      <c r="B151" s="13" t="s">
+      <c r="B151" s="1" t="s">
         <v>218</v>
       </c>
       <c r="C151" s="3">
@@ -7202,7 +7472,7 @@
       <c r="A152" s="11" t="s">
         <v>889</v>
       </c>
-      <c r="B152" s="15" t="s">
+      <c r="B152" s="11" t="s">
         <v>890</v>
       </c>
       <c r="C152">
@@ -7222,7 +7492,7 @@
       <c r="A153" t="s">
         <v>891</v>
       </c>
-      <c r="B153" s="14" t="s">
+      <c r="B153" t="s">
         <v>892</v>
       </c>
       <c r="C153"/>
@@ -7242,7 +7512,7 @@
       <c r="A154" t="s">
         <v>893</v>
       </c>
-      <c r="B154" s="14" t="s">
+      <c r="B154" t="s">
         <v>894</v>
       </c>
       <c r="C154"/>
@@ -7262,7 +7532,7 @@
       <c r="A155" t="s">
         <v>895</v>
       </c>
-      <c r="B155" s="14" t="s">
+      <c r="B155" t="s">
         <v>896</v>
       </c>
       <c r="C155"/>
@@ -7282,7 +7552,7 @@
       <c r="A156" t="s">
         <v>897</v>
       </c>
-      <c r="B156" s="14" t="s">
+      <c r="B156" t="s">
         <v>898</v>
       </c>
       <c r="C156"/>
@@ -7302,7 +7572,7 @@
       <c r="A157" t="s">
         <v>899</v>
       </c>
-      <c r="B157" s="14" t="s">
+      <c r="B157" t="s">
         <v>900</v>
       </c>
       <c r="C157"/>
@@ -7322,7 +7592,7 @@
       <c r="A158" t="s">
         <v>901</v>
       </c>
-      <c r="B158" s="14" t="s">
+      <c r="B158" t="s">
         <v>902</v>
       </c>
       <c r="C158"/>
@@ -7342,7 +7612,7 @@
       <c r="A159" t="s">
         <v>903</v>
       </c>
-      <c r="B159" s="14" t="s">
+      <c r="B159" t="s">
         <v>904</v>
       </c>
       <c r="C159"/>
@@ -7362,7 +7632,7 @@
       <c r="A160" t="s">
         <v>905</v>
       </c>
-      <c r="B160" s="14" t="s">
+      <c r="B160" t="s">
         <v>906</v>
       </c>
       <c r="C160"/>
@@ -7382,7 +7652,7 @@
       <c r="A161" t="s">
         <v>907</v>
       </c>
-      <c r="B161" s="14" t="s">
+      <c r="B161" t="s">
         <v>908</v>
       </c>
       <c r="C161"/>
@@ -7402,7 +7672,7 @@
       <c r="A162" t="s">
         <v>909</v>
       </c>
-      <c r="B162" s="14" t="s">
+      <c r="B162" t="s">
         <v>910</v>
       </c>
       <c r="C162"/>
@@ -7422,7 +7692,7 @@
       <c r="A163" t="s">
         <v>911</v>
       </c>
-      <c r="B163" s="14" t="s">
+      <c r="B163" t="s">
         <v>912</v>
       </c>
       <c r="C163"/>
@@ -7442,7 +7712,7 @@
       <c r="A164" t="s">
         <v>913</v>
       </c>
-      <c r="B164" s="16" t="s">
+      <c r="B164" s="12" t="s">
         <v>1055</v>
       </c>
       <c r="C164"/>
@@ -7462,7 +7732,7 @@
       <c r="A165" t="s">
         <v>914</v>
       </c>
-      <c r="B165" s="14" t="s">
+      <c r="B165" t="s">
         <v>915</v>
       </c>
       <c r="C165"/>
@@ -7482,7 +7752,7 @@
       <c r="A166" t="s">
         <v>916</v>
       </c>
-      <c r="B166" s="14" t="s">
+      <c r="B166" t="s">
         <v>917</v>
       </c>
       <c r="C166"/>
@@ -7502,7 +7772,7 @@
       <c r="A167" t="s">
         <v>918</v>
       </c>
-      <c r="B167" s="14" t="s">
+      <c r="B167" t="s">
         <v>919</v>
       </c>
       <c r="C167"/>
@@ -7522,7 +7792,7 @@
       <c r="A168" t="s">
         <v>920</v>
       </c>
-      <c r="B168" s="14" t="s">
+      <c r="B168" t="s">
         <v>921</v>
       </c>
       <c r="C168"/>
@@ -7542,7 +7812,7 @@
       <c r="A169" t="s">
         <v>922</v>
       </c>
-      <c r="B169" s="14" t="s">
+      <c r="B169" t="s">
         <v>923</v>
       </c>
       <c r="C169"/>
@@ -7562,7 +7832,7 @@
       <c r="A170" t="s">
         <v>924</v>
       </c>
-      <c r="B170" s="14" t="s">
+      <c r="B170" t="s">
         <v>925</v>
       </c>
       <c r="C170"/>
@@ -7582,7 +7852,7 @@
       <c r="A171" t="s">
         <v>926</v>
       </c>
-      <c r="B171" s="14" t="s">
+      <c r="B171" t="s">
         <v>927</v>
       </c>
       <c r="C171"/>
@@ -7602,7 +7872,7 @@
       <c r="A172" t="s">
         <v>928</v>
       </c>
-      <c r="B172" s="14" t="s">
+      <c r="B172" t="s">
         <v>929</v>
       </c>
       <c r="C172"/>
@@ -7622,7 +7892,7 @@
       <c r="A173" t="s">
         <v>930</v>
       </c>
-      <c r="B173" s="14" t="s">
+      <c r="B173" t="s">
         <v>931</v>
       </c>
       <c r="C173"/>
@@ -7642,7 +7912,7 @@
       <c r="A174" t="s">
         <v>932</v>
       </c>
-      <c r="B174" s="14" t="s">
+      <c r="B174" t="s">
         <v>933</v>
       </c>
       <c r="C174"/>
@@ -7662,7 +7932,7 @@
       <c r="A175" t="s">
         <v>934</v>
       </c>
-      <c r="B175" s="14" t="s">
+      <c r="B175" t="s">
         <v>935</v>
       </c>
       <c r="C175"/>
@@ -7682,7 +7952,7 @@
       <c r="A176" t="s">
         <v>936</v>
       </c>
-      <c r="B176" s="14" t="s">
+      <c r="B176" t="s">
         <v>937</v>
       </c>
       <c r="C176"/>
@@ -7702,7 +7972,7 @@
       <c r="A177" t="s">
         <v>938</v>
       </c>
-      <c r="B177" s="14" t="s">
+      <c r="B177" t="s">
         <v>939</v>
       </c>
       <c r="C177">
@@ -7724,7 +7994,7 @@
       <c r="A178" t="s">
         <v>940</v>
       </c>
-      <c r="B178" s="14" t="s">
+      <c r="B178" t="s">
         <v>941</v>
       </c>
       <c r="C178"/>
@@ -7744,7 +8014,7 @@
       <c r="A179" t="s">
         <v>942</v>
       </c>
-      <c r="B179" s="14" t="s">
+      <c r="B179" t="s">
         <v>943</v>
       </c>
       <c r="C179"/>
@@ -7784,7 +8054,7 @@
       <c r="A181" t="s">
         <v>945</v>
       </c>
-      <c r="B181" s="14" t="s">
+      <c r="B181" t="s">
         <v>946</v>
       </c>
       <c r="C181"/>
@@ -7804,7 +8074,7 @@
       <c r="A182" t="s">
         <v>947</v>
       </c>
-      <c r="B182" s="14" t="s">
+      <c r="B182" t="s">
         <v>948</v>
       </c>
       <c r="C182">
@@ -7826,7 +8096,7 @@
       <c r="A183" t="s">
         <v>949</v>
       </c>
-      <c r="B183" s="14" t="s">
+      <c r="B183" t="s">
         <v>950</v>
       </c>
       <c r="C183"/>
@@ -7846,7 +8116,7 @@
       <c r="A184" t="s">
         <v>951</v>
       </c>
-      <c r="B184" s="14" t="s">
+      <c r="B184" t="s">
         <v>952</v>
       </c>
       <c r="C184"/>
@@ -7866,7 +8136,7 @@
       <c r="A185" t="s">
         <v>953</v>
       </c>
-      <c r="B185" s="14" t="s">
+      <c r="B185" t="s">
         <v>954</v>
       </c>
       <c r="C185"/>
@@ -7886,7 +8156,7 @@
       <c r="A186" t="s">
         <v>955</v>
       </c>
-      <c r="B186" s="14" t="s">
+      <c r="B186" t="s">
         <v>956</v>
       </c>
       <c r="C186"/>
@@ -7906,7 +8176,7 @@
       <c r="A187" t="s">
         <v>957</v>
       </c>
-      <c r="B187" s="14" t="s">
+      <c r="B187" t="s">
         <v>958</v>
       </c>
       <c r="C187"/>
@@ -7926,7 +8196,7 @@
       <c r="A188" t="s">
         <v>959</v>
       </c>
-      <c r="B188" s="14" t="s">
+      <c r="B188" t="s">
         <v>960</v>
       </c>
       <c r="C188"/>
@@ -7946,7 +8216,7 @@
       <c r="A189" t="s">
         <v>1057</v>
       </c>
-      <c r="B189" s="14" t="s">
+      <c r="B189" t="s">
         <v>1058</v>
       </c>
       <c r="C189"/>
@@ -7966,7 +8236,7 @@
       <c r="A190" s="2" t="s">
         <v>431</v>
       </c>
-      <c r="B190" s="13" t="s">
+      <c r="B190" s="1" t="s">
         <v>236</v>
       </c>
       <c r="C190" s="3">
@@ -7988,7 +8258,7 @@
       <c r="A191" s="2" t="s">
         <v>432</v>
       </c>
-      <c r="B191" s="13" t="s">
+      <c r="B191" s="1" t="s">
         <v>266</v>
       </c>
       <c r="C191" s="3">
@@ -8010,7 +8280,7 @@
       <c r="A192" s="2" t="s">
         <v>389</v>
       </c>
-      <c r="B192" s="13" t="s">
+      <c r="B192" s="1" t="s">
         <v>195</v>
       </c>
       <c r="C192" s="3">
@@ -8032,7 +8302,7 @@
       <c r="A193" t="s">
         <v>680</v>
       </c>
-      <c r="B193" s="13" t="s">
+      <c r="B193" s="1" t="s">
         <v>509</v>
       </c>
       <c r="E193" s="1" t="s">
@@ -8052,7 +8322,7 @@
       <c r="A194" t="s">
         <v>681</v>
       </c>
-      <c r="B194" s="13" t="s">
+      <c r="B194" s="1" t="s">
         <v>510</v>
       </c>
       <c r="E194" s="1" t="s">
@@ -8072,7 +8342,7 @@
       <c r="A195" t="s">
         <v>681</v>
       </c>
-      <c r="B195" s="13" t="s">
+      <c r="B195" s="1" t="s">
         <v>510</v>
       </c>
       <c r="E195" s="1" t="s">
@@ -8092,7 +8362,7 @@
       <c r="A196" t="s">
         <v>682</v>
       </c>
-      <c r="B196" s="13" t="s">
+      <c r="B196" s="1" t="s">
         <v>507</v>
       </c>
       <c r="C196" s="2">
@@ -8113,7 +8383,7 @@
       <c r="A197" s="2" t="s">
         <v>814</v>
       </c>
-      <c r="B197" s="13" t="s">
+      <c r="B197" s="1" t="s">
         <v>815</v>
       </c>
       <c r="D197" s="6"/>
@@ -8131,7 +8401,7 @@
       <c r="A198" s="2" t="s">
         <v>390</v>
       </c>
-      <c r="B198" s="13" t="s">
+      <c r="B198" s="1" t="s">
         <v>315</v>
       </c>
       <c r="C198" s="3">
@@ -8153,7 +8423,7 @@
       <c r="A199" t="s">
         <v>683</v>
       </c>
-      <c r="B199" s="13" t="s">
+      <c r="B199" s="1" t="s">
         <v>512</v>
       </c>
       <c r="C199" s="2">
@@ -8173,7 +8443,7 @@
       <c r="A200" t="s">
         <v>684</v>
       </c>
-      <c r="B200" s="13" t="s">
+      <c r="B200" s="1" t="s">
         <v>687</v>
       </c>
       <c r="C200" s="2">
@@ -8193,7 +8463,7 @@
       <c r="A201" t="s">
         <v>1061</v>
       </c>
-      <c r="B201" s="14" t="s">
+      <c r="B201" t="s">
         <v>1033</v>
       </c>
       <c r="C201"/>
@@ -8213,7 +8483,7 @@
       <c r="A202" t="s">
         <v>1062</v>
       </c>
-      <c r="B202" s="14" t="s">
+      <c r="B202" t="s">
         <v>1036</v>
       </c>
       <c r="C202">
@@ -8235,7 +8505,7 @@
       <c r="A203" t="s">
         <v>1063</v>
       </c>
-      <c r="B203" s="14" t="s">
+      <c r="B203" t="s">
         <v>1039</v>
       </c>
       <c r="C203"/>
@@ -8255,7 +8525,7 @@
       <c r="A204" t="s">
         <v>491</v>
       </c>
-      <c r="B204" s="13" t="s">
+      <c r="B204" s="1" t="s">
         <v>490</v>
       </c>
       <c r="C204" s="3">
@@ -8277,7 +8547,7 @@
       <c r="A205" s="2" t="s">
         <v>479</v>
       </c>
-      <c r="B205" s="13" t="s">
+      <c r="B205" s="1" t="s">
         <v>115</v>
       </c>
       <c r="C205" s="3">
@@ -8299,7 +8569,7 @@
       <c r="A206" s="2" t="s">
         <v>481</v>
       </c>
-      <c r="B206" s="13" t="s">
+      <c r="B206" s="1" t="s">
         <v>119</v>
       </c>
       <c r="C206" s="3"/>
@@ -8319,7 +8589,7 @@
       <c r="A207" s="2" t="s">
         <v>480</v>
       </c>
-      <c r="B207" s="13" t="s">
+      <c r="B207" s="1" t="s">
         <v>117</v>
       </c>
       <c r="C207" s="3">
@@ -8341,7 +8611,7 @@
       <c r="A208" s="2" t="s">
         <v>514</v>
       </c>
-      <c r="B208" s="13" t="s">
+      <c r="B208" s="1" t="s">
         <v>513</v>
       </c>
       <c r="D208" s="6"/>
@@ -8359,7 +8629,7 @@
       <c r="A209" t="s">
         <v>1000</v>
       </c>
-      <c r="B209" s="14" t="s">
+      <c r="B209" t="s">
         <v>1001</v>
       </c>
       <c r="C209">
@@ -8381,7 +8651,7 @@
       <c r="A210" t="s">
         <v>1004</v>
       </c>
-      <c r="B210" s="14" t="s">
+      <c r="B210" t="s">
         <v>1005</v>
       </c>
       <c r="C210">
@@ -8403,7 +8673,7 @@
       <c r="A211" t="s">
         <v>1008</v>
       </c>
-      <c r="B211" s="14" t="s">
+      <c r="B211" t="s">
         <v>1009</v>
       </c>
       <c r="C211">
@@ -8425,7 +8695,7 @@
       <c r="A212" t="s">
         <v>1012</v>
       </c>
-      <c r="B212" s="14" t="s">
+      <c r="B212" t="s">
         <v>1013</v>
       </c>
       <c r="C212">
@@ -8447,7 +8717,7 @@
       <c r="A213" t="s">
         <v>1016</v>
       </c>
-      <c r="B213" s="14" t="s">
+      <c r="B213" t="s">
         <v>1017</v>
       </c>
       <c r="C213">
@@ -8469,7 +8739,7 @@
       <c r="A214" s="2" t="s">
         <v>391</v>
       </c>
-      <c r="B214" s="13" t="s">
+      <c r="B214" s="1" t="s">
         <v>255</v>
       </c>
       <c r="C214" s="1"/>
@@ -8491,7 +8761,7 @@
       <c r="A215" s="2" t="s">
         <v>392</v>
       </c>
-      <c r="B215" s="13" t="s">
+      <c r="B215" s="1" t="s">
         <v>258</v>
       </c>
       <c r="C215" s="1"/>
@@ -8513,7 +8783,7 @@
       <c r="A216" s="2" t="s">
         <v>393</v>
       </c>
-      <c r="B216" s="13" t="s">
+      <c r="B216" s="1" t="s">
         <v>131</v>
       </c>
       <c r="C216" s="3">
@@ -8535,7 +8805,7 @@
       <c r="A217" s="2" t="s">
         <v>433</v>
       </c>
-      <c r="B217" s="13" t="s">
+      <c r="B217" s="1" t="s">
         <v>228</v>
       </c>
       <c r="C217" s="3">
@@ -8557,7 +8827,7 @@
       <c r="A218" s="2" t="s">
         <v>394</v>
       </c>
-      <c r="B218" s="13" t="s">
+      <c r="B218" s="1" t="s">
         <v>287</v>
       </c>
       <c r="C218" s="3">
@@ -8579,7 +8849,7 @@
       <c r="A219" s="2" t="s">
         <v>434</v>
       </c>
-      <c r="B219" s="13" t="s">
+      <c r="B219" s="1" t="s">
         <v>74</v>
       </c>
       <c r="C219" s="3">
@@ -8601,7 +8871,7 @@
       <c r="A220" s="2" t="s">
         <v>629</v>
       </c>
-      <c r="B220" s="13" t="s">
+      <c r="B220" s="1" t="s">
         <v>305</v>
       </c>
       <c r="C220" s="1">
@@ -8623,7 +8893,7 @@
       <c r="A221" s="2" t="s">
         <v>630</v>
       </c>
-      <c r="B221" s="13" t="s">
+      <c r="B221" s="1" t="s">
         <v>482</v>
       </c>
       <c r="C221" s="1"/>
@@ -8643,7 +8913,7 @@
       <c r="A222" s="2" t="s">
         <v>631</v>
       </c>
-      <c r="B222" s="13" t="s">
+      <c r="B222" s="1" t="s">
         <v>294</v>
       </c>
       <c r="C222" s="1"/>
@@ -8663,7 +8933,7 @@
       <c r="A223" s="2" t="s">
         <v>632</v>
       </c>
-      <c r="B223" s="13" t="s">
+      <c r="B223" s="1" t="s">
         <v>295</v>
       </c>
       <c r="C223" s="1"/>
@@ -8683,7 +8953,7 @@
       <c r="A224" s="2" t="s">
         <v>483</v>
       </c>
-      <c r="B224" s="13" t="s">
+      <c r="B224" s="1" t="s">
         <v>242</v>
       </c>
       <c r="C224" s="3">
@@ -8705,7 +8975,7 @@
       <c r="A225" s="2" t="s">
         <v>484</v>
       </c>
-      <c r="B225" s="13" t="s">
+      <c r="B225" s="1" t="s">
         <v>240</v>
       </c>
       <c r="C225" s="3">
@@ -8727,7 +8997,7 @@
       <c r="A226" s="2" t="s">
         <v>705</v>
       </c>
-      <c r="B226" s="13" t="s">
+      <c r="B226" s="1" t="s">
         <v>702</v>
       </c>
       <c r="C226" s="2">
@@ -8748,7 +9018,7 @@
       <c r="A227" s="2" t="s">
         <v>445</v>
       </c>
-      <c r="B227" s="13" t="s">
+      <c r="B227" s="1" t="s">
         <v>57</v>
       </c>
       <c r="C227" s="3">
@@ -8770,7 +9040,7 @@
       <c r="A228" s="2" t="s">
         <v>447</v>
       </c>
-      <c r="B228" s="13" t="s">
+      <c r="B228" s="1" t="s">
         <v>61</v>
       </c>
       <c r="C228" s="3">
@@ -8792,7 +9062,7 @@
       <c r="A229" s="2" t="s">
         <v>449</v>
       </c>
-      <c r="B229" s="13" t="s">
+      <c r="B229" s="1" t="s">
         <v>450</v>
       </c>
       <c r="E229" s="1" t="s">
@@ -8809,7 +9079,7 @@
       <c r="A230" s="2" t="s">
         <v>446</v>
       </c>
-      <c r="B230" s="13" t="s">
+      <c r="B230" s="1" t="s">
         <v>59</v>
       </c>
       <c r="C230" s="3">
@@ -8831,7 +9101,7 @@
       <c r="A231" s="2" t="s">
         <v>448</v>
       </c>
-      <c r="B231" s="13" t="s">
+      <c r="B231" s="1" t="s">
         <v>62</v>
       </c>
       <c r="C231" s="3">
@@ -8853,7 +9123,7 @@
       <c r="A232" s="2" t="s">
         <v>395</v>
       </c>
-      <c r="B232" s="13" t="s">
+      <c r="B232" s="1" t="s">
         <v>121</v>
       </c>
       <c r="C232" s="3">
@@ -8875,7 +9145,7 @@
       <c r="A233" s="2" t="s">
         <v>396</v>
       </c>
-      <c r="B233" s="13" t="s">
+      <c r="B233" s="1" t="s">
         <v>123</v>
       </c>
       <c r="C233" s="3">
@@ -8897,7 +9167,7 @@
       <c r="A234" s="2" t="s">
         <v>397</v>
       </c>
-      <c r="B234" s="13" t="s">
+      <c r="B234" s="1" t="s">
         <v>122</v>
       </c>
       <c r="C234" s="3">
@@ -8919,7 +9189,7 @@
       <c r="A235" t="s">
         <v>1022</v>
       </c>
-      <c r="B235" s="14" t="s">
+      <c r="B235" t="s">
         <v>1023</v>
       </c>
       <c r="C235">
@@ -8941,7 +9211,7 @@
       <c r="A236" s="11" t="s">
         <v>1026</v>
       </c>
-      <c r="B236" s="14" t="s">
+      <c r="B236" t="s">
         <v>1027</v>
       </c>
       <c r="C236" s="3">
@@ -8963,7 +9233,7 @@
       <c r="A237" s="2" t="s">
         <v>398</v>
       </c>
-      <c r="B237" s="13" t="s">
+      <c r="B237" s="1" t="s">
         <v>282</v>
       </c>
       <c r="C237" s="3">
@@ -8985,7 +9255,7 @@
       <c r="A238" s="2" t="s">
         <v>399</v>
       </c>
-      <c r="B238" s="13" t="s">
+      <c r="B238" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C238" s="3">
@@ -9007,7 +9277,7 @@
       <c r="A239" s="2" t="s">
         <v>806</v>
       </c>
-      <c r="B239" s="13" t="s">
+      <c r="B239" s="1" t="s">
         <v>807</v>
       </c>
       <c r="C239" s="2"/>
@@ -9027,7 +9297,7 @@
       <c r="A240" t="s">
         <v>498</v>
       </c>
-      <c r="B240" s="13" t="s">
+      <c r="B240" s="1" t="s">
         <v>311</v>
       </c>
       <c r="C240" s="3">
@@ -9049,7 +9319,7 @@
       <c r="A241" t="s">
         <v>499</v>
       </c>
-      <c r="B241" s="13" t="s">
+      <c r="B241" s="1" t="s">
         <v>313</v>
       </c>
       <c r="C241" s="3"/>
@@ -9069,7 +9339,7 @@
       <c r="A242" s="2" t="s">
         <v>494</v>
       </c>
-      <c r="B242" s="13" t="s">
+      <c r="B242" s="1" t="s">
         <v>495</v>
       </c>
       <c r="C242" s="3"/>
@@ -9089,7 +9359,7 @@
       <c r="A243" s="2" t="s">
         <v>402</v>
       </c>
-      <c r="B243" s="13" t="s">
+      <c r="B243" s="1" t="s">
         <v>292</v>
       </c>
       <c r="C243" s="3"/>
@@ -9109,7 +9379,7 @@
       <c r="A244" s="11" t="s">
         <v>1028</v>
       </c>
-      <c r="B244" s="14" t="s">
+      <c r="B244" t="s">
         <v>1029</v>
       </c>
       <c r="C244"/>
@@ -9131,7 +9401,7 @@
       <c r="A245" s="2" t="s">
         <v>403</v>
       </c>
-      <c r="B245" s="13" t="s">
+      <c r="B245" s="1" t="s">
         <v>290</v>
       </c>
       <c r="C245" s="3">
@@ -9153,7 +9423,7 @@
       <c r="A246" s="2" t="s">
         <v>666</v>
       </c>
-      <c r="B246" s="13" t="s">
+      <c r="B246" s="1" t="s">
         <v>668</v>
       </c>
       <c r="E246" s="1" t="s">
@@ -9170,7 +9440,7 @@
       <c r="A247" s="2" t="s">
         <v>665</v>
       </c>
-      <c r="B247" s="13" t="s">
+      <c r="B247" s="1" t="s">
         <v>667</v>
       </c>
       <c r="E247" s="1" t="s">
@@ -9187,7 +9457,7 @@
       <c r="A248" s="2" t="s">
         <v>404</v>
       </c>
-      <c r="B248" s="13" t="s">
+      <c r="B248" s="1" t="s">
         <v>213</v>
       </c>
       <c r="C248" s="3">
@@ -9209,7 +9479,7 @@
       <c r="A249" s="2" t="s">
         <v>404</v>
       </c>
-      <c r="B249" s="13" t="s">
+      <c r="B249" s="1" t="s">
         <v>213</v>
       </c>
       <c r="C249" s="3">
@@ -9231,7 +9501,7 @@
       <c r="A250" t="s">
         <v>405</v>
       </c>
-      <c r="B250" s="13" t="s">
+      <c r="B250" s="1" t="s">
         <v>25</v>
       </c>
       <c r="C250" s="3">
@@ -9253,7 +9523,7 @@
       <c r="A251" t="s">
         <v>406</v>
       </c>
-      <c r="B251" s="13" t="s">
+      <c r="B251" s="1" t="s">
         <v>27</v>
       </c>
       <c r="C251" s="3">
@@ -9275,7 +9545,7 @@
       <c r="A252" t="s">
         <v>407</v>
       </c>
-      <c r="B252" s="13" t="s">
+      <c r="B252" s="1" t="s">
         <v>23</v>
       </c>
       <c r="C252" s="3">
@@ -9297,7 +9567,7 @@
       <c r="A253" t="s">
         <v>408</v>
       </c>
-      <c r="B253" s="13" t="s">
+      <c r="B253" s="1" t="s">
         <v>31</v>
       </c>
       <c r="C253" s="3">
@@ -9319,7 +9589,7 @@
       <c r="A254" t="s">
         <v>409</v>
       </c>
-      <c r="B254" s="13" t="s">
+      <c r="B254" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C254" s="3">
@@ -9341,7 +9611,7 @@
       <c r="A255" t="s">
         <v>410</v>
       </c>
-      <c r="B255" s="13" t="s">
+      <c r="B255" s="1" t="s">
         <v>20</v>
       </c>
       <c r="C255" s="3">
@@ -9363,7 +9633,7 @@
       <c r="A256" t="s">
         <v>411</v>
       </c>
-      <c r="B256" s="13" t="s">
+      <c r="B256" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C256" s="3">
@@ -9385,7 +9655,7 @@
       <c r="A257" s="2" t="s">
         <v>452</v>
       </c>
-      <c r="B257" s="13" t="s">
+      <c r="B257" s="1" t="s">
         <v>37</v>
       </c>
       <c r="C257" s="3">
@@ -9407,7 +9677,7 @@
       <c r="A258" t="s">
         <v>412</v>
       </c>
-      <c r="B258" s="13" t="s">
+      <c r="B258" s="1" t="s">
         <v>29</v>
       </c>
       <c r="C258" s="3">
@@ -9429,7 +9699,7 @@
       <c r="A259" s="2" t="s">
         <v>453</v>
       </c>
-      <c r="B259" s="13" t="s">
+      <c r="B259" s="1" t="s">
         <v>39</v>
       </c>
       <c r="C259" s="3">
@@ -9451,7 +9721,7 @@
       <c r="A260" t="s">
         <v>413</v>
       </c>
-      <c r="B260" s="13" t="s">
+      <c r="B260" s="1" t="s">
         <v>35</v>
       </c>
       <c r="C260" s="3">
@@ -9473,7 +9743,7 @@
       <c r="A261" t="s">
         <v>414</v>
       </c>
-      <c r="B261" s="13" t="s">
+      <c r="B261" s="1" t="s">
         <v>22</v>
       </c>
       <c r="C261" s="3">
@@ -9495,7 +9765,7 @@
       <c r="A262" s="2" t="s">
         <v>698</v>
       </c>
-      <c r="B262" s="13" t="s">
+      <c r="B262" s="1" t="s">
         <v>699</v>
       </c>
       <c r="C262" s="2">
@@ -9516,7 +9786,7 @@
       <c r="A263" s="2" t="s">
         <v>443</v>
       </c>
-      <c r="B263" s="13" t="s">
+      <c r="B263" s="1" t="s">
         <v>451</v>
       </c>
       <c r="C263" s="3">
@@ -9537,7 +9807,7 @@
       <c r="A264" s="2" t="s">
         <v>442</v>
       </c>
-      <c r="B264" s="13" t="s">
+      <c r="B264" s="1" t="s">
         <v>326</v>
       </c>
       <c r="C264" s="3">
@@ -9559,7 +9829,7 @@
       <c r="A265" s="2" t="s">
         <v>497</v>
       </c>
-      <c r="B265" s="13" t="s">
+      <c r="B265" s="1" t="s">
         <v>129</v>
       </c>
       <c r="C265" s="3">
@@ -9581,7 +9851,7 @@
       <c r="A266" s="2" t="s">
         <v>820</v>
       </c>
-      <c r="B266" s="13" t="s">
+      <c r="B266" s="1" t="s">
         <v>818</v>
       </c>
       <c r="C266" s="2">
@@ -9602,7 +9872,7 @@
       <c r="A267" s="2" t="s">
         <v>761</v>
       </c>
-      <c r="B267" s="13" t="s">
+      <c r="B267" s="1" t="s">
         <v>753</v>
       </c>
       <c r="C267" s="2">
@@ -9623,7 +9893,7 @@
       <c r="A268" s="2" t="s">
         <v>762</v>
       </c>
-      <c r="B268" s="13" t="s">
+      <c r="B268" s="1" t="s">
         <v>754</v>
       </c>
       <c r="C268" s="2">
@@ -9644,7 +9914,7 @@
       <c r="A269" s="2" t="s">
         <v>763</v>
       </c>
-      <c r="B269" s="13" t="s">
+      <c r="B269" s="1" t="s">
         <v>755</v>
       </c>
       <c r="C269" s="2">
@@ -9665,7 +9935,7 @@
       <c r="A270" s="2" t="s">
         <v>685</v>
       </c>
-      <c r="B270" s="13" t="s">
+      <c r="B270" s="1" t="s">
         <v>511</v>
       </c>
       <c r="C270" s="3"/>
@@ -9687,7 +9957,7 @@
       <c r="A271" t="s">
         <v>415</v>
       </c>
-      <c r="B271" s="13" t="s">
+      <c r="B271" s="1" t="s">
         <v>199</v>
       </c>
       <c r="C271" s="3">
@@ -9709,7 +9979,7 @@
       <c r="A272" t="s">
         <v>416</v>
       </c>
-      <c r="B272" s="13" t="s">
+      <c r="B272" s="1" t="s">
         <v>197</v>
       </c>
       <c r="C272" s="3">
@@ -9731,7 +10001,7 @@
       <c r="A273" t="s">
         <v>417</v>
       </c>
-      <c r="B273" s="13" t="s">
+      <c r="B273" s="1" t="s">
         <v>201</v>
       </c>
       <c r="C273" s="3">
@@ -9753,7 +10023,7 @@
       <c r="A274" t="s">
         <v>418</v>
       </c>
-      <c r="B274" s="13" t="s">
+      <c r="B274" s="1" t="s">
         <v>130</v>
       </c>
       <c r="C274" s="3">
@@ -9775,7 +10045,7 @@
       <c r="A275" s="2" t="s">
         <v>456</v>
       </c>
-      <c r="B275" s="13" t="s">
+      <c r="B275" s="1" t="s">
         <v>64</v>
       </c>
       <c r="C275" s="3">
@@ -9797,7 +10067,7 @@
       <c r="A276" s="2" t="s">
         <v>457</v>
       </c>
-      <c r="B276" s="13" t="s">
+      <c r="B276" s="1" t="s">
         <v>65</v>
       </c>
       <c r="C276" s="3">
@@ -9819,7 +10089,7 @@
       <c r="A277" s="2" t="s">
         <v>458</v>
       </c>
-      <c r="B277" s="13" t="s">
+      <c r="B277" s="1" t="s">
         <v>69</v>
       </c>
       <c r="C277" s="3">
@@ -9841,7 +10111,7 @@
       <c r="A278" s="2" t="s">
         <v>459</v>
       </c>
-      <c r="B278" s="13" t="s">
+      <c r="B278" s="1" t="s">
         <v>67</v>
       </c>
       <c r="C278" s="3">
@@ -9863,7 +10133,7 @@
       <c r="A279" s="2" t="s">
         <v>460</v>
       </c>
-      <c r="B279" s="13" t="s">
+      <c r="B279" s="1" t="s">
         <v>1065</v>
       </c>
       <c r="C279" s="3">
@@ -9885,7 +10155,7 @@
       <c r="A280" s="2" t="s">
         <v>461</v>
       </c>
-      <c r="B280" s="13" t="s">
+      <c r="B280" s="1" t="s">
         <v>72</v>
       </c>
       <c r="C280" s="3">
@@ -9907,7 +10177,7 @@
       <c r="A281" s="2" t="s">
         <v>462</v>
       </c>
-      <c r="B281" s="13" t="s">
+      <c r="B281" s="1" t="s">
         <v>92</v>
       </c>
       <c r="C281" s="3">
@@ -9929,7 +10199,7 @@
       <c r="A282" s="2" t="s">
         <v>464</v>
       </c>
-      <c r="B282" s="13" t="s">
+      <c r="B282" s="1" t="s">
         <v>95</v>
       </c>
       <c r="C282" s="3">
@@ -9951,7 +10221,7 @@
       <c r="A283" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="B283" s="13" t="s">
+      <c r="B283" s="1" t="s">
         <v>86</v>
       </c>
       <c r="C283" s="3">
@@ -9973,7 +10243,7 @@
       <c r="A284" s="2" t="s">
         <v>466</v>
       </c>
-      <c r="B284" s="13" t="s">
+      <c r="B284" s="1" t="s">
         <v>88</v>
       </c>
       <c r="C284" s="3">
@@ -9995,7 +10265,7 @@
       <c r="A285" s="2" t="s">
         <v>467</v>
       </c>
-      <c r="B285" s="13" t="s">
+      <c r="B285" s="1" t="s">
         <v>102</v>
       </c>
       <c r="C285" s="3">
@@ -10017,7 +10287,7 @@
       <c r="A286" s="2" t="s">
         <v>468</v>
       </c>
-      <c r="B286" s="13" t="s">
+      <c r="B286" s="1" t="s">
         <v>110</v>
       </c>
       <c r="C286" s="3">
@@ -10039,7 +10309,7 @@
       <c r="A287" s="2" t="s">
         <v>469</v>
       </c>
-      <c r="B287" s="13" t="s">
+      <c r="B287" s="1" t="s">
         <v>104</v>
       </c>
       <c r="C287" s="3">
@@ -10061,7 +10331,7 @@
       <c r="A288" s="2" t="s">
         <v>470</v>
       </c>
-      <c r="B288" s="13" t="s">
+      <c r="B288" s="1" t="s">
         <v>91</v>
       </c>
       <c r="C288" s="3">
@@ -10083,7 +10353,7 @@
       <c r="A289" s="2" t="s">
         <v>471</v>
       </c>
-      <c r="B289" s="13" t="s">
+      <c r="B289" s="1" t="s">
         <v>108</v>
       </c>
       <c r="C289" s="3">
@@ -10105,7 +10375,7 @@
       <c r="A290" t="s">
         <v>419</v>
       </c>
-      <c r="B290" s="13" t="s">
+      <c r="B290" s="1" t="s">
         <v>280</v>
       </c>
       <c r="C290" s="3">
@@ -10127,7 +10397,7 @@
       <c r="A291" t="s">
         <v>500</v>
       </c>
-      <c r="B291" s="13" t="s">
+      <c r="B291" s="1" t="s">
         <v>203</v>
       </c>
       <c r="C291" s="3">
@@ -10149,7 +10419,7 @@
       <c r="A292" t="s">
         <v>501</v>
       </c>
-      <c r="B292" s="13" t="s">
+      <c r="B292" s="1" t="s">
         <v>205</v>
       </c>
       <c r="C292" s="3">
@@ -10171,7 +10441,7 @@
       <c r="A293" t="s">
         <v>504</v>
       </c>
-      <c r="B293" s="13" t="s">
+      <c r="B293" s="1" t="s">
         <v>210</v>
       </c>
       <c r="C293" s="3">
@@ -10193,7 +10463,7 @@
       <c r="A294" t="s">
         <v>503</v>
       </c>
-      <c r="B294" s="13" t="s">
+      <c r="B294" s="1" t="s">
         <v>208</v>
       </c>
       <c r="C294" s="3">
@@ -10215,7 +10485,7 @@
       <c r="A295" t="s">
         <v>502</v>
       </c>
-      <c r="B295" s="13" t="s">
+      <c r="B295" s="1" t="s">
         <v>207</v>
       </c>
       <c r="C295" s="3">
@@ -10237,7 +10507,7 @@
       <c r="A296" t="s">
         <v>420</v>
       </c>
-      <c r="B296" s="13" t="s">
+      <c r="B296" s="1" t="s">
         <v>296</v>
       </c>
       <c r="C296" s="1"/>
@@ -10257,7 +10527,7 @@
       <c r="A297" t="s">
         <v>1048</v>
       </c>
-      <c r="B297" s="13" t="s">
+      <c r="B297" s="1" t="s">
         <v>1049</v>
       </c>
       <c r="E297" s="1" t="s">
@@ -10268,6 +10538,325 @@
       </c>
       <c r="H297" s="7" t="s">
         <v>1054</v>
+      </c>
+    </row>
+    <row r="298" spans="1:8">
+      <c r="A298" s="2" t="s">
+        <v>1069</v>
+      </c>
+      <c r="B298" s="1" t="s">
+        <v>1070</v>
+      </c>
+      <c r="E298" s="1" t="s">
+        <v>1071</v>
+      </c>
+      <c r="F298" s="2">
+        <v>1</v>
+      </c>
+      <c r="H298" s="2" t="s">
+        <v>1072</v>
+      </c>
+    </row>
+    <row r="299" spans="1:8">
+      <c r="A299" s="2" t="s">
+        <v>1074</v>
+      </c>
+      <c r="B299" s="1" t="s">
+        <v>1073</v>
+      </c>
+      <c r="E299" s="1" t="s">
+        <v>1076</v>
+      </c>
+      <c r="F299" s="2">
+        <v>1</v>
+      </c>
+      <c r="H299" s="7" t="s">
+        <v>1075</v>
+      </c>
+    </row>
+    <row r="300" spans="1:8">
+      <c r="A300" s="2" t="s">
+        <v>1085</v>
+      </c>
+      <c r="B300" s="1" t="s">
+        <v>1077</v>
+      </c>
+      <c r="E300" s="1" t="s">
+        <v>1078</v>
+      </c>
+      <c r="F300" s="2">
+        <v>1</v>
+      </c>
+      <c r="H300" s="2" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="301" spans="1:8">
+      <c r="A301" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B301" s="1" t="s">
+        <v>1080</v>
+      </c>
+      <c r="E301" s="1" t="s">
+        <v>1081</v>
+      </c>
+      <c r="F301" s="2">
+        <v>1</v>
+      </c>
+      <c r="H301" s="2" t="s">
+        <v>1088</v>
+      </c>
+    </row>
+    <row r="302" spans="1:8">
+      <c r="A302" s="2" t="s">
+        <v>1084</v>
+      </c>
+      <c r="B302" s="1" t="s">
+        <v>1082</v>
+      </c>
+      <c r="E302" s="1" t="s">
+        <v>1086</v>
+      </c>
+      <c r="F302" s="2">
+        <v>1</v>
+      </c>
+      <c r="H302" s="2" t="s">
+        <v>1087</v>
+      </c>
+    </row>
+    <row r="303" spans="1:8">
+      <c r="A303" s="2" t="s">
+        <v>1094</v>
+      </c>
+      <c r="B303" s="1" t="s">
+        <v>1089</v>
+      </c>
+      <c r="E303" s="1" t="s">
+        <v>1090</v>
+      </c>
+      <c r="F303" s="2">
+        <v>1</v>
+      </c>
+      <c r="H303" s="7" t="s">
+        <v>1138</v>
+      </c>
+    </row>
+    <row r="304" spans="1:8">
+      <c r="A304" s="2" t="s">
+        <v>1093</v>
+      </c>
+      <c r="B304" s="1" t="s">
+        <v>1091</v>
+      </c>
+      <c r="C304" s="2">
+        <v>6</v>
+      </c>
+      <c r="D304" s="6">
+        <v>0</v>
+      </c>
+      <c r="E304" s="1" t="s">
+        <v>1092</v>
+      </c>
+      <c r="H304" s="7" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="305" spans="1:8">
+      <c r="A305" s="2" t="s">
+        <v>1096</v>
+      </c>
+      <c r="B305" s="1" t="s">
+        <v>1097</v>
+      </c>
+      <c r="E305" s="1" t="s">
+        <v>1140</v>
+      </c>
+      <c r="H305" s="7" t="s">
+        <v>1139</v>
+      </c>
+    </row>
+    <row r="306" spans="1:8">
+      <c r="B306" s="1" t="s">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="307" spans="1:8">
+      <c r="B307" s="1" t="s">
+        <v>1099</v>
+      </c>
+    </row>
+    <row r="308" spans="1:8">
+      <c r="B308" s="1" t="s">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="309" spans="1:8">
+      <c r="B309" s="1" t="s">
+        <v>1101</v>
+      </c>
+    </row>
+    <row r="310" spans="1:8">
+      <c r="B310" s="1" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="311" spans="1:8">
+      <c r="B311" s="1" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="312" spans="1:8">
+      <c r="B312" s="1" t="s">
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="313" spans="1:8">
+      <c r="B313" s="1" t="s">
+        <v>1105</v>
+      </c>
+    </row>
+    <row r="314" spans="1:8">
+      <c r="B314" s="1" t="s">
+        <v>1106</v>
+      </c>
+      <c r="E314" s="2" t="s">
+        <v>1107</v>
+      </c>
+    </row>
+    <row r="315" spans="1:8">
+      <c r="B315" s="1" t="s">
+        <v>1108</v>
+      </c>
+    </row>
+    <row r="316" spans="1:8">
+      <c r="B316" s="1" t="s">
+        <v>1109</v>
+      </c>
+    </row>
+    <row r="317" spans="1:8">
+      <c r="B317" s="1" t="s">
+        <v>1110</v>
+      </c>
+    </row>
+    <row r="318" spans="1:8">
+      <c r="B318" s="1" t="s">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="319" spans="1:8">
+      <c r="B319" s="1" t="s">
+        <v>1112</v>
+      </c>
+    </row>
+    <row r="320" spans="1:8">
+      <c r="B320" s="1" t="s">
+        <v>1113</v>
+      </c>
+    </row>
+    <row r="321" spans="1:8">
+      <c r="B321" s="1" t="s">
+        <v>1114</v>
+      </c>
+    </row>
+    <row r="322" spans="1:8">
+      <c r="B322" s="1" t="s">
+        <v>1115</v>
+      </c>
+    </row>
+    <row r="323" spans="1:8">
+      <c r="B323" s="1" t="s">
+        <v>1116</v>
+      </c>
+    </row>
+    <row r="324" spans="1:8">
+      <c r="B324" s="1" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="325" spans="1:8">
+      <c r="A325" s="2" t="s">
+        <v>1125</v>
+      </c>
+      <c r="B325" s="1" t="s">
+        <v>1118</v>
+      </c>
+      <c r="E325" s="2" t="s">
+        <v>1129</v>
+      </c>
+      <c r="F325" s="2">
+        <v>1</v>
+      </c>
+      <c r="H325" s="2" t="s">
+        <v>1137</v>
+      </c>
+    </row>
+    <row r="326" spans="1:8">
+      <c r="A326" s="2" t="s">
+        <v>1131</v>
+      </c>
+      <c r="B326" s="1" t="s">
+        <v>1119</v>
+      </c>
+      <c r="E326" s="2" t="s">
+        <v>1130</v>
+      </c>
+      <c r="F326" s="2">
+        <v>1</v>
+      </c>
+      <c r="H326" s="2" t="s">
+        <v>1136</v>
+      </c>
+    </row>
+    <row r="327" spans="1:8">
+      <c r="A327" s="2" t="s">
+        <v>1126</v>
+      </c>
+      <c r="B327" s="1" t="s">
+        <v>1120</v>
+      </c>
+      <c r="E327" s="2" t="s">
+        <v>1123</v>
+      </c>
+      <c r="F327" s="2">
+        <v>1</v>
+      </c>
+      <c r="H327" s="2" t="s">
+        <v>1135</v>
+      </c>
+    </row>
+    <row r="328" spans="1:8">
+      <c r="A328" s="2" t="s">
+        <v>1127</v>
+      </c>
+      <c r="B328" s="1" t="s">
+        <v>1121</v>
+      </c>
+      <c r="E328" s="2" t="s">
+        <v>1124</v>
+      </c>
+      <c r="F328" s="2">
+        <v>1</v>
+      </c>
+      <c r="H328" s="2" t="s">
+        <v>1134</v>
+      </c>
+    </row>
+    <row r="329" spans="1:8">
+      <c r="A329" s="2" t="s">
+        <v>1128</v>
+      </c>
+      <c r="B329" s="1" t="s">
+        <v>1122</v>
+      </c>
+      <c r="E329" s="2" t="s">
+        <v>1132</v>
+      </c>
+      <c r="F329" s="2">
+        <v>1</v>
+      </c>
+      <c r="H329" s="2" t="s">
+        <v>1133</v>
       </c>
     </row>
   </sheetData>
@@ -10294,8 +10883,12 @@
     <hyperlink ref="H236" r:id="rId16" xr:uid="{D68E4B30-7851-4C83-872C-73CB17EC5222}"/>
     <hyperlink ref="H16" r:id="rId17" xr:uid="{D73F1000-43A8-440E-9154-148CA29F608D}"/>
     <hyperlink ref="H297" r:id="rId18" xr:uid="{87D8789E-3527-45CB-96CC-A717E2A29CF4}"/>
+    <hyperlink ref="H299" r:id="rId19" xr:uid="{328A7EE8-6C93-4B2F-BFAA-D593F87BE671}"/>
+    <hyperlink ref="H304" r:id="rId20" xr:uid="{A3CEB787-A4DA-499F-A877-2709B0646565}"/>
+    <hyperlink ref="H303" r:id="rId21" xr:uid="{9AEB623B-37CB-4EFD-A4E5-06C08664DCD5}"/>
+    <hyperlink ref="H305" r:id="rId22" xr:uid="{38AF5094-2E8A-4F1F-8FBA-18FEBEAFFB8F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId19"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId23"/>
 </worksheet>
 </file>
--- a/stores.xlsx
+++ b/stores.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\YUMIN\Desktop\B0KT2A_RSVN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D48EB21F-E98A-4FDA-B699-B492D70B591C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0DBBEB4-72AD-4C6B-AF16-1CBA9D9F0F2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{ABFC3117-FCCB-4FF3-804A-FE19451A2004}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1270" uniqueCount="1141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1275" uniqueCount="1146">
   <si>
     <t>룸익스케이프 WHITE</t>
   </si>
@@ -2435,10 +2435,6 @@
   </si>
   <si>
     <t>http://jamsil.cubeescape.co.kr/</t>
-  </si>
-  <si>
-    <t>화-&gt;수 0:00&lt;BR&gt;다음주 토~다다음주 금 1주일치 오픈</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>key_el</t>
@@ -3976,6 +3972,29 @@
   </si>
   <si>
     <t>소녀괴담,파파라치,이레이저,럭키가이,데이드림</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bk_hv</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BLACK H[-]AVEN</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4F : 마지막 기록</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>매주 화요일 오전 11:00 다음주 월~일 회차 오픈</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://naver.me/x2YJOVXU</t>
+  </si>
+  <si>
+    <t>화-&gt;수 0:00 다음주 토~다다음주 금 1주일치 오픈</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -4403,7 +4422,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D839462D-4719-40BB-8925-C1B9F93734CF}">
-  <dimension ref="A1:H329"/>
+  <dimension ref="A1:H330"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="2"/>
@@ -4411,7 +4430,7 @@
     <col min="3" max="4" width="9" style="2" customWidth="1"/>
     <col min="5" max="5" width="85.875" style="2" customWidth="1"/>
     <col min="6" max="6" width="9" style="2" customWidth="1"/>
-    <col min="7" max="7" width="5" style="2" customWidth="1"/>
+    <col min="7" max="7" width="66" style="2" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="62.75" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="16384" width="9" style="2"/>
   </cols>
@@ -4464,10 +4483,10 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="2" t="s">
+        <v>827</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>828</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>829</v>
       </c>
       <c r="C3" s="2">
         <v>7</v>
@@ -4476,7 +4495,7 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>638</v>
@@ -4484,10 +4503,10 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="2" t="s">
+        <v>830</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>831</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>832</v>
       </c>
       <c r="C4" s="2">
         <v>7</v>
@@ -4758,7 +4777,7 @@
       <c r="F16" s="3"/>
       <c r="G16" s="1"/>
       <c r="H16" s="7" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -4937,10 +4956,10 @@
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="2" t="s">
+        <v>832</v>
+      </c>
+      <c r="B25" s="1" t="s">
         <v>833</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>834</v>
       </c>
       <c r="C25" s="3">
         <v>15</v>
@@ -4949,12 +4968,12 @@
         <v>0</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="F25" s="3"/>
       <c r="G25" s="1"/>
       <c r="H25" s="11" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -5045,27 +5064,27 @@
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="2" t="s">
+        <v>790</v>
+      </c>
+      <c r="B30" s="1" t="s">
         <v>791</v>
       </c>
-      <c r="B30" s="1" t="s">
+      <c r="E30" s="1" t="s">
         <v>792</v>
       </c>
-      <c r="E30" s="1" t="s">
-        <v>793</v>
-      </c>
       <c r="F30" s="3">
         <v>1</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="2" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="C31" s="2">
         <v>20</v>
@@ -5074,112 +5093,112 @@
         <v>0</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="2" t="s">
+        <v>777</v>
+      </c>
+      <c r="B32" s="1" t="s">
         <v>778</v>
       </c>
-      <c r="B32" s="1" t="s">
+      <c r="E32" s="1" t="s">
         <v>779</v>
       </c>
-      <c r="E32" s="1" t="s">
-        <v>780</v>
-      </c>
       <c r="F32" s="3">
         <v>1</v>
       </c>
       <c r="H32" s="7" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="2" t="s">
+        <v>773</v>
+      </c>
+      <c r="B33" s="1" t="s">
         <v>774</v>
       </c>
-      <c r="B33" s="1" t="s">
+      <c r="E33" s="1" t="s">
         <v>775</v>
       </c>
-      <c r="E33" s="1" t="s">
+      <c r="F33" s="3">
+        <v>1</v>
+      </c>
+      <c r="H33" s="2" t="s">
         <v>776</v>
-      </c>
-      <c r="F33" s="3">
-        <v>1</v>
-      </c>
-      <c r="H33" s="2" t="s">
-        <v>777</v>
       </c>
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="2" t="s">
+        <v>784</v>
+      </c>
+      <c r="B34" s="1" t="s">
         <v>785</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="E34" s="1" t="s">
+        <v>788</v>
+      </c>
+      <c r="F34" s="3">
+        <v>1</v>
+      </c>
+      <c r="H34" s="2" t="s">
         <v>786</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>789</v>
-      </c>
-      <c r="F34" s="3">
-        <v>1</v>
-      </c>
-      <c r="H34" s="2" t="s">
-        <v>787</v>
       </c>
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="2" t="s">
+        <v>798</v>
+      </c>
+      <c r="B35" s="1" t="s">
         <v>799</v>
       </c>
-      <c r="B35" s="1" t="s">
+      <c r="E35" s="1" t="s">
         <v>800</v>
       </c>
-      <c r="E35" s="1" t="s">
-        <v>801</v>
-      </c>
       <c r="F35" s="3">
         <v>1</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
     </row>
     <row r="36" spans="1:8">
       <c r="A36" s="2" t="s">
+        <v>794</v>
+      </c>
+      <c r="B36" s="1" t="s">
         <v>795</v>
       </c>
-      <c r="B36" s="1" t="s">
+      <c r="E36" s="1" t="s">
         <v>796</v>
       </c>
-      <c r="E36" s="1" t="s">
-        <v>797</v>
-      </c>
       <c r="F36" s="3">
         <v>1</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
     </row>
     <row r="37" spans="1:8">
       <c r="A37" s="2" t="s">
+        <v>781</v>
+      </c>
+      <c r="B37" s="1" t="s">
         <v>782</v>
       </c>
-      <c r="B37" s="1" t="s">
+      <c r="E37" s="1" t="s">
         <v>783</v>
       </c>
-      <c r="E37" s="1" t="s">
-        <v>784</v>
-      </c>
       <c r="F37" s="3">
         <v>1</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -5218,7 +5237,7 @@
         <v>1</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
     </row>
     <row r="40" spans="1:8">
@@ -5235,7 +5254,7 @@
         <v>1</v>
       </c>
       <c r="H40" s="9" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -5623,7 +5642,7 @@
         <v>1</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>697</v>
+        <v>1145</v>
       </c>
       <c r="H59" t="s">
         <v>647</v>
@@ -5653,10 +5672,10 @@
     </row>
     <row r="61" spans="1:8">
       <c r="A61" s="11" t="s">
+        <v>836</v>
+      </c>
+      <c r="B61" t="s">
         <v>837</v>
-      </c>
-      <c r="B61" t="s">
-        <v>838</v>
       </c>
       <c r="C61">
         <v>6</v>
@@ -5665,7 +5684,7 @@
         <v>0</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="F61" s="3"/>
       <c r="G61" s="1"/>
@@ -6244,38 +6263,38 @@
     </row>
     <row r="90" spans="1:8">
       <c r="A90" t="s">
+        <v>839</v>
+      </c>
+      <c r="B90" t="s">
         <v>840</v>
-      </c>
-      <c r="B90" t="s">
-        <v>841</v>
       </c>
       <c r="C90" s="3"/>
       <c r="D90" s="4"/>
       <c r="E90" s="1" t="s">
+        <v>841</v>
+      </c>
+      <c r="F90" s="3">
+        <v>1</v>
+      </c>
+      <c r="H90" s="11" t="s">
         <v>842</v>
-      </c>
-      <c r="F90" s="3">
-        <v>1</v>
-      </c>
-      <c r="H90" s="11" t="s">
-        <v>843</v>
       </c>
     </row>
     <row r="91" spans="1:8">
       <c r="A91" s="2" t="s">
+        <v>822</v>
+      </c>
+      <c r="B91" s="1" t="s">
         <v>823</v>
       </c>
-      <c r="B91" s="1" t="s">
+      <c r="E91" s="1" t="s">
         <v>824</v>
       </c>
-      <c r="E91" s="1" t="s">
+      <c r="F91" s="3">
+        <v>1</v>
+      </c>
+      <c r="H91" s="7" t="s">
         <v>825</v>
-      </c>
-      <c r="F91" s="3">
-        <v>1</v>
-      </c>
-      <c r="H91" s="7" t="s">
-        <v>826</v>
       </c>
     </row>
     <row r="92" spans="1:8">
@@ -6434,257 +6453,257 @@
     </row>
     <row r="99" spans="1:8">
       <c r="A99" s="2" t="s">
+        <v>730</v>
+      </c>
+      <c r="B99" s="1" t="s">
         <v>731</v>
       </c>
-      <c r="B99" s="1" t="s">
-        <v>732</v>
-      </c>
       <c r="E99" s="1" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="F99" s="3">
         <v>1</v>
       </c>
       <c r="H99" s="7" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
     </row>
     <row r="100" spans="1:8">
       <c r="A100" s="2" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="F100" s="3">
         <v>1</v>
       </c>
       <c r="H100" s="7" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
     </row>
     <row r="101" spans="1:8">
       <c r="A101" s="2" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="F101" s="3">
         <v>1</v>
       </c>
       <c r="H101" s="7" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
     </row>
     <row r="102" spans="1:8">
       <c r="A102" s="2" t="s">
+        <v>719</v>
+      </c>
+      <c r="B102" s="1" t="s">
         <v>720</v>
       </c>
-      <c r="B102" s="1" t="s">
-        <v>721</v>
-      </c>
       <c r="E102" s="1" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="F102" s="3">
         <v>1</v>
       </c>
       <c r="H102" s="7" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
     </row>
     <row r="103" spans="1:8">
       <c r="A103" s="2" t="s">
+        <v>717</v>
+      </c>
+      <c r="B103" s="1" t="s">
         <v>718</v>
       </c>
-      <c r="B103" s="1" t="s">
-        <v>719</v>
-      </c>
       <c r="E103" s="1" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="F103" s="3">
         <v>1</v>
       </c>
       <c r="H103" s="7" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
     </row>
     <row r="104" spans="1:8">
       <c r="A104" s="2" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="F104" s="3">
         <v>1</v>
       </c>
       <c r="H104" s="7" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
     </row>
     <row r="105" spans="1:8">
       <c r="A105" s="2" t="s">
+        <v>723</v>
+      </c>
+      <c r="B105" s="1" t="s">
         <v>724</v>
       </c>
-      <c r="B105" s="1" t="s">
-        <v>725</v>
-      </c>
       <c r="E105" s="1" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="F105" s="3">
         <v>1</v>
       </c>
       <c r="H105" s="7" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
     </row>
     <row r="106" spans="1:8">
       <c r="A106" s="2" t="s">
+        <v>727</v>
+      </c>
+      <c r="B106" s="1" t="s">
         <v>728</v>
       </c>
-      <c r="B106" s="1" t="s">
-        <v>729</v>
-      </c>
       <c r="E106" s="1" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="F106" s="3">
         <v>1</v>
       </c>
       <c r="H106" s="7" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
     </row>
     <row r="107" spans="1:8">
       <c r="A107" s="2" t="s">
+        <v>709</v>
+      </c>
+      <c r="B107" s="1" t="s">
         <v>710</v>
       </c>
-      <c r="B107" s="1" t="s">
-        <v>711</v>
-      </c>
       <c r="E107" s="1" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="F107" s="3">
         <v>1</v>
       </c>
       <c r="H107" s="7" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
     </row>
     <row r="108" spans="1:8">
       <c r="A108" s="2" t="s">
+        <v>732</v>
+      </c>
+      <c r="B108" s="1" t="s">
         <v>733</v>
       </c>
-      <c r="B108" s="1" t="s">
-        <v>734</v>
-      </c>
       <c r="E108" s="1" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="F108" s="3">
         <v>1</v>
       </c>
       <c r="H108" s="7" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
     </row>
     <row r="109" spans="1:8">
       <c r="A109" s="2" t="s">
+        <v>725</v>
+      </c>
+      <c r="B109" s="1" t="s">
         <v>726</v>
       </c>
-      <c r="B109" s="1" t="s">
-        <v>727</v>
-      </c>
       <c r="E109" s="1" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="F109" s="3">
         <v>1</v>
       </c>
       <c r="H109" s="7" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
     </row>
     <row r="110" spans="1:8">
       <c r="A110" s="2" t="s">
+        <v>705</v>
+      </c>
+      <c r="B110" s="1" t="s">
         <v>706</v>
       </c>
-      <c r="B110" s="1" t="s">
-        <v>707</v>
-      </c>
       <c r="E110" s="1" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="F110" s="3">
         <v>1</v>
       </c>
       <c r="H110" s="7" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
     </row>
     <row r="111" spans="1:8">
       <c r="A111" s="2" t="s">
+        <v>707</v>
+      </c>
+      <c r="B111" s="1" t="s">
         <v>708</v>
       </c>
-      <c r="B111" s="1" t="s">
-        <v>709</v>
-      </c>
       <c r="E111" s="1" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="F111" s="3">
         <v>1</v>
       </c>
       <c r="H111" s="7" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
     </row>
     <row r="112" spans="1:8">
       <c r="A112" s="2" t="s">
+        <v>711</v>
+      </c>
+      <c r="B112" s="1" t="s">
         <v>712</v>
       </c>
-      <c r="B112" s="1" t="s">
-        <v>713</v>
-      </c>
       <c r="E112" s="1" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="F112" s="3">
         <v>1</v>
       </c>
       <c r="H112" s="7" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
     </row>
     <row r="113" spans="1:8">
       <c r="A113" s="2" t="s">
+        <v>721</v>
+      </c>
+      <c r="B113" s="1" t="s">
         <v>722</v>
       </c>
-      <c r="B113" s="1" t="s">
-        <v>723</v>
-      </c>
       <c r="E113" s="1" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="F113" s="3">
         <v>1</v>
       </c>
       <c r="H113" s="7" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
     </row>
     <row r="114" spans="1:8">
@@ -6711,64 +6730,64 @@
     </row>
     <row r="115" spans="1:8">
       <c r="A115" t="s">
+        <v>843</v>
+      </c>
+      <c r="B115" t="s">
         <v>844</v>
-      </c>
-      <c r="B115" t="s">
-        <v>845</v>
       </c>
       <c r="C115" s="3"/>
       <c r="D115" s="4"/>
       <c r="E115" s="1" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="F115" s="3">
         <v>1</v>
       </c>
       <c r="G115" s="1"/>
       <c r="H115" s="11" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
     </row>
     <row r="116" spans="1:8">
       <c r="A116" t="s">
+        <v>847</v>
+      </c>
+      <c r="B116" t="s">
         <v>848</v>
-      </c>
-      <c r="B116" t="s">
-        <v>849</v>
       </c>
       <c r="C116" s="3"/>
       <c r="D116" s="4"/>
       <c r="E116" s="1" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="F116" s="3">
         <v>1</v>
       </c>
       <c r="G116" s="1"/>
       <c r="H116" s="11" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
     </row>
     <row r="117" spans="1:8">
       <c r="A117" t="s">
+        <v>851</v>
+      </c>
+      <c r="B117" t="s">
         <v>852</v>
-      </c>
-      <c r="B117" t="s">
-        <v>853</v>
       </c>
       <c r="C117" s="3"/>
       <c r="D117" s="4"/>
       <c r="E117" s="1" t="s">
+        <v>853</v>
+      </c>
+      <c r="F117" s="3">
+        <v>1</v>
+      </c>
+      <c r="G117" s="1" t="s">
         <v>854</v>
       </c>
-      <c r="F117" s="3">
-        <v>1</v>
-      </c>
-      <c r="G117" s="1" t="s">
+      <c r="H117" s="11" t="s">
         <v>855</v>
-      </c>
-      <c r="H117" s="11" t="s">
-        <v>856</v>
       </c>
     </row>
     <row r="118" spans="1:8">
@@ -6825,7 +6844,7 @@
       <c r="C120" s="1"/>
       <c r="D120" s="5"/>
       <c r="E120" s="1" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="F120" s="3">
         <v>1</v>
@@ -6837,19 +6856,19 @@
     </row>
     <row r="121" spans="1:8">
       <c r="A121" s="2" t="s">
+        <v>809</v>
+      </c>
+      <c r="B121" s="1" t="s">
         <v>810</v>
       </c>
-      <c r="B121" s="1" t="s">
+      <c r="E121" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="F121" s="3">
+        <v>1</v>
+      </c>
+      <c r="H121" s="7" t="s">
         <v>811</v>
-      </c>
-      <c r="E121" s="1" t="s">
-        <v>813</v>
-      </c>
-      <c r="F121" s="3">
-        <v>1</v>
-      </c>
-      <c r="H121" s="7" t="s">
-        <v>812</v>
       </c>
     </row>
     <row r="122" spans="1:8">
@@ -6876,115 +6895,115 @@
     </row>
     <row r="123" spans="1:8">
       <c r="A123" t="s">
+        <v>856</v>
+      </c>
+      <c r="B123" t="s">
         <v>857</v>
-      </c>
-      <c r="B123" t="s">
-        <v>858</v>
       </c>
       <c r="C123"/>
       <c r="D123" s="11"/>
       <c r="E123" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="F123" s="1">
         <v>1</v>
       </c>
       <c r="G123"/>
       <c r="H123" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
     </row>
     <row r="124" spans="1:8">
       <c r="A124" t="s">
+        <v>858</v>
+      </c>
+      <c r="B124" t="s">
         <v>859</v>
       </c>
-      <c r="B124" t="s">
-        <v>860</v>
-      </c>
       <c r="E124" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="F124" s="1">
         <v>1</v>
       </c>
       <c r="H124" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
     </row>
     <row r="125" spans="1:8">
       <c r="A125" t="s">
+        <v>860</v>
+      </c>
+      <c r="B125" t="s">
         <v>861</v>
       </c>
-      <c r="B125" t="s">
-        <v>862</v>
-      </c>
       <c r="E125" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="F125" s="1">
         <v>1</v>
       </c>
       <c r="H125" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
     </row>
     <row r="126" spans="1:8">
       <c r="A126" t="s">
+        <v>862</v>
+      </c>
+      <c r="B126" t="s">
         <v>863</v>
       </c>
-      <c r="B126" t="s">
-        <v>864</v>
-      </c>
       <c r="E126" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="F126" s="1">
         <v>1</v>
       </c>
       <c r="H126" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
     </row>
     <row r="127" spans="1:8">
       <c r="A127" t="s">
+        <v>864</v>
+      </c>
+      <c r="B127" t="s">
         <v>865</v>
       </c>
-      <c r="B127" t="s">
-        <v>866</v>
-      </c>
       <c r="E127" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="F127" s="1">
         <v>1</v>
       </c>
       <c r="H127" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
     </row>
     <row r="128" spans="1:8">
       <c r="A128" t="s">
+        <v>866</v>
+      </c>
+      <c r="B128" t="s">
         <v>867</v>
       </c>
-      <c r="B128" t="s">
-        <v>868</v>
-      </c>
       <c r="E128" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="F128" s="1">
         <v>1</v>
       </c>
       <c r="H128" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
     </row>
     <row r="129" spans="1:8">
       <c r="A129" t="s">
+        <v>868</v>
+      </c>
+      <c r="B129" t="s">
         <v>869</v>
-      </c>
-      <c r="B129" t="s">
-        <v>870</v>
       </c>
       <c r="C129" s="2">
         <v>6</v>
@@ -6993,36 +7012,36 @@
         <v>0</v>
       </c>
       <c r="E129" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="F129" s="1"/>
       <c r="H129" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
     </row>
     <row r="130" spans="1:8">
       <c r="A130" t="s">
+        <v>870</v>
+      </c>
+      <c r="B130" t="s">
         <v>871</v>
       </c>
-      <c r="B130" t="s">
-        <v>872</v>
-      </c>
       <c r="E130" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="F130" s="1">
         <v>1</v>
       </c>
       <c r="H130" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
     </row>
     <row r="131" spans="1:8">
       <c r="A131" t="s">
+        <v>872</v>
+      </c>
+      <c r="B131" t="s">
         <v>873</v>
-      </c>
-      <c r="B131" t="s">
-        <v>874</v>
       </c>
       <c r="C131" s="2">
         <v>6</v>
@@ -7031,45 +7050,45 @@
         <v>0</v>
       </c>
       <c r="E131" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="F131" s="1"/>
       <c r="H131" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
     </row>
     <row r="132" spans="1:8">
       <c r="A132" t="s">
+        <v>874</v>
+      </c>
+      <c r="B132" t="s">
         <v>875</v>
       </c>
-      <c r="B132" t="s">
-        <v>876</v>
-      </c>
       <c r="E132" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="F132" s="1">
         <v>1</v>
       </c>
       <c r="H132" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
     </row>
     <row r="133" spans="1:8">
       <c r="A133" t="s">
+        <v>1065</v>
+      </c>
+      <c r="B133" t="s">
         <v>1066</v>
       </c>
-      <c r="B133" t="s">
+      <c r="E133" t="s">
         <v>1067</v>
       </c>
-      <c r="E133" t="s">
-        <v>1068</v>
-      </c>
       <c r="F133" s="1">
         <v>1</v>
       </c>
       <c r="H133" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
     </row>
     <row r="134" spans="1:8">
@@ -7135,7 +7154,7 @@
       <c r="F136" s="3"/>
       <c r="G136" s="1"/>
       <c r="H136" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
     </row>
     <row r="137" spans="1:8">
@@ -7223,7 +7242,7 @@
       <c r="F140" s="3"/>
       <c r="G140" s="1"/>
       <c r="H140" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
     </row>
     <row r="141" spans="1:8">
@@ -7470,10 +7489,10 @@
     </row>
     <row r="152" spans="1:8">
       <c r="A152" s="11" t="s">
+        <v>888</v>
+      </c>
+      <c r="B152" s="11" t="s">
         <v>889</v>
-      </c>
-      <c r="B152" s="11" t="s">
-        <v>890</v>
       </c>
       <c r="C152">
         <v>14</v>
@@ -7485,495 +7504,495 @@
       <c r="F152"/>
       <c r="G152"/>
       <c r="H152" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
     </row>
     <row r="153" spans="1:8">
       <c r="A153" t="s">
+        <v>890</v>
+      </c>
+      <c r="B153" t="s">
         <v>891</v>
-      </c>
-      <c r="B153" t="s">
-        <v>892</v>
       </c>
       <c r="C153"/>
       <c r="D153"/>
       <c r="E153" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="F153">
         <v>1</v>
       </c>
       <c r="G153"/>
       <c r="H153" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
     </row>
     <row r="154" spans="1:8">
       <c r="A154" t="s">
+        <v>892</v>
+      </c>
+      <c r="B154" t="s">
         <v>893</v>
-      </c>
-      <c r="B154" t="s">
-        <v>894</v>
       </c>
       <c r="C154"/>
       <c r="D154"/>
       <c r="E154" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="F154">
         <v>1</v>
       </c>
       <c r="G154"/>
       <c r="H154" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
     </row>
     <row r="155" spans="1:8">
       <c r="A155" t="s">
+        <v>894</v>
+      </c>
+      <c r="B155" t="s">
         <v>895</v>
-      </c>
-      <c r="B155" t="s">
-        <v>896</v>
       </c>
       <c r="C155"/>
       <c r="D155"/>
       <c r="E155" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="F155">
         <v>1</v>
       </c>
       <c r="G155"/>
       <c r="H155" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
     </row>
     <row r="156" spans="1:8">
       <c r="A156" t="s">
+        <v>896</v>
+      </c>
+      <c r="B156" t="s">
         <v>897</v>
-      </c>
-      <c r="B156" t="s">
-        <v>898</v>
       </c>
       <c r="C156"/>
       <c r="D156"/>
       <c r="E156" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="F156">
         <v>1</v>
       </c>
       <c r="G156"/>
       <c r="H156" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
     </row>
     <row r="157" spans="1:8">
       <c r="A157" t="s">
+        <v>898</v>
+      </c>
+      <c r="B157" t="s">
         <v>899</v>
-      </c>
-      <c r="B157" t="s">
-        <v>900</v>
       </c>
       <c r="C157"/>
       <c r="D157"/>
       <c r="E157" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="F157">
         <v>1</v>
       </c>
       <c r="G157"/>
       <c r="H157" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
     </row>
     <row r="158" spans="1:8">
       <c r="A158" t="s">
+        <v>900</v>
+      </c>
+      <c r="B158" t="s">
         <v>901</v>
-      </c>
-      <c r="B158" t="s">
-        <v>902</v>
       </c>
       <c r="C158"/>
       <c r="D158"/>
       <c r="E158" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="F158">
         <v>1</v>
       </c>
       <c r="G158"/>
       <c r="H158" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
     </row>
     <row r="159" spans="1:8">
       <c r="A159" t="s">
+        <v>902</v>
+      </c>
+      <c r="B159" t="s">
         <v>903</v>
-      </c>
-      <c r="B159" t="s">
-        <v>904</v>
       </c>
       <c r="C159"/>
       <c r="D159"/>
       <c r="E159" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="F159">
         <v>1</v>
       </c>
       <c r="G159"/>
       <c r="H159" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
     </row>
     <row r="160" spans="1:8">
       <c r="A160" t="s">
+        <v>904</v>
+      </c>
+      <c r="B160" t="s">
         <v>905</v>
-      </c>
-      <c r="B160" t="s">
-        <v>906</v>
       </c>
       <c r="C160"/>
       <c r="D160"/>
       <c r="E160" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="F160">
         <v>1</v>
       </c>
       <c r="G160"/>
       <c r="H160" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
     </row>
     <row r="161" spans="1:8">
       <c r="A161" t="s">
+        <v>906</v>
+      </c>
+      <c r="B161" t="s">
         <v>907</v>
-      </c>
-      <c r="B161" t="s">
-        <v>908</v>
       </c>
       <c r="C161"/>
       <c r="D161"/>
       <c r="E161" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="F161">
         <v>1</v>
       </c>
       <c r="G161"/>
       <c r="H161" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
     </row>
     <row r="162" spans="1:8">
       <c r="A162" t="s">
+        <v>908</v>
+      </c>
+      <c r="B162" t="s">
         <v>909</v>
-      </c>
-      <c r="B162" t="s">
-        <v>910</v>
       </c>
       <c r="C162"/>
       <c r="D162"/>
       <c r="E162" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="F162">
         <v>1</v>
       </c>
       <c r="G162"/>
       <c r="H162" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
     </row>
     <row r="163" spans="1:8">
       <c r="A163" t="s">
+        <v>910</v>
+      </c>
+      <c r="B163" t="s">
         <v>911</v>
-      </c>
-      <c r="B163" t="s">
-        <v>912</v>
       </c>
       <c r="C163"/>
       <c r="D163"/>
       <c r="E163" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="F163">
         <v>1</v>
       </c>
       <c r="G163"/>
       <c r="H163" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
     </row>
     <row r="164" spans="1:8">
       <c r="A164" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="B164" s="12" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="C164"/>
       <c r="D164"/>
       <c r="E164" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="F164">
         <v>1</v>
       </c>
       <c r="G164"/>
       <c r="H164" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
     </row>
     <row r="165" spans="1:8">
       <c r="A165" t="s">
+        <v>913</v>
+      </c>
+      <c r="B165" t="s">
         <v>914</v>
-      </c>
-      <c r="B165" t="s">
-        <v>915</v>
       </c>
       <c r="C165"/>
       <c r="D165"/>
       <c r="E165" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="F165">
         <v>1</v>
       </c>
       <c r="G165"/>
       <c r="H165" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
     </row>
     <row r="166" spans="1:8">
       <c r="A166" t="s">
+        <v>915</v>
+      </c>
+      <c r="B166" t="s">
         <v>916</v>
-      </c>
-      <c r="B166" t="s">
-        <v>917</v>
       </c>
       <c r="C166"/>
       <c r="D166"/>
       <c r="E166" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="F166">
         <v>1</v>
       </c>
       <c r="G166"/>
       <c r="H166" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
     </row>
     <row r="167" spans="1:8">
       <c r="A167" t="s">
+        <v>917</v>
+      </c>
+      <c r="B167" t="s">
         <v>918</v>
-      </c>
-      <c r="B167" t="s">
-        <v>919</v>
       </c>
       <c r="C167"/>
       <c r="D167"/>
       <c r="E167" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="F167">
         <v>1</v>
       </c>
       <c r="G167"/>
       <c r="H167" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
     </row>
     <row r="168" spans="1:8">
       <c r="A168" t="s">
+        <v>919</v>
+      </c>
+      <c r="B168" t="s">
         <v>920</v>
-      </c>
-      <c r="B168" t="s">
-        <v>921</v>
       </c>
       <c r="C168"/>
       <c r="D168"/>
       <c r="E168" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="F168">
         <v>1</v>
       </c>
       <c r="G168"/>
       <c r="H168" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
     </row>
     <row r="169" spans="1:8">
       <c r="A169" t="s">
+        <v>921</v>
+      </c>
+      <c r="B169" t="s">
         <v>922</v>
-      </c>
-      <c r="B169" t="s">
-        <v>923</v>
       </c>
       <c r="C169"/>
       <c r="D169"/>
       <c r="E169" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="F169">
         <v>1</v>
       </c>
       <c r="G169"/>
       <c r="H169" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
     </row>
     <row r="170" spans="1:8">
       <c r="A170" t="s">
+        <v>923</v>
+      </c>
+      <c r="B170" t="s">
         <v>924</v>
-      </c>
-      <c r="B170" t="s">
-        <v>925</v>
       </c>
       <c r="C170"/>
       <c r="D170"/>
       <c r="E170" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F170">
         <v>1</v>
       </c>
       <c r="G170"/>
       <c r="H170" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
     </row>
     <row r="171" spans="1:8">
       <c r="A171" t="s">
+        <v>925</v>
+      </c>
+      <c r="B171" t="s">
         <v>926</v>
-      </c>
-      <c r="B171" t="s">
-        <v>927</v>
       </c>
       <c r="C171"/>
       <c r="D171"/>
       <c r="E171" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="F171">
         <v>1</v>
       </c>
       <c r="G171"/>
       <c r="H171" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
     </row>
     <row r="172" spans="1:8">
       <c r="A172" t="s">
+        <v>927</v>
+      </c>
+      <c r="B172" t="s">
         <v>928</v>
-      </c>
-      <c r="B172" t="s">
-        <v>929</v>
       </c>
       <c r="C172"/>
       <c r="D172"/>
       <c r="E172" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="F172">
         <v>1</v>
       </c>
       <c r="G172"/>
       <c r="H172" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
     </row>
     <row r="173" spans="1:8">
       <c r="A173" t="s">
+        <v>929</v>
+      </c>
+      <c r="B173" t="s">
         <v>930</v>
-      </c>
-      <c r="B173" t="s">
-        <v>931</v>
       </c>
       <c r="C173"/>
       <c r="D173"/>
       <c r="E173" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="F173">
         <v>1</v>
       </c>
       <c r="G173"/>
       <c r="H173" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
     </row>
     <row r="174" spans="1:8">
       <c r="A174" t="s">
+        <v>931</v>
+      </c>
+      <c r="B174" t="s">
         <v>932</v>
-      </c>
-      <c r="B174" t="s">
-        <v>933</v>
       </c>
       <c r="C174"/>
       <c r="D174"/>
       <c r="E174" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="F174">
         <v>1</v>
       </c>
       <c r="G174"/>
       <c r="H174" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
     </row>
     <row r="175" spans="1:8">
       <c r="A175" t="s">
+        <v>933</v>
+      </c>
+      <c r="B175" t="s">
         <v>934</v>
-      </c>
-      <c r="B175" t="s">
-        <v>935</v>
       </c>
       <c r="C175"/>
       <c r="D175"/>
       <c r="E175" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="F175">
         <v>1</v>
       </c>
       <c r="G175"/>
       <c r="H175" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
     </row>
     <row r="176" spans="1:8">
       <c r="A176" t="s">
+        <v>935</v>
+      </c>
+      <c r="B176" t="s">
         <v>936</v>
-      </c>
-      <c r="B176" t="s">
-        <v>937</v>
       </c>
       <c r="C176"/>
       <c r="D176"/>
       <c r="E176" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="F176">
         <v>1</v>
       </c>
       <c r="G176"/>
       <c r="H176" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
     </row>
     <row r="177" spans="1:8">
       <c r="A177" t="s">
+        <v>937</v>
+      </c>
+      <c r="B177" t="s">
         <v>938</v>
-      </c>
-      <c r="B177" t="s">
-        <v>939</v>
       </c>
       <c r="C177">
         <v>14</v>
@@ -7982,100 +8001,100 @@
         <v>0</v>
       </c>
       <c r="E177" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="F177"/>
       <c r="G177"/>
       <c r="H177" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
     </row>
     <row r="178" spans="1:8">
       <c r="A178" t="s">
+        <v>939</v>
+      </c>
+      <c r="B178" t="s">
         <v>940</v>
-      </c>
-      <c r="B178" t="s">
-        <v>941</v>
       </c>
       <c r="C178"/>
       <c r="D178"/>
       <c r="E178" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="F178">
         <v>1</v>
       </c>
       <c r="G178"/>
       <c r="H178" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
     </row>
     <row r="179" spans="1:8">
       <c r="A179" t="s">
+        <v>941</v>
+      </c>
+      <c r="B179" t="s">
         <v>942</v>
-      </c>
-      <c r="B179" t="s">
-        <v>943</v>
       </c>
       <c r="C179"/>
       <c r="D179"/>
       <c r="E179" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="F179">
         <v>1</v>
       </c>
       <c r="G179"/>
       <c r="H179" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
     </row>
     <row r="180" spans="1:8">
       <c r="A180" s="12" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="B180" s="12" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="C180"/>
       <c r="D180"/>
       <c r="E180" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="F180">
         <v>1</v>
       </c>
       <c r="G180"/>
       <c r="H180" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
     </row>
     <row r="181" spans="1:8">
       <c r="A181" t="s">
+        <v>944</v>
+      </c>
+      <c r="B181" t="s">
         <v>945</v>
-      </c>
-      <c r="B181" t="s">
-        <v>946</v>
       </c>
       <c r="C181"/>
       <c r="D181"/>
       <c r="E181" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="F181">
         <v>1</v>
       </c>
       <c r="G181"/>
       <c r="H181" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
     </row>
     <row r="182" spans="1:8">
       <c r="A182" t="s">
+        <v>946</v>
+      </c>
+      <c r="B182" t="s">
         <v>947</v>
-      </c>
-      <c r="B182" t="s">
-        <v>948</v>
       </c>
       <c r="C182">
         <v>14</v>
@@ -8084,152 +8103,152 @@
         <v>0</v>
       </c>
       <c r="E182" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="F182"/>
       <c r="G182"/>
       <c r="H182" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
     </row>
     <row r="183" spans="1:8">
       <c r="A183" t="s">
+        <v>948</v>
+      </c>
+      <c r="B183" t="s">
         <v>949</v>
-      </c>
-      <c r="B183" t="s">
-        <v>950</v>
       </c>
       <c r="C183"/>
       <c r="D183"/>
       <c r="E183" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="F183">
         <v>1</v>
       </c>
       <c r="G183"/>
       <c r="H183" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
     </row>
     <row r="184" spans="1:8">
       <c r="A184" t="s">
+        <v>950</v>
+      </c>
+      <c r="B184" t="s">
         <v>951</v>
-      </c>
-      <c r="B184" t="s">
-        <v>952</v>
       </c>
       <c r="C184"/>
       <c r="D184"/>
       <c r="E184" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="F184">
         <v>1</v>
       </c>
       <c r="G184"/>
       <c r="H184" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
     </row>
     <row r="185" spans="1:8">
       <c r="A185" t="s">
+        <v>952</v>
+      </c>
+      <c r="B185" t="s">
         <v>953</v>
-      </c>
-      <c r="B185" t="s">
-        <v>954</v>
       </c>
       <c r="C185"/>
       <c r="D185"/>
       <c r="E185" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="F185">
         <v>1</v>
       </c>
       <c r="G185"/>
       <c r="H185" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
     </row>
     <row r="186" spans="1:8">
       <c r="A186" t="s">
+        <v>954</v>
+      </c>
+      <c r="B186" t="s">
         <v>955</v>
-      </c>
-      <c r="B186" t="s">
-        <v>956</v>
       </c>
       <c r="C186"/>
       <c r="D186"/>
       <c r="E186" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="F186">
         <v>1</v>
       </c>
       <c r="G186"/>
       <c r="H186" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
     </row>
     <row r="187" spans="1:8">
       <c r="A187" t="s">
+        <v>956</v>
+      </c>
+      <c r="B187" t="s">
         <v>957</v>
-      </c>
-      <c r="B187" t="s">
-        <v>958</v>
       </c>
       <c r="C187"/>
       <c r="D187"/>
       <c r="E187" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="F187">
         <v>1</v>
       </c>
       <c r="G187"/>
       <c r="H187" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
     </row>
     <row r="188" spans="1:8">
       <c r="A188" t="s">
+        <v>958</v>
+      </c>
+      <c r="B188" t="s">
         <v>959</v>
-      </c>
-      <c r="B188" t="s">
-        <v>960</v>
       </c>
       <c r="C188"/>
       <c r="D188"/>
       <c r="E188" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="F188">
         <v>1</v>
       </c>
       <c r="G188"/>
       <c r="H188" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
     </row>
     <row r="189" spans="1:8">
       <c r="A189" t="s">
+        <v>1056</v>
+      </c>
+      <c r="B189" t="s">
         <v>1057</v>
-      </c>
-      <c r="B189" t="s">
-        <v>1058</v>
       </c>
       <c r="C189"/>
       <c r="D189"/>
       <c r="E189" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="F189">
         <v>1</v>
       </c>
       <c r="G189"/>
       <c r="H189" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
     </row>
     <row r="190" spans="1:8">
@@ -8251,7 +8270,7 @@
       <c r="F190" s="3"/>
       <c r="G190" s="1"/>
       <c r="H190" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
     </row>
     <row r="191" spans="1:8">
@@ -8306,13 +8325,13 @@
         <v>509</v>
       </c>
       <c r="E193" s="1" t="s">
+        <v>767</v>
+      </c>
+      <c r="F193" s="2">
+        <v>1</v>
+      </c>
+      <c r="G193" s="2" t="s">
         <v>768</v>
-      </c>
-      <c r="F193" s="2">
-        <v>1</v>
-      </c>
-      <c r="G193" s="2" t="s">
-        <v>769</v>
       </c>
       <c r="H193" s="2" t="s">
         <v>623</v>
@@ -8326,13 +8345,13 @@
         <v>510</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="F194" s="2">
         <v>1</v>
       </c>
       <c r="G194" s="2" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="H194" s="2" t="s">
         <v>624</v>
@@ -8346,13 +8365,13 @@
         <v>510</v>
       </c>
       <c r="E195" s="1" t="s">
+        <v>770</v>
+      </c>
+      <c r="F195" s="2">
+        <v>1</v>
+      </c>
+      <c r="G195" s="2" t="s">
         <v>771</v>
-      </c>
-      <c r="F195" s="2">
-        <v>1</v>
-      </c>
-      <c r="G195" s="2" t="s">
-        <v>772</v>
       </c>
       <c r="H195" s="2" t="s">
         <v>624</v>
@@ -8376,25 +8395,25 @@
       </c>
       <c r="F196" s="3"/>
       <c r="H196" s="2" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="197" spans="1:8">
       <c r="A197" s="2" t="s">
+        <v>813</v>
+      </c>
+      <c r="B197" s="1" t="s">
         <v>814</v>
-      </c>
-      <c r="B197" s="1" t="s">
-        <v>815</v>
       </c>
       <c r="D197" s="6"/>
       <c r="E197" s="1" t="s">
+        <v>815</v>
+      </c>
+      <c r="F197" s="3">
+        <v>1</v>
+      </c>
+      <c r="H197" s="7" t="s">
         <v>816</v>
-      </c>
-      <c r="F197" s="3">
-        <v>1</v>
-      </c>
-      <c r="H197" s="7" t="s">
-        <v>817</v>
       </c>
     </row>
     <row r="198" spans="1:8">
@@ -8436,7 +8455,7 @@
         <v>652</v>
       </c>
       <c r="H199" s="2" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="200" spans="1:8">
@@ -8456,35 +8475,35 @@
         <v>653</v>
       </c>
       <c r="H200" s="2" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="201" spans="1:8">
       <c r="A201" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="B201" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="C201"/>
       <c r="D201" s="11"/>
       <c r="E201" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="F201">
         <v>1</v>
       </c>
       <c r="G201"/>
       <c r="H201" s="11" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="202" spans="1:8">
       <c r="A202" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="B202" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="C202">
         <v>10</v>
@@ -8493,32 +8512,32 @@
         <v>0</v>
       </c>
       <c r="E202" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="F202"/>
       <c r="G202"/>
       <c r="H202" s="11" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="203" spans="1:8">
       <c r="A203" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="B203" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="C203"/>
       <c r="D203" s="11"/>
       <c r="E203" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="F203">
         <v>1</v>
       </c>
       <c r="G203"/>
       <c r="H203" s="11" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="204" spans="1:8">
@@ -8622,15 +8641,15 @@
         <v>1</v>
       </c>
       <c r="H208" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
     </row>
     <row r="209" spans="1:8">
       <c r="A209" t="s">
+        <v>999</v>
+      </c>
+      <c r="B209" t="s">
         <v>1000</v>
-      </c>
-      <c r="B209" t="s">
-        <v>1001</v>
       </c>
       <c r="C209">
         <v>15</v>
@@ -8639,20 +8658,20 @@
         <v>0</v>
       </c>
       <c r="E209" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="F209"/>
       <c r="G209"/>
       <c r="H209" s="11" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="210" spans="1:8">
       <c r="A210" t="s">
+        <v>1003</v>
+      </c>
+      <c r="B210" t="s">
         <v>1004</v>
-      </c>
-      <c r="B210" t="s">
-        <v>1005</v>
       </c>
       <c r="C210">
         <v>15</v>
@@ -8661,20 +8680,20 @@
         <v>0</v>
       </c>
       <c r="E210" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="F210"/>
       <c r="G210"/>
       <c r="H210" s="11" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="211" spans="1:8">
       <c r="A211" t="s">
+        <v>1007</v>
+      </c>
+      <c r="B211" t="s">
         <v>1008</v>
-      </c>
-      <c r="B211" t="s">
-        <v>1009</v>
       </c>
       <c r="C211">
         <v>15</v>
@@ -8683,20 +8702,20 @@
         <v>0</v>
       </c>
       <c r="E211" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="F211"/>
       <c r="G211"/>
       <c r="H211" s="11" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="212" spans="1:8">
       <c r="A212" t="s">
+        <v>1011</v>
+      </c>
+      <c r="B212" t="s">
         <v>1012</v>
-      </c>
-      <c r="B212" t="s">
-        <v>1013</v>
       </c>
       <c r="C212">
         <v>20</v>
@@ -8705,20 +8724,20 @@
         <v>0</v>
       </c>
       <c r="E212" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="F212"/>
       <c r="G212"/>
       <c r="H212" s="11" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="213" spans="1:8">
       <c r="A213" t="s">
+        <v>1015</v>
+      </c>
+      <c r="B213" t="s">
         <v>1016</v>
-      </c>
-      <c r="B213" t="s">
-        <v>1017</v>
       </c>
       <c r="C213">
         <v>15</v>
@@ -8727,12 +8746,12 @@
         <v>0</v>
       </c>
       <c r="E213" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="F213"/>
       <c r="G213"/>
       <c r="H213" s="11" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="214" spans="1:8">
@@ -8859,7 +8878,7 @@
         <v>0</v>
       </c>
       <c r="E219" s="1" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="F219" s="3"/>
       <c r="G219" s="1"/>
@@ -8963,7 +8982,7 @@
         <v>0</v>
       </c>
       <c r="E224" s="1" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="F224" s="3"/>
       <c r="G224" s="1"/>
@@ -8995,10 +9014,10 @@
     </row>
     <row r="226" spans="1:8">
       <c r="A226" s="2" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B226" s="1" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="C226" s="2">
         <v>7</v>
@@ -9007,11 +9026,11 @@
         <v>0.95833333333333337</v>
       </c>
       <c r="E226" s="1" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="F226" s="3"/>
       <c r="H226" s="7" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
     </row>
     <row r="227" spans="1:8">
@@ -9133,7 +9152,7 @@
         <v>0</v>
       </c>
       <c r="E232" s="1" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="F232" s="3"/>
       <c r="G232" s="1"/>
@@ -9187,10 +9206,10 @@
     </row>
     <row r="235" spans="1:8">
       <c r="A235" t="s">
+        <v>1021</v>
+      </c>
+      <c r="B235" t="s">
         <v>1022</v>
-      </c>
-      <c r="B235" t="s">
-        <v>1023</v>
       </c>
       <c r="C235">
         <v>6</v>
@@ -9199,20 +9218,20 @@
         <v>0</v>
       </c>
       <c r="E235" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="F235"/>
       <c r="G235"/>
       <c r="H235" s="7" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="236" spans="1:8">
       <c r="A236" s="11" t="s">
+        <v>1025</v>
+      </c>
+      <c r="B236" t="s">
         <v>1026</v>
-      </c>
-      <c r="B236" t="s">
-        <v>1027</v>
       </c>
       <c r="C236" s="3">
         <v>7</v>
@@ -9221,12 +9240,12 @@
         <v>0.91666666666666663</v>
       </c>
       <c r="E236" s="1" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="F236"/>
       <c r="G236"/>
       <c r="H236" s="7" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="237" spans="1:8">
@@ -9275,22 +9294,22 @@
     </row>
     <row r="239" spans="1:8" customFormat="1">
       <c r="A239" s="2" t="s">
+        <v>805</v>
+      </c>
+      <c r="B239" s="1" t="s">
         <v>806</v>
-      </c>
-      <c r="B239" s="1" t="s">
-        <v>807</v>
       </c>
       <c r="C239" s="2"/>
       <c r="D239" s="2"/>
       <c r="E239" s="1" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="F239" s="3">
         <v>1</v>
       </c>
       <c r="G239" s="2"/>
       <c r="H239" s="7" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
     </row>
     <row r="240" spans="1:8">
@@ -9377,24 +9396,24 @@
     </row>
     <row r="244" spans="1:8">
       <c r="A244" s="11" t="s">
+        <v>1027</v>
+      </c>
+      <c r="B244" t="s">
         <v>1028</v>
-      </c>
-      <c r="B244" t="s">
-        <v>1029</v>
       </c>
       <c r="C244"/>
       <c r="D244" s="11"/>
       <c r="E244" t="s">
+        <v>1029</v>
+      </c>
+      <c r="F244">
+        <v>1</v>
+      </c>
+      <c r="G244" t="s">
         <v>1030</v>
       </c>
-      <c r="F244">
-        <v>1</v>
-      </c>
-      <c r="G244" t="s">
+      <c r="H244" s="7" t="s">
         <v>1031</v>
-      </c>
-      <c r="H244" s="7" t="s">
-        <v>1032</v>
       </c>
     </row>
     <row r="245" spans="1:8">
@@ -9411,7 +9430,7 @@
         <v>0.91666666666666663</v>
       </c>
       <c r="E245" s="1" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="F245" s="3"/>
       <c r="G245" s="1"/>
@@ -9467,7 +9486,7 @@
         <v>0</v>
       </c>
       <c r="E248" s="1" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="F248" s="3"/>
       <c r="G248" s="1"/>
@@ -9489,7 +9508,7 @@
         <v>0</v>
       </c>
       <c r="E249" s="1" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="F249" s="3"/>
       <c r="G249" s="1"/>
@@ -9763,10 +9782,10 @@
     </row>
     <row r="262" spans="1:8">
       <c r="A262" s="2" t="s">
+        <v>697</v>
+      </c>
+      <c r="B262" s="1" t="s">
         <v>698</v>
-      </c>
-      <c r="B262" s="1" t="s">
-        <v>699</v>
       </c>
       <c r="C262" s="2">
         <v>6</v>
@@ -9775,11 +9794,11 @@
         <v>0</v>
       </c>
       <c r="E262" s="1" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="F262" s="3"/>
       <c r="H262" s="7" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
     </row>
     <row r="263" spans="1:8">
@@ -9822,7 +9841,7 @@
       <c r="F264" s="3"/>
       <c r="G264" s="1"/>
       <c r="H264" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
     </row>
     <row r="265" spans="1:8">
@@ -9849,10 +9868,10 @@
     </row>
     <row r="266" spans="1:8">
       <c r="A266" s="2" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="B266" s="1" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="C266" s="2">
         <v>6</v>
@@ -9861,19 +9880,19 @@
         <v>0</v>
       </c>
       <c r="E266" s="1" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="F266" s="3"/>
       <c r="H266" s="7" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
     </row>
     <row r="267" spans="1:8">
       <c r="A267" s="2" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="B267" s="1" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C267" s="2">
         <v>6</v>
@@ -9882,19 +9901,19 @@
         <v>0</v>
       </c>
       <c r="E267" s="10" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="F267" s="3"/>
       <c r="H267" s="2" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
     </row>
     <row r="268" spans="1:8">
       <c r="A268" s="2" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="B268" s="1" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="C268" s="2">
         <v>6</v>
@@ -9903,19 +9922,19 @@
         <v>0</v>
       </c>
       <c r="E268" s="1" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="F268" s="3"/>
       <c r="H268" s="2" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
     </row>
     <row r="269" spans="1:8">
       <c r="A269" s="2" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="B269" s="1" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="C269" s="2">
         <v>6</v>
@@ -9924,11 +9943,11 @@
         <v>0</v>
       </c>
       <c r="E269" s="1" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="F269" s="3"/>
       <c r="H269" s="2" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
     </row>
     <row r="270" spans="1:8">
@@ -9947,7 +9966,7 @@
         <v>1</v>
       </c>
       <c r="G270" s="2" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="H270" t="s">
         <v>650</v>
@@ -10134,7 +10153,7 @@
         <v>460</v>
       </c>
       <c r="B279" s="1" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="C279" s="3">
         <v>6</v>
@@ -10525,129 +10544,129 @@
     </row>
     <row r="297" spans="1:8">
       <c r="A297" t="s">
+        <v>1047</v>
+      </c>
+      <c r="B297" s="1" t="s">
         <v>1048</v>
       </c>
-      <c r="B297" s="1" t="s">
-        <v>1049</v>
-      </c>
       <c r="E297" s="1" t="s">
+        <v>1052</v>
+      </c>
+      <c r="F297" s="2">
+        <v>1</v>
+      </c>
+      <c r="H297" s="7" t="s">
         <v>1053</v>
-      </c>
-      <c r="F297" s="2">
-        <v>1</v>
-      </c>
-      <c r="H297" s="7" t="s">
-        <v>1054</v>
       </c>
     </row>
     <row r="298" spans="1:8">
       <c r="A298" s="2" t="s">
+        <v>1068</v>
+      </c>
+      <c r="B298" s="1" t="s">
         <v>1069</v>
       </c>
-      <c r="B298" s="1" t="s">
+      <c r="E298" s="1" t="s">
         <v>1070</v>
       </c>
-      <c r="E298" s="1" t="s">
+      <c r="F298" s="2">
+        <v>1</v>
+      </c>
+      <c r="H298" s="2" t="s">
         <v>1071</v>
-      </c>
-      <c r="F298" s="2">
-        <v>1</v>
-      </c>
-      <c r="H298" s="2" t="s">
-        <v>1072</v>
       </c>
     </row>
     <row r="299" spans="1:8">
       <c r="A299" s="2" t="s">
+        <v>1073</v>
+      </c>
+      <c r="B299" s="1" t="s">
+        <v>1072</v>
+      </c>
+      <c r="E299" s="1" t="s">
+        <v>1075</v>
+      </c>
+      <c r="F299" s="2">
+        <v>1</v>
+      </c>
+      <c r="H299" s="7" t="s">
         <v>1074</v>
-      </c>
-      <c r="B299" s="1" t="s">
-        <v>1073</v>
-      </c>
-      <c r="E299" s="1" t="s">
-        <v>1076</v>
-      </c>
-      <c r="F299" s="2">
-        <v>1</v>
-      </c>
-      <c r="H299" s="7" t="s">
-        <v>1075</v>
       </c>
     </row>
     <row r="300" spans="1:8">
       <c r="A300" s="2" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="B300" s="1" t="s">
+        <v>1076</v>
+      </c>
+      <c r="E300" s="1" t="s">
         <v>1077</v>
       </c>
-      <c r="E300" s="1" t="s">
+      <c r="F300" s="2">
+        <v>1</v>
+      </c>
+      <c r="H300" s="2" t="s">
         <v>1078</v>
-      </c>
-      <c r="F300" s="2">
-        <v>1</v>
-      </c>
-      <c r="H300" s="2" t="s">
-        <v>1079</v>
       </c>
     </row>
     <row r="301" spans="1:8">
       <c r="A301" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="B301" s="1" t="s">
+        <v>1079</v>
+      </c>
+      <c r="E301" s="1" t="s">
         <v>1080</v>
       </c>
-      <c r="E301" s="1" t="s">
-        <v>1081</v>
-      </c>
       <c r="F301" s="2">
         <v>1</v>
       </c>
       <c r="H301" s="2" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="302" spans="1:8">
       <c r="A302" s="2" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="B302" s="1" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="E302" s="1" t="s">
+        <v>1085</v>
+      </c>
+      <c r="F302" s="2">
+        <v>1</v>
+      </c>
+      <c r="H302" s="2" t="s">
         <v>1086</v>
-      </c>
-      <c r="F302" s="2">
-        <v>1</v>
-      </c>
-      <c r="H302" s="2" t="s">
-        <v>1087</v>
       </c>
     </row>
     <row r="303" spans="1:8">
       <c r="A303" s="2" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="B303" s="1" t="s">
+        <v>1088</v>
+      </c>
+      <c r="E303" s="1" t="s">
         <v>1089</v>
       </c>
-      <c r="E303" s="1" t="s">
-        <v>1090</v>
-      </c>
       <c r="F303" s="2">
         <v>1</v>
       </c>
       <c r="H303" s="7" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="304" spans="1:8">
       <c r="A304" s="2" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="B304" s="1" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="C304" s="2">
         <v>6</v>
@@ -10656,207 +10675,227 @@
         <v>0</v>
       </c>
       <c r="E304" s="1" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="H304" s="7" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="305" spans="1:8">
       <c r="A305" s="2" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B305" s="1" t="s">
         <v>1096</v>
       </c>
-      <c r="B305" s="1" t="s">
-        <v>1097</v>
-      </c>
       <c r="E305" s="1" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="H305" s="7" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="306" spans="1:8">
       <c r="B306" s="1" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="307" spans="1:8">
       <c r="B307" s="1" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="308" spans="1:8">
       <c r="B308" s="1" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="309" spans="1:8">
       <c r="B309" s="1" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="310" spans="1:8">
       <c r="B310" s="1" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="311" spans="1:8">
       <c r="B311" s="1" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="312" spans="1:8">
       <c r="B312" s="1" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="313" spans="1:8">
       <c r="B313" s="1" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="314" spans="1:8">
       <c r="B314" s="1" t="s">
+        <v>1105</v>
+      </c>
+      <c r="E314" s="2" t="s">
         <v>1106</v>
-      </c>
-      <c r="E314" s="2" t="s">
-        <v>1107</v>
       </c>
     </row>
     <row r="315" spans="1:8">
       <c r="B315" s="1" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="316" spans="1:8">
       <c r="B316" s="1" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="317" spans="1:8">
       <c r="B317" s="1" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="318" spans="1:8">
       <c r="B318" s="1" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="319" spans="1:8">
       <c r="B319" s="1" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="320" spans="1:8">
       <c r="B320" s="1" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="321" spans="1:8">
       <c r="B321" s="1" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="322" spans="1:8">
       <c r="B322" s="1" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="323" spans="1:8">
       <c r="B323" s="1" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="324" spans="1:8">
       <c r="B324" s="1" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="325" spans="1:8">
       <c r="A325" s="2" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="B325" s="1" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="E325" s="2" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="F325" s="2">
         <v>1</v>
       </c>
       <c r="H325" s="2" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="326" spans="1:8">
       <c r="A326" s="2" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="B326" s="1" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="E326" s="2" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="F326" s="2">
         <v>1</v>
       </c>
       <c r="H326" s="2" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="327" spans="1:8">
       <c r="A327" s="2" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="B327" s="1" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="E327" s="2" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="F327" s="2">
         <v>1</v>
       </c>
       <c r="H327" s="2" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="328" spans="1:8">
       <c r="A328" s="2" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="B328" s="1" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="E328" s="2" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="F328" s="2">
         <v>1</v>
       </c>
       <c r="H328" s="2" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="329" spans="1:8">
       <c r="A329" s="2" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="B329" s="1" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="E329" s="2" t="s">
+        <v>1131</v>
+      </c>
+      <c r="F329" s="2">
+        <v>1</v>
+      </c>
+      <c r="H329" s="2" t="s">
         <v>1132</v>
       </c>
-      <c r="F329" s="2">
-        <v>1</v>
-      </c>
-      <c r="H329" s="2" t="s">
-        <v>1133</v>
+    </row>
+    <row r="330" spans="1:8">
+      <c r="A330" s="2" t="s">
+        <v>1140</v>
+      </c>
+      <c r="B330" s="1" t="s">
+        <v>1141</v>
+      </c>
+      <c r="E330" t="s">
+        <v>1142</v>
+      </c>
+      <c r="F330" s="2">
+        <v>1</v>
+      </c>
+      <c r="G330" s="2" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H330" s="7" t="s">
+        <v>1144</v>
       </c>
     </row>
   </sheetData>
@@ -10887,8 +10926,9 @@
     <hyperlink ref="H304" r:id="rId20" xr:uid="{A3CEB787-A4DA-499F-A877-2709B0646565}"/>
     <hyperlink ref="H303" r:id="rId21" xr:uid="{9AEB623B-37CB-4EFD-A4E5-06C08664DCD5}"/>
     <hyperlink ref="H305" r:id="rId22" xr:uid="{38AF5094-2E8A-4F1F-8FBA-18FEBEAFFB8F}"/>
+    <hyperlink ref="H330" r:id="rId23" xr:uid="{5EA546E0-B128-4386-8445-FD73AAE43FAB}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId23"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId24"/>
 </worksheet>
 </file>
--- a/stores.xlsx
+++ b/stores.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\YUMIN\Desktop\B0KT2A_RSVN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0DBBEB4-72AD-4C6B-AF16-1CBA9D9F0F2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B2D2E79-8A86-4E40-A8F4-619FE925A1FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{ABFC3117-FCCB-4FF3-804A-FE19451A2004}"/>
   </bookViews>
@@ -1044,10 +1044,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>신촌성심병원,CHASER:한마음폐공장,HANNA IS FIRED,한나는해고됐어,플로이드호텔,FLOYD HOTEL</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>악마와싸우는자,악싸자,기억을잃은자들,사라진성물,클라바리오봉쇄수도원,기잃자</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -3995,6 +3991,10 @@
   </si>
   <si>
     <t>화-&gt;수 0:00 다음주 토~다다음주 금 1주일치 오픈</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>신촌성심병원,CHASER:한마음폐공장,HANNA IS FIRED,한나는해고됐어</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -4437,7 +4437,7 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="2" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>11</v>
@@ -4463,10 +4463,10 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="2" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="C2" s="2">
         <v>7</v>
@@ -4475,18 +4475,18 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="E2" s="2" t="s">
+        <v>636</v>
+      </c>
+      <c r="H2" s="2" t="s">
         <v>637</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>638</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>827</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>828</v>
       </c>
       <c r="C3" s="2">
         <v>7</v>
@@ -4495,18 +4495,18 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="2" t="s">
+        <v>829</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>830</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>831</v>
       </c>
       <c r="C4" s="2">
         <v>7</v>
@@ -4515,12 +4515,12 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="2" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>317</v>
@@ -4532,17 +4532,17 @@
         <v>0</v>
       </c>
       <c r="E5" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="F5" s="3"/>
       <c r="G5" s="1"/>
       <c r="H5" s="1" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="2" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>268</v>
@@ -4559,12 +4559,12 @@
       <c r="F6" s="3"/>
       <c r="G6" s="1"/>
       <c r="H6" s="1" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="2" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>137</v>
@@ -4572,19 +4572,19 @@
       <c r="C7" s="3"/>
       <c r="D7" s="4"/>
       <c r="E7" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F7" s="3">
         <v>1</v>
       </c>
       <c r="G7" s="1"/>
       <c r="H7" s="1" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="2" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>262</v>
@@ -4601,12 +4601,12 @@
       <c r="F8" s="3"/>
       <c r="G8" s="1"/>
       <c r="H8" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="2" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>263</v>
@@ -4618,17 +4618,17 @@
         <v>0</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F9" s="3"/>
       <c r="G9" s="1"/>
       <c r="H9" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="2" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>133</v>
@@ -4645,12 +4645,12 @@
       <c r="F10" s="3"/>
       <c r="G10" s="1"/>
       <c r="H10" s="1" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="2" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>135</v>
@@ -4667,12 +4667,12 @@
       <c r="F11" s="3"/>
       <c r="G11" s="1"/>
       <c r="H11" s="1" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="2" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>233</v>
@@ -4689,12 +4689,12 @@
       <c r="F12" s="3"/>
       <c r="G12" s="1"/>
       <c r="H12" s="1" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="2" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>234</v>
@@ -4706,17 +4706,17 @@
         <v>0</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F13" s="3"/>
       <c r="G13" s="1"/>
       <c r="H13" s="1" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="2" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>235</v>
@@ -4733,12 +4733,12 @@
       <c r="F14" s="3"/>
       <c r="G14" s="1"/>
       <c r="H14" s="1" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>230</v>
@@ -4755,12 +4755,12 @@
       <c r="F15" s="3"/>
       <c r="G15" s="1"/>
       <c r="H15" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>231</v>
@@ -4777,12 +4777,12 @@
       <c r="F16" s="3"/>
       <c r="G16" s="1"/>
       <c r="H16" s="7" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="2" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>212</v>
@@ -4794,17 +4794,17 @@
         <v>0</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>318</v>
+        <v>1145</v>
       </c>
       <c r="F17" s="3"/>
       <c r="G17" s="1"/>
       <c r="H17" s="1" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="2" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>81</v>
@@ -4821,12 +4821,12 @@
       <c r="F18" s="3"/>
       <c r="G18" s="1"/>
       <c r="H18" s="1" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="2" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>83</v>
@@ -4843,12 +4843,12 @@
       <c r="F19" s="3"/>
       <c r="G19" s="1"/>
       <c r="H19" s="1" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="2" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>85</v>
@@ -4865,12 +4865,12 @@
       <c r="F20" s="3"/>
       <c r="G20" s="1"/>
       <c r="H20" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="2" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>79</v>
@@ -4887,32 +4887,32 @@
       <c r="F21" s="3"/>
       <c r="G21" s="1"/>
       <c r="H21" s="1" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="2" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C22" s="3"/>
       <c r="D22" s="4"/>
       <c r="E22" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F22" s="3">
         <v>1</v>
       </c>
       <c r="G22" s="1"/>
       <c r="H22" s="1" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="2" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>77</v>
@@ -4929,12 +4929,12 @@
       <c r="F23" s="3"/>
       <c r="G23" s="1"/>
       <c r="H23" s="1" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="2" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>75</v>
@@ -4951,15 +4951,15 @@
       <c r="F24" s="3"/>
       <c r="G24" s="1"/>
       <c r="H24" s="1" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="2" t="s">
+        <v>831</v>
+      </c>
+      <c r="B25" s="1" t="s">
         <v>832</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>833</v>
       </c>
       <c r="C25" s="3">
         <v>15</v>
@@ -4968,20 +4968,20 @@
         <v>0</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="F25" s="3"/>
       <c r="G25" s="1"/>
       <c r="H25" s="11" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="2" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C26" s="3">
         <v>6</v>
@@ -4990,19 +4990,19 @@
         <v>0</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="F26" s="3"/>
       <c r="H26" s="1" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="2" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C27" s="3">
         <v>6</v>
@@ -5011,16 +5011,16 @@
         <v>0</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F27" s="3"/>
       <c r="H27" s="1" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="2" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>138</v>
@@ -5037,12 +5037,12 @@
       <c r="F28" s="3"/>
       <c r="G28" s="1"/>
       <c r="H28" s="1" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="2" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>140</v>
@@ -5059,32 +5059,32 @@
       <c r="F29" s="3"/>
       <c r="G29" s="1"/>
       <c r="H29" s="1" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="2" t="s">
+        <v>789</v>
+      </c>
+      <c r="B30" s="1" t="s">
         <v>790</v>
       </c>
-      <c r="B30" s="1" t="s">
+      <c r="E30" s="1" t="s">
         <v>791</v>
       </c>
-      <c r="E30" s="1" t="s">
-        <v>792</v>
-      </c>
       <c r="F30" s="3">
         <v>1</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="2" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="C31" s="2">
         <v>20</v>
@@ -5093,120 +5093,120 @@
         <v>0</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="2" t="s">
+        <v>776</v>
+      </c>
+      <c r="B32" s="1" t="s">
         <v>777</v>
       </c>
-      <c r="B32" s="1" t="s">
+      <c r="E32" s="1" t="s">
         <v>778</v>
       </c>
-      <c r="E32" s="1" t="s">
-        <v>779</v>
-      </c>
       <c r="F32" s="3">
         <v>1</v>
       </c>
       <c r="H32" s="7" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="2" t="s">
+        <v>772</v>
+      </c>
+      <c r="B33" s="1" t="s">
         <v>773</v>
       </c>
-      <c r="B33" s="1" t="s">
+      <c r="E33" s="1" t="s">
         <v>774</v>
       </c>
-      <c r="E33" s="1" t="s">
+      <c r="F33" s="3">
+        <v>1</v>
+      </c>
+      <c r="H33" s="2" t="s">
         <v>775</v>
-      </c>
-      <c r="F33" s="3">
-        <v>1</v>
-      </c>
-      <c r="H33" s="2" t="s">
-        <v>776</v>
       </c>
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="2" t="s">
+        <v>783</v>
+      </c>
+      <c r="B34" s="1" t="s">
         <v>784</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="E34" s="1" t="s">
+        <v>787</v>
+      </c>
+      <c r="F34" s="3">
+        <v>1</v>
+      </c>
+      <c r="H34" s="2" t="s">
         <v>785</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>788</v>
-      </c>
-      <c r="F34" s="3">
-        <v>1</v>
-      </c>
-      <c r="H34" s="2" t="s">
-        <v>786</v>
       </c>
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="2" t="s">
+        <v>797</v>
+      </c>
+      <c r="B35" s="1" t="s">
         <v>798</v>
       </c>
-      <c r="B35" s="1" t="s">
+      <c r="E35" s="1" t="s">
         <v>799</v>
       </c>
-      <c r="E35" s="1" t="s">
-        <v>800</v>
-      </c>
       <c r="F35" s="3">
         <v>1</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
     </row>
     <row r="36" spans="1:8">
       <c r="A36" s="2" t="s">
+        <v>793</v>
+      </c>
+      <c r="B36" s="1" t="s">
         <v>794</v>
       </c>
-      <c r="B36" s="1" t="s">
+      <c r="E36" s="1" t="s">
         <v>795</v>
       </c>
-      <c r="E36" s="1" t="s">
-        <v>796</v>
-      </c>
       <c r="F36" s="3">
         <v>1</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
     </row>
     <row r="37" spans="1:8">
       <c r="A37" s="2" t="s">
+        <v>780</v>
+      </c>
+      <c r="B37" s="1" t="s">
         <v>781</v>
       </c>
-      <c r="B37" s="1" t="s">
+      <c r="E37" s="1" t="s">
         <v>782</v>
       </c>
-      <c r="E37" s="1" t="s">
-        <v>783</v>
-      </c>
       <c r="F37" s="3">
         <v>1</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="38" spans="1:8">
       <c r="A38" s="2" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C38" s="3">
         <v>6</v>
@@ -5220,52 +5220,52 @@
       <c r="F38" s="3"/>
       <c r="G38" s="1"/>
       <c r="H38" s="2" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
     </row>
     <row r="39" spans="1:8">
       <c r="A39" s="2" t="s">
+        <v>688</v>
+      </c>
+      <c r="B39" s="1" t="s">
         <v>689</v>
       </c>
-      <c r="B39" s="1" t="s">
-        <v>690</v>
-      </c>
       <c r="E39" s="1" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="F39" s="3">
         <v>1</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
     </row>
     <row r="40" spans="1:8">
       <c r="A40" s="2" t="s">
+        <v>690</v>
+      </c>
+      <c r="B40" s="1" t="s">
         <v>691</v>
       </c>
-      <c r="B40" s="1" t="s">
-        <v>692</v>
-      </c>
       <c r="E40" s="1" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="F40" s="3">
         <v>1</v>
       </c>
       <c r="H40" s="9" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="41" spans="1:8">
       <c r="A41" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B41" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="E41" s="1" t="s">
         <v>454</v>
-      </c>
-      <c r="E41" s="1" t="s">
-        <v>455</v>
       </c>
       <c r="F41" s="3">
         <v>1</v>
@@ -5273,7 +5273,7 @@
     </row>
     <row r="42" spans="1:8">
       <c r="A42" s="2" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>141</v>
@@ -5290,12 +5290,12 @@
       <c r="F42" s="3"/>
       <c r="G42" s="1"/>
       <c r="H42" s="1" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="43" spans="1:8">
       <c r="A43" s="2" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>153</v>
@@ -5310,12 +5310,12 @@
       </c>
       <c r="G43" s="1"/>
       <c r="H43" s="1" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="44" spans="1:8">
       <c r="A44" s="2" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>155</v>
@@ -5332,12 +5332,12 @@
       <c r="F44" s="3"/>
       <c r="G44" s="1"/>
       <c r="H44" s="1" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="45" spans="1:8">
       <c r="A45" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>143</v>
@@ -5354,12 +5354,12 @@
       <c r="F45" s="3"/>
       <c r="G45" s="1"/>
       <c r="H45" s="1" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
     <row r="46" spans="1:8">
       <c r="A46" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>145</v>
@@ -5376,12 +5376,12 @@
       <c r="F46" s="3"/>
       <c r="G46" s="1"/>
       <c r="H46" s="1" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="47" spans="1:8">
       <c r="A47" s="2" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>151</v>
@@ -5396,12 +5396,12 @@
       </c>
       <c r="G47" s="1"/>
       <c r="H47" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
     </row>
     <row r="48" spans="1:8">
       <c r="A48" s="2" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>149</v>
@@ -5416,12 +5416,12 @@
       </c>
       <c r="G48" s="1"/>
       <c r="H48" s="1" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="49" spans="1:8">
       <c r="A49" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>147</v>
@@ -5438,12 +5438,12 @@
       <c r="F49" s="3"/>
       <c r="G49" s="1"/>
       <c r="H49" s="1" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
     </row>
     <row r="50" spans="1:8">
       <c r="A50" s="2" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>8</v>
@@ -5455,17 +5455,17 @@
         <v>0</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="F50" s="3"/>
       <c r="G50" s="1"/>
       <c r="H50" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
     </row>
     <row r="51" spans="1:8">
       <c r="A51" s="2" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>246</v>
@@ -5482,12 +5482,12 @@
       <c r="F51" s="3"/>
       <c r="G51" s="1"/>
       <c r="H51" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
     </row>
     <row r="52" spans="1:8">
       <c r="A52" s="2" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>248</v>
@@ -5504,12 +5504,12 @@
       <c r="F52" s="3"/>
       <c r="G52" s="1"/>
       <c r="H52" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
     </row>
     <row r="53" spans="1:8">
       <c r="A53" s="2" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>250</v>
@@ -5526,12 +5526,12 @@
       <c r="F53" s="3"/>
       <c r="G53" s="1"/>
       <c r="H53" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
     </row>
     <row r="54" spans="1:8">
       <c r="A54" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>125</v>
@@ -5548,12 +5548,12 @@
       <c r="F54" s="3"/>
       <c r="G54" s="1"/>
       <c r="H54" s="1" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="55" spans="1:8">
       <c r="A55" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>293</v>
@@ -5570,12 +5570,12 @@
       <c r="F55" s="1"/>
       <c r="G55" s="1"/>
       <c r="H55" s="1" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="56" spans="1:8">
       <c r="A56" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>252</v>
@@ -5592,18 +5592,18 @@
         <v>254</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="57" spans="1:8">
       <c r="A57" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="F57" s="2">
         <v>1</v>
@@ -5611,46 +5611,46 @@
     </row>
     <row r="58" spans="1:8">
       <c r="A58" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="F58" s="3">
         <v>1</v>
       </c>
       <c r="H58" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
     </row>
     <row r="59" spans="1:8">
       <c r="A59" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="C59" s="3"/>
       <c r="D59" s="6"/>
       <c r="E59" s="1" t="s">
+        <v>645</v>
+      </c>
+      <c r="F59" s="3">
+        <v>1</v>
+      </c>
+      <c r="G59" s="1" t="s">
+        <v>1144</v>
+      </c>
+      <c r="H59" t="s">
         <v>646</v>
-      </c>
-      <c r="F59" s="3">
-        <v>1</v>
-      </c>
-      <c r="G59" s="1" t="s">
-        <v>1145</v>
-      </c>
-      <c r="H59" t="s">
-        <v>647</v>
       </c>
     </row>
     <row r="60" spans="1:8">
       <c r="A60" s="2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>127</v>
@@ -5667,15 +5667,15 @@
       <c r="F60" s="3"/>
       <c r="G60" s="1"/>
       <c r="H60" s="1" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="61" spans="1:8">
       <c r="A61" s="11" t="s">
+        <v>835</v>
+      </c>
+      <c r="B61" t="s">
         <v>836</v>
-      </c>
-      <c r="B61" t="s">
-        <v>837</v>
       </c>
       <c r="C61">
         <v>6</v>
@@ -5684,17 +5684,17 @@
         <v>0</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="F61" s="3"/>
       <c r="G61" s="1"/>
       <c r="H61" s="1" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="62" spans="1:8">
       <c r="A62" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>302</v>
@@ -5711,12 +5711,12 @@
       <c r="F62" s="3"/>
       <c r="G62" s="1"/>
       <c r="H62" s="1" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="63" spans="1:8">
       <c r="A63" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>301</v>
@@ -5731,12 +5731,12 @@
       </c>
       <c r="G63" s="1"/>
       <c r="H63" s="1" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="64" spans="1:8">
       <c r="A64" s="2" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>291</v>
@@ -5753,12 +5753,12 @@
       <c r="F64" s="3"/>
       <c r="G64" s="1"/>
       <c r="H64" s="1" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="65" spans="1:8">
       <c r="A65" s="2" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>2</v>
@@ -5775,12 +5775,12 @@
       <c r="F65" s="3"/>
       <c r="G65" s="1"/>
       <c r="H65" s="2" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="66" spans="1:8">
       <c r="A66" s="2" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>6</v>
@@ -5797,12 +5797,12 @@
       <c r="F66" s="3"/>
       <c r="G66" s="1"/>
       <c r="H66" s="2" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="67" spans="1:8">
       <c r="A67" s="2" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>4</v>
@@ -5819,12 +5819,12 @@
       <c r="F67" s="3"/>
       <c r="G67" s="1"/>
       <c r="H67" s="2" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="68" spans="1:8">
       <c r="A68" s="2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>0</v>
@@ -5841,12 +5841,12 @@
       <c r="F68" s="3"/>
       <c r="G68" s="1"/>
       <c r="H68" s="2" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="69" spans="1:8">
       <c r="A69" s="2" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>261</v>
@@ -5862,12 +5862,12 @@
       </c>
       <c r="F69" s="3"/>
       <c r="H69" s="1" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="70" spans="1:8">
       <c r="A70" s="2" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>181</v>
@@ -5881,12 +5881,12 @@
         <v>1</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
     </row>
     <row r="71" spans="1:8">
       <c r="A71" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>264</v>
@@ -5900,12 +5900,12 @@
         <v>1</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
     </row>
     <row r="72" spans="1:8">
       <c r="A72" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>179</v>
@@ -5919,12 +5919,12 @@
         <v>1</v>
       </c>
       <c r="H72" s="1" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="73" spans="1:8">
       <c r="A73" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>185</v>
@@ -5940,12 +5940,12 @@
       </c>
       <c r="F73" s="3"/>
       <c r="H73" s="1" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
     </row>
     <row r="74" spans="1:8">
       <c r="A74" s="2" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>183</v>
@@ -5961,12 +5961,12 @@
       </c>
       <c r="F74" s="3"/>
       <c r="H74" s="1" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
     </row>
     <row r="75" spans="1:8">
       <c r="A75" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>171</v>
@@ -5980,12 +5980,12 @@
         <v>1</v>
       </c>
       <c r="H75" s="1" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="76" spans="1:8">
       <c r="A76" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>173</v>
@@ -5999,12 +5999,12 @@
         <v>1</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="77" spans="1:8">
       <c r="A77" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>157</v>
@@ -6018,12 +6018,12 @@
         <v>1</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
     </row>
     <row r="78" spans="1:8">
       <c r="A78" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>187</v>
@@ -6039,12 +6039,12 @@
       </c>
       <c r="F78" s="3"/>
       <c r="H78" s="1" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
     </row>
     <row r="79" spans="1:8">
       <c r="A79" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>175</v>
@@ -6058,12 +6058,12 @@
         <v>1</v>
       </c>
       <c r="H79" s="1" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="80" spans="1:8">
       <c r="A80" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>177</v>
@@ -6079,12 +6079,12 @@
       </c>
       <c r="F80" s="3"/>
       <c r="H80" s="1" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="81" spans="1:8">
       <c r="A81" s="2" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>193</v>
@@ -6100,12 +6100,12 @@
       </c>
       <c r="F81" s="3"/>
       <c r="H81" s="1" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
     </row>
     <row r="82" spans="1:8">
       <c r="A82" s="2" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>191</v>
@@ -6121,12 +6121,12 @@
       </c>
       <c r="F82" s="3"/>
       <c r="H82" s="1" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="83" spans="1:8">
       <c r="A83" s="2" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>169</v>
@@ -6142,12 +6142,12 @@
       </c>
       <c r="F83" s="3"/>
       <c r="H83" s="1" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
     </row>
     <row r="84" spans="1:8">
       <c r="A84" s="2" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>167</v>
@@ -6161,12 +6161,12 @@
         <v>1</v>
       </c>
       <c r="H84" s="1" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
     </row>
     <row r="85" spans="1:8">
       <c r="A85" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>159</v>
@@ -6180,12 +6180,12 @@
         <v>1</v>
       </c>
       <c r="H85" s="1" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
     <row r="86" spans="1:8">
       <c r="A86" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>165</v>
@@ -6199,12 +6199,12 @@
         <v>1</v>
       </c>
       <c r="H86" s="1" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="87" spans="1:8">
       <c r="A87" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>163</v>
@@ -6218,12 +6218,12 @@
         <v>1</v>
       </c>
       <c r="H87" s="1" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="88" spans="1:8">
       <c r="A88" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>161</v>
@@ -6237,12 +6237,12 @@
         <v>1</v>
       </c>
       <c r="H88" s="1" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="89" spans="1:8">
       <c r="A89" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>189</v>
@@ -6258,48 +6258,48 @@
       </c>
       <c r="F89" s="3"/>
       <c r="H89" s="1" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
     </row>
     <row r="90" spans="1:8">
       <c r="A90" t="s">
+        <v>838</v>
+      </c>
+      <c r="B90" t="s">
         <v>839</v>
-      </c>
-      <c r="B90" t="s">
-        <v>840</v>
       </c>
       <c r="C90" s="3"/>
       <c r="D90" s="4"/>
       <c r="E90" s="1" t="s">
+        <v>840</v>
+      </c>
+      <c r="F90" s="3">
+        <v>1</v>
+      </c>
+      <c r="H90" s="11" t="s">
         <v>841</v>
-      </c>
-      <c r="F90" s="3">
-        <v>1</v>
-      </c>
-      <c r="H90" s="11" t="s">
-        <v>842</v>
       </c>
     </row>
     <row r="91" spans="1:8">
       <c r="A91" s="2" t="s">
+        <v>821</v>
+      </c>
+      <c r="B91" s="1" t="s">
         <v>822</v>
       </c>
-      <c r="B91" s="1" t="s">
+      <c r="E91" s="1" t="s">
         <v>823</v>
       </c>
-      <c r="E91" s="1" t="s">
+      <c r="F91" s="3">
+        <v>1</v>
+      </c>
+      <c r="H91" s="7" t="s">
         <v>824</v>
-      </c>
-      <c r="F91" s="3">
-        <v>1</v>
-      </c>
-      <c r="H91" s="7" t="s">
-        <v>825</v>
       </c>
     </row>
     <row r="92" spans="1:8">
       <c r="A92" s="2" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>98</v>
@@ -6316,15 +6316,15 @@
       <c r="F92" s="3"/>
       <c r="G92" s="1"/>
       <c r="H92" s="1" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
     </row>
     <row r="93" spans="1:8">
       <c r="A93" s="2" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C93" s="3">
         <v>7</v>
@@ -6338,12 +6338,12 @@
       <c r="F93" s="3"/>
       <c r="G93" s="1"/>
       <c r="H93" s="1" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
     </row>
     <row r="94" spans="1:8">
       <c r="A94" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>106</v>
@@ -6360,12 +6360,12 @@
       <c r="F94" s="3"/>
       <c r="G94" s="1"/>
       <c r="H94" s="1" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
     </row>
     <row r="95" spans="1:8">
       <c r="A95" s="2" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>112</v>
@@ -6382,15 +6382,15 @@
       <c r="F95" s="3"/>
       <c r="G95" s="1"/>
       <c r="H95" s="1" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
     </row>
     <row r="96" spans="1:8">
       <c r="A96" s="2" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C96" s="3">
         <v>7</v>
@@ -6404,15 +6404,15 @@
       <c r="F96" s="3"/>
       <c r="G96" s="1"/>
       <c r="H96" s="1" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
     </row>
     <row r="97" spans="1:8">
       <c r="A97" s="2" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C97" s="3">
         <v>7</v>
@@ -6426,15 +6426,15 @@
       <c r="F97" s="3"/>
       <c r="G97" s="1"/>
       <c r="H97" s="1" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
     </row>
     <row r="98" spans="1:8">
       <c r="A98" s="2" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C98" s="3">
         <v>7</v>
@@ -6448,267 +6448,267 @@
       <c r="F98" s="3"/>
       <c r="G98" s="1"/>
       <c r="H98" s="1" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
     </row>
     <row r="99" spans="1:8">
       <c r="A99" s="2" t="s">
+        <v>729</v>
+      </c>
+      <c r="B99" s="1" t="s">
         <v>730</v>
       </c>
-      <c r="B99" s="1" t="s">
-        <v>731</v>
-      </c>
       <c r="E99" s="1" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="F99" s="3">
         <v>1</v>
       </c>
       <c r="H99" s="7" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="100" spans="1:8">
       <c r="A100" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="F100" s="3">
         <v>1</v>
       </c>
       <c r="H100" s="7" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="101" spans="1:8">
       <c r="A101" s="2" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="F101" s="3">
         <v>1</v>
       </c>
       <c r="H101" s="7" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="102" spans="1:8">
       <c r="A102" s="2" t="s">
+        <v>718</v>
+      </c>
+      <c r="B102" s="1" t="s">
         <v>719</v>
       </c>
-      <c r="B102" s="1" t="s">
-        <v>720</v>
-      </c>
       <c r="E102" s="1" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="F102" s="3">
         <v>1</v>
       </c>
       <c r="H102" s="7" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="103" spans="1:8">
       <c r="A103" s="2" t="s">
+        <v>716</v>
+      </c>
+      <c r="B103" s="1" t="s">
         <v>717</v>
       </c>
-      <c r="B103" s="1" t="s">
-        <v>718</v>
-      </c>
       <c r="E103" s="1" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="F103" s="3">
         <v>1</v>
       </c>
       <c r="H103" s="7" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="104" spans="1:8">
       <c r="A104" s="2" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="F104" s="3">
         <v>1</v>
       </c>
       <c r="H104" s="7" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="105" spans="1:8">
       <c r="A105" s="2" t="s">
+        <v>722</v>
+      </c>
+      <c r="B105" s="1" t="s">
         <v>723</v>
       </c>
-      <c r="B105" s="1" t="s">
-        <v>724</v>
-      </c>
       <c r="E105" s="1" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="F105" s="3">
         <v>1</v>
       </c>
       <c r="H105" s="7" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="106" spans="1:8">
       <c r="A106" s="2" t="s">
+        <v>726</v>
+      </c>
+      <c r="B106" s="1" t="s">
         <v>727</v>
       </c>
-      <c r="B106" s="1" t="s">
-        <v>728</v>
-      </c>
       <c r="E106" s="1" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="F106" s="3">
         <v>1</v>
       </c>
       <c r="H106" s="7" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="107" spans="1:8">
       <c r="A107" s="2" t="s">
+        <v>708</v>
+      </c>
+      <c r="B107" s="1" t="s">
         <v>709</v>
       </c>
-      <c r="B107" s="1" t="s">
-        <v>710</v>
-      </c>
       <c r="E107" s="1" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="F107" s="3">
         <v>1</v>
       </c>
       <c r="H107" s="7" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="108" spans="1:8">
       <c r="A108" s="2" t="s">
+        <v>731</v>
+      </c>
+      <c r="B108" s="1" t="s">
         <v>732</v>
       </c>
-      <c r="B108" s="1" t="s">
-        <v>733</v>
-      </c>
       <c r="E108" s="1" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="F108" s="3">
         <v>1</v>
       </c>
       <c r="H108" s="7" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="109" spans="1:8">
       <c r="A109" s="2" t="s">
+        <v>724</v>
+      </c>
+      <c r="B109" s="1" t="s">
         <v>725</v>
       </c>
-      <c r="B109" s="1" t="s">
-        <v>726</v>
-      </c>
       <c r="E109" s="1" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="F109" s="3">
         <v>1</v>
       </c>
       <c r="H109" s="7" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="110" spans="1:8">
       <c r="A110" s="2" t="s">
+        <v>704</v>
+      </c>
+      <c r="B110" s="1" t="s">
         <v>705</v>
       </c>
-      <c r="B110" s="1" t="s">
-        <v>706</v>
-      </c>
       <c r="E110" s="1" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="F110" s="3">
         <v>1</v>
       </c>
       <c r="H110" s="7" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="111" spans="1:8">
       <c r="A111" s="2" t="s">
+        <v>706</v>
+      </c>
+      <c r="B111" s="1" t="s">
         <v>707</v>
       </c>
-      <c r="B111" s="1" t="s">
-        <v>708</v>
-      </c>
       <c r="E111" s="1" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="F111" s="3">
         <v>1</v>
       </c>
       <c r="H111" s="7" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="112" spans="1:8">
       <c r="A112" s="2" t="s">
+        <v>710</v>
+      </c>
+      <c r="B112" s="1" t="s">
         <v>711</v>
       </c>
-      <c r="B112" s="1" t="s">
-        <v>712</v>
-      </c>
       <c r="E112" s="1" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="F112" s="3">
         <v>1</v>
       </c>
       <c r="H112" s="7" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="113" spans="1:8">
       <c r="A113" s="2" t="s">
+        <v>720</v>
+      </c>
+      <c r="B113" s="1" t="s">
         <v>721</v>
       </c>
-      <c r="B113" s="1" t="s">
-        <v>722</v>
-      </c>
       <c r="E113" s="1" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="F113" s="3">
         <v>1</v>
       </c>
       <c r="H113" s="7" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="114" spans="1:8">
       <c r="A114" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B114" s="1" t="s">
         <v>244</v>
@@ -6725,77 +6725,77 @@
       <c r="F114" s="3"/>
       <c r="G114" s="1"/>
       <c r="H114" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
     </row>
     <row r="115" spans="1:8">
       <c r="A115" t="s">
+        <v>842</v>
+      </c>
+      <c r="B115" t="s">
         <v>843</v>
-      </c>
-      <c r="B115" t="s">
-        <v>844</v>
       </c>
       <c r="C115" s="3"/>
       <c r="D115" s="4"/>
       <c r="E115" s="1" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="F115" s="3">
         <v>1</v>
       </c>
       <c r="G115" s="1"/>
       <c r="H115" s="11" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
     </row>
     <row r="116" spans="1:8">
       <c r="A116" t="s">
+        <v>846</v>
+      </c>
+      <c r="B116" t="s">
         <v>847</v>
-      </c>
-      <c r="B116" t="s">
-        <v>848</v>
       </c>
       <c r="C116" s="3"/>
       <c r="D116" s="4"/>
       <c r="E116" s="1" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="F116" s="3">
         <v>1</v>
       </c>
       <c r="G116" s="1"/>
       <c r="H116" s="11" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
     </row>
     <row r="117" spans="1:8">
       <c r="A117" t="s">
+        <v>850</v>
+      </c>
+      <c r="B117" t="s">
         <v>851</v>
-      </c>
-      <c r="B117" t="s">
-        <v>852</v>
       </c>
       <c r="C117" s="3"/>
       <c r="D117" s="4"/>
       <c r="E117" s="1" t="s">
+        <v>852</v>
+      </c>
+      <c r="F117" s="3">
+        <v>1</v>
+      </c>
+      <c r="G117" s="1" t="s">
         <v>853</v>
       </c>
-      <c r="F117" s="3">
-        <v>1</v>
-      </c>
-      <c r="G117" s="1" t="s">
+      <c r="H117" s="11" t="s">
         <v>854</v>
-      </c>
-      <c r="H117" s="11" t="s">
-        <v>855</v>
       </c>
     </row>
     <row r="118" spans="1:8">
       <c r="A118" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="B118" s="1" t="s">
         <v>400</v>
-      </c>
-      <c r="B118" s="1" t="s">
-        <v>401</v>
       </c>
       <c r="C118" s="3">
         <v>7</v>
@@ -6809,15 +6809,15 @@
       <c r="F118" s="3"/>
       <c r="G118" s="1"/>
       <c r="H118" s="1" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
     </row>
     <row r="119" spans="1:8">
       <c r="A119" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C119" s="3">
         <v>7</v>
@@ -6831,12 +6831,12 @@
       <c r="F119" s="3"/>
       <c r="G119" s="1"/>
       <c r="H119" s="1" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="120" spans="1:8">
       <c r="A120" s="2" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B120" s="1" t="s">
         <v>297</v>
@@ -6844,36 +6844,36 @@
       <c r="C120" s="1"/>
       <c r="D120" s="5"/>
       <c r="E120" s="1" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="F120" s="3">
         <v>1</v>
       </c>
       <c r="G120" s="1"/>
       <c r="H120" s="1" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
     </row>
     <row r="121" spans="1:8">
       <c r="A121" s="2" t="s">
+        <v>808</v>
+      </c>
+      <c r="B121" s="1" t="s">
         <v>809</v>
       </c>
-      <c r="B121" s="1" t="s">
+      <c r="E121" s="1" t="s">
+        <v>811</v>
+      </c>
+      <c r="F121" s="3">
+        <v>1</v>
+      </c>
+      <c r="H121" s="7" t="s">
         <v>810</v>
-      </c>
-      <c r="E121" s="1" t="s">
-        <v>812</v>
-      </c>
-      <c r="F121" s="3">
-        <v>1</v>
-      </c>
-      <c r="H121" s="7" t="s">
-        <v>811</v>
       </c>
     </row>
     <row r="122" spans="1:8">
       <c r="A122" s="2" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B122" s="1" t="s">
         <v>238</v>
@@ -6890,120 +6890,120 @@
       <c r="F122" s="3"/>
       <c r="G122" s="1"/>
       <c r="H122" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="123" spans="1:8">
       <c r="A123" t="s">
+        <v>855</v>
+      </c>
+      <c r="B123" t="s">
         <v>856</v>
-      </c>
-      <c r="B123" t="s">
-        <v>857</v>
       </c>
       <c r="C123"/>
       <c r="D123" s="11"/>
       <c r="E123" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="F123" s="1">
         <v>1</v>
       </c>
       <c r="G123"/>
       <c r="H123" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
     </row>
     <row r="124" spans="1:8">
       <c r="A124" t="s">
+        <v>857</v>
+      </c>
+      <c r="B124" t="s">
         <v>858</v>
       </c>
-      <c r="B124" t="s">
-        <v>859</v>
-      </c>
       <c r="E124" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="F124" s="1">
         <v>1</v>
       </c>
       <c r="H124" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
     </row>
     <row r="125" spans="1:8">
       <c r="A125" t="s">
+        <v>859</v>
+      </c>
+      <c r="B125" t="s">
         <v>860</v>
       </c>
-      <c r="B125" t="s">
-        <v>861</v>
-      </c>
       <c r="E125" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="F125" s="1">
         <v>1</v>
       </c>
       <c r="H125" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
     </row>
     <row r="126" spans="1:8">
       <c r="A126" t="s">
+        <v>861</v>
+      </c>
+      <c r="B126" t="s">
         <v>862</v>
       </c>
-      <c r="B126" t="s">
-        <v>863</v>
-      </c>
       <c r="E126" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="F126" s="1">
         <v>1</v>
       </c>
       <c r="H126" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
     </row>
     <row r="127" spans="1:8">
       <c r="A127" t="s">
+        <v>863</v>
+      </c>
+      <c r="B127" t="s">
         <v>864</v>
       </c>
-      <c r="B127" t="s">
-        <v>865</v>
-      </c>
       <c r="E127" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="F127" s="1">
         <v>1</v>
       </c>
       <c r="H127" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
     </row>
     <row r="128" spans="1:8">
       <c r="A128" t="s">
+        <v>865</v>
+      </c>
+      <c r="B128" t="s">
         <v>866</v>
       </c>
-      <c r="B128" t="s">
-        <v>867</v>
-      </c>
       <c r="E128" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="F128" s="1">
         <v>1</v>
       </c>
       <c r="H128" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
     </row>
     <row r="129" spans="1:8">
       <c r="A129" t="s">
+        <v>867</v>
+      </c>
+      <c r="B129" t="s">
         <v>868</v>
-      </c>
-      <c r="B129" t="s">
-        <v>869</v>
       </c>
       <c r="C129" s="2">
         <v>6</v>
@@ -7012,36 +7012,36 @@
         <v>0</v>
       </c>
       <c r="E129" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="F129" s="1"/>
       <c r="H129" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
     </row>
     <row r="130" spans="1:8">
       <c r="A130" t="s">
+        <v>869</v>
+      </c>
+      <c r="B130" t="s">
         <v>870</v>
       </c>
-      <c r="B130" t="s">
-        <v>871</v>
-      </c>
       <c r="E130" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="F130" s="1">
         <v>1</v>
       </c>
       <c r="H130" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
     </row>
     <row r="131" spans="1:8">
       <c r="A131" t="s">
+        <v>871</v>
+      </c>
+      <c r="B131" t="s">
         <v>872</v>
-      </c>
-      <c r="B131" t="s">
-        <v>873</v>
       </c>
       <c r="C131" s="2">
         <v>6</v>
@@ -7050,50 +7050,50 @@
         <v>0</v>
       </c>
       <c r="E131" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="F131" s="1"/>
       <c r="H131" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
     </row>
     <row r="132" spans="1:8">
       <c r="A132" t="s">
+        <v>873</v>
+      </c>
+      <c r="B132" t="s">
         <v>874</v>
       </c>
-      <c r="B132" t="s">
-        <v>875</v>
-      </c>
       <c r="E132" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="F132" s="1">
         <v>1</v>
       </c>
       <c r="H132" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
     </row>
     <row r="133" spans="1:8">
       <c r="A133" t="s">
+        <v>1064</v>
+      </c>
+      <c r="B133" t="s">
         <v>1065</v>
       </c>
-      <c r="B133" t="s">
+      <c r="E133" t="s">
         <v>1066</v>
       </c>
-      <c r="E133" t="s">
-        <v>1067</v>
-      </c>
       <c r="F133" s="1">
         <v>1</v>
       </c>
       <c r="H133" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
     </row>
     <row r="134" spans="1:8">
       <c r="A134" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B134" s="1" t="s">
         <v>47</v>
@@ -7110,12 +7110,12 @@
       <c r="F134" s="3"/>
       <c r="G134" s="1"/>
       <c r="H134" s="2" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
     </row>
     <row r="135" spans="1:8">
       <c r="A135" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B135" s="1" t="s">
         <v>49</v>
@@ -7132,12 +7132,12 @@
       <c r="F135" s="3"/>
       <c r="G135" s="1"/>
       <c r="H135" s="2" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
     </row>
     <row r="136" spans="1:8">
       <c r="A136" s="2" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B136" s="1" t="s">
         <v>271</v>
@@ -7154,12 +7154,12 @@
       <c r="F136" s="3"/>
       <c r="G136" s="1"/>
       <c r="H136" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
     </row>
     <row r="137" spans="1:8">
       <c r="A137" s="2" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B137" s="1" t="s">
         <v>43</v>
@@ -7176,12 +7176,12 @@
       <c r="F137" s="3"/>
       <c r="G137" s="1"/>
       <c r="H137" s="2" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
     </row>
     <row r="138" spans="1:8">
       <c r="A138" s="2" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B138" s="1" t="s">
         <v>51</v>
@@ -7198,12 +7198,12 @@
       <c r="F138" s="3"/>
       <c r="G138" s="1"/>
       <c r="H138" s="2" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
     </row>
     <row r="139" spans="1:8">
       <c r="A139" s="2" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B139" s="1" t="s">
         <v>53</v>
@@ -7220,12 +7220,12 @@
       <c r="F139" s="3"/>
       <c r="G139" s="1"/>
       <c r="H139" s="2" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
     </row>
     <row r="140" spans="1:8">
       <c r="A140" s="2" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B140" s="1" t="s">
         <v>270</v>
@@ -7242,12 +7242,12 @@
       <c r="F140" s="3"/>
       <c r="G140" s="1"/>
       <c r="H140" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
     </row>
     <row r="141" spans="1:8">
       <c r="A141" s="2" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B141" s="1" t="s">
         <v>55</v>
@@ -7264,15 +7264,15 @@
       <c r="F141" s="3"/>
       <c r="G141" s="1"/>
       <c r="H141" s="2" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
     </row>
     <row r="142" spans="1:8">
       <c r="A142" s="2" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="C142" s="3">
         <v>6</v>
@@ -7281,17 +7281,17 @@
         <v>0.875</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="F142" s="3"/>
       <c r="G142" s="1"/>
       <c r="H142" s="2" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
     </row>
     <row r="143" spans="1:8">
       <c r="A143" s="2" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B143" s="1" t="s">
         <v>41</v>
@@ -7308,12 +7308,12 @@
       <c r="F143" s="3"/>
       <c r="G143" s="1"/>
       <c r="H143" s="2" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
     </row>
     <row r="144" spans="1:8">
       <c r="A144" s="2" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B144" s="1" t="s">
         <v>45</v>
@@ -7330,12 +7330,12 @@
       <c r="F144" s="3"/>
       <c r="G144" s="1"/>
       <c r="H144" s="2" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
     </row>
     <row r="145" spans="1:8">
       <c r="A145" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B145" s="1" t="s">
         <v>220</v>
@@ -7352,12 +7352,12 @@
       <c r="F145" s="3"/>
       <c r="G145" s="1"/>
       <c r="H145" s="1" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
     </row>
     <row r="146" spans="1:8">
       <c r="A146" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B146" s="1" t="s">
         <v>214</v>
@@ -7374,12 +7374,12 @@
       <c r="F146" s="3"/>
       <c r="G146" s="1"/>
       <c r="H146" s="1" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
     </row>
     <row r="147" spans="1:8">
       <c r="A147" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B147" s="1" t="s">
         <v>226</v>
@@ -7396,12 +7396,12 @@
       <c r="F147" s="3"/>
       <c r="G147" s="1"/>
       <c r="H147" s="1" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
     </row>
     <row r="148" spans="1:8">
       <c r="A148" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B148" s="1" t="s">
         <v>216</v>
@@ -7418,12 +7418,12 @@
       <c r="F148" s="3"/>
       <c r="G148" s="1"/>
       <c r="H148" s="1" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
     </row>
     <row r="149" spans="1:8">
       <c r="A149" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B149" s="1" t="s">
         <v>224</v>
@@ -7440,12 +7440,12 @@
       <c r="F149" s="3"/>
       <c r="G149" s="1"/>
       <c r="H149" s="1" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
     </row>
     <row r="150" spans="1:8">
       <c r="A150" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B150" s="1" t="s">
         <v>222</v>
@@ -7462,12 +7462,12 @@
       <c r="F150" s="3"/>
       <c r="G150" s="1"/>
       <c r="H150" s="1" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
     </row>
     <row r="151" spans="1:8">
       <c r="A151" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B151" s="1" t="s">
         <v>218</v>
@@ -7484,15 +7484,15 @@
       <c r="F151" s="3"/>
       <c r="G151" s="1"/>
       <c r="H151" s="1" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
     </row>
     <row r="152" spans="1:8">
       <c r="A152" s="11" t="s">
+        <v>887</v>
+      </c>
+      <c r="B152" s="11" t="s">
         <v>888</v>
-      </c>
-      <c r="B152" s="11" t="s">
-        <v>889</v>
       </c>
       <c r="C152">
         <v>14</v>
@@ -7504,495 +7504,495 @@
       <c r="F152"/>
       <c r="G152"/>
       <c r="H152" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
     </row>
     <row r="153" spans="1:8">
       <c r="A153" t="s">
+        <v>889</v>
+      </c>
+      <c r="B153" t="s">
         <v>890</v>
-      </c>
-      <c r="B153" t="s">
-        <v>891</v>
       </c>
       <c r="C153"/>
       <c r="D153"/>
       <c r="E153" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="F153">
         <v>1</v>
       </c>
       <c r="G153"/>
       <c r="H153" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
     </row>
     <row r="154" spans="1:8">
       <c r="A154" t="s">
+        <v>891</v>
+      </c>
+      <c r="B154" t="s">
         <v>892</v>
-      </c>
-      <c r="B154" t="s">
-        <v>893</v>
       </c>
       <c r="C154"/>
       <c r="D154"/>
       <c r="E154" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="F154">
         <v>1</v>
       </c>
       <c r="G154"/>
       <c r="H154" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
     </row>
     <row r="155" spans="1:8">
       <c r="A155" t="s">
+        <v>893</v>
+      </c>
+      <c r="B155" t="s">
         <v>894</v>
-      </c>
-      <c r="B155" t="s">
-        <v>895</v>
       </c>
       <c r="C155"/>
       <c r="D155"/>
       <c r="E155" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="F155">
         <v>1</v>
       </c>
       <c r="G155"/>
       <c r="H155" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
     </row>
     <row r="156" spans="1:8">
       <c r="A156" t="s">
+        <v>895</v>
+      </c>
+      <c r="B156" t="s">
         <v>896</v>
-      </c>
-      <c r="B156" t="s">
-        <v>897</v>
       </c>
       <c r="C156"/>
       <c r="D156"/>
       <c r="E156" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="F156">
         <v>1</v>
       </c>
       <c r="G156"/>
       <c r="H156" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
     </row>
     <row r="157" spans="1:8">
       <c r="A157" t="s">
+        <v>897</v>
+      </c>
+      <c r="B157" t="s">
         <v>898</v>
-      </c>
-      <c r="B157" t="s">
-        <v>899</v>
       </c>
       <c r="C157"/>
       <c r="D157"/>
       <c r="E157" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="F157">
         <v>1</v>
       </c>
       <c r="G157"/>
       <c r="H157" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
     </row>
     <row r="158" spans="1:8">
       <c r="A158" t="s">
+        <v>899</v>
+      </c>
+      <c r="B158" t="s">
         <v>900</v>
-      </c>
-      <c r="B158" t="s">
-        <v>901</v>
       </c>
       <c r="C158"/>
       <c r="D158"/>
       <c r="E158" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="F158">
         <v>1</v>
       </c>
       <c r="G158"/>
       <c r="H158" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
     </row>
     <row r="159" spans="1:8">
       <c r="A159" t="s">
+        <v>901</v>
+      </c>
+      <c r="B159" t="s">
         <v>902</v>
-      </c>
-      <c r="B159" t="s">
-        <v>903</v>
       </c>
       <c r="C159"/>
       <c r="D159"/>
       <c r="E159" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="F159">
         <v>1</v>
       </c>
       <c r="G159"/>
       <c r="H159" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
     </row>
     <row r="160" spans="1:8">
       <c r="A160" t="s">
+        <v>903</v>
+      </c>
+      <c r="B160" t="s">
         <v>904</v>
-      </c>
-      <c r="B160" t="s">
-        <v>905</v>
       </c>
       <c r="C160"/>
       <c r="D160"/>
       <c r="E160" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="F160">
         <v>1</v>
       </c>
       <c r="G160"/>
       <c r="H160" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
     </row>
     <row r="161" spans="1:8">
       <c r="A161" t="s">
+        <v>905</v>
+      </c>
+      <c r="B161" t="s">
         <v>906</v>
-      </c>
-      <c r="B161" t="s">
-        <v>907</v>
       </c>
       <c r="C161"/>
       <c r="D161"/>
       <c r="E161" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="F161">
         <v>1</v>
       </c>
       <c r="G161"/>
       <c r="H161" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
     </row>
     <row r="162" spans="1:8">
       <c r="A162" t="s">
+        <v>907</v>
+      </c>
+      <c r="B162" t="s">
         <v>908</v>
-      </c>
-      <c r="B162" t="s">
-        <v>909</v>
       </c>
       <c r="C162"/>
       <c r="D162"/>
       <c r="E162" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="F162">
         <v>1</v>
       </c>
       <c r="G162"/>
       <c r="H162" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
     </row>
     <row r="163" spans="1:8">
       <c r="A163" t="s">
+        <v>909</v>
+      </c>
+      <c r="B163" t="s">
         <v>910</v>
-      </c>
-      <c r="B163" t="s">
-        <v>911</v>
       </c>
       <c r="C163"/>
       <c r="D163"/>
       <c r="E163" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="F163">
         <v>1</v>
       </c>
       <c r="G163"/>
       <c r="H163" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
     </row>
     <row r="164" spans="1:8">
       <c r="A164" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="B164" s="12" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="C164"/>
       <c r="D164"/>
       <c r="E164" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="F164">
         <v>1</v>
       </c>
       <c r="G164"/>
       <c r="H164" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
     </row>
     <row r="165" spans="1:8">
       <c r="A165" t="s">
+        <v>912</v>
+      </c>
+      <c r="B165" t="s">
         <v>913</v>
-      </c>
-      <c r="B165" t="s">
-        <v>914</v>
       </c>
       <c r="C165"/>
       <c r="D165"/>
       <c r="E165" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="F165">
         <v>1</v>
       </c>
       <c r="G165"/>
       <c r="H165" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
     </row>
     <row r="166" spans="1:8">
       <c r="A166" t="s">
+        <v>914</v>
+      </c>
+      <c r="B166" t="s">
         <v>915</v>
-      </c>
-      <c r="B166" t="s">
-        <v>916</v>
       </c>
       <c r="C166"/>
       <c r="D166"/>
       <c r="E166" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="F166">
         <v>1</v>
       </c>
       <c r="G166"/>
       <c r="H166" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
     </row>
     <row r="167" spans="1:8">
       <c r="A167" t="s">
+        <v>916</v>
+      </c>
+      <c r="B167" t="s">
         <v>917</v>
-      </c>
-      <c r="B167" t="s">
-        <v>918</v>
       </c>
       <c r="C167"/>
       <c r="D167"/>
       <c r="E167" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="F167">
         <v>1</v>
       </c>
       <c r="G167"/>
       <c r="H167" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
     </row>
     <row r="168" spans="1:8">
       <c r="A168" t="s">
+        <v>918</v>
+      </c>
+      <c r="B168" t="s">
         <v>919</v>
-      </c>
-      <c r="B168" t="s">
-        <v>920</v>
       </c>
       <c r="C168"/>
       <c r="D168"/>
       <c r="E168" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="F168">
         <v>1</v>
       </c>
       <c r="G168"/>
       <c r="H168" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
     </row>
     <row r="169" spans="1:8">
       <c r="A169" t="s">
+        <v>920</v>
+      </c>
+      <c r="B169" t="s">
         <v>921</v>
-      </c>
-      <c r="B169" t="s">
-        <v>922</v>
       </c>
       <c r="C169"/>
       <c r="D169"/>
       <c r="E169" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="F169">
         <v>1</v>
       </c>
       <c r="G169"/>
       <c r="H169" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
     </row>
     <row r="170" spans="1:8">
       <c r="A170" t="s">
+        <v>922</v>
+      </c>
+      <c r="B170" t="s">
         <v>923</v>
-      </c>
-      <c r="B170" t="s">
-        <v>924</v>
       </c>
       <c r="C170"/>
       <c r="D170"/>
       <c r="E170" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="F170">
         <v>1</v>
       </c>
       <c r="G170"/>
       <c r="H170" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
     </row>
     <row r="171" spans="1:8">
       <c r="A171" t="s">
+        <v>924</v>
+      </c>
+      <c r="B171" t="s">
         <v>925</v>
-      </c>
-      <c r="B171" t="s">
-        <v>926</v>
       </c>
       <c r="C171"/>
       <c r="D171"/>
       <c r="E171" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F171">
         <v>1</v>
       </c>
       <c r="G171"/>
       <c r="H171" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
     </row>
     <row r="172" spans="1:8">
       <c r="A172" t="s">
+        <v>926</v>
+      </c>
+      <c r="B172" t="s">
         <v>927</v>
-      </c>
-      <c r="B172" t="s">
-        <v>928</v>
       </c>
       <c r="C172"/>
       <c r="D172"/>
       <c r="E172" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="F172">
         <v>1</v>
       </c>
       <c r="G172"/>
       <c r="H172" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
     </row>
     <row r="173" spans="1:8">
       <c r="A173" t="s">
+        <v>928</v>
+      </c>
+      <c r="B173" t="s">
         <v>929</v>
-      </c>
-      <c r="B173" t="s">
-        <v>930</v>
       </c>
       <c r="C173"/>
       <c r="D173"/>
       <c r="E173" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="F173">
         <v>1</v>
       </c>
       <c r="G173"/>
       <c r="H173" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
     </row>
     <row r="174" spans="1:8">
       <c r="A174" t="s">
+        <v>930</v>
+      </c>
+      <c r="B174" t="s">
         <v>931</v>
-      </c>
-      <c r="B174" t="s">
-        <v>932</v>
       </c>
       <c r="C174"/>
       <c r="D174"/>
       <c r="E174" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="F174">
         <v>1</v>
       </c>
       <c r="G174"/>
       <c r="H174" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
     </row>
     <row r="175" spans="1:8">
       <c r="A175" t="s">
+        <v>932</v>
+      </c>
+      <c r="B175" t="s">
         <v>933</v>
-      </c>
-      <c r="B175" t="s">
-        <v>934</v>
       </c>
       <c r="C175"/>
       <c r="D175"/>
       <c r="E175" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="F175">
         <v>1</v>
       </c>
       <c r="G175"/>
       <c r="H175" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
     </row>
     <row r="176" spans="1:8">
       <c r="A176" t="s">
+        <v>934</v>
+      </c>
+      <c r="B176" t="s">
         <v>935</v>
-      </c>
-      <c r="B176" t="s">
-        <v>936</v>
       </c>
       <c r="C176"/>
       <c r="D176"/>
       <c r="E176" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="F176">
         <v>1</v>
       </c>
       <c r="G176"/>
       <c r="H176" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
     </row>
     <row r="177" spans="1:8">
       <c r="A177" t="s">
+        <v>936</v>
+      </c>
+      <c r="B177" t="s">
         <v>937</v>
-      </c>
-      <c r="B177" t="s">
-        <v>938</v>
       </c>
       <c r="C177">
         <v>14</v>
@@ -8001,100 +8001,100 @@
         <v>0</v>
       </c>
       <c r="E177" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="F177"/>
       <c r="G177"/>
       <c r="H177" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
     </row>
     <row r="178" spans="1:8">
       <c r="A178" t="s">
+        <v>938</v>
+      </c>
+      <c r="B178" t="s">
         <v>939</v>
-      </c>
-      <c r="B178" t="s">
-        <v>940</v>
       </c>
       <c r="C178"/>
       <c r="D178"/>
       <c r="E178" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="F178">
         <v>1</v>
       </c>
       <c r="G178"/>
       <c r="H178" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
     </row>
     <row r="179" spans="1:8">
       <c r="A179" t="s">
+        <v>940</v>
+      </c>
+      <c r="B179" t="s">
         <v>941</v>
-      </c>
-      <c r="B179" t="s">
-        <v>942</v>
       </c>
       <c r="C179"/>
       <c r="D179"/>
       <c r="E179" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="F179">
         <v>1</v>
       </c>
       <c r="G179"/>
       <c r="H179" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
     </row>
     <row r="180" spans="1:8">
       <c r="A180" s="12" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="B180" s="12" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="C180"/>
       <c r="D180"/>
       <c r="E180" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="F180">
         <v>1</v>
       </c>
       <c r="G180"/>
       <c r="H180" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
     </row>
     <row r="181" spans="1:8">
       <c r="A181" t="s">
+        <v>943</v>
+      </c>
+      <c r="B181" t="s">
         <v>944</v>
-      </c>
-      <c r="B181" t="s">
-        <v>945</v>
       </c>
       <c r="C181"/>
       <c r="D181"/>
       <c r="E181" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="F181">
         <v>1</v>
       </c>
       <c r="G181"/>
       <c r="H181" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
     </row>
     <row r="182" spans="1:8">
       <c r="A182" t="s">
+        <v>945</v>
+      </c>
+      <c r="B182" t="s">
         <v>946</v>
-      </c>
-      <c r="B182" t="s">
-        <v>947</v>
       </c>
       <c r="C182">
         <v>14</v>
@@ -8103,157 +8103,157 @@
         <v>0</v>
       </c>
       <c r="E182" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="F182"/>
       <c r="G182"/>
       <c r="H182" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
     </row>
     <row r="183" spans="1:8">
       <c r="A183" t="s">
+        <v>947</v>
+      </c>
+      <c r="B183" t="s">
         <v>948</v>
-      </c>
-      <c r="B183" t="s">
-        <v>949</v>
       </c>
       <c r="C183"/>
       <c r="D183"/>
       <c r="E183" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="F183">
         <v>1</v>
       </c>
       <c r="G183"/>
       <c r="H183" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
     </row>
     <row r="184" spans="1:8">
       <c r="A184" t="s">
+        <v>949</v>
+      </c>
+      <c r="B184" t="s">
         <v>950</v>
-      </c>
-      <c r="B184" t="s">
-        <v>951</v>
       </c>
       <c r="C184"/>
       <c r="D184"/>
       <c r="E184" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="F184">
         <v>1</v>
       </c>
       <c r="G184"/>
       <c r="H184" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
     </row>
     <row r="185" spans="1:8">
       <c r="A185" t="s">
+        <v>951</v>
+      </c>
+      <c r="B185" t="s">
         <v>952</v>
-      </c>
-      <c r="B185" t="s">
-        <v>953</v>
       </c>
       <c r="C185"/>
       <c r="D185"/>
       <c r="E185" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="F185">
         <v>1</v>
       </c>
       <c r="G185"/>
       <c r="H185" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
     </row>
     <row r="186" spans="1:8">
       <c r="A186" t="s">
+        <v>953</v>
+      </c>
+      <c r="B186" t="s">
         <v>954</v>
-      </c>
-      <c r="B186" t="s">
-        <v>955</v>
       </c>
       <c r="C186"/>
       <c r="D186"/>
       <c r="E186" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="F186">
         <v>1</v>
       </c>
       <c r="G186"/>
       <c r="H186" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
     </row>
     <row r="187" spans="1:8">
       <c r="A187" t="s">
+        <v>955</v>
+      </c>
+      <c r="B187" t="s">
         <v>956</v>
-      </c>
-      <c r="B187" t="s">
-        <v>957</v>
       </c>
       <c r="C187"/>
       <c r="D187"/>
       <c r="E187" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="F187">
         <v>1</v>
       </c>
       <c r="G187"/>
       <c r="H187" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
     </row>
     <row r="188" spans="1:8">
       <c r="A188" t="s">
+        <v>957</v>
+      </c>
+      <c r="B188" t="s">
         <v>958</v>
-      </c>
-      <c r="B188" t="s">
-        <v>959</v>
       </c>
       <c r="C188"/>
       <c r="D188"/>
       <c r="E188" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="F188">
         <v>1</v>
       </c>
       <c r="G188"/>
       <c r="H188" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
     </row>
     <row r="189" spans="1:8">
       <c r="A189" t="s">
+        <v>1055</v>
+      </c>
+      <c r="B189" t="s">
         <v>1056</v>
-      </c>
-      <c r="B189" t="s">
-        <v>1057</v>
       </c>
       <c r="C189"/>
       <c r="D189"/>
       <c r="E189" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="F189">
         <v>1</v>
       </c>
       <c r="G189"/>
       <c r="H189" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
     </row>
     <row r="190" spans="1:8">
       <c r="A190" s="2" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B190" s="1" t="s">
         <v>236</v>
@@ -8270,12 +8270,12 @@
       <c r="F190" s="3"/>
       <c r="G190" s="1"/>
       <c r="H190" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
     </row>
     <row r="191" spans="1:8">
       <c r="A191" s="2" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B191" s="1" t="s">
         <v>266</v>
@@ -8292,12 +8292,12 @@
       <c r="F191" s="3"/>
       <c r="G191" s="1"/>
       <c r="H191" s="1" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="192" spans="1:8">
       <c r="A192" s="2" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B192" s="1" t="s">
         <v>195</v>
@@ -8309,80 +8309,80 @@
         <v>0</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="F192" s="3"/>
       <c r="G192" s="1"/>
       <c r="H192" s="1" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
     </row>
     <row r="193" spans="1:8">
       <c r="A193" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="E193" s="1" t="s">
+        <v>766</v>
+      </c>
+      <c r="F193" s="2">
+        <v>1</v>
+      </c>
+      <c r="G193" s="2" t="s">
         <v>767</v>
       </c>
-      <c r="F193" s="2">
-        <v>1</v>
-      </c>
-      <c r="G193" s="2" t="s">
-        <v>768</v>
-      </c>
       <c r="H193" s="2" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="194" spans="1:8">
       <c r="A194" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="F194" s="2">
         <v>1</v>
       </c>
       <c r="G194" s="2" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="H194" s="2" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="195" spans="1:8">
       <c r="A195" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="E195" s="1" t="s">
+        <v>769</v>
+      </c>
+      <c r="F195" s="2">
+        <v>1</v>
+      </c>
+      <c r="G195" s="2" t="s">
         <v>770</v>
       </c>
-      <c r="F195" s="2">
-        <v>1</v>
-      </c>
-      <c r="G195" s="2" t="s">
-        <v>771</v>
-      </c>
       <c r="H195" s="2" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="196" spans="1:8">
       <c r="A196" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="C196" s="2">
         <v>8</v>
@@ -8391,34 +8391,34 @@
         <v>0</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="F196" s="3"/>
       <c r="H196" s="2" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="197" spans="1:8">
       <c r="A197" s="2" t="s">
+        <v>812</v>
+      </c>
+      <c r="B197" s="1" t="s">
         <v>813</v>
-      </c>
-      <c r="B197" s="1" t="s">
-        <v>814</v>
       </c>
       <c r="D197" s="6"/>
       <c r="E197" s="1" t="s">
+        <v>814</v>
+      </c>
+      <c r="F197" s="3">
+        <v>1</v>
+      </c>
+      <c r="H197" s="7" t="s">
         <v>815</v>
-      </c>
-      <c r="F197" s="3">
-        <v>1</v>
-      </c>
-      <c r="H197" s="7" t="s">
-        <v>816</v>
       </c>
     </row>
     <row r="198" spans="1:8">
       <c r="A198" s="2" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B198" s="1" t="s">
         <v>315</v>
@@ -8435,15 +8435,15 @@
       <c r="F198" s="3"/>
       <c r="G198" s="1"/>
       <c r="H198" s="1" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
     </row>
     <row r="199" spans="1:8">
       <c r="A199" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C199" s="2">
         <v>10</v>
@@ -8452,18 +8452,18 @@
         <v>0</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="H199" s="2" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="200" spans="1:8">
       <c r="A200" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="C200" s="2">
         <v>10</v>
@@ -8472,38 +8472,38 @@
         <v>0</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="H200" s="2" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="201" spans="1:8">
       <c r="A201" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B201" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="C201"/>
       <c r="D201" s="11"/>
       <c r="E201" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="F201">
         <v>1</v>
       </c>
       <c r="G201"/>
       <c r="H201" s="11" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="202" spans="1:8">
       <c r="A202" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="B202" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="C202">
         <v>10</v>
@@ -8512,40 +8512,40 @@
         <v>0</v>
       </c>
       <c r="E202" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="F202"/>
       <c r="G202"/>
       <c r="H202" s="11" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="203" spans="1:8">
       <c r="A203" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="B203" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="C203"/>
       <c r="D203" s="11"/>
       <c r="E203" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="F203">
         <v>1</v>
       </c>
       <c r="G203"/>
       <c r="H203" s="11" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="204" spans="1:8">
       <c r="A204" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C204" s="3">
         <v>7</v>
@@ -8559,12 +8559,12 @@
       <c r="F204" s="3"/>
       <c r="G204" s="1"/>
       <c r="H204" s="1" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="205" spans="1:8">
       <c r="A205" s="2" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B205" s="1" t="s">
         <v>115</v>
@@ -8581,12 +8581,12 @@
       <c r="F205" s="3"/>
       <c r="G205" s="1"/>
       <c r="H205" s="1" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
     </row>
     <row r="206" spans="1:8">
       <c r="A206" s="2" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B206" s="1" t="s">
         <v>119</v>
@@ -8601,12 +8601,12 @@
       </c>
       <c r="G206" s="1"/>
       <c r="H206" s="1" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
     </row>
     <row r="207" spans="1:8">
       <c r="A207" s="2" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B207" s="1" t="s">
         <v>117</v>
@@ -8623,33 +8623,33 @@
       <c r="F207" s="3"/>
       <c r="G207" s="1"/>
       <c r="H207" s="1" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
     </row>
     <row r="208" spans="1:8">
       <c r="A208" s="2" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="D208" s="6"/>
       <c r="E208" s="2" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="F208" s="2">
         <v>1</v>
       </c>
       <c r="H208" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
     </row>
     <row r="209" spans="1:8">
       <c r="A209" t="s">
+        <v>998</v>
+      </c>
+      <c r="B209" t="s">
         <v>999</v>
-      </c>
-      <c r="B209" t="s">
-        <v>1000</v>
       </c>
       <c r="C209">
         <v>15</v>
@@ -8658,20 +8658,20 @@
         <v>0</v>
       </c>
       <c r="E209" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="F209"/>
       <c r="G209"/>
       <c r="H209" s="11" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="210" spans="1:8">
       <c r="A210" t="s">
+        <v>1002</v>
+      </c>
+      <c r="B210" t="s">
         <v>1003</v>
-      </c>
-      <c r="B210" t="s">
-        <v>1004</v>
       </c>
       <c r="C210">
         <v>15</v>
@@ -8680,20 +8680,20 @@
         <v>0</v>
       </c>
       <c r="E210" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="F210"/>
       <c r="G210"/>
       <c r="H210" s="11" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="211" spans="1:8">
       <c r="A211" t="s">
+        <v>1006</v>
+      </c>
+      <c r="B211" t="s">
         <v>1007</v>
-      </c>
-      <c r="B211" t="s">
-        <v>1008</v>
       </c>
       <c r="C211">
         <v>15</v>
@@ -8702,20 +8702,20 @@
         <v>0</v>
       </c>
       <c r="E211" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="F211"/>
       <c r="G211"/>
       <c r="H211" s="11" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="212" spans="1:8">
       <c r="A212" t="s">
+        <v>1010</v>
+      </c>
+      <c r="B212" t="s">
         <v>1011</v>
-      </c>
-      <c r="B212" t="s">
-        <v>1012</v>
       </c>
       <c r="C212">
         <v>20</v>
@@ -8724,20 +8724,20 @@
         <v>0</v>
       </c>
       <c r="E212" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="F212"/>
       <c r="G212"/>
       <c r="H212" s="11" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="213" spans="1:8">
       <c r="A213" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B213" t="s">
         <v>1015</v>
-      </c>
-      <c r="B213" t="s">
-        <v>1016</v>
       </c>
       <c r="C213">
         <v>15</v>
@@ -8746,17 +8746,17 @@
         <v>0</v>
       </c>
       <c r="E213" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="F213"/>
       <c r="G213"/>
       <c r="H213" s="11" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="214" spans="1:8">
       <c r="A214" s="2" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B214" s="1" t="s">
         <v>255</v>
@@ -8773,12 +8773,12 @@
         <v>257</v>
       </c>
       <c r="H214" s="2" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
     </row>
     <row r="215" spans="1:8">
       <c r="A215" s="2" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B215" s="1" t="s">
         <v>258</v>
@@ -8795,12 +8795,12 @@
         <v>260</v>
       </c>
       <c r="H215" s="2" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
     </row>
     <row r="216" spans="1:8">
       <c r="A216" s="2" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B216" s="1" t="s">
         <v>131</v>
@@ -8817,12 +8817,12 @@
       <c r="F216" s="3"/>
       <c r="G216" s="1"/>
       <c r="H216" s="1" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
     <row r="217" spans="1:8">
       <c r="A217" s="2" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B217" s="1" t="s">
         <v>228</v>
@@ -8839,12 +8839,12 @@
       <c r="F217" s="3"/>
       <c r="G217" s="1"/>
       <c r="H217" s="1" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="218" spans="1:8">
       <c r="A218" s="2" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B218" s="1" t="s">
         <v>287</v>
@@ -8861,12 +8861,12 @@
       <c r="F218" s="3"/>
       <c r="G218" s="1"/>
       <c r="H218" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
     </row>
     <row r="219" spans="1:8">
       <c r="A219" s="2" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B219" s="1" t="s">
         <v>74</v>
@@ -8878,17 +8878,17 @@
         <v>0</v>
       </c>
       <c r="E219" s="1" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="F219" s="3"/>
       <c r="G219" s="1"/>
       <c r="H219" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="220" spans="1:8">
       <c r="A220" s="2" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B220" s="1" t="s">
         <v>305</v>
@@ -8905,15 +8905,15 @@
       <c r="F220" s="1"/>
       <c r="G220" s="1"/>
       <c r="H220" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="221" spans="1:8">
       <c r="A221" s="2" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="B221" s="1" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C221" s="1"/>
       <c r="D221" s="5"/>
@@ -8925,12 +8925,12 @@
       </c>
       <c r="G221" s="1"/>
       <c r="H221" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
     </row>
     <row r="222" spans="1:8">
       <c r="A222" s="2" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B222" s="1" t="s">
         <v>294</v>
@@ -8945,12 +8945,12 @@
       </c>
       <c r="G222" s="1"/>
       <c r="H222" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
     </row>
     <row r="223" spans="1:8">
       <c r="A223" s="2" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="B223" s="1" t="s">
         <v>295</v>
@@ -8965,12 +8965,12 @@
       </c>
       <c r="G223" s="1"/>
       <c r="H223" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
     </row>
     <row r="224" spans="1:8">
       <c r="A224" s="2" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B224" s="1" t="s">
         <v>242</v>
@@ -8982,17 +8982,17 @@
         <v>0</v>
       </c>
       <c r="E224" s="1" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="F224" s="3"/>
       <c r="G224" s="1"/>
       <c r="H224" s="1" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="225" spans="1:8">
       <c r="A225" s="2" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B225" s="1" t="s">
         <v>240</v>
@@ -9009,15 +9009,15 @@
       <c r="F225" s="3"/>
       <c r="G225" s="1"/>
       <c r="H225" s="2" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
     </row>
     <row r="226" spans="1:8">
       <c r="A226" s="2" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B226" s="1" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="C226" s="2">
         <v>7</v>
@@ -9026,16 +9026,16 @@
         <v>0.95833333333333337</v>
       </c>
       <c r="E226" s="1" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="F226" s="3"/>
       <c r="H226" s="7" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
     </row>
     <row r="227" spans="1:8">
       <c r="A227" s="2" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B227" s="1" t="s">
         <v>57</v>
@@ -9052,12 +9052,12 @@
       <c r="F227" s="3"/>
       <c r="G227" s="1"/>
       <c r="H227" s="2" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
     </row>
     <row r="228" spans="1:8">
       <c r="A228" s="2" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B228" s="1" t="s">
         <v>61</v>
@@ -9069,34 +9069,34 @@
         <v>0</v>
       </c>
       <c r="E228" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="F228" s="3"/>
       <c r="G228" s="1"/>
       <c r="H228" s="2" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
     </row>
     <row r="229" spans="1:8">
       <c r="A229" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="B229" s="1" t="s">
         <v>449</v>
       </c>
-      <c r="B229" s="1" t="s">
-        <v>450</v>
-      </c>
       <c r="E229" s="1" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="F229" s="3">
         <v>1</v>
       </c>
       <c r="H229" s="1" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
     </row>
     <row r="230" spans="1:8">
       <c r="A230" s="2" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B230" s="1" t="s">
         <v>59</v>
@@ -9113,12 +9113,12 @@
       <c r="F230" s="3"/>
       <c r="G230" s="1"/>
       <c r="H230" s="2" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
     </row>
     <row r="231" spans="1:8">
       <c r="A231" s="2" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B231" s="1" t="s">
         <v>62</v>
@@ -9135,12 +9135,12 @@
       <c r="F231" s="3"/>
       <c r="G231" s="1"/>
       <c r="H231" s="2" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
     </row>
     <row r="232" spans="1:8">
       <c r="A232" s="2" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B232" s="1" t="s">
         <v>121</v>
@@ -9152,17 +9152,17 @@
         <v>0</v>
       </c>
       <c r="E232" s="1" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="F232" s="3"/>
       <c r="G232" s="1"/>
       <c r="H232" s="1" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
     </row>
     <row r="233" spans="1:8">
       <c r="A233" s="2" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B233" s="1" t="s">
         <v>123</v>
@@ -9179,12 +9179,12 @@
       <c r="F233" s="3"/>
       <c r="G233" s="1"/>
       <c r="H233" s="1" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
     </row>
     <row r="234" spans="1:8">
       <c r="A234" s="2" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B234" s="1" t="s">
         <v>122</v>
@@ -9201,15 +9201,15 @@
       <c r="F234" s="3"/>
       <c r="G234" s="1"/>
       <c r="H234" s="1" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
     </row>
     <row r="235" spans="1:8">
       <c r="A235" t="s">
+        <v>1020</v>
+      </c>
+      <c r="B235" t="s">
         <v>1021</v>
-      </c>
-      <c r="B235" t="s">
-        <v>1022</v>
       </c>
       <c r="C235">
         <v>6</v>
@@ -9218,20 +9218,20 @@
         <v>0</v>
       </c>
       <c r="E235" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="F235"/>
       <c r="G235"/>
       <c r="H235" s="7" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="236" spans="1:8">
       <c r="A236" s="11" t="s">
+        <v>1024</v>
+      </c>
+      <c r="B236" t="s">
         <v>1025</v>
-      </c>
-      <c r="B236" t="s">
-        <v>1026</v>
       </c>
       <c r="C236" s="3">
         <v>7</v>
@@ -9240,17 +9240,17 @@
         <v>0.91666666666666663</v>
       </c>
       <c r="E236" s="1" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="F236"/>
       <c r="G236"/>
       <c r="H236" s="7" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="237" spans="1:8">
       <c r="A237" s="2" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B237" s="1" t="s">
         <v>282</v>
@@ -9267,12 +9267,12 @@
       <c r="F237" s="3"/>
       <c r="G237" s="1"/>
       <c r="H237" s="1" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
     </row>
     <row r="238" spans="1:8">
       <c r="A238" s="2" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B238" s="1" t="s">
         <v>9</v>
@@ -9289,32 +9289,32 @@
       <c r="F238" s="3"/>
       <c r="G238" s="1"/>
       <c r="H238" s="2" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="239" spans="1:8" customFormat="1">
       <c r="A239" s="2" t="s">
+        <v>804</v>
+      </c>
+      <c r="B239" s="1" t="s">
         <v>805</v>
-      </c>
-      <c r="B239" s="1" t="s">
-        <v>806</v>
       </c>
       <c r="C239" s="2"/>
       <c r="D239" s="2"/>
       <c r="E239" s="1" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="F239" s="3">
         <v>1</v>
       </c>
       <c r="G239" s="2"/>
       <c r="H239" s="7" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
     </row>
     <row r="240" spans="1:8">
       <c r="A240" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B240" s="1" t="s">
         <v>311</v>
@@ -9331,12 +9331,12 @@
       <c r="F240" s="3"/>
       <c r="G240" s="1"/>
       <c r="H240" s="1" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="241" spans="1:8">
       <c r="A241" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B241" s="1" t="s">
         <v>313</v>
@@ -9351,32 +9351,32 @@
       </c>
       <c r="G241" s="1"/>
       <c r="H241" s="1" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
     </row>
     <row r="242" spans="1:8">
       <c r="A242" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="B242" s="1" t="s">
         <v>494</v>
-      </c>
-      <c r="B242" s="1" t="s">
-        <v>495</v>
       </c>
       <c r="C242" s="3"/>
       <c r="D242" s="5"/>
       <c r="E242" s="1" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="F242" s="3">
         <v>1</v>
       </c>
       <c r="G242" s="1"/>
       <c r="H242" s="1" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
     </row>
     <row r="243" spans="1:8">
       <c r="A243" s="2" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B243" s="1" t="s">
         <v>292</v>
@@ -9391,34 +9391,34 @@
       </c>
       <c r="G243" s="1"/>
       <c r="H243" s="1" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
     </row>
     <row r="244" spans="1:8">
       <c r="A244" s="11" t="s">
+        <v>1026</v>
+      </c>
+      <c r="B244" t="s">
         <v>1027</v>
-      </c>
-      <c r="B244" t="s">
-        <v>1028</v>
       </c>
       <c r="C244"/>
       <c r="D244" s="11"/>
       <c r="E244" t="s">
+        <v>1028</v>
+      </c>
+      <c r="F244">
+        <v>1</v>
+      </c>
+      <c r="G244" t="s">
         <v>1029</v>
       </c>
-      <c r="F244">
-        <v>1</v>
-      </c>
-      <c r="G244" t="s">
+      <c r="H244" s="7" t="s">
         <v>1030</v>
-      </c>
-      <c r="H244" s="7" t="s">
-        <v>1031</v>
       </c>
     </row>
     <row r="245" spans="1:8">
       <c r="A245" s="2" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B245" s="1" t="s">
         <v>290</v>
@@ -9430,51 +9430,51 @@
         <v>0.91666666666666663</v>
       </c>
       <c r="E245" s="1" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="F245" s="3"/>
       <c r="G245" s="1"/>
       <c r="H245" s="1" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
     </row>
     <row r="246" spans="1:8">
       <c r="A246" s="2" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B246" s="1" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="E246" s="1" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="F246" s="2">
         <v>1</v>
       </c>
       <c r="H246" s="2" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
     </row>
     <row r="247" spans="1:8">
       <c r="A247" s="2" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B247" s="1" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="E247" s="1" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F247" s="2">
         <v>1</v>
       </c>
       <c r="H247" s="2" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
     </row>
     <row r="248" spans="1:8">
       <c r="A248" s="2" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B248" s="1" t="s">
         <v>213</v>
@@ -9486,17 +9486,17 @@
         <v>0</v>
       </c>
       <c r="E248" s="1" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="F248" s="3"/>
       <c r="G248" s="1"/>
       <c r="H248" s="1" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="249" spans="1:8">
       <c r="A249" s="2" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B249" s="1" t="s">
         <v>213</v>
@@ -9508,17 +9508,17 @@
         <v>0</v>
       </c>
       <c r="E249" s="1" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="F249" s="3"/>
       <c r="G249" s="1"/>
       <c r="H249" s="1" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="250" spans="1:8">
       <c r="A250" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B250" s="1" t="s">
         <v>25</v>
@@ -9535,12 +9535,12 @@
       <c r="F250" s="3"/>
       <c r="G250" s="1"/>
       <c r="H250" s="2" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="251" spans="1:8">
       <c r="A251" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B251" s="1" t="s">
         <v>27</v>
@@ -9557,12 +9557,12 @@
       <c r="F251" s="3"/>
       <c r="G251" s="1"/>
       <c r="H251" s="2" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="252" spans="1:8">
       <c r="A252" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B252" s="1" t="s">
         <v>23</v>
@@ -9579,12 +9579,12 @@
       <c r="F252" s="3"/>
       <c r="G252" s="1"/>
       <c r="H252" s="2" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="253" spans="1:8">
       <c r="A253" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B253" s="1" t="s">
         <v>31</v>
@@ -9601,12 +9601,12 @@
       <c r="F253" s="3"/>
       <c r="G253" s="1"/>
       <c r="H253" s="2" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="254" spans="1:8">
       <c r="A254" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B254" s="1" t="s">
         <v>33</v>
@@ -9623,12 +9623,12 @@
       <c r="F254" s="3"/>
       <c r="G254" s="1"/>
       <c r="H254" s="2" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="255" spans="1:8">
       <c r="A255" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B255" s="1" t="s">
         <v>20</v>
@@ -9645,12 +9645,12 @@
       <c r="F255" s="3"/>
       <c r="G255" s="1"/>
       <c r="H255" s="2" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="256" spans="1:8">
       <c r="A256" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B256" s="1" t="s">
         <v>18</v>
@@ -9667,12 +9667,12 @@
       <c r="F256" s="3"/>
       <c r="G256" s="1"/>
       <c r="H256" s="2" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="257" spans="1:8">
       <c r="A257" s="2" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B257" s="1" t="s">
         <v>37</v>
@@ -9689,12 +9689,12 @@
       <c r="F257" s="3"/>
       <c r="G257" s="1"/>
       <c r="H257" s="2" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="258" spans="1:8">
       <c r="A258" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B258" s="1" t="s">
         <v>29</v>
@@ -9711,12 +9711,12 @@
       <c r="F258" s="3"/>
       <c r="G258" s="1"/>
       <c r="H258" s="2" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="259" spans="1:8">
       <c r="A259" s="2" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B259" s="1" t="s">
         <v>39</v>
@@ -9733,12 +9733,12 @@
       <c r="F259" s="3"/>
       <c r="G259" s="1"/>
       <c r="H259" s="2" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="260" spans="1:8">
       <c r="A260" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B260" s="1" t="s">
         <v>35</v>
@@ -9755,12 +9755,12 @@
       <c r="F260" s="3"/>
       <c r="G260" s="1"/>
       <c r="H260" s="2" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="261" spans="1:8">
       <c r="A261" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B261" s="1" t="s">
         <v>22</v>
@@ -9777,15 +9777,15 @@
       <c r="F261" s="3"/>
       <c r="G261" s="1"/>
       <c r="H261" s="2" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="262" spans="1:8">
       <c r="A262" s="2" t="s">
+        <v>696</v>
+      </c>
+      <c r="B262" s="1" t="s">
         <v>697</v>
-      </c>
-      <c r="B262" s="1" t="s">
-        <v>698</v>
       </c>
       <c r="C262" s="2">
         <v>6</v>
@@ -9794,19 +9794,19 @@
         <v>0</v>
       </c>
       <c r="E262" s="1" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="F262" s="3"/>
       <c r="H262" s="7" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
     </row>
     <row r="263" spans="1:8">
       <c r="A263" s="2" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B263" s="1" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C263" s="3">
         <v>8</v>
@@ -9815,19 +9815,19 @@
         <v>0</v>
       </c>
       <c r="E263" s="1" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="F263" s="3"/>
       <c r="H263" s="1" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
     <row r="264" spans="1:8">
       <c r="A264" s="2" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B264" s="1" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C264" s="3">
         <v>7</v>
@@ -9841,12 +9841,12 @@
       <c r="F264" s="3"/>
       <c r="G264" s="1"/>
       <c r="H264" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
     </row>
     <row r="265" spans="1:8">
       <c r="A265" s="2" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B265" s="1" t="s">
         <v>129</v>
@@ -9858,20 +9858,20 @@
         <v>0</v>
       </c>
       <c r="E265" s="1" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="F265" s="3"/>
       <c r="G265" s="1"/>
       <c r="H265" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="266" spans="1:8">
       <c r="A266" s="2" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="B266" s="1" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="C266" s="2">
         <v>6</v>
@@ -9880,19 +9880,19 @@
         <v>0</v>
       </c>
       <c r="E266" s="1" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="F266" s="3"/>
       <c r="H266" s="7" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
     </row>
     <row r="267" spans="1:8">
       <c r="A267" s="2" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="B267" s="1" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="C267" s="2">
         <v>6</v>
@@ -9901,19 +9901,19 @@
         <v>0</v>
       </c>
       <c r="E267" s="10" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="F267" s="3"/>
       <c r="H267" s="2" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
     </row>
     <row r="268" spans="1:8">
       <c r="A268" s="2" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="B268" s="1" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C268" s="2">
         <v>6</v>
@@ -9922,19 +9922,19 @@
         <v>0</v>
       </c>
       <c r="E268" s="1" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="F268" s="3"/>
       <c r="H268" s="2" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
     </row>
     <row r="269" spans="1:8">
       <c r="A269" s="2" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="B269" s="1" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="C269" s="2">
         <v>6</v>
@@ -9943,38 +9943,38 @@
         <v>0</v>
       </c>
       <c r="E269" s="1" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="F269" s="3"/>
       <c r="H269" s="2" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
     </row>
     <row r="270" spans="1:8">
       <c r="A270" s="2" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="B270" s="1" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C270" s="3"/>
       <c r="D270" s="6"/>
       <c r="E270" s="1" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="F270" s="3">
         <v>1</v>
       </c>
       <c r="G270" s="2" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="H270" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
     </row>
     <row r="271" spans="1:8">
       <c r="A271" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B271" s="1" t="s">
         <v>199</v>
@@ -9991,12 +9991,12 @@
       <c r="F271" s="3"/>
       <c r="G271" s="1"/>
       <c r="H271" s="1" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="272" spans="1:8">
       <c r="A272" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B272" s="1" t="s">
         <v>197</v>
@@ -10013,12 +10013,12 @@
       <c r="F272" s="3"/>
       <c r="G272" s="1"/>
       <c r="H272" s="1" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="273" spans="1:8">
       <c r="A273" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B273" s="1" t="s">
         <v>201</v>
@@ -10035,12 +10035,12 @@
       <c r="F273" s="3"/>
       <c r="G273" s="1"/>
       <c r="H273" s="1" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="274" spans="1:8">
       <c r="A274" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B274" s="1" t="s">
         <v>130</v>
@@ -10052,17 +10052,17 @@
         <v>0.97916666666666663</v>
       </c>
       <c r="E274" s="1" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="F274" s="3"/>
       <c r="G274" s="1"/>
       <c r="H274" s="1" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="275" spans="1:8">
       <c r="A275" s="2" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B275" s="1" t="s">
         <v>64</v>
@@ -10074,17 +10074,17 @@
         <v>0</v>
       </c>
       <c r="E275" s="1" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="F275" s="3"/>
       <c r="G275" s="1"/>
       <c r="H275" s="2" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="276" spans="1:8">
       <c r="A276" s="2" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B276" s="1" t="s">
         <v>65</v>
@@ -10101,12 +10101,12 @@
       <c r="F276" s="3"/>
       <c r="G276" s="1"/>
       <c r="H276" s="2" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="277" spans="1:8">
       <c r="A277" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B277" s="1" t="s">
         <v>69</v>
@@ -10123,12 +10123,12 @@
       <c r="F277" s="3"/>
       <c r="G277" s="1"/>
       <c r="H277" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="278" spans="1:8">
       <c r="A278" s="2" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B278" s="1" t="s">
         <v>67</v>
@@ -10145,15 +10145,15 @@
       <c r="F278" s="3"/>
       <c r="G278" s="1"/>
       <c r="H278" s="2" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="279" spans="1:8">
       <c r="A279" s="2" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B279" s="1" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="C279" s="3">
         <v>6</v>
@@ -10167,12 +10167,12 @@
       <c r="F279" s="3"/>
       <c r="G279" s="1"/>
       <c r="H279" s="2" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="280" spans="1:8">
       <c r="A280" s="2" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B280" s="1" t="s">
         <v>72</v>
@@ -10189,12 +10189,12 @@
       <c r="F280" s="3"/>
       <c r="G280" s="1"/>
       <c r="H280" s="2" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="281" spans="1:8">
       <c r="A281" s="2" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B281" s="1" t="s">
         <v>92</v>
@@ -10211,12 +10211,12 @@
       <c r="F281" s="3"/>
       <c r="G281" s="1"/>
       <c r="H281" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
     </row>
     <row r="282" spans="1:8">
       <c r="A282" s="2" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B282" s="1" t="s">
         <v>95</v>
@@ -10233,12 +10233,12 @@
       <c r="F282" s="3"/>
       <c r="G282" s="1"/>
       <c r="H282" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
     </row>
     <row r="283" spans="1:8">
       <c r="A283" s="2" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B283" s="1" t="s">
         <v>86</v>
@@ -10255,12 +10255,12 @@
       <c r="F283" s="3"/>
       <c r="G283" s="1"/>
       <c r="H283" s="1" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
     </row>
     <row r="284" spans="1:8">
       <c r="A284" s="2" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B284" s="1" t="s">
         <v>88</v>
@@ -10277,12 +10277,12 @@
       <c r="F284" s="3"/>
       <c r="G284" s="1"/>
       <c r="H284" s="1" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
     </row>
     <row r="285" spans="1:8">
       <c r="A285" s="2" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B285" s="1" t="s">
         <v>102</v>
@@ -10299,12 +10299,12 @@
       <c r="F285" s="3"/>
       <c r="G285" s="1"/>
       <c r="H285" s="1" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
     </row>
     <row r="286" spans="1:8">
       <c r="A286" s="2" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B286" s="1" t="s">
         <v>110</v>
@@ -10321,12 +10321,12 @@
       <c r="F286" s="3"/>
       <c r="G286" s="1"/>
       <c r="H286" s="1" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
     </row>
     <row r="287" spans="1:8">
       <c r="A287" s="2" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B287" s="1" t="s">
         <v>104</v>
@@ -10343,12 +10343,12 @@
       <c r="F287" s="3"/>
       <c r="G287" s="1"/>
       <c r="H287" s="1" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
     </row>
     <row r="288" spans="1:8">
       <c r="A288" s="2" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B288" s="1" t="s">
         <v>91</v>
@@ -10360,17 +10360,17 @@
         <v>0</v>
       </c>
       <c r="E288" s="1" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="F288" s="3"/>
       <c r="G288" s="1"/>
       <c r="H288" s="8" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
     </row>
     <row r="289" spans="1:8">
       <c r="A289" s="2" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B289" s="1" t="s">
         <v>108</v>
@@ -10387,12 +10387,12 @@
       <c r="F289" s="3"/>
       <c r="G289" s="1"/>
       <c r="H289" s="1" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
     </row>
     <row r="290" spans="1:8">
       <c r="A290" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B290" s="1" t="s">
         <v>280</v>
@@ -10409,12 +10409,12 @@
       <c r="F290" s="3"/>
       <c r="G290" s="1"/>
       <c r="H290" s="1" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
     </row>
     <row r="291" spans="1:8">
       <c r="A291" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B291" s="1" t="s">
         <v>203</v>
@@ -10431,12 +10431,12 @@
       <c r="F291" s="3"/>
       <c r="G291" s="1"/>
       <c r="H291" s="1" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="292" spans="1:8">
       <c r="A292" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B292" s="1" t="s">
         <v>205</v>
@@ -10453,12 +10453,12 @@
       <c r="F292" s="3"/>
       <c r="G292" s="1"/>
       <c r="H292" s="1" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="293" spans="1:8" customFormat="1">
       <c r="A293" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B293" s="1" t="s">
         <v>210</v>
@@ -10475,12 +10475,12 @@
       <c r="F293" s="3"/>
       <c r="G293" s="1"/>
       <c r="H293" s="1" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="294" spans="1:8" customFormat="1">
       <c r="A294" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B294" s="1" t="s">
         <v>208</v>
@@ -10497,12 +10497,12 @@
       <c r="F294" s="3"/>
       <c r="G294" s="1"/>
       <c r="H294" s="1" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="295" spans="1:8" customFormat="1">
       <c r="A295" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B295" s="1" t="s">
         <v>207</v>
@@ -10514,17 +10514,17 @@
         <v>0</v>
       </c>
       <c r="E295" s="1" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="F295" s="3"/>
       <c r="G295" s="1"/>
       <c r="H295" s="1" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="296" spans="1:8" customFormat="1">
       <c r="A296" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B296" s="1" t="s">
         <v>296</v>
@@ -10539,134 +10539,134 @@
       </c>
       <c r="G296" s="1"/>
       <c r="H296" s="1" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
     </row>
     <row r="297" spans="1:8">
       <c r="A297" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B297" s="1" t="s">
         <v>1047</v>
       </c>
-      <c r="B297" s="1" t="s">
-        <v>1048</v>
-      </c>
       <c r="E297" s="1" t="s">
+        <v>1051</v>
+      </c>
+      <c r="F297" s="2">
+        <v>1</v>
+      </c>
+      <c r="H297" s="7" t="s">
         <v>1052</v>
-      </c>
-      <c r="F297" s="2">
-        <v>1</v>
-      </c>
-      <c r="H297" s="7" t="s">
-        <v>1053</v>
       </c>
     </row>
     <row r="298" spans="1:8">
       <c r="A298" s="2" t="s">
+        <v>1067</v>
+      </c>
+      <c r="B298" s="1" t="s">
         <v>1068</v>
       </c>
-      <c r="B298" s="1" t="s">
+      <c r="E298" s="1" t="s">
         <v>1069</v>
       </c>
-      <c r="E298" s="1" t="s">
+      <c r="F298" s="2">
+        <v>1</v>
+      </c>
+      <c r="H298" s="2" t="s">
         <v>1070</v>
-      </c>
-      <c r="F298" s="2">
-        <v>1</v>
-      </c>
-      <c r="H298" s="2" t="s">
-        <v>1071</v>
       </c>
     </row>
     <row r="299" spans="1:8">
       <c r="A299" s="2" t="s">
+        <v>1072</v>
+      </c>
+      <c r="B299" s="1" t="s">
+        <v>1071</v>
+      </c>
+      <c r="E299" s="1" t="s">
+        <v>1074</v>
+      </c>
+      <c r="F299" s="2">
+        <v>1</v>
+      </c>
+      <c r="H299" s="7" t="s">
         <v>1073</v>
-      </c>
-      <c r="B299" s="1" t="s">
-        <v>1072</v>
-      </c>
-      <c r="E299" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="F299" s="2">
-        <v>1</v>
-      </c>
-      <c r="H299" s="7" t="s">
-        <v>1074</v>
       </c>
     </row>
     <row r="300" spans="1:8">
       <c r="A300" s="2" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="B300" s="1" t="s">
+        <v>1075</v>
+      </c>
+      <c r="E300" s="1" t="s">
         <v>1076</v>
       </c>
-      <c r="E300" s="1" t="s">
+      <c r="F300" s="2">
+        <v>1</v>
+      </c>
+      <c r="H300" s="2" t="s">
         <v>1077</v>
-      </c>
-      <c r="F300" s="2">
-        <v>1</v>
-      </c>
-      <c r="H300" s="2" t="s">
-        <v>1078</v>
       </c>
     </row>
     <row r="301" spans="1:8">
       <c r="A301" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="B301" s="1" t="s">
+        <v>1078</v>
+      </c>
+      <c r="E301" s="1" t="s">
         <v>1079</v>
       </c>
-      <c r="E301" s="1" t="s">
-        <v>1080</v>
-      </c>
       <c r="F301" s="2">
         <v>1</v>
       </c>
       <c r="H301" s="2" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="302" spans="1:8">
       <c r="A302" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="B302" s="1" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="E302" s="1" t="s">
+        <v>1084</v>
+      </c>
+      <c r="F302" s="2">
+        <v>1</v>
+      </c>
+      <c r="H302" s="2" t="s">
         <v>1085</v>
-      </c>
-      <c r="F302" s="2">
-        <v>1</v>
-      </c>
-      <c r="H302" s="2" t="s">
-        <v>1086</v>
       </c>
     </row>
     <row r="303" spans="1:8">
       <c r="A303" s="2" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="B303" s="1" t="s">
+        <v>1087</v>
+      </c>
+      <c r="E303" s="1" t="s">
         <v>1088</v>
       </c>
-      <c r="E303" s="1" t="s">
-        <v>1089</v>
-      </c>
       <c r="F303" s="2">
         <v>1</v>
       </c>
       <c r="H303" s="7" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="304" spans="1:8">
       <c r="A304" s="2" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="B304" s="1" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="C304" s="2">
         <v>6</v>
@@ -10675,227 +10675,227 @@
         <v>0</v>
       </c>
       <c r="E304" s="1" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="H304" s="7" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="305" spans="1:8">
       <c r="A305" s="2" t="s">
+        <v>1094</v>
+      </c>
+      <c r="B305" s="1" t="s">
         <v>1095</v>
       </c>
-      <c r="B305" s="1" t="s">
-        <v>1096</v>
-      </c>
       <c r="E305" s="1" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="H305" s="7" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="306" spans="1:8">
       <c r="B306" s="1" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="307" spans="1:8">
       <c r="B307" s="1" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="308" spans="1:8">
       <c r="B308" s="1" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="309" spans="1:8">
       <c r="B309" s="1" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="310" spans="1:8">
       <c r="B310" s="1" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="311" spans="1:8">
       <c r="B311" s="1" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="312" spans="1:8">
       <c r="B312" s="1" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="313" spans="1:8">
       <c r="B313" s="1" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="314" spans="1:8">
       <c r="B314" s="1" t="s">
+        <v>1104</v>
+      </c>
+      <c r="E314" s="2" t="s">
         <v>1105</v>
-      </c>
-      <c r="E314" s="2" t="s">
-        <v>1106</v>
       </c>
     </row>
     <row r="315" spans="1:8">
       <c r="B315" s="1" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="316" spans="1:8">
       <c r="B316" s="1" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="317" spans="1:8">
       <c r="B317" s="1" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="318" spans="1:8">
       <c r="B318" s="1" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="319" spans="1:8">
       <c r="B319" s="1" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="320" spans="1:8">
       <c r="B320" s="1" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="321" spans="1:8">
       <c r="B321" s="1" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="322" spans="1:8">
       <c r="B322" s="1" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="323" spans="1:8">
       <c r="B323" s="1" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="324" spans="1:8">
       <c r="B324" s="1" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="325" spans="1:8">
       <c r="A325" s="2" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B325" s="1" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="E325" s="2" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="F325" s="2">
         <v>1</v>
       </c>
       <c r="H325" s="2" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="326" spans="1:8">
       <c r="A326" s="2" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="B326" s="1" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="E326" s="2" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="F326" s="2">
         <v>1</v>
       </c>
       <c r="H326" s="2" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="327" spans="1:8">
       <c r="A327" s="2" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="B327" s="1" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="E327" s="2" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="F327" s="2">
         <v>1</v>
       </c>
       <c r="H327" s="2" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="328" spans="1:8">
       <c r="A328" s="2" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="B328" s="1" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="E328" s="2" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="F328" s="2">
         <v>1</v>
       </c>
       <c r="H328" s="2" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="329" spans="1:8">
       <c r="A329" s="2" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="B329" s="1" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="E329" s="2" t="s">
+        <v>1130</v>
+      </c>
+      <c r="F329" s="2">
+        <v>1</v>
+      </c>
+      <c r="H329" s="2" t="s">
         <v>1131</v>
-      </c>
-      <c r="F329" s="2">
-        <v>1</v>
-      </c>
-      <c r="H329" s="2" t="s">
-        <v>1132</v>
       </c>
     </row>
     <row r="330" spans="1:8">
       <c r="A330" s="2" t="s">
+        <v>1139</v>
+      </c>
+      <c r="B330" s="1" t="s">
         <v>1140</v>
       </c>
-      <c r="B330" s="1" t="s">
+      <c r="E330" t="s">
         <v>1141</v>
       </c>
-      <c r="E330" t="s">
+      <c r="F330" s="2">
+        <v>1</v>
+      </c>
+      <c r="G330" s="2" t="s">
         <v>1142</v>
       </c>
-      <c r="F330" s="2">
-        <v>1</v>
-      </c>
-      <c r="G330" s="2" t="s">
+      <c r="H330" s="7" t="s">
         <v>1143</v>
-      </c>
-      <c r="H330" s="7" t="s">
-        <v>1144</v>
       </c>
     </row>
   </sheetData>

--- a/stores.xlsx
+++ b/stores.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\YUMIN\Desktop\B0KT2A_RSVN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B2D2E79-8A86-4E40-A8F4-619FE925A1FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1A8C382-E114-4543-9A98-BEF3996355F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{ABFC3117-FCCB-4FF3-804A-FE19451A2004}"/>
   </bookViews>
@@ -798,27 +798,18 @@
     <t>우정,학교,라이브시네마</t>
   </si>
   <si>
-    <t>매월 1일 00:00 오픈</t>
-  </si>
-  <si>
     <t>엔터팟 1호점</t>
   </si>
   <si>
     <t>비공식수사</t>
   </si>
   <si>
-    <t>매월 1일 18:00 오픈</t>
-  </si>
-  <si>
     <t>엔터팟 2호점</t>
   </si>
   <si>
     <t>미스터리 동네탐정,미동탐</t>
   </si>
   <si>
-    <t>매월 1일 20:00 오픈</t>
-  </si>
-  <si>
     <t>룸즈에이 강남점</t>
   </si>
   <si>
@@ -2251,10 +2242,6 @@
     <t>https://naver.me/GI3hw5ys</t>
   </si>
   <si>
-    <t>찬미특수진료센터,inspecto,getogeto,</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>dkdk,쇼쿠진,chaser:한마음폐공장,혼숨,hereiam,직박구리:남친탐구생활,영안실,복도끝:못다한이야기,못다恨이야기</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -3017,9 +3004,6 @@
     <t>my_dam</t>
   </si>
   <si>
-    <t>미스터리담</t>
-  </si>
-  <si>
     <t>백석담</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -3560,10 +3544,6 @@
   </si>
   <si>
     <t>끼리코구조대,티모의모험,왕자와공주</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>매월 1일 0:00 해당월 오픈</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -3664,10 +3644,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>매주 목요일 23:50 ~ 금요일 00:00 사이에 3주 뒤 수요일까지 열립니다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>sgn_grs</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -3995,6 +3971,34 @@
   </si>
   <si>
     <t>신촌성심병원,CHASER:한마음폐공장,HANNA IS FIRED,한나는해고됐어</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>미스터리 담</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>매월 1일 00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>매월 1일 18:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>매월 1일 20:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>매주 금요일 00:00 3주 뒤 수요일까지 열립니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>찬미특수진료센터,inspecto,getogeto,인스펙토,겟오겟오</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -4437,7 +4441,7 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="2" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>11</v>
@@ -4463,10 +4467,10 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="2" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="C2" s="2">
         <v>7</v>
@@ -4475,18 +4479,18 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="2" t="s">
-        <v>826</v>
+        <v>822</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>827</v>
+        <v>823</v>
       </c>
       <c r="C3" s="2">
         <v>7</v>
@@ -4495,18 +4499,18 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>828</v>
+        <v>824</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="2" t="s">
-        <v>829</v>
+        <v>825</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>830</v>
+        <v>826</v>
       </c>
       <c r="C4" s="2">
         <v>7</v>
@@ -4515,15 +4519,15 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="2" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="C5" s="3">
         <v>6</v>
@@ -4532,20 +4536,20 @@
         <v>0</v>
       </c>
       <c r="E5" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="F5" s="3"/>
       <c r="G5" s="1"/>
       <c r="H5" s="1" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="2" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="C6" s="3">
         <v>7</v>
@@ -4554,17 +4558,17 @@
         <v>0</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="F6" s="3"/>
       <c r="G6" s="1"/>
       <c r="H6" s="1" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="2" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>137</v>
@@ -4572,22 +4576,22 @@
       <c r="C7" s="3"/>
       <c r="D7" s="4"/>
       <c r="E7" s="1" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="F7" s="3">
         <v>1</v>
       </c>
       <c r="G7" s="1"/>
       <c r="H7" s="1" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="2" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="C8" s="3">
         <v>7</v>
@@ -4601,15 +4605,15 @@
       <c r="F8" s="3"/>
       <c r="G8" s="1"/>
       <c r="H8" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="2" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="C9" s="3">
         <v>7</v>
@@ -4618,17 +4622,17 @@
         <v>0</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="F9" s="3"/>
       <c r="G9" s="1"/>
       <c r="H9" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="2" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>133</v>
@@ -4645,12 +4649,12 @@
       <c r="F10" s="3"/>
       <c r="G10" s="1"/>
       <c r="H10" s="1" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="2" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>135</v>
@@ -4667,12 +4671,12 @@
       <c r="F11" s="3"/>
       <c r="G11" s="1"/>
       <c r="H11" s="1" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="2" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>233</v>
@@ -4684,17 +4688,17 @@
         <v>0</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="F12" s="3"/>
       <c r="G12" s="1"/>
       <c r="H12" s="1" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="2" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>234</v>
@@ -4706,17 +4710,17 @@
         <v>0</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="F13" s="3"/>
       <c r="G13" s="1"/>
       <c r="H13" s="1" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="2" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>235</v>
@@ -4728,17 +4732,17 @@
         <v>0</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="F14" s="3"/>
       <c r="G14" s="1"/>
       <c r="H14" s="1" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="2" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>230</v>
@@ -4750,17 +4754,17 @@
         <v>0</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="F15" s="3"/>
       <c r="G15" s="1"/>
       <c r="H15" s="1" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="2" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>231</v>
@@ -4777,12 +4781,12 @@
       <c r="F16" s="3"/>
       <c r="G16" s="1"/>
       <c r="H16" s="7" t="s">
-        <v>1045</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="2" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>212</v>
@@ -4794,17 +4798,17 @@
         <v>0</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>1145</v>
+        <v>1138</v>
       </c>
       <c r="F17" s="3"/>
       <c r="G17" s="1"/>
       <c r="H17" s="1" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="2" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>81</v>
@@ -4821,12 +4825,12 @@
       <c r="F18" s="3"/>
       <c r="G18" s="1"/>
       <c r="H18" s="1" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="2" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>83</v>
@@ -4843,12 +4847,12 @@
       <c r="F19" s="3"/>
       <c r="G19" s="1"/>
       <c r="H19" s="1" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="2" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>85</v>
@@ -4860,17 +4864,17 @@
         <v>0</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="F20" s="3"/>
       <c r="G20" s="1"/>
       <c r="H20" s="1" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="2" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>79</v>
@@ -4887,32 +4891,32 @@
       <c r="F21" s="3"/>
       <c r="G21" s="1"/>
       <c r="H21" s="1" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="2" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="C22" s="3"/>
       <c r="D22" s="4"/>
       <c r="E22" s="1" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="F22" s="3">
         <v>1</v>
       </c>
       <c r="G22" s="1"/>
       <c r="H22" s="1" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="2" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>77</v>
@@ -4929,12 +4933,12 @@
       <c r="F23" s="3"/>
       <c r="G23" s="1"/>
       <c r="H23" s="1" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="2" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>75</v>
@@ -4951,15 +4955,15 @@
       <c r="F24" s="3"/>
       <c r="G24" s="1"/>
       <c r="H24" s="1" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="2" t="s">
-        <v>831</v>
+        <v>827</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>832</v>
+        <v>828</v>
       </c>
       <c r="C25" s="3">
         <v>15</v>
@@ -4968,20 +4972,20 @@
         <v>0</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>833</v>
+        <v>829</v>
       </c>
       <c r="F25" s="3"/>
       <c r="G25" s="1"/>
       <c r="H25" s="11" t="s">
-        <v>834</v>
+        <v>830</v>
       </c>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="2" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C26" s="3">
         <v>6</v>
@@ -4990,19 +4994,19 @@
         <v>0</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="F26" s="3"/>
       <c r="H26" s="1" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="2" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="C27" s="3">
         <v>6</v>
@@ -5011,16 +5015,16 @@
         <v>0</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="F27" s="3"/>
       <c r="H27" s="1" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="2" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>138</v>
@@ -5037,12 +5041,12 @@
       <c r="F28" s="3"/>
       <c r="G28" s="1"/>
       <c r="H28" s="1" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="2" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>140</v>
@@ -5054,37 +5058,37 @@
         <v>0</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="F29" s="3"/>
       <c r="G29" s="1"/>
       <c r="H29" s="1" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="2" t="s">
-        <v>789</v>
+        <v>785</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>790</v>
+        <v>786</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>791</v>
+        <v>787</v>
       </c>
       <c r="F30" s="3">
         <v>1</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>788</v>
+        <v>784</v>
       </c>
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="2" t="s">
-        <v>801</v>
+        <v>797</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>803</v>
+        <v>799</v>
       </c>
       <c r="C31" s="2">
         <v>20</v>
@@ -5093,120 +5097,120 @@
         <v>0</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>802</v>
+        <v>798</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>800</v>
+        <v>796</v>
       </c>
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="2" t="s">
-        <v>776</v>
+        <v>772</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>777</v>
+        <v>773</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>778</v>
+        <v>774</v>
       </c>
       <c r="F32" s="3">
         <v>1</v>
       </c>
       <c r="H32" s="7" t="s">
-        <v>786</v>
+        <v>782</v>
       </c>
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="2" t="s">
-        <v>772</v>
+        <v>768</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>773</v>
+        <v>769</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>774</v>
+        <v>770</v>
       </c>
       <c r="F33" s="3">
         <v>1</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>775</v>
+        <v>771</v>
       </c>
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="2" t="s">
+        <v>779</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>780</v>
+      </c>
+      <c r="E34" s="1" t="s">
         <v>783</v>
       </c>
-      <c r="B34" s="1" t="s">
-        <v>784</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>787</v>
-      </c>
       <c r="F34" s="3">
         <v>1</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>785</v>
+        <v>781</v>
       </c>
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="2" t="s">
-        <v>797</v>
+        <v>793</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>798</v>
+        <v>794</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>799</v>
+        <v>795</v>
       </c>
       <c r="F35" s="3">
         <v>1</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>796</v>
+        <v>792</v>
       </c>
     </row>
     <row r="36" spans="1:8">
       <c r="A36" s="2" t="s">
-        <v>793</v>
+        <v>789</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>794</v>
+        <v>790</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>795</v>
+        <v>791</v>
       </c>
       <c r="F36" s="3">
         <v>1</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>792</v>
+        <v>788</v>
       </c>
     </row>
     <row r="37" spans="1:8">
       <c r="A37" s="2" t="s">
-        <v>780</v>
+        <v>776</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>781</v>
+        <v>777</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>782</v>
+        <v>778</v>
       </c>
       <c r="F37" s="3">
         <v>1</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>779</v>
+        <v>775</v>
       </c>
     </row>
     <row r="38" spans="1:8">
       <c r="A38" s="2" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="C38" s="3">
         <v>6</v>
@@ -5215,57 +5219,57 @@
         <v>0</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="F38" s="3"/>
       <c r="G38" s="1"/>
       <c r="H38" s="2" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
     </row>
     <row r="39" spans="1:8">
       <c r="A39" s="2" t="s">
+        <v>684</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>685</v>
+      </c>
+      <c r="E39" s="1" t="s">
         <v>688</v>
       </c>
-      <c r="B39" s="1" t="s">
-        <v>689</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>692</v>
-      </c>
       <c r="F39" s="3">
         <v>1</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>735</v>
+        <v>731</v>
       </c>
     </row>
     <row r="40" spans="1:8">
       <c r="A40" s="2" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>691</v>
+        <v>687</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>693</v>
+        <v>689</v>
       </c>
       <c r="F40" s="3">
         <v>1</v>
       </c>
       <c r="H40" s="9" t="s">
-        <v>734</v>
+        <v>730</v>
       </c>
     </row>
     <row r="41" spans="1:8">
       <c r="A41" s="2" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="F41" s="3">
         <v>1</v>
@@ -5273,7 +5277,7 @@
     </row>
     <row r="42" spans="1:8">
       <c r="A42" s="2" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>141</v>
@@ -5290,12 +5294,12 @@
       <c r="F42" s="3"/>
       <c r="G42" s="1"/>
       <c r="H42" s="1" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
     </row>
     <row r="43" spans="1:8">
       <c r="A43" s="2" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>153</v>
@@ -5310,12 +5314,12 @@
       </c>
       <c r="G43" s="1"/>
       <c r="H43" s="1" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
     </row>
     <row r="44" spans="1:8">
       <c r="A44" s="2" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>155</v>
@@ -5332,12 +5336,12 @@
       <c r="F44" s="3"/>
       <c r="G44" s="1"/>
       <c r="H44" s="1" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
     </row>
     <row r="45" spans="1:8">
       <c r="A45" s="2" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>143</v>
@@ -5354,12 +5358,12 @@
       <c r="F45" s="3"/>
       <c r="G45" s="1"/>
       <c r="H45" s="1" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
     </row>
     <row r="46" spans="1:8">
       <c r="A46" s="2" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>145</v>
@@ -5376,12 +5380,12 @@
       <c r="F46" s="3"/>
       <c r="G46" s="1"/>
       <c r="H46" s="1" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
     </row>
     <row r="47" spans="1:8">
       <c r="A47" s="2" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>151</v>
@@ -5396,12 +5400,12 @@
       </c>
       <c r="G47" s="1"/>
       <c r="H47" s="1" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="48" spans="1:8">
       <c r="A48" s="2" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>149</v>
@@ -5416,12 +5420,12 @@
       </c>
       <c r="G48" s="1"/>
       <c r="H48" s="1" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
     </row>
     <row r="49" spans="1:8">
       <c r="A49" s="2" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>147</v>
@@ -5438,12 +5442,12 @@
       <c r="F49" s="3"/>
       <c r="G49" s="1"/>
       <c r="H49" s="1" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
     </row>
     <row r="50" spans="1:8">
       <c r="A50" s="2" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>8</v>
@@ -5455,17 +5459,17 @@
         <v>0</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="F50" s="3"/>
       <c r="G50" s="1"/>
       <c r="H50" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
     </row>
     <row r="51" spans="1:8">
       <c r="A51" s="2" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>246</v>
@@ -5482,12 +5486,12 @@
       <c r="F51" s="3"/>
       <c r="G51" s="1"/>
       <c r="H51" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
     </row>
     <row r="52" spans="1:8">
       <c r="A52" s="2" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>248</v>
@@ -5504,12 +5508,12 @@
       <c r="F52" s="3"/>
       <c r="G52" s="1"/>
       <c r="H52" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
     </row>
     <row r="53" spans="1:8">
       <c r="A53" s="2" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>250</v>
@@ -5526,12 +5530,12 @@
       <c r="F53" s="3"/>
       <c r="G53" s="1"/>
       <c r="H53" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
     </row>
     <row r="54" spans="1:8">
       <c r="A54" s="2" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>125</v>
@@ -5548,15 +5552,15 @@
       <c r="F54" s="3"/>
       <c r="G54" s="1"/>
       <c r="H54" s="1" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
     </row>
     <row r="55" spans="1:8">
       <c r="A55" s="2" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="C55" s="1">
         <v>13</v>
@@ -5565,17 +5569,17 @@
         <v>0</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="F55" s="1"/>
       <c r="G55" s="1"/>
       <c r="H55" s="1" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
     </row>
     <row r="56" spans="1:8">
       <c r="A56" s="2" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>252</v>
@@ -5589,21 +5593,21 @@
         <v>1</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>254</v>
+        <v>1140</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
     </row>
     <row r="57" spans="1:8">
       <c r="A57" t="s">
-        <v>676</v>
+        <v>672</v>
       </c>
       <c r="B57" s="1" t="s">
+        <v>638</v>
+      </c>
+      <c r="E57" s="1" t="s">
         <v>641</v>
-      </c>
-      <c r="E57" s="1" t="s">
-        <v>644</v>
       </c>
       <c r="F57" s="2">
         <v>1</v>
@@ -5611,46 +5615,46 @@
     </row>
     <row r="58" spans="1:8">
       <c r="A58" t="s">
-        <v>677</v>
+        <v>673</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="F58" s="3">
         <v>1</v>
       </c>
       <c r="H58" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
     </row>
     <row r="59" spans="1:8">
       <c r="A59" t="s">
-        <v>678</v>
+        <v>674</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C59" s="3"/>
       <c r="D59" s="6"/>
       <c r="E59" s="1" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="F59" s="3">
         <v>1</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>1144</v>
+        <v>1137</v>
       </c>
       <c r="H59" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
     </row>
     <row r="60" spans="1:8">
       <c r="A60" s="2" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>127</v>
@@ -5667,15 +5671,15 @@
       <c r="F60" s="3"/>
       <c r="G60" s="1"/>
       <c r="H60" s="1" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
     </row>
     <row r="61" spans="1:8">
       <c r="A61" s="11" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="B61" t="s">
-        <v>836</v>
+        <v>832</v>
       </c>
       <c r="C61">
         <v>6</v>
@@ -5684,20 +5688,20 @@
         <v>0</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>837</v>
+        <v>833</v>
       </c>
       <c r="F61" s="3"/>
       <c r="G61" s="1"/>
       <c r="H61" s="1" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
     </row>
     <row r="62" spans="1:8">
       <c r="A62" s="2" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="C62" s="3">
         <v>6</v>
@@ -5706,40 +5710,40 @@
         <v>0</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="F62" s="3"/>
       <c r="G62" s="1"/>
       <c r="H62" s="1" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
     </row>
     <row r="63" spans="1:8">
       <c r="A63" s="2" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="C63" s="3"/>
       <c r="D63" s="5"/>
       <c r="E63" s="1" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="F63" s="3">
         <v>1</v>
       </c>
       <c r="G63" s="1"/>
       <c r="H63" s="1" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
     </row>
     <row r="64" spans="1:8">
       <c r="A64" s="2" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="C64" s="3">
         <v>6</v>
@@ -5748,17 +5752,17 @@
         <v>0</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="F64" s="3"/>
       <c r="G64" s="1"/>
       <c r="H64" s="1" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
     </row>
     <row r="65" spans="1:8">
       <c r="A65" s="2" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>2</v>
@@ -5775,12 +5779,12 @@
       <c r="F65" s="3"/>
       <c r="G65" s="1"/>
       <c r="H65" s="2" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
     </row>
     <row r="66" spans="1:8">
       <c r="A66" s="2" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>6</v>
@@ -5797,12 +5801,12 @@
       <c r="F66" s="3"/>
       <c r="G66" s="1"/>
       <c r="H66" s="2" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
     </row>
     <row r="67" spans="1:8">
       <c r="A67" s="2" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>4</v>
@@ -5819,12 +5823,12 @@
       <c r="F67" s="3"/>
       <c r="G67" s="1"/>
       <c r="H67" s="2" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
     </row>
     <row r="68" spans="1:8">
       <c r="A68" s="2" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>0</v>
@@ -5841,15 +5845,15 @@
       <c r="F68" s="3"/>
       <c r="G68" s="1"/>
       <c r="H68" s="2" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
     </row>
     <row r="69" spans="1:8">
       <c r="A69" s="2" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C69" s="3">
         <v>7</v>
@@ -5858,16 +5862,16 @@
         <v>0</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="F69" s="3"/>
       <c r="H69" s="1" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
     </row>
     <row r="70" spans="1:8">
       <c r="A70" s="2" t="s">
-        <v>653</v>
+        <v>649</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>181</v>
@@ -5881,31 +5885,31 @@
         <v>1</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
     </row>
     <row r="71" spans="1:8">
       <c r="A71" t="s">
-        <v>670</v>
+        <v>666</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="C71" s="3"/>
       <c r="D71" s="4"/>
       <c r="E71" s="1" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="F71" s="3">
         <v>1</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
     </row>
     <row r="72" spans="1:8">
       <c r="A72" t="s">
-        <v>671</v>
+        <v>667</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>179</v>
@@ -5919,12 +5923,12 @@
         <v>1</v>
       </c>
       <c r="H72" s="1" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
     </row>
     <row r="73" spans="1:8">
       <c r="A73" t="s">
-        <v>656</v>
+        <v>652</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>185</v>
@@ -5940,12 +5944,12 @@
       </c>
       <c r="F73" s="3"/>
       <c r="H73" s="1" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
     </row>
     <row r="74" spans="1:8">
       <c r="A74" s="2" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>183</v>
@@ -5961,12 +5965,12 @@
       </c>
       <c r="F74" s="3"/>
       <c r="H74" s="1" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
     </row>
     <row r="75" spans="1:8">
       <c r="A75" t="s">
-        <v>658</v>
+        <v>654</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>171</v>
@@ -5980,12 +5984,12 @@
         <v>1</v>
       </c>
       <c r="H75" s="1" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
     </row>
     <row r="76" spans="1:8">
       <c r="A76" t="s">
-        <v>659</v>
+        <v>655</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>173</v>
@@ -5999,12 +6003,12 @@
         <v>1</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
     </row>
     <row r="77" spans="1:8">
       <c r="A77" s="2" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>157</v>
@@ -6018,12 +6022,12 @@
         <v>1</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
     </row>
     <row r="78" spans="1:8">
       <c r="A78" t="s">
-        <v>674</v>
+        <v>670</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>187</v>
@@ -6039,12 +6043,12 @@
       </c>
       <c r="F78" s="3"/>
       <c r="H78" s="1" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
     </row>
     <row r="79" spans="1:8">
       <c r="A79" t="s">
-        <v>672</v>
+        <v>668</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>175</v>
@@ -6058,12 +6062,12 @@
         <v>1</v>
       </c>
       <c r="H79" s="1" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
     </row>
     <row r="80" spans="1:8">
       <c r="A80" t="s">
-        <v>673</v>
+        <v>669</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>177</v>
@@ -6079,12 +6083,12 @@
       </c>
       <c r="F80" s="3"/>
       <c r="H80" s="1" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
     </row>
     <row r="81" spans="1:8">
       <c r="A81" s="2" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>193</v>
@@ -6100,12 +6104,12 @@
       </c>
       <c r="F81" s="3"/>
       <c r="H81" s="1" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
     </row>
     <row r="82" spans="1:8">
       <c r="A82" s="2" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>191</v>
@@ -6121,12 +6125,12 @@
       </c>
       <c r="F82" s="3"/>
       <c r="H82" s="1" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
     </row>
     <row r="83" spans="1:8">
       <c r="A83" s="2" t="s">
-        <v>654</v>
+        <v>650</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>169</v>
@@ -6142,12 +6146,12 @@
       </c>
       <c r="F83" s="3"/>
       <c r="H83" s="1" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
     </row>
     <row r="84" spans="1:8">
       <c r="A84" s="2" t="s">
-        <v>655</v>
+        <v>651</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>167</v>
@@ -6161,12 +6165,12 @@
         <v>1</v>
       </c>
       <c r="H84" s="1" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
     </row>
     <row r="85" spans="1:8">
       <c r="A85" t="s">
-        <v>660</v>
+        <v>656</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>159</v>
@@ -6180,12 +6184,12 @@
         <v>1</v>
       </c>
       <c r="H85" s="1" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
     </row>
     <row r="86" spans="1:8">
       <c r="A86" t="s">
-        <v>661</v>
+        <v>657</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>165</v>
@@ -6199,12 +6203,12 @@
         <v>1</v>
       </c>
       <c r="H86" s="1" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
     </row>
     <row r="87" spans="1:8">
       <c r="A87" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>163</v>
@@ -6218,12 +6222,12 @@
         <v>1</v>
       </c>
       <c r="H87" s="1" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
     </row>
     <row r="88" spans="1:8">
       <c r="A88" t="s">
-        <v>663</v>
+        <v>659</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>161</v>
@@ -6237,12 +6241,12 @@
         <v>1</v>
       </c>
       <c r="H88" s="1" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
     </row>
     <row r="89" spans="1:8">
       <c r="A89" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>189</v>
@@ -6258,48 +6262,48 @@
       </c>
       <c r="F89" s="3"/>
       <c r="H89" s="1" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
     </row>
     <row r="90" spans="1:8">
       <c r="A90" t="s">
-        <v>838</v>
+        <v>834</v>
       </c>
       <c r="B90" t="s">
-        <v>839</v>
+        <v>835</v>
       </c>
       <c r="C90" s="3"/>
       <c r="D90" s="4"/>
       <c r="E90" s="1" t="s">
-        <v>840</v>
+        <v>836</v>
       </c>
       <c r="F90" s="3">
         <v>1</v>
       </c>
       <c r="H90" s="11" t="s">
-        <v>841</v>
+        <v>837</v>
       </c>
     </row>
     <row r="91" spans="1:8">
       <c r="A91" s="2" t="s">
-        <v>821</v>
+        <v>817</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>822</v>
+        <v>818</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>823</v>
+        <v>819</v>
       </c>
       <c r="F91" s="3">
         <v>1</v>
       </c>
       <c r="H91" s="7" t="s">
-        <v>824</v>
+        <v>820</v>
       </c>
     </row>
     <row r="92" spans="1:8">
       <c r="A92" s="2" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>98</v>
@@ -6316,15 +6320,15 @@
       <c r="F92" s="3"/>
       <c r="G92" s="1"/>
       <c r="H92" s="1" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
     </row>
     <row r="93" spans="1:8">
       <c r="A93" s="2" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="C93" s="3">
         <v>7</v>
@@ -6338,12 +6342,12 @@
       <c r="F93" s="3"/>
       <c r="G93" s="1"/>
       <c r="H93" s="1" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
     </row>
     <row r="94" spans="1:8">
       <c r="A94" s="2" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>106</v>
@@ -6360,12 +6364,12 @@
       <c r="F94" s="3"/>
       <c r="G94" s="1"/>
       <c r="H94" s="1" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
     </row>
     <row r="95" spans="1:8">
       <c r="A95" s="2" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>112</v>
@@ -6382,15 +6386,15 @@
       <c r="F95" s="3"/>
       <c r="G95" s="1"/>
       <c r="H95" s="1" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
     </row>
     <row r="96" spans="1:8">
       <c r="A96" s="2" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="C96" s="3">
         <v>7</v>
@@ -6404,15 +6408,15 @@
       <c r="F96" s="3"/>
       <c r="G96" s="1"/>
       <c r="H96" s="1" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
     </row>
     <row r="97" spans="1:8">
       <c r="A97" s="2" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="C97" s="3">
         <v>7</v>
@@ -6426,15 +6430,15 @@
       <c r="F97" s="3"/>
       <c r="G97" s="1"/>
       <c r="H97" s="1" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
     </row>
     <row r="98" spans="1:8">
       <c r="A98" s="2" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="C98" s="3">
         <v>7</v>
@@ -6448,267 +6452,267 @@
       <c r="F98" s="3"/>
       <c r="G98" s="1"/>
       <c r="H98" s="1" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
     </row>
     <row r="99" spans="1:8">
       <c r="A99" s="2" t="s">
-        <v>729</v>
+        <v>725</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>730</v>
+        <v>726</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>749</v>
+        <v>745</v>
       </c>
       <c r="F99" s="3">
         <v>1</v>
       </c>
       <c r="H99" s="7" t="s">
-        <v>754</v>
+        <v>750</v>
       </c>
     </row>
     <row r="100" spans="1:8">
       <c r="A100" s="2" t="s">
-        <v>728</v>
+        <v>724</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>748</v>
+        <v>744</v>
       </c>
       <c r="F100" s="3">
         <v>1</v>
       </c>
       <c r="H100" s="7" t="s">
-        <v>754</v>
+        <v>750</v>
       </c>
     </row>
     <row r="101" spans="1:8">
       <c r="A101" s="2" t="s">
-        <v>713</v>
+        <v>709</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>715</v>
+        <v>711</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>741</v>
+        <v>737</v>
       </c>
       <c r="F101" s="3">
         <v>1</v>
       </c>
       <c r="H101" s="7" t="s">
-        <v>754</v>
+        <v>750</v>
       </c>
     </row>
     <row r="102" spans="1:8">
       <c r="A102" s="2" t="s">
-        <v>718</v>
+        <v>714</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>719</v>
+        <v>715</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>743</v>
+        <v>739</v>
       </c>
       <c r="F102" s="3">
         <v>1</v>
       </c>
       <c r="H102" s="7" t="s">
-        <v>754</v>
+        <v>750</v>
       </c>
     </row>
     <row r="103" spans="1:8">
       <c r="A103" s="2" t="s">
-        <v>716</v>
+        <v>712</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>742</v>
+        <v>738</v>
       </c>
       <c r="F103" s="3">
         <v>1</v>
       </c>
       <c r="H103" s="7" t="s">
-        <v>754</v>
+        <v>750</v>
       </c>
     </row>
     <row r="104" spans="1:8">
       <c r="A104" s="2" t="s">
-        <v>714</v>
+        <v>710</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>740</v>
+        <v>736</v>
       </c>
       <c r="F104" s="3">
         <v>1</v>
       </c>
       <c r="H104" s="7" t="s">
-        <v>754</v>
+        <v>750</v>
       </c>
     </row>
     <row r="105" spans="1:8">
       <c r="A105" s="2" t="s">
-        <v>722</v>
+        <v>718</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>723</v>
+        <v>719</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>745</v>
+        <v>741</v>
       </c>
       <c r="F105" s="3">
         <v>1</v>
       </c>
       <c r="H105" s="7" t="s">
-        <v>754</v>
+        <v>750</v>
       </c>
     </row>
     <row r="106" spans="1:8">
       <c r="A106" s="2" t="s">
-        <v>726</v>
+        <v>722</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>727</v>
+        <v>723</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>747</v>
+        <v>743</v>
       </c>
       <c r="F106" s="3">
         <v>1</v>
       </c>
       <c r="H106" s="7" t="s">
-        <v>754</v>
+        <v>750</v>
       </c>
     </row>
     <row r="107" spans="1:8">
       <c r="A107" s="2" t="s">
-        <v>708</v>
+        <v>704</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>709</v>
+        <v>705</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>738</v>
+        <v>734</v>
       </c>
       <c r="F107" s="3">
         <v>1</v>
       </c>
       <c r="H107" s="7" t="s">
-        <v>754</v>
+        <v>750</v>
       </c>
     </row>
     <row r="108" spans="1:8">
       <c r="A108" s="2" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>732</v>
+        <v>728</v>
       </c>
       <c r="E108" s="1" t="s">
+        <v>746</v>
+      </c>
+      <c r="F108" s="3">
+        <v>1</v>
+      </c>
+      <c r="H108" s="7" t="s">
         <v>750</v>
-      </c>
-      <c r="F108" s="3">
-        <v>1</v>
-      </c>
-      <c r="H108" s="7" t="s">
-        <v>754</v>
       </c>
     </row>
     <row r="109" spans="1:8">
       <c r="A109" s="2" t="s">
-        <v>724</v>
+        <v>720</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>725</v>
+        <v>721</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>746</v>
+        <v>742</v>
       </c>
       <c r="F109" s="3">
         <v>1</v>
       </c>
       <c r="H109" s="7" t="s">
-        <v>754</v>
+        <v>750</v>
       </c>
     </row>
     <row r="110" spans="1:8">
       <c r="A110" s="2" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>733</v>
+        <v>729</v>
       </c>
       <c r="F110" s="3">
         <v>1</v>
       </c>
       <c r="H110" s="7" t="s">
-        <v>754</v>
+        <v>750</v>
       </c>
     </row>
     <row r="111" spans="1:8">
       <c r="A111" s="2" t="s">
-        <v>706</v>
+        <v>702</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>737</v>
+        <v>733</v>
       </c>
       <c r="F111" s="3">
         <v>1</v>
       </c>
       <c r="H111" s="7" t="s">
-        <v>754</v>
+        <v>750</v>
       </c>
     </row>
     <row r="112" spans="1:8">
       <c r="A112" s="2" t="s">
-        <v>710</v>
+        <v>706</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>739</v>
+        <v>735</v>
       </c>
       <c r="F112" s="3">
         <v>1</v>
       </c>
       <c r="H112" s="7" t="s">
-        <v>754</v>
+        <v>750</v>
       </c>
     </row>
     <row r="113" spans="1:8">
       <c r="A113" s="2" t="s">
-        <v>720</v>
+        <v>716</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>721</v>
+        <v>717</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>744</v>
+        <v>740</v>
       </c>
       <c r="F113" s="3">
         <v>1</v>
       </c>
       <c r="H113" s="7" t="s">
-        <v>754</v>
+        <v>750</v>
       </c>
     </row>
     <row r="114" spans="1:8">
       <c r="A114" s="2" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="B114" s="1" t="s">
         <v>244</v>
@@ -6725,77 +6729,77 @@
       <c r="F114" s="3"/>
       <c r="G114" s="1"/>
       <c r="H114" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
     </row>
     <row r="115" spans="1:8">
       <c r="A115" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
       <c r="B115" t="s">
-        <v>843</v>
+        <v>839</v>
       </c>
       <c r="C115" s="3"/>
       <c r="D115" s="4"/>
       <c r="E115" s="1" t="s">
-        <v>844</v>
+        <v>840</v>
       </c>
       <c r="F115" s="3">
         <v>1</v>
       </c>
       <c r="G115" s="1"/>
       <c r="H115" s="11" t="s">
-        <v>845</v>
+        <v>841</v>
       </c>
     </row>
     <row r="116" spans="1:8">
       <c r="A116" t="s">
-        <v>846</v>
+        <v>842</v>
       </c>
       <c r="B116" t="s">
-        <v>847</v>
+        <v>843</v>
       </c>
       <c r="C116" s="3"/>
       <c r="D116" s="4"/>
       <c r="E116" s="1" t="s">
-        <v>848</v>
+        <v>844</v>
       </c>
       <c r="F116" s="3">
         <v>1</v>
       </c>
       <c r="G116" s="1"/>
       <c r="H116" s="11" t="s">
-        <v>849</v>
+        <v>845</v>
       </c>
     </row>
     <row r="117" spans="1:8">
       <c r="A117" t="s">
-        <v>850</v>
+        <v>846</v>
       </c>
       <c r="B117" t="s">
-        <v>851</v>
+        <v>1139</v>
       </c>
       <c r="C117" s="3"/>
       <c r="D117" s="4"/>
       <c r="E117" s="1" t="s">
-        <v>852</v>
+        <v>847</v>
       </c>
       <c r="F117" s="3">
         <v>1</v>
       </c>
       <c r="G117" s="1" t="s">
-        <v>853</v>
+        <v>848</v>
       </c>
       <c r="H117" s="11" t="s">
-        <v>854</v>
+        <v>849</v>
       </c>
     </row>
     <row r="118" spans="1:8">
       <c r="A118" s="2" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="C118" s="3">
         <v>7</v>
@@ -6809,15 +6813,15 @@
       <c r="F118" s="3"/>
       <c r="G118" s="1"/>
       <c r="H118" s="1" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
     </row>
     <row r="119" spans="1:8">
       <c r="A119" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="C119" s="3">
         <v>7</v>
@@ -6826,54 +6830,54 @@
         <v>0.95833333333333337</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="F119" s="3"/>
       <c r="G119" s="1"/>
       <c r="H119" s="1" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
     </row>
     <row r="120" spans="1:8">
       <c r="A120" s="2" t="s">
-        <v>687</v>
+        <v>683</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="C120" s="1"/>
       <c r="D120" s="5"/>
       <c r="E120" s="1" t="s">
-        <v>820</v>
+        <v>816</v>
       </c>
       <c r="F120" s="3">
         <v>1</v>
       </c>
       <c r="G120" s="1"/>
       <c r="H120" s="1" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
     </row>
     <row r="121" spans="1:8">
       <c r="A121" s="2" t="s">
-        <v>808</v>
+        <v>804</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>809</v>
+        <v>805</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="F121" s="3">
         <v>1</v>
       </c>
       <c r="H121" s="7" t="s">
-        <v>810</v>
+        <v>806</v>
       </c>
     </row>
     <row r="122" spans="1:8">
       <c r="A122" s="2" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="B122" s="1" t="s">
         <v>238</v>
@@ -6890,120 +6894,120 @@
       <c r="F122" s="3"/>
       <c r="G122" s="1"/>
       <c r="H122" s="1" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
     </row>
     <row r="123" spans="1:8">
       <c r="A123" t="s">
-        <v>855</v>
+        <v>850</v>
       </c>
       <c r="B123" t="s">
-        <v>856</v>
+        <v>851</v>
       </c>
       <c r="C123"/>
       <c r="D123" s="11"/>
       <c r="E123" t="s">
-        <v>875</v>
+        <v>870</v>
       </c>
       <c r="F123" s="1">
         <v>1</v>
       </c>
       <c r="G123"/>
       <c r="H123" t="s">
-        <v>884</v>
+        <v>879</v>
       </c>
     </row>
     <row r="124" spans="1:8">
       <c r="A124" t="s">
-        <v>857</v>
+        <v>852</v>
       </c>
       <c r="B124" t="s">
-        <v>858</v>
+        <v>853</v>
       </c>
       <c r="E124" t="s">
-        <v>876</v>
+        <v>871</v>
       </c>
       <c r="F124" s="1">
         <v>1</v>
       </c>
       <c r="H124" t="s">
-        <v>885</v>
+        <v>880</v>
       </c>
     </row>
     <row r="125" spans="1:8">
       <c r="A125" t="s">
-        <v>859</v>
+        <v>854</v>
       </c>
       <c r="B125" t="s">
-        <v>860</v>
+        <v>855</v>
       </c>
       <c r="E125" t="s">
-        <v>877</v>
+        <v>872</v>
       </c>
       <c r="F125" s="1">
         <v>1</v>
       </c>
       <c r="H125" t="s">
-        <v>886</v>
+        <v>881</v>
       </c>
     </row>
     <row r="126" spans="1:8">
       <c r="A126" t="s">
-        <v>861</v>
+        <v>856</v>
       </c>
       <c r="B126" t="s">
-        <v>862</v>
+        <v>857</v>
       </c>
       <c r="E126" t="s">
-        <v>878</v>
+        <v>873</v>
       </c>
       <c r="F126" s="1">
         <v>1</v>
       </c>
       <c r="H126" t="s">
-        <v>886</v>
+        <v>881</v>
       </c>
     </row>
     <row r="127" spans="1:8">
       <c r="A127" t="s">
-        <v>863</v>
+        <v>858</v>
       </c>
       <c r="B127" t="s">
-        <v>864</v>
+        <v>859</v>
       </c>
       <c r="E127" t="s">
-        <v>1062</v>
+        <v>1055</v>
       </c>
       <c r="F127" s="1">
         <v>1</v>
       </c>
       <c r="H127" t="s">
-        <v>886</v>
+        <v>881</v>
       </c>
     </row>
     <row r="128" spans="1:8">
       <c r="A128" t="s">
-        <v>865</v>
+        <v>860</v>
       </c>
       <c r="B128" t="s">
-        <v>866</v>
+        <v>861</v>
       </c>
       <c r="E128" t="s">
-        <v>879</v>
+        <v>874</v>
       </c>
       <c r="F128" s="1">
         <v>1</v>
       </c>
       <c r="H128" t="s">
-        <v>886</v>
+        <v>881</v>
       </c>
     </row>
     <row r="129" spans="1:8">
       <c r="A129" t="s">
-        <v>867</v>
+        <v>862</v>
       </c>
       <c r="B129" t="s">
-        <v>868</v>
+        <v>863</v>
       </c>
       <c r="C129" s="2">
         <v>6</v>
@@ -7012,36 +7016,36 @@
         <v>0</v>
       </c>
       <c r="E129" t="s">
-        <v>880</v>
+        <v>875</v>
       </c>
       <c r="F129" s="1"/>
       <c r="H129" t="s">
-        <v>886</v>
+        <v>881</v>
       </c>
     </row>
     <row r="130" spans="1:8">
       <c r="A130" t="s">
-        <v>869</v>
+        <v>864</v>
       </c>
       <c r="B130" t="s">
-        <v>870</v>
+        <v>865</v>
       </c>
       <c r="E130" t="s">
+        <v>876</v>
+      </c>
+      <c r="F130" s="1">
+        <v>1</v>
+      </c>
+      <c r="H130" t="s">
         <v>881</v>
-      </c>
-      <c r="F130" s="1">
-        <v>1</v>
-      </c>
-      <c r="H130" t="s">
-        <v>886</v>
       </c>
     </row>
     <row r="131" spans="1:8">
       <c r="A131" t="s">
-        <v>871</v>
+        <v>866</v>
       </c>
       <c r="B131" t="s">
-        <v>872</v>
+        <v>867</v>
       </c>
       <c r="C131" s="2">
         <v>6</v>
@@ -7050,50 +7054,50 @@
         <v>0</v>
       </c>
       <c r="E131" t="s">
-        <v>882</v>
+        <v>877</v>
       </c>
       <c r="F131" s="1"/>
       <c r="H131" t="s">
-        <v>886</v>
+        <v>881</v>
       </c>
     </row>
     <row r="132" spans="1:8">
       <c r="A132" t="s">
-        <v>873</v>
+        <v>868</v>
       </c>
       <c r="B132" t="s">
-        <v>874</v>
+        <v>869</v>
       </c>
       <c r="E132" t="s">
-        <v>883</v>
+        <v>878</v>
       </c>
       <c r="F132" s="1">
         <v>1</v>
       </c>
       <c r="H132" t="s">
-        <v>886</v>
+        <v>881</v>
       </c>
     </row>
     <row r="133" spans="1:8">
       <c r="A133" t="s">
-        <v>1064</v>
+        <v>1057</v>
       </c>
       <c r="B133" t="s">
-        <v>1065</v>
+        <v>1058</v>
       </c>
       <c r="E133" t="s">
-        <v>1066</v>
+        <v>1059</v>
       </c>
       <c r="F133" s="1">
         <v>1</v>
       </c>
       <c r="H133" t="s">
-        <v>886</v>
+        <v>881</v>
       </c>
     </row>
     <row r="134" spans="1:8">
       <c r="A134" s="2" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="B134" s="1" t="s">
         <v>47</v>
@@ -7110,12 +7114,12 @@
       <c r="F134" s="3"/>
       <c r="G134" s="1"/>
       <c r="H134" s="2" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
     </row>
     <row r="135" spans="1:8">
       <c r="A135" s="2" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="B135" s="1" t="s">
         <v>49</v>
@@ -7132,15 +7136,15 @@
       <c r="F135" s="3"/>
       <c r="G135" s="1"/>
       <c r="H135" s="2" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
     </row>
     <row r="136" spans="1:8">
       <c r="A136" s="2" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="C136" s="3">
         <v>6</v>
@@ -7149,17 +7153,17 @@
         <v>0</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="F136" s="3"/>
       <c r="G136" s="1"/>
       <c r="H136" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
     </row>
     <row r="137" spans="1:8">
       <c r="A137" s="2" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="B137" s="1" t="s">
         <v>43</v>
@@ -7176,12 +7180,12 @@
       <c r="F137" s="3"/>
       <c r="G137" s="1"/>
       <c r="H137" s="2" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
     </row>
     <row r="138" spans="1:8">
       <c r="A138" s="2" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="B138" s="1" t="s">
         <v>51</v>
@@ -7198,12 +7202,12 @@
       <c r="F138" s="3"/>
       <c r="G138" s="1"/>
       <c r="H138" s="2" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
     </row>
     <row r="139" spans="1:8">
       <c r="A139" s="2" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="B139" s="1" t="s">
         <v>53</v>
@@ -7220,15 +7224,15 @@
       <c r="F139" s="3"/>
       <c r="G139" s="1"/>
       <c r="H139" s="2" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
     </row>
     <row r="140" spans="1:8">
       <c r="A140" s="2" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="C140" s="3">
         <v>6</v>
@@ -7237,17 +7241,17 @@
         <v>0</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="F140" s="3"/>
       <c r="G140" s="1"/>
       <c r="H140" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
     </row>
     <row r="141" spans="1:8">
       <c r="A141" s="2" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="B141" s="1" t="s">
         <v>55</v>
@@ -7264,15 +7268,15 @@
       <c r="F141" s="3"/>
       <c r="G141" s="1"/>
       <c r="H141" s="2" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
     </row>
     <row r="142" spans="1:8">
       <c r="A142" s="2" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>685</v>
+        <v>681</v>
       </c>
       <c r="C142" s="3">
         <v>6</v>
@@ -7281,17 +7285,17 @@
         <v>0.875</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="F142" s="3"/>
       <c r="G142" s="1"/>
       <c r="H142" s="2" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
     </row>
     <row r="143" spans="1:8">
       <c r="A143" s="2" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="B143" s="1" t="s">
         <v>41</v>
@@ -7308,12 +7312,12 @@
       <c r="F143" s="3"/>
       <c r="G143" s="1"/>
       <c r="H143" s="2" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
     </row>
     <row r="144" spans="1:8">
       <c r="A144" s="2" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="B144" s="1" t="s">
         <v>45</v>
@@ -7330,12 +7334,12 @@
       <c r="F144" s="3"/>
       <c r="G144" s="1"/>
       <c r="H144" s="2" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
     </row>
     <row r="145" spans="1:8">
       <c r="A145" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="B145" s="1" t="s">
         <v>220</v>
@@ -7352,12 +7356,12 @@
       <c r="F145" s="3"/>
       <c r="G145" s="1"/>
       <c r="H145" s="1" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
     </row>
     <row r="146" spans="1:8">
       <c r="A146" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B146" s="1" t="s">
         <v>214</v>
@@ -7374,12 +7378,12 @@
       <c r="F146" s="3"/>
       <c r="G146" s="1"/>
       <c r="H146" s="1" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
     </row>
     <row r="147" spans="1:8">
       <c r="A147" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="B147" s="1" t="s">
         <v>226</v>
@@ -7396,12 +7400,12 @@
       <c r="F147" s="3"/>
       <c r="G147" s="1"/>
       <c r="H147" s="1" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
     </row>
     <row r="148" spans="1:8">
       <c r="A148" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="B148" s="1" t="s">
         <v>216</v>
@@ -7418,12 +7422,12 @@
       <c r="F148" s="3"/>
       <c r="G148" s="1"/>
       <c r="H148" s="1" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
     </row>
     <row r="149" spans="1:8">
       <c r="A149" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="B149" s="1" t="s">
         <v>224</v>
@@ -7440,12 +7444,12 @@
       <c r="F149" s="3"/>
       <c r="G149" s="1"/>
       <c r="H149" s="1" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
     </row>
     <row r="150" spans="1:8">
       <c r="A150" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="B150" s="1" t="s">
         <v>222</v>
@@ -7462,12 +7466,12 @@
       <c r="F150" s="3"/>
       <c r="G150" s="1"/>
       <c r="H150" s="1" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
     </row>
     <row r="151" spans="1:8">
       <c r="A151" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="B151" s="1" t="s">
         <v>218</v>
@@ -7484,15 +7488,15 @@
       <c r="F151" s="3"/>
       <c r="G151" s="1"/>
       <c r="H151" s="1" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
     </row>
     <row r="152" spans="1:8">
       <c r="A152" s="11" t="s">
-        <v>887</v>
+        <v>882</v>
       </c>
       <c r="B152" s="11" t="s">
-        <v>888</v>
+        <v>883</v>
       </c>
       <c r="C152">
         <v>14</v>
@@ -7504,495 +7508,495 @@
       <c r="F152"/>
       <c r="G152"/>
       <c r="H152" t="s">
-        <v>997</v>
+        <v>992</v>
       </c>
     </row>
     <row r="153" spans="1:8">
       <c r="A153" t="s">
-        <v>889</v>
+        <v>884</v>
       </c>
       <c r="B153" t="s">
-        <v>890</v>
+        <v>885</v>
       </c>
       <c r="C153"/>
       <c r="D153"/>
       <c r="E153" t="s">
-        <v>959</v>
+        <v>954</v>
       </c>
       <c r="F153">
         <v>1</v>
       </c>
       <c r="G153"/>
       <c r="H153" t="s">
-        <v>960</v>
+        <v>955</v>
       </c>
     </row>
     <row r="154" spans="1:8">
       <c r="A154" t="s">
-        <v>891</v>
+        <v>886</v>
       </c>
       <c r="B154" t="s">
-        <v>892</v>
+        <v>887</v>
       </c>
       <c r="C154"/>
       <c r="D154"/>
       <c r="E154" t="s">
-        <v>961</v>
+        <v>956</v>
       </c>
       <c r="F154">
         <v>1</v>
       </c>
       <c r="G154"/>
       <c r="H154" t="s">
-        <v>960</v>
+        <v>955</v>
       </c>
     </row>
     <row r="155" spans="1:8">
       <c r="A155" t="s">
-        <v>893</v>
+        <v>888</v>
       </c>
       <c r="B155" t="s">
-        <v>894</v>
+        <v>889</v>
       </c>
       <c r="C155"/>
       <c r="D155"/>
       <c r="E155" t="s">
-        <v>962</v>
+        <v>957</v>
       </c>
       <c r="F155">
         <v>1</v>
       </c>
       <c r="G155"/>
       <c r="H155" t="s">
-        <v>960</v>
+        <v>955</v>
       </c>
     </row>
     <row r="156" spans="1:8">
       <c r="A156" t="s">
-        <v>895</v>
+        <v>890</v>
       </c>
       <c r="B156" t="s">
-        <v>896</v>
+        <v>891</v>
       </c>
       <c r="C156"/>
       <c r="D156"/>
       <c r="E156" t="s">
-        <v>963</v>
+        <v>958</v>
       </c>
       <c r="F156">
         <v>1</v>
       </c>
       <c r="G156"/>
       <c r="H156" t="s">
-        <v>960</v>
+        <v>955</v>
       </c>
     </row>
     <row r="157" spans="1:8">
       <c r="A157" t="s">
-        <v>897</v>
+        <v>892</v>
       </c>
       <c r="B157" t="s">
-        <v>898</v>
+        <v>893</v>
       </c>
       <c r="C157"/>
       <c r="D157"/>
       <c r="E157" t="s">
-        <v>964</v>
+        <v>959</v>
       </c>
       <c r="F157">
         <v>1</v>
       </c>
       <c r="G157"/>
       <c r="H157" t="s">
-        <v>960</v>
+        <v>955</v>
       </c>
     </row>
     <row r="158" spans="1:8">
       <c r="A158" t="s">
-        <v>899</v>
+        <v>894</v>
       </c>
       <c r="B158" t="s">
-        <v>900</v>
+        <v>895</v>
       </c>
       <c r="C158"/>
       <c r="D158"/>
       <c r="E158" t="s">
-        <v>965</v>
+        <v>960</v>
       </c>
       <c r="F158">
         <v>1</v>
       </c>
       <c r="G158"/>
       <c r="H158" t="s">
-        <v>960</v>
+        <v>955</v>
       </c>
     </row>
     <row r="159" spans="1:8">
       <c r="A159" t="s">
-        <v>901</v>
+        <v>896</v>
       </c>
       <c r="B159" t="s">
-        <v>902</v>
+        <v>897</v>
       </c>
       <c r="C159"/>
       <c r="D159"/>
       <c r="E159" t="s">
-        <v>966</v>
+        <v>961</v>
       </c>
       <c r="F159">
         <v>1</v>
       </c>
       <c r="G159"/>
       <c r="H159" t="s">
-        <v>960</v>
+        <v>955</v>
       </c>
     </row>
     <row r="160" spans="1:8">
       <c r="A160" t="s">
-        <v>903</v>
+        <v>898</v>
       </c>
       <c r="B160" t="s">
-        <v>904</v>
+        <v>899</v>
       </c>
       <c r="C160"/>
       <c r="D160"/>
       <c r="E160" t="s">
-        <v>967</v>
+        <v>962</v>
       </c>
       <c r="F160">
         <v>1</v>
       </c>
       <c r="G160"/>
       <c r="H160" t="s">
-        <v>960</v>
+        <v>955</v>
       </c>
     </row>
     <row r="161" spans="1:8">
       <c r="A161" t="s">
-        <v>905</v>
+        <v>900</v>
       </c>
       <c r="B161" t="s">
-        <v>906</v>
+        <v>901</v>
       </c>
       <c r="C161"/>
       <c r="D161"/>
       <c r="E161" t="s">
-        <v>968</v>
+        <v>963</v>
       </c>
       <c r="F161">
         <v>1</v>
       </c>
       <c r="G161"/>
       <c r="H161" t="s">
-        <v>960</v>
+        <v>955</v>
       </c>
     </row>
     <row r="162" spans="1:8">
       <c r="A162" t="s">
-        <v>907</v>
+        <v>902</v>
       </c>
       <c r="B162" t="s">
-        <v>908</v>
+        <v>903</v>
       </c>
       <c r="C162"/>
       <c r="D162"/>
       <c r="E162" t="s">
-        <v>969</v>
+        <v>964</v>
       </c>
       <c r="F162">
         <v>1</v>
       </c>
       <c r="G162"/>
       <c r="H162" t="s">
-        <v>960</v>
+        <v>955</v>
       </c>
     </row>
     <row r="163" spans="1:8">
       <c r="A163" t="s">
-        <v>909</v>
+        <v>904</v>
       </c>
       <c r="B163" t="s">
-        <v>910</v>
+        <v>905</v>
       </c>
       <c r="C163"/>
       <c r="D163"/>
       <c r="E163" t="s">
-        <v>970</v>
+        <v>965</v>
       </c>
       <c r="F163">
         <v>1</v>
       </c>
       <c r="G163"/>
       <c r="H163" t="s">
-        <v>960</v>
+        <v>955</v>
       </c>
     </row>
     <row r="164" spans="1:8">
       <c r="A164" t="s">
-        <v>911</v>
+        <v>906</v>
       </c>
       <c r="B164" s="12" t="s">
-        <v>1053</v>
+        <v>1047</v>
       </c>
       <c r="C164"/>
       <c r="D164"/>
       <c r="E164" t="s">
-        <v>971</v>
+        <v>966</v>
       </c>
       <c r="F164">
         <v>1</v>
       </c>
       <c r="G164"/>
       <c r="H164" t="s">
-        <v>960</v>
+        <v>955</v>
       </c>
     </row>
     <row r="165" spans="1:8">
       <c r="A165" t="s">
-        <v>912</v>
+        <v>907</v>
       </c>
       <c r="B165" t="s">
-        <v>913</v>
+        <v>908</v>
       </c>
       <c r="C165"/>
       <c r="D165"/>
       <c r="E165" t="s">
-        <v>972</v>
+        <v>967</v>
       </c>
       <c r="F165">
         <v>1</v>
       </c>
       <c r="G165"/>
       <c r="H165" t="s">
-        <v>973</v>
+        <v>968</v>
       </c>
     </row>
     <row r="166" spans="1:8">
       <c r="A166" t="s">
-        <v>914</v>
+        <v>909</v>
       </c>
       <c r="B166" t="s">
-        <v>915</v>
+        <v>910</v>
       </c>
       <c r="C166"/>
       <c r="D166"/>
       <c r="E166" t="s">
-        <v>974</v>
+        <v>969</v>
       </c>
       <c r="F166">
         <v>1</v>
       </c>
       <c r="G166"/>
       <c r="H166" t="s">
-        <v>960</v>
+        <v>955</v>
       </c>
     </row>
     <row r="167" spans="1:8">
       <c r="A167" t="s">
-        <v>916</v>
+        <v>911</v>
       </c>
       <c r="B167" t="s">
-        <v>917</v>
+        <v>912</v>
       </c>
       <c r="C167"/>
       <c r="D167"/>
       <c r="E167" t="s">
-        <v>975</v>
+        <v>970</v>
       </c>
       <c r="F167">
         <v>1</v>
       </c>
       <c r="G167"/>
       <c r="H167" t="s">
-        <v>960</v>
+        <v>955</v>
       </c>
     </row>
     <row r="168" spans="1:8">
       <c r="A168" t="s">
-        <v>918</v>
+        <v>913</v>
       </c>
       <c r="B168" t="s">
-        <v>919</v>
+        <v>914</v>
       </c>
       <c r="C168"/>
       <c r="D168"/>
       <c r="E168" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="F168">
         <v>1</v>
       </c>
       <c r="G168"/>
       <c r="H168" t="s">
-        <v>960</v>
+        <v>955</v>
       </c>
     </row>
     <row r="169" spans="1:8">
       <c r="A169" t="s">
-        <v>920</v>
+        <v>915</v>
       </c>
       <c r="B169" t="s">
-        <v>921</v>
+        <v>916</v>
       </c>
       <c r="C169"/>
       <c r="D169"/>
       <c r="E169" t="s">
-        <v>977</v>
+        <v>972</v>
       </c>
       <c r="F169">
         <v>1</v>
       </c>
       <c r="G169"/>
       <c r="H169" t="s">
-        <v>960</v>
+        <v>955</v>
       </c>
     </row>
     <row r="170" spans="1:8">
       <c r="A170" t="s">
-        <v>922</v>
+        <v>917</v>
       </c>
       <c r="B170" t="s">
-        <v>923</v>
+        <v>918</v>
       </c>
       <c r="C170"/>
       <c r="D170"/>
       <c r="E170" t="s">
-        <v>978</v>
+        <v>973</v>
       </c>
       <c r="F170">
         <v>1</v>
       </c>
       <c r="G170"/>
       <c r="H170" t="s">
-        <v>960</v>
+        <v>955</v>
       </c>
     </row>
     <row r="171" spans="1:8">
       <c r="A171" t="s">
-        <v>924</v>
+        <v>919</v>
       </c>
       <c r="B171" t="s">
-        <v>925</v>
+        <v>920</v>
       </c>
       <c r="C171"/>
       <c r="D171"/>
       <c r="E171" t="s">
-        <v>979</v>
+        <v>974</v>
       </c>
       <c r="F171">
         <v>1</v>
       </c>
       <c r="G171"/>
       <c r="H171" t="s">
-        <v>960</v>
+        <v>955</v>
       </c>
     </row>
     <row r="172" spans="1:8">
       <c r="A172" t="s">
-        <v>926</v>
+        <v>921</v>
       </c>
       <c r="B172" t="s">
-        <v>927</v>
+        <v>922</v>
       </c>
       <c r="C172"/>
       <c r="D172"/>
       <c r="E172" t="s">
-        <v>980</v>
+        <v>975</v>
       </c>
       <c r="F172">
         <v>1</v>
       </c>
       <c r="G172"/>
       <c r="H172" t="s">
-        <v>960</v>
+        <v>955</v>
       </c>
     </row>
     <row r="173" spans="1:8">
       <c r="A173" t="s">
-        <v>928</v>
+        <v>923</v>
       </c>
       <c r="B173" t="s">
-        <v>929</v>
+        <v>924</v>
       </c>
       <c r="C173"/>
       <c r="D173"/>
       <c r="E173" t="s">
-        <v>981</v>
+        <v>976</v>
       </c>
       <c r="F173">
         <v>1</v>
       </c>
       <c r="G173"/>
       <c r="H173" t="s">
-        <v>960</v>
+        <v>955</v>
       </c>
     </row>
     <row r="174" spans="1:8">
       <c r="A174" t="s">
-        <v>930</v>
+        <v>925</v>
       </c>
       <c r="B174" t="s">
-        <v>931</v>
+        <v>926</v>
       </c>
       <c r="C174"/>
       <c r="D174"/>
       <c r="E174" t="s">
-        <v>982</v>
+        <v>977</v>
       </c>
       <c r="F174">
         <v>1</v>
       </c>
       <c r="G174"/>
       <c r="H174" t="s">
-        <v>960</v>
+        <v>955</v>
       </c>
     </row>
     <row r="175" spans="1:8">
       <c r="A175" t="s">
-        <v>932</v>
+        <v>927</v>
       </c>
       <c r="B175" t="s">
-        <v>933</v>
+        <v>928</v>
       </c>
       <c r="C175"/>
       <c r="D175"/>
       <c r="E175" t="s">
-        <v>983</v>
+        <v>978</v>
       </c>
       <c r="F175">
         <v>1</v>
       </c>
       <c r="G175"/>
       <c r="H175" t="s">
-        <v>960</v>
+        <v>955</v>
       </c>
     </row>
     <row r="176" spans="1:8">
       <c r="A176" t="s">
-        <v>934</v>
+        <v>929</v>
       </c>
       <c r="B176" t="s">
-        <v>935</v>
+        <v>930</v>
       </c>
       <c r="C176"/>
       <c r="D176"/>
       <c r="E176" t="s">
-        <v>984</v>
+        <v>979</v>
       </c>
       <c r="F176">
         <v>1</v>
       </c>
       <c r="G176"/>
       <c r="H176" t="s">
-        <v>960</v>
+        <v>955</v>
       </c>
     </row>
     <row r="177" spans="1:8">
       <c r="A177" t="s">
-        <v>936</v>
+        <v>931</v>
       </c>
       <c r="B177" t="s">
-        <v>937</v>
+        <v>932</v>
       </c>
       <c r="C177">
         <v>14</v>
@@ -8001,100 +8005,100 @@
         <v>0</v>
       </c>
       <c r="E177" t="s">
-        <v>985</v>
+        <v>980</v>
       </c>
       <c r="F177"/>
       <c r="G177"/>
       <c r="H177" t="s">
-        <v>960</v>
+        <v>955</v>
       </c>
     </row>
     <row r="178" spans="1:8">
       <c r="A178" t="s">
-        <v>938</v>
+        <v>933</v>
       </c>
       <c r="B178" t="s">
-        <v>939</v>
+        <v>934</v>
       </c>
       <c r="C178"/>
       <c r="D178"/>
       <c r="E178" t="s">
-        <v>986</v>
+        <v>981</v>
       </c>
       <c r="F178">
         <v>1</v>
       </c>
       <c r="G178"/>
       <c r="H178" t="s">
-        <v>960</v>
+        <v>955</v>
       </c>
     </row>
     <row r="179" spans="1:8">
       <c r="A179" t="s">
-        <v>940</v>
+        <v>935</v>
       </c>
       <c r="B179" t="s">
-        <v>941</v>
+        <v>936</v>
       </c>
       <c r="C179"/>
       <c r="D179"/>
       <c r="E179" t="s">
-        <v>987</v>
+        <v>982</v>
       </c>
       <c r="F179">
         <v>1</v>
       </c>
       <c r="G179"/>
       <c r="H179" t="s">
-        <v>960</v>
+        <v>955</v>
       </c>
     </row>
     <row r="180" spans="1:8">
       <c r="A180" s="12" t="s">
-        <v>942</v>
+        <v>937</v>
       </c>
       <c r="B180" s="12" t="s">
-        <v>1054</v>
+        <v>1048</v>
       </c>
       <c r="C180"/>
       <c r="D180"/>
       <c r="E180" t="s">
-        <v>988</v>
+        <v>983</v>
       </c>
       <c r="F180">
         <v>1</v>
       </c>
       <c r="G180"/>
       <c r="H180" t="s">
-        <v>960</v>
+        <v>955</v>
       </c>
     </row>
     <row r="181" spans="1:8">
       <c r="A181" t="s">
-        <v>943</v>
+        <v>938</v>
       </c>
       <c r="B181" t="s">
-        <v>944</v>
+        <v>939</v>
       </c>
       <c r="C181"/>
       <c r="D181"/>
       <c r="E181" t="s">
-        <v>989</v>
+        <v>984</v>
       </c>
       <c r="F181">
         <v>1</v>
       </c>
       <c r="G181"/>
       <c r="H181" t="s">
-        <v>960</v>
+        <v>955</v>
       </c>
     </row>
     <row r="182" spans="1:8">
       <c r="A182" t="s">
-        <v>945</v>
+        <v>940</v>
       </c>
       <c r="B182" t="s">
-        <v>946</v>
+        <v>941</v>
       </c>
       <c r="C182">
         <v>14</v>
@@ -8103,157 +8107,157 @@
         <v>0</v>
       </c>
       <c r="E182" t="s">
-        <v>990</v>
+        <v>985</v>
       </c>
       <c r="F182"/>
       <c r="G182"/>
       <c r="H182" t="s">
-        <v>960</v>
+        <v>955</v>
       </c>
     </row>
     <row r="183" spans="1:8">
       <c r="A183" t="s">
-        <v>947</v>
+        <v>942</v>
       </c>
       <c r="B183" t="s">
-        <v>948</v>
+        <v>943</v>
       </c>
       <c r="C183"/>
       <c r="D183"/>
       <c r="E183" t="s">
-        <v>991</v>
+        <v>986</v>
       </c>
       <c r="F183">
         <v>1</v>
       </c>
       <c r="G183"/>
       <c r="H183" t="s">
-        <v>960</v>
+        <v>955</v>
       </c>
     </row>
     <row r="184" spans="1:8">
       <c r="A184" t="s">
-        <v>949</v>
+        <v>944</v>
       </c>
       <c r="B184" t="s">
-        <v>950</v>
+        <v>945</v>
       </c>
       <c r="C184"/>
       <c r="D184"/>
       <c r="E184" t="s">
-        <v>992</v>
+        <v>987</v>
       </c>
       <c r="F184">
         <v>1</v>
       </c>
       <c r="G184"/>
       <c r="H184" t="s">
-        <v>960</v>
+        <v>955</v>
       </c>
     </row>
     <row r="185" spans="1:8">
       <c r="A185" t="s">
-        <v>951</v>
+        <v>946</v>
       </c>
       <c r="B185" t="s">
-        <v>952</v>
+        <v>947</v>
       </c>
       <c r="C185"/>
       <c r="D185"/>
       <c r="E185" t="s">
-        <v>993</v>
+        <v>988</v>
       </c>
       <c r="F185">
         <v>1</v>
       </c>
       <c r="G185"/>
       <c r="H185" t="s">
-        <v>960</v>
+        <v>955</v>
       </c>
     </row>
     <row r="186" spans="1:8">
       <c r="A186" t="s">
-        <v>953</v>
+        <v>948</v>
       </c>
       <c r="B186" t="s">
-        <v>954</v>
+        <v>949</v>
       </c>
       <c r="C186"/>
       <c r="D186"/>
       <c r="E186" t="s">
-        <v>994</v>
+        <v>989</v>
       </c>
       <c r="F186">
         <v>1</v>
       </c>
       <c r="G186"/>
       <c r="H186" t="s">
-        <v>960</v>
+        <v>955</v>
       </c>
     </row>
     <row r="187" spans="1:8">
       <c r="A187" t="s">
-        <v>955</v>
+        <v>950</v>
       </c>
       <c r="B187" t="s">
-        <v>956</v>
+        <v>951</v>
       </c>
       <c r="C187"/>
       <c r="D187"/>
       <c r="E187" t="s">
-        <v>995</v>
+        <v>990</v>
       </c>
       <c r="F187">
         <v>1</v>
       </c>
       <c r="G187"/>
       <c r="H187" t="s">
-        <v>960</v>
+        <v>955</v>
       </c>
     </row>
     <row r="188" spans="1:8">
       <c r="A188" t="s">
-        <v>957</v>
+        <v>952</v>
       </c>
       <c r="B188" t="s">
-        <v>958</v>
+        <v>953</v>
       </c>
       <c r="C188"/>
       <c r="D188"/>
       <c r="E188" t="s">
-        <v>996</v>
+        <v>991</v>
       </c>
       <c r="F188">
         <v>1</v>
       </c>
       <c r="G188"/>
       <c r="H188" t="s">
-        <v>960</v>
+        <v>955</v>
       </c>
     </row>
     <row r="189" spans="1:8">
       <c r="A189" t="s">
-        <v>1055</v>
+        <v>1049</v>
       </c>
       <c r="B189" t="s">
-        <v>1056</v>
+        <v>1050</v>
       </c>
       <c r="C189"/>
       <c r="D189"/>
       <c r="E189" t="s">
-        <v>1057</v>
+        <v>1051</v>
       </c>
       <c r="F189">
         <v>1</v>
       </c>
       <c r="G189"/>
       <c r="H189" t="s">
-        <v>960</v>
+        <v>955</v>
       </c>
     </row>
     <row r="190" spans="1:8">
       <c r="A190" s="2" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="B190" s="1" t="s">
         <v>236</v>
@@ -8270,15 +8274,15 @@
       <c r="F190" s="3"/>
       <c r="G190" s="1"/>
       <c r="H190" t="s">
-        <v>756</v>
+        <v>752</v>
       </c>
     </row>
     <row r="191" spans="1:8">
       <c r="A191" s="2" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="C191" s="3">
         <v>6</v>
@@ -8287,17 +8291,17 @@
         <v>0.54166666666666663</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="F191" s="3"/>
       <c r="G191" s="1"/>
       <c r="H191" s="1" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
     </row>
     <row r="192" spans="1:8">
       <c r="A192" s="2" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="B192" s="1" t="s">
         <v>195</v>
@@ -8309,80 +8313,80 @@
         <v>0</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="F192" s="3"/>
       <c r="G192" s="1"/>
       <c r="H192" s="1" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
     </row>
     <row r="193" spans="1:8">
       <c r="A193" t="s">
-        <v>679</v>
+        <v>675</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>766</v>
+        <v>762</v>
       </c>
       <c r="F193" s="2">
         <v>1</v>
       </c>
       <c r="G193" s="2" t="s">
-        <v>767</v>
+        <v>763</v>
       </c>
       <c r="H193" s="2" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
     </row>
     <row r="194" spans="1:8">
       <c r="A194" t="s">
-        <v>680</v>
+        <v>676</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
       <c r="F194" s="2">
         <v>1</v>
       </c>
       <c r="G194" s="2" t="s">
-        <v>771</v>
+        <v>767</v>
       </c>
       <c r="H194" s="2" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
     </row>
     <row r="195" spans="1:8">
       <c r="A195" t="s">
-        <v>680</v>
+        <v>676</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>769</v>
+        <v>765</v>
       </c>
       <c r="F195" s="2">
         <v>1</v>
       </c>
       <c r="G195" s="2" t="s">
-        <v>770</v>
+        <v>766</v>
       </c>
       <c r="H195" s="2" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
     </row>
     <row r="196" spans="1:8">
       <c r="A196" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="C196" s="2">
         <v>8</v>
@@ -8391,37 +8395,37 @@
         <v>0</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="F196" s="3"/>
       <c r="H196" s="2" t="s">
-        <v>1050</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="197" spans="1:8">
       <c r="A197" s="2" t="s">
-        <v>812</v>
+        <v>808</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>813</v>
+        <v>809</v>
       </c>
       <c r="D197" s="6"/>
       <c r="E197" s="1" t="s">
-        <v>814</v>
+        <v>810</v>
       </c>
       <c r="F197" s="3">
         <v>1</v>
       </c>
       <c r="H197" s="7" t="s">
-        <v>815</v>
+        <v>811</v>
       </c>
     </row>
     <row r="198" spans="1:8">
       <c r="A198" s="2" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="C198" s="3">
         <v>13</v>
@@ -8430,20 +8434,20 @@
         <v>0</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="F198" s="3"/>
       <c r="G198" s="1"/>
       <c r="H198" s="1" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
     </row>
     <row r="199" spans="1:8">
       <c r="A199" t="s">
-        <v>682</v>
+        <v>678</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="C199" s="2">
         <v>10</v>
@@ -8452,18 +8456,18 @@
         <v>0</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="H199" s="2" t="s">
-        <v>1049</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="200" spans="1:8">
       <c r="A200" t="s">
-        <v>683</v>
+        <v>679</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>686</v>
+        <v>682</v>
       </c>
       <c r="C200" s="2">
         <v>10</v>
@@ -8472,38 +8476,38 @@
         <v>0</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>652</v>
+        <v>648</v>
       </c>
       <c r="H200" s="2" t="s">
-        <v>1048</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="201" spans="1:8">
       <c r="A201" t="s">
-        <v>1059</v>
+        <v>1052</v>
       </c>
       <c r="B201" t="s">
-        <v>1031</v>
+        <v>1025</v>
       </c>
       <c r="C201"/>
       <c r="D201" s="11"/>
       <c r="E201" t="s">
-        <v>1032</v>
+        <v>1026</v>
       </c>
       <c r="F201">
         <v>1</v>
       </c>
       <c r="G201"/>
       <c r="H201" s="11" t="s">
-        <v>1033</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="202" spans="1:8">
       <c r="A202" t="s">
-        <v>1060</v>
+        <v>1053</v>
       </c>
       <c r="B202" t="s">
-        <v>1034</v>
+        <v>1028</v>
       </c>
       <c r="C202">
         <v>10</v>
@@ -8512,40 +8516,40 @@
         <v>0</v>
       </c>
       <c r="E202" t="s">
-        <v>1035</v>
+        <v>1029</v>
       </c>
       <c r="F202"/>
       <c r="G202"/>
       <c r="H202" s="11" t="s">
-        <v>1036</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="203" spans="1:8">
       <c r="A203" t="s">
-        <v>1061</v>
+        <v>1054</v>
       </c>
       <c r="B203" t="s">
-        <v>1037</v>
+        <v>1031</v>
       </c>
       <c r="C203"/>
       <c r="D203" s="11"/>
       <c r="E203" t="s">
-        <v>1038</v>
+        <v>1032</v>
       </c>
       <c r="F203">
         <v>1</v>
       </c>
       <c r="G203"/>
       <c r="H203" s="11" t="s">
-        <v>1039</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="204" spans="1:8">
       <c r="A204" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="C204" s="3">
         <v>7</v>
@@ -8559,12 +8563,12 @@
       <c r="F204" s="3"/>
       <c r="G204" s="1"/>
       <c r="H204" s="1" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
     </row>
     <row r="205" spans="1:8">
       <c r="A205" s="2" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="B205" s="1" t="s">
         <v>115</v>
@@ -8581,12 +8585,12 @@
       <c r="F205" s="3"/>
       <c r="G205" s="1"/>
       <c r="H205" s="1" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
     </row>
     <row r="206" spans="1:8">
       <c r="A206" s="2" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="B206" s="1" t="s">
         <v>119</v>
@@ -8601,12 +8605,12 @@
       </c>
       <c r="G206" s="1"/>
       <c r="H206" s="1" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
     </row>
     <row r="207" spans="1:8">
       <c r="A207" s="2" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="B207" s="1" t="s">
         <v>117</v>
@@ -8623,33 +8627,33 @@
       <c r="F207" s="3"/>
       <c r="G207" s="1"/>
       <c r="H207" s="1" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
     </row>
     <row r="208" spans="1:8">
       <c r="A208" s="2" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="D208" s="6"/>
       <c r="E208" s="2" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="F208" s="2">
         <v>1</v>
       </c>
       <c r="H208" t="s">
-        <v>757</v>
+        <v>753</v>
       </c>
     </row>
     <row r="209" spans="1:8">
       <c r="A209" t="s">
-        <v>998</v>
+        <v>993</v>
       </c>
       <c r="B209" t="s">
-        <v>999</v>
+        <v>994</v>
       </c>
       <c r="C209">
         <v>15</v>
@@ -8658,20 +8662,20 @@
         <v>0</v>
       </c>
       <c r="E209" t="s">
-        <v>1000</v>
+        <v>995</v>
       </c>
       <c r="F209"/>
       <c r="G209"/>
       <c r="H209" s="11" t="s">
-        <v>1001</v>
+        <v>996</v>
       </c>
     </row>
     <row r="210" spans="1:8">
       <c r="A210" t="s">
-        <v>1002</v>
+        <v>997</v>
       </c>
       <c r="B210" t="s">
-        <v>1003</v>
+        <v>998</v>
       </c>
       <c r="C210">
         <v>15</v>
@@ -8680,20 +8684,20 @@
         <v>0</v>
       </c>
       <c r="E210" t="s">
-        <v>1004</v>
+        <v>999</v>
       </c>
       <c r="F210"/>
       <c r="G210"/>
       <c r="H210" s="11" t="s">
-        <v>1005</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="211" spans="1:8">
       <c r="A211" t="s">
-        <v>1006</v>
+        <v>1001</v>
       </c>
       <c r="B211" t="s">
-        <v>1007</v>
+        <v>1002</v>
       </c>
       <c r="C211">
         <v>15</v>
@@ -8702,20 +8706,20 @@
         <v>0</v>
       </c>
       <c r="E211" t="s">
-        <v>1008</v>
+        <v>1003</v>
       </c>
       <c r="F211"/>
       <c r="G211"/>
       <c r="H211" s="11" t="s">
-        <v>1009</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="212" spans="1:8">
       <c r="A212" t="s">
-        <v>1010</v>
+        <v>1005</v>
       </c>
       <c r="B212" t="s">
-        <v>1011</v>
+        <v>1006</v>
       </c>
       <c r="C212">
         <v>20</v>
@@ -8724,20 +8728,20 @@
         <v>0</v>
       </c>
       <c r="E212" t="s">
-        <v>1012</v>
+        <v>1007</v>
       </c>
       <c r="F212"/>
       <c r="G212"/>
       <c r="H212" s="11" t="s">
-        <v>1013</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="213" spans="1:8">
       <c r="A213" t="s">
-        <v>1014</v>
+        <v>1009</v>
       </c>
       <c r="B213" t="s">
-        <v>1015</v>
+        <v>1010</v>
       </c>
       <c r="C213">
         <v>15</v>
@@ -8746,61 +8750,61 @@
         <v>0</v>
       </c>
       <c r="E213" t="s">
-        <v>1016</v>
+        <v>1011</v>
       </c>
       <c r="F213"/>
       <c r="G213"/>
       <c r="H213" s="11" t="s">
-        <v>1017</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="214" spans="1:8">
       <c r="A214" s="2" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C214" s="1"/>
       <c r="D214" s="1"/>
       <c r="E214" s="1" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F214" s="3">
         <v>1</v>
       </c>
       <c r="G214" s="1" t="s">
-        <v>257</v>
+        <v>1141</v>
       </c>
       <c r="H214" s="2" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
     </row>
     <row r="215" spans="1:8">
       <c r="A215" s="2" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C215" s="1"/>
       <c r="D215" s="1"/>
       <c r="E215" s="1" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="F215" s="3">
         <v>1</v>
       </c>
       <c r="G215" s="1" t="s">
-        <v>260</v>
+        <v>1142</v>
       </c>
       <c r="H215" s="2" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
     </row>
     <row r="216" spans="1:8">
       <c r="A216" s="2" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="B216" s="1" t="s">
         <v>131</v>
@@ -8817,12 +8821,12 @@
       <c r="F216" s="3"/>
       <c r="G216" s="1"/>
       <c r="H216" s="1" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
     </row>
     <row r="217" spans="1:8">
       <c r="A217" s="2" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="B217" s="1" t="s">
         <v>228</v>
@@ -8839,15 +8843,15 @@
       <c r="F217" s="3"/>
       <c r="G217" s="1"/>
       <c r="H217" s="1" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
     </row>
     <row r="218" spans="1:8">
       <c r="A218" s="2" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="B218" s="1" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="C218" s="3">
         <v>6</v>
@@ -8856,17 +8860,17 @@
         <v>0</v>
       </c>
       <c r="E218" s="1" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="F218" s="3"/>
       <c r="G218" s="1"/>
       <c r="H218" s="1" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
     </row>
     <row r="219" spans="1:8">
       <c r="A219" s="2" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="B219" s="1" t="s">
         <v>74</v>
@@ -8878,20 +8882,20 @@
         <v>0</v>
       </c>
       <c r="E219" s="1" t="s">
-        <v>1018</v>
+        <v>1013</v>
       </c>
       <c r="F219" s="3"/>
       <c r="G219" s="1"/>
       <c r="H219" s="2" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
     </row>
     <row r="220" spans="1:8">
       <c r="A220" s="2" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="B220" s="1" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="C220" s="1">
         <v>7</v>
@@ -8900,77 +8904,77 @@
         <v>0.91666666666666663</v>
       </c>
       <c r="E220" s="1" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="F220" s="1"/>
       <c r="G220" s="1"/>
       <c r="H220" s="1" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
     </row>
     <row r="221" spans="1:8">
       <c r="A221" s="2" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="B221" s="1" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="C221" s="1"/>
       <c r="D221" s="5"/>
       <c r="E221" s="1" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="F221" s="1">
         <v>1</v>
       </c>
       <c r="G221" s="1"/>
       <c r="H221" s="1" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
     </row>
     <row r="222" spans="1:8">
       <c r="A222" s="2" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="B222" s="1" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="C222" s="1"/>
       <c r="D222" s="1"/>
       <c r="E222" s="1" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="F222" s="1">
         <v>1</v>
       </c>
       <c r="G222" s="1"/>
       <c r="H222" s="1" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
     </row>
     <row r="223" spans="1:8">
       <c r="A223" s="2" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
       <c r="B223" s="1" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="C223" s="1"/>
       <c r="D223" s="1"/>
       <c r="E223" s="1" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="F223" s="1">
         <v>1</v>
       </c>
       <c r="G223" s="1"/>
       <c r="H223" s="1" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
     </row>
     <row r="224" spans="1:8">
       <c r="A224" s="2" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="B224" s="1" t="s">
         <v>242</v>
@@ -8982,17 +8986,17 @@
         <v>0</v>
       </c>
       <c r="E224" s="1" t="s">
-        <v>825</v>
+        <v>821</v>
       </c>
       <c r="F224" s="3"/>
       <c r="G224" s="1"/>
       <c r="H224" s="1" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
     </row>
     <row r="225" spans="1:8">
       <c r="A225" s="2" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="B225" s="1" t="s">
         <v>240</v>
@@ -9009,15 +9013,15 @@
       <c r="F225" s="3"/>
       <c r="G225" s="1"/>
       <c r="H225" s="2" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
     </row>
     <row r="226" spans="1:8">
       <c r="A226" s="2" t="s">
-        <v>703</v>
+        <v>699</v>
       </c>
       <c r="B226" s="1" t="s">
-        <v>700</v>
+        <v>696</v>
       </c>
       <c r="C226" s="2">
         <v>7</v>
@@ -9026,16 +9030,16 @@
         <v>0.95833333333333337</v>
       </c>
       <c r="E226" s="1" t="s">
-        <v>701</v>
+        <v>697</v>
       </c>
       <c r="F226" s="3"/>
       <c r="H226" s="7" t="s">
-        <v>702</v>
+        <v>698</v>
       </c>
     </row>
     <row r="227" spans="1:8">
       <c r="A227" s="2" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="B227" s="1" t="s">
         <v>57</v>
@@ -9052,12 +9056,12 @@
       <c r="F227" s="3"/>
       <c r="G227" s="1"/>
       <c r="H227" s="2" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
     </row>
     <row r="228" spans="1:8">
       <c r="A228" s="2" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="B228" s="1" t="s">
         <v>61</v>
@@ -9069,34 +9073,34 @@
         <v>0</v>
       </c>
       <c r="E228" s="1" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="F228" s="3"/>
       <c r="G228" s="1"/>
       <c r="H228" s="2" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
     </row>
     <row r="229" spans="1:8">
       <c r="A229" s="2" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="B229" s="1" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="E229" s="1" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="F229" s="3">
         <v>1</v>
       </c>
       <c r="H229" s="1" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
     </row>
     <row r="230" spans="1:8">
       <c r="A230" s="2" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="B230" s="1" t="s">
         <v>59</v>
@@ -9113,12 +9117,12 @@
       <c r="F230" s="3"/>
       <c r="G230" s="1"/>
       <c r="H230" s="2" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
     </row>
     <row r="231" spans="1:8">
       <c r="A231" s="2" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="B231" s="1" t="s">
         <v>62</v>
@@ -9135,12 +9139,12 @@
       <c r="F231" s="3"/>
       <c r="G231" s="1"/>
       <c r="H231" s="2" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
     </row>
     <row r="232" spans="1:8">
       <c r="A232" s="2" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="B232" s="1" t="s">
         <v>121</v>
@@ -9152,17 +9156,17 @@
         <v>0</v>
       </c>
       <c r="E232" s="1" t="s">
-        <v>1019</v>
+        <v>1014</v>
       </c>
       <c r="F232" s="3"/>
       <c r="G232" s="1"/>
       <c r="H232" s="1" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
     </row>
     <row r="233" spans="1:8">
       <c r="A233" s="2" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="B233" s="1" t="s">
         <v>123</v>
@@ -9179,12 +9183,12 @@
       <c r="F233" s="3"/>
       <c r="G233" s="1"/>
       <c r="H233" s="1" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
     </row>
     <row r="234" spans="1:8">
       <c r="A234" s="2" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="B234" s="1" t="s">
         <v>122</v>
@@ -9196,20 +9200,20 @@
         <v>0.91666666666666663</v>
       </c>
       <c r="E234" s="1" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="F234" s="3"/>
       <c r="G234" s="1"/>
       <c r="H234" s="1" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
     </row>
     <row r="235" spans="1:8">
       <c r="A235" t="s">
-        <v>1020</v>
+        <v>1015</v>
       </c>
       <c r="B235" t="s">
-        <v>1021</v>
+        <v>1016</v>
       </c>
       <c r="C235">
         <v>6</v>
@@ -9218,20 +9222,20 @@
         <v>0</v>
       </c>
       <c r="E235" t="s">
-        <v>1022</v>
+        <v>1017</v>
       </c>
       <c r="F235"/>
       <c r="G235"/>
       <c r="H235" s="7" t="s">
-        <v>1023</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="236" spans="1:8">
       <c r="A236" s="11" t="s">
-        <v>1024</v>
+        <v>1019</v>
       </c>
       <c r="B236" t="s">
-        <v>1025</v>
+        <v>1020</v>
       </c>
       <c r="C236" s="3">
         <v>7</v>
@@ -9240,20 +9244,20 @@
         <v>0.91666666666666663</v>
       </c>
       <c r="E236" s="1" t="s">
-        <v>1041</v>
+        <v>1035</v>
       </c>
       <c r="F236"/>
       <c r="G236"/>
       <c r="H236" s="7" t="s">
-        <v>1042</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="237" spans="1:8">
       <c r="A237" s="2" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="B237" s="1" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="C237" s="3">
         <v>7</v>
@@ -9262,17 +9266,17 @@
         <v>0.875</v>
       </c>
       <c r="E237" s="1" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F237" s="3"/>
       <c r="G237" s="1"/>
       <c r="H237" s="1" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
     </row>
     <row r="238" spans="1:8">
       <c r="A238" s="2" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="B238" s="1" t="s">
         <v>9</v>
@@ -9289,35 +9293,35 @@
       <c r="F238" s="3"/>
       <c r="G238" s="1"/>
       <c r="H238" s="2" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
     </row>
     <row r="239" spans="1:8" customFormat="1">
       <c r="A239" s="2" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="B239" s="1" t="s">
-        <v>805</v>
+        <v>801</v>
       </c>
       <c r="C239" s="2"/>
       <c r="D239" s="2"/>
       <c r="E239" s="1" t="s">
-        <v>806</v>
+        <v>802</v>
       </c>
       <c r="F239" s="3">
         <v>1</v>
       </c>
       <c r="G239" s="2"/>
       <c r="H239" s="7" t="s">
-        <v>807</v>
+        <v>803</v>
       </c>
     </row>
     <row r="240" spans="1:8">
       <c r="A240" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="B240" s="1" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="C240" s="3">
         <v>13</v>
@@ -9326,102 +9330,102 @@
         <v>0</v>
       </c>
       <c r="E240" s="1" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="F240" s="3"/>
       <c r="G240" s="1"/>
       <c r="H240" s="1" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
     </row>
     <row r="241" spans="1:8">
       <c r="A241" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="B241" s="1" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="C241" s="3"/>
       <c r="D241" s="5"/>
       <c r="E241" s="1" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="F241" s="3">
         <v>1</v>
       </c>
       <c r="G241" s="1"/>
       <c r="H241" s="1" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
     </row>
     <row r="242" spans="1:8">
       <c r="A242" s="2" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="B242" s="1" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="C242" s="3"/>
       <c r="D242" s="5"/>
       <c r="E242" s="1" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="F242" s="3">
         <v>1</v>
       </c>
       <c r="G242" s="1"/>
       <c r="H242" s="1" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="243" spans="1:8">
       <c r="A243" s="2" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="B243" s="1" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="C243" s="3"/>
       <c r="D243" s="5"/>
       <c r="E243" s="1" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="F243" s="3">
         <v>1</v>
       </c>
       <c r="G243" s="1"/>
       <c r="H243" s="1" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="244" spans="1:8">
       <c r="A244" s="11" t="s">
-        <v>1026</v>
+        <v>1021</v>
       </c>
       <c r="B244" t="s">
-        <v>1027</v>
-      </c>
-      <c r="C244"/>
-      <c r="D244" s="11"/>
+        <v>1022</v>
+      </c>
+      <c r="C244">
+        <v>13</v>
+      </c>
+      <c r="D244" s="11" t="s">
+        <v>1143</v>
+      </c>
       <c r="E244" t="s">
-        <v>1028</v>
-      </c>
-      <c r="F244">
-        <v>1</v>
-      </c>
-      <c r="G244" t="s">
-        <v>1029</v>
-      </c>
+        <v>1023</v>
+      </c>
+      <c r="F244"/>
+      <c r="G244"/>
       <c r="H244" s="7" t="s">
-        <v>1030</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="245" spans="1:8">
       <c r="A245" s="2" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="B245" s="1" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="C245" s="3">
         <v>7</v>
@@ -9430,51 +9434,51 @@
         <v>0.91666666666666663</v>
       </c>
       <c r="E245" s="1" t="s">
-        <v>1040</v>
+        <v>1034</v>
       </c>
       <c r="F245" s="3"/>
       <c r="G245" s="1"/>
       <c r="H245" s="1" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
     </row>
     <row r="246" spans="1:8">
       <c r="A246" s="2" t="s">
+        <v>661</v>
+      </c>
+      <c r="B246" s="1" t="s">
+        <v>663</v>
+      </c>
+      <c r="E246" s="1" t="s">
         <v>665</v>
       </c>
-      <c r="B246" s="1" t="s">
-        <v>667</v>
-      </c>
-      <c r="E246" s="1" t="s">
-        <v>669</v>
-      </c>
       <c r="F246" s="2">
         <v>1</v>
       </c>
       <c r="H246" s="2" t="s">
-        <v>695</v>
+        <v>691</v>
       </c>
     </row>
     <row r="247" spans="1:8">
       <c r="A247" s="2" t="s">
+        <v>660</v>
+      </c>
+      <c r="B247" s="1" t="s">
+        <v>662</v>
+      </c>
+      <c r="E247" s="1" t="s">
         <v>664</v>
       </c>
-      <c r="B247" s="1" t="s">
-        <v>666</v>
-      </c>
-      <c r="E247" s="1" t="s">
-        <v>668</v>
-      </c>
       <c r="F247" s="2">
         <v>1</v>
       </c>
       <c r="H247" s="2" t="s">
-        <v>694</v>
+        <v>690</v>
       </c>
     </row>
     <row r="248" spans="1:8">
       <c r="A248" s="2" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="B248" s="1" t="s">
         <v>213</v>
@@ -9486,17 +9490,17 @@
         <v>0</v>
       </c>
       <c r="E248" s="1" t="s">
-        <v>1044</v>
+        <v>1038</v>
       </c>
       <c r="F248" s="3"/>
       <c r="G248" s="1"/>
       <c r="H248" s="1" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
     </row>
     <row r="249" spans="1:8">
       <c r="A249" s="2" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="B249" s="1" t="s">
         <v>213</v>
@@ -9508,17 +9512,17 @@
         <v>0</v>
       </c>
       <c r="E249" s="1" t="s">
-        <v>1043</v>
+        <v>1037</v>
       </c>
       <c r="F249" s="3"/>
       <c r="G249" s="1"/>
       <c r="H249" s="1" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
     </row>
     <row r="250" spans="1:8">
       <c r="A250" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="B250" s="1" t="s">
         <v>25</v>
@@ -9535,12 +9539,12 @@
       <c r="F250" s="3"/>
       <c r="G250" s="1"/>
       <c r="H250" s="2" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
     </row>
     <row r="251" spans="1:8">
       <c r="A251" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="B251" s="1" t="s">
         <v>27</v>
@@ -9557,12 +9561,12 @@
       <c r="F251" s="3"/>
       <c r="G251" s="1"/>
       <c r="H251" s="2" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
     </row>
     <row r="252" spans="1:8">
       <c r="A252" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="B252" s="1" t="s">
         <v>23</v>
@@ -9579,12 +9583,12 @@
       <c r="F252" s="3"/>
       <c r="G252" s="1"/>
       <c r="H252" s="2" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
     </row>
     <row r="253" spans="1:8">
       <c r="A253" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="B253" s="1" t="s">
         <v>31</v>
@@ -9601,12 +9605,12 @@
       <c r="F253" s="3"/>
       <c r="G253" s="1"/>
       <c r="H253" s="2" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
     </row>
     <row r="254" spans="1:8">
       <c r="A254" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="B254" s="1" t="s">
         <v>33</v>
@@ -9623,12 +9627,12 @@
       <c r="F254" s="3"/>
       <c r="G254" s="1"/>
       <c r="H254" s="2" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
     </row>
     <row r="255" spans="1:8">
       <c r="A255" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="B255" s="1" t="s">
         <v>20</v>
@@ -9645,12 +9649,12 @@
       <c r="F255" s="3"/>
       <c r="G255" s="1"/>
       <c r="H255" s="2" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
     </row>
     <row r="256" spans="1:8">
       <c r="A256" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="B256" s="1" t="s">
         <v>18</v>
@@ -9667,12 +9671,12 @@
       <c r="F256" s="3"/>
       <c r="G256" s="1"/>
       <c r="H256" s="2" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
     </row>
     <row r="257" spans="1:8">
       <c r="A257" s="2" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="B257" s="1" t="s">
         <v>37</v>
@@ -9689,12 +9693,12 @@
       <c r="F257" s="3"/>
       <c r="G257" s="1"/>
       <c r="H257" s="2" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
     </row>
     <row r="258" spans="1:8">
       <c r="A258" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="B258" s="1" t="s">
         <v>29</v>
@@ -9711,12 +9715,12 @@
       <c r="F258" s="3"/>
       <c r="G258" s="1"/>
       <c r="H258" s="2" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
     </row>
     <row r="259" spans="1:8">
       <c r="A259" s="2" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="B259" s="1" t="s">
         <v>39</v>
@@ -9733,12 +9737,12 @@
       <c r="F259" s="3"/>
       <c r="G259" s="1"/>
       <c r="H259" s="2" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
     </row>
     <row r="260" spans="1:8">
       <c r="A260" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="B260" s="1" t="s">
         <v>35</v>
@@ -9755,12 +9759,12 @@
       <c r="F260" s="3"/>
       <c r="G260" s="1"/>
       <c r="H260" s="2" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
     </row>
     <row r="261" spans="1:8">
       <c r="A261" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="B261" s="1" t="s">
         <v>22</v>
@@ -9772,20 +9776,20 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="E261" s="1" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="F261" s="3"/>
       <c r="G261" s="1"/>
       <c r="H261" s="2" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
     </row>
     <row r="262" spans="1:8">
       <c r="A262" s="2" t="s">
-        <v>696</v>
+        <v>692</v>
       </c>
       <c r="B262" s="1" t="s">
-        <v>697</v>
+        <v>693</v>
       </c>
       <c r="C262" s="2">
         <v>6</v>
@@ -9794,19 +9798,19 @@
         <v>0</v>
       </c>
       <c r="E262" s="1" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
       <c r="F262" s="3"/>
       <c r="H262" s="7" t="s">
-        <v>736</v>
+        <v>732</v>
       </c>
     </row>
     <row r="263" spans="1:8">
       <c r="A263" s="2" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="B263" s="1" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="C263" s="3">
         <v>8</v>
@@ -9815,19 +9819,19 @@
         <v>0</v>
       </c>
       <c r="E263" s="1" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F263" s="3"/>
       <c r="H263" s="1" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
     </row>
     <row r="264" spans="1:8">
       <c r="A264" s="2" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="B264" s="1" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="C264" s="3">
         <v>7</v>
@@ -9841,12 +9845,12 @@
       <c r="F264" s="3"/>
       <c r="G264" s="1"/>
       <c r="H264" t="s">
-        <v>758</v>
+        <v>754</v>
       </c>
     </row>
     <row r="265" spans="1:8">
       <c r="A265" s="2" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="B265" s="1" t="s">
         <v>129</v>
@@ -9858,20 +9862,20 @@
         <v>0</v>
       </c>
       <c r="E265" s="1" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="F265" s="3"/>
       <c r="G265" s="1"/>
       <c r="H265" s="1" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
     </row>
     <row r="266" spans="1:8">
       <c r="A266" s="2" t="s">
-        <v>818</v>
+        <v>814</v>
       </c>
       <c r="B266" s="1" t="s">
-        <v>816</v>
+        <v>812</v>
       </c>
       <c r="C266" s="2">
         <v>6</v>
@@ -9880,19 +9884,19 @@
         <v>0</v>
       </c>
       <c r="E266" s="1" t="s">
-        <v>817</v>
+        <v>813</v>
       </c>
       <c r="F266" s="3"/>
       <c r="H266" s="7" t="s">
-        <v>819</v>
+        <v>815</v>
       </c>
     </row>
     <row r="267" spans="1:8">
       <c r="A267" s="2" t="s">
-        <v>759</v>
+        <v>755</v>
       </c>
       <c r="B267" s="1" t="s">
-        <v>751</v>
+        <v>747</v>
       </c>
       <c r="C267" s="2">
         <v>6</v>
@@ -9901,19 +9905,19 @@
         <v>0</v>
       </c>
       <c r="E267" s="10" t="s">
-        <v>763</v>
+        <v>759</v>
       </c>
       <c r="F267" s="3"/>
       <c r="H267" s="2" t="s">
-        <v>762</v>
+        <v>758</v>
       </c>
     </row>
     <row r="268" spans="1:8">
       <c r="A268" s="2" t="s">
-        <v>760</v>
+        <v>756</v>
       </c>
       <c r="B268" s="1" t="s">
-        <v>752</v>
+        <v>748</v>
       </c>
       <c r="C268" s="2">
         <v>6</v>
@@ -9922,19 +9926,19 @@
         <v>0</v>
       </c>
       <c r="E268" s="1" t="s">
-        <v>764</v>
+        <v>760</v>
       </c>
       <c r="F268" s="3"/>
       <c r="H268" s="2" t="s">
-        <v>762</v>
+        <v>758</v>
       </c>
     </row>
     <row r="269" spans="1:8">
       <c r="A269" s="2" t="s">
-        <v>761</v>
+        <v>757</v>
       </c>
       <c r="B269" s="1" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="C269" s="2">
         <v>6</v>
@@ -9943,38 +9947,38 @@
         <v>0</v>
       </c>
       <c r="E269" s="1" t="s">
-        <v>765</v>
+        <v>761</v>
       </c>
       <c r="F269" s="3"/>
       <c r="H269" s="2" t="s">
-        <v>762</v>
+        <v>758</v>
       </c>
     </row>
     <row r="270" spans="1:8">
       <c r="A270" s="2" t="s">
-        <v>684</v>
+        <v>680</v>
       </c>
       <c r="B270" s="1" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="C270" s="3"/>
       <c r="D270" s="6"/>
       <c r="E270" s="1" t="s">
-        <v>650</v>
+        <v>1145</v>
       </c>
       <c r="F270" s="3">
         <v>1</v>
       </c>
       <c r="G270" s="2" t="s">
-        <v>1058</v>
+        <v>1144</v>
       </c>
       <c r="H270" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
     </row>
     <row r="271" spans="1:8">
       <c r="A271" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="B271" s="1" t="s">
         <v>199</v>
@@ -9991,12 +9995,12 @@
       <c r="F271" s="3"/>
       <c r="G271" s="1"/>
       <c r="H271" s="1" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
     </row>
     <row r="272" spans="1:8">
       <c r="A272" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="B272" s="1" t="s">
         <v>197</v>
@@ -10013,12 +10017,12 @@
       <c r="F272" s="3"/>
       <c r="G272" s="1"/>
       <c r="H272" s="1" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
     </row>
     <row r="273" spans="1:8">
       <c r="A273" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="B273" s="1" t="s">
         <v>201</v>
@@ -10035,12 +10039,12 @@
       <c r="F273" s="3"/>
       <c r="G273" s="1"/>
       <c r="H273" s="1" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
     </row>
     <row r="274" spans="1:8">
       <c r="A274" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="B274" s="1" t="s">
         <v>130</v>
@@ -10052,17 +10056,17 @@
         <v>0.97916666666666663</v>
       </c>
       <c r="E274" s="1" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="F274" s="3"/>
       <c r="G274" s="1"/>
       <c r="H274" s="1" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="275" spans="1:8">
       <c r="A275" s="2" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="B275" s="1" t="s">
         <v>64</v>
@@ -10074,17 +10078,17 @@
         <v>0</v>
       </c>
       <c r="E275" s="1" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="F275" s="3"/>
       <c r="G275" s="1"/>
       <c r="H275" s="2" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
     </row>
     <row r="276" spans="1:8">
       <c r="A276" s="2" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="B276" s="1" t="s">
         <v>65</v>
@@ -10101,12 +10105,12 @@
       <c r="F276" s="3"/>
       <c r="G276" s="1"/>
       <c r="H276" s="2" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
     </row>
     <row r="277" spans="1:8">
       <c r="A277" s="2" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="B277" s="1" t="s">
         <v>69</v>
@@ -10123,12 +10127,12 @@
       <c r="F277" s="3"/>
       <c r="G277" s="1"/>
       <c r="H277" s="2" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
     </row>
     <row r="278" spans="1:8">
       <c r="A278" s="2" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="B278" s="1" t="s">
         <v>67</v>
@@ -10145,15 +10149,15 @@
       <c r="F278" s="3"/>
       <c r="G278" s="1"/>
       <c r="H278" s="2" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
     </row>
     <row r="279" spans="1:8">
       <c r="A279" s="2" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="B279" s="1" t="s">
-        <v>1063</v>
+        <v>1056</v>
       </c>
       <c r="C279" s="3">
         <v>6</v>
@@ -10167,12 +10171,12 @@
       <c r="F279" s="3"/>
       <c r="G279" s="1"/>
       <c r="H279" s="2" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
     </row>
     <row r="280" spans="1:8">
       <c r="A280" s="2" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="B280" s="1" t="s">
         <v>72</v>
@@ -10189,12 +10193,12 @@
       <c r="F280" s="3"/>
       <c r="G280" s="1"/>
       <c r="H280" s="2" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
     </row>
     <row r="281" spans="1:8">
       <c r="A281" s="2" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="B281" s="1" t="s">
         <v>92</v>
@@ -10211,12 +10215,12 @@
       <c r="F281" s="3"/>
       <c r="G281" s="1"/>
       <c r="H281" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
     </row>
     <row r="282" spans="1:8">
       <c r="A282" s="2" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="B282" s="1" t="s">
         <v>95</v>
@@ -10233,12 +10237,12 @@
       <c r="F282" s="3"/>
       <c r="G282" s="1"/>
       <c r="H282" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
     </row>
     <row r="283" spans="1:8">
       <c r="A283" s="2" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="B283" s="1" t="s">
         <v>86</v>
@@ -10255,12 +10259,12 @@
       <c r="F283" s="3"/>
       <c r="G283" s="1"/>
       <c r="H283" s="1" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
     </row>
     <row r="284" spans="1:8">
       <c r="A284" s="2" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="B284" s="1" t="s">
         <v>88</v>
@@ -10277,12 +10281,12 @@
       <c r="F284" s="3"/>
       <c r="G284" s="1"/>
       <c r="H284" s="1" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
     </row>
     <row r="285" spans="1:8">
       <c r="A285" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="B285" s="1" t="s">
         <v>102</v>
@@ -10299,12 +10303,12 @@
       <c r="F285" s="3"/>
       <c r="G285" s="1"/>
       <c r="H285" s="1" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
     </row>
     <row r="286" spans="1:8">
       <c r="A286" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="B286" s="1" t="s">
         <v>110</v>
@@ -10321,12 +10325,12 @@
       <c r="F286" s="3"/>
       <c r="G286" s="1"/>
       <c r="H286" s="1" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
     </row>
     <row r="287" spans="1:8">
       <c r="A287" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="B287" s="1" t="s">
         <v>104</v>
@@ -10343,12 +10347,12 @@
       <c r="F287" s="3"/>
       <c r="G287" s="1"/>
       <c r="H287" s="1" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
     </row>
     <row r="288" spans="1:8">
       <c r="A288" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="B288" s="1" t="s">
         <v>91</v>
@@ -10360,17 +10364,17 @@
         <v>0</v>
       </c>
       <c r="E288" s="1" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="F288" s="3"/>
       <c r="G288" s="1"/>
       <c r="H288" s="8" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
     </row>
     <row r="289" spans="1:8">
       <c r="A289" s="2" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="B289" s="1" t="s">
         <v>108</v>
@@ -10387,15 +10391,15 @@
       <c r="F289" s="3"/>
       <c r="G289" s="1"/>
       <c r="H289" s="1" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
     </row>
     <row r="290" spans="1:8">
       <c r="A290" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="B290" s="1" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="C290" s="3">
         <v>13</v>
@@ -10404,17 +10408,17 @@
         <v>0</v>
       </c>
       <c r="E290" s="1" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="F290" s="3"/>
       <c r="G290" s="1"/>
       <c r="H290" s="1" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
     </row>
     <row r="291" spans="1:8">
       <c r="A291" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="B291" s="1" t="s">
         <v>203</v>
@@ -10431,12 +10435,12 @@
       <c r="F291" s="3"/>
       <c r="G291" s="1"/>
       <c r="H291" s="1" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
     </row>
     <row r="292" spans="1:8">
       <c r="A292" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="B292" s="1" t="s">
         <v>205</v>
@@ -10453,12 +10457,12 @@
       <c r="F292" s="3"/>
       <c r="G292" s="1"/>
       <c r="H292" s="1" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
     </row>
     <row r="293" spans="1:8" customFormat="1">
       <c r="A293" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="B293" s="1" t="s">
         <v>210</v>
@@ -10475,12 +10479,12 @@
       <c r="F293" s="3"/>
       <c r="G293" s="1"/>
       <c r="H293" s="1" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
     </row>
     <row r="294" spans="1:8" customFormat="1">
       <c r="A294" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="B294" s="1" t="s">
         <v>208</v>
@@ -10497,12 +10501,12 @@
       <c r="F294" s="3"/>
       <c r="G294" s="1"/>
       <c r="H294" s="1" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
     </row>
     <row r="295" spans="1:8" customFormat="1">
       <c r="A295" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="B295" s="1" t="s">
         <v>207</v>
@@ -10514,159 +10518,159 @@
         <v>0</v>
       </c>
       <c r="E295" s="1" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="F295" s="3"/>
       <c r="G295" s="1"/>
       <c r="H295" s="1" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
     </row>
     <row r="296" spans="1:8" customFormat="1">
       <c r="A296" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="B296" s="1" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="C296" s="1"/>
       <c r="D296" s="1"/>
       <c r="E296" s="1" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="F296" s="1">
         <v>1</v>
       </c>
       <c r="G296" s="1"/>
       <c r="H296" s="1" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
     </row>
     <row r="297" spans="1:8">
       <c r="A297" t="s">
+        <v>1040</v>
+      </c>
+      <c r="B297" s="1" t="s">
+        <v>1041</v>
+      </c>
+      <c r="E297" s="1" t="s">
+        <v>1045</v>
+      </c>
+      <c r="F297" s="2">
+        <v>1</v>
+      </c>
+      <c r="H297" s="7" t="s">
         <v>1046</v>
-      </c>
-      <c r="B297" s="1" t="s">
-        <v>1047</v>
-      </c>
-      <c r="E297" s="1" t="s">
-        <v>1051</v>
-      </c>
-      <c r="F297" s="2">
-        <v>1</v>
-      </c>
-      <c r="H297" s="7" t="s">
-        <v>1052</v>
       </c>
     </row>
     <row r="298" spans="1:8">
       <c r="A298" s="2" t="s">
-        <v>1067</v>
+        <v>1060</v>
       </c>
       <c r="B298" s="1" t="s">
-        <v>1068</v>
+        <v>1061</v>
       </c>
       <c r="E298" s="1" t="s">
-        <v>1069</v>
+        <v>1062</v>
       </c>
       <c r="F298" s="2">
         <v>1</v>
       </c>
       <c r="H298" s="2" t="s">
-        <v>1070</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="299" spans="1:8">
       <c r="A299" s="2" t="s">
-        <v>1072</v>
+        <v>1065</v>
       </c>
       <c r="B299" s="1" t="s">
-        <v>1071</v>
+        <v>1064</v>
       </c>
       <c r="E299" s="1" t="s">
-        <v>1074</v>
+        <v>1067</v>
       </c>
       <c r="F299" s="2">
         <v>1</v>
       </c>
       <c r="H299" s="7" t="s">
-        <v>1073</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="300" spans="1:8">
       <c r="A300" s="2" t="s">
-        <v>1083</v>
+        <v>1076</v>
       </c>
       <c r="B300" s="1" t="s">
-        <v>1075</v>
+        <v>1068</v>
       </c>
       <c r="E300" s="1" t="s">
-        <v>1076</v>
+        <v>1069</v>
       </c>
       <c r="F300" s="2">
         <v>1</v>
       </c>
       <c r="H300" s="2" t="s">
-        <v>1077</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="301" spans="1:8">
       <c r="A301" s="2" t="s">
-        <v>1081</v>
+        <v>1074</v>
       </c>
       <c r="B301" s="1" t="s">
-        <v>1078</v>
+        <v>1071</v>
       </c>
       <c r="E301" s="1" t="s">
+        <v>1072</v>
+      </c>
+      <c r="F301" s="2">
+        <v>1</v>
+      </c>
+      <c r="H301" s="2" t="s">
         <v>1079</v>
-      </c>
-      <c r="F301" s="2">
-        <v>1</v>
-      </c>
-      <c r="H301" s="2" t="s">
-        <v>1086</v>
       </c>
     </row>
     <row r="302" spans="1:8">
       <c r="A302" s="2" t="s">
-        <v>1082</v>
+        <v>1075</v>
       </c>
       <c r="B302" s="1" t="s">
-        <v>1080</v>
+        <v>1073</v>
       </c>
       <c r="E302" s="1" t="s">
-        <v>1084</v>
+        <v>1077</v>
       </c>
       <c r="F302" s="2">
         <v>1</v>
       </c>
       <c r="H302" s="2" t="s">
-        <v>1085</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="303" spans="1:8">
       <c r="A303" s="2" t="s">
-        <v>1092</v>
+        <v>1085</v>
       </c>
       <c r="B303" s="1" t="s">
-        <v>1087</v>
+        <v>1080</v>
       </c>
       <c r="E303" s="1" t="s">
-        <v>1088</v>
+        <v>1081</v>
       </c>
       <c r="F303" s="2">
         <v>1</v>
       </c>
       <c r="H303" s="7" t="s">
-        <v>1136</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="304" spans="1:8">
       <c r="A304" s="2" t="s">
-        <v>1091</v>
+        <v>1084</v>
       </c>
       <c r="B304" s="1" t="s">
-        <v>1089</v>
+        <v>1082</v>
       </c>
       <c r="C304" s="2">
         <v>6</v>
@@ -10675,227 +10679,227 @@
         <v>0</v>
       </c>
       <c r="E304" s="1" t="s">
-        <v>1090</v>
+        <v>1083</v>
       </c>
       <c r="H304" s="7" t="s">
-        <v>1093</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="305" spans="1:8">
       <c r="A305" s="2" t="s">
-        <v>1094</v>
+        <v>1087</v>
       </c>
       <c r="B305" s="1" t="s">
-        <v>1095</v>
+        <v>1088</v>
       </c>
       <c r="E305" s="1" t="s">
-        <v>1138</v>
+        <v>1131</v>
       </c>
       <c r="H305" s="7" t="s">
-        <v>1137</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="306" spans="1:8">
       <c r="B306" s="1" t="s">
-        <v>1096</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="307" spans="1:8">
       <c r="B307" s="1" t="s">
-        <v>1097</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="308" spans="1:8">
       <c r="B308" s="1" t="s">
-        <v>1098</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="309" spans="1:8">
       <c r="B309" s="1" t="s">
-        <v>1099</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="310" spans="1:8">
       <c r="B310" s="1" t="s">
-        <v>1100</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="311" spans="1:8">
       <c r="B311" s="1" t="s">
-        <v>1101</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="312" spans="1:8">
       <c r="B312" s="1" t="s">
-        <v>1102</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="313" spans="1:8">
       <c r="B313" s="1" t="s">
-        <v>1103</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="314" spans="1:8">
       <c r="B314" s="1" t="s">
-        <v>1104</v>
+        <v>1097</v>
       </c>
       <c r="E314" s="2" t="s">
-        <v>1105</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="315" spans="1:8">
       <c r="B315" s="1" t="s">
-        <v>1106</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="316" spans="1:8">
       <c r="B316" s="1" t="s">
-        <v>1107</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="317" spans="1:8">
       <c r="B317" s="1" t="s">
-        <v>1108</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="318" spans="1:8">
       <c r="B318" s="1" t="s">
-        <v>1109</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="319" spans="1:8">
       <c r="B319" s="1" t="s">
-        <v>1110</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="320" spans="1:8">
       <c r="B320" s="1" t="s">
-        <v>1111</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="321" spans="1:8">
       <c r="B321" s="1" t="s">
-        <v>1112</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="322" spans="1:8">
       <c r="B322" s="1" t="s">
-        <v>1113</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="323" spans="1:8">
       <c r="B323" s="1" t="s">
-        <v>1114</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="324" spans="1:8">
       <c r="B324" s="1" t="s">
-        <v>1115</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="325" spans="1:8">
       <c r="A325" s="2" t="s">
-        <v>1123</v>
+        <v>1116</v>
       </c>
       <c r="B325" s="1" t="s">
-        <v>1116</v>
+        <v>1109</v>
       </c>
       <c r="E325" s="2" t="s">
-        <v>1127</v>
+        <v>1120</v>
       </c>
       <c r="F325" s="2">
         <v>1</v>
       </c>
       <c r="H325" s="2" t="s">
-        <v>1135</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="326" spans="1:8">
       <c r="A326" s="2" t="s">
-        <v>1129</v>
+        <v>1122</v>
       </c>
       <c r="B326" s="1" t="s">
-        <v>1117</v>
+        <v>1110</v>
       </c>
       <c r="E326" s="2" t="s">
-        <v>1128</v>
+        <v>1121</v>
       </c>
       <c r="F326" s="2">
         <v>1</v>
       </c>
       <c r="H326" s="2" t="s">
-        <v>1134</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="327" spans="1:8">
       <c r="A327" s="2" t="s">
-        <v>1124</v>
+        <v>1117</v>
       </c>
       <c r="B327" s="1" t="s">
-        <v>1118</v>
+        <v>1111</v>
       </c>
       <c r="E327" s="2" t="s">
-        <v>1121</v>
+        <v>1114</v>
       </c>
       <c r="F327" s="2">
         <v>1</v>
       </c>
       <c r="H327" s="2" t="s">
-        <v>1133</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="328" spans="1:8">
       <c r="A328" s="2" t="s">
+        <v>1118</v>
+      </c>
+      <c r="B328" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="E328" s="2" t="s">
+        <v>1115</v>
+      </c>
+      <c r="F328" s="2">
+        <v>1</v>
+      </c>
+      <c r="H328" s="2" t="s">
         <v>1125</v>
-      </c>
-      <c r="B328" s="1" t="s">
-        <v>1119</v>
-      </c>
-      <c r="E328" s="2" t="s">
-        <v>1122</v>
-      </c>
-      <c r="F328" s="2">
-        <v>1</v>
-      </c>
-      <c r="H328" s="2" t="s">
-        <v>1132</v>
       </c>
     </row>
     <row r="329" spans="1:8">
       <c r="A329" s="2" t="s">
-        <v>1126</v>
+        <v>1119</v>
       </c>
       <c r="B329" s="1" t="s">
-        <v>1120</v>
+        <v>1113</v>
       </c>
       <c r="E329" s="2" t="s">
-        <v>1130</v>
+        <v>1123</v>
       </c>
       <c r="F329" s="2">
         <v>1</v>
       </c>
       <c r="H329" s="2" t="s">
-        <v>1131</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="330" spans="1:8">
       <c r="A330" s="2" t="s">
-        <v>1139</v>
+        <v>1132</v>
       </c>
       <c r="B330" s="1" t="s">
-        <v>1140</v>
+        <v>1133</v>
       </c>
       <c r="E330" t="s">
-        <v>1141</v>
+        <v>1134</v>
       </c>
       <c r="F330" s="2">
         <v>1</v>
       </c>
       <c r="G330" s="2" t="s">
-        <v>1142</v>
+        <v>1135</v>
       </c>
       <c r="H330" s="7" t="s">
-        <v>1143</v>
+        <v>1136</v>
       </c>
     </row>
   </sheetData>

--- a/stores.xlsx
+++ b/stores.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\YUMIN\Desktop\B0KT2A_RSVN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1A8C382-E114-4543-9A98-BEF3996355F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5B44E3D-F13A-48AB-989A-CC425AE41AD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{ABFC3117-FCCB-4FF3-804A-FE19451A2004}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1275" uniqueCount="1146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1326" uniqueCount="1192">
   <si>
     <t>룸익스케이프 WHITE</t>
   </si>
@@ -3794,22 +3794,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>방탈출 ESC</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>이스케이프시티 그랜드시티 신촌점</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>탐정크루 신촌2호점</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>시크릿 챔버</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>에필로그</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -3846,160 +3834,344 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>탈출 브라더스</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>패닉이스케이프 목동점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>큐브이스케이프 홍대점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>큐브이스케이프 인천구월점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>큐브이스케이프 전주점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>큐브이스케이프 대전둔산점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>큐브이스케이프 수유점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>deliver,딜리버,좀비스쿨,피고인,헨젤과그레텔,제시의시크릿,피라미드의비밀,신데렐라,집착</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>장기밀매,신데렐라,집착,마션,타이타닉,카타콤,통곡의문</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cb_hd</t>
+  </si>
+  <si>
+    <t>cb_jj</t>
+  </si>
+  <si>
+    <t>cb_dj</t>
+  </si>
+  <si>
+    <t>cb_sy</t>
+  </si>
+  <si>
+    <t>피라미드의 비밀,헨젤과그레텔,towering,타워링,gestapo,게슈타포,게스타포,monkeyhouse,몽키하우스,장기밀매,deliver,딜리버,romeo point,로미오포인트</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>타이타닉,신데렐라,장기밀매,towering,타워링,집착</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cb_ic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>우든펍의비밀,빅토리아호의침몰,거미의둥지,골든아이,the cube,더큐브,사라진천사들,stepfather,마녀의꿈,piggies,집착,트레저헌터,트레져헌터,obsession,treasure hunters</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://suyu.cubeescape.co.kr/</t>
+  </si>
+  <si>
+    <t>http://daejeon.cubeescape.co.kr/</t>
+  </si>
+  <si>
+    <t>http://junju.cubeescape.co.kr/</t>
+  </si>
+  <si>
+    <t>http://incheon.cubeescape.co.kr/</t>
+  </si>
+  <si>
+    <t>http://cubeescape.co.kr/</t>
+  </si>
+  <si>
+    <t>https://naver.me/GJTSSEZr</t>
+  </si>
+  <si>
+    <t>https://naver.me/G65wsmnX</t>
+  </si>
+  <si>
+    <t>소녀괴담,파파라치,이레이저,럭키가이,데이드림</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bk_hv</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BLACK H[-]AVEN</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4F : 마지막 기록</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://naver.me/x2YJOVXU</t>
+  </si>
+  <si>
+    <t>신촌성심병원,CHASER:한마음폐공장,HANNA IS FIRED,한나는해고됐어</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>미스터리 담</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>찬미특수진료센터,inspecto,getogeto,인스펙토,겟오겟오</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>매월 15일 13:00 다음달 예약 오픈</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>매월 1일 00:00 1일~말일 예약 오픈</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>매월 1일 18:00 1일~말일 예약 오픈</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>매월 1일 20:00 1일~말일 예약 오픈</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>매주 금요일 00:00 3주 뒤 수요일까지 예약 오픈</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>매주 화요일 오전 11:00 다음주 월~일 예약 오픈</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sv_kd1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sv_kd2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lucid dream,루시드드림,루드,자각몽,coldcase,콜드케이스,미제사건,the cage,더케이지</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dear marsy,디어마르시,디마,이층복도끝화장실,이복화,무채색인간</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://solver-gd.com/</t>
+  </si>
+  <si>
+    <t>ect_ydp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이스케이프시티 영등포본점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>이스케이프시티 성신여대점</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>이스케이프시티 영등포점</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>탈출 브라더스</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>패닉이스케이프 목동점</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>호텔 레토 성수</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>큐브이스케이프 홍대점</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>큐브이스케이프 인천구월점</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>큐브이스케이프 전주점</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>큐브이스케이프 대전둔산점</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>큐브이스케이프 수유점</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>deliver,딜리버,좀비스쿨,피고인,헨젤과그레텔,제시의시크릿,피라미드의비밀,신데렐라,집착</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>장기밀매,신데렐라,집착,마션,타이타닉,카타콤,통곡의문</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>cb_hd</t>
-  </si>
-  <si>
-    <t>cb_jj</t>
-  </si>
-  <si>
-    <t>cb_dj</t>
-  </si>
-  <si>
-    <t>cb_sy</t>
-  </si>
-  <si>
-    <t>피라미드의 비밀,헨젤과그레텔,towering,타워링,gestapo,게슈타포,게스타포,monkeyhouse,몽키하우스,장기밀매,deliver,딜리버,romeo point,로미오포인트</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>타이타닉,신데렐라,장기밀매,towering,타워링,집착</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>cb_ic</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>우든펍의비밀,빅토리아호의침몰,거미의둥지,골든아이,the cube,더큐브,사라진천사들,stepfather,마녀의꿈,piggies,집착,트레저헌터,트레져헌터,obsession,treasure hunters</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>http://suyu.cubeescape.co.kr/</t>
-  </si>
-  <si>
-    <t>http://daejeon.cubeescape.co.kr/</t>
-  </si>
-  <si>
-    <t>http://junju.cubeescape.co.kr/</t>
-  </si>
-  <si>
-    <t>http://incheon.cubeescape.co.kr/</t>
-  </si>
-  <si>
-    <t>http://cubeescape.co.kr/</t>
-  </si>
-  <si>
-    <t>https://naver.me/GJTSSEZr</t>
-  </si>
-  <si>
-    <t>https://naver.me/G65wsmnX</t>
-  </si>
-  <si>
-    <t>소녀괴담,파파라치,이레이저,럭키가이,데이드림</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>bk_hv</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BLACK H[-]AVEN</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4F : 마지막 기록</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>매주 화요일 오전 11:00 다음주 월~일 회차 오픈</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://naver.me/x2YJOVXU</t>
-  </si>
-  <si>
-    <t>화-&gt;수 0:00 다음주 토~다다음주 금 1주일치 오픈</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>신촌성심병원,CHASER:한마음폐공장,HANNA IS FIRED,한나는해고됐어</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>미스터리 담</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>매월 1일 00:00</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>매월 1일 18:00</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>매월 1일 20:00</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0:00</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>매주 금요일 00:00 3주 뒤 수요일까지 열립니다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>찬미특수진료센터,inspecto,getogeto,인스펙토,겟오겟오</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <t>이스케이프시티 부천신중동점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이스케이프시티 그랜드 시티 신촌점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ect_sswu</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ect_bc</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ect_sc</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>좀비바이러스,마법학교,기억의조각,spy,스파이,카지노의전설,다시만날수있을까?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>알고보면,그녀를찾아서,킬러vs,vs경찰,시험지유출사건</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>부자가될상인가,바람바람바람,추억의전당포,원한</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>연,신의실수,컨티뉴얼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://www.escapecity.kr/</t>
+  </si>
+  <si>
+    <t>ep_lg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Monday night,먼데이나이트,stage,스테이지,다섯번째밤,memory,메모리</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://epilogueescape.com/</t>
+  </si>
+  <si>
+    <t>매주 수요일 15:00 다음주 토~다다음주 금 예약 오픈</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://panorama-escape.com/</t>
+  </si>
+  <si>
+    <t>pm_lw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pm_bs</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>파노라마 부산점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>미래재난리포트</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://naver.me/FutFZ0bm</t>
+  </si>
+  <si>
+    <t>mz_nw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://www.themazenw.co.kr/</t>
+  </si>
+  <si>
+    <t>lost the prince,로스트더프린스,상계동357-8,상의원,secret room,시크릿룸,no one,노원,탐정in new york,탐정인뉴욕,더바틀샵in중계동,더바틀샵인중계동,디셈블,dissemble,delete,딜리트,gold,골드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>esc_bro</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>지하감옥,파라오의비밀,도둑들,원혼의저주,달의제단,미드나잇콜링</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://escapebro.co.kr/</t>
+  </si>
+  <si>
+    <t>pnc_md</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://www.panicescape.com/</t>
+  </si>
+  <si>
+    <t>매직아카데미,ARROW,두얼굴의영주,애로우</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>wtw_esc</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>마법사의세계,지하감옥,드림인베이더,위험한레시피,이상한나라의초대</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://naver.me/xTT2vxAy</t>
+  </si>
+  <si>
+    <t>레토 성수</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lt_ss</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>호텔 레토</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>그녀를 만나기 한시간 전,Dream Factory,드림팩토리,박물관을 털어라,D-Therapy,디테라피,사립고 살인사건</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://naver.me/GsoP5qBO</t>
+  </si>
+  <si>
+    <t>trap_sy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>crew_sc2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>초코의왕,대저택의비밀,출근길,소년의마음,크라임씬-이상한부부이야기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>find_esc</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://crewescape.com/</t>
+  </si>
+  <si>
+    <t>무인도,201호202호,괴담수집가,4,더헝거</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://naver.me/FtGN3koD</t>
   </si>
 </sst>
 </file>
@@ -4434,7 +4606,7 @@
     <col min="3" max="4" width="9" style="2" customWidth="1"/>
     <col min="5" max="5" width="85.875" style="2" customWidth="1"/>
     <col min="6" max="6" width="9" style="2" customWidth="1"/>
-    <col min="7" max="7" width="66" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="47.25" style="2" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="62.75" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="16384" width="9" style="2"/>
   </cols>
@@ -4637,17 +4809,17 @@
       <c r="B10" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="C10" s="3">
-        <v>13</v>
-      </c>
-      <c r="D10" s="4">
-        <v>0.41666666666666669</v>
-      </c>
+      <c r="C10" s="3"/>
+      <c r="D10" s="4"/>
       <c r="E10" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="F10" s="3"/>
-      <c r="G10" s="1"/>
+      <c r="F10" s="3">
+        <v>1</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>1134</v>
+      </c>
       <c r="H10" s="1" t="s">
         <v>516</v>
       </c>
@@ -4659,17 +4831,17 @@
       <c r="B11" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="C11" s="3">
-        <v>13</v>
-      </c>
-      <c r="D11" s="4">
-        <v>0.45833333333333331</v>
-      </c>
+      <c r="C11" s="3"/>
+      <c r="D11" s="4"/>
       <c r="E11" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="F11" s="3"/>
-      <c r="G11" s="1"/>
+      <c r="F11" s="3">
+        <v>1</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>1134</v>
+      </c>
       <c r="H11" s="1" t="s">
         <v>517</v>
       </c>
@@ -4798,7 +4970,7 @@
         <v>0</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>1138</v>
+        <v>1130</v>
       </c>
       <c r="F17" s="3"/>
       <c r="G17" s="1"/>
@@ -5593,7 +5765,7 @@
         <v>1</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>1140</v>
+        <v>1135</v>
       </c>
       <c r="H56" s="2" t="s">
         <v>544</v>
@@ -5646,7 +5818,7 @@
         <v>1</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>1137</v>
+        <v>1161</v>
       </c>
       <c r="H59" t="s">
         <v>643</v>
@@ -6777,7 +6949,7 @@
         <v>846</v>
       </c>
       <c r="B117" t="s">
-        <v>1139</v>
+        <v>1131</v>
       </c>
       <c r="C117" s="3"/>
       <c r="D117" s="4"/>
@@ -8774,7 +8946,7 @@
         <v>1</v>
       </c>
       <c r="G214" s="1" t="s">
-        <v>1141</v>
+        <v>1136</v>
       </c>
       <c r="H214" s="2" t="s">
         <v>583</v>
@@ -8796,7 +8968,7 @@
         <v>1</v>
       </c>
       <c r="G215" s="1" t="s">
-        <v>1142</v>
+        <v>1137</v>
       </c>
       <c r="H215" s="2" t="s">
         <v>583</v>
@@ -9409,7 +9581,7 @@
         <v>13</v>
       </c>
       <c r="D244" s="11" t="s">
-        <v>1143</v>
+        <v>1132</v>
       </c>
       <c r="E244" t="s">
         <v>1023</v>
@@ -9964,13 +10136,13 @@
       <c r="C270" s="3"/>
       <c r="D270" s="6"/>
       <c r="E270" s="1" t="s">
-        <v>1145</v>
+        <v>1133</v>
       </c>
       <c r="F270" s="3">
         <v>1</v>
       </c>
       <c r="G270" s="2" t="s">
-        <v>1144</v>
+        <v>1138</v>
       </c>
       <c r="H270" t="s">
         <v>646</v>
@@ -10662,7 +10834,7 @@
         <v>1</v>
       </c>
       <c r="H303" s="7" t="s">
-        <v>1129</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="304" spans="1:8">
@@ -10693,30 +10865,84 @@
         <v>1088</v>
       </c>
       <c r="E305" s="1" t="s">
-        <v>1131</v>
+        <v>1125</v>
       </c>
       <c r="H305" s="7" t="s">
-        <v>1130</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="306" spans="1:8">
+      <c r="A306" s="2" t="s">
+        <v>1140</v>
+      </c>
       <c r="B306" s="1" t="s">
         <v>1089</v>
       </c>
+      <c r="E306" s="1" t="s">
+        <v>1142</v>
+      </c>
+      <c r="F306" s="2">
+        <v>1</v>
+      </c>
+      <c r="H306" s="2" t="s">
+        <v>1144</v>
+      </c>
     </row>
     <row r="307" spans="1:8">
+      <c r="A307" s="2" t="s">
+        <v>1141</v>
+      </c>
       <c r="B307" s="1" t="s">
         <v>1090</v>
       </c>
+      <c r="E307" s="1" t="s">
+        <v>1143</v>
+      </c>
+      <c r="F307" s="2">
+        <v>1</v>
+      </c>
+      <c r="H307" s="2" t="s">
+        <v>1144</v>
+      </c>
     </row>
     <row r="308" spans="1:8">
+      <c r="A308" s="2" t="s">
+        <v>1186</v>
+      </c>
       <c r="B308" s="1" t="s">
         <v>1091</v>
       </c>
+      <c r="C308" s="2">
+        <v>14</v>
+      </c>
+      <c r="D308" s="6">
+        <v>0</v>
+      </c>
+      <c r="E308" s="1" t="s">
+        <v>1187</v>
+      </c>
+      <c r="H308" s="2" t="s">
+        <v>1189</v>
+      </c>
     </row>
     <row r="309" spans="1:8">
+      <c r="A309" s="2" t="s">
+        <v>1158</v>
+      </c>
       <c r="B309" s="1" t="s">
         <v>1092</v>
+      </c>
+      <c r="C309" s="2">
+        <v>6</v>
+      </c>
+      <c r="D309" s="6">
+        <v>0</v>
+      </c>
+      <c r="E309" s="1" t="s">
+        <v>1159</v>
+      </c>
+      <c r="H309" s="2" t="s">
+        <v>1160</v>
       </c>
     </row>
     <row r="310" spans="1:8">
@@ -10725,26 +10951,74 @@
       </c>
     </row>
     <row r="311" spans="1:8">
+      <c r="A311" s="2" t="s">
+        <v>1163</v>
+      </c>
       <c r="B311" s="1" t="s">
         <v>1094</v>
       </c>
+      <c r="C311" s="2">
+        <v>14</v>
+      </c>
+      <c r="D311" s="6">
+        <v>0</v>
+      </c>
+      <c r="E311" s="2" t="s">
+        <v>1095</v>
+      </c>
+      <c r="H311" s="2" t="s">
+        <v>1162</v>
+      </c>
     </row>
     <row r="312" spans="1:8">
+      <c r="A312" s="2" t="s">
+        <v>1168</v>
+      </c>
       <c r="B312" s="1" t="s">
-        <v>1095</v>
+        <v>1096</v>
+      </c>
+      <c r="E312" s="2" t="s">
+        <v>1170</v>
+      </c>
+      <c r="F312" s="2">
+        <v>1</v>
+      </c>
+      <c r="H312" s="2" t="s">
+        <v>1169</v>
       </c>
     </row>
     <row r="313" spans="1:8">
+      <c r="A313" s="2" t="s">
+        <v>1185</v>
+      </c>
       <c r="B313" s="1" t="s">
-        <v>1096</v>
+        <v>1097</v>
+      </c>
+      <c r="E313" s="2" t="s">
+        <v>1183</v>
+      </c>
+      <c r="F313" s="2">
+        <v>1</v>
+      </c>
+      <c r="H313" s="7" t="s">
+        <v>1184</v>
       </c>
     </row>
     <row r="314" spans="1:8">
+      <c r="A314" s="2" t="s">
+        <v>1188</v>
+      </c>
       <c r="B314" s="1" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="E314" s="2" t="s">
-        <v>1098</v>
+        <v>1190</v>
+      </c>
+      <c r="F314" s="2">
+        <v>1</v>
+      </c>
+      <c r="H314" s="7" t="s">
+        <v>1191</v>
       </c>
     </row>
     <row r="315" spans="1:8">
@@ -10753,153 +11027,267 @@
       </c>
     </row>
     <row r="316" spans="1:8">
+      <c r="A316" s="2" t="s">
+        <v>1177</v>
+      </c>
       <c r="B316" s="1" t="s">
         <v>1100</v>
       </c>
+      <c r="E316" s="2" t="s">
+        <v>1178</v>
+      </c>
+      <c r="F316" s="2">
+        <v>1</v>
+      </c>
+      <c r="H316" s="7" t="s">
+        <v>1179</v>
+      </c>
     </row>
     <row r="317" spans="1:8">
+      <c r="A317" s="2" t="s">
+        <v>1171</v>
+      </c>
       <c r="B317" s="1" t="s">
         <v>1101</v>
       </c>
+      <c r="E317" s="2" t="s">
+        <v>1172</v>
+      </c>
+      <c r="F317" s="2">
+        <v>1</v>
+      </c>
+      <c r="H317" s="2" t="s">
+        <v>1173</v>
+      </c>
     </row>
     <row r="318" spans="1:8">
+      <c r="A318" s="2" t="s">
+        <v>1174</v>
+      </c>
       <c r="B318" s="1" t="s">
         <v>1102</v>
       </c>
+      <c r="E318" s="2" t="s">
+        <v>1176</v>
+      </c>
+      <c r="F318" s="2">
+        <v>1</v>
+      </c>
+      <c r="H318" s="2" t="s">
+        <v>1175</v>
+      </c>
     </row>
     <row r="319" spans="1:8">
+      <c r="A319" s="2" t="s">
+        <v>1181</v>
+      </c>
       <c r="B319" s="1" t="s">
+        <v>1180</v>
+      </c>
+      <c r="C319" s="2">
+        <v>6</v>
+      </c>
+      <c r="D319" s="6">
+        <v>0</v>
+      </c>
+      <c r="E319" s="2" t="s">
+        <v>1182</v>
+      </c>
+    </row>
+    <row r="320" spans="1:8">
+      <c r="A320" s="2" t="s">
+        <v>1110</v>
+      </c>
+      <c r="B320" s="1" t="s">
         <v>1103</v>
       </c>
-    </row>
-    <row r="320" spans="1:8">
-      <c r="B320" s="1" t="s">
+      <c r="E320" s="2" t="s">
+        <v>1114</v>
+      </c>
+      <c r="F320" s="2">
+        <v>1</v>
+      </c>
+      <c r="H320" s="2" t="s">
+        <v>1122</v>
+      </c>
+    </row>
+    <row r="321" spans="1:8">
+      <c r="A321" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="B321" s="1" t="s">
         <v>1104</v>
       </c>
-    </row>
-    <row r="321" spans="1:8">
-      <c r="B321" s="1" t="s">
+      <c r="E321" s="2" t="s">
+        <v>1115</v>
+      </c>
+      <c r="F321" s="2">
+        <v>1</v>
+      </c>
+      <c r="H321" s="2" t="s">
+        <v>1121</v>
+      </c>
+    </row>
+    <row r="322" spans="1:8">
+      <c r="A322" s="2" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B322" s="1" t="s">
         <v>1105</v>
       </c>
-    </row>
-    <row r="322" spans="1:8">
-      <c r="B322" s="1" t="s">
+      <c r="E322" s="2" t="s">
+        <v>1108</v>
+      </c>
+      <c r="F322" s="2">
+        <v>1</v>
+      </c>
+      <c r="H322" s="2" t="s">
+        <v>1120</v>
+      </c>
+    </row>
+    <row r="323" spans="1:8">
+      <c r="A323" s="2" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B323" s="1" t="s">
         <v>1106</v>
       </c>
-    </row>
-    <row r="323" spans="1:8">
-      <c r="B323" s="1" t="s">
+      <c r="E323" s="2" t="s">
+        <v>1109</v>
+      </c>
+      <c r="F323" s="2">
+        <v>1</v>
+      </c>
+      <c r="H323" s="2" t="s">
+        <v>1119</v>
+      </c>
+    </row>
+    <row r="324" spans="1:8">
+      <c r="A324" s="2" t="s">
+        <v>1113</v>
+      </c>
+      <c r="B324" s="1" t="s">
         <v>1107</v>
       </c>
-    </row>
-    <row r="324" spans="1:8">
-      <c r="B324" s="1" t="s">
-        <v>1108</v>
+      <c r="E324" s="2" t="s">
+        <v>1117</v>
+      </c>
+      <c r="F324" s="2">
+        <v>1</v>
+      </c>
+      <c r="H324" s="2" t="s">
+        <v>1118</v>
       </c>
     </row>
     <row r="325" spans="1:8">
       <c r="A325" s="2" t="s">
-        <v>1116</v>
+        <v>1126</v>
       </c>
       <c r="B325" s="1" t="s">
-        <v>1109</v>
-      </c>
-      <c r="E325" s="2" t="s">
-        <v>1120</v>
+        <v>1127</v>
+      </c>
+      <c r="E325" t="s">
+        <v>1128</v>
       </c>
       <c r="F325" s="2">
         <v>1</v>
       </c>
-      <c r="H325" s="2" t="s">
-        <v>1128</v>
+      <c r="G325" s="2" t="s">
+        <v>1139</v>
+      </c>
+      <c r="H325" s="7" t="s">
+        <v>1129</v>
       </c>
     </row>
     <row r="326" spans="1:8">
       <c r="A326" s="2" t="s">
-        <v>1122</v>
+        <v>1145</v>
       </c>
       <c r="B326" s="1" t="s">
-        <v>1110</v>
+        <v>1146</v>
       </c>
       <c r="E326" s="2" t="s">
-        <v>1121</v>
+        <v>1153</v>
       </c>
       <c r="F326" s="2">
         <v>1</v>
       </c>
       <c r="H326" s="2" t="s">
-        <v>1127</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="327" spans="1:8">
       <c r="A327" s="2" t="s">
-        <v>1117</v>
+        <v>1150</v>
       </c>
       <c r="B327" s="1" t="s">
-        <v>1111</v>
+        <v>1147</v>
       </c>
       <c r="E327" s="2" t="s">
-        <v>1114</v>
+        <v>1154</v>
       </c>
       <c r="F327" s="2">
         <v>1</v>
       </c>
       <c r="H327" s="2" t="s">
-        <v>1126</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="328" spans="1:8">
       <c r="A328" s="2" t="s">
-        <v>1118</v>
+        <v>1151</v>
       </c>
       <c r="B328" s="1" t="s">
-        <v>1112</v>
+        <v>1148</v>
       </c>
       <c r="E328" s="2" t="s">
-        <v>1115</v>
+        <v>1155</v>
       </c>
       <c r="F328" s="2">
         <v>1</v>
       </c>
       <c r="H328" s="2" t="s">
-        <v>1125</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="329" spans="1:8">
       <c r="A329" s="2" t="s">
-        <v>1119</v>
+        <v>1152</v>
       </c>
       <c r="B329" s="1" t="s">
-        <v>1113</v>
+        <v>1149</v>
+      </c>
+      <c r="C329" s="2">
+        <v>14</v>
+      </c>
+      <c r="D329" s="6">
+        <v>0</v>
       </c>
       <c r="E329" s="2" t="s">
-        <v>1123</v>
-      </c>
-      <c r="F329" s="2">
-        <v>1</v>
+        <v>1156</v>
       </c>
       <c r="H329" s="2" t="s">
-        <v>1124</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="330" spans="1:8">
       <c r="A330" s="2" t="s">
-        <v>1132</v>
+        <v>1164</v>
       </c>
       <c r="B330" s="1" t="s">
-        <v>1133</v>
-      </c>
-      <c r="E330" t="s">
-        <v>1134</v>
-      </c>
-      <c r="F330" s="2">
-        <v>1</v>
-      </c>
-      <c r="G330" s="2" t="s">
-        <v>1135</v>
+        <v>1165</v>
+      </c>
+      <c r="C330" s="2">
+        <v>12</v>
+      </c>
+      <c r="D330" s="6">
+        <v>0</v>
+      </c>
+      <c r="E330" s="2" t="s">
+        <v>1166</v>
       </c>
       <c r="H330" s="7" t="s">
-        <v>1136</v>
+        <v>1167</v>
       </c>
     </row>
   </sheetData>
@@ -10930,9 +11318,13 @@
     <hyperlink ref="H304" r:id="rId20" xr:uid="{A3CEB787-A4DA-499F-A877-2709B0646565}"/>
     <hyperlink ref="H303" r:id="rId21" xr:uid="{9AEB623B-37CB-4EFD-A4E5-06C08664DCD5}"/>
     <hyperlink ref="H305" r:id="rId22" xr:uid="{38AF5094-2E8A-4F1F-8FBA-18FEBEAFFB8F}"/>
-    <hyperlink ref="H330" r:id="rId23" xr:uid="{5EA546E0-B128-4386-8445-FD73AAE43FAB}"/>
+    <hyperlink ref="H325" r:id="rId23" xr:uid="{5EA546E0-B128-4386-8445-FD73AAE43FAB}"/>
+    <hyperlink ref="H330" r:id="rId24" xr:uid="{A2E3DE51-C084-4528-998F-F094210AAA1D}"/>
+    <hyperlink ref="H316" r:id="rId25" xr:uid="{0A71BEFF-E769-421A-8079-F0AC7ECC9FE2}"/>
+    <hyperlink ref="H313" r:id="rId26" xr:uid="{F2A9379F-C93A-48C6-B140-FD9A9AACF5E0}"/>
+    <hyperlink ref="H314" r:id="rId27" xr:uid="{E90FCA6A-2CCD-4405-8CD0-447FE361C93D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId24"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId28"/>
 </worksheet>
 </file>
--- a/stores.xlsx
+++ b/stores.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\YUMIN\Desktop\B0KT2A_RSVN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5B44E3D-F13A-48AB-989A-CC425AE41AD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49EB91C7-7282-41D4-9DE5-F80D871D0197}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{ABFC3117-FCCB-4FF3-804A-FE19451A2004}"/>
   </bookViews>
@@ -4668,7 +4668,7 @@
         <v>7</v>
       </c>
       <c r="D3" s="6">
-        <v>0.83333333333333337</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>824</v>

--- a/stores.xlsx
+++ b/stores.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\YUMIN\Desktop\B0KT2A_RSVN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49EB91C7-7282-41D4-9DE5-F80D871D0197}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD7AE3B3-4EB4-4E72-8FA9-351497FFEC63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{ABFC3117-FCCB-4FF3-804A-FE19451A2004}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{ABFC3117-FCCB-4FF3-804A-FE19451A2004}"/>
   </bookViews>
   <sheets>
     <sheet name="stores" sheetId="2" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1326" uniqueCount="1192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1331" uniqueCount="1196">
   <si>
     <t>룸익스케이프 WHITE</t>
   </si>
@@ -2058,9 +2058,6 @@
   </si>
   <si>
     <t>https://naver.me/5yPJqzhk</t>
-  </si>
-  <si>
-    <t>&lt;a href=https://zerogangnam.com/</t>
   </si>
   <si>
     <t>https://zeroesc.com</t>
@@ -4172,6 +4169,25 @@
   </si>
   <si>
     <t>https://naver.me/FtGN3koD</t>
+  </si>
+  <si>
+    <t>sh_nbc</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>셜록홈즈 뉴부천점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://hotelletoh.co.kr/</t>
+  </si>
+  <si>
+    <t>https://zerogangnam.com/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>madeon,xiamen,houndred,crack,월간오컬트:폐간호,귀가,마데온,샤먼,하운드레드,크랙</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -4598,7 +4614,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D839462D-4719-40BB-8925-C1B9F93734CF}">
-  <dimension ref="A1:H330"/>
+  <dimension ref="A1:H331"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="2"/>
@@ -4639,10 +4655,10 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="2" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="C2" s="2">
         <v>7</v>
@@ -4651,18 +4667,18 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="E2" s="2" t="s">
+        <v>632</v>
+      </c>
+      <c r="H2" s="2" t="s">
         <v>633</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>634</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="2" t="s">
+        <v>821</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>822</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>823</v>
       </c>
       <c r="C3" s="2">
         <v>7</v>
@@ -4671,18 +4687,18 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="2" t="s">
+        <v>824</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>825</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>826</v>
       </c>
       <c r="C4" s="2">
         <v>7</v>
@@ -4691,7 +4707,7 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -4818,7 +4834,7 @@
         <v>1</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>516</v>
@@ -4840,7 +4856,7 @@
         <v>1</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>517</v>
@@ -4953,7 +4969,7 @@
       <c r="F16" s="3"/>
       <c r="G16" s="1"/>
       <c r="H16" s="7" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -4970,7 +4986,7 @@
         <v>0</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="F17" s="3"/>
       <c r="G17" s="1"/>
@@ -5132,10 +5148,10 @@
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B25" s="1" t="s">
         <v>827</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>828</v>
       </c>
       <c r="C25" s="3">
         <v>15</v>
@@ -5144,12 +5160,12 @@
         <v>0</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="F25" s="3"/>
       <c r="G25" s="1"/>
       <c r="H25" s="11" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -5240,27 +5256,27 @@
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="2" t="s">
+        <v>784</v>
+      </c>
+      <c r="B30" s="1" t="s">
         <v>785</v>
       </c>
-      <c r="B30" s="1" t="s">
+      <c r="E30" s="1" t="s">
         <v>786</v>
       </c>
-      <c r="E30" s="1" t="s">
-        <v>787</v>
-      </c>
       <c r="F30" s="3">
         <v>1</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="2" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="C31" s="2">
         <v>20</v>
@@ -5269,112 +5285,112 @@
         <v>0</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="2" t="s">
+        <v>771</v>
+      </c>
+      <c r="B32" s="1" t="s">
         <v>772</v>
       </c>
-      <c r="B32" s="1" t="s">
+      <c r="E32" s="1" t="s">
         <v>773</v>
       </c>
-      <c r="E32" s="1" t="s">
-        <v>774</v>
-      </c>
       <c r="F32" s="3">
         <v>1</v>
       </c>
       <c r="H32" s="7" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="2" t="s">
+        <v>767</v>
+      </c>
+      <c r="B33" s="1" t="s">
         <v>768</v>
       </c>
-      <c r="B33" s="1" t="s">
+      <c r="E33" s="1" t="s">
         <v>769</v>
       </c>
-      <c r="E33" s="1" t="s">
+      <c r="F33" s="3">
+        <v>1</v>
+      </c>
+      <c r="H33" s="2" t="s">
         <v>770</v>
-      </c>
-      <c r="F33" s="3">
-        <v>1</v>
-      </c>
-      <c r="H33" s="2" t="s">
-        <v>771</v>
       </c>
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="2" t="s">
+        <v>778</v>
+      </c>
+      <c r="B34" s="1" t="s">
         <v>779</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="E34" s="1" t="s">
+        <v>782</v>
+      </c>
+      <c r="F34" s="3">
+        <v>1</v>
+      </c>
+      <c r="H34" s="2" t="s">
         <v>780</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>783</v>
-      </c>
-      <c r="F34" s="3">
-        <v>1</v>
-      </c>
-      <c r="H34" s="2" t="s">
-        <v>781</v>
       </c>
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="2" t="s">
+        <v>792</v>
+      </c>
+      <c r="B35" s="1" t="s">
         <v>793</v>
       </c>
-      <c r="B35" s="1" t="s">
+      <c r="E35" s="1" t="s">
         <v>794</v>
       </c>
-      <c r="E35" s="1" t="s">
-        <v>795</v>
-      </c>
       <c r="F35" s="3">
         <v>1</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
     </row>
     <row r="36" spans="1:8">
       <c r="A36" s="2" t="s">
+        <v>788</v>
+      </c>
+      <c r="B36" s="1" t="s">
         <v>789</v>
       </c>
-      <c r="B36" s="1" t="s">
+      <c r="E36" s="1" t="s">
         <v>790</v>
       </c>
-      <c r="E36" s="1" t="s">
-        <v>791</v>
-      </c>
       <c r="F36" s="3">
         <v>1</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
     </row>
     <row r="37" spans="1:8">
       <c r="A37" s="2" t="s">
+        <v>775</v>
+      </c>
+      <c r="B37" s="1" t="s">
         <v>776</v>
       </c>
-      <c r="B37" s="1" t="s">
+      <c r="E37" s="1" t="s">
         <v>777</v>
       </c>
-      <c r="E37" s="1" t="s">
-        <v>778</v>
-      </c>
       <c r="F37" s="3">
         <v>1</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -5401,36 +5417,36 @@
     </row>
     <row r="39" spans="1:8">
       <c r="A39" s="2" t="s">
+        <v>683</v>
+      </c>
+      <c r="B39" s="1" t="s">
         <v>684</v>
       </c>
-      <c r="B39" s="1" t="s">
-        <v>685</v>
-      </c>
       <c r="E39" s="1" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="F39" s="3">
         <v>1</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
     </row>
     <row r="40" spans="1:8">
       <c r="A40" s="2" t="s">
+        <v>685</v>
+      </c>
+      <c r="B40" s="1" t="s">
         <v>686</v>
       </c>
-      <c r="B40" s="1" t="s">
-        <v>687</v>
-      </c>
       <c r="E40" s="1" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="F40" s="3">
         <v>1</v>
       </c>
       <c r="H40" s="9" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -5631,7 +5647,7 @@
         <v>0</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="F50" s="3"/>
       <c r="G50" s="1"/>
@@ -5765,7 +5781,7 @@
         <v>1</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="H56" s="2" t="s">
         <v>544</v>
@@ -5773,13 +5789,13 @@
     </row>
     <row r="57" spans="1:8">
       <c r="A57" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="F57" s="2">
         <v>1</v>
@@ -5787,41 +5803,41 @@
     </row>
     <row r="58" spans="1:8">
       <c r="A58" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="F58" s="3">
         <v>1</v>
       </c>
       <c r="H58" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
     </row>
     <row r="59" spans="1:8">
       <c r="A59" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="C59" s="3"/>
       <c r="D59" s="6"/>
       <c r="E59" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="F59" s="3">
+        <v>1</v>
+      </c>
+      <c r="G59" s="1" t="s">
+        <v>1160</v>
+      </c>
+      <c r="H59" t="s">
         <v>642</v>
-      </c>
-      <c r="F59" s="3">
-        <v>1</v>
-      </c>
-      <c r="G59" s="1" t="s">
-        <v>1161</v>
-      </c>
-      <c r="H59" t="s">
-        <v>643</v>
       </c>
     </row>
     <row r="60" spans="1:8">
@@ -5848,10 +5864,10 @@
     </row>
     <row r="61" spans="1:8">
       <c r="A61" s="11" t="s">
+        <v>830</v>
+      </c>
+      <c r="B61" t="s">
         <v>831</v>
-      </c>
-      <c r="B61" t="s">
-        <v>832</v>
       </c>
       <c r="C61">
         <v>6</v>
@@ -5860,7 +5876,7 @@
         <v>0</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="F61" s="3"/>
       <c r="G61" s="1"/>
@@ -6043,7 +6059,7 @@
     </row>
     <row r="70" spans="1:8">
       <c r="A70" s="2" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>181</v>
@@ -6062,7 +6078,7 @@
     </row>
     <row r="71" spans="1:8">
       <c r="A71" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>261</v>
@@ -6081,7 +6097,7 @@
     </row>
     <row r="72" spans="1:8">
       <c r="A72" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>179</v>
@@ -6100,7 +6116,7 @@
     </row>
     <row r="73" spans="1:8">
       <c r="A73" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>185</v>
@@ -6121,7 +6137,7 @@
     </row>
     <row r="74" spans="1:8">
       <c r="A74" s="2" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>183</v>
@@ -6142,7 +6158,7 @@
     </row>
     <row r="75" spans="1:8">
       <c r="A75" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>171</v>
@@ -6161,7 +6177,7 @@
     </row>
     <row r="76" spans="1:8">
       <c r="A76" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>173</v>
@@ -6199,7 +6215,7 @@
     </row>
     <row r="78" spans="1:8">
       <c r="A78" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>187</v>
@@ -6220,7 +6236,7 @@
     </row>
     <row r="79" spans="1:8">
       <c r="A79" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>175</v>
@@ -6239,7 +6255,7 @@
     </row>
     <row r="80" spans="1:8">
       <c r="A80" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>177</v>
@@ -6260,7 +6276,7 @@
     </row>
     <row r="81" spans="1:8">
       <c r="A81" s="2" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>193</v>
@@ -6281,7 +6297,7 @@
     </row>
     <row r="82" spans="1:8">
       <c r="A82" s="2" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>191</v>
@@ -6302,7 +6318,7 @@
     </row>
     <row r="83" spans="1:8">
       <c r="A83" s="2" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>169</v>
@@ -6323,7 +6339,7 @@
     </row>
     <row r="84" spans="1:8">
       <c r="A84" s="2" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>167</v>
@@ -6342,7 +6358,7 @@
     </row>
     <row r="85" spans="1:8">
       <c r="A85" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>159</v>
@@ -6361,7 +6377,7 @@
     </row>
     <row r="86" spans="1:8">
       <c r="A86" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>165</v>
@@ -6380,7 +6396,7 @@
     </row>
     <row r="87" spans="1:8">
       <c r="A87" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>163</v>
@@ -6399,7 +6415,7 @@
     </row>
     <row r="88" spans="1:8">
       <c r="A88" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>161</v>
@@ -6418,7 +6434,7 @@
     </row>
     <row r="89" spans="1:8">
       <c r="A89" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>189</v>
@@ -6439,38 +6455,38 @@
     </row>
     <row r="90" spans="1:8">
       <c r="A90" t="s">
+        <v>833</v>
+      </c>
+      <c r="B90" t="s">
         <v>834</v>
-      </c>
-      <c r="B90" t="s">
-        <v>835</v>
       </c>
       <c r="C90" s="3"/>
       <c r="D90" s="4"/>
       <c r="E90" s="1" t="s">
+        <v>835</v>
+      </c>
+      <c r="F90" s="3">
+        <v>1</v>
+      </c>
+      <c r="H90" s="11" t="s">
         <v>836</v>
-      </c>
-      <c r="F90" s="3">
-        <v>1</v>
-      </c>
-      <c r="H90" s="11" t="s">
-        <v>837</v>
       </c>
     </row>
     <row r="91" spans="1:8">
       <c r="A91" s="2" t="s">
+        <v>816</v>
+      </c>
+      <c r="B91" s="1" t="s">
         <v>817</v>
       </c>
-      <c r="B91" s="1" t="s">
+      <c r="E91" s="1" t="s">
         <v>818</v>
       </c>
-      <c r="E91" s="1" t="s">
+      <c r="F91" s="3">
+        <v>1</v>
+      </c>
+      <c r="H91" s="7" t="s">
         <v>819</v>
-      </c>
-      <c r="F91" s="3">
-        <v>1</v>
-      </c>
-      <c r="H91" s="7" t="s">
-        <v>820</v>
       </c>
     </row>
     <row r="92" spans="1:8">
@@ -6492,7 +6508,7 @@
       <c r="F92" s="3"/>
       <c r="G92" s="1"/>
       <c r="H92" s="1" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="93" spans="1:8">
@@ -6514,7 +6530,7 @@
       <c r="F93" s="3"/>
       <c r="G93" s="1"/>
       <c r="H93" s="1" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="94" spans="1:8">
@@ -6536,7 +6552,7 @@
       <c r="F94" s="3"/>
       <c r="G94" s="1"/>
       <c r="H94" s="1" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="95" spans="1:8">
@@ -6558,7 +6574,7 @@
       <c r="F95" s="3"/>
       <c r="G95" s="1"/>
       <c r="H95" s="1" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="96" spans="1:8">
@@ -6580,7 +6596,7 @@
       <c r="F96" s="3"/>
       <c r="G96" s="1"/>
       <c r="H96" s="1" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="97" spans="1:8">
@@ -6602,7 +6618,7 @@
       <c r="F97" s="3"/>
       <c r="G97" s="1"/>
       <c r="H97" s="1" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="98" spans="1:8">
@@ -6624,262 +6640,262 @@
       <c r="F98" s="3"/>
       <c r="G98" s="1"/>
       <c r="H98" s="1" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="99" spans="1:8">
       <c r="A99" s="2" t="s">
+        <v>724</v>
+      </c>
+      <c r="B99" s="1" t="s">
         <v>725</v>
       </c>
-      <c r="B99" s="1" t="s">
-        <v>726</v>
-      </c>
       <c r="E99" s="1" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="F99" s="3">
         <v>1</v>
       </c>
       <c r="H99" s="7" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
     </row>
     <row r="100" spans="1:8">
       <c r="A100" s="2" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="F100" s="3">
         <v>1</v>
       </c>
       <c r="H100" s="7" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
     </row>
     <row r="101" spans="1:8">
       <c r="A101" s="2" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="F101" s="3">
         <v>1</v>
       </c>
       <c r="H101" s="7" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
     </row>
     <row r="102" spans="1:8">
       <c r="A102" s="2" t="s">
+        <v>713</v>
+      </c>
+      <c r="B102" s="1" t="s">
         <v>714</v>
       </c>
-      <c r="B102" s="1" t="s">
-        <v>715</v>
-      </c>
       <c r="E102" s="1" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="F102" s="3">
         <v>1</v>
       </c>
       <c r="H102" s="7" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
     </row>
     <row r="103" spans="1:8">
       <c r="A103" s="2" t="s">
+        <v>711</v>
+      </c>
+      <c r="B103" s="1" t="s">
         <v>712</v>
       </c>
-      <c r="B103" s="1" t="s">
-        <v>713</v>
-      </c>
       <c r="E103" s="1" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="F103" s="3">
         <v>1</v>
       </c>
       <c r="H103" s="7" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
     </row>
     <row r="104" spans="1:8">
       <c r="A104" s="2" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="F104" s="3">
         <v>1</v>
       </c>
       <c r="H104" s="7" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
     </row>
     <row r="105" spans="1:8">
       <c r="A105" s="2" t="s">
+        <v>717</v>
+      </c>
+      <c r="B105" s="1" t="s">
         <v>718</v>
       </c>
-      <c r="B105" s="1" t="s">
-        <v>719</v>
-      </c>
       <c r="E105" s="1" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="F105" s="3">
         <v>1</v>
       </c>
       <c r="H105" s="7" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
     </row>
     <row r="106" spans="1:8">
       <c r="A106" s="2" t="s">
+        <v>721</v>
+      </c>
+      <c r="B106" s="1" t="s">
         <v>722</v>
       </c>
-      <c r="B106" s="1" t="s">
-        <v>723</v>
-      </c>
       <c r="E106" s="1" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="F106" s="3">
         <v>1</v>
       </c>
       <c r="H106" s="7" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
     </row>
     <row r="107" spans="1:8">
       <c r="A107" s="2" t="s">
+        <v>703</v>
+      </c>
+      <c r="B107" s="1" t="s">
         <v>704</v>
       </c>
-      <c r="B107" s="1" t="s">
-        <v>705</v>
-      </c>
       <c r="E107" s="1" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="F107" s="3">
         <v>1</v>
       </c>
       <c r="H107" s="7" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
     </row>
     <row r="108" spans="1:8">
       <c r="A108" s="2" t="s">
+        <v>726</v>
+      </c>
+      <c r="B108" s="1" t="s">
         <v>727</v>
       </c>
-      <c r="B108" s="1" t="s">
-        <v>728</v>
-      </c>
       <c r="E108" s="1" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="F108" s="3">
         <v>1</v>
       </c>
       <c r="H108" s="7" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
     </row>
     <row r="109" spans="1:8">
       <c r="A109" s="2" t="s">
+        <v>719</v>
+      </c>
+      <c r="B109" s="1" t="s">
         <v>720</v>
       </c>
-      <c r="B109" s="1" t="s">
-        <v>721</v>
-      </c>
       <c r="E109" s="1" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="F109" s="3">
         <v>1</v>
       </c>
       <c r="H109" s="7" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
     </row>
     <row r="110" spans="1:8">
       <c r="A110" s="2" t="s">
+        <v>699</v>
+      </c>
+      <c r="B110" s="1" t="s">
         <v>700</v>
       </c>
-      <c r="B110" s="1" t="s">
-        <v>701</v>
-      </c>
       <c r="E110" s="1" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="F110" s="3">
         <v>1</v>
       </c>
       <c r="H110" s="7" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
     </row>
     <row r="111" spans="1:8">
       <c r="A111" s="2" t="s">
+        <v>701</v>
+      </c>
+      <c r="B111" s="1" t="s">
         <v>702</v>
       </c>
-      <c r="B111" s="1" t="s">
-        <v>703</v>
-      </c>
       <c r="E111" s="1" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="F111" s="3">
         <v>1</v>
       </c>
       <c r="H111" s="7" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
     </row>
     <row r="112" spans="1:8">
       <c r="A112" s="2" t="s">
+        <v>705</v>
+      </c>
+      <c r="B112" s="1" t="s">
         <v>706</v>
       </c>
-      <c r="B112" s="1" t="s">
-        <v>707</v>
-      </c>
       <c r="E112" s="1" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="F112" s="3">
         <v>1</v>
       </c>
       <c r="H112" s="7" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
     </row>
     <row r="113" spans="1:8">
       <c r="A113" s="2" t="s">
+        <v>715</v>
+      </c>
+      <c r="B113" s="1" t="s">
         <v>716</v>
       </c>
-      <c r="B113" s="1" t="s">
-        <v>717</v>
-      </c>
       <c r="E113" s="1" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="F113" s="3">
         <v>1</v>
       </c>
       <c r="H113" s="7" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
     </row>
     <row r="114" spans="1:8">
@@ -6906,64 +6922,64 @@
     </row>
     <row r="115" spans="1:8">
       <c r="A115" t="s">
+        <v>837</v>
+      </c>
+      <c r="B115" t="s">
         <v>838</v>
-      </c>
-      <c r="B115" t="s">
-        <v>839</v>
       </c>
       <c r="C115" s="3"/>
       <c r="D115" s="4"/>
       <c r="E115" s="1" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="F115" s="3">
         <v>1</v>
       </c>
       <c r="G115" s="1"/>
       <c r="H115" s="11" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
     </row>
     <row r="116" spans="1:8">
       <c r="A116" t="s">
+        <v>841</v>
+      </c>
+      <c r="B116" t="s">
         <v>842</v>
-      </c>
-      <c r="B116" t="s">
-        <v>843</v>
       </c>
       <c r="C116" s="3"/>
       <c r="D116" s="4"/>
       <c r="E116" s="1" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="F116" s="3">
         <v>1</v>
       </c>
       <c r="G116" s="1"/>
       <c r="H116" s="11" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
     </row>
     <row r="117" spans="1:8">
       <c r="A117" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="B117" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="C117" s="3"/>
       <c r="D117" s="4"/>
       <c r="E117" s="1" t="s">
+        <v>846</v>
+      </c>
+      <c r="F117" s="3">
+        <v>1</v>
+      </c>
+      <c r="G117" s="1" t="s">
         <v>847</v>
       </c>
-      <c r="F117" s="3">
-        <v>1</v>
-      </c>
-      <c r="G117" s="1" t="s">
+      <c r="H117" s="11" t="s">
         <v>848</v>
-      </c>
-      <c r="H117" s="11" t="s">
-        <v>849</v>
       </c>
     </row>
     <row r="118" spans="1:8">
@@ -7007,12 +7023,12 @@
       <c r="F119" s="3"/>
       <c r="G119" s="1"/>
       <c r="H119" s="1" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
     </row>
     <row r="120" spans="1:8">
       <c r="A120" s="2" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="B120" s="1" t="s">
         <v>294</v>
@@ -7020,7 +7036,7 @@
       <c r="C120" s="1"/>
       <c r="D120" s="5"/>
       <c r="E120" s="1" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="F120" s="3">
         <v>1</v>
@@ -7032,19 +7048,19 @@
     </row>
     <row r="121" spans="1:8">
       <c r="A121" s="2" t="s">
+        <v>803</v>
+      </c>
+      <c r="B121" s="1" t="s">
         <v>804</v>
       </c>
-      <c r="B121" s="1" t="s">
+      <c r="E121" s="1" t="s">
+        <v>806</v>
+      </c>
+      <c r="F121" s="3">
+        <v>1</v>
+      </c>
+      <c r="H121" s="7" t="s">
         <v>805</v>
-      </c>
-      <c r="E121" s="1" t="s">
-        <v>807</v>
-      </c>
-      <c r="F121" s="3">
-        <v>1</v>
-      </c>
-      <c r="H121" s="7" t="s">
-        <v>806</v>
       </c>
     </row>
     <row r="122" spans="1:8">
@@ -7071,115 +7087,115 @@
     </row>
     <row r="123" spans="1:8">
       <c r="A123" t="s">
+        <v>849</v>
+      </c>
+      <c r="B123" t="s">
         <v>850</v>
-      </c>
-      <c r="B123" t="s">
-        <v>851</v>
       </c>
       <c r="C123"/>
       <c r="D123" s="11"/>
       <c r="E123" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="F123" s="1">
         <v>1</v>
       </c>
       <c r="G123"/>
       <c r="H123" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="124" spans="1:8">
       <c r="A124" t="s">
+        <v>851</v>
+      </c>
+      <c r="B124" t="s">
         <v>852</v>
       </c>
-      <c r="B124" t="s">
-        <v>853</v>
-      </c>
       <c r="E124" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="F124" s="1">
         <v>1</v>
       </c>
       <c r="H124" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
     </row>
     <row r="125" spans="1:8">
       <c r="A125" t="s">
+        <v>853</v>
+      </c>
+      <c r="B125" t="s">
         <v>854</v>
       </c>
-      <c r="B125" t="s">
-        <v>855</v>
-      </c>
       <c r="E125" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="F125" s="1">
         <v>1</v>
       </c>
       <c r="H125" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
     </row>
     <row r="126" spans="1:8">
       <c r="A126" t="s">
+        <v>855</v>
+      </c>
+      <c r="B126" t="s">
         <v>856</v>
       </c>
-      <c r="B126" t="s">
-        <v>857</v>
-      </c>
       <c r="E126" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="F126" s="1">
         <v>1</v>
       </c>
       <c r="H126" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
     </row>
     <row r="127" spans="1:8">
       <c r="A127" t="s">
+        <v>857</v>
+      </c>
+      <c r="B127" t="s">
         <v>858</v>
       </c>
-      <c r="B127" t="s">
-        <v>859</v>
-      </c>
       <c r="E127" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="F127" s="1">
         <v>1</v>
       </c>
       <c r="H127" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
     </row>
     <row r="128" spans="1:8">
       <c r="A128" t="s">
+        <v>859</v>
+      </c>
+      <c r="B128" t="s">
         <v>860</v>
       </c>
-      <c r="B128" t="s">
-        <v>861</v>
-      </c>
       <c r="E128" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="F128" s="1">
         <v>1</v>
       </c>
       <c r="H128" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
     </row>
     <row r="129" spans="1:8">
       <c r="A129" t="s">
+        <v>861</v>
+      </c>
+      <c r="B129" t="s">
         <v>862</v>
-      </c>
-      <c r="B129" t="s">
-        <v>863</v>
       </c>
       <c r="C129" s="2">
         <v>6</v>
@@ -7188,36 +7204,36 @@
         <v>0</v>
       </c>
       <c r="E129" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="F129" s="1"/>
       <c r="H129" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
     </row>
     <row r="130" spans="1:8">
       <c r="A130" t="s">
+        <v>863</v>
+      </c>
+      <c r="B130" t="s">
         <v>864</v>
       </c>
-      <c r="B130" t="s">
-        <v>865</v>
-      </c>
       <c r="E130" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="F130" s="1">
         <v>1</v>
       </c>
       <c r="H130" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
     </row>
     <row r="131" spans="1:8">
       <c r="A131" t="s">
+        <v>865</v>
+      </c>
+      <c r="B131" t="s">
         <v>866</v>
-      </c>
-      <c r="B131" t="s">
-        <v>867</v>
       </c>
       <c r="C131" s="2">
         <v>6</v>
@@ -7226,45 +7242,45 @@
         <v>0</v>
       </c>
       <c r="E131" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="F131" s="1"/>
       <c r="H131" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
     </row>
     <row r="132" spans="1:8">
       <c r="A132" t="s">
+        <v>867</v>
+      </c>
+      <c r="B132" t="s">
         <v>868</v>
       </c>
-      <c r="B132" t="s">
-        <v>869</v>
-      </c>
       <c r="E132" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="F132" s="1">
         <v>1</v>
       </c>
       <c r="H132" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
     </row>
     <row r="133" spans="1:8">
       <c r="A133" t="s">
+        <v>1056</v>
+      </c>
+      <c r="B133" t="s">
         <v>1057</v>
       </c>
-      <c r="B133" t="s">
+      <c r="E133" t="s">
         <v>1058</v>
       </c>
-      <c r="E133" t="s">
-        <v>1059</v>
-      </c>
       <c r="F133" s="1">
         <v>1</v>
       </c>
       <c r="H133" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
     </row>
     <row r="134" spans="1:8">
@@ -7330,7 +7346,7 @@
       <c r="F136" s="3"/>
       <c r="G136" s="1"/>
       <c r="H136" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
     </row>
     <row r="137" spans="1:8">
@@ -7418,7 +7434,7 @@
       <c r="F140" s="3"/>
       <c r="G140" s="1"/>
       <c r="H140" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
     </row>
     <row r="141" spans="1:8">
@@ -7448,7 +7464,7 @@
         <v>382</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="C142" s="3">
         <v>6</v>
@@ -7665,10 +7681,10 @@
     </row>
     <row r="152" spans="1:8">
       <c r="A152" s="11" t="s">
+        <v>881</v>
+      </c>
+      <c r="B152" s="11" t="s">
         <v>882</v>
-      </c>
-      <c r="B152" s="11" t="s">
-        <v>883</v>
       </c>
       <c r="C152">
         <v>14</v>
@@ -7680,495 +7696,495 @@
       <c r="F152"/>
       <c r="G152"/>
       <c r="H152" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
     </row>
     <row r="153" spans="1:8">
       <c r="A153" t="s">
+        <v>883</v>
+      </c>
+      <c r="B153" t="s">
         <v>884</v>
-      </c>
-      <c r="B153" t="s">
-        <v>885</v>
       </c>
       <c r="C153"/>
       <c r="D153"/>
       <c r="E153" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="F153">
         <v>1</v>
       </c>
       <c r="G153"/>
       <c r="H153" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
     </row>
     <row r="154" spans="1:8">
       <c r="A154" t="s">
+        <v>885</v>
+      </c>
+      <c r="B154" t="s">
         <v>886</v>
-      </c>
-      <c r="B154" t="s">
-        <v>887</v>
       </c>
       <c r="C154"/>
       <c r="D154"/>
       <c r="E154" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="F154">
         <v>1</v>
       </c>
       <c r="G154"/>
       <c r="H154" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
     </row>
     <row r="155" spans="1:8">
       <c r="A155" t="s">
+        <v>887</v>
+      </c>
+      <c r="B155" t="s">
         <v>888</v>
-      </c>
-      <c r="B155" t="s">
-        <v>889</v>
       </c>
       <c r="C155"/>
       <c r="D155"/>
       <c r="E155" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="F155">
         <v>1</v>
       </c>
       <c r="G155"/>
       <c r="H155" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
     </row>
     <row r="156" spans="1:8">
       <c r="A156" t="s">
+        <v>889</v>
+      </c>
+      <c r="B156" t="s">
         <v>890</v>
-      </c>
-      <c r="B156" t="s">
-        <v>891</v>
       </c>
       <c r="C156"/>
       <c r="D156"/>
       <c r="E156" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="F156">
         <v>1</v>
       </c>
       <c r="G156"/>
       <c r="H156" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
     </row>
     <row r="157" spans="1:8">
       <c r="A157" t="s">
+        <v>891</v>
+      </c>
+      <c r="B157" t="s">
         <v>892</v>
-      </c>
-      <c r="B157" t="s">
-        <v>893</v>
       </c>
       <c r="C157"/>
       <c r="D157"/>
       <c r="E157" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="F157">
         <v>1</v>
       </c>
       <c r="G157"/>
       <c r="H157" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
     </row>
     <row r="158" spans="1:8">
       <c r="A158" t="s">
+        <v>893</v>
+      </c>
+      <c r="B158" t="s">
         <v>894</v>
-      </c>
-      <c r="B158" t="s">
-        <v>895</v>
       </c>
       <c r="C158"/>
       <c r="D158"/>
       <c r="E158" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="F158">
         <v>1</v>
       </c>
       <c r="G158"/>
       <c r="H158" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
     </row>
     <row r="159" spans="1:8">
       <c r="A159" t="s">
+        <v>895</v>
+      </c>
+      <c r="B159" t="s">
         <v>896</v>
-      </c>
-      <c r="B159" t="s">
-        <v>897</v>
       </c>
       <c r="C159"/>
       <c r="D159"/>
       <c r="E159" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="F159">
         <v>1</v>
       </c>
       <c r="G159"/>
       <c r="H159" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
     </row>
     <row r="160" spans="1:8">
       <c r="A160" t="s">
+        <v>897</v>
+      </c>
+      <c r="B160" t="s">
         <v>898</v>
-      </c>
-      <c r="B160" t="s">
-        <v>899</v>
       </c>
       <c r="C160"/>
       <c r="D160"/>
       <c r="E160" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="F160">
         <v>1</v>
       </c>
       <c r="G160"/>
       <c r="H160" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
     </row>
     <row r="161" spans="1:8">
       <c r="A161" t="s">
+        <v>899</v>
+      </c>
+      <c r="B161" t="s">
         <v>900</v>
-      </c>
-      <c r="B161" t="s">
-        <v>901</v>
       </c>
       <c r="C161"/>
       <c r="D161"/>
       <c r="E161" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="F161">
         <v>1</v>
       </c>
       <c r="G161"/>
       <c r="H161" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
     </row>
     <row r="162" spans="1:8">
       <c r="A162" t="s">
+        <v>901</v>
+      </c>
+      <c r="B162" t="s">
         <v>902</v>
-      </c>
-      <c r="B162" t="s">
-        <v>903</v>
       </c>
       <c r="C162"/>
       <c r="D162"/>
       <c r="E162" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="F162">
         <v>1</v>
       </c>
       <c r="G162"/>
       <c r="H162" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
     </row>
     <row r="163" spans="1:8">
       <c r="A163" t="s">
+        <v>903</v>
+      </c>
+      <c r="B163" t="s">
         <v>904</v>
-      </c>
-      <c r="B163" t="s">
-        <v>905</v>
       </c>
       <c r="C163"/>
       <c r="D163"/>
       <c r="E163" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="F163">
         <v>1</v>
       </c>
       <c r="G163"/>
       <c r="H163" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
     </row>
     <row r="164" spans="1:8">
       <c r="A164" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="B164" s="12" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="C164"/>
       <c r="D164"/>
       <c r="E164" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="F164">
         <v>1</v>
       </c>
       <c r="G164"/>
       <c r="H164" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
     </row>
     <row r="165" spans="1:8">
       <c r="A165" t="s">
+        <v>906</v>
+      </c>
+      <c r="B165" t="s">
         <v>907</v>
-      </c>
-      <c r="B165" t="s">
-        <v>908</v>
       </c>
       <c r="C165"/>
       <c r="D165"/>
       <c r="E165" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="F165">
         <v>1</v>
       </c>
       <c r="G165"/>
       <c r="H165" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
     </row>
     <row r="166" spans="1:8">
       <c r="A166" t="s">
+        <v>908</v>
+      </c>
+      <c r="B166" t="s">
         <v>909</v>
-      </c>
-      <c r="B166" t="s">
-        <v>910</v>
       </c>
       <c r="C166"/>
       <c r="D166"/>
       <c r="E166" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="F166">
         <v>1</v>
       </c>
       <c r="G166"/>
       <c r="H166" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
     </row>
     <row r="167" spans="1:8">
       <c r="A167" t="s">
+        <v>910</v>
+      </c>
+      <c r="B167" t="s">
         <v>911</v>
-      </c>
-      <c r="B167" t="s">
-        <v>912</v>
       </c>
       <c r="C167"/>
       <c r="D167"/>
       <c r="E167" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="F167">
         <v>1</v>
       </c>
       <c r="G167"/>
       <c r="H167" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
     </row>
     <row r="168" spans="1:8">
       <c r="A168" t="s">
+        <v>912</v>
+      </c>
+      <c r="B168" t="s">
         <v>913</v>
-      </c>
-      <c r="B168" t="s">
-        <v>914</v>
       </c>
       <c r="C168"/>
       <c r="D168"/>
       <c r="E168" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="F168">
         <v>1</v>
       </c>
       <c r="G168"/>
       <c r="H168" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
     </row>
     <row r="169" spans="1:8">
       <c r="A169" t="s">
+        <v>914</v>
+      </c>
+      <c r="B169" t="s">
         <v>915</v>
-      </c>
-      <c r="B169" t="s">
-        <v>916</v>
       </c>
       <c r="C169"/>
       <c r="D169"/>
       <c r="E169" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="F169">
         <v>1</v>
       </c>
       <c r="G169"/>
       <c r="H169" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
     </row>
     <row r="170" spans="1:8">
       <c r="A170" t="s">
+        <v>916</v>
+      </c>
+      <c r="B170" t="s">
         <v>917</v>
-      </c>
-      <c r="B170" t="s">
-        <v>918</v>
       </c>
       <c r="C170"/>
       <c r="D170"/>
       <c r="E170" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="F170">
         <v>1</v>
       </c>
       <c r="G170"/>
       <c r="H170" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
     </row>
     <row r="171" spans="1:8">
       <c r="A171" t="s">
+        <v>918</v>
+      </c>
+      <c r="B171" t="s">
         <v>919</v>
-      </c>
-      <c r="B171" t="s">
-        <v>920</v>
       </c>
       <c r="C171"/>
       <c r="D171"/>
       <c r="E171" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="F171">
         <v>1</v>
       </c>
       <c r="G171"/>
       <c r="H171" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
     </row>
     <row r="172" spans="1:8">
       <c r="A172" t="s">
+        <v>920</v>
+      </c>
+      <c r="B172" t="s">
         <v>921</v>
-      </c>
-      <c r="B172" t="s">
-        <v>922</v>
       </c>
       <c r="C172"/>
       <c r="D172"/>
       <c r="E172" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="F172">
         <v>1</v>
       </c>
       <c r="G172"/>
       <c r="H172" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
     </row>
     <row r="173" spans="1:8">
       <c r="A173" t="s">
+        <v>922</v>
+      </c>
+      <c r="B173" t="s">
         <v>923</v>
-      </c>
-      <c r="B173" t="s">
-        <v>924</v>
       </c>
       <c r="C173"/>
       <c r="D173"/>
       <c r="E173" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="F173">
         <v>1</v>
       </c>
       <c r="G173"/>
       <c r="H173" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
     </row>
     <row r="174" spans="1:8">
       <c r="A174" t="s">
+        <v>924</v>
+      </c>
+      <c r="B174" t="s">
         <v>925</v>
-      </c>
-      <c r="B174" t="s">
-        <v>926</v>
       </c>
       <c r="C174"/>
       <c r="D174"/>
       <c r="E174" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="F174">
         <v>1</v>
       </c>
       <c r="G174"/>
       <c r="H174" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
     </row>
     <row r="175" spans="1:8">
       <c r="A175" t="s">
+        <v>926</v>
+      </c>
+      <c r="B175" t="s">
         <v>927</v>
-      </c>
-      <c r="B175" t="s">
-        <v>928</v>
       </c>
       <c r="C175"/>
       <c r="D175"/>
       <c r="E175" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="F175">
         <v>1</v>
       </c>
       <c r="G175"/>
       <c r="H175" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
     </row>
     <row r="176" spans="1:8">
       <c r="A176" t="s">
+        <v>928</v>
+      </c>
+      <c r="B176" t="s">
         <v>929</v>
-      </c>
-      <c r="B176" t="s">
-        <v>930</v>
       </c>
       <c r="C176"/>
       <c r="D176"/>
       <c r="E176" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="F176">
         <v>1</v>
       </c>
       <c r="G176"/>
       <c r="H176" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
     </row>
     <row r="177" spans="1:8">
       <c r="A177" t="s">
+        <v>930</v>
+      </c>
+      <c r="B177" t="s">
         <v>931</v>
-      </c>
-      <c r="B177" t="s">
-        <v>932</v>
       </c>
       <c r="C177">
         <v>14</v>
@@ -8177,100 +8193,100 @@
         <v>0</v>
       </c>
       <c r="E177" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F177"/>
       <c r="G177"/>
       <c r="H177" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
     </row>
     <row r="178" spans="1:8">
       <c r="A178" t="s">
+        <v>932</v>
+      </c>
+      <c r="B178" t="s">
         <v>933</v>
-      </c>
-      <c r="B178" t="s">
-        <v>934</v>
       </c>
       <c r="C178"/>
       <c r="D178"/>
       <c r="E178" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="F178">
         <v>1</v>
       </c>
       <c r="G178"/>
       <c r="H178" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
     </row>
     <row r="179" spans="1:8">
       <c r="A179" t="s">
+        <v>934</v>
+      </c>
+      <c r="B179" t="s">
         <v>935</v>
-      </c>
-      <c r="B179" t="s">
-        <v>936</v>
       </c>
       <c r="C179"/>
       <c r="D179"/>
       <c r="E179" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="F179">
         <v>1</v>
       </c>
       <c r="G179"/>
       <c r="H179" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
     </row>
     <row r="180" spans="1:8">
       <c r="A180" s="12" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="B180" s="12" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="C180"/>
       <c r="D180"/>
       <c r="E180" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="F180">
         <v>1</v>
       </c>
       <c r="G180"/>
       <c r="H180" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
     </row>
     <row r="181" spans="1:8">
       <c r="A181" t="s">
+        <v>937</v>
+      </c>
+      <c r="B181" t="s">
         <v>938</v>
-      </c>
-      <c r="B181" t="s">
-        <v>939</v>
       </c>
       <c r="C181"/>
       <c r="D181"/>
       <c r="E181" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="F181">
         <v>1</v>
       </c>
       <c r="G181"/>
       <c r="H181" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
     </row>
     <row r="182" spans="1:8">
       <c r="A182" t="s">
+        <v>939</v>
+      </c>
+      <c r="B182" t="s">
         <v>940</v>
-      </c>
-      <c r="B182" t="s">
-        <v>941</v>
       </c>
       <c r="C182">
         <v>14</v>
@@ -8279,152 +8295,152 @@
         <v>0</v>
       </c>
       <c r="E182" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="F182"/>
       <c r="G182"/>
       <c r="H182" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
     </row>
     <row r="183" spans="1:8">
       <c r="A183" t="s">
+        <v>941</v>
+      </c>
+      <c r="B183" t="s">
         <v>942</v>
-      </c>
-      <c r="B183" t="s">
-        <v>943</v>
       </c>
       <c r="C183"/>
       <c r="D183"/>
       <c r="E183" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="F183">
         <v>1</v>
       </c>
       <c r="G183"/>
       <c r="H183" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
     </row>
     <row r="184" spans="1:8">
       <c r="A184" t="s">
+        <v>943</v>
+      </c>
+      <c r="B184" t="s">
         <v>944</v>
-      </c>
-      <c r="B184" t="s">
-        <v>945</v>
       </c>
       <c r="C184"/>
       <c r="D184"/>
       <c r="E184" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="F184">
         <v>1</v>
       </c>
       <c r="G184"/>
       <c r="H184" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
     </row>
     <row r="185" spans="1:8">
       <c r="A185" t="s">
+        <v>945</v>
+      </c>
+      <c r="B185" t="s">
         <v>946</v>
-      </c>
-      <c r="B185" t="s">
-        <v>947</v>
       </c>
       <c r="C185"/>
       <c r="D185"/>
       <c r="E185" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="F185">
         <v>1</v>
       </c>
       <c r="G185"/>
       <c r="H185" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
     </row>
     <row r="186" spans="1:8">
       <c r="A186" t="s">
+        <v>947</v>
+      </c>
+      <c r="B186" t="s">
         <v>948</v>
-      </c>
-      <c r="B186" t="s">
-        <v>949</v>
       </c>
       <c r="C186"/>
       <c r="D186"/>
       <c r="E186" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="F186">
         <v>1</v>
       </c>
       <c r="G186"/>
       <c r="H186" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
     </row>
     <row r="187" spans="1:8">
       <c r="A187" t="s">
+        <v>949</v>
+      </c>
+      <c r="B187" t="s">
         <v>950</v>
-      </c>
-      <c r="B187" t="s">
-        <v>951</v>
       </c>
       <c r="C187"/>
       <c r="D187"/>
       <c r="E187" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="F187">
         <v>1</v>
       </c>
       <c r="G187"/>
       <c r="H187" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
     </row>
     <row r="188" spans="1:8">
       <c r="A188" t="s">
+        <v>951</v>
+      </c>
+      <c r="B188" t="s">
         <v>952</v>
-      </c>
-      <c r="B188" t="s">
-        <v>953</v>
       </c>
       <c r="C188"/>
       <c r="D188"/>
       <c r="E188" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="F188">
         <v>1</v>
       </c>
       <c r="G188"/>
       <c r="H188" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
     </row>
     <row r="189" spans="1:8">
       <c r="A189" t="s">
+        <v>1048</v>
+      </c>
+      <c r="B189" t="s">
         <v>1049</v>
-      </c>
-      <c r="B189" t="s">
-        <v>1050</v>
       </c>
       <c r="C189"/>
       <c r="D189"/>
       <c r="E189" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="F189">
         <v>1</v>
       </c>
       <c r="G189"/>
       <c r="H189" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
     </row>
     <row r="190" spans="1:8">
@@ -8446,7 +8462,7 @@
       <c r="F190" s="3"/>
       <c r="G190" s="1"/>
       <c r="H190" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
     </row>
     <row r="191" spans="1:8">
@@ -8495,67 +8511,67 @@
     </row>
     <row r="193" spans="1:8">
       <c r="A193" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B193" s="1" t="s">
         <v>505</v>
       </c>
       <c r="E193" s="1" t="s">
+        <v>761</v>
+      </c>
+      <c r="F193" s="2">
+        <v>1</v>
+      </c>
+      <c r="G193" s="2" t="s">
         <v>762</v>
       </c>
-      <c r="F193" s="2">
-        <v>1</v>
-      </c>
-      <c r="G193" s="2" t="s">
-        <v>763</v>
-      </c>
       <c r="H193" s="2" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="194" spans="1:8">
       <c r="A194" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B194" s="1" t="s">
         <v>506</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="F194" s="2">
         <v>1</v>
       </c>
       <c r="G194" s="2" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="H194" s="2" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
     </row>
     <row r="195" spans="1:8">
       <c r="A195" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B195" s="1" t="s">
         <v>506</v>
       </c>
       <c r="E195" s="1" t="s">
+        <v>764</v>
+      </c>
+      <c r="F195" s="2">
+        <v>1</v>
+      </c>
+      <c r="G195" s="2" t="s">
         <v>765</v>
       </c>
-      <c r="F195" s="2">
-        <v>1</v>
-      </c>
-      <c r="G195" s="2" t="s">
-        <v>766</v>
-      </c>
       <c r="H195" s="2" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
     </row>
     <row r="196" spans="1:8">
       <c r="A196" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="B196" s="1" t="s">
         <v>503</v>
@@ -8571,25 +8587,25 @@
       </c>
       <c r="F196" s="3"/>
       <c r="H196" s="2" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="197" spans="1:8">
       <c r="A197" s="2" t="s">
+        <v>807</v>
+      </c>
+      <c r="B197" s="1" t="s">
         <v>808</v>
-      </c>
-      <c r="B197" s="1" t="s">
-        <v>809</v>
       </c>
       <c r="D197" s="6"/>
       <c r="E197" s="1" t="s">
+        <v>809</v>
+      </c>
+      <c r="F197" s="3">
+        <v>1</v>
+      </c>
+      <c r="H197" s="7" t="s">
         <v>810</v>
-      </c>
-      <c r="F197" s="3">
-        <v>1</v>
-      </c>
-      <c r="H197" s="7" t="s">
-        <v>811</v>
       </c>
     </row>
     <row r="198" spans="1:8">
@@ -8616,7 +8632,7 @@
     </row>
     <row r="199" spans="1:8">
       <c r="A199" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="B199" s="1" t="s">
         <v>508</v>
@@ -8628,18 +8644,18 @@
         <v>0</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H199" s="2" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="200" spans="1:8">
       <c r="A200" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="C200" s="2">
         <v>10</v>
@@ -8648,38 +8664,38 @@
         <v>0</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H200" s="2" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="201" spans="1:8">
       <c r="A201" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="B201" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="C201"/>
       <c r="D201" s="11"/>
       <c r="E201" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="F201">
         <v>1</v>
       </c>
       <c r="G201"/>
       <c r="H201" s="11" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="202" spans="1:8">
       <c r="A202" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="B202" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="C202">
         <v>10</v>
@@ -8688,32 +8704,32 @@
         <v>0</v>
       </c>
       <c r="E202" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="F202"/>
       <c r="G202"/>
       <c r="H202" s="11" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="203" spans="1:8">
       <c r="A203" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="B203" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="C203"/>
       <c r="D203" s="11"/>
       <c r="E203" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="F203">
         <v>1</v>
       </c>
       <c r="G203"/>
       <c r="H203" s="11" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="204" spans="1:8">
@@ -8735,7 +8751,7 @@
       <c r="F204" s="3"/>
       <c r="G204" s="1"/>
       <c r="H204" s="1" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
     </row>
     <row r="205" spans="1:8">
@@ -8817,15 +8833,15 @@
         <v>1</v>
       </c>
       <c r="H208" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
     </row>
     <row r="209" spans="1:8">
       <c r="A209" t="s">
+        <v>992</v>
+      </c>
+      <c r="B209" t="s">
         <v>993</v>
-      </c>
-      <c r="B209" t="s">
-        <v>994</v>
       </c>
       <c r="C209">
         <v>15</v>
@@ -8834,20 +8850,20 @@
         <v>0</v>
       </c>
       <c r="E209" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="F209"/>
       <c r="G209"/>
       <c r="H209" s="11" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
     </row>
     <row r="210" spans="1:8">
       <c r="A210" t="s">
+        <v>996</v>
+      </c>
+      <c r="B210" t="s">
         <v>997</v>
-      </c>
-      <c r="B210" t="s">
-        <v>998</v>
       </c>
       <c r="C210">
         <v>15</v>
@@ -8856,20 +8872,20 @@
         <v>0</v>
       </c>
       <c r="E210" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="F210"/>
       <c r="G210"/>
       <c r="H210" s="11" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
     </row>
     <row r="211" spans="1:8">
       <c r="A211" t="s">
+        <v>1000</v>
+      </c>
+      <c r="B211" t="s">
         <v>1001</v>
-      </c>
-      <c r="B211" t="s">
-        <v>1002</v>
       </c>
       <c r="C211">
         <v>15</v>
@@ -8878,20 +8894,20 @@
         <v>0</v>
       </c>
       <c r="E211" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="F211"/>
       <c r="G211"/>
       <c r="H211" s="11" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="212" spans="1:8">
       <c r="A212" t="s">
+        <v>1004</v>
+      </c>
+      <c r="B212" t="s">
         <v>1005</v>
-      </c>
-      <c r="B212" t="s">
-        <v>1006</v>
       </c>
       <c r="C212">
         <v>20</v>
@@ -8900,20 +8916,20 @@
         <v>0</v>
       </c>
       <c r="E212" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="F212"/>
       <c r="G212"/>
       <c r="H212" s="11" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="213" spans="1:8">
       <c r="A213" t="s">
+        <v>1008</v>
+      </c>
+      <c r="B213" t="s">
         <v>1009</v>
-      </c>
-      <c r="B213" t="s">
-        <v>1010</v>
       </c>
       <c r="C213">
         <v>15</v>
@@ -8922,12 +8938,12 @@
         <v>0</v>
       </c>
       <c r="E213" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="F213"/>
       <c r="G213"/>
       <c r="H213" s="11" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="214" spans="1:8">
@@ -8946,7 +8962,7 @@
         <v>1</v>
       </c>
       <c r="G214" s="1" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="H214" s="2" t="s">
         <v>583</v>
@@ -8968,7 +8984,7 @@
         <v>1</v>
       </c>
       <c r="G215" s="1" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="H215" s="2" t="s">
         <v>583</v>
@@ -9037,7 +9053,7 @@
       <c r="F218" s="3"/>
       <c r="G218" s="1"/>
       <c r="H218" s="1" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="219" spans="1:8">
@@ -9054,7 +9070,7 @@
         <v>0</v>
       </c>
       <c r="E219" s="1" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="F219" s="3"/>
       <c r="G219" s="1"/>
@@ -9064,7 +9080,7 @@
     </row>
     <row r="220" spans="1:8">
       <c r="A220" s="2" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B220" s="1" t="s">
         <v>302</v>
@@ -9086,7 +9102,7 @@
     </row>
     <row r="221" spans="1:8">
       <c r="A221" s="2" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B221" s="1" t="s">
         <v>478</v>
@@ -9106,7 +9122,7 @@
     </row>
     <row r="222" spans="1:8">
       <c r="A222" s="2" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="B222" s="1" t="s">
         <v>291</v>
@@ -9126,7 +9142,7 @@
     </row>
     <row r="223" spans="1:8">
       <c r="A223" s="2" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B223" s="1" t="s">
         <v>292</v>
@@ -9158,7 +9174,7 @@
         <v>0</v>
       </c>
       <c r="E224" s="1" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="F224" s="3"/>
       <c r="G224" s="1"/>
@@ -9190,10 +9206,10 @@
     </row>
     <row r="226" spans="1:8">
       <c r="A226" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="B226" s="1" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="C226" s="2">
         <v>7</v>
@@ -9202,11 +9218,11 @@
         <v>0.95833333333333337</v>
       </c>
       <c r="E226" s="1" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="F226" s="3"/>
       <c r="H226" s="7" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
     </row>
     <row r="227" spans="1:8">
@@ -9227,8 +9243,8 @@
       </c>
       <c r="F227" s="3"/>
       <c r="G227" s="1"/>
-      <c r="H227" s="2" t="s">
-        <v>591</v>
+      <c r="H227" s="7" t="s">
+        <v>1194</v>
       </c>
     </row>
     <row r="228" spans="1:8">
@@ -9250,7 +9266,7 @@
       <c r="F228" s="3"/>
       <c r="G228" s="1"/>
       <c r="H228" s="2" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
     </row>
     <row r="229" spans="1:8">
@@ -9267,7 +9283,7 @@
         <v>1</v>
       </c>
       <c r="H229" s="1" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="230" spans="1:8">
@@ -9289,7 +9305,7 @@
       <c r="F230" s="3"/>
       <c r="G230" s="1"/>
       <c r="H230" s="2" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
     </row>
     <row r="231" spans="1:8">
@@ -9311,7 +9327,7 @@
       <c r="F231" s="3"/>
       <c r="G231" s="1"/>
       <c r="H231" s="2" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
     </row>
     <row r="232" spans="1:8">
@@ -9328,12 +9344,12 @@
         <v>0</v>
       </c>
       <c r="E232" s="1" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="F232" s="3"/>
       <c r="G232" s="1"/>
       <c r="H232" s="1" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
     </row>
     <row r="233" spans="1:8">
@@ -9355,7 +9371,7 @@
       <c r="F233" s="3"/>
       <c r="G233" s="1"/>
       <c r="H233" s="1" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
     </row>
     <row r="234" spans="1:8">
@@ -9377,15 +9393,15 @@
       <c r="F234" s="3"/>
       <c r="G234" s="1"/>
       <c r="H234" s="1" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
     </row>
     <row r="235" spans="1:8">
       <c r="A235" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B235" t="s">
         <v>1015</v>
-      </c>
-      <c r="B235" t="s">
-        <v>1016</v>
       </c>
       <c r="C235">
         <v>6</v>
@@ -9394,20 +9410,20 @@
         <v>0</v>
       </c>
       <c r="E235" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="F235"/>
       <c r="G235"/>
       <c r="H235" s="7" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="236" spans="1:8">
       <c r="A236" s="11" t="s">
+        <v>1018</v>
+      </c>
+      <c r="B236" t="s">
         <v>1019</v>
-      </c>
-      <c r="B236" t="s">
-        <v>1020</v>
       </c>
       <c r="C236" s="3">
         <v>7</v>
@@ -9416,12 +9432,12 @@
         <v>0.91666666666666663</v>
       </c>
       <c r="E236" s="1" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="F236"/>
       <c r="G236"/>
       <c r="H236" s="7" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="237" spans="1:8">
@@ -9443,7 +9459,7 @@
       <c r="F237" s="3"/>
       <c r="G237" s="1"/>
       <c r="H237" s="1" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
     </row>
     <row r="238" spans="1:8">
@@ -9465,27 +9481,27 @@
       <c r="F238" s="3"/>
       <c r="G238" s="1"/>
       <c r="H238" s="2" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
     </row>
     <row r="239" spans="1:8" customFormat="1">
       <c r="A239" s="2" t="s">
+        <v>799</v>
+      </c>
+      <c r="B239" s="1" t="s">
         <v>800</v>
-      </c>
-      <c r="B239" s="1" t="s">
-        <v>801</v>
       </c>
       <c r="C239" s="2"/>
       <c r="D239" s="2"/>
       <c r="E239" s="1" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="F239" s="3">
         <v>1</v>
       </c>
       <c r="G239" s="2"/>
       <c r="H239" s="7" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
     </row>
     <row r="240" spans="1:8">
@@ -9507,7 +9523,7 @@
       <c r="F240" s="3"/>
       <c r="G240" s="1"/>
       <c r="H240" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
     </row>
     <row r="241" spans="1:8">
@@ -9527,7 +9543,7 @@
       </c>
       <c r="G241" s="1"/>
       <c r="H241" s="1" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
     </row>
     <row r="242" spans="1:8">
@@ -9547,7 +9563,7 @@
       </c>
       <c r="G242" s="1"/>
       <c r="H242" s="1" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
     </row>
     <row r="243" spans="1:8">
@@ -9567,29 +9583,29 @@
       </c>
       <c r="G243" s="1"/>
       <c r="H243" s="1" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
     </row>
     <row r="244" spans="1:8">
       <c r="A244" s="11" t="s">
+        <v>1020</v>
+      </c>
+      <c r="B244" t="s">
         <v>1021</v>
-      </c>
-      <c r="B244" t="s">
-        <v>1022</v>
       </c>
       <c r="C244">
         <v>13</v>
       </c>
       <c r="D244" s="11" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="E244" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="F244"/>
       <c r="G244"/>
       <c r="H244" s="7" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="245" spans="1:8">
@@ -9606,46 +9622,46 @@
         <v>0.91666666666666663</v>
       </c>
       <c r="E245" s="1" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="F245" s="3"/>
       <c r="G245" s="1"/>
       <c r="H245" s="1" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="246" spans="1:8">
       <c r="A246" s="2" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B246" s="1" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="E246" s="1" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="F246" s="2">
         <v>1</v>
       </c>
       <c r="H246" s="2" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
     </row>
     <row r="247" spans="1:8">
       <c r="A247" s="2" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="B247" s="1" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="E247" s="1" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="F247" s="2">
         <v>1</v>
       </c>
       <c r="H247" s="2" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
     </row>
     <row r="248" spans="1:8">
@@ -9662,12 +9678,12 @@
         <v>0</v>
       </c>
       <c r="E248" s="1" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="F248" s="3"/>
       <c r="G248" s="1"/>
       <c r="H248" s="1" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="249" spans="1:8">
@@ -9684,12 +9700,12 @@
         <v>0</v>
       </c>
       <c r="E249" s="1" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="F249" s="3"/>
       <c r="G249" s="1"/>
       <c r="H249" s="1" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="250" spans="1:8">
@@ -9711,7 +9727,7 @@
       <c r="F250" s="3"/>
       <c r="G250" s="1"/>
       <c r="H250" s="2" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
     </row>
     <row r="251" spans="1:8">
@@ -9733,7 +9749,7 @@
       <c r="F251" s="3"/>
       <c r="G251" s="1"/>
       <c r="H251" s="2" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
     </row>
     <row r="252" spans="1:8">
@@ -9755,7 +9771,7 @@
       <c r="F252" s="3"/>
       <c r="G252" s="1"/>
       <c r="H252" s="2" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
     </row>
     <row r="253" spans="1:8">
@@ -9777,7 +9793,7 @@
       <c r="F253" s="3"/>
       <c r="G253" s="1"/>
       <c r="H253" s="2" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
     </row>
     <row r="254" spans="1:8">
@@ -9799,7 +9815,7 @@
       <c r="F254" s="3"/>
       <c r="G254" s="1"/>
       <c r="H254" s="2" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
     </row>
     <row r="255" spans="1:8">
@@ -9821,7 +9837,7 @@
       <c r="F255" s="3"/>
       <c r="G255" s="1"/>
       <c r="H255" s="2" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
     </row>
     <row r="256" spans="1:8">
@@ -9843,7 +9859,7 @@
       <c r="F256" s="3"/>
       <c r="G256" s="1"/>
       <c r="H256" s="2" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
     </row>
     <row r="257" spans="1:8">
@@ -9865,7 +9881,7 @@
       <c r="F257" s="3"/>
       <c r="G257" s="1"/>
       <c r="H257" s="2" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
     </row>
     <row r="258" spans="1:8">
@@ -9887,7 +9903,7 @@
       <c r="F258" s="3"/>
       <c r="G258" s="1"/>
       <c r="H258" s="2" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
     </row>
     <row r="259" spans="1:8">
@@ -9909,7 +9925,7 @@
       <c r="F259" s="3"/>
       <c r="G259" s="1"/>
       <c r="H259" s="2" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
     </row>
     <row r="260" spans="1:8">
@@ -9931,7 +9947,7 @@
       <c r="F260" s="3"/>
       <c r="G260" s="1"/>
       <c r="H260" s="2" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
     </row>
     <row r="261" spans="1:8">
@@ -9953,15 +9969,15 @@
       <c r="F261" s="3"/>
       <c r="G261" s="1"/>
       <c r="H261" s="2" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
     </row>
     <row r="262" spans="1:8">
       <c r="A262" s="2" t="s">
+        <v>691</v>
+      </c>
+      <c r="B262" s="1" t="s">
         <v>692</v>
-      </c>
-      <c r="B262" s="1" t="s">
-        <v>693</v>
       </c>
       <c r="C262" s="2">
         <v>6</v>
@@ -9970,11 +9986,11 @@
         <v>0</v>
       </c>
       <c r="E262" s="1" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="F262" s="3"/>
       <c r="H262" s="7" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
     </row>
     <row r="263" spans="1:8">
@@ -9995,7 +10011,7 @@
       </c>
       <c r="F263" s="3"/>
       <c r="H263" s="1" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
     </row>
     <row r="264" spans="1:8">
@@ -10017,7 +10033,7 @@
       <c r="F264" s="3"/>
       <c r="G264" s="1"/>
       <c r="H264" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
     </row>
     <row r="265" spans="1:8">
@@ -10039,15 +10055,15 @@
       <c r="F265" s="3"/>
       <c r="G265" s="1"/>
       <c r="H265" s="1" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="266" spans="1:8">
       <c r="A266" s="2" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="B266" s="1" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="C266" s="2">
         <v>6</v>
@@ -10056,19 +10072,19 @@
         <v>0</v>
       </c>
       <c r="E266" s="1" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="F266" s="3"/>
       <c r="H266" s="7" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="267" spans="1:8">
       <c r="A267" s="2" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="B267" s="1" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="C267" s="2">
         <v>6</v>
@@ -10077,19 +10093,19 @@
         <v>0</v>
       </c>
       <c r="E267" s="10" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="F267" s="3"/>
       <c r="H267" s="2" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
     </row>
     <row r="268" spans="1:8">
       <c r="A268" s="2" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="B268" s="1" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="C268" s="2">
         <v>6</v>
@@ -10098,19 +10114,19 @@
         <v>0</v>
       </c>
       <c r="E268" s="1" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="F268" s="3"/>
       <c r="H268" s="2" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
     </row>
     <row r="269" spans="1:8">
       <c r="A269" s="2" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="B269" s="1" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="C269" s="2">
         <v>6</v>
@@ -10119,16 +10135,16 @@
         <v>0</v>
       </c>
       <c r="E269" s="1" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="F269" s="3"/>
       <c r="H269" s="2" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
     </row>
     <row r="270" spans="1:8">
       <c r="A270" s="2" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="B270" s="1" t="s">
         <v>507</v>
@@ -10136,16 +10152,16 @@
       <c r="C270" s="3"/>
       <c r="D270" s="6"/>
       <c r="E270" s="1" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="F270" s="3">
         <v>1</v>
       </c>
       <c r="G270" s="2" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="H270" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
     </row>
     <row r="271" spans="1:8">
@@ -10167,7 +10183,7 @@
       <c r="F271" s="3"/>
       <c r="G271" s="1"/>
       <c r="H271" s="1" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="272" spans="1:8">
@@ -10189,7 +10205,7 @@
       <c r="F272" s="3"/>
       <c r="G272" s="1"/>
       <c r="H272" s="1" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="273" spans="1:8">
@@ -10211,7 +10227,7 @@
       <c r="F273" s="3"/>
       <c r="G273" s="1"/>
       <c r="H273" s="1" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="274" spans="1:8">
@@ -10228,12 +10244,12 @@
         <v>0.97916666666666663</v>
       </c>
       <c r="E274" s="1" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="F274" s="3"/>
       <c r="G274" s="1"/>
       <c r="H274" s="1" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
     <row r="275" spans="1:8">
@@ -10250,12 +10266,12 @@
         <v>0</v>
       </c>
       <c r="E275" s="1" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="F275" s="3"/>
       <c r="G275" s="1"/>
       <c r="H275" s="2" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="276" spans="1:8">
@@ -10277,7 +10293,7 @@
       <c r="F276" s="3"/>
       <c r="G276" s="1"/>
       <c r="H276" s="2" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="277" spans="1:8">
@@ -10299,7 +10315,7 @@
       <c r="F277" s="3"/>
       <c r="G277" s="1"/>
       <c r="H277" s="2" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="278" spans="1:8">
@@ -10321,7 +10337,7 @@
       <c r="F278" s="3"/>
       <c r="G278" s="1"/>
       <c r="H278" s="2" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="279" spans="1:8">
@@ -10329,7 +10345,7 @@
         <v>456</v>
       </c>
       <c r="B279" s="1" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="C279" s="3">
         <v>6</v>
@@ -10343,7 +10359,7 @@
       <c r="F279" s="3"/>
       <c r="G279" s="1"/>
       <c r="H279" s="2" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="280" spans="1:8">
@@ -10365,7 +10381,7 @@
       <c r="F280" s="3"/>
       <c r="G280" s="1"/>
       <c r="H280" s="2" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="281" spans="1:8">
@@ -10387,7 +10403,7 @@
       <c r="F281" s="3"/>
       <c r="G281" s="1"/>
       <c r="H281" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="282" spans="1:8">
@@ -10409,7 +10425,7 @@
       <c r="F282" s="3"/>
       <c r="G282" s="1"/>
       <c r="H282" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="283" spans="1:8">
@@ -10431,7 +10447,7 @@
       <c r="F283" s="3"/>
       <c r="G283" s="1"/>
       <c r="H283" s="1" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="284" spans="1:8">
@@ -10453,7 +10469,7 @@
       <c r="F284" s="3"/>
       <c r="G284" s="1"/>
       <c r="H284" s="1" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="285" spans="1:8">
@@ -10475,7 +10491,7 @@
       <c r="F285" s="3"/>
       <c r="G285" s="1"/>
       <c r="H285" s="1" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="286" spans="1:8">
@@ -10497,7 +10513,7 @@
       <c r="F286" s="3"/>
       <c r="G286" s="1"/>
       <c r="H286" s="1" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="287" spans="1:8">
@@ -10519,7 +10535,7 @@
       <c r="F287" s="3"/>
       <c r="G287" s="1"/>
       <c r="H287" s="1" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="288" spans="1:8">
@@ -10541,7 +10557,7 @@
       <c r="F288" s="3"/>
       <c r="G288" s="1"/>
       <c r="H288" s="8" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="289" spans="1:8">
@@ -10563,7 +10579,7 @@
       <c r="F289" s="3"/>
       <c r="G289" s="1"/>
       <c r="H289" s="1" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="290" spans="1:8">
@@ -10585,7 +10601,7 @@
       <c r="F290" s="3"/>
       <c r="G290" s="1"/>
       <c r="H290" s="1" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="291" spans="1:8">
@@ -10607,7 +10623,7 @@
       <c r="F291" s="3"/>
       <c r="G291" s="1"/>
       <c r="H291" s="1" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="292" spans="1:8">
@@ -10629,7 +10645,7 @@
       <c r="F292" s="3"/>
       <c r="G292" s="1"/>
       <c r="H292" s="1" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="293" spans="1:8" customFormat="1">
@@ -10651,7 +10667,7 @@
       <c r="F293" s="3"/>
       <c r="G293" s="1"/>
       <c r="H293" s="1" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="294" spans="1:8" customFormat="1">
@@ -10673,7 +10689,7 @@
       <c r="F294" s="3"/>
       <c r="G294" s="1"/>
       <c r="H294" s="1" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="295" spans="1:8" customFormat="1">
@@ -10695,7 +10711,7 @@
       <c r="F295" s="3"/>
       <c r="G295" s="1"/>
       <c r="H295" s="1" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="296" spans="1:8" customFormat="1">
@@ -10715,134 +10731,134 @@
       </c>
       <c r="G296" s="1"/>
       <c r="H296" s="1" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="297" spans="1:8">
       <c r="A297" t="s">
+        <v>1039</v>
+      </c>
+      <c r="B297" s="1" t="s">
         <v>1040</v>
       </c>
-      <c r="B297" s="1" t="s">
-        <v>1041</v>
-      </c>
       <c r="E297" s="1" t="s">
+        <v>1044</v>
+      </c>
+      <c r="F297" s="2">
+        <v>1</v>
+      </c>
+      <c r="H297" s="7" t="s">
         <v>1045</v>
-      </c>
-      <c r="F297" s="2">
-        <v>1</v>
-      </c>
-      <c r="H297" s="7" t="s">
-        <v>1046</v>
       </c>
     </row>
     <row r="298" spans="1:8">
       <c r="A298" s="2" t="s">
+        <v>1059</v>
+      </c>
+      <c r="B298" s="1" t="s">
         <v>1060</v>
       </c>
-      <c r="B298" s="1" t="s">
+      <c r="E298" s="1" t="s">
         <v>1061</v>
       </c>
-      <c r="E298" s="1" t="s">
+      <c r="F298" s="2">
+        <v>1</v>
+      </c>
+      <c r="H298" s="2" t="s">
         <v>1062</v>
-      </c>
-      <c r="F298" s="2">
-        <v>1</v>
-      </c>
-      <c r="H298" s="2" t="s">
-        <v>1063</v>
       </c>
     </row>
     <row r="299" spans="1:8">
       <c r="A299" s="2" t="s">
+        <v>1064</v>
+      </c>
+      <c r="B299" s="1" t="s">
+        <v>1063</v>
+      </c>
+      <c r="E299" s="1" t="s">
+        <v>1066</v>
+      </c>
+      <c r="F299" s="2">
+        <v>1</v>
+      </c>
+      <c r="H299" s="7" t="s">
         <v>1065</v>
-      </c>
-      <c r="B299" s="1" t="s">
-        <v>1064</v>
-      </c>
-      <c r="E299" s="1" t="s">
-        <v>1067</v>
-      </c>
-      <c r="F299" s="2">
-        <v>1</v>
-      </c>
-      <c r="H299" s="7" t="s">
-        <v>1066</v>
       </c>
     </row>
     <row r="300" spans="1:8">
       <c r="A300" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="B300" s="1" t="s">
+        <v>1067</v>
+      </c>
+      <c r="E300" s="1" t="s">
         <v>1068</v>
       </c>
-      <c r="E300" s="1" t="s">
+      <c r="F300" s="2">
+        <v>1</v>
+      </c>
+      <c r="H300" s="2" t="s">
         <v>1069</v>
-      </c>
-      <c r="F300" s="2">
-        <v>1</v>
-      </c>
-      <c r="H300" s="2" t="s">
-        <v>1070</v>
       </c>
     </row>
     <row r="301" spans="1:8">
       <c r="A301" s="2" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="B301" s="1" t="s">
+        <v>1070</v>
+      </c>
+      <c r="E301" s="1" t="s">
         <v>1071</v>
       </c>
-      <c r="E301" s="1" t="s">
-        <v>1072</v>
-      </c>
       <c r="F301" s="2">
         <v>1</v>
       </c>
       <c r="H301" s="2" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="302" spans="1:8">
       <c r="A302" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="B302" s="1" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="E302" s="1" t="s">
+        <v>1076</v>
+      </c>
+      <c r="F302" s="2">
+        <v>1</v>
+      </c>
+      <c r="H302" s="2" t="s">
         <v>1077</v>
-      </c>
-      <c r="F302" s="2">
-        <v>1</v>
-      </c>
-      <c r="H302" s="2" t="s">
-        <v>1078</v>
       </c>
     </row>
     <row r="303" spans="1:8">
       <c r="A303" s="2" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="B303" s="1" t="s">
+        <v>1079</v>
+      </c>
+      <c r="E303" s="1" t="s">
         <v>1080</v>
       </c>
-      <c r="E303" s="1" t="s">
-        <v>1081</v>
-      </c>
       <c r="F303" s="2">
         <v>1</v>
       </c>
       <c r="H303" s="7" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="304" spans="1:8">
       <c r="A304" s="2" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="B304" s="1" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="C304" s="2">
         <v>6</v>
@@ -10851,66 +10867,66 @@
         <v>0</v>
       </c>
       <c r="E304" s="1" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H304" s="7" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="305" spans="1:8">
       <c r="A305" s="2" t="s">
+        <v>1086</v>
+      </c>
+      <c r="B305" s="1" t="s">
         <v>1087</v>
       </c>
-      <c r="B305" s="1" t="s">
-        <v>1088</v>
-      </c>
       <c r="E305" s="1" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="H305" s="7" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="306" spans="1:8">
       <c r="A306" s="2" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="B306" s="1" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="E306" s="1" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="F306" s="2">
         <v>1</v>
       </c>
       <c r="H306" s="2" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="307" spans="1:8">
       <c r="A307" s="2" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="B307" s="1" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="E307" s="1" t="s">
+        <v>1142</v>
+      </c>
+      <c r="F307" s="2">
+        <v>1</v>
+      </c>
+      <c r="H307" s="2" t="s">
         <v>1143</v>
-      </c>
-      <c r="F307" s="2">
-        <v>1</v>
-      </c>
-      <c r="H307" s="2" t="s">
-        <v>1144</v>
       </c>
     </row>
     <row r="308" spans="1:8">
       <c r="A308" s="2" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="B308" s="1" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="C308" s="2">
         <v>14</v>
@@ -10919,18 +10935,18 @@
         <v>0</v>
       </c>
       <c r="E308" s="1" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="H308" s="2" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="309" spans="1:8">
       <c r="A309" s="2" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="B309" s="1" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="C309" s="2">
         <v>6</v>
@@ -10939,23 +10955,23 @@
         <v>0</v>
       </c>
       <c r="E309" s="1" t="s">
+        <v>1158</v>
+      </c>
+      <c r="H309" s="2" t="s">
         <v>1159</v>
-      </c>
-      <c r="H309" s="2" t="s">
-        <v>1160</v>
       </c>
     </row>
     <row r="310" spans="1:8">
       <c r="B310" s="1" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="311" spans="1:8">
       <c r="A311" s="2" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="B311" s="1" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="C311" s="2">
         <v>14</v>
@@ -10964,125 +10980,125 @@
         <v>0</v>
       </c>
       <c r="E311" s="2" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="H311" s="2" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="312" spans="1:8">
       <c r="A312" s="2" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B312" s="1" t="s">
+        <v>1095</v>
+      </c>
+      <c r="E312" s="2" t="s">
+        <v>1169</v>
+      </c>
+      <c r="F312" s="2">
+        <v>1</v>
+      </c>
+      <c r="H312" s="2" t="s">
         <v>1168</v>
-      </c>
-      <c r="B312" s="1" t="s">
-        <v>1096</v>
-      </c>
-      <c r="E312" s="2" t="s">
-        <v>1170</v>
-      </c>
-      <c r="F312" s="2">
-        <v>1</v>
-      </c>
-      <c r="H312" s="2" t="s">
-        <v>1169</v>
       </c>
     </row>
     <row r="313" spans="1:8">
       <c r="A313" s="2" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="B313" s="1" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="E313" s="2" t="s">
+        <v>1182</v>
+      </c>
+      <c r="F313" s="2">
+        <v>1</v>
+      </c>
+      <c r="H313" s="7" t="s">
         <v>1183</v>
-      </c>
-      <c r="F313" s="2">
-        <v>1</v>
-      </c>
-      <c r="H313" s="7" t="s">
-        <v>1184</v>
       </c>
     </row>
     <row r="314" spans="1:8">
       <c r="A314" s="2" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="B314" s="1" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="E314" s="2" t="s">
+        <v>1189</v>
+      </c>
+      <c r="F314" s="2">
+        <v>1</v>
+      </c>
+      <c r="H314" s="7" t="s">
         <v>1190</v>
-      </c>
-      <c r="F314" s="2">
-        <v>1</v>
-      </c>
-      <c r="H314" s="7" t="s">
-        <v>1191</v>
       </c>
     </row>
     <row r="315" spans="1:8">
       <c r="B315" s="1" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="316" spans="1:8">
       <c r="A316" s="2" t="s">
+        <v>1176</v>
+      </c>
+      <c r="B316" s="1" t="s">
+        <v>1099</v>
+      </c>
+      <c r="E316" s="2" t="s">
         <v>1177</v>
       </c>
-      <c r="B316" s="1" t="s">
-        <v>1100</v>
-      </c>
-      <c r="E316" s="2" t="s">
+      <c r="F316" s="2">
+        <v>1</v>
+      </c>
+      <c r="H316" s="7" t="s">
         <v>1178</v>
-      </c>
-      <c r="F316" s="2">
-        <v>1</v>
-      </c>
-      <c r="H316" s="7" t="s">
-        <v>1179</v>
       </c>
     </row>
     <row r="317" spans="1:8">
       <c r="A317" s="2" t="s">
+        <v>1170</v>
+      </c>
+      <c r="B317" s="1" t="s">
+        <v>1100</v>
+      </c>
+      <c r="E317" s="2" t="s">
         <v>1171</v>
       </c>
-      <c r="B317" s="1" t="s">
-        <v>1101</v>
-      </c>
-      <c r="E317" s="2" t="s">
+      <c r="F317" s="2">
+        <v>1</v>
+      </c>
+      <c r="H317" s="2" t="s">
         <v>1172</v>
-      </c>
-      <c r="F317" s="2">
-        <v>1</v>
-      </c>
-      <c r="H317" s="2" t="s">
-        <v>1173</v>
       </c>
     </row>
     <row r="318" spans="1:8">
       <c r="A318" s="2" t="s">
+        <v>1173</v>
+      </c>
+      <c r="B318" s="1" t="s">
+        <v>1101</v>
+      </c>
+      <c r="E318" s="2" t="s">
+        <v>1175</v>
+      </c>
+      <c r="F318" s="2">
+        <v>1</v>
+      </c>
+      <c r="H318" s="2" t="s">
         <v>1174</v>
-      </c>
-      <c r="B318" s="1" t="s">
-        <v>1102</v>
-      </c>
-      <c r="E318" s="2" t="s">
-        <v>1176</v>
-      </c>
-      <c r="F318" s="2">
-        <v>1</v>
-      </c>
-      <c r="H318" s="2" t="s">
-        <v>1175</v>
       </c>
     </row>
     <row r="319" spans="1:8">
       <c r="A319" s="2" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="B319" s="1" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="C319" s="2">
         <v>6</v>
@@ -11091,171 +11107,174 @@
         <v>0</v>
       </c>
       <c r="E319" s="2" t="s">
-        <v>1182</v>
+        <v>1181</v>
+      </c>
+      <c r="H319" s="2" t="s">
+        <v>1193</v>
       </c>
     </row>
     <row r="320" spans="1:8">
       <c r="A320" s="2" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="B320" s="1" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="E320" s="2" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="F320" s="2">
         <v>1</v>
       </c>
       <c r="H320" s="2" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="321" spans="1:8">
       <c r="A321" s="2" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="B321" s="1" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="E321" s="2" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="F321" s="2">
         <v>1</v>
       </c>
       <c r="H321" s="2" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="322" spans="1:8">
       <c r="A322" s="2" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="B322" s="1" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="E322" s="2" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="F322" s="2">
         <v>1</v>
       </c>
       <c r="H322" s="2" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="323" spans="1:8">
       <c r="A323" s="2" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="B323" s="1" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="E323" s="2" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="F323" s="2">
         <v>1</v>
       </c>
       <c r="H323" s="2" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="324" spans="1:8">
       <c r="A324" s="2" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="B324" s="1" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="E324" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="F324" s="2">
+        <v>1</v>
+      </c>
+      <c r="H324" s="2" t="s">
         <v>1117</v>
-      </c>
-      <c r="F324" s="2">
-        <v>1</v>
-      </c>
-      <c r="H324" s="2" t="s">
-        <v>1118</v>
       </c>
     </row>
     <row r="325" spans="1:8">
       <c r="A325" s="2" t="s">
+        <v>1125</v>
+      </c>
+      <c r="B325" s="1" t="s">
         <v>1126</v>
       </c>
-      <c r="B325" s="1" t="s">
+      <c r="E325" t="s">
         <v>1127</v>
       </c>
-      <c r="E325" t="s">
+      <c r="F325" s="2">
+        <v>1</v>
+      </c>
+      <c r="G325" s="2" t="s">
+        <v>1138</v>
+      </c>
+      <c r="H325" s="7" t="s">
         <v>1128</v>
-      </c>
-      <c r="F325" s="2">
-        <v>1</v>
-      </c>
-      <c r="G325" s="2" t="s">
-        <v>1139</v>
-      </c>
-      <c r="H325" s="7" t="s">
-        <v>1129</v>
       </c>
     </row>
     <row r="326" spans="1:8">
       <c r="A326" s="2" t="s">
+        <v>1144</v>
+      </c>
+      <c r="B326" s="1" t="s">
         <v>1145</v>
       </c>
-      <c r="B326" s="1" t="s">
-        <v>1146</v>
-      </c>
       <c r="E326" s="2" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="F326" s="2">
         <v>1</v>
       </c>
       <c r="H326" s="2" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="327" spans="1:8">
       <c r="A327" s="2" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="B327" s="1" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="E327" s="2" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="F327" s="2">
         <v>1</v>
       </c>
       <c r="H327" s="2" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="328" spans="1:8">
       <c r="A328" s="2" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="B328" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="E328" s="2" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="F328" s="2">
         <v>1</v>
       </c>
       <c r="H328" s="2" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="329" spans="1:8">
       <c r="A329" s="2" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="B329" s="1" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="C329" s="2">
         <v>14</v>
@@ -11264,18 +11283,18 @@
         <v>0</v>
       </c>
       <c r="E329" s="2" t="s">
+        <v>1155</v>
+      </c>
+      <c r="H329" s="2" t="s">
         <v>1156</v>
-      </c>
-      <c r="H329" s="2" t="s">
-        <v>1157</v>
       </c>
     </row>
     <row r="330" spans="1:8">
       <c r="A330" s="2" t="s">
+        <v>1163</v>
+      </c>
+      <c r="B330" s="1" t="s">
         <v>1164</v>
-      </c>
-      <c r="B330" s="1" t="s">
-        <v>1165</v>
       </c>
       <c r="C330" s="2">
         <v>12</v>
@@ -11284,10 +11303,27 @@
         <v>0</v>
       </c>
       <c r="E330" s="2" t="s">
+        <v>1165</v>
+      </c>
+      <c r="H330" s="7" t="s">
         <v>1166</v>
       </c>
-      <c r="H330" s="7" t="s">
-        <v>1167</v>
+    </row>
+    <row r="331" spans="1:8">
+      <c r="A331" s="2" t="s">
+        <v>1191</v>
+      </c>
+      <c r="B331" s="1" t="s">
+        <v>1192</v>
+      </c>
+      <c r="E331" s="2" t="s">
+        <v>1195</v>
+      </c>
+      <c r="F331" s="2">
+        <v>1</v>
+      </c>
+      <c r="H331" t="s">
+        <v>954</v>
       </c>
     </row>
   </sheetData>
@@ -11323,8 +11359,9 @@
     <hyperlink ref="H316" r:id="rId25" xr:uid="{0A71BEFF-E769-421A-8079-F0AC7ECC9FE2}"/>
     <hyperlink ref="H313" r:id="rId26" xr:uid="{F2A9379F-C93A-48C6-B140-FD9A9AACF5E0}"/>
     <hyperlink ref="H314" r:id="rId27" xr:uid="{E90FCA6A-2CCD-4405-8CD0-447FE361C93D}"/>
+    <hyperlink ref="H227" r:id="rId28" xr:uid="{672E3111-F001-48E9-B557-648E8ECCC539}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId28"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId29"/>
 </worksheet>
 </file>
--- a/stores.xlsx
+++ b/stores.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\YUMIN\Desktop\B0KT2A_RSVN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD7AE3B3-4EB4-4E72-8FA9-351497FFEC63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D6CA7BA-E5BD-480E-8EFE-14C766AAEE6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{ABFC3117-FCCB-4FF3-804A-FE19451A2004}"/>
   </bookViews>
@@ -16,6 +16,7 @@
     <sheet name="stores" sheetId="2" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -2187,10 +2188,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>다이얼</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>https://play33.kr/</t>
   </si>
   <si>
@@ -2923,10 +2920,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>강천여자고등학교,강천여고</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>33_hd</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -3015,9 +3008,6 @@
   </si>
   <si>
     <t>브레이크아웃 이스케이프 홍대점</t>
-  </si>
-  <si>
-    <t>sg_hd</t>
   </si>
   <si>
     <t>비밀의 숲 홍대점</t>
@@ -4187,6 +4177,18 @@
   </si>
   <si>
     <t>madeon,xiamen,houndred,crack,월간오컬트:폐간호,귀가,마데온,샤먼,하운드레드,크랙</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sfr_hd</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>다이얼,그날,목격자</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>강천여자고등학교,강천여고,자각몽</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -4655,7 +4657,7 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="2" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>631</v>
@@ -4667,18 +4669,18 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="E2" s="2" t="s">
+        <v>1194</v>
+      </c>
+      <c r="H2" s="2" t="s">
         <v>632</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>633</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="2" t="s">
+        <v>820</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>821</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>822</v>
       </c>
       <c r="C3" s="2">
         <v>7</v>
@@ -4687,27 +4689,25 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>823</v>
+        <v>1195</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="2" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="C4" s="2">
         <v>7</v>
       </c>
-      <c r="D4" s="6">
-        <v>0.83333333333333337</v>
-      </c>
+      <c r="D4" s="6"/>
       <c r="H4" s="2" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -4834,7 +4834,7 @@
         <v>1</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>1133</v>
+        <v>1130</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>516</v>
@@ -4856,7 +4856,7 @@
         <v>1</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>1133</v>
+        <v>1130</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>517</v>
@@ -4969,7 +4969,7 @@
       <c r="F16" s="3"/>
       <c r="G16" s="1"/>
       <c r="H16" s="7" t="s">
-        <v>1038</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -4986,7 +4986,7 @@
         <v>0</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>1129</v>
+        <v>1126</v>
       </c>
       <c r="F17" s="3"/>
       <c r="G17" s="1"/>
@@ -5148,10 +5148,10 @@
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="2" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="C25" s="3">
         <v>15</v>
@@ -5160,12 +5160,12 @@
         <v>0</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="F25" s="3"/>
       <c r="G25" s="1"/>
       <c r="H25" s="11" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -5256,27 +5256,27 @@
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="2" t="s">
+        <v>783</v>
+      </c>
+      <c r="B30" s="1" t="s">
         <v>784</v>
       </c>
-      <c r="B30" s="1" t="s">
+      <c r="E30" s="1" t="s">
         <v>785</v>
       </c>
-      <c r="E30" s="1" t="s">
-        <v>786</v>
-      </c>
       <c r="F30" s="3">
         <v>1</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="2" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="C31" s="2">
         <v>20</v>
@@ -5285,112 +5285,112 @@
         <v>0</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="2" t="s">
+        <v>770</v>
+      </c>
+      <c r="B32" s="1" t="s">
         <v>771</v>
       </c>
-      <c r="B32" s="1" t="s">
+      <c r="E32" s="1" t="s">
         <v>772</v>
       </c>
-      <c r="E32" s="1" t="s">
-        <v>773</v>
-      </c>
       <c r="F32" s="3">
         <v>1</v>
       </c>
       <c r="H32" s="7" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="2" t="s">
+        <v>766</v>
+      </c>
+      <c r="B33" s="1" t="s">
         <v>767</v>
       </c>
-      <c r="B33" s="1" t="s">
+      <c r="E33" s="1" t="s">
         <v>768</v>
       </c>
-      <c r="E33" s="1" t="s">
+      <c r="F33" s="3">
+        <v>1</v>
+      </c>
+      <c r="H33" s="2" t="s">
         <v>769</v>
-      </c>
-      <c r="F33" s="3">
-        <v>1</v>
-      </c>
-      <c r="H33" s="2" t="s">
-        <v>770</v>
       </c>
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="2" t="s">
+        <v>777</v>
+      </c>
+      <c r="B34" s="1" t="s">
         <v>778</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="E34" s="1" t="s">
+        <v>781</v>
+      </c>
+      <c r="F34" s="3">
+        <v>1</v>
+      </c>
+      <c r="H34" s="2" t="s">
         <v>779</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>782</v>
-      </c>
-      <c r="F34" s="3">
-        <v>1</v>
-      </c>
-      <c r="H34" s="2" t="s">
-        <v>780</v>
       </c>
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="2" t="s">
+        <v>791</v>
+      </c>
+      <c r="B35" s="1" t="s">
         <v>792</v>
       </c>
-      <c r="B35" s="1" t="s">
+      <c r="E35" s="1" t="s">
         <v>793</v>
       </c>
-      <c r="E35" s="1" t="s">
-        <v>794</v>
-      </c>
       <c r="F35" s="3">
         <v>1</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
     </row>
     <row r="36" spans="1:8">
       <c r="A36" s="2" t="s">
+        <v>787</v>
+      </c>
+      <c r="B36" s="1" t="s">
         <v>788</v>
       </c>
-      <c r="B36" s="1" t="s">
+      <c r="E36" s="1" t="s">
         <v>789</v>
       </c>
-      <c r="E36" s="1" t="s">
-        <v>790</v>
-      </c>
       <c r="F36" s="3">
         <v>1</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
     </row>
     <row r="37" spans="1:8">
       <c r="A37" s="2" t="s">
+        <v>774</v>
+      </c>
+      <c r="B37" s="1" t="s">
         <v>775</v>
       </c>
-      <c r="B37" s="1" t="s">
+      <c r="E37" s="1" t="s">
         <v>776</v>
       </c>
-      <c r="E37" s="1" t="s">
-        <v>777</v>
-      </c>
       <c r="F37" s="3">
         <v>1</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -5417,36 +5417,36 @@
     </row>
     <row r="39" spans="1:8">
       <c r="A39" s="2" t="s">
+        <v>682</v>
+      </c>
+      <c r="B39" s="1" t="s">
         <v>683</v>
       </c>
-      <c r="B39" s="1" t="s">
-        <v>684</v>
-      </c>
       <c r="E39" s="1" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="F39" s="3">
         <v>1</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="40" spans="1:8">
       <c r="A40" s="2" t="s">
+        <v>684</v>
+      </c>
+      <c r="B40" s="1" t="s">
         <v>685</v>
       </c>
-      <c r="B40" s="1" t="s">
-        <v>686</v>
-      </c>
       <c r="E40" s="1" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="F40" s="3">
         <v>1</v>
       </c>
       <c r="H40" s="9" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -5781,7 +5781,7 @@
         <v>1</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>1134</v>
+        <v>1131</v>
       </c>
       <c r="H56" s="2" t="s">
         <v>544</v>
@@ -5789,13 +5789,13 @@
     </row>
     <row r="57" spans="1:8">
       <c r="A57" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="F57" s="2">
         <v>1</v>
@@ -5803,41 +5803,41 @@
     </row>
     <row r="58" spans="1:8">
       <c r="A58" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="F58" s="3">
         <v>1</v>
       </c>
       <c r="H58" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
     </row>
     <row r="59" spans="1:8">
       <c r="A59" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="C59" s="3"/>
       <c r="D59" s="6"/>
       <c r="E59" s="1" t="s">
+        <v>640</v>
+      </c>
+      <c r="F59" s="3">
+        <v>1</v>
+      </c>
+      <c r="G59" s="1" t="s">
+        <v>1157</v>
+      </c>
+      <c r="H59" t="s">
         <v>641</v>
-      </c>
-      <c r="F59" s="3">
-        <v>1</v>
-      </c>
-      <c r="G59" s="1" t="s">
-        <v>1160</v>
-      </c>
-      <c r="H59" t="s">
-        <v>642</v>
       </c>
     </row>
     <row r="60" spans="1:8">
@@ -5864,10 +5864,10 @@
     </row>
     <row r="61" spans="1:8">
       <c r="A61" s="11" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="B61" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="C61">
         <v>6</v>
@@ -5876,7 +5876,7 @@
         <v>0</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="F61" s="3"/>
       <c r="G61" s="1"/>
@@ -6059,7 +6059,7 @@
     </row>
     <row r="70" spans="1:8">
       <c r="A70" s="2" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>181</v>
@@ -6078,7 +6078,7 @@
     </row>
     <row r="71" spans="1:8">
       <c r="A71" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>261</v>
@@ -6097,7 +6097,7 @@
     </row>
     <row r="72" spans="1:8">
       <c r="A72" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>179</v>
@@ -6116,7 +6116,7 @@
     </row>
     <row r="73" spans="1:8">
       <c r="A73" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>185</v>
@@ -6137,7 +6137,7 @@
     </row>
     <row r="74" spans="1:8">
       <c r="A74" s="2" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>183</v>
@@ -6158,7 +6158,7 @@
     </row>
     <row r="75" spans="1:8">
       <c r="A75" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>171</v>
@@ -6177,7 +6177,7 @@
     </row>
     <row r="76" spans="1:8">
       <c r="A76" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>173</v>
@@ -6215,7 +6215,7 @@
     </row>
     <row r="78" spans="1:8">
       <c r="A78" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>187</v>
@@ -6236,7 +6236,7 @@
     </row>
     <row r="79" spans="1:8">
       <c r="A79" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>175</v>
@@ -6255,7 +6255,7 @@
     </row>
     <row r="80" spans="1:8">
       <c r="A80" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>177</v>
@@ -6276,7 +6276,7 @@
     </row>
     <row r="81" spans="1:8">
       <c r="A81" s="2" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>193</v>
@@ -6297,7 +6297,7 @@
     </row>
     <row r="82" spans="1:8">
       <c r="A82" s="2" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>191</v>
@@ -6318,7 +6318,7 @@
     </row>
     <row r="83" spans="1:8">
       <c r="A83" s="2" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>169</v>
@@ -6339,7 +6339,7 @@
     </row>
     <row r="84" spans="1:8">
       <c r="A84" s="2" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>167</v>
@@ -6358,7 +6358,7 @@
     </row>
     <row r="85" spans="1:8">
       <c r="A85" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>159</v>
@@ -6377,7 +6377,7 @@
     </row>
     <row r="86" spans="1:8">
       <c r="A86" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>165</v>
@@ -6396,7 +6396,7 @@
     </row>
     <row r="87" spans="1:8">
       <c r="A87" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>163</v>
@@ -6415,7 +6415,7 @@
     </row>
     <row r="88" spans="1:8">
       <c r="A88" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>161</v>
@@ -6434,7 +6434,7 @@
     </row>
     <row r="89" spans="1:8">
       <c r="A89" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>189</v>
@@ -6455,38 +6455,38 @@
     </row>
     <row r="90" spans="1:8">
       <c r="A90" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="B90" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="C90" s="3"/>
       <c r="D90" s="4"/>
       <c r="E90" s="1" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="F90" s="3">
         <v>1</v>
       </c>
       <c r="H90" s="11" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="91" spans="1:8">
       <c r="A91" s="2" t="s">
+        <v>815</v>
+      </c>
+      <c r="B91" s="1" t="s">
         <v>816</v>
       </c>
-      <c r="B91" s="1" t="s">
+      <c r="E91" s="1" t="s">
         <v>817</v>
       </c>
-      <c r="E91" s="1" t="s">
+      <c r="F91" s="3">
+        <v>1</v>
+      </c>
+      <c r="H91" s="7" t="s">
         <v>818</v>
-      </c>
-      <c r="F91" s="3">
-        <v>1</v>
-      </c>
-      <c r="H91" s="7" t="s">
-        <v>819</v>
       </c>
     </row>
     <row r="92" spans="1:8">
@@ -6645,257 +6645,257 @@
     </row>
     <row r="99" spans="1:8">
       <c r="A99" s="2" t="s">
+        <v>723</v>
+      </c>
+      <c r="B99" s="1" t="s">
         <v>724</v>
       </c>
-      <c r="B99" s="1" t="s">
-        <v>725</v>
-      </c>
       <c r="E99" s="1" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="F99" s="3">
         <v>1</v>
       </c>
       <c r="H99" s="7" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
     </row>
     <row r="100" spans="1:8">
       <c r="A100" s="2" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="F100" s="3">
         <v>1</v>
       </c>
       <c r="H100" s="7" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
     </row>
     <row r="101" spans="1:8">
       <c r="A101" s="2" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="F101" s="3">
         <v>1</v>
       </c>
       <c r="H101" s="7" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
     </row>
     <row r="102" spans="1:8">
       <c r="A102" s="2" t="s">
+        <v>712</v>
+      </c>
+      <c r="B102" s="1" t="s">
         <v>713</v>
       </c>
-      <c r="B102" s="1" t="s">
-        <v>714</v>
-      </c>
       <c r="E102" s="1" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="F102" s="3">
         <v>1</v>
       </c>
       <c r="H102" s="7" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
     </row>
     <row r="103" spans="1:8">
       <c r="A103" s="2" t="s">
+        <v>710</v>
+      </c>
+      <c r="B103" s="1" t="s">
         <v>711</v>
       </c>
-      <c r="B103" s="1" t="s">
-        <v>712</v>
-      </c>
       <c r="E103" s="1" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="F103" s="3">
         <v>1</v>
       </c>
       <c r="H103" s="7" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
     </row>
     <row r="104" spans="1:8">
       <c r="A104" s="2" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="F104" s="3">
         <v>1</v>
       </c>
       <c r="H104" s="7" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
     </row>
     <row r="105" spans="1:8">
       <c r="A105" s="2" t="s">
+        <v>716</v>
+      </c>
+      <c r="B105" s="1" t="s">
         <v>717</v>
       </c>
-      <c r="B105" s="1" t="s">
-        <v>718</v>
-      </c>
       <c r="E105" s="1" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="F105" s="3">
         <v>1</v>
       </c>
       <c r="H105" s="7" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
     </row>
     <row r="106" spans="1:8">
       <c r="A106" s="2" t="s">
+        <v>720</v>
+      </c>
+      <c r="B106" s="1" t="s">
         <v>721</v>
       </c>
-      <c r="B106" s="1" t="s">
-        <v>722</v>
-      </c>
       <c r="E106" s="1" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="F106" s="3">
         <v>1</v>
       </c>
       <c r="H106" s="7" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
     </row>
     <row r="107" spans="1:8">
       <c r="A107" s="2" t="s">
+        <v>702</v>
+      </c>
+      <c r="B107" s="1" t="s">
         <v>703</v>
       </c>
-      <c r="B107" s="1" t="s">
-        <v>704</v>
-      </c>
       <c r="E107" s="1" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="F107" s="3">
         <v>1</v>
       </c>
       <c r="H107" s="7" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
     </row>
     <row r="108" spans="1:8">
       <c r="A108" s="2" t="s">
+        <v>725</v>
+      </c>
+      <c r="B108" s="1" t="s">
         <v>726</v>
       </c>
-      <c r="B108" s="1" t="s">
-        <v>727</v>
-      </c>
       <c r="E108" s="1" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="F108" s="3">
         <v>1</v>
       </c>
       <c r="H108" s="7" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
     </row>
     <row r="109" spans="1:8">
       <c r="A109" s="2" t="s">
+        <v>718</v>
+      </c>
+      <c r="B109" s="1" t="s">
         <v>719</v>
       </c>
-      <c r="B109" s="1" t="s">
-        <v>720</v>
-      </c>
       <c r="E109" s="1" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="F109" s="3">
         <v>1</v>
       </c>
       <c r="H109" s="7" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
     </row>
     <row r="110" spans="1:8">
       <c r="A110" s="2" t="s">
+        <v>698</v>
+      </c>
+      <c r="B110" s="1" t="s">
         <v>699</v>
       </c>
-      <c r="B110" s="1" t="s">
-        <v>700</v>
-      </c>
       <c r="E110" s="1" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="F110" s="3">
         <v>1</v>
       </c>
       <c r="H110" s="7" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
     </row>
     <row r="111" spans="1:8">
       <c r="A111" s="2" t="s">
+        <v>700</v>
+      </c>
+      <c r="B111" s="1" t="s">
         <v>701</v>
       </c>
-      <c r="B111" s="1" t="s">
-        <v>702</v>
-      </c>
       <c r="E111" s="1" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="F111" s="3">
         <v>1</v>
       </c>
       <c r="H111" s="7" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
     </row>
     <row r="112" spans="1:8">
       <c r="A112" s="2" t="s">
+        <v>704</v>
+      </c>
+      <c r="B112" s="1" t="s">
         <v>705</v>
       </c>
-      <c r="B112" s="1" t="s">
-        <v>706</v>
-      </c>
       <c r="E112" s="1" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="F112" s="3">
         <v>1</v>
       </c>
       <c r="H112" s="7" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
     </row>
     <row r="113" spans="1:8">
       <c r="A113" s="2" t="s">
+        <v>714</v>
+      </c>
+      <c r="B113" s="1" t="s">
         <v>715</v>
       </c>
-      <c r="B113" s="1" t="s">
-        <v>716</v>
-      </c>
       <c r="E113" s="1" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="F113" s="3">
         <v>1</v>
       </c>
       <c r="H113" s="7" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
     </row>
     <row r="114" spans="1:8">
@@ -6922,64 +6922,64 @@
     </row>
     <row r="115" spans="1:8">
       <c r="A115" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="B115" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="C115" s="3"/>
       <c r="D115" s="4"/>
       <c r="E115" s="1" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="F115" s="3">
         <v>1</v>
       </c>
       <c r="G115" s="1"/>
       <c r="H115" s="11" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
     </row>
     <row r="116" spans="1:8">
       <c r="A116" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="B116" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="C116" s="3"/>
       <c r="D116" s="4"/>
       <c r="E116" s="1" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="F116" s="3">
         <v>1</v>
       </c>
       <c r="G116" s="1"/>
       <c r="H116" s="11" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
     </row>
     <row r="117" spans="1:8">
       <c r="A117" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="B117" t="s">
-        <v>1130</v>
+        <v>1127</v>
       </c>
       <c r="C117" s="3"/>
       <c r="D117" s="4"/>
       <c r="E117" s="1" t="s">
+        <v>844</v>
+      </c>
+      <c r="F117" s="3">
+        <v>1</v>
+      </c>
+      <c r="G117" s="1" t="s">
+        <v>845</v>
+      </c>
+      <c r="H117" s="11" t="s">
         <v>846</v>
-      </c>
-      <c r="F117" s="3">
-        <v>1</v>
-      </c>
-      <c r="G117" s="1" t="s">
-        <v>847</v>
-      </c>
-      <c r="H117" s="11" t="s">
-        <v>848</v>
       </c>
     </row>
     <row r="118" spans="1:8">
@@ -7028,7 +7028,7 @@
     </row>
     <row r="120" spans="1:8">
       <c r="A120" s="2" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B120" s="1" t="s">
         <v>294</v>
@@ -7036,7 +7036,7 @@
       <c r="C120" s="1"/>
       <c r="D120" s="5"/>
       <c r="E120" s="1" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="F120" s="3">
         <v>1</v>
@@ -7048,19 +7048,19 @@
     </row>
     <row r="121" spans="1:8">
       <c r="A121" s="2" t="s">
+        <v>802</v>
+      </c>
+      <c r="B121" s="1" t="s">
         <v>803</v>
       </c>
-      <c r="B121" s="1" t="s">
+      <c r="E121" s="1" t="s">
+        <v>805</v>
+      </c>
+      <c r="F121" s="3">
+        <v>1</v>
+      </c>
+      <c r="H121" s="7" t="s">
         <v>804</v>
-      </c>
-      <c r="E121" s="1" t="s">
-        <v>806</v>
-      </c>
-      <c r="F121" s="3">
-        <v>1</v>
-      </c>
-      <c r="H121" s="7" t="s">
-        <v>805</v>
       </c>
     </row>
     <row r="122" spans="1:8">
@@ -7087,115 +7087,115 @@
     </row>
     <row r="123" spans="1:8">
       <c r="A123" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="B123" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="C123"/>
       <c r="D123" s="11"/>
       <c r="E123" t="s">
-        <v>869</v>
+        <v>866</v>
       </c>
       <c r="F123" s="1">
         <v>1</v>
       </c>
       <c r="G123"/>
       <c r="H123" t="s">
-        <v>878</v>
+        <v>875</v>
       </c>
     </row>
     <row r="124" spans="1:8">
       <c r="A124" t="s">
-        <v>851</v>
+        <v>1193</v>
       </c>
       <c r="B124" t="s">
-        <v>852</v>
+        <v>849</v>
       </c>
       <c r="E124" t="s">
-        <v>870</v>
+        <v>867</v>
       </c>
       <c r="F124" s="1">
         <v>1</v>
       </c>
       <c r="H124" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
     </row>
     <row r="125" spans="1:8">
       <c r="A125" t="s">
-        <v>853</v>
+        <v>850</v>
       </c>
       <c r="B125" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="E125" t="s">
-        <v>871</v>
+        <v>868</v>
       </c>
       <c r="F125" s="1">
         <v>1</v>
       </c>
       <c r="H125" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
     </row>
     <row r="126" spans="1:8">
       <c r="A126" t="s">
-        <v>855</v>
+        <v>852</v>
       </c>
       <c r="B126" t="s">
-        <v>856</v>
+        <v>853</v>
       </c>
       <c r="E126" t="s">
-        <v>872</v>
+        <v>869</v>
       </c>
       <c r="F126" s="1">
         <v>1</v>
       </c>
       <c r="H126" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
     </row>
     <row r="127" spans="1:8">
       <c r="A127" t="s">
-        <v>857</v>
+        <v>854</v>
       </c>
       <c r="B127" t="s">
-        <v>858</v>
+        <v>855</v>
       </c>
       <c r="E127" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
       <c r="F127" s="1">
         <v>1</v>
       </c>
       <c r="H127" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
     </row>
     <row r="128" spans="1:8">
       <c r="A128" t="s">
-        <v>859</v>
+        <v>856</v>
       </c>
       <c r="B128" t="s">
-        <v>860</v>
+        <v>857</v>
       </c>
       <c r="E128" t="s">
-        <v>873</v>
+        <v>870</v>
       </c>
       <c r="F128" s="1">
         <v>1</v>
       </c>
       <c r="H128" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
     </row>
     <row r="129" spans="1:8">
       <c r="A129" t="s">
-        <v>861</v>
+        <v>858</v>
       </c>
       <c r="B129" t="s">
-        <v>862</v>
+        <v>859</v>
       </c>
       <c r="C129" s="2">
         <v>6</v>
@@ -7204,36 +7204,36 @@
         <v>0</v>
       </c>
       <c r="E129" t="s">
-        <v>874</v>
+        <v>871</v>
       </c>
       <c r="F129" s="1"/>
       <c r="H129" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
     </row>
     <row r="130" spans="1:8">
       <c r="A130" t="s">
-        <v>863</v>
+        <v>860</v>
       </c>
       <c r="B130" t="s">
-        <v>864</v>
+        <v>861</v>
       </c>
       <c r="E130" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="F130" s="1">
         <v>1</v>
       </c>
       <c r="H130" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
     </row>
     <row r="131" spans="1:8">
       <c r="A131" t="s">
-        <v>865</v>
+        <v>862</v>
       </c>
       <c r="B131" t="s">
-        <v>866</v>
+        <v>863</v>
       </c>
       <c r="C131" s="2">
         <v>6</v>
@@ -7242,45 +7242,45 @@
         <v>0</v>
       </c>
       <c r="E131" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="F131" s="1"/>
       <c r="H131" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
     </row>
     <row r="132" spans="1:8">
       <c r="A132" t="s">
-        <v>867</v>
+        <v>864</v>
       </c>
       <c r="B132" t="s">
-        <v>868</v>
+        <v>865</v>
       </c>
       <c r="E132" t="s">
+        <v>874</v>
+      </c>
+      <c r="F132" s="1">
+        <v>1</v>
+      </c>
+      <c r="H132" t="s">
         <v>877</v>
-      </c>
-      <c r="F132" s="1">
-        <v>1</v>
-      </c>
-      <c r="H132" t="s">
-        <v>880</v>
       </c>
     </row>
     <row r="133" spans="1:8">
       <c r="A133" t="s">
-        <v>1056</v>
+        <v>1053</v>
       </c>
       <c r="B133" t="s">
-        <v>1057</v>
+        <v>1054</v>
       </c>
       <c r="E133" t="s">
-        <v>1058</v>
+        <v>1055</v>
       </c>
       <c r="F133" s="1">
         <v>1</v>
       </c>
       <c r="H133" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
     </row>
     <row r="134" spans="1:8">
@@ -7346,7 +7346,7 @@
       <c r="F136" s="3"/>
       <c r="G136" s="1"/>
       <c r="H136" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
     </row>
     <row r="137" spans="1:8">
@@ -7434,7 +7434,7 @@
       <c r="F140" s="3"/>
       <c r="G140" s="1"/>
       <c r="H140" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
     </row>
     <row r="141" spans="1:8">
@@ -7464,7 +7464,7 @@
         <v>382</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="C142" s="3">
         <v>6</v>
@@ -7681,10 +7681,10 @@
     </row>
     <row r="152" spans="1:8">
       <c r="A152" s="11" t="s">
-        <v>881</v>
+        <v>878</v>
       </c>
       <c r="B152" s="11" t="s">
-        <v>882</v>
+        <v>879</v>
       </c>
       <c r="C152">
         <v>14</v>
@@ -7696,495 +7696,495 @@
       <c r="F152"/>
       <c r="G152"/>
       <c r="H152" t="s">
-        <v>991</v>
+        <v>988</v>
       </c>
     </row>
     <row r="153" spans="1:8">
       <c r="A153" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="B153" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="C153"/>
       <c r="D153"/>
       <c r="E153" t="s">
-        <v>953</v>
+        <v>950</v>
       </c>
       <c r="F153">
         <v>1</v>
       </c>
       <c r="G153"/>
       <c r="H153" t="s">
-        <v>954</v>
+        <v>951</v>
       </c>
     </row>
     <row r="154" spans="1:8">
       <c r="A154" t="s">
-        <v>885</v>
+        <v>882</v>
       </c>
       <c r="B154" t="s">
-        <v>886</v>
+        <v>883</v>
       </c>
       <c r="C154"/>
       <c r="D154"/>
       <c r="E154" t="s">
-        <v>955</v>
+        <v>952</v>
       </c>
       <c r="F154">
         <v>1</v>
       </c>
       <c r="G154"/>
       <c r="H154" t="s">
-        <v>954</v>
+        <v>951</v>
       </c>
     </row>
     <row r="155" spans="1:8">
       <c r="A155" t="s">
-        <v>887</v>
+        <v>884</v>
       </c>
       <c r="B155" t="s">
-        <v>888</v>
+        <v>885</v>
       </c>
       <c r="C155"/>
       <c r="D155"/>
       <c r="E155" t="s">
-        <v>956</v>
+        <v>953</v>
       </c>
       <c r="F155">
         <v>1</v>
       </c>
       <c r="G155"/>
       <c r="H155" t="s">
-        <v>954</v>
+        <v>951</v>
       </c>
     </row>
     <row r="156" spans="1:8">
       <c r="A156" t="s">
-        <v>889</v>
+        <v>886</v>
       </c>
       <c r="B156" t="s">
-        <v>890</v>
+        <v>887</v>
       </c>
       <c r="C156"/>
       <c r="D156"/>
       <c r="E156" t="s">
-        <v>957</v>
+        <v>954</v>
       </c>
       <c r="F156">
         <v>1</v>
       </c>
       <c r="G156"/>
       <c r="H156" t="s">
-        <v>954</v>
+        <v>951</v>
       </c>
     </row>
     <row r="157" spans="1:8">
       <c r="A157" t="s">
-        <v>891</v>
+        <v>888</v>
       </c>
       <c r="B157" t="s">
-        <v>892</v>
+        <v>889</v>
       </c>
       <c r="C157"/>
       <c r="D157"/>
       <c r="E157" t="s">
-        <v>958</v>
+        <v>955</v>
       </c>
       <c r="F157">
         <v>1</v>
       </c>
       <c r="G157"/>
       <c r="H157" t="s">
-        <v>954</v>
+        <v>951</v>
       </c>
     </row>
     <row r="158" spans="1:8">
       <c r="A158" t="s">
-        <v>893</v>
+        <v>890</v>
       </c>
       <c r="B158" t="s">
-        <v>894</v>
+        <v>891</v>
       </c>
       <c r="C158"/>
       <c r="D158"/>
       <c r="E158" t="s">
-        <v>959</v>
+        <v>956</v>
       </c>
       <c r="F158">
         <v>1</v>
       </c>
       <c r="G158"/>
       <c r="H158" t="s">
-        <v>954</v>
+        <v>951</v>
       </c>
     </row>
     <row r="159" spans="1:8">
       <c r="A159" t="s">
-        <v>895</v>
+        <v>892</v>
       </c>
       <c r="B159" t="s">
-        <v>896</v>
+        <v>893</v>
       </c>
       <c r="C159"/>
       <c r="D159"/>
       <c r="E159" t="s">
-        <v>960</v>
+        <v>957</v>
       </c>
       <c r="F159">
         <v>1</v>
       </c>
       <c r="G159"/>
       <c r="H159" t="s">
-        <v>954</v>
+        <v>951</v>
       </c>
     </row>
     <row r="160" spans="1:8">
       <c r="A160" t="s">
-        <v>897</v>
+        <v>894</v>
       </c>
       <c r="B160" t="s">
-        <v>898</v>
+        <v>895</v>
       </c>
       <c r="C160"/>
       <c r="D160"/>
       <c r="E160" t="s">
-        <v>961</v>
+        <v>958</v>
       </c>
       <c r="F160">
         <v>1</v>
       </c>
       <c r="G160"/>
       <c r="H160" t="s">
-        <v>954</v>
+        <v>951</v>
       </c>
     </row>
     <row r="161" spans="1:8">
       <c r="A161" t="s">
-        <v>899</v>
+        <v>896</v>
       </c>
       <c r="B161" t="s">
-        <v>900</v>
+        <v>897</v>
       </c>
       <c r="C161"/>
       <c r="D161"/>
       <c r="E161" t="s">
-        <v>962</v>
+        <v>959</v>
       </c>
       <c r="F161">
         <v>1</v>
       </c>
       <c r="G161"/>
       <c r="H161" t="s">
-        <v>954</v>
+        <v>951</v>
       </c>
     </row>
     <row r="162" spans="1:8">
       <c r="A162" t="s">
-        <v>901</v>
+        <v>898</v>
       </c>
       <c r="B162" t="s">
-        <v>902</v>
+        <v>899</v>
       </c>
       <c r="C162"/>
       <c r="D162"/>
       <c r="E162" t="s">
-        <v>963</v>
+        <v>960</v>
       </c>
       <c r="F162">
         <v>1</v>
       </c>
       <c r="G162"/>
       <c r="H162" t="s">
-        <v>954</v>
+        <v>951</v>
       </c>
     </row>
     <row r="163" spans="1:8">
       <c r="A163" t="s">
-        <v>903</v>
+        <v>900</v>
       </c>
       <c r="B163" t="s">
-        <v>904</v>
+        <v>901</v>
       </c>
       <c r="C163"/>
       <c r="D163"/>
       <c r="E163" t="s">
-        <v>964</v>
+        <v>961</v>
       </c>
       <c r="F163">
         <v>1</v>
       </c>
       <c r="G163"/>
       <c r="H163" t="s">
-        <v>954</v>
+        <v>951</v>
       </c>
     </row>
     <row r="164" spans="1:8">
       <c r="A164" t="s">
-        <v>905</v>
+        <v>902</v>
       </c>
       <c r="B164" s="12" t="s">
-        <v>1046</v>
+        <v>1043</v>
       </c>
       <c r="C164"/>
       <c r="D164"/>
       <c r="E164" t="s">
-        <v>965</v>
+        <v>962</v>
       </c>
       <c r="F164">
         <v>1</v>
       </c>
       <c r="G164"/>
       <c r="H164" t="s">
-        <v>954</v>
+        <v>951</v>
       </c>
     </row>
     <row r="165" spans="1:8">
       <c r="A165" t="s">
-        <v>906</v>
+        <v>903</v>
       </c>
       <c r="B165" t="s">
-        <v>907</v>
+        <v>904</v>
       </c>
       <c r="C165"/>
       <c r="D165"/>
       <c r="E165" t="s">
-        <v>966</v>
+        <v>963</v>
       </c>
       <c r="F165">
         <v>1</v>
       </c>
       <c r="G165"/>
       <c r="H165" t="s">
-        <v>967</v>
+        <v>964</v>
       </c>
     </row>
     <row r="166" spans="1:8">
       <c r="A166" t="s">
-        <v>908</v>
+        <v>905</v>
       </c>
       <c r="B166" t="s">
-        <v>909</v>
+        <v>906</v>
       </c>
       <c r="C166"/>
       <c r="D166"/>
       <c r="E166" t="s">
-        <v>968</v>
+        <v>965</v>
       </c>
       <c r="F166">
         <v>1</v>
       </c>
       <c r="G166"/>
       <c r="H166" t="s">
-        <v>954</v>
+        <v>951</v>
       </c>
     </row>
     <row r="167" spans="1:8">
       <c r="A167" t="s">
-        <v>910</v>
+        <v>907</v>
       </c>
       <c r="B167" t="s">
-        <v>911</v>
+        <v>908</v>
       </c>
       <c r="C167"/>
       <c r="D167"/>
       <c r="E167" t="s">
-        <v>969</v>
+        <v>966</v>
       </c>
       <c r="F167">
         <v>1</v>
       </c>
       <c r="G167"/>
       <c r="H167" t="s">
-        <v>954</v>
+        <v>951</v>
       </c>
     </row>
     <row r="168" spans="1:8">
       <c r="A168" t="s">
-        <v>912</v>
+        <v>909</v>
       </c>
       <c r="B168" t="s">
-        <v>913</v>
+        <v>910</v>
       </c>
       <c r="C168"/>
       <c r="D168"/>
       <c r="E168" t="s">
-        <v>970</v>
+        <v>967</v>
       </c>
       <c r="F168">
         <v>1</v>
       </c>
       <c r="G168"/>
       <c r="H168" t="s">
-        <v>954</v>
+        <v>951</v>
       </c>
     </row>
     <row r="169" spans="1:8">
       <c r="A169" t="s">
-        <v>914</v>
+        <v>911</v>
       </c>
       <c r="B169" t="s">
-        <v>915</v>
+        <v>912</v>
       </c>
       <c r="C169"/>
       <c r="D169"/>
       <c r="E169" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="F169">
         <v>1</v>
       </c>
       <c r="G169"/>
       <c r="H169" t="s">
-        <v>954</v>
+        <v>951</v>
       </c>
     </row>
     <row r="170" spans="1:8">
       <c r="A170" t="s">
-        <v>916</v>
+        <v>913</v>
       </c>
       <c r="B170" t="s">
-        <v>917</v>
+        <v>914</v>
       </c>
       <c r="C170"/>
       <c r="D170"/>
       <c r="E170" t="s">
-        <v>972</v>
+        <v>969</v>
       </c>
       <c r="F170">
         <v>1</v>
       </c>
       <c r="G170"/>
       <c r="H170" t="s">
-        <v>954</v>
+        <v>951</v>
       </c>
     </row>
     <row r="171" spans="1:8">
       <c r="A171" t="s">
-        <v>918</v>
+        <v>915</v>
       </c>
       <c r="B171" t="s">
-        <v>919</v>
+        <v>916</v>
       </c>
       <c r="C171"/>
       <c r="D171"/>
       <c r="E171" t="s">
-        <v>973</v>
+        <v>970</v>
       </c>
       <c r="F171">
         <v>1</v>
       </c>
       <c r="G171"/>
       <c r="H171" t="s">
-        <v>954</v>
+        <v>951</v>
       </c>
     </row>
     <row r="172" spans="1:8">
       <c r="A172" t="s">
-        <v>920</v>
+        <v>917</v>
       </c>
       <c r="B172" t="s">
-        <v>921</v>
+        <v>918</v>
       </c>
       <c r="C172"/>
       <c r="D172"/>
       <c r="E172" t="s">
-        <v>974</v>
+        <v>971</v>
       </c>
       <c r="F172">
         <v>1</v>
       </c>
       <c r="G172"/>
       <c r="H172" t="s">
-        <v>954</v>
+        <v>951</v>
       </c>
     </row>
     <row r="173" spans="1:8">
       <c r="A173" t="s">
-        <v>922</v>
+        <v>919</v>
       </c>
       <c r="B173" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="C173"/>
       <c r="D173"/>
       <c r="E173" t="s">
-        <v>975</v>
+        <v>972</v>
       </c>
       <c r="F173">
         <v>1</v>
       </c>
       <c r="G173"/>
       <c r="H173" t="s">
-        <v>954</v>
+        <v>951</v>
       </c>
     </row>
     <row r="174" spans="1:8">
       <c r="A174" t="s">
-        <v>924</v>
+        <v>921</v>
       </c>
       <c r="B174" t="s">
-        <v>925</v>
+        <v>922</v>
       </c>
       <c r="C174"/>
       <c r="D174"/>
       <c r="E174" t="s">
-        <v>976</v>
+        <v>973</v>
       </c>
       <c r="F174">
         <v>1</v>
       </c>
       <c r="G174"/>
       <c r="H174" t="s">
-        <v>954</v>
+        <v>951</v>
       </c>
     </row>
     <row r="175" spans="1:8">
       <c r="A175" t="s">
-        <v>926</v>
+        <v>923</v>
       </c>
       <c r="B175" t="s">
-        <v>927</v>
+        <v>924</v>
       </c>
       <c r="C175"/>
       <c r="D175"/>
       <c r="E175" t="s">
-        <v>977</v>
+        <v>974</v>
       </c>
       <c r="F175">
         <v>1</v>
       </c>
       <c r="G175"/>
       <c r="H175" t="s">
-        <v>954</v>
+        <v>951</v>
       </c>
     </row>
     <row r="176" spans="1:8">
       <c r="A176" t="s">
-        <v>928</v>
+        <v>925</v>
       </c>
       <c r="B176" t="s">
-        <v>929</v>
+        <v>926</v>
       </c>
       <c r="C176"/>
       <c r="D176"/>
       <c r="E176" t="s">
-        <v>978</v>
+        <v>975</v>
       </c>
       <c r="F176">
         <v>1</v>
       </c>
       <c r="G176"/>
       <c r="H176" t="s">
-        <v>954</v>
+        <v>951</v>
       </c>
     </row>
     <row r="177" spans="1:8">
       <c r="A177" t="s">
-        <v>930</v>
+        <v>927</v>
       </c>
       <c r="B177" t="s">
-        <v>931</v>
+        <v>928</v>
       </c>
       <c r="C177">
         <v>14</v>
@@ -8193,100 +8193,100 @@
         <v>0</v>
       </c>
       <c r="E177" t="s">
-        <v>979</v>
+        <v>976</v>
       </c>
       <c r="F177"/>
       <c r="G177"/>
       <c r="H177" t="s">
-        <v>954</v>
+        <v>951</v>
       </c>
     </row>
     <row r="178" spans="1:8">
       <c r="A178" t="s">
-        <v>932</v>
+        <v>929</v>
       </c>
       <c r="B178" t="s">
-        <v>933</v>
+        <v>930</v>
       </c>
       <c r="C178"/>
       <c r="D178"/>
       <c r="E178" t="s">
-        <v>980</v>
+        <v>977</v>
       </c>
       <c r="F178">
         <v>1</v>
       </c>
       <c r="G178"/>
       <c r="H178" t="s">
-        <v>954</v>
+        <v>951</v>
       </c>
     </row>
     <row r="179" spans="1:8">
       <c r="A179" t="s">
-        <v>934</v>
+        <v>931</v>
       </c>
       <c r="B179" t="s">
-        <v>935</v>
+        <v>932</v>
       </c>
       <c r="C179"/>
       <c r="D179"/>
       <c r="E179" t="s">
-        <v>981</v>
+        <v>978</v>
       </c>
       <c r="F179">
         <v>1</v>
       </c>
       <c r="G179"/>
       <c r="H179" t="s">
-        <v>954</v>
+        <v>951</v>
       </c>
     </row>
     <row r="180" spans="1:8">
       <c r="A180" s="12" t="s">
-        <v>936</v>
+        <v>933</v>
       </c>
       <c r="B180" s="12" t="s">
-        <v>1047</v>
+        <v>1044</v>
       </c>
       <c r="C180"/>
       <c r="D180"/>
       <c r="E180" t="s">
-        <v>982</v>
+        <v>979</v>
       </c>
       <c r="F180">
         <v>1</v>
       </c>
       <c r="G180"/>
       <c r="H180" t="s">
-        <v>954</v>
+        <v>951</v>
       </c>
     </row>
     <row r="181" spans="1:8">
       <c r="A181" t="s">
-        <v>937</v>
+        <v>934</v>
       </c>
       <c r="B181" t="s">
-        <v>938</v>
+        <v>935</v>
       </c>
       <c r="C181"/>
       <c r="D181"/>
       <c r="E181" t="s">
-        <v>983</v>
+        <v>980</v>
       </c>
       <c r="F181">
         <v>1</v>
       </c>
       <c r="G181"/>
       <c r="H181" t="s">
-        <v>954</v>
+        <v>951</v>
       </c>
     </row>
     <row r="182" spans="1:8">
       <c r="A182" t="s">
-        <v>939</v>
+        <v>936</v>
       </c>
       <c r="B182" t="s">
-        <v>940</v>
+        <v>937</v>
       </c>
       <c r="C182">
         <v>14</v>
@@ -8295,152 +8295,152 @@
         <v>0</v>
       </c>
       <c r="E182" t="s">
-        <v>984</v>
+        <v>981</v>
       </c>
       <c r="F182"/>
       <c r="G182"/>
       <c r="H182" t="s">
-        <v>954</v>
+        <v>951</v>
       </c>
     </row>
     <row r="183" spans="1:8">
       <c r="A183" t="s">
-        <v>941</v>
+        <v>938</v>
       </c>
       <c r="B183" t="s">
-        <v>942</v>
+        <v>939</v>
       </c>
       <c r="C183"/>
       <c r="D183"/>
       <c r="E183" t="s">
-        <v>985</v>
+        <v>982</v>
       </c>
       <c r="F183">
         <v>1</v>
       </c>
       <c r="G183"/>
       <c r="H183" t="s">
-        <v>954</v>
+        <v>951</v>
       </c>
     </row>
     <row r="184" spans="1:8">
       <c r="A184" t="s">
-        <v>943</v>
+        <v>940</v>
       </c>
       <c r="B184" t="s">
-        <v>944</v>
+        <v>941</v>
       </c>
       <c r="C184"/>
       <c r="D184"/>
       <c r="E184" t="s">
-        <v>986</v>
+        <v>983</v>
       </c>
       <c r="F184">
         <v>1</v>
       </c>
       <c r="G184"/>
       <c r="H184" t="s">
-        <v>954</v>
+        <v>951</v>
       </c>
     </row>
     <row r="185" spans="1:8">
       <c r="A185" t="s">
-        <v>945</v>
+        <v>942</v>
       </c>
       <c r="B185" t="s">
-        <v>946</v>
+        <v>943</v>
       </c>
       <c r="C185"/>
       <c r="D185"/>
       <c r="E185" t="s">
-        <v>987</v>
+        <v>984</v>
       </c>
       <c r="F185">
         <v>1</v>
       </c>
       <c r="G185"/>
       <c r="H185" t="s">
-        <v>954</v>
+        <v>951</v>
       </c>
     </row>
     <row r="186" spans="1:8">
       <c r="A186" t="s">
-        <v>947</v>
+        <v>944</v>
       </c>
       <c r="B186" t="s">
-        <v>948</v>
+        <v>945</v>
       </c>
       <c r="C186"/>
       <c r="D186"/>
       <c r="E186" t="s">
-        <v>988</v>
+        <v>985</v>
       </c>
       <c r="F186">
         <v>1</v>
       </c>
       <c r="G186"/>
       <c r="H186" t="s">
-        <v>954</v>
+        <v>951</v>
       </c>
     </row>
     <row r="187" spans="1:8">
       <c r="A187" t="s">
-        <v>949</v>
+        <v>946</v>
       </c>
       <c r="B187" t="s">
-        <v>950</v>
+        <v>947</v>
       </c>
       <c r="C187"/>
       <c r="D187"/>
       <c r="E187" t="s">
-        <v>989</v>
+        <v>986</v>
       </c>
       <c r="F187">
         <v>1</v>
       </c>
       <c r="G187"/>
       <c r="H187" t="s">
-        <v>954</v>
+        <v>951</v>
       </c>
     </row>
     <row r="188" spans="1:8">
       <c r="A188" t="s">
-        <v>951</v>
+        <v>948</v>
       </c>
       <c r="B188" t="s">
-        <v>952</v>
+        <v>949</v>
       </c>
       <c r="C188"/>
       <c r="D188"/>
       <c r="E188" t="s">
-        <v>990</v>
+        <v>987</v>
       </c>
       <c r="F188">
         <v>1</v>
       </c>
       <c r="G188"/>
       <c r="H188" t="s">
-        <v>954</v>
+        <v>951</v>
       </c>
     </row>
     <row r="189" spans="1:8">
       <c r="A189" t="s">
-        <v>1048</v>
+        <v>1045</v>
       </c>
       <c r="B189" t="s">
-        <v>1049</v>
+        <v>1046</v>
       </c>
       <c r="C189"/>
       <c r="D189"/>
       <c r="E189" t="s">
-        <v>1050</v>
+        <v>1047</v>
       </c>
       <c r="F189">
         <v>1</v>
       </c>
       <c r="G189"/>
       <c r="H189" t="s">
-        <v>954</v>
+        <v>951</v>
       </c>
     </row>
     <row r="190" spans="1:8">
@@ -8462,7 +8462,7 @@
       <c r="F190" s="3"/>
       <c r="G190" s="1"/>
       <c r="H190" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
     </row>
     <row r="191" spans="1:8">
@@ -8511,19 +8511,19 @@
     </row>
     <row r="193" spans="1:8">
       <c r="A193" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B193" s="1" t="s">
         <v>505</v>
       </c>
       <c r="E193" s="1" t="s">
+        <v>760</v>
+      </c>
+      <c r="F193" s="2">
+        <v>1</v>
+      </c>
+      <c r="G193" s="2" t="s">
         <v>761</v>
-      </c>
-      <c r="F193" s="2">
-        <v>1</v>
-      </c>
-      <c r="G193" s="2" t="s">
-        <v>762</v>
       </c>
       <c r="H193" s="2" t="s">
         <v>618</v>
@@ -8531,19 +8531,19 @@
     </row>
     <row r="194" spans="1:8">
       <c r="A194" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B194" s="1" t="s">
         <v>506</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="F194" s="2">
         <v>1</v>
       </c>
       <c r="G194" s="2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="H194" s="2" t="s">
         <v>619</v>
@@ -8551,19 +8551,19 @@
     </row>
     <row r="195" spans="1:8">
       <c r="A195" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B195" s="1" t="s">
         <v>506</v>
       </c>
       <c r="E195" s="1" t="s">
+        <v>763</v>
+      </c>
+      <c r="F195" s="2">
+        <v>1</v>
+      </c>
+      <c r="G195" s="2" t="s">
         <v>764</v>
-      </c>
-      <c r="F195" s="2">
-        <v>1</v>
-      </c>
-      <c r="G195" s="2" t="s">
-        <v>765</v>
       </c>
       <c r="H195" s="2" t="s">
         <v>619</v>
@@ -8571,7 +8571,7 @@
     </row>
     <row r="196" spans="1:8">
       <c r="A196" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B196" s="1" t="s">
         <v>503</v>
@@ -8587,25 +8587,25 @@
       </c>
       <c r="F196" s="3"/>
       <c r="H196" s="2" t="s">
-        <v>1043</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="197" spans="1:8">
       <c r="A197" s="2" t="s">
+        <v>806</v>
+      </c>
+      <c r="B197" s="1" t="s">
         <v>807</v>
-      </c>
-      <c r="B197" s="1" t="s">
-        <v>808</v>
       </c>
       <c r="D197" s="6"/>
       <c r="E197" s="1" t="s">
+        <v>808</v>
+      </c>
+      <c r="F197" s="3">
+        <v>1</v>
+      </c>
+      <c r="H197" s="7" t="s">
         <v>809</v>
-      </c>
-      <c r="F197" s="3">
-        <v>1</v>
-      </c>
-      <c r="H197" s="7" t="s">
-        <v>810</v>
       </c>
     </row>
     <row r="198" spans="1:8">
@@ -8632,7 +8632,7 @@
     </row>
     <row r="199" spans="1:8">
       <c r="A199" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="B199" s="1" t="s">
         <v>508</v>
@@ -8644,18 +8644,18 @@
         <v>0</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="H199" s="2" t="s">
-        <v>1042</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="200" spans="1:8">
       <c r="A200" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="C200" s="2">
         <v>10</v>
@@ -8664,38 +8664,38 @@
         <v>0</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H200" s="2" t="s">
-        <v>1041</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="201" spans="1:8">
       <c r="A201" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="B201" t="s">
-        <v>1024</v>
+        <v>1021</v>
       </c>
       <c r="C201"/>
       <c r="D201" s="11"/>
       <c r="E201" t="s">
-        <v>1025</v>
+        <v>1022</v>
       </c>
       <c r="F201">
         <v>1</v>
       </c>
       <c r="G201"/>
       <c r="H201" s="11" t="s">
-        <v>1026</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="202" spans="1:8">
       <c r="A202" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
       <c r="B202" t="s">
-        <v>1027</v>
+        <v>1024</v>
       </c>
       <c r="C202">
         <v>10</v>
@@ -8704,32 +8704,32 @@
         <v>0</v>
       </c>
       <c r="E202" t="s">
-        <v>1028</v>
+        <v>1025</v>
       </c>
       <c r="F202"/>
       <c r="G202"/>
       <c r="H202" s="11" t="s">
-        <v>1029</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="203" spans="1:8">
       <c r="A203" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="B203" t="s">
-        <v>1030</v>
+        <v>1027</v>
       </c>
       <c r="C203"/>
       <c r="D203" s="11"/>
       <c r="E203" t="s">
-        <v>1031</v>
+        <v>1028</v>
       </c>
       <c r="F203">
         <v>1</v>
       </c>
       <c r="G203"/>
       <c r="H203" s="11" t="s">
-        <v>1032</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="204" spans="1:8">
@@ -8833,15 +8833,15 @@
         <v>1</v>
       </c>
       <c r="H208" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
     </row>
     <row r="209" spans="1:8">
       <c r="A209" t="s">
-        <v>992</v>
+        <v>989</v>
       </c>
       <c r="B209" t="s">
-        <v>993</v>
+        <v>990</v>
       </c>
       <c r="C209">
         <v>15</v>
@@ -8850,20 +8850,20 @@
         <v>0</v>
       </c>
       <c r="E209" t="s">
-        <v>994</v>
+        <v>991</v>
       </c>
       <c r="F209"/>
       <c r="G209"/>
       <c r="H209" s="11" t="s">
-        <v>995</v>
+        <v>992</v>
       </c>
     </row>
     <row r="210" spans="1:8">
       <c r="A210" t="s">
-        <v>996</v>
+        <v>993</v>
       </c>
       <c r="B210" t="s">
-        <v>997</v>
+        <v>994</v>
       </c>
       <c r="C210">
         <v>15</v>
@@ -8872,20 +8872,20 @@
         <v>0</v>
       </c>
       <c r="E210" t="s">
-        <v>998</v>
+        <v>995</v>
       </c>
       <c r="F210"/>
       <c r="G210"/>
       <c r="H210" s="11" t="s">
-        <v>999</v>
+        <v>996</v>
       </c>
     </row>
     <row r="211" spans="1:8">
       <c r="A211" t="s">
-        <v>1000</v>
+        <v>997</v>
       </c>
       <c r="B211" t="s">
-        <v>1001</v>
+        <v>998</v>
       </c>
       <c r="C211">
         <v>15</v>
@@ -8894,20 +8894,20 @@
         <v>0</v>
       </c>
       <c r="E211" t="s">
-        <v>1002</v>
+        <v>999</v>
       </c>
       <c r="F211"/>
       <c r="G211"/>
       <c r="H211" s="11" t="s">
-        <v>1003</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="212" spans="1:8">
       <c r="A212" t="s">
-        <v>1004</v>
+        <v>1001</v>
       </c>
       <c r="B212" t="s">
-        <v>1005</v>
+        <v>1002</v>
       </c>
       <c r="C212">
         <v>20</v>
@@ -8916,20 +8916,20 @@
         <v>0</v>
       </c>
       <c r="E212" t="s">
-        <v>1006</v>
+        <v>1003</v>
       </c>
       <c r="F212"/>
       <c r="G212"/>
       <c r="H212" s="11" t="s">
-        <v>1007</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="213" spans="1:8">
       <c r="A213" t="s">
-        <v>1008</v>
+        <v>1005</v>
       </c>
       <c r="B213" t="s">
-        <v>1009</v>
+        <v>1006</v>
       </c>
       <c r="C213">
         <v>15</v>
@@ -8938,12 +8938,12 @@
         <v>0</v>
       </c>
       <c r="E213" t="s">
-        <v>1010</v>
+        <v>1007</v>
       </c>
       <c r="F213"/>
       <c r="G213"/>
       <c r="H213" s="11" t="s">
-        <v>1011</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="214" spans="1:8">
@@ -8962,7 +8962,7 @@
         <v>1</v>
       </c>
       <c r="G214" s="1" t="s">
-        <v>1135</v>
+        <v>1132</v>
       </c>
       <c r="H214" s="2" t="s">
         <v>583</v>
@@ -8984,7 +8984,7 @@
         <v>1</v>
       </c>
       <c r="G215" s="1" t="s">
-        <v>1136</v>
+        <v>1133</v>
       </c>
       <c r="H215" s="2" t="s">
         <v>583</v>
@@ -9070,7 +9070,7 @@
         <v>0</v>
       </c>
       <c r="E219" s="1" t="s">
-        <v>1012</v>
+        <v>1009</v>
       </c>
       <c r="F219" s="3"/>
       <c r="G219" s="1"/>
@@ -9174,7 +9174,7 @@
         <v>0</v>
       </c>
       <c r="E224" s="1" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="F224" s="3"/>
       <c r="G224" s="1"/>
@@ -9206,10 +9206,10 @@
     </row>
     <row r="226" spans="1:8">
       <c r="A226" s="2" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="B226" s="1" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="C226" s="2">
         <v>7</v>
@@ -9218,11 +9218,11 @@
         <v>0.95833333333333337</v>
       </c>
       <c r="E226" s="1" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="F226" s="3"/>
       <c r="H226" s="7" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
     </row>
     <row r="227" spans="1:8">
@@ -9244,7 +9244,7 @@
       <c r="F227" s="3"/>
       <c r="G227" s="1"/>
       <c r="H227" s="7" t="s">
-        <v>1194</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="228" spans="1:8">
@@ -9344,7 +9344,7 @@
         <v>0</v>
       </c>
       <c r="E232" s="1" t="s">
-        <v>1013</v>
+        <v>1010</v>
       </c>
       <c r="F232" s="3"/>
       <c r="G232" s="1"/>
@@ -9398,10 +9398,10 @@
     </row>
     <row r="235" spans="1:8">
       <c r="A235" t="s">
-        <v>1014</v>
+        <v>1011</v>
       </c>
       <c r="B235" t="s">
-        <v>1015</v>
+        <v>1012</v>
       </c>
       <c r="C235">
         <v>6</v>
@@ -9410,20 +9410,20 @@
         <v>0</v>
       </c>
       <c r="E235" t="s">
-        <v>1016</v>
+        <v>1013</v>
       </c>
       <c r="F235"/>
       <c r="G235"/>
       <c r="H235" s="7" t="s">
-        <v>1017</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="236" spans="1:8">
       <c r="A236" s="11" t="s">
-        <v>1018</v>
+        <v>1015</v>
       </c>
       <c r="B236" t="s">
-        <v>1019</v>
+        <v>1016</v>
       </c>
       <c r="C236" s="3">
         <v>7</v>
@@ -9432,12 +9432,12 @@
         <v>0.91666666666666663</v>
       </c>
       <c r="E236" s="1" t="s">
-        <v>1034</v>
+        <v>1031</v>
       </c>
       <c r="F236"/>
       <c r="G236"/>
       <c r="H236" s="7" t="s">
-        <v>1035</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="237" spans="1:8">
@@ -9486,22 +9486,22 @@
     </row>
     <row r="239" spans="1:8" customFormat="1">
       <c r="A239" s="2" t="s">
+        <v>798</v>
+      </c>
+      <c r="B239" s="1" t="s">
         <v>799</v>
-      </c>
-      <c r="B239" s="1" t="s">
-        <v>800</v>
       </c>
       <c r="C239" s="2"/>
       <c r="D239" s="2"/>
       <c r="E239" s="1" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="F239" s="3">
         <v>1</v>
       </c>
       <c r="G239" s="2"/>
       <c r="H239" s="7" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
     </row>
     <row r="240" spans="1:8">
@@ -9588,24 +9588,24 @@
     </row>
     <row r="244" spans="1:8">
       <c r="A244" s="11" t="s">
-        <v>1020</v>
+        <v>1017</v>
       </c>
       <c r="B244" t="s">
-        <v>1021</v>
+        <v>1018</v>
       </c>
       <c r="C244">
         <v>13</v>
       </c>
       <c r="D244" s="11" t="s">
-        <v>1131</v>
+        <v>1128</v>
       </c>
       <c r="E244" t="s">
-        <v>1022</v>
+        <v>1019</v>
       </c>
       <c r="F244"/>
       <c r="G244"/>
       <c r="H244" s="7" t="s">
-        <v>1023</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="245" spans="1:8">
@@ -9622,7 +9622,7 @@
         <v>0.91666666666666663</v>
       </c>
       <c r="E245" s="1" t="s">
-        <v>1033</v>
+        <v>1030</v>
       </c>
       <c r="F245" s="3"/>
       <c r="G245" s="1"/>
@@ -9632,36 +9632,36 @@
     </row>
     <row r="246" spans="1:8">
       <c r="A246" s="2" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="B246" s="1" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="E246" s="1" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="F246" s="2">
         <v>1</v>
       </c>
       <c r="H246" s="2" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
     </row>
     <row r="247" spans="1:8">
       <c r="A247" s="2" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B247" s="1" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="E247" s="1" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="F247" s="2">
         <v>1</v>
       </c>
       <c r="H247" s="2" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
     </row>
     <row r="248" spans="1:8">
@@ -9678,7 +9678,7 @@
         <v>0</v>
       </c>
       <c r="E248" s="1" t="s">
-        <v>1037</v>
+        <v>1034</v>
       </c>
       <c r="F248" s="3"/>
       <c r="G248" s="1"/>
@@ -9700,7 +9700,7 @@
         <v>0</v>
       </c>
       <c r="E249" s="1" t="s">
-        <v>1036</v>
+        <v>1033</v>
       </c>
       <c r="F249" s="3"/>
       <c r="G249" s="1"/>
@@ -9974,10 +9974,10 @@
     </row>
     <row r="262" spans="1:8">
       <c r="A262" s="2" t="s">
+        <v>690</v>
+      </c>
+      <c r="B262" s="1" t="s">
         <v>691</v>
-      </c>
-      <c r="B262" s="1" t="s">
-        <v>692</v>
       </c>
       <c r="C262" s="2">
         <v>6</v>
@@ -9986,11 +9986,11 @@
         <v>0</v>
       </c>
       <c r="E262" s="1" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="F262" s="3"/>
       <c r="H262" s="7" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
     </row>
     <row r="263" spans="1:8">
@@ -10033,7 +10033,7 @@
       <c r="F264" s="3"/>
       <c r="G264" s="1"/>
       <c r="H264" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
     </row>
     <row r="265" spans="1:8">
@@ -10060,10 +10060,10 @@
     </row>
     <row r="266" spans="1:8">
       <c r="A266" s="2" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="B266" s="1" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="C266" s="2">
         <v>6</v>
@@ -10072,19 +10072,19 @@
         <v>0</v>
       </c>
       <c r="E266" s="1" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="F266" s="3"/>
       <c r="H266" s="7" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="267" spans="1:8">
       <c r="A267" s="2" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B267" s="1" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="C267" s="2">
         <v>6</v>
@@ -10093,19 +10093,19 @@
         <v>0</v>
       </c>
       <c r="E267" s="10" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="F267" s="3"/>
       <c r="H267" s="2" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
     </row>
     <row r="268" spans="1:8">
       <c r="A268" s="2" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="B268" s="1" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="C268" s="2">
         <v>6</v>
@@ -10114,19 +10114,19 @@
         <v>0</v>
       </c>
       <c r="E268" s="1" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="F268" s="3"/>
       <c r="H268" s="2" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
     </row>
     <row r="269" spans="1:8">
       <c r="A269" s="2" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="B269" s="1" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="C269" s="2">
         <v>6</v>
@@ -10135,16 +10135,16 @@
         <v>0</v>
       </c>
       <c r="E269" s="1" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="F269" s="3"/>
       <c r="H269" s="2" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
     </row>
     <row r="270" spans="1:8">
       <c r="A270" s="2" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B270" s="1" t="s">
         <v>507</v>
@@ -10152,16 +10152,16 @@
       <c r="C270" s="3"/>
       <c r="D270" s="6"/>
       <c r="E270" s="1" t="s">
-        <v>1132</v>
+        <v>1129</v>
       </c>
       <c r="F270" s="3">
         <v>1</v>
       </c>
       <c r="G270" s="2" t="s">
-        <v>1137</v>
+        <v>1134</v>
       </c>
       <c r="H270" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
     </row>
     <row r="271" spans="1:8">
@@ -10345,7 +10345,7 @@
         <v>456</v>
       </c>
       <c r="B279" s="1" t="s">
-        <v>1055</v>
+        <v>1052</v>
       </c>
       <c r="C279" s="3">
         <v>6</v>
@@ -10736,129 +10736,129 @@
     </row>
     <row r="297" spans="1:8">
       <c r="A297" t="s">
-        <v>1039</v>
+        <v>1036</v>
       </c>
       <c r="B297" s="1" t="s">
-        <v>1040</v>
+        <v>1037</v>
       </c>
       <c r="E297" s="1" t="s">
-        <v>1044</v>
+        <v>1041</v>
       </c>
       <c r="F297" s="2">
         <v>1</v>
       </c>
       <c r="H297" s="7" t="s">
-        <v>1045</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="298" spans="1:8">
       <c r="A298" s="2" t="s">
+        <v>1056</v>
+      </c>
+      <c r="B298" s="1" t="s">
+        <v>1057</v>
+      </c>
+      <c r="E298" s="1" t="s">
+        <v>1058</v>
+      </c>
+      <c r="F298" s="2">
+        <v>1</v>
+      </c>
+      <c r="H298" s="2" t="s">
         <v>1059</v>
-      </c>
-      <c r="B298" s="1" t="s">
-        <v>1060</v>
-      </c>
-      <c r="E298" s="1" t="s">
-        <v>1061</v>
-      </c>
-      <c r="F298" s="2">
-        <v>1</v>
-      </c>
-      <c r="H298" s="2" t="s">
-        <v>1062</v>
       </c>
     </row>
     <row r="299" spans="1:8">
       <c r="A299" s="2" t="s">
-        <v>1064</v>
+        <v>1061</v>
       </c>
       <c r="B299" s="1" t="s">
+        <v>1060</v>
+      </c>
+      <c r="E299" s="1" t="s">
         <v>1063</v>
       </c>
-      <c r="E299" s="1" t="s">
-        <v>1066</v>
-      </c>
       <c r="F299" s="2">
         <v>1</v>
       </c>
       <c r="H299" s="7" t="s">
-        <v>1065</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="300" spans="1:8">
       <c r="A300" s="2" t="s">
-        <v>1075</v>
+        <v>1072</v>
       </c>
       <c r="B300" s="1" t="s">
-        <v>1067</v>
+        <v>1064</v>
       </c>
       <c r="E300" s="1" t="s">
-        <v>1068</v>
+        <v>1065</v>
       </c>
       <c r="F300" s="2">
         <v>1</v>
       </c>
       <c r="H300" s="2" t="s">
-        <v>1069</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="301" spans="1:8">
       <c r="A301" s="2" t="s">
-        <v>1073</v>
+        <v>1070</v>
       </c>
       <c r="B301" s="1" t="s">
-        <v>1070</v>
+        <v>1067</v>
       </c>
       <c r="E301" s="1" t="s">
-        <v>1071</v>
+        <v>1068</v>
       </c>
       <c r="F301" s="2">
         <v>1</v>
       </c>
       <c r="H301" s="2" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="302" spans="1:8">
       <c r="A302" s="2" t="s">
+        <v>1071</v>
+      </c>
+      <c r="B302" s="1" t="s">
+        <v>1069</v>
+      </c>
+      <c r="E302" s="1" t="s">
+        <v>1073</v>
+      </c>
+      <c r="F302" s="2">
+        <v>1</v>
+      </c>
+      <c r="H302" s="2" t="s">
         <v>1074</v>
-      </c>
-      <c r="B302" s="1" t="s">
-        <v>1072</v>
-      </c>
-      <c r="E302" s="1" t="s">
-        <v>1076</v>
-      </c>
-      <c r="F302" s="2">
-        <v>1</v>
-      </c>
-      <c r="H302" s="2" t="s">
-        <v>1077</v>
       </c>
     </row>
     <row r="303" spans="1:8">
       <c r="A303" s="2" t="s">
-        <v>1084</v>
+        <v>1081</v>
       </c>
       <c r="B303" s="1" t="s">
-        <v>1079</v>
+        <v>1076</v>
       </c>
       <c r="E303" s="1" t="s">
-        <v>1080</v>
+        <v>1077</v>
       </c>
       <c r="F303" s="2">
         <v>1</v>
       </c>
       <c r="H303" s="7" t="s">
-        <v>1122</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="304" spans="1:8">
       <c r="A304" s="2" t="s">
-        <v>1083</v>
+        <v>1080</v>
       </c>
       <c r="B304" s="1" t="s">
-        <v>1081</v>
+        <v>1078</v>
       </c>
       <c r="C304" s="2">
         <v>6</v>
@@ -10867,66 +10867,66 @@
         <v>0</v>
       </c>
       <c r="E304" s="1" t="s">
+        <v>1079</v>
+      </c>
+      <c r="H304" s="7" t="s">
         <v>1082</v>
-      </c>
-      <c r="H304" s="7" t="s">
-        <v>1085</v>
       </c>
     </row>
     <row r="305" spans="1:8">
       <c r="A305" s="2" t="s">
-        <v>1086</v>
+        <v>1083</v>
       </c>
       <c r="B305" s="1" t="s">
-        <v>1087</v>
+        <v>1084</v>
       </c>
       <c r="E305" s="1" t="s">
-        <v>1124</v>
+        <v>1121</v>
       </c>
       <c r="H305" s="7" t="s">
-        <v>1123</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="306" spans="1:8">
       <c r="A306" s="2" t="s">
-        <v>1139</v>
+        <v>1136</v>
       </c>
       <c r="B306" s="1" t="s">
-        <v>1088</v>
+        <v>1085</v>
       </c>
       <c r="E306" s="1" t="s">
-        <v>1141</v>
+        <v>1138</v>
       </c>
       <c r="F306" s="2">
         <v>1</v>
       </c>
       <c r="H306" s="2" t="s">
-        <v>1143</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="307" spans="1:8">
       <c r="A307" s="2" t="s">
+        <v>1137</v>
+      </c>
+      <c r="B307" s="1" t="s">
+        <v>1086</v>
+      </c>
+      <c r="E307" s="1" t="s">
+        <v>1139</v>
+      </c>
+      <c r="F307" s="2">
+        <v>1</v>
+      </c>
+      <c r="H307" s="2" t="s">
         <v>1140</v>
-      </c>
-      <c r="B307" s="1" t="s">
-        <v>1089</v>
-      </c>
-      <c r="E307" s="1" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F307" s="2">
-        <v>1</v>
-      </c>
-      <c r="H307" s="2" t="s">
-        <v>1143</v>
       </c>
     </row>
     <row r="308" spans="1:8">
       <c r="A308" s="2" t="s">
-        <v>1185</v>
+        <v>1182</v>
       </c>
       <c r="B308" s="1" t="s">
-        <v>1090</v>
+        <v>1087</v>
       </c>
       <c r="C308" s="2">
         <v>14</v>
@@ -10935,18 +10935,18 @@
         <v>0</v>
       </c>
       <c r="E308" s="1" t="s">
-        <v>1186</v>
+        <v>1183</v>
       </c>
       <c r="H308" s="2" t="s">
-        <v>1188</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="309" spans="1:8">
       <c r="A309" s="2" t="s">
-        <v>1157</v>
+        <v>1154</v>
       </c>
       <c r="B309" s="1" t="s">
-        <v>1091</v>
+        <v>1088</v>
       </c>
       <c r="C309" s="2">
         <v>6</v>
@@ -10955,23 +10955,23 @@
         <v>0</v>
       </c>
       <c r="E309" s="1" t="s">
-        <v>1158</v>
+        <v>1155</v>
       </c>
       <c r="H309" s="2" t="s">
-        <v>1159</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="310" spans="1:8">
       <c r="B310" s="1" t="s">
-        <v>1092</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="311" spans="1:8">
       <c r="A311" s="2" t="s">
-        <v>1162</v>
+        <v>1159</v>
       </c>
       <c r="B311" s="1" t="s">
-        <v>1093</v>
+        <v>1090</v>
       </c>
       <c r="C311" s="2">
         <v>14</v>
@@ -10980,125 +10980,125 @@
         <v>0</v>
       </c>
       <c r="E311" s="2" t="s">
-        <v>1094</v>
+        <v>1091</v>
       </c>
       <c r="H311" s="2" t="s">
-        <v>1161</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="312" spans="1:8">
       <c r="A312" s="2" t="s">
-        <v>1167</v>
+        <v>1164</v>
       </c>
       <c r="B312" s="1" t="s">
-        <v>1095</v>
+        <v>1092</v>
       </c>
       <c r="E312" s="2" t="s">
-        <v>1169</v>
+        <v>1166</v>
       </c>
       <c r="F312" s="2">
         <v>1</v>
       </c>
       <c r="H312" s="2" t="s">
-        <v>1168</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="313" spans="1:8">
       <c r="A313" s="2" t="s">
-        <v>1184</v>
+        <v>1181</v>
       </c>
       <c r="B313" s="1" t="s">
-        <v>1096</v>
+        <v>1093</v>
       </c>
       <c r="E313" s="2" t="s">
-        <v>1182</v>
+        <v>1179</v>
       </c>
       <c r="F313" s="2">
         <v>1</v>
       </c>
       <c r="H313" s="7" t="s">
-        <v>1183</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="314" spans="1:8">
       <c r="A314" s="2" t="s">
+        <v>1184</v>
+      </c>
+      <c r="B314" s="1" t="s">
+        <v>1094</v>
+      </c>
+      <c r="E314" s="2" t="s">
+        <v>1186</v>
+      </c>
+      <c r="F314" s="2">
+        <v>1</v>
+      </c>
+      <c r="H314" s="7" t="s">
         <v>1187</v>
-      </c>
-      <c r="B314" s="1" t="s">
-        <v>1097</v>
-      </c>
-      <c r="E314" s="2" t="s">
-        <v>1189</v>
-      </c>
-      <c r="F314" s="2">
-        <v>1</v>
-      </c>
-      <c r="H314" s="7" t="s">
-        <v>1190</v>
       </c>
     </row>
     <row r="315" spans="1:8">
       <c r="B315" s="1" t="s">
-        <v>1098</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="316" spans="1:8">
       <c r="A316" s="2" t="s">
-        <v>1176</v>
+        <v>1173</v>
       </c>
       <c r="B316" s="1" t="s">
-        <v>1099</v>
+        <v>1096</v>
       </c>
       <c r="E316" s="2" t="s">
-        <v>1177</v>
+        <v>1174</v>
       </c>
       <c r="F316" s="2">
         <v>1</v>
       </c>
       <c r="H316" s="7" t="s">
-        <v>1178</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="317" spans="1:8">
       <c r="A317" s="2" t="s">
-        <v>1170</v>
+        <v>1167</v>
       </c>
       <c r="B317" s="1" t="s">
-        <v>1100</v>
+        <v>1097</v>
       </c>
       <c r="E317" s="2" t="s">
-        <v>1171</v>
+        <v>1168</v>
       </c>
       <c r="F317" s="2">
         <v>1</v>
       </c>
       <c r="H317" s="2" t="s">
-        <v>1172</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="318" spans="1:8">
       <c r="A318" s="2" t="s">
-        <v>1173</v>
+        <v>1170</v>
       </c>
       <c r="B318" s="1" t="s">
-        <v>1101</v>
+        <v>1098</v>
       </c>
       <c r="E318" s="2" t="s">
-        <v>1175</v>
+        <v>1172</v>
       </c>
       <c r="F318" s="2">
         <v>1</v>
       </c>
       <c r="H318" s="2" t="s">
-        <v>1174</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="319" spans="1:8">
       <c r="A319" s="2" t="s">
-        <v>1180</v>
+        <v>1177</v>
       </c>
       <c r="B319" s="1" t="s">
-        <v>1179</v>
+        <v>1176</v>
       </c>
       <c r="C319" s="2">
         <v>6</v>
@@ -11107,174 +11107,174 @@
         <v>0</v>
       </c>
       <c r="E319" s="2" t="s">
-        <v>1181</v>
+        <v>1178</v>
       </c>
       <c r="H319" s="2" t="s">
-        <v>1193</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="320" spans="1:8">
       <c r="A320" s="2" t="s">
-        <v>1109</v>
+        <v>1106</v>
       </c>
       <c r="B320" s="1" t="s">
-        <v>1102</v>
+        <v>1099</v>
       </c>
       <c r="E320" s="2" t="s">
-        <v>1113</v>
+        <v>1110</v>
       </c>
       <c r="F320" s="2">
         <v>1</v>
       </c>
       <c r="H320" s="2" t="s">
-        <v>1121</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="321" spans="1:8">
       <c r="A321" s="2" t="s">
-        <v>1115</v>
+        <v>1112</v>
       </c>
       <c r="B321" s="1" t="s">
-        <v>1103</v>
+        <v>1100</v>
       </c>
       <c r="E321" s="2" t="s">
-        <v>1114</v>
+        <v>1111</v>
       </c>
       <c r="F321" s="2">
         <v>1</v>
       </c>
       <c r="H321" s="2" t="s">
-        <v>1120</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="322" spans="1:8">
       <c r="A322" s="2" t="s">
-        <v>1110</v>
+        <v>1107</v>
       </c>
       <c r="B322" s="1" t="s">
+        <v>1101</v>
+      </c>
+      <c r="E322" s="2" t="s">
         <v>1104</v>
       </c>
-      <c r="E322" s="2" t="s">
-        <v>1107</v>
-      </c>
       <c r="F322" s="2">
         <v>1</v>
       </c>
       <c r="H322" s="2" t="s">
-        <v>1119</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="323" spans="1:8">
       <c r="A323" s="2" t="s">
-        <v>1111</v>
+        <v>1108</v>
       </c>
       <c r="B323" s="1" t="s">
+        <v>1102</v>
+      </c>
+      <c r="E323" s="2" t="s">
         <v>1105</v>
       </c>
-      <c r="E323" s="2" t="s">
-        <v>1108</v>
-      </c>
       <c r="F323" s="2">
         <v>1</v>
       </c>
       <c r="H323" s="2" t="s">
-        <v>1118</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="324" spans="1:8">
       <c r="A324" s="2" t="s">
-        <v>1112</v>
+        <v>1109</v>
       </c>
       <c r="B324" s="1" t="s">
-        <v>1106</v>
+        <v>1103</v>
       </c>
       <c r="E324" s="2" t="s">
-        <v>1116</v>
+        <v>1113</v>
       </c>
       <c r="F324" s="2">
         <v>1</v>
       </c>
       <c r="H324" s="2" t="s">
-        <v>1117</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="325" spans="1:8">
       <c r="A325" s="2" t="s">
+        <v>1122</v>
+      </c>
+      <c r="B325" s="1" t="s">
+        <v>1123</v>
+      </c>
+      <c r="E325" t="s">
+        <v>1124</v>
+      </c>
+      <c r="F325" s="2">
+        <v>1</v>
+      </c>
+      <c r="G325" s="2" t="s">
+        <v>1135</v>
+      </c>
+      <c r="H325" s="7" t="s">
         <v>1125</v>
-      </c>
-      <c r="B325" s="1" t="s">
-        <v>1126</v>
-      </c>
-      <c r="E325" t="s">
-        <v>1127</v>
-      </c>
-      <c r="F325" s="2">
-        <v>1</v>
-      </c>
-      <c r="G325" s="2" t="s">
-        <v>1138</v>
-      </c>
-      <c r="H325" s="7" t="s">
-        <v>1128</v>
       </c>
     </row>
     <row r="326" spans="1:8">
       <c r="A326" s="2" t="s">
-        <v>1144</v>
+        <v>1141</v>
       </c>
       <c r="B326" s="1" t="s">
-        <v>1145</v>
+        <v>1142</v>
       </c>
       <c r="E326" s="2" t="s">
-        <v>1152</v>
+        <v>1149</v>
       </c>
       <c r="F326" s="2">
         <v>1</v>
       </c>
       <c r="H326" s="2" t="s">
-        <v>1156</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="327" spans="1:8">
       <c r="A327" s="2" t="s">
-        <v>1149</v>
+        <v>1146</v>
       </c>
       <c r="B327" s="1" t="s">
-        <v>1146</v>
+        <v>1143</v>
       </c>
       <c r="E327" s="2" t="s">
+        <v>1150</v>
+      </c>
+      <c r="F327" s="2">
+        <v>1</v>
+      </c>
+      <c r="H327" s="2" t="s">
         <v>1153</v>
-      </c>
-      <c r="F327" s="2">
-        <v>1</v>
-      </c>
-      <c r="H327" s="2" t="s">
-        <v>1156</v>
       </c>
     </row>
     <row r="328" spans="1:8">
       <c r="A328" s="2" t="s">
-        <v>1150</v>
+        <v>1147</v>
       </c>
       <c r="B328" s="1" t="s">
-        <v>1147</v>
+        <v>1144</v>
       </c>
       <c r="E328" s="2" t="s">
-        <v>1154</v>
+        <v>1151</v>
       </c>
       <c r="F328" s="2">
         <v>1</v>
       </c>
       <c r="H328" s="2" t="s">
-        <v>1156</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="329" spans="1:8">
       <c r="A329" s="2" t="s">
-        <v>1151</v>
+        <v>1148</v>
       </c>
       <c r="B329" s="1" t="s">
-        <v>1148</v>
+        <v>1145</v>
       </c>
       <c r="C329" s="2">
         <v>14</v>
@@ -11283,18 +11283,18 @@
         <v>0</v>
       </c>
       <c r="E329" s="2" t="s">
-        <v>1155</v>
+        <v>1152</v>
       </c>
       <c r="H329" s="2" t="s">
-        <v>1156</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="330" spans="1:8">
       <c r="A330" s="2" t="s">
-        <v>1163</v>
+        <v>1160</v>
       </c>
       <c r="B330" s="1" t="s">
-        <v>1164</v>
+        <v>1161</v>
       </c>
       <c r="C330" s="2">
         <v>12</v>
@@ -11303,27 +11303,27 @@
         <v>0</v>
       </c>
       <c r="E330" s="2" t="s">
-        <v>1165</v>
+        <v>1162</v>
       </c>
       <c r="H330" s="7" t="s">
-        <v>1166</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="331" spans="1:8">
       <c r="A331" s="2" t="s">
-        <v>1191</v>
+        <v>1188</v>
       </c>
       <c r="B331" s="1" t="s">
+        <v>1189</v>
+      </c>
+      <c r="E331" s="2" t="s">
         <v>1192</v>
       </c>
-      <c r="E331" s="2" t="s">
-        <v>1195</v>
-      </c>
       <c r="F331" s="2">
         <v>1</v>
       </c>
       <c r="H331" t="s">
-        <v>954</v>
+        <v>951</v>
       </c>
     </row>
   </sheetData>

--- a/stores.xlsx
+++ b/stores.xlsx
@@ -8,15 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\YUMIN\Desktop\B0KT2A_RSVN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D6CA7BA-E5BD-480E-8EFE-14C766AAEE6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F7A76C2-3B30-4CB4-B9FB-2C7860ABE809}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{ABFC3117-FCCB-4FF3-804A-FE19451A2004}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{ABFC3117-FCCB-4FF3-804A-FE19451A2004}"/>
   </bookViews>
   <sheets>
     <sheet name="stores" sheetId="2" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -35,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1331" uniqueCount="1196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1332" uniqueCount="1197">
   <si>
     <t>룸익스케이프 WHITE</t>
   </si>
@@ -175,9 +174,6 @@
     <t>비트포비아 홍대던전3</t>
   </si>
   <si>
-    <t>그달동네,이미지세탁소,경성연쇄실종사건,AND I MET E,앤아멧이</t>
-  </si>
-  <si>
     <t>비트포비아 강남던전</t>
   </si>
   <si>
@@ -710,9 +706,6 @@
   </si>
   <si>
     <t>상상의 문 수원2호점</t>
-  </si>
-  <si>
-    <t>성지기숙학원:특수교정반,낙화:떨어지는 꽃,알케이드 빌리지</t>
   </si>
   <si>
     <t>상상의 문 부평점</t>
@@ -4189,6 +4182,18 @@
   </si>
   <si>
     <t>강천여자고등학교,강천여고,자각몽</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>그달동네,이미지세탁소,경성연쇄실종사건,AND I MET E,앤아멧이,이세소</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>오시리스,OSIRIS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>성지기숙학원:특수교정반,낙화:떨어지는 꽃,알케이드 빌리지,OKCUT,오케이컷,OK컷,HINDSIGHT,하인드사이트,춘화각:피할수없는저주</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -4631,7 +4636,7 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="2" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>11</v>
@@ -4657,10 +4662,10 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="2" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="C2" s="2">
         <v>7</v>
@@ -4669,18 +4674,18 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>1194</v>
+        <v>1192</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="2" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="C3" s="2">
         <v>7</v>
@@ -4689,33 +4694,33 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>1195</v>
+        <v>1193</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="2" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="C4" s="2">
         <v>7</v>
       </c>
       <c r="D4" s="6"/>
       <c r="H4" s="2" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="2" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C5" s="3">
         <v>6</v>
@@ -4724,20 +4729,20 @@
         <v>0</v>
       </c>
       <c r="E5" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="F5" s="3"/>
       <c r="G5" s="1"/>
       <c r="H5" s="1" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="2" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C6" s="3">
         <v>7</v>
@@ -4746,40 +4751,40 @@
         <v>0</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="F6" s="3"/>
       <c r="G6" s="1"/>
       <c r="H6" s="1" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="2" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C7" s="3"/>
       <c r="D7" s="4"/>
       <c r="E7" s="1" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="F7" s="3">
         <v>1</v>
       </c>
       <c r="G7" s="1"/>
       <c r="H7" s="1" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="2" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C8" s="3">
         <v>7</v>
@@ -4788,20 +4793,20 @@
         <v>0</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="F8" s="3"/>
       <c r="G8" s="1"/>
       <c r="H8" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="2" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C9" s="3">
         <v>7</v>
@@ -4810,64 +4815,64 @@
         <v>0</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="F9" s="3"/>
       <c r="G9" s="1"/>
       <c r="H9" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="2" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C10" s="3"/>
       <c r="D10" s="4"/>
       <c r="E10" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F10" s="3">
         <v>1</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>1130</v>
+        <v>1128</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="2" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C11" s="3"/>
       <c r="D11" s="4"/>
       <c r="E11" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F11" s="3">
         <v>1</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>1130</v>
+        <v>1128</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C12" s="3">
         <v>9</v>
@@ -4876,20 +4881,20 @@
         <v>0</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="F12" s="3"/>
       <c r="G12" s="1"/>
       <c r="H12" s="1" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="2" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C13" s="3">
         <v>9</v>
@@ -4898,20 +4903,20 @@
         <v>0</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="F13" s="3"/>
       <c r="G13" s="1"/>
       <c r="H13" s="1" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="2" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C14" s="3">
         <v>9</v>
@@ -4920,20 +4925,20 @@
         <v>0</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="F14" s="3"/>
       <c r="G14" s="1"/>
       <c r="H14" s="1" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="2" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C15" s="3">
         <v>6</v>
@@ -4942,20 +4947,20 @@
         <v>0</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="F15" s="3"/>
       <c r="G15" s="1"/>
       <c r="H15" s="1" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="2" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C16" s="3">
         <v>6</v>
@@ -4964,20 +4969,20 @@
         <v>0</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="F16" s="3"/>
       <c r="G16" s="1"/>
       <c r="H16" s="7" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="2" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C17" s="3">
         <v>13</v>
@@ -4986,20 +4991,20 @@
         <v>0</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>1126</v>
+        <v>1124</v>
       </c>
       <c r="F17" s="3"/>
       <c r="G17" s="1"/>
       <c r="H17" s="1" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="2" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C18" s="3">
         <v>7</v>
@@ -5008,20 +5013,20 @@
         <v>0</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F18" s="3"/>
       <c r="G18" s="1"/>
       <c r="H18" s="1" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="2" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C19" s="3">
         <v>27</v>
@@ -5030,20 +5035,20 @@
         <v>0</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F19" s="3"/>
       <c r="G19" s="1"/>
       <c r="H19" s="1" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="2" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C20" s="3">
         <v>7</v>
@@ -5052,20 +5057,20 @@
         <v>0</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="F20" s="3"/>
       <c r="G20" s="1"/>
       <c r="H20" s="1" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="2" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C21" s="3">
         <v>28</v>
@@ -5074,40 +5079,40 @@
         <v>0</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F21" s="3"/>
       <c r="G21" s="1"/>
       <c r="H21" s="1" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="2" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C22" s="3"/>
       <c r="D22" s="4"/>
       <c r="E22" s="1" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="F22" s="3">
         <v>1</v>
       </c>
       <c r="G22" s="1"/>
       <c r="H22" s="1" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="2" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C23" s="3">
         <v>28</v>
@@ -5116,20 +5121,20 @@
         <v>0</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F23" s="3"/>
       <c r="G23" s="1"/>
       <c r="H23" s="1" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="2" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C24" s="3">
         <v>28</v>
@@ -5138,20 +5143,20 @@
         <v>0</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F24" s="3"/>
       <c r="G24" s="1"/>
       <c r="H24" s="1" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="2" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="C25" s="3">
         <v>15</v>
@@ -5160,20 +5165,20 @@
         <v>0</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="F25" s="3"/>
       <c r="G25" s="1"/>
       <c r="H25" s="11" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="2" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="C26" s="3">
         <v>6</v>
@@ -5182,19 +5187,19 @@
         <v>0</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="F26" s="3"/>
       <c r="H26" s="1" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="2" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="C27" s="3">
         <v>6</v>
@@ -5203,19 +5208,19 @@
         <v>0</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="F27" s="3"/>
       <c r="H27" s="1" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="2" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C28" s="3">
         <v>6</v>
@@ -5224,20 +5229,20 @@
         <v>0</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F28" s="3"/>
       <c r="G28" s="1"/>
       <c r="H28" s="1" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="2" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C29" s="3">
         <v>6</v>
@@ -5246,37 +5251,37 @@
         <v>0</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="F29" s="3"/>
       <c r="G29" s="1"/>
       <c r="H29" s="1" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="2" t="s">
+        <v>781</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>782</v>
+      </c>
+      <c r="E30" s="1" t="s">
         <v>783</v>
       </c>
-      <c r="B30" s="1" t="s">
-        <v>784</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>785</v>
-      </c>
       <c r="F30" s="3">
         <v>1</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="2" t="s">
+        <v>793</v>
+      </c>
+      <c r="B31" s="1" t="s">
         <v>795</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>797</v>
       </c>
       <c r="C31" s="2">
         <v>20</v>
@@ -5285,120 +5290,120 @@
         <v>0</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="2" t="s">
+        <v>768</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>769</v>
+      </c>
+      <c r="E32" s="1" t="s">
         <v>770</v>
       </c>
-      <c r="B32" s="1" t="s">
-        <v>771</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>772</v>
-      </c>
       <c r="F32" s="3">
         <v>1</v>
       </c>
       <c r="H32" s="7" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="2" t="s">
+        <v>764</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>765</v>
+      </c>
+      <c r="E33" s="1" t="s">
         <v>766</v>
       </c>
-      <c r="B33" s="1" t="s">
+      <c r="F33" s="3">
+        <v>1</v>
+      </c>
+      <c r="H33" s="2" t="s">
         <v>767</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>768</v>
-      </c>
-      <c r="F33" s="3">
-        <v>1</v>
-      </c>
-      <c r="H33" s="2" t="s">
-        <v>769</v>
       </c>
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="2" t="s">
+        <v>775</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>776</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>779</v>
+      </c>
+      <c r="F34" s="3">
+        <v>1</v>
+      </c>
+      <c r="H34" s="2" t="s">
         <v>777</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>778</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>781</v>
-      </c>
-      <c r="F34" s="3">
-        <v>1</v>
-      </c>
-      <c r="H34" s="2" t="s">
-        <v>779</v>
       </c>
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="2" t="s">
+        <v>789</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>790</v>
+      </c>
+      <c r="E35" s="1" t="s">
         <v>791</v>
       </c>
-      <c r="B35" s="1" t="s">
-        <v>792</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>793</v>
-      </c>
       <c r="F35" s="3">
         <v>1</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
     </row>
     <row r="36" spans="1:8">
       <c r="A36" s="2" t="s">
+        <v>785</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>786</v>
+      </c>
+      <c r="E36" s="1" t="s">
         <v>787</v>
       </c>
-      <c r="B36" s="1" t="s">
-        <v>788</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>789</v>
-      </c>
       <c r="F36" s="3">
         <v>1</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
     </row>
     <row r="37" spans="1:8">
       <c r="A37" s="2" t="s">
+        <v>772</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>773</v>
+      </c>
+      <c r="E37" s="1" t="s">
         <v>774</v>
       </c>
-      <c r="B37" s="1" t="s">
-        <v>775</v>
-      </c>
-      <c r="E37" s="1" t="s">
-        <v>776</v>
-      </c>
       <c r="F37" s="3">
         <v>1</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
     </row>
     <row r="38" spans="1:8">
       <c r="A38" s="2" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C38" s="3">
         <v>6</v>
@@ -5407,57 +5412,57 @@
         <v>0</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="F38" s="3"/>
       <c r="G38" s="1"/>
       <c r="H38" s="2" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
     </row>
     <row r="39" spans="1:8">
       <c r="A39" s="2" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="F39" s="3">
         <v>1</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
     </row>
     <row r="40" spans="1:8">
       <c r="A40" s="2" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="B40" s="1" t="s">
+        <v>683</v>
+      </c>
+      <c r="E40" s="1" t="s">
         <v>685</v>
       </c>
-      <c r="E40" s="1" t="s">
-        <v>687</v>
-      </c>
       <c r="F40" s="3">
         <v>1</v>
       </c>
       <c r="H40" s="9" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
     </row>
     <row r="41" spans="1:8">
       <c r="A41" s="2" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="F41" s="3">
         <v>1</v>
@@ -5465,10 +5470,10 @@
     </row>
     <row r="42" spans="1:8">
       <c r="A42" s="2" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C42" s="3">
         <v>6</v>
@@ -5477,40 +5482,40 @@
         <v>0</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F42" s="3"/>
       <c r="G42" s="1"/>
       <c r="H42" s="1" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
     </row>
     <row r="43" spans="1:8">
       <c r="A43" s="2" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C43" s="3"/>
       <c r="D43" s="4"/>
       <c r="E43" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F43" s="3">
         <v>1</v>
       </c>
       <c r="G43" s="1"/>
       <c r="H43" s="1" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
     </row>
     <row r="44" spans="1:8">
       <c r="A44" s="2" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C44" s="3">
         <v>6</v>
@@ -5519,20 +5524,20 @@
         <v>0</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F44" s="3"/>
       <c r="G44" s="1"/>
       <c r="H44" s="1" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
     </row>
     <row r="45" spans="1:8">
       <c r="A45" s="2" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C45" s="3">
         <v>6</v>
@@ -5541,20 +5546,20 @@
         <v>0</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F45" s="3"/>
       <c r="G45" s="1"/>
       <c r="H45" s="1" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
     </row>
     <row r="46" spans="1:8">
       <c r="A46" s="2" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C46" s="3">
         <v>6</v>
@@ -5563,60 +5568,60 @@
         <v>0</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F46" s="3"/>
       <c r="G46" s="1"/>
       <c r="H46" s="1" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
     </row>
     <row r="47" spans="1:8">
       <c r="A47" s="2" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C47" s="3"/>
       <c r="D47" s="4"/>
       <c r="E47" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="F47" s="3">
         <v>1</v>
       </c>
       <c r="G47" s="1"/>
       <c r="H47" s="1" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
     </row>
     <row r="48" spans="1:8">
       <c r="A48" s="2" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C48" s="3"/>
       <c r="D48" s="4"/>
       <c r="E48" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F48" s="3">
         <v>1</v>
       </c>
       <c r="G48" s="1"/>
       <c r="H48" s="1" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
     </row>
     <row r="49" spans="1:8">
       <c r="A49" s="2" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C49" s="3">
         <v>6</v>
@@ -5625,17 +5630,17 @@
         <v>0</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F49" s="3"/>
       <c r="G49" s="1"/>
       <c r="H49" s="1" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
     </row>
     <row r="50" spans="1:8">
       <c r="A50" s="2" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>8</v>
@@ -5647,20 +5652,20 @@
         <v>0</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="F50" s="3"/>
       <c r="G50" s="1"/>
       <c r="H50" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
     </row>
     <row r="51" spans="1:8">
       <c r="A51" s="2" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C51" s="3">
         <v>14</v>
@@ -5669,20 +5674,20 @@
         <v>0</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="F51" s="3"/>
       <c r="G51" s="1"/>
       <c r="H51" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
     </row>
     <row r="52" spans="1:8">
       <c r="A52" s="2" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C52" s="3">
         <v>15</v>
@@ -5691,20 +5696,20 @@
         <v>0.95833333333333337</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="F52" s="3"/>
       <c r="G52" s="1"/>
       <c r="H52" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
     </row>
     <row r="53" spans="1:8">
       <c r="A53" s="2" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C53" s="3">
         <v>7</v>
@@ -5713,20 +5718,20 @@
         <v>0.97916666666666663</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="F53" s="3"/>
       <c r="G53" s="1"/>
       <c r="H53" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
     </row>
     <row r="54" spans="1:8">
       <c r="A54" s="2" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C54" s="3">
         <v>6</v>
@@ -5735,20 +5740,20 @@
         <v>0</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F54" s="3"/>
       <c r="G54" s="1"/>
       <c r="H54" s="1" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
     </row>
     <row r="55" spans="1:8">
       <c r="A55" s="2" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C55" s="1">
         <v>13</v>
@@ -5757,45 +5762,45 @@
         <v>0</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="F55" s="1"/>
       <c r="G55" s="1"/>
       <c r="H55" s="1" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
     </row>
     <row r="56" spans="1:8">
       <c r="A56" s="2" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C56" s="1"/>
       <c r="D56" s="1"/>
       <c r="E56" s="1" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="F56" s="3">
         <v>1</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>1131</v>
+        <v>1129</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
     </row>
     <row r="57" spans="1:8">
       <c r="A57" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="F57" s="2">
         <v>1</v>
@@ -5803,49 +5808,49 @@
     </row>
     <row r="58" spans="1:8">
       <c r="A58" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="F58" s="3">
         <v>1</v>
       </c>
       <c r="H58" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
     </row>
     <row r="59" spans="1:8">
       <c r="A59" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="C59" s="3"/>
       <c r="D59" s="6"/>
       <c r="E59" s="1" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="F59" s="3">
         <v>1</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>1157</v>
+        <v>1155</v>
       </c>
       <c r="H59" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
     </row>
     <row r="60" spans="1:8">
       <c r="A60" s="2" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C60" s="3">
         <v>7</v>
@@ -5854,20 +5859,20 @@
         <v>0.875</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F60" s="3"/>
       <c r="G60" s="1"/>
       <c r="H60" s="1" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
     </row>
     <row r="61" spans="1:8">
       <c r="A61" s="11" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="B61" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="C61">
         <v>6</v>
@@ -5876,20 +5881,20 @@
         <v>0</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="F61" s="3"/>
       <c r="G61" s="1"/>
       <c r="H61" s="1" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
     </row>
     <row r="62" spans="1:8">
       <c r="A62" s="2" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C62" s="3">
         <v>6</v>
@@ -5898,40 +5903,40 @@
         <v>0</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="F62" s="3"/>
       <c r="G62" s="1"/>
       <c r="H62" s="1" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
     </row>
     <row r="63" spans="1:8">
       <c r="A63" s="2" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C63" s="3"/>
       <c r="D63" s="5"/>
       <c r="E63" s="1" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="F63" s="3">
         <v>1</v>
       </c>
       <c r="G63" s="1"/>
       <c r="H63" s="1" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
     </row>
     <row r="64" spans="1:8">
       <c r="A64" s="2" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C64" s="3">
         <v>6</v>
@@ -5940,17 +5945,17 @@
         <v>0</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="F64" s="3"/>
       <c r="G64" s="1"/>
       <c r="H64" s="1" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
     </row>
     <row r="65" spans="1:8">
       <c r="A65" s="2" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>2</v>
@@ -5967,12 +5972,12 @@
       <c r="F65" s="3"/>
       <c r="G65" s="1"/>
       <c r="H65" s="2" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
     </row>
     <row r="66" spans="1:8">
       <c r="A66" s="2" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>6</v>
@@ -5989,12 +5994,12 @@
       <c r="F66" s="3"/>
       <c r="G66" s="1"/>
       <c r="H66" s="2" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
     </row>
     <row r="67" spans="1:8">
       <c r="A67" s="2" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>4</v>
@@ -6011,12 +6016,12 @@
       <c r="F67" s="3"/>
       <c r="G67" s="1"/>
       <c r="H67" s="2" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
     </row>
     <row r="68" spans="1:8">
       <c r="A68" s="2" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>0</v>
@@ -6033,15 +6038,15 @@
       <c r="F68" s="3"/>
       <c r="G68" s="1"/>
       <c r="H68" s="2" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
     </row>
     <row r="69" spans="1:8">
       <c r="A69" s="2" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C69" s="3">
         <v>7</v>
@@ -6050,76 +6055,76 @@
         <v>0</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="F69" s="3"/>
       <c r="H69" s="1" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
     </row>
     <row r="70" spans="1:8">
       <c r="A70" s="2" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C70" s="3"/>
       <c r="D70" s="4"/>
       <c r="E70" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F70" s="3">
         <v>1</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
     </row>
     <row r="71" spans="1:8">
       <c r="A71" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C71" s="3"/>
       <c r="D71" s="4"/>
       <c r="E71" s="1" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="F71" s="3">
         <v>1</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
     </row>
     <row r="72" spans="1:8">
       <c r="A72" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C72" s="3"/>
       <c r="D72" s="4"/>
       <c r="E72" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F72" s="3">
         <v>1</v>
       </c>
       <c r="H72" s="1" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
     </row>
     <row r="73" spans="1:8">
       <c r="A73" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C73" s="3">
         <v>15</v>
@@ -6128,19 +6133,19 @@
         <v>0</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F73" s="3"/>
       <c r="H73" s="1" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
     </row>
     <row r="74" spans="1:8">
       <c r="A74" s="2" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C74" s="3">
         <v>15</v>
@@ -6149,76 +6154,76 @@
         <v>0</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F74" s="3"/>
       <c r="H74" s="1" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
     </row>
     <row r="75" spans="1:8">
       <c r="A75" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C75" s="3"/>
       <c r="D75" s="4"/>
       <c r="E75" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F75" s="3">
         <v>1</v>
       </c>
       <c r="H75" s="1" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
     </row>
     <row r="76" spans="1:8">
       <c r="A76" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C76" s="3"/>
       <c r="D76" s="4"/>
       <c r="E76" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F76" s="3">
         <v>1</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
     </row>
     <row r="77" spans="1:8">
       <c r="A77" s="2" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C77" s="3"/>
       <c r="D77" s="4"/>
       <c r="E77" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F77" s="3">
         <v>1</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
     </row>
     <row r="78" spans="1:8">
       <c r="A78" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C78" s="3">
         <v>15</v>
@@ -6227,38 +6232,38 @@
         <v>0</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F78" s="3"/>
       <c r="H78" s="1" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
     </row>
     <row r="79" spans="1:8">
       <c r="A79" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C79" s="3"/>
       <c r="D79" s="4"/>
       <c r="E79" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F79" s="3">
         <v>1</v>
       </c>
       <c r="H79" s="1" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
     </row>
     <row r="80" spans="1:8">
       <c r="A80" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C80" s="3">
         <v>15</v>
@@ -6267,19 +6272,19 @@
         <v>0</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F80" s="3"/>
       <c r="H80" s="1" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
     </row>
     <row r="81" spans="1:8">
       <c r="A81" s="2" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C81" s="3">
         <v>7</v>
@@ -6288,19 +6293,19 @@
         <v>0</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F81" s="3"/>
       <c r="H81" s="1" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
     </row>
     <row r="82" spans="1:8">
       <c r="A82" s="2" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C82" s="3">
         <v>7</v>
@@ -6309,19 +6314,19 @@
         <v>0</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F82" s="3"/>
       <c r="H82" s="1" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
     </row>
     <row r="83" spans="1:8">
       <c r="A83" s="2" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C83" s="3">
         <v>14</v>
@@ -6330,114 +6335,114 @@
         <v>0</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F83" s="3"/>
       <c r="H83" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
     </row>
     <row r="84" spans="1:8">
       <c r="A84" s="2" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C84" s="3"/>
       <c r="D84" s="4"/>
       <c r="E84" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F84" s="3">
         <v>1</v>
       </c>
       <c r="H84" s="1" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
     </row>
     <row r="85" spans="1:8">
       <c r="A85" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C85" s="3"/>
       <c r="D85" s="4"/>
       <c r="E85" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F85" s="3">
         <v>1</v>
       </c>
       <c r="H85" s="1" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
     </row>
     <row r="86" spans="1:8">
       <c r="A86" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C86" s="3"/>
       <c r="D86" s="4"/>
       <c r="E86" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F86" s="3">
         <v>1</v>
       </c>
       <c r="H86" s="1" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
     </row>
     <row r="87" spans="1:8">
       <c r="A87" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C87" s="3"/>
       <c r="D87" s="4"/>
       <c r="E87" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F87" s="3">
         <v>1</v>
       </c>
       <c r="H87" s="1" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
     </row>
     <row r="88" spans="1:8">
       <c r="A88" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C88" s="3"/>
       <c r="D88" s="4"/>
       <c r="E88" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F88" s="3">
         <v>1</v>
       </c>
       <c r="H88" s="1" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
     </row>
     <row r="89" spans="1:8">
       <c r="A89" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C89" s="3">
         <v>15</v>
@@ -6446,55 +6451,55 @@
         <v>0</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F89" s="3"/>
       <c r="H89" s="1" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
     </row>
     <row r="90" spans="1:8">
       <c r="A90" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="B90" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="C90" s="3"/>
       <c r="D90" s="4"/>
       <c r="E90" s="1" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="F90" s="3">
         <v>1</v>
       </c>
       <c r="H90" s="11" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
     </row>
     <row r="91" spans="1:8">
       <c r="A91" s="2" t="s">
+        <v>813</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>814</v>
+      </c>
+      <c r="E91" s="1" t="s">
         <v>815</v>
       </c>
-      <c r="B91" s="1" t="s">
+      <c r="F91" s="3">
+        <v>1</v>
+      </c>
+      <c r="H91" s="7" t="s">
         <v>816</v>
-      </c>
-      <c r="E91" s="1" t="s">
-        <v>817</v>
-      </c>
-      <c r="F91" s="3">
-        <v>1</v>
-      </c>
-      <c r="H91" s="7" t="s">
-        <v>818</v>
       </c>
     </row>
     <row r="92" spans="1:8">
       <c r="A92" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C92" s="3">
         <v>7</v>
@@ -6503,20 +6508,20 @@
         <v>0</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F92" s="3"/>
       <c r="G92" s="1"/>
       <c r="H92" s="1" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
     </row>
     <row r="93" spans="1:8">
       <c r="A93" s="2" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="C93" s="3">
         <v>7</v>
@@ -6525,20 +6530,20 @@
         <v>0</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F93" s="3"/>
       <c r="G93" s="1"/>
       <c r="H93" s="1" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
     </row>
     <row r="94" spans="1:8">
       <c r="A94" s="2" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C94" s="3">
         <v>7</v>
@@ -6547,20 +6552,20 @@
         <v>0</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F94" s="3"/>
       <c r="G94" s="1"/>
       <c r="H94" s="1" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
     </row>
     <row r="95" spans="1:8">
       <c r="A95" s="2" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C95" s="3">
         <v>7</v>
@@ -6569,20 +6574,20 @@
         <v>0</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F95" s="3"/>
       <c r="G95" s="1"/>
       <c r="H95" s="1" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
     </row>
     <row r="96" spans="1:8">
       <c r="A96" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="C96" s="3">
         <v>7</v>
@@ -6591,20 +6596,20 @@
         <v>0</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F96" s="3"/>
       <c r="G96" s="1"/>
       <c r="H96" s="1" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
     </row>
     <row r="97" spans="1:8">
       <c r="A97" s="2" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="C97" s="3">
         <v>7</v>
@@ -6613,20 +6618,20 @@
         <v>0</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F97" s="3"/>
       <c r="G97" s="1"/>
       <c r="H97" s="1" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
     </row>
     <row r="98" spans="1:8">
       <c r="A98" s="2" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="C98" s="3">
         <v>7</v>
@@ -6635,275 +6640,275 @@
         <v>0</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F98" s="3"/>
       <c r="G98" s="1"/>
       <c r="H98" s="1" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
     </row>
     <row r="99" spans="1:8">
       <c r="A99" s="2" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="F99" s="3">
         <v>1</v>
       </c>
       <c r="H99" s="7" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
     </row>
     <row r="100" spans="1:8">
       <c r="A100" s="2" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="F100" s="3">
         <v>1</v>
       </c>
       <c r="H100" s="7" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
     </row>
     <row r="101" spans="1:8">
       <c r="A101" s="2" t="s">
+        <v>705</v>
+      </c>
+      <c r="B101" s="1" t="s">
         <v>707</v>
       </c>
-      <c r="B101" s="1" t="s">
-        <v>709</v>
-      </c>
       <c r="E101" s="1" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="F101" s="3">
         <v>1</v>
       </c>
       <c r="H101" s="7" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
     </row>
     <row r="102" spans="1:8">
       <c r="A102" s="2" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="F102" s="3">
         <v>1</v>
       </c>
       <c r="H102" s="7" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
     </row>
     <row r="103" spans="1:8">
       <c r="A103" s="2" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="F103" s="3">
         <v>1</v>
       </c>
       <c r="H103" s="7" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
     </row>
     <row r="104" spans="1:8">
       <c r="A104" s="2" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="F104" s="3">
         <v>1</v>
       </c>
       <c r="H104" s="7" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
     </row>
     <row r="105" spans="1:8">
       <c r="A105" s="2" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="F105" s="3">
         <v>1</v>
       </c>
       <c r="H105" s="7" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
     </row>
     <row r="106" spans="1:8">
       <c r="A106" s="2" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="F106" s="3">
         <v>1</v>
       </c>
       <c r="H106" s="7" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
     </row>
     <row r="107" spans="1:8">
       <c r="A107" s="2" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="F107" s="3">
         <v>1</v>
       </c>
       <c r="H107" s="7" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
     </row>
     <row r="108" spans="1:8">
       <c r="A108" s="2" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="F108" s="3">
         <v>1</v>
       </c>
       <c r="H108" s="7" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
     </row>
     <row r="109" spans="1:8">
       <c r="A109" s="2" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="F109" s="3">
         <v>1</v>
       </c>
       <c r="H109" s="7" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
     </row>
     <row r="110" spans="1:8">
       <c r="A110" s="2" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="F110" s="3">
         <v>1</v>
       </c>
       <c r="H110" s="7" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
     </row>
     <row r="111" spans="1:8">
       <c r="A111" s="2" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="F111" s="3">
         <v>1</v>
       </c>
       <c r="H111" s="7" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
     </row>
     <row r="112" spans="1:8">
       <c r="A112" s="2" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="F112" s="3">
         <v>1</v>
       </c>
       <c r="H112" s="7" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
     </row>
     <row r="113" spans="1:8">
       <c r="A113" s="2" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="F113" s="3">
         <v>1</v>
       </c>
       <c r="H113" s="7" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
     </row>
     <row r="114" spans="1:8">
       <c r="A114" s="2" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C114" s="3">
         <v>6</v>
@@ -6912,82 +6917,82 @@
         <v>0</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="F114" s="3"/>
       <c r="G114" s="1"/>
       <c r="H114" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
     </row>
     <row r="115" spans="1:8">
       <c r="A115" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="B115" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="C115" s="3"/>
       <c r="D115" s="4"/>
       <c r="E115" s="1" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="F115" s="3">
         <v>1</v>
       </c>
       <c r="G115" s="1"/>
       <c r="H115" s="11" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="116" spans="1:8">
       <c r="A116" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="B116" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="C116" s="3"/>
       <c r="D116" s="4"/>
       <c r="E116" s="1" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="F116" s="3">
         <v>1</v>
       </c>
       <c r="G116" s="1"/>
       <c r="H116" s="11" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
     </row>
     <row r="117" spans="1:8">
       <c r="A117" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="B117" t="s">
-        <v>1127</v>
+        <v>1125</v>
       </c>
       <c r="C117" s="3"/>
       <c r="D117" s="4"/>
       <c r="E117" s="1" t="s">
+        <v>842</v>
+      </c>
+      <c r="F117" s="3">
+        <v>1</v>
+      </c>
+      <c r="G117" s="1" t="s">
+        <v>843</v>
+      </c>
+      <c r="H117" s="11" t="s">
         <v>844</v>
-      </c>
-      <c r="F117" s="3">
-        <v>1</v>
-      </c>
-      <c r="G117" s="1" t="s">
-        <v>845</v>
-      </c>
-      <c r="H117" s="11" t="s">
-        <v>846</v>
       </c>
     </row>
     <row r="118" spans="1:8">
       <c r="A118" s="2" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C118" s="3">
         <v>7</v>
@@ -6996,20 +7001,20 @@
         <v>0</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F118" s="3"/>
       <c r="G118" s="1"/>
       <c r="H118" s="1" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
     </row>
     <row r="119" spans="1:8">
       <c r="A119" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="C119" s="3">
         <v>7</v>
@@ -7018,57 +7023,57 @@
         <v>0.95833333333333337</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F119" s="3"/>
       <c r="G119" s="1"/>
       <c r="H119" s="1" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
     </row>
     <row r="120" spans="1:8">
       <c r="A120" s="2" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C120" s="1"/>
       <c r="D120" s="5"/>
       <c r="E120" s="1" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="F120" s="3">
         <v>1</v>
       </c>
       <c r="G120" s="1"/>
       <c r="H120" s="1" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
     </row>
     <row r="121" spans="1:8">
       <c r="A121" s="2" t="s">
+        <v>800</v>
+      </c>
+      <c r="B121" s="1" t="s">
+        <v>801</v>
+      </c>
+      <c r="E121" s="1" t="s">
+        <v>803</v>
+      </c>
+      <c r="F121" s="3">
+        <v>1</v>
+      </c>
+      <c r="H121" s="7" t="s">
         <v>802</v>
-      </c>
-      <c r="B121" s="1" t="s">
-        <v>803</v>
-      </c>
-      <c r="E121" s="1" t="s">
-        <v>805</v>
-      </c>
-      <c r="F121" s="3">
-        <v>1</v>
-      </c>
-      <c r="H121" s="7" t="s">
-        <v>804</v>
       </c>
     </row>
     <row r="122" spans="1:8">
       <c r="A122" s="2" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C122" s="3">
         <v>14</v>
@@ -7077,125 +7082,125 @@
         <v>0</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="F122" s="3"/>
       <c r="G122" s="1"/>
       <c r="H122" s="1" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
     </row>
     <row r="123" spans="1:8">
       <c r="A123" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="B123" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="C123"/>
       <c r="D123" s="11"/>
       <c r="E123" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="F123" s="1">
         <v>1</v>
       </c>
       <c r="G123"/>
       <c r="H123" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
     </row>
     <row r="124" spans="1:8">
       <c r="A124" t="s">
-        <v>1193</v>
+        <v>1191</v>
       </c>
       <c r="B124" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="E124" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="F124" s="1">
         <v>1</v>
       </c>
       <c r="H124" t="s">
-        <v>876</v>
+        <v>874</v>
       </c>
     </row>
     <row r="125" spans="1:8">
       <c r="A125" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="B125" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="E125" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="F125" s="1">
         <v>1</v>
       </c>
       <c r="H125" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
     </row>
     <row r="126" spans="1:8">
       <c r="A126" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="B126" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="E126" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
       <c r="F126" s="1">
         <v>1</v>
       </c>
       <c r="H126" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
     </row>
     <row r="127" spans="1:8">
       <c r="A127" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="B127" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
       <c r="E127" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="F127" s="1">
         <v>1</v>
       </c>
       <c r="H127" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
     </row>
     <row r="128" spans="1:8">
       <c r="A128" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
       <c r="B128" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="E128" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="F128" s="1">
         <v>1</v>
       </c>
       <c r="H128" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
     </row>
     <row r="129" spans="1:8">
       <c r="A129" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="B129" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="C129" s="2">
         <v>6</v>
@@ -7204,36 +7209,36 @@
         <v>0</v>
       </c>
       <c r="E129" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="F129" s="1"/>
       <c r="H129" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
     </row>
     <row r="130" spans="1:8">
       <c r="A130" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="B130" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="E130" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="F130" s="1">
         <v>1</v>
       </c>
       <c r="H130" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
     </row>
     <row r="131" spans="1:8">
       <c r="A131" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="B131" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="C131" s="2">
         <v>6</v>
@@ -7242,53 +7247,53 @@
         <v>0</v>
       </c>
       <c r="E131" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="F131" s="1"/>
       <c r="H131" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
     </row>
     <row r="132" spans="1:8">
       <c r="A132" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="B132" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="E132" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
       <c r="F132" s="1">
         <v>1</v>
       </c>
       <c r="H132" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
     </row>
     <row r="133" spans="1:8">
       <c r="A133" t="s">
+        <v>1051</v>
+      </c>
+      <c r="B133" t="s">
+        <v>1052</v>
+      </c>
+      <c r="E133" t="s">
         <v>1053</v>
       </c>
-      <c r="B133" t="s">
-        <v>1054</v>
-      </c>
-      <c r="E133" t="s">
-        <v>1055</v>
-      </c>
       <c r="F133" s="1">
         <v>1</v>
       </c>
       <c r="H133" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
     </row>
     <row r="134" spans="1:8">
       <c r="A134" s="2" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C134" s="3">
         <v>6</v>
@@ -7297,20 +7302,20 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F134" s="3"/>
       <c r="G134" s="1"/>
       <c r="H134" s="2" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
     </row>
     <row r="135" spans="1:8">
       <c r="A135" s="2" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C135" s="3">
         <v>6</v>
@@ -7319,20 +7324,20 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F135" s="3"/>
       <c r="G135" s="1"/>
       <c r="H135" s="2" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
     </row>
     <row r="136" spans="1:8">
       <c r="A136" s="2" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C136" s="3">
         <v>6</v>
@@ -7341,17 +7346,17 @@
         <v>0</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="F136" s="3"/>
       <c r="G136" s="1"/>
       <c r="H136" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
     </row>
     <row r="137" spans="1:8">
       <c r="A137" s="2" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B137" s="1" t="s">
         <v>43</v>
@@ -7368,15 +7373,15 @@
       <c r="F137" s="3"/>
       <c r="G137" s="1"/>
       <c r="H137" s="2" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
     </row>
     <row r="138" spans="1:8">
       <c r="A138" s="2" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C138" s="3">
         <v>6</v>
@@ -7385,20 +7390,20 @@
         <v>0.75</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F138" s="3"/>
       <c r="G138" s="1"/>
       <c r="H138" s="2" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
     </row>
     <row r="139" spans="1:8">
       <c r="A139" s="2" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C139" s="3">
         <v>6</v>
@@ -7407,20 +7412,20 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F139" s="3"/>
       <c r="G139" s="1"/>
       <c r="H139" s="2" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
     </row>
     <row r="140" spans="1:8">
       <c r="A140" s="2" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C140" s="3">
         <v>6</v>
@@ -7429,20 +7434,20 @@
         <v>0</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="F140" s="3"/>
       <c r="G140" s="1"/>
       <c r="H140" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
     </row>
     <row r="141" spans="1:8">
       <c r="A141" s="2" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C141" s="3">
         <v>6</v>
@@ -7451,20 +7456,20 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F141" s="3"/>
       <c r="G141" s="1"/>
       <c r="H141" s="2" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
     </row>
     <row r="142" spans="1:8">
       <c r="A142" s="2" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="C142" s="3">
         <v>6</v>
@@ -7473,17 +7478,17 @@
         <v>0.875</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="F142" s="3"/>
       <c r="G142" s="1"/>
       <c r="H142" s="2" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
     </row>
     <row r="143" spans="1:8">
       <c r="A143" s="2" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B143" s="1" t="s">
         <v>41</v>
@@ -7500,12 +7505,12 @@
       <c r="F143" s="3"/>
       <c r="G143" s="1"/>
       <c r="H143" s="2" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
     </row>
     <row r="144" spans="1:8">
       <c r="A144" s="2" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="B144" s="1" t="s">
         <v>45</v>
@@ -7517,20 +7522,20 @@
         <v>0.625</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>46</v>
+        <v>1194</v>
       </c>
       <c r="F144" s="3"/>
       <c r="G144" s="1"/>
       <c r="H144" s="2" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
     </row>
     <row r="145" spans="1:8">
       <c r="A145" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C145" s="3">
         <v>6</v>
@@ -7539,20 +7544,20 @@
         <v>0</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F145" s="3"/>
       <c r="G145" s="1"/>
       <c r="H145" s="1" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
     </row>
     <row r="146" spans="1:8">
       <c r="A146" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C146" s="3">
         <v>6</v>
@@ -7561,20 +7566,20 @@
         <v>0</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F146" s="3"/>
       <c r="G146" s="1"/>
       <c r="H146" s="1" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
     </row>
     <row r="147" spans="1:8">
       <c r="A147" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C147" s="3">
         <v>6</v>
@@ -7583,20 +7588,20 @@
         <v>0</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="F147" s="3"/>
       <c r="G147" s="1"/>
       <c r="H147" s="1" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
     </row>
     <row r="148" spans="1:8">
       <c r="A148" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C148" s="3">
         <v>6</v>
@@ -7605,20 +7610,20 @@
         <v>0</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F148" s="3"/>
       <c r="G148" s="1"/>
       <c r="H148" s="1" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
     </row>
     <row r="149" spans="1:8">
       <c r="A149" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C149" s="3">
         <v>6</v>
@@ -7627,20 +7632,20 @@
         <v>0</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>225</v>
+        <v>1196</v>
       </c>
       <c r="F149" s="3"/>
       <c r="G149" s="1"/>
       <c r="H149" s="1" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
     </row>
     <row r="150" spans="1:8">
       <c r="A150" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C150" s="3">
         <v>6</v>
@@ -7649,20 +7654,20 @@
         <v>0</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F150" s="3"/>
       <c r="G150" s="1"/>
       <c r="H150" s="1" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
     </row>
     <row r="151" spans="1:8">
       <c r="A151" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C151" s="3">
         <v>6</v>
@@ -7671,20 +7676,20 @@
         <v>0</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F151" s="3"/>
       <c r="G151" s="1"/>
       <c r="H151" s="1" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
     </row>
     <row r="152" spans="1:8">
       <c r="A152" s="11" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
       <c r="B152" s="11" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="C152">
         <v>14</v>
@@ -7692,499 +7697,501 @@
       <c r="D152" s="4">
         <v>0</v>
       </c>
-      <c r="E152"/>
+      <c r="E152" s="1" t="s">
+        <v>1195</v>
+      </c>
       <c r="F152"/>
       <c r="G152"/>
       <c r="H152" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
     </row>
     <row r="153" spans="1:8">
       <c r="A153" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
       <c r="B153" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="C153"/>
       <c r="D153"/>
       <c r="E153" t="s">
-        <v>950</v>
+        <v>948</v>
       </c>
       <c r="F153">
         <v>1</v>
       </c>
       <c r="G153"/>
       <c r="H153" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
     </row>
     <row r="154" spans="1:8">
       <c r="A154" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
       <c r="B154" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
       <c r="C154"/>
       <c r="D154"/>
       <c r="E154" t="s">
-        <v>952</v>
+        <v>950</v>
       </c>
       <c r="F154">
         <v>1</v>
       </c>
       <c r="G154"/>
       <c r="H154" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
     </row>
     <row r="155" spans="1:8">
       <c r="A155" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
       <c r="B155" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="C155"/>
       <c r="D155"/>
       <c r="E155" t="s">
-        <v>953</v>
+        <v>951</v>
       </c>
       <c r="F155">
         <v>1</v>
       </c>
       <c r="G155"/>
       <c r="H155" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
     </row>
     <row r="156" spans="1:8">
       <c r="A156" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="B156" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
       <c r="C156"/>
       <c r="D156"/>
       <c r="E156" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="F156">
         <v>1</v>
       </c>
       <c r="G156"/>
       <c r="H156" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
     </row>
     <row r="157" spans="1:8">
       <c r="A157" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="B157" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="C157"/>
       <c r="D157"/>
       <c r="E157" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
       <c r="F157">
         <v>1</v>
       </c>
       <c r="G157"/>
       <c r="H157" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
     </row>
     <row r="158" spans="1:8">
       <c r="A158" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="B158" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="C158"/>
       <c r="D158"/>
       <c r="E158" t="s">
-        <v>956</v>
+        <v>954</v>
       </c>
       <c r="F158">
         <v>1</v>
       </c>
       <c r="G158"/>
       <c r="H158" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
     </row>
     <row r="159" spans="1:8">
       <c r="A159" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="B159" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="C159"/>
       <c r="D159"/>
       <c r="E159" t="s">
-        <v>957</v>
+        <v>955</v>
       </c>
       <c r="F159">
         <v>1</v>
       </c>
       <c r="G159"/>
       <c r="H159" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
     </row>
     <row r="160" spans="1:8">
       <c r="A160" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="B160" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="C160"/>
       <c r="D160"/>
       <c r="E160" t="s">
-        <v>958</v>
+        <v>956</v>
       </c>
       <c r="F160">
         <v>1</v>
       </c>
       <c r="G160"/>
       <c r="H160" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
     </row>
     <row r="161" spans="1:8">
       <c r="A161" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="B161" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="C161"/>
       <c r="D161"/>
       <c r="E161" t="s">
-        <v>959</v>
+        <v>957</v>
       </c>
       <c r="F161">
         <v>1</v>
       </c>
       <c r="G161"/>
       <c r="H161" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
     </row>
     <row r="162" spans="1:8">
       <c r="A162" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
       <c r="B162" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
       <c r="C162"/>
       <c r="D162"/>
       <c r="E162" t="s">
-        <v>960</v>
+        <v>958</v>
       </c>
       <c r="F162">
         <v>1</v>
       </c>
       <c r="G162"/>
       <c r="H162" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
     </row>
     <row r="163" spans="1:8">
       <c r="A163" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="B163" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
       <c r="C163"/>
       <c r="D163"/>
       <c r="E163" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
       <c r="F163">
         <v>1</v>
       </c>
       <c r="G163"/>
       <c r="H163" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
     </row>
     <row r="164" spans="1:8">
       <c r="A164" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="B164" s="12" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
       <c r="C164"/>
       <c r="D164"/>
       <c r="E164" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
       <c r="F164">
         <v>1</v>
       </c>
       <c r="G164"/>
       <c r="H164" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
     </row>
     <row r="165" spans="1:8">
       <c r="A165" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
       <c r="B165" t="s">
-        <v>904</v>
+        <v>902</v>
       </c>
       <c r="C165"/>
       <c r="D165"/>
       <c r="E165" t="s">
-        <v>963</v>
+        <v>961</v>
       </c>
       <c r="F165">
         <v>1</v>
       </c>
       <c r="G165"/>
       <c r="H165" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
     </row>
     <row r="166" spans="1:8">
       <c r="A166" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
       <c r="B166" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
       <c r="C166"/>
       <c r="D166"/>
       <c r="E166" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
       <c r="F166">
         <v>1</v>
       </c>
       <c r="G166"/>
       <c r="H166" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
     </row>
     <row r="167" spans="1:8">
       <c r="A167" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
       <c r="B167" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
       <c r="C167"/>
       <c r="D167"/>
       <c r="E167" t="s">
-        <v>966</v>
+        <v>964</v>
       </c>
       <c r="F167">
         <v>1</v>
       </c>
       <c r="G167"/>
       <c r="H167" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
     </row>
     <row r="168" spans="1:8">
       <c r="A168" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="B168" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="C168"/>
       <c r="D168"/>
       <c r="E168" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
       <c r="F168">
         <v>1</v>
       </c>
       <c r="G168"/>
       <c r="H168" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
     </row>
     <row r="169" spans="1:8">
       <c r="A169" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="B169" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="C169"/>
       <c r="D169"/>
       <c r="E169" t="s">
-        <v>968</v>
+        <v>966</v>
       </c>
       <c r="F169">
         <v>1</v>
       </c>
       <c r="G169"/>
       <c r="H169" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
     </row>
     <row r="170" spans="1:8">
       <c r="A170" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="B170" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
       <c r="C170"/>
       <c r="D170"/>
       <c r="E170" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
       <c r="F170">
         <v>1</v>
       </c>
       <c r="G170"/>
       <c r="H170" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
     </row>
     <row r="171" spans="1:8">
       <c r="A171" t="s">
-        <v>915</v>
+        <v>913</v>
       </c>
       <c r="B171" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
       <c r="C171"/>
       <c r="D171"/>
       <c r="E171" t="s">
-        <v>970</v>
+        <v>968</v>
       </c>
       <c r="F171">
         <v>1</v>
       </c>
       <c r="G171"/>
       <c r="H171" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
     </row>
     <row r="172" spans="1:8">
       <c r="A172" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="B172" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="C172"/>
       <c r="D172"/>
       <c r="E172" t="s">
-        <v>971</v>
+        <v>969</v>
       </c>
       <c r="F172">
         <v>1</v>
       </c>
       <c r="G172"/>
       <c r="H172" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
     </row>
     <row r="173" spans="1:8">
       <c r="A173" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
       <c r="B173" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
       <c r="C173"/>
       <c r="D173"/>
       <c r="E173" t="s">
-        <v>972</v>
+        <v>970</v>
       </c>
       <c r="F173">
         <v>1</v>
       </c>
       <c r="G173"/>
       <c r="H173" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
     </row>
     <row r="174" spans="1:8">
       <c r="A174" t="s">
-        <v>921</v>
+        <v>919</v>
       </c>
       <c r="B174" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="C174"/>
       <c r="D174"/>
       <c r="E174" t="s">
-        <v>973</v>
+        <v>971</v>
       </c>
       <c r="F174">
         <v>1</v>
       </c>
       <c r="G174"/>
       <c r="H174" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
     </row>
     <row r="175" spans="1:8">
       <c r="A175" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
       <c r="B175" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
       <c r="C175"/>
       <c r="D175"/>
       <c r="E175" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
       <c r="F175">
         <v>1</v>
       </c>
       <c r="G175"/>
       <c r="H175" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
     </row>
     <row r="176" spans="1:8">
       <c r="A176" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="B176" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="C176"/>
       <c r="D176"/>
       <c r="E176" t="s">
-        <v>975</v>
+        <v>973</v>
       </c>
       <c r="F176">
         <v>1</v>
       </c>
       <c r="G176"/>
       <c r="H176" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
     </row>
     <row r="177" spans="1:8">
       <c r="A177" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="B177" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="C177">
         <v>14</v>
@@ -8193,100 +8200,100 @@
         <v>0</v>
       </c>
       <c r="E177" t="s">
-        <v>976</v>
+        <v>974</v>
       </c>
       <c r="F177"/>
       <c r="G177"/>
       <c r="H177" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
     </row>
     <row r="178" spans="1:8">
       <c r="A178" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="B178" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="C178"/>
       <c r="D178"/>
       <c r="E178" t="s">
-        <v>977</v>
+        <v>975</v>
       </c>
       <c r="F178">
         <v>1</v>
       </c>
       <c r="G178"/>
       <c r="H178" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
     </row>
     <row r="179" spans="1:8">
       <c r="A179" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
       <c r="B179" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
       <c r="C179"/>
       <c r="D179"/>
       <c r="E179" t="s">
-        <v>978</v>
+        <v>976</v>
       </c>
       <c r="F179">
         <v>1</v>
       </c>
       <c r="G179"/>
       <c r="H179" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
     </row>
     <row r="180" spans="1:8">
       <c r="A180" s="12" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="B180" s="12" t="s">
-        <v>1044</v>
+        <v>1042</v>
       </c>
       <c r="C180"/>
       <c r="D180"/>
       <c r="E180" t="s">
-        <v>979</v>
+        <v>977</v>
       </c>
       <c r="F180">
         <v>1</v>
       </c>
       <c r="G180"/>
       <c r="H180" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
     </row>
     <row r="181" spans="1:8">
       <c r="A181" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
       <c r="B181" t="s">
-        <v>935</v>
+        <v>933</v>
       </c>
       <c r="C181"/>
       <c r="D181"/>
       <c r="E181" t="s">
-        <v>980</v>
+        <v>978</v>
       </c>
       <c r="F181">
         <v>1</v>
       </c>
       <c r="G181"/>
       <c r="H181" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
     </row>
     <row r="182" spans="1:8">
       <c r="A182" t="s">
-        <v>936</v>
+        <v>934</v>
       </c>
       <c r="B182" t="s">
-        <v>937</v>
+        <v>935</v>
       </c>
       <c r="C182">
         <v>14</v>
@@ -8295,160 +8302,160 @@
         <v>0</v>
       </c>
       <c r="E182" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="F182"/>
       <c r="G182"/>
       <c r="H182" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
     </row>
     <row r="183" spans="1:8">
       <c r="A183" t="s">
-        <v>938</v>
+        <v>936</v>
       </c>
       <c r="B183" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
       <c r="C183"/>
       <c r="D183"/>
       <c r="E183" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="F183">
         <v>1</v>
       </c>
       <c r="G183"/>
       <c r="H183" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
     </row>
     <row r="184" spans="1:8">
       <c r="A184" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
       <c r="B184" t="s">
-        <v>941</v>
+        <v>939</v>
       </c>
       <c r="C184"/>
       <c r="D184"/>
       <c r="E184" t="s">
-        <v>983</v>
+        <v>981</v>
       </c>
       <c r="F184">
         <v>1</v>
       </c>
       <c r="G184"/>
       <c r="H184" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
     </row>
     <row r="185" spans="1:8">
       <c r="A185" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
       <c r="B185" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
       <c r="C185"/>
       <c r="D185"/>
       <c r="E185" t="s">
-        <v>984</v>
+        <v>982</v>
       </c>
       <c r="F185">
         <v>1</v>
       </c>
       <c r="G185"/>
       <c r="H185" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
     </row>
     <row r="186" spans="1:8">
       <c r="A186" t="s">
-        <v>944</v>
+        <v>942</v>
       </c>
       <c r="B186" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
       <c r="C186"/>
       <c r="D186"/>
       <c r="E186" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
       <c r="F186">
         <v>1</v>
       </c>
       <c r="G186"/>
       <c r="H186" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
     </row>
     <row r="187" spans="1:8">
       <c r="A187" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
       <c r="B187" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
       <c r="C187"/>
       <c r="D187"/>
       <c r="E187" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="F187">
         <v>1</v>
       </c>
       <c r="G187"/>
       <c r="H187" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
     </row>
     <row r="188" spans="1:8">
       <c r="A188" t="s">
-        <v>948</v>
+        <v>946</v>
       </c>
       <c r="B188" t="s">
-        <v>949</v>
+        <v>947</v>
       </c>
       <c r="C188"/>
       <c r="D188"/>
       <c r="E188" t="s">
-        <v>987</v>
+        <v>985</v>
       </c>
       <c r="F188">
         <v>1</v>
       </c>
       <c r="G188"/>
       <c r="H188" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
     </row>
     <row r="189" spans="1:8">
       <c r="A189" t="s">
-        <v>1045</v>
+        <v>1043</v>
       </c>
       <c r="B189" t="s">
-        <v>1046</v>
+        <v>1044</v>
       </c>
       <c r="C189"/>
       <c r="D189"/>
       <c r="E189" t="s">
-        <v>1047</v>
+        <v>1045</v>
       </c>
       <c r="F189">
         <v>1</v>
       </c>
       <c r="G189"/>
       <c r="H189" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
     </row>
     <row r="190" spans="1:8">
       <c r="A190" s="2" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C190" s="3">
         <v>6</v>
@@ -8457,20 +8464,20 @@
         <v>0</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="F190" s="3"/>
       <c r="G190" s="1"/>
       <c r="H190" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
     </row>
     <row r="191" spans="1:8">
       <c r="A191" s="2" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C191" s="3">
         <v>6</v>
@@ -8479,20 +8486,20 @@
         <v>0.54166666666666663</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="F191" s="3"/>
       <c r="G191" s="1"/>
       <c r="H191" s="1" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
     </row>
     <row r="192" spans="1:8">
       <c r="A192" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C192" s="3">
         <v>13</v>
@@ -8501,80 +8508,80 @@
         <v>0</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="F192" s="3"/>
       <c r="G192" s="1"/>
       <c r="H192" s="1" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
     </row>
     <row r="193" spans="1:8">
       <c r="A193" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="F193" s="2">
         <v>1</v>
       </c>
       <c r="G193" s="2" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="H193" s="2" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
     </row>
     <row r="194" spans="1:8">
       <c r="A194" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="F194" s="2">
         <v>1</v>
       </c>
       <c r="G194" s="2" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="H194" s="2" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
     </row>
     <row r="195" spans="1:8">
       <c r="A195" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="F195" s="2">
         <v>1</v>
       </c>
       <c r="G195" s="2" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="H195" s="2" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
     </row>
     <row r="196" spans="1:8">
       <c r="A196" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="C196" s="2">
         <v>8</v>
@@ -8583,37 +8590,37 @@
         <v>0</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="F196" s="3"/>
       <c r="H196" s="2" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="197" spans="1:8">
       <c r="A197" s="2" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="D197" s="6"/>
       <c r="E197" s="1" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="F197" s="3">
         <v>1</v>
       </c>
       <c r="H197" s="7" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
     </row>
     <row r="198" spans="1:8">
       <c r="A198" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C198" s="3">
         <v>13</v>
@@ -8622,20 +8629,20 @@
         <v>0</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="F198" s="3"/>
       <c r="G198" s="1"/>
       <c r="H198" s="1" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
     </row>
     <row r="199" spans="1:8">
       <c r="A199" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="C199" s="2">
         <v>10</v>
@@ -8644,18 +8651,18 @@
         <v>0</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="H199" s="2" t="s">
-        <v>1039</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="200" spans="1:8">
       <c r="A200" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="C200" s="2">
         <v>10</v>
@@ -8664,38 +8671,38 @@
         <v>0</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="H200" s="2" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="201" spans="1:8">
       <c r="A201" t="s">
-        <v>1048</v>
+        <v>1046</v>
       </c>
       <c r="B201" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="C201"/>
       <c r="D201" s="11"/>
       <c r="E201" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="F201">
         <v>1</v>
       </c>
       <c r="G201"/>
       <c r="H201" s="11" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="202" spans="1:8">
       <c r="A202" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="B202" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
       <c r="C202">
         <v>10</v>
@@ -8704,40 +8711,40 @@
         <v>0</v>
       </c>
       <c r="E202" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="F202"/>
       <c r="G202"/>
       <c r="H202" s="11" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="203" spans="1:8">
       <c r="A203" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
       <c r="B203" t="s">
-        <v>1027</v>
+        <v>1025</v>
       </c>
       <c r="C203"/>
       <c r="D203" s="11"/>
       <c r="E203" t="s">
-        <v>1028</v>
+        <v>1026</v>
       </c>
       <c r="F203">
         <v>1</v>
       </c>
       <c r="G203"/>
       <c r="H203" s="11" t="s">
-        <v>1029</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="204" spans="1:8">
       <c r="A204" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="C204" s="3">
         <v>7</v>
@@ -8746,20 +8753,20 @@
         <v>0</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F204" s="3"/>
       <c r="G204" s="1"/>
       <c r="H204" s="1" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
     </row>
     <row r="205" spans="1:8">
       <c r="A205" s="2" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C205" s="3">
         <v>6</v>
@@ -8768,40 +8775,40 @@
         <v>0</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F205" s="3"/>
       <c r="G205" s="1"/>
       <c r="H205" s="1" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
     </row>
     <row r="206" spans="1:8">
       <c r="A206" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C206" s="3"/>
       <c r="D206" s="4"/>
       <c r="E206" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F206" s="3">
         <v>1</v>
       </c>
       <c r="G206" s="1"/>
       <c r="H206" s="1" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
     </row>
     <row r="207" spans="1:8">
       <c r="A207" s="2" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C207" s="3">
         <v>10</v>
@@ -8810,38 +8817,38 @@
         <v>0</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F207" s="3"/>
       <c r="G207" s="1"/>
       <c r="H207" s="1" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
     </row>
     <row r="208" spans="1:8">
       <c r="A208" s="2" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="D208" s="6"/>
       <c r="E208" s="2" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="F208" s="2">
         <v>1</v>
       </c>
       <c r="H208" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
     </row>
     <row r="209" spans="1:8">
       <c r="A209" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="B209" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
       <c r="C209">
         <v>15</v>
@@ -8850,20 +8857,20 @@
         <v>0</v>
       </c>
       <c r="E209" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="F209"/>
       <c r="G209"/>
       <c r="H209" s="11" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
     </row>
     <row r="210" spans="1:8">
       <c r="A210" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
       <c r="B210" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="C210">
         <v>15</v>
@@ -8872,20 +8879,20 @@
         <v>0</v>
       </c>
       <c r="E210" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="F210"/>
       <c r="G210"/>
       <c r="H210" s="11" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
     </row>
     <row r="211" spans="1:8">
       <c r="A211" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
       <c r="B211" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
       <c r="C211">
         <v>15</v>
@@ -8894,20 +8901,20 @@
         <v>0</v>
       </c>
       <c r="E211" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="F211"/>
       <c r="G211"/>
       <c r="H211" s="11" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
     </row>
     <row r="212" spans="1:8">
       <c r="A212" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="B212" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="C212">
         <v>20</v>
@@ -8916,20 +8923,20 @@
         <v>0</v>
       </c>
       <c r="E212" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="F212"/>
       <c r="G212"/>
       <c r="H212" s="11" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="213" spans="1:8">
       <c r="A213" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="B213" t="s">
-        <v>1006</v>
+        <v>1004</v>
       </c>
       <c r="C213">
         <v>15</v>
@@ -8938,64 +8945,64 @@
         <v>0</v>
       </c>
       <c r="E213" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="F213"/>
       <c r="G213"/>
       <c r="H213" s="11" t="s">
-        <v>1008</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="214" spans="1:8">
       <c r="A214" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C214" s="1"/>
       <c r="D214" s="1"/>
       <c r="E214" s="1" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="F214" s="3">
         <v>1</v>
       </c>
       <c r="G214" s="1" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="H214" s="2" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
     </row>
     <row r="215" spans="1:8">
       <c r="A215" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C215" s="1"/>
       <c r="D215" s="1"/>
       <c r="E215" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F215" s="3">
         <v>1</v>
       </c>
       <c r="G215" s="1" t="s">
-        <v>1133</v>
+        <v>1131</v>
       </c>
       <c r="H215" s="2" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
     </row>
     <row r="216" spans="1:8">
       <c r="A216" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C216" s="3">
         <v>7</v>
@@ -9004,20 +9011,20 @@
         <v>0.91666666666666663</v>
       </c>
       <c r="E216" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F216" s="3"/>
       <c r="G216" s="1"/>
       <c r="H216" s="1" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="217" spans="1:8">
       <c r="A217" s="2" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="B217" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C217" s="3">
         <v>6</v>
@@ -9026,20 +9033,20 @@
         <v>0</v>
       </c>
       <c r="E217" s="1" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="F217" s="3"/>
       <c r="G217" s="1"/>
       <c r="H217" s="1" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
     </row>
     <row r="218" spans="1:8">
       <c r="A218" s="2" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="B218" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C218" s="3">
         <v>6</v>
@@ -9048,20 +9055,20 @@
         <v>0</v>
       </c>
       <c r="E218" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="F218" s="3"/>
       <c r="G218" s="1"/>
       <c r="H218" s="1" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
     </row>
     <row r="219" spans="1:8">
       <c r="A219" s="2" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="B219" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C219" s="3">
         <v>6</v>
@@ -9070,20 +9077,20 @@
         <v>0</v>
       </c>
       <c r="E219" s="1" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="F219" s="3"/>
       <c r="G219" s="1"/>
       <c r="H219" s="2" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="220" spans="1:8">
       <c r="A220" s="2" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="B220" s="1" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C220" s="1">
         <v>7</v>
@@ -9092,80 +9099,80 @@
         <v>0.91666666666666663</v>
       </c>
       <c r="E220" s="1" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F220" s="1"/>
       <c r="G220" s="1"/>
       <c r="H220" s="1" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
     </row>
     <row r="221" spans="1:8">
       <c r="A221" s="2" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="B221" s="1" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="C221" s="1"/>
       <c r="D221" s="5"/>
       <c r="E221" s="1" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="F221" s="1">
         <v>1</v>
       </c>
       <c r="G221" s="1"/>
       <c r="H221" s="1" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="222" spans="1:8">
       <c r="A222" s="2" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="B222" s="1" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C222" s="1"/>
       <c r="D222" s="1"/>
       <c r="E222" s="1" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="F222" s="1">
         <v>1</v>
       </c>
       <c r="G222" s="1"/>
       <c r="H222" s="1" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="223" spans="1:8">
       <c r="A223" s="2" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="B223" s="1" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C223" s="1"/>
       <c r="D223" s="1"/>
       <c r="E223" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="F223" s="1">
         <v>1</v>
       </c>
       <c r="G223" s="1"/>
       <c r="H223" s="1" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="224" spans="1:8">
       <c r="A224" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="B224" s="1" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C224" s="3">
         <v>6</v>
@@ -9174,20 +9181,20 @@
         <v>0</v>
       </c>
       <c r="E224" s="1" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="F224" s="3"/>
       <c r="G224" s="1"/>
       <c r="H224" s="1" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
     </row>
     <row r="225" spans="1:8">
       <c r="A225" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="B225" s="1" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C225" s="3">
         <v>29</v>
@@ -9196,20 +9203,20 @@
         <v>0</v>
       </c>
       <c r="E225" s="1" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="F225" s="3"/>
       <c r="G225" s="1"/>
       <c r="H225" s="2" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
     </row>
     <row r="226" spans="1:8">
       <c r="A226" s="2" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="B226" s="1" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="C226" s="2">
         <v>7</v>
@@ -9218,19 +9225,19 @@
         <v>0.95833333333333337</v>
       </c>
       <c r="E226" s="1" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="F226" s="3"/>
       <c r="H226" s="7" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
     </row>
     <row r="227" spans="1:8">
       <c r="A227" s="2" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="B227" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C227" s="3">
         <v>14</v>
@@ -9239,20 +9246,20 @@
         <v>0</v>
       </c>
       <c r="E227" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F227" s="3"/>
       <c r="G227" s="1"/>
       <c r="H227" s="7" t="s">
-        <v>1191</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="228" spans="1:8">
       <c r="A228" s="2" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="B228" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C228" s="3">
         <v>14</v>
@@ -9261,37 +9268,37 @@
         <v>0</v>
       </c>
       <c r="E228" s="1" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="F228" s="3"/>
       <c r="G228" s="1"/>
       <c r="H228" s="2" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
     </row>
     <row r="229" spans="1:8">
       <c r="A229" s="2" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="B229" s="1" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="E229" s="1" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="F229" s="3">
         <v>1</v>
       </c>
       <c r="H229" s="1" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
     </row>
     <row r="230" spans="1:8">
       <c r="A230" s="2" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="B230" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C230" s="3">
         <v>14</v>
@@ -9300,20 +9307,20 @@
         <v>0</v>
       </c>
       <c r="E230" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F230" s="3"/>
       <c r="G230" s="1"/>
       <c r="H230" s="2" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
     </row>
     <row r="231" spans="1:8">
       <c r="A231" s="2" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="B231" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C231" s="3">
         <v>14</v>
@@ -9322,20 +9329,20 @@
         <v>0</v>
       </c>
       <c r="E231" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F231" s="3"/>
       <c r="G231" s="1"/>
       <c r="H231" s="2" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
     </row>
     <row r="232" spans="1:8">
       <c r="A232" s="2" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="B232" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C232" s="3">
         <v>14</v>
@@ -9344,20 +9351,20 @@
         <v>0</v>
       </c>
       <c r="E232" s="1" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="F232" s="3"/>
       <c r="G232" s="1"/>
       <c r="H232" s="1" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
     </row>
     <row r="233" spans="1:8">
       <c r="A233" s="2" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="B233" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C233" s="3">
         <v>7</v>
@@ -9366,20 +9373,20 @@
         <v>0.91666666666666663</v>
       </c>
       <c r="E233" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F233" s="3"/>
       <c r="G233" s="1"/>
       <c r="H233" s="1" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
     </row>
     <row r="234" spans="1:8">
       <c r="A234" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B234" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C234" s="3">
         <v>7</v>
@@ -9388,20 +9395,20 @@
         <v>0.91666666666666663</v>
       </c>
       <c r="E234" s="1" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F234" s="3"/>
       <c r="G234" s="1"/>
       <c r="H234" s="1" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
     </row>
     <row r="235" spans="1:8">
       <c r="A235" t="s">
-        <v>1011</v>
+        <v>1009</v>
       </c>
       <c r="B235" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="C235">
         <v>6</v>
@@ -9410,20 +9417,20 @@
         <v>0</v>
       </c>
       <c r="E235" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="F235"/>
       <c r="G235"/>
       <c r="H235" s="7" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="236" spans="1:8">
       <c r="A236" s="11" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
       <c r="B236" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
       <c r="C236" s="3">
         <v>7</v>
@@ -9432,20 +9439,20 @@
         <v>0.91666666666666663</v>
       </c>
       <c r="E236" s="1" t="s">
-        <v>1031</v>
+        <v>1029</v>
       </c>
       <c r="F236"/>
       <c r="G236"/>
       <c r="H236" s="7" t="s">
-        <v>1032</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="237" spans="1:8">
       <c r="A237" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="B237" s="1" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C237" s="3">
         <v>7</v>
@@ -9454,17 +9461,17 @@
         <v>0.875</v>
       </c>
       <c r="E237" s="1" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="F237" s="3"/>
       <c r="G237" s="1"/>
       <c r="H237" s="1" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
     </row>
     <row r="238" spans="1:8">
       <c r="A238" s="2" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="B238" s="1" t="s">
         <v>9</v>
@@ -9481,35 +9488,35 @@
       <c r="F238" s="3"/>
       <c r="G238" s="1"/>
       <c r="H238" s="2" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
     </row>
     <row r="239" spans="1:8" customFormat="1">
       <c r="A239" s="2" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="B239" s="1" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="C239" s="2"/>
       <c r="D239" s="2"/>
       <c r="E239" s="1" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="F239" s="3">
         <v>1</v>
       </c>
       <c r="G239" s="2"/>
       <c r="H239" s="7" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
     </row>
     <row r="240" spans="1:8">
       <c r="A240" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="B240" s="1" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C240" s="3">
         <v>13</v>
@@ -9518,102 +9525,102 @@
         <v>0</v>
       </c>
       <c r="E240" s="1" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="F240" s="3"/>
       <c r="G240" s="1"/>
       <c r="H240" s="1" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
     </row>
     <row r="241" spans="1:8">
       <c r="A241" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="B241" s="1" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C241" s="3"/>
       <c r="D241" s="5"/>
       <c r="E241" s="1" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="F241" s="3">
         <v>1</v>
       </c>
       <c r="G241" s="1"/>
       <c r="H241" s="1" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
     </row>
     <row r="242" spans="1:8">
       <c r="A242" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="B242" s="1" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="C242" s="3"/>
       <c r="D242" s="5"/>
       <c r="E242" s="1" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="F242" s="3">
         <v>1</v>
       </c>
       <c r="G242" s="1"/>
       <c r="H242" s="1" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
     </row>
     <row r="243" spans="1:8">
       <c r="A243" s="2" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="B243" s="1" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C243" s="3"/>
       <c r="D243" s="5"/>
       <c r="E243" s="1" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="F243" s="3">
         <v>1</v>
       </c>
       <c r="G243" s="1"/>
       <c r="H243" s="1" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
     </row>
     <row r="244" spans="1:8">
       <c r="A244" s="11" t="s">
-        <v>1017</v>
+        <v>1015</v>
       </c>
       <c r="B244" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
       <c r="C244">
         <v>13</v>
       </c>
       <c r="D244" s="11" t="s">
-        <v>1128</v>
+        <v>1126</v>
       </c>
       <c r="E244" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="F244"/>
       <c r="G244"/>
       <c r="H244" s="7" t="s">
-        <v>1020</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="245" spans="1:8">
       <c r="A245" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="B245" s="1" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C245" s="3">
         <v>7</v>
@@ -9622,54 +9629,54 @@
         <v>0.91666666666666663</v>
       </c>
       <c r="E245" s="1" t="s">
-        <v>1030</v>
+        <v>1028</v>
       </c>
       <c r="F245" s="3"/>
       <c r="G245" s="1"/>
       <c r="H245" s="1" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="246" spans="1:8">
       <c r="A246" s="2" t="s">
+        <v>657</v>
+      </c>
+      <c r="B246" s="1" t="s">
         <v>659</v>
       </c>
-      <c r="B246" s="1" t="s">
+      <c r="E246" s="1" t="s">
         <v>661</v>
       </c>
-      <c r="E246" s="1" t="s">
-        <v>663</v>
-      </c>
       <c r="F246" s="2">
         <v>1</v>
       </c>
       <c r="H246" s="2" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
     </row>
     <row r="247" spans="1:8">
       <c r="A247" s="2" t="s">
+        <v>656</v>
+      </c>
+      <c r="B247" s="1" t="s">
         <v>658</v>
       </c>
-      <c r="B247" s="1" t="s">
+      <c r="E247" s="1" t="s">
         <v>660</v>
       </c>
-      <c r="E247" s="1" t="s">
-        <v>662</v>
-      </c>
       <c r="F247" s="2">
         <v>1</v>
       </c>
       <c r="H247" s="2" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
     </row>
     <row r="248" spans="1:8">
       <c r="A248" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="B248" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C248" s="3">
         <v>6</v>
@@ -9678,20 +9685,20 @@
         <v>0</v>
       </c>
       <c r="E248" s="1" t="s">
-        <v>1034</v>
+        <v>1032</v>
       </c>
       <c r="F248" s="3"/>
       <c r="G248" s="1"/>
       <c r="H248" s="1" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="249" spans="1:8">
       <c r="A249" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="B249" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C249" s="3">
         <v>13</v>
@@ -9700,17 +9707,17 @@
         <v>0</v>
       </c>
       <c r="E249" s="1" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
       <c r="F249" s="3"/>
       <c r="G249" s="1"/>
       <c r="H249" s="1" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="250" spans="1:8">
       <c r="A250" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B250" s="1" t="s">
         <v>25</v>
@@ -9727,12 +9734,12 @@
       <c r="F250" s="3"/>
       <c r="G250" s="1"/>
       <c r="H250" s="2" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
     </row>
     <row r="251" spans="1:8">
       <c r="A251" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="B251" s="1" t="s">
         <v>27</v>
@@ -9749,12 +9756,12 @@
       <c r="F251" s="3"/>
       <c r="G251" s="1"/>
       <c r="H251" s="2" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
     </row>
     <row r="252" spans="1:8">
       <c r="A252" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="B252" s="1" t="s">
         <v>23</v>
@@ -9771,12 +9778,12 @@
       <c r="F252" s="3"/>
       <c r="G252" s="1"/>
       <c r="H252" s="2" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
     </row>
     <row r="253" spans="1:8">
       <c r="A253" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B253" s="1" t="s">
         <v>31</v>
@@ -9793,12 +9800,12 @@
       <c r="F253" s="3"/>
       <c r="G253" s="1"/>
       <c r="H253" s="2" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
     </row>
     <row r="254" spans="1:8">
       <c r="A254" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B254" s="1" t="s">
         <v>33</v>
@@ -9815,12 +9822,12 @@
       <c r="F254" s="3"/>
       <c r="G254" s="1"/>
       <c r="H254" s="2" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
     </row>
     <row r="255" spans="1:8">
       <c r="A255" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="B255" s="1" t="s">
         <v>20</v>
@@ -9837,12 +9844,12 @@
       <c r="F255" s="3"/>
       <c r="G255" s="1"/>
       <c r="H255" s="2" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
     </row>
     <row r="256" spans="1:8">
       <c r="A256" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="B256" s="1" t="s">
         <v>18</v>
@@ -9859,12 +9866,12 @@
       <c r="F256" s="3"/>
       <c r="G256" s="1"/>
       <c r="H256" s="2" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
     </row>
     <row r="257" spans="1:8">
       <c r="A257" s="2" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="B257" s="1" t="s">
         <v>37</v>
@@ -9881,12 +9888,12 @@
       <c r="F257" s="3"/>
       <c r="G257" s="1"/>
       <c r="H257" s="2" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
     </row>
     <row r="258" spans="1:8">
       <c r="A258" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="B258" s="1" t="s">
         <v>29</v>
@@ -9903,12 +9910,12 @@
       <c r="F258" s="3"/>
       <c r="G258" s="1"/>
       <c r="H258" s="2" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
     </row>
     <row r="259" spans="1:8">
       <c r="A259" s="2" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="B259" s="1" t="s">
         <v>39</v>
@@ -9925,12 +9932,12 @@
       <c r="F259" s="3"/>
       <c r="G259" s="1"/>
       <c r="H259" s="2" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
     </row>
     <row r="260" spans="1:8">
       <c r="A260" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="B260" s="1" t="s">
         <v>35</v>
@@ -9947,12 +9954,12 @@
       <c r="F260" s="3"/>
       <c r="G260" s="1"/>
       <c r="H260" s="2" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
     </row>
     <row r="261" spans="1:8">
       <c r="A261" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="B261" s="1" t="s">
         <v>22</v>
@@ -9964,20 +9971,20 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="E261" s="1" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="F261" s="3"/>
       <c r="G261" s="1"/>
       <c r="H261" s="2" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
     </row>
     <row r="262" spans="1:8">
       <c r="A262" s="2" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="B262" s="1" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="C262" s="2">
         <v>6</v>
@@ -9986,19 +9993,19 @@
         <v>0</v>
       </c>
       <c r="E262" s="1" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="F262" s="3"/>
       <c r="H262" s="7" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
     </row>
     <row r="263" spans="1:8">
       <c r="A263" s="2" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="B263" s="1" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="C263" s="3">
         <v>8</v>
@@ -10007,19 +10014,19 @@
         <v>0</v>
       </c>
       <c r="E263" s="1" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="F263" s="3"/>
       <c r="H263" s="1" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
     </row>
     <row r="264" spans="1:8">
       <c r="A264" s="2" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="B264" s="1" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C264" s="3">
         <v>7</v>
@@ -10028,20 +10035,20 @@
         <v>0</v>
       </c>
       <c r="E264" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F264" s="3"/>
       <c r="G264" s="1"/>
       <c r="H264" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
     </row>
     <row r="265" spans="1:8">
       <c r="A265" s="2" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="B265" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C265" s="3">
         <v>7</v>
@@ -10050,20 +10057,20 @@
         <v>0</v>
       </c>
       <c r="E265" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="F265" s="3"/>
       <c r="G265" s="1"/>
       <c r="H265" s="1" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
     </row>
     <row r="266" spans="1:8">
       <c r="A266" s="2" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="B266" s="1" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="C266" s="2">
         <v>6</v>
@@ -10072,19 +10079,19 @@
         <v>0</v>
       </c>
       <c r="E266" s="1" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="F266" s="3"/>
       <c r="H266" s="7" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
     </row>
     <row r="267" spans="1:8">
       <c r="A267" s="2" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="B267" s="1" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="C267" s="2">
         <v>6</v>
@@ -10093,19 +10100,19 @@
         <v>0</v>
       </c>
       <c r="E267" s="10" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="F267" s="3"/>
       <c r="H267" s="2" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
     </row>
     <row r="268" spans="1:8">
       <c r="A268" s="2" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="B268" s="1" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="C268" s="2">
         <v>6</v>
@@ -10114,19 +10121,19 @@
         <v>0</v>
       </c>
       <c r="E268" s="1" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="F268" s="3"/>
       <c r="H268" s="2" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
     </row>
     <row r="269" spans="1:8">
       <c r="A269" s="2" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="B269" s="1" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="C269" s="2">
         <v>6</v>
@@ -10135,41 +10142,41 @@
         <v>0</v>
       </c>
       <c r="E269" s="1" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="F269" s="3"/>
       <c r="H269" s="2" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
     </row>
     <row r="270" spans="1:8">
       <c r="A270" s="2" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="B270" s="1" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="C270" s="3"/>
       <c r="D270" s="6"/>
       <c r="E270" s="1" t="s">
-        <v>1129</v>
+        <v>1127</v>
       </c>
       <c r="F270" s="3">
         <v>1</v>
       </c>
       <c r="G270" s="2" t="s">
-        <v>1134</v>
+        <v>1132</v>
       </c>
       <c r="H270" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
     </row>
     <row r="271" spans="1:8">
       <c r="A271" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="B271" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C271" s="3">
         <v>6</v>
@@ -10178,20 +10185,20 @@
         <v>0</v>
       </c>
       <c r="E271" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F271" s="3"/>
       <c r="G271" s="1"/>
       <c r="H271" s="1" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
     </row>
     <row r="272" spans="1:8">
       <c r="A272" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="B272" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C272" s="3">
         <v>6</v>
@@ -10200,20 +10207,20 @@
         <v>0</v>
       </c>
       <c r="E272" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F272" s="3"/>
       <c r="G272" s="1"/>
       <c r="H272" s="1" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
     </row>
     <row r="273" spans="1:8">
       <c r="A273" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="B273" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C273" s="3">
         <v>6</v>
@@ -10222,20 +10229,20 @@
         <v>0</v>
       </c>
       <c r="E273" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F273" s="3"/>
       <c r="G273" s="1"/>
       <c r="H273" s="1" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
     </row>
     <row r="274" spans="1:8">
       <c r="A274" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="B274" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C274" s="3">
         <v>7</v>
@@ -10244,20 +10251,20 @@
         <v>0.97916666666666663</v>
       </c>
       <c r="E274" s="1" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="F274" s="3"/>
       <c r="G274" s="1"/>
       <c r="H274" s="1" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
     </row>
     <row r="275" spans="1:8">
       <c r="A275" s="2" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="B275" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C275" s="3">
         <v>6</v>
@@ -10266,20 +10273,20 @@
         <v>0</v>
       </c>
       <c r="E275" s="1" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="F275" s="3"/>
       <c r="G275" s="1"/>
       <c r="H275" s="2" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
     </row>
     <row r="276" spans="1:8">
       <c r="A276" s="2" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B276" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C276" s="3">
         <v>13</v>
@@ -10288,20 +10295,20 @@
         <v>0</v>
       </c>
       <c r="E276" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F276" s="3"/>
       <c r="G276" s="1"/>
       <c r="H276" s="2" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
     </row>
     <row r="277" spans="1:8">
       <c r="A277" s="2" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="B277" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C277" s="3">
         <v>6</v>
@@ -10310,20 +10317,20 @@
         <v>0</v>
       </c>
       <c r="E277" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F277" s="3"/>
       <c r="G277" s="1"/>
       <c r="H277" s="2" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
     </row>
     <row r="278" spans="1:8">
       <c r="A278" s="2" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="B278" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C278" s="3">
         <v>6</v>
@@ -10332,20 +10339,20 @@
         <v>0</v>
       </c>
       <c r="E278" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F278" s="3"/>
       <c r="G278" s="1"/>
       <c r="H278" s="2" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
     </row>
     <row r="279" spans="1:8">
       <c r="A279" s="2" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="B279" s="1" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="C279" s="3">
         <v>6</v>
@@ -10354,20 +10361,20 @@
         <v>0</v>
       </c>
       <c r="E279" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F279" s="3"/>
       <c r="G279" s="1"/>
       <c r="H279" s="2" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
     </row>
     <row r="280" spans="1:8">
       <c r="A280" s="2" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="B280" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C280" s="3">
         <v>6</v>
@@ -10376,20 +10383,20 @@
         <v>0</v>
       </c>
       <c r="E280" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F280" s="3"/>
       <c r="G280" s="1"/>
       <c r="H280" s="2" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
     </row>
     <row r="281" spans="1:8">
       <c r="A281" s="2" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="B281" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C281" s="3">
         <v>7</v>
@@ -10398,20 +10405,20 @@
         <v>0</v>
       </c>
       <c r="E281" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F281" s="3"/>
       <c r="G281" s="1"/>
       <c r="H281" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
     </row>
     <row r="282" spans="1:8">
       <c r="A282" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="B282" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C282" s="3">
         <v>7</v>
@@ -10420,20 +10427,20 @@
         <v>0</v>
       </c>
       <c r="E282" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F282" s="3"/>
       <c r="G282" s="1"/>
       <c r="H282" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
     </row>
     <row r="283" spans="1:8">
       <c r="A283" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="B283" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C283" s="3">
         <v>7</v>
@@ -10442,20 +10449,20 @@
         <v>0</v>
       </c>
       <c r="E283" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F283" s="3"/>
       <c r="G283" s="1"/>
       <c r="H283" s="1" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
     </row>
     <row r="284" spans="1:8">
       <c r="A284" s="2" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="B284" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C284" s="3">
         <v>7</v>
@@ -10464,20 +10471,20 @@
         <v>0</v>
       </c>
       <c r="E284" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F284" s="3"/>
       <c r="G284" s="1"/>
       <c r="H284" s="1" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
     </row>
     <row r="285" spans="1:8">
       <c r="A285" s="2" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="B285" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C285" s="3">
         <v>7</v>
@@ -10486,20 +10493,20 @@
         <v>0</v>
       </c>
       <c r="E285" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F285" s="3"/>
       <c r="G285" s="1"/>
       <c r="H285" s="1" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
     </row>
     <row r="286" spans="1:8">
       <c r="A286" s="2" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="B286" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C286" s="3">
         <v>7</v>
@@ -10508,20 +10515,20 @@
         <v>0</v>
       </c>
       <c r="E286" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F286" s="3"/>
       <c r="G286" s="1"/>
       <c r="H286" s="1" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
     </row>
     <row r="287" spans="1:8">
       <c r="A287" s="2" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="B287" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C287" s="3">
         <v>7</v>
@@ -10530,20 +10537,20 @@
         <v>0</v>
       </c>
       <c r="E287" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F287" s="3"/>
       <c r="G287" s="1"/>
       <c r="H287" s="1" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
     </row>
     <row r="288" spans="1:8">
       <c r="A288" s="2" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="B288" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C288" s="3">
         <v>7</v>
@@ -10552,20 +10559,20 @@
         <v>0</v>
       </c>
       <c r="E288" s="1" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="F288" s="3"/>
       <c r="G288" s="1"/>
       <c r="H288" s="8" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
     </row>
     <row r="289" spans="1:8">
       <c r="A289" s="2" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="B289" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C289" s="3">
         <v>7</v>
@@ -10574,20 +10581,20 @@
         <v>0</v>
       </c>
       <c r="E289" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F289" s="3"/>
       <c r="G289" s="1"/>
       <c r="H289" s="1" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
     </row>
     <row r="290" spans="1:8">
       <c r="A290" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="B290" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C290" s="3">
         <v>13</v>
@@ -10596,20 +10603,20 @@
         <v>0</v>
       </c>
       <c r="E290" s="1" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="F290" s="3"/>
       <c r="G290" s="1"/>
       <c r="H290" s="1" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
     </row>
     <row r="291" spans="1:8">
       <c r="A291" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="B291" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C291" s="3">
         <v>6</v>
@@ -10618,20 +10625,20 @@
         <v>0</v>
       </c>
       <c r="E291" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F291" s="3"/>
       <c r="G291" s="1"/>
       <c r="H291" s="1" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
     </row>
     <row r="292" spans="1:8">
       <c r="A292" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="B292" s="1" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C292" s="3">
         <v>6</v>
@@ -10640,20 +10647,20 @@
         <v>0</v>
       </c>
       <c r="E292" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F292" s="3"/>
       <c r="G292" s="1"/>
       <c r="H292" s="1" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
     </row>
     <row r="293" spans="1:8" customFormat="1">
       <c r="A293" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="B293" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C293" s="3">
         <v>6</v>
@@ -10662,20 +10669,20 @@
         <v>0</v>
       </c>
       <c r="E293" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F293" s="3"/>
       <c r="G293" s="1"/>
       <c r="H293" s="1" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
     </row>
     <row r="294" spans="1:8" customFormat="1">
       <c r="A294" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="B294" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C294" s="3">
         <v>6</v>
@@ -10684,20 +10691,20 @@
         <v>0</v>
       </c>
       <c r="E294" s="1" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F294" s="3"/>
       <c r="G294" s="1"/>
       <c r="H294" s="1" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
     </row>
     <row r="295" spans="1:8" customFormat="1">
       <c r="A295" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="B295" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C295" s="3">
         <v>6</v>
@@ -10706,159 +10713,159 @@
         <v>0</v>
       </c>
       <c r="E295" s="1" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="F295" s="3"/>
       <c r="G295" s="1"/>
       <c r="H295" s="1" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
     </row>
     <row r="296" spans="1:8" customFormat="1">
       <c r="A296" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B296" s="1" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C296" s="1"/>
       <c r="D296" s="1"/>
       <c r="E296" s="1" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="F296" s="1">
         <v>1</v>
       </c>
       <c r="G296" s="1"/>
       <c r="H296" s="1" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
     </row>
     <row r="297" spans="1:8">
       <c r="A297" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="B297" s="1" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
       <c r="E297" s="1" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
       <c r="F297" s="2">
         <v>1</v>
       </c>
       <c r="H297" s="7" t="s">
-        <v>1042</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="298" spans="1:8">
       <c r="A298" s="2" t="s">
+        <v>1054</v>
+      </c>
+      <c r="B298" s="1" t="s">
+        <v>1055</v>
+      </c>
+      <c r="E298" s="1" t="s">
         <v>1056</v>
       </c>
-      <c r="B298" s="1" t="s">
+      <c r="F298" s="2">
+        <v>1</v>
+      </c>
+      <c r="H298" s="2" t="s">
         <v>1057</v>
-      </c>
-      <c r="E298" s="1" t="s">
-        <v>1058</v>
-      </c>
-      <c r="F298" s="2">
-        <v>1</v>
-      </c>
-      <c r="H298" s="2" t="s">
-        <v>1059</v>
       </c>
     </row>
     <row r="299" spans="1:8">
       <c r="A299" s="2" t="s">
+        <v>1059</v>
+      </c>
+      <c r="B299" s="1" t="s">
+        <v>1058</v>
+      </c>
+      <c r="E299" s="1" t="s">
         <v>1061</v>
       </c>
-      <c r="B299" s="1" t="s">
+      <c r="F299" s="2">
+        <v>1</v>
+      </c>
+      <c r="H299" s="7" t="s">
         <v>1060</v>
-      </c>
-      <c r="E299" s="1" t="s">
-        <v>1063</v>
-      </c>
-      <c r="F299" s="2">
-        <v>1</v>
-      </c>
-      <c r="H299" s="7" t="s">
-        <v>1062</v>
       </c>
     </row>
     <row r="300" spans="1:8">
       <c r="A300" s="2" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
       <c r="B300" s="1" t="s">
+        <v>1062</v>
+      </c>
+      <c r="E300" s="1" t="s">
+        <v>1063</v>
+      </c>
+      <c r="F300" s="2">
+        <v>1</v>
+      </c>
+      <c r="H300" s="2" t="s">
         <v>1064</v>
-      </c>
-      <c r="E300" s="1" t="s">
-        <v>1065</v>
-      </c>
-      <c r="F300" s="2">
-        <v>1</v>
-      </c>
-      <c r="H300" s="2" t="s">
-        <v>1066</v>
       </c>
     </row>
     <row r="301" spans="1:8">
       <c r="A301" s="2" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
       <c r="B301" s="1" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="E301" s="1" t="s">
-        <v>1068</v>
+        <v>1066</v>
       </c>
       <c r="F301" s="2">
         <v>1</v>
       </c>
       <c r="H301" s="2" t="s">
-        <v>1075</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="302" spans="1:8">
       <c r="A302" s="2" t="s">
+        <v>1069</v>
+      </c>
+      <c r="B302" s="1" t="s">
+        <v>1067</v>
+      </c>
+      <c r="E302" s="1" t="s">
         <v>1071</v>
       </c>
-      <c r="B302" s="1" t="s">
-        <v>1069</v>
-      </c>
-      <c r="E302" s="1" t="s">
-        <v>1073</v>
-      </c>
       <c r="F302" s="2">
         <v>1</v>
       </c>
       <c r="H302" s="2" t="s">
-        <v>1074</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="303" spans="1:8">
       <c r="A303" s="2" t="s">
-        <v>1081</v>
+        <v>1079</v>
       </c>
       <c r="B303" s="1" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="E303" s="1" t="s">
-        <v>1077</v>
+        <v>1075</v>
       </c>
       <c r="F303" s="2">
         <v>1</v>
       </c>
       <c r="H303" s="7" t="s">
-        <v>1119</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="304" spans="1:8">
       <c r="A304" s="2" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
       <c r="B304" s="1" t="s">
-        <v>1078</v>
+        <v>1076</v>
       </c>
       <c r="C304" s="2">
         <v>6</v>
@@ -10867,66 +10874,66 @@
         <v>0</v>
       </c>
       <c r="E304" s="1" t="s">
-        <v>1079</v>
+        <v>1077</v>
       </c>
       <c r="H304" s="7" t="s">
-        <v>1082</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="305" spans="1:8">
       <c r="A305" s="2" t="s">
-        <v>1083</v>
+        <v>1081</v>
       </c>
       <c r="B305" s="1" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="E305" s="1" t="s">
-        <v>1121</v>
+        <v>1119</v>
       </c>
       <c r="H305" s="7" t="s">
-        <v>1120</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="306" spans="1:8">
       <c r="A306" s="2" t="s">
+        <v>1134</v>
+      </c>
+      <c r="B306" s="1" t="s">
+        <v>1083</v>
+      </c>
+      <c r="E306" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B306" s="1" t="s">
-        <v>1085</v>
-      </c>
-      <c r="E306" s="1" t="s">
+      <c r="F306" s="2">
+        <v>1</v>
+      </c>
+      <c r="H306" s="2" t="s">
         <v>1138</v>
-      </c>
-      <c r="F306" s="2">
-        <v>1</v>
-      </c>
-      <c r="H306" s="2" t="s">
-        <v>1140</v>
       </c>
     </row>
     <row r="307" spans="1:8">
       <c r="A307" s="2" t="s">
+        <v>1135</v>
+      </c>
+      <c r="B307" s="1" t="s">
+        <v>1084</v>
+      </c>
+      <c r="E307" s="1" t="s">
         <v>1137</v>
       </c>
-      <c r="B307" s="1" t="s">
-        <v>1086</v>
-      </c>
-      <c r="E307" s="1" t="s">
-        <v>1139</v>
-      </c>
       <c r="F307" s="2">
         <v>1</v>
       </c>
       <c r="H307" s="2" t="s">
-        <v>1140</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="308" spans="1:8">
       <c r="A308" s="2" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="B308" s="1" t="s">
-        <v>1087</v>
+        <v>1085</v>
       </c>
       <c r="C308" s="2">
         <v>14</v>
@@ -10935,18 +10942,18 @@
         <v>0</v>
       </c>
       <c r="E308" s="1" t="s">
+        <v>1181</v>
+      </c>
+      <c r="H308" s="2" t="s">
         <v>1183</v>
-      </c>
-      <c r="H308" s="2" t="s">
-        <v>1185</v>
       </c>
     </row>
     <row r="309" spans="1:8">
       <c r="A309" s="2" t="s">
-        <v>1154</v>
+        <v>1152</v>
       </c>
       <c r="B309" s="1" t="s">
-        <v>1088</v>
+        <v>1086</v>
       </c>
       <c r="C309" s="2">
         <v>6</v>
@@ -10955,23 +10962,23 @@
         <v>0</v>
       </c>
       <c r="E309" s="1" t="s">
-        <v>1155</v>
+        <v>1153</v>
       </c>
       <c r="H309" s="2" t="s">
-        <v>1156</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="310" spans="1:8">
       <c r="B310" s="1" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="311" spans="1:8">
       <c r="A311" s="2" t="s">
-        <v>1159</v>
+        <v>1157</v>
       </c>
       <c r="B311" s="1" t="s">
-        <v>1090</v>
+        <v>1088</v>
       </c>
       <c r="C311" s="2">
         <v>14</v>
@@ -10980,125 +10987,125 @@
         <v>0</v>
       </c>
       <c r="E311" s="2" t="s">
-        <v>1091</v>
+        <v>1089</v>
       </c>
       <c r="H311" s="2" t="s">
-        <v>1158</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="312" spans="1:8">
       <c r="A312" s="2" t="s">
+        <v>1162</v>
+      </c>
+      <c r="B312" s="1" t="s">
+        <v>1090</v>
+      </c>
+      <c r="E312" s="2" t="s">
         <v>1164</v>
       </c>
-      <c r="B312" s="1" t="s">
-        <v>1092</v>
-      </c>
-      <c r="E312" s="2" t="s">
-        <v>1166</v>
-      </c>
       <c r="F312" s="2">
         <v>1</v>
       </c>
       <c r="H312" s="2" t="s">
-        <v>1165</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="313" spans="1:8">
       <c r="A313" s="2" t="s">
-        <v>1181</v>
+        <v>1179</v>
       </c>
       <c r="B313" s="1" t="s">
-        <v>1093</v>
+        <v>1091</v>
       </c>
       <c r="E313" s="2" t="s">
-        <v>1179</v>
+        <v>1177</v>
       </c>
       <c r="F313" s="2">
         <v>1</v>
       </c>
       <c r="H313" s="7" t="s">
-        <v>1180</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="314" spans="1:8">
       <c r="A314" s="2" t="s">
+        <v>1182</v>
+      </c>
+      <c r="B314" s="1" t="s">
+        <v>1092</v>
+      </c>
+      <c r="E314" s="2" t="s">
         <v>1184</v>
       </c>
-      <c r="B314" s="1" t="s">
-        <v>1094</v>
-      </c>
-      <c r="E314" s="2" t="s">
-        <v>1186</v>
-      </c>
       <c r="F314" s="2">
         <v>1</v>
       </c>
       <c r="H314" s="7" t="s">
-        <v>1187</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="315" spans="1:8">
       <c r="B315" s="1" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="316" spans="1:8">
       <c r="A316" s="2" t="s">
+        <v>1171</v>
+      </c>
+      <c r="B316" s="1" t="s">
+        <v>1094</v>
+      </c>
+      <c r="E316" s="2" t="s">
+        <v>1172</v>
+      </c>
+      <c r="F316" s="2">
+        <v>1</v>
+      </c>
+      <c r="H316" s="7" t="s">
         <v>1173</v>
-      </c>
-      <c r="B316" s="1" t="s">
-        <v>1096</v>
-      </c>
-      <c r="E316" s="2" t="s">
-        <v>1174</v>
-      </c>
-      <c r="F316" s="2">
-        <v>1</v>
-      </c>
-      <c r="H316" s="7" t="s">
-        <v>1175</v>
       </c>
     </row>
     <row r="317" spans="1:8">
       <c r="A317" s="2" t="s">
+        <v>1165</v>
+      </c>
+      <c r="B317" s="1" t="s">
+        <v>1095</v>
+      </c>
+      <c r="E317" s="2" t="s">
+        <v>1166</v>
+      </c>
+      <c r="F317" s="2">
+        <v>1</v>
+      </c>
+      <c r="H317" s="2" t="s">
         <v>1167</v>
-      </c>
-      <c r="B317" s="1" t="s">
-        <v>1097</v>
-      </c>
-      <c r="E317" s="2" t="s">
-        <v>1168</v>
-      </c>
-      <c r="F317" s="2">
-        <v>1</v>
-      </c>
-      <c r="H317" s="2" t="s">
-        <v>1169</v>
       </c>
     </row>
     <row r="318" spans="1:8">
       <c r="A318" s="2" t="s">
+        <v>1168</v>
+      </c>
+      <c r="B318" s="1" t="s">
+        <v>1096</v>
+      </c>
+      <c r="E318" s="2" t="s">
         <v>1170</v>
       </c>
-      <c r="B318" s="1" t="s">
-        <v>1098</v>
-      </c>
-      <c r="E318" s="2" t="s">
-        <v>1172</v>
-      </c>
       <c r="F318" s="2">
         <v>1</v>
       </c>
       <c r="H318" s="2" t="s">
-        <v>1171</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="319" spans="1:8">
       <c r="A319" s="2" t="s">
-        <v>1177</v>
+        <v>1175</v>
       </c>
       <c r="B319" s="1" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
       <c r="C319" s="2">
         <v>6</v>
@@ -11107,174 +11114,174 @@
         <v>0</v>
       </c>
       <c r="E319" s="2" t="s">
-        <v>1178</v>
+        <v>1176</v>
       </c>
       <c r="H319" s="2" t="s">
-        <v>1190</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="320" spans="1:8">
       <c r="A320" s="2" t="s">
-        <v>1106</v>
+        <v>1104</v>
       </c>
       <c r="B320" s="1" t="s">
-        <v>1099</v>
+        <v>1097</v>
       </c>
       <c r="E320" s="2" t="s">
-        <v>1110</v>
+        <v>1108</v>
       </c>
       <c r="F320" s="2">
         <v>1</v>
       </c>
       <c r="H320" s="2" t="s">
-        <v>1118</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="321" spans="1:8">
       <c r="A321" s="2" t="s">
-        <v>1112</v>
+        <v>1110</v>
       </c>
       <c r="B321" s="1" t="s">
-        <v>1100</v>
+        <v>1098</v>
       </c>
       <c r="E321" s="2" t="s">
-        <v>1111</v>
+        <v>1109</v>
       </c>
       <c r="F321" s="2">
         <v>1</v>
       </c>
       <c r="H321" s="2" t="s">
-        <v>1117</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="322" spans="1:8">
       <c r="A322" s="2" t="s">
-        <v>1107</v>
+        <v>1105</v>
       </c>
       <c r="B322" s="1" t="s">
-        <v>1101</v>
+        <v>1099</v>
       </c>
       <c r="E322" s="2" t="s">
-        <v>1104</v>
+        <v>1102</v>
       </c>
       <c r="F322" s="2">
         <v>1</v>
       </c>
       <c r="H322" s="2" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="323" spans="1:8">
       <c r="A323" s="2" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="B323" s="1" t="s">
-        <v>1102</v>
+        <v>1100</v>
       </c>
       <c r="E323" s="2" t="s">
-        <v>1105</v>
+        <v>1103</v>
       </c>
       <c r="F323" s="2">
         <v>1</v>
       </c>
       <c r="H323" s="2" t="s">
-        <v>1115</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="324" spans="1:8">
       <c r="A324" s="2" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="B324" s="1" t="s">
-        <v>1103</v>
+        <v>1101</v>
       </c>
       <c r="E324" s="2" t="s">
-        <v>1113</v>
+        <v>1111</v>
       </c>
       <c r="F324" s="2">
         <v>1</v>
       </c>
       <c r="H324" s="2" t="s">
-        <v>1114</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="325" spans="1:8">
       <c r="A325" s="2" t="s">
+        <v>1120</v>
+      </c>
+      <c r="B325" s="1" t="s">
+        <v>1121</v>
+      </c>
+      <c r="E325" t="s">
         <v>1122</v>
       </c>
-      <c r="B325" s="1" t="s">
+      <c r="F325" s="2">
+        <v>1</v>
+      </c>
+      <c r="G325" s="2" t="s">
+        <v>1133</v>
+      </c>
+      <c r="H325" s="7" t="s">
         <v>1123</v>
-      </c>
-      <c r="E325" t="s">
-        <v>1124</v>
-      </c>
-      <c r="F325" s="2">
-        <v>1</v>
-      </c>
-      <c r="G325" s="2" t="s">
-        <v>1135</v>
-      </c>
-      <c r="H325" s="7" t="s">
-        <v>1125</v>
       </c>
     </row>
     <row r="326" spans="1:8">
       <c r="A326" s="2" t="s">
-        <v>1141</v>
+        <v>1139</v>
       </c>
       <c r="B326" s="1" t="s">
-        <v>1142</v>
+        <v>1140</v>
       </c>
       <c r="E326" s="2" t="s">
-        <v>1149</v>
+        <v>1147</v>
       </c>
       <c r="F326" s="2">
         <v>1</v>
       </c>
       <c r="H326" s="2" t="s">
-        <v>1153</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="327" spans="1:8">
       <c r="A327" s="2" t="s">
-        <v>1146</v>
+        <v>1144</v>
       </c>
       <c r="B327" s="1" t="s">
-        <v>1143</v>
+        <v>1141</v>
       </c>
       <c r="E327" s="2" t="s">
-        <v>1150</v>
+        <v>1148</v>
       </c>
       <c r="F327" s="2">
         <v>1</v>
       </c>
       <c r="H327" s="2" t="s">
-        <v>1153</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="328" spans="1:8">
       <c r="A328" s="2" t="s">
-        <v>1147</v>
+        <v>1145</v>
       </c>
       <c r="B328" s="1" t="s">
-        <v>1144</v>
+        <v>1142</v>
       </c>
       <c r="E328" s="2" t="s">
+        <v>1149</v>
+      </c>
+      <c r="F328" s="2">
+        <v>1</v>
+      </c>
+      <c r="H328" s="2" t="s">
         <v>1151</v>
-      </c>
-      <c r="F328" s="2">
-        <v>1</v>
-      </c>
-      <c r="H328" s="2" t="s">
-        <v>1153</v>
       </c>
     </row>
     <row r="329" spans="1:8">
       <c r="A329" s="2" t="s">
-        <v>1148</v>
+        <v>1146</v>
       </c>
       <c r="B329" s="1" t="s">
-        <v>1145</v>
+        <v>1143</v>
       </c>
       <c r="C329" s="2">
         <v>14</v>
@@ -11283,18 +11290,18 @@
         <v>0</v>
       </c>
       <c r="E329" s="2" t="s">
-        <v>1152</v>
+        <v>1150</v>
       </c>
       <c r="H329" s="2" t="s">
-        <v>1153</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="330" spans="1:8">
       <c r="A330" s="2" t="s">
-        <v>1160</v>
+        <v>1158</v>
       </c>
       <c r="B330" s="1" t="s">
-        <v>1161</v>
+        <v>1159</v>
       </c>
       <c r="C330" s="2">
         <v>12</v>
@@ -11303,27 +11310,27 @@
         <v>0</v>
       </c>
       <c r="E330" s="2" t="s">
-        <v>1162</v>
+        <v>1160</v>
       </c>
       <c r="H330" s="7" t="s">
-        <v>1163</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="331" spans="1:8">
       <c r="A331" s="2" t="s">
-        <v>1188</v>
+        <v>1186</v>
       </c>
       <c r="B331" s="1" t="s">
-        <v>1189</v>
+        <v>1187</v>
       </c>
       <c r="E331" s="2" t="s">
-        <v>1192</v>
+        <v>1190</v>
       </c>
       <c r="F331" s="2">
         <v>1</v>
       </c>
       <c r="H331" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
     </row>
   </sheetData>

--- a/stores.xlsx
+++ b/stores.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\YUMIN\Desktop\B0KT2A_RSVN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F7A76C2-3B30-4CB4-B9FB-2C7860ABE809}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1EF88BC-C97A-49A9-AB27-88AE19B03A03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{ABFC3117-FCCB-4FF3-804A-FE19451A2004}"/>
   </bookViews>
@@ -2427,10 +2427,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>이스케이프컴퍼니,이케컴,escape company</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>https://naver.me/5FEJkSkH</t>
   </si>
   <si>
@@ -4194,6 +4190,10 @@
   </si>
   <si>
     <t>성지기숙학원:특수교정반,낙화:떨어지는 꽃,알케이드 빌리지,OKCUT,오케이컷,OK컷,HINDSIGHT,하인드사이트,춘화각:피할수없는저주</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이스케이프컴퍼니,이케컴,escape company,방자전</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -4674,7 +4674,7 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>630</v>
@@ -4682,10 +4682,10 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="2" t="s">
+        <v>817</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>818</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>819</v>
       </c>
       <c r="C3" s="2">
         <v>7</v>
@@ -4694,7 +4694,7 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>630</v>
@@ -4702,10 +4702,10 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="2" t="s">
+        <v>819</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>820</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>821</v>
       </c>
       <c r="C4" s="2">
         <v>7</v>
@@ -4839,7 +4839,7 @@
         <v>1</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>514</v>
@@ -4861,7 +4861,7 @@
         <v>1</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>515</v>
@@ -4974,7 +4974,7 @@
       <c r="F16" s="3"/>
       <c r="G16" s="1"/>
       <c r="H16" s="7" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -4991,7 +4991,7 @@
         <v>0</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="F17" s="3"/>
       <c r="G17" s="1"/>
@@ -5153,10 +5153,10 @@
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="2" t="s">
+        <v>821</v>
+      </c>
+      <c r="B25" s="1" t="s">
         <v>822</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>823</v>
       </c>
       <c r="C25" s="3">
         <v>15</v>
@@ -5165,12 +5165,12 @@
         <v>0</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="F25" s="3"/>
       <c r="G25" s="1"/>
       <c r="H25" s="11" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -5261,27 +5261,27 @@
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="2" t="s">
+        <v>780</v>
+      </c>
+      <c r="B30" s="1" t="s">
         <v>781</v>
       </c>
-      <c r="B30" s="1" t="s">
+      <c r="E30" s="1" t="s">
         <v>782</v>
       </c>
-      <c r="E30" s="1" t="s">
-        <v>783</v>
-      </c>
       <c r="F30" s="3">
         <v>1</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="2" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="C31" s="2">
         <v>20</v>
@@ -5290,112 +5290,112 @@
         <v>0</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="2" t="s">
+        <v>767</v>
+      </c>
+      <c r="B32" s="1" t="s">
         <v>768</v>
       </c>
-      <c r="B32" s="1" t="s">
+      <c r="E32" s="1" t="s">
         <v>769</v>
       </c>
-      <c r="E32" s="1" t="s">
-        <v>770</v>
-      </c>
       <c r="F32" s="3">
         <v>1</v>
       </c>
       <c r="H32" s="7" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="2" t="s">
+        <v>763</v>
+      </c>
+      <c r="B33" s="1" t="s">
         <v>764</v>
       </c>
-      <c r="B33" s="1" t="s">
+      <c r="E33" s="1" t="s">
         <v>765</v>
       </c>
-      <c r="E33" s="1" t="s">
+      <c r="F33" s="3">
+        <v>1</v>
+      </c>
+      <c r="H33" s="2" t="s">
         <v>766</v>
-      </c>
-      <c r="F33" s="3">
-        <v>1</v>
-      </c>
-      <c r="H33" s="2" t="s">
-        <v>767</v>
       </c>
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="2" t="s">
+        <v>774</v>
+      </c>
+      <c r="B34" s="1" t="s">
         <v>775</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="E34" s="1" t="s">
+        <v>778</v>
+      </c>
+      <c r="F34" s="3">
+        <v>1</v>
+      </c>
+      <c r="H34" s="2" t="s">
         <v>776</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>779</v>
-      </c>
-      <c r="F34" s="3">
-        <v>1</v>
-      </c>
-      <c r="H34" s="2" t="s">
-        <v>777</v>
       </c>
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="2" t="s">
+        <v>788</v>
+      </c>
+      <c r="B35" s="1" t="s">
         <v>789</v>
       </c>
-      <c r="B35" s="1" t="s">
+      <c r="E35" s="1" t="s">
         <v>790</v>
       </c>
-      <c r="E35" s="1" t="s">
-        <v>791</v>
-      </c>
       <c r="F35" s="3">
         <v>1</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
     </row>
     <row r="36" spans="1:8">
       <c r="A36" s="2" t="s">
+        <v>784</v>
+      </c>
+      <c r="B36" s="1" t="s">
         <v>785</v>
       </c>
-      <c r="B36" s="1" t="s">
+      <c r="E36" s="1" t="s">
         <v>786</v>
       </c>
-      <c r="E36" s="1" t="s">
-        <v>787</v>
-      </c>
       <c r="F36" s="3">
         <v>1</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
     </row>
     <row r="37" spans="1:8">
       <c r="A37" s="2" t="s">
+        <v>771</v>
+      </c>
+      <c r="B37" s="1" t="s">
         <v>772</v>
       </c>
-      <c r="B37" s="1" t="s">
+      <c r="E37" s="1" t="s">
         <v>773</v>
       </c>
-      <c r="E37" s="1" t="s">
-        <v>774</v>
-      </c>
       <c r="F37" s="3">
         <v>1</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -5434,7 +5434,7 @@
         <v>1</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
     </row>
     <row r="40" spans="1:8">
@@ -5451,7 +5451,7 @@
         <v>1</v>
       </c>
       <c r="H40" s="9" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -5786,7 +5786,7 @@
         <v>1</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="H56" s="2" t="s">
         <v>542</v>
@@ -5839,7 +5839,7 @@
         <v>1</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="H59" t="s">
         <v>639</v>
@@ -5869,10 +5869,10 @@
     </row>
     <row r="61" spans="1:8">
       <c r="A61" s="11" t="s">
+        <v>825</v>
+      </c>
+      <c r="B61" t="s">
         <v>826</v>
-      </c>
-      <c r="B61" t="s">
-        <v>827</v>
       </c>
       <c r="C61">
         <v>6</v>
@@ -5881,7 +5881,7 @@
         <v>0</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="F61" s="3"/>
       <c r="G61" s="1"/>
@@ -6460,38 +6460,38 @@
     </row>
     <row r="90" spans="1:8">
       <c r="A90" t="s">
+        <v>828</v>
+      </c>
+      <c r="B90" t="s">
         <v>829</v>
-      </c>
-      <c r="B90" t="s">
-        <v>830</v>
       </c>
       <c r="C90" s="3"/>
       <c r="D90" s="4"/>
       <c r="E90" s="1" t="s">
+        <v>830</v>
+      </c>
+      <c r="F90" s="3">
+        <v>1</v>
+      </c>
+      <c r="H90" s="11" t="s">
         <v>831</v>
-      </c>
-      <c r="F90" s="3">
-        <v>1</v>
-      </c>
-      <c r="H90" s="11" t="s">
-        <v>832</v>
       </c>
     </row>
     <row r="91" spans="1:8">
       <c r="A91" s="2" t="s">
+        <v>812</v>
+      </c>
+      <c r="B91" s="1" t="s">
         <v>813</v>
       </c>
-      <c r="B91" s="1" t="s">
+      <c r="E91" s="1" t="s">
         <v>814</v>
       </c>
-      <c r="E91" s="1" t="s">
+      <c r="F91" s="3">
+        <v>1</v>
+      </c>
+      <c r="H91" s="7" t="s">
         <v>815</v>
-      </c>
-      <c r="F91" s="3">
-        <v>1</v>
-      </c>
-      <c r="H91" s="7" t="s">
-        <v>816</v>
       </c>
     </row>
     <row r="92" spans="1:8">
@@ -6650,257 +6650,257 @@
     </row>
     <row r="99" spans="1:8">
       <c r="A99" s="2" t="s">
+        <v>720</v>
+      </c>
+      <c r="B99" s="1" t="s">
         <v>721</v>
       </c>
-      <c r="B99" s="1" t="s">
-        <v>722</v>
-      </c>
       <c r="E99" s="1" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="F99" s="3">
         <v>1</v>
       </c>
       <c r="H99" s="7" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
     </row>
     <row r="100" spans="1:8">
       <c r="A100" s="2" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>691</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="F100" s="3">
         <v>1</v>
       </c>
       <c r="H100" s="7" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
     </row>
     <row r="101" spans="1:8">
       <c r="A101" s="2" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="F101" s="3">
         <v>1</v>
       </c>
       <c r="H101" s="7" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
     </row>
     <row r="102" spans="1:8">
       <c r="A102" s="2" t="s">
+        <v>709</v>
+      </c>
+      <c r="B102" s="1" t="s">
         <v>710</v>
       </c>
-      <c r="B102" s="1" t="s">
-        <v>711</v>
-      </c>
       <c r="E102" s="1" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="F102" s="3">
         <v>1</v>
       </c>
       <c r="H102" s="7" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
     </row>
     <row r="103" spans="1:8">
       <c r="A103" s="2" t="s">
+        <v>707</v>
+      </c>
+      <c r="B103" s="1" t="s">
         <v>708</v>
       </c>
-      <c r="B103" s="1" t="s">
-        <v>709</v>
-      </c>
       <c r="E103" s="1" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="F103" s="3">
         <v>1</v>
       </c>
       <c r="H103" s="7" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
     </row>
     <row r="104" spans="1:8">
       <c r="A104" s="2" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="F104" s="3">
         <v>1</v>
       </c>
       <c r="H104" s="7" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
     </row>
     <row r="105" spans="1:8">
       <c r="A105" s="2" t="s">
+        <v>713</v>
+      </c>
+      <c r="B105" s="1" t="s">
         <v>714</v>
       </c>
-      <c r="B105" s="1" t="s">
-        <v>715</v>
-      </c>
       <c r="E105" s="1" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="F105" s="3">
         <v>1</v>
       </c>
       <c r="H105" s="7" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
     </row>
     <row r="106" spans="1:8">
       <c r="A106" s="2" t="s">
+        <v>717</v>
+      </c>
+      <c r="B106" s="1" t="s">
         <v>718</v>
       </c>
-      <c r="B106" s="1" t="s">
-        <v>719</v>
-      </c>
       <c r="E106" s="1" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="F106" s="3">
         <v>1</v>
       </c>
       <c r="H106" s="7" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
     </row>
     <row r="107" spans="1:8">
       <c r="A107" s="2" t="s">
+        <v>699</v>
+      </c>
+      <c r="B107" s="1" t="s">
         <v>700</v>
       </c>
-      <c r="B107" s="1" t="s">
-        <v>701</v>
-      </c>
       <c r="E107" s="1" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="F107" s="3">
         <v>1</v>
       </c>
       <c r="H107" s="7" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
     </row>
     <row r="108" spans="1:8">
       <c r="A108" s="2" t="s">
+        <v>722</v>
+      </c>
+      <c r="B108" s="1" t="s">
         <v>723</v>
       </c>
-      <c r="B108" s="1" t="s">
-        <v>724</v>
-      </c>
       <c r="E108" s="1" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="F108" s="3">
         <v>1</v>
       </c>
       <c r="H108" s="7" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
     </row>
     <row r="109" spans="1:8">
       <c r="A109" s="2" t="s">
+        <v>715</v>
+      </c>
+      <c r="B109" s="1" t="s">
         <v>716</v>
       </c>
-      <c r="B109" s="1" t="s">
-        <v>717</v>
-      </c>
       <c r="E109" s="1" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="F109" s="3">
         <v>1</v>
       </c>
       <c r="H109" s="7" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
     </row>
     <row r="110" spans="1:8">
       <c r="A110" s="2" t="s">
+        <v>695</v>
+      </c>
+      <c r="B110" s="1" t="s">
         <v>696</v>
       </c>
-      <c r="B110" s="1" t="s">
-        <v>697</v>
-      </c>
       <c r="E110" s="1" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="F110" s="3">
         <v>1</v>
       </c>
       <c r="H110" s="7" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
     </row>
     <row r="111" spans="1:8">
       <c r="A111" s="2" t="s">
+        <v>697</v>
+      </c>
+      <c r="B111" s="1" t="s">
         <v>698</v>
       </c>
-      <c r="B111" s="1" t="s">
-        <v>699</v>
-      </c>
       <c r="E111" s="1" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="F111" s="3">
         <v>1</v>
       </c>
       <c r="H111" s="7" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
     </row>
     <row r="112" spans="1:8">
       <c r="A112" s="2" t="s">
+        <v>701</v>
+      </c>
+      <c r="B112" s="1" t="s">
         <v>702</v>
       </c>
-      <c r="B112" s="1" t="s">
-        <v>703</v>
-      </c>
       <c r="E112" s="1" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="F112" s="3">
         <v>1</v>
       </c>
       <c r="H112" s="7" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
     </row>
     <row r="113" spans="1:8">
       <c r="A113" s="2" t="s">
+        <v>711</v>
+      </c>
+      <c r="B113" s="1" t="s">
         <v>712</v>
       </c>
-      <c r="B113" s="1" t="s">
-        <v>713</v>
-      </c>
       <c r="E113" s="1" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="F113" s="3">
         <v>1</v>
       </c>
       <c r="H113" s="7" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
     </row>
     <row r="114" spans="1:8">
@@ -6927,64 +6927,64 @@
     </row>
     <row r="115" spans="1:8">
       <c r="A115" t="s">
+        <v>832</v>
+      </c>
+      <c r="B115" t="s">
         <v>833</v>
-      </c>
-      <c r="B115" t="s">
-        <v>834</v>
       </c>
       <c r="C115" s="3"/>
       <c r="D115" s="4"/>
       <c r="E115" s="1" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="F115" s="3">
         <v>1</v>
       </c>
       <c r="G115" s="1"/>
       <c r="H115" s="11" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
     </row>
     <row r="116" spans="1:8">
       <c r="A116" t="s">
+        <v>836</v>
+      </c>
+      <c r="B116" t="s">
         <v>837</v>
-      </c>
-      <c r="B116" t="s">
-        <v>838</v>
       </c>
       <c r="C116" s="3"/>
       <c r="D116" s="4"/>
       <c r="E116" s="1" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="F116" s="3">
         <v>1</v>
       </c>
       <c r="G116" s="1"/>
       <c r="H116" s="11" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="117" spans="1:8">
       <c r="A117" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="B117" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="C117" s="3"/>
       <c r="D117" s="4"/>
       <c r="E117" s="1" t="s">
+        <v>841</v>
+      </c>
+      <c r="F117" s="3">
+        <v>1</v>
+      </c>
+      <c r="G117" s="1" t="s">
         <v>842</v>
       </c>
-      <c r="F117" s="3">
-        <v>1</v>
-      </c>
-      <c r="G117" s="1" t="s">
+      <c r="H117" s="11" t="s">
         <v>843</v>
-      </c>
-      <c r="H117" s="11" t="s">
-        <v>844</v>
       </c>
     </row>
     <row r="118" spans="1:8">
@@ -7041,7 +7041,7 @@
       <c r="C120" s="1"/>
       <c r="D120" s="5"/>
       <c r="E120" s="1" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="F120" s="3">
         <v>1</v>
@@ -7053,19 +7053,19 @@
     </row>
     <row r="121" spans="1:8">
       <c r="A121" s="2" t="s">
+        <v>799</v>
+      </c>
+      <c r="B121" s="1" t="s">
         <v>800</v>
       </c>
-      <c r="B121" s="1" t="s">
+      <c r="E121" s="1" t="s">
+        <v>802</v>
+      </c>
+      <c r="F121" s="3">
+        <v>1</v>
+      </c>
+      <c r="H121" s="7" t="s">
         <v>801</v>
-      </c>
-      <c r="E121" s="1" t="s">
-        <v>803</v>
-      </c>
-      <c r="F121" s="3">
-        <v>1</v>
-      </c>
-      <c r="H121" s="7" t="s">
-        <v>802</v>
       </c>
     </row>
     <row r="122" spans="1:8">
@@ -7092,115 +7092,115 @@
     </row>
     <row r="123" spans="1:8">
       <c r="A123" t="s">
+        <v>844</v>
+      </c>
+      <c r="B123" t="s">
         <v>845</v>
-      </c>
-      <c r="B123" t="s">
-        <v>846</v>
       </c>
       <c r="C123"/>
       <c r="D123" s="11"/>
       <c r="E123" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="F123" s="1">
         <v>1</v>
       </c>
       <c r="G123"/>
       <c r="H123" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
     </row>
     <row r="124" spans="1:8">
       <c r="A124" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="B124" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="E124" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="F124" s="1">
         <v>1</v>
       </c>
       <c r="H124" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
     </row>
     <row r="125" spans="1:8">
       <c r="A125" t="s">
+        <v>847</v>
+      </c>
+      <c r="B125" t="s">
         <v>848</v>
       </c>
-      <c r="B125" t="s">
-        <v>849</v>
-      </c>
       <c r="E125" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="F125" s="1">
         <v>1</v>
       </c>
       <c r="H125" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
     </row>
     <row r="126" spans="1:8">
       <c r="A126" t="s">
+        <v>849</v>
+      </c>
+      <c r="B126" t="s">
         <v>850</v>
       </c>
-      <c r="B126" t="s">
-        <v>851</v>
-      </c>
       <c r="E126" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="F126" s="1">
         <v>1</v>
       </c>
       <c r="H126" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
     </row>
     <row r="127" spans="1:8">
       <c r="A127" t="s">
+        <v>851</v>
+      </c>
+      <c r="B127" t="s">
         <v>852</v>
       </c>
-      <c r="B127" t="s">
-        <v>853</v>
-      </c>
       <c r="E127" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="F127" s="1">
         <v>1</v>
       </c>
       <c r="H127" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
     </row>
     <row r="128" spans="1:8">
       <c r="A128" t="s">
+        <v>853</v>
+      </c>
+      <c r="B128" t="s">
         <v>854</v>
       </c>
-      <c r="B128" t="s">
-        <v>855</v>
-      </c>
       <c r="E128" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="F128" s="1">
         <v>1</v>
       </c>
       <c r="H128" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
     </row>
     <row r="129" spans="1:8">
       <c r="A129" t="s">
+        <v>855</v>
+      </c>
+      <c r="B129" t="s">
         <v>856</v>
-      </c>
-      <c r="B129" t="s">
-        <v>857</v>
       </c>
       <c r="C129" s="2">
         <v>6</v>
@@ -7209,36 +7209,36 @@
         <v>0</v>
       </c>
       <c r="E129" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="F129" s="1"/>
       <c r="H129" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
     </row>
     <row r="130" spans="1:8">
       <c r="A130" t="s">
+        <v>857</v>
+      </c>
+      <c r="B130" t="s">
         <v>858</v>
       </c>
-      <c r="B130" t="s">
-        <v>859</v>
-      </c>
       <c r="E130" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="F130" s="1">
         <v>1</v>
       </c>
       <c r="H130" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
     </row>
     <row r="131" spans="1:8">
       <c r="A131" t="s">
+        <v>859</v>
+      </c>
+      <c r="B131" t="s">
         <v>860</v>
-      </c>
-      <c r="B131" t="s">
-        <v>861</v>
       </c>
       <c r="C131" s="2">
         <v>6</v>
@@ -7247,45 +7247,45 @@
         <v>0</v>
       </c>
       <c r="E131" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="F131" s="1"/>
       <c r="H131" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
     </row>
     <row r="132" spans="1:8">
       <c r="A132" t="s">
+        <v>861</v>
+      </c>
+      <c r="B132" t="s">
         <v>862</v>
       </c>
-      <c r="B132" t="s">
-        <v>863</v>
-      </c>
       <c r="E132" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="F132" s="1">
         <v>1</v>
       </c>
       <c r="H132" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
     </row>
     <row r="133" spans="1:8">
       <c r="A133" t="s">
+        <v>1050</v>
+      </c>
+      <c r="B133" t="s">
         <v>1051</v>
       </c>
-      <c r="B133" t="s">
+      <c r="E133" t="s">
         <v>1052</v>
       </c>
-      <c r="E133" t="s">
-        <v>1053</v>
-      </c>
       <c r="F133" s="1">
         <v>1</v>
       </c>
       <c r="H133" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
     </row>
     <row r="134" spans="1:8">
@@ -7351,7 +7351,7 @@
       <c r="F136" s="3"/>
       <c r="G136" s="1"/>
       <c r="H136" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
     </row>
     <row r="137" spans="1:8">
@@ -7439,7 +7439,7 @@
       <c r="F140" s="3"/>
       <c r="G140" s="1"/>
       <c r="H140" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
     </row>
     <row r="141" spans="1:8">
@@ -7522,7 +7522,7 @@
         <v>0.625</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="F144" s="3"/>
       <c r="G144" s="1"/>
@@ -7632,7 +7632,7 @@
         <v>0</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="F149" s="3"/>
       <c r="G149" s="1"/>
@@ -7686,10 +7686,10 @@
     </row>
     <row r="152" spans="1:8">
       <c r="A152" s="11" t="s">
+        <v>875</v>
+      </c>
+      <c r="B152" s="11" t="s">
         <v>876</v>
-      </c>
-      <c r="B152" s="11" t="s">
-        <v>877</v>
       </c>
       <c r="C152">
         <v>14</v>
@@ -7698,500 +7698,500 @@
         <v>0</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="F152"/>
       <c r="G152"/>
       <c r="H152" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
     </row>
     <row r="153" spans="1:8">
       <c r="A153" t="s">
+        <v>877</v>
+      </c>
+      <c r="B153" t="s">
         <v>878</v>
-      </c>
-      <c r="B153" t="s">
-        <v>879</v>
       </c>
       <c r="C153"/>
       <c r="D153"/>
       <c r="E153" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="F153">
         <v>1</v>
       </c>
       <c r="G153"/>
       <c r="H153" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
     </row>
     <row r="154" spans="1:8">
       <c r="A154" t="s">
+        <v>879</v>
+      </c>
+      <c r="B154" t="s">
         <v>880</v>
-      </c>
-      <c r="B154" t="s">
-        <v>881</v>
       </c>
       <c r="C154"/>
       <c r="D154"/>
       <c r="E154" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="F154">
         <v>1</v>
       </c>
       <c r="G154"/>
       <c r="H154" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
     </row>
     <row r="155" spans="1:8">
       <c r="A155" t="s">
+        <v>881</v>
+      </c>
+      <c r="B155" t="s">
         <v>882</v>
-      </c>
-      <c r="B155" t="s">
-        <v>883</v>
       </c>
       <c r="C155"/>
       <c r="D155"/>
       <c r="E155" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="F155">
         <v>1</v>
       </c>
       <c r="G155"/>
       <c r="H155" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
     </row>
     <row r="156" spans="1:8">
       <c r="A156" t="s">
+        <v>883</v>
+      </c>
+      <c r="B156" t="s">
         <v>884</v>
-      </c>
-      <c r="B156" t="s">
-        <v>885</v>
       </c>
       <c r="C156"/>
       <c r="D156"/>
       <c r="E156" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="F156">
         <v>1</v>
       </c>
       <c r="G156"/>
       <c r="H156" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
     </row>
     <row r="157" spans="1:8">
       <c r="A157" t="s">
+        <v>885</v>
+      </c>
+      <c r="B157" t="s">
         <v>886</v>
-      </c>
-      <c r="B157" t="s">
-        <v>887</v>
       </c>
       <c r="C157"/>
       <c r="D157"/>
       <c r="E157" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="F157">
         <v>1</v>
       </c>
       <c r="G157"/>
       <c r="H157" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
     </row>
     <row r="158" spans="1:8">
       <c r="A158" t="s">
+        <v>887</v>
+      </c>
+      <c r="B158" t="s">
         <v>888</v>
-      </c>
-      <c r="B158" t="s">
-        <v>889</v>
       </c>
       <c r="C158"/>
       <c r="D158"/>
       <c r="E158" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="F158">
         <v>1</v>
       </c>
       <c r="G158"/>
       <c r="H158" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
     </row>
     <row r="159" spans="1:8">
       <c r="A159" t="s">
+        <v>889</v>
+      </c>
+      <c r="B159" t="s">
         <v>890</v>
-      </c>
-      <c r="B159" t="s">
-        <v>891</v>
       </c>
       <c r="C159"/>
       <c r="D159"/>
       <c r="E159" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="F159">
         <v>1</v>
       </c>
       <c r="G159"/>
       <c r="H159" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
     </row>
     <row r="160" spans="1:8">
       <c r="A160" t="s">
+        <v>891</v>
+      </c>
+      <c r="B160" t="s">
         <v>892</v>
-      </c>
-      <c r="B160" t="s">
-        <v>893</v>
       </c>
       <c r="C160"/>
       <c r="D160"/>
       <c r="E160" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="F160">
         <v>1</v>
       </c>
       <c r="G160"/>
       <c r="H160" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
     </row>
     <row r="161" spans="1:8">
       <c r="A161" t="s">
+        <v>893</v>
+      </c>
+      <c r="B161" t="s">
         <v>894</v>
-      </c>
-      <c r="B161" t="s">
-        <v>895</v>
       </c>
       <c r="C161"/>
       <c r="D161"/>
       <c r="E161" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="F161">
         <v>1</v>
       </c>
       <c r="G161"/>
       <c r="H161" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
     </row>
     <row r="162" spans="1:8">
       <c r="A162" t="s">
+        <v>895</v>
+      </c>
+      <c r="B162" t="s">
         <v>896</v>
-      </c>
-      <c r="B162" t="s">
-        <v>897</v>
       </c>
       <c r="C162"/>
       <c r="D162"/>
       <c r="E162" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="F162">
         <v>1</v>
       </c>
       <c r="G162"/>
       <c r="H162" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
     </row>
     <row r="163" spans="1:8">
       <c r="A163" t="s">
+        <v>897</v>
+      </c>
+      <c r="B163" t="s">
         <v>898</v>
-      </c>
-      <c r="B163" t="s">
-        <v>899</v>
       </c>
       <c r="C163"/>
       <c r="D163"/>
       <c r="E163" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="F163">
         <v>1</v>
       </c>
       <c r="G163"/>
       <c r="H163" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
     </row>
     <row r="164" spans="1:8">
       <c r="A164" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="B164" s="12" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="C164"/>
       <c r="D164"/>
       <c r="E164" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="F164">
         <v>1</v>
       </c>
       <c r="G164"/>
       <c r="H164" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
     </row>
     <row r="165" spans="1:8">
       <c r="A165" t="s">
+        <v>900</v>
+      </c>
+      <c r="B165" t="s">
         <v>901</v>
-      </c>
-      <c r="B165" t="s">
-        <v>902</v>
       </c>
       <c r="C165"/>
       <c r="D165"/>
       <c r="E165" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="F165">
         <v>1</v>
       </c>
       <c r="G165"/>
       <c r="H165" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
     </row>
     <row r="166" spans="1:8">
       <c r="A166" t="s">
+        <v>902</v>
+      </c>
+      <c r="B166" t="s">
         <v>903</v>
-      </c>
-      <c r="B166" t="s">
-        <v>904</v>
       </c>
       <c r="C166"/>
       <c r="D166"/>
       <c r="E166" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="F166">
         <v>1</v>
       </c>
       <c r="G166"/>
       <c r="H166" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
     </row>
     <row r="167" spans="1:8">
       <c r="A167" t="s">
+        <v>904</v>
+      </c>
+      <c r="B167" t="s">
         <v>905</v>
-      </c>
-      <c r="B167" t="s">
-        <v>906</v>
       </c>
       <c r="C167"/>
       <c r="D167"/>
       <c r="E167" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="F167">
         <v>1</v>
       </c>
       <c r="G167"/>
       <c r="H167" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
     </row>
     <row r="168" spans="1:8">
       <c r="A168" t="s">
+        <v>906</v>
+      </c>
+      <c r="B168" t="s">
         <v>907</v>
-      </c>
-      <c r="B168" t="s">
-        <v>908</v>
       </c>
       <c r="C168"/>
       <c r="D168"/>
       <c r="E168" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="F168">
         <v>1</v>
       </c>
       <c r="G168"/>
       <c r="H168" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
     </row>
     <row r="169" spans="1:8">
       <c r="A169" t="s">
+        <v>908</v>
+      </c>
+      <c r="B169" t="s">
         <v>909</v>
-      </c>
-      <c r="B169" t="s">
-        <v>910</v>
       </c>
       <c r="C169"/>
       <c r="D169"/>
       <c r="E169" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="F169">
         <v>1</v>
       </c>
       <c r="G169"/>
       <c r="H169" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
     </row>
     <row r="170" spans="1:8">
       <c r="A170" t="s">
+        <v>910</v>
+      </c>
+      <c r="B170" t="s">
         <v>911</v>
-      </c>
-      <c r="B170" t="s">
-        <v>912</v>
       </c>
       <c r="C170"/>
       <c r="D170"/>
       <c r="E170" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="F170">
         <v>1</v>
       </c>
       <c r="G170"/>
       <c r="H170" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
     </row>
     <row r="171" spans="1:8">
       <c r="A171" t="s">
+        <v>912</v>
+      </c>
+      <c r="B171" t="s">
         <v>913</v>
-      </c>
-      <c r="B171" t="s">
-        <v>914</v>
       </c>
       <c r="C171"/>
       <c r="D171"/>
       <c r="E171" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="F171">
         <v>1</v>
       </c>
       <c r="G171"/>
       <c r="H171" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
     </row>
     <row r="172" spans="1:8">
       <c r="A172" t="s">
+        <v>914</v>
+      </c>
+      <c r="B172" t="s">
         <v>915</v>
-      </c>
-      <c r="B172" t="s">
-        <v>916</v>
       </c>
       <c r="C172"/>
       <c r="D172"/>
       <c r="E172" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="F172">
         <v>1</v>
       </c>
       <c r="G172"/>
       <c r="H172" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
     </row>
     <row r="173" spans="1:8">
       <c r="A173" t="s">
+        <v>916</v>
+      </c>
+      <c r="B173" t="s">
         <v>917</v>
-      </c>
-      <c r="B173" t="s">
-        <v>918</v>
       </c>
       <c r="C173"/>
       <c r="D173"/>
       <c r="E173" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="F173">
         <v>1</v>
       </c>
       <c r="G173"/>
       <c r="H173" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
     </row>
     <row r="174" spans="1:8">
       <c r="A174" t="s">
+        <v>918</v>
+      </c>
+      <c r="B174" t="s">
         <v>919</v>
-      </c>
-      <c r="B174" t="s">
-        <v>920</v>
       </c>
       <c r="C174"/>
       <c r="D174"/>
       <c r="E174" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="F174">
         <v>1</v>
       </c>
       <c r="G174"/>
       <c r="H174" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
     </row>
     <row r="175" spans="1:8">
       <c r="A175" t="s">
+        <v>920</v>
+      </c>
+      <c r="B175" t="s">
         <v>921</v>
-      </c>
-      <c r="B175" t="s">
-        <v>922</v>
       </c>
       <c r="C175"/>
       <c r="D175"/>
       <c r="E175" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="F175">
         <v>1</v>
       </c>
       <c r="G175"/>
       <c r="H175" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
     </row>
     <row r="176" spans="1:8">
       <c r="A176" t="s">
+        <v>922</v>
+      </c>
+      <c r="B176" t="s">
         <v>923</v>
-      </c>
-      <c r="B176" t="s">
-        <v>924</v>
       </c>
       <c r="C176"/>
       <c r="D176"/>
       <c r="E176" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="F176">
         <v>1</v>
       </c>
       <c r="G176"/>
       <c r="H176" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
     </row>
     <row r="177" spans="1:8">
       <c r="A177" t="s">
+        <v>924</v>
+      </c>
+      <c r="B177" t="s">
         <v>925</v>
-      </c>
-      <c r="B177" t="s">
-        <v>926</v>
       </c>
       <c r="C177">
         <v>14</v>
@@ -8200,100 +8200,100 @@
         <v>0</v>
       </c>
       <c r="E177" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="F177"/>
       <c r="G177"/>
       <c r="H177" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
     </row>
     <row r="178" spans="1:8">
       <c r="A178" t="s">
+        <v>926</v>
+      </c>
+      <c r="B178" t="s">
         <v>927</v>
-      </c>
-      <c r="B178" t="s">
-        <v>928</v>
       </c>
       <c r="C178"/>
       <c r="D178"/>
       <c r="E178" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="F178">
         <v>1</v>
       </c>
       <c r="G178"/>
       <c r="H178" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
     </row>
     <row r="179" spans="1:8">
       <c r="A179" t="s">
+        <v>928</v>
+      </c>
+      <c r="B179" t="s">
         <v>929</v>
-      </c>
-      <c r="B179" t="s">
-        <v>930</v>
       </c>
       <c r="C179"/>
       <c r="D179"/>
       <c r="E179" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="F179">
         <v>1</v>
       </c>
       <c r="G179"/>
       <c r="H179" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
     </row>
     <row r="180" spans="1:8">
       <c r="A180" s="12" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="B180" s="12" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="C180"/>
       <c r="D180"/>
       <c r="E180" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="F180">
         <v>1</v>
       </c>
       <c r="G180"/>
       <c r="H180" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
     </row>
     <row r="181" spans="1:8">
       <c r="A181" t="s">
+        <v>931</v>
+      </c>
+      <c r="B181" t="s">
         <v>932</v>
-      </c>
-      <c r="B181" t="s">
-        <v>933</v>
       </c>
       <c r="C181"/>
       <c r="D181"/>
       <c r="E181" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="F181">
         <v>1</v>
       </c>
       <c r="G181"/>
       <c r="H181" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
     </row>
     <row r="182" spans="1:8">
       <c r="A182" t="s">
+        <v>933</v>
+      </c>
+      <c r="B182" t="s">
         <v>934</v>
-      </c>
-      <c r="B182" t="s">
-        <v>935</v>
       </c>
       <c r="C182">
         <v>14</v>
@@ -8302,152 +8302,152 @@
         <v>0</v>
       </c>
       <c r="E182" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="F182"/>
       <c r="G182"/>
       <c r="H182" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
     </row>
     <row r="183" spans="1:8">
       <c r="A183" t="s">
+        <v>935</v>
+      </c>
+      <c r="B183" t="s">
         <v>936</v>
-      </c>
-      <c r="B183" t="s">
-        <v>937</v>
       </c>
       <c r="C183"/>
       <c r="D183"/>
       <c r="E183" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F183">
         <v>1</v>
       </c>
       <c r="G183"/>
       <c r="H183" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
     </row>
     <row r="184" spans="1:8">
       <c r="A184" t="s">
+        <v>937</v>
+      </c>
+      <c r="B184" t="s">
         <v>938</v>
-      </c>
-      <c r="B184" t="s">
-        <v>939</v>
       </c>
       <c r="C184"/>
       <c r="D184"/>
       <c r="E184" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="F184">
         <v>1</v>
       </c>
       <c r="G184"/>
       <c r="H184" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
     </row>
     <row r="185" spans="1:8">
       <c r="A185" t="s">
+        <v>939</v>
+      </c>
+      <c r="B185" t="s">
         <v>940</v>
-      </c>
-      <c r="B185" t="s">
-        <v>941</v>
       </c>
       <c r="C185"/>
       <c r="D185"/>
       <c r="E185" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="F185">
         <v>1</v>
       </c>
       <c r="G185"/>
       <c r="H185" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
     </row>
     <row r="186" spans="1:8">
       <c r="A186" t="s">
+        <v>941</v>
+      </c>
+      <c r="B186" t="s">
         <v>942</v>
-      </c>
-      <c r="B186" t="s">
-        <v>943</v>
       </c>
       <c r="C186"/>
       <c r="D186"/>
       <c r="E186" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="F186">
         <v>1</v>
       </c>
       <c r="G186"/>
       <c r="H186" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
     </row>
     <row r="187" spans="1:8">
       <c r="A187" t="s">
+        <v>943</v>
+      </c>
+      <c r="B187" t="s">
         <v>944</v>
-      </c>
-      <c r="B187" t="s">
-        <v>945</v>
       </c>
       <c r="C187"/>
       <c r="D187"/>
       <c r="E187" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="F187">
         <v>1</v>
       </c>
       <c r="G187"/>
       <c r="H187" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
     </row>
     <row r="188" spans="1:8">
       <c r="A188" t="s">
+        <v>945</v>
+      </c>
+      <c r="B188" t="s">
         <v>946</v>
-      </c>
-      <c r="B188" t="s">
-        <v>947</v>
       </c>
       <c r="C188"/>
       <c r="D188"/>
       <c r="E188" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="F188">
         <v>1</v>
       </c>
       <c r="G188"/>
       <c r="H188" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
     </row>
     <row r="189" spans="1:8">
       <c r="A189" t="s">
+        <v>1042</v>
+      </c>
+      <c r="B189" t="s">
         <v>1043</v>
-      </c>
-      <c r="B189" t="s">
-        <v>1044</v>
       </c>
       <c r="C189"/>
       <c r="D189"/>
       <c r="E189" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="F189">
         <v>1</v>
       </c>
       <c r="G189"/>
       <c r="H189" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
     </row>
     <row r="190" spans="1:8">
@@ -8469,7 +8469,7 @@
       <c r="F190" s="3"/>
       <c r="G190" s="1"/>
       <c r="H190" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
     </row>
     <row r="191" spans="1:8">
@@ -8524,13 +8524,13 @@
         <v>503</v>
       </c>
       <c r="E193" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="F193" s="2">
+        <v>1</v>
+      </c>
+      <c r="G193" s="2" t="s">
         <v>758</v>
-      </c>
-      <c r="F193" s="2">
-        <v>1</v>
-      </c>
-      <c r="G193" s="2" t="s">
-        <v>759</v>
       </c>
       <c r="H193" s="2" t="s">
         <v>616</v>
@@ -8544,13 +8544,13 @@
         <v>504</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="F194" s="2">
         <v>1</v>
       </c>
       <c r="G194" s="2" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="H194" s="2" t="s">
         <v>617</v>
@@ -8564,13 +8564,13 @@
         <v>504</v>
       </c>
       <c r="E195" s="1" t="s">
+        <v>760</v>
+      </c>
+      <c r="F195" s="2">
+        <v>1</v>
+      </c>
+      <c r="G195" s="2" t="s">
         <v>761</v>
-      </c>
-      <c r="F195" s="2">
-        <v>1</v>
-      </c>
-      <c r="G195" s="2" t="s">
-        <v>762</v>
       </c>
       <c r="H195" s="2" t="s">
         <v>617</v>
@@ -8594,25 +8594,25 @@
       </c>
       <c r="F196" s="3"/>
       <c r="H196" s="2" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="197" spans="1:8">
       <c r="A197" s="2" t="s">
+        <v>803</v>
+      </c>
+      <c r="B197" s="1" t="s">
         <v>804</v>
-      </c>
-      <c r="B197" s="1" t="s">
-        <v>805</v>
       </c>
       <c r="D197" s="6"/>
       <c r="E197" s="1" t="s">
+        <v>805</v>
+      </c>
+      <c r="F197" s="3">
+        <v>1</v>
+      </c>
+      <c r="H197" s="7" t="s">
         <v>806</v>
-      </c>
-      <c r="F197" s="3">
-        <v>1</v>
-      </c>
-      <c r="H197" s="7" t="s">
-        <v>807</v>
       </c>
     </row>
     <row r="198" spans="1:8">
@@ -8654,7 +8654,7 @@
         <v>643</v>
       </c>
       <c r="H199" s="2" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="200" spans="1:8">
@@ -8674,35 +8674,35 @@
         <v>644</v>
       </c>
       <c r="H200" s="2" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="201" spans="1:8">
       <c r="A201" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="B201" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="C201"/>
       <c r="D201" s="11"/>
       <c r="E201" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="F201">
         <v>1</v>
       </c>
       <c r="G201"/>
       <c r="H201" s="11" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="202" spans="1:8">
       <c r="A202" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="B202" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="C202">
         <v>10</v>
@@ -8711,32 +8711,32 @@
         <v>0</v>
       </c>
       <c r="E202" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="F202"/>
       <c r="G202"/>
       <c r="H202" s="11" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="203" spans="1:8">
       <c r="A203" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="B203" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="C203"/>
       <c r="D203" s="11"/>
       <c r="E203" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="F203">
         <v>1</v>
       </c>
       <c r="G203"/>
       <c r="H203" s="11" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="204" spans="1:8">
@@ -8840,15 +8840,15 @@
         <v>1</v>
       </c>
       <c r="H208" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
     </row>
     <row r="209" spans="1:8">
       <c r="A209" t="s">
+        <v>986</v>
+      </c>
+      <c r="B209" t="s">
         <v>987</v>
-      </c>
-      <c r="B209" t="s">
-        <v>988</v>
       </c>
       <c r="C209">
         <v>15</v>
@@ -8857,20 +8857,20 @@
         <v>0</v>
       </c>
       <c r="E209" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="F209"/>
       <c r="G209"/>
       <c r="H209" s="11" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
     </row>
     <row r="210" spans="1:8">
       <c r="A210" t="s">
+        <v>990</v>
+      </c>
+      <c r="B210" t="s">
         <v>991</v>
-      </c>
-      <c r="B210" t="s">
-        <v>992</v>
       </c>
       <c r="C210">
         <v>15</v>
@@ -8879,20 +8879,20 @@
         <v>0</v>
       </c>
       <c r="E210" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="F210"/>
       <c r="G210"/>
       <c r="H210" s="11" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
     </row>
     <row r="211" spans="1:8">
       <c r="A211" t="s">
+        <v>994</v>
+      </c>
+      <c r="B211" t="s">
         <v>995</v>
-      </c>
-      <c r="B211" t="s">
-        <v>996</v>
       </c>
       <c r="C211">
         <v>15</v>
@@ -8901,20 +8901,20 @@
         <v>0</v>
       </c>
       <c r="E211" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="F211"/>
       <c r="G211"/>
       <c r="H211" s="11" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
     </row>
     <row r="212" spans="1:8">
       <c r="A212" t="s">
+        <v>998</v>
+      </c>
+      <c r="B212" t="s">
         <v>999</v>
-      </c>
-      <c r="B212" t="s">
-        <v>1000</v>
       </c>
       <c r="C212">
         <v>20</v>
@@ -8923,20 +8923,20 @@
         <v>0</v>
       </c>
       <c r="E212" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="F212"/>
       <c r="G212"/>
       <c r="H212" s="11" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="213" spans="1:8">
       <c r="A213" t="s">
+        <v>1002</v>
+      </c>
+      <c r="B213" t="s">
         <v>1003</v>
-      </c>
-      <c r="B213" t="s">
-        <v>1004</v>
       </c>
       <c r="C213">
         <v>15</v>
@@ -8945,12 +8945,12 @@
         <v>0</v>
       </c>
       <c r="E213" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="F213"/>
       <c r="G213"/>
       <c r="H213" s="11" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="214" spans="1:8">
@@ -8969,7 +8969,7 @@
         <v>1</v>
       </c>
       <c r="G214" s="1" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="H214" s="2" t="s">
         <v>581</v>
@@ -8991,7 +8991,7 @@
         <v>1</v>
       </c>
       <c r="G215" s="1" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="H215" s="2" t="s">
         <v>581</v>
@@ -9077,7 +9077,7 @@
         <v>0</v>
       </c>
       <c r="E219" s="1" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="F219" s="3"/>
       <c r="G219" s="1"/>
@@ -9181,7 +9181,7 @@
         <v>0</v>
       </c>
       <c r="E224" s="1" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="F224" s="3"/>
       <c r="G224" s="1"/>
@@ -9213,7 +9213,7 @@
     </row>
     <row r="226" spans="1:8">
       <c r="A226" s="2" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="B226" s="1" t="s">
         <v>692</v>
@@ -9225,11 +9225,11 @@
         <v>0.95833333333333337</v>
       </c>
       <c r="E226" s="1" t="s">
-        <v>693</v>
+        <v>1196</v>
       </c>
       <c r="F226" s="3"/>
       <c r="H226" s="7" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="227" spans="1:8">
@@ -9251,7 +9251,7 @@
       <c r="F227" s="3"/>
       <c r="G227" s="1"/>
       <c r="H227" s="7" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="228" spans="1:8">
@@ -9351,7 +9351,7 @@
         <v>0</v>
       </c>
       <c r="E232" s="1" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="F232" s="3"/>
       <c r="G232" s="1"/>
@@ -9405,10 +9405,10 @@
     </row>
     <row r="235" spans="1:8">
       <c r="A235" t="s">
+        <v>1008</v>
+      </c>
+      <c r="B235" t="s">
         <v>1009</v>
-      </c>
-      <c r="B235" t="s">
-        <v>1010</v>
       </c>
       <c r="C235">
         <v>6</v>
@@ -9417,20 +9417,20 @@
         <v>0</v>
       </c>
       <c r="E235" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="F235"/>
       <c r="G235"/>
       <c r="H235" s="7" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="236" spans="1:8">
       <c r="A236" s="11" t="s">
+        <v>1012</v>
+      </c>
+      <c r="B236" t="s">
         <v>1013</v>
-      </c>
-      <c r="B236" t="s">
-        <v>1014</v>
       </c>
       <c r="C236" s="3">
         <v>7</v>
@@ -9439,12 +9439,12 @@
         <v>0.91666666666666663</v>
       </c>
       <c r="E236" s="1" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="F236"/>
       <c r="G236"/>
       <c r="H236" s="7" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="237" spans="1:8">
@@ -9493,22 +9493,22 @@
     </row>
     <row r="239" spans="1:8" customFormat="1">
       <c r="A239" s="2" t="s">
+        <v>795</v>
+      </c>
+      <c r="B239" s="1" t="s">
         <v>796</v>
-      </c>
-      <c r="B239" s="1" t="s">
-        <v>797</v>
       </c>
       <c r="C239" s="2"/>
       <c r="D239" s="2"/>
       <c r="E239" s="1" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="F239" s="3">
         <v>1</v>
       </c>
       <c r="G239" s="2"/>
       <c r="H239" s="7" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
     </row>
     <row r="240" spans="1:8">
@@ -9595,24 +9595,24 @@
     </row>
     <row r="244" spans="1:8">
       <c r="A244" s="11" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B244" t="s">
         <v>1015</v>
-      </c>
-      <c r="B244" t="s">
-        <v>1016</v>
       </c>
       <c r="C244">
         <v>13</v>
       </c>
       <c r="D244" s="11" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="E244" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="F244"/>
       <c r="G244"/>
       <c r="H244" s="7" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="245" spans="1:8">
@@ -9629,7 +9629,7 @@
         <v>0.91666666666666663</v>
       </c>
       <c r="E245" s="1" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="F245" s="3"/>
       <c r="G245" s="1"/>
@@ -9685,7 +9685,7 @@
         <v>0</v>
       </c>
       <c r="E248" s="1" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="F248" s="3"/>
       <c r="G248" s="1"/>
@@ -9707,7 +9707,7 @@
         <v>0</v>
       </c>
       <c r="E249" s="1" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="F249" s="3"/>
       <c r="G249" s="1"/>
@@ -9997,7 +9997,7 @@
       </c>
       <c r="F262" s="3"/>
       <c r="H262" s="7" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
     </row>
     <row r="263" spans="1:8">
@@ -10040,7 +10040,7 @@
       <c r="F264" s="3"/>
       <c r="G264" s="1"/>
       <c r="H264" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
     </row>
     <row r="265" spans="1:8">
@@ -10067,10 +10067,10 @@
     </row>
     <row r="266" spans="1:8">
       <c r="A266" s="2" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="B266" s="1" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="C266" s="2">
         <v>6</v>
@@ -10079,19 +10079,19 @@
         <v>0</v>
       </c>
       <c r="E266" s="1" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="F266" s="3"/>
       <c r="H266" s="7" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
     </row>
     <row r="267" spans="1:8">
       <c r="A267" s="2" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="B267" s="1" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="C267" s="2">
         <v>6</v>
@@ -10100,19 +10100,19 @@
         <v>0</v>
       </c>
       <c r="E267" s="10" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="F267" s="3"/>
       <c r="H267" s="2" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
     </row>
     <row r="268" spans="1:8">
       <c r="A268" s="2" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="B268" s="1" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="C268" s="2">
         <v>6</v>
@@ -10121,19 +10121,19 @@
         <v>0</v>
       </c>
       <c r="E268" s="1" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="F268" s="3"/>
       <c r="H268" s="2" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
     </row>
     <row r="269" spans="1:8">
       <c r="A269" s="2" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="B269" s="1" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="C269" s="2">
         <v>6</v>
@@ -10142,11 +10142,11 @@
         <v>0</v>
       </c>
       <c r="E269" s="1" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="F269" s="3"/>
       <c r="H269" s="2" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
     </row>
     <row r="270" spans="1:8">
@@ -10159,13 +10159,13 @@
       <c r="C270" s="3"/>
       <c r="D270" s="6"/>
       <c r="E270" s="1" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="F270" s="3">
         <v>1</v>
       </c>
       <c r="G270" s="2" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="H270" t="s">
         <v>642</v>
@@ -10352,7 +10352,7 @@
         <v>454</v>
       </c>
       <c r="B279" s="1" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="C279" s="3">
         <v>6</v>
@@ -10743,129 +10743,129 @@
     </row>
     <row r="297" spans="1:8">
       <c r="A297" t="s">
+        <v>1033</v>
+      </c>
+      <c r="B297" s="1" t="s">
         <v>1034</v>
       </c>
-      <c r="B297" s="1" t="s">
-        <v>1035</v>
-      </c>
       <c r="E297" s="1" t="s">
+        <v>1038</v>
+      </c>
+      <c r="F297" s="2">
+        <v>1</v>
+      </c>
+      <c r="H297" s="7" t="s">
         <v>1039</v>
-      </c>
-      <c r="F297" s="2">
-        <v>1</v>
-      </c>
-      <c r="H297" s="7" t="s">
-        <v>1040</v>
       </c>
     </row>
     <row r="298" spans="1:8">
       <c r="A298" s="2" t="s">
+        <v>1053</v>
+      </c>
+      <c r="B298" s="1" t="s">
         <v>1054</v>
       </c>
-      <c r="B298" s="1" t="s">
+      <c r="E298" s="1" t="s">
         <v>1055</v>
       </c>
-      <c r="E298" s="1" t="s">
+      <c r="F298" s="2">
+        <v>1</v>
+      </c>
+      <c r="H298" s="2" t="s">
         <v>1056</v>
-      </c>
-      <c r="F298" s="2">
-        <v>1</v>
-      </c>
-      <c r="H298" s="2" t="s">
-        <v>1057</v>
       </c>
     </row>
     <row r="299" spans="1:8">
       <c r="A299" s="2" t="s">
+        <v>1058</v>
+      </c>
+      <c r="B299" s="1" t="s">
+        <v>1057</v>
+      </c>
+      <c r="E299" s="1" t="s">
+        <v>1060</v>
+      </c>
+      <c r="F299" s="2">
+        <v>1</v>
+      </c>
+      <c r="H299" s="7" t="s">
         <v>1059</v>
-      </c>
-      <c r="B299" s="1" t="s">
-        <v>1058</v>
-      </c>
-      <c r="E299" s="1" t="s">
-        <v>1061</v>
-      </c>
-      <c r="F299" s="2">
-        <v>1</v>
-      </c>
-      <c r="H299" s="7" t="s">
-        <v>1060</v>
       </c>
     </row>
     <row r="300" spans="1:8">
       <c r="A300" s="2" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="B300" s="1" t="s">
+        <v>1061</v>
+      </c>
+      <c r="E300" s="1" t="s">
         <v>1062</v>
       </c>
-      <c r="E300" s="1" t="s">
+      <c r="F300" s="2">
+        <v>1</v>
+      </c>
+      <c r="H300" s="2" t="s">
         <v>1063</v>
-      </c>
-      <c r="F300" s="2">
-        <v>1</v>
-      </c>
-      <c r="H300" s="2" t="s">
-        <v>1064</v>
       </c>
     </row>
     <row r="301" spans="1:8">
       <c r="A301" s="2" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="B301" s="1" t="s">
+        <v>1064</v>
+      </c>
+      <c r="E301" s="1" t="s">
         <v>1065</v>
       </c>
-      <c r="E301" s="1" t="s">
-        <v>1066</v>
-      </c>
       <c r="F301" s="2">
         <v>1</v>
       </c>
       <c r="H301" s="2" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="302" spans="1:8">
       <c r="A302" s="2" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="B302" s="1" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="E302" s="1" t="s">
+        <v>1070</v>
+      </c>
+      <c r="F302" s="2">
+        <v>1</v>
+      </c>
+      <c r="H302" s="2" t="s">
         <v>1071</v>
-      </c>
-      <c r="F302" s="2">
-        <v>1</v>
-      </c>
-      <c r="H302" s="2" t="s">
-        <v>1072</v>
       </c>
     </row>
     <row r="303" spans="1:8">
       <c r="A303" s="2" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="B303" s="1" t="s">
+        <v>1073</v>
+      </c>
+      <c r="E303" s="1" t="s">
         <v>1074</v>
       </c>
-      <c r="E303" s="1" t="s">
-        <v>1075</v>
-      </c>
       <c r="F303" s="2">
         <v>1</v>
       </c>
       <c r="H303" s="7" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="304" spans="1:8">
       <c r="A304" s="2" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="B304" s="1" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="C304" s="2">
         <v>6</v>
@@ -10874,66 +10874,66 @@
         <v>0</v>
       </c>
       <c r="E304" s="1" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="H304" s="7" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="305" spans="1:8">
       <c r="A305" s="2" t="s">
+        <v>1080</v>
+      </c>
+      <c r="B305" s="1" t="s">
         <v>1081</v>
       </c>
-      <c r="B305" s="1" t="s">
-        <v>1082</v>
-      </c>
       <c r="E305" s="1" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="H305" s="7" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="306" spans="1:8">
       <c r="A306" s="2" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="B306" s="1" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="E306" s="1" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="F306" s="2">
         <v>1</v>
       </c>
       <c r="H306" s="2" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="307" spans="1:8">
       <c r="A307" s="2" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="B307" s="1" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="E307" s="1" t="s">
+        <v>1136</v>
+      </c>
+      <c r="F307" s="2">
+        <v>1</v>
+      </c>
+      <c r="H307" s="2" t="s">
         <v>1137</v>
-      </c>
-      <c r="F307" s="2">
-        <v>1</v>
-      </c>
-      <c r="H307" s="2" t="s">
-        <v>1138</v>
       </c>
     </row>
     <row r="308" spans="1:8">
       <c r="A308" s="2" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="B308" s="1" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="C308" s="2">
         <v>14</v>
@@ -10942,18 +10942,18 @@
         <v>0</v>
       </c>
       <c r="E308" s="1" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="H308" s="2" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="309" spans="1:8">
       <c r="A309" s="2" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="B309" s="1" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="C309" s="2">
         <v>6</v>
@@ -10962,23 +10962,23 @@
         <v>0</v>
       </c>
       <c r="E309" s="1" t="s">
+        <v>1152</v>
+      </c>
+      <c r="H309" s="2" t="s">
         <v>1153</v>
-      </c>
-      <c r="H309" s="2" t="s">
-        <v>1154</v>
       </c>
     </row>
     <row r="310" spans="1:8">
       <c r="B310" s="1" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="311" spans="1:8">
       <c r="A311" s="2" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="B311" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="C311" s="2">
         <v>14</v>
@@ -10987,125 +10987,125 @@
         <v>0</v>
       </c>
       <c r="E311" s="2" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="H311" s="2" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="312" spans="1:8">
       <c r="A312" s="2" t="s">
+        <v>1161</v>
+      </c>
+      <c r="B312" s="1" t="s">
+        <v>1089</v>
+      </c>
+      <c r="E312" s="2" t="s">
+        <v>1163</v>
+      </c>
+      <c r="F312" s="2">
+        <v>1</v>
+      </c>
+      <c r="H312" s="2" t="s">
         <v>1162</v>
-      </c>
-      <c r="B312" s="1" t="s">
-        <v>1090</v>
-      </c>
-      <c r="E312" s="2" t="s">
-        <v>1164</v>
-      </c>
-      <c r="F312" s="2">
-        <v>1</v>
-      </c>
-      <c r="H312" s="2" t="s">
-        <v>1163</v>
       </c>
     </row>
     <row r="313" spans="1:8">
       <c r="A313" s="2" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="B313" s="1" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="E313" s="2" t="s">
+        <v>1176</v>
+      </c>
+      <c r="F313" s="2">
+        <v>1</v>
+      </c>
+      <c r="H313" s="7" t="s">
         <v>1177</v>
-      </c>
-      <c r="F313" s="2">
-        <v>1</v>
-      </c>
-      <c r="H313" s="7" t="s">
-        <v>1178</v>
       </c>
     </row>
     <row r="314" spans="1:8">
       <c r="A314" s="2" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="B314" s="1" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="E314" s="2" t="s">
+        <v>1183</v>
+      </c>
+      <c r="F314" s="2">
+        <v>1</v>
+      </c>
+      <c r="H314" s="7" t="s">
         <v>1184</v>
-      </c>
-      <c r="F314" s="2">
-        <v>1</v>
-      </c>
-      <c r="H314" s="7" t="s">
-        <v>1185</v>
       </c>
     </row>
     <row r="315" spans="1:8">
       <c r="B315" s="1" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="316" spans="1:8">
       <c r="A316" s="2" t="s">
+        <v>1170</v>
+      </c>
+      <c r="B316" s="1" t="s">
+        <v>1093</v>
+      </c>
+      <c r="E316" s="2" t="s">
         <v>1171</v>
       </c>
-      <c r="B316" s="1" t="s">
-        <v>1094</v>
-      </c>
-      <c r="E316" s="2" t="s">
+      <c r="F316" s="2">
+        <v>1</v>
+      </c>
+      <c r="H316" s="7" t="s">
         <v>1172</v>
-      </c>
-      <c r="F316" s="2">
-        <v>1</v>
-      </c>
-      <c r="H316" s="7" t="s">
-        <v>1173</v>
       </c>
     </row>
     <row r="317" spans="1:8">
       <c r="A317" s="2" t="s">
+        <v>1164</v>
+      </c>
+      <c r="B317" s="1" t="s">
+        <v>1094</v>
+      </c>
+      <c r="E317" s="2" t="s">
         <v>1165</v>
       </c>
-      <c r="B317" s="1" t="s">
-        <v>1095</v>
-      </c>
-      <c r="E317" s="2" t="s">
+      <c r="F317" s="2">
+        <v>1</v>
+      </c>
+      <c r="H317" s="2" t="s">
         <v>1166</v>
-      </c>
-      <c r="F317" s="2">
-        <v>1</v>
-      </c>
-      <c r="H317" s="2" t="s">
-        <v>1167</v>
       </c>
     </row>
     <row r="318" spans="1:8">
       <c r="A318" s="2" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B318" s="1" t="s">
+        <v>1095</v>
+      </c>
+      <c r="E318" s="2" t="s">
+        <v>1169</v>
+      </c>
+      <c r="F318" s="2">
+        <v>1</v>
+      </c>
+      <c r="H318" s="2" t="s">
         <v>1168</v>
-      </c>
-      <c r="B318" s="1" t="s">
-        <v>1096</v>
-      </c>
-      <c r="E318" s="2" t="s">
-        <v>1170</v>
-      </c>
-      <c r="F318" s="2">
-        <v>1</v>
-      </c>
-      <c r="H318" s="2" t="s">
-        <v>1169</v>
       </c>
     </row>
     <row r="319" spans="1:8">
       <c r="A319" s="2" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="B319" s="1" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="C319" s="2">
         <v>6</v>
@@ -11114,174 +11114,174 @@
         <v>0</v>
       </c>
       <c r="E319" s="2" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="H319" s="2" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="320" spans="1:8">
       <c r="A320" s="2" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="B320" s="1" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="E320" s="2" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="F320" s="2">
         <v>1</v>
       </c>
       <c r="H320" s="2" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="321" spans="1:8">
       <c r="A321" s="2" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="B321" s="1" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="E321" s="2" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="F321" s="2">
         <v>1</v>
       </c>
       <c r="H321" s="2" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="322" spans="1:8">
       <c r="A322" s="2" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="B322" s="1" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="E322" s="2" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="F322" s="2">
         <v>1</v>
       </c>
       <c r="H322" s="2" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="323" spans="1:8">
       <c r="A323" s="2" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="B323" s="1" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="E323" s="2" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="F323" s="2">
         <v>1</v>
       </c>
       <c r="H323" s="2" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="324" spans="1:8">
       <c r="A324" s="2" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="B324" s="1" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="E324" s="2" t="s">
+        <v>1110</v>
+      </c>
+      <c r="F324" s="2">
+        <v>1</v>
+      </c>
+      <c r="H324" s="2" t="s">
         <v>1111</v>
-      </c>
-      <c r="F324" s="2">
-        <v>1</v>
-      </c>
-      <c r="H324" s="2" t="s">
-        <v>1112</v>
       </c>
     </row>
     <row r="325" spans="1:8">
       <c r="A325" s="2" t="s">
+        <v>1119</v>
+      </c>
+      <c r="B325" s="1" t="s">
         <v>1120</v>
       </c>
-      <c r="B325" s="1" t="s">
+      <c r="E325" t="s">
         <v>1121</v>
       </c>
-      <c r="E325" t="s">
+      <c r="F325" s="2">
+        <v>1</v>
+      </c>
+      <c r="G325" s="2" t="s">
+        <v>1132</v>
+      </c>
+      <c r="H325" s="7" t="s">
         <v>1122</v>
-      </c>
-      <c r="F325" s="2">
-        <v>1</v>
-      </c>
-      <c r="G325" s="2" t="s">
-        <v>1133</v>
-      </c>
-      <c r="H325" s="7" t="s">
-        <v>1123</v>
       </c>
     </row>
     <row r="326" spans="1:8">
       <c r="A326" s="2" t="s">
+        <v>1138</v>
+      </c>
+      <c r="B326" s="1" t="s">
         <v>1139</v>
       </c>
-      <c r="B326" s="1" t="s">
-        <v>1140</v>
-      </c>
       <c r="E326" s="2" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="F326" s="2">
         <v>1</v>
       </c>
       <c r="H326" s="2" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="327" spans="1:8">
       <c r="A327" s="2" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="B327" s="1" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="E327" s="2" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="F327" s="2">
         <v>1</v>
       </c>
       <c r="H327" s="2" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="328" spans="1:8">
       <c r="A328" s="2" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="B328" s="1" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="E328" s="2" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="F328" s="2">
         <v>1</v>
       </c>
       <c r="H328" s="2" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="329" spans="1:8">
       <c r="A329" s="2" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="B329" s="1" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="C329" s="2">
         <v>14</v>
@@ -11290,18 +11290,18 @@
         <v>0</v>
       </c>
       <c r="E329" s="2" t="s">
+        <v>1149</v>
+      </c>
+      <c r="H329" s="2" t="s">
         <v>1150</v>
-      </c>
-      <c r="H329" s="2" t="s">
-        <v>1151</v>
       </c>
     </row>
     <row r="330" spans="1:8">
       <c r="A330" s="2" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B330" s="1" t="s">
         <v>1158</v>
-      </c>
-      <c r="B330" s="1" t="s">
-        <v>1159</v>
       </c>
       <c r="C330" s="2">
         <v>12</v>
@@ -11310,27 +11310,27 @@
         <v>0</v>
       </c>
       <c r="E330" s="2" t="s">
+        <v>1159</v>
+      </c>
+      <c r="H330" s="7" t="s">
         <v>1160</v>
-      </c>
-      <c r="H330" s="7" t="s">
-        <v>1161</v>
       </c>
     </row>
     <row r="331" spans="1:8">
       <c r="A331" s="2" t="s">
+        <v>1185</v>
+      </c>
+      <c r="B331" s="1" t="s">
         <v>1186</v>
       </c>
-      <c r="B331" s="1" t="s">
-        <v>1187</v>
-      </c>
       <c r="E331" s="2" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="F331" s="2">
         <v>1</v>
       </c>
       <c r="H331" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
     </row>
   </sheetData>

--- a/stores.xlsx
+++ b/stores.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\YUMIN\Desktop\B0KT2A_RSVN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C891974A-D352-4433-93A8-A902E5044542}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F520BBC6-7039-4EFF-9D38-F84D3A28954E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{ABFC3117-FCCB-4FF3-804A-FE19451A2004}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1323" uniqueCount="1190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1339" uniqueCount="1202">
   <si>
     <t>룸익스케이프 WHITE</t>
   </si>
@@ -3048,10 +3048,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>강천여자고등학교,강천여고,자각몽</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>피안화</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -4179,10 +4175,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>PUPPET PLAY,퍼펫플레이</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>파란</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -4340,6 +4332,61 @@
   </si>
   <si>
     <t>https://naver.me/GCvjk8Um</t>
+  </si>
+  <si>
+    <t>PUPPET PLAY,퍼펫플레이,룰더데이,RULE THE DAY</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>강천여자고등학교,강천여고,자각몽,좌충우돌꼬마마법사</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ser_dsr</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>서울이스케이프룸 대구동성로점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>카지노,팩토리,엘리베이터,파킹랏,춘단화,오모테나시,만찬,접견</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ser_bp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>서울이스케이프룸 부평점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ser_sm</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>서울이스케이프룸 부산서면점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>죽음을부르는재즈바,죽재바,유러피안스파이,회장님의서재,알카트라즈지하감옥,404호살인사건</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pm_hd</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>파노라마 홍대입구점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>룰더데이,ruletheday</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://naver.me/5o0Qylbb</t>
   </si>
 </sst>
 </file>
@@ -4419,7 +4466,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -4451,10 +4498,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -4772,7 +4816,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D839462D-4719-40BB-8925-C1B9F93734CF}">
-  <dimension ref="A1:H328"/>
+  <dimension ref="A1:H332"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="2"/>
@@ -4882,7 +4926,7 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>866</v>
+        <v>1189</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>453</v>
@@ -4898,9 +4942,11 @@
       <c r="C6" s="2">
         <v>7</v>
       </c>
-      <c r="D6" s="6"/>
+      <c r="D6" s="6">
+        <v>0.83333333333333337</v>
+      </c>
       <c r="E6" s="2" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>453</v>
@@ -4920,7 +4966,7 @@
         <v>0</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="F7" s="3"/>
       <c r="G7" s="1"/>
@@ -4941,8 +4987,8 @@
       <c r="D8" s="4">
         <v>0</v>
       </c>
-      <c r="E8" s="13" t="s">
-        <v>869</v>
+      <c r="E8" s="2" t="s">
+        <v>868</v>
       </c>
       <c r="F8" s="3"/>
       <c r="G8" s="1"/>
@@ -4959,8 +5005,8 @@
       </c>
       <c r="C9" s="3"/>
       <c r="D9" s="4"/>
-      <c r="E9" s="13" t="s">
-        <v>870</v>
+      <c r="E9" s="2" t="s">
+        <v>869</v>
       </c>
       <c r="F9" s="3">
         <v>1</v>
@@ -4983,8 +5029,8 @@
       <c r="D10" s="4">
         <v>0</v>
       </c>
-      <c r="E10" s="13" t="s">
-        <v>871</v>
+      <c r="E10" s="2" t="s">
+        <v>870</v>
       </c>
       <c r="F10" s="3"/>
       <c r="G10" s="1"/>
@@ -5005,8 +5051,8 @@
       <c r="D11" s="4">
         <v>0</v>
       </c>
-      <c r="E11" s="13" t="s">
-        <v>872</v>
+      <c r="E11" s="2" t="s">
+        <v>871</v>
       </c>
       <c r="F11" s="3"/>
       <c r="G11" s="1"/>
@@ -5023,8 +5069,8 @@
       </c>
       <c r="C12" s="3"/>
       <c r="D12" s="4"/>
-      <c r="E12" s="13" t="s">
-        <v>873</v>
+      <c r="E12" s="2" t="s">
+        <v>872</v>
       </c>
       <c r="F12" s="3">
         <v>1</v>
@@ -5045,8 +5091,8 @@
       </c>
       <c r="C13" s="3"/>
       <c r="D13" s="4"/>
-      <c r="E13" s="13" t="s">
-        <v>874</v>
+      <c r="E13" s="2" t="s">
+        <v>873</v>
       </c>
       <c r="F13" s="3">
         <v>1</v>
@@ -5071,8 +5117,8 @@
       <c r="D14" s="4">
         <v>0</v>
       </c>
-      <c r="E14" s="13" t="s">
-        <v>875</v>
+      <c r="E14" s="2" t="s">
+        <v>874</v>
       </c>
       <c r="F14" s="3"/>
       <c r="G14" s="1"/>
@@ -5093,8 +5139,8 @@
       <c r="D15" s="4">
         <v>0</v>
       </c>
-      <c r="E15" s="13" t="s">
-        <v>876</v>
+      <c r="E15" s="2" t="s">
+        <v>875</v>
       </c>
       <c r="F15" s="3"/>
       <c r="G15" s="1"/>
@@ -5115,8 +5161,8 @@
       <c r="D16" s="4">
         <v>0</v>
       </c>
-      <c r="E16" s="13" t="s">
-        <v>877</v>
+      <c r="E16" s="2" t="s">
+        <v>876</v>
       </c>
       <c r="F16" s="3"/>
       <c r="G16" s="1"/>
@@ -5137,13 +5183,13 @@
       <c r="D17" s="4">
         <v>0</v>
       </c>
-      <c r="E17" s="13" t="s">
-        <v>878</v>
+      <c r="E17" s="2" t="s">
+        <v>877</v>
       </c>
       <c r="F17" s="3"/>
       <c r="G17" s="1"/>
       <c r="H17" s="7" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -5159,8 +5205,8 @@
       <c r="D18" s="4">
         <v>0</v>
       </c>
-      <c r="E18" s="13" t="s">
-        <v>880</v>
+      <c r="E18" s="2" t="s">
+        <v>879</v>
       </c>
       <c r="F18" s="3"/>
       <c r="G18" s="1"/>
@@ -5181,8 +5227,8 @@
       <c r="D19" s="4">
         <v>0</v>
       </c>
-      <c r="E19" s="13" t="s">
-        <v>881</v>
+      <c r="E19" s="2" t="s">
+        <v>880</v>
       </c>
       <c r="F19" s="3"/>
       <c r="G19" s="1"/>
@@ -5203,8 +5249,8 @@
       <c r="D20" s="4">
         <v>0</v>
       </c>
-      <c r="E20" s="13" t="s">
-        <v>882</v>
+      <c r="E20" s="2" t="s">
+        <v>881</v>
       </c>
       <c r="F20" s="3"/>
       <c r="G20" s="1"/>
@@ -5225,8 +5271,8 @@
       <c r="D21" s="4">
         <v>0</v>
       </c>
-      <c r="E21" s="13" t="s">
-        <v>884</v>
+      <c r="E21" s="2" t="s">
+        <v>883</v>
       </c>
       <c r="F21" s="3"/>
       <c r="G21" s="1"/>
@@ -5247,8 +5293,8 @@
       <c r="D22" s="4">
         <v>0</v>
       </c>
-      <c r="E22" s="13" t="s">
-        <v>883</v>
+      <c r="E22" s="2" t="s">
+        <v>882</v>
       </c>
       <c r="F22" s="3"/>
       <c r="G22" s="1"/>
@@ -5269,8 +5315,8 @@
       <c r="D23" s="4">
         <v>0</v>
       </c>
-      <c r="E23" s="13" t="s">
-        <v>885</v>
+      <c r="E23" s="2" t="s">
+        <v>884</v>
       </c>
       <c r="F23" s="3"/>
       <c r="G23" s="1"/>
@@ -5287,8 +5333,8 @@
       </c>
       <c r="C24" s="3"/>
       <c r="D24" s="4"/>
-      <c r="E24" s="13" t="s">
-        <v>886</v>
+      <c r="E24" s="2" t="s">
+        <v>885</v>
       </c>
       <c r="F24" s="3">
         <v>1</v>
@@ -5311,8 +5357,8 @@
       <c r="D25" s="4">
         <v>0</v>
       </c>
-      <c r="E25" s="13" t="s">
-        <v>887</v>
+      <c r="E25" s="2" t="s">
+        <v>886</v>
       </c>
       <c r="F25" s="3"/>
       <c r="G25" s="1"/>
@@ -5333,8 +5379,8 @@
       <c r="D26" s="4">
         <v>0</v>
       </c>
-      <c r="E26" s="13" t="s">
-        <v>888</v>
+      <c r="E26" s="2" t="s">
+        <v>887</v>
       </c>
       <c r="F26" s="3"/>
       <c r="G26" s="1"/>
@@ -5375,8 +5421,8 @@
       <c r="D28" s="6">
         <v>0</v>
       </c>
-      <c r="E28" s="13" t="s">
-        <v>889</v>
+      <c r="E28" s="2" t="s">
+        <v>888</v>
       </c>
       <c r="F28" s="3"/>
       <c r="H28" s="1" t="s">
@@ -5396,8 +5442,8 @@
       <c r="D29" s="6">
         <v>0</v>
       </c>
-      <c r="E29" s="13" t="s">
-        <v>890</v>
+      <c r="E29" s="2" t="s">
+        <v>889</v>
       </c>
       <c r="F29" s="3"/>
       <c r="H29" s="1" t="s">
@@ -5417,8 +5463,8 @@
       <c r="D30" s="4">
         <v>0</v>
       </c>
-      <c r="E30" s="13" t="s">
-        <v>891</v>
+      <c r="E30" s="2" t="s">
+        <v>890</v>
       </c>
       <c r="F30" s="3"/>
       <c r="G30" s="1"/>
@@ -5439,8 +5485,8 @@
       <c r="D31" s="4">
         <v>0</v>
       </c>
-      <c r="E31" s="13" t="s">
-        <v>892</v>
+      <c r="E31" s="2" t="s">
+        <v>891</v>
       </c>
       <c r="F31" s="3"/>
       <c r="G31" s="1"/>
@@ -5455,8 +5501,8 @@
       <c r="B32" s="1" t="s">
         <v>567</v>
       </c>
-      <c r="E32" s="13" t="s">
-        <v>893</v>
+      <c r="E32" s="2" t="s">
+        <v>892</v>
       </c>
       <c r="F32" s="3">
         <v>1</v>
@@ -5478,8 +5524,8 @@
       <c r="D33" s="6">
         <v>0</v>
       </c>
-      <c r="E33" s="13" t="s">
-        <v>894</v>
+      <c r="E33" s="2" t="s">
+        <v>893</v>
       </c>
       <c r="H33" s="2" t="s">
         <v>574</v>
@@ -5492,8 +5538,8 @@
       <c r="B34" s="1" t="s">
         <v>557</v>
       </c>
-      <c r="E34" s="13" t="s">
-        <v>895</v>
+      <c r="E34" s="2" t="s">
+        <v>894</v>
       </c>
       <c r="F34" s="3">
         <v>1</v>
@@ -5509,8 +5555,8 @@
       <c r="B35" s="1" t="s">
         <v>554</v>
       </c>
-      <c r="E35" s="13" t="s">
-        <v>896</v>
+      <c r="E35" s="2" t="s">
+        <v>895</v>
       </c>
       <c r="F35" s="3">
         <v>1</v>
@@ -5526,8 +5572,8 @@
       <c r="B36" s="1" t="s">
         <v>562</v>
       </c>
-      <c r="E36" s="13" t="s">
-        <v>897</v>
+      <c r="E36" s="2" t="s">
+        <v>896</v>
       </c>
       <c r="F36" s="3">
         <v>1</v>
@@ -5543,8 +5589,8 @@
       <c r="B37" s="1" t="s">
         <v>573</v>
       </c>
-      <c r="E37" s="13" t="s">
-        <v>898</v>
+      <c r="E37" s="2" t="s">
+        <v>897</v>
       </c>
       <c r="F37" s="3">
         <v>1</v>
@@ -5560,8 +5606,8 @@
       <c r="B38" s="1" t="s">
         <v>570</v>
       </c>
-      <c r="E38" s="13" t="s">
-        <v>899</v>
+      <c r="E38" s="2" t="s">
+        <v>898</v>
       </c>
       <c r="F38" s="3">
         <v>1</v>
@@ -5577,8 +5623,8 @@
       <c r="B39" s="1" t="s">
         <v>560</v>
       </c>
-      <c r="E39" s="13" t="s">
-        <v>900</v>
+      <c r="E39" s="2" t="s">
+        <v>899</v>
       </c>
       <c r="F39" s="3">
         <v>1</v>
@@ -5594,8 +5640,8 @@
       <c r="B40" s="1" t="s">
         <v>780</v>
       </c>
-      <c r="E40" s="13" t="s">
-        <v>901</v>
+      <c r="E40" s="2" t="s">
+        <v>900</v>
       </c>
       <c r="F40" s="2">
         <v>1</v>
@@ -5617,8 +5663,8 @@
       <c r="D41" s="4">
         <v>0</v>
       </c>
-      <c r="E41" s="13" t="s">
-        <v>902</v>
+      <c r="E41" s="2" t="s">
+        <v>901</v>
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="1"/>
@@ -5633,8 +5679,8 @@
       <c r="B42" s="1" t="s">
         <v>781</v>
       </c>
-      <c r="E42" s="13" t="s">
-        <v>903</v>
+      <c r="E42" s="2" t="s">
+        <v>902</v>
       </c>
       <c r="F42" s="2">
         <v>1</v>
@@ -5650,8 +5696,8 @@
       <c r="B43" s="1" t="s">
         <v>782</v>
       </c>
-      <c r="E43" s="13" t="s">
-        <v>904</v>
+      <c r="E43" s="2" t="s">
+        <v>903</v>
       </c>
       <c r="F43" s="2">
         <v>1</v>
@@ -5667,8 +5713,8 @@
       <c r="B44" s="1" t="s">
         <v>497</v>
       </c>
-      <c r="E44" s="13" t="s">
-        <v>905</v>
+      <c r="E44" s="2" t="s">
+        <v>904</v>
       </c>
       <c r="F44" s="3">
         <v>1</v>
@@ -5684,8 +5730,8 @@
       <c r="B45" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="E45" s="13" t="s">
-        <v>906</v>
+      <c r="E45" s="2" t="s">
+        <v>905</v>
       </c>
       <c r="F45" s="3">
         <v>1</v>
@@ -5701,8 +5747,8 @@
       <c r="B46" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="E46" s="13" t="s">
-        <v>907</v>
+      <c r="E46" s="2" t="s">
+        <v>906</v>
       </c>
       <c r="F46" s="3">
         <v>1</v>
@@ -5721,8 +5767,8 @@
       <c r="D47" s="4">
         <v>0</v>
       </c>
-      <c r="E47" s="13" t="s">
-        <v>908</v>
+      <c r="E47" s="2" t="s">
+        <v>907</v>
       </c>
       <c r="F47" s="3"/>
       <c r="G47" s="1"/>
@@ -5739,8 +5785,8 @@
       </c>
       <c r="C48" s="3"/>
       <c r="D48" s="4"/>
-      <c r="E48" s="13" t="s">
-        <v>909</v>
+      <c r="E48" s="2" t="s">
+        <v>908</v>
       </c>
       <c r="F48" s="3">
         <v>1</v>
@@ -5763,8 +5809,8 @@
       <c r="D49" s="4">
         <v>0</v>
       </c>
-      <c r="E49" s="13" t="s">
-        <v>910</v>
+      <c r="E49" s="2" t="s">
+        <v>909</v>
       </c>
       <c r="F49" s="3"/>
       <c r="G49" s="1"/>
@@ -5785,8 +5831,8 @@
       <c r="D50" s="4">
         <v>0</v>
       </c>
-      <c r="E50" s="13" t="s">
-        <v>911</v>
+      <c r="E50" s="2" t="s">
+        <v>910</v>
       </c>
       <c r="F50" s="3"/>
       <c r="G50" s="1"/>
@@ -5807,8 +5853,8 @@
       <c r="D51" s="4">
         <v>0</v>
       </c>
-      <c r="E51" s="13" t="s">
-        <v>912</v>
+      <c r="E51" s="2" t="s">
+        <v>911</v>
       </c>
       <c r="F51" s="3"/>
       <c r="G51" s="1"/>
@@ -5825,8 +5871,8 @@
       </c>
       <c r="C52" s="3"/>
       <c r="D52" s="4"/>
-      <c r="E52" s="13" t="s">
-        <v>913</v>
+      <c r="E52" s="2" t="s">
+        <v>912</v>
       </c>
       <c r="F52" s="3">
         <v>1</v>
@@ -5845,8 +5891,8 @@
       </c>
       <c r="C53" s="3"/>
       <c r="D53" s="4"/>
-      <c r="E53" s="13" t="s">
-        <v>918</v>
+      <c r="E53" s="2" t="s">
+        <v>917</v>
       </c>
       <c r="F53" s="3">
         <v>1</v>
@@ -5869,8 +5915,8 @@
       <c r="D54" s="4">
         <v>0</v>
       </c>
-      <c r="E54" s="13" t="s">
-        <v>919</v>
+      <c r="E54" s="2" t="s">
+        <v>918</v>
       </c>
       <c r="F54" s="3"/>
       <c r="G54" s="1"/>
@@ -5891,8 +5937,8 @@
       <c r="D55" s="4">
         <v>0</v>
       </c>
-      <c r="E55" s="13" t="s">
-        <v>914</v>
+      <c r="E55" s="2" t="s">
+        <v>913</v>
       </c>
       <c r="F55" s="3"/>
       <c r="G55" s="1"/>
@@ -5913,8 +5959,8 @@
       <c r="D56" s="4">
         <v>0</v>
       </c>
-      <c r="E56" s="13" t="s">
-        <v>915</v>
+      <c r="E56" s="2" t="s">
+        <v>914</v>
       </c>
       <c r="F56" s="3"/>
       <c r="G56" s="1"/>
@@ -5935,8 +5981,8 @@
       <c r="D57" s="4">
         <v>0.95833333333333337</v>
       </c>
-      <c r="E57" s="13" t="s">
-        <v>916</v>
+      <c r="E57" s="2" t="s">
+        <v>915</v>
       </c>
       <c r="F57" s="3"/>
       <c r="G57" s="1"/>
@@ -5957,8 +6003,8 @@
       <c r="D58" s="4">
         <v>0.97916666666666663</v>
       </c>
-      <c r="E58" s="13" t="s">
-        <v>917</v>
+      <c r="E58" s="2" t="s">
+        <v>916</v>
       </c>
       <c r="F58" s="3"/>
       <c r="G58" s="1"/>
@@ -5979,8 +6025,8 @@
       <c r="D59" s="4">
         <v>0</v>
       </c>
-      <c r="E59" s="13" t="s">
-        <v>920</v>
+      <c r="E59" s="2" t="s">
+        <v>919</v>
       </c>
       <c r="F59" s="3"/>
       <c r="G59" s="1"/>
@@ -6001,8 +6047,8 @@
       <c r="D60" s="5">
         <v>0</v>
       </c>
-      <c r="E60" s="13" t="s">
-        <v>921</v>
+      <c r="E60" s="2" t="s">
+        <v>920</v>
       </c>
       <c r="F60" s="1"/>
       <c r="G60" s="1"/>
@@ -6017,8 +6063,8 @@
       <c r="B61" s="1" t="s">
         <v>762</v>
       </c>
-      <c r="E61" s="13" t="s">
-        <v>922</v>
+      <c r="E61" s="2" t="s">
+        <v>921</v>
       </c>
       <c r="F61" s="2">
         <v>1</v>
@@ -6036,8 +6082,8 @@
       </c>
       <c r="C62" s="1"/>
       <c r="D62" s="1"/>
-      <c r="E62" s="13" t="s">
-        <v>923</v>
+      <c r="E62" s="2" t="s">
+        <v>922</v>
       </c>
       <c r="F62" s="3">
         <v>1</v>
@@ -6056,8 +6102,8 @@
       <c r="B63" s="1" t="s">
         <v>457</v>
       </c>
-      <c r="E63" s="13" t="s">
-        <v>924</v>
+      <c r="E63" s="2" t="s">
+        <v>923</v>
       </c>
       <c r="F63" s="2">
         <v>1</v>
@@ -6070,8 +6116,8 @@
       <c r="B64" s="1" t="s">
         <v>458</v>
       </c>
-      <c r="E64" s="13" t="s">
-        <v>925</v>
+      <c r="E64" s="2" t="s">
+        <v>924</v>
       </c>
       <c r="F64" s="3">
         <v>1</v>
@@ -6089,8 +6135,8 @@
       </c>
       <c r="C65" s="3"/>
       <c r="D65" s="6"/>
-      <c r="E65" s="13" t="s">
-        <v>926</v>
+      <c r="E65" s="2" t="s">
+        <v>925</v>
       </c>
       <c r="F65" s="3">
         <v>1</v>
@@ -6115,8 +6161,8 @@
       <c r="D66" s="4">
         <v>0.875</v>
       </c>
-      <c r="E66" s="13" t="s">
-        <v>927</v>
+      <c r="E66" s="2" t="s">
+        <v>926</v>
       </c>
       <c r="F66" s="3"/>
       <c r="G66" s="1"/>
@@ -6137,8 +6183,8 @@
       <c r="D67" s="6">
         <v>0</v>
       </c>
-      <c r="E67" s="13" t="s">
-        <v>928</v>
+      <c r="E67" s="2" t="s">
+        <v>927</v>
       </c>
       <c r="H67" s="2" t="s">
         <v>851</v>
@@ -6157,8 +6203,8 @@
       <c r="D68" s="5">
         <v>0</v>
       </c>
-      <c r="E68" s="13" t="s">
-        <v>929</v>
+      <c r="E68" s="2" t="s">
+        <v>928</v>
       </c>
       <c r="F68" s="3"/>
       <c r="G68" s="1"/>
@@ -6179,8 +6225,8 @@
       <c r="D69" s="5">
         <v>0</v>
       </c>
-      <c r="E69" s="13" t="s">
-        <v>930</v>
+      <c r="E69" s="2" t="s">
+        <v>929</v>
       </c>
       <c r="F69" s="3"/>
       <c r="G69" s="1"/>
@@ -6197,8 +6243,8 @@
       </c>
       <c r="C70" s="3"/>
       <c r="D70" s="5"/>
-      <c r="E70" s="13" t="s">
-        <v>931</v>
+      <c r="E70" s="2" t="s">
+        <v>930</v>
       </c>
       <c r="F70" s="3">
         <v>1</v>
@@ -6221,8 +6267,8 @@
       <c r="D71" s="5">
         <v>0</v>
       </c>
-      <c r="E71" s="13" t="s">
-        <v>932</v>
+      <c r="E71" s="2" t="s">
+        <v>931</v>
       </c>
       <c r="F71" s="3"/>
       <c r="G71" s="1"/>
@@ -6243,8 +6289,8 @@
       <c r="D72" s="4">
         <v>0</v>
       </c>
-      <c r="E72" s="13" t="s">
-        <v>933</v>
+      <c r="E72" s="2" t="s">
+        <v>932</v>
       </c>
       <c r="F72" s="3"/>
       <c r="G72" s="1"/>
@@ -6265,8 +6311,8 @@
       <c r="D73" s="4">
         <v>0.91666666666666663</v>
       </c>
-      <c r="E73" s="13" t="s">
-        <v>934</v>
+      <c r="E73" s="2" t="s">
+        <v>933</v>
       </c>
       <c r="F73" s="3"/>
       <c r="G73" s="1"/>
@@ -6287,8 +6333,8 @@
       <c r="D74" s="4">
         <v>0</v>
       </c>
-      <c r="E74" s="13" t="s">
-        <v>935</v>
+      <c r="E74" s="2" t="s">
+        <v>934</v>
       </c>
       <c r="F74" s="3"/>
       <c r="G74" s="1"/>
@@ -6309,8 +6355,8 @@
       <c r="D75" s="4">
         <v>0</v>
       </c>
-      <c r="E75" s="13" t="s">
-        <v>936</v>
+      <c r="E75" s="2" t="s">
+        <v>935</v>
       </c>
       <c r="F75" s="3"/>
       <c r="G75" s="1"/>
@@ -6331,8 +6377,8 @@
       <c r="D76" s="4">
         <v>0</v>
       </c>
-      <c r="E76" s="13" t="s">
-        <v>937</v>
+      <c r="E76" s="2" t="s">
+        <v>936</v>
       </c>
       <c r="F76" s="3"/>
       <c r="H76" s="1" t="s">
@@ -6348,8 +6394,8 @@
       </c>
       <c r="C77" s="3"/>
       <c r="D77" s="4"/>
-      <c r="E77" s="13" t="s">
-        <v>938</v>
+      <c r="E77" s="2" t="s">
+        <v>937</v>
       </c>
       <c r="F77" s="3">
         <v>1</v>
@@ -6367,8 +6413,8 @@
       </c>
       <c r="C78" s="3"/>
       <c r="D78" s="4"/>
-      <c r="E78" s="13" t="s">
-        <v>939</v>
+      <c r="E78" s="2" t="s">
+        <v>938</v>
       </c>
       <c r="F78" s="3">
         <v>1</v>
@@ -6386,8 +6432,8 @@
       </c>
       <c r="C79" s="3"/>
       <c r="D79" s="4"/>
-      <c r="E79" s="13" t="s">
-        <v>940</v>
+      <c r="E79" s="2" t="s">
+        <v>939</v>
       </c>
       <c r="F79" s="3">
         <v>1</v>
@@ -6409,8 +6455,8 @@
       <c r="D80" s="4">
         <v>0</v>
       </c>
-      <c r="E80" s="13" t="s">
-        <v>941</v>
+      <c r="E80" s="2" t="s">
+        <v>940</v>
       </c>
       <c r="F80" s="3"/>
       <c r="H80" s="1" t="s">
@@ -6430,8 +6476,8 @@
       <c r="D81" s="4">
         <v>0</v>
       </c>
-      <c r="E81" s="13" t="s">
-        <v>942</v>
+      <c r="E81" s="2" t="s">
+        <v>941</v>
       </c>
       <c r="F81" s="3"/>
       <c r="H81" s="1" t="s">
@@ -6447,8 +6493,8 @@
       </c>
       <c r="C82" s="3"/>
       <c r="D82" s="4"/>
-      <c r="E82" s="13" t="s">
-        <v>943</v>
+      <c r="E82" s="2" t="s">
+        <v>942</v>
       </c>
       <c r="F82" s="3">
         <v>1</v>
@@ -6466,8 +6512,8 @@
       </c>
       <c r="C83" s="3"/>
       <c r="D83" s="4"/>
-      <c r="E83" s="13" t="s">
-        <v>944</v>
+      <c r="E83" s="2" t="s">
+        <v>943</v>
       </c>
       <c r="F83" s="3">
         <v>1</v>
@@ -6485,8 +6531,8 @@
       </c>
       <c r="C84" s="3"/>
       <c r="D84" s="4"/>
-      <c r="E84" s="13" t="s">
-        <v>945</v>
+      <c r="E84" s="2" t="s">
+        <v>944</v>
       </c>
       <c r="F84" s="3">
         <v>1</v>
@@ -6508,8 +6554,8 @@
       <c r="D85" s="4">
         <v>0</v>
       </c>
-      <c r="E85" s="13" t="s">
-        <v>946</v>
+      <c r="E85" s="2" t="s">
+        <v>945</v>
       </c>
       <c r="F85" s="3"/>
       <c r="H85" s="1" t="s">
@@ -6525,8 +6571,8 @@
       </c>
       <c r="C86" s="3"/>
       <c r="D86" s="4"/>
-      <c r="E86" s="13" t="s">
-        <v>947</v>
+      <c r="E86" s="2" t="s">
+        <v>946</v>
       </c>
       <c r="F86" s="3">
         <v>1</v>
@@ -6548,8 +6594,8 @@
       <c r="D87" s="4">
         <v>0</v>
       </c>
-      <c r="E87" s="13" t="s">
-        <v>948</v>
+      <c r="E87" s="2" t="s">
+        <v>947</v>
       </c>
       <c r="F87" s="3"/>
       <c r="H87" s="1" t="s">
@@ -6569,8 +6615,8 @@
       <c r="D88" s="4">
         <v>0</v>
       </c>
-      <c r="E88" s="13" t="s">
-        <v>949</v>
+      <c r="E88" s="2" t="s">
+        <v>948</v>
       </c>
       <c r="F88" s="3"/>
       <c r="H88" s="1" t="s">
@@ -6590,8 +6636,8 @@
       <c r="D89" s="4">
         <v>0</v>
       </c>
-      <c r="E89" s="13" t="s">
-        <v>950</v>
+      <c r="E89" s="2" t="s">
+        <v>949</v>
       </c>
       <c r="F89" s="3"/>
       <c r="H89" s="1" t="s">
@@ -6611,8 +6657,8 @@
       <c r="D90" s="4">
         <v>0</v>
       </c>
-      <c r="E90" s="13" t="s">
-        <v>951</v>
+      <c r="E90" s="2" t="s">
+        <v>950</v>
       </c>
       <c r="F90" s="3"/>
       <c r="H90" s="1" t="s">
@@ -6628,8 +6674,8 @@
       </c>
       <c r="C91" s="3"/>
       <c r="D91" s="4"/>
-      <c r="E91" s="13" t="s">
-        <v>952</v>
+      <c r="E91" s="2" t="s">
+        <v>951</v>
       </c>
       <c r="F91" s="3">
         <v>1</v>
@@ -6647,8 +6693,8 @@
       </c>
       <c r="C92" s="3"/>
       <c r="D92" s="4"/>
-      <c r="E92" s="13" t="s">
-        <v>953</v>
+      <c r="E92" s="2" t="s">
+        <v>952</v>
       </c>
       <c r="F92" s="3">
         <v>1</v>
@@ -6666,8 +6712,8 @@
       </c>
       <c r="C93" s="3"/>
       <c r="D93" s="4"/>
-      <c r="E93" s="13" t="s">
-        <v>954</v>
+      <c r="E93" s="2" t="s">
+        <v>953</v>
       </c>
       <c r="F93" s="3">
         <v>1</v>
@@ -6685,8 +6731,8 @@
       </c>
       <c r="C94" s="3"/>
       <c r="D94" s="4"/>
-      <c r="E94" s="13" t="s">
-        <v>955</v>
+      <c r="E94" s="2" t="s">
+        <v>954</v>
       </c>
       <c r="F94" s="3">
         <v>1</v>
@@ -6704,8 +6750,8 @@
       </c>
       <c r="C95" s="3"/>
       <c r="D95" s="4"/>
-      <c r="E95" s="13" t="s">
-        <v>956</v>
+      <c r="E95" s="2" t="s">
+        <v>955</v>
       </c>
       <c r="F95" s="3">
         <v>1</v>
@@ -6727,8 +6773,8 @@
       <c r="D96" s="4">
         <v>0</v>
       </c>
-      <c r="E96" s="13" t="s">
-        <v>957</v>
+      <c r="E96" s="2" t="s">
+        <v>956</v>
       </c>
       <c r="F96" s="3"/>
       <c r="H96" s="1" t="s">
@@ -6744,8 +6790,8 @@
       </c>
       <c r="C97" s="3"/>
       <c r="D97" s="4"/>
-      <c r="E97" s="13" t="s">
-        <v>958</v>
+      <c r="E97" s="2" t="s">
+        <v>957</v>
       </c>
       <c r="F97" s="3">
         <v>1</v>
@@ -6761,8 +6807,8 @@
       <c r="B98" s="1" t="s">
         <v>587</v>
       </c>
-      <c r="E98" s="13" t="s">
-        <v>959</v>
+      <c r="E98" s="2" t="s">
+        <v>958</v>
       </c>
       <c r="F98" s="3">
         <v>1</v>
@@ -6784,8 +6830,8 @@
       <c r="D99" s="4">
         <v>0</v>
       </c>
-      <c r="E99" s="13" t="s">
-        <v>960</v>
+      <c r="E99" s="2" t="s">
+        <v>959</v>
       </c>
       <c r="F99" s="3"/>
       <c r="G99" s="1"/>
@@ -6806,8 +6852,8 @@
       <c r="D100" s="4">
         <v>0</v>
       </c>
-      <c r="E100" s="13" t="s">
-        <v>961</v>
+      <c r="E100" s="2" t="s">
+        <v>960</v>
       </c>
       <c r="F100" s="3"/>
       <c r="G100" s="1"/>
@@ -6828,8 +6874,8 @@
       <c r="D101" s="4">
         <v>0</v>
       </c>
-      <c r="E101" s="13" t="s">
-        <v>962</v>
+      <c r="E101" s="2" t="s">
+        <v>961</v>
       </c>
       <c r="F101" s="3"/>
       <c r="G101" s="1"/>
@@ -6850,8 +6896,8 @@
       <c r="D102" s="4">
         <v>0</v>
       </c>
-      <c r="E102" s="13" t="s">
-        <v>963</v>
+      <c r="E102" s="2" t="s">
+        <v>962</v>
       </c>
       <c r="F102" s="3"/>
       <c r="G102" s="1"/>
@@ -6872,8 +6918,8 @@
       <c r="D103" s="4">
         <v>0</v>
       </c>
-      <c r="E103" s="13" t="s">
-        <v>964</v>
+      <c r="E103" s="2" t="s">
+        <v>963</v>
       </c>
       <c r="F103" s="3"/>
       <c r="G103" s="1"/>
@@ -6894,8 +6940,8 @@
       <c r="D104" s="4">
         <v>0</v>
       </c>
-      <c r="E104" s="13" t="s">
-        <v>965</v>
+      <c r="E104" s="2" t="s">
+        <v>964</v>
       </c>
       <c r="F104" s="3"/>
       <c r="G104" s="1"/>
@@ -6916,8 +6962,8 @@
       <c r="D105" s="4">
         <v>0</v>
       </c>
-      <c r="E105" s="13" t="s">
-        <v>966</v>
+      <c r="E105" s="2" t="s">
+        <v>965</v>
       </c>
       <c r="F105" s="3"/>
       <c r="G105" s="1"/>
@@ -6932,8 +6978,8 @@
       <c r="B106" s="1" t="s">
         <v>532</v>
       </c>
-      <c r="E106" s="13" t="s">
-        <v>967</v>
+      <c r="E106" s="2" t="s">
+        <v>966</v>
       </c>
       <c r="F106" s="3">
         <v>1</v>
@@ -6949,8 +6995,8 @@
       <c r="B107" s="1" t="s">
         <v>504</v>
       </c>
-      <c r="E107" s="13" t="s">
-        <v>968</v>
+      <c r="E107" s="2" t="s">
+        <v>967</v>
       </c>
       <c r="F107" s="3">
         <v>1</v>
@@ -6966,8 +7012,8 @@
       <c r="B108" s="1" t="s">
         <v>519</v>
       </c>
-      <c r="E108" s="13" t="s">
-        <v>969</v>
+      <c r="E108" s="2" t="s">
+        <v>968</v>
       </c>
       <c r="F108" s="3">
         <v>1</v>
@@ -6983,8 +7029,8 @@
       <c r="B109" s="1" t="s">
         <v>521</v>
       </c>
-      <c r="E109" s="13" t="s">
-        <v>970</v>
+      <c r="E109" s="2" t="s">
+        <v>969</v>
       </c>
       <c r="F109" s="3">
         <v>1</v>
@@ -7000,8 +7046,8 @@
       <c r="B110" s="1" t="s">
         <v>516</v>
       </c>
-      <c r="E110" s="13" t="s">
-        <v>971</v>
+      <c r="E110" s="2" t="s">
+        <v>970</v>
       </c>
       <c r="F110" s="3">
         <v>1</v>
@@ -7017,8 +7063,8 @@
       <c r="B111" s="1" t="s">
         <v>525</v>
       </c>
-      <c r="E111" s="13" t="s">
-        <v>972</v>
+      <c r="E111" s="2" t="s">
+        <v>971</v>
       </c>
       <c r="F111" s="3">
         <v>1</v>
@@ -7034,8 +7080,8 @@
       <c r="B112" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="E112" s="13" t="s">
-        <v>973</v>
+      <c r="E112" s="2" t="s">
+        <v>972</v>
       </c>
       <c r="F112" s="3">
         <v>1</v>
@@ -7051,8 +7097,8 @@
       <c r="B113" s="1" t="s">
         <v>513</v>
       </c>
-      <c r="E113" s="13" t="s">
-        <v>974</v>
+      <c r="E113" s="2" t="s">
+        <v>973</v>
       </c>
       <c r="F113" s="3">
         <v>1</v>
@@ -7068,8 +7114,8 @@
       <c r="B114" s="1" t="s">
         <v>534</v>
       </c>
-      <c r="E114" s="13" t="s">
-        <v>975</v>
+      <c r="E114" s="2" t="s">
+        <v>974</v>
       </c>
       <c r="F114" s="3">
         <v>1</v>
@@ -7085,8 +7131,8 @@
       <c r="B115" s="1" t="s">
         <v>527</v>
       </c>
-      <c r="E115" s="13" t="s">
-        <v>976</v>
+      <c r="E115" s="2" t="s">
+        <v>975</v>
       </c>
       <c r="F115" s="3">
         <v>1</v>
@@ -7102,8 +7148,8 @@
       <c r="B116" s="1" t="s">
         <v>509</v>
       </c>
-      <c r="E116" s="13" t="s">
-        <v>977</v>
+      <c r="E116" s="2" t="s">
+        <v>976</v>
       </c>
       <c r="F116" s="3">
         <v>1</v>
@@ -7119,8 +7165,8 @@
       <c r="B117" s="1" t="s">
         <v>511</v>
       </c>
-      <c r="E117" s="13" t="s">
-        <v>978</v>
+      <c r="E117" s="2" t="s">
+        <v>977</v>
       </c>
       <c r="F117" s="3">
         <v>1</v>
@@ -7136,8 +7182,8 @@
       <c r="B118" s="1" t="s">
         <v>515</v>
       </c>
-      <c r="E118" s="13" t="s">
-        <v>979</v>
+      <c r="E118" s="2" t="s">
+        <v>978</v>
       </c>
       <c r="F118" s="3">
         <v>1</v>
@@ -7153,8 +7199,8 @@
       <c r="B119" s="1" t="s">
         <v>523</v>
       </c>
-      <c r="E119" s="13" t="s">
-        <v>980</v>
+      <c r="E119" s="2" t="s">
+        <v>979</v>
       </c>
       <c r="F119" s="3">
         <v>1</v>
@@ -7176,8 +7222,8 @@
       <c r="D120" s="4">
         <v>0</v>
       </c>
-      <c r="E120" s="13" t="s">
-        <v>981</v>
+      <c r="E120" s="2" t="s">
+        <v>980</v>
       </c>
       <c r="F120" s="3"/>
       <c r="G120" s="1"/>
@@ -7194,8 +7240,8 @@
       </c>
       <c r="C121" s="3"/>
       <c r="D121" s="4"/>
-      <c r="E121" s="13" t="s">
-        <v>982</v>
+      <c r="E121" s="2" t="s">
+        <v>981</v>
       </c>
       <c r="F121" s="3">
         <v>1</v>
@@ -7214,8 +7260,8 @@
       </c>
       <c r="C122" s="3"/>
       <c r="D122" s="4"/>
-      <c r="E122" s="13" t="s">
-        <v>983</v>
+      <c r="E122" s="2" t="s">
+        <v>982</v>
       </c>
       <c r="F122" s="3">
         <v>1</v>
@@ -7234,8 +7280,8 @@
       <c r="B123" s="1" t="s">
         <v>739</v>
       </c>
-      <c r="E123" s="13" t="s">
-        <v>1185</v>
+      <c r="E123" s="2" t="s">
+        <v>1183</v>
       </c>
       <c r="F123" s="2">
         <v>1</v>
@@ -7253,8 +7299,8 @@
       </c>
       <c r="C124" s="3"/>
       <c r="D124" s="4"/>
-      <c r="E124" s="13" t="s">
-        <v>984</v>
+      <c r="E124" s="2" t="s">
+        <v>983</v>
       </c>
       <c r="F124" s="3">
         <v>1</v>
@@ -7271,8 +7317,8 @@
       <c r="B125" s="1" t="s">
         <v>759</v>
       </c>
-      <c r="E125" s="13" t="s">
-        <v>985</v>
+      <c r="E125" s="2" t="s">
+        <v>984</v>
       </c>
       <c r="F125" s="2">
         <v>1</v>
@@ -7294,8 +7340,8 @@
       <c r="D126" s="4">
         <v>0</v>
       </c>
-      <c r="E126" s="13" t="s">
-        <v>986</v>
+      <c r="E126" s="2" t="s">
+        <v>985</v>
       </c>
       <c r="F126" s="3"/>
       <c r="G126" s="1"/>
@@ -7316,8 +7362,8 @@
       <c r="D127" s="4">
         <v>0.95833333333333337</v>
       </c>
-      <c r="E127" s="13" t="s">
-        <v>987</v>
+      <c r="E127" s="2" t="s">
+        <v>986</v>
       </c>
       <c r="F127" s="3"/>
       <c r="G127" s="1"/>
@@ -7334,8 +7380,8 @@
       </c>
       <c r="C128" s="1"/>
       <c r="D128" s="5"/>
-      <c r="E128" s="13" t="s">
-        <v>988</v>
+      <c r="E128" s="2" t="s">
+        <v>987</v>
       </c>
       <c r="F128" s="3">
         <v>1</v>
@@ -7352,8 +7398,8 @@
       <c r="B129" s="1" t="s">
         <v>578</v>
       </c>
-      <c r="E129" s="13" t="s">
-        <v>989</v>
+      <c r="E129" s="2" t="s">
+        <v>988</v>
       </c>
       <c r="F129" s="3">
         <v>1</v>
@@ -7375,8 +7421,8 @@
       <c r="D130" s="4">
         <v>0</v>
       </c>
-      <c r="E130" s="13" t="s">
-        <v>990</v>
+      <c r="E130" s="2" t="s">
+        <v>989</v>
       </c>
       <c r="F130" s="3"/>
       <c r="G130" s="1"/>
@@ -7393,8 +7439,8 @@
       </c>
       <c r="C131"/>
       <c r="D131" s="11"/>
-      <c r="E131" s="14" t="s">
-        <v>991</v>
+      <c r="E131" s="13" t="s">
+        <v>990</v>
       </c>
       <c r="F131" s="1">
         <v>1</v>
@@ -7411,8 +7457,8 @@
       <c r="B132" t="s">
         <v>612</v>
       </c>
-      <c r="E132" s="13" t="s">
-        <v>992</v>
+      <c r="E132" s="2" t="s">
+        <v>991</v>
       </c>
       <c r="F132" s="1">
         <v>1</v>
@@ -7428,8 +7474,8 @@
       <c r="B133" t="s">
         <v>614</v>
       </c>
-      <c r="E133" s="13" t="s">
-        <v>993</v>
+      <c r="E133" s="2" t="s">
+        <v>992</v>
       </c>
       <c r="F133" s="1">
         <v>1</v>
@@ -7445,8 +7491,8 @@
       <c r="B134" t="s">
         <v>616</v>
       </c>
-      <c r="E134" s="13" t="s">
-        <v>994</v>
+      <c r="E134" s="2" t="s">
+        <v>993</v>
       </c>
       <c r="F134" s="1">
         <v>1</v>
@@ -7462,8 +7508,8 @@
       <c r="B135" t="s">
         <v>618</v>
       </c>
-      <c r="E135" s="13" t="s">
-        <v>995</v>
+      <c r="E135" s="2" t="s">
+        <v>994</v>
       </c>
       <c r="F135" s="1">
         <v>1</v>
@@ -7479,8 +7525,8 @@
       <c r="B136" t="s">
         <v>620</v>
       </c>
-      <c r="E136" s="13" t="s">
-        <v>996</v>
+      <c r="E136" s="2" t="s">
+        <v>995</v>
       </c>
       <c r="F136" s="1">
         <v>1</v>
@@ -7502,8 +7548,8 @@
       <c r="D137" s="6">
         <v>0</v>
       </c>
-      <c r="E137" s="13" t="s">
-        <v>997</v>
+      <c r="E137" s="2" t="s">
+        <v>996</v>
       </c>
       <c r="F137" s="1"/>
       <c r="H137" t="s">
@@ -7517,8 +7563,8 @@
       <c r="B138" t="s">
         <v>624</v>
       </c>
-      <c r="E138" s="13" t="s">
-        <v>998</v>
+      <c r="E138" s="2" t="s">
+        <v>997</v>
       </c>
       <c r="F138" s="1">
         <v>1</v>
@@ -7540,8 +7586,8 @@
       <c r="D139" s="6">
         <v>0</v>
       </c>
-      <c r="E139" s="13" t="s">
-        <v>999</v>
+      <c r="E139" s="2" t="s">
+        <v>998</v>
       </c>
       <c r="F139" s="1"/>
       <c r="H139" t="s">
@@ -7555,8 +7601,8 @@
       <c r="B140" t="s">
         <v>628</v>
       </c>
-      <c r="E140" s="13" t="s">
-        <v>1000</v>
+      <c r="E140" s="2" t="s">
+        <v>999</v>
       </c>
       <c r="F140" s="1">
         <v>1</v>
@@ -7572,8 +7618,8 @@
       <c r="B141" t="s">
         <v>752</v>
       </c>
-      <c r="E141" s="13" t="s">
-        <v>1001</v>
+      <c r="E141" s="2" t="s">
+        <v>1000</v>
       </c>
       <c r="F141" s="1">
         <v>1</v>
@@ -7595,8 +7641,8 @@
       <c r="D142" s="4">
         <v>0.66666666666666663</v>
       </c>
-      <c r="E142" s="13" t="s">
-        <v>1002</v>
+      <c r="E142" s="2" t="s">
+        <v>1001</v>
       </c>
       <c r="F142" s="3"/>
       <c r="G142" s="1"/>
@@ -7617,8 +7663,8 @@
       <c r="D143" s="4">
         <v>0.70833333333333337</v>
       </c>
-      <c r="E143" s="13" t="s">
-        <v>1003</v>
+      <c r="E143" s="2" t="s">
+        <v>1002</v>
       </c>
       <c r="F143" s="3"/>
       <c r="G143" s="1"/>
@@ -7639,8 +7685,8 @@
       <c r="D144" s="4">
         <v>0.58333333333333337</v>
       </c>
-      <c r="E144" s="13" t="s">
-        <v>1004</v>
+      <c r="E144" s="2" t="s">
+        <v>1003</v>
       </c>
       <c r="F144" s="3"/>
       <c r="G144" s="1"/>
@@ -7661,8 +7707,8 @@
       <c r="D145" s="4">
         <v>0.75</v>
       </c>
-      <c r="E145" s="13" t="s">
-        <v>1005</v>
+      <c r="E145" s="2" t="s">
+        <v>1004</v>
       </c>
       <c r="F145" s="3"/>
       <c r="G145" s="1"/>
@@ -7683,8 +7729,8 @@
       <c r="D146" s="4">
         <v>0.79166666666666663</v>
       </c>
-      <c r="E146" s="13" t="s">
-        <v>1006</v>
+      <c r="E146" s="2" t="s">
+        <v>1005</v>
       </c>
       <c r="F146" s="3"/>
       <c r="G146" s="1"/>
@@ -7705,8 +7751,8 @@
       <c r="D147" s="4">
         <v>0</v>
       </c>
-      <c r="E147" s="13" t="s">
-        <v>1007</v>
+      <c r="E147" s="2" t="s">
+        <v>1006</v>
       </c>
       <c r="F147" s="3"/>
       <c r="G147" s="1"/>
@@ -7727,8 +7773,8 @@
       <c r="D148" s="4">
         <v>0.83333333333333337</v>
       </c>
-      <c r="E148" s="13" t="s">
-        <v>1008</v>
+      <c r="E148" s="2" t="s">
+        <v>1007</v>
       </c>
       <c r="F148" s="3"/>
       <c r="G148" s="1"/>
@@ -7749,8 +7795,8 @@
       <c r="D149" s="4">
         <v>0.875</v>
       </c>
-      <c r="E149" s="13" t="s">
-        <v>1009</v>
+      <c r="E149" s="2" t="s">
+        <v>1008</v>
       </c>
       <c r="F149" s="3"/>
       <c r="G149" s="1"/>
@@ -7771,8 +7817,8 @@
       <c r="D150" s="4">
         <v>0.54166666666666663</v>
       </c>
-      <c r="E150" s="13" t="s">
-        <v>1010</v>
+      <c r="E150" s="2" t="s">
+        <v>1009</v>
       </c>
       <c r="F150" s="3"/>
       <c r="G150" s="1"/>
@@ -7793,8 +7839,8 @@
       <c r="D151" s="4">
         <v>0.625</v>
       </c>
-      <c r="E151" s="13" t="s">
-        <v>1011</v>
+      <c r="E151" s="2" t="s">
+        <v>1010</v>
       </c>
       <c r="F151" s="3"/>
       <c r="G151" s="1"/>
@@ -7815,8 +7861,8 @@
       <c r="D152" s="4">
         <v>0</v>
       </c>
-      <c r="E152" s="13" t="s">
-        <v>1012</v>
+      <c r="E152" s="2" t="s">
+        <v>1011</v>
       </c>
       <c r="F152" s="3"/>
       <c r="G152" s="1"/>
@@ -7837,8 +7883,8 @@
       <c r="D153" s="4">
         <v>0</v>
       </c>
-      <c r="E153" s="13" t="s">
-        <v>1013</v>
+      <c r="E153" s="2" t="s">
+        <v>1012</v>
       </c>
       <c r="F153" s="3"/>
       <c r="G153" s="1"/>
@@ -7859,8 +7905,8 @@
       <c r="D154" s="4">
         <v>0</v>
       </c>
-      <c r="E154" s="13" t="s">
-        <v>1014</v>
+      <c r="E154" s="2" t="s">
+        <v>1013</v>
       </c>
       <c r="F154" s="3"/>
       <c r="G154" s="1"/>
@@ -7881,8 +7927,8 @@
       <c r="D155" s="4">
         <v>0</v>
       </c>
-      <c r="E155" s="13" t="s">
-        <v>1015</v>
+      <c r="E155" s="2" t="s">
+        <v>1014</v>
       </c>
       <c r="F155" s="3"/>
       <c r="G155" s="1"/>
@@ -7903,8 +7949,8 @@
       <c r="D156" s="4">
         <v>0</v>
       </c>
-      <c r="E156" s="13" t="s">
-        <v>1016</v>
+      <c r="E156" s="2" t="s">
+        <v>1015</v>
       </c>
       <c r="F156" s="3"/>
       <c r="G156" s="1"/>
@@ -7925,8 +7971,8 @@
       <c r="D157" s="4">
         <v>0</v>
       </c>
-      <c r="E157" s="13" t="s">
-        <v>1017</v>
+      <c r="E157" s="2" t="s">
+        <v>1016</v>
       </c>
       <c r="F157" s="3"/>
       <c r="G157" s="1"/>
@@ -7947,8 +7993,8 @@
       <c r="D158" s="4">
         <v>0</v>
       </c>
-      <c r="E158" s="13" t="s">
-        <v>1018</v>
+      <c r="E158" s="2" t="s">
+        <v>1017</v>
       </c>
       <c r="F158"/>
       <c r="G158"/>
@@ -7957,76 +8003,82 @@
       </c>
     </row>
     <row r="159" spans="1:8">
-      <c r="A159" t="s">
-        <v>634</v>
-      </c>
-      <c r="B159" t="s">
-        <v>635</v>
-      </c>
-      <c r="C159"/>
-      <c r="D159"/>
-      <c r="E159" s="13" t="s">
-        <v>1019</v>
-      </c>
-      <c r="F159">
-        <v>1</v>
-      </c>
+      <c r="A159" s="11" t="s">
+        <v>1190</v>
+      </c>
+      <c r="B159" s="11" t="s">
+        <v>1191</v>
+      </c>
+      <c r="C159" s="3">
+        <v>14</v>
+      </c>
+      <c r="D159" s="4">
+        <v>0</v>
+      </c>
+      <c r="E159" s="2" t="s">
+        <v>1192</v>
+      </c>
+      <c r="F159"/>
       <c r="G159"/>
       <c r="H159" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
     </row>
     <row r="160" spans="1:8">
-      <c r="A160" t="s">
-        <v>636</v>
-      </c>
-      <c r="B160" t="s">
-        <v>637</v>
-      </c>
-      <c r="C160"/>
-      <c r="D160"/>
-      <c r="E160" s="13" t="s">
-        <v>1020</v>
-      </c>
-      <c r="F160">
-        <v>1</v>
-      </c>
+      <c r="A160" s="11" t="s">
+        <v>1193</v>
+      </c>
+      <c r="B160" s="11" t="s">
+        <v>1194</v>
+      </c>
+      <c r="C160" s="3">
+        <v>14</v>
+      </c>
+      <c r="D160" s="4">
+        <v>0</v>
+      </c>
+      <c r="E160" s="2" t="s">
+        <v>1197</v>
+      </c>
+      <c r="F160"/>
       <c r="G160"/>
       <c r="H160" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
     </row>
     <row r="161" spans="1:8">
-      <c r="A161" t="s">
-        <v>746</v>
-      </c>
-      <c r="B161" t="s">
-        <v>1022</v>
-      </c>
-      <c r="C161"/>
-      <c r="D161"/>
-      <c r="E161" s="13" t="s">
-        <v>1021</v>
-      </c>
-      <c r="F161">
-        <v>1</v>
-      </c>
+      <c r="A161" s="11" t="s">
+        <v>1195</v>
+      </c>
+      <c r="B161" s="11" t="s">
+        <v>1196</v>
+      </c>
+      <c r="C161" s="3">
+        <v>14</v>
+      </c>
+      <c r="D161" s="4">
+        <v>0</v>
+      </c>
+      <c r="E161" s="2" t="s">
+        <v>1197</v>
+      </c>
+      <c r="F161"/>
       <c r="G161"/>
       <c r="H161" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
     </row>
     <row r="162" spans="1:8">
       <c r="A162" t="s">
-        <v>638</v>
+        <v>634</v>
       </c>
       <c r="B162" t="s">
-        <v>639</v>
+        <v>635</v>
       </c>
       <c r="C162"/>
       <c r="D162"/>
-      <c r="E162" s="13" t="s">
-        <v>1023</v>
+      <c r="E162" s="2" t="s">
+        <v>1018</v>
       </c>
       <c r="F162">
         <v>1</v>
@@ -8038,15 +8090,15 @@
     </row>
     <row r="163" spans="1:8">
       <c r="A163" t="s">
-        <v>640</v>
+        <v>636</v>
       </c>
       <c r="B163" t="s">
-        <v>641</v>
+        <v>637</v>
       </c>
       <c r="C163"/>
       <c r="D163"/>
-      <c r="E163" s="13" t="s">
-        <v>1024</v>
+      <c r="E163" s="2" t="s">
+        <v>1019</v>
       </c>
       <c r="F163">
         <v>1</v>
@@ -8058,15 +8110,15 @@
     </row>
     <row r="164" spans="1:8">
       <c r="A164" t="s">
-        <v>642</v>
+        <v>746</v>
       </c>
       <c r="B164" t="s">
-        <v>643</v>
+        <v>1021</v>
       </c>
       <c r="C164"/>
       <c r="D164"/>
-      <c r="E164" s="13" t="s">
-        <v>1025</v>
+      <c r="E164" s="2" t="s">
+        <v>1020</v>
       </c>
       <c r="F164">
         <v>1</v>
@@ -8077,33 +8129,36 @@
       </c>
     </row>
     <row r="165" spans="1:8">
-      <c r="A165" s="2" t="s">
-        <v>849</v>
-      </c>
-      <c r="B165" s="1" t="s">
-        <v>850</v>
-      </c>
-      <c r="E165" s="13" t="s">
-        <v>1026</v>
-      </c>
-      <c r="F165" s="2">
-        <v>1</v>
-      </c>
+      <c r="A165" t="s">
+        <v>638</v>
+      </c>
+      <c r="B165" t="s">
+        <v>639</v>
+      </c>
+      <c r="C165"/>
+      <c r="D165"/>
+      <c r="E165" s="2" t="s">
+        <v>1022</v>
+      </c>
+      <c r="F165">
+        <v>1</v>
+      </c>
+      <c r="G165"/>
       <c r="H165" t="s">
         <v>704</v>
       </c>
     </row>
     <row r="166" spans="1:8">
       <c r="A166" t="s">
-        <v>644</v>
+        <v>640</v>
       </c>
       <c r="B166" t="s">
-        <v>645</v>
+        <v>641</v>
       </c>
       <c r="C166"/>
       <c r="D166"/>
-      <c r="E166" s="13" t="s">
-        <v>1027</v>
+      <c r="E166" s="2" t="s">
+        <v>1023</v>
       </c>
       <c r="F166">
         <v>1</v>
@@ -8115,15 +8170,15 @@
     </row>
     <row r="167" spans="1:8">
       <c r="A167" t="s">
-        <v>646</v>
+        <v>642</v>
       </c>
       <c r="B167" t="s">
-        <v>647</v>
+        <v>643</v>
       </c>
       <c r="C167"/>
       <c r="D167"/>
-      <c r="E167" s="13" t="s">
-        <v>1028</v>
+      <c r="E167" s="2" t="s">
+        <v>1024</v>
       </c>
       <c r="F167">
         <v>1</v>
@@ -8134,36 +8189,33 @@
       </c>
     </row>
     <row r="168" spans="1:8">
-      <c r="A168" t="s">
-        <v>648</v>
-      </c>
-      <c r="B168" t="s">
-        <v>649</v>
-      </c>
-      <c r="C168"/>
-      <c r="D168"/>
-      <c r="E168" s="13" t="s">
-        <v>1029</v>
-      </c>
-      <c r="F168">
-        <v>1</v>
-      </c>
-      <c r="G168"/>
+      <c r="A168" s="2" t="s">
+        <v>849</v>
+      </c>
+      <c r="B168" s="1" t="s">
+        <v>850</v>
+      </c>
+      <c r="E168" s="2" t="s">
+        <v>1025</v>
+      </c>
+      <c r="F168" s="2">
+        <v>1</v>
+      </c>
       <c r="H168" t="s">
         <v>704</v>
       </c>
     </row>
     <row r="169" spans="1:8">
       <c r="A169" t="s">
-        <v>650</v>
+        <v>644</v>
       </c>
       <c r="B169" t="s">
-        <v>651</v>
+        <v>645</v>
       </c>
       <c r="C169"/>
       <c r="D169"/>
-      <c r="E169" s="13" t="s">
-        <v>1030</v>
+      <c r="E169" s="2" t="s">
+        <v>1026</v>
       </c>
       <c r="F169">
         <v>1</v>
@@ -8175,15 +8227,15 @@
     </row>
     <row r="170" spans="1:8">
       <c r="A170" t="s">
-        <v>652</v>
+        <v>646</v>
       </c>
       <c r="B170" t="s">
-        <v>653</v>
+        <v>647</v>
       </c>
       <c r="C170"/>
       <c r="D170"/>
-      <c r="E170" s="13" t="s">
-        <v>1031</v>
+      <c r="E170" s="2" t="s">
+        <v>1027</v>
       </c>
       <c r="F170">
         <v>1</v>
@@ -8195,15 +8247,15 @@
     </row>
     <row r="171" spans="1:8">
       <c r="A171" t="s">
-        <v>654</v>
+        <v>648</v>
       </c>
       <c r="B171" t="s">
-        <v>655</v>
+        <v>649</v>
       </c>
       <c r="C171"/>
       <c r="D171"/>
-      <c r="E171" s="13" t="s">
-        <v>1032</v>
+      <c r="E171" s="2" t="s">
+        <v>1028</v>
       </c>
       <c r="F171">
         <v>1</v>
@@ -8215,15 +8267,15 @@
     </row>
     <row r="172" spans="1:8">
       <c r="A172" t="s">
-        <v>656</v>
-      </c>
-      <c r="B172" s="12" t="s">
-        <v>744</v>
+        <v>650</v>
+      </c>
+      <c r="B172" t="s">
+        <v>651</v>
       </c>
       <c r="C172"/>
       <c r="D172"/>
-      <c r="E172" s="13" t="s">
-        <v>1033</v>
+      <c r="E172" s="2" t="s">
+        <v>1029</v>
       </c>
       <c r="F172">
         <v>1</v>
@@ -8235,35 +8287,35 @@
     </row>
     <row r="173" spans="1:8">
       <c r="A173" t="s">
-        <v>657</v>
+        <v>652</v>
       </c>
       <c r="B173" t="s">
-        <v>658</v>
+        <v>653</v>
       </c>
       <c r="C173"/>
       <c r="D173"/>
-      <c r="E173" s="13" t="s">
-        <v>1034</v>
+      <c r="E173" s="2" t="s">
+        <v>1030</v>
       </c>
       <c r="F173">
         <v>1</v>
       </c>
       <c r="G173"/>
       <c r="H173" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
     </row>
     <row r="174" spans="1:8">
       <c r="A174" t="s">
-        <v>659</v>
+        <v>654</v>
       </c>
       <c r="B174" t="s">
-        <v>660</v>
+        <v>655</v>
       </c>
       <c r="C174"/>
       <c r="D174"/>
-      <c r="E174" s="13" t="s">
-        <v>1035</v>
+      <c r="E174" s="2" t="s">
+        <v>1031</v>
       </c>
       <c r="F174">
         <v>1</v>
@@ -8275,15 +8327,15 @@
     </row>
     <row r="175" spans="1:8">
       <c r="A175" t="s">
-        <v>661</v>
-      </c>
-      <c r="B175" t="s">
-        <v>662</v>
+        <v>656</v>
+      </c>
+      <c r="B175" s="12" t="s">
+        <v>744</v>
       </c>
       <c r="C175"/>
       <c r="D175"/>
-      <c r="E175" s="13" t="s">
-        <v>1036</v>
+      <c r="E175" s="2" t="s">
+        <v>1032</v>
       </c>
       <c r="F175">
         <v>1</v>
@@ -8295,35 +8347,35 @@
     </row>
     <row r="176" spans="1:8">
       <c r="A176" t="s">
-        <v>663</v>
+        <v>657</v>
       </c>
       <c r="B176" t="s">
-        <v>664</v>
+        <v>658</v>
       </c>
       <c r="C176"/>
       <c r="D176"/>
-      <c r="E176" s="13" t="s">
-        <v>1037</v>
+      <c r="E176" s="2" t="s">
+        <v>1033</v>
       </c>
       <c r="F176">
         <v>1</v>
       </c>
       <c r="G176"/>
       <c r="H176" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
     </row>
     <row r="177" spans="1:8">
       <c r="A177" t="s">
-        <v>665</v>
+        <v>659</v>
       </c>
       <c r="B177" t="s">
-        <v>666</v>
+        <v>660</v>
       </c>
       <c r="C177"/>
       <c r="D177"/>
-      <c r="E177" s="13" t="s">
-        <v>1038</v>
+      <c r="E177" s="2" t="s">
+        <v>1034</v>
       </c>
       <c r="F177">
         <v>1</v>
@@ -8335,15 +8387,15 @@
     </row>
     <row r="178" spans="1:8">
       <c r="A178" t="s">
-        <v>667</v>
+        <v>661</v>
       </c>
       <c r="B178" t="s">
-        <v>668</v>
+        <v>662</v>
       </c>
       <c r="C178"/>
       <c r="D178"/>
-      <c r="E178" s="13" t="s">
-        <v>1039</v>
+      <c r="E178" s="2" t="s">
+        <v>1035</v>
       </c>
       <c r="F178">
         <v>1</v>
@@ -8355,15 +8407,15 @@
     </row>
     <row r="179" spans="1:8">
       <c r="A179" t="s">
-        <v>669</v>
+        <v>663</v>
       </c>
       <c r="B179" t="s">
-        <v>670</v>
+        <v>664</v>
       </c>
       <c r="C179"/>
       <c r="D179"/>
-      <c r="E179" s="13" t="s">
-        <v>1040</v>
+      <c r="E179" s="2" t="s">
+        <v>1036</v>
       </c>
       <c r="F179">
         <v>1</v>
@@ -8375,15 +8427,15 @@
     </row>
     <row r="180" spans="1:8">
       <c r="A180" t="s">
-        <v>671</v>
+        <v>665</v>
       </c>
       <c r="B180" t="s">
-        <v>672</v>
+        <v>666</v>
       </c>
       <c r="C180"/>
       <c r="D180"/>
-      <c r="E180" s="13" t="s">
-        <v>1041</v>
+      <c r="E180" s="2" t="s">
+        <v>1037</v>
       </c>
       <c r="F180">
         <v>1</v>
@@ -8395,15 +8447,15 @@
     </row>
     <row r="181" spans="1:8">
       <c r="A181" t="s">
-        <v>673</v>
+        <v>667</v>
       </c>
       <c r="B181" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="C181"/>
       <c r="D181"/>
-      <c r="E181" s="13" t="s">
-        <v>1042</v>
+      <c r="E181" s="2" t="s">
+        <v>1038</v>
       </c>
       <c r="F181">
         <v>1</v>
@@ -8415,15 +8467,15 @@
     </row>
     <row r="182" spans="1:8">
       <c r="A182" t="s">
-        <v>675</v>
+        <v>669</v>
       </c>
       <c r="B182" t="s">
-        <v>676</v>
+        <v>670</v>
       </c>
       <c r="C182"/>
       <c r="D182"/>
-      <c r="E182" s="13" t="s">
-        <v>1043</v>
+      <c r="E182" s="2" t="s">
+        <v>1039</v>
       </c>
       <c r="F182">
         <v>1</v>
@@ -8435,15 +8487,15 @@
     </row>
     <row r="183" spans="1:8">
       <c r="A183" t="s">
-        <v>677</v>
+        <v>671</v>
       </c>
       <c r="B183" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
       <c r="C183"/>
       <c r="D183"/>
-      <c r="E183" s="13" t="s">
-        <v>1044</v>
+      <c r="E183" s="2" t="s">
+        <v>1040</v>
       </c>
       <c r="F183">
         <v>1</v>
@@ -8455,15 +8507,15 @@
     </row>
     <row r="184" spans="1:8">
       <c r="A184" t="s">
-        <v>679</v>
+        <v>673</v>
       </c>
       <c r="B184" t="s">
-        <v>680</v>
+        <v>674</v>
       </c>
       <c r="C184"/>
       <c r="D184"/>
-      <c r="E184" s="13" t="s">
-        <v>1045</v>
+      <c r="E184" s="2" t="s">
+        <v>1041</v>
       </c>
       <c r="F184">
         <v>1</v>
@@ -8475,21 +8527,19 @@
     </row>
     <row r="185" spans="1:8">
       <c r="A185" t="s">
-        <v>681</v>
+        <v>675</v>
       </c>
       <c r="B185" t="s">
-        <v>682</v>
-      </c>
-      <c r="C185">
-        <v>14</v>
-      </c>
-      <c r="D185" s="4">
-        <v>0</v>
-      </c>
-      <c r="E185" s="13" t="s">
-        <v>1046</v>
-      </c>
-      <c r="F185"/>
+        <v>676</v>
+      </c>
+      <c r="C185"/>
+      <c r="D185"/>
+      <c r="E185" s="2" t="s">
+        <v>1042</v>
+      </c>
+      <c r="F185">
+        <v>1</v>
+      </c>
       <c r="G185"/>
       <c r="H185" t="s">
         <v>704</v>
@@ -8497,15 +8547,15 @@
     </row>
     <row r="186" spans="1:8">
       <c r="A186" t="s">
-        <v>683</v>
+        <v>677</v>
       </c>
       <c r="B186" t="s">
-        <v>684</v>
+        <v>678</v>
       </c>
       <c r="C186"/>
       <c r="D186"/>
-      <c r="E186" s="13" t="s">
-        <v>1047</v>
+      <c r="E186" s="2" t="s">
+        <v>1043</v>
       </c>
       <c r="F186">
         <v>1</v>
@@ -8517,15 +8567,15 @@
     </row>
     <row r="187" spans="1:8">
       <c r="A187" t="s">
-        <v>685</v>
+        <v>679</v>
       </c>
       <c r="B187" t="s">
-        <v>686</v>
+        <v>680</v>
       </c>
       <c r="C187"/>
       <c r="D187"/>
-      <c r="E187" s="13" t="s">
-        <v>1048</v>
+      <c r="E187" s="2" t="s">
+        <v>1044</v>
       </c>
       <c r="F187">
         <v>1</v>
@@ -8536,20 +8586,22 @@
       </c>
     </row>
     <row r="188" spans="1:8">
-      <c r="A188" s="12" t="s">
-        <v>687</v>
-      </c>
-      <c r="B188" s="12" t="s">
-        <v>745</v>
-      </c>
-      <c r="C188"/>
-      <c r="D188"/>
-      <c r="E188" s="13" t="s">
-        <v>1049</v>
-      </c>
-      <c r="F188">
-        <v>1</v>
-      </c>
+      <c r="A188" t="s">
+        <v>681</v>
+      </c>
+      <c r="B188" t="s">
+        <v>682</v>
+      </c>
+      <c r="C188">
+        <v>14</v>
+      </c>
+      <c r="D188" s="4">
+        <v>0</v>
+      </c>
+      <c r="E188" s="2" t="s">
+        <v>1045</v>
+      </c>
+      <c r="F188"/>
       <c r="G188"/>
       <c r="H188" t="s">
         <v>704</v>
@@ -8557,15 +8609,15 @@
     </row>
     <row r="189" spans="1:8">
       <c r="A189" t="s">
-        <v>688</v>
+        <v>683</v>
       </c>
       <c r="B189" t="s">
-        <v>689</v>
+        <v>684</v>
       </c>
       <c r="C189"/>
       <c r="D189"/>
-      <c r="E189" s="13" t="s">
-        <v>1050</v>
+      <c r="E189" s="2" t="s">
+        <v>1046</v>
       </c>
       <c r="F189">
         <v>1</v>
@@ -8577,37 +8629,35 @@
     </row>
     <row r="190" spans="1:8">
       <c r="A190" t="s">
-        <v>690</v>
+        <v>685</v>
       </c>
       <c r="B190" t="s">
-        <v>691</v>
-      </c>
-      <c r="C190">
-        <v>14</v>
-      </c>
-      <c r="D190" s="4">
-        <v>0</v>
-      </c>
-      <c r="E190" s="13" t="s">
-        <v>1051</v>
-      </c>
-      <c r="F190"/>
+        <v>686</v>
+      </c>
+      <c r="C190"/>
+      <c r="D190"/>
+      <c r="E190" s="2" t="s">
+        <v>1047</v>
+      </c>
+      <c r="F190">
+        <v>1</v>
+      </c>
       <c r="G190"/>
       <c r="H190" t="s">
         <v>704</v>
       </c>
     </row>
     <row r="191" spans="1:8">
-      <c r="A191" t="s">
-        <v>692</v>
-      </c>
-      <c r="B191" t="s">
-        <v>693</v>
+      <c r="A191" s="12" t="s">
+        <v>687</v>
+      </c>
+      <c r="B191" s="12" t="s">
+        <v>745</v>
       </c>
       <c r="C191"/>
       <c r="D191"/>
-      <c r="E191" s="13" t="s">
-        <v>1052</v>
+      <c r="E191" s="2" t="s">
+        <v>1048</v>
       </c>
       <c r="F191">
         <v>1</v>
@@ -8619,15 +8669,15 @@
     </row>
     <row r="192" spans="1:8">
       <c r="A192" t="s">
-        <v>694</v>
+        <v>688</v>
       </c>
       <c r="B192" t="s">
-        <v>695</v>
+        <v>689</v>
       </c>
       <c r="C192"/>
       <c r="D192"/>
-      <c r="E192" s="13" t="s">
-        <v>1053</v>
+      <c r="E192" s="2" t="s">
+        <v>1049</v>
       </c>
       <c r="F192">
         <v>1</v>
@@ -8639,19 +8689,21 @@
     </row>
     <row r="193" spans="1:8">
       <c r="A193" t="s">
-        <v>696</v>
+        <v>690</v>
       </c>
       <c r="B193" t="s">
-        <v>697</v>
-      </c>
-      <c r="C193"/>
-      <c r="D193"/>
-      <c r="E193" s="13" t="s">
-        <v>1054</v>
-      </c>
-      <c r="F193">
-        <v>1</v>
-      </c>
+        <v>691</v>
+      </c>
+      <c r="C193">
+        <v>14</v>
+      </c>
+      <c r="D193" s="4">
+        <v>0</v>
+      </c>
+      <c r="E193" s="2" t="s">
+        <v>1050</v>
+      </c>
+      <c r="F193"/>
       <c r="G193"/>
       <c r="H193" t="s">
         <v>704</v>
@@ -8659,15 +8711,15 @@
     </row>
     <row r="194" spans="1:8">
       <c r="A194" t="s">
-        <v>698</v>
+        <v>692</v>
       </c>
       <c r="B194" t="s">
-        <v>699</v>
+        <v>693</v>
       </c>
       <c r="C194"/>
       <c r="D194"/>
-      <c r="E194" s="13" t="s">
-        <v>1055</v>
+      <c r="E194" s="2" t="s">
+        <v>1051</v>
       </c>
       <c r="F194">
         <v>1</v>
@@ -8679,15 +8731,15 @@
     </row>
     <row r="195" spans="1:8">
       <c r="A195" t="s">
-        <v>700</v>
+        <v>694</v>
       </c>
       <c r="B195" t="s">
-        <v>701</v>
+        <v>695</v>
       </c>
       <c r="C195"/>
       <c r="D195"/>
-      <c r="E195" s="13" t="s">
-        <v>1056</v>
+      <c r="E195" s="2" t="s">
+        <v>1052</v>
       </c>
       <c r="F195">
         <v>1</v>
@@ -8699,15 +8751,15 @@
     </row>
     <row r="196" spans="1:8">
       <c r="A196" t="s">
-        <v>702</v>
+        <v>696</v>
       </c>
       <c r="B196" t="s">
-        <v>703</v>
+        <v>697</v>
       </c>
       <c r="C196"/>
       <c r="D196"/>
-      <c r="E196" s="13" t="s">
-        <v>1057</v>
+      <c r="E196" s="2" t="s">
+        <v>1053</v>
       </c>
       <c r="F196">
         <v>1</v>
@@ -8718,592 +8770,586 @@
       </c>
     </row>
     <row r="197" spans="1:8">
-      <c r="A197" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="B197" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="C197" s="3">
-        <v>6</v>
-      </c>
-      <c r="D197" s="4">
-        <v>0</v>
-      </c>
-      <c r="E197" s="13" t="s">
-        <v>1058</v>
-      </c>
-      <c r="F197" s="3"/>
-      <c r="G197" s="1"/>
+      <c r="A197" t="s">
+        <v>698</v>
+      </c>
+      <c r="B197" t="s">
+        <v>699</v>
+      </c>
+      <c r="C197"/>
+      <c r="D197"/>
+      <c r="E197" s="2" t="s">
+        <v>1054</v>
+      </c>
+      <c r="F197">
+        <v>1</v>
+      </c>
+      <c r="G197"/>
       <c r="H197" t="s">
-        <v>543</v>
+        <v>704</v>
       </c>
     </row>
     <row r="198" spans="1:8">
-      <c r="A198" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="B198" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="C198" s="3">
-        <v>6</v>
-      </c>
-      <c r="D198" s="4">
-        <v>0.54166666666666663</v>
-      </c>
-      <c r="E198" s="13" t="s">
-        <v>1059</v>
-      </c>
-      <c r="F198" s="3"/>
-      <c r="G198" s="1"/>
-      <c r="H198" s="1" t="s">
-        <v>403</v>
+      <c r="A198" t="s">
+        <v>700</v>
+      </c>
+      <c r="B198" t="s">
+        <v>701</v>
+      </c>
+      <c r="C198"/>
+      <c r="D198"/>
+      <c r="E198" s="2" t="s">
+        <v>1055</v>
+      </c>
+      <c r="F198">
+        <v>1</v>
+      </c>
+      <c r="G198"/>
+      <c r="H198" t="s">
+        <v>704</v>
       </c>
     </row>
     <row r="199" spans="1:8">
-      <c r="A199" s="2" t="s">
-        <v>813</v>
-      </c>
-      <c r="B199" s="1" t="s">
-        <v>775</v>
-      </c>
-      <c r="E199" s="13" t="s">
-        <v>1060</v>
-      </c>
-      <c r="F199" s="2">
-        <v>1</v>
-      </c>
-      <c r="H199" s="2" t="s">
-        <v>815</v>
+      <c r="A199" t="s">
+        <v>702</v>
+      </c>
+      <c r="B199" t="s">
+        <v>703</v>
+      </c>
+      <c r="C199"/>
+      <c r="D199"/>
+      <c r="E199" s="2" t="s">
+        <v>1056</v>
+      </c>
+      <c r="F199">
+        <v>1</v>
+      </c>
+      <c r="G199"/>
+      <c r="H199" t="s">
+        <v>704</v>
       </c>
     </row>
     <row r="200" spans="1:8">
       <c r="A200" s="2" t="s">
-        <v>814</v>
+        <v>264</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>776</v>
-      </c>
-      <c r="E200" s="13" t="s">
-        <v>1061</v>
-      </c>
-      <c r="F200" s="2">
-        <v>1</v>
-      </c>
-      <c r="H200" s="2" t="s">
-        <v>815</v>
+        <v>127</v>
+      </c>
+      <c r="C200" s="3">
+        <v>6</v>
+      </c>
+      <c r="D200" s="4">
+        <v>0</v>
+      </c>
+      <c r="E200" s="2" t="s">
+        <v>1057</v>
+      </c>
+      <c r="F200" s="3"/>
+      <c r="G200" s="1"/>
+      <c r="H200" t="s">
+        <v>543</v>
       </c>
     </row>
     <row r="201" spans="1:8">
       <c r="A201" s="2" t="s">
-        <v>225</v>
+        <v>265</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>104</v>
+        <v>141</v>
       </c>
       <c r="C201" s="3">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D201" s="4">
-        <v>0</v>
-      </c>
-      <c r="E201" s="13" t="s">
-        <v>1062</v>
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="E201" s="2" t="s">
+        <v>1058</v>
       </c>
       <c r="F201" s="3"/>
       <c r="G201" s="1"/>
       <c r="H201" s="1" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="202" spans="1:8">
+      <c r="A202" s="2" t="s">
+        <v>813</v>
+      </c>
+      <c r="B202" s="1" t="s">
+        <v>775</v>
+      </c>
+      <c r="E202" s="2" t="s">
+        <v>1059</v>
+      </c>
+      <c r="F202" s="2">
+        <v>1</v>
+      </c>
+      <c r="H202" s="2" t="s">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="203" spans="1:8">
+      <c r="A203" s="2" t="s">
+        <v>814</v>
+      </c>
+      <c r="B203" s="1" t="s">
+        <v>776</v>
+      </c>
+      <c r="E203" s="2" t="s">
+        <v>1060</v>
+      </c>
+      <c r="F203" s="2">
+        <v>1</v>
+      </c>
+      <c r="H203" s="2" t="s">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="204" spans="1:8">
+      <c r="A204" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="B204" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C204" s="3">
+        <v>13</v>
+      </c>
+      <c r="D204" s="4">
+        <v>0</v>
+      </c>
+      <c r="E204" s="2" t="s">
+        <v>1061</v>
+      </c>
+      <c r="F204" s="3"/>
+      <c r="G204" s="1"/>
+      <c r="H204" s="1" t="s">
         <v>404</v>
-      </c>
-    </row>
-    <row r="202" spans="1:8">
-      <c r="A202" t="s">
-        <v>487</v>
-      </c>
-      <c r="B202" s="1" t="s">
-        <v>331</v>
-      </c>
-      <c r="E202" s="13" t="s">
-        <v>1063</v>
-      </c>
-      <c r="F202" s="2">
-        <v>1</v>
-      </c>
-      <c r="G202" s="2" t="s">
-        <v>550</v>
-      </c>
-      <c r="H202" s="2" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="203" spans="1:8">
-      <c r="A203" t="s">
-        <v>488</v>
-      </c>
-      <c r="B203" s="1" t="s">
-        <v>332</v>
-      </c>
-      <c r="E203" s="13" t="s">
-        <v>1066</v>
-      </c>
-      <c r="F203" s="2">
-        <v>1</v>
-      </c>
-      <c r="G203" s="2" t="s">
-        <v>552</v>
-      </c>
-      <c r="H203" s="2" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="204" spans="1:8">
-      <c r="A204" t="s">
-        <v>488</v>
-      </c>
-      <c r="B204" s="1" t="s">
-        <v>332</v>
-      </c>
-      <c r="E204" s="13" t="s">
-        <v>1067</v>
-      </c>
-      <c r="F204" s="2">
-        <v>1</v>
-      </c>
-      <c r="G204" s="2" t="s">
-        <v>551</v>
-      </c>
-      <c r="H204" s="2" t="s">
-        <v>443</v>
       </c>
     </row>
     <row r="205" spans="1:8">
       <c r="A205" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>330</v>
-      </c>
-      <c r="C205" s="2">
-        <v>8</v>
-      </c>
-      <c r="D205" s="6">
-        <v>0</v>
-      </c>
-      <c r="E205" s="13" t="s">
-        <v>1064</v>
-      </c>
-      <c r="F205" s="3"/>
+        <v>331</v>
+      </c>
+      <c r="E205" s="2" t="s">
+        <v>1062</v>
+      </c>
+      <c r="F205" s="2">
+        <v>1</v>
+      </c>
+      <c r="G205" s="2" t="s">
+        <v>550</v>
+      </c>
       <c r="H205" s="2" t="s">
-        <v>742</v>
+        <v>442</v>
       </c>
     </row>
     <row r="206" spans="1:8">
-      <c r="A206" s="2" t="s">
-        <v>580</v>
+      <c r="A206" t="s">
+        <v>488</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>581</v>
-      </c>
-      <c r="D206" s="6"/>
-      <c r="E206" s="13" t="s">
+        <v>332</v>
+      </c>
+      <c r="E206" s="2" t="s">
         <v>1065</v>
       </c>
-      <c r="F206" s="3">
-        <v>1</v>
-      </c>
-      <c r="H206" s="7" t="s">
-        <v>582</v>
+      <c r="F206" s="2">
+        <v>1</v>
+      </c>
+      <c r="G206" s="2" t="s">
+        <v>552</v>
+      </c>
+      <c r="H206" s="2" t="s">
+        <v>443</v>
       </c>
     </row>
     <row r="207" spans="1:8">
-      <c r="A207" s="2" t="s">
-        <v>226</v>
+      <c r="A207" t="s">
+        <v>488</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="C207" s="3">
-        <v>13</v>
-      </c>
-      <c r="D207" s="5">
-        <v>0</v>
-      </c>
-      <c r="E207" s="13" t="s">
-        <v>1068</v>
-      </c>
-      <c r="F207" s="3"/>
-      <c r="G207" s="1"/>
-      <c r="H207" s="1" t="s">
-        <v>405</v>
+        <v>332</v>
+      </c>
+      <c r="E207" s="2" t="s">
+        <v>1066</v>
+      </c>
+      <c r="F207" s="2">
+        <v>1</v>
+      </c>
+      <c r="G207" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="H207" s="2" t="s">
+        <v>443</v>
       </c>
     </row>
     <row r="208" spans="1:8">
       <c r="A208" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="C208" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D208" s="6">
         <v>0</v>
       </c>
-      <c r="E208" s="13" t="s">
-        <v>1069</v>
-      </c>
+      <c r="E208" s="2" t="s">
+        <v>1063</v>
+      </c>
+      <c r="F208" s="3"/>
       <c r="H208" s="2" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
     </row>
     <row r="209" spans="1:8">
-      <c r="A209" t="s">
-        <v>491</v>
+      <c r="A209" s="2" t="s">
+        <v>580</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>494</v>
-      </c>
-      <c r="C209" s="2">
-        <v>10</v>
-      </c>
-      <c r="D209" s="6">
-        <v>0</v>
-      </c>
-      <c r="E209" s="13" t="s">
-        <v>1070</v>
-      </c>
-      <c r="H209" s="2" t="s">
-        <v>740</v>
+        <v>581</v>
+      </c>
+      <c r="D209" s="6"/>
+      <c r="E209" s="2" t="s">
+        <v>1064</v>
+      </c>
+      <c r="F209" s="3">
+        <v>1</v>
+      </c>
+      <c r="H209" s="7" t="s">
+        <v>582</v>
       </c>
     </row>
     <row r="210" spans="1:8">
-      <c r="A210" t="s">
-        <v>747</v>
-      </c>
-      <c r="B210" t="s">
-        <v>730</v>
-      </c>
-      <c r="C210"/>
-      <c r="D210" s="11"/>
-      <c r="E210" s="13" t="s">
-        <v>1071</v>
-      </c>
-      <c r="F210">
-        <v>1</v>
-      </c>
-      <c r="G210"/>
-      <c r="H210" s="11" t="s">
-        <v>731</v>
+      <c r="A210" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="B210" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="C210" s="3">
+        <v>13</v>
+      </c>
+      <c r="D210" s="5">
+        <v>0</v>
+      </c>
+      <c r="E210" s="2" t="s">
+        <v>1067</v>
+      </c>
+      <c r="F210" s="3"/>
+      <c r="G210" s="1"/>
+      <c r="H210" s="1" t="s">
+        <v>405</v>
       </c>
     </row>
     <row r="211" spans="1:8">
       <c r="A211" t="s">
-        <v>748</v>
-      </c>
-      <c r="B211" t="s">
-        <v>732</v>
-      </c>
-      <c r="C211">
+        <v>490</v>
+      </c>
+      <c r="B211" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="C211" s="2">
         <v>10</v>
       </c>
-      <c r="D211" s="4">
-        <v>0</v>
-      </c>
-      <c r="E211" s="13" t="s">
-        <v>1072</v>
-      </c>
-      <c r="F211"/>
-      <c r="G211"/>
-      <c r="H211" s="11" t="s">
-        <v>733</v>
+      <c r="D211" s="6">
+        <v>0</v>
+      </c>
+      <c r="E211" s="2" t="s">
+        <v>1068</v>
+      </c>
+      <c r="H211" s="2" t="s">
+        <v>741</v>
       </c>
     </row>
     <row r="212" spans="1:8">
       <c r="A212" t="s">
-        <v>749</v>
-      </c>
-      <c r="B212" t="s">
-        <v>734</v>
-      </c>
-      <c r="C212"/>
-      <c r="D212" s="11"/>
-      <c r="E212" s="13" t="s">
-        <v>1073</v>
-      </c>
-      <c r="F212">
-        <v>1</v>
-      </c>
-      <c r="G212"/>
-      <c r="H212" s="11" t="s">
-        <v>735</v>
+        <v>491</v>
+      </c>
+      <c r="B212" s="1" t="s">
+        <v>494</v>
+      </c>
+      <c r="C212" s="2">
+        <v>10</v>
+      </c>
+      <c r="D212" s="6">
+        <v>0</v>
+      </c>
+      <c r="E212" s="2" t="s">
+        <v>1069</v>
+      </c>
+      <c r="H212" s="2" t="s">
+        <v>740</v>
       </c>
     </row>
     <row r="213" spans="1:8">
-      <c r="A213" s="2" t="s">
-        <v>753</v>
-      </c>
-      <c r="B213" s="1" t="s">
-        <v>754</v>
-      </c>
-      <c r="E213" s="13" t="s">
-        <v>1074</v>
-      </c>
-      <c r="F213" s="2">
-        <v>1</v>
-      </c>
-      <c r="H213" s="2" t="s">
-        <v>755</v>
+      <c r="A213" t="s">
+        <v>747</v>
+      </c>
+      <c r="B213" t="s">
+        <v>730</v>
+      </c>
+      <c r="C213"/>
+      <c r="D213" s="11"/>
+      <c r="E213" s="2" t="s">
+        <v>1070</v>
+      </c>
+      <c r="F213">
+        <v>1</v>
+      </c>
+      <c r="G213"/>
+      <c r="H213" s="11" t="s">
+        <v>731</v>
       </c>
     </row>
     <row r="214" spans="1:8">
       <c r="A214" t="s">
-        <v>317</v>
-      </c>
-      <c r="B214" s="1" t="s">
-        <v>316</v>
-      </c>
-      <c r="C214" s="3">
-        <v>7</v>
+        <v>748</v>
+      </c>
+      <c r="B214" t="s">
+        <v>732</v>
+      </c>
+      <c r="C214">
+        <v>10</v>
       </c>
       <c r="D214" s="4">
         <v>0</v>
       </c>
-      <c r="E214" s="13" t="s">
-        <v>1075</v>
-      </c>
-      <c r="F214" s="3"/>
-      <c r="G214" s="1"/>
-      <c r="H214" s="1" t="s">
-        <v>445</v>
+      <c r="E214" s="2" t="s">
+        <v>1071</v>
+      </c>
+      <c r="F214"/>
+      <c r="G214"/>
+      <c r="H214" s="11" t="s">
+        <v>733</v>
       </c>
     </row>
     <row r="215" spans="1:8">
-      <c r="A215" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="B215" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C215" s="3">
-        <v>6</v>
-      </c>
-      <c r="D215" s="4">
-        <v>0</v>
-      </c>
-      <c r="E215" s="13" t="s">
-        <v>1076</v>
-      </c>
-      <c r="F215" s="3"/>
-      <c r="G215" s="1"/>
-      <c r="H215" s="1" t="s">
-        <v>406</v>
+      <c r="A215" t="s">
+        <v>749</v>
+      </c>
+      <c r="B215" t="s">
+        <v>734</v>
+      </c>
+      <c r="C215"/>
+      <c r="D215" s="11"/>
+      <c r="E215" s="2" t="s">
+        <v>1072</v>
+      </c>
+      <c r="F215">
+        <v>1</v>
+      </c>
+      <c r="G215"/>
+      <c r="H215" s="11" t="s">
+        <v>735</v>
       </c>
     </row>
     <row r="216" spans="1:8">
       <c r="A216" s="2" t="s">
-        <v>309</v>
+        <v>753</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="C216" s="3"/>
-      <c r="D216" s="4"/>
-      <c r="E216" s="13" t="s">
-        <v>1077</v>
-      </c>
-      <c r="F216" s="3">
-        <v>1</v>
-      </c>
-      <c r="G216" s="1"/>
-      <c r="H216" s="1" t="s">
-        <v>406</v>
+        <v>754</v>
+      </c>
+      <c r="E216" s="2" t="s">
+        <v>1073</v>
+      </c>
+      <c r="F216" s="2">
+        <v>1</v>
+      </c>
+      <c r="H216" s="2" t="s">
+        <v>755</v>
       </c>
     </row>
     <row r="217" spans="1:8">
-      <c r="A217" s="2" t="s">
-        <v>308</v>
+      <c r="A217" t="s">
+        <v>317</v>
       </c>
       <c r="B217" s="1" t="s">
-        <v>62</v>
+        <v>316</v>
       </c>
       <c r="C217" s="3">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D217" s="4">
         <v>0</v>
       </c>
-      <c r="E217" s="13" t="s">
-        <v>1078</v>
+      <c r="E217" s="2" t="s">
+        <v>1074</v>
       </c>
       <c r="F217" s="3"/>
       <c r="G217" s="1"/>
       <c r="H217" s="1" t="s">
-        <v>406</v>
+        <v>445</v>
       </c>
     </row>
     <row r="218" spans="1:8">
       <c r="A218" s="2" t="s">
-        <v>771</v>
+        <v>307</v>
       </c>
       <c r="B218" s="1" t="s">
-        <v>768</v>
-      </c>
-      <c r="E218" s="13" t="s">
-        <v>1079</v>
-      </c>
-      <c r="F218" s="2">
-        <v>1</v>
-      </c>
-      <c r="H218" s="7" t="s">
-        <v>801</v>
+        <v>61</v>
+      </c>
+      <c r="C218" s="3">
+        <v>6</v>
+      </c>
+      <c r="D218" s="4">
+        <v>0</v>
+      </c>
+      <c r="E218" s="2" t="s">
+        <v>1075</v>
+      </c>
+      <c r="F218" s="3"/>
+      <c r="G218" s="1"/>
+      <c r="H218" s="1" t="s">
+        <v>406</v>
       </c>
     </row>
     <row r="219" spans="1:8">
       <c r="A219" s="2" t="s">
-        <v>773</v>
+        <v>309</v>
       </c>
       <c r="B219" s="1" t="s">
-        <v>774</v>
-      </c>
-      <c r="E219" s="13" t="s">
-        <v>1080</v>
-      </c>
-      <c r="H219" s="7" t="s">
-        <v>802</v>
+        <v>63</v>
+      </c>
+      <c r="C219" s="3"/>
+      <c r="D219" s="4"/>
+      <c r="E219" s="2" t="s">
+        <v>1076</v>
+      </c>
+      <c r="F219" s="3">
+        <v>1</v>
+      </c>
+      <c r="G219" s="1"/>
+      <c r="H219" s="1" t="s">
+        <v>406</v>
       </c>
     </row>
     <row r="220" spans="1:8">
       <c r="A220" s="2" t="s">
-        <v>825</v>
+        <v>308</v>
       </c>
       <c r="B220" s="1" t="s">
-        <v>778</v>
-      </c>
-      <c r="C220" s="2">
-        <v>6</v>
-      </c>
-      <c r="D220" s="6">
-        <v>0</v>
-      </c>
-      <c r="E220" s="13" t="s">
-        <v>1081</v>
-      </c>
-      <c r="H220" s="2" t="s">
-        <v>826</v>
+        <v>62</v>
+      </c>
+      <c r="C220" s="3">
+        <v>10</v>
+      </c>
+      <c r="D220" s="4">
+        <v>0</v>
+      </c>
+      <c r="E220" s="2" t="s">
+        <v>1077</v>
+      </c>
+      <c r="F220" s="3"/>
+      <c r="G220" s="1"/>
+      <c r="H220" s="1" t="s">
+        <v>406</v>
       </c>
     </row>
     <row r="221" spans="1:8">
       <c r="A221" s="2" t="s">
+        <v>771</v>
+      </c>
+      <c r="B221" s="1" t="s">
+        <v>768</v>
+      </c>
+      <c r="E221" s="2" t="s">
+        <v>1078</v>
+      </c>
+      <c r="F221" s="2">
+        <v>1</v>
+      </c>
+      <c r="H221" s="7" t="s">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="222" spans="1:8">
+      <c r="A222" s="2" t="s">
+        <v>773</v>
+      </c>
+      <c r="B222" s="1" t="s">
+        <v>774</v>
+      </c>
+      <c r="E222" s="2" t="s">
+        <v>1079</v>
+      </c>
+      <c r="H222" s="7" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="223" spans="1:8">
+      <c r="A223" s="2" t="s">
+        <v>825</v>
+      </c>
+      <c r="B223" s="1" t="s">
+        <v>778</v>
+      </c>
+      <c r="C223" s="2">
+        <v>6</v>
+      </c>
+      <c r="D223" s="6">
+        <v>0</v>
+      </c>
+      <c r="E223" s="2" t="s">
+        <v>1080</v>
+      </c>
+      <c r="H223" s="2" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="224" spans="1:8">
+      <c r="A224" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="B221" s="1" t="s">
+      <c r="B224" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="D221" s="6"/>
-      <c r="E221" s="13" t="s">
-        <v>1082</v>
-      </c>
-      <c r="F221" s="2">
-        <v>1</v>
-      </c>
-      <c r="H221" t="s">
+      <c r="D224" s="6"/>
+      <c r="E224" s="2" t="s">
+        <v>1081</v>
+      </c>
+      <c r="F224" s="2">
+        <v>1</v>
+      </c>
+      <c r="H224" t="s">
         <v>544</v>
-      </c>
-    </row>
-    <row r="222" spans="1:8">
-      <c r="A222" t="s">
-        <v>707</v>
-      </c>
-      <c r="B222" t="s">
-        <v>708</v>
-      </c>
-      <c r="C222">
-        <v>15</v>
-      </c>
-      <c r="D222" s="4">
-        <v>0</v>
-      </c>
-      <c r="E222"/>
-      <c r="F222"/>
-      <c r="G222"/>
-      <c r="H222" s="11" t="s">
-        <v>709</v>
-      </c>
-    </row>
-    <row r="223" spans="1:8">
-      <c r="A223" t="s">
-        <v>710</v>
-      </c>
-      <c r="B223" t="s">
-        <v>711</v>
-      </c>
-      <c r="C223">
-        <v>15</v>
-      </c>
-      <c r="D223" s="4">
-        <v>0</v>
-      </c>
-      <c r="E223" t="s">
-        <v>1083</v>
-      </c>
-      <c r="F223"/>
-      <c r="G223"/>
-      <c r="H223" s="11" t="s">
-        <v>712</v>
-      </c>
-    </row>
-    <row r="224" spans="1:8">
-      <c r="A224" t="s">
-        <v>713</v>
-      </c>
-      <c r="B224" t="s">
-        <v>714</v>
-      </c>
-      <c r="C224">
-        <v>15</v>
-      </c>
-      <c r="D224" s="4">
-        <v>0</v>
-      </c>
-      <c r="E224" t="s">
-        <v>1084</v>
-      </c>
-      <c r="F224"/>
-      <c r="G224"/>
-      <c r="H224" s="11" t="s">
-        <v>715</v>
       </c>
     </row>
     <row r="225" spans="1:8">
       <c r="A225" t="s">
-        <v>716</v>
+        <v>707</v>
       </c>
       <c r="B225" t="s">
-        <v>717</v>
+        <v>708</v>
       </c>
       <c r="C225">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D225" s="4">
         <v>0</v>
       </c>
-      <c r="E225" t="s">
-        <v>1085</v>
-      </c>
+      <c r="E225"/>
       <c r="F225"/>
       <c r="G225"/>
       <c r="H225" s="11" t="s">
-        <v>718</v>
+        <v>709</v>
       </c>
     </row>
     <row r="226" spans="1:8">
       <c r="A226" t="s">
-        <v>719</v>
+        <v>710</v>
       </c>
       <c r="B226" t="s">
-        <v>720</v>
+        <v>711</v>
       </c>
       <c r="C226">
         <v>15</v>
@@ -9311,124 +9357,129 @@
       <c r="D226" s="4">
         <v>0</v>
       </c>
-      <c r="E226"/>
+      <c r="E226" t="s">
+        <v>1082</v>
+      </c>
       <c r="F226"/>
       <c r="G226"/>
       <c r="H226" s="11" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="227" spans="1:8">
+      <c r="A227" t="s">
+        <v>713</v>
+      </c>
+      <c r="B227" t="s">
+        <v>714</v>
+      </c>
+      <c r="C227">
+        <v>15</v>
+      </c>
+      <c r="D227" s="4">
+        <v>0</v>
+      </c>
+      <c r="E227" t="s">
+        <v>1083</v>
+      </c>
+      <c r="F227"/>
+      <c r="G227"/>
+      <c r="H227" s="11" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="228" spans="1:8">
+      <c r="A228" t="s">
+        <v>716</v>
+      </c>
+      <c r="B228" t="s">
+        <v>717</v>
+      </c>
+      <c r="C228">
+        <v>20</v>
+      </c>
+      <c r="D228" s="4">
+        <v>0</v>
+      </c>
+      <c r="E228" t="s">
+        <v>1084</v>
+      </c>
+      <c r="F228"/>
+      <c r="G228"/>
+      <c r="H228" s="11" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="229" spans="1:8">
+      <c r="A229" t="s">
+        <v>719</v>
+      </c>
+      <c r="B229" t="s">
+        <v>720</v>
+      </c>
+      <c r="C229">
+        <v>15</v>
+      </c>
+      <c r="D229" s="4">
+        <v>0</v>
+      </c>
+      <c r="E229"/>
+      <c r="F229"/>
+      <c r="G229"/>
+      <c r="H229" s="11" t="s">
         <v>721</v>
-      </c>
-    </row>
-    <row r="227" spans="1:8">
-      <c r="A227" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="B227" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="C227" s="1"/>
-      <c r="D227" s="1"/>
-      <c r="E227" s="1" t="s">
-        <v>1086</v>
-      </c>
-      <c r="F227" s="3">
-        <v>1</v>
-      </c>
-      <c r="G227" s="1" t="s">
-        <v>810</v>
-      </c>
-      <c r="H227" s="2" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="228" spans="1:8">
-      <c r="A228" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="B228" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="C228" s="3">
-        <v>7</v>
-      </c>
-      <c r="D228" s="4">
-        <v>0.91666666666666663</v>
-      </c>
-      <c r="E228" s="1" t="s">
-        <v>1087</v>
-      </c>
-      <c r="F228" s="3"/>
-      <c r="G228" s="1"/>
-      <c r="H228" s="1" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="229" spans="1:8">
-      <c r="A229" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="B229" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="C229" s="3">
-        <v>6</v>
-      </c>
-      <c r="D229" s="4">
-        <v>0</v>
-      </c>
-      <c r="E229" s="1" t="s">
-        <v>1088</v>
-      </c>
-      <c r="F229" s="3"/>
-      <c r="G229" s="1"/>
-      <c r="H229" s="1" t="s">
-        <v>409</v>
       </c>
     </row>
     <row r="230" spans="1:8">
       <c r="A230" s="2" t="s">
-        <v>839</v>
+        <v>227</v>
       </c>
       <c r="B230" s="1" t="s">
-        <v>783</v>
-      </c>
+        <v>136</v>
+      </c>
+      <c r="C230" s="1"/>
+      <c r="D230" s="1"/>
       <c r="E230" s="1" t="s">
-        <v>1089</v>
-      </c>
-      <c r="F230" s="2">
-        <v>1</v>
-      </c>
-      <c r="H230" s="7" t="s">
-        <v>840</v>
+        <v>1085</v>
+      </c>
+      <c r="F230" s="3">
+        <v>1</v>
+      </c>
+      <c r="G230" s="1" t="s">
+        <v>810</v>
+      </c>
+      <c r="H230" s="2" t="s">
+        <v>407</v>
       </c>
     </row>
     <row r="231" spans="1:8">
       <c r="A231" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B231" s="1" t="s">
-        <v>146</v>
+        <v>71</v>
       </c>
       <c r="C231" s="3">
-        <v>6</v>
-      </c>
-      <c r="D231" s="5">
-        <v>0</v>
+        <v>7</v>
+      </c>
+      <c r="D231" s="4">
+        <v>0.91666666666666663</v>
       </c>
       <c r="E231" s="1" t="s">
-        <v>1090</v>
+        <v>1086</v>
       </c>
       <c r="F231" s="3"/>
       <c r="G231" s="1"/>
       <c r="H231" s="1" t="s">
-        <v>446</v>
+        <v>408</v>
       </c>
     </row>
     <row r="232" spans="1:8">
       <c r="A232" s="2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B232" s="1" t="s">
-        <v>42</v>
+        <v>121</v>
       </c>
       <c r="C232" s="3">
         <v>6</v>
@@ -9437,206 +9488,216 @@
         <v>0</v>
       </c>
       <c r="E232" s="1" t="s">
-        <v>1091</v>
+        <v>1087</v>
       </c>
       <c r="F232" s="3"/>
       <c r="G232" s="1"/>
-      <c r="H232" s="2" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="233" spans="1:8" customFormat="1">
+      <c r="H232" s="1" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="233" spans="1:8">
       <c r="A233" s="2" t="s">
-        <v>448</v>
+        <v>839</v>
       </c>
       <c r="B233" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="C233" s="1">
-        <v>7</v>
-      </c>
-      <c r="D233" s="5">
-        <v>0.91666666666666663</v>
+        <v>783</v>
       </c>
       <c r="E233" s="1" t="s">
-        <v>1092</v>
-      </c>
-      <c r="F233" s="1"/>
-      <c r="G233" s="1"/>
-      <c r="H233" s="1" t="s">
-        <v>411</v>
+        <v>1088</v>
+      </c>
+      <c r="F233" s="2">
+        <v>1</v>
+      </c>
+      <c r="H233" s="7" t="s">
+        <v>840</v>
       </c>
     </row>
     <row r="234" spans="1:8">
       <c r="A234" s="2" t="s">
-        <v>449</v>
+        <v>229</v>
       </c>
       <c r="B234" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="C234" s="1"/>
-      <c r="D234" s="5"/>
+        <v>146</v>
+      </c>
+      <c r="C234" s="3">
+        <v>6</v>
+      </c>
+      <c r="D234" s="5">
+        <v>0</v>
+      </c>
       <c r="E234" s="1" t="s">
-        <v>1093</v>
-      </c>
-      <c r="F234" s="1">
-        <v>1</v>
-      </c>
+        <v>1089</v>
+      </c>
+      <c r="F234" s="3"/>
       <c r="G234" s="1"/>
       <c r="H234" s="1" t="s">
-        <v>412</v>
+        <v>446</v>
       </c>
     </row>
     <row r="235" spans="1:8">
       <c r="A235" s="2" t="s">
-        <v>450</v>
+        <v>267</v>
       </c>
       <c r="B235" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="C235" s="1"/>
-      <c r="D235" s="1"/>
+        <v>42</v>
+      </c>
+      <c r="C235" s="3">
+        <v>6</v>
+      </c>
+      <c r="D235" s="4">
+        <v>0</v>
+      </c>
       <c r="E235" s="1" t="s">
-        <v>1094</v>
-      </c>
-      <c r="F235" s="1">
-        <v>1</v>
-      </c>
+        <v>1090</v>
+      </c>
+      <c r="F235" s="3"/>
       <c r="G235" s="1"/>
-      <c r="H235" s="1" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="236" spans="1:8">
+      <c r="H235" s="2" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="236" spans="1:8" customFormat="1">
       <c r="A236" s="2" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="B236" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="C236" s="1"/>
-      <c r="D236" s="1"/>
+        <v>157</v>
+      </c>
+      <c r="C236" s="1">
+        <v>7</v>
+      </c>
+      <c r="D236" s="5">
+        <v>0.91666666666666663</v>
+      </c>
       <c r="E236" s="1" t="s">
-        <v>1095</v>
-      </c>
-      <c r="F236" s="1">
-        <v>1</v>
-      </c>
+        <v>1091</v>
+      </c>
+      <c r="F236" s="1"/>
       <c r="G236" s="1"/>
       <c r="H236" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="237" spans="1:8">
       <c r="A237" s="2" t="s">
-        <v>311</v>
+        <v>449</v>
       </c>
       <c r="B237" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="C237" s="3">
-        <v>6</v>
-      </c>
-      <c r="D237" s="4">
-        <v>0</v>
-      </c>
+        <v>310</v>
+      </c>
+      <c r="C237" s="1"/>
+      <c r="D237" s="5"/>
       <c r="E237" s="1" t="s">
-        <v>1096</v>
-      </c>
-      <c r="F237" s="3"/>
+        <v>1092</v>
+      </c>
+      <c r="F237" s="1">
+        <v>1</v>
+      </c>
       <c r="G237" s="1"/>
       <c r="H237" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="238" spans="1:8">
       <c r="A238" s="2" t="s">
-        <v>312</v>
+        <v>450</v>
       </c>
       <c r="B238" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="C238" s="3">
-        <v>29</v>
-      </c>
-      <c r="D238" s="4">
-        <v>0</v>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="C238" s="1"/>
+      <c r="D238" s="1"/>
       <c r="E238" s="1" t="s">
-        <v>1097</v>
-      </c>
-      <c r="F238" s="3"/>
+        <v>1093</v>
+      </c>
+      <c r="F238" s="1">
+        <v>1</v>
+      </c>
       <c r="G238" s="1"/>
-      <c r="H238" s="2" t="s">
-        <v>414</v>
+      <c r="H238" s="1" t="s">
+        <v>412</v>
       </c>
     </row>
     <row r="239" spans="1:8">
       <c r="A239" s="2" t="s">
-        <v>823</v>
+        <v>451</v>
       </c>
       <c r="B239" s="1" t="s">
-        <v>820</v>
-      </c>
-      <c r="C239" s="2">
-        <v>14</v>
-      </c>
-      <c r="D239" s="6">
-        <v>0</v>
-      </c>
+        <v>152</v>
+      </c>
+      <c r="C239" s="1"/>
+      <c r="D239" s="1"/>
       <c r="E239" s="1" t="s">
-        <v>1098</v>
-      </c>
-      <c r="H239" s="2" t="s">
-        <v>824</v>
+        <v>1094</v>
+      </c>
+      <c r="F239" s="1">
+        <v>1</v>
+      </c>
+      <c r="G239" s="1"/>
+      <c r="H239" s="1" t="s">
+        <v>412</v>
       </c>
     </row>
     <row r="240" spans="1:8">
       <c r="A240" s="2" t="s">
-        <v>822</v>
+        <v>311</v>
       </c>
       <c r="B240" s="1" t="s">
-        <v>819</v>
+        <v>130</v>
+      </c>
+      <c r="C240" s="3">
+        <v>6</v>
+      </c>
+      <c r="D240" s="4">
+        <v>0</v>
       </c>
       <c r="E240" s="1" t="s">
-        <v>1099</v>
-      </c>
-      <c r="F240" s="2">
-        <v>1</v>
-      </c>
-      <c r="H240" s="2" t="s">
-        <v>824</v>
+        <v>1095</v>
+      </c>
+      <c r="F240" s="3"/>
+      <c r="G240" s="1"/>
+      <c r="H240" s="1" t="s">
+        <v>413</v>
       </c>
     </row>
     <row r="241" spans="1:8">
       <c r="A241" s="2" t="s">
-        <v>821</v>
+        <v>312</v>
       </c>
       <c r="B241" s="1" t="s">
-        <v>818</v>
+        <v>129</v>
+      </c>
+      <c r="C241" s="3">
+        <v>29</v>
+      </c>
+      <c r="D241" s="4">
+        <v>0</v>
       </c>
       <c r="E241" s="1" t="s">
-        <v>1100</v>
-      </c>
-      <c r="F241" s="2">
-        <v>1</v>
-      </c>
+        <v>1096</v>
+      </c>
+      <c r="F241" s="3"/>
+      <c r="G241" s="1"/>
       <c r="H241" s="2" t="s">
-        <v>824</v>
+        <v>414</v>
       </c>
     </row>
     <row r="242" spans="1:8">
       <c r="A242" s="2" t="s">
-        <v>816</v>
+        <v>823</v>
       </c>
       <c r="B242" s="1" t="s">
-        <v>817</v>
+        <v>820</v>
+      </c>
+      <c r="C242" s="2">
+        <v>14</v>
+      </c>
+      <c r="D242" s="6">
+        <v>0</v>
       </c>
       <c r="E242" s="1" t="s">
-        <v>1101</v>
-      </c>
-      <c r="F242" s="2">
-        <v>1</v>
+        <v>1097</v>
       </c>
       <c r="H242" s="2" t="s">
         <v>824</v>
@@ -9644,92 +9705,82 @@
     </row>
     <row r="243" spans="1:8">
       <c r="A243" s="2" t="s">
-        <v>507</v>
+        <v>822</v>
       </c>
       <c r="B243" s="1" t="s">
-        <v>505</v>
-      </c>
-      <c r="C243" s="2">
-        <v>7</v>
-      </c>
-      <c r="D243" s="6">
-        <v>0.95833333333333337</v>
+        <v>819</v>
       </c>
       <c r="E243" s="1" t="s">
-        <v>1102</v>
-      </c>
-      <c r="F243" s="3"/>
-      <c r="H243" s="7" t="s">
-        <v>506</v>
+        <v>1098</v>
+      </c>
+      <c r="F243" s="2">
+        <v>1</v>
+      </c>
+      <c r="H243" s="2" t="s">
+        <v>824</v>
       </c>
     </row>
     <row r="244" spans="1:8">
       <c r="A244" s="2" t="s">
-        <v>275</v>
+        <v>821</v>
       </c>
       <c r="B244" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C244" s="3">
-        <v>14</v>
-      </c>
-      <c r="D244" s="4">
-        <v>0</v>
+        <v>818</v>
       </c>
       <c r="E244" s="1" t="s">
-        <v>1103</v>
-      </c>
-      <c r="F244" s="3"/>
-      <c r="G244" s="1"/>
-      <c r="H244" s="7" t="s">
-        <v>852</v>
+        <v>1099</v>
+      </c>
+      <c r="F244" s="2">
+        <v>1</v>
+      </c>
+      <c r="H244" s="2" t="s">
+        <v>824</v>
       </c>
     </row>
     <row r="245" spans="1:8">
       <c r="A245" s="2" t="s">
-        <v>277</v>
+        <v>816</v>
       </c>
       <c r="B245" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C245" s="3">
-        <v>14</v>
-      </c>
-      <c r="D245" s="4">
-        <v>0</v>
+        <v>817</v>
       </c>
       <c r="E245" s="1" t="s">
-        <v>1104</v>
-      </c>
-      <c r="F245" s="3"/>
-      <c r="G245" s="1"/>
+        <v>1100</v>
+      </c>
+      <c r="F245" s="2">
+        <v>1</v>
+      </c>
       <c r="H245" s="2" t="s">
-        <v>415</v>
+        <v>824</v>
       </c>
     </row>
     <row r="246" spans="1:8">
       <c r="A246" s="2" t="s">
-        <v>279</v>
+        <v>507</v>
       </c>
       <c r="B246" s="1" t="s">
-        <v>280</v>
+        <v>505</v>
+      </c>
+      <c r="C246" s="2">
+        <v>7</v>
+      </c>
+      <c r="D246" s="6">
+        <v>0.95833333333333337</v>
       </c>
       <c r="E246" s="1" t="s">
-        <v>1105</v>
-      </c>
-      <c r="F246" s="3">
-        <v>1</v>
-      </c>
-      <c r="H246" s="1" t="s">
-        <v>416</v>
+        <v>1101</v>
+      </c>
+      <c r="F246" s="3"/>
+      <c r="H246" s="7" t="s">
+        <v>506</v>
       </c>
     </row>
     <row r="247" spans="1:8">
       <c r="A247" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B247" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C247" s="3">
         <v>14</v>
@@ -9738,20 +9789,20 @@
         <v>0</v>
       </c>
       <c r="E247" s="1" t="s">
-        <v>1106</v>
+        <v>1102</v>
       </c>
       <c r="F247" s="3"/>
       <c r="G247" s="1"/>
-      <c r="H247" s="2" t="s">
-        <v>417</v>
+      <c r="H247" s="7" t="s">
+        <v>852</v>
       </c>
     </row>
     <row r="248" spans="1:8">
       <c r="A248" s="2" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B248" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C248" s="3">
         <v>14</v>
@@ -9760,108 +9811,103 @@
         <v>0</v>
       </c>
       <c r="E248" s="1" t="s">
-        <v>1107</v>
+        <v>1103</v>
       </c>
       <c r="F248" s="3"/>
       <c r="G248" s="1"/>
       <c r="H248" s="2" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
     </row>
     <row r="249" spans="1:8">
       <c r="A249" s="2" t="s">
-        <v>230</v>
+        <v>279</v>
       </c>
       <c r="B249" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C249" s="3">
-        <v>14</v>
-      </c>
-      <c r="D249" s="4">
-        <v>0</v>
+        <v>280</v>
       </c>
       <c r="E249" s="1" t="s">
-        <v>1108</v>
-      </c>
-      <c r="F249" s="3"/>
-      <c r="G249" s="1"/>
+        <v>1104</v>
+      </c>
+      <c r="F249" s="3">
+        <v>1</v>
+      </c>
       <c r="H249" s="1" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
     </row>
     <row r="250" spans="1:8">
       <c r="A250" s="2" t="s">
-        <v>231</v>
+        <v>276</v>
       </c>
       <c r="B250" s="1" t="s">
-        <v>66</v>
+        <v>34</v>
       </c>
       <c r="C250" s="3">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D250" s="4">
-        <v>0.91666666666666663</v>
+        <v>0</v>
       </c>
       <c r="E250" s="1" t="s">
-        <v>1109</v>
+        <v>1105</v>
       </c>
       <c r="F250" s="3"/>
       <c r="G250" s="1"/>
-      <c r="H250" s="1" t="s">
-        <v>419</v>
+      <c r="H250" s="2" t="s">
+        <v>417</v>
       </c>
     </row>
     <row r="251" spans="1:8">
       <c r="A251" s="2" t="s">
-        <v>232</v>
+        <v>278</v>
       </c>
       <c r="B251" s="1" t="s">
-        <v>65</v>
+        <v>36</v>
       </c>
       <c r="C251" s="3">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D251" s="4">
-        <v>0.91666666666666663</v>
+        <v>0</v>
       </c>
       <c r="E251" s="1" t="s">
-        <v>1110</v>
+        <v>1106</v>
       </c>
       <c r="F251" s="3"/>
       <c r="G251" s="1"/>
-      <c r="H251" s="1" t="s">
+      <c r="H251" s="2" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="252" spans="1:8">
+      <c r="A252" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="B252" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C252" s="3">
+        <v>14</v>
+      </c>
+      <c r="D252" s="4">
+        <v>0</v>
+      </c>
+      <c r="E252" s="1" t="s">
+        <v>1107</v>
+      </c>
+      <c r="F252" s="3"/>
+      <c r="G252" s="1"/>
+      <c r="H252" s="1" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="252" spans="1:8">
-      <c r="A252" t="s">
-        <v>722</v>
-      </c>
-      <c r="B252" t="s">
-        <v>723</v>
-      </c>
-      <c r="C252">
-        <v>6</v>
-      </c>
-      <c r="D252" s="4">
-        <v>0</v>
-      </c>
-      <c r="E252" s="1" t="s">
-        <v>1111</v>
-      </c>
-      <c r="F252"/>
-      <c r="G252"/>
-      <c r="H252" s="7" t="s">
-        <v>724</v>
-      </c>
-    </row>
     <row r="253" spans="1:8">
-      <c r="A253" s="11" t="s">
-        <v>725</v>
-      </c>
-      <c r="B253" t="s">
-        <v>726</v>
+      <c r="A253" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="B253" s="1" t="s">
+        <v>66</v>
       </c>
       <c r="C253" s="3">
         <v>7</v>
@@ -9870,439 +9916,439 @@
         <v>0.91666666666666663</v>
       </c>
       <c r="E253" s="1" t="s">
-        <v>1112</v>
-      </c>
-      <c r="F253"/>
-      <c r="G253"/>
-      <c r="H253" s="7" t="s">
-        <v>736</v>
+        <v>1108</v>
+      </c>
+      <c r="F253" s="3"/>
+      <c r="G253" s="1"/>
+      <c r="H253" s="1" t="s">
+        <v>419</v>
       </c>
     </row>
     <row r="254" spans="1:8">
       <c r="A254" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B254" s="1" t="s">
-        <v>145</v>
+        <v>65</v>
       </c>
       <c r="C254" s="3">
         <v>7</v>
       </c>
-      <c r="D254" s="5">
-        <v>0.875</v>
+      <c r="D254" s="4">
+        <v>0.91666666666666663</v>
       </c>
       <c r="E254" s="1" t="s">
-        <v>1113</v>
+        <v>1109</v>
       </c>
       <c r="F254" s="3"/>
       <c r="G254" s="1"/>
       <c r="H254" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="255" spans="1:8">
-      <c r="A255" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="B255" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C255" s="3">
+      <c r="A255" t="s">
+        <v>722</v>
+      </c>
+      <c r="B255" t="s">
+        <v>723</v>
+      </c>
+      <c r="C255">
         <v>6</v>
       </c>
       <c r="D255" s="4">
         <v>0</v>
       </c>
       <c r="E255" s="1" t="s">
-        <v>1114</v>
-      </c>
-      <c r="F255" s="3"/>
-      <c r="G255" s="1"/>
-      <c r="H255" s="2" t="s">
-        <v>421</v>
+        <v>1110</v>
+      </c>
+      <c r="F255"/>
+      <c r="G255"/>
+      <c r="H255" s="7" t="s">
+        <v>724</v>
       </c>
     </row>
     <row r="256" spans="1:8">
-      <c r="A256" t="s">
-        <v>323</v>
-      </c>
-      <c r="B256" s="1" t="s">
-        <v>158</v>
+      <c r="A256" s="11" t="s">
+        <v>725</v>
+      </c>
+      <c r="B256" t="s">
+        <v>726</v>
       </c>
       <c r="C256" s="3">
-        <v>13</v>
-      </c>
-      <c r="D256" s="5">
-        <v>0</v>
+        <v>7</v>
+      </c>
+      <c r="D256" s="4">
+        <v>0.91666666666666663</v>
       </c>
       <c r="E256" s="1" t="s">
-        <v>1115</v>
-      </c>
-      <c r="F256" s="3"/>
-      <c r="G256" s="1"/>
-      <c r="H256" s="1" t="s">
-        <v>422</v>
+        <v>1111</v>
+      </c>
+      <c r="F256"/>
+      <c r="G256"/>
+      <c r="H256" s="7" t="s">
+        <v>736</v>
       </c>
     </row>
     <row r="257" spans="1:8">
-      <c r="A257" t="s">
-        <v>324</v>
+      <c r="A257" s="2" t="s">
+        <v>233</v>
       </c>
       <c r="B257" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="C257" s="3"/>
-      <c r="D257" s="5"/>
+        <v>145</v>
+      </c>
+      <c r="C257" s="3">
+        <v>7</v>
+      </c>
+      <c r="D257" s="5">
+        <v>0.875</v>
+      </c>
       <c r="E257" s="1" t="s">
-        <v>1116</v>
-      </c>
-      <c r="F257" s="3">
-        <v>1</v>
-      </c>
+        <v>1112</v>
+      </c>
+      <c r="F257" s="3"/>
       <c r="G257" s="1"/>
       <c r="H257" s="1" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
     </row>
     <row r="258" spans="1:8">
       <c r="A258" s="2" t="s">
-        <v>320</v>
+        <v>234</v>
       </c>
       <c r="B258" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="C258" s="3"/>
-      <c r="D258" s="5"/>
+        <v>5</v>
+      </c>
+      <c r="C258" s="3">
+        <v>6</v>
+      </c>
+      <c r="D258" s="4">
+        <v>0</v>
+      </c>
       <c r="E258" s="1" t="s">
-        <v>1117</v>
-      </c>
-      <c r="F258" s="3">
-        <v>1</v>
-      </c>
+        <v>1113</v>
+      </c>
+      <c r="F258" s="3"/>
       <c r="G258" s="1"/>
-      <c r="H258" s="1" t="s">
-        <v>424</v>
+      <c r="H258" s="2" t="s">
+        <v>421</v>
       </c>
     </row>
     <row r="259" spans="1:8">
-      <c r="A259" s="2" t="s">
-        <v>237</v>
+      <c r="A259" t="s">
+        <v>323</v>
       </c>
       <c r="B259" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="C259" s="3"/>
-      <c r="D259" s="5"/>
+        <v>158</v>
+      </c>
+      <c r="C259" s="3">
+        <v>13</v>
+      </c>
+      <c r="D259" s="5">
+        <v>0</v>
+      </c>
       <c r="E259" s="1" t="s">
-        <v>1118</v>
-      </c>
-      <c r="F259" s="3">
-        <v>1</v>
-      </c>
+        <v>1114</v>
+      </c>
+      <c r="F259" s="3"/>
       <c r="G259" s="1"/>
       <c r="H259" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
     </row>
     <row r="260" spans="1:8">
-      <c r="A260" s="11" t="s">
-        <v>727</v>
-      </c>
-      <c r="B260" t="s">
-        <v>728</v>
-      </c>
-      <c r="C260">
-        <v>13</v>
-      </c>
-      <c r="D260" s="11" t="s">
-        <v>807</v>
-      </c>
+      <c r="A260" t="s">
+        <v>324</v>
+      </c>
+      <c r="B260" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C260" s="3"/>
+      <c r="D260" s="5"/>
       <c r="E260" s="1" t="s">
-        <v>1119</v>
-      </c>
-      <c r="F260"/>
-      <c r="G260"/>
-      <c r="H260" s="7" t="s">
-        <v>729</v>
+        <v>1115</v>
+      </c>
+      <c r="F260" s="3">
+        <v>1</v>
+      </c>
+      <c r="G260" s="1"/>
+      <c r="H260" s="1" t="s">
+        <v>423</v>
       </c>
     </row>
     <row r="261" spans="1:8">
       <c r="A261" s="2" t="s">
-        <v>770</v>
+        <v>320</v>
       </c>
       <c r="B261" s="1" t="s">
-        <v>769</v>
-      </c>
-      <c r="C261" s="2">
-        <v>6</v>
-      </c>
-      <c r="D261" s="6">
-        <v>0</v>
-      </c>
+        <v>321</v>
+      </c>
+      <c r="C261" s="3"/>
+      <c r="D261" s="5"/>
       <c r="E261" s="1" t="s">
-        <v>1120</v>
-      </c>
-      <c r="H261" s="7" t="s">
-        <v>772</v>
+        <v>1116</v>
+      </c>
+      <c r="F261" s="3">
+        <v>1</v>
+      </c>
+      <c r="G261" s="1"/>
+      <c r="H261" s="1" t="s">
+        <v>424</v>
       </c>
     </row>
     <row r="262" spans="1:8">
       <c r="A262" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B262" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="C262" s="3">
-        <v>7</v>
-      </c>
-      <c r="D262" s="5">
-        <v>0.91666666666666663</v>
-      </c>
+        <v>149</v>
+      </c>
+      <c r="C262" s="3"/>
+      <c r="D262" s="5"/>
       <c r="E262" s="1" t="s">
-        <v>1121</v>
-      </c>
-      <c r="F262" s="3"/>
+        <v>1117</v>
+      </c>
+      <c r="F262" s="3">
+        <v>1</v>
+      </c>
       <c r="G262" s="1"/>
       <c r="H262" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="263" spans="1:8">
-      <c r="A263" s="2" t="s">
-        <v>793</v>
-      </c>
-      <c r="B263" s="1" t="s">
-        <v>789</v>
+      <c r="A263" s="11" t="s">
+        <v>727</v>
+      </c>
+      <c r="B263" t="s">
+        <v>728</v>
+      </c>
+      <c r="C263">
+        <v>13</v>
+      </c>
+      <c r="D263" s="11" t="s">
+        <v>807</v>
       </c>
       <c r="E263" s="1" t="s">
-        <v>1122</v>
-      </c>
-      <c r="F263" s="2">
-        <v>1</v>
-      </c>
-      <c r="H263" s="2" t="s">
-        <v>797</v>
+        <v>1118</v>
+      </c>
+      <c r="F263"/>
+      <c r="G263"/>
+      <c r="H263" s="7" t="s">
+        <v>729</v>
       </c>
     </row>
     <row r="264" spans="1:8">
       <c r="A264" s="2" t="s">
-        <v>794</v>
+        <v>770</v>
       </c>
       <c r="B264" s="1" t="s">
-        <v>790</v>
+        <v>769</v>
+      </c>
+      <c r="C264" s="2">
+        <v>6</v>
+      </c>
+      <c r="D264" s="6">
+        <v>0</v>
       </c>
       <c r="E264" s="1" t="s">
-        <v>1123</v>
-      </c>
-      <c r="F264" s="2">
-        <v>1</v>
-      </c>
-      <c r="H264" s="2" t="s">
-        <v>796</v>
+        <v>1119</v>
+      </c>
+      <c r="H264" s="7" t="s">
+        <v>772</v>
       </c>
     </row>
     <row r="265" spans="1:8">
       <c r="A265" s="2" t="s">
-        <v>795</v>
+        <v>238</v>
       </c>
       <c r="B265" s="1" t="s">
-        <v>787</v>
+        <v>147</v>
+      </c>
+      <c r="C265" s="3">
+        <v>7</v>
+      </c>
+      <c r="D265" s="5">
+        <v>0.91666666666666663</v>
       </c>
       <c r="E265" s="1" t="s">
-        <v>1124</v>
-      </c>
-      <c r="F265" s="2">
-        <v>1</v>
-      </c>
-      <c r="H265" s="2" t="s">
-        <v>799</v>
+        <v>1120</v>
+      </c>
+      <c r="F265" s="3"/>
+      <c r="G265" s="1"/>
+      <c r="H265" s="1" t="s">
+        <v>425</v>
       </c>
     </row>
     <row r="266" spans="1:8">
       <c r="A266" s="2" t="s">
-        <v>475</v>
+        <v>793</v>
       </c>
       <c r="B266" s="1" t="s">
-        <v>477</v>
+        <v>789</v>
       </c>
       <c r="E266" s="1" t="s">
-        <v>1125</v>
+        <v>1121</v>
       </c>
       <c r="F266" s="2">
         <v>1</v>
       </c>
       <c r="H266" s="2" t="s">
-        <v>501</v>
+        <v>797</v>
       </c>
     </row>
     <row r="267" spans="1:8">
       <c r="A267" s="2" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="B267" s="1" t="s">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="E267" s="1" t="s">
-        <v>1126</v>
+        <v>1122</v>
       </c>
       <c r="F267" s="2">
         <v>1</v>
       </c>
       <c r="H267" s="2" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
     </row>
     <row r="268" spans="1:8">
       <c r="A268" s="2" t="s">
-        <v>474</v>
+        <v>795</v>
       </c>
       <c r="B268" s="1" t="s">
-        <v>476</v>
+        <v>787</v>
       </c>
       <c r="E268" s="1" t="s">
-        <v>1127</v>
+        <v>1123</v>
       </c>
       <c r="F268" s="2">
         <v>1</v>
       </c>
       <c r="H268" s="2" t="s">
-        <v>500</v>
+        <v>799</v>
       </c>
     </row>
     <row r="269" spans="1:8">
       <c r="A269" s="2" t="s">
-        <v>791</v>
+        <v>475</v>
       </c>
       <c r="B269" s="1" t="s">
-        <v>786</v>
+        <v>477</v>
       </c>
       <c r="E269" s="1" t="s">
-        <v>1128</v>
+        <v>1124</v>
       </c>
       <c r="F269" s="2">
         <v>1</v>
       </c>
       <c r="H269" s="2" t="s">
-        <v>800</v>
+        <v>501</v>
       </c>
     </row>
     <row r="270" spans="1:8">
       <c r="A270" s="2" t="s">
-        <v>239</v>
+        <v>792</v>
       </c>
       <c r="B270" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="C270" s="3">
-        <v>6</v>
-      </c>
-      <c r="D270" s="4">
-        <v>0</v>
+        <v>788</v>
       </c>
       <c r="E270" s="1" t="s">
-        <v>1130</v>
-      </c>
-      <c r="F270" s="3"/>
-      <c r="G270" s="1"/>
-      <c r="H270" s="1" t="s">
-        <v>426</v>
+        <v>1125</v>
+      </c>
+      <c r="F270" s="2">
+        <v>1</v>
+      </c>
+      <c r="H270" s="2" t="s">
+        <v>798</v>
       </c>
     </row>
     <row r="271" spans="1:8">
       <c r="A271" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="B271" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="E271" s="1" t="s">
+        <v>1126</v>
+      </c>
+      <c r="F271" s="2">
+        <v>1</v>
+      </c>
+      <c r="H271" s="2" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="272" spans="1:8">
+      <c r="A272" s="2" t="s">
+        <v>791</v>
+      </c>
+      <c r="B272" s="1" t="s">
+        <v>786</v>
+      </c>
+      <c r="E272" s="1" t="s">
+        <v>1127</v>
+      </c>
+      <c r="F272" s="2">
+        <v>1</v>
+      </c>
+      <c r="H272" s="2" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="273" spans="1:8">
+      <c r="A273" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="B271" s="1" t="s">
+      <c r="B273" s="1" t="s">
         <v>114</v>
-      </c>
-      <c r="C271" s="3">
-        <v>13</v>
-      </c>
-      <c r="D271" s="4">
-        <v>0</v>
-      </c>
-      <c r="E271" s="1" t="s">
-        <v>1129</v>
-      </c>
-      <c r="F271" s="3"/>
-      <c r="G271" s="1"/>
-      <c r="H271" s="1" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="272" spans="1:8">
-      <c r="A272" t="s">
-        <v>240</v>
-      </c>
-      <c r="B272" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C272" s="3">
-        <v>6</v>
-      </c>
-      <c r="D272" s="4">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="E272" s="1" t="s">
-        <v>1131</v>
-      </c>
-      <c r="F272" s="3"/>
-      <c r="G272" s="1"/>
-      <c r="H272" s="2" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="273" spans="1:8">
-      <c r="A273" t="s">
-        <v>241</v>
-      </c>
-      <c r="B273" s="1" t="s">
-        <v>18</v>
       </c>
       <c r="C273" s="3">
         <v>6</v>
       </c>
       <c r="D273" s="4">
-        <v>0.41666666666666669</v>
+        <v>0</v>
       </c>
       <c r="E273" s="1" t="s">
-        <v>1132</v>
+        <v>1129</v>
       </c>
       <c r="F273" s="3"/>
       <c r="G273" s="1"/>
-      <c r="H273" s="2" t="s">
-        <v>427</v>
+      <c r="H273" s="1" t="s">
+        <v>426</v>
       </c>
     </row>
     <row r="274" spans="1:8">
-      <c r="A274" t="s">
-        <v>242</v>
+      <c r="A274" s="2" t="s">
+        <v>239</v>
       </c>
       <c r="B274" s="1" t="s">
-        <v>16</v>
+        <v>114</v>
       </c>
       <c r="C274" s="3">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D274" s="4">
-        <v>0.47916666666666669</v>
+        <v>0</v>
       </c>
       <c r="E274" s="1" t="s">
-        <v>1133</v>
+        <v>1128</v>
       </c>
       <c r="F274" s="3"/>
       <c r="G274" s="1"/>
-      <c r="H274" s="2" t="s">
-        <v>427</v>
+      <c r="H274" s="1" t="s">
+        <v>426</v>
       </c>
     </row>
     <row r="275" spans="1:8">
       <c r="A275" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="B275" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C275" s="3">
         <v>6</v>
@@ -10311,7 +10357,7 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="E275" s="1" t="s">
-        <v>1134</v>
+        <v>1130</v>
       </c>
       <c r="F275" s="3"/>
       <c r="G275" s="1"/>
@@ -10321,19 +10367,19 @@
     </row>
     <row r="276" spans="1:8">
       <c r="A276" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="B276" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C276" s="3">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D276" s="4">
-        <v>0.75</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="E276" s="1" t="s">
-        <v>1135</v>
+        <v>1131</v>
       </c>
       <c r="F276" s="3"/>
       <c r="G276" s="1"/>
@@ -10343,19 +10389,19 @@
     </row>
     <row r="277" spans="1:8">
       <c r="A277" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="B277" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C277" s="3">
         <v>6</v>
       </c>
       <c r="D277" s="4">
-        <v>0.4375</v>
+        <v>0.47916666666666669</v>
       </c>
       <c r="E277" s="1" t="s">
-        <v>1136</v>
+        <v>1132</v>
       </c>
       <c r="F277" s="3"/>
       <c r="G277" s="1"/>
@@ -10365,19 +10411,19 @@
     </row>
     <row r="278" spans="1:8">
       <c r="A278" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="B278" s="1" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="C278" s="3">
         <v>6</v>
       </c>
       <c r="D278" s="4">
-        <v>0.5625</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="E278" s="1" t="s">
-        <v>1137</v>
+        <v>1133</v>
       </c>
       <c r="F278" s="3"/>
       <c r="G278" s="1"/>
@@ -10386,11 +10432,11 @@
       </c>
     </row>
     <row r="279" spans="1:8">
-      <c r="A279" s="2" t="s">
-        <v>282</v>
+      <c r="A279" t="s">
+        <v>244</v>
       </c>
       <c r="B279" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C279" s="3">
         <v>13</v>
@@ -10399,7 +10445,7 @@
         <v>0.75</v>
       </c>
       <c r="E279" s="1" t="s">
-        <v>1138</v>
+        <v>1134</v>
       </c>
       <c r="F279" s="3"/>
       <c r="G279" s="1"/>
@@ -10409,19 +10455,19 @@
     </row>
     <row r="280" spans="1:8">
       <c r="A280" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B280" s="1" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C280" s="3">
         <v>6</v>
       </c>
       <c r="D280" s="4">
-        <v>0.41666666666666669</v>
+        <v>0.4375</v>
       </c>
       <c r="E280" s="1" t="s">
-        <v>1139</v>
+        <v>1135</v>
       </c>
       <c r="F280" s="3"/>
       <c r="G280" s="1"/>
@@ -10430,20 +10476,20 @@
       </c>
     </row>
     <row r="281" spans="1:8">
-      <c r="A281" s="2" t="s">
-        <v>283</v>
+      <c r="A281" t="s">
+        <v>246</v>
       </c>
       <c r="B281" s="1" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C281" s="3">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D281" s="4">
-        <v>0.75</v>
+        <v>0.5625</v>
       </c>
       <c r="E281" s="1" t="s">
-        <v>1140</v>
+        <v>1136</v>
       </c>
       <c r="F281" s="3"/>
       <c r="G281" s="1"/>
@@ -10452,20 +10498,20 @@
       </c>
     </row>
     <row r="282" spans="1:8">
-      <c r="A282" t="s">
-        <v>248</v>
+      <c r="A282" s="2" t="s">
+        <v>282</v>
       </c>
       <c r="B282" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C282" s="3">
         <v>13</v>
       </c>
       <c r="D282" s="4">
-        <v>0.83333333333333337</v>
+        <v>0.75</v>
       </c>
       <c r="E282" s="1" t="s">
-        <v>1141</v>
+        <v>1137</v>
       </c>
       <c r="F282" s="3"/>
       <c r="G282" s="1"/>
@@ -10475,19 +10521,19 @@
     </row>
     <row r="283" spans="1:8">
       <c r="A283" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B283" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C283" s="3">
         <v>6</v>
       </c>
       <c r="D283" s="4">
-        <v>0.45833333333333331</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="E283" s="1" t="s">
-        <v>1184</v>
+        <v>1138</v>
       </c>
       <c r="F283" s="3"/>
       <c r="G283" s="1"/>
@@ -10497,218 +10543,222 @@
     </row>
     <row r="284" spans="1:8">
       <c r="A284" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="B284" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C284" s="3">
+        <v>13</v>
+      </c>
+      <c r="D284" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="E284" s="1" t="s">
+        <v>1139</v>
+      </c>
+      <c r="F284" s="3"/>
+      <c r="G284" s="1"/>
+      <c r="H284" s="2" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="285" spans="1:8">
+      <c r="A285" t="s">
+        <v>248</v>
+      </c>
+      <c r="B285" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C285" s="3">
+        <v>13</v>
+      </c>
+      <c r="D285" s="4">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="E285" s="1" t="s">
+        <v>1140</v>
+      </c>
+      <c r="F285" s="3"/>
+      <c r="G285" s="1"/>
+      <c r="H285" s="2" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="286" spans="1:8">
+      <c r="A286" t="s">
+        <v>249</v>
+      </c>
+      <c r="B286" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C286" s="3">
+        <v>6</v>
+      </c>
+      <c r="D286" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="E286" s="1" t="s">
+        <v>1182</v>
+      </c>
+      <c r="F286" s="3"/>
+      <c r="G286" s="1"/>
+      <c r="H286" s="2" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="287" spans="1:8">
+      <c r="A287" s="2" t="s">
         <v>502</v>
       </c>
-      <c r="B284" s="1" t="s">
+      <c r="B287" s="1" t="s">
         <v>503</v>
       </c>
-      <c r="C284" s="2">
+      <c r="C287" s="2">
         <v>6</v>
       </c>
-      <c r="D284" s="6">
-        <v>0</v>
-      </c>
-      <c r="E284" s="1" t="s">
+      <c r="D287" s="6">
+        <v>0</v>
+      </c>
+      <c r="E287" s="1" t="s">
+        <v>1141</v>
+      </c>
+      <c r="F287" s="3"/>
+      <c r="H287" s="7" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="288" spans="1:8">
+      <c r="A288" s="2" t="s">
+        <v>835</v>
+      </c>
+      <c r="B288" s="1" t="s">
+        <v>784</v>
+      </c>
+      <c r="E288" s="1" t="s">
         <v>1142</v>
       </c>
-      <c r="F284" s="3"/>
-      <c r="H284" s="7" t="s">
-        <v>537</v>
-      </c>
-    </row>
-    <row r="285" spans="1:8">
-      <c r="A285" s="2" t="s">
-        <v>835</v>
-      </c>
-      <c r="B285" s="1" t="s">
-        <v>784</v>
-      </c>
-      <c r="E285" s="1" t="s">
-        <v>1143</v>
-      </c>
-      <c r="F285" s="2">
-        <v>1</v>
-      </c>
-      <c r="H285" s="2" t="s">
+      <c r="F288" s="2">
+        <v>1</v>
+      </c>
+      <c r="H288" s="2" t="s">
         <v>836</v>
-      </c>
-    </row>
-    <row r="286" spans="1:8" customFormat="1">
-      <c r="A286" s="2" t="s">
-        <v>845</v>
-      </c>
-      <c r="B286" s="1" t="s">
-        <v>777</v>
-      </c>
-      <c r="C286" s="2">
-        <v>14</v>
-      </c>
-      <c r="D286" s="6">
-        <v>0</v>
-      </c>
-      <c r="E286" s="1" t="s">
-        <v>1144</v>
-      </c>
-      <c r="F286" s="2"/>
-      <c r="G286" s="2"/>
-      <c r="H286" s="2" t="s">
-        <v>847</v>
-      </c>
-    </row>
-    <row r="287" spans="1:8" customFormat="1">
-      <c r="A287" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="B287" s="1" t="s">
-        <v>281</v>
-      </c>
-      <c r="C287" s="3">
-        <v>8</v>
-      </c>
-      <c r="D287" s="6">
-        <v>0</v>
-      </c>
-      <c r="E287" s="1" t="s">
-        <v>1145</v>
-      </c>
-      <c r="F287" s="3"/>
-      <c r="G287" s="2"/>
-      <c r="H287" s="1" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="288" spans="1:8" customFormat="1">
-      <c r="A288" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="B288" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="C288" s="3">
-        <v>7</v>
-      </c>
-      <c r="D288" s="4">
-        <v>0</v>
-      </c>
-      <c r="E288" s="1" t="s">
-        <v>1146</v>
-      </c>
-      <c r="F288" s="3"/>
-      <c r="G288" s="1"/>
-      <c r="H288" t="s">
-        <v>545</v>
       </c>
     </row>
     <row r="289" spans="1:8" customFormat="1">
       <c r="A289" s="2" t="s">
+        <v>845</v>
+      </c>
+      <c r="B289" s="1" t="s">
+        <v>777</v>
+      </c>
+      <c r="C289" s="2">
+        <v>14</v>
+      </c>
+      <c r="D289" s="6">
+        <v>0</v>
+      </c>
+      <c r="E289" s="1" t="s">
+        <v>1143</v>
+      </c>
+      <c r="F289" s="2"/>
+      <c r="G289" s="2"/>
+      <c r="H289" s="2" t="s">
+        <v>847</v>
+      </c>
+    </row>
+    <row r="290" spans="1:8" customFormat="1">
+      <c r="A290" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="B290" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="C290" s="3">
+        <v>8</v>
+      </c>
+      <c r="D290" s="6">
+        <v>0</v>
+      </c>
+      <c r="E290" s="1" t="s">
+        <v>1144</v>
+      </c>
+      <c r="F290" s="3"/>
+      <c r="G290" s="2"/>
+      <c r="H290" s="1" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="291" spans="1:8" customFormat="1">
+      <c r="A291" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="B291" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="C291" s="3">
+        <v>7</v>
+      </c>
+      <c r="D291" s="4">
+        <v>0</v>
+      </c>
+      <c r="E291" s="1" t="s">
+        <v>1145</v>
+      </c>
+      <c r="F291" s="3"/>
+      <c r="G291" s="1"/>
+      <c r="H291" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="292" spans="1:8" customFormat="1">
+      <c r="A292" s="2" t="s">
         <v>322</v>
       </c>
-      <c r="B289" s="1" t="s">
+      <c r="B292" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="C289" s="3">
+      <c r="C292" s="3">
         <v>7</v>
       </c>
-      <c r="D289" s="4">
-        <v>0</v>
-      </c>
-      <c r="E289" s="1" t="s">
-        <v>1147</v>
-      </c>
-      <c r="F289" s="3"/>
-      <c r="G289" s="1"/>
-      <c r="H289" s="1" t="s">
+      <c r="D292" s="4">
+        <v>0</v>
+      </c>
+      <c r="E292" s="1" t="s">
+        <v>1146</v>
+      </c>
+      <c r="F292" s="3"/>
+      <c r="G292" s="1"/>
+      <c r="H292" s="1" t="s">
         <v>430</v>
-      </c>
-    </row>
-    <row r="290" spans="1:8">
-      <c r="A290" s="2" t="s">
-        <v>830</v>
-      </c>
-      <c r="B290" s="1" t="s">
-        <v>831</v>
-      </c>
-      <c r="C290" s="2">
-        <v>12</v>
-      </c>
-      <c r="D290" s="6">
-        <v>0</v>
-      </c>
-      <c r="E290" s="1" t="s">
-        <v>1148</v>
-      </c>
-      <c r="H290" s="7" t="s">
-        <v>832</v>
-      </c>
-    </row>
-    <row r="291" spans="1:8">
-      <c r="A291" s="2" t="s">
-        <v>584</v>
-      </c>
-      <c r="B291" s="1" t="s">
-        <v>583</v>
-      </c>
-      <c r="C291" s="2">
-        <v>6</v>
-      </c>
-      <c r="D291" s="6">
-        <v>0</v>
-      </c>
-      <c r="E291" s="1" t="s">
-        <v>1149</v>
-      </c>
-      <c r="F291" s="3"/>
-      <c r="H291" s="7" t="s">
-        <v>585</v>
-      </c>
-    </row>
-    <row r="292" spans="1:8">
-      <c r="A292" s="2" t="s">
-        <v>829</v>
-      </c>
-      <c r="B292" s="1" t="s">
-        <v>779</v>
-      </c>
-      <c r="C292" s="2">
-        <v>14</v>
-      </c>
-      <c r="D292" s="6">
-        <v>0</v>
-      </c>
-      <c r="E292" s="1" t="s">
-        <v>1150</v>
-      </c>
-      <c r="H292" s="2" t="s">
-        <v>828</v>
       </c>
     </row>
     <row r="293" spans="1:8">
       <c r="A293" s="2" t="s">
-        <v>546</v>
+        <v>830</v>
       </c>
       <c r="B293" s="1" t="s">
-        <v>538</v>
+        <v>831</v>
       </c>
       <c r="C293" s="2">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D293" s="6">
         <v>0</v>
       </c>
-      <c r="E293" s="10" t="s">
-        <v>1151</v>
-      </c>
-      <c r="F293" s="3"/>
-      <c r="H293" s="2" t="s">
-        <v>549</v>
+      <c r="E293" s="1" t="s">
+        <v>1147</v>
+      </c>
+      <c r="H293" s="7" t="s">
+        <v>832</v>
       </c>
     </row>
     <row r="294" spans="1:8">
       <c r="A294" s="2" t="s">
-        <v>547</v>
+        <v>584</v>
       </c>
       <c r="B294" s="1" t="s">
-        <v>539</v>
+        <v>583</v>
       </c>
       <c r="C294" s="2">
         <v>6</v>
@@ -10717,167 +10767,163 @@
         <v>0</v>
       </c>
       <c r="E294" s="1" t="s">
-        <v>1152</v>
+        <v>1188</v>
       </c>
       <c r="F294" s="3"/>
-      <c r="H294" s="2" t="s">
-        <v>549</v>
+      <c r="H294" s="7" t="s">
+        <v>585</v>
       </c>
     </row>
     <row r="295" spans="1:8">
       <c r="A295" s="2" t="s">
-        <v>548</v>
+        <v>829</v>
       </c>
       <c r="B295" s="1" t="s">
-        <v>540</v>
+        <v>779</v>
       </c>
       <c r="C295" s="2">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="D295" s="6">
         <v>0</v>
       </c>
       <c r="E295" s="1" t="s">
-        <v>1153</v>
-      </c>
-      <c r="F295" s="3"/>
+        <v>1148</v>
+      </c>
       <c r="H295" s="2" t="s">
-        <v>549</v>
+        <v>828</v>
       </c>
     </row>
     <row r="296" spans="1:8">
       <c r="A296" s="2" t="s">
-        <v>492</v>
+        <v>546</v>
       </c>
       <c r="B296" s="1" t="s">
-        <v>333</v>
-      </c>
-      <c r="C296" s="3"/>
-      <c r="D296" s="6"/>
-      <c r="E296" s="1" t="s">
-        <v>1154</v>
-      </c>
-      <c r="F296" s="3">
-        <v>1</v>
-      </c>
-      <c r="G296" s="2" t="s">
-        <v>811</v>
-      </c>
-      <c r="H296" t="s">
-        <v>462</v>
+        <v>538</v>
+      </c>
+      <c r="C296" s="2">
+        <v>6</v>
+      </c>
+      <c r="D296" s="6">
+        <v>0</v>
+      </c>
+      <c r="E296" s="10" t="s">
+        <v>1149</v>
+      </c>
+      <c r="F296" s="3"/>
+      <c r="H296" s="2" t="s">
+        <v>549</v>
       </c>
     </row>
     <row r="297" spans="1:8">
       <c r="A297" s="2" t="s">
+        <v>547</v>
+      </c>
+      <c r="B297" s="1" t="s">
+        <v>539</v>
+      </c>
+      <c r="C297" s="2">
+        <v>6</v>
+      </c>
+      <c r="D297" s="6">
+        <v>0</v>
+      </c>
+      <c r="E297" s="1" t="s">
+        <v>1150</v>
+      </c>
+      <c r="F297" s="3"/>
+      <c r="H297" s="2" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="298" spans="1:8">
+      <c r="A298" s="2" t="s">
+        <v>548</v>
+      </c>
+      <c r="B298" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="C298" s="2">
+        <v>6</v>
+      </c>
+      <c r="D298" s="6">
+        <v>0</v>
+      </c>
+      <c r="E298" s="1" t="s">
+        <v>1151</v>
+      </c>
+      <c r="F298" s="3"/>
+      <c r="H298" s="2" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="299" spans="1:8">
+      <c r="A299" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="B299" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="C299" s="3"/>
+      <c r="D299" s="6"/>
+      <c r="E299" s="1" t="s">
+        <v>1152</v>
+      </c>
+      <c r="F299" s="3">
+        <v>1</v>
+      </c>
+      <c r="G299" s="2" t="s">
+        <v>811</v>
+      </c>
+      <c r="H299" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="300" spans="1:8">
+      <c r="A300" s="2" t="s">
         <v>837</v>
       </c>
-      <c r="B297" s="1" t="s">
+      <c r="B300" s="1" t="s">
         <v>785</v>
       </c>
-      <c r="E297" s="1" t="s">
-        <v>1155</v>
-      </c>
-      <c r="F297" s="2">
-        <v>1</v>
-      </c>
-      <c r="H297" s="2" t="s">
+      <c r="E300" s="1" t="s">
+        <v>1153</v>
+      </c>
+      <c r="F300" s="2">
+        <v>1</v>
+      </c>
+      <c r="H300" s="2" t="s">
         <v>838</v>
-      </c>
-    </row>
-    <row r="298" spans="1:8">
-      <c r="A298" t="s">
-        <v>250</v>
-      </c>
-      <c r="B298" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="C298" s="3">
-        <v>6</v>
-      </c>
-      <c r="D298" s="4">
-        <v>0</v>
-      </c>
-      <c r="E298" s="1" t="s">
-        <v>1156</v>
-      </c>
-      <c r="F298" s="3"/>
-      <c r="G298" s="1"/>
-      <c r="H298" s="1" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="299" spans="1:8">
-      <c r="A299" t="s">
-        <v>251</v>
-      </c>
-      <c r="B299" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="C299" s="3">
-        <v>6</v>
-      </c>
-      <c r="D299" s="4">
-        <v>0</v>
-      </c>
-      <c r="E299" s="1" t="s">
-        <v>1157</v>
-      </c>
-      <c r="F299" s="3"/>
-      <c r="G299" s="1"/>
-      <c r="H299" s="1" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="300" spans="1:8">
-      <c r="A300" t="s">
-        <v>252</v>
-      </c>
-      <c r="B300" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="C300" s="3">
-        <v>6</v>
-      </c>
-      <c r="D300" s="4">
-        <v>0</v>
-      </c>
-      <c r="E300" s="1" t="s">
-        <v>1158</v>
-      </c>
-      <c r="F300" s="3"/>
-      <c r="G300" s="1"/>
-      <c r="H300" s="1" t="s">
-        <v>431</v>
       </c>
     </row>
     <row r="301" spans="1:8">
       <c r="A301" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="B301" s="1" t="s">
-        <v>70</v>
+        <v>106</v>
       </c>
       <c r="C301" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D301" s="4">
-        <v>0.97916666666666663</v>
+        <v>0</v>
       </c>
       <c r="E301" s="1" t="s">
-        <v>1159</v>
+        <v>1154</v>
       </c>
       <c r="F301" s="3"/>
       <c r="G301" s="1"/>
       <c r="H301" s="1" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="302" spans="1:8">
-      <c r="A302" s="2" t="s">
-        <v>285</v>
+      <c r="A302" t="s">
+        <v>251</v>
       </c>
       <c r="B302" s="1" t="s">
-        <v>37</v>
+        <v>105</v>
       </c>
       <c r="C302" s="3">
         <v>6</v>
@@ -10886,64 +10932,64 @@
         <v>0</v>
       </c>
       <c r="E302" s="1" t="s">
-        <v>1160</v>
+        <v>1155</v>
       </c>
       <c r="F302" s="3"/>
       <c r="G302" s="1"/>
-      <c r="H302" s="2" t="s">
-        <v>433</v>
+      <c r="H302" s="1" t="s">
+        <v>431</v>
       </c>
     </row>
     <row r="303" spans="1:8">
-      <c r="A303" s="2" t="s">
-        <v>286</v>
+      <c r="A303" t="s">
+        <v>252</v>
       </c>
       <c r="B303" s="1" t="s">
-        <v>38</v>
+        <v>107</v>
       </c>
       <c r="C303" s="3">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D303" s="4">
         <v>0</v>
       </c>
       <c r="E303" s="1" t="s">
-        <v>1161</v>
+        <v>1156</v>
       </c>
       <c r="F303" s="3"/>
       <c r="G303" s="1"/>
-      <c r="H303" s="2" t="s">
-        <v>434</v>
+      <c r="H303" s="1" t="s">
+        <v>431</v>
       </c>
     </row>
     <row r="304" spans="1:8">
-      <c r="A304" s="2" t="s">
-        <v>287</v>
+      <c r="A304" t="s">
+        <v>253</v>
       </c>
       <c r="B304" s="1" t="s">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="C304" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D304" s="4">
-        <v>0</v>
+        <v>0.97916666666666663</v>
       </c>
       <c r="E304" s="1" t="s">
-        <v>1162</v>
+        <v>1157</v>
       </c>
       <c r="F304" s="3"/>
       <c r="G304" s="1"/>
-      <c r="H304" s="2" t="s">
-        <v>435</v>
+      <c r="H304" s="1" t="s">
+        <v>432</v>
       </c>
     </row>
     <row r="305" spans="1:8">
       <c r="A305" s="2" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="B305" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C305" s="3">
         <v>6</v>
@@ -10952,42 +10998,42 @@
         <v>0</v>
       </c>
       <c r="E305" s="1" t="s">
-        <v>1163</v>
+        <v>1158</v>
       </c>
       <c r="F305" s="3"/>
       <c r="G305" s="1"/>
       <c r="H305" s="2" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
     </row>
     <row r="306" spans="1:8">
       <c r="A306" s="2" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="B306" s="1" t="s">
-        <v>750</v>
+        <v>38</v>
       </c>
       <c r="C306" s="3">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D306" s="4">
         <v>0</v>
       </c>
       <c r="E306" s="1" t="s">
-        <v>1164</v>
+        <v>1159</v>
       </c>
       <c r="F306" s="3"/>
       <c r="G306" s="1"/>
       <c r="H306" s="2" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
     </row>
     <row r="307" spans="1:8">
       <c r="A307" s="2" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="B307" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C307" s="3">
         <v>6</v>
@@ -10996,103 +11042,103 @@
         <v>0</v>
       </c>
       <c r="E307" s="1" t="s">
-        <v>1165</v>
+        <v>1160</v>
       </c>
       <c r="F307" s="3"/>
       <c r="G307" s="1"/>
       <c r="H307" s="2" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
     </row>
     <row r="308" spans="1:8">
       <c r="A308" s="2" t="s">
-        <v>757</v>
+        <v>288</v>
       </c>
       <c r="B308" s="1" t="s">
-        <v>756</v>
+        <v>39</v>
+      </c>
+      <c r="C308" s="3">
+        <v>6</v>
+      </c>
+      <c r="D308" s="4">
+        <v>0</v>
       </c>
       <c r="E308" s="1" t="s">
-        <v>1166</v>
-      </c>
-      <c r="F308" s="2">
-        <v>1</v>
-      </c>
-      <c r="H308" s="7" t="s">
-        <v>758</v>
+        <v>1161</v>
+      </c>
+      <c r="F308" s="3"/>
+      <c r="G308" s="1"/>
+      <c r="H308" s="2" t="s">
+        <v>436</v>
       </c>
     </row>
     <row r="309" spans="1:8">
       <c r="A309" s="2" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B309" s="1" t="s">
-        <v>52</v>
+        <v>750</v>
       </c>
       <c r="C309" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D309" s="4">
         <v>0</v>
       </c>
       <c r="E309" s="1" t="s">
-        <v>1167</v>
+        <v>1162</v>
       </c>
       <c r="F309" s="3"/>
       <c r="G309" s="1"/>
-      <c r="H309" t="s">
-        <v>447</v>
+      <c r="H309" s="2" t="s">
+        <v>437</v>
       </c>
     </row>
     <row r="310" spans="1:8">
       <c r="A310" s="2" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B310" s="1" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="C310" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D310" s="4">
         <v>0</v>
       </c>
       <c r="E310" s="1" t="s">
-        <v>1168</v>
+        <v>1163</v>
       </c>
       <c r="F310" s="3"/>
       <c r="G310" s="1"/>
-      <c r="H310" t="s">
-        <v>447</v>
+      <c r="H310" s="2" t="s">
+        <v>438</v>
       </c>
     </row>
     <row r="311" spans="1:8">
       <c r="A311" s="2" t="s">
-        <v>293</v>
+        <v>757</v>
       </c>
       <c r="B311" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C311" s="3">
-        <v>7</v>
-      </c>
-      <c r="D311" s="4">
-        <v>0</v>
+        <v>756</v>
       </c>
       <c r="E311" s="1" t="s">
-        <v>1169</v>
-      </c>
-      <c r="F311" s="3"/>
-      <c r="G311" s="1"/>
-      <c r="H311" s="1" t="s">
-        <v>447</v>
+        <v>1164</v>
+      </c>
+      <c r="F311" s="2">
+        <v>1</v>
+      </c>
+      <c r="H311" s="7" t="s">
+        <v>758</v>
       </c>
     </row>
     <row r="312" spans="1:8">
       <c r="A312" s="2" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="B312" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C312" s="3">
         <v>7</v>
@@ -11101,20 +11147,20 @@
         <v>0</v>
       </c>
       <c r="E312" s="1" t="s">
-        <v>1170</v>
+        <v>1165</v>
       </c>
       <c r="F312" s="3"/>
       <c r="G312" s="1"/>
-      <c r="H312" s="1" t="s">
+      <c r="H312" t="s">
         <v>447</v>
       </c>
     </row>
     <row r="313" spans="1:8">
       <c r="A313" s="2" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="B313" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C313" s="3">
         <v>7</v>
@@ -11123,20 +11169,20 @@
         <v>0</v>
       </c>
       <c r="E313" s="1" t="s">
-        <v>1171</v>
+        <v>1166</v>
       </c>
       <c r="F313" s="3"/>
       <c r="G313" s="1"/>
-      <c r="H313" s="1" t="s">
+      <c r="H313" t="s">
         <v>447</v>
       </c>
     </row>
     <row r="314" spans="1:8">
       <c r="A314" s="2" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="B314" s="1" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="C314" s="3">
         <v>7</v>
@@ -11145,7 +11191,7 @@
         <v>0</v>
       </c>
       <c r="E314" s="1" t="s">
-        <v>1172</v>
+        <v>1167</v>
       </c>
       <c r="F314" s="3"/>
       <c r="G314" s="1"/>
@@ -11155,10 +11201,10 @@
     </row>
     <row r="315" spans="1:8">
       <c r="A315" s="2" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="B315" s="1" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="C315" s="3">
         <v>7</v>
@@ -11167,7 +11213,7 @@
         <v>0</v>
       </c>
       <c r="E315" s="1" t="s">
-        <v>1173</v>
+        <v>1168</v>
       </c>
       <c r="F315" s="3"/>
       <c r="G315" s="1"/>
@@ -11177,10 +11223,10 @@
     </row>
     <row r="316" spans="1:8">
       <c r="A316" s="2" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="B316" s="1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C316" s="3">
         <v>7</v>
@@ -11189,20 +11235,20 @@
         <v>0</v>
       </c>
       <c r="E316" s="1" t="s">
-        <v>1174</v>
+        <v>1169</v>
       </c>
       <c r="F316" s="3"/>
       <c r="G316" s="1"/>
-      <c r="H316" s="8" t="s">
+      <c r="H316" s="1" t="s">
         <v>447</v>
       </c>
     </row>
     <row r="317" spans="1:8">
       <c r="A317" s="2" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="B317" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C317" s="3">
         <v>7</v>
@@ -11211,7 +11257,7 @@
         <v>0</v>
       </c>
       <c r="E317" s="1" t="s">
-        <v>1175</v>
+        <v>1170</v>
       </c>
       <c r="F317" s="3"/>
       <c r="G317" s="1"/>
@@ -11220,99 +11266,99 @@
       </c>
     </row>
     <row r="318" spans="1:8">
-      <c r="A318" t="s">
-        <v>254</v>
+      <c r="A318" s="2" t="s">
+        <v>297</v>
       </c>
       <c r="B318" s="1" t="s">
-        <v>144</v>
+        <v>56</v>
       </c>
       <c r="C318" s="3">
-        <v>13</v>
-      </c>
-      <c r="D318" s="5">
+        <v>7</v>
+      </c>
+      <c r="D318" s="4">
         <v>0</v>
       </c>
       <c r="E318" s="1" t="s">
-        <v>1176</v>
+        <v>1171</v>
       </c>
       <c r="F318" s="3"/>
       <c r="G318" s="1"/>
       <c r="H318" s="1" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="319" spans="1:8">
-      <c r="A319" t="s">
-        <v>325</v>
+      <c r="A319" s="2" t="s">
+        <v>298</v>
       </c>
       <c r="B319" s="1" t="s">
-        <v>108</v>
+        <v>51</v>
       </c>
       <c r="C319" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D319" s="4">
         <v>0</v>
       </c>
       <c r="E319" s="1" t="s">
-        <v>1177</v>
+        <v>1172</v>
       </c>
       <c r="F319" s="3"/>
       <c r="G319" s="1"/>
-      <c r="H319" s="1" t="s">
-        <v>440</v>
+      <c r="H319" s="8" t="s">
+        <v>447</v>
       </c>
     </row>
     <row r="320" spans="1:8">
-      <c r="A320" t="s">
-        <v>326</v>
+      <c r="A320" s="2" t="s">
+        <v>299</v>
       </c>
       <c r="B320" s="1" t="s">
-        <v>109</v>
+        <v>58</v>
       </c>
       <c r="C320" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D320" s="4">
         <v>0</v>
       </c>
       <c r="E320" s="1" t="s">
-        <v>1178</v>
+        <v>1173</v>
       </c>
       <c r="F320" s="3"/>
       <c r="G320" s="1"/>
       <c r="H320" s="1" t="s">
-        <v>440</v>
+        <v>447</v>
       </c>
     </row>
     <row r="321" spans="1:8">
       <c r="A321" t="s">
-        <v>329</v>
+        <v>254</v>
       </c>
       <c r="B321" s="1" t="s">
-        <v>112</v>
+        <v>144</v>
       </c>
       <c r="C321" s="3">
-        <v>6</v>
-      </c>
-      <c r="D321" s="4">
+        <v>13</v>
+      </c>
+      <c r="D321" s="5">
         <v>0</v>
       </c>
       <c r="E321" s="1" t="s">
-        <v>1179</v>
+        <v>1174</v>
       </c>
       <c r="F321" s="3"/>
       <c r="G321" s="1"/>
       <c r="H321" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="322" spans="1:8">
       <c r="A322" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="B322" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C322" s="3">
         <v>6</v>
@@ -11321,7 +11367,7 @@
         <v>0</v>
       </c>
       <c r="E322" s="1" t="s">
-        <v>1180</v>
+        <v>1175</v>
       </c>
       <c r="F322" s="3"/>
       <c r="G322" s="1"/>
@@ -11331,10 +11377,10 @@
     </row>
     <row r="323" spans="1:8">
       <c r="A323" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B323" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C323" s="3">
         <v>6</v>
@@ -11343,7 +11389,7 @@
         <v>0</v>
       </c>
       <c r="E323" s="1" t="s">
-        <v>1181</v>
+        <v>1176</v>
       </c>
       <c r="F323" s="3"/>
       <c r="G323" s="1"/>
@@ -11353,141 +11399,228 @@
     </row>
     <row r="324" spans="1:8">
       <c r="A324" t="s">
-        <v>255</v>
+        <v>329</v>
       </c>
       <c r="B324" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="C324" s="1"/>
-      <c r="D324" s="1"/>
+        <v>112</v>
+      </c>
+      <c r="C324" s="3">
+        <v>6</v>
+      </c>
+      <c r="D324" s="4">
+        <v>0</v>
+      </c>
       <c r="E324" s="1" t="s">
-        <v>1182</v>
-      </c>
-      <c r="F324" s="1">
-        <v>1</v>
-      </c>
+        <v>1177</v>
+      </c>
+      <c r="F324" s="3"/>
       <c r="G324" s="1"/>
       <c r="H324" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="325" spans="1:8">
-      <c r="A325" s="2" t="s">
-        <v>857</v>
+      <c r="A325" t="s">
+        <v>328</v>
       </c>
       <c r="B325" s="1" t="s">
-        <v>854</v>
+        <v>111</v>
       </c>
       <c r="C325" s="3">
         <v>6</v>
       </c>
-      <c r="D325" s="6">
+      <c r="D325" s="4">
         <v>0</v>
       </c>
       <c r="E325" s="1" t="s">
-        <v>1183</v>
-      </c>
-      <c r="H325" s="2" t="s">
-        <v>856</v>
+        <v>1178</v>
+      </c>
+      <c r="F325" s="3"/>
+      <c r="G325" s="1"/>
+      <c r="H325" s="1" t="s">
+        <v>440</v>
       </c>
     </row>
     <row r="326" spans="1:8">
-      <c r="A326" s="2" t="s">
-        <v>858</v>
+      <c r="A326" t="s">
+        <v>327</v>
       </c>
       <c r="B326" s="1" t="s">
-        <v>855</v>
+        <v>110</v>
       </c>
       <c r="C326" s="3">
         <v>6</v>
       </c>
-      <c r="D326" s="6">
+      <c r="D326" s="4">
         <v>0</v>
       </c>
       <c r="E326" s="1" t="s">
-        <v>1183</v>
-      </c>
-      <c r="H326" s="2" t="s">
-        <v>856</v>
+        <v>1179</v>
+      </c>
+      <c r="F326" s="3"/>
+      <c r="G326" s="1"/>
+      <c r="H326" s="1" t="s">
+        <v>440</v>
       </c>
     </row>
     <row r="327" spans="1:8">
-      <c r="A327" s="2" t="s">
-        <v>859</v>
+      <c r="A327" t="s">
+        <v>255</v>
       </c>
       <c r="B327" s="1" t="s">
-        <v>860</v>
-      </c>
-      <c r="C327" s="3">
-        <v>7</v>
-      </c>
-      <c r="D327" s="6">
-        <v>0</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="C327" s="1"/>
+      <c r="D327" s="1"/>
       <c r="E327" s="1" t="s">
-        <v>861</v>
-      </c>
-      <c r="H327" s="2" t="s">
-        <v>862</v>
+        <v>1180</v>
+      </c>
+      <c r="F327" s="1">
+        <v>1</v>
+      </c>
+      <c r="G327" s="1"/>
+      <c r="H327" s="1" t="s">
+        <v>441</v>
       </c>
     </row>
     <row r="328" spans="1:8">
       <c r="A328" s="2" t="s">
+        <v>857</v>
+      </c>
+      <c r="B328" s="1" t="s">
+        <v>854</v>
+      </c>
+      <c r="C328" s="3">
+        <v>6</v>
+      </c>
+      <c r="D328" s="6">
+        <v>0</v>
+      </c>
+      <c r="E328" s="1" t="s">
+        <v>1181</v>
+      </c>
+      <c r="H328" s="2" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="329" spans="1:8">
+      <c r="A329" s="2" t="s">
+        <v>858</v>
+      </c>
+      <c r="B329" s="1" t="s">
+        <v>855</v>
+      </c>
+      <c r="C329" s="3">
+        <v>6</v>
+      </c>
+      <c r="D329" s="6">
+        <v>0</v>
+      </c>
+      <c r="E329" s="1" t="s">
+        <v>1181</v>
+      </c>
+      <c r="H329" s="2" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="330" spans="1:8">
+      <c r="A330" s="2" t="s">
+        <v>859</v>
+      </c>
+      <c r="B330" s="1" t="s">
+        <v>860</v>
+      </c>
+      <c r="C330" s="3">
+        <v>7</v>
+      </c>
+      <c r="D330" s="6">
+        <v>0</v>
+      </c>
+      <c r="E330" s="1" t="s">
+        <v>861</v>
+      </c>
+      <c r="H330" s="2" t="s">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="331" spans="1:8">
+      <c r="A331" s="2" t="s">
+        <v>1184</v>
+      </c>
+      <c r="B331" s="1" t="s">
+        <v>1185</v>
+      </c>
+      <c r="C331" s="3">
+        <v>7</v>
+      </c>
+      <c r="D331" s="6">
+        <v>0</v>
+      </c>
+      <c r="E331" s="1" t="s">
         <v>1186</v>
       </c>
-      <c r="B328" s="1" t="s">
+      <c r="H331" s="7" t="s">
         <v>1187</v>
       </c>
-      <c r="C328" s="3">
-        <v>7</v>
-      </c>
-      <c r="D328" s="6">
-        <v>0</v>
-      </c>
-      <c r="E328" s="1" t="s">
-        <v>1188</v>
-      </c>
-      <c r="H328" s="7" t="s">
-        <v>1189</v>
+    </row>
+    <row r="332" spans="1:8">
+      <c r="A332" s="2" t="s">
+        <v>1198</v>
+      </c>
+      <c r="B332" s="1" t="s">
+        <v>1199</v>
+      </c>
+      <c r="C332" s="3">
+        <v>8</v>
+      </c>
+      <c r="D332" s="6">
+        <v>0</v>
+      </c>
+      <c r="E332" s="1" t="s">
+        <v>1200</v>
+      </c>
+      <c r="H332" s="7" t="s">
+        <v>1201</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H324">
-    <sortCondition ref="B2:B324"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H327">
+    <sortCondition ref="B2:B327"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="H316" r:id="rId1" xr:uid="{08510EB6-59FE-461F-9934-59900452DB70}"/>
-    <hyperlink ref="H243" r:id="rId2" xr:uid="{092C464B-EEF0-45C5-9E7F-9E5BB1389ECD}"/>
-    <hyperlink ref="H284" r:id="rId3" xr:uid="{D8D98BE9-F998-4931-BC78-1FA8DBB2DF8D}"/>
+    <hyperlink ref="H319" r:id="rId1" xr:uid="{08510EB6-59FE-461F-9934-59900452DB70}"/>
+    <hyperlink ref="H246" r:id="rId2" xr:uid="{092C464B-EEF0-45C5-9E7F-9E5BB1389ECD}"/>
+    <hyperlink ref="H287" r:id="rId3" xr:uid="{D8D98BE9-F998-4931-BC78-1FA8DBB2DF8D}"/>
     <hyperlink ref="H45" r:id="rId4" xr:uid="{3BEBF5F8-81B1-4909-98FA-8DDD635C8EA6}"/>
     <hyperlink ref="H44" r:id="rId5" xr:uid="{65D202DC-0DAE-445A-B96C-C36AAC898769}"/>
     <hyperlink ref="H116" r:id="rId6" xr:uid="{25A9BA66-0BC2-4AD9-A0BE-F4C36298AC2D}"/>
-    <hyperlink ref="H205:H217" r:id="rId7" display="http://www.murderparker.com/" xr:uid="{E958893D-4F52-4648-BDD7-4971EF621EF9}"/>
+    <hyperlink ref="H208:H220" r:id="rId7" display="http://www.murderparker.com/" xr:uid="{E958893D-4F52-4648-BDD7-4971EF621EF9}"/>
     <hyperlink ref="H34" r:id="rId8" xr:uid="{4B96B214-31AC-4DCE-B6F6-D54C0FEB4666}"/>
     <hyperlink ref="H129" r:id="rId9" xr:uid="{25B31E9F-543F-4E86-89DB-207AA2179ACF}"/>
-    <hyperlink ref="H206" r:id="rId10" xr:uid="{9827A6D5-ED28-4225-87FD-B74EDF207367}"/>
-    <hyperlink ref="H291" r:id="rId11" xr:uid="{5FF5509A-E557-47E9-9497-31CDE0FE2F49}"/>
+    <hyperlink ref="H209" r:id="rId10" xr:uid="{9827A6D5-ED28-4225-87FD-B74EDF207367}"/>
+    <hyperlink ref="H294" r:id="rId11" xr:uid="{5FF5509A-E557-47E9-9497-31CDE0FE2F49}"/>
     <hyperlink ref="H98" r:id="rId12" xr:uid="{C22B731B-9B71-4E64-B35B-0DA8918E1D6C}"/>
-    <hyperlink ref="H252" r:id="rId13" xr:uid="{9F031169-FBE6-490D-BE8C-7652770F2FC7}"/>
-    <hyperlink ref="H260" r:id="rId14" xr:uid="{8A0F8F21-47D9-40AB-B76D-AB1080B92C60}"/>
-    <hyperlink ref="H253" r:id="rId15" xr:uid="{D68E4B30-7851-4C83-872C-73CB17EC5222}"/>
+    <hyperlink ref="H255" r:id="rId13" xr:uid="{9F031169-FBE6-490D-BE8C-7652770F2FC7}"/>
+    <hyperlink ref="H263" r:id="rId14" xr:uid="{8A0F8F21-47D9-40AB-B76D-AB1080B92C60}"/>
+    <hyperlink ref="H256" r:id="rId15" xr:uid="{D68E4B30-7851-4C83-872C-73CB17EC5222}"/>
     <hyperlink ref="H18" r:id="rId16" xr:uid="{D73F1000-43A8-440E-9154-148CA29F608D}"/>
     <hyperlink ref="H123" r:id="rId17" xr:uid="{87D8789E-3527-45CB-96CC-A717E2A29CF4}"/>
-    <hyperlink ref="H308" r:id="rId18" xr:uid="{328A7EE8-6C93-4B2F-BFAA-D593F87BE671}"/>
-    <hyperlink ref="H261" r:id="rId19" xr:uid="{A3CEB787-A4DA-499F-A877-2709B0646565}"/>
-    <hyperlink ref="H218" r:id="rId20" xr:uid="{9AEB623B-37CB-4EFD-A4E5-06C08664DCD5}"/>
-    <hyperlink ref="H219" r:id="rId21" xr:uid="{38AF5094-2E8A-4F1F-8FBA-18FEBEAFFB8F}"/>
+    <hyperlink ref="H311" r:id="rId18" xr:uid="{328A7EE8-6C93-4B2F-BFAA-D593F87BE671}"/>
+    <hyperlink ref="H264" r:id="rId19" xr:uid="{A3CEB787-A4DA-499F-A877-2709B0646565}"/>
+    <hyperlink ref="H221" r:id="rId20" xr:uid="{9AEB623B-37CB-4EFD-A4E5-06C08664DCD5}"/>
+    <hyperlink ref="H222" r:id="rId21" xr:uid="{38AF5094-2E8A-4F1F-8FBA-18FEBEAFFB8F}"/>
     <hyperlink ref="H2" r:id="rId22" xr:uid="{5EA546E0-B128-4386-8445-FD73AAE43FAB}"/>
-    <hyperlink ref="H290" r:id="rId23" xr:uid="{A2E3DE51-C084-4528-998F-F094210AAA1D}"/>
-    <hyperlink ref="H230" r:id="rId24" xr:uid="{0A71BEFF-E769-421A-8079-F0AC7ECC9FE2}"/>
+    <hyperlink ref="H293" r:id="rId23" xr:uid="{A2E3DE51-C084-4528-998F-F094210AAA1D}"/>
+    <hyperlink ref="H233" r:id="rId24" xr:uid="{0A71BEFF-E769-421A-8079-F0AC7ECC9FE2}"/>
     <hyperlink ref="H42" r:id="rId25" xr:uid="{F2A9379F-C93A-48C6-B140-FD9A9AACF5E0}"/>
     <hyperlink ref="H43" r:id="rId26" xr:uid="{E90FCA6A-2CCD-4405-8CD0-447FE361C93D}"/>
-    <hyperlink ref="H244" r:id="rId27" xr:uid="{672E3111-F001-48E9-B557-648E8ECCC539}"/>
+    <hyperlink ref="H247" r:id="rId27" xr:uid="{672E3111-F001-48E9-B557-648E8ECCC539}"/>
     <hyperlink ref="H17" r:id="rId28" xr:uid="{6C38C4F4-6013-4ADB-86CA-36E82A9014E4}"/>
-    <hyperlink ref="H328" r:id="rId29" xr:uid="{B10E19EA-1086-4C62-A06E-EADC0D68A22A}"/>
+    <hyperlink ref="H331" r:id="rId29" xr:uid="{B10E19EA-1086-4C62-A06E-EADC0D68A22A}"/>
+    <hyperlink ref="H332" r:id="rId30" xr:uid="{42B4AACC-DBCA-4AD0-AE58-190A0A1836B2}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId30"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId31"/>
 </worksheet>
 </file>
--- a/stores.xlsx
+++ b/stores.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\YUMIN\Desktop\B0KT2A_RSVN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F520BBC6-7039-4EFF-9D38-F84D3A28954E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF0F471E-A5DF-4C44-8CFF-0691127337FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{ABFC3117-FCCB-4FF3-804A-FE19451A2004}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1339" uniqueCount="1202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1339" uniqueCount="1199">
   <si>
     <t>룸익스케이프 WHITE</t>
   </si>
@@ -1988,14 +1988,6 @@
     <t>http://www.thecode12.kr/</t>
   </si>
   <si>
-    <t>tcd_sl</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>더 코드 신림점</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>http://www.thecode11.kr/</t>
   </si>
   <si>
@@ -2016,10 +2008,6 @@
   </si>
   <si>
     <t>http://thecode06.kr/</t>
-  </si>
-  <si>
-    <t>http://thecode09.kr/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>http://thecode02.kr/</t>
@@ -2835,10 +2823,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>매월 1일 00:00 1일~말일 예약 오픈</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>매월 1일 18:00 1일~말일 예약 오픈</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -3159,10 +3143,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>아파트,위자보드:위험한장난,다시시작된살인사건,세기의명화를훔치는도둑들,의문의동창회</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>도둑들#2:다이어몬드블루문,피의일요일,냉동창고:살인사건#2,도박꾼:마지막베팅</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -4031,10 +4011,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>사요나라세이크,붐붐박사의불꽃놀이유토피아</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>창귀</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -4387,6 +4363,18 @@
   </si>
   <si>
     <t>https://naver.me/5o0Qylbb</t>
+  </si>
+  <si>
+    <t>매월 1일 00:00 다음 달 1일~말일 예약 오픈</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>붐붐박사의불꽃놀이유토피아</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>사요나라세이코</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -4857,39 +4845,39 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="2" t="s">
-        <v>803</v>
+        <v>800</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>804</v>
+        <v>801</v>
       </c>
       <c r="E2" t="s">
-        <v>863</v>
+        <v>859</v>
       </c>
       <c r="F2" s="2">
         <v>1</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>812</v>
+        <v>808</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>805</v>
+        <v>802</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="2" t="s">
-        <v>763</v>
+        <v>760</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>761</v>
+        <v>758</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>864</v>
+        <v>860</v>
       </c>
       <c r="F3" s="2">
         <v>1</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>767</v>
+        <v>764</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -4906,7 +4894,7 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>865</v>
+        <v>861</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>453</v>
@@ -4914,10 +4902,10 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="2" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="C5" s="2">
         <v>7</v>
@@ -4926,7 +4914,7 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>1189</v>
+        <v>1183</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>453</v>
@@ -4934,10 +4922,10 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="2" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="C6" s="2">
         <v>7</v>
@@ -4946,7 +4934,7 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>866</v>
+        <v>862</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>453</v>
@@ -4966,7 +4954,7 @@
         <v>0</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>867</v>
+        <v>863</v>
       </c>
       <c r="F7" s="3"/>
       <c r="G7" s="1"/>
@@ -4988,7 +4976,7 @@
         <v>0</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>868</v>
+        <v>864</v>
       </c>
       <c r="F8" s="3"/>
       <c r="G8" s="1"/>
@@ -5006,7 +4994,7 @@
       <c r="C9" s="3"/>
       <c r="D9" s="4"/>
       <c r="E9" s="2" t="s">
-        <v>869</v>
+        <v>865</v>
       </c>
       <c r="F9" s="3">
         <v>1</v>
@@ -5030,7 +5018,7 @@
         <v>0</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>870</v>
+        <v>866</v>
       </c>
       <c r="F10" s="3"/>
       <c r="G10" s="1"/>
@@ -5052,7 +5040,7 @@
         <v>0</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>871</v>
+        <v>867</v>
       </c>
       <c r="F11" s="3"/>
       <c r="G11" s="1"/>
@@ -5070,13 +5058,13 @@
       <c r="C12" s="3"/>
       <c r="D12" s="4"/>
       <c r="E12" s="2" t="s">
-        <v>872</v>
+        <v>868</v>
       </c>
       <c r="F12" s="3">
         <v>1</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>808</v>
+        <v>805</v>
       </c>
       <c r="H12" s="1" t="s">
         <v>341</v>
@@ -5092,13 +5080,13 @@
       <c r="C13" s="3"/>
       <c r="D13" s="4"/>
       <c r="E13" s="2" t="s">
-        <v>873</v>
+        <v>869</v>
       </c>
       <c r="F13" s="3">
         <v>1</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>808</v>
+        <v>805</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>342</v>
@@ -5118,7 +5106,7 @@
         <v>0</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>874</v>
+        <v>870</v>
       </c>
       <c r="F14" s="3"/>
       <c r="G14" s="1"/>
@@ -5140,7 +5128,7 @@
         <v>0</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
       <c r="F15" s="3"/>
       <c r="G15" s="1"/>
@@ -5162,7 +5150,7 @@
         <v>0</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>876</v>
+        <v>872</v>
       </c>
       <c r="F16" s="3"/>
       <c r="G16" s="1"/>
@@ -5184,12 +5172,12 @@
         <v>0</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>877</v>
+        <v>873</v>
       </c>
       <c r="F17" s="3"/>
       <c r="G17" s="1"/>
       <c r="H17" s="7" t="s">
-        <v>878</v>
+        <v>874</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -5206,12 +5194,12 @@
         <v>0</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>879</v>
+        <v>875</v>
       </c>
       <c r="F18" s="3"/>
       <c r="G18" s="1"/>
       <c r="H18" s="7" t="s">
-        <v>737</v>
+        <v>734</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -5228,7 +5216,7 @@
         <v>0</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>880</v>
+        <v>876</v>
       </c>
       <c r="F19" s="3"/>
       <c r="G19" s="1"/>
@@ -5250,7 +5238,7 @@
         <v>0</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>881</v>
+        <v>877</v>
       </c>
       <c r="F20" s="3"/>
       <c r="G20" s="1"/>
@@ -5272,7 +5260,7 @@
         <v>0</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
       <c r="F21" s="3"/>
       <c r="G21" s="1"/>
@@ -5294,7 +5282,7 @@
         <v>0</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>882</v>
+        <v>878</v>
       </c>
       <c r="F22" s="3"/>
       <c r="G22" s="1"/>
@@ -5316,7 +5304,7 @@
         <v>0</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>884</v>
+        <v>880</v>
       </c>
       <c r="F23" s="3"/>
       <c r="G23" s="1"/>
@@ -5334,7 +5322,7 @@
       <c r="C24" s="3"/>
       <c r="D24" s="4"/>
       <c r="E24" s="2" t="s">
-        <v>885</v>
+        <v>881</v>
       </c>
       <c r="F24" s="3">
         <v>1</v>
@@ -5358,7 +5346,7 @@
         <v>0</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>886</v>
+        <v>882</v>
       </c>
       <c r="F25" s="3"/>
       <c r="G25" s="1"/>
@@ -5380,7 +5368,7 @@
         <v>0</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>887</v>
+        <v>883</v>
       </c>
       <c r="F26" s="3"/>
       <c r="G26" s="1"/>
@@ -5390,10 +5378,10 @@
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="2" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="C27" s="3">
         <v>15</v>
@@ -5405,7 +5393,7 @@
       <c r="F27" s="3"/>
       <c r="G27" s="1"/>
       <c r="H27" s="11" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -5422,7 +5410,7 @@
         <v>0</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>888</v>
+        <v>884</v>
       </c>
       <c r="F28" s="3"/>
       <c r="H28" s="1" t="s">
@@ -5443,7 +5431,7 @@
         <v>0</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>889</v>
+        <v>885</v>
       </c>
       <c r="F29" s="3"/>
       <c r="H29" s="1" t="s">
@@ -5464,7 +5452,7 @@
         <v>0</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>890</v>
+        <v>886</v>
       </c>
       <c r="F30" s="3"/>
       <c r="G30" s="1"/>
@@ -5486,7 +5474,7 @@
         <v>0</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>891</v>
+        <v>887</v>
       </c>
       <c r="F31" s="3"/>
       <c r="G31" s="1"/>
@@ -5496,27 +5484,27 @@
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="2" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>892</v>
+        <v>888</v>
       </c>
       <c r="F32" s="3">
         <v>1</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="2" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="C33" s="2">
         <v>20</v>
@@ -5525,283 +5513,288 @@
         <v>0</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>893</v>
+        <v>889</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="2" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>894</v>
+        <v>890</v>
       </c>
       <c r="F34" s="3">
         <v>1</v>
       </c>
-      <c r="H34" s="7" t="s">
-        <v>564</v>
+      <c r="H34" s="2" t="s">
+        <v>555</v>
       </c>
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="2" t="s">
-        <v>553</v>
+        <v>559</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>554</v>
+        <v>560</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>895</v>
+        <v>891</v>
       </c>
       <c r="F35" s="3">
         <v>1</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>555</v>
+        <v>561</v>
       </c>
     </row>
     <row r="36" spans="1:8">
       <c r="A36" s="2" t="s">
-        <v>561</v>
+        <v>569</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>562</v>
+        <v>570</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>896</v>
+        <v>892</v>
       </c>
       <c r="F36" s="3">
         <v>1</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>563</v>
+        <v>568</v>
       </c>
     </row>
     <row r="37" spans="1:8">
       <c r="A37" s="2" t="s">
-        <v>572</v>
+        <v>566</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>573</v>
+        <v>567</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>897</v>
+        <v>893</v>
       </c>
       <c r="F37" s="3">
         <v>1</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>571</v>
+        <v>565</v>
       </c>
     </row>
     <row r="38" spans="1:8">
       <c r="A38" s="2" t="s">
-        <v>569</v>
+        <v>557</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>570</v>
+        <v>558</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>898</v>
+        <v>894</v>
       </c>
       <c r="F38" s="3">
         <v>1</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>568</v>
+        <v>556</v>
       </c>
     </row>
     <row r="39" spans="1:8">
       <c r="A39" s="2" t="s">
-        <v>559</v>
+        <v>829</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>560</v>
+        <v>777</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>899</v>
-      </c>
-      <c r="F39" s="3">
+        <v>895</v>
+      </c>
+      <c r="F39" s="2">
         <v>1</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>558</v>
+        <v>830</v>
       </c>
     </row>
     <row r="40" spans="1:8">
       <c r="A40" s="2" t="s">
-        <v>833</v>
+        <v>188</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>780</v>
+        <v>162</v>
+      </c>
+      <c r="C40" s="3">
+        <v>6</v>
+      </c>
+      <c r="D40" s="4">
+        <v>0</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>900</v>
-      </c>
-      <c r="F40" s="2">
-        <v>1</v>
-      </c>
+        <v>896</v>
+      </c>
+      <c r="F40" s="3"/>
+      <c r="G40" s="1"/>
       <c r="H40" s="2" t="s">
-        <v>834</v>
+        <v>355</v>
       </c>
     </row>
     <row r="41" spans="1:8">
       <c r="A41" s="2" t="s">
-        <v>188</v>
+        <v>840</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="C41" s="3">
-        <v>6</v>
-      </c>
-      <c r="D41" s="4">
-        <v>0</v>
+        <v>778</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>901</v>
-      </c>
-      <c r="F41" s="3"/>
-      <c r="G41" s="1"/>
-      <c r="H41" s="2" t="s">
-        <v>355</v>
+        <v>897</v>
+      </c>
+      <c r="F41" s="2">
+        <v>1</v>
+      </c>
+      <c r="H41" s="7" t="s">
+        <v>839</v>
       </c>
     </row>
     <row r="42" spans="1:8">
       <c r="A42" s="2" t="s">
+        <v>842</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>779</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>898</v>
+      </c>
+      <c r="F42" s="2">
+        <v>1</v>
+      </c>
+      <c r="H42" s="7" t="s">
         <v>844</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>781</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>902</v>
-      </c>
-      <c r="F42" s="2">
-        <v>1</v>
-      </c>
-      <c r="H42" s="7" t="s">
-        <v>843</v>
       </c>
     </row>
     <row r="43" spans="1:8">
       <c r="A43" s="2" t="s">
-        <v>846</v>
+        <v>496</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>782</v>
+        <v>497</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>903</v>
-      </c>
-      <c r="F43" s="2">
-        <v>1</v>
-      </c>
-      <c r="H43" s="7" t="s">
-        <v>848</v>
+        <v>899</v>
+      </c>
+      <c r="F43" s="3">
+        <v>1</v>
+      </c>
+      <c r="H43" s="9" t="s">
+        <v>536</v>
       </c>
     </row>
     <row r="44" spans="1:8">
       <c r="A44" s="2" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>904</v>
+        <v>900</v>
       </c>
       <c r="F44" s="3">
         <v>1</v>
       </c>
       <c r="H44" s="9" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="45" spans="1:8">
       <c r="A45" s="2" t="s">
-        <v>498</v>
+        <v>215</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>499</v>
+        <v>284</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>905</v>
+        <v>901</v>
       </c>
       <c r="F45" s="3">
         <v>1</v>
-      </c>
-      <c r="H45" s="9" t="s">
-        <v>535</v>
       </c>
     </row>
     <row r="46" spans="1:8">
       <c r="A46" s="2" t="s">
-        <v>215</v>
+        <v>189</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>284</v>
+        <v>77</v>
+      </c>
+      <c r="C46" s="3">
+        <v>6</v>
+      </c>
+      <c r="D46" s="4">
+        <v>0</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>906</v>
-      </c>
-      <c r="F46" s="3">
-        <v>1</v>
+        <v>902</v>
+      </c>
+      <c r="F46" s="3"/>
+      <c r="G46" s="1"/>
+      <c r="H46" s="1" t="s">
+        <v>356</v>
       </c>
     </row>
     <row r="47" spans="1:8">
       <c r="A47" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="C47" s="3">
-        <v>6</v>
-      </c>
-      <c r="D47" s="4">
-        <v>0</v>
-      </c>
+        <v>83</v>
+      </c>
+      <c r="C47" s="3"/>
+      <c r="D47" s="4"/>
       <c r="E47" s="2" t="s">
-        <v>907</v>
-      </c>
-      <c r="F47" s="3"/>
+        <v>903</v>
+      </c>
+      <c r="F47" s="3">
+        <v>1</v>
+      </c>
       <c r="G47" s="1"/>
       <c r="H47" s="1" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="48" spans="1:8">
       <c r="A48" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="C48" s="3"/>
-      <c r="D48" s="4"/>
+        <v>84</v>
+      </c>
+      <c r="C48" s="3">
+        <v>6</v>
+      </c>
+      <c r="D48" s="4">
+        <v>0</v>
+      </c>
       <c r="E48" s="2" t="s">
-        <v>908</v>
-      </c>
-      <c r="F48" s="3">
-        <v>1</v>
-      </c>
+        <v>904</v>
+      </c>
+      <c r="F48" s="3"/>
       <c r="G48" s="1"/>
       <c r="H48" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="49" spans="1:8">
       <c r="A49" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="C49" s="3">
         <v>6</v>
@@ -5810,20 +5803,20 @@
         <v>0</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>909</v>
+        <v>905</v>
       </c>
       <c r="F49" s="3"/>
       <c r="G49" s="1"/>
       <c r="H49" s="1" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="50" spans="1:8">
       <c r="A50" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C50" s="3">
         <v>6</v>
@@ -5832,42 +5825,40 @@
         <v>0</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="F50" s="3"/>
       <c r="G50" s="1"/>
       <c r="H50" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="51" spans="1:8">
       <c r="A51" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="C51" s="3">
-        <v>6</v>
-      </c>
-      <c r="D51" s="4">
-        <v>0</v>
-      </c>
+        <v>82</v>
+      </c>
+      <c r="C51" s="3"/>
+      <c r="D51" s="4"/>
       <c r="E51" s="2" t="s">
-        <v>911</v>
-      </c>
-      <c r="F51" s="3"/>
+        <v>907</v>
+      </c>
+      <c r="F51" s="3">
+        <v>1</v>
+      </c>
       <c r="G51" s="1"/>
       <c r="H51" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="52" spans="1:8">
       <c r="A52" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C52" s="3"/>
       <c r="D52" s="4"/>
@@ -5879,35 +5870,37 @@
       </c>
       <c r="G52" s="1"/>
       <c r="H52" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="53" spans="1:8">
       <c r="A53" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="C53" s="3"/>
-      <c r="D53" s="4"/>
+        <v>80</v>
+      </c>
+      <c r="C53" s="3">
+        <v>6</v>
+      </c>
+      <c r="D53" s="4">
+        <v>0</v>
+      </c>
       <c r="E53" s="2" t="s">
-        <v>917</v>
-      </c>
-      <c r="F53" s="3">
-        <v>1</v>
-      </c>
+        <v>913</v>
+      </c>
+      <c r="F53" s="3"/>
       <c r="G53" s="1"/>
       <c r="H53" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="54" spans="1:8">
       <c r="A54" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>80</v>
+        <v>4</v>
       </c>
       <c r="C54" s="3">
         <v>6</v>
@@ -5916,51 +5909,51 @@
         <v>0</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>918</v>
+        <v>908</v>
       </c>
       <c r="F54" s="3"/>
       <c r="G54" s="1"/>
-      <c r="H54" s="1" t="s">
-        <v>363</v>
+      <c r="H54" t="s">
+        <v>364</v>
       </c>
     </row>
     <row r="55" spans="1:8">
       <c r="A55" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>4</v>
+        <v>132</v>
       </c>
       <c r="C55" s="3">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="D55" s="4">
         <v>0</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>913</v>
+        <v>909</v>
       </c>
       <c r="F55" s="3"/>
       <c r="G55" s="1"/>
       <c r="H55" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="56" spans="1:8">
       <c r="A56" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C56" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D56" s="4">
-        <v>0</v>
+        <v>0.95833333333333337</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>914</v>
+        <v>910</v>
       </c>
       <c r="F56" s="3"/>
       <c r="G56" s="1"/>
@@ -5970,19 +5963,19 @@
     </row>
     <row r="57" spans="1:8">
       <c r="A57" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C57" s="3">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="D57" s="4">
-        <v>0.95833333333333337</v>
+        <v>0.97916666666666663</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>915</v>
+        <v>911</v>
       </c>
       <c r="F57" s="3"/>
       <c r="G57" s="1"/>
@@ -5992,219 +5985,219 @@
     </row>
     <row r="58" spans="1:8">
       <c r="A58" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>134</v>
+        <v>67</v>
       </c>
       <c r="C58" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D58" s="4">
-        <v>0.97916666666666663</v>
+        <v>0</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
       <c r="F58" s="3"/>
       <c r="G58" s="1"/>
-      <c r="H58" t="s">
-        <v>365</v>
+      <c r="H58" s="1" t="s">
+        <v>366</v>
       </c>
     </row>
     <row r="59" spans="1:8">
       <c r="A59" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="C59" s="3">
-        <v>6</v>
-      </c>
-      <c r="D59" s="4">
+        <v>150</v>
+      </c>
+      <c r="C59" s="1">
+        <v>13</v>
+      </c>
+      <c r="D59" s="5">
         <v>0</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>919</v>
-      </c>
-      <c r="F59" s="3"/>
+        <v>915</v>
+      </c>
+      <c r="F59" s="1"/>
       <c r="G59" s="1"/>
       <c r="H59" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="60" spans="1:8">
       <c r="A60" s="2" t="s">
-        <v>202</v>
+        <v>761</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="C60" s="1">
-        <v>13</v>
-      </c>
-      <c r="D60" s="5">
-        <v>0</v>
+        <v>759</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>920</v>
-      </c>
-      <c r="F60" s="1"/>
-      <c r="G60" s="1"/>
-      <c r="H60" s="1" t="s">
-        <v>367</v>
+        <v>916</v>
+      </c>
+      <c r="F60" s="2">
+        <v>1</v>
+      </c>
+      <c r="H60" s="2" t="s">
+        <v>763</v>
       </c>
     </row>
     <row r="61" spans="1:8">
       <c r="A61" s="2" t="s">
-        <v>764</v>
+        <v>203</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>762</v>
-      </c>
+        <v>135</v>
+      </c>
+      <c r="C61" s="1"/>
+      <c r="D61" s="1"/>
       <c r="E61" s="2" t="s">
-        <v>921</v>
-      </c>
-      <c r="F61" s="2">
-        <v>1</v>
+        <v>917</v>
+      </c>
+      <c r="F61" s="3">
+        <v>1</v>
+      </c>
+      <c r="G61" s="1" t="s">
+        <v>1196</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>766</v>
+        <v>368</v>
       </c>
     </row>
     <row r="62" spans="1:8">
-      <c r="A62" s="2" t="s">
-        <v>203</v>
+      <c r="A62" t="s">
+        <v>484</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="C62" s="1"/>
-      <c r="D62" s="1"/>
+        <v>457</v>
+      </c>
       <c r="E62" s="2" t="s">
-        <v>922</v>
-      </c>
-      <c r="F62" s="3">
-        <v>1</v>
-      </c>
-      <c r="G62" s="1" t="s">
-        <v>809</v>
-      </c>
-      <c r="H62" s="2" t="s">
-        <v>368</v>
+        <v>918</v>
+      </c>
+      <c r="F62" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="63" spans="1:8">
       <c r="A63" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>923</v>
-      </c>
-      <c r="F63" s="2">
-        <v>1</v>
+        <v>919</v>
+      </c>
+      <c r="F63" s="3">
+        <v>1</v>
+      </c>
+      <c r="H63" t="s">
+        <v>461</v>
       </c>
     </row>
     <row r="64" spans="1:8">
       <c r="A64" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>458</v>
-      </c>
+        <v>459</v>
+      </c>
+      <c r="C64" s="3"/>
+      <c r="D64" s="6"/>
       <c r="E64" s="2" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="F64" s="3">
         <v>1</v>
       </c>
+      <c r="G64" s="1" t="s">
+        <v>823</v>
+      </c>
       <c r="H64" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="65" spans="1:8">
-      <c r="A65" t="s">
-        <v>486</v>
+      <c r="A65" s="2" t="s">
+        <v>204</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>459</v>
-      </c>
-      <c r="C65" s="3"/>
-      <c r="D65" s="6"/>
+        <v>68</v>
+      </c>
+      <c r="C65" s="3">
+        <v>7</v>
+      </c>
+      <c r="D65" s="4">
+        <v>0.875</v>
+      </c>
       <c r="E65" s="2" t="s">
-        <v>925</v>
-      </c>
-      <c r="F65" s="3">
-        <v>1</v>
-      </c>
-      <c r="G65" s="1" t="s">
-        <v>827</v>
-      </c>
-      <c r="H65" t="s">
-        <v>460</v>
+        <v>921</v>
+      </c>
+      <c r="F65" s="3"/>
+      <c r="G65" s="1"/>
+      <c r="H65" s="1" t="s">
+        <v>369</v>
       </c>
     </row>
     <row r="66" spans="1:8">
       <c r="A66" s="2" t="s">
-        <v>204</v>
+        <v>838</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C66" s="3">
-        <v>7</v>
-      </c>
-      <c r="D66" s="4">
-        <v>0.875</v>
+        <v>837</v>
+      </c>
+      <c r="C66" s="2">
+        <v>6</v>
+      </c>
+      <c r="D66" s="6">
+        <v>0</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>926</v>
-      </c>
-      <c r="F66" s="3"/>
-      <c r="G66" s="1"/>
-      <c r="H66" s="1" t="s">
-        <v>369</v>
+        <v>922</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>847</v>
       </c>
     </row>
     <row r="67" spans="1:8">
-      <c r="A67" s="2" t="s">
-        <v>842</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>841</v>
-      </c>
-      <c r="C67" s="2">
+      <c r="A67" s="11" t="s">
+        <v>593</v>
+      </c>
+      <c r="B67" t="s">
+        <v>594</v>
+      </c>
+      <c r="C67">
         <v>6</v>
       </c>
-      <c r="D67" s="6">
+      <c r="D67" s="5">
         <v>0</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>927</v>
-      </c>
-      <c r="H67" s="2" t="s">
-        <v>851</v>
+        <v>923</v>
+      </c>
+      <c r="F67" s="3"/>
+      <c r="G67" s="1"/>
+      <c r="H67" s="1" t="s">
+        <v>370</v>
       </c>
     </row>
     <row r="68" spans="1:8">
-      <c r="A68" s="11" t="s">
-        <v>596</v>
-      </c>
-      <c r="B68" t="s">
-        <v>597</v>
-      </c>
-      <c r="C68">
+      <c r="A68" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="C68" s="3">
         <v>6</v>
       </c>
       <c r="D68" s="5">
         <v>0</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>928</v>
+        <v>924</v>
       </c>
       <c r="F68" s="3"/>
       <c r="G68" s="1"/>
@@ -6214,118 +6207,118 @@
     </row>
     <row r="69" spans="1:8">
       <c r="A69" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="C69" s="3">
-        <v>6</v>
-      </c>
-      <c r="D69" s="5">
-        <v>0</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="C69" s="3"/>
+      <c r="D69" s="5"/>
       <c r="E69" s="2" t="s">
-        <v>929</v>
-      </c>
-      <c r="F69" s="3"/>
+        <v>925</v>
+      </c>
+      <c r="F69" s="3">
+        <v>1</v>
+      </c>
       <c r="G69" s="1"/>
       <c r="H69" s="1" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="70" spans="1:8">
       <c r="A70" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="C70" s="3"/>
-      <c r="D70" s="5"/>
+        <v>148</v>
+      </c>
+      <c r="C70" s="3">
+        <v>6</v>
+      </c>
+      <c r="D70" s="5">
+        <v>0</v>
+      </c>
       <c r="E70" s="2" t="s">
-        <v>930</v>
-      </c>
-      <c r="F70" s="3">
-        <v>1</v>
-      </c>
+        <v>926</v>
+      </c>
+      <c r="F70" s="3"/>
       <c r="G70" s="1"/>
       <c r="H70" s="1" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="71" spans="1:8">
       <c r="A71" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>148</v>
+        <v>1</v>
       </c>
       <c r="C71" s="3">
         <v>6</v>
       </c>
-      <c r="D71" s="5">
+      <c r="D71" s="4">
         <v>0</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>931</v>
+        <v>927</v>
       </c>
       <c r="F71" s="3"/>
       <c r="G71" s="1"/>
-      <c r="H71" s="1" t="s">
-        <v>370</v>
+      <c r="H71" s="2" t="s">
+        <v>372</v>
       </c>
     </row>
     <row r="72" spans="1:8">
       <c r="A72" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C72" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D72" s="4">
-        <v>0</v>
+        <v>0.91666666666666663</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>932</v>
+        <v>928</v>
       </c>
       <c r="F72" s="3"/>
       <c r="G72" s="1"/>
       <c r="H72" s="2" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="73" spans="1:8">
       <c r="A73" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C73" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D73" s="4">
-        <v>0.91666666666666663</v>
+        <v>0</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>933</v>
+        <v>929</v>
       </c>
       <c r="F73" s="3"/>
       <c r="G73" s="1"/>
       <c r="H73" s="2" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="74" spans="1:8">
       <c r="A74" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C74" s="3">
         <v>6</v>
@@ -6334,120 +6327,119 @@
         <v>0</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>934</v>
+        <v>930</v>
       </c>
       <c r="F74" s="3"/>
       <c r="G74" s="1"/>
       <c r="H74" s="2" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="75" spans="1:8">
       <c r="A75" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>0</v>
+        <v>137</v>
       </c>
       <c r="C75" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D75" s="4">
         <v>0</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>935</v>
+        <v>931</v>
       </c>
       <c r="F75" s="3"/>
-      <c r="G75" s="1"/>
-      <c r="H75" s="2" t="s">
-        <v>375</v>
+      <c r="H75" s="1" t="s">
+        <v>376</v>
       </c>
     </row>
     <row r="76" spans="1:8">
       <c r="A76" s="2" t="s">
-        <v>212</v>
+        <v>463</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="C76" s="3">
-        <v>7</v>
-      </c>
-      <c r="D76" s="4">
-        <v>0</v>
-      </c>
+        <v>97</v>
+      </c>
+      <c r="C76" s="3"/>
+      <c r="D76" s="4"/>
       <c r="E76" s="2" t="s">
-        <v>936</v>
-      </c>
-      <c r="F76" s="3"/>
+        <v>932</v>
+      </c>
+      <c r="F76" s="3">
+        <v>1</v>
+      </c>
       <c r="H76" s="1" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="77" spans="1:8">
-      <c r="A77" s="2" t="s">
-        <v>463</v>
+      <c r="A77" t="s">
+        <v>478</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>97</v>
+        <v>140</v>
       </c>
       <c r="C77" s="3"/>
       <c r="D77" s="4"/>
       <c r="E77" s="2" t="s">
-        <v>937</v>
+        <v>933</v>
       </c>
       <c r="F77" s="3">
         <v>1</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="78" spans="1:8">
       <c r="A78" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>140</v>
+        <v>96</v>
       </c>
       <c r="C78" s="3"/>
       <c r="D78" s="4"/>
       <c r="E78" s="2" t="s">
-        <v>938</v>
+        <v>934</v>
       </c>
       <c r="F78" s="3">
         <v>1</v>
       </c>
       <c r="H78" s="1" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="79" spans="1:8">
       <c r="A79" t="s">
-        <v>479</v>
+        <v>466</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="C79" s="3"/>
-      <c r="D79" s="4"/>
+        <v>99</v>
+      </c>
+      <c r="C79" s="3">
+        <v>15</v>
+      </c>
+      <c r="D79" s="4">
+        <v>0</v>
+      </c>
       <c r="E79" s="2" t="s">
-        <v>939</v>
-      </c>
-      <c r="F79" s="3">
-        <v>1</v>
-      </c>
+        <v>935</v>
+      </c>
+      <c r="F79" s="3"/>
       <c r="H79" s="1" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="80" spans="1:8">
-      <c r="A80" t="s">
-        <v>466</v>
+      <c r="A80" s="2" t="s">
+        <v>467</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C80" s="3">
         <v>15</v>
@@ -6456,158 +6448,158 @@
         <v>0</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>940</v>
+        <v>936</v>
       </c>
       <c r="F80" s="3"/>
       <c r="H80" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="81" spans="1:8">
-      <c r="A81" s="2" t="s">
-        <v>467</v>
+      <c r="A81" t="s">
+        <v>468</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="C81" s="3">
-        <v>15</v>
-      </c>
-      <c r="D81" s="4">
-        <v>0</v>
-      </c>
+        <v>92</v>
+      </c>
+      <c r="C81" s="3"/>
+      <c r="D81" s="4"/>
       <c r="E81" s="2" t="s">
-        <v>941</v>
-      </c>
-      <c r="F81" s="3"/>
+        <v>937</v>
+      </c>
+      <c r="F81" s="3">
+        <v>1</v>
+      </c>
       <c r="H81" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="82" spans="1:8">
       <c r="A82" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C82" s="3"/>
       <c r="D82" s="4"/>
       <c r="E82" s="2" t="s">
-        <v>942</v>
+        <v>938</v>
       </c>
       <c r="F82" s="3">
         <v>1</v>
       </c>
       <c r="H82" s="1" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="83" spans="1:8">
-      <c r="A83" t="s">
-        <v>469</v>
+      <c r="A83" s="2" t="s">
+        <v>213</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="C83" s="3"/>
       <c r="D83" s="4"/>
       <c r="E83" s="2" t="s">
-        <v>943</v>
+        <v>939</v>
       </c>
       <c r="F83" s="3">
         <v>1</v>
       </c>
       <c r="H83" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="84" spans="1:8">
-      <c r="A84" s="2" t="s">
-        <v>213</v>
+      <c r="A84" t="s">
+        <v>482</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="C84" s="3"/>
-      <c r="D84" s="4"/>
+        <v>100</v>
+      </c>
+      <c r="C84" s="3">
+        <v>15</v>
+      </c>
+      <c r="D84" s="4">
+        <v>0</v>
+      </c>
       <c r="E84" s="2" t="s">
-        <v>944</v>
-      </c>
-      <c r="F84" s="3">
-        <v>1</v>
-      </c>
+        <v>940</v>
+      </c>
+      <c r="F84" s="3"/>
       <c r="H84" s="1" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="85" spans="1:8">
       <c r="A85" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="C85" s="3">
-        <v>15</v>
-      </c>
-      <c r="D85" s="4">
-        <v>0</v>
-      </c>
+        <v>94</v>
+      </c>
+      <c r="C85" s="3"/>
+      <c r="D85" s="4"/>
       <c r="E85" s="2" t="s">
-        <v>945</v>
-      </c>
-      <c r="F85" s="3"/>
+        <v>941</v>
+      </c>
+      <c r="F85" s="3">
+        <v>1</v>
+      </c>
       <c r="H85" s="1" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="86" spans="1:8">
       <c r="A86" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="C86" s="3"/>
-      <c r="D86" s="4"/>
+        <v>95</v>
+      </c>
+      <c r="C86" s="3">
+        <v>15</v>
+      </c>
+      <c r="D86" s="4">
+        <v>0</v>
+      </c>
       <c r="E86" s="2" t="s">
-        <v>946</v>
-      </c>
-      <c r="F86" s="3">
-        <v>1</v>
-      </c>
+        <v>942</v>
+      </c>
+      <c r="F86" s="3"/>
       <c r="H86" s="1" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="87" spans="1:8">
-      <c r="A87" t="s">
-        <v>481</v>
+      <c r="A87" s="2" t="s">
+        <v>455</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="C87" s="3">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="D87" s="4">
         <v>0</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>947</v>
+        <v>943</v>
       </c>
       <c r="F87" s="3"/>
       <c r="H87" s="1" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="88" spans="1:8">
       <c r="A88" s="2" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C88" s="3">
         <v>7</v>
@@ -6616,213 +6608,214 @@
         <v>0</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>948</v>
+        <v>944</v>
       </c>
       <c r="F88" s="3"/>
       <c r="H88" s="1" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="89" spans="1:8">
       <c r="A89" s="2" t="s">
-        <v>456</v>
+        <v>464</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="C89" s="3">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D89" s="4">
         <v>0</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>949</v>
+        <v>945</v>
       </c>
       <c r="F89" s="3"/>
       <c r="H89" s="1" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="90" spans="1:8">
       <c r="A90" s="2" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="C90" s="3">
-        <v>14</v>
-      </c>
-      <c r="D90" s="4">
-        <v>0</v>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="C90" s="3"/>
+      <c r="D90" s="4"/>
       <c r="E90" s="2" t="s">
-        <v>950</v>
-      </c>
-      <c r="F90" s="3"/>
+        <v>946</v>
+      </c>
+      <c r="F90" s="3">
+        <v>1</v>
+      </c>
       <c r="H90" s="1" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="91" spans="1:8">
-      <c r="A91" s="2" t="s">
-        <v>465</v>
+      <c r="A91" t="s">
+        <v>470</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C91" s="3"/>
       <c r="D91" s="4"/>
       <c r="E91" s="2" t="s">
-        <v>951</v>
+        <v>947</v>
       </c>
       <c r="F91" s="3">
         <v>1</v>
       </c>
       <c r="H91" s="1" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="92" spans="1:8">
       <c r="A92" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C92" s="3"/>
       <c r="D92" s="4"/>
       <c r="E92" s="2" t="s">
-        <v>952</v>
+        <v>948</v>
       </c>
       <c r="F92" s="3">
         <v>1</v>
       </c>
       <c r="H92" s="1" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="93" spans="1:8">
       <c r="A93" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C93" s="3"/>
       <c r="D93" s="4"/>
       <c r="E93" s="2" t="s">
-        <v>953</v>
+        <v>949</v>
       </c>
       <c r="F93" s="3">
         <v>1</v>
       </c>
       <c r="H93" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="94" spans="1:8">
       <c r="A94" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C94" s="3"/>
       <c r="D94" s="4"/>
       <c r="E94" s="2" t="s">
-        <v>954</v>
+        <v>950</v>
       </c>
       <c r="F94" s="3">
         <v>1</v>
       </c>
       <c r="H94" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="95" spans="1:8">
       <c r="A95" t="s">
-        <v>473</v>
+        <v>483</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="C95" s="3"/>
-      <c r="D95" s="4"/>
+        <v>101</v>
+      </c>
+      <c r="C95" s="3">
+        <v>15</v>
+      </c>
+      <c r="D95" s="4">
+        <v>0</v>
+      </c>
       <c r="E95" s="2" t="s">
-        <v>955</v>
-      </c>
-      <c r="F95" s="3">
-        <v>1</v>
-      </c>
+        <v>951</v>
+      </c>
+      <c r="F95" s="3"/>
       <c r="H95" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="96" spans="1:8">
       <c r="A96" t="s">
-        <v>483</v>
-      </c>
-      <c r="B96" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="C96" s="3">
-        <v>15</v>
-      </c>
-      <c r="D96" s="4">
-        <v>0</v>
-      </c>
+        <v>595</v>
+      </c>
+      <c r="B96" t="s">
+        <v>596</v>
+      </c>
+      <c r="C96" s="3"/>
+      <c r="D96" s="4"/>
       <c r="E96" s="2" t="s">
-        <v>956</v>
-      </c>
-      <c r="F96" s="3"/>
-      <c r="H96" s="1" t="s">
-        <v>396</v>
+        <v>952</v>
+      </c>
+      <c r="F96" s="3">
+        <v>1</v>
+      </c>
+      <c r="H96" s="11" t="s">
+        <v>597</v>
       </c>
     </row>
     <row r="97" spans="1:8">
-      <c r="A97" t="s">
-        <v>598</v>
-      </c>
-      <c r="B97" t="s">
-        <v>599</v>
-      </c>
-      <c r="C97" s="3"/>
-      <c r="D97" s="4"/>
+      <c r="A97" s="2" t="s">
+        <v>583</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>584</v>
+      </c>
       <c r="E97" s="2" t="s">
-        <v>957</v>
+        <v>953</v>
       </c>
       <c r="F97" s="3">
         <v>1</v>
       </c>
-      <c r="H97" s="11" t="s">
-        <v>600</v>
+      <c r="H97" s="7" t="s">
+        <v>585</v>
       </c>
     </row>
     <row r="98" spans="1:8">
       <c r="A98" s="2" t="s">
-        <v>586</v>
+        <v>300</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>587</v>
+        <v>54</v>
+      </c>
+      <c r="C98" s="3">
+        <v>7</v>
+      </c>
+      <c r="D98" s="4">
+        <v>0</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>958</v>
-      </c>
-      <c r="F98" s="3">
-        <v>1</v>
-      </c>
-      <c r="H98" s="7" t="s">
-        <v>588</v>
+        <v>954</v>
+      </c>
+      <c r="F98" s="3"/>
+      <c r="G98" s="1"/>
+      <c r="H98" s="1" t="s">
+        <v>444</v>
       </c>
     </row>
     <row r="99" spans="1:8">
       <c r="A99" s="2" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>54</v>
+        <v>313</v>
       </c>
       <c r="C99" s="3">
         <v>7</v>
@@ -6831,7 +6824,7 @@
         <v>0</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>959</v>
+        <v>955</v>
       </c>
       <c r="F99" s="3"/>
       <c r="G99" s="1"/>
@@ -6841,10 +6834,10 @@
     </row>
     <row r="100" spans="1:8">
       <c r="A100" s="2" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>313</v>
+        <v>57</v>
       </c>
       <c r="C100" s="3">
         <v>7</v>
@@ -6853,7 +6846,7 @@
         <v>0</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>960</v>
+        <v>956</v>
       </c>
       <c r="F100" s="3"/>
       <c r="G100" s="1"/>
@@ -6863,10 +6856,10 @@
     </row>
     <row r="101" spans="1:8">
       <c r="A101" s="2" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C101" s="3">
         <v>7</v>
@@ -6875,7 +6868,7 @@
         <v>0</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>961</v>
+        <v>957</v>
       </c>
       <c r="F101" s="3"/>
       <c r="G101" s="1"/>
@@ -6885,10 +6878,10 @@
     </row>
     <row r="102" spans="1:8">
       <c r="A102" s="2" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>60</v>
+        <v>314</v>
       </c>
       <c r="C102" s="3">
         <v>7</v>
@@ -6897,7 +6890,7 @@
         <v>0</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>962</v>
+        <v>958</v>
       </c>
       <c r="F102" s="3"/>
       <c r="G102" s="1"/>
@@ -6907,10 +6900,10 @@
     </row>
     <row r="103" spans="1:8">
       <c r="A103" s="2" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C103" s="3">
         <v>7</v>
@@ -6919,7 +6912,7 @@
         <v>0</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>963</v>
+        <v>959</v>
       </c>
       <c r="F103" s="3"/>
       <c r="G103" s="1"/>
@@ -6929,10 +6922,10 @@
     </row>
     <row r="104" spans="1:8">
       <c r="A104" s="2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="C104" s="3">
         <v>7</v>
@@ -6941,7 +6934,7 @@
         <v>0</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>964</v>
+        <v>960</v>
       </c>
       <c r="F104" s="3"/>
       <c r="G104" s="1"/>
@@ -6951,35 +6944,30 @@
     </row>
     <row r="105" spans="1:8">
       <c r="A105" s="2" t="s">
-        <v>303</v>
+        <v>531</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="C105" s="3">
-        <v>7</v>
-      </c>
-      <c r="D105" s="4">
-        <v>0</v>
+        <v>532</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>965</v>
-      </c>
-      <c r="F105" s="3"/>
-      <c r="G105" s="1"/>
-      <c r="H105" s="1" t="s">
-        <v>444</v>
+        <v>961</v>
+      </c>
+      <c r="F105" s="3">
+        <v>1</v>
+      </c>
+      <c r="H105" s="7" t="s">
+        <v>541</v>
       </c>
     </row>
     <row r="106" spans="1:8">
       <c r="A106" s="2" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>532</v>
+        <v>504</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>966</v>
+        <v>962</v>
       </c>
       <c r="F106" s="3">
         <v>1</v>
@@ -6990,13 +6978,13 @@
     </row>
     <row r="107" spans="1:8">
       <c r="A107" s="2" t="s">
-        <v>530</v>
+        <v>517</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>504</v>
+        <v>519</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>967</v>
+        <v>963</v>
       </c>
       <c r="F107" s="3">
         <v>1</v>
@@ -7007,13 +6995,13 @@
     </row>
     <row r="108" spans="1:8">
       <c r="A108" s="2" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>968</v>
+        <v>964</v>
       </c>
       <c r="F108" s="3">
         <v>1</v>
@@ -7024,13 +7012,13 @@
     </row>
     <row r="109" spans="1:8">
       <c r="A109" s="2" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>969</v>
+        <v>965</v>
       </c>
       <c r="F109" s="3">
         <v>1</v>
@@ -7041,13 +7029,13 @@
     </row>
     <row r="110" spans="1:8">
       <c r="A110" s="2" t="s">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>516</v>
+        <v>525</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>970</v>
+        <v>966</v>
       </c>
       <c r="F110" s="3">
         <v>1</v>
@@ -7058,13 +7046,13 @@
     </row>
     <row r="111" spans="1:8">
       <c r="A111" s="2" t="s">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="F111" s="3">
         <v>1</v>
@@ -7075,13 +7063,13 @@
     </row>
     <row r="112" spans="1:8">
       <c r="A112" s="2" t="s">
-        <v>528</v>
+        <v>512</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>529</v>
+        <v>513</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>972</v>
+        <v>968</v>
       </c>
       <c r="F112" s="3">
         <v>1</v>
@@ -7092,13 +7080,13 @@
     </row>
     <row r="113" spans="1:8">
       <c r="A113" s="2" t="s">
-        <v>512</v>
+        <v>533</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>513</v>
+        <v>534</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>973</v>
+        <v>969</v>
       </c>
       <c r="F113" s="3">
         <v>1</v>
@@ -7109,13 +7097,13 @@
     </row>
     <row r="114" spans="1:8">
       <c r="A114" s="2" t="s">
-        <v>533</v>
+        <v>526</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>534</v>
+        <v>527</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>974</v>
+        <v>970</v>
       </c>
       <c r="F114" s="3">
         <v>1</v>
@@ -7126,13 +7114,13 @@
     </row>
     <row r="115" spans="1:8">
       <c r="A115" s="2" t="s">
-        <v>526</v>
+        <v>508</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>527</v>
+        <v>509</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>975</v>
+        <v>971</v>
       </c>
       <c r="F115" s="3">
         <v>1</v>
@@ -7143,13 +7131,13 @@
     </row>
     <row r="116" spans="1:8">
       <c r="A116" s="2" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>976</v>
+        <v>972</v>
       </c>
       <c r="F116" s="3">
         <v>1</v>
@@ -7160,13 +7148,13 @@
     </row>
     <row r="117" spans="1:8">
       <c r="A117" s="2" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>977</v>
+        <v>973</v>
       </c>
       <c r="F117" s="3">
         <v>1</v>
@@ -7177,13 +7165,13 @@
     </row>
     <row r="118" spans="1:8">
       <c r="A118" s="2" t="s">
-        <v>514</v>
+        <v>522</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>515</v>
+        <v>523</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>978</v>
+        <v>974</v>
       </c>
       <c r="F118" s="3">
         <v>1</v>
@@ -7194,455 +7182,460 @@
     </row>
     <row r="119" spans="1:8">
       <c r="A119" s="2" t="s">
-        <v>522</v>
+        <v>214</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>523</v>
+        <v>131</v>
+      </c>
+      <c r="C119" s="3">
+        <v>6</v>
+      </c>
+      <c r="D119" s="4">
+        <v>0</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>979</v>
-      </c>
-      <c r="F119" s="3">
-        <v>1</v>
-      </c>
-      <c r="H119" s="7" t="s">
-        <v>541</v>
+        <v>975</v>
+      </c>
+      <c r="F119" s="3"/>
+      <c r="G119" s="1"/>
+      <c r="H119" t="s">
+        <v>397</v>
       </c>
     </row>
     <row r="120" spans="1:8">
-      <c r="A120" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="B120" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="C120" s="3">
-        <v>6</v>
-      </c>
-      <c r="D120" s="4">
-        <v>0</v>
-      </c>
+      <c r="A120" t="s">
+        <v>598</v>
+      </c>
+      <c r="B120" t="s">
+        <v>599</v>
+      </c>
+      <c r="C120" s="3"/>
+      <c r="D120" s="4"/>
       <c r="E120" s="2" t="s">
-        <v>980</v>
-      </c>
-      <c r="F120" s="3"/>
+        <v>976</v>
+      </c>
+      <c r="F120" s="3">
+        <v>1</v>
+      </c>
       <c r="G120" s="1"/>
-      <c r="H120" t="s">
-        <v>397</v>
+      <c r="H120" s="11" t="s">
+        <v>600</v>
       </c>
     </row>
     <row r="121" spans="1:8">
       <c r="A121" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="B121" t="s">
-        <v>602</v>
+        <v>803</v>
       </c>
       <c r="C121" s="3"/>
       <c r="D121" s="4"/>
       <c r="E121" s="2" t="s">
-        <v>981</v>
+        <v>977</v>
       </c>
       <c r="F121" s="3">
         <v>1</v>
       </c>
-      <c r="G121" s="1"/>
+      <c r="G121" s="1" t="s">
+        <v>605</v>
+      </c>
       <c r="H121" s="11" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
     </row>
     <row r="122" spans="1:8">
       <c r="A122" t="s">
-        <v>607</v>
-      </c>
-      <c r="B122" t="s">
-        <v>806</v>
-      </c>
-      <c r="C122" s="3"/>
-      <c r="D122" s="4"/>
+        <v>735</v>
+      </c>
+      <c r="B122" s="1" t="s">
+        <v>736</v>
+      </c>
       <c r="E122" s="2" t="s">
-        <v>982</v>
-      </c>
-      <c r="F122" s="3">
-        <v>1</v>
-      </c>
-      <c r="G122" s="1" t="s">
-        <v>608</v>
-      </c>
-      <c r="H122" s="11" t="s">
-        <v>609</v>
+        <v>1177</v>
+      </c>
+      <c r="F122" s="2">
+        <v>1</v>
+      </c>
+      <c r="H122" s="7" t="s">
+        <v>740</v>
       </c>
     </row>
     <row r="123" spans="1:8">
       <c r="A123" t="s">
-        <v>738</v>
-      </c>
-      <c r="B123" s="1" t="s">
-        <v>739</v>
-      </c>
+        <v>601</v>
+      </c>
+      <c r="B123" t="s">
+        <v>602</v>
+      </c>
+      <c r="C123" s="3"/>
+      <c r="D123" s="4"/>
       <c r="E123" s="2" t="s">
-        <v>1183</v>
-      </c>
-      <c r="F123" s="2">
-        <v>1</v>
-      </c>
-      <c r="H123" s="7" t="s">
-        <v>743</v>
+        <v>978</v>
+      </c>
+      <c r="F123" s="3">
+        <v>1</v>
+      </c>
+      <c r="G123" s="1"/>
+      <c r="H123" s="11" t="s">
+        <v>603</v>
       </c>
     </row>
     <row r="124" spans="1:8">
-      <c r="A124" t="s">
-        <v>604</v>
-      </c>
-      <c r="B124" t="s">
-        <v>605</v>
-      </c>
-      <c r="C124" s="3"/>
-      <c r="D124" s="4"/>
+      <c r="A124" s="2" t="s">
+        <v>762</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>756</v>
+      </c>
       <c r="E124" s="2" t="s">
-        <v>983</v>
-      </c>
-      <c r="F124" s="3">
-        <v>1</v>
-      </c>
-      <c r="G124" s="1"/>
-      <c r="H124" s="11" t="s">
-        <v>606</v>
+        <v>979</v>
+      </c>
+      <c r="F124" s="2">
+        <v>1</v>
+      </c>
+      <c r="H124" s="2" t="s">
+        <v>757</v>
       </c>
     </row>
     <row r="125" spans="1:8">
       <c r="A125" s="2" t="s">
-        <v>765</v>
+        <v>235</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>759</v>
+        <v>236</v>
+      </c>
+      <c r="C125" s="3">
+        <v>7</v>
+      </c>
+      <c r="D125" s="4">
+        <v>0</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>984</v>
-      </c>
-      <c r="F125" s="2">
-        <v>1</v>
-      </c>
-      <c r="H125" s="2" t="s">
-        <v>760</v>
+        <v>980</v>
+      </c>
+      <c r="F125" s="3"/>
+      <c r="G125" s="1"/>
+      <c r="H125" s="1" t="s">
+        <v>398</v>
       </c>
     </row>
     <row r="126" spans="1:8">
-      <c r="A126" s="2" t="s">
-        <v>235</v>
+      <c r="A126" t="s">
+        <v>268</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>236</v>
+        <v>319</v>
       </c>
       <c r="C126" s="3">
         <v>7</v>
       </c>
       <c r="D126" s="4">
-        <v>0</v>
+        <v>0.95833333333333337</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>985</v>
+        <v>981</v>
       </c>
       <c r="F126" s="3"/>
       <c r="G126" s="1"/>
       <c r="H126" s="1" t="s">
-        <v>398</v>
+        <v>429</v>
       </c>
     </row>
     <row r="127" spans="1:8">
-      <c r="A127" t="s">
-        <v>268</v>
+      <c r="A127" s="2" t="s">
+        <v>495</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>319</v>
-      </c>
-      <c r="C127" s="3">
-        <v>7</v>
-      </c>
-      <c r="D127" s="4">
-        <v>0.95833333333333337</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="C127" s="1"/>
+      <c r="D127" s="5"/>
       <c r="E127" s="2" t="s">
-        <v>986</v>
-      </c>
-      <c r="F127" s="3"/>
+        <v>982</v>
+      </c>
+      <c r="F127" s="3">
+        <v>1</v>
+      </c>
       <c r="G127" s="1"/>
       <c r="H127" s="1" t="s">
-        <v>429</v>
+        <v>399</v>
       </c>
     </row>
     <row r="128" spans="1:8">
       <c r="A128" s="2" t="s">
-        <v>495</v>
+        <v>574</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="C128" s="1"/>
-      <c r="D128" s="5"/>
+        <v>575</v>
+      </c>
       <c r="E128" s="2" t="s">
-        <v>987</v>
+        <v>983</v>
       </c>
       <c r="F128" s="3">
         <v>1</v>
       </c>
-      <c r="G128" s="1"/>
-      <c r="H128" s="1" t="s">
-        <v>399</v>
+      <c r="H128" s="7" t="s">
+        <v>576</v>
       </c>
     </row>
     <row r="129" spans="1:8">
       <c r="A129" s="2" t="s">
-        <v>577</v>
+        <v>256</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>578</v>
+        <v>128</v>
+      </c>
+      <c r="C129" s="3">
+        <v>14</v>
+      </c>
+      <c r="D129" s="4">
+        <v>0</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>988</v>
-      </c>
-      <c r="F129" s="3">
-        <v>1</v>
-      </c>
-      <c r="H129" s="7" t="s">
-        <v>579</v>
+        <v>984</v>
+      </c>
+      <c r="F129" s="3"/>
+      <c r="G129" s="1"/>
+      <c r="H129" s="1" t="s">
+        <v>400</v>
       </c>
     </row>
     <row r="130" spans="1:8">
-      <c r="A130" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="B130" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="C130" s="3">
-        <v>14</v>
-      </c>
-      <c r="D130" s="4">
-        <v>0</v>
-      </c>
-      <c r="E130" s="2" t="s">
-        <v>989</v>
-      </c>
-      <c r="F130" s="3"/>
-      <c r="G130" s="1"/>
-      <c r="H130" s="1" t="s">
-        <v>400</v>
+      <c r="A130" t="s">
+        <v>607</v>
+      </c>
+      <c r="B130" t="s">
+        <v>608</v>
+      </c>
+      <c r="C130"/>
+      <c r="D130" s="11"/>
+      <c r="E130" s="13" t="s">
+        <v>985</v>
+      </c>
+      <c r="F130" s="1">
+        <v>1</v>
+      </c>
+      <c r="G130"/>
+      <c r="H130" t="s">
+        <v>626</v>
       </c>
     </row>
     <row r="131" spans="1:8">
       <c r="A131" t="s">
-        <v>610</v>
+        <v>849</v>
       </c>
       <c r="B131" t="s">
-        <v>611</v>
-      </c>
-      <c r="C131"/>
-      <c r="D131" s="11"/>
-      <c r="E131" s="13" t="s">
-        <v>990</v>
+        <v>609</v>
+      </c>
+      <c r="E131" s="2" t="s">
+        <v>986</v>
       </c>
       <c r="F131" s="1">
         <v>1</v>
       </c>
-      <c r="G131"/>
       <c r="H131" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
     </row>
     <row r="132" spans="1:8">
       <c r="A132" t="s">
-        <v>853</v>
+        <v>610</v>
       </c>
       <c r="B132" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>991</v>
+        <v>987</v>
       </c>
       <c r="F132" s="1">
         <v>1</v>
       </c>
       <c r="H132" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
     </row>
     <row r="133" spans="1:8">
       <c r="A133" t="s">
+        <v>612</v>
+      </c>
+      <c r="B133" t="s">
         <v>613</v>
       </c>
-      <c r="B133" t="s">
-        <v>614</v>
-      </c>
       <c r="E133" s="2" t="s">
-        <v>992</v>
+        <v>988</v>
       </c>
       <c r="F133" s="1">
         <v>1</v>
       </c>
       <c r="H133" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
     </row>
     <row r="134" spans="1:8">
       <c r="A134" t="s">
+        <v>614</v>
+      </c>
+      <c r="B134" t="s">
         <v>615</v>
       </c>
-      <c r="B134" t="s">
-        <v>616</v>
-      </c>
       <c r="E134" s="2" t="s">
-        <v>993</v>
+        <v>989</v>
       </c>
       <c r="F134" s="1">
         <v>1</v>
       </c>
       <c r="H134" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
     </row>
     <row r="135" spans="1:8">
       <c r="A135" t="s">
+        <v>616</v>
+      </c>
+      <c r="B135" t="s">
         <v>617</v>
       </c>
-      <c r="B135" t="s">
-        <v>618</v>
-      </c>
       <c r="E135" s="2" t="s">
-        <v>994</v>
+        <v>990</v>
       </c>
       <c r="F135" s="1">
         <v>1</v>
       </c>
       <c r="H135" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
     </row>
     <row r="136" spans="1:8">
       <c r="A136" t="s">
+        <v>618</v>
+      </c>
+      <c r="B136" t="s">
         <v>619</v>
       </c>
-      <c r="B136" t="s">
-        <v>620</v>
+      <c r="C136" s="2">
+        <v>6</v>
+      </c>
+      <c r="D136" s="6">
+        <v>0</v>
       </c>
       <c r="E136" s="2" t="s">
-        <v>995</v>
-      </c>
-      <c r="F136" s="1">
-        <v>1</v>
-      </c>
+        <v>991</v>
+      </c>
+      <c r="F136" s="1"/>
       <c r="H136" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
     </row>
     <row r="137" spans="1:8">
       <c r="A137" t="s">
+        <v>620</v>
+      </c>
+      <c r="B137" t="s">
         <v>621</v>
       </c>
-      <c r="B137" t="s">
-        <v>622</v>
-      </c>
-      <c r="C137" s="2">
-        <v>6</v>
-      </c>
-      <c r="D137" s="6">
-        <v>0</v>
-      </c>
       <c r="E137" s="2" t="s">
-        <v>996</v>
-      </c>
-      <c r="F137" s="1"/>
+        <v>992</v>
+      </c>
+      <c r="F137" s="1">
+        <v>1</v>
+      </c>
       <c r="H137" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
     </row>
     <row r="138" spans="1:8">
       <c r="A138" t="s">
+        <v>622</v>
+      </c>
+      <c r="B138" t="s">
         <v>623</v>
       </c>
-      <c r="B138" t="s">
-        <v>624</v>
+      <c r="C138" s="2">
+        <v>6</v>
+      </c>
+      <c r="D138" s="6">
+        <v>0</v>
       </c>
       <c r="E138" s="2" t="s">
-        <v>997</v>
-      </c>
-      <c r="F138" s="1">
-        <v>1</v>
-      </c>
+        <v>993</v>
+      </c>
+      <c r="F138" s="1"/>
       <c r="H138" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
     </row>
     <row r="139" spans="1:8">
       <c r="A139" t="s">
+        <v>624</v>
+      </c>
+      <c r="B139" t="s">
         <v>625</v>
       </c>
-      <c r="B139" t="s">
-        <v>626</v>
-      </c>
-      <c r="C139" s="2">
-        <v>6</v>
-      </c>
-      <c r="D139" s="6">
-        <v>0</v>
-      </c>
       <c r="E139" s="2" t="s">
-        <v>998</v>
-      </c>
-      <c r="F139" s="1"/>
+        <v>994</v>
+      </c>
+      <c r="F139" s="1">
+        <v>1</v>
+      </c>
       <c r="H139" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
     </row>
     <row r="140" spans="1:8">
       <c r="A140" t="s">
-        <v>627</v>
+        <v>748</v>
       </c>
       <c r="B140" t="s">
+        <v>749</v>
+      </c>
+      <c r="E140" s="2" t="s">
+        <v>995</v>
+      </c>
+      <c r="F140" s="1">
+        <v>1</v>
+      </c>
+      <c r="H140" t="s">
         <v>628</v>
       </c>
-      <c r="E140" s="2" t="s">
-        <v>999</v>
-      </c>
-      <c r="F140" s="1">
-        <v>1</v>
-      </c>
-      <c r="H140" t="s">
-        <v>631</v>
-      </c>
     </row>
     <row r="141" spans="1:8">
-      <c r="A141" t="s">
-        <v>751</v>
-      </c>
-      <c r="B141" t="s">
-        <v>752</v>
+      <c r="A141" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="B141" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C141" s="3">
+        <v>6</v>
+      </c>
+      <c r="D141" s="4">
+        <v>0.66666666666666663</v>
       </c>
       <c r="E141" s="2" t="s">
-        <v>1000</v>
-      </c>
-      <c r="F141" s="1">
-        <v>1</v>
-      </c>
-      <c r="H141" t="s">
-        <v>631</v>
+        <v>996</v>
+      </c>
+      <c r="F141" s="3"/>
+      <c r="G141" s="1"/>
+      <c r="H141" s="2" t="s">
+        <v>401</v>
       </c>
     </row>
     <row r="142" spans="1:8">
       <c r="A142" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C142" s="3">
         <v>6</v>
       </c>
       <c r="D142" s="4">
-        <v>0.66666666666666663</v>
+        <v>0.70833333333333337</v>
       </c>
       <c r="E142" s="2" t="s">
-        <v>1001</v>
+        <v>997</v>
       </c>
       <c r="F142" s="3"/>
       <c r="G142" s="1"/>
@@ -7652,19 +7645,19 @@
     </row>
     <row r="143" spans="1:8">
       <c r="A143" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C143" s="3">
         <v>6</v>
       </c>
       <c r="D143" s="4">
-        <v>0.70833333333333337</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="E143" s="2" t="s">
-        <v>1002</v>
+        <v>998</v>
       </c>
       <c r="F143" s="3"/>
       <c r="G143" s="1"/>
@@ -7674,19 +7667,19 @@
     </row>
     <row r="144" spans="1:8">
       <c r="A144" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C144" s="3">
         <v>6</v>
       </c>
       <c r="D144" s="4">
-        <v>0.58333333333333337</v>
+        <v>0.75</v>
       </c>
       <c r="E144" s="2" t="s">
-        <v>1003</v>
+        <v>999</v>
       </c>
       <c r="F144" s="3"/>
       <c r="G144" s="1"/>
@@ -7696,19 +7689,19 @@
     </row>
     <row r="145" spans="1:8">
       <c r="A145" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C145" s="3">
         <v>6</v>
       </c>
       <c r="D145" s="4">
-        <v>0.75</v>
+        <v>0.79166666666666663</v>
       </c>
       <c r="E145" s="2" t="s">
-        <v>1004</v>
+        <v>1000</v>
       </c>
       <c r="F145" s="3"/>
       <c r="G145" s="1"/>
@@ -7718,63 +7711,63 @@
     </row>
     <row r="146" spans="1:8">
       <c r="A146" s="2" t="s">
-        <v>220</v>
+        <v>257</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>31</v>
+        <v>143</v>
       </c>
       <c r="C146" s="3">
         <v>6</v>
       </c>
       <c r="D146" s="4">
-        <v>0.79166666666666663</v>
+        <v>0</v>
       </c>
       <c r="E146" s="2" t="s">
-        <v>1005</v>
+        <v>1001</v>
       </c>
       <c r="F146" s="3"/>
       <c r="G146" s="1"/>
-      <c r="H146" s="2" t="s">
-        <v>401</v>
+      <c r="H146" t="s">
+        <v>542</v>
       </c>
     </row>
     <row r="147" spans="1:8">
       <c r="A147" s="2" t="s">
-        <v>257</v>
+        <v>221</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>143</v>
+        <v>32</v>
       </c>
       <c r="C147" s="3">
         <v>6</v>
       </c>
       <c r="D147" s="4">
-        <v>0</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="E147" s="2" t="s">
-        <v>1006</v>
+        <v>1002</v>
       </c>
       <c r="F147" s="3"/>
       <c r="G147" s="1"/>
-      <c r="H147" t="s">
-        <v>542</v>
+      <c r="H147" s="2" t="s">
+        <v>401</v>
       </c>
     </row>
     <row r="148" spans="1:8">
       <c r="A148" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>32</v>
+        <v>493</v>
       </c>
       <c r="C148" s="3">
         <v>6</v>
       </c>
       <c r="D148" s="4">
-        <v>0.83333333333333337</v>
+        <v>0.875</v>
       </c>
       <c r="E148" s="2" t="s">
-        <v>1007</v>
+        <v>1003</v>
       </c>
       <c r="F148" s="3"/>
       <c r="G148" s="1"/>
@@ -7784,19 +7777,19 @@
     </row>
     <row r="149" spans="1:8">
       <c r="A149" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>493</v>
+        <v>25</v>
       </c>
       <c r="C149" s="3">
         <v>6</v>
       </c>
       <c r="D149" s="4">
-        <v>0.875</v>
+        <v>0.54166666666666663</v>
       </c>
       <c r="E149" s="2" t="s">
-        <v>1008</v>
+        <v>1004</v>
       </c>
       <c r="F149" s="3"/>
       <c r="G149" s="1"/>
@@ -7806,19 +7799,19 @@
     </row>
     <row r="150" spans="1:8">
       <c r="A150" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C150" s="3">
         <v>6</v>
       </c>
       <c r="D150" s="4">
-        <v>0.54166666666666663</v>
+        <v>0.625</v>
       </c>
       <c r="E150" s="2" t="s">
-        <v>1009</v>
+        <v>1005</v>
       </c>
       <c r="F150" s="3"/>
       <c r="G150" s="1"/>
@@ -7827,33 +7820,33 @@
       </c>
     </row>
     <row r="151" spans="1:8">
-      <c r="A151" s="2" t="s">
-        <v>224</v>
+      <c r="A151" t="s">
+        <v>258</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>27</v>
+        <v>117</v>
       </c>
       <c r="C151" s="3">
         <v>6</v>
       </c>
       <c r="D151" s="4">
-        <v>0.625</v>
+        <v>0</v>
       </c>
       <c r="E151" s="2" t="s">
-        <v>1010</v>
+        <v>1006</v>
       </c>
       <c r="F151" s="3"/>
       <c r="G151" s="1"/>
-      <c r="H151" s="2" t="s">
-        <v>401</v>
+      <c r="H151" s="1" t="s">
+        <v>402</v>
       </c>
     </row>
     <row r="152" spans="1:8">
       <c r="A152" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C152" s="3">
         <v>6</v>
@@ -7862,7 +7855,7 @@
         <v>0</v>
       </c>
       <c r="E152" s="2" t="s">
-        <v>1011</v>
+        <v>1007</v>
       </c>
       <c r="F152" s="3"/>
       <c r="G152" s="1"/>
@@ -7872,10 +7865,10 @@
     </row>
     <row r="153" spans="1:8">
       <c r="A153" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="C153" s="3">
         <v>6</v>
@@ -7884,7 +7877,7 @@
         <v>0</v>
       </c>
       <c r="E153" s="2" t="s">
-        <v>1012</v>
+        <v>1008</v>
       </c>
       <c r="F153" s="3"/>
       <c r="G153" s="1"/>
@@ -7894,10 +7887,10 @@
     </row>
     <row r="154" spans="1:8">
       <c r="A154" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="C154" s="3">
         <v>6</v>
@@ -7906,7 +7899,7 @@
         <v>0</v>
       </c>
       <c r="E154" s="2" t="s">
-        <v>1013</v>
+        <v>1009</v>
       </c>
       <c r="F154" s="3"/>
       <c r="G154" s="1"/>
@@ -7916,10 +7909,10 @@
     </row>
     <row r="155" spans="1:8">
       <c r="A155" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C155" s="3">
         <v>6</v>
@@ -7928,7 +7921,7 @@
         <v>0</v>
       </c>
       <c r="E155" s="2" t="s">
-        <v>1014</v>
+        <v>1010</v>
       </c>
       <c r="F155" s="3"/>
       <c r="G155" s="1"/>
@@ -7938,10 +7931,10 @@
     </row>
     <row r="156" spans="1:8">
       <c r="A156" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C156" s="3">
         <v>6</v>
@@ -7950,7 +7943,7 @@
         <v>0</v>
       </c>
       <c r="E156" s="2" t="s">
-        <v>1015</v>
+        <v>1011</v>
       </c>
       <c r="F156" s="3"/>
       <c r="G156" s="1"/>
@@ -7959,55 +7952,55 @@
       </c>
     </row>
     <row r="157" spans="1:8">
-      <c r="A157" t="s">
-        <v>263</v>
-      </c>
-      <c r="B157" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="C157" s="3">
-        <v>6</v>
+      <c r="A157" s="11" t="s">
+        <v>629</v>
+      </c>
+      <c r="B157" s="11" t="s">
+        <v>630</v>
+      </c>
+      <c r="C157">
+        <v>14</v>
       </c>
       <c r="D157" s="4">
         <v>0</v>
       </c>
       <c r="E157" s="2" t="s">
-        <v>1016</v>
-      </c>
-      <c r="F157" s="3"/>
-      <c r="G157" s="1"/>
-      <c r="H157" s="1" t="s">
-        <v>402</v>
+        <v>1012</v>
+      </c>
+      <c r="F157"/>
+      <c r="G157"/>
+      <c r="H157" t="s">
+        <v>703</v>
       </c>
     </row>
     <row r="158" spans="1:8">
       <c r="A158" s="11" t="s">
-        <v>632</v>
+        <v>1184</v>
       </c>
       <c r="B158" s="11" t="s">
-        <v>633</v>
-      </c>
-      <c r="C158">
+        <v>1185</v>
+      </c>
+      <c r="C158" s="3">
         <v>14</v>
       </c>
       <c r="D158" s="4">
         <v>0</v>
       </c>
       <c r="E158" s="2" t="s">
-        <v>1017</v>
+        <v>1186</v>
       </c>
       <c r="F158"/>
       <c r="G158"/>
       <c r="H158" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
     </row>
     <row r="159" spans="1:8">
       <c r="A159" s="11" t="s">
-        <v>1190</v>
+        <v>1187</v>
       </c>
       <c r="B159" s="11" t="s">
-        <v>1191</v>
+        <v>1188</v>
       </c>
       <c r="C159" s="3">
         <v>14</v>
@@ -8016,20 +8009,20 @@
         <v>0</v>
       </c>
       <c r="E159" s="2" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="F159"/>
       <c r="G159"/>
       <c r="H159" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
     </row>
     <row r="160" spans="1:8">
       <c r="A160" s="11" t="s">
-        <v>1193</v>
+        <v>1189</v>
       </c>
       <c r="B160" s="11" t="s">
-        <v>1194</v>
+        <v>1190</v>
       </c>
       <c r="C160" s="3">
         <v>14</v>
@@ -8038,915 +8031,913 @@
         <v>0</v>
       </c>
       <c r="E160" s="2" t="s">
-        <v>1197</v>
+        <v>1191</v>
       </c>
       <c r="F160"/>
       <c r="G160"/>
       <c r="H160" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
     </row>
     <row r="161" spans="1:8">
-      <c r="A161" s="11" t="s">
-        <v>1195</v>
-      </c>
-      <c r="B161" s="11" t="s">
-        <v>1196</v>
-      </c>
-      <c r="C161" s="3">
-        <v>14</v>
-      </c>
-      <c r="D161" s="4">
-        <v>0</v>
-      </c>
+      <c r="A161" t="s">
+        <v>631</v>
+      </c>
+      <c r="B161" t="s">
+        <v>632</v>
+      </c>
+      <c r="C161"/>
+      <c r="D161"/>
       <c r="E161" s="2" t="s">
-        <v>1197</v>
-      </c>
-      <c r="F161"/>
+        <v>1013</v>
+      </c>
+      <c r="F161">
+        <v>1</v>
+      </c>
       <c r="G161"/>
       <c r="H161" t="s">
-        <v>706</v>
+        <v>701</v>
       </c>
     </row>
     <row r="162" spans="1:8">
       <c r="A162" t="s">
+        <v>633</v>
+      </c>
+      <c r="B162" t="s">
         <v>634</v>
-      </c>
-      <c r="B162" t="s">
-        <v>635</v>
       </c>
       <c r="C162"/>
       <c r="D162"/>
       <c r="E162" s="2" t="s">
-        <v>1018</v>
+        <v>1014</v>
       </c>
       <c r="F162">
         <v>1</v>
       </c>
       <c r="G162"/>
       <c r="H162" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
     </row>
     <row r="163" spans="1:8">
       <c r="A163" t="s">
-        <v>636</v>
+        <v>743</v>
       </c>
       <c r="B163" t="s">
-        <v>637</v>
+        <v>1016</v>
       </c>
       <c r="C163"/>
       <c r="D163"/>
       <c r="E163" s="2" t="s">
-        <v>1019</v>
+        <v>1015</v>
       </c>
       <c r="F163">
         <v>1</v>
       </c>
       <c r="G163"/>
       <c r="H163" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
     </row>
     <row r="164" spans="1:8">
       <c r="A164" t="s">
-        <v>746</v>
+        <v>635</v>
       </c>
       <c r="B164" t="s">
-        <v>1021</v>
+        <v>636</v>
       </c>
       <c r="C164"/>
       <c r="D164"/>
       <c r="E164" s="2" t="s">
-        <v>1020</v>
+        <v>1017</v>
       </c>
       <c r="F164">
         <v>1</v>
       </c>
       <c r="G164"/>
       <c r="H164" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
     </row>
     <row r="165" spans="1:8">
       <c r="A165" t="s">
+        <v>637</v>
+      </c>
+      <c r="B165" t="s">
         <v>638</v>
-      </c>
-      <c r="B165" t="s">
-        <v>639</v>
       </c>
       <c r="C165"/>
       <c r="D165"/>
       <c r="E165" s="2" t="s">
-        <v>1022</v>
+        <v>1018</v>
       </c>
       <c r="F165">
         <v>1</v>
       </c>
       <c r="G165"/>
       <c r="H165" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
     </row>
     <row r="166" spans="1:8">
       <c r="A166" t="s">
+        <v>639</v>
+      </c>
+      <c r="B166" t="s">
         <v>640</v>
-      </c>
-      <c r="B166" t="s">
-        <v>641</v>
       </c>
       <c r="C166"/>
       <c r="D166"/>
       <c r="E166" s="2" t="s">
-        <v>1023</v>
+        <v>1019</v>
       </c>
       <c r="F166">
         <v>1</v>
       </c>
       <c r="G166"/>
       <c r="H166" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
     </row>
     <row r="167" spans="1:8">
-      <c r="A167" t="s">
+      <c r="A167" s="2" t="s">
+        <v>845</v>
+      </c>
+      <c r="B167" s="1" t="s">
+        <v>846</v>
+      </c>
+      <c r="E167" s="2" t="s">
+        <v>1020</v>
+      </c>
+      <c r="F167" s="2">
+        <v>1</v>
+      </c>
+      <c r="H167" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="168" spans="1:8">
+      <c r="A168" t="s">
+        <v>641</v>
+      </c>
+      <c r="B168" t="s">
         <v>642</v>
       </c>
-      <c r="B167" t="s">
-        <v>643</v>
-      </c>
-      <c r="C167"/>
-      <c r="D167"/>
-      <c r="E167" s="2" t="s">
-        <v>1024</v>
-      </c>
-      <c r="F167">
-        <v>1</v>
-      </c>
-      <c r="G167"/>
-      <c r="H167" t="s">
-        <v>704</v>
-      </c>
-    </row>
-    <row r="168" spans="1:8">
-      <c r="A168" s="2" t="s">
-        <v>849</v>
-      </c>
-      <c r="B168" s="1" t="s">
-        <v>850</v>
-      </c>
+      <c r="C168"/>
+      <c r="D168"/>
       <c r="E168" s="2" t="s">
-        <v>1025</v>
-      </c>
-      <c r="F168" s="2">
-        <v>1</v>
-      </c>
+        <v>1021</v>
+      </c>
+      <c r="F168">
+        <v>1</v>
+      </c>
+      <c r="G168"/>
       <c r="H168" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
     </row>
     <row r="169" spans="1:8">
       <c r="A169" t="s">
+        <v>643</v>
+      </c>
+      <c r="B169" t="s">
         <v>644</v>
-      </c>
-      <c r="B169" t="s">
-        <v>645</v>
       </c>
       <c r="C169"/>
       <c r="D169"/>
       <c r="E169" s="2" t="s">
-        <v>1026</v>
+        <v>1022</v>
       </c>
       <c r="F169">
         <v>1</v>
       </c>
       <c r="G169"/>
       <c r="H169" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
     </row>
     <row r="170" spans="1:8">
       <c r="A170" t="s">
+        <v>645</v>
+      </c>
+      <c r="B170" t="s">
         <v>646</v>
-      </c>
-      <c r="B170" t="s">
-        <v>647</v>
       </c>
       <c r="C170"/>
       <c r="D170"/>
       <c r="E170" s="2" t="s">
-        <v>1027</v>
+        <v>1023</v>
       </c>
       <c r="F170">
         <v>1</v>
       </c>
       <c r="G170"/>
       <c r="H170" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
     </row>
     <row r="171" spans="1:8">
       <c r="A171" t="s">
+        <v>647</v>
+      </c>
+      <c r="B171" t="s">
         <v>648</v>
-      </c>
-      <c r="B171" t="s">
-        <v>649</v>
       </c>
       <c r="C171"/>
       <c r="D171"/>
       <c r="E171" s="2" t="s">
-        <v>1028</v>
+        <v>1024</v>
       </c>
       <c r="F171">
         <v>1</v>
       </c>
       <c r="G171"/>
       <c r="H171" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
     </row>
     <row r="172" spans="1:8">
       <c r="A172" t="s">
+        <v>649</v>
+      </c>
+      <c r="B172" t="s">
         <v>650</v>
-      </c>
-      <c r="B172" t="s">
-        <v>651</v>
       </c>
       <c r="C172"/>
       <c r="D172"/>
       <c r="E172" s="2" t="s">
-        <v>1029</v>
+        <v>1025</v>
       </c>
       <c r="F172">
         <v>1</v>
       </c>
       <c r="G172"/>
       <c r="H172" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
     </row>
     <row r="173" spans="1:8">
       <c r="A173" t="s">
+        <v>651</v>
+      </c>
+      <c r="B173" t="s">
         <v>652</v>
-      </c>
-      <c r="B173" t="s">
-        <v>653</v>
       </c>
       <c r="C173"/>
       <c r="D173"/>
       <c r="E173" s="2" t="s">
-        <v>1030</v>
+        <v>1026</v>
       </c>
       <c r="F173">
         <v>1</v>
       </c>
       <c r="G173"/>
       <c r="H173" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
     </row>
     <row r="174" spans="1:8">
       <c r="A174" t="s">
-        <v>654</v>
-      </c>
-      <c r="B174" t="s">
-        <v>655</v>
+        <v>653</v>
+      </c>
+      <c r="B174" s="12" t="s">
+        <v>741</v>
       </c>
       <c r="C174"/>
       <c r="D174"/>
       <c r="E174" s="2" t="s">
-        <v>1031</v>
+        <v>1027</v>
       </c>
       <c r="F174">
         <v>1</v>
       </c>
       <c r="G174"/>
       <c r="H174" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
     </row>
     <row r="175" spans="1:8">
       <c r="A175" t="s">
-        <v>656</v>
-      </c>
-      <c r="B175" s="12" t="s">
-        <v>744</v>
+        <v>654</v>
+      </c>
+      <c r="B175" t="s">
+        <v>655</v>
       </c>
       <c r="C175"/>
       <c r="D175"/>
       <c r="E175" s="2" t="s">
-        <v>1032</v>
+        <v>1028</v>
       </c>
       <c r="F175">
         <v>1</v>
       </c>
       <c r="G175"/>
       <c r="H175" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
     </row>
     <row r="176" spans="1:8">
       <c r="A176" t="s">
+        <v>656</v>
+      </c>
+      <c r="B176" t="s">
         <v>657</v>
-      </c>
-      <c r="B176" t="s">
-        <v>658</v>
       </c>
       <c r="C176"/>
       <c r="D176"/>
       <c r="E176" s="2" t="s">
-        <v>1033</v>
+        <v>1029</v>
       </c>
       <c r="F176">
         <v>1</v>
       </c>
       <c r="G176"/>
       <c r="H176" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
     </row>
     <row r="177" spans="1:8">
       <c r="A177" t="s">
+        <v>658</v>
+      </c>
+      <c r="B177" t="s">
         <v>659</v>
-      </c>
-      <c r="B177" t="s">
-        <v>660</v>
       </c>
       <c r="C177"/>
       <c r="D177"/>
       <c r="E177" s="2" t="s">
-        <v>1034</v>
+        <v>1030</v>
       </c>
       <c r="F177">
         <v>1</v>
       </c>
       <c r="G177"/>
       <c r="H177" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
     </row>
     <row r="178" spans="1:8">
       <c r="A178" t="s">
+        <v>660</v>
+      </c>
+      <c r="B178" t="s">
         <v>661</v>
-      </c>
-      <c r="B178" t="s">
-        <v>662</v>
       </c>
       <c r="C178"/>
       <c r="D178"/>
       <c r="E178" s="2" t="s">
-        <v>1035</v>
+        <v>1031</v>
       </c>
       <c r="F178">
         <v>1</v>
       </c>
       <c r="G178"/>
       <c r="H178" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
     </row>
     <row r="179" spans="1:8">
       <c r="A179" t="s">
+        <v>662</v>
+      </c>
+      <c r="B179" t="s">
         <v>663</v>
-      </c>
-      <c r="B179" t="s">
-        <v>664</v>
       </c>
       <c r="C179"/>
       <c r="D179"/>
       <c r="E179" s="2" t="s">
-        <v>1036</v>
+        <v>1032</v>
       </c>
       <c r="F179">
         <v>1</v>
       </c>
       <c r="G179"/>
       <c r="H179" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
     </row>
     <row r="180" spans="1:8">
       <c r="A180" t="s">
+        <v>664</v>
+      </c>
+      <c r="B180" t="s">
         <v>665</v>
-      </c>
-      <c r="B180" t="s">
-        <v>666</v>
       </c>
       <c r="C180"/>
       <c r="D180"/>
       <c r="E180" s="2" t="s">
-        <v>1037</v>
+        <v>1033</v>
       </c>
       <c r="F180">
         <v>1</v>
       </c>
       <c r="G180"/>
       <c r="H180" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
     </row>
     <row r="181" spans="1:8">
       <c r="A181" t="s">
+        <v>666</v>
+      </c>
+      <c r="B181" t="s">
         <v>667</v>
-      </c>
-      <c r="B181" t="s">
-        <v>668</v>
       </c>
       <c r="C181"/>
       <c r="D181"/>
       <c r="E181" s="2" t="s">
-        <v>1038</v>
+        <v>1034</v>
       </c>
       <c r="F181">
         <v>1</v>
       </c>
       <c r="G181"/>
       <c r="H181" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
     </row>
     <row r="182" spans="1:8">
       <c r="A182" t="s">
+        <v>668</v>
+      </c>
+      <c r="B182" t="s">
         <v>669</v>
-      </c>
-      <c r="B182" t="s">
-        <v>670</v>
       </c>
       <c r="C182"/>
       <c r="D182"/>
       <c r="E182" s="2" t="s">
-        <v>1039</v>
+        <v>1035</v>
       </c>
       <c r="F182">
         <v>1</v>
       </c>
       <c r="G182"/>
       <c r="H182" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
     </row>
     <row r="183" spans="1:8">
       <c r="A183" t="s">
+        <v>670</v>
+      </c>
+      <c r="B183" t="s">
         <v>671</v>
-      </c>
-      <c r="B183" t="s">
-        <v>672</v>
       </c>
       <c r="C183"/>
       <c r="D183"/>
       <c r="E183" s="2" t="s">
-        <v>1040</v>
+        <v>1036</v>
       </c>
       <c r="F183">
         <v>1</v>
       </c>
       <c r="G183"/>
       <c r="H183" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
     </row>
     <row r="184" spans="1:8">
       <c r="A184" t="s">
+        <v>672</v>
+      </c>
+      <c r="B184" t="s">
         <v>673</v>
-      </c>
-      <c r="B184" t="s">
-        <v>674</v>
       </c>
       <c r="C184"/>
       <c r="D184"/>
       <c r="E184" s="2" t="s">
-        <v>1041</v>
+        <v>1037</v>
       </c>
       <c r="F184">
         <v>1</v>
       </c>
       <c r="G184"/>
       <c r="H184" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
     </row>
     <row r="185" spans="1:8">
       <c r="A185" t="s">
+        <v>674</v>
+      </c>
+      <c r="B185" t="s">
         <v>675</v>
-      </c>
-      <c r="B185" t="s">
-        <v>676</v>
       </c>
       <c r="C185"/>
       <c r="D185"/>
       <c r="E185" s="2" t="s">
-        <v>1042</v>
+        <v>1038</v>
       </c>
       <c r="F185">
         <v>1</v>
       </c>
       <c r="G185"/>
       <c r="H185" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
     </row>
     <row r="186" spans="1:8">
       <c r="A186" t="s">
+        <v>676</v>
+      </c>
+      <c r="B186" t="s">
         <v>677</v>
-      </c>
-      <c r="B186" t="s">
-        <v>678</v>
       </c>
       <c r="C186"/>
       <c r="D186"/>
       <c r="E186" s="2" t="s">
-        <v>1043</v>
+        <v>1039</v>
       </c>
       <c r="F186">
         <v>1</v>
       </c>
       <c r="G186"/>
       <c r="H186" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
     </row>
     <row r="187" spans="1:8">
       <c r="A187" t="s">
+        <v>678</v>
+      </c>
+      <c r="B187" t="s">
         <v>679</v>
       </c>
-      <c r="B187" t="s">
-        <v>680</v>
-      </c>
-      <c r="C187"/>
-      <c r="D187"/>
+      <c r="C187">
+        <v>14</v>
+      </c>
+      <c r="D187" s="4">
+        <v>0</v>
+      </c>
       <c r="E187" s="2" t="s">
-        <v>1044</v>
-      </c>
-      <c r="F187">
-        <v>1</v>
-      </c>
+        <v>1040</v>
+      </c>
+      <c r="F187"/>
       <c r="G187"/>
       <c r="H187" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
     </row>
     <row r="188" spans="1:8">
       <c r="A188" t="s">
+        <v>680</v>
+      </c>
+      <c r="B188" t="s">
         <v>681</v>
       </c>
-      <c r="B188" t="s">
-        <v>682</v>
-      </c>
-      <c r="C188">
-        <v>14</v>
-      </c>
-      <c r="D188" s="4">
-        <v>0</v>
-      </c>
+      <c r="C188"/>
+      <c r="D188"/>
       <c r="E188" s="2" t="s">
-        <v>1045</v>
-      </c>
-      <c r="F188"/>
+        <v>1041</v>
+      </c>
+      <c r="F188">
+        <v>1</v>
+      </c>
       <c r="G188"/>
       <c r="H188" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
     </row>
     <row r="189" spans="1:8">
       <c r="A189" t="s">
+        <v>682</v>
+      </c>
+      <c r="B189" t="s">
         <v>683</v>
-      </c>
-      <c r="B189" t="s">
-        <v>684</v>
       </c>
       <c r="C189"/>
       <c r="D189"/>
       <c r="E189" s="2" t="s">
-        <v>1046</v>
+        <v>1042</v>
       </c>
       <c r="F189">
         <v>1</v>
       </c>
       <c r="G189"/>
       <c r="H189" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
     </row>
     <row r="190" spans="1:8">
-      <c r="A190" t="s">
-        <v>685</v>
-      </c>
-      <c r="B190" t="s">
-        <v>686</v>
+      <c r="A190" s="12" t="s">
+        <v>684</v>
+      </c>
+      <c r="B190" s="12" t="s">
+        <v>742</v>
       </c>
       <c r="C190"/>
       <c r="D190"/>
       <c r="E190" s="2" t="s">
-        <v>1047</v>
+        <v>1043</v>
       </c>
       <c r="F190">
         <v>1</v>
       </c>
       <c r="G190"/>
       <c r="H190" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
     </row>
     <row r="191" spans="1:8">
-      <c r="A191" s="12" t="s">
-        <v>687</v>
-      </c>
-      <c r="B191" s="12" t="s">
-        <v>745</v>
+      <c r="A191" t="s">
+        <v>685</v>
+      </c>
+      <c r="B191" t="s">
+        <v>686</v>
       </c>
       <c r="C191"/>
       <c r="D191"/>
       <c r="E191" s="2" t="s">
-        <v>1048</v>
+        <v>1044</v>
       </c>
       <c r="F191">
         <v>1</v>
       </c>
       <c r="G191"/>
       <c r="H191" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
     </row>
     <row r="192" spans="1:8">
       <c r="A192" t="s">
+        <v>687</v>
+      </c>
+      <c r="B192" t="s">
         <v>688</v>
       </c>
-      <c r="B192" t="s">
-        <v>689</v>
-      </c>
-      <c r="C192"/>
-      <c r="D192"/>
+      <c r="C192">
+        <v>14</v>
+      </c>
+      <c r="D192" s="4">
+        <v>0</v>
+      </c>
       <c r="E192" s="2" t="s">
-        <v>1049</v>
-      </c>
-      <c r="F192">
-        <v>1</v>
-      </c>
+        <v>1045</v>
+      </c>
+      <c r="F192"/>
       <c r="G192"/>
       <c r="H192" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
     </row>
     <row r="193" spans="1:8">
       <c r="A193" t="s">
+        <v>689</v>
+      </c>
+      <c r="B193" t="s">
         <v>690</v>
       </c>
-      <c r="B193" t="s">
-        <v>691</v>
-      </c>
-      <c r="C193">
-        <v>14</v>
-      </c>
-      <c r="D193" s="4">
-        <v>0</v>
-      </c>
+      <c r="C193"/>
+      <c r="D193"/>
       <c r="E193" s="2" t="s">
-        <v>1050</v>
-      </c>
-      <c r="F193"/>
+        <v>1046</v>
+      </c>
+      <c r="F193">
+        <v>1</v>
+      </c>
       <c r="G193"/>
       <c r="H193" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
     </row>
     <row r="194" spans="1:8">
       <c r="A194" t="s">
+        <v>691</v>
+      </c>
+      <c r="B194" t="s">
         <v>692</v>
-      </c>
-      <c r="B194" t="s">
-        <v>693</v>
       </c>
       <c r="C194"/>
       <c r="D194"/>
       <c r="E194" s="2" t="s">
-        <v>1051</v>
+        <v>1047</v>
       </c>
       <c r="F194">
         <v>1</v>
       </c>
       <c r="G194"/>
       <c r="H194" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
     </row>
     <row r="195" spans="1:8">
       <c r="A195" t="s">
+        <v>693</v>
+      </c>
+      <c r="B195" t="s">
         <v>694</v>
-      </c>
-      <c r="B195" t="s">
-        <v>695</v>
       </c>
       <c r="C195"/>
       <c r="D195"/>
       <c r="E195" s="2" t="s">
-        <v>1052</v>
+        <v>1048</v>
       </c>
       <c r="F195">
         <v>1</v>
       </c>
       <c r="G195"/>
       <c r="H195" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
     </row>
     <row r="196" spans="1:8">
       <c r="A196" t="s">
+        <v>695</v>
+      </c>
+      <c r="B196" t="s">
         <v>696</v>
-      </c>
-      <c r="B196" t="s">
-        <v>697</v>
       </c>
       <c r="C196"/>
       <c r="D196"/>
       <c r="E196" s="2" t="s">
-        <v>1053</v>
+        <v>1049</v>
       </c>
       <c r="F196">
         <v>1</v>
       </c>
       <c r="G196"/>
       <c r="H196" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
     </row>
     <row r="197" spans="1:8">
       <c r="A197" t="s">
+        <v>697</v>
+      </c>
+      <c r="B197" t="s">
         <v>698</v>
-      </c>
-      <c r="B197" t="s">
-        <v>699</v>
       </c>
       <c r="C197"/>
       <c r="D197"/>
       <c r="E197" s="2" t="s">
-        <v>1054</v>
+        <v>1050</v>
       </c>
       <c r="F197">
         <v>1</v>
       </c>
       <c r="G197"/>
       <c r="H197" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
     </row>
     <row r="198" spans="1:8">
       <c r="A198" t="s">
+        <v>699</v>
+      </c>
+      <c r="B198" t="s">
         <v>700</v>
-      </c>
-      <c r="B198" t="s">
-        <v>701</v>
       </c>
       <c r="C198"/>
       <c r="D198"/>
       <c r="E198" s="2" t="s">
-        <v>1055</v>
+        <v>1051</v>
       </c>
       <c r="F198">
         <v>1</v>
       </c>
       <c r="G198"/>
       <c r="H198" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
     </row>
     <row r="199" spans="1:8">
-      <c r="A199" t="s">
-        <v>702</v>
-      </c>
-      <c r="B199" t="s">
-        <v>703</v>
-      </c>
-      <c r="C199"/>
-      <c r="D199"/>
+      <c r="A199" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="B199" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="C199" s="3">
+        <v>6</v>
+      </c>
+      <c r="D199" s="4">
+        <v>0</v>
+      </c>
       <c r="E199" s="2" t="s">
-        <v>1056</v>
-      </c>
-      <c r="F199">
-        <v>1</v>
-      </c>
-      <c r="G199"/>
+        <v>1052</v>
+      </c>
+      <c r="F199" s="3"/>
+      <c r="G199" s="1"/>
       <c r="H199" t="s">
-        <v>704</v>
+        <v>543</v>
       </c>
     </row>
     <row r="200" spans="1:8">
       <c r="A200" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="C200" s="3">
         <v>6</v>
       </c>
       <c r="D200" s="4">
-        <v>0</v>
+        <v>0.54166666666666663</v>
       </c>
       <c r="E200" s="2" t="s">
-        <v>1057</v>
+        <v>1053</v>
       </c>
       <c r="F200" s="3"/>
       <c r="G200" s="1"/>
-      <c r="H200" t="s">
-        <v>543</v>
+      <c r="H200" s="1" t="s">
+        <v>403</v>
       </c>
     </row>
     <row r="201" spans="1:8">
       <c r="A201" s="2" t="s">
-        <v>265</v>
+        <v>809</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="C201" s="3">
-        <v>6</v>
-      </c>
-      <c r="D201" s="4">
-        <v>0.54166666666666663</v>
+        <v>772</v>
       </c>
       <c r="E201" s="2" t="s">
-        <v>1058</v>
-      </c>
-      <c r="F201" s="3"/>
-      <c r="G201" s="1"/>
-      <c r="H201" s="1" t="s">
-        <v>403</v>
+        <v>1054</v>
+      </c>
+      <c r="F201" s="2">
+        <v>1</v>
+      </c>
+      <c r="H201" s="2" t="s">
+        <v>811</v>
       </c>
     </row>
     <row r="202" spans="1:8">
       <c r="A202" s="2" t="s">
-        <v>813</v>
+        <v>810</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="E202" s="2" t="s">
-        <v>1059</v>
+        <v>1055</v>
       </c>
       <c r="F202" s="2">
         <v>1</v>
       </c>
       <c r="H202" s="2" t="s">
-        <v>815</v>
+        <v>811</v>
       </c>
     </row>
     <row r="203" spans="1:8">
       <c r="A203" s="2" t="s">
-        <v>814</v>
+        <v>225</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>776</v>
+        <v>104</v>
+      </c>
+      <c r="C203" s="3">
+        <v>13</v>
+      </c>
+      <c r="D203" s="4">
+        <v>0</v>
       </c>
       <c r="E203" s="2" t="s">
-        <v>1060</v>
-      </c>
-      <c r="F203" s="2">
-        <v>1</v>
-      </c>
-      <c r="H203" s="2" t="s">
-        <v>815</v>
+        <v>1056</v>
+      </c>
+      <c r="F203" s="3"/>
+      <c r="G203" s="1"/>
+      <c r="H203" s="1" t="s">
+        <v>404</v>
       </c>
     </row>
     <row r="204" spans="1:8">
-      <c r="A204" s="2" t="s">
-        <v>225</v>
+      <c r="A204" t="s">
+        <v>487</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="C204" s="3">
-        <v>13</v>
-      </c>
-      <c r="D204" s="4">
-        <v>0</v>
+        <v>331</v>
       </c>
       <c r="E204" s="2" t="s">
-        <v>1061</v>
-      </c>
-      <c r="F204" s="3"/>
-      <c r="G204" s="1"/>
-      <c r="H204" s="1" t="s">
-        <v>404</v>
+        <v>1057</v>
+      </c>
+      <c r="F204" s="2">
+        <v>1</v>
+      </c>
+      <c r="G204" s="2" t="s">
+        <v>550</v>
+      </c>
+      <c r="H204" s="2" t="s">
+        <v>442</v>
       </c>
     </row>
     <row r="205" spans="1:8">
       <c r="A205" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E205" s="2" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
       <c r="F205" s="2">
         <v>1</v>
       </c>
       <c r="G205" s="2" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="H205" s="2" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="206" spans="1:8">
@@ -8957,13 +8948,13 @@
         <v>332</v>
       </c>
       <c r="E206" s="2" t="s">
-        <v>1065</v>
+        <v>1061</v>
       </c>
       <c r="F206" s="2">
         <v>1</v>
       </c>
       <c r="G206" s="2" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H206" s="2" t="s">
         <v>443</v>
@@ -8971,91 +8962,91 @@
     </row>
     <row r="207" spans="1:8">
       <c r="A207" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>332</v>
+        <v>330</v>
+      </c>
+      <c r="C207" s="2">
+        <v>8</v>
+      </c>
+      <c r="D207" s="6">
+        <v>0</v>
       </c>
       <c r="E207" s="2" t="s">
-        <v>1066</v>
-      </c>
-      <c r="F207" s="2">
-        <v>1</v>
-      </c>
-      <c r="G207" s="2" t="s">
-        <v>551</v>
-      </c>
+        <v>1058</v>
+      </c>
+      <c r="F207" s="3"/>
       <c r="H207" s="2" t="s">
-        <v>443</v>
+        <v>739</v>
       </c>
     </row>
     <row r="208" spans="1:8">
-      <c r="A208" t="s">
-        <v>489</v>
+      <c r="A208" s="2" t="s">
+        <v>577</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>330</v>
-      </c>
-      <c r="C208" s="2">
-        <v>8</v>
-      </c>
-      <c r="D208" s="6">
-        <v>0</v>
-      </c>
+        <v>578</v>
+      </c>
+      <c r="D208" s="6"/>
       <c r="E208" s="2" t="s">
-        <v>1063</v>
-      </c>
-      <c r="F208" s="3"/>
-      <c r="H208" s="2" t="s">
-        <v>742</v>
+        <v>1059</v>
+      </c>
+      <c r="F208" s="3">
+        <v>1</v>
+      </c>
+      <c r="H208" s="7" t="s">
+        <v>579</v>
       </c>
     </row>
     <row r="209" spans="1:8">
       <c r="A209" s="2" t="s">
-        <v>580</v>
+        <v>226</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>581</v>
-      </c>
-      <c r="D209" s="6"/>
+        <v>160</v>
+      </c>
+      <c r="C209" s="3">
+        <v>13</v>
+      </c>
+      <c r="D209" s="5">
+        <v>0</v>
+      </c>
       <c r="E209" s="2" t="s">
-        <v>1064</v>
-      </c>
-      <c r="F209" s="3">
-        <v>1</v>
-      </c>
-      <c r="H209" s="7" t="s">
-        <v>582</v>
+        <v>1062</v>
+      </c>
+      <c r="F209" s="3"/>
+      <c r="G209" s="1"/>
+      <c r="H209" s="1" t="s">
+        <v>405</v>
       </c>
     </row>
     <row r="210" spans="1:8">
-      <c r="A210" s="2" t="s">
-        <v>226</v>
+      <c r="A210" t="s">
+        <v>490</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="C210" s="3">
-        <v>13</v>
-      </c>
-      <c r="D210" s="5">
+        <v>334</v>
+      </c>
+      <c r="C210" s="2">
+        <v>10</v>
+      </c>
+      <c r="D210" s="6">
         <v>0</v>
       </c>
       <c r="E210" s="2" t="s">
-        <v>1067</v>
-      </c>
-      <c r="F210" s="3"/>
-      <c r="G210" s="1"/>
-      <c r="H210" s="1" t="s">
-        <v>405</v>
+        <v>1063</v>
+      </c>
+      <c r="H210" s="2" t="s">
+        <v>738</v>
       </c>
     </row>
     <row r="211" spans="1:8">
       <c r="A211" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>334</v>
+        <v>494</v>
       </c>
       <c r="C211" s="2">
         <v>10</v>
@@ -9064,150 +9055,150 @@
         <v>0</v>
       </c>
       <c r="E211" s="2" t="s">
-        <v>1068</v>
+        <v>1064</v>
       </c>
       <c r="H211" s="2" t="s">
-        <v>741</v>
+        <v>737</v>
       </c>
     </row>
     <row r="212" spans="1:8">
       <c r="A212" t="s">
-        <v>491</v>
-      </c>
-      <c r="B212" s="1" t="s">
-        <v>494</v>
-      </c>
-      <c r="C212" s="2">
-        <v>10</v>
-      </c>
-      <c r="D212" s="6">
-        <v>0</v>
-      </c>
+        <v>744</v>
+      </c>
+      <c r="B212" t="s">
+        <v>727</v>
+      </c>
+      <c r="C212"/>
+      <c r="D212" s="11"/>
       <c r="E212" s="2" t="s">
-        <v>1069</v>
-      </c>
-      <c r="H212" s="2" t="s">
-        <v>740</v>
+        <v>1065</v>
+      </c>
+      <c r="F212">
+        <v>1</v>
+      </c>
+      <c r="G212"/>
+      <c r="H212" s="11" t="s">
+        <v>728</v>
       </c>
     </row>
     <row r="213" spans="1:8">
       <c r="A213" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="B213" t="s">
-        <v>730</v>
-      </c>
-      <c r="C213"/>
-      <c r="D213" s="11"/>
+        <v>729</v>
+      </c>
+      <c r="C213">
+        <v>10</v>
+      </c>
+      <c r="D213" s="4">
+        <v>0</v>
+      </c>
       <c r="E213" s="2" t="s">
-        <v>1070</v>
-      </c>
-      <c r="F213">
-        <v>1</v>
-      </c>
+        <v>1066</v>
+      </c>
+      <c r="F213"/>
       <c r="G213"/>
       <c r="H213" s="11" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
     </row>
     <row r="214" spans="1:8">
       <c r="A214" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="B214" t="s">
-        <v>732</v>
-      </c>
-      <c r="C214">
-        <v>10</v>
-      </c>
-      <c r="D214" s="4">
-        <v>0</v>
-      </c>
+        <v>731</v>
+      </c>
+      <c r="C214"/>
+      <c r="D214" s="11"/>
       <c r="E214" s="2" t="s">
-        <v>1071</v>
-      </c>
-      <c r="F214"/>
+        <v>1067</v>
+      </c>
+      <c r="F214">
+        <v>1</v>
+      </c>
       <c r="G214"/>
       <c r="H214" s="11" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
     </row>
     <row r="215" spans="1:8">
-      <c r="A215" t="s">
-        <v>749</v>
-      </c>
-      <c r="B215" t="s">
-        <v>734</v>
-      </c>
-      <c r="C215"/>
-      <c r="D215" s="11"/>
+      <c r="A215" s="2" t="s">
+        <v>750</v>
+      </c>
+      <c r="B215" s="1" t="s">
+        <v>751</v>
+      </c>
       <c r="E215" s="2" t="s">
-        <v>1072</v>
-      </c>
-      <c r="F215">
-        <v>1</v>
-      </c>
-      <c r="G215"/>
-      <c r="H215" s="11" t="s">
-        <v>735</v>
+        <v>1068</v>
+      </c>
+      <c r="F215" s="2">
+        <v>1</v>
+      </c>
+      <c r="H215" s="2" t="s">
+        <v>752</v>
       </c>
     </row>
     <row r="216" spans="1:8">
-      <c r="A216" s="2" t="s">
-        <v>753</v>
+      <c r="A216" t="s">
+        <v>317</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>754</v>
+        <v>316</v>
+      </c>
+      <c r="C216" s="3">
+        <v>7</v>
+      </c>
+      <c r="D216" s="4">
+        <v>0</v>
       </c>
       <c r="E216" s="2" t="s">
-        <v>1073</v>
-      </c>
-      <c r="F216" s="2">
-        <v>1</v>
-      </c>
-      <c r="H216" s="2" t="s">
-        <v>755</v>
+        <v>1069</v>
+      </c>
+      <c r="F216" s="3"/>
+      <c r="G216" s="1"/>
+      <c r="H216" s="1" t="s">
+        <v>445</v>
       </c>
     </row>
     <row r="217" spans="1:8">
-      <c r="A217" t="s">
-        <v>317</v>
+      <c r="A217" s="2" t="s">
+        <v>307</v>
       </c>
       <c r="B217" s="1" t="s">
-        <v>316</v>
+        <v>61</v>
       </c>
       <c r="C217" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D217" s="4">
         <v>0</v>
       </c>
       <c r="E217" s="2" t="s">
-        <v>1074</v>
+        <v>1070</v>
       </c>
       <c r="F217" s="3"/>
       <c r="G217" s="1"/>
       <c r="H217" s="1" t="s">
-        <v>445</v>
+        <v>406</v>
       </c>
     </row>
     <row r="218" spans="1:8">
       <c r="A218" s="2" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B218" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C218" s="3">
-        <v>6</v>
-      </c>
-      <c r="D218" s="4">
-        <v>0</v>
-      </c>
+        <v>63</v>
+      </c>
+      <c r="C218" s="3"/>
+      <c r="D218" s="4"/>
       <c r="E218" s="2" t="s">
-        <v>1075</v>
-      </c>
-      <c r="F218" s="3"/>
+        <v>1071</v>
+      </c>
+      <c r="F218" s="3">
+        <v>1</v>
+      </c>
       <c r="G218" s="1"/>
       <c r="H218" s="1" t="s">
         <v>406</v>
@@ -9215,19 +9206,21 @@
     </row>
     <row r="219" spans="1:8">
       <c r="A219" s="2" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B219" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="C219" s="3"/>
-      <c r="D219" s="4"/>
+        <v>62</v>
+      </c>
+      <c r="C219" s="3">
+        <v>10</v>
+      </c>
+      <c r="D219" s="4">
+        <v>0</v>
+      </c>
       <c r="E219" s="2" t="s">
-        <v>1076</v>
-      </c>
-      <c r="F219" s="3">
-        <v>1</v>
-      </c>
+        <v>1072</v>
+      </c>
+      <c r="F219" s="3"/>
       <c r="G219" s="1"/>
       <c r="H219" s="1" t="s">
         <v>406</v>
@@ -9235,93 +9228,91 @@
     </row>
     <row r="220" spans="1:8">
       <c r="A220" s="2" t="s">
-        <v>308</v>
+        <v>768</v>
       </c>
       <c r="B220" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="C220" s="3">
-        <v>10</v>
-      </c>
-      <c r="D220" s="4">
-        <v>0</v>
+        <v>765</v>
       </c>
       <c r="E220" s="2" t="s">
-        <v>1077</v>
-      </c>
-      <c r="F220" s="3"/>
-      <c r="G220" s="1"/>
-      <c r="H220" s="1" t="s">
-        <v>406</v>
+        <v>1073</v>
+      </c>
+      <c r="F220" s="2">
+        <v>1</v>
+      </c>
+      <c r="H220" s="7" t="s">
+        <v>798</v>
       </c>
     </row>
     <row r="221" spans="1:8">
       <c r="A221" s="2" t="s">
+        <v>770</v>
+      </c>
+      <c r="B221" s="1" t="s">
         <v>771</v>
       </c>
-      <c r="B221" s="1" t="s">
-        <v>768</v>
-      </c>
       <c r="E221" s="2" t="s">
-        <v>1078</v>
-      </c>
-      <c r="F221" s="2">
-        <v>1</v>
+        <v>1074</v>
       </c>
       <c r="H221" s="7" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
     </row>
     <row r="222" spans="1:8">
       <c r="A222" s="2" t="s">
-        <v>773</v>
+        <v>821</v>
       </c>
       <c r="B222" s="1" t="s">
-        <v>774</v>
+        <v>775</v>
+      </c>
+      <c r="C222" s="2">
+        <v>6</v>
+      </c>
+      <c r="D222" s="6">
+        <v>0</v>
       </c>
       <c r="E222" s="2" t="s">
-        <v>1079</v>
-      </c>
-      <c r="H222" s="7" t="s">
-        <v>802</v>
+        <v>1075</v>
+      </c>
+      <c r="H222" s="2" t="s">
+        <v>822</v>
       </c>
     </row>
     <row r="223" spans="1:8">
       <c r="A223" s="2" t="s">
-        <v>825</v>
+        <v>336</v>
       </c>
       <c r="B223" s="1" t="s">
-        <v>778</v>
-      </c>
-      <c r="C223" s="2">
-        <v>6</v>
-      </c>
-      <c r="D223" s="6">
-        <v>0</v>
-      </c>
+        <v>335</v>
+      </c>
+      <c r="D223" s="6"/>
       <c r="E223" s="2" t="s">
-        <v>1080</v>
-      </c>
-      <c r="H223" s="2" t="s">
-        <v>826</v>
+        <v>1076</v>
+      </c>
+      <c r="F223" s="2">
+        <v>1</v>
+      </c>
+      <c r="H223" t="s">
+        <v>544</v>
       </c>
     </row>
     <row r="224" spans="1:8">
-      <c r="A224" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="B224" s="1" t="s">
-        <v>335</v>
-      </c>
-      <c r="D224" s="6"/>
-      <c r="E224" s="2" t="s">
-        <v>1081</v>
-      </c>
-      <c r="F224" s="2">
-        <v>1</v>
-      </c>
-      <c r="H224" t="s">
-        <v>544</v>
+      <c r="A224" t="s">
+        <v>704</v>
+      </c>
+      <c r="B224" t="s">
+        <v>705</v>
+      </c>
+      <c r="C224">
+        <v>15</v>
+      </c>
+      <c r="D224" s="4">
+        <v>0</v>
+      </c>
+      <c r="E224"/>
+      <c r="F224"/>
+      <c r="G224"/>
+      <c r="H224" s="11" t="s">
+        <v>706</v>
       </c>
     </row>
     <row r="225" spans="1:8">
@@ -9337,7 +9328,9 @@
       <c r="D225" s="4">
         <v>0</v>
       </c>
-      <c r="E225"/>
+      <c r="E225" t="s">
+        <v>1077</v>
+      </c>
       <c r="F225"/>
       <c r="G225"/>
       <c r="H225" s="11" t="s">
@@ -9358,7 +9351,7 @@
         <v>0</v>
       </c>
       <c r="E226" t="s">
-        <v>1082</v>
+        <v>1078</v>
       </c>
       <c r="F226"/>
       <c r="G226"/>
@@ -9374,13 +9367,13 @@
         <v>714</v>
       </c>
       <c r="C227">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D227" s="4">
         <v>0</v>
       </c>
       <c r="E227" t="s">
-        <v>1083</v>
+        <v>1079</v>
       </c>
       <c r="F227"/>
       <c r="G227"/>
@@ -9396,14 +9389,12 @@
         <v>717</v>
       </c>
       <c r="C228">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D228" s="4">
         <v>0</v>
       </c>
-      <c r="E228" t="s">
-        <v>1084</v>
-      </c>
+      <c r="E228"/>
       <c r="F228"/>
       <c r="G228"/>
       <c r="H228" s="11" t="s">
@@ -9411,185 +9402,185 @@
       </c>
     </row>
     <row r="229" spans="1:8">
-      <c r="A229" t="s">
-        <v>719</v>
-      </c>
-      <c r="B229" t="s">
-        <v>720</v>
-      </c>
-      <c r="C229">
-        <v>15</v>
-      </c>
-      <c r="D229" s="4">
-        <v>0</v>
-      </c>
-      <c r="E229"/>
-      <c r="F229"/>
-      <c r="G229"/>
-      <c r="H229" s="11" t="s">
-        <v>721</v>
+      <c r="A229" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B229" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="C229" s="1"/>
+      <c r="D229" s="1"/>
+      <c r="E229" s="1" t="s">
+        <v>1080</v>
+      </c>
+      <c r="F229" s="3">
+        <v>1</v>
+      </c>
+      <c r="G229" s="1" t="s">
+        <v>806</v>
+      </c>
+      <c r="H229" s="2" t="s">
+        <v>407</v>
       </c>
     </row>
     <row r="230" spans="1:8">
       <c r="A230" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B230" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="C230" s="1"/>
-      <c r="D230" s="1"/>
+        <v>71</v>
+      </c>
+      <c r="C230" s="3">
+        <v>7</v>
+      </c>
+      <c r="D230" s="4">
+        <v>0.91666666666666663</v>
+      </c>
       <c r="E230" s="1" t="s">
-        <v>1085</v>
-      </c>
-      <c r="F230" s="3">
-        <v>1</v>
-      </c>
-      <c r="G230" s="1" t="s">
-        <v>810</v>
-      </c>
-      <c r="H230" s="2" t="s">
-        <v>407</v>
+        <v>1081</v>
+      </c>
+      <c r="F230" s="3"/>
+      <c r="G230" s="1"/>
+      <c r="H230" s="1" t="s">
+        <v>408</v>
       </c>
     </row>
     <row r="231" spans="1:8">
       <c r="A231" s="2" t="s">
-        <v>228</v>
+        <v>266</v>
       </c>
       <c r="B231" s="1" t="s">
-        <v>71</v>
+        <v>121</v>
       </c>
       <c r="C231" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D231" s="4">
-        <v>0.91666666666666663</v>
+        <v>0</v>
       </c>
       <c r="E231" s="1" t="s">
-        <v>1086</v>
+        <v>1082</v>
       </c>
       <c r="F231" s="3"/>
       <c r="G231" s="1"/>
       <c r="H231" s="1" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="232" spans="1:8">
       <c r="A232" s="2" t="s">
-        <v>266</v>
+        <v>835</v>
       </c>
       <c r="B232" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="C232" s="3">
-        <v>6</v>
-      </c>
-      <c r="D232" s="4">
-        <v>0</v>
+        <v>780</v>
       </c>
       <c r="E232" s="1" t="s">
-        <v>1087</v>
-      </c>
-      <c r="F232" s="3"/>
-      <c r="G232" s="1"/>
-      <c r="H232" s="1" t="s">
-        <v>409</v>
+        <v>1083</v>
+      </c>
+      <c r="F232" s="2">
+        <v>1</v>
+      </c>
+      <c r="H232" s="7" t="s">
+        <v>836</v>
       </c>
     </row>
     <row r="233" spans="1:8">
       <c r="A233" s="2" t="s">
-        <v>839</v>
+        <v>229</v>
       </c>
       <c r="B233" s="1" t="s">
-        <v>783</v>
+        <v>146</v>
+      </c>
+      <c r="C233" s="3">
+        <v>6</v>
+      </c>
+      <c r="D233" s="5">
+        <v>0</v>
       </c>
       <c r="E233" s="1" t="s">
-        <v>1088</v>
-      </c>
-      <c r="F233" s="2">
-        <v>1</v>
-      </c>
-      <c r="H233" s="7" t="s">
-        <v>840</v>
+        <v>1084</v>
+      </c>
+      <c r="F233" s="3"/>
+      <c r="G233" s="1"/>
+      <c r="H233" s="1" t="s">
+        <v>446</v>
       </c>
     </row>
     <row r="234" spans="1:8">
       <c r="A234" s="2" t="s">
-        <v>229</v>
+        <v>267</v>
       </c>
       <c r="B234" s="1" t="s">
-        <v>146</v>
+        <v>42</v>
       </c>
       <c r="C234" s="3">
         <v>6</v>
       </c>
-      <c r="D234" s="5">
+      <c r="D234" s="4">
         <v>0</v>
       </c>
       <c r="E234" s="1" t="s">
-        <v>1089</v>
+        <v>1085</v>
       </c>
       <c r="F234" s="3"/>
       <c r="G234" s="1"/>
-      <c r="H234" s="1" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="235" spans="1:8">
+      <c r="H234" s="2" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="235" spans="1:8" customFormat="1">
       <c r="A235" s="2" t="s">
-        <v>267</v>
+        <v>448</v>
       </c>
       <c r="B235" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C235" s="3">
-        <v>6</v>
-      </c>
-      <c r="D235" s="4">
-        <v>0</v>
+        <v>157</v>
+      </c>
+      <c r="C235" s="1">
+        <v>7</v>
+      </c>
+      <c r="D235" s="5">
+        <v>0.91666666666666663</v>
       </c>
       <c r="E235" s="1" t="s">
-        <v>1090</v>
-      </c>
-      <c r="F235" s="3"/>
+        <v>1086</v>
+      </c>
+      <c r="F235" s="1"/>
       <c r="G235" s="1"/>
-      <c r="H235" s="2" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="236" spans="1:8" customFormat="1">
+      <c r="H235" s="1" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="236" spans="1:8">
       <c r="A236" s="2" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B236" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="C236" s="1">
-        <v>7</v>
-      </c>
-      <c r="D236" s="5">
-        <v>0.91666666666666663</v>
-      </c>
+        <v>310</v>
+      </c>
+      <c r="C236" s="1"/>
+      <c r="D236" s="5"/>
       <c r="E236" s="1" t="s">
-        <v>1091</v>
-      </c>
-      <c r="F236" s="1"/>
+        <v>1087</v>
+      </c>
+      <c r="F236" s="1">
+        <v>1</v>
+      </c>
       <c r="G236" s="1"/>
       <c r="H236" s="1" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="237" spans="1:8">
       <c r="A237" s="2" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B237" s="1" t="s">
-        <v>310</v>
+        <v>151</v>
       </c>
       <c r="C237" s="1"/>
-      <c r="D237" s="5"/>
+      <c r="D237" s="1"/>
       <c r="E237" s="1" t="s">
-        <v>1092</v>
+        <v>1088</v>
       </c>
       <c r="F237" s="1">
         <v>1</v>
@@ -9601,15 +9592,15 @@
     </row>
     <row r="238" spans="1:8">
       <c r="A238" s="2" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B238" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C238" s="1"/>
       <c r="D238" s="1"/>
       <c r="E238" s="1" t="s">
-      